--- a/2020_LogAnalyzer_Leeheesuk.xlsx
+++ b/2020_LogAnalyzer_Leeheesuk.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="22827"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC78E1D0-1727-4FB0-92B4-0060C529998C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFD66819-B3F4-4B54-9863-F216C464F42E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UI" sheetId="7" r:id="rId1"/>
@@ -13,7 +13,7 @@
     <sheet name="UI_상세" sheetId="17" r:id="rId3"/>
     <sheet name="Table" sheetId="10" r:id="rId4"/>
     <sheet name="Table_0408" sheetId="15" r:id="rId5"/>
-    <sheet name="Table_0429" sheetId="16" r:id="rId6"/>
+    <sheet name="Table_0619_0429" sheetId="16" r:id="rId6"/>
     <sheet name="Pilot" sheetId="11" r:id="rId7"/>
     <sheet name="아키텍처" sheetId="9" r:id="rId8"/>
     <sheet name="기능요건" sheetId="8" r:id="rId9"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1336" uniqueCount="842">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1379" uniqueCount="862">
   <si>
     <t>구분</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4095,6 +4095,71 @@
   </si>
   <si>
     <t>R</t>
+  </si>
+  <si>
+    <t>fdate</t>
+  </si>
+  <si>
+    <t>ftime</t>
+  </si>
+  <si>
+    <t>hhmmss</t>
+  </si>
+  <si>
+    <t>CharField
+(8)</t>
+  </si>
+  <si>
+    <t>CharField
+(6)</t>
+  </si>
+  <si>
+    <t>CharField
+(4)</t>
+  </si>
+  <si>
+    <t>CharField
+(2)</t>
+  </si>
+  <si>
+    <t>fdatetime</t>
+  </si>
+  <si>
+    <t>날짜</t>
+  </si>
+  <si>
+    <t>시간</t>
+  </si>
+  <si>
+    <t>날짜시간</t>
+  </si>
+  <si>
+    <t>CharField
+(14)</t>
+  </si>
+  <si>
+    <t>YYYYMMDDhhmmss</t>
+  </si>
+  <si>
+    <t>통계 공식 - LogDetail Table</t>
+  </si>
+  <si>
+    <t>기본 조건 충족</t>
+  </si>
+  <si>
+    <t>전체 건수</t>
+  </si>
+  <si>
+    <t>상태코드 Grouping, Count 후 &lt; 5</t>
+  </si>
+  <si>
+    <t>Requests Top5</t>
+  </si>
+  <si>
+    <t>Status Codes Top5</t>
+  </si>
+  <si>
+    <t>Requests Grouping, Count 후 &lt; 5</t>
   </si>
 </sst>
 </file>
@@ -4321,7 +4386,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4367,6 +4432,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4653,7 +4724,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="136">
+  <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4886,6 +4957,12 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5011,6 +5088,30 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -11398,51 +11499,51 @@
     </row>
     <row r="17" spans="1:13">
       <c r="J17" s="19"/>
-      <c r="K17" s="95" t="s">
+      <c r="K17" s="97" t="s">
         <v>538</v>
       </c>
-      <c r="L17" s="96"/>
-      <c r="M17" s="97"/>
+      <c r="L17" s="98"/>
+      <c r="M17" s="99"/>
     </row>
     <row r="18" spans="1:13">
       <c r="J18" s="19">
         <v>1</v>
       </c>
-      <c r="K18" s="98" t="s">
+      <c r="K18" s="100" t="s">
         <v>539</v>
       </c>
-      <c r="L18" s="99"/>
-      <c r="M18" s="100"/>
+      <c r="L18" s="101"/>
+      <c r="M18" s="102"/>
     </row>
     <row r="19" spans="1:13">
       <c r="J19" s="19">
         <v>2</v>
       </c>
-      <c r="K19" s="98" t="s">
+      <c r="K19" s="100" t="s">
         <v>540</v>
       </c>
-      <c r="L19" s="99"/>
-      <c r="M19" s="100"/>
+      <c r="L19" s="101"/>
+      <c r="M19" s="102"/>
     </row>
     <row r="20" spans="1:13">
       <c r="J20" s="19">
         <v>3</v>
       </c>
-      <c r="K20" s="98" t="s">
+      <c r="K20" s="100" t="s">
         <v>541</v>
       </c>
-      <c r="L20" s="99"/>
-      <c r="M20" s="100"/>
+      <c r="L20" s="101"/>
+      <c r="M20" s="102"/>
     </row>
     <row r="21" spans="1:13">
       <c r="J21" s="19">
         <v>4</v>
       </c>
-      <c r="K21" s="98" t="s">
+      <c r="K21" s="100" t="s">
         <v>542</v>
       </c>
-      <c r="L21" s="99"/>
-      <c r="M21" s="100"/>
+      <c r="L21" s="101"/>
+      <c r="M21" s="102"/>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="44" t="s">
@@ -11534,11 +11635,11 @@
       <c r="B1" s="25" t="s">
         <v>327</v>
       </c>
-      <c r="E1" s="130" t="s">
+      <c r="E1" s="132" t="s">
         <v>726</v>
       </c>
-      <c r="F1" s="130"/>
-      <c r="G1" s="130"/>
+      <c r="F1" s="132"/>
+      <c r="G1" s="132"/>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="19" t="s">
@@ -11547,11 +11648,11 @@
       <c r="B2" s="19" t="s">
         <v>257</v>
       </c>
-      <c r="E2" s="131" t="s">
+      <c r="E2" s="133" t="s">
         <v>727</v>
       </c>
-      <c r="F2" s="131"/>
-      <c r="G2" s="131"/>
+      <c r="F2" s="133"/>
+      <c r="G2" s="133"/>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="19" t="s">
@@ -11568,10 +11669,10 @@
       <c r="B4" s="19" t="s">
         <v>259</v>
       </c>
-      <c r="E4" s="130" t="s">
+      <c r="E4" s="132" t="s">
         <v>724</v>
       </c>
-      <c r="F4" s="130"/>
+      <c r="F4" s="132"/>
       <c r="G4" s="25" t="s">
         <v>725</v>
       </c>
@@ -11583,16 +11684,16 @@
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="E5" s="129" t="s">
+      <c r="E5" s="131" t="s">
         <v>722</v>
       </c>
-      <c r="F5" s="129" t="s">
+      <c r="F5" s="131" t="s">
         <v>723</v>
       </c>
       <c r="G5" s="72" t="s">
         <v>749</v>
       </c>
-      <c r="H5" s="128" t="s">
+      <c r="H5" s="130" t="s">
         <v>750</v>
       </c>
       <c r="J5" t="s">
@@ -11603,12 +11704,12 @@
       <c r="A6" t="s">
         <v>261</v>
       </c>
-      <c r="E6" s="129"/>
-      <c r="F6" s="129"/>
+      <c r="E6" s="131"/>
+      <c r="F6" s="131"/>
       <c r="G6" s="72" t="s">
         <v>748</v>
       </c>
-      <c r="H6" s="129"/>
+      <c r="H6" s="131"/>
       <c r="J6" t="s">
         <v>731</v>
       </c>
@@ -11947,7 +12048,7 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="129" t="s">
+      <c r="A2" s="131" t="s">
         <v>380</v>
       </c>
       <c r="B2" s="61" t="s">
@@ -11961,7 +12062,7 @@
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="129"/>
+      <c r="A3" s="131"/>
       <c r="B3" s="20" t="s">
         <v>262</v>
       </c>
@@ -11973,7 +12074,7 @@
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="129"/>
+      <c r="A4" s="131"/>
       <c r="B4" s="20" t="s">
         <v>386</v>
       </c>
@@ -11985,7 +12086,7 @@
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="129"/>
+      <c r="A5" s="131"/>
       <c r="B5" s="61" t="s">
         <v>545</v>
       </c>
@@ -11997,7 +12098,7 @@
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="129"/>
+      <c r="A6" s="131"/>
       <c r="B6" s="20" t="s">
         <v>389</v>
       </c>
@@ -12009,7 +12110,7 @@
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="129"/>
+      <c r="A7" s="131"/>
       <c r="B7" s="20" t="s">
         <v>391</v>
       </c>
@@ -13590,7 +13691,7 @@
       <c r="R4" s="13" t="s">
         <v>809</v>
       </c>
-      <c r="S4" s="132" t="s">
+      <c r="S4" s="134" t="s">
         <v>810</v>
       </c>
     </row>
@@ -13607,7 +13708,7 @@
       <c r="R5" s="13" t="s">
         <v>353</v>
       </c>
-      <c r="S5" s="133" t="s">
+      <c r="S5" s="135" t="s">
         <v>813</v>
       </c>
     </row>
@@ -13624,7 +13725,7 @@
       <c r="R6" s="9" t="s">
         <v>603</v>
       </c>
-      <c r="S6" s="133"/>
+      <c r="S6" s="135"/>
     </row>
     <row r="7" spans="3:20">
       <c r="O7" s="85" t="s">
@@ -13639,7 +13740,7 @@
       <c r="R7" s="9" t="s">
         <v>604</v>
       </c>
-      <c r="S7" s="133"/>
+      <c r="S7" s="135"/>
     </row>
     <row r="8" spans="3:20">
       <c r="O8" s="85" t="s">
@@ -13654,7 +13755,7 @@
       <c r="R8" s="9" t="s">
         <v>351</v>
       </c>
-      <c r="S8" s="133"/>
+      <c r="S8" s="135"/>
     </row>
     <row r="9" spans="3:20">
       <c r="O9" s="85" t="s">
@@ -13669,7 +13770,7 @@
       <c r="R9" s="9" t="s">
         <v>350</v>
       </c>
-      <c r="S9" s="133"/>
+      <c r="S9" s="135"/>
     </row>
     <row r="10" spans="3:20">
       <c r="Q10" s="9" t="s">
@@ -13678,7 +13779,7 @@
       <c r="R10" s="9" t="s">
         <v>349</v>
       </c>
-      <c r="S10" s="132" t="s">
+      <c r="S10" s="134" t="s">
         <v>812</v>
       </c>
       <c r="T10" t="s">
@@ -13689,18 +13790,18 @@
       <c r="C14" t="s">
         <v>805</v>
       </c>
-      <c r="Q14" s="134" t="s">
+      <c r="Q14" s="136" t="s">
         <v>834</v>
       </c>
     </row>
     <row r="15" spans="3:20">
-      <c r="Q15" s="135" t="s">
+      <c r="Q15" s="137" t="s">
         <v>836</v>
       </c>
       <c r="R15" s="9" t="s">
         <v>818</v>
       </c>
-      <c r="S15" s="94" t="s">
+      <c r="S15" s="96" t="s">
         <v>822</v>
       </c>
     </row>
@@ -13708,7 +13809,7 @@
       <c r="C16" s="10" t="s">
         <v>313</v>
       </c>
-      <c r="D16" s="94" t="s">
+      <c r="D16" s="96" t="s">
         <v>814</v>
       </c>
       <c r="E16" s="10" t="s">
@@ -13729,87 +13830,87 @@
       <c r="J16" s="10" t="s">
         <v>817</v>
       </c>
-      <c r="Q16" s="123"/>
+      <c r="Q16" s="125"/>
       <c r="R16" s="9" t="s">
         <v>819</v>
       </c>
-      <c r="S16" s="94" t="s">
+      <c r="S16" s="96" t="s">
         <v>822</v>
       </c>
     </row>
     <row r="17" spans="10:19">
       <c r="J17" s="85"/>
-      <c r="Q17" s="123"/>
+      <c r="Q17" s="125"/>
       <c r="R17" s="9" t="s">
         <v>820</v>
       </c>
-      <c r="S17" s="94" t="s">
+      <c r="S17" s="96" t="s">
         <v>823</v>
       </c>
     </row>
     <row r="18" spans="10:19">
-      <c r="Q18" s="123"/>
+      <c r="Q18" s="125"/>
       <c r="R18" s="9" t="s">
         <v>821</v>
       </c>
-      <c r="S18" s="94" t="s">
+      <c r="S18" s="96" t="s">
         <v>823</v>
       </c>
     </row>
     <row r="19" spans="10:19">
-      <c r="Q19" s="123"/>
+      <c r="Q19" s="125"/>
       <c r="R19" s="9" t="s">
         <v>828</v>
       </c>
-      <c r="S19" s="94"/>
+      <c r="S19" s="96"/>
     </row>
     <row r="20" spans="10:19">
-      <c r="Q20" s="123"/>
+      <c r="Q20" s="125"/>
       <c r="R20" s="9" t="s">
         <v>829</v>
       </c>
-      <c r="S20" s="94"/>
+      <c r="S20" s="96"/>
     </row>
     <row r="21" spans="10:19">
-      <c r="Q21" s="123"/>
+      <c r="Q21" s="125"/>
       <c r="R21" s="9" t="s">
         <v>830</v>
       </c>
-      <c r="S21" s="94" t="s">
+      <c r="S21" s="96" t="s">
         <v>832</v>
       </c>
     </row>
     <row r="22" spans="10:19">
-      <c r="Q22" s="124"/>
+      <c r="Q22" s="126"/>
       <c r="R22" s="9" t="s">
         <v>831</v>
       </c>
-      <c r="S22" s="94" t="s">
+      <c r="S22" s="96" t="s">
         <v>833</v>
       </c>
     </row>
     <row r="23" spans="10:19">
-      <c r="Q23" s="135" t="s">
+      <c r="Q23" s="137" t="s">
         <v>835</v>
       </c>
       <c r="R23" s="9" t="s">
         <v>825</v>
       </c>
-      <c r="S23" s="94"/>
+      <c r="S23" s="96"/>
     </row>
     <row r="24" spans="10:19">
-      <c r="Q24" s="123"/>
+      <c r="Q24" s="125"/>
       <c r="R24" s="9" t="s">
         <v>826</v>
       </c>
-      <c r="S24" s="94"/>
+      <c r="S24" s="96"/>
     </row>
     <row r="25" spans="10:19">
-      <c r="Q25" s="124"/>
+      <c r="Q25" s="126"/>
       <c r="R25" s="9" t="s">
         <v>827</v>
       </c>
-      <c r="S25" s="94"/>
+      <c r="S25" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -13979,19 +14080,19 @@
       <c r="E7" s="32" t="s">
         <v>450</v>
       </c>
-      <c r="F7" s="101" t="s">
+      <c r="F7" s="103" t="s">
         <v>442</v>
       </c>
-      <c r="G7" s="101"/>
-      <c r="H7" s="101"/>
-      <c r="I7" s="101"/>
-      <c r="J7" s="101"/>
-      <c r="K7" s="101"/>
-      <c r="L7" s="101"/>
-      <c r="M7" s="101"/>
-      <c r="N7" s="101"/>
-      <c r="O7" s="101"/>
-      <c r="P7" s="101"/>
+      <c r="G7" s="103"/>
+      <c r="H7" s="103"/>
+      <c r="I7" s="103"/>
+      <c r="J7" s="103"/>
+      <c r="K7" s="103"/>
+      <c r="L7" s="103"/>
+      <c r="M7" s="103"/>
+      <c r="N7" s="103"/>
+      <c r="O7" s="103"/>
+      <c r="P7" s="103"/>
     </row>
     <row r="8" spans="1:17">
       <c r="B8" s="33" t="s">
@@ -14212,40 +14313,40 @@
       <c r="A24" s="36" t="s">
         <v>456</v>
       </c>
-      <c r="B24" s="102" t="s">
+      <c r="B24" s="104" t="s">
         <v>458</v>
       </c>
-      <c r="C24" s="102"/>
-      <c r="D24" s="102"/>
-      <c r="E24" s="102"/>
-      <c r="F24" s="102"/>
-      <c r="G24" s="102"/>
+      <c r="C24" s="104"/>
+      <c r="D24" s="104"/>
+      <c r="E24" s="104"/>
+      <c r="F24" s="104"/>
+      <c r="G24" s="104"/>
     </row>
     <row r="25" spans="1:7" ht="30">
       <c r="A25" s="36" t="s">
         <v>463</v>
       </c>
-      <c r="B25" s="103" t="s">
+      <c r="B25" s="105" t="s">
         <v>465</v>
       </c>
-      <c r="C25" s="103"/>
-      <c r="D25" s="103"/>
-      <c r="E25" s="103"/>
-      <c r="F25" s="103"/>
-      <c r="G25" s="103"/>
+      <c r="C25" s="105"/>
+      <c r="D25" s="105"/>
+      <c r="E25" s="105"/>
+      <c r="F25" s="105"/>
+      <c r="G25" s="105"/>
     </row>
     <row r="26" spans="1:7" ht="159" customHeight="1">
       <c r="A26" s="36" t="s">
         <v>460</v>
       </c>
-      <c r="B26" s="102" t="s">
+      <c r="B26" s="104" t="s">
         <v>461</v>
       </c>
-      <c r="C26" s="102"/>
-      <c r="D26" s="102"/>
-      <c r="E26" s="102"/>
-      <c r="F26" s="102"/>
-      <c r="G26" s="102"/>
+      <c r="C26" s="104"/>
+      <c r="D26" s="104"/>
+      <c r="E26" s="104"/>
+      <c r="F26" s="104"/>
+      <c r="G26" s="104"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -14759,29 +14860,29 @@
       <c r="B27" s="84" t="s">
         <v>622</v>
       </c>
-      <c r="C27" s="106" t="s">
+      <c r="C27" s="108" t="s">
         <v>623</v>
       </c>
-      <c r="D27" s="107"/>
+      <c r="D27" s="109"/>
       <c r="E27" s="84" t="s">
         <v>622</v>
       </c>
-      <c r="F27" s="106" t="s">
+      <c r="F27" s="108" t="s">
         <v>623</v>
       </c>
-      <c r="G27" s="107"/>
+      <c r="G27" s="109"/>
       <c r="H27" s="84" t="s">
         <v>622</v>
       </c>
-      <c r="I27" s="106" t="s">
+      <c r="I27" s="108" t="s">
         <v>623</v>
       </c>
-      <c r="J27" s="107"/>
-      <c r="L27" s="118" t="s">
+      <c r="J27" s="109"/>
+      <c r="L27" s="120" t="s">
         <v>695</v>
       </c>
-      <c r="M27" s="118"/>
-      <c r="N27" s="118"/>
+      <c r="M27" s="120"/>
+      <c r="N27" s="120"/>
     </row>
     <row r="28" spans="1:14" ht="32.25" thickBot="1">
       <c r="A28" s="85">
@@ -14790,29 +14891,29 @@
       <c r="B28" s="73" t="s">
         <v>624</v>
       </c>
-      <c r="C28" s="104" t="s">
+      <c r="C28" s="106" t="s">
         <v>625</v>
       </c>
-      <c r="D28" s="105"/>
+      <c r="D28" s="107"/>
       <c r="E28" s="74" t="s">
         <v>646</v>
       </c>
-      <c r="F28" s="108" t="s">
+      <c r="F28" s="110" t="s">
         <v>647</v>
       </c>
-      <c r="G28" s="109"/>
+      <c r="G28" s="111"/>
       <c r="H28" s="73" t="s">
         <v>668</v>
       </c>
-      <c r="I28" s="104" t="s">
+      <c r="I28" s="106" t="s">
         <v>669</v>
       </c>
-      <c r="J28" s="105"/>
-      <c r="L28" s="119" t="s">
+      <c r="J28" s="107"/>
+      <c r="L28" s="121" t="s">
         <v>696</v>
       </c>
-      <c r="M28" s="119"/>
-      <c r="N28" s="119"/>
+      <c r="M28" s="121"/>
+      <c r="N28" s="121"/>
     </row>
     <row r="29" spans="1:14" ht="31.5" thickBot="1">
       <c r="A29" s="85">
@@ -14821,29 +14922,29 @@
       <c r="B29" s="74" t="s">
         <v>626</v>
       </c>
-      <c r="C29" s="108" t="s">
+      <c r="C29" s="110" t="s">
         <v>627</v>
       </c>
-      <c r="D29" s="109"/>
+      <c r="D29" s="111"/>
       <c r="E29" s="73" t="s">
         <v>648</v>
       </c>
-      <c r="F29" s="104" t="s">
+      <c r="F29" s="106" t="s">
         <v>649</v>
       </c>
-      <c r="G29" s="105"/>
+      <c r="G29" s="107"/>
       <c r="H29" s="74" t="s">
         <v>670</v>
       </c>
-      <c r="I29" s="112" t="s">
+      <c r="I29" s="114" t="s">
         <v>671</v>
       </c>
-      <c r="J29" s="113"/>
-      <c r="L29" s="118" t="s">
+      <c r="J29" s="115"/>
+      <c r="L29" s="120" t="s">
         <v>697</v>
       </c>
-      <c r="M29" s="118"/>
-      <c r="N29" s="118"/>
+      <c r="M29" s="120"/>
+      <c r="N29" s="120"/>
     </row>
     <row r="30" spans="1:14" ht="15.75" thickBot="1">
       <c r="A30" s="85">
@@ -14852,29 +14953,29 @@
       <c r="B30" s="73" t="s">
         <v>628</v>
       </c>
-      <c r="C30" s="104" t="s">
+      <c r="C30" s="106" t="s">
         <v>629</v>
       </c>
-      <c r="D30" s="105"/>
+      <c r="D30" s="107"/>
       <c r="E30" s="74" t="s">
         <v>650</v>
       </c>
-      <c r="F30" s="108" t="s">
+      <c r="F30" s="110" t="s">
         <v>651</v>
       </c>
-      <c r="G30" s="109"/>
+      <c r="G30" s="111"/>
       <c r="H30" s="73" t="s">
         <v>672</v>
       </c>
-      <c r="I30" s="104" t="s">
+      <c r="I30" s="106" t="s">
         <v>673</v>
       </c>
-      <c r="J30" s="105"/>
-      <c r="L30" s="119" t="s">
+      <c r="J30" s="107"/>
+      <c r="L30" s="121" t="s">
         <v>698</v>
       </c>
-      <c r="M30" s="119"/>
-      <c r="N30" s="119"/>
+      <c r="M30" s="121"/>
+      <c r="N30" s="121"/>
     </row>
     <row r="31" spans="1:14" ht="17.25" customHeight="1" thickBot="1">
       <c r="A31" s="85">
@@ -14883,29 +14984,29 @@
       <c r="B31" s="74" t="s">
         <v>630</v>
       </c>
-      <c r="C31" s="108" t="s">
+      <c r="C31" s="110" t="s">
         <v>631</v>
       </c>
-      <c r="D31" s="109"/>
+      <c r="D31" s="111"/>
       <c r="E31" s="73" t="s">
         <v>652</v>
       </c>
-      <c r="F31" s="104" t="s">
+      <c r="F31" s="106" t="s">
         <v>653</v>
       </c>
-      <c r="G31" s="105"/>
+      <c r="G31" s="107"/>
       <c r="H31" s="74" t="s">
         <v>674</v>
       </c>
-      <c r="I31" s="108" t="s">
+      <c r="I31" s="110" t="s">
         <v>675</v>
       </c>
-      <c r="J31" s="109"/>
-      <c r="L31" s="118" t="s">
+      <c r="J31" s="111"/>
+      <c r="L31" s="120" t="s">
         <v>699</v>
       </c>
-      <c r="M31" s="118"/>
-      <c r="N31" s="118"/>
+      <c r="M31" s="120"/>
+      <c r="N31" s="120"/>
     </row>
     <row r="32" spans="1:14" ht="43.5" customHeight="1" thickBot="1">
       <c r="A32" s="85">
@@ -14914,29 +15015,29 @@
       <c r="B32" s="73" t="s">
         <v>632</v>
       </c>
-      <c r="C32" s="104" t="s">
+      <c r="C32" s="106" t="s">
         <v>633</v>
       </c>
-      <c r="D32" s="105"/>
+      <c r="D32" s="107"/>
       <c r="E32" s="74" t="s">
         <v>654</v>
       </c>
-      <c r="F32" s="108" t="s">
+      <c r="F32" s="110" t="s">
         <v>655</v>
       </c>
-      <c r="G32" s="109"/>
+      <c r="G32" s="111"/>
       <c r="H32" s="73" t="s">
         <v>676</v>
       </c>
-      <c r="I32" s="104" t="s">
+      <c r="I32" s="106" t="s">
         <v>677</v>
       </c>
-      <c r="J32" s="105"/>
-      <c r="L32" s="119" t="s">
+      <c r="J32" s="107"/>
+      <c r="L32" s="121" t="s">
         <v>700</v>
       </c>
-      <c r="M32" s="119"/>
-      <c r="N32" s="119"/>
+      <c r="M32" s="121"/>
+      <c r="N32" s="121"/>
     </row>
     <row r="33" spans="1:14" ht="31.5" customHeight="1" thickBot="1">
       <c r="A33" s="85">
@@ -14945,29 +15046,29 @@
       <c r="B33" s="74" t="s">
         <v>634</v>
       </c>
-      <c r="C33" s="108" t="s">
+      <c r="C33" s="110" t="s">
         <v>635</v>
       </c>
-      <c r="D33" s="109"/>
+      <c r="D33" s="111"/>
       <c r="E33" s="73" t="s">
         <v>656</v>
       </c>
-      <c r="F33" s="104" t="s">
+      <c r="F33" s="106" t="s">
         <v>657</v>
       </c>
-      <c r="G33" s="105"/>
+      <c r="G33" s="107"/>
       <c r="H33" s="74" t="s">
         <v>678</v>
       </c>
-      <c r="I33" s="110" t="s">
+      <c r="I33" s="112" t="s">
         <v>679</v>
       </c>
-      <c r="J33" s="111"/>
-      <c r="L33" s="118" t="s">
+      <c r="J33" s="113"/>
+      <c r="L33" s="120" t="s">
         <v>701</v>
       </c>
-      <c r="M33" s="118"/>
-      <c r="N33" s="118"/>
+      <c r="M33" s="120"/>
+      <c r="N33" s="120"/>
     </row>
     <row r="34" spans="1:14" ht="28.5" customHeight="1" thickBot="1">
       <c r="A34" s="85">
@@ -14976,29 +15077,29 @@
       <c r="B34" s="73" t="s">
         <v>636</v>
       </c>
-      <c r="C34" s="104" t="s">
+      <c r="C34" s="106" t="s">
         <v>637</v>
       </c>
-      <c r="D34" s="105"/>
+      <c r="D34" s="107"/>
       <c r="E34" s="74" t="s">
         <v>658</v>
       </c>
-      <c r="F34" s="108" t="s">
+      <c r="F34" s="110" t="s">
         <v>659</v>
       </c>
-      <c r="G34" s="109"/>
+      <c r="G34" s="111"/>
       <c r="H34" s="73" t="s">
         <v>680</v>
       </c>
-      <c r="I34" s="114" t="s">
+      <c r="I34" s="116" t="s">
         <v>681</v>
       </c>
-      <c r="J34" s="115"/>
-      <c r="L34" s="119" t="s">
+      <c r="J34" s="117"/>
+      <c r="L34" s="121" t="s">
         <v>702</v>
       </c>
-      <c r="M34" s="119"/>
-      <c r="N34" s="119"/>
+      <c r="M34" s="121"/>
+      <c r="N34" s="121"/>
     </row>
     <row r="35" spans="1:14" ht="31.5" customHeight="1" thickBot="1">
       <c r="A35" s="85">
@@ -15007,29 +15108,29 @@
       <c r="B35" s="74" t="s">
         <v>638</v>
       </c>
-      <c r="C35" s="108" t="s">
+      <c r="C35" s="110" t="s">
         <v>639</v>
       </c>
-      <c r="D35" s="109"/>
+      <c r="D35" s="111"/>
       <c r="E35" s="73" t="s">
         <v>660</v>
       </c>
-      <c r="F35" s="104" t="s">
+      <c r="F35" s="106" t="s">
         <v>661</v>
       </c>
-      <c r="G35" s="105"/>
+      <c r="G35" s="107"/>
       <c r="H35" s="81" t="s">
         <v>682</v>
       </c>
-      <c r="I35" s="108" t="s">
+      <c r="I35" s="110" t="s">
         <v>683</v>
       </c>
-      <c r="J35" s="109"/>
-      <c r="L35" s="118" t="s">
+      <c r="J35" s="111"/>
+      <c r="L35" s="120" t="s">
         <v>703</v>
       </c>
-      <c r="M35" s="118"/>
-      <c r="N35" s="118"/>
+      <c r="M35" s="120"/>
+      <c r="N35" s="120"/>
     </row>
     <row r="36" spans="1:14" ht="60.75" thickBot="1">
       <c r="A36" s="85">
@@ -15038,17 +15139,17 @@
       <c r="B36" s="73" t="s">
         <v>640</v>
       </c>
-      <c r="C36" s="104" t="s">
+      <c r="C36" s="106" t="s">
         <v>641</v>
       </c>
-      <c r="D36" s="105"/>
+      <c r="D36" s="107"/>
       <c r="E36" s="74" t="s">
         <v>662</v>
       </c>
-      <c r="F36" s="108" t="s">
+      <c r="F36" s="110" t="s">
         <v>663</v>
       </c>
-      <c r="G36" s="109"/>
+      <c r="G36" s="111"/>
       <c r="H36" s="82"/>
       <c r="I36" s="75" t="s">
         <v>684</v>
@@ -15056,11 +15157,11 @@
       <c r="J36" s="76" t="s">
         <v>685</v>
       </c>
-      <c r="L36" s="119" t="s">
+      <c r="L36" s="121" t="s">
         <v>704</v>
       </c>
-      <c r="M36" s="119"/>
-      <c r="N36" s="119"/>
+      <c r="M36" s="121"/>
+      <c r="N36" s="121"/>
     </row>
     <row r="37" spans="1:14" ht="75.75" thickBot="1">
       <c r="A37" s="85">
@@ -15069,17 +15170,17 @@
       <c r="B37" s="74" t="s">
         <v>642</v>
       </c>
-      <c r="C37" s="108" t="s">
+      <c r="C37" s="110" t="s">
         <v>643</v>
       </c>
-      <c r="D37" s="109"/>
+      <c r="D37" s="111"/>
       <c r="E37" s="73" t="s">
         <v>664</v>
       </c>
-      <c r="F37" s="104" t="s">
+      <c r="F37" s="106" t="s">
         <v>665</v>
       </c>
-      <c r="G37" s="105"/>
+      <c r="G37" s="107"/>
       <c r="H37" s="82"/>
       <c r="I37" s="77" t="s">
         <v>686</v>
@@ -15095,17 +15196,17 @@
       <c r="B38" s="73" t="s">
         <v>644</v>
       </c>
-      <c r="C38" s="104" t="s">
+      <c r="C38" s="106" t="s">
         <v>645</v>
       </c>
-      <c r="D38" s="105"/>
+      <c r="D38" s="107"/>
       <c r="E38" s="74" t="s">
         <v>666</v>
       </c>
-      <c r="F38" s="108" t="s">
+      <c r="F38" s="110" t="s">
         <v>667</v>
       </c>
-      <c r="G38" s="109"/>
+      <c r="G38" s="111"/>
       <c r="H38" s="82"/>
       <c r="I38" s="79" t="s">
         <v>688</v>
@@ -15121,22 +15222,22 @@
       <c r="B39" s="74" t="s">
         <v>693</v>
       </c>
-      <c r="C39" s="110" t="s">
+      <c r="C39" s="112" t="s">
         <v>694</v>
       </c>
-      <c r="D39" s="111"/>
+      <c r="D39" s="113"/>
       <c r="E39" s="73" t="s">
         <v>691</v>
       </c>
-      <c r="F39" s="114" t="s">
+      <c r="F39" s="116" t="s">
         <v>692</v>
       </c>
-      <c r="G39" s="115"/>
+      <c r="G39" s="117"/>
       <c r="H39" s="83"/>
-      <c r="I39" s="116" t="s">
+      <c r="I39" s="118" t="s">
         <v>690</v>
       </c>
-      <c r="J39" s="117"/>
+      <c r="J39" s="119"/>
     </row>
     <row r="40" spans="1:14" ht="58.5" customHeight="1"/>
     <row r="42" spans="1:14" ht="31.5" customHeight="1"/>
@@ -15221,7 +15322,7 @@
     <col min="8" max="8" width="17.42578125" customWidth="1"/>
     <col min="9" max="9" width="13.7109375" customWidth="1"/>
     <col min="10" max="11" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="33.42578125" customWidth="1"/>
+    <col min="12" max="12" width="17.85546875" customWidth="1"/>
     <col min="13" max="14" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="13.85546875" customWidth="1"/>
@@ -15309,24 +15410,30 @@
         <v>50</v>
       </c>
       <c r="G5" s="89"/>
+      <c r="L5" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="M5" s="13" t="s">
+        <v>345</v>
+      </c>
     </row>
     <row r="6" spans="1:14">
       <c r="L6" s="9" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M6" s="13" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="34" t="s">
         <v>575</v>
       </c>
-      <c r="L7" s="9" t="s">
-        <v>314</v>
-      </c>
-      <c r="M7" s="13" t="s">
-        <v>353</v>
+      <c r="L7" s="50" t="s">
+        <v>602</v>
+      </c>
+      <c r="M7" s="50" t="s">
+        <v>603</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -15348,11 +15455,11 @@
       <c r="G8" s="33" t="s">
         <v>416</v>
       </c>
-      <c r="L8" s="50" t="s">
-        <v>602</v>
-      </c>
-      <c r="M8" s="50" t="s">
-        <v>603</v>
+      <c r="L8" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="M8" s="9" t="s">
+        <v>604</v>
       </c>
       <c r="N8" t="s">
         <v>605</v>
@@ -15378,10 +15485,10 @@
         <v>467</v>
       </c>
       <c r="L9" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M9" s="9" t="s">
-        <v>604</v>
+        <v>351</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="30">
@@ -15404,10 +15511,10 @@
         <v>455</v>
       </c>
       <c r="L10" s="9" t="s">
-        <v>347</v>
+        <v>315</v>
       </c>
       <c r="M10" s="9" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -15422,17 +15529,9 @@
       <c r="H11" s="36"/>
       <c r="I11" s="36"/>
       <c r="L11" s="9" t="s">
-        <v>315</v>
+        <v>348</v>
       </c>
       <c r="M11" s="9" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="L12" s="9" t="s">
-        <v>348</v>
-      </c>
-      <c r="M12" s="9" t="s">
         <v>349</v>
       </c>
     </row>
@@ -15449,6 +15548,9 @@
       <c r="H13" s="87"/>
       <c r="I13" s="87"/>
       <c r="J13" s="87"/>
+      <c r="K13" s="94"/>
+      <c r="L13" s="94"/>
+      <c r="M13" s="94"/>
     </row>
     <row r="14" spans="1:14">
       <c r="B14" s="39" t="s">
@@ -15478,6 +15580,15 @@
       <c r="J14" s="33" t="s">
         <v>424</v>
       </c>
+      <c r="K14" s="33" t="s">
+        <v>842</v>
+      </c>
+      <c r="L14" s="33" t="s">
+        <v>843</v>
+      </c>
+      <c r="M14" s="33" t="s">
+        <v>849</v>
+      </c>
     </row>
     <row r="15" spans="1:14">
       <c r="B15" s="89" t="s">
@@ -15507,8 +15618,17 @@
       <c r="J15" s="89" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" ht="45">
+      <c r="K15" s="138" t="s">
+        <v>850</v>
+      </c>
+      <c r="L15" s="138" t="s">
+        <v>851</v>
+      </c>
+      <c r="M15" s="138" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="30">
       <c r="B16" s="66" t="s">
         <v>587</v>
       </c>
@@ -15518,23 +15638,32 @@
       <c r="D16" s="66" t="s">
         <v>573</v>
       </c>
-      <c r="E16" s="66" t="s">
-        <v>589</v>
-      </c>
-      <c r="F16" s="66" t="s">
-        <v>589</v>
-      </c>
-      <c r="G16" s="66" t="s">
-        <v>589</v>
-      </c>
-      <c r="H16" s="66" t="s">
-        <v>589</v>
-      </c>
-      <c r="I16" s="66" t="s">
-        <v>589</v>
-      </c>
-      <c r="J16" s="66" t="s">
-        <v>589</v>
+      <c r="E16" s="139" t="s">
+        <v>847</v>
+      </c>
+      <c r="F16" s="139" t="s">
+        <v>848</v>
+      </c>
+      <c r="G16" s="139" t="s">
+        <v>848</v>
+      </c>
+      <c r="H16" s="139" t="s">
+        <v>848</v>
+      </c>
+      <c r="I16" s="139" t="s">
+        <v>848</v>
+      </c>
+      <c r="J16" s="139" t="s">
+        <v>848</v>
+      </c>
+      <c r="K16" s="139" t="s">
+        <v>845</v>
+      </c>
+      <c r="L16" s="139" t="s">
+        <v>846</v>
+      </c>
+      <c r="M16" s="139" t="s">
+        <v>853</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -15549,6 +15678,15 @@
       <c r="H17" s="68"/>
       <c r="I17" s="69"/>
       <c r="J17" s="69"/>
+      <c r="K17" s="140" t="s">
+        <v>822</v>
+      </c>
+      <c r="L17" s="140" t="s">
+        <v>844</v>
+      </c>
+      <c r="M17" s="140" t="s">
+        <v>854</v>
+      </c>
     </row>
     <row r="19" spans="1:14">
       <c r="B19" s="65" t="s">
@@ -15700,29 +15838,29 @@
       <c r="B27" s="84" t="s">
         <v>622</v>
       </c>
-      <c r="C27" s="106" t="s">
+      <c r="C27" s="108" t="s">
         <v>623</v>
       </c>
-      <c r="D27" s="107"/>
+      <c r="D27" s="109"/>
       <c r="E27" s="84" t="s">
         <v>622</v>
       </c>
-      <c r="F27" s="106" t="s">
+      <c r="F27" s="108" t="s">
         <v>623</v>
       </c>
-      <c r="G27" s="107"/>
+      <c r="G27" s="109"/>
       <c r="H27" s="84" t="s">
         <v>622</v>
       </c>
-      <c r="I27" s="106" t="s">
+      <c r="I27" s="108" t="s">
         <v>623</v>
       </c>
-      <c r="J27" s="107"/>
-      <c r="L27" s="118" t="s">
+      <c r="J27" s="109"/>
+      <c r="L27" s="120" t="s">
         <v>695</v>
       </c>
-      <c r="M27" s="118"/>
-      <c r="N27" s="118"/>
+      <c r="M27" s="120"/>
+      <c r="N27" s="120"/>
     </row>
     <row r="28" spans="1:14" ht="32.25" thickBot="1">
       <c r="A28" s="85">
@@ -15731,29 +15869,29 @@
       <c r="B28" s="73" t="s">
         <v>624</v>
       </c>
-      <c r="C28" s="104" t="s">
+      <c r="C28" s="106" t="s">
         <v>625</v>
       </c>
-      <c r="D28" s="105"/>
+      <c r="D28" s="107"/>
       <c r="E28" s="74" t="s">
         <v>646</v>
       </c>
-      <c r="F28" s="108" t="s">
+      <c r="F28" s="110" t="s">
         <v>647</v>
       </c>
-      <c r="G28" s="109"/>
+      <c r="G28" s="111"/>
       <c r="H28" s="73" t="s">
         <v>668</v>
       </c>
-      <c r="I28" s="104" t="s">
+      <c r="I28" s="106" t="s">
         <v>669</v>
       </c>
-      <c r="J28" s="105"/>
-      <c r="L28" s="119" t="s">
+      <c r="J28" s="107"/>
+      <c r="L28" s="121" t="s">
         <v>696</v>
       </c>
-      <c r="M28" s="119"/>
-      <c r="N28" s="119"/>
+      <c r="M28" s="121"/>
+      <c r="N28" s="121"/>
     </row>
     <row r="29" spans="1:14" ht="31.5" thickBot="1">
       <c r="A29" s="85">
@@ -15762,29 +15900,29 @@
       <c r="B29" s="74" t="s">
         <v>626</v>
       </c>
-      <c r="C29" s="108" t="s">
+      <c r="C29" s="110" t="s">
         <v>627</v>
       </c>
-      <c r="D29" s="109"/>
+      <c r="D29" s="111"/>
       <c r="E29" s="73" t="s">
         <v>648</v>
       </c>
-      <c r="F29" s="104" t="s">
+      <c r="F29" s="106" t="s">
         <v>649</v>
       </c>
-      <c r="G29" s="105"/>
+      <c r="G29" s="107"/>
       <c r="H29" s="74" t="s">
         <v>670</v>
       </c>
-      <c r="I29" s="112" t="s">
+      <c r="I29" s="114" t="s">
         <v>671</v>
       </c>
-      <c r="J29" s="113"/>
-      <c r="L29" s="118" t="s">
+      <c r="J29" s="115"/>
+      <c r="L29" s="120" t="s">
         <v>697</v>
       </c>
-      <c r="M29" s="118"/>
-      <c r="N29" s="118"/>
+      <c r="M29" s="120"/>
+      <c r="N29" s="120"/>
     </row>
     <row r="30" spans="1:14" ht="15.75" thickBot="1">
       <c r="A30" s="85">
@@ -15793,29 +15931,29 @@
       <c r="B30" s="73" t="s">
         <v>628</v>
       </c>
-      <c r="C30" s="104" t="s">
+      <c r="C30" s="106" t="s">
         <v>629</v>
       </c>
-      <c r="D30" s="105"/>
+      <c r="D30" s="107"/>
       <c r="E30" s="74" t="s">
         <v>650</v>
       </c>
-      <c r="F30" s="108" t="s">
+      <c r="F30" s="110" t="s">
         <v>651</v>
       </c>
-      <c r="G30" s="109"/>
+      <c r="G30" s="111"/>
       <c r="H30" s="73" t="s">
         <v>672</v>
       </c>
-      <c r="I30" s="104" t="s">
+      <c r="I30" s="106" t="s">
         <v>673</v>
       </c>
-      <c r="J30" s="105"/>
-      <c r="L30" s="119" t="s">
+      <c r="J30" s="107"/>
+      <c r="L30" s="121" t="s">
         <v>698</v>
       </c>
-      <c r="M30" s="119"/>
-      <c r="N30" s="119"/>
+      <c r="M30" s="121"/>
+      <c r="N30" s="121"/>
     </row>
     <row r="31" spans="1:14" ht="17.25" customHeight="1" thickBot="1">
       <c r="A31" s="85">
@@ -15824,29 +15962,29 @@
       <c r="B31" s="74" t="s">
         <v>630</v>
       </c>
-      <c r="C31" s="108" t="s">
+      <c r="C31" s="110" t="s">
         <v>631</v>
       </c>
-      <c r="D31" s="109"/>
+      <c r="D31" s="111"/>
       <c r="E31" s="73" t="s">
         <v>652</v>
       </c>
-      <c r="F31" s="104" t="s">
+      <c r="F31" s="106" t="s">
         <v>653</v>
       </c>
-      <c r="G31" s="105"/>
+      <c r="G31" s="107"/>
       <c r="H31" s="74" t="s">
         <v>674</v>
       </c>
-      <c r="I31" s="108" t="s">
+      <c r="I31" s="110" t="s">
         <v>675</v>
       </c>
-      <c r="J31" s="109"/>
-      <c r="L31" s="118" t="s">
+      <c r="J31" s="111"/>
+      <c r="L31" s="120" t="s">
         <v>699</v>
       </c>
-      <c r="M31" s="118"/>
-      <c r="N31" s="118"/>
+      <c r="M31" s="120"/>
+      <c r="N31" s="120"/>
     </row>
     <row r="32" spans="1:14" ht="43.5" customHeight="1" thickBot="1">
       <c r="A32" s="85">
@@ -15855,29 +15993,29 @@
       <c r="B32" s="73" t="s">
         <v>632</v>
       </c>
-      <c r="C32" s="104" t="s">
+      <c r="C32" s="106" t="s">
         <v>633</v>
       </c>
-      <c r="D32" s="105"/>
+      <c r="D32" s="107"/>
       <c r="E32" s="74" t="s">
         <v>654</v>
       </c>
-      <c r="F32" s="108" t="s">
+      <c r="F32" s="110" t="s">
         <v>655</v>
       </c>
-      <c r="G32" s="109"/>
+      <c r="G32" s="111"/>
       <c r="H32" s="73" t="s">
         <v>676</v>
       </c>
-      <c r="I32" s="104" t="s">
+      <c r="I32" s="106" t="s">
         <v>677</v>
       </c>
-      <c r="J32" s="105"/>
-      <c r="L32" s="119" t="s">
+      <c r="J32" s="107"/>
+      <c r="L32" s="121" t="s">
         <v>700</v>
       </c>
-      <c r="M32" s="119"/>
-      <c r="N32" s="119"/>
+      <c r="M32" s="121"/>
+      <c r="N32" s="121"/>
     </row>
     <row r="33" spans="1:14" ht="31.5" customHeight="1" thickBot="1">
       <c r="A33" s="85">
@@ -15886,29 +16024,29 @@
       <c r="B33" s="74" t="s">
         <v>634</v>
       </c>
-      <c r="C33" s="108" t="s">
+      <c r="C33" s="110" t="s">
         <v>635</v>
       </c>
-      <c r="D33" s="109"/>
+      <c r="D33" s="111"/>
       <c r="E33" s="73" t="s">
         <v>656</v>
       </c>
-      <c r="F33" s="104" t="s">
+      <c r="F33" s="106" t="s">
         <v>657</v>
       </c>
-      <c r="G33" s="105"/>
+      <c r="G33" s="107"/>
       <c r="H33" s="74" t="s">
         <v>678</v>
       </c>
-      <c r="I33" s="110" t="s">
+      <c r="I33" s="112" t="s">
         <v>679</v>
       </c>
-      <c r="J33" s="111"/>
-      <c r="L33" s="118" t="s">
+      <c r="J33" s="113"/>
+      <c r="L33" s="120" t="s">
         <v>701</v>
       </c>
-      <c r="M33" s="118"/>
-      <c r="N33" s="118"/>
+      <c r="M33" s="120"/>
+      <c r="N33" s="120"/>
     </row>
     <row r="34" spans="1:14" ht="28.5" customHeight="1" thickBot="1">
       <c r="A34" s="85">
@@ -15917,29 +16055,29 @@
       <c r="B34" s="73" t="s">
         <v>636</v>
       </c>
-      <c r="C34" s="104" t="s">
+      <c r="C34" s="106" t="s">
         <v>637</v>
       </c>
-      <c r="D34" s="105"/>
+      <c r="D34" s="107"/>
       <c r="E34" s="74" t="s">
         <v>658</v>
       </c>
-      <c r="F34" s="108" t="s">
+      <c r="F34" s="110" t="s">
         <v>659</v>
       </c>
-      <c r="G34" s="109"/>
+      <c r="G34" s="111"/>
       <c r="H34" s="73" t="s">
         <v>680</v>
       </c>
-      <c r="I34" s="114" t="s">
+      <c r="I34" s="116" t="s">
         <v>681</v>
       </c>
-      <c r="J34" s="115"/>
-      <c r="L34" s="119" t="s">
+      <c r="J34" s="117"/>
+      <c r="L34" s="121" t="s">
         <v>702</v>
       </c>
-      <c r="M34" s="119"/>
-      <c r="N34" s="119"/>
+      <c r="M34" s="121"/>
+      <c r="N34" s="121"/>
     </row>
     <row r="35" spans="1:14" ht="31.5" customHeight="1" thickBot="1">
       <c r="A35" s="85">
@@ -15948,29 +16086,29 @@
       <c r="B35" s="74" t="s">
         <v>638</v>
       </c>
-      <c r="C35" s="108" t="s">
+      <c r="C35" s="110" t="s">
         <v>639</v>
       </c>
-      <c r="D35" s="109"/>
+      <c r="D35" s="111"/>
       <c r="E35" s="73" t="s">
         <v>660</v>
       </c>
-      <c r="F35" s="104" t="s">
+      <c r="F35" s="106" t="s">
         <v>661</v>
       </c>
-      <c r="G35" s="105"/>
+      <c r="G35" s="107"/>
       <c r="H35" s="81" t="s">
         <v>682</v>
       </c>
-      <c r="I35" s="108" t="s">
+      <c r="I35" s="110" t="s">
         <v>683</v>
       </c>
-      <c r="J35" s="109"/>
-      <c r="L35" s="118" t="s">
+      <c r="J35" s="111"/>
+      <c r="L35" s="120" t="s">
         <v>703</v>
       </c>
-      <c r="M35" s="118"/>
-      <c r="N35" s="118"/>
+      <c r="M35" s="120"/>
+      <c r="N35" s="120"/>
     </row>
     <row r="36" spans="1:14" ht="60.75" thickBot="1">
       <c r="A36" s="85">
@@ -15979,17 +16117,17 @@
       <c r="B36" s="73" t="s">
         <v>640</v>
       </c>
-      <c r="C36" s="104" t="s">
+      <c r="C36" s="106" t="s">
         <v>641</v>
       </c>
-      <c r="D36" s="105"/>
+      <c r="D36" s="107"/>
       <c r="E36" s="74" t="s">
         <v>662</v>
       </c>
-      <c r="F36" s="108" t="s">
+      <c r="F36" s="110" t="s">
         <v>663</v>
       </c>
-      <c r="G36" s="109"/>
+      <c r="G36" s="111"/>
       <c r="H36" s="82"/>
       <c r="I36" s="75" t="s">
         <v>684</v>
@@ -15997,11 +16135,11 @@
       <c r="J36" s="76" t="s">
         <v>685</v>
       </c>
-      <c r="L36" s="119" t="s">
+      <c r="L36" s="121" t="s">
         <v>704</v>
       </c>
-      <c r="M36" s="119"/>
-      <c r="N36" s="119"/>
+      <c r="M36" s="121"/>
+      <c r="N36" s="121"/>
     </row>
     <row r="37" spans="1:14" ht="75.75" thickBot="1">
       <c r="A37" s="85">
@@ -16010,17 +16148,17 @@
       <c r="B37" s="74" t="s">
         <v>642</v>
       </c>
-      <c r="C37" s="108" t="s">
+      <c r="C37" s="110" t="s">
         <v>643</v>
       </c>
-      <c r="D37" s="109"/>
+      <c r="D37" s="111"/>
       <c r="E37" s="73" t="s">
         <v>664</v>
       </c>
-      <c r="F37" s="104" t="s">
+      <c r="F37" s="106" t="s">
         <v>665</v>
       </c>
-      <c r="G37" s="105"/>
+      <c r="G37" s="107"/>
       <c r="H37" s="82"/>
       <c r="I37" s="77" t="s">
         <v>686</v>
@@ -16036,17 +16174,17 @@
       <c r="B38" s="73" t="s">
         <v>644</v>
       </c>
-      <c r="C38" s="104" t="s">
+      <c r="C38" s="106" t="s">
         <v>645</v>
       </c>
-      <c r="D38" s="105"/>
+      <c r="D38" s="107"/>
       <c r="E38" s="74" t="s">
         <v>666</v>
       </c>
-      <c r="F38" s="108" t="s">
+      <c r="F38" s="110" t="s">
         <v>667</v>
       </c>
-      <c r="G38" s="109"/>
+      <c r="G38" s="111"/>
       <c r="H38" s="82"/>
       <c r="I38" s="79" t="s">
         <v>688</v>
@@ -16062,22 +16200,22 @@
       <c r="B39" s="74" t="s">
         <v>693</v>
       </c>
-      <c r="C39" s="110" t="s">
+      <c r="C39" s="112" t="s">
         <v>694</v>
       </c>
-      <c r="D39" s="111"/>
+      <c r="D39" s="113"/>
       <c r="E39" s="73" t="s">
         <v>691</v>
       </c>
-      <c r="F39" s="114" t="s">
+      <c r="F39" s="116" t="s">
         <v>692</v>
       </c>
-      <c r="G39" s="115"/>
+      <c r="G39" s="117"/>
       <c r="H39" s="83"/>
-      <c r="I39" s="116" t="s">
+      <c r="I39" s="118" t="s">
         <v>690</v>
       </c>
-      <c r="J39" s="117"/>
+      <c r="J39" s="119"/>
     </row>
     <row r="40" spans="1:14" ht="58.5" customHeight="1"/>
     <row r="41" spans="1:14">
@@ -16909,7 +17047,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L43"/>
+  <dimension ref="A1:O43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
@@ -16923,9 +17061,11 @@
     <col min="9" max="9" width="10.140625" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" style="60" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="32.28515625" customWidth="1"/>
+    <col min="13" max="13" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="31.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:15">
       <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
@@ -16960,17 +17100,17 @@
         <v>408</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A2" s="120" t="s">
+    <row r="2" spans="1:15" ht="16.5" customHeight="1">
+      <c r="A2" s="122" t="s">
         <v>505</v>
       </c>
-      <c r="B2" s="125" t="s">
+      <c r="B2" s="127" t="s">
         <v>507</v>
       </c>
-      <c r="C2" s="120" t="s">
+      <c r="C2" s="122" t="s">
         <v>509</v>
       </c>
-      <c r="D2" s="120" t="s">
+      <c r="D2" s="122" t="s">
         <v>557</v>
       </c>
       <c r="E2" s="8"/>
@@ -16989,11 +17129,11 @@
         <v>407</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="123"/>
-      <c r="B3" s="126"/>
-      <c r="C3" s="121"/>
-      <c r="D3" s="121"/>
+    <row r="3" spans="1:15">
+      <c r="A3" s="125"/>
+      <c r="B3" s="128"/>
+      <c r="C3" s="123"/>
+      <c r="D3" s="123"/>
       <c r="E3" s="11"/>
       <c r="F3" s="9" t="s">
         <v>310</v>
@@ -17010,11 +17150,11 @@
         <v>548</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="123"/>
-      <c r="B4" s="126"/>
-      <c r="C4" s="121"/>
-      <c r="D4" s="122"/>
+    <row r="4" spans="1:15">
+      <c r="A4" s="125"/>
+      <c r="B4" s="128"/>
+      <c r="C4" s="123"/>
+      <c r="D4" s="124"/>
       <c r="E4" s="11"/>
       <c r="F4" s="9" t="s">
         <v>311</v>
@@ -17028,10 +17168,10 @@
       <c r="I4" s="58"/>
       <c r="J4" s="10"/>
     </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="123"/>
-      <c r="B5" s="126"/>
-      <c r="C5" s="122"/>
+    <row r="5" spans="1:15">
+      <c r="A5" s="125"/>
+      <c r="B5" s="128"/>
+      <c r="C5" s="124"/>
       <c r="D5" s="47" t="s">
         <v>556</v>
       </c>
@@ -17050,13 +17190,13 @@
         <v>562</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="123"/>
-      <c r="B6" s="126"/>
-      <c r="C6" s="120" t="s">
+    <row r="6" spans="1:15">
+      <c r="A6" s="125"/>
+      <c r="B6" s="128"/>
+      <c r="C6" s="122" t="s">
         <v>508</v>
       </c>
-      <c r="D6" s="120" t="s">
+      <c r="D6" s="122" t="s">
         <v>512</v>
       </c>
       <c r="E6" s="11"/>
@@ -17072,11 +17212,11 @@
       <c r="I6" s="58"/>
       <c r="J6" s="10"/>
     </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="123"/>
-      <c r="B7" s="126"/>
-      <c r="C7" s="121"/>
-      <c r="D7" s="121"/>
+    <row r="7" spans="1:15">
+      <c r="A7" s="125"/>
+      <c r="B7" s="128"/>
+      <c r="C7" s="123"/>
+      <c r="D7" s="123"/>
       <c r="E7" s="11"/>
       <c r="F7" s="9" t="s">
         <v>313</v>
@@ -17090,11 +17230,11 @@
       <c r="I7" s="58"/>
       <c r="J7" s="10"/>
     </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="123"/>
-      <c r="B8" s="126"/>
-      <c r="C8" s="121"/>
-      <c r="D8" s="121"/>
+    <row r="8" spans="1:15">
+      <c r="A8" s="125"/>
+      <c r="B8" s="128"/>
+      <c r="C8" s="123"/>
+      <c r="D8" s="123"/>
       <c r="E8" s="11"/>
       <c r="F8" s="9" t="s">
         <v>314</v>
@@ -17108,11 +17248,11 @@
       <c r="I8" s="58"/>
       <c r="J8" s="10"/>
     </row>
-    <row r="9" spans="1:12">
-      <c r="A9" s="123"/>
-      <c r="B9" s="126"/>
-      <c r="C9" s="121"/>
-      <c r="D9" s="121"/>
+    <row r="9" spans="1:15">
+      <c r="A9" s="125"/>
+      <c r="B9" s="128"/>
+      <c r="C9" s="123"/>
+      <c r="D9" s="123"/>
       <c r="E9" s="8"/>
       <c r="F9" s="9" t="s">
         <v>346</v>
@@ -17126,11 +17266,11 @@
       <c r="I9" s="57"/>
       <c r="J9" s="10"/>
     </row>
-    <row r="10" spans="1:12">
-      <c r="A10" s="123"/>
-      <c r="B10" s="126"/>
-      <c r="C10" s="121"/>
-      <c r="D10" s="121"/>
+    <row r="10" spans="1:15">
+      <c r="A10" s="125"/>
+      <c r="B10" s="128"/>
+      <c r="C10" s="123"/>
+      <c r="D10" s="123"/>
       <c r="E10" s="8"/>
       <c r="F10" s="9" t="s">
         <v>347</v>
@@ -17144,11 +17284,11 @@
       <c r="I10" s="57"/>
       <c r="J10" s="10"/>
     </row>
-    <row r="11" spans="1:12">
-      <c r="A11" s="123"/>
-      <c r="B11" s="126"/>
-      <c r="C11" s="121"/>
-      <c r="D11" s="121"/>
+    <row r="11" spans="1:15">
+      <c r="A11" s="125"/>
+      <c r="B11" s="128"/>
+      <c r="C11" s="123"/>
+      <c r="D11" s="123"/>
       <c r="E11" s="8"/>
       <c r="F11" s="9" t="s">
         <v>315</v>
@@ -17162,11 +17302,11 @@
       <c r="I11" s="57"/>
       <c r="J11" s="10"/>
     </row>
-    <row r="12" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A12" s="123"/>
-      <c r="B12" s="126"/>
-      <c r="C12" s="121"/>
-      <c r="D12" s="121"/>
+    <row r="12" spans="1:15" ht="16.5" customHeight="1">
+      <c r="A12" s="125"/>
+      <c r="B12" s="128"/>
+      <c r="C12" s="123"/>
+      <c r="D12" s="123"/>
       <c r="E12" s="8"/>
       <c r="F12" s="9" t="s">
         <v>348</v>
@@ -17180,11 +17320,11 @@
       <c r="I12" s="57"/>
       <c r="J12" s="10"/>
     </row>
-    <row r="13" spans="1:12">
-      <c r="A13" s="123"/>
-      <c r="B13" s="126"/>
-      <c r="C13" s="121"/>
-      <c r="D13" s="121"/>
+    <row r="13" spans="1:15">
+      <c r="A13" s="125"/>
+      <c r="B13" s="128"/>
+      <c r="C13" s="123"/>
+      <c r="D13" s="123"/>
       <c r="E13" s="11"/>
       <c r="F13" s="9" t="s">
         <v>316</v>
@@ -17200,11 +17340,11 @@
         <v>564</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
-      <c r="A14" s="123"/>
-      <c r="B14" s="126"/>
-      <c r="C14" s="121"/>
-      <c r="D14" s="122"/>
+    <row r="14" spans="1:15">
+      <c r="A14" s="125"/>
+      <c r="B14" s="128"/>
+      <c r="C14" s="123"/>
+      <c r="D14" s="124"/>
       <c r="E14" s="11"/>
       <c r="F14" s="9" t="s">
         <v>318</v>
@@ -17218,10 +17358,10 @@
       <c r="I14" s="58"/>
       <c r="J14" s="10"/>
     </row>
-    <row r="15" spans="1:12" ht="30">
-      <c r="A15" s="123"/>
-      <c r="B15" s="126"/>
-      <c r="C15" s="121"/>
+    <row r="15" spans="1:15" ht="30">
+      <c r="A15" s="125"/>
+      <c r="B15" s="128"/>
+      <c r="C15" s="123"/>
       <c r="D15" s="22" t="s">
         <v>513</v>
       </c>
@@ -17237,14 +17377,22 @@
       </c>
       <c r="I15" s="58"/>
       <c r="J15" s="10"/>
-    </row>
-    <row r="16" spans="1:12">
-      <c r="A16" s="123"/>
-      <c r="B16" s="126"/>
-      <c r="C16" s="120" t="s">
+      <c r="L15" s="141" t="s">
+        <v>855</v>
+      </c>
+      <c r="M15" s="95"/>
+      <c r="N15" s="95"/>
+      <c r="O15" s="95" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" s="125"/>
+      <c r="B16" s="128"/>
+      <c r="C16" s="122" t="s">
         <v>510</v>
       </c>
-      <c r="D16" s="120" t="s">
+      <c r="D16" s="122" t="s">
         <v>514</v>
       </c>
       <c r="E16" s="11"/>
@@ -17259,12 +17407,24 @@
       </c>
       <c r="I16" s="58"/>
       <c r="J16" s="10"/>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="123"/>
-      <c r="B17" s="126"/>
-      <c r="C17" s="121"/>
-      <c r="D17" s="121"/>
+      <c r="L16" s="143" t="s">
+        <v>364</v>
+      </c>
+      <c r="M16" s="142" t="s">
+        <v>361</v>
+      </c>
+      <c r="N16" s="142">
+        <v>1</v>
+      </c>
+      <c r="O16" s="95" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
+      <c r="A17" s="125"/>
+      <c r="B17" s="128"/>
+      <c r="C17" s="123"/>
+      <c r="D17" s="123"/>
       <c r="E17" s="19"/>
       <c r="F17" s="9" t="s">
         <v>365</v>
@@ -17277,12 +17437,21 @@
       </c>
       <c r="I17" s="58"/>
       <c r="J17" s="10"/>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="123"/>
-      <c r="B18" s="126"/>
-      <c r="C18" s="121"/>
-      <c r="D18" s="121"/>
+      <c r="L17" s="143" t="s">
+        <v>332</v>
+      </c>
+      <c r="M17" s="142" t="s">
+        <v>366</v>
+      </c>
+      <c r="N17" s="143">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
+      <c r="A18" s="125"/>
+      <c r="B18" s="128"/>
+      <c r="C18" s="123"/>
+      <c r="D18" s="123"/>
       <c r="E18" s="19"/>
       <c r="F18" s="49" t="s">
         <v>560</v>
@@ -17297,12 +17466,21 @@
       <c r="J18" s="10" t="s">
         <v>563</v>
       </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="123"/>
-      <c r="B19" s="126"/>
-      <c r="C19" s="121"/>
-      <c r="D19" s="121"/>
+      <c r="L18" s="143" t="s">
+        <v>333</v>
+      </c>
+      <c r="M18" s="142" t="s">
+        <v>367</v>
+      </c>
+      <c r="N18" s="143">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
+      <c r="A19" s="125"/>
+      <c r="B19" s="128"/>
+      <c r="C19" s="123"/>
+      <c r="D19" s="123"/>
       <c r="E19" s="8"/>
       <c r="F19" s="9" t="s">
         <v>332</v>
@@ -17315,12 +17493,22 @@
       </c>
       <c r="I19" s="57"/>
       <c r="J19" s="10"/>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="123"/>
-      <c r="B20" s="126"/>
-      <c r="C20" s="121"/>
-      <c r="D20" s="121"/>
+      <c r="L19" s="143" t="s">
+        <v>335</v>
+      </c>
+      <c r="M19" s="142" t="s">
+        <v>369</v>
+      </c>
+      <c r="N19" s="144">
+        <v>1</v>
+      </c>
+      <c r="O19" s="95"/>
+    </row>
+    <row r="20" spans="1:15">
+      <c r="A20" s="125"/>
+      <c r="B20" s="128"/>
+      <c r="C20" s="123"/>
+      <c r="D20" s="123"/>
       <c r="E20" s="8"/>
       <c r="F20" s="9" t="s">
         <v>333</v>
@@ -17333,12 +17521,22 @@
       </c>
       <c r="I20" s="57"/>
       <c r="J20" s="10"/>
-    </row>
-    <row r="21" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A21" s="123"/>
-      <c r="B21" s="126"/>
-      <c r="C21" s="121"/>
-      <c r="D21" s="121"/>
+      <c r="L20" s="143" t="s">
+        <v>336</v>
+      </c>
+      <c r="M20" s="142" t="s">
+        <v>370</v>
+      </c>
+      <c r="N20" s="143">
+        <v>2</v>
+      </c>
+      <c r="O20" s="95"/>
+    </row>
+    <row r="21" spans="1:15" ht="16.5" customHeight="1">
+      <c r="A21" s="125"/>
+      <c r="B21" s="128"/>
+      <c r="C21" s="123"/>
+      <c r="D21" s="123"/>
       <c r="E21" s="14"/>
       <c r="F21" s="9" t="s">
         <v>334</v>
@@ -17353,12 +17551,24 @@
       <c r="J21" s="10" t="s">
         <v>564</v>
       </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="123"/>
-      <c r="B22" s="126"/>
-      <c r="C22" s="121"/>
-      <c r="D22" s="121"/>
+      <c r="L21" s="143" t="s">
+        <v>860</v>
+      </c>
+      <c r="M21" s="142" t="s">
+        <v>362</v>
+      </c>
+      <c r="N21" s="142">
+        <v>1</v>
+      </c>
+      <c r="O21" s="95" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
+      <c r="A22" s="125"/>
+      <c r="B22" s="128"/>
+      <c r="C22" s="123"/>
+      <c r="D22" s="123"/>
       <c r="E22" s="14"/>
       <c r="F22" s="9" t="s">
         <v>335</v>
@@ -17371,12 +17581,24 @@
       </c>
       <c r="I22" s="59"/>
       <c r="J22" s="10"/>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="123"/>
-      <c r="B23" s="126"/>
-      <c r="C23" s="121"/>
-      <c r="D23" s="121"/>
+      <c r="L22" s="145" t="s">
+        <v>859</v>
+      </c>
+      <c r="M22" s="142" t="s">
+        <v>363</v>
+      </c>
+      <c r="N22" s="143">
+        <v>1</v>
+      </c>
+      <c r="O22" s="95" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
+      <c r="A23" s="125"/>
+      <c r="B23" s="128"/>
+      <c r="C23" s="123"/>
+      <c r="D23" s="123"/>
       <c r="E23" s="14"/>
       <c r="F23" s="9" t="s">
         <v>336</v>
@@ -17389,12 +17611,22 @@
       </c>
       <c r="I23" s="59"/>
       <c r="J23" s="10"/>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="123"/>
-      <c r="B24" s="126"/>
-      <c r="C24" s="121"/>
-      <c r="D24" s="121"/>
+      <c r="L23" s="143" t="s">
+        <v>339</v>
+      </c>
+      <c r="M23" s="142" t="s">
+        <v>373</v>
+      </c>
+      <c r="N23" s="144">
+        <v>1</v>
+      </c>
+      <c r="O23" s="95"/>
+    </row>
+    <row r="24" spans="1:15">
+      <c r="A24" s="125"/>
+      <c r="B24" s="128"/>
+      <c r="C24" s="123"/>
+      <c r="D24" s="123"/>
       <c r="E24" s="8"/>
       <c r="F24" s="9" t="s">
         <v>337</v>
@@ -17407,12 +17639,22 @@
       </c>
       <c r="I24" s="57"/>
       <c r="J24" s="10"/>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="123"/>
-      <c r="B25" s="126"/>
-      <c r="C25" s="121"/>
-      <c r="D25" s="121"/>
+      <c r="L24" s="143" t="s">
+        <v>340</v>
+      </c>
+      <c r="M24" s="142" t="s">
+        <v>372</v>
+      </c>
+      <c r="N24" s="144">
+        <v>1</v>
+      </c>
+      <c r="O24" s="95"/>
+    </row>
+    <row r="25" spans="1:15">
+      <c r="A25" s="125"/>
+      <c r="B25" s="128"/>
+      <c r="C25" s="123"/>
+      <c r="D25" s="123"/>
       <c r="E25" s="8"/>
       <c r="F25" s="9" t="s">
         <v>374</v>
@@ -17427,12 +17669,22 @@
       <c r="J25" s="10" t="s">
         <v>564</v>
       </c>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="123"/>
-      <c r="B26" s="126"/>
-      <c r="C26" s="121"/>
-      <c r="D26" s="121"/>
+      <c r="L25" s="143" t="s">
+        <v>337</v>
+      </c>
+      <c r="M25" s="142" t="s">
+        <v>371</v>
+      </c>
+      <c r="N25" s="143">
+        <v>2</v>
+      </c>
+      <c r="O25" s="95"/>
+    </row>
+    <row r="26" spans="1:15">
+      <c r="A26" s="125"/>
+      <c r="B26" s="128"/>
+      <c r="C26" s="123"/>
+      <c r="D26" s="123"/>
       <c r="E26" s="8"/>
       <c r="F26" s="9" t="s">
         <v>338</v>
@@ -17445,12 +17697,22 @@
       </c>
       <c r="I26" s="57"/>
       <c r="J26" s="10"/>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="123"/>
-      <c r="B27" s="126"/>
-      <c r="C27" s="121"/>
-      <c r="D27" s="121"/>
+      <c r="L26" s="143" t="s">
+        <v>338</v>
+      </c>
+      <c r="M26" s="142" t="s">
+        <v>376</v>
+      </c>
+      <c r="N26" s="143">
+        <v>2</v>
+      </c>
+      <c r="O26" s="95"/>
+    </row>
+    <row r="27" spans="1:15">
+      <c r="A27" s="125"/>
+      <c r="B27" s="128"/>
+      <c r="C27" s="123"/>
+      <c r="D27" s="123"/>
       <c r="E27" s="8"/>
       <c r="F27" s="9" t="s">
         <v>339</v>
@@ -17463,12 +17725,22 @@
       </c>
       <c r="I27" s="58"/>
       <c r="J27" s="10"/>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="123"/>
-      <c r="B28" s="126"/>
-      <c r="C28" s="121"/>
-      <c r="D28" s="121"/>
+      <c r="L27" s="143" t="s">
+        <v>334</v>
+      </c>
+      <c r="M27" s="142" t="s">
+        <v>368</v>
+      </c>
+      <c r="N27" s="142">
+        <v>3</v>
+      </c>
+      <c r="O27" s="95"/>
+    </row>
+    <row r="28" spans="1:15">
+      <c r="A28" s="125"/>
+      <c r="B28" s="128"/>
+      <c r="C28" s="123"/>
+      <c r="D28" s="123"/>
       <c r="E28" s="8"/>
       <c r="F28" s="9" t="s">
         <v>340</v>
@@ -17481,12 +17753,22 @@
       </c>
       <c r="I28" s="57"/>
       <c r="J28" s="10"/>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="123"/>
-      <c r="B29" s="126"/>
-      <c r="C29" s="121"/>
-      <c r="D29" s="122"/>
+      <c r="L28" s="143" t="s">
+        <v>374</v>
+      </c>
+      <c r="M28" s="143" t="s">
+        <v>375</v>
+      </c>
+      <c r="N28" s="143">
+        <v>3</v>
+      </c>
+      <c r="O28" s="95"/>
+    </row>
+    <row r="29" spans="1:15">
+      <c r="A29" s="125"/>
+      <c r="B29" s="128"/>
+      <c r="C29" s="123"/>
+      <c r="D29" s="124"/>
       <c r="E29" s="8"/>
       <c r="F29" s="50" t="s">
         <v>323</v>
@@ -17500,11 +17782,11 @@
       <c r="I29" s="59"/>
       <c r="J29" s="10"/>
     </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="123"/>
-      <c r="B30" s="126"/>
-      <c r="C30" s="121"/>
-      <c r="D30" s="120" t="s">
+    <row r="30" spans="1:15">
+      <c r="A30" s="125"/>
+      <c r="B30" s="128"/>
+      <c r="C30" s="123"/>
+      <c r="D30" s="122" t="s">
         <v>519</v>
       </c>
       <c r="E30" s="8"/>
@@ -17520,11 +17802,11 @@
       <c r="I30" s="59"/>
       <c r="J30" s="10"/>
     </row>
-    <row r="31" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A31" s="123"/>
-      <c r="B31" s="126"/>
-      <c r="C31" s="121"/>
-      <c r="D31" s="121"/>
+    <row r="31" spans="1:15" ht="16.5" customHeight="1">
+      <c r="A31" s="125"/>
+      <c r="B31" s="128"/>
+      <c r="C31" s="123"/>
+      <c r="D31" s="123"/>
       <c r="E31" s="8"/>
       <c r="F31" s="9" t="s">
         <v>325</v>
@@ -17538,11 +17820,11 @@
       <c r="I31" s="59"/>
       <c r="J31" s="10"/>
     </row>
-    <row r="32" spans="1:10">
-      <c r="A32" s="123"/>
-      <c r="B32" s="126"/>
-      <c r="C32" s="122"/>
-      <c r="D32" s="122"/>
+    <row r="32" spans="1:15">
+      <c r="A32" s="125"/>
+      <c r="B32" s="128"/>
+      <c r="C32" s="124"/>
+      <c r="D32" s="124"/>
       <c r="E32" s="8"/>
       <c r="F32" s="50" t="s">
         <v>322</v>
@@ -17557,12 +17839,12 @@
       <c r="J32" s="10"/>
     </row>
     <row r="33" spans="1:10" ht="25.5" customHeight="1">
-      <c r="A33" s="123"/>
-      <c r="B33" s="126"/>
-      <c r="C33" s="120" t="s">
+      <c r="A33" s="125"/>
+      <c r="B33" s="128"/>
+      <c r="C33" s="122" t="s">
         <v>341</v>
       </c>
-      <c r="D33" s="120" t="s">
+      <c r="D33" s="122" t="s">
         <v>518</v>
       </c>
       <c r="E33" s="8"/>
@@ -17579,10 +17861,10 @@
       <c r="J33" s="10"/>
     </row>
     <row r="34" spans="1:10" ht="22.5" customHeight="1">
-      <c r="A34" s="123"/>
-      <c r="B34" s="127"/>
-      <c r="C34" s="122"/>
-      <c r="D34" s="122"/>
+      <c r="A34" s="125"/>
+      <c r="B34" s="129"/>
+      <c r="C34" s="124"/>
+      <c r="D34" s="124"/>
       <c r="E34" s="8"/>
       <c r="F34" s="9" t="s">
         <v>331</v>
@@ -17597,7 +17879,7 @@
       <c r="J34" s="10"/>
     </row>
     <row r="35" spans="1:10">
-      <c r="A35" s="123"/>
+      <c r="A35" s="125"/>
       <c r="B35" s="29" t="s">
         <v>328</v>
       </c>
@@ -17621,14 +17903,14 @@
       <c r="J35" s="10"/>
     </row>
     <row r="36" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A36" s="123"/>
-      <c r="B36" s="125" t="s">
+      <c r="A36" s="125"/>
+      <c r="B36" s="127" t="s">
         <v>506</v>
       </c>
-      <c r="C36" s="120" t="s">
+      <c r="C36" s="122" t="s">
         <v>511</v>
       </c>
-      <c r="D36" s="120" t="s">
+      <c r="D36" s="122" t="s">
         <v>517</v>
       </c>
       <c r="E36" s="8" t="s">
@@ -17647,10 +17929,10 @@
       <c r="J36" s="10"/>
     </row>
     <row r="37" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A37" s="123"/>
-      <c r="B37" s="126"/>
-      <c r="C37" s="123"/>
-      <c r="D37" s="123"/>
+      <c r="A37" s="125"/>
+      <c r="B37" s="128"/>
+      <c r="C37" s="125"/>
+      <c r="D37" s="125"/>
       <c r="E37" s="17"/>
       <c r="F37" s="9" t="s">
         <v>304</v>
@@ -17665,10 +17947,10 @@
       <c r="J37" s="10"/>
     </row>
     <row r="38" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A38" s="123"/>
-      <c r="B38" s="126"/>
-      <c r="C38" s="123"/>
-      <c r="D38" s="123"/>
+      <c r="A38" s="125"/>
+      <c r="B38" s="128"/>
+      <c r="C38" s="125"/>
+      <c r="D38" s="125"/>
       <c r="E38" s="17"/>
       <c r="F38" s="9" t="s">
         <v>305</v>
@@ -17683,10 +17965,10 @@
       <c r="J38" s="10"/>
     </row>
     <row r="39" spans="1:10">
-      <c r="A39" s="123"/>
-      <c r="B39" s="126"/>
-      <c r="C39" s="123"/>
-      <c r="D39" s="124"/>
+      <c r="A39" s="125"/>
+      <c r="B39" s="128"/>
+      <c r="C39" s="125"/>
+      <c r="D39" s="126"/>
       <c r="E39" s="17"/>
       <c r="F39" s="9" t="s">
         <v>305</v>
@@ -17701,10 +17983,10 @@
       <c r="J39" s="10"/>
     </row>
     <row r="40" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A40" s="123"/>
-      <c r="B40" s="126"/>
-      <c r="C40" s="123"/>
-      <c r="D40" s="120" t="s">
+      <c r="A40" s="125"/>
+      <c r="B40" s="128"/>
+      <c r="C40" s="125"/>
+      <c r="D40" s="122" t="s">
         <v>516</v>
       </c>
       <c r="E40" s="8"/>
@@ -17721,10 +18003,10 @@
       <c r="J40" s="10"/>
     </row>
     <row r="41" spans="1:10">
-      <c r="A41" s="123"/>
-      <c r="B41" s="126"/>
-      <c r="C41" s="123"/>
-      <c r="D41" s="124"/>
+      <c r="A41" s="125"/>
+      <c r="B41" s="128"/>
+      <c r="C41" s="125"/>
+      <c r="D41" s="126"/>
       <c r="E41" s="8"/>
       <c r="F41" s="9" t="s">
         <v>289</v>
@@ -17739,10 +18021,10 @@
       <c r="J41" s="10"/>
     </row>
     <row r="42" spans="1:10">
-      <c r="A42" s="123"/>
-      <c r="B42" s="126"/>
-      <c r="C42" s="123"/>
-      <c r="D42" s="120" t="s">
+      <c r="A42" s="125"/>
+      <c r="B42" s="128"/>
+      <c r="C42" s="125"/>
+      <c r="D42" s="122" t="s">
         <v>515</v>
       </c>
       <c r="E42" s="8"/>
@@ -17759,10 +18041,10 @@
       <c r="J42" s="10"/>
     </row>
     <row r="43" spans="1:10">
-      <c r="A43" s="124"/>
-      <c r="B43" s="127"/>
-      <c r="C43" s="124"/>
-      <c r="D43" s="124"/>
+      <c r="A43" s="126"/>
+      <c r="B43" s="129"/>
+      <c r="C43" s="126"/>
+      <c r="D43" s="126"/>
       <c r="E43" s="8"/>
       <c r="F43" s="9" t="s">
         <v>301</v>
@@ -17777,6 +18059,9 @@
       <c r="J43" s="10"/>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="L16:N28">
+    <sortCondition ref="N16:N28"/>
+  </sortState>
   <mergeCells count="16">
     <mergeCell ref="C2:C5"/>
     <mergeCell ref="C6:C15"/>

--- a/2020_LogAnalyzer_Leeheesuk.xlsx
+++ b/2020_LogAnalyzer_Leeheesuk.xlsx
@@ -3,37 +3,47 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="22827"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFD66819-B3F4-4B54-9863-F216C464F42E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73E27247-9E3D-4199-B8D2-D48B3BA90C23}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2925" yWindow="0" windowWidth="23910" windowHeight="10335" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UI" sheetId="7" r:id="rId1"/>
     <sheet name="UI_0401피드백" sheetId="13" r:id="rId2"/>
-    <sheet name="UI_상세" sheetId="17" r:id="rId3"/>
-    <sheet name="Table" sheetId="10" r:id="rId4"/>
-    <sheet name="Table_0408" sheetId="15" r:id="rId5"/>
-    <sheet name="Table_0619_0429" sheetId="16" r:id="rId6"/>
-    <sheet name="Pilot" sheetId="11" r:id="rId7"/>
-    <sheet name="아키텍처" sheetId="9" r:id="rId8"/>
-    <sheet name="기능요건" sheetId="8" r:id="rId9"/>
-    <sheet name="기능요건_0401피드백" sheetId="14" r:id="rId10"/>
-    <sheet name="비기능요건" sheetId="6" r:id="rId11"/>
-    <sheet name="지원포맷" sheetId="1" r:id="rId12"/>
-    <sheet name="고려사항" sheetId="5" r:id="rId13"/>
-    <sheet name="기능 - AWStats" sheetId="2" r:id="rId14"/>
-    <sheet name="기능 - apachelogviewer" sheetId="4" r:id="rId15"/>
-    <sheet name="기능 - goaccess" sheetId="3" r:id="rId16"/>
+    <sheet name="UI_Initialization" sheetId="19" r:id="rId3"/>
+    <sheet name="UI_Detail" sheetId="17" r:id="rId4"/>
+    <sheet name="ChartJS" sheetId="18" r:id="rId5"/>
+    <sheet name="Table" sheetId="10" r:id="rId6"/>
+    <sheet name="Table_0408" sheetId="15" r:id="rId7"/>
+    <sheet name="Table_0619_0429" sheetId="16" r:id="rId8"/>
+    <sheet name="Pilot" sheetId="11" r:id="rId9"/>
+    <sheet name="아키텍처" sheetId="9" r:id="rId10"/>
+    <sheet name="기능요건" sheetId="8" r:id="rId11"/>
+    <sheet name="기능요건_0401피드백" sheetId="14" r:id="rId12"/>
+    <sheet name="비기능요건" sheetId="6" r:id="rId13"/>
+    <sheet name="지원포맷" sheetId="1" r:id="rId14"/>
+    <sheet name="고려사항" sheetId="5" r:id="rId15"/>
+    <sheet name="기능 - AWStats" sheetId="2" r:id="rId16"/>
+    <sheet name="기능 - apachelogviewer" sheetId="4" r:id="rId17"/>
+    <sheet name="기능 - goaccess" sheetId="3" r:id="rId18"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">기능요건!$A$1:$L$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="10">기능요건!$A$1:$L$43</definedName>
   </definedNames>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1379" uniqueCount="862">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1484" uniqueCount="924">
   <si>
     <t>구분</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3651,10 +3661,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>진행중</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Searching, Ordering, Paging 기능</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -4144,6 +4150,9 @@
     <t>통계 공식 - LogDetail Table</t>
   </si>
   <si>
+    <t>전체</t>
+  </si>
+  <si>
     <t>기본 조건 충족</t>
   </si>
   <si>
@@ -4160,6 +4169,322 @@
   </si>
   <si>
     <t>Requests Grouping, Count 후 &lt; 5</t>
+  </si>
+  <si>
+    <t>전체 평균 처리시간, 분산</t>
+  </si>
+  <si>
+    <t>버전</t>
+  </si>
+  <si>
+    <t>2.9.3</t>
+  </si>
+  <si>
+    <t>vue-chartjs</t>
+  </si>
+  <si>
+    <t>3.5.0</t>
+  </si>
+  <si>
+    <t>chart 성능</t>
+  </si>
+  <si>
+    <t>chart 데이터 이동은 props를 이용한다.</t>
+  </si>
+  <si>
+    <r>
+      <t>&lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF062873"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>bar-chart</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF212529"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4070A0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>:data</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF666666"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4070A0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"barChartData"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF212529"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4070A0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>:options</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF666666"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4070A0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"barChartOptions"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF212529"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4070A0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>:height</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF666666"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4070A0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"200"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF212529"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> /&gt;</t>
+    </r>
+  </si>
+  <si>
+    <t>(예시;)</t>
+  </si>
+  <si>
+    <t>~05/31</t>
+  </si>
+  <si>
+    <t>~06/26</t>
+  </si>
+  <si>
+    <t>신규 Project 생성</t>
+  </si>
+  <si>
+    <t>기존 Project 로딩</t>
+  </si>
+  <si>
+    <t>로그포맷 설정</t>
+  </si>
+  <si>
+    <t>로딩 데이터범위 설정</t>
+  </si>
+  <si>
+    <t>- 전체
+'- From일시 ~ To일시</t>
+  </si>
+  <si>
+    <t>STEP1</t>
+  </si>
+  <si>
+    <t>STEP2</t>
+  </si>
+  <si>
+    <t>STEP3</t>
+  </si>
+  <si>
+    <t>로그파일 선택</t>
+  </si>
+  <si>
+    <t>추가 가능</t>
+  </si>
+  <si>
+    <t>현재 Session관련</t>
+  </si>
+  <si>
+    <t>상태 보여주기</t>
+  </si>
+  <si>
+    <t>Project</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New </t>
+  </si>
+  <si>
+    <t>Exist</t>
+  </si>
+  <si>
+    <t>project_name</t>
+  </si>
+  <si>
+    <t>project_description</t>
+  </si>
+  <si>
+    <t>uploader</t>
+  </si>
+  <si>
+    <t>created</t>
+  </si>
+  <si>
+    <t>New</t>
+  </si>
+  <si>
+    <t>ROW 선택 후 OK : Loading</t>
+  </si>
+  <si>
+    <t>Step1</t>
+  </si>
+  <si>
+    <t>Next(Step2)</t>
+  </si>
+  <si>
+    <t>Step2</t>
+  </si>
+  <si>
+    <t>Cancel</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>file</t>
+  </si>
+  <si>
+    <t>file format</t>
+  </si>
+  <si>
+    <t>버튼</t>
+  </si>
+  <si>
+    <t>DropBox</t>
+  </si>
+  <si>
+    <t>file size (자동계산)</t>
+  </si>
+  <si>
+    <t>기본선택</t>
+  </si>
+  <si>
+    <t>Custom</t>
+  </si>
+  <si>
+    <t>data range</t>
+  </si>
+  <si>
+    <t>From 일시~ To 일시</t>
+  </si>
+  <si>
+    <t>Prev(Step1)</t>
+  </si>
+  <si>
+    <t>Next(Step3)</t>
+  </si>
+  <si>
+    <t>Step3</t>
+  </si>
+  <si>
+    <t>최종확인</t>
+  </si>
+  <si>
+    <t>New/Exist</t>
+  </si>
+  <si>
+    <t>Prev(Step2)</t>
+  </si>
+  <si>
+    <t>기본 화면</t>
+  </si>
+  <si>
+    <t>현재 정보</t>
+  </si>
+  <si>
+    <t>Add(Step2)</t>
+  </si>
+  <si>
+    <t>file upload부분</t>
+  </si>
+  <si>
+    <t>Single File</t>
+  </si>
+  <si>
+    <t>Multi File</t>
+  </si>
+  <si>
+    <t>Editable</t>
+  </si>
+  <si>
+    <t>https://serversideup.net/uploading-files-vuejs-axios/</t>
+  </si>
+  <si>
+    <t>file_object</t>
+  </si>
+  <si>
+    <t>creator</t>
   </si>
 </sst>
 </file>
@@ -4169,7 +4494,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="36">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4385,8 +4710,47 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF212529"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF062873"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF4070A0"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF666666"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <strike/>
+      <sz val="11"/>
+      <color rgb="FF0C4B33"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4441,8 +4805,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="24">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -4719,12 +5095,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="146">
+  <cellXfs count="161">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5112,6 +5503,49 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -6681,16 +7115,19 @@
             </a:rPr>
             <a:t>Analysis.vue</a:t>
           </a:r>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
-            <a:solidFill>
-              <a:schemeClr val="accent6">
-                <a:lumMod val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:latin typeface="+mn-ea"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-ea"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>촘ㄳ</a:t>
+          </a:r>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -9483,10 +9920,1153 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>92450</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>161924</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>335057</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>85724</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="41" name="TextBox 40">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D439EEC-5195-462F-B549-7A20EF31DD32}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6140825" y="2638424"/>
+          <a:ext cx="1461807" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="15875" cmpd="sng">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Async</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>처리</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>45382</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>321228</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>45943</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F64F4168-27D0-4E78-A53B-355208820030}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="619125" y="426382"/>
+          <a:ext cx="5188503" cy="3305736"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>22973</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>523875</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>167528</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="TextBox 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{923323E0-482F-4924-814C-396224F7CD8F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="632573" y="76200"/>
+          <a:ext cx="2329702" cy="281828"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" indent="0"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0B02BE"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-ea"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Init.vue</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
+            <a:solidFill>
+              <a:srgbClr val="0B02BE"/>
+            </a:solidFill>
+            <a:latin typeface="+mn-ea"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>390525</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="그림 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DA519542-7A6E-4B5B-9A96-787727AA820D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="619125" y="3905250"/>
+          <a:ext cx="5257800" cy="2028825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>1371601</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>361951</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="TextBox 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EFA95299-4DE8-400B-AC3D-B88F5C9E1697}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10801351" y="3067050"/>
+          <a:ext cx="1714500" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="15875" cmpd="sng">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="r"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>click</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>1362076</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>352426</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="TextBox 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD822984-38A5-46E3-A48B-326FF26417C8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10791826" y="4400550"/>
+          <a:ext cx="1714500" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="15875" cmpd="sng">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="r"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>click</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>552451</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="TextBox 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F80E5D0-5333-4463-A18C-F3283D3915B9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6038851" y="4772025"/>
+          <a:ext cx="2200274" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="15875" cmpd="sng">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="r"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>project</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> id </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>받아야 한다</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>1371601</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="9" name="직선 화살표 연결선 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ECAA7CDC-A18E-4A55-813A-32047BC694F0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="5" idx="1"/>
+          <a:endCxn id="7" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="8239125" y="3219450"/>
+          <a:ext cx="2562226" cy="1704975"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>1362076</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="10" name="직선 화살표 연결선 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40DAC3AC-A6AE-4B4F-9215-CA5E30BDB0E2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="6" idx="1"/>
+          <a:endCxn id="7" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="8239125" y="4552950"/>
+          <a:ext cx="2552701" cy="371475"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>380999</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>47624</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="TextBox 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{05D0547B-7D63-46EA-BA92-D97051E9290E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12534899" y="4400550"/>
+          <a:ext cx="1495425" cy="295275"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>logmaster</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>생성</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>390524</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>57149</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="TextBox 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{572F11A4-3390-44D0-932E-C0330210EF6B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12544424" y="6124575"/>
+          <a:ext cx="1495425" cy="295275"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>logfile</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>생성</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>380999</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>47624</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="TextBox 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E62E934-0751-4700-B537-9BDAEA21C99A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12534899" y="7839075"/>
+          <a:ext cx="1495425" cy="295275"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>logdetail</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>생성</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>380999</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>47624</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="TextBox 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF75973D-1005-47D8-9505-B965BC6FA0E8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12534899" y="3076575"/>
+          <a:ext cx="1495425" cy="295275"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>logmaster</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>생성</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>1362076</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>352426</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="TextBox 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B77DF554-59AF-4BE4-8ED9-6C846D3F7C27}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10791826" y="6134100"/>
+          <a:ext cx="1714500" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="15875" cmpd="sng">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="r"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>click</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>1362076</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>352426</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name="TextBox 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{29C49E49-408F-4CEB-B941-6C7C75AAD017}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10791826" y="7848600"/>
+          <a:ext cx="1714500" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="15875" cmpd="sng">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="r"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>click</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -10350,10 +11930,134 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>371476</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>90208</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>120464</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>14008</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="TextBox 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{70FD3AE4-E03D-49E8-819B-7E988C4080E3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3990976" y="3138208"/>
+          <a:ext cx="4492438" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="15875" cmpd="sng">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="r"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>TODO</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> : </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Row </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>클릭시 상세페이지 로딩필요</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>로그 전체 확인</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -10928,7 +12632,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -11606,6 +13310,1071 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>405</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:O43"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" customWidth="1"/>
+    <col min="4" max="4" width="20.42578125" customWidth="1"/>
+    <col min="5" max="5" width="1.85546875" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="23" customWidth="1"/>
+    <col min="7" max="7" width="34.42578125" customWidth="1"/>
+    <col min="8" max="8" width="10.42578125" customWidth="1"/>
+    <col min="9" max="9" width="10.140625" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" style="60" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="32.28515625" customWidth="1"/>
+    <col min="13" max="13" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="31.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15">
+      <c r="A1" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="26" t="s">
+        <v>291</v>
+      </c>
+      <c r="C1" s="26" t="s">
+        <v>293</v>
+      </c>
+      <c r="D1" s="26" t="s">
+        <v>286</v>
+      </c>
+      <c r="E1" s="26" t="s">
+        <v>294</v>
+      </c>
+      <c r="F1" s="26" t="s">
+        <v>287</v>
+      </c>
+      <c r="G1" s="26" t="s">
+        <v>288</v>
+      </c>
+      <c r="H1" s="26" t="s">
+        <v>307</v>
+      </c>
+      <c r="I1" s="56" t="s">
+        <v>292</v>
+      </c>
+      <c r="J1" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="L1" s="31" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="16.5" customHeight="1">
+      <c r="A2" s="122" t="s">
+        <v>505</v>
+      </c>
+      <c r="B2" s="127" t="s">
+        <v>507</v>
+      </c>
+      <c r="C2" s="122" t="s">
+        <v>509</v>
+      </c>
+      <c r="D2" s="122" t="s">
+        <v>557</v>
+      </c>
+      <c r="E2" s="8"/>
+      <c r="F2" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="H2" s="10">
+        <v>1</v>
+      </c>
+      <c r="I2" s="57"/>
+      <c r="J2" s="10"/>
+      <c r="L2" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" s="125"/>
+      <c r="B3" s="128"/>
+      <c r="C3" s="123"/>
+      <c r="D3" s="123"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="H3" s="12">
+        <v>2</v>
+      </c>
+      <c r="I3" s="58"/>
+      <c r="J3" s="10"/>
+      <c r="L3" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" s="125"/>
+      <c r="B4" s="128"/>
+      <c r="C4" s="123"/>
+      <c r="D4" s="124"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="H4" s="12">
+        <v>2</v>
+      </c>
+      <c r="I4" s="58"/>
+      <c r="J4" s="10"/>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" s="125"/>
+      <c r="B5" s="128"/>
+      <c r="C5" s="124"/>
+      <c r="D5" s="47" t="s">
+        <v>556</v>
+      </c>
+      <c r="E5" s="11"/>
+      <c r="F5" s="9" t="s">
+        <v>559</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>558</v>
+      </c>
+      <c r="H5" s="12">
+        <v>3</v>
+      </c>
+      <c r="I5" s="58"/>
+      <c r="J5" s="10" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" s="125"/>
+      <c r="B6" s="128"/>
+      <c r="C6" s="122" t="s">
+        <v>508</v>
+      </c>
+      <c r="D6" s="122" t="s">
+        <v>512</v>
+      </c>
+      <c r="E6" s="11"/>
+      <c r="F6" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="H6" s="12">
+        <v>2</v>
+      </c>
+      <c r="I6" s="58"/>
+      <c r="J6" s="10"/>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" s="125"/>
+      <c r="B7" s="128"/>
+      <c r="C7" s="123"/>
+      <c r="D7" s="123"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>345</v>
+      </c>
+      <c r="H7" s="12">
+        <v>1</v>
+      </c>
+      <c r="I7" s="58"/>
+      <c r="J7" s="10"/>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" s="125"/>
+      <c r="B8" s="128"/>
+      <c r="C8" s="123"/>
+      <c r="D8" s="123"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>353</v>
+      </c>
+      <c r="H8" s="12">
+        <v>1</v>
+      </c>
+      <c r="I8" s="58"/>
+      <c r="J8" s="10"/>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" s="125"/>
+      <c r="B9" s="128"/>
+      <c r="C9" s="123"/>
+      <c r="D9" s="123"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>352</v>
+      </c>
+      <c r="H9" s="10">
+        <v>1</v>
+      </c>
+      <c r="I9" s="57"/>
+      <c r="J9" s="10"/>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" s="125"/>
+      <c r="B10" s="128"/>
+      <c r="C10" s="123"/>
+      <c r="D10" s="123"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="H10" s="10">
+        <v>1</v>
+      </c>
+      <c r="I10" s="57"/>
+      <c r="J10" s="10"/>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" s="125"/>
+      <c r="B11" s="128"/>
+      <c r="C11" s="123"/>
+      <c r="D11" s="123"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="H11" s="10">
+        <v>1</v>
+      </c>
+      <c r="I11" s="57"/>
+      <c r="J11" s="10"/>
+    </row>
+    <row r="12" spans="1:15" ht="16.5" customHeight="1">
+      <c r="A12" s="125"/>
+      <c r="B12" s="128"/>
+      <c r="C12" s="123"/>
+      <c r="D12" s="123"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="H12" s="10">
+        <v>1</v>
+      </c>
+      <c r="I12" s="57"/>
+      <c r="J12" s="10"/>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" s="125"/>
+      <c r="B13" s="128"/>
+      <c r="C13" s="123"/>
+      <c r="D13" s="123"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="9" t="s">
+        <v>316</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="H13" s="12">
+        <v>3</v>
+      </c>
+      <c r="I13" s="58"/>
+      <c r="J13" s="10" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" s="125"/>
+      <c r="B14" s="128"/>
+      <c r="C14" s="123"/>
+      <c r="D14" s="124"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="H14" s="12">
+        <v>2</v>
+      </c>
+      <c r="I14" s="58"/>
+      <c r="J14" s="10"/>
+    </row>
+    <row r="15" spans="1:15" ht="30">
+      <c r="A15" s="125"/>
+      <c r="B15" s="128"/>
+      <c r="C15" s="123"/>
+      <c r="D15" s="22" t="s">
+        <v>513</v>
+      </c>
+      <c r="E15" s="11"/>
+      <c r="F15" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="H15" s="12">
+        <v>1</v>
+      </c>
+      <c r="I15" s="58"/>
+      <c r="J15" s="10"/>
+      <c r="L15" s="141" t="s">
+        <v>854</v>
+      </c>
+      <c r="M15" s="95"/>
+      <c r="N15" s="95"/>
+      <c r="O15" s="95" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" s="125"/>
+      <c r="B16" s="128"/>
+      <c r="C16" s="122" t="s">
+        <v>510</v>
+      </c>
+      <c r="D16" s="122" t="s">
+        <v>514</v>
+      </c>
+      <c r="E16" s="11"/>
+      <c r="F16" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>361</v>
+      </c>
+      <c r="H16" s="12">
+        <v>1</v>
+      </c>
+      <c r="I16" s="58"/>
+      <c r="J16" s="10"/>
+      <c r="L16" s="143" t="s">
+        <v>364</v>
+      </c>
+      <c r="M16" s="142" t="s">
+        <v>361</v>
+      </c>
+      <c r="N16" s="147">
+        <v>1</v>
+      </c>
+      <c r="O16" s="95" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
+      <c r="A17" s="125"/>
+      <c r="B17" s="128"/>
+      <c r="C17" s="123"/>
+      <c r="D17" s="123"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="9" t="s">
+        <v>365</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>362</v>
+      </c>
+      <c r="H17" s="12">
+        <v>1</v>
+      </c>
+      <c r="I17" s="58"/>
+      <c r="J17" s="10"/>
+      <c r="L17" s="143" t="s">
+        <v>332</v>
+      </c>
+      <c r="M17" s="142" t="s">
+        <v>366</v>
+      </c>
+      <c r="N17" s="148">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
+      <c r="A18" s="125"/>
+      <c r="B18" s="128"/>
+      <c r="C18" s="123"/>
+      <c r="D18" s="123"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="49" t="s">
+        <v>560</v>
+      </c>
+      <c r="G18" s="13" t="s">
+        <v>363</v>
+      </c>
+      <c r="H18" s="10">
+        <v>1</v>
+      </c>
+      <c r="I18" s="57"/>
+      <c r="J18" s="10" t="s">
+        <v>563</v>
+      </c>
+      <c r="L18" s="143" t="s">
+        <v>333</v>
+      </c>
+      <c r="M18" s="142" t="s">
+        <v>367</v>
+      </c>
+      <c r="N18" s="148">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
+      <c r="A19" s="125"/>
+      <c r="B19" s="128"/>
+      <c r="C19" s="123"/>
+      <c r="D19" s="123"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="G19" s="13" t="s">
+        <v>366</v>
+      </c>
+      <c r="H19" s="10">
+        <v>1</v>
+      </c>
+      <c r="I19" s="57"/>
+      <c r="J19" s="10"/>
+      <c r="L19" s="143" t="s">
+        <v>335</v>
+      </c>
+      <c r="M19" s="142" t="s">
+        <v>369</v>
+      </c>
+      <c r="N19" s="149">
+        <v>1</v>
+      </c>
+      <c r="O19" s="95"/>
+    </row>
+    <row r="20" spans="1:15">
+      <c r="A20" s="125"/>
+      <c r="B20" s="128"/>
+      <c r="C20" s="123"/>
+      <c r="D20" s="123"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="G20" s="13" t="s">
+        <v>367</v>
+      </c>
+      <c r="H20" s="10">
+        <v>1</v>
+      </c>
+      <c r="I20" s="57"/>
+      <c r="J20" s="10"/>
+      <c r="L20" s="143" t="s">
+        <v>336</v>
+      </c>
+      <c r="M20" s="142" t="s">
+        <v>370</v>
+      </c>
+      <c r="N20" s="143">
+        <v>2</v>
+      </c>
+      <c r="O20" s="95"/>
+    </row>
+    <row r="21" spans="1:15" ht="16.5" customHeight="1">
+      <c r="A21" s="125"/>
+      <c r="B21" s="128"/>
+      <c r="C21" s="123"/>
+      <c r="D21" s="123"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="G21" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="H21" s="16">
+        <v>3</v>
+      </c>
+      <c r="I21" s="59"/>
+      <c r="J21" s="10" t="s">
+        <v>564</v>
+      </c>
+      <c r="L21" s="143" t="s">
+        <v>860</v>
+      </c>
+      <c r="M21" s="142" t="s">
+        <v>362</v>
+      </c>
+      <c r="N21" s="147">
+        <v>1</v>
+      </c>
+      <c r="O21" s="95" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
+      <c r="A22" s="125"/>
+      <c r="B22" s="128"/>
+      <c r="C22" s="123"/>
+      <c r="D22" s="123"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>369</v>
+      </c>
+      <c r="H22" s="16">
+        <v>1</v>
+      </c>
+      <c r="I22" s="59"/>
+      <c r="J22" s="10"/>
+      <c r="L22" s="145" t="s">
+        <v>859</v>
+      </c>
+      <c r="M22" s="142" t="s">
+        <v>363</v>
+      </c>
+      <c r="N22" s="148">
+        <v>1</v>
+      </c>
+      <c r="O22" s="95" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
+      <c r="A23" s="125"/>
+      <c r="B23" s="128"/>
+      <c r="C23" s="123"/>
+      <c r="D23" s="123"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>370</v>
+      </c>
+      <c r="H23" s="16">
+        <v>2</v>
+      </c>
+      <c r="I23" s="59"/>
+      <c r="J23" s="10"/>
+      <c r="L23" s="143" t="s">
+        <v>339</v>
+      </c>
+      <c r="M23" s="142" t="s">
+        <v>373</v>
+      </c>
+      <c r="N23" s="144">
+        <v>1</v>
+      </c>
+      <c r="O23" s="95"/>
+    </row>
+    <row r="24" spans="1:15">
+      <c r="A24" s="125"/>
+      <c r="B24" s="128"/>
+      <c r="C24" s="123"/>
+      <c r="D24" s="123"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="9" t="s">
+        <v>337</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>371</v>
+      </c>
+      <c r="H24" s="10">
+        <v>2</v>
+      </c>
+      <c r="I24" s="57"/>
+      <c r="J24" s="10"/>
+      <c r="L24" s="143" t="s">
+        <v>340</v>
+      </c>
+      <c r="M24" s="142" t="s">
+        <v>372</v>
+      </c>
+      <c r="N24" s="144">
+        <v>1</v>
+      </c>
+      <c r="O24" s="95"/>
+    </row>
+    <row r="25" spans="1:15">
+      <c r="A25" s="125"/>
+      <c r="B25" s="128"/>
+      <c r="C25" s="123"/>
+      <c r="D25" s="123"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>375</v>
+      </c>
+      <c r="H25" s="10">
+        <v>3</v>
+      </c>
+      <c r="I25" s="57"/>
+      <c r="J25" s="10" t="s">
+        <v>564</v>
+      </c>
+      <c r="L25" s="143" t="s">
+        <v>337</v>
+      </c>
+      <c r="M25" s="142" t="s">
+        <v>371</v>
+      </c>
+      <c r="N25" s="143">
+        <v>2</v>
+      </c>
+      <c r="O25" s="95"/>
+    </row>
+    <row r="26" spans="1:15">
+      <c r="A26" s="125"/>
+      <c r="B26" s="128"/>
+      <c r="C26" s="123"/>
+      <c r="D26" s="123"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="G26" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="H26" s="10">
+        <v>2</v>
+      </c>
+      <c r="I26" s="57"/>
+      <c r="J26" s="10"/>
+      <c r="L26" s="143" t="s">
+        <v>338</v>
+      </c>
+      <c r="M26" s="142" t="s">
+        <v>376</v>
+      </c>
+      <c r="N26" s="143">
+        <v>2</v>
+      </c>
+      <c r="O26" s="95"/>
+    </row>
+    <row r="27" spans="1:15">
+      <c r="A27" s="125"/>
+      <c r="B27" s="128"/>
+      <c r="C27" s="123"/>
+      <c r="D27" s="123"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>373</v>
+      </c>
+      <c r="H27" s="12">
+        <v>1</v>
+      </c>
+      <c r="I27" s="58"/>
+      <c r="J27" s="10"/>
+      <c r="L27" s="143" t="s">
+        <v>334</v>
+      </c>
+      <c r="M27" s="142" t="s">
+        <v>368</v>
+      </c>
+      <c r="N27" s="142">
+        <v>3</v>
+      </c>
+      <c r="O27" s="95"/>
+    </row>
+    <row r="28" spans="1:15">
+      <c r="A28" s="125"/>
+      <c r="B28" s="128"/>
+      <c r="C28" s="123"/>
+      <c r="D28" s="123"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="G28" s="13" t="s">
+        <v>372</v>
+      </c>
+      <c r="H28" s="10">
+        <v>1</v>
+      </c>
+      <c r="I28" s="57"/>
+      <c r="J28" s="10"/>
+      <c r="L28" s="143" t="s">
+        <v>374</v>
+      </c>
+      <c r="M28" s="143" t="s">
+        <v>375</v>
+      </c>
+      <c r="N28" s="143">
+        <v>3</v>
+      </c>
+      <c r="O28" s="95"/>
+    </row>
+    <row r="29" spans="1:15">
+      <c r="A29" s="125"/>
+      <c r="B29" s="128"/>
+      <c r="C29" s="123"/>
+      <c r="D29" s="124"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="50" t="s">
+        <v>323</v>
+      </c>
+      <c r="G29" s="50" t="s">
+        <v>358</v>
+      </c>
+      <c r="H29" s="51">
+        <v>3</v>
+      </c>
+      <c r="I29" s="59"/>
+      <c r="J29" s="10"/>
+    </row>
+    <row r="30" spans="1:15">
+      <c r="A30" s="125"/>
+      <c r="B30" s="128"/>
+      <c r="C30" s="123"/>
+      <c r="D30" s="122" t="s">
+        <v>519</v>
+      </c>
+      <c r="E30" s="8"/>
+      <c r="F30" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="H30" s="16">
+        <v>1</v>
+      </c>
+      <c r="I30" s="59"/>
+      <c r="J30" s="10"/>
+      <c r="L30" s="146" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" ht="16.5" customHeight="1">
+      <c r="A31" s="125"/>
+      <c r="B31" s="128"/>
+      <c r="C31" s="123"/>
+      <c r="D31" s="123"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="H31" s="16">
+        <v>1</v>
+      </c>
+      <c r="I31" s="59"/>
+      <c r="J31" s="10"/>
+    </row>
+    <row r="32" spans="1:15">
+      <c r="A32" s="125"/>
+      <c r="B32" s="128"/>
+      <c r="C32" s="124"/>
+      <c r="D32" s="124"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="50" t="s">
+        <v>322</v>
+      </c>
+      <c r="G32" s="50" t="s">
+        <v>321</v>
+      </c>
+      <c r="H32" s="51">
+        <v>3</v>
+      </c>
+      <c r="I32" s="59"/>
+      <c r="J32" s="10"/>
+    </row>
+    <row r="33" spans="1:10" ht="25.5" customHeight="1">
+      <c r="A33" s="125"/>
+      <c r="B33" s="128"/>
+      <c r="C33" s="122" t="s">
+        <v>341</v>
+      </c>
+      <c r="D33" s="122" t="s">
+        <v>518</v>
+      </c>
+      <c r="E33" s="8"/>
+      <c r="F33" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="H33" s="16">
+        <v>1</v>
+      </c>
+      <c r="I33" s="59"/>
+      <c r="J33" s="10"/>
+    </row>
+    <row r="34" spans="1:10" ht="22.5" customHeight="1">
+      <c r="A34" s="125"/>
+      <c r="B34" s="129"/>
+      <c r="C34" s="124"/>
+      <c r="D34" s="124"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="G34" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="H34" s="16">
+        <v>2</v>
+      </c>
+      <c r="I34" s="59"/>
+      <c r="J34" s="10"/>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" s="125"/>
+      <c r="B35" s="29" t="s">
+        <v>328</v>
+      </c>
+      <c r="C35" s="27" t="s">
+        <v>330</v>
+      </c>
+      <c r="D35" s="27" t="s">
+        <v>330</v>
+      </c>
+      <c r="E35" s="28"/>
+      <c r="F35" s="27" t="s">
+        <v>330</v>
+      </c>
+      <c r="G35" s="10" t="s">
+        <v>329</v>
+      </c>
+      <c r="H35" s="16" t="s">
+        <v>330</v>
+      </c>
+      <c r="I35" s="59"/>
+      <c r="J35" s="10"/>
+    </row>
+    <row r="36" spans="1:10" ht="16.5" customHeight="1">
+      <c r="A36" s="125"/>
+      <c r="B36" s="127" t="s">
+        <v>506</v>
+      </c>
+      <c r="C36" s="122" t="s">
+        <v>511</v>
+      </c>
+      <c r="D36" s="122" t="s">
+        <v>517</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="H36" s="10">
+        <v>2</v>
+      </c>
+      <c r="I36" s="57"/>
+      <c r="J36" s="10"/>
+    </row>
+    <row r="37" spans="1:10" ht="16.5" customHeight="1">
+      <c r="A37" s="125"/>
+      <c r="B37" s="128"/>
+      <c r="C37" s="125"/>
+      <c r="D37" s="125"/>
+      <c r="E37" s="17"/>
+      <c r="F37" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="G37" s="15" t="s">
+        <v>306</v>
+      </c>
+      <c r="H37" s="16">
+        <v>1</v>
+      </c>
+      <c r="I37" s="57"/>
+      <c r="J37" s="10"/>
+    </row>
+    <row r="38" spans="1:10" ht="16.5" customHeight="1">
+      <c r="A38" s="125"/>
+      <c r="B38" s="128"/>
+      <c r="C38" s="125"/>
+      <c r="D38" s="125"/>
+      <c r="E38" s="17"/>
+      <c r="F38" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="G38" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="H38" s="16">
+        <v>1</v>
+      </c>
+      <c r="I38" s="57"/>
+      <c r="J38" s="10"/>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" s="125"/>
+      <c r="B39" s="128"/>
+      <c r="C39" s="125"/>
+      <c r="D39" s="126"/>
+      <c r="E39" s="17"/>
+      <c r="F39" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="G39" s="15" t="s">
+        <v>320</v>
+      </c>
+      <c r="H39" s="16">
+        <v>2</v>
+      </c>
+      <c r="I39" s="57"/>
+      <c r="J39" s="10"/>
+    </row>
+    <row r="40" spans="1:10" ht="16.5" customHeight="1">
+      <c r="A40" s="125"/>
+      <c r="B40" s="128"/>
+      <c r="C40" s="125"/>
+      <c r="D40" s="122" t="s">
+        <v>516</v>
+      </c>
+      <c r="E40" s="8"/>
+      <c r="F40" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="G40" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="H40" s="10">
+        <v>2</v>
+      </c>
+      <c r="I40" s="57"/>
+      <c r="J40" s="10"/>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" s="125"/>
+      <c r="B41" s="128"/>
+      <c r="C41" s="125"/>
+      <c r="D41" s="126"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="G41" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="H41" s="10">
+        <v>2</v>
+      </c>
+      <c r="I41" s="57"/>
+      <c r="J41" s="10"/>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" s="125"/>
+      <c r="B42" s="128"/>
+      <c r="C42" s="125"/>
+      <c r="D42" s="122" t="s">
+        <v>515</v>
+      </c>
+      <c r="E42" s="8"/>
+      <c r="F42" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="G42" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="H42" s="10">
+        <v>2</v>
+      </c>
+      <c r="I42" s="57"/>
+      <c r="J42" s="10"/>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="126"/>
+      <c r="B43" s="129"/>
+      <c r="C43" s="126"/>
+      <c r="D43" s="126"/>
+      <c r="E43" s="8"/>
+      <c r="F43" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="G43" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="H43" s="10">
+        <v>2</v>
+      </c>
+      <c r="I43" s="57"/>
+      <c r="J43" s="10"/>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="L16:N28">
+    <sortCondition ref="N16:N28"/>
+  </sortState>
+  <mergeCells count="16">
+    <mergeCell ref="C2:C5"/>
+    <mergeCell ref="C6:C15"/>
+    <mergeCell ref="A2:A43"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="B36:B43"/>
+    <mergeCell ref="C36:C43"/>
+    <mergeCell ref="D36:D39"/>
+    <mergeCell ref="B2:B34"/>
+    <mergeCell ref="C16:C32"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="D16:D29"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="D6:D14"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="64" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -11616,7 +14385,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:J27"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -11636,7 +14405,7 @@
         <v>327</v>
       </c>
       <c r="E1" s="132" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="F1" s="132"/>
       <c r="G1" s="132"/>
@@ -11649,7 +14418,7 @@
         <v>257</v>
       </c>
       <c r="E2" s="133" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="F2" s="133"/>
       <c r="G2" s="133"/>
@@ -11670,34 +14439,34 @@
         <v>259</v>
       </c>
       <c r="E4" s="132" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="F4" s="132"/>
       <c r="G4" s="25" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H4" s="25" t="s">
+        <v>727</v>
+      </c>
+      <c r="J4" t="s">
         <v>728</v>
-      </c>
-      <c r="J4" t="s">
-        <v>729</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="E5" s="131" t="s">
+        <v>721</v>
+      </c>
+      <c r="F5" s="131" t="s">
         <v>722</v>
       </c>
-      <c r="F5" s="131" t="s">
-        <v>723</v>
-      </c>
       <c r="G5" s="72" t="s">
+        <v>748</v>
+      </c>
+      <c r="H5" s="130" t="s">
         <v>749</v>
       </c>
-      <c r="H5" s="130" t="s">
-        <v>750</v>
-      </c>
       <c r="J5" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -11707,11 +14476,11 @@
       <c r="E6" s="131"/>
       <c r="F6" s="131"/>
       <c r="G6" s="72" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H6" s="131"/>
       <c r="J6" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -11719,10 +14488,10 @@
         <v>395</v>
       </c>
       <c r="B7" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="J7" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -11733,7 +14502,7 @@
         <v>396</v>
       </c>
       <c r="J8" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -11741,10 +14510,10 @@
         <v>274</v>
       </c>
       <c r="B9" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="J9" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -11752,7 +14521,7 @@
         <v>397</v>
       </c>
       <c r="J10" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -11760,23 +14529,23 @@
         <v>565</v>
       </c>
       <c r="J11" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="J12" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="B13" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C13" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="J13" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -11784,19 +14553,19 @@
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C14" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="G14" t="s">
+        <v>796</v>
+      </c>
+      <c r="H14" t="s">
         <v>797</v>
       </c>
-      <c r="H14" t="s">
-        <v>798</v>
-      </c>
       <c r="J14" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -11804,16 +14573,16 @@
         <v>2</v>
       </c>
       <c r="B15" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C15" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="G15" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="J15" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -11821,71 +14590,71 @@
         <v>3</v>
       </c>
       <c r="B16" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="C16" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="G16" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="J16" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="17" spans="10:10">
       <c r="J17" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="18" spans="10:10">
       <c r="J18" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="19" spans="10:10">
       <c r="J19" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="20" spans="10:10">
       <c r="J20" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="21" spans="10:10">
       <c r="J21" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="22" spans="10:10">
       <c r="J22" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="23" spans="10:10">
       <c r="J23" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="24" spans="10:10">
       <c r="J24" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="25" spans="10:10">
       <c r="J25" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="26" spans="10:10">
       <c r="J26" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="27" spans="10:10">
       <c r="J27" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
   </sheetData>
@@ -11903,7 +14672,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -12019,7 +14788,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -12209,7 +14978,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:B48"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -12470,7 +15239,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:E96"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -13353,7 +16122,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:E28"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -13574,7 +16343,7 @@
       <c r="B2" s="54"/>
       <c r="C2" s="54"/>
       <c r="M2" s="5" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -13584,7 +16353,7 @@
       <c r="B3" s="54"/>
       <c r="C3" s="54"/>
       <c r="M3" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -13594,7 +16363,7 @@
       <c r="B4" s="54"/>
       <c r="C4" s="54"/>
       <c r="M4" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -13669,6 +16438,362 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AFB2ECB-8FBD-4799-95D6-EF37601202CB}">
+  <dimension ref="F4:V41"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="11" max="11" width="10" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.42578125" customWidth="1"/>
+    <col min="22" max="22" width="21" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="11:15">
+      <c r="L4" t="s">
+        <v>878</v>
+      </c>
+      <c r="M4" t="s">
+        <v>879</v>
+      </c>
+      <c r="N4" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="5" spans="11:15">
+      <c r="L5" t="s">
+        <v>874</v>
+      </c>
+      <c r="M5" t="s">
+        <v>882</v>
+      </c>
+      <c r="O5" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="6" spans="11:15">
+      <c r="L6" t="s">
+        <v>873</v>
+      </c>
+      <c r="M6" t="s">
+        <v>881</v>
+      </c>
+      <c r="N6" t="s">
+        <v>875</v>
+      </c>
+      <c r="O6" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="7" spans="11:15">
+      <c r="N7" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="8" spans="11:15" ht="35.25" customHeight="1">
+      <c r="M8" s="151"/>
+      <c r="N8" s="151" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="10" spans="11:15">
+      <c r="K10" s="154" t="s">
+        <v>914</v>
+      </c>
+      <c r="L10" s="154" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="12" spans="11:15">
+      <c r="K12" s="5" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="13" spans="11:15">
+      <c r="L13" t="s">
+        <v>885</v>
+      </c>
+      <c r="M13" t="s">
+        <v>886</v>
+      </c>
+      <c r="N13" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="14" spans="11:15">
+      <c r="K14" t="s">
+        <v>892</v>
+      </c>
+      <c r="L14" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="15" spans="11:15">
+      <c r="L15" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="16" spans="11:15">
+      <c r="N16" s="5" t="s">
+        <v>897</v>
+      </c>
+      <c r="O16" s="5" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="20" spans="7:22">
+      <c r="K20" t="s">
+        <v>887</v>
+      </c>
+      <c r="L20" t="s">
+        <v>888</v>
+      </c>
+      <c r="M20" t="s">
+        <v>889</v>
+      </c>
+      <c r="N20" t="s">
+        <v>890</v>
+      </c>
+      <c r="O20" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="21" spans="7:22">
+      <c r="L21" t="s">
+        <v>893</v>
+      </c>
+      <c r="T21" s="136" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="22" spans="7:22">
+      <c r="T22" s="137" t="s">
+        <v>835</v>
+      </c>
+      <c r="U22" s="9" t="s">
+        <v>817</v>
+      </c>
+      <c r="V22" s="96" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="23" spans="7:22">
+      <c r="N23" s="5" t="s">
+        <v>898</v>
+      </c>
+      <c r="O23" s="5" t="s">
+        <v>916</v>
+      </c>
+      <c r="T23" s="125"/>
+      <c r="U23" s="9" t="s">
+        <v>818</v>
+      </c>
+      <c r="V23" s="96" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="24" spans="7:22">
+      <c r="T24" s="125"/>
+      <c r="U24" s="9" t="s">
+        <v>819</v>
+      </c>
+      <c r="V24" s="96" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="25" spans="7:22">
+      <c r="K25" s="5" t="s">
+        <v>896</v>
+      </c>
+      <c r="T25" s="125"/>
+      <c r="U25" s="9" t="s">
+        <v>820</v>
+      </c>
+      <c r="V25" s="96" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="26" spans="7:22">
+      <c r="L26" s="155" t="s">
+        <v>899</v>
+      </c>
+      <c r="M26" t="s">
+        <v>901</v>
+      </c>
+      <c r="N26" t="s">
+        <v>903</v>
+      </c>
+      <c r="T26" s="125"/>
+      <c r="U26" s="9" t="s">
+        <v>827</v>
+      </c>
+      <c r="V26" s="96"/>
+    </row>
+    <row r="27" spans="7:22">
+      <c r="L27" t="s">
+        <v>900</v>
+      </c>
+      <c r="M27" t="s">
+        <v>902</v>
+      </c>
+      <c r="T27" s="125"/>
+      <c r="U27" s="9" t="s">
+        <v>828</v>
+      </c>
+      <c r="V27" s="96"/>
+    </row>
+    <row r="28" spans="7:22">
+      <c r="M28" t="s">
+        <v>904</v>
+      </c>
+      <c r="T28" s="125"/>
+      <c r="U28" s="9" t="s">
+        <v>829</v>
+      </c>
+      <c r="V28" s="96" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="29" spans="7:22">
+      <c r="M29" t="s">
+        <v>905</v>
+      </c>
+      <c r="T29" s="126"/>
+      <c r="U29" s="9" t="s">
+        <v>830</v>
+      </c>
+      <c r="V29" s="96" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="30" spans="7:22">
+      <c r="L30" t="s">
+        <v>906</v>
+      </c>
+      <c r="M30" t="s">
+        <v>855</v>
+      </c>
+      <c r="T30" s="157" t="s">
+        <v>834</v>
+      </c>
+      <c r="U30" s="50" t="s">
+        <v>824</v>
+      </c>
+      <c r="V30" s="158"/>
+    </row>
+    <row r="31" spans="7:22">
+      <c r="M31" t="s">
+        <v>907</v>
+      </c>
+      <c r="T31" s="159"/>
+      <c r="U31" s="50" t="s">
+        <v>825</v>
+      </c>
+      <c r="V31" s="158"/>
+    </row>
+    <row r="32" spans="7:22">
+      <c r="G32" t="s">
+        <v>917</v>
+      </c>
+      <c r="N32" s="5" t="s">
+        <v>908</v>
+      </c>
+      <c r="O32" s="5" t="s">
+        <v>909</v>
+      </c>
+      <c r="T32" s="160"/>
+      <c r="U32" s="50" t="s">
+        <v>826</v>
+      </c>
+      <c r="V32" s="158"/>
+    </row>
+    <row r="33" spans="6:15">
+      <c r="F33">
+        <v>1</v>
+      </c>
+      <c r="G33" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="34" spans="6:15">
+      <c r="F34">
+        <v>2</v>
+      </c>
+      <c r="G34" t="s">
+        <v>919</v>
+      </c>
+      <c r="K34" s="5" t="s">
+        <v>910</v>
+      </c>
+      <c r="L34" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="35" spans="6:15">
+      <c r="F35">
+        <v>2</v>
+      </c>
+      <c r="G35" t="s">
+        <v>920</v>
+      </c>
+      <c r="L35" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="36" spans="6:15">
+      <c r="F36" s="7" t="s">
+        <v>921</v>
+      </c>
+      <c r="L36" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="37" spans="6:15">
+      <c r="L37" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="38" spans="6:15">
+      <c r="L38" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="39" spans="6:15">
+      <c r="L39" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="40" spans="6:15">
+      <c r="L40" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="41" spans="6:15">
+      <c r="N41" s="5" t="s">
+        <v>913</v>
+      </c>
+      <c r="O41" s="5" t="s">
+        <v>898</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="T30:T32"/>
+    <mergeCell ref="T22:T29"/>
+  </mergeCells>
+  <phoneticPr fontId="34" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="F36" r:id="rId1" xr:uid="{B558E3CB-EC43-4C25-B54E-A7FCA077240B}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1BB8830-A4C2-4502-B356-CACAF31E4129}">
   <dimension ref="C4:T25"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -13689,15 +16814,15 @@
         <v>313</v>
       </c>
       <c r="R4" s="13" t="s">
+        <v>808</v>
+      </c>
+      <c r="S4" s="134" t="s">
         <v>809</v>
-      </c>
-      <c r="S4" s="134" t="s">
-        <v>810</v>
       </c>
     </row>
     <row r="5" spans="3:20">
       <c r="O5" s="85" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="P5" s="85">
         <v>1</v>
@@ -13709,12 +16834,12 @@
         <v>353</v>
       </c>
       <c r="S5" s="135" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="6" spans="3:20">
       <c r="O6" s="85" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="P6" s="85">
         <v>2</v>
@@ -13729,7 +16854,7 @@
     </row>
     <row r="7" spans="3:20">
       <c r="O7" s="85" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="P7" s="85">
         <v>3</v>
@@ -13744,7 +16869,7 @@
     </row>
     <row r="8" spans="3:20">
       <c r="O8" s="85" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="P8" s="85">
         <v>4</v>
@@ -13759,7 +16884,7 @@
     </row>
     <row r="9" spans="3:20">
       <c r="O9" s="85" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="P9" s="85">
         <v>5</v>
@@ -13780,29 +16905,29 @@
         <v>349</v>
       </c>
       <c r="S10" s="134" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="T10" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="14" spans="3:20">
       <c r="C14" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="Q14" s="136" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="15" spans="3:20">
       <c r="Q15" s="137" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="R15" s="9" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="S15" s="96" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="16" spans="3:20">
@@ -13810,7 +16935,7 @@
         <v>313</v>
       </c>
       <c r="D16" s="96" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>314</v>
@@ -13819,96 +16944,96 @@
         <v>312</v>
       </c>
       <c r="G16" s="10" t="s">
+        <v>814</v>
+      </c>
+      <c r="H16" s="10" t="s">
         <v>815</v>
-      </c>
-      <c r="H16" s="10" t="s">
-        <v>816</v>
       </c>
       <c r="I16" s="10" t="s">
         <v>315</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="Q16" s="125"/>
       <c r="R16" s="9" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="S16" s="96" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="17" spans="10:19">
       <c r="J17" s="85"/>
       <c r="Q17" s="125"/>
       <c r="R17" s="9" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="S17" s="96" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="18" spans="10:19">
       <c r="Q18" s="125"/>
       <c r="R18" s="9" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="S18" s="96" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="19" spans="10:19">
       <c r="Q19" s="125"/>
       <c r="R19" s="9" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="S19" s="96"/>
     </row>
     <row r="20" spans="10:19">
       <c r="Q20" s="125"/>
       <c r="R20" s="9" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="S20" s="96"/>
     </row>
     <row r="21" spans="10:19">
       <c r="Q21" s="125"/>
       <c r="R21" s="9" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="S21" s="96" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="22" spans="10:19">
       <c r="Q22" s="126"/>
       <c r="R22" s="9" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="S22" s="96" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="23" spans="10:19">
       <c r="Q23" s="137" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="R23" s="9" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="S23" s="96"/>
     </row>
     <row r="24" spans="10:19">
       <c r="Q24" s="125"/>
       <c r="R24" s="9" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="S24" s="96"/>
     </row>
     <row r="25" spans="10:19">
       <c r="Q25" s="126"/>
       <c r="R25" s="9" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="S25" s="96"/>
     </row>
@@ -13924,7 +17049,54 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40AA86BA-F3A4-4754-BF0E-F316D4665692}">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>863</v>
+      </c>
+      <c r="B1" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>863</v>
+      </c>
+      <c r="B4" t="s">
+        <v>866</v>
+      </c>
+      <c r="D4" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15.75" thickBot="1">
+      <c r="A6" t="s">
+        <v>868</v>
+      </c>
+      <c r="E6" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15.75" thickBot="1">
+      <c r="A7" s="150" t="s">
+        <v>869</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -14364,7 +17536,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -15304,7 +18476,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -15316,7 +18488,7 @@
     <col min="2" max="2" width="23.42578125" customWidth="1"/>
     <col min="3" max="3" width="21.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="18.85546875" customWidth="1"/>
     <col min="6" max="6" width="15.5703125" customWidth="1"/>
     <col min="7" max="7" width="15" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17.42578125" customWidth="1"/>
@@ -15345,11 +18517,11 @@
       <c r="D2" s="33" t="s">
         <v>571</v>
       </c>
-      <c r="E2" s="33" t="s">
+      <c r="E2" s="37" t="s">
         <v>584</v>
       </c>
       <c r="F2" s="33" t="s">
-        <v>413</v>
+        <v>923</v>
       </c>
       <c r="G2" s="33" t="s">
         <v>416</v>
@@ -15363,9 +18535,9 @@
         <v>470</v>
       </c>
       <c r="D3" s="89" t="s">
-        <v>824</v>
-      </c>
-      <c r="E3" s="89" t="s">
+        <v>823</v>
+      </c>
+      <c r="E3" s="152" t="s">
         <v>434</v>
       </c>
       <c r="F3" s="89" t="s">
@@ -15385,7 +18557,7 @@
       <c r="D4" s="66" t="s">
         <v>573</v>
       </c>
-      <c r="E4" s="66" t="s">
+      <c r="E4" s="153" t="s">
         <v>453</v>
       </c>
       <c r="F4" s="66" t="s">
@@ -15403,7 +18575,7 @@
       <c r="D5" s="89">
         <v>300</v>
       </c>
-      <c r="E5" s="89">
+      <c r="E5" s="152">
         <v>100</v>
       </c>
       <c r="F5" s="89">
@@ -15429,6 +18601,9 @@
       <c r="A7" s="34" t="s">
         <v>575</v>
       </c>
+      <c r="F7" s="156" t="s">
+        <v>922</v>
+      </c>
       <c r="L7" s="50" t="s">
         <v>602</v>
       </c>
@@ -15447,12 +18622,15 @@
         <v>583</v>
       </c>
       <c r="E8" s="33" t="s">
+        <v>584</v>
+      </c>
+      <c r="F8" s="37" t="s">
         <v>578</v>
       </c>
-      <c r="F8" s="33" t="s">
+      <c r="G8" s="33" t="s">
         <v>577</v>
       </c>
-      <c r="G8" s="33" t="s">
+      <c r="H8" s="33" t="s">
         <v>416</v>
       </c>
       <c r="L8" s="9" t="s">
@@ -15475,13 +18653,16 @@
       <c r="D9" s="89" t="s">
         <v>432</v>
       </c>
-      <c r="E9" s="89" t="s">
+      <c r="E9" s="96" t="s">
+        <v>434</v>
+      </c>
+      <c r="F9" s="89" t="s">
         <v>433</v>
       </c>
-      <c r="F9" s="89" t="s">
+      <c r="G9" s="89" t="s">
         <v>580</v>
       </c>
-      <c r="G9" s="89" t="s">
+      <c r="H9" s="89" t="s">
         <v>467</v>
       </c>
       <c r="L9" s="9" t="s">
@@ -15502,12 +18683,15 @@
         <v>453</v>
       </c>
       <c r="E10" s="66" t="s">
+        <v>453</v>
+      </c>
+      <c r="F10" s="66" t="s">
         <v>456</v>
       </c>
-      <c r="F10" s="67" t="s">
+      <c r="G10" s="67" t="s">
         <v>462</v>
       </c>
-      <c r="G10" s="66" t="s">
+      <c r="H10" s="66" t="s">
         <v>455</v>
       </c>
       <c r="L10" s="9" t="s">
@@ -15523,10 +18707,12 @@
       <c r="D11" s="89">
         <v>100</v>
       </c>
-      <c r="E11" s="67"/>
+      <c r="E11" s="96">
+        <v>100</v>
+      </c>
       <c r="F11" s="67"/>
       <c r="G11" s="67"/>
-      <c r="H11" s="36"/>
+      <c r="H11" s="67"/>
       <c r="I11" s="36"/>
       <c r="L11" s="9" t="s">
         <v>348</v>
@@ -15581,13 +18767,13 @@
         <v>424</v>
       </c>
       <c r="K14" s="33" t="s">
+        <v>841</v>
+      </c>
+      <c r="L14" s="33" t="s">
         <v>842</v>
       </c>
-      <c r="L14" s="33" t="s">
-        <v>843</v>
-      </c>
       <c r="M14" s="33" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -15601,13 +18787,13 @@
         <v>437</v>
       </c>
       <c r="E15" s="89" t="s">
+        <v>805</v>
+      </c>
+      <c r="F15" s="89" t="s">
         <v>806</v>
       </c>
-      <c r="F15" s="89" t="s">
+      <c r="G15" s="89" t="s">
         <v>807</v>
-      </c>
-      <c r="G15" s="89" t="s">
-        <v>808</v>
       </c>
       <c r="H15" s="89" t="s">
         <v>438</v>
@@ -15619,13 +18805,13 @@
         <v>440</v>
       </c>
       <c r="K15" s="138" t="s">
+        <v>849</v>
+      </c>
+      <c r="L15" s="138" t="s">
         <v>850</v>
       </c>
-      <c r="L15" s="138" t="s">
+      <c r="M15" s="138" t="s">
         <v>851</v>
-      </c>
-      <c r="M15" s="138" t="s">
-        <v>852</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="30">
@@ -15639,31 +18825,31 @@
         <v>573</v>
       </c>
       <c r="E16" s="139" t="s">
+        <v>846</v>
+      </c>
+      <c r="F16" s="139" t="s">
         <v>847</v>
       </c>
-      <c r="F16" s="139" t="s">
-        <v>848</v>
-      </c>
       <c r="G16" s="139" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H16" s="139" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="I16" s="139" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="J16" s="139" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="K16" s="139" t="s">
+        <v>844</v>
+      </c>
+      <c r="L16" s="139" t="s">
         <v>845</v>
       </c>
-      <c r="L16" s="139" t="s">
-        <v>846</v>
-      </c>
       <c r="M16" s="139" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -15679,13 +18865,13 @@
       <c r="I17" s="69"/>
       <c r="J17" s="69"/>
       <c r="K17" s="140" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="L17" s="140" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="M17" s="140" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -16220,27 +19406,27 @@
     <row r="40" spans="1:14" ht="58.5" customHeight="1"/>
     <row r="41" spans="1:14">
       <c r="A41" s="34" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="D41" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="42" spans="1:14">
       <c r="B42" s="39" t="s">
+        <v>767</v>
+      </c>
+      <c r="C42" s="64" t="s">
+        <v>778</v>
+      </c>
+      <c r="D42" s="33" t="s">
+        <v>755</v>
+      </c>
+      <c r="E42" s="33" t="s">
         <v>768</v>
       </c>
-      <c r="C42" s="64" t="s">
-        <v>779</v>
-      </c>
-      <c r="D42" s="33" t="s">
-        <v>756</v>
-      </c>
-      <c r="E42" s="33" t="s">
-        <v>769</v>
-      </c>
       <c r="F42" s="33" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="G42" s="33" t="s">
         <v>416</v>
@@ -16260,16 +19446,16 @@
         <v>430</v>
       </c>
       <c r="C43" s="89" t="s">
+        <v>753</v>
+      </c>
+      <c r="D43" s="89" t="s">
+        <v>756</v>
+      </c>
+      <c r="E43" s="89" t="s">
         <v>754</v>
       </c>
-      <c r="D43" s="89" t="s">
-        <v>757</v>
-      </c>
-      <c r="E43" s="89" t="s">
-        <v>755</v>
-      </c>
       <c r="F43" s="89" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="G43" s="89" t="s">
         <v>467</v>
@@ -16332,13 +19518,13 @@
     </row>
     <row r="46" spans="1:14" ht="20.25" customHeight="1">
       <c r="C46" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="D46" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="E46" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="L46" s="18" t="s">
         <v>271</v>
@@ -16352,7 +19538,7 @@
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="34" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="L47" s="19" t="s">
         <v>266</v>
@@ -16366,16 +19552,16 @@
     </row>
     <row r="48" spans="1:14">
       <c r="B48" s="39" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="C48" s="64" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="D48" s="91" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E48" s="33" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="F48" s="33" t="s">
         <v>416</v>
@@ -16398,10 +19584,10 @@
         <v>430</v>
       </c>
       <c r="D49" s="89" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="E49" s="89" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F49" s="89" t="s">
         <v>467</v>
@@ -16447,33 +19633,33 @@
     </row>
     <row r="52" spans="2:14">
       <c r="C52" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="D52" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="E52" t="s">
         <v>641</v>
       </c>
       <c r="F52" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="G52" s="93" t="s">
+        <v>784</v>
+      </c>
+      <c r="H52" s="93" t="s">
+        <v>759</v>
+      </c>
+      <c r="I52" s="93" t="s">
         <v>785</v>
       </c>
-      <c r="H52" s="93" t="s">
-        <v>760</v>
-      </c>
-      <c r="I52" s="93" t="s">
+      <c r="J52" s="93" t="s">
         <v>786</v>
-      </c>
-      <c r="J52" s="93" t="s">
-        <v>787</v>
       </c>
     </row>
     <row r="53" spans="2:14">
       <c r="D53" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="E53" t="s">
         <v>643</v>
@@ -16484,27 +19670,27 @@
     </row>
     <row r="54" spans="2:14">
       <c r="C54" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="55" spans="2:14">
       <c r="C55" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="56" spans="2:14">
       <c r="C56" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="57" spans="2:14">
       <c r="C57" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="58" spans="2:14">
       <c r="C58" s="92" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
   </sheetData>
@@ -16571,7 +19757,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -16705,7 +19891,7 @@
         <v>715</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>716</v>
@@ -16717,22 +19903,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="86" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B7" s="86" t="s">
         <v>472</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="E7" s="86" t="s">
-        <v>721</v>
-      </c>
-      <c r="F7" s="86" t="s">
-        <v>717</v>
+        <v>720</v>
+      </c>
+      <c r="F7" s="96" t="s">
+        <v>503</v>
       </c>
       <c r="G7" s="86"/>
     </row>
@@ -16767,13 +19953,13 @@
         <v>473</v>
       </c>
       <c r="C9" s="19" t="s">
+        <v>718</v>
+      </c>
+      <c r="D9" s="19" t="s">
         <v>719</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="E9" s="20" t="s">
         <v>720</v>
-      </c>
-      <c r="E9" s="20" t="s">
-        <v>721</v>
       </c>
       <c r="F9" s="89" t="s">
         <v>503</v>
@@ -16793,8 +19979,12 @@
       <c r="D10" s="19" t="s">
         <v>488</v>
       </c>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
+      <c r="E10" s="20" t="s">
+        <v>871</v>
+      </c>
+      <c r="F10" s="96" t="s">
+        <v>503</v>
+      </c>
       <c r="G10" s="20" t="s">
         <v>708</v>
       </c>
@@ -16812,8 +20002,12 @@
       <c r="D11" s="19" t="s">
         <v>489</v>
       </c>
-      <c r="E11" s="20"/>
-      <c r="F11" s="20"/>
+      <c r="E11" s="96" t="s">
+        <v>871</v>
+      </c>
+      <c r="F11" s="96" t="s">
+        <v>503</v>
+      </c>
       <c r="G11" s="20" t="s">
         <v>708</v>
       </c>
@@ -16831,8 +20025,12 @@
       <c r="D12" s="19" t="s">
         <v>490</v>
       </c>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
+      <c r="E12" s="96" t="s">
+        <v>871</v>
+      </c>
+      <c r="F12" s="96" t="s">
+        <v>503</v>
+      </c>
       <c r="G12" s="20" t="s">
         <v>708</v>
       </c>
@@ -16850,8 +20048,12 @@
       <c r="D13" s="19" t="s">
         <v>486</v>
       </c>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
+      <c r="E13" s="96" t="s">
+        <v>872</v>
+      </c>
+      <c r="F13" s="96" t="s">
+        <v>503</v>
+      </c>
       <c r="G13" s="20" t="s">
         <v>708</v>
       </c>
@@ -16869,8 +20071,12 @@
       <c r="D14" s="19" t="s">
         <v>487</v>
       </c>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
+      <c r="E14" s="96" t="s">
+        <v>872</v>
+      </c>
+      <c r="F14" s="96" t="s">
+        <v>503</v>
+      </c>
       <c r="G14" s="20" t="s">
         <v>708</v>
       </c>
@@ -16888,8 +20094,12 @@
       <c r="D15" s="19" t="s">
         <v>712</v>
       </c>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
+      <c r="E15" s="96" t="s">
+        <v>871</v>
+      </c>
+      <c r="F15" s="96" t="s">
+        <v>503</v>
+      </c>
       <c r="G15" s="20"/>
     </row>
     <row r="17" spans="1:5">
@@ -17022,1066 +20232,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" t="s">
-        <v>405</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:O43"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" customWidth="1"/>
-    <col min="4" max="4" width="20.42578125" customWidth="1"/>
-    <col min="5" max="5" width="1.85546875" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="23" customWidth="1"/>
-    <col min="7" max="7" width="34.42578125" customWidth="1"/>
-    <col min="8" max="8" width="10.42578125" customWidth="1"/>
-    <col min="9" max="9" width="10.140625" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" style="60" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="32.28515625" customWidth="1"/>
-    <col min="13" max="13" width="26.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="31.42578125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:15">
-      <c r="A1" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="26" t="s">
-        <v>291</v>
-      </c>
-      <c r="C1" s="26" t="s">
-        <v>293</v>
-      </c>
-      <c r="D1" s="26" t="s">
-        <v>286</v>
-      </c>
-      <c r="E1" s="26" t="s">
-        <v>294</v>
-      </c>
-      <c r="F1" s="26" t="s">
-        <v>287</v>
-      </c>
-      <c r="G1" s="26" t="s">
-        <v>288</v>
-      </c>
-      <c r="H1" s="26" t="s">
-        <v>307</v>
-      </c>
-      <c r="I1" s="56" t="s">
-        <v>292</v>
-      </c>
-      <c r="J1" s="26" t="s">
-        <v>561</v>
-      </c>
-      <c r="L1" s="31" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" ht="16.5" customHeight="1">
-      <c r="A2" s="122" t="s">
-        <v>505</v>
-      </c>
-      <c r="B2" s="127" t="s">
-        <v>507</v>
-      </c>
-      <c r="C2" s="122" t="s">
-        <v>509</v>
-      </c>
-      <c r="D2" s="122" t="s">
-        <v>557</v>
-      </c>
-      <c r="E2" s="8"/>
-      <c r="F2" s="9" t="s">
-        <v>309</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>344</v>
-      </c>
-      <c r="H2" s="10">
-        <v>1</v>
-      </c>
-      <c r="I2" s="57"/>
-      <c r="J2" s="10"/>
-      <c r="L2" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
-      <c r="A3" s="125"/>
-      <c r="B3" s="128"/>
-      <c r="C3" s="123"/>
-      <c r="D3" s="123"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="9" t="s">
-        <v>310</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>360</v>
-      </c>
-      <c r="H3" s="12">
-        <v>2</v>
-      </c>
-      <c r="I3" s="58"/>
-      <c r="J3" s="10"/>
-      <c r="L3" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
-      <c r="A4" s="125"/>
-      <c r="B4" s="128"/>
-      <c r="C4" s="123"/>
-      <c r="D4" s="124"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="9" t="s">
-        <v>311</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>359</v>
-      </c>
-      <c r="H4" s="12">
-        <v>2</v>
-      </c>
-      <c r="I4" s="58"/>
-      <c r="J4" s="10"/>
-    </row>
-    <row r="5" spans="1:15">
-      <c r="A5" s="125"/>
-      <c r="B5" s="128"/>
-      <c r="C5" s="124"/>
-      <c r="D5" s="47" t="s">
-        <v>556</v>
-      </c>
-      <c r="E5" s="11"/>
-      <c r="F5" s="9" t="s">
-        <v>559</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>558</v>
-      </c>
-      <c r="H5" s="12">
-        <v>3</v>
-      </c>
-      <c r="I5" s="58"/>
-      <c r="J5" s="10" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
-      <c r="A6" s="125"/>
-      <c r="B6" s="128"/>
-      <c r="C6" s="122" t="s">
-        <v>508</v>
-      </c>
-      <c r="D6" s="122" t="s">
-        <v>512</v>
-      </c>
-      <c r="E6" s="11"/>
-      <c r="F6" s="9" t="s">
-        <v>312</v>
-      </c>
-      <c r="G6" s="13" t="s">
-        <v>317</v>
-      </c>
-      <c r="H6" s="12">
-        <v>2</v>
-      </c>
-      <c r="I6" s="58"/>
-      <c r="J6" s="10"/>
-    </row>
-    <row r="7" spans="1:15">
-      <c r="A7" s="125"/>
-      <c r="B7" s="128"/>
-      <c r="C7" s="123"/>
-      <c r="D7" s="123"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="9" t="s">
-        <v>313</v>
-      </c>
-      <c r="G7" s="13" t="s">
-        <v>345</v>
-      </c>
-      <c r="H7" s="12">
-        <v>1</v>
-      </c>
-      <c r="I7" s="58"/>
-      <c r="J7" s="10"/>
-    </row>
-    <row r="8" spans="1:15">
-      <c r="A8" s="125"/>
-      <c r="B8" s="128"/>
-      <c r="C8" s="123"/>
-      <c r="D8" s="123"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="9" t="s">
-        <v>314</v>
-      </c>
-      <c r="G8" s="13" t="s">
-        <v>353</v>
-      </c>
-      <c r="H8" s="12">
-        <v>1</v>
-      </c>
-      <c r="I8" s="58"/>
-      <c r="J8" s="10"/>
-    </row>
-    <row r="9" spans="1:15">
-      <c r="A9" s="125"/>
-      <c r="B9" s="128"/>
-      <c r="C9" s="123"/>
-      <c r="D9" s="123"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="9" t="s">
-        <v>346</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>352</v>
-      </c>
-      <c r="H9" s="10">
-        <v>1</v>
-      </c>
-      <c r="I9" s="57"/>
-      <c r="J9" s="10"/>
-    </row>
-    <row r="10" spans="1:15">
-      <c r="A10" s="125"/>
-      <c r="B10" s="128"/>
-      <c r="C10" s="123"/>
-      <c r="D10" s="123"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="9" t="s">
-        <v>347</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>351</v>
-      </c>
-      <c r="H10" s="10">
-        <v>1</v>
-      </c>
-      <c r="I10" s="57"/>
-      <c r="J10" s="10"/>
-    </row>
-    <row r="11" spans="1:15">
-      <c r="A11" s="125"/>
-      <c r="B11" s="128"/>
-      <c r="C11" s="123"/>
-      <c r="D11" s="123"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="9" t="s">
-        <v>315</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>350</v>
-      </c>
-      <c r="H11" s="10">
-        <v>1</v>
-      </c>
-      <c r="I11" s="57"/>
-      <c r="J11" s="10"/>
-    </row>
-    <row r="12" spans="1:15" ht="16.5" customHeight="1">
-      <c r="A12" s="125"/>
-      <c r="B12" s="128"/>
-      <c r="C12" s="123"/>
-      <c r="D12" s="123"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="9" t="s">
-        <v>348</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>349</v>
-      </c>
-      <c r="H12" s="10">
-        <v>1</v>
-      </c>
-      <c r="I12" s="57"/>
-      <c r="J12" s="10"/>
-    </row>
-    <row r="13" spans="1:15">
-      <c r="A13" s="125"/>
-      <c r="B13" s="128"/>
-      <c r="C13" s="123"/>
-      <c r="D13" s="123"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="9" t="s">
-        <v>316</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>354</v>
-      </c>
-      <c r="H13" s="12">
-        <v>3</v>
-      </c>
-      <c r="I13" s="58"/>
-      <c r="J13" s="10" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
-      <c r="A14" s="125"/>
-      <c r="B14" s="128"/>
-      <c r="C14" s="123"/>
-      <c r="D14" s="124"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="9" t="s">
-        <v>318</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>355</v>
-      </c>
-      <c r="H14" s="12">
-        <v>2</v>
-      </c>
-      <c r="I14" s="58"/>
-      <c r="J14" s="10"/>
-    </row>
-    <row r="15" spans="1:15" ht="30">
-      <c r="A15" s="125"/>
-      <c r="B15" s="128"/>
-      <c r="C15" s="123"/>
-      <c r="D15" s="22" t="s">
-        <v>513</v>
-      </c>
-      <c r="E15" s="11"/>
-      <c r="F15" s="9" t="s">
-        <v>343</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>342</v>
-      </c>
-      <c r="H15" s="12">
-        <v>1</v>
-      </c>
-      <c r="I15" s="58"/>
-      <c r="J15" s="10"/>
-      <c r="L15" s="141" t="s">
-        <v>855</v>
-      </c>
-      <c r="M15" s="95"/>
-      <c r="N15" s="95"/>
-      <c r="O15" s="95" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
-      <c r="A16" s="125"/>
-      <c r="B16" s="128"/>
-      <c r="C16" s="122" t="s">
-        <v>510</v>
-      </c>
-      <c r="D16" s="122" t="s">
-        <v>514</v>
-      </c>
-      <c r="E16" s="11"/>
-      <c r="F16" s="9" t="s">
-        <v>364</v>
-      </c>
-      <c r="G16" s="13" t="s">
-        <v>361</v>
-      </c>
-      <c r="H16" s="12">
-        <v>1</v>
-      </c>
-      <c r="I16" s="58"/>
-      <c r="J16" s="10"/>
-      <c r="L16" s="143" t="s">
-        <v>364</v>
-      </c>
-      <c r="M16" s="142" t="s">
-        <v>361</v>
-      </c>
-      <c r="N16" s="142">
-        <v>1</v>
-      </c>
-      <c r="O16" s="95" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15">
-      <c r="A17" s="125"/>
-      <c r="B17" s="128"/>
-      <c r="C17" s="123"/>
-      <c r="D17" s="123"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="9" t="s">
-        <v>365</v>
-      </c>
-      <c r="G17" s="13" t="s">
-        <v>362</v>
-      </c>
-      <c r="H17" s="12">
-        <v>1</v>
-      </c>
-      <c r="I17" s="58"/>
-      <c r="J17" s="10"/>
-      <c r="L17" s="143" t="s">
-        <v>332</v>
-      </c>
-      <c r="M17" s="142" t="s">
-        <v>366</v>
-      </c>
-      <c r="N17" s="143">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15">
-      <c r="A18" s="125"/>
-      <c r="B18" s="128"/>
-      <c r="C18" s="123"/>
-      <c r="D18" s="123"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="49" t="s">
-        <v>560</v>
-      </c>
-      <c r="G18" s="13" t="s">
-        <v>363</v>
-      </c>
-      <c r="H18" s="10">
-        <v>1</v>
-      </c>
-      <c r="I18" s="57"/>
-      <c r="J18" s="10" t="s">
-        <v>563</v>
-      </c>
-      <c r="L18" s="143" t="s">
-        <v>333</v>
-      </c>
-      <c r="M18" s="142" t="s">
-        <v>367</v>
-      </c>
-      <c r="N18" s="143">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15">
-      <c r="A19" s="125"/>
-      <c r="B19" s="128"/>
-      <c r="C19" s="123"/>
-      <c r="D19" s="123"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="9" t="s">
-        <v>332</v>
-      </c>
-      <c r="G19" s="13" t="s">
-        <v>366</v>
-      </c>
-      <c r="H19" s="10">
-        <v>1</v>
-      </c>
-      <c r="I19" s="57"/>
-      <c r="J19" s="10"/>
-      <c r="L19" s="143" t="s">
-        <v>335</v>
-      </c>
-      <c r="M19" s="142" t="s">
-        <v>369</v>
-      </c>
-      <c r="N19" s="144">
-        <v>1</v>
-      </c>
-      <c r="O19" s="95"/>
-    </row>
-    <row r="20" spans="1:15">
-      <c r="A20" s="125"/>
-      <c r="B20" s="128"/>
-      <c r="C20" s="123"/>
-      <c r="D20" s="123"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="9" t="s">
-        <v>333</v>
-      </c>
-      <c r="G20" s="13" t="s">
-        <v>367</v>
-      </c>
-      <c r="H20" s="10">
-        <v>1</v>
-      </c>
-      <c r="I20" s="57"/>
-      <c r="J20" s="10"/>
-      <c r="L20" s="143" t="s">
-        <v>336</v>
-      </c>
-      <c r="M20" s="142" t="s">
-        <v>370</v>
-      </c>
-      <c r="N20" s="143">
-        <v>2</v>
-      </c>
-      <c r="O20" s="95"/>
-    </row>
-    <row r="21" spans="1:15" ht="16.5" customHeight="1">
-      <c r="A21" s="125"/>
-      <c r="B21" s="128"/>
-      <c r="C21" s="123"/>
-      <c r="D21" s="123"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="9" t="s">
-        <v>334</v>
-      </c>
-      <c r="G21" s="13" t="s">
-        <v>368</v>
-      </c>
-      <c r="H21" s="16">
-        <v>3</v>
-      </c>
-      <c r="I21" s="59"/>
-      <c r="J21" s="10" t="s">
-        <v>564</v>
-      </c>
-      <c r="L21" s="143" t="s">
-        <v>860</v>
-      </c>
-      <c r="M21" s="142" t="s">
-        <v>362</v>
-      </c>
-      <c r="N21" s="142">
-        <v>1</v>
-      </c>
-      <c r="O21" s="95" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15">
-      <c r="A22" s="125"/>
-      <c r="B22" s="128"/>
-      <c r="C22" s="123"/>
-      <c r="D22" s="123"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="9" t="s">
-        <v>335</v>
-      </c>
-      <c r="G22" s="13" t="s">
-        <v>369</v>
-      </c>
-      <c r="H22" s="16">
-        <v>1</v>
-      </c>
-      <c r="I22" s="59"/>
-      <c r="J22" s="10"/>
-      <c r="L22" s="145" t="s">
-        <v>859</v>
-      </c>
-      <c r="M22" s="142" t="s">
-        <v>363</v>
-      </c>
-      <c r="N22" s="143">
-        <v>1</v>
-      </c>
-      <c r="O22" s="95" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15">
-      <c r="A23" s="125"/>
-      <c r="B23" s="128"/>
-      <c r="C23" s="123"/>
-      <c r="D23" s="123"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="9" t="s">
-        <v>336</v>
-      </c>
-      <c r="G23" s="13" t="s">
-        <v>370</v>
-      </c>
-      <c r="H23" s="16">
-        <v>2</v>
-      </c>
-      <c r="I23" s="59"/>
-      <c r="J23" s="10"/>
-      <c r="L23" s="143" t="s">
-        <v>339</v>
-      </c>
-      <c r="M23" s="142" t="s">
-        <v>373</v>
-      </c>
-      <c r="N23" s="144">
-        <v>1</v>
-      </c>
-      <c r="O23" s="95"/>
-    </row>
-    <row r="24" spans="1:15">
-      <c r="A24" s="125"/>
-      <c r="B24" s="128"/>
-      <c r="C24" s="123"/>
-      <c r="D24" s="123"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="9" t="s">
-        <v>337</v>
-      </c>
-      <c r="G24" s="13" t="s">
-        <v>371</v>
-      </c>
-      <c r="H24" s="10">
-        <v>2</v>
-      </c>
-      <c r="I24" s="57"/>
-      <c r="J24" s="10"/>
-      <c r="L24" s="143" t="s">
-        <v>340</v>
-      </c>
-      <c r="M24" s="142" t="s">
-        <v>372</v>
-      </c>
-      <c r="N24" s="144">
-        <v>1</v>
-      </c>
-      <c r="O24" s="95"/>
-    </row>
-    <row r="25" spans="1:15">
-      <c r="A25" s="125"/>
-      <c r="B25" s="128"/>
-      <c r="C25" s="123"/>
-      <c r="D25" s="123"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="9" t="s">
-        <v>374</v>
-      </c>
-      <c r="G25" s="13" t="s">
-        <v>375</v>
-      </c>
-      <c r="H25" s="10">
-        <v>3</v>
-      </c>
-      <c r="I25" s="57"/>
-      <c r="J25" s="10" t="s">
-        <v>564</v>
-      </c>
-      <c r="L25" s="143" t="s">
-        <v>337</v>
-      </c>
-      <c r="M25" s="142" t="s">
-        <v>371</v>
-      </c>
-      <c r="N25" s="143">
-        <v>2</v>
-      </c>
-      <c r="O25" s="95"/>
-    </row>
-    <row r="26" spans="1:15">
-      <c r="A26" s="125"/>
-      <c r="B26" s="128"/>
-      <c r="C26" s="123"/>
-      <c r="D26" s="123"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="9" t="s">
-        <v>338</v>
-      </c>
-      <c r="G26" s="13" t="s">
-        <v>376</v>
-      </c>
-      <c r="H26" s="10">
-        <v>2</v>
-      </c>
-      <c r="I26" s="57"/>
-      <c r="J26" s="10"/>
-      <c r="L26" s="143" t="s">
-        <v>338</v>
-      </c>
-      <c r="M26" s="142" t="s">
-        <v>376</v>
-      </c>
-      <c r="N26" s="143">
-        <v>2</v>
-      </c>
-      <c r="O26" s="95"/>
-    </row>
-    <row r="27" spans="1:15">
-      <c r="A27" s="125"/>
-      <c r="B27" s="128"/>
-      <c r="C27" s="123"/>
-      <c r="D27" s="123"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="9" t="s">
-        <v>339</v>
-      </c>
-      <c r="G27" s="13" t="s">
-        <v>373</v>
-      </c>
-      <c r="H27" s="12">
-        <v>1</v>
-      </c>
-      <c r="I27" s="58"/>
-      <c r="J27" s="10"/>
-      <c r="L27" s="143" t="s">
-        <v>334</v>
-      </c>
-      <c r="M27" s="142" t="s">
-        <v>368</v>
-      </c>
-      <c r="N27" s="142">
-        <v>3</v>
-      </c>
-      <c r="O27" s="95"/>
-    </row>
-    <row r="28" spans="1:15">
-      <c r="A28" s="125"/>
-      <c r="B28" s="128"/>
-      <c r="C28" s="123"/>
-      <c r="D28" s="123"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="9" t="s">
-        <v>340</v>
-      </c>
-      <c r="G28" s="13" t="s">
-        <v>372</v>
-      </c>
-      <c r="H28" s="10">
-        <v>1</v>
-      </c>
-      <c r="I28" s="57"/>
-      <c r="J28" s="10"/>
-      <c r="L28" s="143" t="s">
-        <v>374</v>
-      </c>
-      <c r="M28" s="143" t="s">
-        <v>375</v>
-      </c>
-      <c r="N28" s="143">
-        <v>3</v>
-      </c>
-      <c r="O28" s="95"/>
-    </row>
-    <row r="29" spans="1:15">
-      <c r="A29" s="125"/>
-      <c r="B29" s="128"/>
-      <c r="C29" s="123"/>
-      <c r="D29" s="124"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="50" t="s">
-        <v>323</v>
-      </c>
-      <c r="G29" s="50" t="s">
-        <v>358</v>
-      </c>
-      <c r="H29" s="51">
-        <v>3</v>
-      </c>
-      <c r="I29" s="59"/>
-      <c r="J29" s="10"/>
-    </row>
-    <row r="30" spans="1:15">
-      <c r="A30" s="125"/>
-      <c r="B30" s="128"/>
-      <c r="C30" s="123"/>
-      <c r="D30" s="122" t="s">
-        <v>519</v>
-      </c>
-      <c r="E30" s="8"/>
-      <c r="F30" s="9" t="s">
-        <v>324</v>
-      </c>
-      <c r="G30" s="9" t="s">
-        <v>356</v>
-      </c>
-      <c r="H30" s="16">
-        <v>1</v>
-      </c>
-      <c r="I30" s="59"/>
-      <c r="J30" s="10"/>
-    </row>
-    <row r="31" spans="1:15" ht="16.5" customHeight="1">
-      <c r="A31" s="125"/>
-      <c r="B31" s="128"/>
-      <c r="C31" s="123"/>
-      <c r="D31" s="123"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="9" t="s">
-        <v>325</v>
-      </c>
-      <c r="G31" s="9" t="s">
-        <v>357</v>
-      </c>
-      <c r="H31" s="16">
-        <v>1</v>
-      </c>
-      <c r="I31" s="59"/>
-      <c r="J31" s="10"/>
-    </row>
-    <row r="32" spans="1:15">
-      <c r="A32" s="125"/>
-      <c r="B32" s="128"/>
-      <c r="C32" s="124"/>
-      <c r="D32" s="124"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="50" t="s">
-        <v>322</v>
-      </c>
-      <c r="G32" s="50" t="s">
-        <v>321</v>
-      </c>
-      <c r="H32" s="51">
-        <v>3</v>
-      </c>
-      <c r="I32" s="59"/>
-      <c r="J32" s="10"/>
-    </row>
-    <row r="33" spans="1:10" ht="25.5" customHeight="1">
-      <c r="A33" s="125"/>
-      <c r="B33" s="128"/>
-      <c r="C33" s="122" t="s">
-        <v>341</v>
-      </c>
-      <c r="D33" s="122" t="s">
-        <v>518</v>
-      </c>
-      <c r="E33" s="8"/>
-      <c r="F33" s="9" t="s">
-        <v>308</v>
-      </c>
-      <c r="G33" s="9" t="s">
-        <v>378</v>
-      </c>
-      <c r="H33" s="16">
-        <v>1</v>
-      </c>
-      <c r="I33" s="59"/>
-      <c r="J33" s="10"/>
-    </row>
-    <row r="34" spans="1:10" ht="22.5" customHeight="1">
-      <c r="A34" s="125"/>
-      <c r="B34" s="129"/>
-      <c r="C34" s="124"/>
-      <c r="D34" s="124"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="9" t="s">
-        <v>331</v>
-      </c>
-      <c r="G34" s="9" t="s">
-        <v>377</v>
-      </c>
-      <c r="H34" s="16">
-        <v>2</v>
-      </c>
-      <c r="I34" s="59"/>
-      <c r="J34" s="10"/>
-    </row>
-    <row r="35" spans="1:10">
-      <c r="A35" s="125"/>
-      <c r="B35" s="29" t="s">
-        <v>328</v>
-      </c>
-      <c r="C35" s="27" t="s">
-        <v>330</v>
-      </c>
-      <c r="D35" s="27" t="s">
-        <v>330</v>
-      </c>
-      <c r="E35" s="28"/>
-      <c r="F35" s="27" t="s">
-        <v>330</v>
-      </c>
-      <c r="G35" s="10" t="s">
-        <v>329</v>
-      </c>
-      <c r="H35" s="16" t="s">
-        <v>330</v>
-      </c>
-      <c r="I35" s="59"/>
-      <c r="J35" s="10"/>
-    </row>
-    <row r="36" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A36" s="125"/>
-      <c r="B36" s="127" t="s">
-        <v>506</v>
-      </c>
-      <c r="C36" s="122" t="s">
-        <v>511</v>
-      </c>
-      <c r="D36" s="122" t="s">
-        <v>517</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>295</v>
-      </c>
-      <c r="F36" s="9" t="s">
-        <v>296</v>
-      </c>
-      <c r="G36" s="9" t="s">
-        <v>303</v>
-      </c>
-      <c r="H36" s="10">
-        <v>2</v>
-      </c>
-      <c r="I36" s="57"/>
-      <c r="J36" s="10"/>
-    </row>
-    <row r="37" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A37" s="125"/>
-      <c r="B37" s="128"/>
-      <c r="C37" s="125"/>
-      <c r="D37" s="125"/>
-      <c r="E37" s="17"/>
-      <c r="F37" s="9" t="s">
-        <v>304</v>
-      </c>
-      <c r="G37" s="15" t="s">
-        <v>306</v>
-      </c>
-      <c r="H37" s="16">
-        <v>1</v>
-      </c>
-      <c r="I37" s="57"/>
-      <c r="J37" s="10"/>
-    </row>
-    <row r="38" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A38" s="125"/>
-      <c r="B38" s="128"/>
-      <c r="C38" s="125"/>
-      <c r="D38" s="125"/>
-      <c r="E38" s="17"/>
-      <c r="F38" s="9" t="s">
-        <v>305</v>
-      </c>
-      <c r="G38" s="15" t="s">
-        <v>319</v>
-      </c>
-      <c r="H38" s="16">
-        <v>1</v>
-      </c>
-      <c r="I38" s="57"/>
-      <c r="J38" s="10"/>
-    </row>
-    <row r="39" spans="1:10">
-      <c r="A39" s="125"/>
-      <c r="B39" s="128"/>
-      <c r="C39" s="125"/>
-      <c r="D39" s="126"/>
-      <c r="E39" s="17"/>
-      <c r="F39" s="9" t="s">
-        <v>305</v>
-      </c>
-      <c r="G39" s="15" t="s">
-        <v>320</v>
-      </c>
-      <c r="H39" s="16">
-        <v>2</v>
-      </c>
-      <c r="I39" s="57"/>
-      <c r="J39" s="10"/>
-    </row>
-    <row r="40" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A40" s="125"/>
-      <c r="B40" s="128"/>
-      <c r="C40" s="125"/>
-      <c r="D40" s="122" t="s">
-        <v>516</v>
-      </c>
-      <c r="E40" s="8"/>
-      <c r="F40" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="G40" s="9" t="s">
-        <v>298</v>
-      </c>
-      <c r="H40" s="10">
-        <v>2</v>
-      </c>
-      <c r="I40" s="57"/>
-      <c r="J40" s="10"/>
-    </row>
-    <row r="41" spans="1:10">
-      <c r="A41" s="125"/>
-      <c r="B41" s="128"/>
-      <c r="C41" s="125"/>
-      <c r="D41" s="126"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="9" t="s">
-        <v>289</v>
-      </c>
-      <c r="G41" s="9" t="s">
-        <v>299</v>
-      </c>
-      <c r="H41" s="10">
-        <v>2</v>
-      </c>
-      <c r="I41" s="57"/>
-      <c r="J41" s="10"/>
-    </row>
-    <row r="42" spans="1:10">
-      <c r="A42" s="125"/>
-      <c r="B42" s="128"/>
-      <c r="C42" s="125"/>
-      <c r="D42" s="122" t="s">
-        <v>515</v>
-      </c>
-      <c r="E42" s="8"/>
-      <c r="F42" s="9" t="s">
-        <v>290</v>
-      </c>
-      <c r="G42" s="9" t="s">
-        <v>300</v>
-      </c>
-      <c r="H42" s="10">
-        <v>2</v>
-      </c>
-      <c r="I42" s="57"/>
-      <c r="J42" s="10"/>
-    </row>
-    <row r="43" spans="1:10">
-      <c r="A43" s="126"/>
-      <c r="B43" s="129"/>
-      <c r="C43" s="126"/>
-      <c r="D43" s="126"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="9" t="s">
-        <v>301</v>
-      </c>
-      <c r="G43" s="9" t="s">
-        <v>302</v>
-      </c>
-      <c r="H43" s="10">
-        <v>2</v>
-      </c>
-      <c r="I43" s="57"/>
-      <c r="J43" s="10"/>
-    </row>
-  </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="L16:N28">
-    <sortCondition ref="N16:N28"/>
-  </sortState>
-  <mergeCells count="16">
-    <mergeCell ref="C2:C5"/>
-    <mergeCell ref="C6:C15"/>
-    <mergeCell ref="A2:A43"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="B36:B43"/>
-    <mergeCell ref="C36:C43"/>
-    <mergeCell ref="D36:D39"/>
-    <mergeCell ref="B2:B34"/>
-    <mergeCell ref="C16:C32"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="D16:D29"/>
-    <mergeCell ref="D30:D32"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="D6:D14"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="64" orientation="landscape" r:id="rId1"/>
-</worksheet>
 </file>
--- a/2020_LogAnalyzer_Leeheesuk.xlsx
+++ b/2020_LogAnalyzer_Leeheesuk.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="22827"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73E27247-9E3D-4199-B8D2-D48B3BA90C23}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{843249BB-3D0A-4455-9100-7E0768611011}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2925" yWindow="0" windowWidth="23910" windowHeight="10335" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15990" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UI" sheetId="7" r:id="rId1"/>

--- a/2020_LogAnalyzer_Leeheesuk.xlsx
+++ b/2020_LogAnalyzer_Leeheesuk.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="22827"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{843249BB-3D0A-4455-9100-7E0768611011}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE4B6B15-A582-4180-B3FA-1C7BC187F684}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15990" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UI" sheetId="7" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1484" uniqueCount="924">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1489" uniqueCount="926">
   <si>
     <t>구분</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4485,6 +4485,12 @@
   </si>
   <si>
     <t>creator</t>
+  </si>
+  <si>
+    <t>Multifile 차리위해 들고 있어야 한다.</t>
+  </si>
+  <si>
+    <t>http://www.cdrf.co/3.1/rest_framework.viewsets/ModelViewSet.html#get_queryset</t>
   </si>
 </sst>
 </file>
@@ -4750,7 +4756,7 @@
       <family val="3"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4814,6 +4820,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5115,7 +5127,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="161">
+  <cellXfs count="166">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5546,6 +5558,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -17445,6 +17472,9 @@
       <c r="B16" s="7" t="s">
         <v>464</v>
       </c>
+      <c r="H16" s="7" t="s">
+        <v>925</v>
+      </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="36" t="s">
@@ -17530,9 +17560,10 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="B16" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
+    <hyperlink ref="H16" r:id="rId2" location="get_queryset" display="http://www.cdrf.co/3.1/rest_framework.viewsets/ModelViewSet.html - get_queryset" xr:uid="{EB3C776D-0C15-44A0-B9CD-1A860C621EC3}"/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="61" orientation="landscape" verticalDpi="0" r:id="rId2"/>
+  <pageSetup paperSize="9" scale="61" orientation="landscape" verticalDpi="0" r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -18921,6 +18952,13 @@
       <c r="K20" s="33" t="s">
         <v>416</v>
       </c>
+      <c r="L20" s="161" t="s">
+        <v>569</v>
+      </c>
+      <c r="M20" s="164" t="s">
+        <v>924</v>
+      </c>
+      <c r="N20" s="165"/>
     </row>
     <row r="21" spans="1:14">
       <c r="B21" s="89" t="s">
@@ -18953,6 +18991,9 @@
       <c r="K21" s="89" t="s">
         <v>467</v>
       </c>
+      <c r="L21" s="162" t="s">
+        <v>430</v>
+      </c>
     </row>
     <row r="22" spans="1:14" ht="30">
       <c r="B22" s="66" t="s">
@@ -18985,6 +19026,9 @@
       <c r="K22" s="66" t="s">
         <v>593</v>
       </c>
+      <c r="L22" s="163" t="s">
+        <v>459</v>
+      </c>
     </row>
     <row r="23" spans="1:14">
       <c r="B23" s="68">
@@ -19013,6 +19057,7 @@
         <v>200</v>
       </c>
       <c r="K23" s="68"/>
+      <c r="L23" s="162"/>
     </row>
     <row r="25" spans="1:14">
       <c r="B25" s="7" t="s">
@@ -19694,7 +19739,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="46">
+  <mergeCells count="47">
+    <mergeCell ref="M20:N20"/>
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="I27:J27"/>

--- a/2020_LogAnalyzer_Leeheesuk.xlsx
+++ b/2020_LogAnalyzer_Leeheesuk.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="22827"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB42F411-B6D7-4B16-BF97-890FD725C0FA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEF1774C-93EE-4777-837A-3E6E0AA66876}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2040" yWindow="315" windowWidth="23910" windowHeight="14385" firstSheet="12" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UI" sheetId="7" r:id="rId1"/>
@@ -17,20 +17,21 @@
     <sheet name="Table" sheetId="10" r:id="rId7"/>
     <sheet name="Table_0408" sheetId="15" r:id="rId8"/>
     <sheet name="Table_0619_0429" sheetId="16" r:id="rId9"/>
-    <sheet name="Pilot" sheetId="11" r:id="rId10"/>
-    <sheet name="아키텍처" sheetId="9" r:id="rId11"/>
-    <sheet name="기능요건" sheetId="8" r:id="rId12"/>
-    <sheet name="기능요건_0401피드백" sheetId="14" r:id="rId13"/>
-    <sheet name="비기능요건" sheetId="6" r:id="rId14"/>
-    <sheet name="지원포맷" sheetId="1" r:id="rId15"/>
-    <sheet name="로그로맷 항목설명" sheetId="21" r:id="rId16"/>
-    <sheet name="고려사항" sheetId="5" r:id="rId17"/>
-    <sheet name="기능 - AWStats" sheetId="2" r:id="rId18"/>
-    <sheet name="기능 - apachelogviewer" sheetId="4" r:id="rId19"/>
-    <sheet name="기능 - goaccess" sheetId="3" r:id="rId20"/>
+    <sheet name="LogFile Test_0717" sheetId="22" r:id="rId10"/>
+    <sheet name="Pilot" sheetId="11" r:id="rId11"/>
+    <sheet name="아키텍처" sheetId="9" r:id="rId12"/>
+    <sheet name="기능요건" sheetId="8" r:id="rId13"/>
+    <sheet name="기능요건_0401피드백" sheetId="14" r:id="rId14"/>
+    <sheet name="비기능요건" sheetId="6" r:id="rId15"/>
+    <sheet name="지원포맷" sheetId="1" r:id="rId16"/>
+    <sheet name="로그로맷 항목설명" sheetId="21" r:id="rId17"/>
+    <sheet name="고려사항" sheetId="5" r:id="rId18"/>
+    <sheet name="기능 - AWStats" sheetId="2" r:id="rId19"/>
+    <sheet name="기능 - apachelogviewer" sheetId="4" r:id="rId20"/>
+    <sheet name="기능 - goaccess" sheetId="3" r:id="rId21"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="11">기능요건!$A$1:$M$45</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="12">기능요건!$A$1:$M$45</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1864" uniqueCount="1169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1918" uniqueCount="1206">
   <si>
     <t>구분</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -5306,6 +5307,151 @@
   </si>
   <si>
     <t>https://docs.microsoft.com/en-us/windows/win32/http/iis-logging</t>
+  </si>
+  <si>
+    <t>불러오기 
+기능관련</t>
+  </si>
+  <si>
+    <t>https://docs.djangoproject.com/en/1.8/ref/models/database-functions/</t>
+  </si>
+  <si>
+    <t>추가(07/15)</t>
+  </si>
+  <si>
+    <t>파일포맷</t>
+  </si>
+  <si>
+    <t>파일크기</t>
+  </si>
+  <si>
+    <t>파일구분</t>
+  </si>
+  <si>
+    <t>mposlogs</t>
+  </si>
+  <si>
+    <t>access_log-2019-02-21</t>
+  </si>
+  <si>
+    <t>로그구분</t>
+  </si>
+  <si>
+    <t>apache</t>
+  </si>
+  <si>
+    <t>216KB</t>
+  </si>
+  <si>
+    <t>"%v, %{X-Forwarded-For}i %l %u %t \"%r\" %&gt;s %b" common</t>
+  </si>
+  <si>
+    <t>비고</t>
+  </si>
+  <si>
+    <t>Virtual Host</t>
+  </si>
+  <si>
+    <r>
+      <t>서버가 수신한 요청에서 </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF003366"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>Foobar</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF003366"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF003366"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> 헤더의 내용.
+※ 예 : X-Forwarded-For</t>
+    </r>
+  </si>
+  <si>
+    <t>samplelog</t>
+  </si>
+  <si>
+    <t>'%h %l %u %t \"%r\" %&gt;s %b'</t>
+  </si>
+  <si>
+    <t>common</t>
+  </si>
+  <si>
+    <t>테스트</t>
+  </si>
+  <si>
+    <t>HOM1-W-F11_Samsungcard</t>
+  </si>
+  <si>
+    <t>acslog</t>
+  </si>
+  <si>
+    <t>%h %l %u %t "%r" %s %b "%{Referer}i" "%{Cookie}i" %D</t>
+  </si>
+  <si>
+    <t>access-itct-20200702.log</t>
+  </si>
+  <si>
+    <t>12MB</t>
+  </si>
+  <si>
+    <t>이슈</t>
+  </si>
+  <si>
+    <t>HOM1-W-F11.log.chunk001.Test</t>
+  </si>
+  <si>
+    <t>10MB</t>
+  </si>
+  <si>
+    <t>"%h %{X-Forwarded-For}i %l %u %v %t \"%r\" %&gt;s %B \"%{Referer}i\" \"%{User-Agent}i\"
+\"%{JSESSIONID}C\" %a %{env}e %f %p %D" combined</t>
+  </si>
+  <si>
+    <t>900KB</t>
+  </si>
+  <si>
+    <t>업로드시간(s) - DB</t>
+  </si>
+  <si>
+    <t>access_log_900K</t>
+  </si>
+  <si>
+    <t>%{X-Forwarded-For}I 에 여러 IP가나오는 부분을 해결해야 한다.
+※ 오류가 난 부분을 별도로 뺄 수 있는가? 후처리</t>
+  </si>
+  <si>
+    <t>100MB</t>
+  </si>
+  <si>
+    <t>500MB</t>
+  </si>
+  <si>
+    <t>1GB</t>
+  </si>
+  <si>
+    <t>2GB</t>
+  </si>
+  <si>
+    <t>4GB</t>
   </si>
 </sst>
 </file>
@@ -5938,7 +6084,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="179">
+  <cellXfs count="191">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6241,6 +6387,42 @@
     <xf numFmtId="0" fontId="16" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -6280,6 +6462,12 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -6289,11 +6477,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -6307,24 +6495,6 @@
     <xf numFmtId="0" fontId="22" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -6336,6 +6506,24 @@
     </xf>
     <xf numFmtId="0" fontId="23" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -6351,6 +6539,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6373,50 +6570,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -10793,16 +10975,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>92450</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>2</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>161924</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>335057</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>394610</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>85724</xdr:rowOff>
+      <xdr:rowOff>40821</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -10817,8 +10999,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6140825" y="2638424"/>
-          <a:ext cx="1461807" cy="304800"/>
+          <a:off x="5456466" y="2638424"/>
+          <a:ext cx="3456215" cy="259897"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -10871,7 +11053,31 @@
                 <a:srgbClr val="FF0000"/>
               </a:solidFill>
             </a:rPr>
-            <a:t>처리</a:t>
+            <a:t>처리 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> - </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>분산비동기 처리 고려 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(Celery?)</a:t>
           </a:r>
           <a:endParaRPr lang="en-US" sz="1100">
             <a:solidFill>
@@ -15273,51 +15479,51 @@
     </row>
     <row r="17" spans="1:13">
       <c r="J17" s="19"/>
-      <c r="K17" s="118" t="s">
+      <c r="K17" s="132" t="s">
         <v>537</v>
       </c>
-      <c r="L17" s="119"/>
-      <c r="M17" s="120"/>
+      <c r="L17" s="133"/>
+      <c r="M17" s="134"/>
     </row>
     <row r="18" spans="1:13">
       <c r="J18" s="19">
         <v>1</v>
       </c>
-      <c r="K18" s="121" t="s">
+      <c r="K18" s="135" t="s">
         <v>538</v>
       </c>
-      <c r="L18" s="122"/>
-      <c r="M18" s="123"/>
+      <c r="L18" s="136"/>
+      <c r="M18" s="137"/>
     </row>
     <row r="19" spans="1:13">
       <c r="J19" s="19">
         <v>2</v>
       </c>
-      <c r="K19" s="121" t="s">
+      <c r="K19" s="135" t="s">
         <v>539</v>
       </c>
-      <c r="L19" s="122"/>
-      <c r="M19" s="123"/>
+      <c r="L19" s="136"/>
+      <c r="M19" s="137"/>
     </row>
     <row r="20" spans="1:13">
       <c r="J20" s="19">
         <v>3</v>
       </c>
-      <c r="K20" s="121" t="s">
+      <c r="K20" s="135" t="s">
         <v>540</v>
       </c>
-      <c r="L20" s="122"/>
-      <c r="M20" s="123"/>
+      <c r="L20" s="136"/>
+      <c r="M20" s="137"/>
     </row>
     <row r="21" spans="1:13">
       <c r="J21" s="19">
         <v>4</v>
       </c>
-      <c r="K21" s="121" t="s">
+      <c r="K21" s="135" t="s">
         <v>541</v>
       </c>
-      <c r="L21" s="122"/>
-      <c r="M21" s="123"/>
+      <c r="L21" s="136"/>
+      <c r="M21" s="137"/>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="43" t="s">
@@ -15380,6 +15586,312 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F01B713B-7546-4B5B-BF06-08BB58B1A0C8}">
+  <dimension ref="A1:J16"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.28515625" customWidth="1"/>
+    <col min="2" max="2" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" customWidth="1"/>
+    <col min="5" max="5" width="66.7109375" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" style="81" customWidth="1"/>
+    <col min="7" max="7" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="60.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="186" t="s">
+        <v>848</v>
+      </c>
+      <c r="B1" s="186" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C1" s="186" t="s">
+        <v>640</v>
+      </c>
+      <c r="D1" s="186" t="s">
+        <v>1177</v>
+      </c>
+      <c r="E1" s="186" t="s">
+        <v>1172</v>
+      </c>
+      <c r="F1" s="186" t="s">
+        <v>1173</v>
+      </c>
+      <c r="G1" s="186" t="s">
+        <v>1198</v>
+      </c>
+      <c r="H1" s="186" t="s">
+        <v>1181</v>
+      </c>
+      <c r="I1" s="186" t="s">
+        <v>1187</v>
+      </c>
+      <c r="J1" s="186" t="s">
+        <v>1193</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="187">
+        <v>44028</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>1176</v>
+      </c>
+      <c r="D2" s="118" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>1180</v>
+      </c>
+      <c r="F2" s="118" t="s">
+        <v>1179</v>
+      </c>
+      <c r="G2" s="118">
+        <v>0.36</v>
+      </c>
+      <c r="H2" s="118" t="s">
+        <v>1182</v>
+      </c>
+      <c r="I2" s="118" t="s">
+        <v>895</v>
+      </c>
+      <c r="J2" s="188" t="s">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="187">
+        <v>44028</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>1199</v>
+      </c>
+      <c r="D3" s="118" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>1185</v>
+      </c>
+      <c r="F3" s="118" t="s">
+        <v>1197</v>
+      </c>
+      <c r="G3" s="118">
+        <v>0.78</v>
+      </c>
+      <c r="H3" s="118" t="s">
+        <v>1186</v>
+      </c>
+      <c r="I3" s="118" t="s">
+        <v>895</v>
+      </c>
+      <c r="J3" s="189"/>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="187">
+        <v>44029</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>1191</v>
+      </c>
+      <c r="D4" s="118" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>1190</v>
+      </c>
+      <c r="F4" s="118" t="s">
+        <v>1192</v>
+      </c>
+      <c r="G4" s="118">
+        <v>5.83</v>
+      </c>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118" t="s">
+        <v>895</v>
+      </c>
+      <c r="J4" s="189"/>
+    </row>
+    <row r="5" spans="1:10" ht="45">
+      <c r="A5" s="187">
+        <v>44029</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D5" s="118" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>1196</v>
+      </c>
+      <c r="F5" s="118" t="s">
+        <v>1195</v>
+      </c>
+      <c r="G5" s="118">
+        <v>2.21</v>
+      </c>
+      <c r="H5" s="118"/>
+      <c r="I5" s="118" t="s">
+        <v>895</v>
+      </c>
+      <c r="J5" s="190"/>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="182"/>
+      <c r="B6" s="182"/>
+      <c r="C6" s="182"/>
+      <c r="D6" s="182"/>
+      <c r="E6" s="182"/>
+      <c r="F6" s="183" t="s">
+        <v>1201</v>
+      </c>
+      <c r="G6" s="182"/>
+      <c r="H6" s="182"/>
+      <c r="I6" s="182"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="182"/>
+      <c r="B7" s="182"/>
+      <c r="C7" s="182"/>
+      <c r="D7" s="182"/>
+      <c r="E7" s="182"/>
+      <c r="F7" s="183" t="s">
+        <v>1202</v>
+      </c>
+      <c r="G7" s="182"/>
+      <c r="H7" s="182"/>
+      <c r="I7" s="182"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="182"/>
+      <c r="B8" s="182"/>
+      <c r="C8" s="182"/>
+      <c r="D8" s="182"/>
+      <c r="E8" s="182"/>
+      <c r="F8" s="183" t="s">
+        <v>1203</v>
+      </c>
+      <c r="G8" s="182"/>
+      <c r="H8" s="182"/>
+      <c r="I8" s="182"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="182"/>
+      <c r="B9" s="182"/>
+      <c r="C9" s="182"/>
+      <c r="D9" s="182"/>
+      <c r="E9" s="182"/>
+      <c r="F9" s="183" t="s">
+        <v>1204</v>
+      </c>
+      <c r="G9" s="182"/>
+      <c r="H9" s="182"/>
+      <c r="I9" s="182"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="182"/>
+      <c r="B10" s="182"/>
+      <c r="C10" s="182"/>
+      <c r="D10" s="182"/>
+      <c r="E10" s="182"/>
+      <c r="F10" s="183" t="s">
+        <v>1205</v>
+      </c>
+      <c r="G10" s="182"/>
+      <c r="H10" s="182"/>
+      <c r="I10" s="182"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="182"/>
+      <c r="B11" s="182"/>
+      <c r="C11" s="182"/>
+      <c r="D11" s="182"/>
+      <c r="E11" s="182"/>
+      <c r="F11" s="183"/>
+      <c r="G11" s="182"/>
+      <c r="H11" s="182"/>
+      <c r="I11" s="182"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="182"/>
+      <c r="B12" s="182"/>
+      <c r="C12" s="182"/>
+      <c r="D12" s="182"/>
+      <c r="E12" s="182"/>
+      <c r="F12" s="183"/>
+      <c r="G12" s="182"/>
+      <c r="H12" s="182"/>
+      <c r="I12" s="182"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="182"/>
+      <c r="B13" s="182"/>
+      <c r="C13" s="182"/>
+      <c r="D13" s="182"/>
+      <c r="E13" s="182"/>
+      <c r="F13" s="183"/>
+      <c r="G13" s="182"/>
+      <c r="H13" s="182"/>
+      <c r="I13" s="182"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="182"/>
+      <c r="B14" s="182"/>
+      <c r="C14" s="182"/>
+      <c r="D14" s="182"/>
+      <c r="E14" s="182"/>
+      <c r="F14" s="183"/>
+      <c r="G14" s="182"/>
+      <c r="H14" s="182"/>
+      <c r="I14" s="182"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="182"/>
+      <c r="B15" s="182"/>
+      <c r="C15" s="182"/>
+      <c r="D15" s="182"/>
+      <c r="E15" s="182"/>
+      <c r="F15" s="183"/>
+      <c r="G15" s="182"/>
+      <c r="H15" s="182"/>
+      <c r="I15" s="182"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="182"/>
+      <c r="B16" s="182"/>
+      <c r="C16" s="182"/>
+      <c r="D16" s="182"/>
+      <c r="E16" s="182"/>
+      <c r="F16" s="183"/>
+      <c r="G16" s="182"/>
+      <c r="H16" s="182"/>
+      <c r="I16" s="182"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="J2:J5"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -15856,7 +16368,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -15874,7 +16386,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -15937,16 +16449,16 @@
       </c>
     </row>
     <row r="2" spans="1:16" ht="16.5" customHeight="1">
-      <c r="A2" s="152" t="s">
+      <c r="A2" s="168" t="s">
         <v>504</v>
       </c>
-      <c r="B2" s="155" t="s">
+      <c r="B2" s="174" t="s">
         <v>506</v>
       </c>
-      <c r="C2" s="152" t="s">
+      <c r="C2" s="168" t="s">
         <v>508</v>
       </c>
-      <c r="D2" s="152" t="s">
+      <c r="D2" s="168" t="s">
         <v>556</v>
       </c>
       <c r="E2" s="8"/>
@@ -15959,7 +16471,7 @@
       <c r="H2" s="10">
         <v>1</v>
       </c>
-      <c r="I2" s="168">
+      <c r="I2" s="121">
         <v>44043</v>
       </c>
       <c r="J2" s="10"/>
@@ -15969,10 +16481,10 @@
       </c>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" s="128"/>
-      <c r="B3" s="156"/>
-      <c r="C3" s="153"/>
-      <c r="D3" s="153"/>
+      <c r="A3" s="142"/>
+      <c r="B3" s="175"/>
+      <c r="C3" s="169"/>
+      <c r="D3" s="169"/>
       <c r="E3" s="11"/>
       <c r="F3" s="9" t="s">
         <v>310</v>
@@ -15983,7 +16495,7 @@
       <c r="H3" s="12">
         <v>2</v>
       </c>
-      <c r="I3" s="168"/>
+      <c r="I3" s="121"/>
       <c r="J3" s="10"/>
       <c r="K3" s="10"/>
       <c r="M3" s="19" t="s">
@@ -15991,10 +16503,10 @@
       </c>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="128"/>
-      <c r="B4" s="156"/>
-      <c r="C4" s="153"/>
-      <c r="D4" s="154"/>
+      <c r="A4" s="142"/>
+      <c r="B4" s="175"/>
+      <c r="C4" s="169"/>
+      <c r="D4" s="170"/>
       <c r="E4" s="11"/>
       <c r="F4" s="9" t="s">
         <v>311</v>
@@ -16005,14 +16517,14 @@
       <c r="H4" s="12">
         <v>2</v>
       </c>
-      <c r="I4" s="168"/>
+      <c r="I4" s="121"/>
       <c r="J4" s="10"/>
       <c r="K4" s="10"/>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" s="128"/>
-      <c r="B5" s="156"/>
-      <c r="C5" s="154"/>
+      <c r="A5" s="142"/>
+      <c r="B5" s="175"/>
+      <c r="C5" s="170"/>
       <c r="D5" s="46" t="s">
         <v>555</v>
       </c>
@@ -16026,7 +16538,7 @@
       <c r="H5" s="12" t="s">
         <v>965</v>
       </c>
-      <c r="I5" s="168">
+      <c r="I5" s="121">
         <v>44043</v>
       </c>
       <c r="J5" s="10" t="s">
@@ -16035,12 +16547,12 @@
       <c r="K5" s="10"/>
     </row>
     <row r="6" spans="1:16">
-      <c r="A6" s="128"/>
-      <c r="B6" s="156"/>
-      <c r="C6" s="152" t="s">
+      <c r="A6" s="142"/>
+      <c r="B6" s="175"/>
+      <c r="C6" s="168" t="s">
         <v>507</v>
       </c>
-      <c r="D6" s="152" t="s">
+      <c r="D6" s="168" t="s">
         <v>511</v>
       </c>
       <c r="E6" s="11"/>
@@ -16053,17 +16565,17 @@
       <c r="H6" s="12" t="s">
         <v>966</v>
       </c>
-      <c r="I6" s="168">
+      <c r="I6" s="121">
         <v>44043</v>
       </c>
       <c r="J6" s="10"/>
       <c r="K6" s="10"/>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="128"/>
-      <c r="B7" s="156"/>
-      <c r="C7" s="153"/>
-      <c r="D7" s="153"/>
+      <c r="A7" s="142"/>
+      <c r="B7" s="175"/>
+      <c r="C7" s="169"/>
+      <c r="D7" s="169"/>
       <c r="E7" s="11"/>
       <c r="F7" s="9" t="s">
         <v>313</v>
@@ -16074,17 +16586,17 @@
       <c r="H7" s="12">
         <v>1</v>
       </c>
-      <c r="I7" s="168">
+      <c r="I7" s="121">
         <v>44043</v>
       </c>
       <c r="J7" s="10"/>
       <c r="K7" s="10"/>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" s="128"/>
-      <c r="B8" s="156"/>
-      <c r="C8" s="153"/>
-      <c r="D8" s="153"/>
+      <c r="A8" s="142"/>
+      <c r="B8" s="175"/>
+      <c r="C8" s="169"/>
+      <c r="D8" s="169"/>
       <c r="E8" s="11"/>
       <c r="F8" s="9" t="s">
         <v>314</v>
@@ -16095,17 +16607,17 @@
       <c r="H8" s="12">
         <v>1</v>
       </c>
-      <c r="I8" s="168">
+      <c r="I8" s="121">
         <v>44043</v>
       </c>
       <c r="J8" s="10"/>
       <c r="K8" s="10"/>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9" s="128"/>
-      <c r="B9" s="156"/>
-      <c r="C9" s="153"/>
-      <c r="D9" s="153"/>
+      <c r="A9" s="142"/>
+      <c r="B9" s="175"/>
+      <c r="C9" s="169"/>
+      <c r="D9" s="169"/>
       <c r="E9" s="8"/>
       <c r="F9" s="9" t="s">
         <v>345</v>
@@ -16116,17 +16628,17 @@
       <c r="H9" s="10">
         <v>1</v>
       </c>
-      <c r="I9" s="168">
+      <c r="I9" s="121">
         <v>44043</v>
       </c>
       <c r="J9" s="10"/>
       <c r="K9" s="10"/>
     </row>
     <row r="10" spans="1:16">
-      <c r="A10" s="128"/>
-      <c r="B10" s="156"/>
-      <c r="C10" s="153"/>
-      <c r="D10" s="153"/>
+      <c r="A10" s="142"/>
+      <c r="B10" s="175"/>
+      <c r="C10" s="169"/>
+      <c r="D10" s="169"/>
       <c r="E10" s="8"/>
       <c r="F10" s="9" t="s">
         <v>346</v>
@@ -16137,17 +16649,17 @@
       <c r="H10" s="10">
         <v>1</v>
       </c>
-      <c r="I10" s="168">
+      <c r="I10" s="121">
         <v>44043</v>
       </c>
       <c r="J10" s="10"/>
       <c r="K10" s="10"/>
     </row>
     <row r="11" spans="1:16">
-      <c r="A11" s="128"/>
-      <c r="B11" s="156"/>
-      <c r="C11" s="153"/>
-      <c r="D11" s="153"/>
+      <c r="A11" s="142"/>
+      <c r="B11" s="175"/>
+      <c r="C11" s="169"/>
+      <c r="D11" s="169"/>
       <c r="E11" s="8"/>
       <c r="F11" s="9" t="s">
         <v>315</v>
@@ -16158,17 +16670,17 @@
       <c r="H11" s="10">
         <v>1</v>
       </c>
-      <c r="I11" s="168">
+      <c r="I11" s="121">
         <v>44043</v>
       </c>
       <c r="J11" s="10"/>
       <c r="K11" s="10"/>
     </row>
     <row r="12" spans="1:16" ht="16.5" customHeight="1">
-      <c r="A12" s="128"/>
-      <c r="B12" s="156"/>
-      <c r="C12" s="153"/>
-      <c r="D12" s="153"/>
+      <c r="A12" s="142"/>
+      <c r="B12" s="175"/>
+      <c r="C12" s="169"/>
+      <c r="D12" s="169"/>
       <c r="E12" s="8"/>
       <c r="F12" s="9" t="s">
         <v>347</v>
@@ -16179,17 +16691,17 @@
       <c r="H12" s="10">
         <v>1</v>
       </c>
-      <c r="I12" s="168">
+      <c r="I12" s="121">
         <v>44043</v>
       </c>
       <c r="J12" s="10"/>
       <c r="K12" s="10"/>
     </row>
     <row r="13" spans="1:16">
-      <c r="A13" s="128"/>
-      <c r="B13" s="156"/>
-      <c r="C13" s="153"/>
-      <c r="D13" s="153"/>
+      <c r="A13" s="142"/>
+      <c r="B13" s="175"/>
+      <c r="C13" s="169"/>
+      <c r="D13" s="169"/>
       <c r="E13" s="11"/>
       <c r="F13" s="9" t="s">
         <v>316</v>
@@ -16200,17 +16712,17 @@
       <c r="H13" s="12">
         <v>3</v>
       </c>
-      <c r="I13" s="168"/>
+      <c r="I13" s="121"/>
       <c r="J13" s="10" t="s">
         <v>563</v>
       </c>
       <c r="K13" s="10"/>
     </row>
     <row r="14" spans="1:16">
-      <c r="A14" s="128"/>
-      <c r="B14" s="156"/>
-      <c r="C14" s="153"/>
-      <c r="D14" s="154"/>
+      <c r="A14" s="142"/>
+      <c r="B14" s="175"/>
+      <c r="C14" s="169"/>
+      <c r="D14" s="170"/>
       <c r="E14" s="11"/>
       <c r="F14" s="9" t="s">
         <v>318</v>
@@ -16221,14 +16733,14 @@
       <c r="H14" s="12">
         <v>2</v>
       </c>
-      <c r="I14" s="168"/>
+      <c r="I14" s="121"/>
       <c r="J14" s="10"/>
       <c r="K14" s="10"/>
     </row>
     <row r="15" spans="1:16" ht="30">
-      <c r="A15" s="128"/>
-      <c r="B15" s="156"/>
-      <c r="C15" s="153"/>
+      <c r="A15" s="142"/>
+      <c r="B15" s="175"/>
+      <c r="C15" s="169"/>
       <c r="D15" s="22" t="s">
         <v>512</v>
       </c>
@@ -16242,12 +16754,12 @@
       <c r="H15" s="12">
         <v>1</v>
       </c>
-      <c r="I15" s="168">
+      <c r="I15" s="121">
         <v>44043</v>
       </c>
       <c r="J15" s="10"/>
       <c r="K15" s="10"/>
-      <c r="M15" s="171" t="s">
+      <c r="M15" s="124" t="s">
         <v>853</v>
       </c>
       <c r="N15" s="91"/>
@@ -16257,12 +16769,12 @@
       </c>
     </row>
     <row r="16" spans="1:16" ht="15" customHeight="1">
-      <c r="A16" s="128"/>
-      <c r="B16" s="156"/>
-      <c r="C16" s="152" t="s">
+      <c r="A16" s="142"/>
+      <c r="B16" s="175"/>
+      <c r="C16" s="168" t="s">
         <v>509</v>
       </c>
-      <c r="D16" s="152" t="s">
+      <c r="D16" s="168" t="s">
         <v>513</v>
       </c>
       <c r="E16" s="11"/>
@@ -16275,7 +16787,7 @@
       <c r="H16" s="12">
         <v>1</v>
       </c>
-      <c r="I16" s="168">
+      <c r="I16" s="121">
         <v>44043</v>
       </c>
       <c r="J16" s="10"/>
@@ -16294,10 +16806,10 @@
       </c>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="128"/>
-      <c r="B17" s="156"/>
-      <c r="C17" s="153"/>
-      <c r="D17" s="153"/>
+      <c r="A17" s="142"/>
+      <c r="B17" s="175"/>
+      <c r="C17" s="169"/>
+      <c r="D17" s="169"/>
       <c r="E17" s="19"/>
       <c r="F17" s="9" t="s">
         <v>364</v>
@@ -16308,7 +16820,7 @@
       <c r="H17" s="12">
         <v>1</v>
       </c>
-      <c r="I17" s="168">
+      <c r="I17" s="121">
         <v>44043</v>
       </c>
       <c r="J17" s="10"/>
@@ -16324,10 +16836,10 @@
       </c>
     </row>
     <row r="18" spans="1:16">
-      <c r="A18" s="128"/>
-      <c r="B18" s="156"/>
-      <c r="C18" s="153"/>
-      <c r="D18" s="153"/>
+      <c r="A18" s="142"/>
+      <c r="B18" s="175"/>
+      <c r="C18" s="169"/>
+      <c r="D18" s="169"/>
       <c r="E18" s="19"/>
       <c r="F18" s="48" t="s">
         <v>559</v>
@@ -16338,7 +16850,7 @@
       <c r="H18" s="10">
         <v>1</v>
       </c>
-      <c r="I18" s="168">
+      <c r="I18" s="121">
         <v>44043</v>
       </c>
       <c r="J18" s="10" t="s">
@@ -16356,10 +16868,10 @@
       </c>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="128"/>
-      <c r="B19" s="156"/>
-      <c r="C19" s="153"/>
-      <c r="D19" s="153"/>
+      <c r="A19" s="142"/>
+      <c r="B19" s="175"/>
+      <c r="C19" s="169"/>
+      <c r="D19" s="169"/>
       <c r="E19" s="8"/>
       <c r="F19" s="9" t="s">
         <v>332</v>
@@ -16370,7 +16882,7 @@
       <c r="H19" s="10">
         <v>1</v>
       </c>
-      <c r="I19" s="168">
+      <c r="I19" s="121">
         <v>44043</v>
       </c>
       <c r="J19" s="10"/>
@@ -16387,10 +16899,10 @@
       <c r="P19" s="91"/>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" s="128"/>
-      <c r="B20" s="156"/>
-      <c r="C20" s="153"/>
-      <c r="D20" s="153"/>
+      <c r="A20" s="142"/>
+      <c r="B20" s="175"/>
+      <c r="C20" s="169"/>
+      <c r="D20" s="169"/>
       <c r="E20" s="8"/>
       <c r="F20" s="9" t="s">
         <v>333</v>
@@ -16401,7 +16913,7 @@
       <c r="H20" s="10">
         <v>1</v>
       </c>
-      <c r="I20" s="168">
+      <c r="I20" s="121">
         <v>44043</v>
       </c>
       <c r="J20" s="10"/>
@@ -16418,10 +16930,10 @@
       <c r="P20" s="91"/>
     </row>
     <row r="21" spans="1:16" ht="16.5" customHeight="1">
-      <c r="A21" s="128"/>
-      <c r="B21" s="156"/>
-      <c r="C21" s="153"/>
-      <c r="D21" s="153"/>
+      <c r="A21" s="142"/>
+      <c r="B21" s="175"/>
+      <c r="C21" s="169"/>
+      <c r="D21" s="169"/>
       <c r="E21" s="14"/>
       <c r="F21" s="9" t="s">
         <v>334</v>
@@ -16432,7 +16944,7 @@
       <c r="H21" s="16">
         <v>3</v>
       </c>
-      <c r="I21" s="168"/>
+      <c r="I21" s="121"/>
       <c r="J21" s="10" t="s">
         <v>563</v>
       </c>
@@ -16451,10 +16963,10 @@
       </c>
     </row>
     <row r="22" spans="1:16">
-      <c r="A22" s="128"/>
-      <c r="B22" s="156"/>
-      <c r="C22" s="153"/>
-      <c r="D22" s="153"/>
+      <c r="A22" s="142"/>
+      <c r="B22" s="175"/>
+      <c r="C22" s="169"/>
+      <c r="D22" s="169"/>
       <c r="E22" s="14"/>
       <c r="F22" s="9" t="s">
         <v>335</v>
@@ -16465,7 +16977,7 @@
       <c r="H22" s="16">
         <v>1</v>
       </c>
-      <c r="I22" s="168">
+      <c r="I22" s="121">
         <v>44043</v>
       </c>
       <c r="J22" s="10"/>
@@ -16484,10 +16996,10 @@
       </c>
     </row>
     <row r="23" spans="1:16">
-      <c r="A23" s="128"/>
-      <c r="B23" s="156"/>
-      <c r="C23" s="153"/>
-      <c r="D23" s="153"/>
+      <c r="A23" s="142"/>
+      <c r="B23" s="175"/>
+      <c r="C23" s="169"/>
+      <c r="D23" s="169"/>
       <c r="E23" s="14"/>
       <c r="F23" s="9" t="s">
         <v>336</v>
@@ -16498,7 +17010,7 @@
       <c r="H23" s="16" t="s">
         <v>966</v>
       </c>
-      <c r="I23" s="168">
+      <c r="I23" s="121">
         <v>44043</v>
       </c>
       <c r="J23" s="10"/>
@@ -16515,10 +17027,10 @@
       <c r="P23" s="91"/>
     </row>
     <row r="24" spans="1:16">
-      <c r="A24" s="128"/>
-      <c r="B24" s="156"/>
-      <c r="C24" s="153"/>
-      <c r="D24" s="153"/>
+      <c r="A24" s="142"/>
+      <c r="B24" s="175"/>
+      <c r="C24" s="169"/>
+      <c r="D24" s="169"/>
       <c r="E24" s="8"/>
       <c r="F24" s="9" t="s">
         <v>337</v>
@@ -16529,12 +17041,12 @@
       <c r="H24" s="10" t="s">
         <v>966</v>
       </c>
-      <c r="I24" s="168">
+      <c r="I24" s="121">
         <v>44043</v>
       </c>
       <c r="J24" s="10"/>
       <c r="K24" s="10"/>
-      <c r="M24" s="172" t="s">
+      <c r="M24" s="125" t="s">
         <v>970</v>
       </c>
       <c r="N24" s="98" t="s">
@@ -16546,10 +17058,10 @@
       <c r="P24" s="91"/>
     </row>
     <row r="25" spans="1:16">
-      <c r="A25" s="128"/>
-      <c r="B25" s="156"/>
-      <c r="C25" s="153"/>
-      <c r="D25" s="153"/>
+      <c r="A25" s="142"/>
+      <c r="B25" s="175"/>
+      <c r="C25" s="169"/>
+      <c r="D25" s="169"/>
       <c r="E25" s="8"/>
       <c r="F25" s="9" t="s">
         <v>373</v>
@@ -16560,7 +17072,7 @@
       <c r="H25" s="10">
         <v>3</v>
       </c>
-      <c r="I25" s="168"/>
+      <c r="I25" s="121"/>
       <c r="J25" s="10" t="s">
         <v>563</v>
       </c>
@@ -16577,10 +17089,10 @@
       <c r="P25" s="91"/>
     </row>
     <row r="26" spans="1:16">
-      <c r="A26" s="128"/>
-      <c r="B26" s="156"/>
-      <c r="C26" s="153"/>
-      <c r="D26" s="153"/>
+      <c r="A26" s="142"/>
+      <c r="B26" s="175"/>
+      <c r="C26" s="169"/>
+      <c r="D26" s="169"/>
       <c r="E26" s="8"/>
       <c r="F26" s="9" t="s">
         <v>338</v>
@@ -16591,7 +17103,7 @@
       <c r="H26" s="10">
         <v>2</v>
       </c>
-      <c r="I26" s="168"/>
+      <c r="I26" s="121"/>
       <c r="J26" s="10"/>
       <c r="K26" s="10"/>
       <c r="M26" s="99" t="s">
@@ -16606,10 +17118,10 @@
       <c r="P26" s="91"/>
     </row>
     <row r="27" spans="1:16">
-      <c r="A27" s="128"/>
-      <c r="B27" s="156"/>
-      <c r="C27" s="153"/>
-      <c r="D27" s="153"/>
+      <c r="A27" s="142"/>
+      <c r="B27" s="175"/>
+      <c r="C27" s="169"/>
+      <c r="D27" s="169"/>
       <c r="E27" s="8"/>
       <c r="F27" s="9" t="s">
         <v>339</v>
@@ -16617,10 +17129,10 @@
       <c r="G27" s="13" t="s">
         <v>372</v>
       </c>
-      <c r="H27" s="169" t="s">
+      <c r="H27" s="122" t="s">
         <v>967</v>
       </c>
-      <c r="I27" s="168"/>
+      <c r="I27" s="121"/>
       <c r="J27" s="10"/>
       <c r="K27" s="10"/>
       <c r="M27" s="99" t="s">
@@ -16635,12 +17147,12 @@
       <c r="P27" s="91"/>
     </row>
     <row r="28" spans="1:16">
-      <c r="A28" s="128"/>
-      <c r="B28" s="156"/>
-      <c r="C28" s="153"/>
-      <c r="D28" s="153"/>
+      <c r="A28" s="142"/>
+      <c r="B28" s="175"/>
+      <c r="C28" s="169"/>
+      <c r="D28" s="169"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="172" t="s">
+      <c r="F28" s="125" t="s">
         <v>970</v>
       </c>
       <c r="G28" s="13" t="s">
@@ -16649,7 +17161,7 @@
       <c r="H28" s="10">
         <v>1</v>
       </c>
-      <c r="I28" s="168">
+      <c r="I28" s="121">
         <v>44043</v>
       </c>
       <c r="J28" s="10"/>
@@ -16666,10 +17178,10 @@
       <c r="P28" s="91"/>
     </row>
     <row r="29" spans="1:16">
-      <c r="A29" s="128"/>
-      <c r="B29" s="156"/>
-      <c r="C29" s="153"/>
-      <c r="D29" s="153"/>
+      <c r="A29" s="142"/>
+      <c r="B29" s="175"/>
+      <c r="C29" s="169"/>
+      <c r="D29" s="169"/>
       <c r="E29" s="8"/>
       <c r="F29" s="9" t="s">
         <v>960</v>
@@ -16680,17 +17192,17 @@
       <c r="H29" s="16">
         <v>2</v>
       </c>
-      <c r="I29" s="168"/>
+      <c r="I29" s="121"/>
       <c r="J29" s="10"/>
       <c r="K29" s="10" t="s">
         <v>959</v>
       </c>
     </row>
     <row r="30" spans="1:16">
-      <c r="A30" s="128"/>
-      <c r="B30" s="156"/>
-      <c r="C30" s="153"/>
-      <c r="D30" s="154"/>
+      <c r="A30" s="142"/>
+      <c r="B30" s="175"/>
+      <c r="C30" s="169"/>
+      <c r="D30" s="170"/>
       <c r="E30" s="8"/>
       <c r="F30" s="49" t="s">
         <v>323</v>
@@ -16701,17 +17213,17 @@
       <c r="H30" s="114">
         <v>3</v>
       </c>
-      <c r="I30" s="168"/>
+      <c r="I30" s="121"/>
       <c r="J30" s="10"/>
-      <c r="K30" s="167" t="s">
+      <c r="K30" s="171" t="s">
         <v>964</v>
       </c>
     </row>
     <row r="31" spans="1:16">
-      <c r="A31" s="128"/>
-      <c r="B31" s="156"/>
-      <c r="C31" s="153"/>
-      <c r="D31" s="152" t="s">
+      <c r="A31" s="142"/>
+      <c r="B31" s="175"/>
+      <c r="C31" s="169"/>
+      <c r="D31" s="168" t="s">
         <v>518</v>
       </c>
       <c r="E31" s="8"/>
@@ -16724,20 +17236,20 @@
       <c r="H31" s="16">
         <v>1</v>
       </c>
-      <c r="I31" s="168">
+      <c r="I31" s="121">
         <v>44043</v>
       </c>
       <c r="J31" s="10"/>
-      <c r="K31" s="165"/>
+      <c r="K31" s="172"/>
       <c r="M31" s="102" t="s">
         <v>860</v>
       </c>
     </row>
     <row r="32" spans="1:16" ht="16.5" customHeight="1">
-      <c r="A32" s="128"/>
-      <c r="B32" s="156"/>
-      <c r="C32" s="153"/>
-      <c r="D32" s="153"/>
+      <c r="A32" s="142"/>
+      <c r="B32" s="175"/>
+      <c r="C32" s="169"/>
+      <c r="D32" s="169"/>
       <c r="E32" s="8"/>
       <c r="F32" s="9" t="s">
         <v>325</v>
@@ -16748,17 +17260,17 @@
       <c r="H32" s="16">
         <v>1</v>
       </c>
-      <c r="I32" s="168">
+      <c r="I32" s="121">
         <v>44043</v>
       </c>
       <c r="J32" s="10"/>
-      <c r="K32" s="165"/>
+      <c r="K32" s="172"/>
     </row>
     <row r="33" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A33" s="128"/>
-      <c r="B33" s="156"/>
-      <c r="C33" s="153"/>
-      <c r="D33" s="153"/>
+      <c r="A33" s="142"/>
+      <c r="B33" s="175"/>
+      <c r="C33" s="169"/>
+      <c r="D33" s="169"/>
       <c r="E33" s="8"/>
       <c r="F33" s="9" t="s">
         <v>962</v>
@@ -16769,19 +17281,19 @@
       <c r="H33" s="16">
         <v>2</v>
       </c>
-      <c r="I33" s="168">
+      <c r="I33" s="121">
         <v>44043</v>
       </c>
       <c r="J33" s="10" t="s">
         <v>959</v>
       </c>
-      <c r="K33" s="166"/>
+      <c r="K33" s="173"/>
     </row>
     <row r="34" spans="1:11">
-      <c r="A34" s="128"/>
-      <c r="B34" s="156"/>
-      <c r="C34" s="154"/>
-      <c r="D34" s="154"/>
+      <c r="A34" s="142"/>
+      <c r="B34" s="175"/>
+      <c r="C34" s="170"/>
+      <c r="D34" s="170"/>
       <c r="E34" s="8"/>
       <c r="F34" s="49" t="s">
         <v>322</v>
@@ -16792,17 +17304,17 @@
       <c r="H34" s="50">
         <v>3</v>
       </c>
-      <c r="I34" s="168"/>
+      <c r="I34" s="121"/>
       <c r="J34" s="10"/>
       <c r="K34" s="10"/>
     </row>
     <row r="35" spans="1:11">
-      <c r="A35" s="128"/>
-      <c r="B35" s="156"/>
-      <c r="C35" s="152" t="s">
+      <c r="A35" s="142"/>
+      <c r="B35" s="175"/>
+      <c r="C35" s="168" t="s">
         <v>340</v>
       </c>
-      <c r="D35" s="152" t="s">
+      <c r="D35" s="168" t="s">
         <v>517</v>
       </c>
       <c r="E35" s="8"/>
@@ -16815,17 +17327,17 @@
       <c r="H35" s="16">
         <v>1</v>
       </c>
-      <c r="I35" s="168">
+      <c r="I35" s="121">
         <v>44043</v>
       </c>
       <c r="J35" s="10"/>
       <c r="K35" s="10"/>
     </row>
     <row r="36" spans="1:11">
-      <c r="A36" s="128"/>
-      <c r="B36" s="157"/>
-      <c r="C36" s="154"/>
-      <c r="D36" s="154"/>
+      <c r="A36" s="142"/>
+      <c r="B36" s="176"/>
+      <c r="C36" s="170"/>
+      <c r="D36" s="170"/>
       <c r="E36" s="8"/>
       <c r="F36" s="9" t="s">
         <v>331</v>
@@ -16833,15 +17345,15 @@
       <c r="G36" s="9" t="s">
         <v>376</v>
       </c>
-      <c r="H36" s="170" t="s">
+      <c r="H36" s="123" t="s">
         <v>968</v>
       </c>
-      <c r="I36" s="168"/>
+      <c r="I36" s="121"/>
       <c r="J36" s="10"/>
       <c r="K36" s="10"/>
     </row>
     <row r="37" spans="1:11">
-      <c r="A37" s="128"/>
+      <c r="A37" s="142"/>
       <c r="B37" s="29" t="s">
         <v>328</v>
       </c>
@@ -16861,19 +17373,19 @@
       <c r="H37" s="16" t="s">
         <v>330</v>
       </c>
-      <c r="I37" s="168"/>
+      <c r="I37" s="121"/>
       <c r="J37" s="10"/>
       <c r="K37" s="10"/>
     </row>
     <row r="38" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A38" s="128"/>
-      <c r="B38" s="155" t="s">
+      <c r="A38" s="142"/>
+      <c r="B38" s="174" t="s">
         <v>505</v>
       </c>
-      <c r="C38" s="152" t="s">
+      <c r="C38" s="168" t="s">
         <v>510</v>
       </c>
-      <c r="D38" s="152" t="s">
+      <c r="D38" s="168" t="s">
         <v>516</v>
       </c>
       <c r="E38" s="8" t="s">
@@ -16888,15 +17400,15 @@
       <c r="H38" s="10">
         <v>2</v>
       </c>
-      <c r="I38" s="168"/>
+      <c r="I38" s="121"/>
       <c r="J38" s="10"/>
       <c r="K38" s="10"/>
     </row>
     <row r="39" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A39" s="128"/>
-      <c r="B39" s="156"/>
-      <c r="C39" s="128"/>
-      <c r="D39" s="128"/>
+      <c r="A39" s="142"/>
+      <c r="B39" s="175"/>
+      <c r="C39" s="142"/>
+      <c r="D39" s="142"/>
       <c r="E39" s="17"/>
       <c r="F39" s="9" t="s">
         <v>304</v>
@@ -16907,17 +17419,17 @@
       <c r="H39" s="16">
         <v>1</v>
       </c>
-      <c r="I39" s="168">
+      <c r="I39" s="121">
         <v>44043</v>
       </c>
       <c r="J39" s="10"/>
       <c r="K39" s="10"/>
     </row>
     <row r="40" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A40" s="128"/>
-      <c r="B40" s="156"/>
-      <c r="C40" s="128"/>
-      <c r="D40" s="128"/>
+      <c r="A40" s="142"/>
+      <c r="B40" s="175"/>
+      <c r="C40" s="142"/>
+      <c r="D40" s="142"/>
       <c r="E40" s="17"/>
       <c r="F40" s="9" t="s">
         <v>305</v>
@@ -16928,17 +17440,17 @@
       <c r="H40" s="16">
         <v>1</v>
       </c>
-      <c r="I40" s="168">
+      <c r="I40" s="121">
         <v>44043</v>
       </c>
       <c r="J40" s="10"/>
       <c r="K40" s="10"/>
     </row>
     <row r="41" spans="1:11">
-      <c r="A41" s="128"/>
-      <c r="B41" s="156"/>
-      <c r="C41" s="128"/>
-      <c r="D41" s="129"/>
+      <c r="A41" s="142"/>
+      <c r="B41" s="175"/>
+      <c r="C41" s="142"/>
+      <c r="D41" s="143"/>
       <c r="E41" s="17"/>
       <c r="F41" s="9" t="s">
         <v>305</v>
@@ -16949,15 +17461,15 @@
       <c r="H41" s="16">
         <v>2</v>
       </c>
-      <c r="I41" s="168"/>
+      <c r="I41" s="121"/>
       <c r="J41" s="10"/>
       <c r="K41" s="10"/>
     </row>
     <row r="42" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A42" s="128"/>
-      <c r="B42" s="156"/>
-      <c r="C42" s="128"/>
-      <c r="D42" s="152" t="s">
+      <c r="A42" s="142"/>
+      <c r="B42" s="175"/>
+      <c r="C42" s="142"/>
+      <c r="D42" s="168" t="s">
         <v>515</v>
       </c>
       <c r="E42" s="8"/>
@@ -16967,18 +17479,22 @@
       <c r="G42" s="9" t="s">
         <v>298</v>
       </c>
-      <c r="H42" s="10">
-        <v>2</v>
-      </c>
-      <c r="I42" s="168"/>
+      <c r="H42" s="10" t="s">
+        <v>966</v>
+      </c>
+      <c r="I42" s="121">
+        <v>44043</v>
+      </c>
       <c r="J42" s="10"/>
-      <c r="K42" s="10"/>
+      <c r="K42" s="171" t="s">
+        <v>1169</v>
+      </c>
     </row>
     <row r="43" spans="1:11">
-      <c r="A43" s="128"/>
-      <c r="B43" s="156"/>
-      <c r="C43" s="128"/>
-      <c r="D43" s="129"/>
+      <c r="A43" s="142"/>
+      <c r="B43" s="175"/>
+      <c r="C43" s="142"/>
+      <c r="D43" s="143"/>
       <c r="E43" s="8"/>
       <c r="F43" s="9" t="s">
         <v>289</v>
@@ -16986,18 +17502,20 @@
       <c r="G43" s="9" t="s">
         <v>299</v>
       </c>
-      <c r="H43" s="10">
-        <v>2</v>
-      </c>
-      <c r="I43" s="168"/>
+      <c r="H43" s="10" t="s">
+        <v>966</v>
+      </c>
+      <c r="I43" s="121">
+        <v>44043</v>
+      </c>
       <c r="J43" s="10"/>
-      <c r="K43" s="10"/>
+      <c r="K43" s="181"/>
     </row>
     <row r="44" spans="1:11">
-      <c r="A44" s="128"/>
-      <c r="B44" s="156"/>
-      <c r="C44" s="128"/>
-      <c r="D44" s="152" t="s">
+      <c r="A44" s="142"/>
+      <c r="B44" s="175"/>
+      <c r="C44" s="142"/>
+      <c r="D44" s="168" t="s">
         <v>514</v>
       </c>
       <c r="E44" s="8"/>
@@ -17010,15 +17528,15 @@
       <c r="H44" s="10">
         <v>2</v>
       </c>
-      <c r="I44" s="168"/>
+      <c r="I44" s="121"/>
       <c r="J44" s="10"/>
       <c r="K44" s="10"/>
     </row>
     <row r="45" spans="1:11">
-      <c r="A45" s="129"/>
-      <c r="B45" s="157"/>
-      <c r="C45" s="129"/>
-      <c r="D45" s="129"/>
+      <c r="A45" s="143"/>
+      <c r="B45" s="176"/>
+      <c r="C45" s="143"/>
+      <c r="D45" s="143"/>
       <c r="E45" s="8"/>
       <c r="F45" s="9" t="s">
         <v>301</v>
@@ -17029,7 +17547,7 @@
       <c r="H45" s="10">
         <v>2</v>
       </c>
-      <c r="I45" s="168"/>
+      <c r="I45" s="121"/>
       <c r="J45" s="10"/>
       <c r="K45" s="10"/>
     </row>
@@ -17037,7 +17555,9 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="M16:O28">
     <sortCondition ref="O16:O28"/>
   </sortState>
-  <mergeCells count="17">
+  <mergeCells count="18">
+    <mergeCell ref="D6:D14"/>
+    <mergeCell ref="K42:K43"/>
     <mergeCell ref="D16:D30"/>
     <mergeCell ref="K30:K33"/>
     <mergeCell ref="C2:C5"/>
@@ -17054,7 +17574,6 @@
     <mergeCell ref="D31:D34"/>
     <mergeCell ref="D35:D36"/>
     <mergeCell ref="D2:D4"/>
-    <mergeCell ref="D6:D14"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -17062,7 +17581,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -17073,7 +17592,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:J27"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -17092,11 +17611,11 @@
       <c r="B1" s="25" t="s">
         <v>327</v>
       </c>
-      <c r="E1" s="160" t="s">
+      <c r="E1" s="179" t="s">
         <v>724</v>
       </c>
-      <c r="F1" s="160"/>
-      <c r="G1" s="160"/>
+      <c r="F1" s="179"/>
+      <c r="G1" s="179"/>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="19" t="s">
@@ -17105,11 +17624,11 @@
       <c r="B2" s="19" t="s">
         <v>257</v>
       </c>
-      <c r="E2" s="161" t="s">
+      <c r="E2" s="180" t="s">
         <v>725</v>
       </c>
-      <c r="F2" s="161"/>
-      <c r="G2" s="161"/>
+      <c r="F2" s="180"/>
+      <c r="G2" s="180"/>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="19" t="s">
@@ -17126,10 +17645,10 @@
       <c r="B4" s="19" t="s">
         <v>259</v>
       </c>
-      <c r="E4" s="160" t="s">
+      <c r="E4" s="179" t="s">
         <v>722</v>
       </c>
-      <c r="F4" s="160"/>
+      <c r="F4" s="179"/>
       <c r="G4" s="25" t="s">
         <v>723</v>
       </c>
@@ -17141,16 +17660,16 @@
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="E5" s="159" t="s">
+      <c r="E5" s="178" t="s">
         <v>720</v>
       </c>
-      <c r="F5" s="159" t="s">
+      <c r="F5" s="178" t="s">
         <v>721</v>
       </c>
       <c r="G5" s="68" t="s">
         <v>747</v>
       </c>
-      <c r="H5" s="158" t="s">
+      <c r="H5" s="177" t="s">
         <v>748</v>
       </c>
       <c r="J5" t="s">
@@ -17161,12 +17680,12 @@
       <c r="A6" t="s">
         <v>261</v>
       </c>
-      <c r="E6" s="159"/>
-      <c r="F6" s="159"/>
+      <c r="E6" s="178"/>
+      <c r="F6" s="178"/>
       <c r="G6" s="68" t="s">
         <v>746</v>
       </c>
-      <c r="H6" s="159"/>
+      <c r="H6" s="178"/>
       <c r="J6" t="s">
         <v>729</v>
       </c>
@@ -17360,7 +17879,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -17476,7 +17995,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37379847-1933-4532-BA71-36026569AE7D}">
   <dimension ref="A1:C113"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -17487,13 +18006,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="173" t="s">
+      <c r="A1" s="126" t="s">
         <v>976</v>
       </c>
-      <c r="B1" s="174" t="s">
+      <c r="B1" s="127" t="s">
         <v>977</v>
       </c>
-      <c r="C1" s="174" t="s">
+      <c r="C1" s="127" t="s">
         <v>978</v>
       </c>
     </row>
@@ -17949,120 +18468,120 @@
       </c>
     </row>
     <row r="43" spans="1:3">
-      <c r="A43" s="175" t="s">
+      <c r="A43" s="128" t="s">
         <v>385</v>
       </c>
-      <c r="B43" s="175" t="s">
+      <c r="B43" s="128" t="s">
         <v>1056</v>
       </c>
-      <c r="C43" s="175" t="s">
+      <c r="C43" s="128" t="s">
         <v>1057</v>
       </c>
     </row>
     <row r="44" spans="1:3">
-      <c r="A44" s="175" t="s">
+      <c r="A44" s="128" t="s">
         <v>385</v>
       </c>
-      <c r="B44" s="175" t="s">
+      <c r="B44" s="128" t="s">
         <v>1058</v>
       </c>
-      <c r="C44" s="175" t="s">
+      <c r="C44" s="128" t="s">
         <v>980</v>
       </c>
     </row>
     <row r="45" spans="1:3">
-      <c r="A45" s="175" t="s">
+      <c r="A45" s="128" t="s">
         <v>385</v>
       </c>
-      <c r="B45" s="175" t="s">
+      <c r="B45" s="128" t="s">
         <v>1059</v>
       </c>
-      <c r="C45" s="175" t="s">
+      <c r="C45" s="128" t="s">
         <v>1060</v>
       </c>
     </row>
     <row r="46" spans="1:3">
-      <c r="A46" s="175" t="s">
+      <c r="A46" s="128" t="s">
         <v>385</v>
       </c>
-      <c r="B46" s="175" t="s">
+      <c r="B46" s="128" t="s">
         <v>619</v>
       </c>
-      <c r="C46" s="175" t="s">
+      <c r="C46" s="128" t="s">
         <v>1061</v>
       </c>
     </row>
     <row r="47" spans="1:3">
-      <c r="A47" s="175" t="s">
+      <c r="A47" s="128" t="s">
         <v>385</v>
       </c>
-      <c r="B47" s="175" t="s">
+      <c r="B47" s="128" t="s">
         <v>617</v>
       </c>
-      <c r="C47" s="175" t="s">
+      <c r="C47" s="128" t="s">
         <v>1062</v>
       </c>
     </row>
     <row r="48" spans="1:3">
-      <c r="A48" s="175" t="s">
+      <c r="A48" s="128" t="s">
         <v>385</v>
       </c>
-      <c r="B48" s="175" t="s">
+      <c r="B48" s="128" t="s">
         <v>1063</v>
       </c>
-      <c r="C48" s="175" t="s">
+      <c r="C48" s="128" t="s">
         <v>1064</v>
       </c>
     </row>
     <row r="49" spans="1:3">
-      <c r="A49" s="175" t="s">
+      <c r="A49" s="128" t="s">
         <v>385</v>
       </c>
-      <c r="B49" s="175" t="s">
+      <c r="B49" s="128" t="s">
         <v>1065</v>
       </c>
-      <c r="C49" s="175" t="s">
+      <c r="C49" s="128" t="s">
         <v>1066</v>
       </c>
     </row>
     <row r="50" spans="1:3">
-      <c r="A50" s="175" t="s">
+      <c r="A50" s="128" t="s">
         <v>385</v>
       </c>
-      <c r="B50" s="175" t="s">
+      <c r="B50" s="128" t="s">
         <v>1067</v>
       </c>
-      <c r="C50" s="175" t="s">
+      <c r="C50" s="128" t="s">
         <v>1068</v>
       </c>
     </row>
     <row r="51" spans="1:3">
-      <c r="A51" s="175" t="s">
+      <c r="A51" s="128" t="s">
         <v>385</v>
       </c>
-      <c r="B51" s="175" t="s">
+      <c r="B51" s="128" t="s">
         <v>1069</v>
       </c>
-      <c r="C51" s="175" t="s">
+      <c r="C51" s="128" t="s">
         <v>1070</v>
       </c>
     </row>
     <row r="52" spans="1:3">
-      <c r="A52" s="175" t="s">
+      <c r="A52" s="128" t="s">
         <v>385</v>
       </c>
-      <c r="B52" s="175" t="s">
+      <c r="B52" s="128" t="s">
         <v>1071</v>
       </c>
-      <c r="C52" s="175" t="s">
+      <c r="C52" s="128" t="s">
         <v>1072</v>
       </c>
     </row>
     <row r="53" spans="1:3">
-      <c r="A53" s="175" t="s">
+      <c r="A53" s="128" t="s">
         <v>385</v>
       </c>
-      <c r="B53" s="175" t="s">
+      <c r="B53" s="128" t="s">
         <v>1073</v>
       </c>
       <c r="C53" s="19" t="s">
@@ -18070,10 +18589,10 @@
       </c>
     </row>
     <row r="54" spans="1:3">
-      <c r="A54" s="175" t="s">
+      <c r="A54" s="128" t="s">
         <v>385</v>
       </c>
-      <c r="B54" s="175" t="s">
+      <c r="B54" s="128" t="s">
         <v>1075</v>
       </c>
       <c r="C54" s="19" t="s">
@@ -18081,7 +18600,7 @@
       </c>
     </row>
     <row r="55" spans="1:3">
-      <c r="A55" s="175" t="s">
+      <c r="A55" s="128" t="s">
         <v>385</v>
       </c>
       <c r="B55" s="19" t="s">
@@ -18092,7 +18611,7 @@
       </c>
     </row>
     <row r="56" spans="1:3">
-      <c r="A56" s="175" t="s">
+      <c r="A56" s="128" t="s">
         <v>385</v>
       </c>
       <c r="B56" s="19" t="s">
@@ -18103,7 +18622,7 @@
       </c>
     </row>
     <row r="57" spans="1:3">
-      <c r="A57" s="175" t="s">
+      <c r="A57" s="128" t="s">
         <v>385</v>
       </c>
       <c r="B57" s="19" t="s">
@@ -18114,7 +18633,7 @@
       </c>
     </row>
     <row r="58" spans="1:3" ht="30">
-      <c r="A58" s="175" t="s">
+      <c r="A58" s="128" t="s">
         <v>385</v>
       </c>
       <c r="B58" s="19" t="s">
@@ -18125,7 +18644,7 @@
       </c>
     </row>
     <row r="59" spans="1:3">
-      <c r="A59" s="175" t="s">
+      <c r="A59" s="128" t="s">
         <v>385</v>
       </c>
       <c r="B59" s="19" t="s">
@@ -18136,7 +18655,7 @@
       </c>
     </row>
     <row r="60" spans="1:3">
-      <c r="A60" s="175" t="s">
+      <c r="A60" s="128" t="s">
         <v>385</v>
       </c>
       <c r="B60" s="19" t="s">
@@ -18150,10 +18669,10 @@
       <c r="A61" s="19" t="s">
         <v>1088</v>
       </c>
-      <c r="B61" s="176" t="s">
+      <c r="B61" s="129" t="s">
         <v>1089</v>
       </c>
-      <c r="C61" s="176" t="s">
+      <c r="C61" s="129" t="s">
         <v>1090</v>
       </c>
     </row>
@@ -18161,10 +18680,10 @@
       <c r="A62" s="19" t="s">
         <v>1088</v>
       </c>
-      <c r="B62" s="177" t="s">
+      <c r="B62" s="130" t="s">
         <v>1091</v>
       </c>
-      <c r="C62" s="177" t="s">
+      <c r="C62" s="130" t="s">
         <v>1092</v>
       </c>
     </row>
@@ -18172,10 +18691,10 @@
       <c r="A63" s="19" t="s">
         <v>1088</v>
       </c>
-      <c r="B63" s="177" t="s">
+      <c r="B63" s="130" t="s">
         <v>1093</v>
       </c>
-      <c r="C63" s="177" t="s">
+      <c r="C63" s="130" t="s">
         <v>1094</v>
       </c>
     </row>
@@ -18183,10 +18702,10 @@
       <c r="A64" s="19" t="s">
         <v>1088</v>
       </c>
-      <c r="B64" s="177" t="s">
+      <c r="B64" s="130" t="s">
         <v>1095</v>
       </c>
-      <c r="C64" s="177" t="s">
+      <c r="C64" s="130" t="s">
         <v>1096</v>
       </c>
     </row>
@@ -18194,10 +18713,10 @@
       <c r="A65" s="19" t="s">
         <v>1088</v>
       </c>
-      <c r="B65" s="177" t="s">
+      <c r="B65" s="130" t="s">
         <v>1097</v>
       </c>
-      <c r="C65" s="177" t="s">
+      <c r="C65" s="130" t="s">
         <v>1098</v>
       </c>
     </row>
@@ -18205,10 +18724,10 @@
       <c r="A66" s="19" t="s">
         <v>1088</v>
       </c>
-      <c r="B66" s="177" t="s">
+      <c r="B66" s="130" t="s">
         <v>1099</v>
       </c>
-      <c r="C66" s="177" t="s">
+      <c r="C66" s="130" t="s">
         <v>1100</v>
       </c>
     </row>
@@ -18216,10 +18735,10 @@
       <c r="A67" s="19" t="s">
         <v>1088</v>
       </c>
-      <c r="B67" s="177" t="s">
+      <c r="B67" s="130" t="s">
         <v>1101</v>
       </c>
-      <c r="C67" s="177" t="s">
+      <c r="C67" s="130" t="s">
         <v>1102</v>
       </c>
     </row>
@@ -18227,10 +18746,10 @@
       <c r="A68" s="19" t="s">
         <v>1088</v>
       </c>
-      <c r="B68" s="177" t="s">
+      <c r="B68" s="130" t="s">
         <v>1103</v>
       </c>
-      <c r="C68" s="177" t="s">
+      <c r="C68" s="130" t="s">
         <v>1104</v>
       </c>
     </row>
@@ -18238,10 +18757,10 @@
       <c r="A69" s="19" t="s">
         <v>1088</v>
       </c>
-      <c r="B69" s="177" t="s">
+      <c r="B69" s="130" t="s">
         <v>1105</v>
       </c>
-      <c r="C69" s="177" t="s">
+      <c r="C69" s="130" t="s">
         <v>1106</v>
       </c>
     </row>
@@ -18249,10 +18768,10 @@
       <c r="A70" s="19" t="s">
         <v>1088</v>
       </c>
-      <c r="B70" s="177" t="s">
+      <c r="B70" s="130" t="s">
         <v>1107</v>
       </c>
-      <c r="C70" s="177" t="s">
+      <c r="C70" s="130" t="s">
         <v>1108</v>
       </c>
     </row>
@@ -18260,10 +18779,10 @@
       <c r="A71" s="19" t="s">
         <v>1088</v>
       </c>
-      <c r="B71" s="177" t="s">
+      <c r="B71" s="130" t="s">
         <v>1109</v>
       </c>
-      <c r="C71" s="177" t="s">
+      <c r="C71" s="130" t="s">
         <v>1110</v>
       </c>
     </row>
@@ -18271,10 +18790,10 @@
       <c r="A72" s="19" t="s">
         <v>1088</v>
       </c>
-      <c r="B72" s="177" t="s">
+      <c r="B72" s="130" t="s">
         <v>1111</v>
       </c>
-      <c r="C72" s="177" t="s">
+      <c r="C72" s="130" t="s">
         <v>1112</v>
       </c>
     </row>
@@ -18282,10 +18801,10 @@
       <c r="A73" s="19" t="s">
         <v>1088</v>
       </c>
-      <c r="B73" s="177" t="s">
+      <c r="B73" s="130" t="s">
         <v>1113</v>
       </c>
-      <c r="C73" s="177" t="s">
+      <c r="C73" s="130" t="s">
         <v>1114</v>
       </c>
     </row>
@@ -18293,10 +18812,10 @@
       <c r="A74" s="19" t="s">
         <v>1088</v>
       </c>
-      <c r="B74" s="177" t="s">
+      <c r="B74" s="130" t="s">
         <v>1115</v>
       </c>
-      <c r="C74" s="177" t="s">
+      <c r="C74" s="130" t="s">
         <v>1116</v>
       </c>
     </row>
@@ -18304,10 +18823,10 @@
       <c r="A75" s="19" t="s">
         <v>1088</v>
       </c>
-      <c r="B75" s="177" t="s">
+      <c r="B75" s="130" t="s">
         <v>1117</v>
       </c>
-      <c r="C75" s="177" t="s">
+      <c r="C75" s="130" t="s">
         <v>1118</v>
       </c>
     </row>
@@ -18315,10 +18834,10 @@
       <c r="A76" s="19" t="s">
         <v>1088</v>
       </c>
-      <c r="B76" s="177" t="s">
+      <c r="B76" s="130" t="s">
         <v>1119</v>
       </c>
-      <c r="C76" s="177" t="s">
+      <c r="C76" s="130" t="s">
         <v>1120</v>
       </c>
     </row>
@@ -18326,10 +18845,10 @@
       <c r="A77" s="19" t="s">
         <v>1088</v>
       </c>
-      <c r="B77" s="177" t="s">
+      <c r="B77" s="130" t="s">
         <v>1121</v>
       </c>
-      <c r="C77" s="177" t="s">
+      <c r="C77" s="130" t="s">
         <v>1122</v>
       </c>
     </row>
@@ -18337,10 +18856,10 @@
       <c r="A78" s="19" t="s">
         <v>1088</v>
       </c>
-      <c r="B78" s="177" t="s">
+      <c r="B78" s="130" t="s">
         <v>1123</v>
       </c>
-      <c r="C78" s="177" t="s">
+      <c r="C78" s="130" t="s">
         <v>1124</v>
       </c>
     </row>
@@ -18348,10 +18867,10 @@
       <c r="A79" s="19" t="s">
         <v>1088</v>
       </c>
-      <c r="B79" s="177" t="s">
+      <c r="B79" s="130" t="s">
         <v>1125</v>
       </c>
-      <c r="C79" s="177" t="s">
+      <c r="C79" s="130" t="s">
         <v>1126</v>
       </c>
     </row>
@@ -18359,10 +18878,10 @@
       <c r="A80" s="19" t="s">
         <v>1088</v>
       </c>
-      <c r="B80" s="177" t="s">
+      <c r="B80" s="130" t="s">
         <v>1127</v>
       </c>
-      <c r="C80" s="177" t="s">
+      <c r="C80" s="130" t="s">
         <v>1128</v>
       </c>
     </row>
@@ -18370,10 +18889,10 @@
       <c r="A81" s="19" t="s">
         <v>1088</v>
       </c>
-      <c r="B81" s="177" t="s">
+      <c r="B81" s="130" t="s">
         <v>1129</v>
       </c>
-      <c r="C81" s="177" t="s">
+      <c r="C81" s="130" t="s">
         <v>1130</v>
       </c>
     </row>
@@ -18381,10 +18900,10 @@
       <c r="A82" s="19" t="s">
         <v>1088</v>
       </c>
-      <c r="B82" s="177" t="s">
+      <c r="B82" s="130" t="s">
         <v>1131</v>
       </c>
-      <c r="C82" s="177" t="s">
+      <c r="C82" s="130" t="s">
         <v>1132</v>
       </c>
     </row>
@@ -18392,10 +18911,10 @@
       <c r="A83" s="19" t="s">
         <v>1088</v>
       </c>
-      <c r="B83" s="177" t="s">
+      <c r="B83" s="130" t="s">
         <v>1133</v>
       </c>
-      <c r="C83" s="177" t="s">
+      <c r="C83" s="130" t="s">
         <v>1134</v>
       </c>
     </row>
@@ -18403,10 +18922,10 @@
       <c r="A84" s="19" t="s">
         <v>1135</v>
       </c>
-      <c r="B84" s="177" t="s">
+      <c r="B84" s="130" t="s">
         <v>1136</v>
       </c>
-      <c r="C84" s="177" t="s">
+      <c r="C84" s="130" t="s">
         <v>1110</v>
       </c>
     </row>
@@ -18414,10 +18933,10 @@
       <c r="A85" s="19" t="s">
         <v>1135</v>
       </c>
-      <c r="B85" s="177" t="s">
+      <c r="B85" s="130" t="s">
         <v>1137</v>
       </c>
-      <c r="C85" s="177" t="s">
+      <c r="C85" s="130" t="s">
         <v>1138</v>
       </c>
     </row>
@@ -18425,10 +18944,10 @@
       <c r="A86" s="19" t="s">
         <v>1135</v>
       </c>
-      <c r="B86" s="177" t="s">
+      <c r="B86" s="130" t="s">
         <v>1139</v>
       </c>
-      <c r="C86" s="177" t="s">
+      <c r="C86" s="130" t="s">
         <v>1140</v>
       </c>
     </row>
@@ -18436,10 +18955,10 @@
       <c r="A87" s="19" t="s">
         <v>1135</v>
       </c>
-      <c r="B87" s="177" t="s">
+      <c r="B87" s="130" t="s">
         <v>1141</v>
       </c>
-      <c r="C87" s="177" t="s">
+      <c r="C87" s="130" t="s">
         <v>1142</v>
       </c>
     </row>
@@ -18447,10 +18966,10 @@
       <c r="A88" s="19" t="s">
         <v>1135</v>
       </c>
-      <c r="B88" s="177" t="s">
+      <c r="B88" s="130" t="s">
         <v>1143</v>
       </c>
-      <c r="C88" s="177" t="s">
+      <c r="C88" s="130" t="s">
         <v>1112</v>
       </c>
     </row>
@@ -18458,10 +18977,10 @@
       <c r="A89" s="19" t="s">
         <v>1135</v>
       </c>
-      <c r="B89" s="177" t="s">
+      <c r="B89" s="130" t="s">
         <v>1144</v>
       </c>
-      <c r="C89" s="177" t="s">
+      <c r="C89" s="130" t="s">
         <v>1145</v>
       </c>
     </row>
@@ -18469,10 +18988,10 @@
       <c r="A90" s="19" t="s">
         <v>1135</v>
       </c>
-      <c r="B90" s="177" t="s">
+      <c r="B90" s="130" t="s">
         <v>1146</v>
       </c>
-      <c r="C90" s="177" t="s">
+      <c r="C90" s="130" t="s">
         <v>1147</v>
       </c>
     </row>
@@ -18480,10 +18999,10 @@
       <c r="A91" s="19" t="s">
         <v>1148</v>
       </c>
-      <c r="B91" s="177" t="s">
+      <c r="B91" s="130" t="s">
         <v>1149</v>
       </c>
-      <c r="C91" s="177" t="s">
+      <c r="C91" s="130" t="s">
         <v>1110</v>
       </c>
     </row>
@@ -18491,10 +19010,10 @@
       <c r="A92" s="19" t="s">
         <v>1148</v>
       </c>
-      <c r="B92" s="177" t="s">
+      <c r="B92" s="130" t="s">
         <v>1139</v>
       </c>
-      <c r="C92" s="177" t="s">
+      <c r="C92" s="130" t="s">
         <v>1140</v>
       </c>
     </row>
@@ -18502,10 +19021,10 @@
       <c r="A93" s="19" t="s">
         <v>1148</v>
       </c>
-      <c r="B93" s="177" t="s">
+      <c r="B93" s="130" t="s">
         <v>313</v>
       </c>
-      <c r="C93" s="177" t="s">
+      <c r="C93" s="130" t="s">
         <v>1090</v>
       </c>
     </row>
@@ -18513,10 +19032,10 @@
       <c r="A94" s="19" t="s">
         <v>1148</v>
       </c>
-      <c r="B94" s="177" t="s">
+      <c r="B94" s="130" t="s">
         <v>812</v>
       </c>
-      <c r="C94" s="177" t="s">
+      <c r="C94" s="130" t="s">
         <v>1150</v>
       </c>
     </row>
@@ -18524,10 +19043,10 @@
       <c r="A95" s="19" t="s">
         <v>1148</v>
       </c>
-      <c r="B95" s="177" t="s">
+      <c r="B95" s="130" t="s">
         <v>1151</v>
       </c>
-      <c r="C95" s="177" t="s">
+      <c r="C95" s="130" t="s">
         <v>1094</v>
       </c>
     </row>
@@ -18535,10 +19054,10 @@
       <c r="A96" s="19" t="s">
         <v>1148</v>
       </c>
-      <c r="B96" s="177" t="s">
+      <c r="B96" s="130" t="s">
         <v>1152</v>
       </c>
-      <c r="C96" s="177" t="s">
+      <c r="C96" s="130" t="s">
         <v>1096</v>
       </c>
     </row>
@@ -18546,10 +19065,10 @@
       <c r="A97" s="19" t="s">
         <v>1148</v>
       </c>
-      <c r="B97" s="177" t="s">
+      <c r="B97" s="130" t="s">
         <v>1153</v>
       </c>
-      <c r="C97" s="177" t="s">
+      <c r="C97" s="130" t="s">
         <v>1098</v>
       </c>
     </row>
@@ -18557,10 +19076,10 @@
       <c r="A98" s="19" t="s">
         <v>1148</v>
       </c>
-      <c r="B98" s="177" t="s">
+      <c r="B98" s="130" t="s">
         <v>1154</v>
       </c>
-      <c r="C98" s="177" t="s">
+      <c r="C98" s="130" t="s">
         <v>1132</v>
       </c>
     </row>
@@ -18568,10 +19087,10 @@
       <c r="A99" s="19" t="s">
         <v>1148</v>
       </c>
-      <c r="B99" s="177" t="s">
+      <c r="B99" s="130" t="s">
         <v>1155</v>
       </c>
-      <c r="C99" s="177" t="s">
+      <c r="C99" s="130" t="s">
         <v>1156</v>
       </c>
     </row>
@@ -18579,10 +19098,10 @@
       <c r="A100" s="19" t="s">
         <v>1148</v>
       </c>
-      <c r="B100" s="177" t="s">
+      <c r="B100" s="130" t="s">
         <v>1157</v>
       </c>
-      <c r="C100" s="177" t="s">
+      <c r="C100" s="130" t="s">
         <v>1128</v>
       </c>
     </row>
@@ -18590,10 +19109,10 @@
       <c r="A101" s="19" t="s">
         <v>1148</v>
       </c>
-      <c r="B101" s="177" t="s">
+      <c r="B101" s="130" t="s">
         <v>1144</v>
       </c>
-      <c r="C101" s="177" t="s">
+      <c r="C101" s="130" t="s">
         <v>1158</v>
       </c>
     </row>
@@ -18601,10 +19120,10 @@
       <c r="A102" s="19" t="s">
         <v>1148</v>
       </c>
-      <c r="B102" s="177" t="s">
+      <c r="B102" s="130" t="s">
         <v>1159</v>
       </c>
-      <c r="C102" s="177" t="s">
+      <c r="C102" s="130" t="s">
         <v>1160</v>
       </c>
     </row>
@@ -18612,10 +19131,10 @@
       <c r="A103" s="19" t="s">
         <v>1148</v>
       </c>
-      <c r="B103" s="177" t="s">
+      <c r="B103" s="130" t="s">
         <v>1161</v>
       </c>
-      <c r="C103" s="177" t="s">
+      <c r="C103" s="130" t="s">
         <v>1162</v>
       </c>
     </row>
@@ -18623,10 +19142,10 @@
       <c r="A104" s="19" t="s">
         <v>1148</v>
       </c>
-      <c r="B104" s="177" t="s">
+      <c r="B104" s="130" t="s">
         <v>1163</v>
       </c>
-      <c r="C104" s="177" t="s">
+      <c r="C104" s="130" t="s">
         <v>1102</v>
       </c>
     </row>
@@ -18634,10 +19153,10 @@
       <c r="A105" s="19" t="s">
         <v>1148</v>
       </c>
-      <c r="B105" s="177" t="s">
+      <c r="B105" s="130" t="s">
         <v>1164</v>
       </c>
-      <c r="C105" s="177" t="s">
+      <c r="C105" s="130" t="s">
         <v>1165</v>
       </c>
     </row>
@@ -18660,13 +19179,13 @@
       <c r="A112" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="B112" s="178"/>
+      <c r="B112" s="131"/>
     </row>
     <row r="113" spans="1:2" ht="16.5">
       <c r="A113" s="7" t="s">
         <v>1168</v>
       </c>
-      <c r="B113" s="178"/>
+      <c r="B113" s="131"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -18681,7 +19200,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -18710,7 +19229,7 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="159" t="s">
+      <c r="A2" s="178" t="s">
         <v>379</v>
       </c>
       <c r="B2" s="57" t="s">
@@ -18724,7 +19243,7 @@
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="159"/>
+      <c r="A3" s="178"/>
       <c r="B3" s="20" t="s">
         <v>262</v>
       </c>
@@ -18736,7 +19255,7 @@
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="159"/>
+      <c r="A4" s="178"/>
       <c r="B4" s="20" t="s">
         <v>385</v>
       </c>
@@ -18748,7 +19267,7 @@
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="159"/>
+      <c r="A5" s="178"/>
       <c r="B5" s="57" t="s">
         <v>544</v>
       </c>
@@ -18760,7 +19279,7 @@
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="159"/>
+      <c r="A6" s="178"/>
       <c r="B6" s="20" t="s">
         <v>388</v>
       </c>
@@ -18772,7 +19291,7 @@
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="159"/>
+      <c r="A7" s="178"/>
       <c r="B7" s="20" t="s">
         <v>390</v>
       </c>
@@ -18871,7 +19390,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:B48"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -19123,889 +19642,6 @@
     <row r="48" spans="1:2">
       <c r="A48" s="2" t="s">
         <v>52</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
-  <dimension ref="A1:E96"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="32.7109375" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="6" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="6" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="1" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="1" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="1" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="6" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="6" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="4" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" t="s">
-        <v>123</v>
-      </c>
-      <c r="B32" t="s">
-        <v>124</v>
-      </c>
-      <c r="C32" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" t="s">
-        <v>126</v>
-      </c>
-      <c r="B33" t="s">
-        <v>124</v>
-      </c>
-      <c r="C33" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" t="s">
-        <v>128</v>
-      </c>
-      <c r="B34" t="s">
-        <v>124</v>
-      </c>
-      <c r="C34" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" t="s">
-        <v>130</v>
-      </c>
-      <c r="B35" t="s">
-        <v>124</v>
-      </c>
-      <c r="C35" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" t="s">
-        <v>132</v>
-      </c>
-      <c r="B36" t="s">
-        <v>124</v>
-      </c>
-      <c r="C36" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" t="s">
-        <v>134</v>
-      </c>
-      <c r="B37" t="s">
-        <v>124</v>
-      </c>
-      <c r="C37" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" t="s">
-        <v>136</v>
-      </c>
-      <c r="B38" t="s">
-        <v>124</v>
-      </c>
-      <c r="C38" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" t="s">
-        <v>138</v>
-      </c>
-      <c r="B39" t="s">
-        <v>124</v>
-      </c>
-      <c r="C39" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" t="s">
-        <v>140</v>
-      </c>
-      <c r="B40" t="s">
-        <v>124</v>
-      </c>
-      <c r="C40" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" t="s">
-        <v>142</v>
-      </c>
-      <c r="B41" t="s">
-        <v>124</v>
-      </c>
-      <c r="C41" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" t="s">
-        <v>126</v>
-      </c>
-      <c r="B42" t="s">
-        <v>124</v>
-      </c>
-      <c r="C42" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" t="s">
-        <v>128</v>
-      </c>
-      <c r="B43" t="s">
-        <v>124</v>
-      </c>
-      <c r="C43" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" t="s">
-        <v>130</v>
-      </c>
-      <c r="B44" t="s">
-        <v>124</v>
-      </c>
-      <c r="C44" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" t="s">
-        <v>132</v>
-      </c>
-      <c r="B45" t="s">
-        <v>124</v>
-      </c>
-      <c r="C45" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" t="s">
-        <v>134</v>
-      </c>
-      <c r="B46" t="s">
-        <v>124</v>
-      </c>
-      <c r="C46" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" t="s">
-        <v>149</v>
-      </c>
-      <c r="B47" t="s">
-        <v>124</v>
-      </c>
-      <c r="C47" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" t="s">
-        <v>151</v>
-      </c>
-      <c r="B48" t="s">
-        <v>124</v>
-      </c>
-      <c r="C48" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" t="s">
-        <v>153</v>
-      </c>
-      <c r="B49" t="s">
-        <v>124</v>
-      </c>
-      <c r="C49" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" t="s">
-        <v>136</v>
-      </c>
-      <c r="B50" t="s">
-        <v>124</v>
-      </c>
-      <c r="C50" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" t="s">
-        <v>156</v>
-      </c>
-      <c r="B51" t="s">
-        <v>124</v>
-      </c>
-      <c r="C51" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" t="s">
-        <v>158</v>
-      </c>
-      <c r="B52" t="s">
-        <v>124</v>
-      </c>
-      <c r="C52" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53" t="s">
-        <v>160</v>
-      </c>
-      <c r="B53" t="s">
-        <v>124</v>
-      </c>
-      <c r="C53" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3">
-      <c r="A54" t="s">
-        <v>162</v>
-      </c>
-      <c r="B54" t="s">
-        <v>124</v>
-      </c>
-      <c r="C54" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
-      <c r="A55" t="s">
-        <v>164</v>
-      </c>
-      <c r="B55" t="s">
-        <v>124</v>
-      </c>
-      <c r="C55" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3">
-      <c r="A56" t="s">
-        <v>166</v>
-      </c>
-      <c r="B56" t="s">
-        <v>124</v>
-      </c>
-      <c r="C56" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3">
-      <c r="A57" t="s">
-        <v>168</v>
-      </c>
-      <c r="B57" t="s">
-        <v>124</v>
-      </c>
-      <c r="C57" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3">
-      <c r="A58" t="s">
-        <v>170</v>
-      </c>
-      <c r="B58" t="s">
-        <v>124</v>
-      </c>
-      <c r="C58" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3">
-      <c r="A59" t="s">
-        <v>172</v>
-      </c>
-      <c r="B59" t="s">
-        <v>124</v>
-      </c>
-      <c r="C59" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3">
-      <c r="A60" t="s">
-        <v>174</v>
-      </c>
-      <c r="B60" t="s">
-        <v>124</v>
-      </c>
-      <c r="C60" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3">
-      <c r="A61" t="s">
-        <v>176</v>
-      </c>
-      <c r="B61" t="s">
-        <v>124</v>
-      </c>
-      <c r="C61" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3">
-      <c r="A62" t="s">
-        <v>178</v>
-      </c>
-      <c r="B62" t="s">
-        <v>124</v>
-      </c>
-      <c r="C62" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3">
-      <c r="A63" t="s">
-        <v>180</v>
-      </c>
-      <c r="B63" t="s">
-        <v>124</v>
-      </c>
-      <c r="C63" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3">
-      <c r="A64" t="s">
-        <v>182</v>
-      </c>
-      <c r="B64" t="s">
-        <v>124</v>
-      </c>
-      <c r="C64" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3">
-      <c r="A65" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3">
-      <c r="A66" t="s">
-        <v>57</v>
-      </c>
-      <c r="B66" t="s">
-        <v>58</v>
-      </c>
-      <c r="C66" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3">
-      <c r="A67" t="s">
-        <v>60</v>
-      </c>
-      <c r="B67" t="s">
-        <v>58</v>
-      </c>
-      <c r="C67" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3">
-      <c r="A68" t="s">
-        <v>62</v>
-      </c>
-      <c r="B68" t="s">
-        <v>58</v>
-      </c>
-      <c r="C68" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3">
-      <c r="A69" t="s">
-        <v>64</v>
-      </c>
-      <c r="B69" t="s">
-        <v>58</v>
-      </c>
-      <c r="C69" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3">
-      <c r="A70" t="s">
-        <v>66</v>
-      </c>
-      <c r="B70" t="s">
-        <v>58</v>
-      </c>
-      <c r="C70" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3">
-      <c r="A71" t="s">
-        <v>68</v>
-      </c>
-      <c r="B71" t="s">
-        <v>58</v>
-      </c>
-      <c r="C71" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3">
-      <c r="A72" t="s">
-        <v>70</v>
-      </c>
-      <c r="B72" t="s">
-        <v>58</v>
-      </c>
-      <c r="C72" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3">
-      <c r="A73" t="s">
-        <v>72</v>
-      </c>
-      <c r="B73" t="s">
-        <v>58</v>
-      </c>
-      <c r="C73" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3">
-      <c r="A74" t="s">
-        <v>74</v>
-      </c>
-      <c r="B74" t="s">
-        <v>58</v>
-      </c>
-      <c r="C74" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3">
-      <c r="A75" t="s">
-        <v>76</v>
-      </c>
-      <c r="B75" t="s">
-        <v>58</v>
-      </c>
-      <c r="C75" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3">
-      <c r="A76" t="s">
-        <v>78</v>
-      </c>
-      <c r="B76" t="s">
-        <v>58</v>
-      </c>
-      <c r="C76" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3">
-      <c r="A77" t="s">
-        <v>80</v>
-      </c>
-      <c r="B77" t="s">
-        <v>81</v>
-      </c>
-      <c r="C77" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3">
-      <c r="A78" t="s">
-        <v>83</v>
-      </c>
-      <c r="B78" t="s">
-        <v>81</v>
-      </c>
-      <c r="C78" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3">
-      <c r="A79" t="s">
-        <v>85</v>
-      </c>
-      <c r="B79" t="s">
-        <v>81</v>
-      </c>
-      <c r="C79" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3">
-      <c r="A80" t="s">
-        <v>87</v>
-      </c>
-      <c r="B80" t="s">
-        <v>81</v>
-      </c>
-      <c r="C80" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3">
-      <c r="A81" t="s">
-        <v>89</v>
-      </c>
-      <c r="B81" t="s">
-        <v>81</v>
-      </c>
-      <c r="C81" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3">
-      <c r="A82" t="s">
-        <v>91</v>
-      </c>
-      <c r="B82" t="s">
-        <v>81</v>
-      </c>
-      <c r="C82" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3">
-      <c r="A83" t="s">
-        <v>93</v>
-      </c>
-      <c r="B83" t="s">
-        <v>81</v>
-      </c>
-      <c r="C83" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3">
-      <c r="A84" t="s">
-        <v>95</v>
-      </c>
-      <c r="B84" t="s">
-        <v>81</v>
-      </c>
-      <c r="C84" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3">
-      <c r="A85" t="s">
-        <v>97</v>
-      </c>
-      <c r="B85" t="s">
-        <v>81</v>
-      </c>
-      <c r="C85" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3">
-      <c r="A86" t="s">
-        <v>99</v>
-      </c>
-      <c r="B86" t="s">
-        <v>81</v>
-      </c>
-      <c r="C86" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3">
-      <c r="A87" t="s">
-        <v>101</v>
-      </c>
-      <c r="B87" t="s">
-        <v>81</v>
-      </c>
-      <c r="C87" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3">
-      <c r="A88" t="s">
-        <v>103</v>
-      </c>
-      <c r="B88" t="s">
-        <v>81</v>
-      </c>
-      <c r="C88" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3">
-      <c r="A89" t="s">
-        <v>105</v>
-      </c>
-      <c r="B89" t="s">
-        <v>81</v>
-      </c>
-      <c r="C89" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3">
-      <c r="A90" t="s">
-        <v>107</v>
-      </c>
-      <c r="B90" t="s">
-        <v>81</v>
-      </c>
-      <c r="C90" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3">
-      <c r="A91" t="s">
-        <v>109</v>
-      </c>
-      <c r="B91" t="s">
-        <v>81</v>
-      </c>
-      <c r="C91" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3">
-      <c r="A92" t="s">
-        <v>111</v>
-      </c>
-      <c r="B92" t="s">
-        <v>81</v>
-      </c>
-      <c r="C92" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3">
-      <c r="A93" t="s">
-        <v>113</v>
-      </c>
-      <c r="B93" t="s">
-        <v>81</v>
-      </c>
-      <c r="C93" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3">
-      <c r="A94" t="s">
-        <v>115</v>
-      </c>
-      <c r="B94" t="s">
-        <v>116</v>
-      </c>
-      <c r="C94" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3">
-      <c r="A95" t="s">
-        <v>118</v>
-      </c>
-      <c r="B95" t="s">
-        <v>116</v>
-      </c>
-      <c r="C95" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3">
-      <c r="A96" t="s">
-        <v>120</v>
-      </c>
-      <c r="B96" t="s">
-        <v>121</v>
-      </c>
-      <c r="C96" t="s">
-        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -20136,6 +19772,889 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+  <dimension ref="A1:E96"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="32.7109375" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="6" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="6" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="1" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="1" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="6" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="6" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="4" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>123</v>
+      </c>
+      <c r="B32" t="s">
+        <v>124</v>
+      </c>
+      <c r="C32" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>126</v>
+      </c>
+      <c r="B33" t="s">
+        <v>124</v>
+      </c>
+      <c r="C33" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>128</v>
+      </c>
+      <c r="B34" t="s">
+        <v>124</v>
+      </c>
+      <c r="C34" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>130</v>
+      </c>
+      <c r="B35" t="s">
+        <v>124</v>
+      </c>
+      <c r="C35" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
+        <v>132</v>
+      </c>
+      <c r="B36" t="s">
+        <v>124</v>
+      </c>
+      <c r="C36" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
+        <v>134</v>
+      </c>
+      <c r="B37" t="s">
+        <v>124</v>
+      </c>
+      <c r="C37" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
+        <v>136</v>
+      </c>
+      <c r="B38" t="s">
+        <v>124</v>
+      </c>
+      <c r="C38" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
+        <v>138</v>
+      </c>
+      <c r="B39" t="s">
+        <v>124</v>
+      </c>
+      <c r="C39" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" t="s">
+        <v>140</v>
+      </c>
+      <c r="B40" t="s">
+        <v>124</v>
+      </c>
+      <c r="C40" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
+        <v>142</v>
+      </c>
+      <c r="B41" t="s">
+        <v>124</v>
+      </c>
+      <c r="C41" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
+        <v>126</v>
+      </c>
+      <c r="B42" t="s">
+        <v>124</v>
+      </c>
+      <c r="C42" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" t="s">
+        <v>128</v>
+      </c>
+      <c r="B43" t="s">
+        <v>124</v>
+      </c>
+      <c r="C43" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
+        <v>130</v>
+      </c>
+      <c r="B44" t="s">
+        <v>124</v>
+      </c>
+      <c r="C44" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" t="s">
+        <v>132</v>
+      </c>
+      <c r="B45" t="s">
+        <v>124</v>
+      </c>
+      <c r="C45" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" t="s">
+        <v>134</v>
+      </c>
+      <c r="B46" t="s">
+        <v>124</v>
+      </c>
+      <c r="C46" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" t="s">
+        <v>149</v>
+      </c>
+      <c r="B47" t="s">
+        <v>124</v>
+      </c>
+      <c r="C47" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" t="s">
+        <v>151</v>
+      </c>
+      <c r="B48" t="s">
+        <v>124</v>
+      </c>
+      <c r="C48" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" t="s">
+        <v>153</v>
+      </c>
+      <c r="B49" t="s">
+        <v>124</v>
+      </c>
+      <c r="C49" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" t="s">
+        <v>136</v>
+      </c>
+      <c r="B50" t="s">
+        <v>124</v>
+      </c>
+      <c r="C50" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" t="s">
+        <v>156</v>
+      </c>
+      <c r="B51" t="s">
+        <v>124</v>
+      </c>
+      <c r="C51" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" t="s">
+        <v>158</v>
+      </c>
+      <c r="B52" t="s">
+        <v>124</v>
+      </c>
+      <c r="C52" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" t="s">
+        <v>160</v>
+      </c>
+      <c r="B53" t="s">
+        <v>124</v>
+      </c>
+      <c r="C53" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" t="s">
+        <v>162</v>
+      </c>
+      <c r="B54" t="s">
+        <v>124</v>
+      </c>
+      <c r="C54" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" t="s">
+        <v>164</v>
+      </c>
+      <c r="B55" t="s">
+        <v>124</v>
+      </c>
+      <c r="C55" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" t="s">
+        <v>166</v>
+      </c>
+      <c r="B56" t="s">
+        <v>124</v>
+      </c>
+      <c r="C56" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" t="s">
+        <v>168</v>
+      </c>
+      <c r="B57" t="s">
+        <v>124</v>
+      </c>
+      <c r="C57" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" t="s">
+        <v>170</v>
+      </c>
+      <c r="B58" t="s">
+        <v>124</v>
+      </c>
+      <c r="C58" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" t="s">
+        <v>172</v>
+      </c>
+      <c r="B59" t="s">
+        <v>124</v>
+      </c>
+      <c r="C59" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" t="s">
+        <v>174</v>
+      </c>
+      <c r="B60" t="s">
+        <v>124</v>
+      </c>
+      <c r="C60" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" t="s">
+        <v>176</v>
+      </c>
+      <c r="B61" t="s">
+        <v>124</v>
+      </c>
+      <c r="C61" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" t="s">
+        <v>178</v>
+      </c>
+      <c r="B62" t="s">
+        <v>124</v>
+      </c>
+      <c r="C62" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" t="s">
+        <v>180</v>
+      </c>
+      <c r="B63" t="s">
+        <v>124</v>
+      </c>
+      <c r="C63" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" t="s">
+        <v>182</v>
+      </c>
+      <c r="B64" t="s">
+        <v>124</v>
+      </c>
+      <c r="C64" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" t="s">
+        <v>57</v>
+      </c>
+      <c r="B66" t="s">
+        <v>58</v>
+      </c>
+      <c r="C66" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" t="s">
+        <v>60</v>
+      </c>
+      <c r="B67" t="s">
+        <v>58</v>
+      </c>
+      <c r="C67" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" t="s">
+        <v>62</v>
+      </c>
+      <c r="B68" t="s">
+        <v>58</v>
+      </c>
+      <c r="C68" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" t="s">
+        <v>64</v>
+      </c>
+      <c r="B69" t="s">
+        <v>58</v>
+      </c>
+      <c r="C69" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" t="s">
+        <v>66</v>
+      </c>
+      <c r="B70" t="s">
+        <v>58</v>
+      </c>
+      <c r="C70" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" t="s">
+        <v>68</v>
+      </c>
+      <c r="B71" t="s">
+        <v>58</v>
+      </c>
+      <c r="C71" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" t="s">
+        <v>70</v>
+      </c>
+      <c r="B72" t="s">
+        <v>58</v>
+      </c>
+      <c r="C72" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" t="s">
+        <v>72</v>
+      </c>
+      <c r="B73" t="s">
+        <v>58</v>
+      </c>
+      <c r="C73" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" t="s">
+        <v>74</v>
+      </c>
+      <c r="B74" t="s">
+        <v>58</v>
+      </c>
+      <c r="C74" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" t="s">
+        <v>76</v>
+      </c>
+      <c r="B75" t="s">
+        <v>58</v>
+      </c>
+      <c r="C75" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" t="s">
+        <v>78</v>
+      </c>
+      <c r="B76" t="s">
+        <v>58</v>
+      </c>
+      <c r="C76" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" t="s">
+        <v>80</v>
+      </c>
+      <c r="B77" t="s">
+        <v>81</v>
+      </c>
+      <c r="C77" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" t="s">
+        <v>83</v>
+      </c>
+      <c r="B78" t="s">
+        <v>81</v>
+      </c>
+      <c r="C78" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" t="s">
+        <v>85</v>
+      </c>
+      <c r="B79" t="s">
+        <v>81</v>
+      </c>
+      <c r="C79" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" t="s">
+        <v>87</v>
+      </c>
+      <c r="B80" t="s">
+        <v>81</v>
+      </c>
+      <c r="C80" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" t="s">
+        <v>89</v>
+      </c>
+      <c r="B81" t="s">
+        <v>81</v>
+      </c>
+      <c r="C81" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" t="s">
+        <v>91</v>
+      </c>
+      <c r="B82" t="s">
+        <v>81</v>
+      </c>
+      <c r="C82" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83" t="s">
+        <v>93</v>
+      </c>
+      <c r="B83" t="s">
+        <v>81</v>
+      </c>
+      <c r="C83" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84" t="s">
+        <v>95</v>
+      </c>
+      <c r="B84" t="s">
+        <v>81</v>
+      </c>
+      <c r="C84" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85" t="s">
+        <v>97</v>
+      </c>
+      <c r="B85" t="s">
+        <v>81</v>
+      </c>
+      <c r="C85" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86" t="s">
+        <v>99</v>
+      </c>
+      <c r="B86" t="s">
+        <v>81</v>
+      </c>
+      <c r="C86" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87" t="s">
+        <v>101</v>
+      </c>
+      <c r="B87" t="s">
+        <v>81</v>
+      </c>
+      <c r="C87" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88" t="s">
+        <v>103</v>
+      </c>
+      <c r="B88" t="s">
+        <v>81</v>
+      </c>
+      <c r="C88" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89" t="s">
+        <v>105</v>
+      </c>
+      <c r="B89" t="s">
+        <v>81</v>
+      </c>
+      <c r="C89" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" t="s">
+        <v>107</v>
+      </c>
+      <c r="B90" t="s">
+        <v>81</v>
+      </c>
+      <c r="C90" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91" t="s">
+        <v>109</v>
+      </c>
+      <c r="B91" t="s">
+        <v>81</v>
+      </c>
+      <c r="C91" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" t="s">
+        <v>111</v>
+      </c>
+      <c r="B92" t="s">
+        <v>81</v>
+      </c>
+      <c r="C92" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93" t="s">
+        <v>113</v>
+      </c>
+      <c r="B93" t="s">
+        <v>81</v>
+      </c>
+      <c r="C93" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94" t="s">
+        <v>115</v>
+      </c>
+      <c r="B94" t="s">
+        <v>116</v>
+      </c>
+      <c r="C94" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95" t="s">
+        <v>118</v>
+      </c>
+      <c r="B95" t="s">
+        <v>116</v>
+      </c>
+      <c r="C95" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96" t="s">
+        <v>120</v>
+      </c>
+      <c r="B96" t="s">
+        <v>121</v>
+      </c>
+      <c r="C96" t="s">
+        <v>122</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:E28"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -20463,7 +20982,7 @@
       </c>
     </row>
     <row r="22" spans="7:22">
-      <c r="T22" s="127" t="s">
+      <c r="T22" s="141" t="s">
         <v>834</v>
       </c>
       <c r="U22" s="9" t="s">
@@ -20480,7 +20999,7 @@
       <c r="O23" s="5" t="s">
         <v>913</v>
       </c>
-      <c r="T23" s="128"/>
+      <c r="T23" s="142"/>
       <c r="U23" s="9" t="s">
         <v>817</v>
       </c>
@@ -20489,7 +21008,7 @@
       </c>
     </row>
     <row r="24" spans="7:22">
-      <c r="T24" s="128"/>
+      <c r="T24" s="142"/>
       <c r="U24" s="9" t="s">
         <v>818</v>
       </c>
@@ -20501,7 +21020,7 @@
       <c r="K25" s="5" t="s">
         <v>893</v>
       </c>
-      <c r="T25" s="128"/>
+      <c r="T25" s="142"/>
       <c r="U25" s="9" t="s">
         <v>819</v>
       </c>
@@ -20519,7 +21038,7 @@
       <c r="N26" t="s">
         <v>900</v>
       </c>
-      <c r="T26" s="128"/>
+      <c r="T26" s="142"/>
       <c r="U26" s="9" t="s">
         <v>826</v>
       </c>
@@ -20532,7 +21051,7 @@
       <c r="M27" t="s">
         <v>899</v>
       </c>
-      <c r="T27" s="128"/>
+      <c r="T27" s="142"/>
       <c r="U27" s="9" t="s">
         <v>827</v>
       </c>
@@ -20542,7 +21061,7 @@
       <c r="M28" t="s">
         <v>901</v>
       </c>
-      <c r="T28" s="128"/>
+      <c r="T28" s="142"/>
       <c r="U28" s="9" t="s">
         <v>828</v>
       </c>
@@ -20554,7 +21073,7 @@
       <c r="M29" t="s">
         <v>902</v>
       </c>
-      <c r="T29" s="129"/>
+      <c r="T29" s="143"/>
       <c r="U29" s="9" t="s">
         <v>829</v>
       </c>
@@ -20569,7 +21088,7 @@
       <c r="M30" t="s">
         <v>854</v>
       </c>
-      <c r="T30" s="124" t="s">
+      <c r="T30" s="138" t="s">
         <v>833</v>
       </c>
       <c r="U30" s="49" t="s">
@@ -20581,7 +21100,7 @@
       <c r="M31" t="s">
         <v>904</v>
       </c>
-      <c r="T31" s="125"/>
+      <c r="T31" s="139"/>
       <c r="U31" s="49" t="s">
         <v>824</v>
       </c>
@@ -20597,7 +21116,7 @@
       <c r="O32" s="5" t="s">
         <v>906</v>
       </c>
-      <c r="T32" s="126"/>
+      <c r="T32" s="140"/>
       <c r="U32" s="49" t="s">
         <v>825</v>
       </c>
@@ -20726,7 +21245,7 @@
       <c r="R5" s="13" t="s">
         <v>352</v>
       </c>
-      <c r="S5" s="130" t="s">
+      <c r="S5" s="144" t="s">
         <v>811</v>
       </c>
     </row>
@@ -20743,7 +21262,7 @@
       <c r="R6" s="9" t="s">
         <v>602</v>
       </c>
-      <c r="S6" s="130"/>
+      <c r="S6" s="144"/>
     </row>
     <row r="7" spans="3:20">
       <c r="O7" s="81" t="s">
@@ -20758,7 +21277,7 @@
       <c r="R7" s="9" t="s">
         <v>603</v>
       </c>
-      <c r="S7" s="130"/>
+      <c r="S7" s="144"/>
     </row>
     <row r="8" spans="3:20">
       <c r="O8" s="81" t="s">
@@ -20773,7 +21292,7 @@
       <c r="R8" s="9" t="s">
         <v>350</v>
       </c>
-      <c r="S8" s="130"/>
+      <c r="S8" s="144"/>
     </row>
     <row r="9" spans="3:20">
       <c r="O9" s="81" t="s">
@@ -20788,7 +21307,7 @@
       <c r="R9" s="9" t="s">
         <v>349</v>
       </c>
-      <c r="S9" s="130"/>
+      <c r="S9" s="144"/>
     </row>
     <row r="10" spans="3:20">
       <c r="Q10" s="9" t="s">
@@ -20813,7 +21332,7 @@
       </c>
     </row>
     <row r="15" spans="3:20">
-      <c r="Q15" s="127" t="s">
+      <c r="Q15" s="141" t="s">
         <v>834</v>
       </c>
       <c r="R15" s="9" t="s">
@@ -20848,7 +21367,7 @@
       <c r="J16" s="10" t="s">
         <v>815</v>
       </c>
-      <c r="Q16" s="128"/>
+      <c r="Q16" s="142"/>
       <c r="R16" s="9" t="s">
         <v>817</v>
       </c>
@@ -20858,7 +21377,7 @@
     </row>
     <row r="17" spans="10:19">
       <c r="J17" s="81"/>
-      <c r="Q17" s="128"/>
+      <c r="Q17" s="142"/>
       <c r="R17" s="9" t="s">
         <v>818</v>
       </c>
@@ -20867,7 +21386,7 @@
       </c>
     </row>
     <row r="18" spans="10:19">
-      <c r="Q18" s="128"/>
+      <c r="Q18" s="142"/>
       <c r="R18" s="9" t="s">
         <v>819</v>
       </c>
@@ -20876,21 +21395,21 @@
       </c>
     </row>
     <row r="19" spans="10:19">
-      <c r="Q19" s="128"/>
+      <c r="Q19" s="142"/>
       <c r="R19" s="9" t="s">
         <v>826</v>
       </c>
       <c r="S19" s="92"/>
     </row>
     <row r="20" spans="10:19">
-      <c r="Q20" s="128"/>
+      <c r="Q20" s="142"/>
       <c r="R20" s="9" t="s">
         <v>827</v>
       </c>
       <c r="S20" s="92"/>
     </row>
     <row r="21" spans="10:19">
-      <c r="Q21" s="128"/>
+      <c r="Q21" s="142"/>
       <c r="R21" s="9" t="s">
         <v>828</v>
       </c>
@@ -20899,7 +21418,7 @@
       </c>
     </row>
     <row r="22" spans="10:19">
-      <c r="Q22" s="129"/>
+      <c r="Q22" s="143"/>
       <c r="R22" s="9" t="s">
         <v>829</v>
       </c>
@@ -20908,7 +21427,7 @@
       </c>
     </row>
     <row r="23" spans="10:19">
-      <c r="Q23" s="127" t="s">
+      <c r="Q23" s="141" t="s">
         <v>833</v>
       </c>
       <c r="R23" s="9" t="s">
@@ -20917,14 +21436,14 @@
       <c r="S23" s="92"/>
     </row>
     <row r="24" spans="10:19">
-      <c r="Q24" s="128"/>
+      <c r="Q24" s="142"/>
       <c r="R24" s="9" t="s">
         <v>824</v>
       </c>
       <c r="S24" s="92"/>
     </row>
     <row r="25" spans="10:19">
-      <c r="Q25" s="129"/>
+      <c r="Q25" s="143"/>
       <c r="R25" s="9" t="s">
         <v>825</v>
       </c>
@@ -20989,39 +21508,39 @@
       <c r="B1" t="s">
         <v>862</v>
       </c>
-      <c r="J1" s="163" t="s">
+      <c r="J1" s="145" t="s">
         <v>957</v>
       </c>
-      <c r="K1" s="164"/>
-      <c r="L1" s="164"/>
-      <c r="M1" s="164"/>
-      <c r="N1" s="164"/>
-      <c r="O1" s="164"/>
-      <c r="P1" s="164"/>
-      <c r="Q1" s="164"/>
+      <c r="K1" s="146"/>
+      <c r="L1" s="146"/>
+      <c r="M1" s="146"/>
+      <c r="N1" s="146"/>
+      <c r="O1" s="146"/>
+      <c r="P1" s="146"/>
+      <c r="Q1" s="146"/>
     </row>
     <row r="2" spans="1:17">
-      <c r="J2" s="164"/>
-      <c r="K2" s="164"/>
-      <c r="L2" s="164"/>
-      <c r="M2" s="164"/>
-      <c r="N2" s="164"/>
-      <c r="O2" s="164"/>
-      <c r="P2" s="164"/>
-      <c r="Q2" s="164"/>
+      <c r="J2" s="146"/>
+      <c r="K2" s="146"/>
+      <c r="L2" s="146"/>
+      <c r="M2" s="146"/>
+      <c r="N2" s="146"/>
+      <c r="O2" s="146"/>
+      <c r="P2" s="146"/>
+      <c r="Q2" s="146"/>
     </row>
     <row r="3" spans="1:17">
       <c r="A3" t="s">
         <v>863</v>
       </c>
-      <c r="J3" s="164"/>
-      <c r="K3" s="164"/>
-      <c r="L3" s="164"/>
-      <c r="M3" s="164"/>
-      <c r="N3" s="164"/>
-      <c r="O3" s="164"/>
-      <c r="P3" s="164"/>
-      <c r="Q3" s="164"/>
+      <c r="J3" s="146"/>
+      <c r="K3" s="146"/>
+      <c r="L3" s="146"/>
+      <c r="M3" s="146"/>
+      <c r="N3" s="146"/>
+      <c r="O3" s="146"/>
+      <c r="P3" s="146"/>
+      <c r="Q3" s="146"/>
     </row>
     <row r="4" spans="1:17">
       <c r="A4" t="s">
@@ -21033,24 +21552,24 @@
       <c r="D4" t="s">
         <v>865</v>
       </c>
-      <c r="J4" s="164"/>
-      <c r="K4" s="164"/>
-      <c r="L4" s="164"/>
-      <c r="M4" s="164"/>
-      <c r="N4" s="164"/>
-      <c r="O4" s="164"/>
-      <c r="P4" s="164"/>
-      <c r="Q4" s="164"/>
+      <c r="J4" s="146"/>
+      <c r="K4" s="146"/>
+      <c r="L4" s="146"/>
+      <c r="M4" s="146"/>
+      <c r="N4" s="146"/>
+      <c r="O4" s="146"/>
+      <c r="P4" s="146"/>
+      <c r="Q4" s="146"/>
     </row>
     <row r="5" spans="1:17">
-      <c r="J5" s="164"/>
-      <c r="K5" s="164"/>
-      <c r="L5" s="164"/>
-      <c r="M5" s="164"/>
-      <c r="N5" s="164"/>
-      <c r="O5" s="164"/>
-      <c r="P5" s="164"/>
-      <c r="Q5" s="164"/>
+      <c r="J5" s="146"/>
+      <c r="K5" s="146"/>
+      <c r="L5" s="146"/>
+      <c r="M5" s="146"/>
+      <c r="N5" s="146"/>
+      <c r="O5" s="146"/>
+      <c r="P5" s="146"/>
+      <c r="Q5" s="146"/>
     </row>
     <row r="6" spans="1:17" ht="15.75" thickBot="1">
       <c r="A6" t="s">
@@ -21059,38 +21578,38 @@
       <c r="E6" t="s">
         <v>923</v>
       </c>
-      <c r="J6" s="164"/>
-      <c r="K6" s="164"/>
-      <c r="L6" s="164"/>
-      <c r="M6" s="164"/>
-      <c r="N6" s="164"/>
-      <c r="O6" s="164"/>
-      <c r="P6" s="164"/>
-      <c r="Q6" s="164"/>
+      <c r="J6" s="146"/>
+      <c r="K6" s="146"/>
+      <c r="L6" s="146"/>
+      <c r="M6" s="146"/>
+      <c r="N6" s="146"/>
+      <c r="O6" s="146"/>
+      <c r="P6" s="146"/>
+      <c r="Q6" s="146"/>
     </row>
     <row r="7" spans="1:17" ht="15.75" thickBot="1">
       <c r="A7" s="106" t="s">
         <v>867</v>
       </c>
-      <c r="J7" s="164"/>
-      <c r="K7" s="164"/>
-      <c r="L7" s="164"/>
-      <c r="M7" s="164"/>
-      <c r="N7" s="164"/>
-      <c r="O7" s="164"/>
-      <c r="P7" s="164"/>
-      <c r="Q7" s="164"/>
+      <c r="J7" s="146"/>
+      <c r="K7" s="146"/>
+      <c r="L7" s="146"/>
+      <c r="M7" s="146"/>
+      <c r="N7" s="146"/>
+      <c r="O7" s="146"/>
+      <c r="P7" s="146"/>
+      <c r="Q7" s="146"/>
     </row>
     <row r="8" spans="1:17">
-      <c r="A8" s="162"/>
-      <c r="J8" s="164"/>
-      <c r="K8" s="164"/>
-      <c r="L8" s="164"/>
-      <c r="M8" s="164"/>
-      <c r="N8" s="164"/>
-      <c r="O8" s="164"/>
-      <c r="P8" s="164"/>
-      <c r="Q8" s="164"/>
+      <c r="A8" s="120"/>
+      <c r="J8" s="146"/>
+      <c r="K8" s="146"/>
+      <c r="L8" s="146"/>
+      <c r="M8" s="146"/>
+      <c r="N8" s="146"/>
+      <c r="O8" s="146"/>
+      <c r="P8" s="146"/>
+      <c r="Q8" s="146"/>
     </row>
     <row r="9" spans="1:17">
       <c r="A9" t="s">
@@ -21099,14 +21618,14 @@
       <c r="B9" t="s">
         <v>929</v>
       </c>
-      <c r="J9" s="164"/>
-      <c r="K9" s="164"/>
-      <c r="L9" s="164"/>
-      <c r="M9" s="164"/>
-      <c r="N9" s="164"/>
-      <c r="O9" s="164"/>
-      <c r="P9" s="164"/>
-      <c r="Q9" s="164"/>
+      <c r="J9" s="146"/>
+      <c r="K9" s="146"/>
+      <c r="L9" s="146"/>
+      <c r="M9" s="146"/>
+      <c r="N9" s="146"/>
+      <c r="O9" s="146"/>
+      <c r="P9" s="146"/>
+      <c r="Q9" s="146"/>
     </row>
     <row r="10" spans="1:17">
       <c r="A10" t="s">
@@ -21127,14 +21646,14 @@
       <c r="H10" t="s">
         <v>955</v>
       </c>
-      <c r="J10" s="164"/>
-      <c r="K10" s="164"/>
-      <c r="L10" s="164"/>
-      <c r="M10" s="164"/>
-      <c r="N10" s="164"/>
-      <c r="O10" s="164"/>
-      <c r="P10" s="164"/>
-      <c r="Q10" s="164"/>
+      <c r="J10" s="146"/>
+      <c r="K10" s="146"/>
+      <c r="L10" s="146"/>
+      <c r="M10" s="146"/>
+      <c r="N10" s="146"/>
+      <c r="O10" s="146"/>
+      <c r="P10" s="146"/>
+      <c r="Q10" s="146"/>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" t="s">
@@ -21155,14 +21674,14 @@
       <c r="H11" t="s">
         <v>956</v>
       </c>
-      <c r="J11" s="164"/>
-      <c r="K11" s="164"/>
-      <c r="L11" s="164"/>
-      <c r="M11" s="164"/>
-      <c r="N11" s="164"/>
-      <c r="O11" s="164"/>
-      <c r="P11" s="164"/>
-      <c r="Q11" s="164"/>
+      <c r="J11" s="146"/>
+      <c r="K11" s="146"/>
+      <c r="L11" s="146"/>
+      <c r="M11" s="146"/>
+      <c r="N11" s="146"/>
+      <c r="O11" s="146"/>
+      <c r="P11" s="146"/>
+      <c r="Q11" s="146"/>
     </row>
     <row r="12" spans="1:17">
       <c r="B12" t="s">
@@ -21177,14 +21696,14 @@
       <c r="H12" t="s">
         <v>956</v>
       </c>
-      <c r="J12" s="164"/>
-      <c r="K12" s="164"/>
-      <c r="L12" s="164"/>
-      <c r="M12" s="164"/>
-      <c r="N12" s="164"/>
-      <c r="O12" s="164"/>
-      <c r="P12" s="164"/>
-      <c r="Q12" s="164"/>
+      <c r="J12" s="146"/>
+      <c r="K12" s="146"/>
+      <c r="L12" s="146"/>
+      <c r="M12" s="146"/>
+      <c r="N12" s="146"/>
+      <c r="O12" s="146"/>
+      <c r="P12" s="146"/>
+      <c r="Q12" s="146"/>
     </row>
     <row r="13" spans="1:17">
       <c r="F13" t="s">
@@ -21196,24 +21715,24 @@
       <c r="H13" t="s">
         <v>956</v>
       </c>
-      <c r="J13" s="164"/>
-      <c r="K13" s="164"/>
-      <c r="L13" s="164"/>
-      <c r="M13" s="164"/>
-      <c r="N13" s="164"/>
-      <c r="O13" s="164"/>
-      <c r="P13" s="164"/>
-      <c r="Q13" s="164"/>
+      <c r="J13" s="146"/>
+      <c r="K13" s="146"/>
+      <c r="L13" s="146"/>
+      <c r="M13" s="146"/>
+      <c r="N13" s="146"/>
+      <c r="O13" s="146"/>
+      <c r="P13" s="146"/>
+      <c r="Q13" s="146"/>
     </row>
     <row r="14" spans="1:17">
-      <c r="J14" s="164"/>
-      <c r="K14" s="164"/>
-      <c r="L14" s="164"/>
-      <c r="M14" s="164"/>
-      <c r="N14" s="164"/>
-      <c r="O14" s="164"/>
-      <c r="P14" s="164"/>
-      <c r="Q14" s="164"/>
+      <c r="J14" s="146"/>
+      <c r="K14" s="146"/>
+      <c r="L14" s="146"/>
+      <c r="M14" s="146"/>
+      <c r="N14" s="146"/>
+      <c r="O14" s="146"/>
+      <c r="P14" s="146"/>
+      <c r="Q14" s="146"/>
     </row>
     <row r="15" spans="1:17">
       <c r="A15" t="s">
@@ -21222,27 +21741,27 @@
       <c r="C15" t="s">
         <v>952</v>
       </c>
-      <c r="J15" s="164"/>
-      <c r="K15" s="164"/>
-      <c r="L15" s="164"/>
-      <c r="M15" s="164"/>
-      <c r="N15" s="164"/>
-      <c r="O15" s="164"/>
-      <c r="P15" s="164"/>
-      <c r="Q15" s="164"/>
+      <c r="J15" s="146"/>
+      <c r="K15" s="146"/>
+      <c r="L15" s="146"/>
+      <c r="M15" s="146"/>
+      <c r="N15" s="146"/>
+      <c r="O15" s="146"/>
+      <c r="P15" s="146"/>
+      <c r="Q15" s="146"/>
     </row>
     <row r="16" spans="1:17">
       <c r="A16" t="s">
         <v>942</v>
       </c>
-      <c r="J16" s="164"/>
-      <c r="K16" s="164"/>
-      <c r="L16" s="164"/>
-      <c r="M16" s="164"/>
-      <c r="N16" s="164"/>
-      <c r="O16" s="164"/>
-      <c r="P16" s="164"/>
-      <c r="Q16" s="164"/>
+      <c r="J16" s="146"/>
+      <c r="K16" s="146"/>
+      <c r="L16" s="146"/>
+      <c r="M16" s="146"/>
+      <c r="N16" s="146"/>
+      <c r="O16" s="146"/>
+      <c r="P16" s="146"/>
+      <c r="Q16" s="146"/>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="5" t="s">
@@ -21464,19 +21983,19 @@
       <c r="E7" s="31" t="s">
         <v>449</v>
       </c>
-      <c r="F7" s="131" t="s">
+      <c r="F7" s="147" t="s">
         <v>441</v>
       </c>
-      <c r="G7" s="131"/>
-      <c r="H7" s="131"/>
-      <c r="I7" s="131"/>
-      <c r="J7" s="131"/>
-      <c r="K7" s="131"/>
-      <c r="L7" s="131"/>
-      <c r="M7" s="131"/>
-      <c r="N7" s="131"/>
-      <c r="O7" s="131"/>
-      <c r="P7" s="131"/>
+      <c r="G7" s="147"/>
+      <c r="H7" s="147"/>
+      <c r="I7" s="147"/>
+      <c r="J7" s="147"/>
+      <c r="K7" s="147"/>
+      <c r="L7" s="147"/>
+      <c r="M7" s="147"/>
+      <c r="N7" s="147"/>
+      <c r="O7" s="147"/>
+      <c r="P7" s="147"/>
     </row>
     <row r="8" spans="1:17">
       <c r="B8" s="32" t="s">
@@ -21700,40 +22219,40 @@
       <c r="A24" s="35" t="s">
         <v>455</v>
       </c>
-      <c r="B24" s="132" t="s">
+      <c r="B24" s="148" t="s">
         <v>457</v>
       </c>
-      <c r="C24" s="132"/>
-      <c r="D24" s="132"/>
-      <c r="E24" s="132"/>
-      <c r="F24" s="132"/>
-      <c r="G24" s="132"/>
+      <c r="C24" s="148"/>
+      <c r="D24" s="148"/>
+      <c r="E24" s="148"/>
+      <c r="F24" s="148"/>
+      <c r="G24" s="148"/>
     </row>
     <row r="25" spans="1:7" ht="30">
       <c r="A25" s="35" t="s">
         <v>462</v>
       </c>
-      <c r="B25" s="133" t="s">
+      <c r="B25" s="149" t="s">
         <v>464</v>
       </c>
-      <c r="C25" s="133"/>
-      <c r="D25" s="133"/>
-      <c r="E25" s="133"/>
-      <c r="F25" s="133"/>
-      <c r="G25" s="133"/>
+      <c r="C25" s="149"/>
+      <c r="D25" s="149"/>
+      <c r="E25" s="149"/>
+      <c r="F25" s="149"/>
+      <c r="G25" s="149"/>
     </row>
     <row r="26" spans="1:7" ht="159" customHeight="1">
       <c r="A26" s="35" t="s">
         <v>459</v>
       </c>
-      <c r="B26" s="132" t="s">
+      <c r="B26" s="148" t="s">
         <v>460</v>
       </c>
-      <c r="C26" s="132"/>
-      <c r="D26" s="132"/>
-      <c r="E26" s="132"/>
-      <c r="F26" s="132"/>
-      <c r="G26" s="132"/>
+      <c r="C26" s="148"/>
+      <c r="D26" s="148"/>
+      <c r="E26" s="148"/>
+      <c r="F26" s="148"/>
+      <c r="G26" s="148"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -22248,29 +22767,29 @@
       <c r="B27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="C27" s="136" t="s">
+      <c r="C27" s="152" t="s">
         <v>622</v>
       </c>
-      <c r="D27" s="137"/>
+      <c r="D27" s="153"/>
       <c r="E27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="F27" s="136" t="s">
+      <c r="F27" s="152" t="s">
         <v>622</v>
       </c>
-      <c r="G27" s="137"/>
+      <c r="G27" s="153"/>
       <c r="H27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="I27" s="136" t="s">
+      <c r="I27" s="152" t="s">
         <v>622</v>
       </c>
-      <c r="J27" s="137"/>
-      <c r="L27" s="134" t="s">
+      <c r="J27" s="153"/>
+      <c r="L27" s="164" t="s">
         <v>694</v>
       </c>
-      <c r="M27" s="134"/>
-      <c r="N27" s="134"/>
+      <c r="M27" s="164"/>
+      <c r="N27" s="164"/>
     </row>
     <row r="28" spans="1:14" ht="32.25" thickBot="1">
       <c r="A28" s="81">
@@ -22279,29 +22798,29 @@
       <c r="B28" s="69" t="s">
         <v>623</v>
       </c>
-      <c r="C28" s="144" t="s">
+      <c r="C28" s="150" t="s">
         <v>624</v>
       </c>
-      <c r="D28" s="145"/>
+      <c r="D28" s="151"/>
       <c r="E28" s="70" t="s">
         <v>645</v>
       </c>
-      <c r="F28" s="138" t="s">
+      <c r="F28" s="154" t="s">
         <v>646</v>
       </c>
-      <c r="G28" s="139"/>
+      <c r="G28" s="155"/>
       <c r="H28" s="69" t="s">
         <v>667</v>
       </c>
-      <c r="I28" s="144" t="s">
+      <c r="I28" s="150" t="s">
         <v>668</v>
       </c>
-      <c r="J28" s="145"/>
-      <c r="L28" s="135" t="s">
+      <c r="J28" s="151"/>
+      <c r="L28" s="165" t="s">
         <v>695</v>
       </c>
-      <c r="M28" s="135"/>
-      <c r="N28" s="135"/>
+      <c r="M28" s="165"/>
+      <c r="N28" s="165"/>
     </row>
     <row r="29" spans="1:14" ht="31.5" thickBot="1">
       <c r="A29" s="81">
@@ -22310,29 +22829,29 @@
       <c r="B29" s="70" t="s">
         <v>625</v>
       </c>
-      <c r="C29" s="138" t="s">
+      <c r="C29" s="154" t="s">
         <v>626</v>
       </c>
-      <c r="D29" s="139"/>
+      <c r="D29" s="155"/>
       <c r="E29" s="69" t="s">
         <v>647</v>
       </c>
-      <c r="F29" s="144" t="s">
+      <c r="F29" s="150" t="s">
         <v>648</v>
       </c>
-      <c r="G29" s="145"/>
+      <c r="G29" s="151"/>
       <c r="H29" s="70" t="s">
         <v>669</v>
       </c>
-      <c r="I29" s="148" t="s">
+      <c r="I29" s="158" t="s">
         <v>670</v>
       </c>
-      <c r="J29" s="149"/>
-      <c r="L29" s="134" t="s">
+      <c r="J29" s="159"/>
+      <c r="L29" s="164" t="s">
         <v>696</v>
       </c>
-      <c r="M29" s="134"/>
-      <c r="N29" s="134"/>
+      <c r="M29" s="164"/>
+      <c r="N29" s="164"/>
     </row>
     <row r="30" spans="1:14" ht="15.75" thickBot="1">
       <c r="A30" s="81">
@@ -22341,29 +22860,29 @@
       <c r="B30" s="69" t="s">
         <v>627</v>
       </c>
-      <c r="C30" s="144" t="s">
+      <c r="C30" s="150" t="s">
         <v>628</v>
       </c>
-      <c r="D30" s="145"/>
+      <c r="D30" s="151"/>
       <c r="E30" s="70" t="s">
         <v>649</v>
       </c>
-      <c r="F30" s="138" t="s">
+      <c r="F30" s="154" t="s">
         <v>650</v>
       </c>
-      <c r="G30" s="139"/>
+      <c r="G30" s="155"/>
       <c r="H30" s="69" t="s">
         <v>671</v>
       </c>
-      <c r="I30" s="144" t="s">
+      <c r="I30" s="150" t="s">
         <v>672</v>
       </c>
-      <c r="J30" s="145"/>
-      <c r="L30" s="135" t="s">
+      <c r="J30" s="151"/>
+      <c r="L30" s="165" t="s">
         <v>697</v>
       </c>
-      <c r="M30" s="135"/>
-      <c r="N30" s="135"/>
+      <c r="M30" s="165"/>
+      <c r="N30" s="165"/>
     </row>
     <row r="31" spans="1:14" ht="17.25" customHeight="1" thickBot="1">
       <c r="A31" s="81">
@@ -22372,29 +22891,29 @@
       <c r="B31" s="70" t="s">
         <v>629</v>
       </c>
-      <c r="C31" s="138" t="s">
+      <c r="C31" s="154" t="s">
         <v>630</v>
       </c>
-      <c r="D31" s="139"/>
+      <c r="D31" s="155"/>
       <c r="E31" s="69" t="s">
         <v>651</v>
       </c>
-      <c r="F31" s="144" t="s">
+      <c r="F31" s="150" t="s">
         <v>652</v>
       </c>
-      <c r="G31" s="145"/>
+      <c r="G31" s="151"/>
       <c r="H31" s="70" t="s">
         <v>673</v>
       </c>
-      <c r="I31" s="138" t="s">
+      <c r="I31" s="154" t="s">
         <v>674</v>
       </c>
-      <c r="J31" s="139"/>
-      <c r="L31" s="134" t="s">
+      <c r="J31" s="155"/>
+      <c r="L31" s="164" t="s">
         <v>698</v>
       </c>
-      <c r="M31" s="134"/>
-      <c r="N31" s="134"/>
+      <c r="M31" s="164"/>
+      <c r="N31" s="164"/>
     </row>
     <row r="32" spans="1:14" ht="43.5" customHeight="1" thickBot="1">
       <c r="A32" s="81">
@@ -22403,29 +22922,29 @@
       <c r="B32" s="69" t="s">
         <v>631</v>
       </c>
-      <c r="C32" s="144" t="s">
+      <c r="C32" s="150" t="s">
         <v>632</v>
       </c>
-      <c r="D32" s="145"/>
+      <c r="D32" s="151"/>
       <c r="E32" s="70" t="s">
         <v>653</v>
       </c>
-      <c r="F32" s="138" t="s">
+      <c r="F32" s="154" t="s">
         <v>654</v>
       </c>
-      <c r="G32" s="139"/>
+      <c r="G32" s="155"/>
       <c r="H32" s="69" t="s">
         <v>675</v>
       </c>
-      <c r="I32" s="144" t="s">
+      <c r="I32" s="150" t="s">
         <v>676</v>
       </c>
-      <c r="J32" s="145"/>
-      <c r="L32" s="135" t="s">
+      <c r="J32" s="151"/>
+      <c r="L32" s="165" t="s">
         <v>699</v>
       </c>
-      <c r="M32" s="135"/>
-      <c r="N32" s="135"/>
+      <c r="M32" s="165"/>
+      <c r="N32" s="165"/>
     </row>
     <row r="33" spans="1:14" ht="31.5" customHeight="1" thickBot="1">
       <c r="A33" s="81">
@@ -22434,29 +22953,29 @@
       <c r="B33" s="70" t="s">
         <v>633</v>
       </c>
-      <c r="C33" s="138" t="s">
+      <c r="C33" s="154" t="s">
         <v>634</v>
       </c>
-      <c r="D33" s="139"/>
+      <c r="D33" s="155"/>
       <c r="E33" s="69" t="s">
         <v>655</v>
       </c>
-      <c r="F33" s="144" t="s">
+      <c r="F33" s="150" t="s">
         <v>656</v>
       </c>
-      <c r="G33" s="145"/>
+      <c r="G33" s="151"/>
       <c r="H33" s="70" t="s">
         <v>677</v>
       </c>
-      <c r="I33" s="146" t="s">
+      <c r="I33" s="156" t="s">
         <v>678</v>
       </c>
-      <c r="J33" s="147"/>
-      <c r="L33" s="134" t="s">
+      <c r="J33" s="157"/>
+      <c r="L33" s="164" t="s">
         <v>700</v>
       </c>
-      <c r="M33" s="134"/>
-      <c r="N33" s="134"/>
+      <c r="M33" s="164"/>
+      <c r="N33" s="164"/>
     </row>
     <row r="34" spans="1:14" ht="28.5" customHeight="1" thickBot="1">
       <c r="A34" s="81">
@@ -22465,29 +22984,29 @@
       <c r="B34" s="69" t="s">
         <v>635</v>
       </c>
-      <c r="C34" s="144" t="s">
+      <c r="C34" s="150" t="s">
         <v>636</v>
       </c>
-      <c r="D34" s="145"/>
+      <c r="D34" s="151"/>
       <c r="E34" s="70" t="s">
         <v>657</v>
       </c>
-      <c r="F34" s="138" t="s">
+      <c r="F34" s="154" t="s">
         <v>658</v>
       </c>
-      <c r="G34" s="139"/>
+      <c r="G34" s="155"/>
       <c r="H34" s="69" t="s">
         <v>679</v>
       </c>
-      <c r="I34" s="142" t="s">
+      <c r="I34" s="160" t="s">
         <v>680</v>
       </c>
-      <c r="J34" s="143"/>
-      <c r="L34" s="135" t="s">
+      <c r="J34" s="161"/>
+      <c r="L34" s="165" t="s">
         <v>701</v>
       </c>
-      <c r="M34" s="135"/>
-      <c r="N34" s="135"/>
+      <c r="M34" s="165"/>
+      <c r="N34" s="165"/>
     </row>
     <row r="35" spans="1:14" ht="31.5" customHeight="1" thickBot="1">
       <c r="A35" s="81">
@@ -22496,29 +23015,29 @@
       <c r="B35" s="70" t="s">
         <v>637</v>
       </c>
-      <c r="C35" s="138" t="s">
+      <c r="C35" s="154" t="s">
         <v>638</v>
       </c>
-      <c r="D35" s="139"/>
+      <c r="D35" s="155"/>
       <c r="E35" s="69" t="s">
         <v>659</v>
       </c>
-      <c r="F35" s="144" t="s">
+      <c r="F35" s="150" t="s">
         <v>660</v>
       </c>
-      <c r="G35" s="145"/>
+      <c r="G35" s="151"/>
       <c r="H35" s="77" t="s">
         <v>681</v>
       </c>
-      <c r="I35" s="138" t="s">
+      <c r="I35" s="154" t="s">
         <v>682</v>
       </c>
-      <c r="J35" s="139"/>
-      <c r="L35" s="134" t="s">
+      <c r="J35" s="155"/>
+      <c r="L35" s="164" t="s">
         <v>702</v>
       </c>
-      <c r="M35" s="134"/>
-      <c r="N35" s="134"/>
+      <c r="M35" s="164"/>
+      <c r="N35" s="164"/>
     </row>
     <row r="36" spans="1:14" ht="60.75" thickBot="1">
       <c r="A36" s="81">
@@ -22527,17 +23046,17 @@
       <c r="B36" s="69" t="s">
         <v>639</v>
       </c>
-      <c r="C36" s="144" t="s">
+      <c r="C36" s="150" t="s">
         <v>640</v>
       </c>
-      <c r="D36" s="145"/>
+      <c r="D36" s="151"/>
       <c r="E36" s="70" t="s">
         <v>661</v>
       </c>
-      <c r="F36" s="138" t="s">
+      <c r="F36" s="154" t="s">
         <v>662</v>
       </c>
-      <c r="G36" s="139"/>
+      <c r="G36" s="155"/>
       <c r="H36" s="78"/>
       <c r="I36" s="71" t="s">
         <v>683</v>
@@ -22545,11 +23064,11 @@
       <c r="J36" s="72" t="s">
         <v>684</v>
       </c>
-      <c r="L36" s="135" t="s">
+      <c r="L36" s="165" t="s">
         <v>703</v>
       </c>
-      <c r="M36" s="135"/>
-      <c r="N36" s="135"/>
+      <c r="M36" s="165"/>
+      <c r="N36" s="165"/>
     </row>
     <row r="37" spans="1:14" ht="75.75" thickBot="1">
       <c r="A37" s="81">
@@ -22558,17 +23077,17 @@
       <c r="B37" s="70" t="s">
         <v>641</v>
       </c>
-      <c r="C37" s="138" t="s">
+      <c r="C37" s="154" t="s">
         <v>642</v>
       </c>
-      <c r="D37" s="139"/>
+      <c r="D37" s="155"/>
       <c r="E37" s="69" t="s">
         <v>663</v>
       </c>
-      <c r="F37" s="144" t="s">
+      <c r="F37" s="150" t="s">
         <v>664</v>
       </c>
-      <c r="G37" s="145"/>
+      <c r="G37" s="151"/>
       <c r="H37" s="78"/>
       <c r="I37" s="73" t="s">
         <v>685</v>
@@ -22584,17 +23103,17 @@
       <c r="B38" s="69" t="s">
         <v>643</v>
       </c>
-      <c r="C38" s="144" t="s">
+      <c r="C38" s="150" t="s">
         <v>644</v>
       </c>
-      <c r="D38" s="145"/>
+      <c r="D38" s="151"/>
       <c r="E38" s="70" t="s">
         <v>665</v>
       </c>
-      <c r="F38" s="138" t="s">
+      <c r="F38" s="154" t="s">
         <v>666</v>
       </c>
-      <c r="G38" s="139"/>
+      <c r="G38" s="155"/>
       <c r="H38" s="78"/>
       <c r="I38" s="75" t="s">
         <v>687</v>
@@ -22610,40 +23129,46 @@
       <c r="B39" s="70" t="s">
         <v>692</v>
       </c>
-      <c r="C39" s="146" t="s">
+      <c r="C39" s="156" t="s">
         <v>693</v>
       </c>
-      <c r="D39" s="147"/>
+      <c r="D39" s="157"/>
       <c r="E39" s="69" t="s">
         <v>690</v>
       </c>
-      <c r="F39" s="142" t="s">
+      <c r="F39" s="160" t="s">
         <v>691</v>
       </c>
-      <c r="G39" s="143"/>
+      <c r="G39" s="161"/>
       <c r="H39" s="79"/>
-      <c r="I39" s="140" t="s">
+      <c r="I39" s="162" t="s">
         <v>689</v>
       </c>
-      <c r="J39" s="141"/>
+      <c r="J39" s="163"/>
     </row>
     <row r="40" spans="1:14" ht="58.5" customHeight="1"/>
     <row r="42" spans="1:14" ht="31.5" customHeight="1"/>
     <row r="43" spans="1:14" ht="31.5" customHeight="1"/>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F33:G33"/>
     <mergeCell ref="C39:D39"/>
     <mergeCell ref="I29:J29"/>
     <mergeCell ref="I30:J30"/>
@@ -22660,24 +23185,18 @@
     <mergeCell ref="F30:G30"/>
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="F32:G32"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
@@ -22710,8 +23229,9 @@
     <col min="8" max="8" width="17.42578125" customWidth="1"/>
     <col min="9" max="9" width="13.7109375" customWidth="1"/>
     <col min="10" max="11" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.85546875" customWidth="1"/>
-    <col min="13" max="14" width="25.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="31.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="25.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="81.28515625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="13.85546875" customWidth="1"/>
     <col min="17" max="17" width="12.85546875" bestFit="1" customWidth="1"/>
@@ -22820,6 +23340,10 @@
       <c r="F7" s="112" t="s">
         <v>919</v>
       </c>
+      <c r="I7" s="184" t="s">
+        <v>1171</v>
+      </c>
+      <c r="J7" s="184"/>
       <c r="L7" s="49" t="s">
         <v>601</v>
       </c>
@@ -22837,7 +23361,7 @@
       <c r="D8" s="32" t="s">
         <v>582</v>
       </c>
-      <c r="E8" s="32" t="s">
+      <c r="E8" s="185" t="s">
         <v>583</v>
       </c>
       <c r="F8" s="36" t="s">
@@ -22848,6 +23372,12 @@
       </c>
       <c r="H8" s="32" t="s">
         <v>415</v>
+      </c>
+      <c r="I8" s="32" t="s">
+        <v>777</v>
+      </c>
+      <c r="J8" s="32" t="s">
+        <v>754</v>
       </c>
       <c r="L8" s="9" t="s">
         <v>345</v>
@@ -22869,7 +23399,7 @@
       <c r="D9" s="85" t="s">
         <v>431</v>
       </c>
-      <c r="E9" s="92" t="s">
+      <c r="E9" s="64" t="s">
         <v>433</v>
       </c>
       <c r="F9" s="85" t="s">
@@ -22880,6 +23410,12 @@
       </c>
       <c r="H9" s="85" t="s">
         <v>466</v>
+      </c>
+      <c r="I9" s="119" t="s">
+        <v>752</v>
+      </c>
+      <c r="J9" s="119" t="s">
+        <v>755</v>
       </c>
       <c r="L9" s="9" t="s">
         <v>346</v>
@@ -22909,6 +23445,12 @@
       </c>
       <c r="H10" s="62" t="s">
         <v>454</v>
+      </c>
+      <c r="I10" s="62" t="s">
+        <v>452</v>
+      </c>
+      <c r="J10" s="62" t="s">
+        <v>452</v>
       </c>
       <c r="L10" s="9" t="s">
         <v>315</v>
@@ -22923,13 +23465,14 @@
       <c r="D11" s="85">
         <v>100</v>
       </c>
-      <c r="E11" s="92">
+      <c r="E11" s="64">
         <v>100</v>
       </c>
       <c r="F11" s="63"/>
       <c r="G11" s="63"/>
       <c r="H11" s="63"/>
-      <c r="I11" s="35"/>
+      <c r="I11" s="63"/>
+      <c r="J11" s="63"/>
       <c r="L11" s="9" t="s">
         <v>347</v>
       </c>
@@ -23140,10 +23683,10 @@
       <c r="L20" s="115" t="s">
         <v>568</v>
       </c>
-      <c r="M20" s="150" t="s">
+      <c r="M20" s="166" t="s">
         <v>921</v>
       </c>
-      <c r="N20" s="151"/>
+      <c r="N20" s="167"/>
     </row>
     <row r="21" spans="1:14">
       <c r="B21" s="85" t="s">
@@ -23248,66 +23791,73 @@
       <c r="B25" s="7" t="s">
         <v>620</v>
       </c>
-    </row>
-    <row r="26" spans="1:14" ht="15.75" thickBot="1"/>
+      <c r="F25" s="7" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="15.75" thickBot="1">
+      <c r="F26" s="7" t="s">
+        <v>1170</v>
+      </c>
+    </row>
     <row r="27" spans="1:14" ht="15.75" thickBot="1">
       <c r="B27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="C27" s="136" t="s">
+      <c r="C27" s="152" t="s">
         <v>622</v>
       </c>
-      <c r="D27" s="137"/>
+      <c r="D27" s="153"/>
       <c r="E27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="F27" s="136" t="s">
+      <c r="F27" s="152" t="s">
         <v>622</v>
       </c>
-      <c r="G27" s="137"/>
+      <c r="G27" s="153"/>
       <c r="H27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="I27" s="136" t="s">
+      <c r="I27" s="152" t="s">
         <v>622</v>
       </c>
-      <c r="J27" s="137"/>
-      <c r="L27" s="134" t="s">
+      <c r="J27" s="153"/>
+      <c r="L27" s="164" t="s">
         <v>694</v>
       </c>
-      <c r="M27" s="134"/>
-      <c r="N27" s="134"/>
-    </row>
-    <row r="28" spans="1:14" ht="16.5" thickBot="1">
+      <c r="M27" s="164"/>
+      <c r="N27" s="164"/>
+    </row>
+    <row r="28" spans="1:14" ht="49.5" customHeight="1" thickBot="1">
       <c r="A28" s="81">
         <v>1</v>
       </c>
       <c r="B28" s="69" t="s">
         <v>623</v>
       </c>
-      <c r="C28" s="144" t="s">
+      <c r="C28" s="150" t="s">
         <v>624</v>
       </c>
-      <c r="D28" s="145"/>
+      <c r="D28" s="151"/>
       <c r="E28" s="70" t="s">
         <v>645</v>
       </c>
-      <c r="F28" s="138" t="s">
-        <v>646</v>
-      </c>
-      <c r="G28" s="139"/>
+      <c r="F28" s="154" t="s">
+        <v>1183</v>
+      </c>
+      <c r="G28" s="155"/>
       <c r="H28" s="69" t="s">
         <v>667</v>
       </c>
-      <c r="I28" s="144" t="s">
+      <c r="I28" s="150" t="s">
         <v>668</v>
       </c>
-      <c r="J28" s="145"/>
-      <c r="L28" s="135" t="s">
+      <c r="J28" s="151"/>
+      <c r="L28" s="165" t="s">
         <v>695</v>
       </c>
-      <c r="M28" s="135"/>
-      <c r="N28" s="135"/>
+      <c r="M28" s="165"/>
+      <c r="N28" s="165"/>
     </row>
     <row r="29" spans="1:14" ht="31.5" thickBot="1">
       <c r="A29" s="81">
@@ -23316,29 +23866,29 @@
       <c r="B29" s="70" t="s">
         <v>625</v>
       </c>
-      <c r="C29" s="138" t="s">
+      <c r="C29" s="154" t="s">
         <v>626</v>
       </c>
-      <c r="D29" s="139"/>
+      <c r="D29" s="155"/>
       <c r="E29" s="69" t="s">
         <v>647</v>
       </c>
-      <c r="F29" s="144" t="s">
+      <c r="F29" s="150" t="s">
         <v>648</v>
       </c>
-      <c r="G29" s="145"/>
+      <c r="G29" s="151"/>
       <c r="H29" s="70" t="s">
         <v>669</v>
       </c>
-      <c r="I29" s="148" t="s">
+      <c r="I29" s="158" t="s">
         <v>670</v>
       </c>
-      <c r="J29" s="149"/>
-      <c r="L29" s="134" t="s">
+      <c r="J29" s="159"/>
+      <c r="L29" s="164" t="s">
         <v>696</v>
       </c>
-      <c r="M29" s="134"/>
-      <c r="N29" s="134"/>
+      <c r="M29" s="164"/>
+      <c r="N29" s="164"/>
     </row>
     <row r="30" spans="1:14" ht="15.75" thickBot="1">
       <c r="A30" s="81">
@@ -23347,29 +23897,29 @@
       <c r="B30" s="69" t="s">
         <v>627</v>
       </c>
-      <c r="C30" s="144" t="s">
+      <c r="C30" s="150" t="s">
         <v>628</v>
       </c>
-      <c r="D30" s="145"/>
+      <c r="D30" s="151"/>
       <c r="E30" s="70" t="s">
         <v>649</v>
       </c>
-      <c r="F30" s="138" t="s">
+      <c r="F30" s="154" t="s">
         <v>650</v>
       </c>
-      <c r="G30" s="139"/>
+      <c r="G30" s="155"/>
       <c r="H30" s="69" t="s">
         <v>671</v>
       </c>
-      <c r="I30" s="144" t="s">
+      <c r="I30" s="150" t="s">
         <v>672</v>
       </c>
-      <c r="J30" s="145"/>
-      <c r="L30" s="135" t="s">
+      <c r="J30" s="151"/>
+      <c r="L30" s="165" t="s">
         <v>697</v>
       </c>
-      <c r="M30" s="135"/>
-      <c r="N30" s="135"/>
+      <c r="M30" s="165"/>
+      <c r="N30" s="165"/>
     </row>
     <row r="31" spans="1:14" ht="17.25" customHeight="1" thickBot="1">
       <c r="A31" s="81">
@@ -23378,29 +23928,29 @@
       <c r="B31" s="70" t="s">
         <v>629</v>
       </c>
-      <c r="C31" s="138" t="s">
+      <c r="C31" s="154" t="s">
         <v>630</v>
       </c>
-      <c r="D31" s="139"/>
+      <c r="D31" s="155"/>
       <c r="E31" s="69" t="s">
         <v>651</v>
       </c>
-      <c r="F31" s="144" t="s">
+      <c r="F31" s="150" t="s">
         <v>652</v>
       </c>
-      <c r="G31" s="145"/>
+      <c r="G31" s="151"/>
       <c r="H31" s="70" t="s">
         <v>673</v>
       </c>
-      <c r="I31" s="138" t="s">
+      <c r="I31" s="154" t="s">
         <v>674</v>
       </c>
-      <c r="J31" s="139"/>
-      <c r="L31" s="134" t="s">
+      <c r="J31" s="155"/>
+      <c r="L31" s="164" t="s">
         <v>698</v>
       </c>
-      <c r="M31" s="134"/>
-      <c r="N31" s="134"/>
+      <c r="M31" s="164"/>
+      <c r="N31" s="164"/>
     </row>
     <row r="32" spans="1:14" ht="43.5" customHeight="1" thickBot="1">
       <c r="A32" s="81">
@@ -23409,29 +23959,29 @@
       <c r="B32" s="69" t="s">
         <v>631</v>
       </c>
-      <c r="C32" s="144" t="s">
+      <c r="C32" s="150" t="s">
         <v>632</v>
       </c>
-      <c r="D32" s="145"/>
+      <c r="D32" s="151"/>
       <c r="E32" s="70" t="s">
         <v>653</v>
       </c>
-      <c r="F32" s="138" t="s">
+      <c r="F32" s="154" t="s">
         <v>654</v>
       </c>
-      <c r="G32" s="139"/>
+      <c r="G32" s="155"/>
       <c r="H32" s="69" t="s">
         <v>675</v>
       </c>
-      <c r="I32" s="144" t="s">
+      <c r="I32" s="150" t="s">
         <v>676</v>
       </c>
-      <c r="J32" s="145"/>
-      <c r="L32" s="135" t="s">
+      <c r="J32" s="151"/>
+      <c r="L32" s="165" t="s">
         <v>699</v>
       </c>
-      <c r="M32" s="135"/>
-      <c r="N32" s="135"/>
+      <c r="M32" s="165"/>
+      <c r="N32" s="165"/>
     </row>
     <row r="33" spans="1:14" ht="31.5" customHeight="1" thickBot="1">
       <c r="A33" s="81">
@@ -23440,29 +23990,29 @@
       <c r="B33" s="70" t="s">
         <v>633</v>
       </c>
-      <c r="C33" s="138" t="s">
+      <c r="C33" s="154" t="s">
         <v>634</v>
       </c>
-      <c r="D33" s="139"/>
+      <c r="D33" s="155"/>
       <c r="E33" s="69" t="s">
         <v>655</v>
       </c>
-      <c r="F33" s="144" t="s">
+      <c r="F33" s="150" t="s">
         <v>656</v>
       </c>
-      <c r="G33" s="145"/>
+      <c r="G33" s="151"/>
       <c r="H33" s="70" t="s">
         <v>677</v>
       </c>
-      <c r="I33" s="146" t="s">
+      <c r="I33" s="156" t="s">
         <v>678</v>
       </c>
-      <c r="J33" s="147"/>
-      <c r="L33" s="134" t="s">
+      <c r="J33" s="157"/>
+      <c r="L33" s="164" t="s">
         <v>700</v>
       </c>
-      <c r="M33" s="134"/>
-      <c r="N33" s="134"/>
+      <c r="M33" s="164"/>
+      <c r="N33" s="164"/>
     </row>
     <row r="34" spans="1:14" ht="28.5" customHeight="1" thickBot="1">
       <c r="A34" s="81">
@@ -23471,29 +24021,29 @@
       <c r="B34" s="69" t="s">
         <v>635</v>
       </c>
-      <c r="C34" s="144" t="s">
+      <c r="C34" s="150" t="s">
         <v>636</v>
       </c>
-      <c r="D34" s="145"/>
+      <c r="D34" s="151"/>
       <c r="E34" s="70" t="s">
         <v>657</v>
       </c>
-      <c r="F34" s="138" t="s">
+      <c r="F34" s="154" t="s">
         <v>658</v>
       </c>
-      <c r="G34" s="139"/>
+      <c r="G34" s="155"/>
       <c r="H34" s="69" t="s">
         <v>679</v>
       </c>
-      <c r="I34" s="142" t="s">
+      <c r="I34" s="160" t="s">
         <v>680</v>
       </c>
-      <c r="J34" s="143"/>
-      <c r="L34" s="135" t="s">
+      <c r="J34" s="161"/>
+      <c r="L34" s="165" t="s">
         <v>701</v>
       </c>
-      <c r="M34" s="135"/>
-      <c r="N34" s="135"/>
+      <c r="M34" s="165"/>
+      <c r="N34" s="165"/>
     </row>
     <row r="35" spans="1:14" ht="31.5" customHeight="1" thickBot="1">
       <c r="A35" s="81">
@@ -23502,29 +24052,29 @@
       <c r="B35" s="70" t="s">
         <v>637</v>
       </c>
-      <c r="C35" s="138" t="s">
+      <c r="C35" s="154" t="s">
         <v>638</v>
       </c>
-      <c r="D35" s="139"/>
+      <c r="D35" s="155"/>
       <c r="E35" s="69" t="s">
         <v>659</v>
       </c>
-      <c r="F35" s="144" t="s">
+      <c r="F35" s="150" t="s">
         <v>660</v>
       </c>
-      <c r="G35" s="145"/>
+      <c r="G35" s="151"/>
       <c r="H35" s="77" t="s">
         <v>681</v>
       </c>
-      <c r="I35" s="138" t="s">
+      <c r="I35" s="154" t="s">
         <v>682</v>
       </c>
-      <c r="J35" s="139"/>
-      <c r="L35" s="134" t="s">
+      <c r="J35" s="155"/>
+      <c r="L35" s="164" t="s">
         <v>702</v>
       </c>
-      <c r="M35" s="134"/>
-      <c r="N35" s="134"/>
+      <c r="M35" s="164"/>
+      <c r="N35" s="164"/>
     </row>
     <row r="36" spans="1:14" ht="60.75" thickBot="1">
       <c r="A36" s="81">
@@ -23533,17 +24083,17 @@
       <c r="B36" s="69" t="s">
         <v>639</v>
       </c>
-      <c r="C36" s="144" t="s">
+      <c r="C36" s="150" t="s">
         <v>640</v>
       </c>
-      <c r="D36" s="145"/>
+      <c r="D36" s="151"/>
       <c r="E36" s="70" t="s">
         <v>661</v>
       </c>
-      <c r="F36" s="138" t="s">
+      <c r="F36" s="154" t="s">
         <v>662</v>
       </c>
-      <c r="G36" s="139"/>
+      <c r="G36" s="155"/>
       <c r="H36" s="78"/>
       <c r="I36" s="71" t="s">
         <v>683</v>
@@ -23551,11 +24101,11 @@
       <c r="J36" s="72" t="s">
         <v>684</v>
       </c>
-      <c r="L36" s="135" t="s">
+      <c r="L36" s="165" t="s">
         <v>703</v>
       </c>
-      <c r="M36" s="135"/>
-      <c r="N36" s="135"/>
+      <c r="M36" s="165"/>
+      <c r="N36" s="165"/>
     </row>
     <row r="37" spans="1:14" ht="75.75" thickBot="1">
       <c r="A37" s="81">
@@ -23564,17 +24114,17 @@
       <c r="B37" s="70" t="s">
         <v>641</v>
       </c>
-      <c r="C37" s="138" t="s">
+      <c r="C37" s="154" t="s">
         <v>642</v>
       </c>
-      <c r="D37" s="139"/>
+      <c r="D37" s="155"/>
       <c r="E37" s="69" t="s">
         <v>663</v>
       </c>
-      <c r="F37" s="144" t="s">
+      <c r="F37" s="150" t="s">
         <v>664</v>
       </c>
-      <c r="G37" s="145"/>
+      <c r="G37" s="151"/>
       <c r="H37" s="78"/>
       <c r="I37" s="73" t="s">
         <v>685</v>
@@ -23590,17 +24140,17 @@
       <c r="B38" s="69" t="s">
         <v>643</v>
       </c>
-      <c r="C38" s="144" t="s">
+      <c r="C38" s="150" t="s">
         <v>644</v>
       </c>
-      <c r="D38" s="145"/>
+      <c r="D38" s="151"/>
       <c r="E38" s="70" t="s">
         <v>665</v>
       </c>
-      <c r="F38" s="138" t="s">
+      <c r="F38" s="154" t="s">
         <v>666</v>
       </c>
-      <c r="G38" s="139"/>
+      <c r="G38" s="155"/>
       <c r="H38" s="78"/>
       <c r="I38" s="75" t="s">
         <v>687</v>
@@ -23616,22 +24166,22 @@
       <c r="B39" s="70" t="s">
         <v>692</v>
       </c>
-      <c r="C39" s="146" t="s">
+      <c r="C39" s="156" t="s">
         <v>693</v>
       </c>
-      <c r="D39" s="147"/>
+      <c r="D39" s="157"/>
       <c r="E39" s="69" t="s">
         <v>690</v>
       </c>
-      <c r="F39" s="142" t="s">
+      <c r="F39" s="160" t="s">
         <v>691</v>
       </c>
-      <c r="G39" s="143"/>
+      <c r="G39" s="161"/>
       <c r="H39" s="79"/>
-      <c r="I39" s="140" t="s">
+      <c r="I39" s="162" t="s">
         <v>689</v>
       </c>
-      <c r="J39" s="141"/>
+      <c r="J39" s="163"/>
     </row>
     <row r="40" spans="1:14" ht="58.5" customHeight="1"/>
     <row r="41" spans="1:14">
@@ -23746,7 +24296,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="46" spans="1:14" ht="20.25" customHeight="1">
+    <row r="46" spans="1:14" ht="45">
       <c r="C46" t="s">
         <v>765</v>
       </c>
@@ -23810,8 +24360,8 @@
       <c r="B49" s="85" t="s">
         <v>429</v>
       </c>
-      <c r="C49" s="85" t="s">
-        <v>429</v>
+      <c r="C49" s="119" t="s">
+        <v>752</v>
       </c>
       <c r="D49" s="85" t="s">
         <v>762</v>
@@ -23835,7 +24385,7 @@
         <v>458</v>
       </c>
       <c r="C50" s="62" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="D50" s="62" t="s">
         <v>452</v>
@@ -23924,7 +24474,45 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="47">
+  <mergeCells count="48">
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="L35:N35"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="F36:G36"/>
     <mergeCell ref="L36:N36"/>
@@ -23935,43 +24523,6 @@
     <mergeCell ref="F38:G38"/>
     <mergeCell ref="C39:D39"/>
     <mergeCell ref="F39:G39"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="L27:N27"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
@@ -23982,8 +24533,10 @@
     <hyperlink ref="C39" r:id="rId5" display="https://httpd.apache.org/docs/2.4/ko/mod/mod_logio.html" xr:uid="{00000000-0004-0000-0400-000004000000}"/>
     <hyperlink ref="N45" r:id="rId6" xr:uid="{00000000-0004-0000-0400-000005000000}"/>
     <hyperlink ref="N47" r:id="rId7" xr:uid="{00000000-0004-0000-0400-000006000000}"/>
+    <hyperlink ref="F25" r:id="rId8" location="get_queryset" display="http://www.cdrf.co/3.1/rest_framework.viewsets/ModelViewSet.html - get_queryset" xr:uid="{18731035-636B-4224-A441-F48B2BAB6B00}"/>
+    <hyperlink ref="F26" r:id="rId9" xr:uid="{CA52AF34-938E-473A-9B54-35DD9A569DF0}"/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="50" orientation="landscape" r:id="rId8"/>
+  <pageSetup paperSize="9" scale="50" orientation="landscape" r:id="rId10"/>
 </worksheet>
 </file>
--- a/2020_LogAnalyzer_Leeheesuk.xlsx
+++ b/2020_LogAnalyzer_Leeheesuk.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="22827"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEF1774C-93EE-4777-837A-3E6E0AA66876}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1E40A86-166D-4A09-A8EA-E93242DD895C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1590" yWindow="345" windowWidth="25035" windowHeight="12255" firstSheet="8" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UI" sheetId="7" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1918" uniqueCount="1206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1957" uniqueCount="1224">
   <si>
     <t>구분</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -5429,9 +5429,6 @@
     <t>900KB</t>
   </si>
   <si>
-    <t>업로드시간(s) - DB</t>
-  </si>
-  <si>
     <t>access_log_900K</t>
   </si>
   <si>
@@ -5452,6 +5449,84 @@
   </si>
   <si>
     <t>4GB</t>
+  </si>
+  <si>
+    <t>8GB</t>
+  </si>
+  <si>
+    <t>UI에서 파일 업로드가 완료되는 시간도 고려해야 한다.</t>
+  </si>
+  <si>
+    <t>DB 업로드시간(s)
+파일업로드 이후..</t>
+  </si>
+  <si>
+    <t>Single</t>
+  </si>
+  <si>
+    <t>HOM1-W-F11.log.chunk100MB</t>
+  </si>
+  <si>
+    <t>Duration to create temporary csv : 13.121999025344849
+To DB, Total Duration : 18.975000381469727</t>
+  </si>
+  <si>
+    <t>300MB</t>
+  </si>
+  <si>
+    <t>Duration to create temporary csv : 36.633187770843506
+To DB, Total Duration : 56.910199880599976</t>
+  </si>
+  <si>
+    <t>HOM1-W-F11.log.chunk500MB</t>
+  </si>
+  <si>
+    <t>CPU 증설고려</t>
+  </si>
+  <si>
+    <t>664076 Lines</t>
+  </si>
+  <si>
+    <t>Duration to create temporary csv : 60.75799870491028
+To DB, Total Duration : 96.19961142539978</t>
+  </si>
+  <si>
+    <t>HOM1-W-F11.log.1GB</t>
+  </si>
+  <si>
+    <t>Duration to create temporary csv : 123.52013039588928
+To DB, Total Duration : 224.22548174858093</t>
+  </si>
+  <si>
+    <t>5312608 Lines</t>
+  </si>
+  <si>
+    <t>HOM1-W-F11.log.2GB</t>
+  </si>
+  <si>
+    <t>HOM1-W-F11.log.chunk300MB</t>
+  </si>
+  <si>
+    <t>2656304 Lines, 파일 전송시간 약 53s
+※ OSError: [Errno 28] No space left on device</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1328152  Lines
+※ Memory Error 떨어짐, 메모리 확보 후 테스트 재진행
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>※ 1GB 이상일때 MP 수행, 최적 시간 구할 것(사이즈, 시간)</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -5461,7 +5536,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
-  <fonts count="37">
+  <fonts count="39">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5721,6 +5796,22 @@
       <color rgb="FF171717"/>
       <name val="Segoe UI"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="15">
@@ -6084,7 +6175,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="191">
+  <cellXfs count="192">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6585,9 +6676,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6599,6 +6687,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -14335,6 +14429,55 @@
 
 <file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>15688</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2628034</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>148593</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ADFCAFFE-D5C5-45CC-B83D-F9CD3026B904}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="875179" y="4778188"/>
+          <a:ext cx="6929973" cy="3561905"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -14908,7 +15051,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -15587,54 +15730,54 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F01B713B-7546-4B5B-BF06-08BB58B1A0C8}">
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" customWidth="1"/>
     <col min="2" max="2" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29" customWidth="1"/>
     <col min="4" max="4" width="10.42578125" customWidth="1"/>
     <col min="5" max="5" width="66.7109375" customWidth="1"/>
     <col min="6" max="6" width="12.85546875" style="81" customWidth="1"/>
-    <col min="7" max="7" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="60.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29.85546875" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" style="81" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="60.42578125" style="182" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="186" t="s">
+    <row r="1" spans="1:10" ht="30">
+      <c r="A1" s="190" t="s">
         <v>848</v>
       </c>
-      <c r="B1" s="186" t="s">
+      <c r="B1" s="190" t="s">
         <v>1174</v>
       </c>
-      <c r="C1" s="186" t="s">
+      <c r="C1" s="190" t="s">
         <v>640</v>
       </c>
-      <c r="D1" s="186" t="s">
+      <c r="D1" s="190" t="s">
         <v>1177</v>
       </c>
-      <c r="E1" s="186" t="s">
+      <c r="E1" s="190" t="s">
         <v>1172</v>
       </c>
-      <c r="F1" s="186" t="s">
+      <c r="F1" s="190" t="s">
         <v>1173</v>
       </c>
-      <c r="G1" s="186" t="s">
-        <v>1198</v>
-      </c>
-      <c r="H1" s="186" t="s">
+      <c r="G1" s="191" t="s">
+        <v>1207</v>
+      </c>
+      <c r="H1" s="190" t="s">
         <v>1181</v>
       </c>
-      <c r="I1" s="186" t="s">
+      <c r="I1" s="190" t="s">
         <v>1187</v>
       </c>
-      <c r="J1" s="186" t="s">
+      <c r="J1" s="190" t="s">
         <v>1193</v>
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="187">
+      <c r="A2" s="186">
         <v>44028</v>
       </c>
       <c r="B2" s="8" t="s">
@@ -15661,19 +15804,19 @@
       <c r="I2" s="118" t="s">
         <v>895</v>
       </c>
-      <c r="J2" s="188" t="s">
-        <v>1200</v>
+      <c r="J2" s="187" t="s">
+        <v>1199</v>
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="187">
+      <c r="A3" s="186">
         <v>44028</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>1184</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="D3" s="118" t="s">
         <v>1178</v>
@@ -15693,10 +15836,10 @@
       <c r="I3" s="118" t="s">
         <v>895</v>
       </c>
-      <c r="J3" s="189"/>
+      <c r="J3" s="188"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="187">
+      <c r="A4" s="186">
         <v>44029</v>
       </c>
       <c r="B4" s="8" t="s">
@@ -15721,10 +15864,10 @@
       <c r="I4" s="118" t="s">
         <v>895</v>
       </c>
-      <c r="J4" s="189"/>
+      <c r="J4" s="188"/>
     </row>
     <row r="5" spans="1:10" ht="45">
-      <c r="A5" s="187">
+      <c r="A5" s="186">
         <v>44029</v>
       </c>
       <c r="B5" s="8" t="s">
@@ -15749,104 +15892,199 @@
       <c r="I5" s="118" t="s">
         <v>895</v>
       </c>
-      <c r="J5" s="190"/>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="182"/>
-      <c r="B6" s="182"/>
-      <c r="C6" s="182"/>
-      <c r="D6" s="182"/>
-      <c r="E6" s="182"/>
-      <c r="F6" s="183" t="s">
+      <c r="J5" s="189"/>
+    </row>
+    <row r="6" spans="1:10" ht="60">
+      <c r="A6" s="186">
+        <v>44029</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>1209</v>
+      </c>
+      <c r="D6" s="118" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>1196</v>
+      </c>
+      <c r="F6" s="118" t="s">
+        <v>1200</v>
+      </c>
+      <c r="G6" s="18" t="s">
+        <v>1210</v>
+      </c>
+      <c r="H6" s="118" t="s">
+        <v>1208</v>
+      </c>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="60">
+      <c r="A7" s="186">
+        <v>44029</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>1221</v>
+      </c>
+      <c r="D7" s="118" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>1196</v>
+      </c>
+      <c r="F7" s="118" t="s">
+        <v>1211</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>1212</v>
+      </c>
+      <c r="H7" s="118" t="s">
+        <v>1208</v>
+      </c>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+    </row>
+    <row r="8" spans="1:10" ht="60">
+      <c r="A8" s="186">
+        <v>44029</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>1213</v>
+      </c>
+      <c r="D8" s="118" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>1196</v>
+      </c>
+      <c r="F8" s="118" t="s">
         <v>1201</v>
       </c>
-      <c r="G6" s="182"/>
-      <c r="H6" s="182"/>
-      <c r="I6" s="182"/>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="182"/>
-      <c r="B7" s="182"/>
-      <c r="C7" s="182"/>
-      <c r="D7" s="182"/>
-      <c r="E7" s="182"/>
-      <c r="F7" s="183" t="s">
+      <c r="G8" s="18" t="s">
+        <v>1216</v>
+      </c>
+      <c r="H8" s="118" t="s">
+        <v>1208</v>
+      </c>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8" t="s">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="60">
+      <c r="A9" s="186">
+        <v>44029</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D9" s="118" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>1196</v>
+      </c>
+      <c r="F9" s="118" t="s">
         <v>1202</v>
       </c>
-      <c r="G7" s="182"/>
-      <c r="H7" s="182"/>
-      <c r="I7" s="182"/>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="182"/>
-      <c r="B8" s="182"/>
-      <c r="C8" s="182"/>
-      <c r="D8" s="182"/>
-      <c r="E8" s="182"/>
-      <c r="F8" s="183" t="s">
+      <c r="G9" s="18" t="s">
+        <v>1218</v>
+      </c>
+      <c r="H9" s="118" t="s">
+        <v>1208</v>
+      </c>
+      <c r="I9" s="8"/>
+      <c r="J9" s="18" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="45">
+      <c r="A10" s="186">
+        <v>44029</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D10" s="118" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>1196</v>
+      </c>
+      <c r="F10" s="118" t="s">
         <v>1203</v>
       </c>
-      <c r="G8" s="182"/>
-      <c r="H8" s="182"/>
-      <c r="I8" s="182"/>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="182"/>
-      <c r="B9" s="182"/>
-      <c r="C9" s="182"/>
-      <c r="D9" s="182"/>
-      <c r="E9" s="182"/>
-      <c r="F9" s="183" t="s">
+      <c r="G10" s="8"/>
+      <c r="H10" s="118" t="s">
+        <v>1208</v>
+      </c>
+      <c r="I10" s="8"/>
+      <c r="J10" s="18" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="118" t="s">
         <v>1204</v>
       </c>
-      <c r="G9" s="182"/>
-      <c r="H9" s="182"/>
-      <c r="I9" s="182"/>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="182"/>
-      <c r="B10" s="182"/>
-      <c r="C10" s="182"/>
-      <c r="D10" s="182"/>
-      <c r="E10" s="182"/>
-      <c r="F10" s="183" t="s">
+      <c r="G11" s="8"/>
+      <c r="H11" s="118" t="s">
+        <v>1208</v>
+      </c>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="118" t="s">
         <v>1205</v>
       </c>
-      <c r="G10" s="182"/>
-      <c r="H10" s="182"/>
-      <c r="I10" s="182"/>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="182"/>
-      <c r="B11" s="182"/>
-      <c r="C11" s="182"/>
-      <c r="D11" s="182"/>
-      <c r="E11" s="182"/>
-      <c r="F11" s="183"/>
-      <c r="G11" s="182"/>
-      <c r="H11" s="182"/>
-      <c r="I11" s="182"/>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="182"/>
-      <c r="B12" s="182"/>
-      <c r="C12" s="182"/>
-      <c r="D12" s="182"/>
-      <c r="E12" s="182"/>
-      <c r="F12" s="183"/>
-      <c r="G12" s="182"/>
-      <c r="H12" s="182"/>
-      <c r="I12" s="182"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="118" t="s">
+        <v>1208</v>
+      </c>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="182"/>
       <c r="B13" s="182"/>
       <c r="C13" s="182"/>
       <c r="D13" s="182"/>
-      <c r="E13" s="182"/>
+      <c r="E13" s="182" t="s">
+        <v>1214</v>
+      </c>
       <c r="F13" s="183"/>
       <c r="G13" s="182"/>
-      <c r="H13" s="182"/>
+      <c r="H13" s="183"/>
       <c r="I13" s="182"/>
     </row>
     <row r="14" spans="1:10">
@@ -15857,7 +16095,7 @@
       <c r="E14" s="182"/>
       <c r="F14" s="183"/>
       <c r="G14" s="182"/>
-      <c r="H14" s="182"/>
+      <c r="H14" s="183"/>
       <c r="I14" s="182"/>
     </row>
     <row r="15" spans="1:10">
@@ -15868,7 +16106,7 @@
       <c r="E15" s="182"/>
       <c r="F15" s="183"/>
       <c r="G15" s="182"/>
-      <c r="H15" s="182"/>
+      <c r="H15" s="183"/>
       <c r="I15" s="182"/>
     </row>
     <row r="16" spans="1:10">
@@ -15879,8 +16117,19 @@
       <c r="E16" s="182"/>
       <c r="F16" s="183"/>
       <c r="G16" s="182"/>
-      <c r="H16" s="182"/>
+      <c r="H16" s="183"/>
       <c r="I16" s="182"/>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="182"/>
+      <c r="B17" s="182"/>
+      <c r="C17" s="182"/>
+      <c r="D17" s="182"/>
+      <c r="E17" s="182"/>
+      <c r="F17" s="183"/>
+      <c r="G17" s="182"/>
+      <c r="H17" s="183"/>
+      <c r="I17" s="182"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -15888,6 +16137,7 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -17599,8 +17849,8 @@
   <cols>
     <col min="1" max="1" width="9.28515625" customWidth="1"/>
     <col min="2" max="2" width="26.5703125" customWidth="1"/>
-    <col min="7" max="7" width="64.5703125" customWidth="1"/>
-    <col min="8" max="8" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="77.85546875" customWidth="1"/>
+    <col min="8" max="8" width="30.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8.85546875" customWidth="1"/>
   </cols>
   <sheetData>

--- a/2020_LogAnalyzer_Leeheesuk.xlsx
+++ b/2020_LogAnalyzer_Leeheesuk.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="22827"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1E40A86-166D-4A09-A8EA-E93242DD895C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72130773-F0C9-492F-BC86-F2E36F76932E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1590" yWindow="345" windowWidth="25035" windowHeight="12255" firstSheet="8" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" firstSheet="10" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UI" sheetId="7" r:id="rId1"/>
@@ -17,12 +17,12 @@
     <sheet name="Table" sheetId="10" r:id="rId7"/>
     <sheet name="Table_0408" sheetId="15" r:id="rId8"/>
     <sheet name="Table_0619_0429" sheetId="16" r:id="rId9"/>
-    <sheet name="LogFile Test_0717" sheetId="22" r:id="rId10"/>
-    <sheet name="Pilot" sheetId="11" r:id="rId11"/>
-    <sheet name="아키텍처" sheetId="9" r:id="rId12"/>
-    <sheet name="기능요건" sheetId="8" r:id="rId13"/>
-    <sheet name="기능요건_0401피드백" sheetId="14" r:id="rId14"/>
-    <sheet name="비기능요건" sheetId="6" r:id="rId15"/>
+    <sheet name="Pilot" sheetId="11" r:id="rId10"/>
+    <sheet name="아키텍처" sheetId="9" r:id="rId11"/>
+    <sheet name="기능요건" sheetId="8" r:id="rId12"/>
+    <sheet name="기능요건_0401피드백" sheetId="14" r:id="rId13"/>
+    <sheet name="비기능요건" sheetId="6" r:id="rId14"/>
+    <sheet name="성능테스트_0717" sheetId="22" r:id="rId15"/>
     <sheet name="지원포맷" sheetId="1" r:id="rId16"/>
     <sheet name="로그로맷 항목설명" sheetId="21" r:id="rId17"/>
     <sheet name="고려사항" sheetId="5" r:id="rId18"/>
@@ -31,7 +31,7 @@
     <sheet name="기능 - goaccess" sheetId="3" r:id="rId21"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="12">기능요건!$A$1:$M$45</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="11">기능요건!$A$1:$M$45</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1957" uniqueCount="1224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2009" uniqueCount="1261">
   <si>
     <t>구분</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3960,10 +3960,6 @@
   </si>
   <si>
     <t>세부 Steps : 전체 line 수 세기 -&gt; process 수만큼 병렬처리 -&gt; csv 파일생성</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>8G가능(combined IO 기준 480s)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -5481,12 +5477,6 @@
     <t>HOM1-W-F11.log.chunk500MB</t>
   </si>
   <si>
-    <t>CPU 증설고려</t>
-  </si>
-  <si>
-    <t>664076 Lines</t>
-  </si>
-  <si>
     <t>Duration to create temporary csv : 60.75799870491028
 To DB, Total Duration : 96.19961142539978</t>
   </si>
@@ -5498,6 +5488,9 @@
 To DB, Total Duration : 224.22548174858093</t>
   </si>
   <si>
+    <t>2656304 Lines</t>
+  </si>
+  <si>
     <t>5312608 Lines</t>
   </si>
   <si>
@@ -5507,12 +5500,115 @@
     <t>HOM1-W-F11.log.chunk300MB</t>
   </si>
   <si>
-    <t>2656304 Lines, 파일 전송시간 약 53s
-※ OSError: [Errno 28] No space left on device</t>
+    <t>CPU, Memory 증설 필요</t>
+  </si>
+  <si>
+    <t>MP</t>
+  </si>
+  <si>
+    <t>TODO</t>
+  </si>
+  <si>
+    <t>process 수</t>
+  </si>
+  <si>
+    <t>## df 나누어 읽기 : 총 작업 시간 15.459</t>
+  </si>
+  <si>
+    <t>## df 나누어 읽기 : 총 작업 시간 18.069</t>
+  </si>
+  <si>
+    <t>## df 나누어 읽기 : 총 작업 시간 46.7167</t>
+  </si>
+  <si>
+    <t>파일생성 시간</t>
+  </si>
+  <si>
+    <t>## df 나누어 읽기 : 총 작업 시간 55.5753</t>
+  </si>
+  <si>
+    <t>## df 나누어 읽기 : 총 작업 시간 107.0229</t>
+  </si>
+  <si>
+    <t>## df 나누어 읽기 : 총 작업 시간 91.2467</t>
+  </si>
+  <si>
+    <t>목표시간 : 2GB 기준, 300s (5m)</t>
+  </si>
+  <si>
+    <t>7/17/2020
+7/20/2020</t>
+  </si>
+  <si>
+    <t>11677321 Lines</t>
+  </si>
+  <si>
+    <t>## df 나누어 읽기 : 총 작업 시간 504.1735</t>
+  </si>
+  <si>
+    <t>## df 나누어 읽기 : 총 작업 시간 408.6061</t>
+  </si>
+  <si>
+    <t>## df 나누어 읽기 : 총 작업 시간 46.4991</t>
+  </si>
+  <si>
+    <t>## df 나누어 읽기 : 총 작업 시간 87.7165</t>
+  </si>
+  <si>
+    <t>1GB 네트웍시간</t>
+  </si>
+  <si>
+    <t>17s</t>
+  </si>
+  <si>
+    <t>dataframe 가공</t>
+  </si>
+  <si>
+    <t>dataframe으로 읽기(from_csv)</t>
+  </si>
+  <si>
+    <t>csv 파일 생성(to_csv)</t>
+  </si>
+  <si>
+    <t>postgres copy 로 INSERT</t>
+  </si>
+  <si>
+    <t>INSERT
+FLOW</t>
+  </si>
+  <si>
+    <t>StringIO</t>
+  </si>
+  <si>
+    <t>Duration to create temporary csv : 54.79590201377869
+To DB, Total Duration : 92.77517986297607</t>
+  </si>
+  <si>
+    <t>Memory Error</t>
+  </si>
+  <si>
+    <t>Duration to create temporary csv : 241.90100407600403
+To DB, Total Duration : 626.6962890625</t>
+  </si>
+  <si>
+    <t>1GB
+(기준)</t>
+  </si>
+  <si>
+    <t>2656304 Lines, , 파일 전송시간 약 2.6m(150s)
+[Errno 28] No space left on device</t>
+  </si>
+  <si>
+    <t>차후 고려</t>
+  </si>
+  <si>
+    <t>664076 Lines
+* goaccess와 비슷한 수준, apache log viewer는 라인 한계 존재
+  (12172 라인 등, 숫자는 변경됨)</t>
   </si>
   <si>
     <r>
-      <t xml:space="preserve">1328152  Lines
+      <t xml:space="preserve">1328152  Lines, , 파일 전송시간 약 53s
 ※ Memory Error 떨어짐, 메모리 확보 후 테스트 재진행
 </t>
     </r>
@@ -5525,8 +5621,29 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>※ 1GB 이상일때 MP 수행, 최적 시간 구할 것(사이즈, 시간)</t>
+      <t>※ 1GB 이상일때 MP 수행 필요한가? - 성능상 이점이 적음</t>
     </r>
+  </si>
+  <si>
+    <t>8G가능(combined IO 기준 480s)</t>
+  </si>
+  <si>
+    <t>Parsing Only</t>
+  </si>
+  <si>
+    <t>MP 테스트</t>
+  </si>
+  <si>
+    <t>access log 파일 준비</t>
+  </si>
+  <si>
+    <t>File I/O</t>
+  </si>
+  <si>
+    <t>CPU 연산 : MP 효과 구간</t>
+  </si>
+  <si>
+    <t>Network + DB I/O</t>
   </si>
 </sst>
 </file>
@@ -6175,7 +6292,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="192">
+  <cellXfs count="204">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6478,6 +6595,9 @@
     <xf numFmtId="0" fontId="16" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6693,6 +6813,39 @@
     </xf>
     <xf numFmtId="0" fontId="37" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -14429,55 +14582,6 @@
 
 <file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>15688</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>2628034</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>148593</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="그림 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ADFCAFFE-D5C5-45CC-B83D-F9CD3026B904}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="875179" y="4778188"/>
-          <a:ext cx="6929973" cy="3561905"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -15051,7 +15155,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -15265,6 +15369,55 @@
         <a:xfrm>
           <a:off x="9915526" y="2552701"/>
           <a:ext cx="3905250" cy="1181099"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>15688</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2628034</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>148593</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ADFCAFFE-D5C5-45CC-B83D-F9CD3026B904}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="875179" y="4778188"/>
+          <a:ext cx="6929973" cy="3561905"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -15622,51 +15775,51 @@
     </row>
     <row r="17" spans="1:13">
       <c r="J17" s="19"/>
-      <c r="K17" s="132" t="s">
+      <c r="K17" s="133" t="s">
         <v>537</v>
       </c>
-      <c r="L17" s="133"/>
-      <c r="M17" s="134"/>
+      <c r="L17" s="134"/>
+      <c r="M17" s="135"/>
     </row>
     <row r="18" spans="1:13">
       <c r="J18" s="19">
         <v>1</v>
       </c>
-      <c r="K18" s="135" t="s">
+      <c r="K18" s="136" t="s">
         <v>538</v>
       </c>
-      <c r="L18" s="136"/>
-      <c r="M18" s="137"/>
+      <c r="L18" s="137"/>
+      <c r="M18" s="138"/>
     </row>
     <row r="19" spans="1:13">
       <c r="J19" s="19">
         <v>2</v>
       </c>
-      <c r="K19" s="135" t="s">
+      <c r="K19" s="136" t="s">
         <v>539</v>
       </c>
-      <c r="L19" s="136"/>
-      <c r="M19" s="137"/>
+      <c r="L19" s="137"/>
+      <c r="M19" s="138"/>
     </row>
     <row r="20" spans="1:13">
       <c r="J20" s="19">
         <v>3</v>
       </c>
-      <c r="K20" s="135" t="s">
+      <c r="K20" s="136" t="s">
         <v>540</v>
       </c>
-      <c r="L20" s="136"/>
-      <c r="M20" s="137"/>
+      <c r="L20" s="137"/>
+      <c r="M20" s="138"/>
     </row>
     <row r="21" spans="1:13">
       <c r="J21" s="19">
         <v>4</v>
       </c>
-      <c r="K21" s="135" t="s">
+      <c r="K21" s="136" t="s">
         <v>541</v>
       </c>
-      <c r="L21" s="136"/>
-      <c r="M21" s="137"/>
+      <c r="L21" s="137"/>
+      <c r="M21" s="138"/>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="43" t="s">
@@ -15729,419 +15882,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F01B713B-7546-4B5B-BF06-08BB58B1A0C8}">
-  <dimension ref="A1:J17"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="12.28515625" customWidth="1"/>
-    <col min="2" max="2" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29" customWidth="1"/>
-    <col min="4" max="4" width="10.42578125" customWidth="1"/>
-    <col min="5" max="5" width="66.7109375" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" style="81" customWidth="1"/>
-    <col min="7" max="7" width="29.85546875" customWidth="1"/>
-    <col min="8" max="8" width="12.140625" style="81" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="60.42578125" style="182" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" ht="30">
-      <c r="A1" s="190" t="s">
-        <v>848</v>
-      </c>
-      <c r="B1" s="190" t="s">
-        <v>1174</v>
-      </c>
-      <c r="C1" s="190" t="s">
-        <v>640</v>
-      </c>
-      <c r="D1" s="190" t="s">
-        <v>1177</v>
-      </c>
-      <c r="E1" s="190" t="s">
-        <v>1172</v>
-      </c>
-      <c r="F1" s="190" t="s">
-        <v>1173</v>
-      </c>
-      <c r="G1" s="191" t="s">
-        <v>1207</v>
-      </c>
-      <c r="H1" s="190" t="s">
-        <v>1181</v>
-      </c>
-      <c r="I1" s="190" t="s">
-        <v>1187</v>
-      </c>
-      <c r="J1" s="190" t="s">
-        <v>1193</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="186">
-        <v>44028</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>1175</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>1176</v>
-      </c>
-      <c r="D2" s="118" t="s">
-        <v>1178</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>1180</v>
-      </c>
-      <c r="F2" s="118" t="s">
-        <v>1179</v>
-      </c>
-      <c r="G2" s="118">
-        <v>0.36</v>
-      </c>
-      <c r="H2" s="118" t="s">
-        <v>1182</v>
-      </c>
-      <c r="I2" s="118" t="s">
-        <v>895</v>
-      </c>
-      <c r="J2" s="187" t="s">
-        <v>1199</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="186">
-        <v>44028</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>1184</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>1198</v>
-      </c>
-      <c r="D3" s="118" t="s">
-        <v>1178</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>1185</v>
-      </c>
-      <c r="F3" s="118" t="s">
-        <v>1197</v>
-      </c>
-      <c r="G3" s="118">
-        <v>0.78</v>
-      </c>
-      <c r="H3" s="118" t="s">
-        <v>1186</v>
-      </c>
-      <c r="I3" s="118" t="s">
-        <v>895</v>
-      </c>
-      <c r="J3" s="188"/>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="186">
-        <v>44029</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>1189</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>1191</v>
-      </c>
-      <c r="D4" s="118" t="s">
-        <v>1178</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>1190</v>
-      </c>
-      <c r="F4" s="118" t="s">
-        <v>1192</v>
-      </c>
-      <c r="G4" s="118">
-        <v>5.83</v>
-      </c>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118" t="s">
-        <v>895</v>
-      </c>
-      <c r="J4" s="188"/>
-    </row>
-    <row r="5" spans="1:10" ht="45">
-      <c r="A5" s="186">
-        <v>44029</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>1188</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>1194</v>
-      </c>
-      <c r="D5" s="118" t="s">
-        <v>1178</v>
-      </c>
-      <c r="E5" s="18" t="s">
-        <v>1196</v>
-      </c>
-      <c r="F5" s="118" t="s">
-        <v>1195</v>
-      </c>
-      <c r="G5" s="118">
-        <v>2.21</v>
-      </c>
-      <c r="H5" s="118"/>
-      <c r="I5" s="118" t="s">
-        <v>895</v>
-      </c>
-      <c r="J5" s="189"/>
-    </row>
-    <row r="6" spans="1:10" ht="60">
-      <c r="A6" s="186">
-        <v>44029</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>1188</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>1209</v>
-      </c>
-      <c r="D6" s="118" t="s">
-        <v>1178</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>1196</v>
-      </c>
-      <c r="F6" s="118" t="s">
-        <v>1200</v>
-      </c>
-      <c r="G6" s="18" t="s">
-        <v>1210</v>
-      </c>
-      <c r="H6" s="118" t="s">
-        <v>1208</v>
-      </c>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8" t="s">
-        <v>1206</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="60">
-      <c r="A7" s="186">
-        <v>44029</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>1188</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>1221</v>
-      </c>
-      <c r="D7" s="118" t="s">
-        <v>1178</v>
-      </c>
-      <c r="E7" s="18" t="s">
-        <v>1196</v>
-      </c>
-      <c r="F7" s="118" t="s">
-        <v>1211</v>
-      </c>
-      <c r="G7" s="18" t="s">
-        <v>1212</v>
-      </c>
-      <c r="H7" s="118" t="s">
-        <v>1208</v>
-      </c>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-    </row>
-    <row r="8" spans="1:10" ht="60">
-      <c r="A8" s="186">
-        <v>44029</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>1188</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>1213</v>
-      </c>
-      <c r="D8" s="118" t="s">
-        <v>1178</v>
-      </c>
-      <c r="E8" s="18" t="s">
-        <v>1196</v>
-      </c>
-      <c r="F8" s="118" t="s">
-        <v>1201</v>
-      </c>
-      <c r="G8" s="18" t="s">
-        <v>1216</v>
-      </c>
-      <c r="H8" s="118" t="s">
-        <v>1208</v>
-      </c>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8" t="s">
-        <v>1215</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="60">
-      <c r="A9" s="186">
-        <v>44029</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>1188</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>1217</v>
-      </c>
-      <c r="D9" s="118" t="s">
-        <v>1178</v>
-      </c>
-      <c r="E9" s="18" t="s">
-        <v>1196</v>
-      </c>
-      <c r="F9" s="118" t="s">
-        <v>1202</v>
-      </c>
-      <c r="G9" s="18" t="s">
-        <v>1218</v>
-      </c>
-      <c r="H9" s="118" t="s">
-        <v>1208</v>
-      </c>
-      <c r="I9" s="8"/>
-      <c r="J9" s="18" t="s">
-        <v>1223</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="45">
-      <c r="A10" s="186">
-        <v>44029</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>1188</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>1220</v>
-      </c>
-      <c r="D10" s="118" t="s">
-        <v>1178</v>
-      </c>
-      <c r="E10" s="18" t="s">
-        <v>1196</v>
-      </c>
-      <c r="F10" s="118" t="s">
-        <v>1203</v>
-      </c>
-      <c r="G10" s="8"/>
-      <c r="H10" s="118" t="s">
-        <v>1208</v>
-      </c>
-      <c r="I10" s="8"/>
-      <c r="J10" s="18" t="s">
-        <v>1222</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="118" t="s">
-        <v>1204</v>
-      </c>
-      <c r="G11" s="8"/>
-      <c r="H11" s="118" t="s">
-        <v>1208</v>
-      </c>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8" t="s">
-        <v>1219</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="118" t="s">
-        <v>1205</v>
-      </c>
-      <c r="G12" s="8"/>
-      <c r="H12" s="118" t="s">
-        <v>1208</v>
-      </c>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="182"/>
-      <c r="B13" s="182"/>
-      <c r="C13" s="182"/>
-      <c r="D13" s="182"/>
-      <c r="E13" s="182" t="s">
-        <v>1214</v>
-      </c>
-      <c r="F13" s="183"/>
-      <c r="G13" s="182"/>
-      <c r="H13" s="183"/>
-      <c r="I13" s="182"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="182"/>
-      <c r="B14" s="182"/>
-      <c r="C14" s="182"/>
-      <c r="D14" s="182"/>
-      <c r="E14" s="182"/>
-      <c r="F14" s="183"/>
-      <c r="G14" s="182"/>
-      <c r="H14" s="183"/>
-      <c r="I14" s="182"/>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="182"/>
-      <c r="B15" s="182"/>
-      <c r="C15" s="182"/>
-      <c r="D15" s="182"/>
-      <c r="E15" s="182"/>
-      <c r="F15" s="183"/>
-      <c r="G15" s="182"/>
-      <c r="H15" s="183"/>
-      <c r="I15" s="182"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="182"/>
-      <c r="B16" s="182"/>
-      <c r="C16" s="182"/>
-      <c r="D16" s="182"/>
-      <c r="E16" s="182"/>
-      <c r="F16" s="183"/>
-      <c r="G16" s="182"/>
-      <c r="H16" s="183"/>
-      <c r="I16" s="182"/>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" s="182"/>
-      <c r="B17" s="182"/>
-      <c r="C17" s="182"/>
-      <c r="D17" s="182"/>
-      <c r="E17" s="182"/>
-      <c r="F17" s="183"/>
-      <c r="G17" s="182"/>
-      <c r="H17" s="183"/>
-      <c r="I17" s="182"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="J2:J5"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -16364,7 +16104,7 @@
         <v>487</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="F10" s="92" t="s">
         <v>502</v>
@@ -16387,7 +16127,7 @@
         <v>488</v>
       </c>
       <c r="E11" s="92" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="F11" s="92" t="s">
         <v>502</v>
@@ -16410,7 +16150,7 @@
         <v>489</v>
       </c>
       <c r="E12" s="92" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="F12" s="92" t="s">
         <v>502</v>
@@ -16433,7 +16173,7 @@
         <v>485</v>
       </c>
       <c r="E13" s="92" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="F13" s="92" t="s">
         <v>502</v>
@@ -16456,7 +16196,7 @@
         <v>486</v>
       </c>
       <c r="E14" s="92" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="F14" s="92" t="s">
         <v>502</v>
@@ -16479,7 +16219,7 @@
         <v>711</v>
       </c>
       <c r="E15" s="92" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="F15" s="92" t="s">
         <v>502</v>
@@ -16618,7 +16358,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -16636,7 +16376,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -16692,23 +16432,23 @@
         <v>560</v>
       </c>
       <c r="K1" s="26" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="M1" s="26" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="16.5" customHeight="1">
-      <c r="A2" s="168" t="s">
+      <c r="A2" s="169" t="s">
         <v>504</v>
       </c>
-      <c r="B2" s="174" t="s">
+      <c r="B2" s="175" t="s">
         <v>506</v>
       </c>
-      <c r="C2" s="168" t="s">
+      <c r="C2" s="169" t="s">
         <v>508</v>
       </c>
-      <c r="D2" s="168" t="s">
+      <c r="D2" s="169" t="s">
         <v>556</v>
       </c>
       <c r="E2" s="8"/>
@@ -16721,7 +16461,7 @@
       <c r="H2" s="10">
         <v>1</v>
       </c>
-      <c r="I2" s="121">
+      <c r="I2" s="122">
         <v>44043</v>
       </c>
       <c r="J2" s="10"/>
@@ -16731,10 +16471,10 @@
       </c>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" s="142"/>
-      <c r="B3" s="175"/>
-      <c r="C3" s="169"/>
-      <c r="D3" s="169"/>
+      <c r="A3" s="143"/>
+      <c r="B3" s="176"/>
+      <c r="C3" s="170"/>
+      <c r="D3" s="170"/>
       <c r="E3" s="11"/>
       <c r="F3" s="9" t="s">
         <v>310</v>
@@ -16745,7 +16485,7 @@
       <c r="H3" s="12">
         <v>2</v>
       </c>
-      <c r="I3" s="121"/>
+      <c r="I3" s="122"/>
       <c r="J3" s="10"/>
       <c r="K3" s="10"/>
       <c r="M3" s="19" t="s">
@@ -16753,10 +16493,10 @@
       </c>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="142"/>
-      <c r="B4" s="175"/>
-      <c r="C4" s="169"/>
-      <c r="D4" s="170"/>
+      <c r="A4" s="143"/>
+      <c r="B4" s="176"/>
+      <c r="C4" s="170"/>
+      <c r="D4" s="171"/>
       <c r="E4" s="11"/>
       <c r="F4" s="9" t="s">
         <v>311</v>
@@ -16767,14 +16507,14 @@
       <c r="H4" s="12">
         <v>2</v>
       </c>
-      <c r="I4" s="121"/>
+      <c r="I4" s="122"/>
       <c r="J4" s="10"/>
       <c r="K4" s="10"/>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" s="142"/>
-      <c r="B5" s="175"/>
-      <c r="C5" s="170"/>
+      <c r="A5" s="143"/>
+      <c r="B5" s="176"/>
+      <c r="C5" s="171"/>
       <c r="D5" s="46" t="s">
         <v>555</v>
       </c>
@@ -16786,9 +16526,9 @@
         <v>557</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>965</v>
-      </c>
-      <c r="I5" s="121">
+        <v>964</v>
+      </c>
+      <c r="I5" s="122">
         <v>44043</v>
       </c>
       <c r="J5" s="10" t="s">
@@ -16797,12 +16537,12 @@
       <c r="K5" s="10"/>
     </row>
     <row r="6" spans="1:16">
-      <c r="A6" s="142"/>
-      <c r="B6" s="175"/>
-      <c r="C6" s="168" t="s">
+      <c r="A6" s="143"/>
+      <c r="B6" s="176"/>
+      <c r="C6" s="169" t="s">
         <v>507</v>
       </c>
-      <c r="D6" s="168" t="s">
+      <c r="D6" s="169" t="s">
         <v>511</v>
       </c>
       <c r="E6" s="11"/>
@@ -16813,19 +16553,19 @@
         <v>317</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>966</v>
-      </c>
-      <c r="I6" s="121">
+        <v>965</v>
+      </c>
+      <c r="I6" s="122">
         <v>44043</v>
       </c>
       <c r="J6" s="10"/>
       <c r="K6" s="10"/>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="142"/>
-      <c r="B7" s="175"/>
-      <c r="C7" s="169"/>
-      <c r="D7" s="169"/>
+      <c r="A7" s="143"/>
+      <c r="B7" s="176"/>
+      <c r="C7" s="170"/>
+      <c r="D7" s="170"/>
       <c r="E7" s="11"/>
       <c r="F7" s="9" t="s">
         <v>313</v>
@@ -16836,17 +16576,17 @@
       <c r="H7" s="12">
         <v>1</v>
       </c>
-      <c r="I7" s="121">
+      <c r="I7" s="122">
         <v>44043</v>
       </c>
       <c r="J7" s="10"/>
       <c r="K7" s="10"/>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" s="142"/>
-      <c r="B8" s="175"/>
-      <c r="C8" s="169"/>
-      <c r="D8" s="169"/>
+      <c r="A8" s="143"/>
+      <c r="B8" s="176"/>
+      <c r="C8" s="170"/>
+      <c r="D8" s="170"/>
       <c r="E8" s="11"/>
       <c r="F8" s="9" t="s">
         <v>314</v>
@@ -16857,17 +16597,17 @@
       <c r="H8" s="12">
         <v>1</v>
       </c>
-      <c r="I8" s="121">
+      <c r="I8" s="122">
         <v>44043</v>
       </c>
       <c r="J8" s="10"/>
       <c r="K8" s="10"/>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9" s="142"/>
-      <c r="B9" s="175"/>
-      <c r="C9" s="169"/>
-      <c r="D9" s="169"/>
+      <c r="A9" s="143"/>
+      <c r="B9" s="176"/>
+      <c r="C9" s="170"/>
+      <c r="D9" s="170"/>
       <c r="E9" s="8"/>
       <c r="F9" s="9" t="s">
         <v>345</v>
@@ -16878,17 +16618,17 @@
       <c r="H9" s="10">
         <v>1</v>
       </c>
-      <c r="I9" s="121">
+      <c r="I9" s="122">
         <v>44043</v>
       </c>
       <c r="J9" s="10"/>
       <c r="K9" s="10"/>
     </row>
     <row r="10" spans="1:16">
-      <c r="A10" s="142"/>
-      <c r="B10" s="175"/>
-      <c r="C10" s="169"/>
-      <c r="D10" s="169"/>
+      <c r="A10" s="143"/>
+      <c r="B10" s="176"/>
+      <c r="C10" s="170"/>
+      <c r="D10" s="170"/>
       <c r="E10" s="8"/>
       <c r="F10" s="9" t="s">
         <v>346</v>
@@ -16899,17 +16639,17 @@
       <c r="H10" s="10">
         <v>1</v>
       </c>
-      <c r="I10" s="121">
+      <c r="I10" s="122">
         <v>44043</v>
       </c>
       <c r="J10" s="10"/>
       <c r="K10" s="10"/>
     </row>
     <row r="11" spans="1:16">
-      <c r="A11" s="142"/>
-      <c r="B11" s="175"/>
-      <c r="C11" s="169"/>
-      <c r="D11" s="169"/>
+      <c r="A11" s="143"/>
+      <c r="B11" s="176"/>
+      <c r="C11" s="170"/>
+      <c r="D11" s="170"/>
       <c r="E11" s="8"/>
       <c r="F11" s="9" t="s">
         <v>315</v>
@@ -16920,17 +16660,17 @@
       <c r="H11" s="10">
         <v>1</v>
       </c>
-      <c r="I11" s="121">
+      <c r="I11" s="122">
         <v>44043</v>
       </c>
       <c r="J11" s="10"/>
       <c r="K11" s="10"/>
     </row>
     <row r="12" spans="1:16" ht="16.5" customHeight="1">
-      <c r="A12" s="142"/>
-      <c r="B12" s="175"/>
-      <c r="C12" s="169"/>
-      <c r="D12" s="169"/>
+      <c r="A12" s="143"/>
+      <c r="B12" s="176"/>
+      <c r="C12" s="170"/>
+      <c r="D12" s="170"/>
       <c r="E12" s="8"/>
       <c r="F12" s="9" t="s">
         <v>347</v>
@@ -16941,17 +16681,17 @@
       <c r="H12" s="10">
         <v>1</v>
       </c>
-      <c r="I12" s="121">
+      <c r="I12" s="122">
         <v>44043</v>
       </c>
       <c r="J12" s="10"/>
       <c r="K12" s="10"/>
     </row>
     <row r="13" spans="1:16">
-      <c r="A13" s="142"/>
-      <c r="B13" s="175"/>
-      <c r="C13" s="169"/>
-      <c r="D13" s="169"/>
+      <c r="A13" s="143"/>
+      <c r="B13" s="176"/>
+      <c r="C13" s="170"/>
+      <c r="D13" s="170"/>
       <c r="E13" s="11"/>
       <c r="F13" s="9" t="s">
         <v>316</v>
@@ -16962,17 +16702,17 @@
       <c r="H13" s="12">
         <v>3</v>
       </c>
-      <c r="I13" s="121"/>
+      <c r="I13" s="122"/>
       <c r="J13" s="10" t="s">
         <v>563</v>
       </c>
       <c r="K13" s="10"/>
     </row>
     <row r="14" spans="1:16">
-      <c r="A14" s="142"/>
-      <c r="B14" s="175"/>
-      <c r="C14" s="169"/>
-      <c r="D14" s="170"/>
+      <c r="A14" s="143"/>
+      <c r="B14" s="176"/>
+      <c r="C14" s="170"/>
+      <c r="D14" s="171"/>
       <c r="E14" s="11"/>
       <c r="F14" s="9" t="s">
         <v>318</v>
@@ -16983,14 +16723,14 @@
       <c r="H14" s="12">
         <v>2</v>
       </c>
-      <c r="I14" s="121"/>
+      <c r="I14" s="122"/>
       <c r="J14" s="10"/>
       <c r="K14" s="10"/>
     </row>
     <row r="15" spans="1:16" ht="30">
-      <c r="A15" s="142"/>
-      <c r="B15" s="175"/>
-      <c r="C15" s="169"/>
+      <c r="A15" s="143"/>
+      <c r="B15" s="176"/>
+      <c r="C15" s="170"/>
       <c r="D15" s="22" t="s">
         <v>512</v>
       </c>
@@ -17004,27 +16744,27 @@
       <c r="H15" s="12">
         <v>1</v>
       </c>
-      <c r="I15" s="121">
+      <c r="I15" s="122">
         <v>44043</v>
       </c>
       <c r="J15" s="10"/>
       <c r="K15" s="10"/>
-      <c r="M15" s="124" t="s">
-        <v>853</v>
+      <c r="M15" s="125" t="s">
+        <v>852</v>
       </c>
       <c r="N15" s="91"/>
       <c r="O15" s="91"/>
       <c r="P15" s="91" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="15" customHeight="1">
-      <c r="A16" s="142"/>
-      <c r="B16" s="175"/>
-      <c r="C16" s="168" t="s">
+      <c r="A16" s="143"/>
+      <c r="B16" s="176"/>
+      <c r="C16" s="169" t="s">
         <v>509</v>
       </c>
-      <c r="D16" s="168" t="s">
+      <c r="D16" s="169" t="s">
         <v>513</v>
       </c>
       <c r="E16" s="11"/>
@@ -17037,7 +16777,7 @@
       <c r="H16" s="12">
         <v>1</v>
       </c>
-      <c r="I16" s="121">
+      <c r="I16" s="122">
         <v>44043</v>
       </c>
       <c r="J16" s="10"/>
@@ -17052,14 +16792,14 @@
         <v>1</v>
       </c>
       <c r="P16" s="91" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="142"/>
-      <c r="B17" s="175"/>
-      <c r="C17" s="169"/>
-      <c r="D17" s="169"/>
+      <c r="A17" s="143"/>
+      <c r="B17" s="176"/>
+      <c r="C17" s="170"/>
+      <c r="D17" s="170"/>
       <c r="E17" s="19"/>
       <c r="F17" s="9" t="s">
         <v>364</v>
@@ -17070,7 +16810,7 @@
       <c r="H17" s="12">
         <v>1</v>
       </c>
-      <c r="I17" s="121">
+      <c r="I17" s="122">
         <v>44043</v>
       </c>
       <c r="J17" s="10"/>
@@ -17086,21 +16826,21 @@
       </c>
     </row>
     <row r="18" spans="1:16">
-      <c r="A18" s="142"/>
-      <c r="B18" s="175"/>
-      <c r="C18" s="169"/>
-      <c r="D18" s="169"/>
+      <c r="A18" s="143"/>
+      <c r="B18" s="176"/>
+      <c r="C18" s="170"/>
+      <c r="D18" s="170"/>
       <c r="E18" s="19"/>
       <c r="F18" s="48" t="s">
         <v>559</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H18" s="10">
         <v>1</v>
       </c>
-      <c r="I18" s="121">
+      <c r="I18" s="122">
         <v>44043</v>
       </c>
       <c r="J18" s="10" t="s">
@@ -17118,10 +16858,10 @@
       </c>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="142"/>
-      <c r="B19" s="175"/>
-      <c r="C19" s="169"/>
-      <c r="D19" s="169"/>
+      <c r="A19" s="143"/>
+      <c r="B19" s="176"/>
+      <c r="C19" s="170"/>
+      <c r="D19" s="170"/>
       <c r="E19" s="8"/>
       <c r="F19" s="9" t="s">
         <v>332</v>
@@ -17132,7 +16872,7 @@
       <c r="H19" s="10">
         <v>1</v>
       </c>
-      <c r="I19" s="121">
+      <c r="I19" s="122">
         <v>44043</v>
       </c>
       <c r="J19" s="10"/>
@@ -17149,10 +16889,10 @@
       <c r="P19" s="91"/>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" s="142"/>
-      <c r="B20" s="175"/>
-      <c r="C20" s="169"/>
-      <c r="D20" s="169"/>
+      <c r="A20" s="143"/>
+      <c r="B20" s="176"/>
+      <c r="C20" s="170"/>
+      <c r="D20" s="170"/>
       <c r="E20" s="8"/>
       <c r="F20" s="9" t="s">
         <v>333</v>
@@ -17163,7 +16903,7 @@
       <c r="H20" s="10">
         <v>1</v>
       </c>
-      <c r="I20" s="121">
+      <c r="I20" s="122">
         <v>44043</v>
       </c>
       <c r="J20" s="10"/>
@@ -17180,10 +16920,10 @@
       <c r="P20" s="91"/>
     </row>
     <row r="21" spans="1:16" ht="16.5" customHeight="1">
-      <c r="A21" s="142"/>
-      <c r="B21" s="175"/>
-      <c r="C21" s="169"/>
-      <c r="D21" s="169"/>
+      <c r="A21" s="143"/>
+      <c r="B21" s="176"/>
+      <c r="C21" s="170"/>
+      <c r="D21" s="170"/>
       <c r="E21" s="14"/>
       <c r="F21" s="9" t="s">
         <v>334</v>
@@ -17194,13 +16934,13 @@
       <c r="H21" s="16">
         <v>3</v>
       </c>
-      <c r="I21" s="121"/>
+      <c r="I21" s="122"/>
       <c r="J21" s="10" t="s">
         <v>563</v>
       </c>
       <c r="K21" s="10"/>
       <c r="M21" s="99" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="N21" s="98" t="s">
         <v>361</v>
@@ -17209,14 +16949,14 @@
         <v>1</v>
       </c>
       <c r="P21" s="91" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
     </row>
     <row r="22" spans="1:16">
-      <c r="A22" s="142"/>
-      <c r="B22" s="175"/>
-      <c r="C22" s="169"/>
-      <c r="D22" s="169"/>
+      <c r="A22" s="143"/>
+      <c r="B22" s="176"/>
+      <c r="C22" s="170"/>
+      <c r="D22" s="170"/>
       <c r="E22" s="14"/>
       <c r="F22" s="9" t="s">
         <v>335</v>
@@ -17227,13 +16967,13 @@
       <c r="H22" s="16">
         <v>1</v>
       </c>
-      <c r="I22" s="121">
+      <c r="I22" s="122">
         <v>44043</v>
       </c>
       <c r="J22" s="10"/>
       <c r="K22" s="10"/>
       <c r="M22" s="101" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="N22" s="98" t="s">
         <v>362</v>
@@ -17242,14 +16982,14 @@
         <v>1</v>
       </c>
       <c r="P22" s="91" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="23" spans="1:16">
-      <c r="A23" s="142"/>
-      <c r="B23" s="175"/>
-      <c r="C23" s="169"/>
-      <c r="D23" s="169"/>
+      <c r="A23" s="143"/>
+      <c r="B23" s="176"/>
+      <c r="C23" s="170"/>
+      <c r="D23" s="170"/>
       <c r="E23" s="14"/>
       <c r="F23" s="9" t="s">
         <v>336</v>
@@ -17258,9 +16998,9 @@
         <v>369</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>966</v>
-      </c>
-      <c r="I23" s="121">
+        <v>965</v>
+      </c>
+      <c r="I23" s="122">
         <v>44043</v>
       </c>
       <c r="J23" s="10"/>
@@ -17272,15 +17012,15 @@
         <v>372</v>
       </c>
       <c r="O23" s="100" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="P23" s="91"/>
     </row>
     <row r="24" spans="1:16">
-      <c r="A24" s="142"/>
-      <c r="B24" s="175"/>
-      <c r="C24" s="169"/>
-      <c r="D24" s="169"/>
+      <c r="A24" s="143"/>
+      <c r="B24" s="176"/>
+      <c r="C24" s="170"/>
+      <c r="D24" s="170"/>
       <c r="E24" s="8"/>
       <c r="F24" s="9" t="s">
         <v>337</v>
@@ -17289,15 +17029,15 @@
         <v>370</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>966</v>
-      </c>
-      <c r="I24" s="121">
+        <v>965</v>
+      </c>
+      <c r="I24" s="122">
         <v>44043</v>
       </c>
       <c r="J24" s="10"/>
       <c r="K24" s="10"/>
-      <c r="M24" s="125" t="s">
-        <v>970</v>
+      <c r="M24" s="126" t="s">
+        <v>969</v>
       </c>
       <c r="N24" s="98" t="s">
         <v>371</v>
@@ -17308,10 +17048,10 @@
       <c r="P24" s="91"/>
     </row>
     <row r="25" spans="1:16">
-      <c r="A25" s="142"/>
-      <c r="B25" s="175"/>
-      <c r="C25" s="169"/>
-      <c r="D25" s="169"/>
+      <c r="A25" s="143"/>
+      <c r="B25" s="176"/>
+      <c r="C25" s="170"/>
+      <c r="D25" s="170"/>
       <c r="E25" s="8"/>
       <c r="F25" s="9" t="s">
         <v>373</v>
@@ -17322,7 +17062,7 @@
       <c r="H25" s="10">
         <v>3</v>
       </c>
-      <c r="I25" s="121"/>
+      <c r="I25" s="122"/>
       <c r="J25" s="10" t="s">
         <v>563</v>
       </c>
@@ -17339,10 +17079,10 @@
       <c r="P25" s="91"/>
     </row>
     <row r="26" spans="1:16">
-      <c r="A26" s="142"/>
-      <c r="B26" s="175"/>
-      <c r="C26" s="169"/>
-      <c r="D26" s="169"/>
+      <c r="A26" s="143"/>
+      <c r="B26" s="176"/>
+      <c r="C26" s="170"/>
+      <c r="D26" s="170"/>
       <c r="E26" s="8"/>
       <c r="F26" s="9" t="s">
         <v>338</v>
@@ -17353,7 +17093,7 @@
       <c r="H26" s="10">
         <v>2</v>
       </c>
-      <c r="I26" s="121"/>
+      <c r="I26" s="122"/>
       <c r="J26" s="10"/>
       <c r="K26" s="10"/>
       <c r="M26" s="99" t="s">
@@ -17368,10 +17108,10 @@
       <c r="P26" s="91"/>
     </row>
     <row r="27" spans="1:16">
-      <c r="A27" s="142"/>
-      <c r="B27" s="175"/>
-      <c r="C27" s="169"/>
-      <c r="D27" s="169"/>
+      <c r="A27" s="143"/>
+      <c r="B27" s="176"/>
+      <c r="C27" s="170"/>
+      <c r="D27" s="170"/>
       <c r="E27" s="8"/>
       <c r="F27" s="9" t="s">
         <v>339</v>
@@ -17379,10 +17119,10 @@
       <c r="G27" s="13" t="s">
         <v>372</v>
       </c>
-      <c r="H27" s="122" t="s">
-        <v>967</v>
-      </c>
-      <c r="I27" s="121"/>
+      <c r="H27" s="123" t="s">
+        <v>966</v>
+      </c>
+      <c r="I27" s="122"/>
       <c r="J27" s="10"/>
       <c r="K27" s="10"/>
       <c r="M27" s="99" t="s">
@@ -17397,13 +17137,13 @@
       <c r="P27" s="91"/>
     </row>
     <row r="28" spans="1:16">
-      <c r="A28" s="142"/>
-      <c r="B28" s="175"/>
-      <c r="C28" s="169"/>
-      <c r="D28" s="169"/>
+      <c r="A28" s="143"/>
+      <c r="B28" s="176"/>
+      <c r="C28" s="170"/>
+      <c r="D28" s="170"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="125" t="s">
-        <v>970</v>
+      <c r="F28" s="126" t="s">
+        <v>969</v>
       </c>
       <c r="G28" s="13" t="s">
         <v>371</v>
@@ -17411,7 +17151,7 @@
       <c r="H28" s="10">
         <v>1</v>
       </c>
-      <c r="I28" s="121">
+      <c r="I28" s="122">
         <v>44043</v>
       </c>
       <c r="J28" s="10"/>
@@ -17428,31 +17168,31 @@
       <c r="P28" s="91"/>
     </row>
     <row r="29" spans="1:16">
-      <c r="A29" s="142"/>
-      <c r="B29" s="175"/>
-      <c r="C29" s="169"/>
-      <c r="D29" s="169"/>
+      <c r="A29" s="143"/>
+      <c r="B29" s="176"/>
+      <c r="C29" s="170"/>
+      <c r="D29" s="170"/>
       <c r="E29" s="8"/>
       <c r="F29" s="9" t="s">
+        <v>959</v>
+      </c>
+      <c r="G29" s="9" t="s">
         <v>960</v>
-      </c>
-      <c r="G29" s="9" t="s">
-        <v>961</v>
       </c>
       <c r="H29" s="16">
         <v>2</v>
       </c>
-      <c r="I29" s="121"/>
+      <c r="I29" s="122"/>
       <c r="J29" s="10"/>
       <c r="K29" s="10" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="30" spans="1:16">
-      <c r="A30" s="142"/>
-      <c r="B30" s="175"/>
-      <c r="C30" s="169"/>
-      <c r="D30" s="170"/>
+      <c r="A30" s="143"/>
+      <c r="B30" s="176"/>
+      <c r="C30" s="170"/>
+      <c r="D30" s="171"/>
       <c r="E30" s="8"/>
       <c r="F30" s="49" t="s">
         <v>323</v>
@@ -17463,17 +17203,17 @@
       <c r="H30" s="114">
         <v>3</v>
       </c>
-      <c r="I30" s="121"/>
+      <c r="I30" s="122"/>
       <c r="J30" s="10"/>
-      <c r="K30" s="171" t="s">
-        <v>964</v>
+      <c r="K30" s="172" t="s">
+        <v>963</v>
       </c>
     </row>
     <row r="31" spans="1:16">
-      <c r="A31" s="142"/>
-      <c r="B31" s="175"/>
-      <c r="C31" s="169"/>
-      <c r="D31" s="168" t="s">
+      <c r="A31" s="143"/>
+      <c r="B31" s="176"/>
+      <c r="C31" s="170"/>
+      <c r="D31" s="169" t="s">
         <v>518</v>
       </c>
       <c r="E31" s="8"/>
@@ -17486,20 +17226,20 @@
       <c r="H31" s="16">
         <v>1</v>
       </c>
-      <c r="I31" s="121">
+      <c r="I31" s="122">
         <v>44043</v>
       </c>
       <c r="J31" s="10"/>
-      <c r="K31" s="172"/>
+      <c r="K31" s="173"/>
       <c r="M31" s="102" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="32" spans="1:16" ht="16.5" customHeight="1">
-      <c r="A32" s="142"/>
-      <c r="B32" s="175"/>
-      <c r="C32" s="169"/>
-      <c r="D32" s="169"/>
+      <c r="A32" s="143"/>
+      <c r="B32" s="176"/>
+      <c r="C32" s="170"/>
+      <c r="D32" s="170"/>
       <c r="E32" s="8"/>
       <c r="F32" s="9" t="s">
         <v>325</v>
@@ -17510,40 +17250,40 @@
       <c r="H32" s="16">
         <v>1</v>
       </c>
-      <c r="I32" s="121">
+      <c r="I32" s="122">
         <v>44043</v>
       </c>
       <c r="J32" s="10"/>
-      <c r="K32" s="172"/>
+      <c r="K32" s="173"/>
     </row>
     <row r="33" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A33" s="142"/>
-      <c r="B33" s="175"/>
-      <c r="C33" s="169"/>
-      <c r="D33" s="169"/>
+      <c r="A33" s="143"/>
+      <c r="B33" s="176"/>
+      <c r="C33" s="170"/>
+      <c r="D33" s="170"/>
       <c r="E33" s="8"/>
       <c r="F33" s="9" t="s">
+        <v>961</v>
+      </c>
+      <c r="G33" s="9" t="s">
         <v>962</v>
-      </c>
-      <c r="G33" s="9" t="s">
-        <v>963</v>
       </c>
       <c r="H33" s="16">
         <v>2</v>
       </c>
-      <c r="I33" s="121">
+      <c r="I33" s="122">
         <v>44043</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>959</v>
-      </c>
-      <c r="K33" s="173"/>
+        <v>958</v>
+      </c>
+      <c r="K33" s="174"/>
     </row>
     <row r="34" spans="1:11">
-      <c r="A34" s="142"/>
-      <c r="B34" s="175"/>
-      <c r="C34" s="170"/>
-      <c r="D34" s="170"/>
+      <c r="A34" s="143"/>
+      <c r="B34" s="176"/>
+      <c r="C34" s="171"/>
+      <c r="D34" s="171"/>
       <c r="E34" s="8"/>
       <c r="F34" s="49" t="s">
         <v>322</v>
@@ -17554,17 +17294,17 @@
       <c r="H34" s="50">
         <v>3</v>
       </c>
-      <c r="I34" s="121"/>
+      <c r="I34" s="122"/>
       <c r="J34" s="10"/>
       <c r="K34" s="10"/>
     </row>
     <row r="35" spans="1:11">
-      <c r="A35" s="142"/>
-      <c r="B35" s="175"/>
-      <c r="C35" s="168" t="s">
+      <c r="A35" s="143"/>
+      <c r="B35" s="176"/>
+      <c r="C35" s="169" t="s">
         <v>340</v>
       </c>
-      <c r="D35" s="168" t="s">
+      <c r="D35" s="169" t="s">
         <v>517</v>
       </c>
       <c r="E35" s="8"/>
@@ -17577,17 +17317,17 @@
       <c r="H35" s="16">
         <v>1</v>
       </c>
-      <c r="I35" s="121">
+      <c r="I35" s="122">
         <v>44043</v>
       </c>
       <c r="J35" s="10"/>
       <c r="K35" s="10"/>
     </row>
     <row r="36" spans="1:11">
-      <c r="A36" s="142"/>
-      <c r="B36" s="176"/>
-      <c r="C36" s="170"/>
-      <c r="D36" s="170"/>
+      <c r="A36" s="143"/>
+      <c r="B36" s="177"/>
+      <c r="C36" s="171"/>
+      <c r="D36" s="171"/>
       <c r="E36" s="8"/>
       <c r="F36" s="9" t="s">
         <v>331</v>
@@ -17595,15 +17335,15 @@
       <c r="G36" s="9" t="s">
         <v>376</v>
       </c>
-      <c r="H36" s="123" t="s">
-        <v>968</v>
-      </c>
-      <c r="I36" s="121"/>
+      <c r="H36" s="124" t="s">
+        <v>967</v>
+      </c>
+      <c r="I36" s="122"/>
       <c r="J36" s="10"/>
       <c r="K36" s="10"/>
     </row>
     <row r="37" spans="1:11">
-      <c r="A37" s="142"/>
+      <c r="A37" s="143"/>
       <c r="B37" s="29" t="s">
         <v>328</v>
       </c>
@@ -17623,19 +17363,19 @@
       <c r="H37" s="16" t="s">
         <v>330</v>
       </c>
-      <c r="I37" s="121"/>
+      <c r="I37" s="122"/>
       <c r="J37" s="10"/>
       <c r="K37" s="10"/>
     </row>
     <row r="38" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A38" s="142"/>
-      <c r="B38" s="174" t="s">
+      <c r="A38" s="143"/>
+      <c r="B38" s="175" t="s">
         <v>505</v>
       </c>
-      <c r="C38" s="168" t="s">
+      <c r="C38" s="169" t="s">
         <v>510</v>
       </c>
-      <c r="D38" s="168" t="s">
+      <c r="D38" s="169" t="s">
         <v>516</v>
       </c>
       <c r="E38" s="8" t="s">
@@ -17650,15 +17390,15 @@
       <c r="H38" s="10">
         <v>2</v>
       </c>
-      <c r="I38" s="121"/>
+      <c r="I38" s="122"/>
       <c r="J38" s="10"/>
       <c r="K38" s="10"/>
     </row>
     <row r="39" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A39" s="142"/>
-      <c r="B39" s="175"/>
-      <c r="C39" s="142"/>
-      <c r="D39" s="142"/>
+      <c r="A39" s="143"/>
+      <c r="B39" s="176"/>
+      <c r="C39" s="143"/>
+      <c r="D39" s="143"/>
       <c r="E39" s="17"/>
       <c r="F39" s="9" t="s">
         <v>304</v>
@@ -17669,17 +17409,17 @@
       <c r="H39" s="16">
         <v>1</v>
       </c>
-      <c r="I39" s="121">
+      <c r="I39" s="122">
         <v>44043</v>
       </c>
       <c r="J39" s="10"/>
       <c r="K39" s="10"/>
     </row>
     <row r="40" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A40" s="142"/>
-      <c r="B40" s="175"/>
-      <c r="C40" s="142"/>
-      <c r="D40" s="142"/>
+      <c r="A40" s="143"/>
+      <c r="B40" s="176"/>
+      <c r="C40" s="143"/>
+      <c r="D40" s="143"/>
       <c r="E40" s="17"/>
       <c r="F40" s="9" t="s">
         <v>305</v>
@@ -17690,17 +17430,17 @@
       <c r="H40" s="16">
         <v>1</v>
       </c>
-      <c r="I40" s="121">
+      <c r="I40" s="122">
         <v>44043</v>
       </c>
       <c r="J40" s="10"/>
       <c r="K40" s="10"/>
     </row>
     <row r="41" spans="1:11">
-      <c r="A41" s="142"/>
-      <c r="B41" s="175"/>
-      <c r="C41" s="142"/>
-      <c r="D41" s="143"/>
+      <c r="A41" s="143"/>
+      <c r="B41" s="176"/>
+      <c r="C41" s="143"/>
+      <c r="D41" s="144"/>
       <c r="E41" s="17"/>
       <c r="F41" s="9" t="s">
         <v>305</v>
@@ -17711,15 +17451,15 @@
       <c r="H41" s="16">
         <v>2</v>
       </c>
-      <c r="I41" s="121"/>
+      <c r="I41" s="122"/>
       <c r="J41" s="10"/>
       <c r="K41" s="10"/>
     </row>
     <row r="42" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A42" s="142"/>
-      <c r="B42" s="175"/>
-      <c r="C42" s="142"/>
-      <c r="D42" s="168" t="s">
+      <c r="A42" s="143"/>
+      <c r="B42" s="176"/>
+      <c r="C42" s="143"/>
+      <c r="D42" s="169" t="s">
         <v>515</v>
       </c>
       <c r="E42" s="8"/>
@@ -17730,21 +17470,21 @@
         <v>298</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>966</v>
-      </c>
-      <c r="I42" s="121">
+        <v>965</v>
+      </c>
+      <c r="I42" s="122">
         <v>44043</v>
       </c>
       <c r="J42" s="10"/>
-      <c r="K42" s="171" t="s">
-        <v>1169</v>
+      <c r="K42" s="172" t="s">
+        <v>1168</v>
       </c>
     </row>
     <row r="43" spans="1:11">
-      <c r="A43" s="142"/>
-      <c r="B43" s="175"/>
-      <c r="C43" s="142"/>
-      <c r="D43" s="143"/>
+      <c r="A43" s="143"/>
+      <c r="B43" s="176"/>
+      <c r="C43" s="143"/>
+      <c r="D43" s="144"/>
       <c r="E43" s="8"/>
       <c r="F43" s="9" t="s">
         <v>289</v>
@@ -17753,19 +17493,19 @@
         <v>299</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>966</v>
-      </c>
-      <c r="I43" s="121">
+        <v>965</v>
+      </c>
+      <c r="I43" s="122">
         <v>44043</v>
       </c>
       <c r="J43" s="10"/>
-      <c r="K43" s="181"/>
+      <c r="K43" s="182"/>
     </row>
     <row r="44" spans="1:11">
-      <c r="A44" s="142"/>
-      <c r="B44" s="175"/>
-      <c r="C44" s="142"/>
-      <c r="D44" s="168" t="s">
+      <c r="A44" s="143"/>
+      <c r="B44" s="176"/>
+      <c r="C44" s="143"/>
+      <c r="D44" s="169" t="s">
         <v>514</v>
       </c>
       <c r="E44" s="8"/>
@@ -17778,15 +17518,15 @@
       <c r="H44" s="10">
         <v>2</v>
       </c>
-      <c r="I44" s="121"/>
+      <c r="I44" s="122"/>
       <c r="J44" s="10"/>
       <c r="K44" s="10"/>
     </row>
     <row r="45" spans="1:11">
-      <c r="A45" s="143"/>
-      <c r="B45" s="176"/>
-      <c r="C45" s="143"/>
-      <c r="D45" s="143"/>
+      <c r="A45" s="144"/>
+      <c r="B45" s="177"/>
+      <c r="C45" s="144"/>
+      <c r="D45" s="144"/>
       <c r="E45" s="8"/>
       <c r="F45" s="9" t="s">
         <v>301</v>
@@ -17797,7 +17537,7 @@
       <c r="H45" s="10">
         <v>2</v>
       </c>
-      <c r="I45" s="121"/>
+      <c r="I45" s="122"/>
       <c r="J45" s="10"/>
       <c r="K45" s="10"/>
     </row>
@@ -17831,7 +17571,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -17842,7 +17582,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:J27"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -17852,6 +17592,7 @@
     <col min="7" max="7" width="77.85546875" customWidth="1"/>
     <col min="8" max="8" width="30.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8.85546875" customWidth="1"/>
+    <col min="10" max="10" width="61.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -17861,11 +17602,11 @@
       <c r="B1" s="25" t="s">
         <v>327</v>
       </c>
-      <c r="E1" s="179" t="s">
+      <c r="E1" s="180" t="s">
         <v>724</v>
       </c>
-      <c r="F1" s="179"/>
-      <c r="G1" s="179"/>
+      <c r="F1" s="180"/>
+      <c r="G1" s="180"/>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="19" t="s">
@@ -17874,11 +17615,11 @@
       <c r="B2" s="19" t="s">
         <v>257</v>
       </c>
-      <c r="E2" s="180" t="s">
+      <c r="E2" s="181" t="s">
         <v>725</v>
       </c>
-      <c r="F2" s="180"/>
-      <c r="G2" s="180"/>
+      <c r="F2" s="181"/>
+      <c r="G2" s="181"/>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="19" t="s">
@@ -17895,31 +17636,31 @@
       <c r="B4" s="19" t="s">
         <v>259</v>
       </c>
-      <c r="E4" s="179" t="s">
+      <c r="E4" s="180" t="s">
         <v>722</v>
       </c>
-      <c r="F4" s="179"/>
+      <c r="F4" s="180"/>
       <c r="G4" s="25" t="s">
         <v>723</v>
       </c>
       <c r="H4" s="25" t="s">
         <v>726</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="6" t="s">
         <v>727</v>
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="E5" s="178" t="s">
+      <c r="E5" s="179" t="s">
         <v>720</v>
       </c>
-      <c r="F5" s="178" t="s">
+      <c r="F5" s="179" t="s">
         <v>721</v>
       </c>
       <c r="G5" s="68" t="s">
         <v>747</v>
       </c>
-      <c r="H5" s="177" t="s">
+      <c r="H5" s="178" t="s">
         <v>748</v>
       </c>
       <c r="J5" t="s">
@@ -17930,12 +17671,12 @@
       <c r="A6" t="s">
         <v>261</v>
       </c>
-      <c r="E6" s="178"/>
-      <c r="F6" s="178"/>
+      <c r="E6" s="179"/>
+      <c r="F6" s="179"/>
       <c r="G6" s="68" t="s">
         <v>746</v>
       </c>
-      <c r="H6" s="178"/>
+      <c r="H6" s="179"/>
       <c r="J6" t="s">
         <v>729</v>
       </c>
@@ -17967,7 +17708,7 @@
         <v>274</v>
       </c>
       <c r="B9" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="J9" t="s">
         <v>732</v>
@@ -17977,7 +17718,7 @@
       <c r="A10" t="s">
         <v>396</v>
       </c>
-      <c r="J10" t="s">
+      <c r="J10" s="6" t="s">
         <v>733</v>
       </c>
     </row>
@@ -18001,6 +17742,9 @@
       <c r="C13" t="s">
         <v>790</v>
       </c>
+      <c r="H13" t="s">
+        <v>1255</v>
+      </c>
       <c r="J13" t="s">
         <v>735</v>
       </c>
@@ -18019,7 +17763,7 @@
         <v>795</v>
       </c>
       <c r="H14" t="s">
-        <v>796</v>
+        <v>1254</v>
       </c>
       <c r="J14" t="s">
         <v>736</v>
@@ -18036,7 +17780,7 @@
         <v>793</v>
       </c>
       <c r="G15" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="J15" t="s">
         <v>732</v>
@@ -18053,7 +17797,7 @@
         <v>792</v>
       </c>
       <c r="G16" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="J16" t="s">
         <v>737</v>
@@ -18080,7 +17824,7 @@
       </c>
     </row>
     <row r="21" spans="10:10">
-      <c r="J21" t="s">
+      <c r="J21" s="6" t="s">
         <v>744</v>
       </c>
     </row>
@@ -18126,6 +17870,645 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F01B713B-7546-4B5B-BF06-08BB58B1A0C8}">
+  <dimension ref="A1:K47"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.28515625" customWidth="1"/>
+    <col min="2" max="2" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" customWidth="1"/>
+    <col min="5" max="5" width="66.7109375" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="81" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="37.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="33.5703125" customWidth="1"/>
+    <col min="9" max="9" width="12.140625" style="81" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="60.42578125" style="183" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="30">
+      <c r="A1" s="191" t="s">
+        <v>847</v>
+      </c>
+      <c r="B1" s="191" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C1" s="191" t="s">
+        <v>640</v>
+      </c>
+      <c r="D1" s="191" t="s">
+        <v>1176</v>
+      </c>
+      <c r="E1" s="191" t="s">
+        <v>1171</v>
+      </c>
+      <c r="F1" s="191" t="s">
+        <v>1172</v>
+      </c>
+      <c r="G1" s="192" t="s">
+        <v>1206</v>
+      </c>
+      <c r="H1" s="192" t="s">
+        <v>1245</v>
+      </c>
+      <c r="I1" s="191" t="s">
+        <v>1180</v>
+      </c>
+      <c r="J1" s="191" t="s">
+        <v>1186</v>
+      </c>
+      <c r="K1" s="191" t="s">
+        <v>1192</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="187">
+        <v>44028</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>1175</v>
+      </c>
+      <c r="D2" s="119" t="s">
+        <v>1177</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>1179</v>
+      </c>
+      <c r="F2" s="119" t="s">
+        <v>1178</v>
+      </c>
+      <c r="G2" s="119">
+        <v>0.36</v>
+      </c>
+      <c r="H2" s="119"/>
+      <c r="I2" s="119" t="s">
+        <v>1181</v>
+      </c>
+      <c r="J2" s="119" t="s">
+        <v>894</v>
+      </c>
+      <c r="K2" s="188" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="187">
+        <v>44028</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>1197</v>
+      </c>
+      <c r="D3" s="119" t="s">
+        <v>1177</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>1184</v>
+      </c>
+      <c r="F3" s="119" t="s">
+        <v>1196</v>
+      </c>
+      <c r="G3" s="119">
+        <v>0.78</v>
+      </c>
+      <c r="H3" s="119"/>
+      <c r="I3" s="119" t="s">
+        <v>1185</v>
+      </c>
+      <c r="J3" s="119" t="s">
+        <v>894</v>
+      </c>
+      <c r="K3" s="189"/>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="187">
+        <v>44029</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>1190</v>
+      </c>
+      <c r="D4" s="119" t="s">
+        <v>1177</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>1189</v>
+      </c>
+      <c r="F4" s="119" t="s">
+        <v>1191</v>
+      </c>
+      <c r="G4" s="119">
+        <v>5.83</v>
+      </c>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="119" t="s">
+        <v>894</v>
+      </c>
+      <c r="K4" s="189"/>
+    </row>
+    <row r="5" spans="1:11" ht="45">
+      <c r="A5" s="187">
+        <v>44029</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>1193</v>
+      </c>
+      <c r="D5" s="119" t="s">
+        <v>1177</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>1195</v>
+      </c>
+      <c r="F5" s="119" t="s">
+        <v>1194</v>
+      </c>
+      <c r="G5" s="119">
+        <v>2.21</v>
+      </c>
+      <c r="H5" s="119"/>
+      <c r="I5" s="119"/>
+      <c r="J5" s="119" t="s">
+        <v>894</v>
+      </c>
+      <c r="K5" s="190"/>
+    </row>
+    <row r="6" spans="1:11" ht="60">
+      <c r="A6" s="187">
+        <v>44029</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>1208</v>
+      </c>
+      <c r="D6" s="119" t="s">
+        <v>1177</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>1195</v>
+      </c>
+      <c r="F6" s="119" t="s">
+        <v>1199</v>
+      </c>
+      <c r="G6" s="18" t="s">
+        <v>1209</v>
+      </c>
+      <c r="H6" s="18"/>
+      <c r="I6" s="119" t="s">
+        <v>1207</v>
+      </c>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8" t="s">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="60">
+      <c r="A7" s="187">
+        <v>44029</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>1219</v>
+      </c>
+      <c r="D7" s="119" t="s">
+        <v>1177</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>1195</v>
+      </c>
+      <c r="F7" s="119" t="s">
+        <v>1210</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>1211</v>
+      </c>
+      <c r="H7" s="18"/>
+      <c r="I7" s="119" t="s">
+        <v>1207</v>
+      </c>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+    </row>
+    <row r="8" spans="1:11" ht="60">
+      <c r="A8" s="187">
+        <v>44029</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>1212</v>
+      </c>
+      <c r="D8" s="119" t="s">
+        <v>1177</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>1195</v>
+      </c>
+      <c r="F8" s="119" t="s">
+        <v>1200</v>
+      </c>
+      <c r="G8" s="18" t="s">
+        <v>1213</v>
+      </c>
+      <c r="H8" s="18" t="s">
+        <v>1246</v>
+      </c>
+      <c r="I8" s="119" t="s">
+        <v>1207</v>
+      </c>
+      <c r="J8" s="8"/>
+      <c r="K8" s="18" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="60">
+      <c r="A9" s="187">
+        <v>44029</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D9" s="119" t="s">
+        <v>1177</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>1195</v>
+      </c>
+      <c r="F9" s="202" t="s">
+        <v>1249</v>
+      </c>
+      <c r="G9" s="18" t="s">
+        <v>1215</v>
+      </c>
+      <c r="H9" s="198" t="s">
+        <v>1247</v>
+      </c>
+      <c r="I9" s="119" t="s">
+        <v>1207</v>
+      </c>
+      <c r="J9" s="8"/>
+      <c r="K9" s="18" t="s">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="45">
+      <c r="A10" s="197" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>1218</v>
+      </c>
+      <c r="D10" s="119" t="s">
+        <v>1177</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>1195</v>
+      </c>
+      <c r="F10" s="119" t="s">
+        <v>1202</v>
+      </c>
+      <c r="G10" s="18" t="s">
+        <v>1248</v>
+      </c>
+      <c r="H10" s="18"/>
+      <c r="I10" s="119" t="s">
+        <v>1207</v>
+      </c>
+      <c r="J10" s="8"/>
+      <c r="K10" s="18" t="s">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="45">
+      <c r="A11" s="195" t="s">
+        <v>1222</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>1218</v>
+      </c>
+      <c r="D11" s="119" t="s">
+        <v>1177</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>1195</v>
+      </c>
+      <c r="F11" s="119" t="s">
+        <v>1202</v>
+      </c>
+      <c r="G11" s="194" t="s">
+        <v>1251</v>
+      </c>
+      <c r="H11" s="194"/>
+      <c r="I11" s="119" t="s">
+        <v>1221</v>
+      </c>
+      <c r="J11" s="8"/>
+      <c r="K11" s="18" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="119" t="s">
+        <v>1203</v>
+      </c>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="119" t="s">
+        <v>1207</v>
+      </c>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="119" t="s">
+        <v>1204</v>
+      </c>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="119" t="s">
+        <v>1207</v>
+      </c>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="183"/>
+      <c r="B14" s="183"/>
+      <c r="C14" s="183"/>
+      <c r="D14" s="183"/>
+      <c r="E14" s="193" t="s">
+        <v>1220</v>
+      </c>
+      <c r="F14" s="184"/>
+      <c r="G14" s="193" t="s">
+        <v>1231</v>
+      </c>
+      <c r="H14" s="183"/>
+      <c r="I14" s="184"/>
+      <c r="J14" s="183"/>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="183"/>
+      <c r="B15" s="183"/>
+      <c r="C15" s="183"/>
+      <c r="D15" s="183"/>
+      <c r="E15" s="183"/>
+      <c r="F15" s="184"/>
+      <c r="G15" s="183" t="s">
+        <v>1238</v>
+      </c>
+      <c r="H15" s="183" t="s">
+        <v>1239</v>
+      </c>
+      <c r="I15" s="184"/>
+      <c r="J15" s="183"/>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="183"/>
+      <c r="B16" s="183"/>
+      <c r="C16" s="183"/>
+      <c r="D16" s="183"/>
+      <c r="E16" s="183"/>
+      <c r="G16" s="183"/>
+      <c r="H16" s="183"/>
+      <c r="I16" s="184"/>
+      <c r="J16" s="183"/>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="183"/>
+      <c r="B17" s="183"/>
+      <c r="C17" s="183"/>
+      <c r="D17" s="183"/>
+      <c r="E17" s="183"/>
+      <c r="F17" s="200" t="s">
+        <v>1244</v>
+      </c>
+      <c r="G17" s="183" t="s">
+        <v>1257</v>
+      </c>
+      <c r="H17" s="118">
+        <v>0</v>
+      </c>
+      <c r="I17" s="184"/>
+      <c r="J17" s="183"/>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="183"/>
+      <c r="B18" s="183"/>
+      <c r="C18" s="183"/>
+      <c r="D18" s="183"/>
+      <c r="E18" s="183"/>
+      <c r="F18" s="199"/>
+      <c r="G18" s="183" t="s">
+        <v>1241</v>
+      </c>
+      <c r="H18" s="118" t="s">
+        <v>1258</v>
+      </c>
+      <c r="I18" s="184"/>
+      <c r="J18" s="183"/>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="F19" s="199"/>
+      <c r="G19" s="183" t="s">
+        <v>1240</v>
+      </c>
+      <c r="H19" s="203" t="s">
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="F20" s="199"/>
+      <c r="G20" s="183" t="s">
+        <v>1242</v>
+      </c>
+      <c r="H20" s="118" t="s">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="F21" s="199"/>
+      <c r="G21" s="183" t="s">
+        <v>1243</v>
+      </c>
+      <c r="H21" s="203" t="s">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="G22" s="201"/>
+    </row>
+    <row r="35" spans="5:7">
+      <c r="E35" s="196" t="s">
+        <v>1256</v>
+      </c>
+      <c r="F35" t="s">
+        <v>1223</v>
+      </c>
+      <c r="G35" t="s">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="36" spans="5:7">
+      <c r="E36" s="196" t="s">
+        <v>1210</v>
+      </c>
+      <c r="F36" s="81">
+        <v>1</v>
+      </c>
+      <c r="G36" t="s">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="37" spans="5:7">
+      <c r="E37" s="196" t="s">
+        <v>1210</v>
+      </c>
+      <c r="F37" s="81">
+        <v>8</v>
+      </c>
+      <c r="G37" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="38" spans="5:7">
+      <c r="E38" s="196" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F38" s="81">
+        <v>1</v>
+      </c>
+      <c r="G38" t="s">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="39" spans="5:7">
+      <c r="E39" s="196" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F39" s="81">
+        <v>4</v>
+      </c>
+      <c r="G39" t="s">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="40" spans="5:7">
+      <c r="E40" s="196" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F40" s="81">
+        <v>8</v>
+      </c>
+      <c r="G40" t="s">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="41" spans="5:7">
+      <c r="E41" s="196" t="s">
+        <v>1202</v>
+      </c>
+      <c r="F41" s="81">
+        <v>1</v>
+      </c>
+      <c r="G41" t="s">
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="42" spans="5:7">
+      <c r="E42" s="196" t="s">
+        <v>1202</v>
+      </c>
+      <c r="F42" s="81">
+        <v>4</v>
+      </c>
+      <c r="G42" t="s">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="43" spans="5:7">
+      <c r="E43" s="196" t="s">
+        <v>1202</v>
+      </c>
+      <c r="F43" s="81">
+        <v>8</v>
+      </c>
+      <c r="G43" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="46" spans="5:7">
+      <c r="E46" s="196" t="s">
+        <v>1204</v>
+      </c>
+      <c r="F46" s="81">
+        <v>1</v>
+      </c>
+      <c r="G46" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="47" spans="5:7">
+      <c r="E47" s="196" t="s">
+        <v>1204</v>
+      </c>
+      <c r="F47" s="81">
+        <v>8</v>
+      </c>
+      <c r="G47" t="s">
+        <v>1235</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="K2:K5"/>
+    <mergeCell ref="F17:F21"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -18256,14 +18639,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="126" t="s">
+      <c r="A1" s="127" t="s">
+        <v>975</v>
+      </c>
+      <c r="B1" s="128" t="s">
         <v>976</v>
       </c>
-      <c r="B1" s="127" t="s">
+      <c r="C1" s="128" t="s">
         <v>977</v>
-      </c>
-      <c r="C1" s="127" t="s">
-        <v>978</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -18271,10 +18654,10 @@
         <v>758</v>
       </c>
       <c r="B2" s="19" t="s">
+        <v>978</v>
+      </c>
+      <c r="C2" s="19" t="s">
         <v>979</v>
-      </c>
-      <c r="C2" s="19" t="s">
-        <v>980</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -18282,10 +18665,10 @@
         <v>758</v>
       </c>
       <c r="B3" s="19" t="s">
+        <v>980</v>
+      </c>
+      <c r="C3" s="19" t="s">
         <v>981</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>982</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -18293,10 +18676,10 @@
         <v>758</v>
       </c>
       <c r="B4" s="19" t="s">
+        <v>982</v>
+      </c>
+      <c r="C4" s="19" t="s">
         <v>983</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>984</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -18304,10 +18687,10 @@
         <v>758</v>
       </c>
       <c r="B5" s="19" t="s">
+        <v>984</v>
+      </c>
+      <c r="C5" s="19" t="s">
         <v>985</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>986</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -18315,10 +18698,10 @@
         <v>758</v>
       </c>
       <c r="B6" s="19" t="s">
+        <v>986</v>
+      </c>
+      <c r="C6" s="19" t="s">
         <v>987</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>988</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -18326,10 +18709,10 @@
         <v>758</v>
       </c>
       <c r="B7" s="19" t="s">
+        <v>988</v>
+      </c>
+      <c r="C7" s="19" t="s">
         <v>989</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>990</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -18337,10 +18720,10 @@
         <v>758</v>
       </c>
       <c r="B8" s="19" t="s">
+        <v>990</v>
+      </c>
+      <c r="C8" s="19" t="s">
         <v>991</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>992</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -18348,10 +18731,10 @@
         <v>758</v>
       </c>
       <c r="B9" s="19" t="s">
+        <v>992</v>
+      </c>
+      <c r="C9" s="19" t="s">
         <v>993</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>994</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -18359,10 +18742,10 @@
         <v>758</v>
       </c>
       <c r="B10" s="19" t="s">
+        <v>994</v>
+      </c>
+      <c r="C10" s="19" t="s">
         <v>995</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>996</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -18370,10 +18753,10 @@
         <v>758</v>
       </c>
       <c r="B11" s="19" t="s">
+        <v>996</v>
+      </c>
+      <c r="C11" s="19" t="s">
         <v>997</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>998</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -18381,10 +18764,10 @@
         <v>758</v>
       </c>
       <c r="B12" s="19" t="s">
+        <v>998</v>
+      </c>
+      <c r="C12" s="19" t="s">
         <v>999</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>1000</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -18392,10 +18775,10 @@
         <v>758</v>
       </c>
       <c r="B13" s="19" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C13" s="19" t="s">
         <v>1001</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>1002</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -18403,10 +18786,10 @@
         <v>758</v>
       </c>
       <c r="B14" s="19" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C14" s="19" t="s">
         <v>1003</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>1004</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -18414,10 +18797,10 @@
         <v>758</v>
       </c>
       <c r="B15" s="19" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C15" s="19" t="s">
         <v>1005</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>1006</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -18425,10 +18808,10 @@
         <v>758</v>
       </c>
       <c r="B16" s="19" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C16" s="19" t="s">
         <v>1007</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>1008</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -18436,10 +18819,10 @@
         <v>758</v>
       </c>
       <c r="B17" s="19" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C17" s="19" t="s">
         <v>1009</v>
-      </c>
-      <c r="C17" s="19" t="s">
-        <v>1010</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -18447,10 +18830,10 @@
         <v>758</v>
       </c>
       <c r="B18" s="19" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C18" s="19" t="s">
         <v>1011</v>
-      </c>
-      <c r="C18" s="19" t="s">
-        <v>1012</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -18458,10 +18841,10 @@
         <v>758</v>
       </c>
       <c r="B19" s="19" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C19" s="19" t="s">
         <v>1013</v>
-      </c>
-      <c r="C19" s="19" t="s">
-        <v>1014</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -18469,10 +18852,10 @@
         <v>758</v>
       </c>
       <c r="B20" s="19" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C20" s="19" t="s">
         <v>1015</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>1016</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -18480,10 +18863,10 @@
         <v>758</v>
       </c>
       <c r="B21" s="19" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C21" s="19" t="s">
         <v>1017</v>
-      </c>
-      <c r="C21" s="19" t="s">
-        <v>1018</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -18491,10 +18874,10 @@
         <v>758</v>
       </c>
       <c r="B22" s="19" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C22" s="19" t="s">
         <v>1019</v>
-      </c>
-      <c r="C22" s="19" t="s">
-        <v>1020</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -18502,10 +18885,10 @@
         <v>758</v>
       </c>
       <c r="B23" s="19" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C23" s="19" t="s">
         <v>1021</v>
-      </c>
-      <c r="C23" s="19" t="s">
-        <v>1022</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -18513,10 +18896,10 @@
         <v>758</v>
       </c>
       <c r="B24" s="19" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C24" s="19" t="s">
         <v>1023</v>
-      </c>
-      <c r="C24" s="19" t="s">
-        <v>1024</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -18524,10 +18907,10 @@
         <v>758</v>
       </c>
       <c r="B25" s="19" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C25" s="19" t="s">
         <v>1025</v>
-      </c>
-      <c r="C25" s="19" t="s">
-        <v>1026</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -18535,10 +18918,10 @@
         <v>758</v>
       </c>
       <c r="B26" s="19" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C26" s="19" t="s">
         <v>1027</v>
-      </c>
-      <c r="C26" s="19" t="s">
-        <v>1028</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -18546,10 +18929,10 @@
         <v>758</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -18557,10 +18940,10 @@
         <v>758</v>
       </c>
       <c r="B28" s="19" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C28" s="19" t="s">
         <v>1030</v>
-      </c>
-      <c r="C28" s="19" t="s">
-        <v>1031</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -18568,10 +18951,10 @@
         <v>758</v>
       </c>
       <c r="B29" s="19" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C29" s="19" t="s">
         <v>1032</v>
-      </c>
-      <c r="C29" s="19" t="s">
-        <v>1033</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -18579,10 +18962,10 @@
         <v>758</v>
       </c>
       <c r="B30" s="19" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C30" s="19" t="s">
         <v>1034</v>
-      </c>
-      <c r="C30" s="19" t="s">
-        <v>1035</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -18590,10 +18973,10 @@
         <v>758</v>
       </c>
       <c r="B31" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C31" s="19" t="s">
         <v>1036</v>
-      </c>
-      <c r="C31" s="19" t="s">
-        <v>1037</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -18601,10 +18984,10 @@
         <v>758</v>
       </c>
       <c r="B32" s="19" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C32" s="19" t="s">
         <v>1038</v>
-      </c>
-      <c r="C32" s="19" t="s">
-        <v>1039</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -18612,10 +18995,10 @@
         <v>758</v>
       </c>
       <c r="B33" s="19" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C33" s="19" t="s">
         <v>1040</v>
-      </c>
-      <c r="C33" s="19" t="s">
-        <v>1041</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -18623,10 +19006,10 @@
         <v>758</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -18634,10 +19017,10 @@
         <v>758</v>
       </c>
       <c r="B35" s="19" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C35" s="19" t="s">
         <v>1043</v>
-      </c>
-      <c r="C35" s="19" t="s">
-        <v>1044</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -18645,10 +19028,10 @@
         <v>758</v>
       </c>
       <c r="B36" s="19" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C36" s="19" t="s">
         <v>1045</v>
-      </c>
-      <c r="C36" s="19" t="s">
-        <v>1046</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -18656,10 +19039,10 @@
         <v>758</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -18667,10 +19050,10 @@
         <v>758</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -18678,10 +19061,10 @@
         <v>758</v>
       </c>
       <c r="B39" s="19" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C39" s="19" t="s">
         <v>1049</v>
-      </c>
-      <c r="C39" s="19" t="s">
-        <v>1050</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -18689,10 +19072,10 @@
         <v>758</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -18700,10 +19083,10 @@
         <v>758</v>
       </c>
       <c r="B41" s="19" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C41" s="19" t="s">
         <v>1052</v>
-      </c>
-      <c r="C41" s="19" t="s">
-        <v>1053</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -18711,713 +19094,713 @@
         <v>758</v>
       </c>
       <c r="B42" s="19" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C42" s="19" t="s">
         <v>1054</v>
       </c>
-      <c r="C42" s="19" t="s">
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="129" t="s">
+        <v>385</v>
+      </c>
+      <c r="B43" s="129" t="s">
         <v>1055</v>
       </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="128" t="s">
+      <c r="C43" s="129" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="129" t="s">
         <v>385</v>
       </c>
-      <c r="B43" s="128" t="s">
-        <v>1056</v>
-      </c>
-      <c r="C43" s="128" t="s">
+      <c r="B44" s="129" t="s">
         <v>1057</v>
       </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="128" t="s">
+      <c r="C44" s="129" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="129" t="s">
         <v>385</v>
       </c>
-      <c r="B44" s="128" t="s">
+      <c r="B45" s="129" t="s">
         <v>1058</v>
       </c>
-      <c r="C44" s="128" t="s">
-        <v>980</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="128" t="s">
+      <c r="C45" s="129" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="129" t="s">
         <v>385</v>
       </c>
-      <c r="B45" s="128" t="s">
-        <v>1059</v>
-      </c>
-      <c r="C45" s="128" t="s">
+      <c r="B46" s="129" t="s">
+        <v>619</v>
+      </c>
+      <c r="C46" s="129" t="s">
         <v>1060</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="128" t="s">
+    <row r="47" spans="1:3">
+      <c r="A47" s="129" t="s">
         <v>385</v>
       </c>
-      <c r="B46" s="128" t="s">
-        <v>619</v>
-      </c>
-      <c r="C46" s="128" t="s">
+      <c r="B47" s="129" t="s">
+        <v>617</v>
+      </c>
+      <c r="C47" s="129" t="s">
         <v>1061</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="128" t="s">
+    <row r="48" spans="1:3">
+      <c r="A48" s="129" t="s">
         <v>385</v>
       </c>
-      <c r="B47" s="128" t="s">
-        <v>617</v>
-      </c>
-      <c r="C47" s="128" t="s">
+      <c r="B48" s="129" t="s">
         <v>1062</v>
       </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="128" t="s">
+      <c r="C48" s="129" t="s">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="129" t="s">
         <v>385</v>
       </c>
-      <c r="B48" s="128" t="s">
-        <v>1063</v>
-      </c>
-      <c r="C48" s="128" t="s">
+      <c r="B49" s="129" t="s">
         <v>1064</v>
       </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="128" t="s">
+      <c r="C49" s="129" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="129" t="s">
         <v>385</v>
       </c>
-      <c r="B49" s="128" t="s">
-        <v>1065</v>
-      </c>
-      <c r="C49" s="128" t="s">
+      <c r="B50" s="129" t="s">
         <v>1066</v>
       </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="128" t="s">
+      <c r="C50" s="129" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="129" t="s">
         <v>385</v>
       </c>
-      <c r="B50" s="128" t="s">
-        <v>1067</v>
-      </c>
-      <c r="C50" s="128" t="s">
+      <c r="B51" s="129" t="s">
         <v>1068</v>
       </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="128" t="s">
+      <c r="C51" s="129" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="129" t="s">
         <v>385</v>
       </c>
-      <c r="B51" s="128" t="s">
-        <v>1069</v>
-      </c>
-      <c r="C51" s="128" t="s">
+      <c r="B52" s="129" t="s">
         <v>1070</v>
       </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="128" t="s">
+      <c r="C52" s="129" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" s="129" t="s">
         <v>385</v>
       </c>
-      <c r="B52" s="128" t="s">
-        <v>1071</v>
-      </c>
-      <c r="C52" s="128" t="s">
+      <c r="B53" s="129" t="s">
         <v>1072</v>
       </c>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="128" t="s">
+      <c r="C53" s="19" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" s="129" t="s">
         <v>385</v>
       </c>
-      <c r="B53" s="128" t="s">
-        <v>1073</v>
-      </c>
-      <c r="C53" s="19" t="s">
+      <c r="B54" s="129" t="s">
         <v>1074</v>
       </c>
-    </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="128" t="s">
+      <c r="C54" s="19" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" s="129" t="s">
         <v>385</v>
       </c>
-      <c r="B54" s="128" t="s">
-        <v>1075</v>
-      </c>
-      <c r="C54" s="19" t="s">
+      <c r="B55" s="19" t="s">
         <v>1076</v>
       </c>
-    </row>
-    <row r="55" spans="1:3">
-      <c r="A55" s="128" t="s">
+      <c r="C55" s="19" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" s="129" t="s">
         <v>385</v>
       </c>
-      <c r="B55" s="19" t="s">
-        <v>1077</v>
-      </c>
-      <c r="C55" s="19" t="s">
+      <c r="B56" s="19" t="s">
         <v>1078</v>
       </c>
-    </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="128" t="s">
+      <c r="C56" s="19" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" s="129" t="s">
         <v>385</v>
       </c>
-      <c r="B56" s="19" t="s">
-        <v>1079</v>
-      </c>
-      <c r="C56" s="19" t="s">
+      <c r="B57" s="19" t="s">
         <v>1080</v>
       </c>
-    </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="128" t="s">
+      <c r="C57" s="19" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="30">
+      <c r="A58" s="129" t="s">
         <v>385</v>
       </c>
-      <c r="B57" s="19" t="s">
-        <v>1081</v>
-      </c>
-      <c r="C57" s="19" t="s">
+      <c r="B58" s="19" t="s">
         <v>1082</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" ht="30">
-      <c r="A58" s="128" t="s">
+      <c r="C58" s="23" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" s="129" t="s">
         <v>385</v>
       </c>
-      <c r="B58" s="19" t="s">
-        <v>1083</v>
-      </c>
-      <c r="C58" s="23" t="s">
+      <c r="B59" s="19" t="s">
         <v>1084</v>
       </c>
-    </row>
-    <row r="59" spans="1:3">
-      <c r="A59" s="128" t="s">
+      <c r="C59" s="19" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" s="129" t="s">
         <v>385</v>
       </c>
-      <c r="B59" s="19" t="s">
-        <v>1085</v>
-      </c>
-      <c r="C59" s="19" t="s">
+      <c r="B60" s="19" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C60" s="19" t="s">
         <v>1086</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3">
-      <c r="A60" s="128" t="s">
-        <v>385</v>
-      </c>
-      <c r="B60" s="19" t="s">
-        <v>1059</v>
-      </c>
-      <c r="C60" s="19" t="s">
-        <v>1087</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="16.5">
       <c r="A61" s="19" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B61" s="130" t="s">
         <v>1088</v>
       </c>
-      <c r="B61" s="129" t="s">
+      <c r="C61" s="130" t="s">
         <v>1089</v>
-      </c>
-      <c r="C61" s="129" t="s">
-        <v>1090</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="16.5">
       <c r="A62" s="19" t="s">
-        <v>1088</v>
-      </c>
-      <c r="B62" s="130" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B62" s="131" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C62" s="131" t="s">
         <v>1091</v>
-      </c>
-      <c r="C62" s="130" t="s">
-        <v>1092</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="16.5">
       <c r="A63" s="19" t="s">
-        <v>1088</v>
-      </c>
-      <c r="B63" s="130" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B63" s="131" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C63" s="131" t="s">
         <v>1093</v>
-      </c>
-      <c r="C63" s="130" t="s">
-        <v>1094</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="16.5">
       <c r="A64" s="19" t="s">
-        <v>1088</v>
-      </c>
-      <c r="B64" s="130" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B64" s="131" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C64" s="131" t="s">
         <v>1095</v>
-      </c>
-      <c r="C64" s="130" t="s">
-        <v>1096</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="16.5">
       <c r="A65" s="19" t="s">
-        <v>1088</v>
-      </c>
-      <c r="B65" s="130" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B65" s="131" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C65" s="131" t="s">
         <v>1097</v>
-      </c>
-      <c r="C65" s="130" t="s">
-        <v>1098</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="16.5">
       <c r="A66" s="19" t="s">
-        <v>1088</v>
-      </c>
-      <c r="B66" s="130" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B66" s="131" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C66" s="131" t="s">
         <v>1099</v>
-      </c>
-      <c r="C66" s="130" t="s">
-        <v>1100</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="16.5">
       <c r="A67" s="19" t="s">
-        <v>1088</v>
-      </c>
-      <c r="B67" s="130" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B67" s="131" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C67" s="131" t="s">
         <v>1101</v>
-      </c>
-      <c r="C67" s="130" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="16.5">
       <c r="A68" s="19" t="s">
-        <v>1088</v>
-      </c>
-      <c r="B68" s="130" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B68" s="131" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C68" s="131" t="s">
         <v>1103</v>
-      </c>
-      <c r="C68" s="130" t="s">
-        <v>1104</v>
       </c>
     </row>
     <row r="69" spans="1:3" ht="16.5">
       <c r="A69" s="19" t="s">
-        <v>1088</v>
-      </c>
-      <c r="B69" s="130" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B69" s="131" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C69" s="131" t="s">
         <v>1105</v>
-      </c>
-      <c r="C69" s="130" t="s">
-        <v>1106</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="16.5">
       <c r="A70" s="19" t="s">
-        <v>1088</v>
-      </c>
-      <c r="B70" s="130" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B70" s="131" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C70" s="131" t="s">
         <v>1107</v>
-      </c>
-      <c r="C70" s="130" t="s">
-        <v>1108</v>
       </c>
     </row>
     <row r="71" spans="1:3" ht="16.5">
       <c r="A71" s="19" t="s">
-        <v>1088</v>
-      </c>
-      <c r="B71" s="130" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B71" s="131" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C71" s="131" t="s">
         <v>1109</v>
-      </c>
-      <c r="C71" s="130" t="s">
-        <v>1110</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="16.5">
       <c r="A72" s="19" t="s">
-        <v>1088</v>
-      </c>
-      <c r="B72" s="130" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B72" s="131" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C72" s="131" t="s">
         <v>1111</v>
-      </c>
-      <c r="C72" s="130" t="s">
-        <v>1112</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="16.5">
       <c r="A73" s="19" t="s">
-        <v>1088</v>
-      </c>
-      <c r="B73" s="130" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B73" s="131" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C73" s="131" t="s">
         <v>1113</v>
-      </c>
-      <c r="C73" s="130" t="s">
-        <v>1114</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="16.5">
       <c r="A74" s="19" t="s">
-        <v>1088</v>
-      </c>
-      <c r="B74" s="130" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B74" s="131" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C74" s="131" t="s">
         <v>1115</v>
-      </c>
-      <c r="C74" s="130" t="s">
-        <v>1116</v>
       </c>
     </row>
     <row r="75" spans="1:3" ht="16.5">
       <c r="A75" s="19" t="s">
-        <v>1088</v>
-      </c>
-      <c r="B75" s="130" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B75" s="131" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C75" s="131" t="s">
         <v>1117</v>
-      </c>
-      <c r="C75" s="130" t="s">
-        <v>1118</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="16.5">
       <c r="A76" s="19" t="s">
-        <v>1088</v>
-      </c>
-      <c r="B76" s="130" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B76" s="131" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C76" s="131" t="s">
         <v>1119</v>
-      </c>
-      <c r="C76" s="130" t="s">
-        <v>1120</v>
       </c>
     </row>
     <row r="77" spans="1:3" ht="16.5">
       <c r="A77" s="19" t="s">
-        <v>1088</v>
-      </c>
-      <c r="B77" s="130" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B77" s="131" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C77" s="131" t="s">
         <v>1121</v>
-      </c>
-      <c r="C77" s="130" t="s">
-        <v>1122</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="16.5">
       <c r="A78" s="19" t="s">
-        <v>1088</v>
-      </c>
-      <c r="B78" s="130" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B78" s="131" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C78" s="131" t="s">
         <v>1123</v>
-      </c>
-      <c r="C78" s="130" t="s">
-        <v>1124</v>
       </c>
     </row>
     <row r="79" spans="1:3" ht="16.5">
       <c r="A79" s="19" t="s">
-        <v>1088</v>
-      </c>
-      <c r="B79" s="130" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B79" s="131" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C79" s="131" t="s">
         <v>1125</v>
-      </c>
-      <c r="C79" s="130" t="s">
-        <v>1126</v>
       </c>
     </row>
     <row r="80" spans="1:3" ht="16.5">
       <c r="A80" s="19" t="s">
-        <v>1088</v>
-      </c>
-      <c r="B80" s="130" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B80" s="131" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C80" s="131" t="s">
         <v>1127</v>
-      </c>
-      <c r="C80" s="130" t="s">
-        <v>1128</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="16.5">
       <c r="A81" s="19" t="s">
-        <v>1088</v>
-      </c>
-      <c r="B81" s="130" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B81" s="131" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C81" s="131" t="s">
         <v>1129</v>
-      </c>
-      <c r="C81" s="130" t="s">
-        <v>1130</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="16.5">
       <c r="A82" s="19" t="s">
-        <v>1088</v>
-      </c>
-      <c r="B82" s="130" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B82" s="131" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C82" s="131" t="s">
         <v>1131</v>
-      </c>
-      <c r="C82" s="130" t="s">
-        <v>1132</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="16.5">
       <c r="A83" s="19" t="s">
-        <v>1088</v>
-      </c>
-      <c r="B83" s="130" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B83" s="131" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C83" s="131" t="s">
         <v>1133</v>
-      </c>
-      <c r="C83" s="130" t="s">
-        <v>1134</v>
       </c>
     </row>
     <row r="84" spans="1:3" ht="16.5">
       <c r="A84" s="19" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B84" s="131" t="s">
         <v>1135</v>
       </c>
-      <c r="B84" s="130" t="s">
-        <v>1136</v>
-      </c>
-      <c r="C84" s="130" t="s">
-        <v>1110</v>
+      <c r="C84" s="131" t="s">
+        <v>1109</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="16.5">
       <c r="A85" s="19" t="s">
-        <v>1135</v>
-      </c>
-      <c r="B85" s="130" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B85" s="131" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C85" s="131" t="s">
         <v>1137</v>
-      </c>
-      <c r="C85" s="130" t="s">
-        <v>1138</v>
       </c>
     </row>
     <row r="86" spans="1:3" ht="33">
       <c r="A86" s="19" t="s">
-        <v>1135</v>
-      </c>
-      <c r="B86" s="130" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B86" s="131" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C86" s="131" t="s">
         <v>1139</v>
-      </c>
-      <c r="C86" s="130" t="s">
-        <v>1140</v>
       </c>
     </row>
     <row r="87" spans="1:3" ht="49.5">
       <c r="A87" s="19" t="s">
-        <v>1135</v>
-      </c>
-      <c r="B87" s="130" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B87" s="131" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C87" s="131" t="s">
         <v>1141</v>
-      </c>
-      <c r="C87" s="130" t="s">
-        <v>1142</v>
       </c>
     </row>
     <row r="88" spans="1:3" ht="33">
       <c r="A88" s="19" t="s">
-        <v>1135</v>
-      </c>
-      <c r="B88" s="130" t="s">
-        <v>1143</v>
-      </c>
-      <c r="C88" s="130" t="s">
-        <v>1112</v>
+        <v>1134</v>
+      </c>
+      <c r="B88" s="131" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C88" s="131" t="s">
+        <v>1111</v>
       </c>
     </row>
     <row r="89" spans="1:3" ht="16.5">
       <c r="A89" s="19" t="s">
-        <v>1135</v>
-      </c>
-      <c r="B89" s="130" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B89" s="131" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C89" s="131" t="s">
         <v>1144</v>
-      </c>
-      <c r="C89" s="130" t="s">
-        <v>1145</v>
       </c>
     </row>
     <row r="90" spans="1:3" ht="16.5">
       <c r="A90" s="19" t="s">
-        <v>1135</v>
-      </c>
-      <c r="B90" s="130" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B90" s="131" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C90" s="131" t="s">
         <v>1146</v>
-      </c>
-      <c r="C90" s="130" t="s">
-        <v>1147</v>
       </c>
     </row>
     <row r="91" spans="1:3" ht="16.5">
       <c r="A91" s="19" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B91" s="131" t="s">
         <v>1148</v>
       </c>
-      <c r="B91" s="130" t="s">
-        <v>1149</v>
-      </c>
-      <c r="C91" s="130" t="s">
-        <v>1110</v>
+      <c r="C91" s="131" t="s">
+        <v>1109</v>
       </c>
     </row>
     <row r="92" spans="1:3" ht="33">
       <c r="A92" s="19" t="s">
-        <v>1148</v>
-      </c>
-      <c r="B92" s="130" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B92" s="131" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C92" s="131" t="s">
         <v>1139</v>
-      </c>
-      <c r="C92" s="130" t="s">
-        <v>1140</v>
       </c>
     </row>
     <row r="93" spans="1:3" ht="16.5">
       <c r="A93" s="19" t="s">
-        <v>1148</v>
-      </c>
-      <c r="B93" s="130" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B93" s="131" t="s">
         <v>313</v>
       </c>
-      <c r="C93" s="130" t="s">
-        <v>1090</v>
+      <c r="C93" s="131" t="s">
+        <v>1089</v>
       </c>
     </row>
     <row r="94" spans="1:3" ht="16.5">
       <c r="A94" s="19" t="s">
-        <v>1148</v>
-      </c>
-      <c r="B94" s="130" t="s">
-        <v>812</v>
-      </c>
-      <c r="C94" s="130" t="s">
-        <v>1150</v>
+        <v>1147</v>
+      </c>
+      <c r="B94" s="131" t="s">
+        <v>811</v>
+      </c>
+      <c r="C94" s="131" t="s">
+        <v>1149</v>
       </c>
     </row>
     <row r="95" spans="1:3" ht="16.5">
       <c r="A95" s="19" t="s">
-        <v>1148</v>
-      </c>
-      <c r="B95" s="130" t="s">
-        <v>1151</v>
-      </c>
-      <c r="C95" s="130" t="s">
-        <v>1094</v>
+        <v>1147</v>
+      </c>
+      <c r="B95" s="131" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C95" s="131" t="s">
+        <v>1093</v>
       </c>
     </row>
     <row r="96" spans="1:3" ht="16.5">
       <c r="A96" s="19" t="s">
-        <v>1148</v>
-      </c>
-      <c r="B96" s="130" t="s">
-        <v>1152</v>
-      </c>
-      <c r="C96" s="130" t="s">
-        <v>1096</v>
+        <v>1147</v>
+      </c>
+      <c r="B96" s="131" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C96" s="131" t="s">
+        <v>1095</v>
       </c>
     </row>
     <row r="97" spans="1:3" ht="16.5">
       <c r="A97" s="19" t="s">
-        <v>1148</v>
-      </c>
-      <c r="B97" s="130" t="s">
-        <v>1153</v>
-      </c>
-      <c r="C97" s="130" t="s">
-        <v>1098</v>
+        <v>1147</v>
+      </c>
+      <c r="B97" s="131" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C97" s="131" t="s">
+        <v>1097</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="16.5">
       <c r="A98" s="19" t="s">
-        <v>1148</v>
-      </c>
-      <c r="B98" s="130" t="s">
-        <v>1154</v>
-      </c>
-      <c r="C98" s="130" t="s">
-        <v>1132</v>
+        <v>1147</v>
+      </c>
+      <c r="B98" s="131" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C98" s="131" t="s">
+        <v>1131</v>
       </c>
     </row>
     <row r="99" spans="1:3" ht="16.5">
       <c r="A99" s="19" t="s">
-        <v>1148</v>
-      </c>
-      <c r="B99" s="130" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B99" s="131" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C99" s="131" t="s">
         <v>1155</v>
-      </c>
-      <c r="C99" s="130" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="100" spans="1:3" ht="16.5">
       <c r="A100" s="19" t="s">
-        <v>1148</v>
-      </c>
-      <c r="B100" s="130" t="s">
-        <v>1157</v>
-      </c>
-      <c r="C100" s="130" t="s">
-        <v>1128</v>
+        <v>1147</v>
+      </c>
+      <c r="B100" s="131" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C100" s="131" t="s">
+        <v>1127</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="16.5">
       <c r="A101" s="19" t="s">
-        <v>1148</v>
-      </c>
-      <c r="B101" s="130" t="s">
-        <v>1144</v>
-      </c>
-      <c r="C101" s="130" t="s">
-        <v>1158</v>
+        <v>1147</v>
+      </c>
+      <c r="B101" s="131" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C101" s="131" t="s">
+        <v>1157</v>
       </c>
     </row>
     <row r="102" spans="1:3" ht="16.5">
       <c r="A102" s="19" t="s">
-        <v>1148</v>
-      </c>
-      <c r="B102" s="130" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B102" s="131" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C102" s="131" t="s">
         <v>1159</v>
-      </c>
-      <c r="C102" s="130" t="s">
-        <v>1160</v>
       </c>
     </row>
     <row r="103" spans="1:3" ht="16.5">
       <c r="A103" s="19" t="s">
-        <v>1148</v>
-      </c>
-      <c r="B103" s="130" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B103" s="131" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C103" s="131" t="s">
         <v>1161</v>
-      </c>
-      <c r="C103" s="130" t="s">
-        <v>1162</v>
       </c>
     </row>
     <row r="104" spans="1:3" ht="16.5">
       <c r="A104" s="19" t="s">
-        <v>1148</v>
-      </c>
-      <c r="B104" s="130" t="s">
-        <v>1163</v>
-      </c>
-      <c r="C104" s="130" t="s">
-        <v>1102</v>
+        <v>1147</v>
+      </c>
+      <c r="B104" s="131" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C104" s="131" t="s">
+        <v>1101</v>
       </c>
     </row>
     <row r="105" spans="1:3" ht="16.5">
       <c r="A105" s="19" t="s">
-        <v>1148</v>
-      </c>
-      <c r="B105" s="130" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B105" s="131" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C105" s="131" t="s">
         <v>1164</v>
-      </c>
-      <c r="C105" s="130" t="s">
-        <v>1165</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107" s="7" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" s="7" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -19429,13 +19812,13 @@
       <c r="A112" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="B112" s="131"/>
+      <c r="B112" s="132"/>
     </row>
     <row r="113" spans="1:2" ht="16.5">
       <c r="A113" s="7" t="s">
-        <v>1168</v>
-      </c>
-      <c r="B113" s="131"/>
+        <v>1167</v>
+      </c>
+      <c r="B113" s="132"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -19479,7 +19862,7 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="178" t="s">
+      <c r="A2" s="179" t="s">
         <v>379</v>
       </c>
       <c r="B2" s="57" t="s">
@@ -19493,7 +19876,7 @@
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="178"/>
+      <c r="A3" s="179"/>
       <c r="B3" s="20" t="s">
         <v>262</v>
       </c>
@@ -19505,7 +19888,7 @@
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="178"/>
+      <c r="A4" s="179"/>
       <c r="B4" s="20" t="s">
         <v>385</v>
       </c>
@@ -19517,7 +19900,7 @@
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="178"/>
+      <c r="A5" s="179"/>
       <c r="B5" s="57" t="s">
         <v>544</v>
       </c>
@@ -19529,7 +19912,7 @@
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="178"/>
+      <c r="A6" s="179"/>
       <c r="B6" s="20" t="s">
         <v>388</v>
       </c>
@@ -19541,7 +19924,7 @@
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="178"/>
+      <c r="A7" s="179"/>
       <c r="B7" s="20" t="s">
         <v>390</v>
       </c>
@@ -19927,7 +20310,7 @@
       <c r="B2" s="53"/>
       <c r="C2" s="53"/>
       <c r="M2" s="5" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -19937,7 +20320,7 @@
       <c r="B3" s="53"/>
       <c r="C3" s="53"/>
       <c r="M3" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -19947,7 +20330,7 @@
       <c r="B4" s="53"/>
       <c r="C4" s="53"/>
       <c r="M4" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -21116,259 +21499,259 @@
   <sheetData>
     <row r="4" spans="11:15">
       <c r="L4" t="s">
+        <v>874</v>
+      </c>
+      <c r="M4" t="s">
         <v>875</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>876</v>
-      </c>
-      <c r="N4" t="s">
-        <v>877</v>
       </c>
     </row>
     <row r="5" spans="11:15">
       <c r="L5" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="M5" t="s">
+        <v>878</v>
+      </c>
+      <c r="O5" t="s">
         <v>879</v>
-      </c>
-      <c r="O5" t="s">
-        <v>880</v>
       </c>
     </row>
     <row r="6" spans="11:15">
       <c r="L6" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="M6" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="N6" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="O6" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="7" spans="11:15">
       <c r="N7" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="8" spans="11:15" ht="35.25" customHeight="1">
       <c r="M8" s="107"/>
       <c r="N8" s="107" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
     </row>
     <row r="10" spans="11:15">
       <c r="K10" s="110" t="s">
+        <v>910</v>
+      </c>
+      <c r="L10" s="110" t="s">
         <v>911</v>
-      </c>
-      <c r="L10" s="110" t="s">
-        <v>912</v>
       </c>
     </row>
     <row r="12" spans="11:15">
       <c r="K12" s="5" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="13" spans="11:15">
       <c r="L13" t="s">
+        <v>881</v>
+      </c>
+      <c r="M13" t="s">
         <v>882</v>
       </c>
-      <c r="M13" t="s">
+      <c r="N13" t="s">
         <v>883</v>
-      </c>
-      <c r="N13" t="s">
-        <v>884</v>
       </c>
     </row>
     <row r="14" spans="11:15">
       <c r="K14" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="L14" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="15" spans="11:15">
       <c r="L15" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="16" spans="11:15">
       <c r="N16" s="5" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="O16" s="5" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="20" spans="7:22">
       <c r="K20" t="s">
+        <v>883</v>
+      </c>
+      <c r="L20" t="s">
         <v>884</v>
       </c>
-      <c r="L20" t="s">
+      <c r="M20" t="s">
         <v>885</v>
       </c>
-      <c r="M20" t="s">
+      <c r="N20" t="s">
         <v>886</v>
       </c>
-      <c r="N20" t="s">
+      <c r="O20" t="s">
         <v>887</v>
-      </c>
-      <c r="O20" t="s">
-        <v>888</v>
       </c>
     </row>
     <row r="21" spans="7:22">
       <c r="L21" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="T21" s="94" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="22" spans="7:22">
-      <c r="T22" s="141" t="s">
-        <v>834</v>
+      <c r="T22" s="142" t="s">
+        <v>833</v>
       </c>
       <c r="U22" s="9" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="V22" s="92" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="23" spans="7:22">
       <c r="N23" s="5" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="O23" s="5" t="s">
-        <v>913</v>
-      </c>
-      <c r="T23" s="142"/>
+        <v>912</v>
+      </c>
+      <c r="T23" s="143"/>
       <c r="U23" s="9" t="s">
+        <v>816</v>
+      </c>
+      <c r="V23" s="92" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="24" spans="7:22">
+      <c r="T24" s="143"/>
+      <c r="U24" s="9" t="s">
         <v>817</v>
       </c>
-      <c r="V23" s="92" t="s">
+      <c r="V24" s="92" t="s">
         <v>820</v>
-      </c>
-    </row>
-    <row r="24" spans="7:22">
-      <c r="T24" s="142"/>
-      <c r="U24" s="9" t="s">
-        <v>818</v>
-      </c>
-      <c r="V24" s="92" t="s">
-        <v>821</v>
       </c>
     </row>
     <row r="25" spans="7:22">
       <c r="K25" s="5" t="s">
-        <v>893</v>
-      </c>
-      <c r="T25" s="142"/>
+        <v>892</v>
+      </c>
+      <c r="T25" s="143"/>
       <c r="U25" s="9" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="V25" s="92" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="26" spans="7:22">
       <c r="L26" s="111" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="M26" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="N26" t="s">
-        <v>900</v>
-      </c>
-      <c r="T26" s="142"/>
+        <v>899</v>
+      </c>
+      <c r="T26" s="143"/>
       <c r="U26" s="9" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="V26" s="92"/>
     </row>
     <row r="27" spans="7:22">
       <c r="L27" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="M27" t="s">
-        <v>899</v>
-      </c>
-      <c r="T27" s="142"/>
+        <v>898</v>
+      </c>
+      <c r="T27" s="143"/>
       <c r="U27" s="9" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="V27" s="92"/>
     </row>
     <row r="28" spans="7:22">
       <c r="M28" t="s">
-        <v>901</v>
-      </c>
-      <c r="T28" s="142"/>
+        <v>900</v>
+      </c>
+      <c r="T28" s="143"/>
       <c r="U28" s="9" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="V28" s="92" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="29" spans="7:22">
       <c r="M29" t="s">
-        <v>902</v>
-      </c>
-      <c r="T29" s="143"/>
+        <v>901</v>
+      </c>
+      <c r="T29" s="144"/>
       <c r="U29" s="9" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="V29" s="92" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="30" spans="7:22">
       <c r="L30" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="M30" t="s">
-        <v>854</v>
-      </c>
-      <c r="T30" s="138" t="s">
-        <v>833</v>
+        <v>853</v>
+      </c>
+      <c r="T30" s="139" t="s">
+        <v>832</v>
       </c>
       <c r="U30" s="49" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="V30" s="113"/>
     </row>
     <row r="31" spans="7:22">
       <c r="M31" t="s">
-        <v>904</v>
-      </c>
-      <c r="T31" s="139"/>
+        <v>903</v>
+      </c>
+      <c r="T31" s="140"/>
       <c r="U31" s="49" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="V31" s="113"/>
     </row>
     <row r="32" spans="7:22">
       <c r="G32" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="N32" s="5" t="s">
+        <v>904</v>
+      </c>
+      <c r="O32" s="5" t="s">
         <v>905</v>
       </c>
-      <c r="O32" s="5" t="s">
-        <v>906</v>
-      </c>
-      <c r="T32" s="140"/>
+      <c r="T32" s="141"/>
       <c r="U32" s="49" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="V32" s="113"/>
     </row>
@@ -21377,7 +21760,7 @@
         <v>1</v>
       </c>
       <c r="G33" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="34" spans="6:15">
@@ -21385,13 +21768,13 @@
         <v>2</v>
       </c>
       <c r="G34" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="K34" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="L34" t="s">
         <v>907</v>
-      </c>
-      <c r="L34" t="s">
-        <v>908</v>
       </c>
     </row>
     <row r="35" spans="6:15">
@@ -21399,46 +21782,46 @@
         <v>2</v>
       </c>
       <c r="G35" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="L35" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="36" spans="6:15">
       <c r="F36" s="7" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="L36" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="37" spans="6:15">
       <c r="L37" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="38" spans="6:15">
       <c r="L38" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
     <row r="39" spans="6:15">
       <c r="L39" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
     </row>
     <row r="40" spans="6:15">
       <c r="L40" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="41" spans="6:15">
       <c r="N41" s="5" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="O41" s="5" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
   </sheetData>
@@ -21476,15 +21859,15 @@
         <v>313</v>
       </c>
       <c r="R4" s="13" t="s">
+        <v>806</v>
+      </c>
+      <c r="S4" s="93" t="s">
         <v>807</v>
-      </c>
-      <c r="S4" s="93" t="s">
-        <v>808</v>
       </c>
     </row>
     <row r="5" spans="3:20">
       <c r="O5" s="81" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="P5" s="81">
         <v>1</v>
@@ -21495,13 +21878,13 @@
       <c r="R5" s="13" t="s">
         <v>352</v>
       </c>
-      <c r="S5" s="144" t="s">
-        <v>811</v>
+      <c r="S5" s="145" t="s">
+        <v>810</v>
       </c>
     </row>
     <row r="6" spans="3:20">
       <c r="O6" s="81" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="P6" s="81">
         <v>2</v>
@@ -21512,11 +21895,11 @@
       <c r="R6" s="9" t="s">
         <v>602</v>
       </c>
-      <c r="S6" s="144"/>
+      <c r="S6" s="145"/>
     </row>
     <row r="7" spans="3:20">
       <c r="O7" s="81" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="P7" s="81">
         <v>3</v>
@@ -21527,11 +21910,11 @@
       <c r="R7" s="9" t="s">
         <v>603</v>
       </c>
-      <c r="S7" s="144"/>
+      <c r="S7" s="145"/>
     </row>
     <row r="8" spans="3:20">
       <c r="O8" s="81" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="P8" s="81">
         <v>4</v>
@@ -21542,11 +21925,11 @@
       <c r="R8" s="9" t="s">
         <v>350</v>
       </c>
-      <c r="S8" s="144"/>
+      <c r="S8" s="145"/>
     </row>
     <row r="9" spans="3:20">
       <c r="O9" s="81" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="P9" s="81">
         <v>5</v>
@@ -21557,7 +21940,7 @@
       <c r="R9" s="9" t="s">
         <v>349</v>
       </c>
-      <c r="S9" s="144"/>
+      <c r="S9" s="145"/>
     </row>
     <row r="10" spans="3:20">
       <c r="Q10" s="9" t="s">
@@ -21567,29 +21950,29 @@
         <v>348</v>
       </c>
       <c r="S10" s="93" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="T10" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="14" spans="3:20">
       <c r="C14" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="Q14" s="94" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="15" spans="3:20">
-      <c r="Q15" s="141" t="s">
-        <v>834</v>
+      <c r="Q15" s="142" t="s">
+        <v>833</v>
       </c>
       <c r="R15" s="9" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="S15" s="92" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="16" spans="3:20">
@@ -21597,7 +21980,7 @@
         <v>313</v>
       </c>
       <c r="D16" s="92" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>314</v>
@@ -21606,96 +21989,96 @@
         <v>312</v>
       </c>
       <c r="G16" s="10" t="s">
+        <v>812</v>
+      </c>
+      <c r="H16" s="10" t="s">
         <v>813</v>
-      </c>
-      <c r="H16" s="10" t="s">
-        <v>814</v>
       </c>
       <c r="I16" s="10" t="s">
         <v>315</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>815</v>
-      </c>
-      <c r="Q16" s="142"/>
+        <v>814</v>
+      </c>
+      <c r="Q16" s="143"/>
       <c r="R16" s="9" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="S16" s="92" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="17" spans="10:19">
       <c r="J17" s="81"/>
-      <c r="Q17" s="142"/>
+      <c r="Q17" s="143"/>
       <c r="R17" s="9" t="s">
+        <v>817</v>
+      </c>
+      <c r="S17" s="92" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="18" spans="10:19">
+      <c r="Q18" s="143"/>
+      <c r="R18" s="9" t="s">
         <v>818</v>
       </c>
-      <c r="S17" s="92" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="18" spans="10:19">
-      <c r="Q18" s="142"/>
-      <c r="R18" s="9" t="s">
-        <v>819</v>
-      </c>
       <c r="S18" s="92" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="19" spans="10:19">
-      <c r="Q19" s="142"/>
+      <c r="Q19" s="143"/>
       <c r="R19" s="9" t="s">
+        <v>825</v>
+      </c>
+      <c r="S19" s="92"/>
+    </row>
+    <row r="20" spans="10:19">
+      <c r="Q20" s="143"/>
+      <c r="R20" s="9" t="s">
         <v>826</v>
       </c>
-      <c r="S19" s="92"/>
-    </row>
-    <row r="20" spans="10:19">
-      <c r="Q20" s="142"/>
-      <c r="R20" s="9" t="s">
+      <c r="S20" s="92"/>
+    </row>
+    <row r="21" spans="10:19">
+      <c r="Q21" s="143"/>
+      <c r="R21" s="9" t="s">
         <v>827</v>
       </c>
-      <c r="S20" s="92"/>
-    </row>
-    <row r="21" spans="10:19">
-      <c r="Q21" s="142"/>
-      <c r="R21" s="9" t="s">
+      <c r="S21" s="92" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="22" spans="10:19">
+      <c r="Q22" s="144"/>
+      <c r="R22" s="9" t="s">
         <v>828</v>
       </c>
-      <c r="S21" s="92" t="s">
+      <c r="S22" s="92" t="s">
         <v>830</v>
       </c>
     </row>
-    <row r="22" spans="10:19">
-      <c r="Q22" s="143"/>
-      <c r="R22" s="9" t="s">
-        <v>829</v>
-      </c>
-      <c r="S22" s="92" t="s">
-        <v>831</v>
-      </c>
-    </row>
     <row r="23" spans="10:19">
-      <c r="Q23" s="141" t="s">
-        <v>833</v>
+      <c r="Q23" s="142" t="s">
+        <v>832</v>
       </c>
       <c r="R23" s="9" t="s">
+        <v>822</v>
+      </c>
+      <c r="S23" s="92"/>
+    </row>
+    <row r="24" spans="10:19">
+      <c r="Q24" s="143"/>
+      <c r="R24" s="9" t="s">
         <v>823</v>
       </c>
-      <c r="S23" s="92"/>
-    </row>
-    <row r="24" spans="10:19">
-      <c r="Q24" s="142"/>
-      <c r="R24" s="9" t="s">
+      <c r="S24" s="92"/>
+    </row>
+    <row r="25" spans="10:19">
+      <c r="Q25" s="144"/>
+      <c r="R25" s="9" t="s">
         <v>824</v>
-      </c>
-      <c r="S24" s="92"/>
-    </row>
-    <row r="25" spans="10:19">
-      <c r="Q25" s="143"/>
-      <c r="R25" s="9" t="s">
-        <v>825</v>
       </c>
       <c r="S25" s="92"/>
     </row>
@@ -21718,22 +22101,22 @@
   <sheetData>
     <row r="10" spans="14:14">
       <c r="N10" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="14" spans="14:14">
       <c r="N14" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="15" spans="14:14">
       <c r="N15" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="24" spans="14:14">
       <c r="N24" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
   </sheetData>
@@ -21753,319 +22136,319 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" t="s">
+        <v>860</v>
+      </c>
+      <c r="B1" t="s">
         <v>861</v>
       </c>
-      <c r="B1" t="s">
-        <v>862</v>
-      </c>
-      <c r="J1" s="145" t="s">
-        <v>957</v>
-      </c>
-      <c r="K1" s="146"/>
-      <c r="L1" s="146"/>
-      <c r="M1" s="146"/>
-      <c r="N1" s="146"/>
-      <c r="O1" s="146"/>
-      <c r="P1" s="146"/>
-      <c r="Q1" s="146"/>
+      <c r="J1" s="146" t="s">
+        <v>956</v>
+      </c>
+      <c r="K1" s="147"/>
+      <c r="L1" s="147"/>
+      <c r="M1" s="147"/>
+      <c r="N1" s="147"/>
+      <c r="O1" s="147"/>
+      <c r="P1" s="147"/>
+      <c r="Q1" s="147"/>
     </row>
     <row r="2" spans="1:17">
-      <c r="J2" s="146"/>
-      <c r="K2" s="146"/>
-      <c r="L2" s="146"/>
-      <c r="M2" s="146"/>
-      <c r="N2" s="146"/>
-      <c r="O2" s="146"/>
-      <c r="P2" s="146"/>
-      <c r="Q2" s="146"/>
+      <c r="J2" s="147"/>
+      <c r="K2" s="147"/>
+      <c r="L2" s="147"/>
+      <c r="M2" s="147"/>
+      <c r="N2" s="147"/>
+      <c r="O2" s="147"/>
+      <c r="P2" s="147"/>
+      <c r="Q2" s="147"/>
     </row>
     <row r="3" spans="1:17">
       <c r="A3" t="s">
-        <v>863</v>
-      </c>
-      <c r="J3" s="146"/>
-      <c r="K3" s="146"/>
-      <c r="L3" s="146"/>
-      <c r="M3" s="146"/>
-      <c r="N3" s="146"/>
-      <c r="O3" s="146"/>
-      <c r="P3" s="146"/>
-      <c r="Q3" s="146"/>
+        <v>862</v>
+      </c>
+      <c r="J3" s="147"/>
+      <c r="K3" s="147"/>
+      <c r="L3" s="147"/>
+      <c r="M3" s="147"/>
+      <c r="N3" s="147"/>
+      <c r="O3" s="147"/>
+      <c r="P3" s="147"/>
+      <c r="Q3" s="147"/>
     </row>
     <row r="4" spans="1:17">
       <c r="A4" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B4" t="s">
+        <v>863</v>
+      </c>
+      <c r="D4" t="s">
         <v>864</v>
       </c>
-      <c r="D4" t="s">
-        <v>865</v>
-      </c>
-      <c r="J4" s="146"/>
-      <c r="K4" s="146"/>
-      <c r="L4" s="146"/>
-      <c r="M4" s="146"/>
-      <c r="N4" s="146"/>
-      <c r="O4" s="146"/>
-      <c r="P4" s="146"/>
-      <c r="Q4" s="146"/>
+      <c r="J4" s="147"/>
+      <c r="K4" s="147"/>
+      <c r="L4" s="147"/>
+      <c r="M4" s="147"/>
+      <c r="N4" s="147"/>
+      <c r="O4" s="147"/>
+      <c r="P4" s="147"/>
+      <c r="Q4" s="147"/>
     </row>
     <row r="5" spans="1:17">
-      <c r="J5" s="146"/>
-      <c r="K5" s="146"/>
-      <c r="L5" s="146"/>
-      <c r="M5" s="146"/>
-      <c r="N5" s="146"/>
-      <c r="O5" s="146"/>
-      <c r="P5" s="146"/>
-      <c r="Q5" s="146"/>
+      <c r="J5" s="147"/>
+      <c r="K5" s="147"/>
+      <c r="L5" s="147"/>
+      <c r="M5" s="147"/>
+      <c r="N5" s="147"/>
+      <c r="O5" s="147"/>
+      <c r="P5" s="147"/>
+      <c r="Q5" s="147"/>
     </row>
     <row r="6" spans="1:17" ht="15.75" thickBot="1">
       <c r="A6" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="E6" t="s">
-        <v>923</v>
-      </c>
-      <c r="J6" s="146"/>
-      <c r="K6" s="146"/>
-      <c r="L6" s="146"/>
-      <c r="M6" s="146"/>
-      <c r="N6" s="146"/>
-      <c r="O6" s="146"/>
-      <c r="P6" s="146"/>
-      <c r="Q6" s="146"/>
+        <v>922</v>
+      </c>
+      <c r="J6" s="147"/>
+      <c r="K6" s="147"/>
+      <c r="L6" s="147"/>
+      <c r="M6" s="147"/>
+      <c r="N6" s="147"/>
+      <c r="O6" s="147"/>
+      <c r="P6" s="147"/>
+      <c r="Q6" s="147"/>
     </row>
     <row r="7" spans="1:17" ht="15.75" thickBot="1">
       <c r="A7" s="106" t="s">
-        <v>867</v>
-      </c>
-      <c r="J7" s="146"/>
-      <c r="K7" s="146"/>
-      <c r="L7" s="146"/>
-      <c r="M7" s="146"/>
-      <c r="N7" s="146"/>
-      <c r="O7" s="146"/>
-      <c r="P7" s="146"/>
-      <c r="Q7" s="146"/>
+        <v>866</v>
+      </c>
+      <c r="J7" s="147"/>
+      <c r="K7" s="147"/>
+      <c r="L7" s="147"/>
+      <c r="M7" s="147"/>
+      <c r="N7" s="147"/>
+      <c r="O7" s="147"/>
+      <c r="P7" s="147"/>
+      <c r="Q7" s="147"/>
     </row>
     <row r="8" spans="1:17">
-      <c r="A8" s="120"/>
-      <c r="J8" s="146"/>
-      <c r="K8" s="146"/>
-      <c r="L8" s="146"/>
-      <c r="M8" s="146"/>
-      <c r="N8" s="146"/>
-      <c r="O8" s="146"/>
-      <c r="P8" s="146"/>
-      <c r="Q8" s="146"/>
+      <c r="A8" s="121"/>
+      <c r="J8" s="147"/>
+      <c r="K8" s="147"/>
+      <c r="L8" s="147"/>
+      <c r="M8" s="147"/>
+      <c r="N8" s="147"/>
+      <c r="O8" s="147"/>
+      <c r="P8" s="147"/>
+      <c r="Q8" s="147"/>
     </row>
     <row r="9" spans="1:17">
       <c r="A9" t="s">
+        <v>927</v>
+      </c>
+      <c r="B9" t="s">
         <v>928</v>
       </c>
-      <c r="B9" t="s">
-        <v>929</v>
-      </c>
-      <c r="J9" s="146"/>
-      <c r="K9" s="146"/>
-      <c r="L9" s="146"/>
-      <c r="M9" s="146"/>
-      <c r="N9" s="146"/>
-      <c r="O9" s="146"/>
-      <c r="P9" s="146"/>
-      <c r="Q9" s="146"/>
+      <c r="J9" s="147"/>
+      <c r="K9" s="147"/>
+      <c r="L9" s="147"/>
+      <c r="M9" s="147"/>
+      <c r="N9" s="147"/>
+      <c r="O9" s="147"/>
+      <c r="P9" s="147"/>
+      <c r="Q9" s="147"/>
     </row>
     <row r="10" spans="1:17">
       <c r="A10" t="s">
+        <v>923</v>
+      </c>
+      <c r="B10" t="s">
         <v>924</v>
       </c>
-      <c r="B10" t="s">
-        <v>925</v>
-      </c>
       <c r="E10" t="s">
+        <v>929</v>
+      </c>
+      <c r="F10" t="s">
         <v>930</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>931</v>
       </c>
-      <c r="G10" t="s">
-        <v>932</v>
-      </c>
       <c r="H10" t="s">
-        <v>955</v>
-      </c>
-      <c r="J10" s="146"/>
-      <c r="K10" s="146"/>
-      <c r="L10" s="146"/>
-      <c r="M10" s="146"/>
-      <c r="N10" s="146"/>
-      <c r="O10" s="146"/>
-      <c r="P10" s="146"/>
-      <c r="Q10" s="146"/>
+        <v>954</v>
+      </c>
+      <c r="J10" s="147"/>
+      <c r="K10" s="147"/>
+      <c r="L10" s="147"/>
+      <c r="M10" s="147"/>
+      <c r="N10" s="147"/>
+      <c r="O10" s="147"/>
+      <c r="P10" s="147"/>
+      <c r="Q10" s="147"/>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" t="s">
+        <v>952</v>
+      </c>
+      <c r="B11" t="s">
+        <v>925</v>
+      </c>
+      <c r="E11" t="s">
         <v>953</v>
       </c>
-      <c r="B11" t="s">
-        <v>926</v>
-      </c>
-      <c r="E11" t="s">
-        <v>954</v>
-      </c>
       <c r="F11" t="s">
+        <v>932</v>
+      </c>
+      <c r="G11" t="s">
         <v>933</v>
       </c>
-      <c r="G11" t="s">
-        <v>934</v>
-      </c>
       <c r="H11" t="s">
-        <v>956</v>
-      </c>
-      <c r="J11" s="146"/>
-      <c r="K11" s="146"/>
-      <c r="L11" s="146"/>
-      <c r="M11" s="146"/>
-      <c r="N11" s="146"/>
-      <c r="O11" s="146"/>
-      <c r="P11" s="146"/>
-      <c r="Q11" s="146"/>
+        <v>955</v>
+      </c>
+      <c r="J11" s="147"/>
+      <c r="K11" s="147"/>
+      <c r="L11" s="147"/>
+      <c r="M11" s="147"/>
+      <c r="N11" s="147"/>
+      <c r="O11" s="147"/>
+      <c r="P11" s="147"/>
+      <c r="Q11" s="147"/>
     </row>
     <row r="12" spans="1:17">
       <c r="B12" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="F12" t="s">
+        <v>934</v>
+      </c>
+      <c r="G12" t="s">
         <v>935</v>
       </c>
-      <c r="G12" t="s">
-        <v>936</v>
-      </c>
       <c r="H12" t="s">
-        <v>956</v>
-      </c>
-      <c r="J12" s="146"/>
-      <c r="K12" s="146"/>
-      <c r="L12" s="146"/>
-      <c r="M12" s="146"/>
-      <c r="N12" s="146"/>
-      <c r="O12" s="146"/>
-      <c r="P12" s="146"/>
-      <c r="Q12" s="146"/>
+        <v>955</v>
+      </c>
+      <c r="J12" s="147"/>
+      <c r="K12" s="147"/>
+      <c r="L12" s="147"/>
+      <c r="M12" s="147"/>
+      <c r="N12" s="147"/>
+      <c r="O12" s="147"/>
+      <c r="P12" s="147"/>
+      <c r="Q12" s="147"/>
     </row>
     <row r="13" spans="1:17">
       <c r="F13" t="s">
+        <v>936</v>
+      </c>
+      <c r="G13" t="s">
         <v>937</v>
       </c>
-      <c r="G13" t="s">
-        <v>938</v>
-      </c>
       <c r="H13" t="s">
-        <v>956</v>
-      </c>
-      <c r="J13" s="146"/>
-      <c r="K13" s="146"/>
-      <c r="L13" s="146"/>
-      <c r="M13" s="146"/>
-      <c r="N13" s="146"/>
-      <c r="O13" s="146"/>
-      <c r="P13" s="146"/>
-      <c r="Q13" s="146"/>
+        <v>955</v>
+      </c>
+      <c r="J13" s="147"/>
+      <c r="K13" s="147"/>
+      <c r="L13" s="147"/>
+      <c r="M13" s="147"/>
+      <c r="N13" s="147"/>
+      <c r="O13" s="147"/>
+      <c r="P13" s="147"/>
+      <c r="Q13" s="147"/>
     </row>
     <row r="14" spans="1:17">
-      <c r="J14" s="146"/>
-      <c r="K14" s="146"/>
-      <c r="L14" s="146"/>
-      <c r="M14" s="146"/>
-      <c r="N14" s="146"/>
-      <c r="O14" s="146"/>
-      <c r="P14" s="146"/>
-      <c r="Q14" s="146"/>
+      <c r="J14" s="147"/>
+      <c r="K14" s="147"/>
+      <c r="L14" s="147"/>
+      <c r="M14" s="147"/>
+      <c r="N14" s="147"/>
+      <c r="O14" s="147"/>
+      <c r="P14" s="147"/>
+      <c r="Q14" s="147"/>
     </row>
     <row r="15" spans="1:17">
       <c r="A15" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="C15" t="s">
-        <v>952</v>
-      </c>
-      <c r="J15" s="146"/>
-      <c r="K15" s="146"/>
-      <c r="L15" s="146"/>
-      <c r="M15" s="146"/>
-      <c r="N15" s="146"/>
-      <c r="O15" s="146"/>
-      <c r="P15" s="146"/>
-      <c r="Q15" s="146"/>
+        <v>951</v>
+      </c>
+      <c r="J15" s="147"/>
+      <c r="K15" s="147"/>
+      <c r="L15" s="147"/>
+      <c r="M15" s="147"/>
+      <c r="N15" s="147"/>
+      <c r="O15" s="147"/>
+      <c r="P15" s="147"/>
+      <c r="Q15" s="147"/>
     </row>
     <row r="16" spans="1:17">
       <c r="A16" t="s">
-        <v>942</v>
-      </c>
-      <c r="J16" s="146"/>
-      <c r="K16" s="146"/>
-      <c r="L16" s="146"/>
-      <c r="M16" s="146"/>
-      <c r="N16" s="146"/>
-      <c r="O16" s="146"/>
-      <c r="P16" s="146"/>
-      <c r="Q16" s="146"/>
+        <v>941</v>
+      </c>
+      <c r="J16" s="147"/>
+      <c r="K16" s="147"/>
+      <c r="L16" s="147"/>
+      <c r="M16" s="147"/>
+      <c r="N16" s="147"/>
+      <c r="O16" s="147"/>
+      <c r="P16" s="147"/>
+      <c r="Q16" s="147"/>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="5" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="5" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
   </sheetData>
@@ -22233,19 +22616,19 @@
       <c r="E7" s="31" t="s">
         <v>449</v>
       </c>
-      <c r="F7" s="147" t="s">
+      <c r="F7" s="148" t="s">
         <v>441</v>
       </c>
-      <c r="G7" s="147"/>
-      <c r="H7" s="147"/>
-      <c r="I7" s="147"/>
-      <c r="J7" s="147"/>
-      <c r="K7" s="147"/>
-      <c r="L7" s="147"/>
-      <c r="M7" s="147"/>
-      <c r="N7" s="147"/>
-      <c r="O7" s="147"/>
-      <c r="P7" s="147"/>
+      <c r="G7" s="148"/>
+      <c r="H7" s="148"/>
+      <c r="I7" s="148"/>
+      <c r="J7" s="148"/>
+      <c r="K7" s="148"/>
+      <c r="L7" s="148"/>
+      <c r="M7" s="148"/>
+      <c r="N7" s="148"/>
+      <c r="O7" s="148"/>
+      <c r="P7" s="148"/>
     </row>
     <row r="8" spans="1:17">
       <c r="B8" s="32" t="s">
@@ -22427,7 +22810,7 @@
         <v>463</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -22469,40 +22852,40 @@
       <c r="A24" s="35" t="s">
         <v>455</v>
       </c>
-      <c r="B24" s="148" t="s">
+      <c r="B24" s="149" t="s">
         <v>457</v>
       </c>
-      <c r="C24" s="148"/>
-      <c r="D24" s="148"/>
-      <c r="E24" s="148"/>
-      <c r="F24" s="148"/>
-      <c r="G24" s="148"/>
+      <c r="C24" s="149"/>
+      <c r="D24" s="149"/>
+      <c r="E24" s="149"/>
+      <c r="F24" s="149"/>
+      <c r="G24" s="149"/>
     </row>
     <row r="25" spans="1:7" ht="30">
       <c r="A25" s="35" t="s">
         <v>462</v>
       </c>
-      <c r="B25" s="149" t="s">
+      <c r="B25" s="150" t="s">
         <v>464</v>
       </c>
-      <c r="C25" s="149"/>
-      <c r="D25" s="149"/>
-      <c r="E25" s="149"/>
-      <c r="F25" s="149"/>
-      <c r="G25" s="149"/>
+      <c r="C25" s="150"/>
+      <c r="D25" s="150"/>
+      <c r="E25" s="150"/>
+      <c r="F25" s="150"/>
+      <c r="G25" s="150"/>
     </row>
     <row r="26" spans="1:7" ht="159" customHeight="1">
       <c r="A26" s="35" t="s">
         <v>459</v>
       </c>
-      <c r="B26" s="148" t="s">
+      <c r="B26" s="149" t="s">
         <v>460</v>
       </c>
-      <c r="C26" s="148"/>
-      <c r="D26" s="148"/>
-      <c r="E26" s="148"/>
-      <c r="F26" s="148"/>
-      <c r="G26" s="148"/>
+      <c r="C26" s="149"/>
+      <c r="D26" s="149"/>
+      <c r="E26" s="149"/>
+      <c r="F26" s="149"/>
+      <c r="G26" s="149"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -23017,29 +23400,29 @@
       <c r="B27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="C27" s="152" t="s">
+      <c r="C27" s="153" t="s">
         <v>622</v>
       </c>
-      <c r="D27" s="153"/>
+      <c r="D27" s="154"/>
       <c r="E27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="F27" s="152" t="s">
+      <c r="F27" s="153" t="s">
         <v>622</v>
       </c>
-      <c r="G27" s="153"/>
+      <c r="G27" s="154"/>
       <c r="H27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="I27" s="152" t="s">
+      <c r="I27" s="153" t="s">
         <v>622</v>
       </c>
-      <c r="J27" s="153"/>
-      <c r="L27" s="164" t="s">
+      <c r="J27" s="154"/>
+      <c r="L27" s="165" t="s">
         <v>694</v>
       </c>
-      <c r="M27" s="164"/>
-      <c r="N27" s="164"/>
+      <c r="M27" s="165"/>
+      <c r="N27" s="165"/>
     </row>
     <row r="28" spans="1:14" ht="32.25" thickBot="1">
       <c r="A28" s="81">
@@ -23048,29 +23431,29 @@
       <c r="B28" s="69" t="s">
         <v>623</v>
       </c>
-      <c r="C28" s="150" t="s">
+      <c r="C28" s="151" t="s">
         <v>624</v>
       </c>
-      <c r="D28" s="151"/>
+      <c r="D28" s="152"/>
       <c r="E28" s="70" t="s">
         <v>645</v>
       </c>
-      <c r="F28" s="154" t="s">
+      <c r="F28" s="155" t="s">
         <v>646</v>
       </c>
-      <c r="G28" s="155"/>
+      <c r="G28" s="156"/>
       <c r="H28" s="69" t="s">
         <v>667</v>
       </c>
-      <c r="I28" s="150" t="s">
+      <c r="I28" s="151" t="s">
         <v>668</v>
       </c>
-      <c r="J28" s="151"/>
-      <c r="L28" s="165" t="s">
+      <c r="J28" s="152"/>
+      <c r="L28" s="166" t="s">
         <v>695</v>
       </c>
-      <c r="M28" s="165"/>
-      <c r="N28" s="165"/>
+      <c r="M28" s="166"/>
+      <c r="N28" s="166"/>
     </row>
     <row r="29" spans="1:14" ht="31.5" thickBot="1">
       <c r="A29" s="81">
@@ -23079,29 +23462,29 @@
       <c r="B29" s="70" t="s">
         <v>625</v>
       </c>
-      <c r="C29" s="154" t="s">
+      <c r="C29" s="155" t="s">
         <v>626</v>
       </c>
-      <c r="D29" s="155"/>
+      <c r="D29" s="156"/>
       <c r="E29" s="69" t="s">
         <v>647</v>
       </c>
-      <c r="F29" s="150" t="s">
+      <c r="F29" s="151" t="s">
         <v>648</v>
       </c>
-      <c r="G29" s="151"/>
+      <c r="G29" s="152"/>
       <c r="H29" s="70" t="s">
         <v>669</v>
       </c>
-      <c r="I29" s="158" t="s">
+      <c r="I29" s="159" t="s">
         <v>670</v>
       </c>
-      <c r="J29" s="159"/>
-      <c r="L29" s="164" t="s">
+      <c r="J29" s="160"/>
+      <c r="L29" s="165" t="s">
         <v>696</v>
       </c>
-      <c r="M29" s="164"/>
-      <c r="N29" s="164"/>
+      <c r="M29" s="165"/>
+      <c r="N29" s="165"/>
     </row>
     <row r="30" spans="1:14" ht="15.75" thickBot="1">
       <c r="A30" s="81">
@@ -23110,29 +23493,29 @@
       <c r="B30" s="69" t="s">
         <v>627</v>
       </c>
-      <c r="C30" s="150" t="s">
+      <c r="C30" s="151" t="s">
         <v>628</v>
       </c>
-      <c r="D30" s="151"/>
+      <c r="D30" s="152"/>
       <c r="E30" s="70" t="s">
         <v>649</v>
       </c>
-      <c r="F30" s="154" t="s">
+      <c r="F30" s="155" t="s">
         <v>650</v>
       </c>
-      <c r="G30" s="155"/>
+      <c r="G30" s="156"/>
       <c r="H30" s="69" t="s">
         <v>671</v>
       </c>
-      <c r="I30" s="150" t="s">
+      <c r="I30" s="151" t="s">
         <v>672</v>
       </c>
-      <c r="J30" s="151"/>
-      <c r="L30" s="165" t="s">
+      <c r="J30" s="152"/>
+      <c r="L30" s="166" t="s">
         <v>697</v>
       </c>
-      <c r="M30" s="165"/>
-      <c r="N30" s="165"/>
+      <c r="M30" s="166"/>
+      <c r="N30" s="166"/>
     </row>
     <row r="31" spans="1:14" ht="17.25" customHeight="1" thickBot="1">
       <c r="A31" s="81">
@@ -23141,29 +23524,29 @@
       <c r="B31" s="70" t="s">
         <v>629</v>
       </c>
-      <c r="C31" s="154" t="s">
+      <c r="C31" s="155" t="s">
         <v>630</v>
       </c>
-      <c r="D31" s="155"/>
+      <c r="D31" s="156"/>
       <c r="E31" s="69" t="s">
         <v>651</v>
       </c>
-      <c r="F31" s="150" t="s">
+      <c r="F31" s="151" t="s">
         <v>652</v>
       </c>
-      <c r="G31" s="151"/>
+      <c r="G31" s="152"/>
       <c r="H31" s="70" t="s">
         <v>673</v>
       </c>
-      <c r="I31" s="154" t="s">
+      <c r="I31" s="155" t="s">
         <v>674</v>
       </c>
-      <c r="J31" s="155"/>
-      <c r="L31" s="164" t="s">
+      <c r="J31" s="156"/>
+      <c r="L31" s="165" t="s">
         <v>698</v>
       </c>
-      <c r="M31" s="164"/>
-      <c r="N31" s="164"/>
+      <c r="M31" s="165"/>
+      <c r="N31" s="165"/>
     </row>
     <row r="32" spans="1:14" ht="43.5" customHeight="1" thickBot="1">
       <c r="A32" s="81">
@@ -23172,29 +23555,29 @@
       <c r="B32" s="69" t="s">
         <v>631</v>
       </c>
-      <c r="C32" s="150" t="s">
+      <c r="C32" s="151" t="s">
         <v>632</v>
       </c>
-      <c r="D32" s="151"/>
+      <c r="D32" s="152"/>
       <c r="E32" s="70" t="s">
         <v>653</v>
       </c>
-      <c r="F32" s="154" t="s">
+      <c r="F32" s="155" t="s">
         <v>654</v>
       </c>
-      <c r="G32" s="155"/>
+      <c r="G32" s="156"/>
       <c r="H32" s="69" t="s">
         <v>675</v>
       </c>
-      <c r="I32" s="150" t="s">
+      <c r="I32" s="151" t="s">
         <v>676</v>
       </c>
-      <c r="J32" s="151"/>
-      <c r="L32" s="165" t="s">
+      <c r="J32" s="152"/>
+      <c r="L32" s="166" t="s">
         <v>699</v>
       </c>
-      <c r="M32" s="165"/>
-      <c r="N32" s="165"/>
+      <c r="M32" s="166"/>
+      <c r="N32" s="166"/>
     </row>
     <row r="33" spans="1:14" ht="31.5" customHeight="1" thickBot="1">
       <c r="A33" s="81">
@@ -23203,29 +23586,29 @@
       <c r="B33" s="70" t="s">
         <v>633</v>
       </c>
-      <c r="C33" s="154" t="s">
+      <c r="C33" s="155" t="s">
         <v>634</v>
       </c>
-      <c r="D33" s="155"/>
+      <c r="D33" s="156"/>
       <c r="E33" s="69" t="s">
         <v>655</v>
       </c>
-      <c r="F33" s="150" t="s">
+      <c r="F33" s="151" t="s">
         <v>656</v>
       </c>
-      <c r="G33" s="151"/>
+      <c r="G33" s="152"/>
       <c r="H33" s="70" t="s">
         <v>677</v>
       </c>
-      <c r="I33" s="156" t="s">
+      <c r="I33" s="157" t="s">
         <v>678</v>
       </c>
-      <c r="J33" s="157"/>
-      <c r="L33" s="164" t="s">
+      <c r="J33" s="158"/>
+      <c r="L33" s="165" t="s">
         <v>700</v>
       </c>
-      <c r="M33" s="164"/>
-      <c r="N33" s="164"/>
+      <c r="M33" s="165"/>
+      <c r="N33" s="165"/>
     </row>
     <row r="34" spans="1:14" ht="28.5" customHeight="1" thickBot="1">
       <c r="A34" s="81">
@@ -23234,29 +23617,29 @@
       <c r="B34" s="69" t="s">
         <v>635</v>
       </c>
-      <c r="C34" s="150" t="s">
+      <c r="C34" s="151" t="s">
         <v>636</v>
       </c>
-      <c r="D34" s="151"/>
+      <c r="D34" s="152"/>
       <c r="E34" s="70" t="s">
         <v>657</v>
       </c>
-      <c r="F34" s="154" t="s">
+      <c r="F34" s="155" t="s">
         <v>658</v>
       </c>
-      <c r="G34" s="155"/>
+      <c r="G34" s="156"/>
       <c r="H34" s="69" t="s">
         <v>679</v>
       </c>
-      <c r="I34" s="160" t="s">
+      <c r="I34" s="161" t="s">
         <v>680</v>
       </c>
-      <c r="J34" s="161"/>
-      <c r="L34" s="165" t="s">
+      <c r="J34" s="162"/>
+      <c r="L34" s="166" t="s">
         <v>701</v>
       </c>
-      <c r="M34" s="165"/>
-      <c r="N34" s="165"/>
+      <c r="M34" s="166"/>
+      <c r="N34" s="166"/>
     </row>
     <row r="35" spans="1:14" ht="31.5" customHeight="1" thickBot="1">
       <c r="A35" s="81">
@@ -23265,29 +23648,29 @@
       <c r="B35" s="70" t="s">
         <v>637</v>
       </c>
-      <c r="C35" s="154" t="s">
+      <c r="C35" s="155" t="s">
         <v>638</v>
       </c>
-      <c r="D35" s="155"/>
+      <c r="D35" s="156"/>
       <c r="E35" s="69" t="s">
         <v>659</v>
       </c>
-      <c r="F35" s="150" t="s">
+      <c r="F35" s="151" t="s">
         <v>660</v>
       </c>
-      <c r="G35" s="151"/>
+      <c r="G35" s="152"/>
       <c r="H35" s="77" t="s">
         <v>681</v>
       </c>
-      <c r="I35" s="154" t="s">
+      <c r="I35" s="155" t="s">
         <v>682</v>
       </c>
-      <c r="J35" s="155"/>
-      <c r="L35" s="164" t="s">
+      <c r="J35" s="156"/>
+      <c r="L35" s="165" t="s">
         <v>702</v>
       </c>
-      <c r="M35" s="164"/>
-      <c r="N35" s="164"/>
+      <c r="M35" s="165"/>
+      <c r="N35" s="165"/>
     </row>
     <row r="36" spans="1:14" ht="60.75" thickBot="1">
       <c r="A36" s="81">
@@ -23296,17 +23679,17 @@
       <c r="B36" s="69" t="s">
         <v>639</v>
       </c>
-      <c r="C36" s="150" t="s">
+      <c r="C36" s="151" t="s">
         <v>640</v>
       </c>
-      <c r="D36" s="151"/>
+      <c r="D36" s="152"/>
       <c r="E36" s="70" t="s">
         <v>661</v>
       </c>
-      <c r="F36" s="154" t="s">
+      <c r="F36" s="155" t="s">
         <v>662</v>
       </c>
-      <c r="G36" s="155"/>
+      <c r="G36" s="156"/>
       <c r="H36" s="78"/>
       <c r="I36" s="71" t="s">
         <v>683</v>
@@ -23314,11 +23697,11 @@
       <c r="J36" s="72" t="s">
         <v>684</v>
       </c>
-      <c r="L36" s="165" t="s">
+      <c r="L36" s="166" t="s">
         <v>703</v>
       </c>
-      <c r="M36" s="165"/>
-      <c r="N36" s="165"/>
+      <c r="M36" s="166"/>
+      <c r="N36" s="166"/>
     </row>
     <row r="37" spans="1:14" ht="75.75" thickBot="1">
       <c r="A37" s="81">
@@ -23327,17 +23710,17 @@
       <c r="B37" s="70" t="s">
         <v>641</v>
       </c>
-      <c r="C37" s="154" t="s">
+      <c r="C37" s="155" t="s">
         <v>642</v>
       </c>
-      <c r="D37" s="155"/>
+      <c r="D37" s="156"/>
       <c r="E37" s="69" t="s">
         <v>663</v>
       </c>
-      <c r="F37" s="150" t="s">
+      <c r="F37" s="151" t="s">
         <v>664</v>
       </c>
-      <c r="G37" s="151"/>
+      <c r="G37" s="152"/>
       <c r="H37" s="78"/>
       <c r="I37" s="73" t="s">
         <v>685</v>
@@ -23353,17 +23736,17 @@
       <c r="B38" s="69" t="s">
         <v>643</v>
       </c>
-      <c r="C38" s="150" t="s">
+      <c r="C38" s="151" t="s">
         <v>644</v>
       </c>
-      <c r="D38" s="151"/>
+      <c r="D38" s="152"/>
       <c r="E38" s="70" t="s">
         <v>665</v>
       </c>
-      <c r="F38" s="154" t="s">
+      <c r="F38" s="155" t="s">
         <v>666</v>
       </c>
-      <c r="G38" s="155"/>
+      <c r="G38" s="156"/>
       <c r="H38" s="78"/>
       <c r="I38" s="75" t="s">
         <v>687</v>
@@ -23379,22 +23762,22 @@
       <c r="B39" s="70" t="s">
         <v>692</v>
       </c>
-      <c r="C39" s="156" t="s">
+      <c r="C39" s="157" t="s">
         <v>693</v>
       </c>
-      <c r="D39" s="157"/>
+      <c r="D39" s="158"/>
       <c r="E39" s="69" t="s">
         <v>690</v>
       </c>
-      <c r="F39" s="160" t="s">
+      <c r="F39" s="161" t="s">
         <v>691</v>
       </c>
-      <c r="G39" s="161"/>
+      <c r="G39" s="162"/>
       <c r="H39" s="79"/>
-      <c r="I39" s="162" t="s">
+      <c r="I39" s="163" t="s">
         <v>689</v>
       </c>
-      <c r="J39" s="163"/>
+      <c r="J39" s="164"/>
     </row>
     <row r="40" spans="1:14" ht="58.5" customHeight="1"/>
     <row r="42" spans="1:14" ht="31.5" customHeight="1"/>
@@ -23507,7 +23890,7 @@
         <v>583</v>
       </c>
       <c r="F2" s="32" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="G2" s="32" t="s">
         <v>415</v>
@@ -23521,7 +23904,7 @@
         <v>469</v>
       </c>
       <c r="D3" s="85" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="E3" s="108" t="s">
         <v>433</v>
@@ -23588,12 +23971,12 @@
         <v>574</v>
       </c>
       <c r="F7" s="112" t="s">
-        <v>919</v>
-      </c>
-      <c r="I7" s="184" t="s">
-        <v>1171</v>
-      </c>
-      <c r="J7" s="184"/>
+        <v>918</v>
+      </c>
+      <c r="I7" s="185" t="s">
+        <v>1170</v>
+      </c>
+      <c r="J7" s="185"/>
       <c r="L7" s="49" t="s">
         <v>601</v>
       </c>
@@ -23611,7 +23994,7 @@
       <c r="D8" s="32" t="s">
         <v>582</v>
       </c>
-      <c r="E8" s="185" t="s">
+      <c r="E8" s="186" t="s">
         <v>583</v>
       </c>
       <c r="F8" s="36" t="s">
@@ -23661,10 +24044,10 @@
       <c r="H9" s="85" t="s">
         <v>466</v>
       </c>
-      <c r="I9" s="119" t="s">
+      <c r="I9" s="120" t="s">
         <v>752</v>
       </c>
-      <c r="J9" s="119" t="s">
+      <c r="J9" s="120" t="s">
         <v>755</v>
       </c>
       <c r="L9" s="9" t="s">
@@ -23776,13 +24159,13 @@
         <v>423</v>
       </c>
       <c r="K14" s="32" t="s">
+        <v>839</v>
+      </c>
+      <c r="L14" s="32" t="s">
         <v>840</v>
       </c>
-      <c r="L14" s="32" t="s">
-        <v>841</v>
-      </c>
       <c r="M14" s="32" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -23796,13 +24179,13 @@
         <v>436</v>
       </c>
       <c r="E15" s="85" t="s">
+        <v>803</v>
+      </c>
+      <c r="F15" s="85" t="s">
         <v>804</v>
       </c>
-      <c r="F15" s="85" t="s">
+      <c r="G15" s="85" t="s">
         <v>805</v>
-      </c>
-      <c r="G15" s="85" t="s">
-        <v>806</v>
       </c>
       <c r="H15" s="85" t="s">
         <v>437</v>
@@ -23814,13 +24197,13 @@
         <v>439</v>
       </c>
       <c r="K15" s="95" t="s">
+        <v>847</v>
+      </c>
+      <c r="L15" s="95" t="s">
         <v>848</v>
       </c>
-      <c r="L15" s="95" t="s">
+      <c r="M15" s="95" t="s">
         <v>849</v>
-      </c>
-      <c r="M15" s="95" t="s">
-        <v>850</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="30">
@@ -23834,31 +24217,31 @@
         <v>572</v>
       </c>
       <c r="E16" s="96" t="s">
+        <v>844</v>
+      </c>
+      <c r="F16" s="96" t="s">
         <v>845</v>
       </c>
-      <c r="F16" s="96" t="s">
-        <v>846</v>
-      </c>
       <c r="G16" s="96" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="H16" s="96" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="I16" s="96" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="J16" s="96" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="K16" s="96" t="s">
+        <v>842</v>
+      </c>
+      <c r="L16" s="96" t="s">
         <v>843</v>
       </c>
-      <c r="L16" s="96" t="s">
-        <v>844</v>
-      </c>
       <c r="M16" s="96" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -23874,13 +24257,13 @@
       <c r="I17" s="65"/>
       <c r="J17" s="65"/>
       <c r="K17" s="97" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="L17" s="97" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="M17" s="97" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -23933,10 +24316,10 @@
       <c r="L20" s="115" t="s">
         <v>568</v>
       </c>
-      <c r="M20" s="166" t="s">
-        <v>921</v>
-      </c>
-      <c r="N20" s="167"/>
+      <c r="M20" s="167" t="s">
+        <v>920</v>
+      </c>
+      <c r="N20" s="168"/>
     </row>
     <row r="21" spans="1:14">
       <c r="B21" s="85" t="s">
@@ -24042,41 +24425,41 @@
         <v>620</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="15.75" thickBot="1">
       <c r="F26" s="7" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="15.75" thickBot="1">
       <c r="B27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="C27" s="152" t="s">
+      <c r="C27" s="153" t="s">
         <v>622</v>
       </c>
-      <c r="D27" s="153"/>
+      <c r="D27" s="154"/>
       <c r="E27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="F27" s="152" t="s">
+      <c r="F27" s="153" t="s">
         <v>622</v>
       </c>
-      <c r="G27" s="153"/>
+      <c r="G27" s="154"/>
       <c r="H27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="I27" s="152" t="s">
+      <c r="I27" s="153" t="s">
         <v>622</v>
       </c>
-      <c r="J27" s="153"/>
-      <c r="L27" s="164" t="s">
+      <c r="J27" s="154"/>
+      <c r="L27" s="165" t="s">
         <v>694</v>
       </c>
-      <c r="M27" s="164"/>
-      <c r="N27" s="164"/>
+      <c r="M27" s="165"/>
+      <c r="N27" s="165"/>
     </row>
     <row r="28" spans="1:14" ht="49.5" customHeight="1" thickBot="1">
       <c r="A28" s="81">
@@ -24085,29 +24468,29 @@
       <c r="B28" s="69" t="s">
         <v>623</v>
       </c>
-      <c r="C28" s="150" t="s">
+      <c r="C28" s="151" t="s">
         <v>624</v>
       </c>
-      <c r="D28" s="151"/>
+      <c r="D28" s="152"/>
       <c r="E28" s="70" t="s">
         <v>645</v>
       </c>
-      <c r="F28" s="154" t="s">
-        <v>1183</v>
-      </c>
-      <c r="G28" s="155"/>
+      <c r="F28" s="155" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G28" s="156"/>
       <c r="H28" s="69" t="s">
         <v>667</v>
       </c>
-      <c r="I28" s="150" t="s">
+      <c r="I28" s="151" t="s">
         <v>668</v>
       </c>
-      <c r="J28" s="151"/>
-      <c r="L28" s="165" t="s">
+      <c r="J28" s="152"/>
+      <c r="L28" s="166" t="s">
         <v>695</v>
       </c>
-      <c r="M28" s="165"/>
-      <c r="N28" s="165"/>
+      <c r="M28" s="166"/>
+      <c r="N28" s="166"/>
     </row>
     <row r="29" spans="1:14" ht="31.5" thickBot="1">
       <c r="A29" s="81">
@@ -24116,29 +24499,29 @@
       <c r="B29" s="70" t="s">
         <v>625</v>
       </c>
-      <c r="C29" s="154" t="s">
+      <c r="C29" s="155" t="s">
         <v>626</v>
       </c>
-      <c r="D29" s="155"/>
+      <c r="D29" s="156"/>
       <c r="E29" s="69" t="s">
         <v>647</v>
       </c>
-      <c r="F29" s="150" t="s">
+      <c r="F29" s="151" t="s">
         <v>648</v>
       </c>
-      <c r="G29" s="151"/>
+      <c r="G29" s="152"/>
       <c r="H29" s="70" t="s">
         <v>669</v>
       </c>
-      <c r="I29" s="158" t="s">
+      <c r="I29" s="159" t="s">
         <v>670</v>
       </c>
-      <c r="J29" s="159"/>
-      <c r="L29" s="164" t="s">
+      <c r="J29" s="160"/>
+      <c r="L29" s="165" t="s">
         <v>696</v>
       </c>
-      <c r="M29" s="164"/>
-      <c r="N29" s="164"/>
+      <c r="M29" s="165"/>
+      <c r="N29" s="165"/>
     </row>
     <row r="30" spans="1:14" ht="15.75" thickBot="1">
       <c r="A30" s="81">
@@ -24147,29 +24530,29 @@
       <c r="B30" s="69" t="s">
         <v>627</v>
       </c>
-      <c r="C30" s="150" t="s">
+      <c r="C30" s="151" t="s">
         <v>628</v>
       </c>
-      <c r="D30" s="151"/>
+      <c r="D30" s="152"/>
       <c r="E30" s="70" t="s">
         <v>649</v>
       </c>
-      <c r="F30" s="154" t="s">
+      <c r="F30" s="155" t="s">
         <v>650</v>
       </c>
-      <c r="G30" s="155"/>
+      <c r="G30" s="156"/>
       <c r="H30" s="69" t="s">
         <v>671</v>
       </c>
-      <c r="I30" s="150" t="s">
+      <c r="I30" s="151" t="s">
         <v>672</v>
       </c>
-      <c r="J30" s="151"/>
-      <c r="L30" s="165" t="s">
+      <c r="J30" s="152"/>
+      <c r="L30" s="166" t="s">
         <v>697</v>
       </c>
-      <c r="M30" s="165"/>
-      <c r="N30" s="165"/>
+      <c r="M30" s="166"/>
+      <c r="N30" s="166"/>
     </row>
     <row r="31" spans="1:14" ht="17.25" customHeight="1" thickBot="1">
       <c r="A31" s="81">
@@ -24178,29 +24561,29 @@
       <c r="B31" s="70" t="s">
         <v>629</v>
       </c>
-      <c r="C31" s="154" t="s">
+      <c r="C31" s="155" t="s">
         <v>630</v>
       </c>
-      <c r="D31" s="155"/>
+      <c r="D31" s="156"/>
       <c r="E31" s="69" t="s">
         <v>651</v>
       </c>
-      <c r="F31" s="150" t="s">
+      <c r="F31" s="151" t="s">
         <v>652</v>
       </c>
-      <c r="G31" s="151"/>
+      <c r="G31" s="152"/>
       <c r="H31" s="70" t="s">
         <v>673</v>
       </c>
-      <c r="I31" s="154" t="s">
+      <c r="I31" s="155" t="s">
         <v>674</v>
       </c>
-      <c r="J31" s="155"/>
-      <c r="L31" s="164" t="s">
+      <c r="J31" s="156"/>
+      <c r="L31" s="165" t="s">
         <v>698</v>
       </c>
-      <c r="M31" s="164"/>
-      <c r="N31" s="164"/>
+      <c r="M31" s="165"/>
+      <c r="N31" s="165"/>
     </row>
     <row r="32" spans="1:14" ht="43.5" customHeight="1" thickBot="1">
       <c r="A32" s="81">
@@ -24209,29 +24592,29 @@
       <c r="B32" s="69" t="s">
         <v>631</v>
       </c>
-      <c r="C32" s="150" t="s">
+      <c r="C32" s="151" t="s">
         <v>632</v>
       </c>
-      <c r="D32" s="151"/>
+      <c r="D32" s="152"/>
       <c r="E32" s="70" t="s">
         <v>653</v>
       </c>
-      <c r="F32" s="154" t="s">
+      <c r="F32" s="155" t="s">
         <v>654</v>
       </c>
-      <c r="G32" s="155"/>
+      <c r="G32" s="156"/>
       <c r="H32" s="69" t="s">
         <v>675</v>
       </c>
-      <c r="I32" s="150" t="s">
+      <c r="I32" s="151" t="s">
         <v>676</v>
       </c>
-      <c r="J32" s="151"/>
-      <c r="L32" s="165" t="s">
+      <c r="J32" s="152"/>
+      <c r="L32" s="166" t="s">
         <v>699</v>
       </c>
-      <c r="M32" s="165"/>
-      <c r="N32" s="165"/>
+      <c r="M32" s="166"/>
+      <c r="N32" s="166"/>
     </row>
     <row r="33" spans="1:14" ht="31.5" customHeight="1" thickBot="1">
       <c r="A33" s="81">
@@ -24240,29 +24623,29 @@
       <c r="B33" s="70" t="s">
         <v>633</v>
       </c>
-      <c r="C33" s="154" t="s">
+      <c r="C33" s="155" t="s">
         <v>634</v>
       </c>
-      <c r="D33" s="155"/>
+      <c r="D33" s="156"/>
       <c r="E33" s="69" t="s">
         <v>655</v>
       </c>
-      <c r="F33" s="150" t="s">
+      <c r="F33" s="151" t="s">
         <v>656</v>
       </c>
-      <c r="G33" s="151"/>
+      <c r="G33" s="152"/>
       <c r="H33" s="70" t="s">
         <v>677</v>
       </c>
-      <c r="I33" s="156" t="s">
+      <c r="I33" s="157" t="s">
         <v>678</v>
       </c>
-      <c r="J33" s="157"/>
-      <c r="L33" s="164" t="s">
+      <c r="J33" s="158"/>
+      <c r="L33" s="165" t="s">
         <v>700</v>
       </c>
-      <c r="M33" s="164"/>
-      <c r="N33" s="164"/>
+      <c r="M33" s="165"/>
+      <c r="N33" s="165"/>
     </row>
     <row r="34" spans="1:14" ht="28.5" customHeight="1" thickBot="1">
       <c r="A34" s="81">
@@ -24271,29 +24654,29 @@
       <c r="B34" s="69" t="s">
         <v>635</v>
       </c>
-      <c r="C34" s="150" t="s">
+      <c r="C34" s="151" t="s">
         <v>636</v>
       </c>
-      <c r="D34" s="151"/>
+      <c r="D34" s="152"/>
       <c r="E34" s="70" t="s">
         <v>657</v>
       </c>
-      <c r="F34" s="154" t="s">
+      <c r="F34" s="155" t="s">
         <v>658</v>
       </c>
-      <c r="G34" s="155"/>
+      <c r="G34" s="156"/>
       <c r="H34" s="69" t="s">
         <v>679</v>
       </c>
-      <c r="I34" s="160" t="s">
+      <c r="I34" s="161" t="s">
         <v>680</v>
       </c>
-      <c r="J34" s="161"/>
-      <c r="L34" s="165" t="s">
+      <c r="J34" s="162"/>
+      <c r="L34" s="166" t="s">
         <v>701</v>
       </c>
-      <c r="M34" s="165"/>
-      <c r="N34" s="165"/>
+      <c r="M34" s="166"/>
+      <c r="N34" s="166"/>
     </row>
     <row r="35" spans="1:14" ht="31.5" customHeight="1" thickBot="1">
       <c r="A35" s="81">
@@ -24302,29 +24685,29 @@
       <c r="B35" s="70" t="s">
         <v>637</v>
       </c>
-      <c r="C35" s="154" t="s">
+      <c r="C35" s="155" t="s">
         <v>638</v>
       </c>
-      <c r="D35" s="155"/>
+      <c r="D35" s="156"/>
       <c r="E35" s="69" t="s">
         <v>659</v>
       </c>
-      <c r="F35" s="150" t="s">
+      <c r="F35" s="151" t="s">
         <v>660</v>
       </c>
-      <c r="G35" s="151"/>
+      <c r="G35" s="152"/>
       <c r="H35" s="77" t="s">
         <v>681</v>
       </c>
-      <c r="I35" s="154" t="s">
+      <c r="I35" s="155" t="s">
         <v>682</v>
       </c>
-      <c r="J35" s="155"/>
-      <c r="L35" s="164" t="s">
+      <c r="J35" s="156"/>
+      <c r="L35" s="165" t="s">
         <v>702</v>
       </c>
-      <c r="M35" s="164"/>
-      <c r="N35" s="164"/>
+      <c r="M35" s="165"/>
+      <c r="N35" s="165"/>
     </row>
     <row r="36" spans="1:14" ht="60.75" thickBot="1">
       <c r="A36" s="81">
@@ -24333,17 +24716,17 @@
       <c r="B36" s="69" t="s">
         <v>639</v>
       </c>
-      <c r="C36" s="150" t="s">
+      <c r="C36" s="151" t="s">
         <v>640</v>
       </c>
-      <c r="D36" s="151"/>
+      <c r="D36" s="152"/>
       <c r="E36" s="70" t="s">
         <v>661</v>
       </c>
-      <c r="F36" s="154" t="s">
+      <c r="F36" s="155" t="s">
         <v>662</v>
       </c>
-      <c r="G36" s="155"/>
+      <c r="G36" s="156"/>
       <c r="H36" s="78"/>
       <c r="I36" s="71" t="s">
         <v>683</v>
@@ -24351,11 +24734,11 @@
       <c r="J36" s="72" t="s">
         <v>684</v>
       </c>
-      <c r="L36" s="165" t="s">
+      <c r="L36" s="166" t="s">
         <v>703</v>
       </c>
-      <c r="M36" s="165"/>
-      <c r="N36" s="165"/>
+      <c r="M36" s="166"/>
+      <c r="N36" s="166"/>
     </row>
     <row r="37" spans="1:14" ht="75.75" thickBot="1">
       <c r="A37" s="81">
@@ -24364,17 +24747,17 @@
       <c r="B37" s="70" t="s">
         <v>641</v>
       </c>
-      <c r="C37" s="154" t="s">
+      <c r="C37" s="155" t="s">
         <v>642</v>
       </c>
-      <c r="D37" s="155"/>
+      <c r="D37" s="156"/>
       <c r="E37" s="69" t="s">
         <v>663</v>
       </c>
-      <c r="F37" s="150" t="s">
+      <c r="F37" s="151" t="s">
         <v>664</v>
       </c>
-      <c r="G37" s="151"/>
+      <c r="G37" s="152"/>
       <c r="H37" s="78"/>
       <c r="I37" s="73" t="s">
         <v>685</v>
@@ -24390,17 +24773,17 @@
       <c r="B38" s="69" t="s">
         <v>643</v>
       </c>
-      <c r="C38" s="150" t="s">
+      <c r="C38" s="151" t="s">
         <v>644</v>
       </c>
-      <c r="D38" s="151"/>
+      <c r="D38" s="152"/>
       <c r="E38" s="70" t="s">
         <v>665</v>
       </c>
-      <c r="F38" s="154" t="s">
+      <c r="F38" s="155" t="s">
         <v>666</v>
       </c>
-      <c r="G38" s="155"/>
+      <c r="G38" s="156"/>
       <c r="H38" s="78"/>
       <c r="I38" s="75" t="s">
         <v>687</v>
@@ -24416,22 +24799,22 @@
       <c r="B39" s="70" t="s">
         <v>692</v>
       </c>
-      <c r="C39" s="156" t="s">
+      <c r="C39" s="157" t="s">
         <v>693</v>
       </c>
-      <c r="D39" s="157"/>
+      <c r="D39" s="158"/>
       <c r="E39" s="69" t="s">
         <v>690</v>
       </c>
-      <c r="F39" s="160" t="s">
+      <c r="F39" s="161" t="s">
         <v>691</v>
       </c>
-      <c r="G39" s="161"/>
+      <c r="G39" s="162"/>
       <c r="H39" s="79"/>
-      <c r="I39" s="162" t="s">
+      <c r="I39" s="163" t="s">
         <v>689</v>
       </c>
-      <c r="J39" s="163"/>
+      <c r="J39" s="164"/>
     </row>
     <row r="40" spans="1:14" ht="58.5" customHeight="1"/>
     <row r="41" spans="1:14">
@@ -24610,7 +24993,7 @@
       <c r="B49" s="85" t="s">
         <v>429</v>
       </c>
-      <c r="C49" s="119" t="s">
+      <c r="C49" s="120" t="s">
         <v>752</v>
       </c>
       <c r="D49" s="85" t="s">

--- a/2020_LogAnalyzer_Leeheesuk.xlsx
+++ b/2020_LogAnalyzer_Leeheesuk.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="22827"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72130773-F0C9-492F-BC86-F2E36F76932E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0A825EA-7FF9-44F0-9FFE-78C8C1343DE3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" firstSheet="10" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UI" sheetId="7" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2009" uniqueCount="1261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2030" uniqueCount="1271">
   <si>
     <t>구분</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4395,9 +4395,6 @@
     <t>Step2</t>
   </si>
   <si>
-    <t>Cancel</t>
-  </si>
-  <si>
     <t>OK</t>
   </si>
   <si>
@@ -4450,9 +4447,6 @@
   </si>
   <si>
     <t>현재 정보</t>
-  </si>
-  <si>
-    <t>Add(Step2)</t>
   </si>
   <si>
     <t>file upload부분</t>
@@ -5533,9 +5527,6 @@
     <t>## df 나누어 읽기 : 총 작업 시간 91.2467</t>
   </si>
   <si>
-    <t>목표시간 : 2GB 기준, 300s (5m)</t>
-  </si>
-  <si>
     <t>7/17/2020
 7/20/2020</t>
   </si>
@@ -5575,9 +5566,6 @@
   <si>
     <t>INSERT
 FLOW</t>
-  </si>
-  <si>
-    <t>StringIO</t>
   </si>
   <si>
     <t>Duration to create temporary csv : 54.79590201377869
@@ -5634,9 +5622,6 @@
     <t>MP 테스트</t>
   </si>
   <si>
-    <t>access log 파일 준비</t>
-  </si>
-  <si>
     <t>File I/O</t>
   </si>
   <si>
@@ -5644,6 +5629,52 @@
   </si>
   <si>
     <t>Network + DB I/O</t>
+  </si>
+  <si>
+    <t>목표시간 : 1GB 기준, 300s (5m) 이내</t>
+  </si>
+  <si>
+    <t>StringIO 테스트</t>
+  </si>
+  <si>
+    <t>access log 파일 업로드</t>
+  </si>
+  <si>
+    <t>Network</t>
+  </si>
+  <si>
+    <t>차트 Mapping</t>
+  </si>
+  <si>
+    <t>시, 시분, 시분초 평균
+Line</t>
+  </si>
+  <si>
+    <t>Stacked Bar</t>
+  </si>
+  <si>
+    <t>20x/40x 및 50x 비율</t>
+  </si>
+  <si>
+    <t>Status 오류비율</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>없음</t>
+  </si>
+  <si>
+    <t>Next</t>
+  </si>
+  <si>
+    <t>Prev(기본화면)</t>
+  </si>
+  <si>
+    <t>TAB번호</t>
+  </si>
+  <si>
+    <t>Next(Step2 or Step3)</t>
   </si>
 </sst>
 </file>
@@ -5653,7 +5684,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
-  <fonts count="39">
+  <fonts count="40">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5930,6 +5961,11 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="15">
     <fill>
@@ -6017,7 +6053,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="23">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -6287,12 +6323,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="204">
+  <cellXfs count="209">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6595,8 +6640,8 @@
     <xf numFmtId="0" fontId="16" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6615,9 +6660,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
@@ -6832,20 +6874,34 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -11352,7 +11408,7 @@
       <xdr:col>9</xdr:col>
       <xdr:colOff>321228</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>45943</xdr:rowOff>
+      <xdr:rowOff>34737</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -11478,7 +11534,7 @@
       <xdr:col>9</xdr:col>
       <xdr:colOff>390525</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:rowOff>17369</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -11513,13 +11569,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>1371601</xdr:colOff>
       <xdr:row>14</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>361951</xdr:colOff>
       <xdr:row>16</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
@@ -11584,16 +11640,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>1362076</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:rowOff>86846</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>352426</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:rowOff>10646</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -11608,8 +11664,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10791826" y="4400550"/>
-          <a:ext cx="1714500" cy="304800"/>
+          <a:off x="11368929" y="4356287"/>
+          <a:ext cx="1713379" cy="316006"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -11655,13 +11711,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>552451</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
+      <xdr:col>13</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
       <xdr:row>25</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
@@ -11733,15 +11789,7 @@
                 <a:srgbClr val="FF0000"/>
               </a:solidFill>
             </a:rPr>
-            <a:t>받아야 한다</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>.</a:t>
+            <a:t>필요</a:t>
           </a:r>
           <a:endParaRPr lang="en-US" sz="1100">
             <a:solidFill>
@@ -11755,13 +11803,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
+      <xdr:col>13</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
       <xdr:row>15</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>1371601</xdr:colOff>
       <xdr:row>24</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
@@ -11811,13 +11859,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
+      <xdr:col>13</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:rowOff>54349</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>1362076</xdr:colOff>
       <xdr:row>24</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
@@ -11838,8 +11886,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="8239125" y="4552950"/>
-          <a:ext cx="2552701" cy="371475"/>
+          <a:off x="8810625" y="4514290"/>
+          <a:ext cx="2558304" cy="433107"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -11867,16 +11915,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>380999</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>380998</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:rowOff>142876</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>47624</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>537882</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>89648</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -11891,8 +11939,440 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12534899" y="4400550"/>
-          <a:ext cx="1495425" cy="295275"/>
+          <a:off x="13110880" y="4412317"/>
+          <a:ext cx="2577355" cy="910478"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>logmaster</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>  </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>존재 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>: project id </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>가져오기</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>                                (Row</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>선택시</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>파일 추가여부 확인</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(Y:Step2, N:Step3)</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>390523</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>537881</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="TextBox 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{572F11A4-3390-44D0-932E-C0330210EF6B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13120405" y="6147547"/>
+          <a:ext cx="2567829" cy="306481"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>logfile</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>생성</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>380999</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>152399</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>593912</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>78440</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="TextBox 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E62E934-0751-4700-B537-9BDAEA21C99A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13110881" y="7873252"/>
+          <a:ext cx="2633384" cy="889747"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>New</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> : </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>logdetail</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>생성</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Exist : </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>이미 생성된 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>1</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>건 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Detail </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>정보 가져오기</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>380998</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>504264</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="TextBox 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF75973D-1005-47D8-9505-B965BC6FA0E8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13110880" y="3088341"/>
+          <a:ext cx="2543737" cy="295275"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -11962,298 +12442,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>390524</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>57149</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="14" name="TextBox 13">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{572F11A4-3390-44D0-932E-C0330210EF6B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="12544424" y="6124575"/>
-          <a:ext cx="1495425" cy="295275"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>logfile</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>생성</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1100">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>380999</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>47624</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="15" name="TextBox 14">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E62E934-0751-4700-B537-9BDAEA21C99A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="12534899" y="7839075"/>
-          <a:ext cx="1495425" cy="295275"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>logdetail</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>생성</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1100">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>380999</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>47624</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="16" name="TextBox 15">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF75973D-1005-47D8-9505-B965BC6FA0E8}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="12534899" y="3076575"/>
-          <a:ext cx="1495425" cy="295275"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>logmaster</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>생성</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1100">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>13</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>1362076</xdr:colOff>
       <xdr:row>30</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>352426</xdr:colOff>
       <xdr:row>32</xdr:row>
       <xdr:rowOff>85725</xdr:rowOff>
@@ -12318,13 +12513,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>1362076</xdr:colOff>
       <xdr:row>39</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>352426</xdr:colOff>
       <xdr:row>41</xdr:row>
       <xdr:rowOff>85725</xdr:rowOff>
@@ -12344,6 +12539,161 @@
         <a:xfrm>
           <a:off x="10791826" y="7848600"/>
           <a:ext cx="1714500" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="15875" cmpd="sng">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="r"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>click</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>530040</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>112059</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>25214</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>180414</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="TextBox 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{80A4B39B-EA68-48B6-8835-97AC30238B32}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6581216" y="6297706"/>
+          <a:ext cx="2206998" cy="460561"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="15875" cmpd="sng">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="r"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>logfile id </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>필요</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>145674</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>424703</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>69474</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="TextBox 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD032AD7-02F8-4AB9-8ACF-9680E575B3F3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10836088" y="1927409"/>
+          <a:ext cx="1713380" cy="304800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -15775,51 +16125,51 @@
     </row>
     <row r="17" spans="1:13">
       <c r="J17" s="19"/>
-      <c r="K17" s="133" t="s">
+      <c r="K17" s="132" t="s">
         <v>537</v>
       </c>
-      <c r="L17" s="134"/>
-      <c r="M17" s="135"/>
+      <c r="L17" s="133"/>
+      <c r="M17" s="134"/>
     </row>
     <row r="18" spans="1:13">
       <c r="J18" s="19">
         <v>1</v>
       </c>
-      <c r="K18" s="136" t="s">
+      <c r="K18" s="135" t="s">
         <v>538</v>
       </c>
-      <c r="L18" s="137"/>
-      <c r="M18" s="138"/>
+      <c r="L18" s="136"/>
+      <c r="M18" s="137"/>
     </row>
     <row r="19" spans="1:13">
       <c r="J19" s="19">
         <v>2</v>
       </c>
-      <c r="K19" s="136" t="s">
+      <c r="K19" s="135" t="s">
         <v>539</v>
       </c>
-      <c r="L19" s="137"/>
-      <c r="M19" s="138"/>
+      <c r="L19" s="136"/>
+      <c r="M19" s="137"/>
     </row>
     <row r="20" spans="1:13">
       <c r="J20" s="19">
         <v>3</v>
       </c>
-      <c r="K20" s="136" t="s">
+      <c r="K20" s="135" t="s">
         <v>540</v>
       </c>
-      <c r="L20" s="137"/>
-      <c r="M20" s="138"/>
+      <c r="L20" s="136"/>
+      <c r="M20" s="137"/>
     </row>
     <row r="21" spans="1:13">
       <c r="J21" s="19">
         <v>4</v>
       </c>
-      <c r="K21" s="136" t="s">
+      <c r="K21" s="135" t="s">
         <v>541</v>
       </c>
-      <c r="L21" s="137"/>
-      <c r="M21" s="138"/>
+      <c r="L21" s="136"/>
+      <c r="M21" s="137"/>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="43" t="s">
@@ -16381,10 +16731,10 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P45"/>
+  <dimension ref="A1:Q45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.140625" customWidth="1"/>
     <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.7109375" customWidth="1"/>
     <col min="4" max="4" width="20.42578125" customWidth="1"/>
@@ -16395,12 +16745,13 @@
     <col min="9" max="9" width="10.140625" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" style="56" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.85546875" style="56" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="40.28515625" customWidth="1"/>
+    <col min="13" max="13" width="28.5703125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="26.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="31.42578125" customWidth="1"/>
+    <col min="15" max="15" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="31.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:17">
       <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
@@ -16432,23 +16783,23 @@
         <v>560</v>
       </c>
       <c r="K1" s="26" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="M1" s="26" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="16.5" customHeight="1">
-      <c r="A2" s="169" t="s">
+    <row r="2" spans="1:17" ht="16.5" customHeight="1">
+      <c r="A2" s="168" t="s">
         <v>504</v>
       </c>
-      <c r="B2" s="175" t="s">
+      <c r="B2" s="174" t="s">
         <v>506</v>
       </c>
-      <c r="C2" s="169" t="s">
+      <c r="C2" s="168" t="s">
         <v>508</v>
       </c>
-      <c r="D2" s="169" t="s">
+      <c r="D2" s="168" t="s">
         <v>556</v>
       </c>
       <c r="E2" s="8"/>
@@ -16470,11 +16821,11 @@
         <v>406</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
-      <c r="A3" s="143"/>
-      <c r="B3" s="176"/>
-      <c r="C3" s="170"/>
-      <c r="D3" s="170"/>
+    <row r="3" spans="1:17">
+      <c r="A3" s="142"/>
+      <c r="B3" s="175"/>
+      <c r="C3" s="169"/>
+      <c r="D3" s="169"/>
       <c r="E3" s="11"/>
       <c r="F3" s="9" t="s">
         <v>310</v>
@@ -16492,11 +16843,11 @@
         <v>547</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
-      <c r="A4" s="143"/>
-      <c r="B4" s="176"/>
-      <c r="C4" s="170"/>
-      <c r="D4" s="171"/>
+    <row r="4" spans="1:17">
+      <c r="A4" s="142"/>
+      <c r="B4" s="175"/>
+      <c r="C4" s="169"/>
+      <c r="D4" s="170"/>
       <c r="E4" s="11"/>
       <c r="F4" s="9" t="s">
         <v>311</v>
@@ -16511,10 +16862,10 @@
       <c r="J4" s="10"/>
       <c r="K4" s="10"/>
     </row>
-    <row r="5" spans="1:16">
-      <c r="A5" s="143"/>
-      <c r="B5" s="176"/>
-      <c r="C5" s="171"/>
+    <row r="5" spans="1:17">
+      <c r="A5" s="142"/>
+      <c r="B5" s="175"/>
+      <c r="C5" s="170"/>
       <c r="D5" s="46" t="s">
         <v>555</v>
       </c>
@@ -16526,7 +16877,7 @@
         <v>557</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="I5" s="122">
         <v>44043</v>
@@ -16536,13 +16887,13 @@
       </c>
       <c r="K5" s="10"/>
     </row>
-    <row r="6" spans="1:16">
-      <c r="A6" s="143"/>
-      <c r="B6" s="176"/>
-      <c r="C6" s="169" t="s">
+    <row r="6" spans="1:17">
+      <c r="A6" s="142"/>
+      <c r="B6" s="175"/>
+      <c r="C6" s="168" t="s">
         <v>507</v>
       </c>
-      <c r="D6" s="169" t="s">
+      <c r="D6" s="168" t="s">
         <v>511</v>
       </c>
       <c r="E6" s="11"/>
@@ -16553,7 +16904,7 @@
         <v>317</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="I6" s="122">
         <v>44043</v>
@@ -16561,11 +16912,11 @@
       <c r="J6" s="10"/>
       <c r="K6" s="10"/>
     </row>
-    <row r="7" spans="1:16">
-      <c r="A7" s="143"/>
-      <c r="B7" s="176"/>
-      <c r="C7" s="170"/>
-      <c r="D7" s="170"/>
+    <row r="7" spans="1:17">
+      <c r="A7" s="142"/>
+      <c r="B7" s="175"/>
+      <c r="C7" s="169"/>
+      <c r="D7" s="169"/>
       <c r="E7" s="11"/>
       <c r="F7" s="9" t="s">
         <v>313</v>
@@ -16582,11 +16933,11 @@
       <c r="J7" s="10"/>
       <c r="K7" s="10"/>
     </row>
-    <row r="8" spans="1:16">
-      <c r="A8" s="143"/>
-      <c r="B8" s="176"/>
-      <c r="C8" s="170"/>
-      <c r="D8" s="170"/>
+    <row r="8" spans="1:17">
+      <c r="A8" s="142"/>
+      <c r="B8" s="175"/>
+      <c r="C8" s="169"/>
+      <c r="D8" s="169"/>
       <c r="E8" s="11"/>
       <c r="F8" s="9" t="s">
         <v>314</v>
@@ -16603,11 +16954,11 @@
       <c r="J8" s="10"/>
       <c r="K8" s="10"/>
     </row>
-    <row r="9" spans="1:16">
-      <c r="A9" s="143"/>
-      <c r="B9" s="176"/>
-      <c r="C9" s="170"/>
-      <c r="D9" s="170"/>
+    <row r="9" spans="1:17">
+      <c r="A9" s="142"/>
+      <c r="B9" s="175"/>
+      <c r="C9" s="169"/>
+      <c r="D9" s="169"/>
       <c r="E9" s="8"/>
       <c r="F9" s="9" t="s">
         <v>345</v>
@@ -16624,11 +16975,11 @@
       <c r="J9" s="10"/>
       <c r="K9" s="10"/>
     </row>
-    <row r="10" spans="1:16">
-      <c r="A10" s="143"/>
-      <c r="B10" s="176"/>
-      <c r="C10" s="170"/>
-      <c r="D10" s="170"/>
+    <row r="10" spans="1:17">
+      <c r="A10" s="142"/>
+      <c r="B10" s="175"/>
+      <c r="C10" s="169"/>
+      <c r="D10" s="169"/>
       <c r="E10" s="8"/>
       <c r="F10" s="9" t="s">
         <v>346</v>
@@ -16645,11 +16996,11 @@
       <c r="J10" s="10"/>
       <c r="K10" s="10"/>
     </row>
-    <row r="11" spans="1:16">
-      <c r="A11" s="143"/>
-      <c r="B11" s="176"/>
-      <c r="C11" s="170"/>
-      <c r="D11" s="170"/>
+    <row r="11" spans="1:17">
+      <c r="A11" s="142"/>
+      <c r="B11" s="175"/>
+      <c r="C11" s="169"/>
+      <c r="D11" s="169"/>
       <c r="E11" s="8"/>
       <c r="F11" s="9" t="s">
         <v>315</v>
@@ -16666,11 +17017,11 @@
       <c r="J11" s="10"/>
       <c r="K11" s="10"/>
     </row>
-    <row r="12" spans="1:16" ht="16.5" customHeight="1">
-      <c r="A12" s="143"/>
-      <c r="B12" s="176"/>
-      <c r="C12" s="170"/>
-      <c r="D12" s="170"/>
+    <row r="12" spans="1:17" ht="16.5" customHeight="1">
+      <c r="A12" s="142"/>
+      <c r="B12" s="175"/>
+      <c r="C12" s="169"/>
+      <c r="D12" s="169"/>
       <c r="E12" s="8"/>
       <c r="F12" s="9" t="s">
         <v>347</v>
@@ -16687,11 +17038,11 @@
       <c r="J12" s="10"/>
       <c r="K12" s="10"/>
     </row>
-    <row r="13" spans="1:16">
-      <c r="A13" s="143"/>
-      <c r="B13" s="176"/>
-      <c r="C13" s="170"/>
-      <c r="D13" s="170"/>
+    <row r="13" spans="1:17" ht="30">
+      <c r="A13" s="142"/>
+      <c r="B13" s="175"/>
+      <c r="C13" s="169"/>
+      <c r="D13" s="169"/>
       <c r="E13" s="11"/>
       <c r="F13" s="9" t="s">
         <v>316</v>
@@ -16707,12 +17058,15 @@
         <v>563</v>
       </c>
       <c r="K13" s="10"/>
-    </row>
-    <row r="14" spans="1:16">
-      <c r="A14" s="143"/>
-      <c r="B14" s="176"/>
-      <c r="C14" s="170"/>
-      <c r="D14" s="171"/>
+      <c r="O13" s="102" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17">
+      <c r="A14" s="142"/>
+      <c r="B14" s="175"/>
+      <c r="C14" s="169"/>
+      <c r="D14" s="170"/>
       <c r="E14" s="11"/>
       <c r="F14" s="9" t="s">
         <v>318</v>
@@ -16727,10 +17081,10 @@
       <c r="J14" s="10"/>
       <c r="K14" s="10"/>
     </row>
-    <row r="15" spans="1:16" ht="30">
-      <c r="A15" s="143"/>
-      <c r="B15" s="176"/>
-      <c r="C15" s="170"/>
+    <row r="15" spans="1:17" ht="30">
+      <c r="A15" s="142"/>
+      <c r="B15" s="175"/>
+      <c r="C15" s="169"/>
       <c r="D15" s="22" t="s">
         <v>512</v>
       </c>
@@ -16749,22 +17103,25 @@
       </c>
       <c r="J15" s="10"/>
       <c r="K15" s="10"/>
-      <c r="M15" s="125" t="s">
+      <c r="M15" s="203" t="s">
         <v>852</v>
       </c>
-      <c r="N15" s="91"/>
-      <c r="O15" s="91"/>
-      <c r="P15" s="91" t="s">
-        <v>968</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" ht="15" customHeight="1">
-      <c r="A16" s="143"/>
-      <c r="B16" s="176"/>
-      <c r="C16" s="169" t="s">
+      <c r="N15" s="204"/>
+      <c r="O15" s="118" t="s">
+        <v>1260</v>
+      </c>
+      <c r="P15" s="91"/>
+      <c r="Q15" s="91" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" ht="30">
+      <c r="A16" s="142"/>
+      <c r="B16" s="175"/>
+      <c r="C16" s="168" t="s">
         <v>509</v>
       </c>
-      <c r="D16" s="169" t="s">
+      <c r="D16" s="168" t="s">
         <v>513</v>
       </c>
       <c r="E16" s="11"/>
@@ -16788,18 +17145,21 @@
       <c r="N16" s="98" t="s">
         <v>360</v>
       </c>
-      <c r="O16" s="103">
+      <c r="O16" s="99" t="s">
+        <v>1261</v>
+      </c>
+      <c r="P16" s="103">
         <v>1</v>
       </c>
-      <c r="P16" s="91" t="s">
+      <c r="Q16" s="91" t="s">
         <v>854</v>
       </c>
     </row>
-    <row r="17" spans="1:16">
-      <c r="A17" s="143"/>
-      <c r="B17" s="176"/>
-      <c r="C17" s="170"/>
-      <c r="D17" s="170"/>
+    <row r="17" spans="1:17">
+      <c r="A17" s="142"/>
+      <c r="B17" s="175"/>
+      <c r="C17" s="169"/>
+      <c r="D17" s="169"/>
       <c r="E17" s="19"/>
       <c r="F17" s="9" t="s">
         <v>364</v>
@@ -16821,21 +17181,24 @@
       <c r="N17" s="98" t="s">
         <v>365</v>
       </c>
-      <c r="O17" s="104">
+      <c r="O17" s="99" t="s">
+        <v>1265</v>
+      </c>
+      <c r="P17" s="104">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:16">
-      <c r="A18" s="143"/>
-      <c r="B18" s="176"/>
-      <c r="C18" s="170"/>
-      <c r="D18" s="170"/>
+    <row r="18" spans="1:17">
+      <c r="A18" s="142"/>
+      <c r="B18" s="175"/>
+      <c r="C18" s="169"/>
+      <c r="D18" s="169"/>
       <c r="E18" s="19"/>
       <c r="F18" s="48" t="s">
         <v>559</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="H18" s="10">
         <v>1</v>
@@ -16853,15 +17216,18 @@
       <c r="N18" s="98" t="s">
         <v>366</v>
       </c>
-      <c r="O18" s="104">
+      <c r="O18" s="99" t="s">
+        <v>1265</v>
+      </c>
+      <c r="P18" s="104">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:16">
-      <c r="A19" s="143"/>
-      <c r="B19" s="176"/>
-      <c r="C19" s="170"/>
-      <c r="D19" s="170"/>
+    <row r="19" spans="1:17">
+      <c r="A19" s="142"/>
+      <c r="B19" s="175"/>
+      <c r="C19" s="169"/>
+      <c r="D19" s="169"/>
       <c r="E19" s="8"/>
       <c r="F19" s="9" t="s">
         <v>332</v>
@@ -16883,16 +17249,19 @@
       <c r="N19" s="98" t="s">
         <v>368</v>
       </c>
-      <c r="O19" s="105">
+      <c r="O19" s="99" t="s">
+        <v>1265</v>
+      </c>
+      <c r="P19" s="105">
         <v>1</v>
       </c>
-      <c r="P19" s="91"/>
-    </row>
-    <row r="20" spans="1:16">
-      <c r="A20" s="143"/>
-      <c r="B20" s="176"/>
-      <c r="C20" s="170"/>
-      <c r="D20" s="170"/>
+      <c r="Q19" s="91"/>
+    </row>
+    <row r="20" spans="1:17">
+      <c r="A20" s="142"/>
+      <c r="B20" s="175"/>
+      <c r="C20" s="169"/>
+      <c r="D20" s="169"/>
       <c r="E20" s="8"/>
       <c r="F20" s="9" t="s">
         <v>333</v>
@@ -16914,16 +17283,19 @@
       <c r="N20" s="98" t="s">
         <v>369</v>
       </c>
-      <c r="O20" s="99">
+      <c r="O20" s="99" t="s">
+        <v>1265</v>
+      </c>
+      <c r="P20" s="99">
         <v>2</v>
       </c>
-      <c r="P20" s="91"/>
-    </row>
-    <row r="21" spans="1:16" ht="16.5" customHeight="1">
-      <c r="A21" s="143"/>
-      <c r="B21" s="176"/>
-      <c r="C21" s="170"/>
-      <c r="D21" s="170"/>
+      <c r="Q20" s="91"/>
+    </row>
+    <row r="21" spans="1:17" ht="16.5" customHeight="1">
+      <c r="A21" s="142"/>
+      <c r="B21" s="175"/>
+      <c r="C21" s="169"/>
+      <c r="D21" s="169"/>
       <c r="E21" s="14"/>
       <c r="F21" s="9" t="s">
         <v>334</v>
@@ -16945,18 +17317,21 @@
       <c r="N21" s="98" t="s">
         <v>361</v>
       </c>
-      <c r="O21" s="103">
+      <c r="O21" s="99" t="s">
+        <v>81</v>
+      </c>
+      <c r="P21" s="103">
         <v>1</v>
       </c>
-      <c r="P21" s="91" t="s">
+      <c r="Q21" s="91" t="s">
         <v>855</v>
       </c>
     </row>
-    <row r="22" spans="1:16">
-      <c r="A22" s="143"/>
-      <c r="B22" s="176"/>
-      <c r="C22" s="170"/>
-      <c r="D22" s="170"/>
+    <row r="22" spans="1:17">
+      <c r="A22" s="142"/>
+      <c r="B22" s="175"/>
+      <c r="C22" s="169"/>
+      <c r="D22" s="169"/>
       <c r="E22" s="14"/>
       <c r="F22" s="9" t="s">
         <v>335</v>
@@ -16978,18 +17353,21 @@
       <c r="N22" s="98" t="s">
         <v>362</v>
       </c>
-      <c r="O22" s="104">
+      <c r="O22" s="99" t="s">
+        <v>81</v>
+      </c>
+      <c r="P22" s="104">
         <v>1</v>
       </c>
-      <c r="P22" s="91" t="s">
+      <c r="Q22" s="91" t="s">
         <v>858</v>
       </c>
     </row>
-    <row r="23" spans="1:16">
-      <c r="A23" s="143"/>
-      <c r="B23" s="176"/>
-      <c r="C23" s="170"/>
-      <c r="D23" s="170"/>
+    <row r="23" spans="1:17">
+      <c r="A23" s="142"/>
+      <c r="B23" s="175"/>
+      <c r="C23" s="169"/>
+      <c r="D23" s="169"/>
       <c r="E23" s="14"/>
       <c r="F23" s="9" t="s">
         <v>336</v>
@@ -16998,7 +17376,7 @@
         <v>369</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="I23" s="122">
         <v>44043</v>
@@ -17011,16 +17389,19 @@
       <c r="N23" s="98" t="s">
         <v>372</v>
       </c>
-      <c r="O23" s="100" t="s">
-        <v>966</v>
-      </c>
-      <c r="P23" s="91"/>
-    </row>
-    <row r="24" spans="1:16">
-      <c r="A24" s="143"/>
-      <c r="B24" s="176"/>
-      <c r="C24" s="170"/>
-      <c r="D24" s="170"/>
+      <c r="O23" s="99" t="s">
+        <v>81</v>
+      </c>
+      <c r="P23" s="100" t="s">
+        <v>964</v>
+      </c>
+      <c r="Q23" s="91"/>
+    </row>
+    <row r="24" spans="1:17">
+      <c r="A24" s="142"/>
+      <c r="B24" s="175"/>
+      <c r="C24" s="169"/>
+      <c r="D24" s="169"/>
       <c r="E24" s="8"/>
       <c r="F24" s="9" t="s">
         <v>337</v>
@@ -17029,29 +17410,32 @@
         <v>370</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="I24" s="122">
         <v>44043</v>
       </c>
       <c r="J24" s="10"/>
       <c r="K24" s="10"/>
-      <c r="M24" s="126" t="s">
-        <v>969</v>
+      <c r="M24" s="125" t="s">
+        <v>967</v>
       </c>
       <c r="N24" s="98" t="s">
         <v>371</v>
       </c>
-      <c r="O24" s="100">
+      <c r="O24" s="99" t="s">
+        <v>81</v>
+      </c>
+      <c r="P24" s="100">
         <v>1</v>
       </c>
-      <c r="P24" s="91"/>
-    </row>
-    <row r="25" spans="1:16">
-      <c r="A25" s="143"/>
-      <c r="B25" s="176"/>
-      <c r="C25" s="170"/>
-      <c r="D25" s="170"/>
+      <c r="Q24" s="91"/>
+    </row>
+    <row r="25" spans="1:17">
+      <c r="A25" s="142"/>
+      <c r="B25" s="175"/>
+      <c r="C25" s="169"/>
+      <c r="D25" s="169"/>
       <c r="E25" s="8"/>
       <c r="F25" s="9" t="s">
         <v>373</v>
@@ -17073,16 +17457,19 @@
       <c r="N25" s="98" t="s">
         <v>370</v>
       </c>
-      <c r="O25" s="99">
+      <c r="O25" s="99" t="s">
+        <v>1265</v>
+      </c>
+      <c r="P25" s="99">
         <v>2</v>
       </c>
-      <c r="P25" s="91"/>
-    </row>
-    <row r="26" spans="1:16">
-      <c r="A26" s="143"/>
-      <c r="B26" s="176"/>
-      <c r="C26" s="170"/>
-      <c r="D26" s="170"/>
+      <c r="Q25" s="91"/>
+    </row>
+    <row r="26" spans="1:17">
+      <c r="A26" s="142"/>
+      <c r="B26" s="175"/>
+      <c r="C26" s="169"/>
+      <c r="D26" s="169"/>
       <c r="E26" s="8"/>
       <c r="F26" s="9" t="s">
         <v>338</v>
@@ -17102,16 +17489,19 @@
       <c r="N26" s="98" t="s">
         <v>375</v>
       </c>
-      <c r="O26" s="99">
+      <c r="O26" s="99" t="s">
+        <v>81</v>
+      </c>
+      <c r="P26" s="99">
         <v>2</v>
       </c>
-      <c r="P26" s="91"/>
-    </row>
-    <row r="27" spans="1:16">
-      <c r="A27" s="143"/>
-      <c r="B27" s="176"/>
-      <c r="C27" s="170"/>
-      <c r="D27" s="170"/>
+      <c r="Q26" s="91"/>
+    </row>
+    <row r="27" spans="1:17">
+      <c r="A27" s="142"/>
+      <c r="B27" s="175"/>
+      <c r="C27" s="169"/>
+      <c r="D27" s="169"/>
       <c r="E27" s="8"/>
       <c r="F27" s="9" t="s">
         <v>339</v>
@@ -17120,7 +17510,7 @@
         <v>372</v>
       </c>
       <c r="H27" s="123" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="I27" s="122"/>
       <c r="J27" s="10"/>
@@ -17131,19 +17521,22 @@
       <c r="N27" s="98" t="s">
         <v>367</v>
       </c>
-      <c r="O27" s="98">
+      <c r="O27" s="99" t="s">
+        <v>1265</v>
+      </c>
+      <c r="P27" s="98">
         <v>3</v>
       </c>
-      <c r="P27" s="91"/>
-    </row>
-    <row r="28" spans="1:16">
-      <c r="A28" s="143"/>
-      <c r="B28" s="176"/>
-      <c r="C28" s="170"/>
-      <c r="D28" s="170"/>
+      <c r="Q27" s="91"/>
+    </row>
+    <row r="28" spans="1:17">
+      <c r="A28" s="142"/>
+      <c r="B28" s="175"/>
+      <c r="C28" s="169"/>
+      <c r="D28" s="169"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="126" t="s">
-        <v>969</v>
+      <c r="F28" s="125" t="s">
+        <v>967</v>
       </c>
       <c r="G28" s="13" t="s">
         <v>371</v>
@@ -17162,22 +17555,25 @@
       <c r="N28" s="99" t="s">
         <v>374</v>
       </c>
-      <c r="O28" s="99">
+      <c r="O28" s="99" t="s">
+        <v>1265</v>
+      </c>
+      <c r="P28" s="99">
         <v>3</v>
       </c>
-      <c r="P28" s="91"/>
-    </row>
-    <row r="29" spans="1:16">
-      <c r="A29" s="143"/>
-      <c r="B29" s="176"/>
-      <c r="C29" s="170"/>
-      <c r="D29" s="170"/>
+      <c r="Q28" s="91"/>
+    </row>
+    <row r="29" spans="1:17">
+      <c r="A29" s="142"/>
+      <c r="B29" s="175"/>
+      <c r="C29" s="169"/>
+      <c r="D29" s="169"/>
       <c r="E29" s="8"/>
       <c r="F29" s="9" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="H29" s="16">
         <v>2</v>
@@ -17185,14 +17581,14 @@
       <c r="I29" s="122"/>
       <c r="J29" s="10"/>
       <c r="K29" s="10" t="s">
-        <v>958</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16">
-      <c r="A30" s="143"/>
-      <c r="B30" s="176"/>
-      <c r="C30" s="170"/>
-      <c r="D30" s="171"/>
+        <v>956</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17">
+      <c r="A30" s="142"/>
+      <c r="B30" s="175"/>
+      <c r="C30" s="169"/>
+      <c r="D30" s="170"/>
       <c r="E30" s="8"/>
       <c r="F30" s="49" t="s">
         <v>323</v>
@@ -17205,15 +17601,24 @@
       </c>
       <c r="I30" s="122"/>
       <c r="J30" s="10"/>
-      <c r="K30" s="172" t="s">
-        <v>963</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16">
-      <c r="A31" s="143"/>
-      <c r="B31" s="176"/>
-      <c r="C31" s="170"/>
-      <c r="D31" s="169" t="s">
+      <c r="K30" s="171" t="s">
+        <v>961</v>
+      </c>
+      <c r="M30" s="102" t="s">
+        <v>1263</v>
+      </c>
+      <c r="N30" s="102" t="s">
+        <v>1264</v>
+      </c>
+      <c r="O30" t="s">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17">
+      <c r="A31" s="142"/>
+      <c r="B31" s="175"/>
+      <c r="C31" s="169"/>
+      <c r="D31" s="168" t="s">
         <v>518</v>
       </c>
       <c r="E31" s="8"/>
@@ -17230,16 +17635,13 @@
         <v>44043</v>
       </c>
       <c r="J31" s="10"/>
-      <c r="K31" s="173"/>
-      <c r="M31" s="102" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" ht="16.5" customHeight="1">
-      <c r="A32" s="143"/>
-      <c r="B32" s="176"/>
-      <c r="C32" s="170"/>
-      <c r="D32" s="170"/>
+      <c r="K31" s="172"/>
+    </row>
+    <row r="32" spans="1:17" ht="16.5" customHeight="1">
+      <c r="A32" s="142"/>
+      <c r="B32" s="175"/>
+      <c r="C32" s="169"/>
+      <c r="D32" s="169"/>
       <c r="E32" s="8"/>
       <c r="F32" s="9" t="s">
         <v>325</v>
@@ -17254,19 +17656,19 @@
         <v>44043</v>
       </c>
       <c r="J32" s="10"/>
-      <c r="K32" s="173"/>
+      <c r="K32" s="172"/>
     </row>
     <row r="33" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A33" s="143"/>
-      <c r="B33" s="176"/>
-      <c r="C33" s="170"/>
-      <c r="D33" s="170"/>
+      <c r="A33" s="142"/>
+      <c r="B33" s="175"/>
+      <c r="C33" s="169"/>
+      <c r="D33" s="169"/>
       <c r="E33" s="8"/>
       <c r="F33" s="9" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="H33" s="16">
         <v>2</v>
@@ -17275,15 +17677,15 @@
         <v>44043</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>958</v>
-      </c>
-      <c r="K33" s="174"/>
+        <v>956</v>
+      </c>
+      <c r="K33" s="173"/>
     </row>
     <row r="34" spans="1:11">
-      <c r="A34" s="143"/>
-      <c r="B34" s="176"/>
-      <c r="C34" s="171"/>
-      <c r="D34" s="171"/>
+      <c r="A34" s="142"/>
+      <c r="B34" s="175"/>
+      <c r="C34" s="170"/>
+      <c r="D34" s="170"/>
       <c r="E34" s="8"/>
       <c r="F34" s="49" t="s">
         <v>322</v>
@@ -17299,12 +17701,12 @@
       <c r="K34" s="10"/>
     </row>
     <row r="35" spans="1:11">
-      <c r="A35" s="143"/>
-      <c r="B35" s="176"/>
-      <c r="C35" s="169" t="s">
+      <c r="A35" s="142"/>
+      <c r="B35" s="175"/>
+      <c r="C35" s="168" t="s">
         <v>340</v>
       </c>
-      <c r="D35" s="169" t="s">
+      <c r="D35" s="168" t="s">
         <v>517</v>
       </c>
       <c r="E35" s="8"/>
@@ -17324,10 +17726,10 @@
       <c r="K35" s="10"/>
     </row>
     <row r="36" spans="1:11">
-      <c r="A36" s="143"/>
-      <c r="B36" s="177"/>
-      <c r="C36" s="171"/>
-      <c r="D36" s="171"/>
+      <c r="A36" s="142"/>
+      <c r="B36" s="176"/>
+      <c r="C36" s="170"/>
+      <c r="D36" s="170"/>
       <c r="E36" s="8"/>
       <c r="F36" s="9" t="s">
         <v>331</v>
@@ -17336,14 +17738,14 @@
         <v>376</v>
       </c>
       <c r="H36" s="124" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="I36" s="122"/>
       <c r="J36" s="10"/>
       <c r="K36" s="10"/>
     </row>
     <row r="37" spans="1:11">
-      <c r="A37" s="143"/>
+      <c r="A37" s="142"/>
       <c r="B37" s="29" t="s">
         <v>328</v>
       </c>
@@ -17368,14 +17770,14 @@
       <c r="K37" s="10"/>
     </row>
     <row r="38" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A38" s="143"/>
-      <c r="B38" s="175" t="s">
+      <c r="A38" s="142"/>
+      <c r="B38" s="174" t="s">
         <v>505</v>
       </c>
-      <c r="C38" s="169" t="s">
+      <c r="C38" s="168" t="s">
         <v>510</v>
       </c>
-      <c r="D38" s="169" t="s">
+      <c r="D38" s="168" t="s">
         <v>516</v>
       </c>
       <c r="E38" s="8" t="s">
@@ -17395,10 +17797,10 @@
       <c r="K38" s="10"/>
     </row>
     <row r="39" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A39" s="143"/>
-      <c r="B39" s="176"/>
-      <c r="C39" s="143"/>
-      <c r="D39" s="143"/>
+      <c r="A39" s="142"/>
+      <c r="B39" s="175"/>
+      <c r="C39" s="142"/>
+      <c r="D39" s="142"/>
       <c r="E39" s="17"/>
       <c r="F39" s="9" t="s">
         <v>304</v>
@@ -17416,10 +17818,10 @@
       <c r="K39" s="10"/>
     </row>
     <row r="40" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A40" s="143"/>
-      <c r="B40" s="176"/>
-      <c r="C40" s="143"/>
-      <c r="D40" s="143"/>
+      <c r="A40" s="142"/>
+      <c r="B40" s="175"/>
+      <c r="C40" s="142"/>
+      <c r="D40" s="142"/>
       <c r="E40" s="17"/>
       <c r="F40" s="9" t="s">
         <v>305</v>
@@ -17437,10 +17839,10 @@
       <c r="K40" s="10"/>
     </row>
     <row r="41" spans="1:11">
-      <c r="A41" s="143"/>
-      <c r="B41" s="176"/>
-      <c r="C41" s="143"/>
-      <c r="D41" s="144"/>
+      <c r="A41" s="142"/>
+      <c r="B41" s="175"/>
+      <c r="C41" s="142"/>
+      <c r="D41" s="143"/>
       <c r="E41" s="17"/>
       <c r="F41" s="9" t="s">
         <v>305</v>
@@ -17456,10 +17858,10 @@
       <c r="K41" s="10"/>
     </row>
     <row r="42" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A42" s="143"/>
-      <c r="B42" s="176"/>
-      <c r="C42" s="143"/>
-      <c r="D42" s="169" t="s">
+      <c r="A42" s="142"/>
+      <c r="B42" s="175"/>
+      <c r="C42" s="142"/>
+      <c r="D42" s="168" t="s">
         <v>515</v>
       </c>
       <c r="E42" s="8"/>
@@ -17470,21 +17872,21 @@
         <v>298</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="I42" s="122">
         <v>44043</v>
       </c>
       <c r="J42" s="10"/>
-      <c r="K42" s="172" t="s">
-        <v>1168</v>
+      <c r="K42" s="171" t="s">
+        <v>1166</v>
       </c>
     </row>
     <row r="43" spans="1:11">
-      <c r="A43" s="143"/>
-      <c r="B43" s="176"/>
-      <c r="C43" s="143"/>
-      <c r="D43" s="144"/>
+      <c r="A43" s="142"/>
+      <c r="B43" s="175"/>
+      <c r="C43" s="142"/>
+      <c r="D43" s="143"/>
       <c r="E43" s="8"/>
       <c r="F43" s="9" t="s">
         <v>289</v>
@@ -17493,19 +17895,19 @@
         <v>299</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="I43" s="122">
         <v>44043</v>
       </c>
       <c r="J43" s="10"/>
-      <c r="K43" s="182"/>
+      <c r="K43" s="181"/>
     </row>
     <row r="44" spans="1:11">
-      <c r="A44" s="143"/>
-      <c r="B44" s="176"/>
-      <c r="C44" s="143"/>
-      <c r="D44" s="169" t="s">
+      <c r="A44" s="142"/>
+      <c r="B44" s="175"/>
+      <c r="C44" s="142"/>
+      <c r="D44" s="168" t="s">
         <v>514</v>
       </c>
       <c r="E44" s="8"/>
@@ -17523,10 +17925,10 @@
       <c r="K44" s="10"/>
     </row>
     <row r="45" spans="1:11">
-      <c r="A45" s="144"/>
-      <c r="B45" s="177"/>
-      <c r="C45" s="144"/>
-      <c r="D45" s="144"/>
+      <c r="A45" s="143"/>
+      <c r="B45" s="176"/>
+      <c r="C45" s="143"/>
+      <c r="D45" s="143"/>
       <c r="E45" s="8"/>
       <c r="F45" s="9" t="s">
         <v>301</v>
@@ -17542,12 +17944,13 @@
       <c r="K45" s="10"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="M16:O28">
-    <sortCondition ref="O16:O28"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="M16:P28">
+    <sortCondition ref="P16:P28"/>
   </sortState>
-  <mergeCells count="18">
+  <mergeCells count="19">
     <mergeCell ref="D6:D14"/>
     <mergeCell ref="K42:K43"/>
+    <mergeCell ref="M15:N15"/>
     <mergeCell ref="D16:D30"/>
     <mergeCell ref="K30:K33"/>
     <mergeCell ref="C2:C5"/>
@@ -17602,11 +18005,11 @@
       <c r="B1" s="25" t="s">
         <v>327</v>
       </c>
-      <c r="E1" s="180" t="s">
+      <c r="E1" s="179" t="s">
         <v>724</v>
       </c>
-      <c r="F1" s="180"/>
-      <c r="G1" s="180"/>
+      <c r="F1" s="179"/>
+      <c r="G1" s="179"/>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="19" t="s">
@@ -17615,11 +18018,11 @@
       <c r="B2" s="19" t="s">
         <v>257</v>
       </c>
-      <c r="E2" s="181" t="s">
+      <c r="E2" s="180" t="s">
         <v>725</v>
       </c>
-      <c r="F2" s="181"/>
-      <c r="G2" s="181"/>
+      <c r="F2" s="180"/>
+      <c r="G2" s="180"/>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="19" t="s">
@@ -17636,10 +18039,10 @@
       <c r="B4" s="19" t="s">
         <v>259</v>
       </c>
-      <c r="E4" s="180" t="s">
+      <c r="E4" s="179" t="s">
         <v>722</v>
       </c>
-      <c r="F4" s="180"/>
+      <c r="F4" s="179"/>
       <c r="G4" s="25" t="s">
         <v>723</v>
       </c>
@@ -17651,16 +18054,16 @@
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="E5" s="179" t="s">
+      <c r="E5" s="178" t="s">
         <v>720</v>
       </c>
-      <c r="F5" s="179" t="s">
+      <c r="F5" s="178" t="s">
         <v>721</v>
       </c>
       <c r="G5" s="68" t="s">
         <v>747</v>
       </c>
-      <c r="H5" s="178" t="s">
+      <c r="H5" s="177" t="s">
         <v>748</v>
       </c>
       <c r="J5" t="s">
@@ -17671,12 +18074,12 @@
       <c r="A6" t="s">
         <v>261</v>
       </c>
-      <c r="E6" s="179"/>
-      <c r="F6" s="179"/>
+      <c r="E6" s="178"/>
+      <c r="F6" s="178"/>
       <c r="G6" s="68" t="s">
         <v>746</v>
       </c>
-      <c r="H6" s="179"/>
+      <c r="H6" s="178"/>
       <c r="J6" t="s">
         <v>729</v>
       </c>
@@ -17743,7 +18146,7 @@
         <v>790</v>
       </c>
       <c r="H13" t="s">
-        <v>1255</v>
+        <v>1251</v>
       </c>
       <c r="J13" t="s">
         <v>735</v>
@@ -17763,7 +18166,7 @@
         <v>795</v>
       </c>
       <c r="H14" t="s">
-        <v>1254</v>
+        <v>1250</v>
       </c>
       <c r="J14" t="s">
         <v>736</v>
@@ -17875,7 +18278,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F01B713B-7546-4B5B-BF06-08BB58B1A0C8}">
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" customWidth="1"/>
@@ -17884,129 +18287,129 @@
     <col min="4" max="4" width="10.42578125" customWidth="1"/>
     <col min="5" max="5" width="66.7109375" customWidth="1"/>
     <col min="6" max="6" width="10.7109375" style="81" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="37.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="33.5703125" customWidth="1"/>
+    <col min="7" max="7" width="33" customWidth="1"/>
+    <col min="8" max="8" width="38.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.140625" style="81" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="60.42578125" style="183" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="60.42578125" style="182" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30">
-      <c r="A1" s="191" t="s">
+      <c r="A1" s="190" t="s">
         <v>847</v>
       </c>
-      <c r="B1" s="191" t="s">
+      <c r="B1" s="190" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C1" s="190" t="s">
+        <v>640</v>
+      </c>
+      <c r="D1" s="190" t="s">
+        <v>1174</v>
+      </c>
+      <c r="E1" s="190" t="s">
+        <v>1169</v>
+      </c>
+      <c r="F1" s="190" t="s">
+        <v>1170</v>
+      </c>
+      <c r="G1" s="191" t="s">
+        <v>1204</v>
+      </c>
+      <c r="H1" s="191" t="s">
+        <v>1257</v>
+      </c>
+      <c r="I1" s="190" t="s">
+        <v>1178</v>
+      </c>
+      <c r="J1" s="190" t="s">
+        <v>1184</v>
+      </c>
+      <c r="K1" s="190" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="186">
+        <v>44028</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>1173</v>
       </c>
-      <c r="C1" s="191" t="s">
-        <v>640</v>
-      </c>
-      <c r="D1" s="191" t="s">
+      <c r="D2" s="119" t="s">
+        <v>1175</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>1177</v>
+      </c>
+      <c r="F2" s="119" t="s">
         <v>1176</v>
-      </c>
-      <c r="E1" s="191" t="s">
-        <v>1171</v>
-      </c>
-      <c r="F1" s="191" t="s">
-        <v>1172</v>
-      </c>
-      <c r="G1" s="192" t="s">
-        <v>1206</v>
-      </c>
-      <c r="H1" s="192" t="s">
-        <v>1245</v>
-      </c>
-      <c r="I1" s="191" t="s">
-        <v>1180</v>
-      </c>
-      <c r="J1" s="191" t="s">
-        <v>1186</v>
-      </c>
-      <c r="K1" s="191" t="s">
-        <v>1192</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="187">
-        <v>44028</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>1174</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>1175</v>
-      </c>
-      <c r="D2" s="119" t="s">
-        <v>1177</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>1179</v>
-      </c>
-      <c r="F2" s="119" t="s">
-        <v>1178</v>
       </c>
       <c r="G2" s="119">
         <v>0.36</v>
       </c>
       <c r="H2" s="119"/>
       <c r="I2" s="119" t="s">
+        <v>1179</v>
+      </c>
+      <c r="J2" s="119" t="s">
+        <v>893</v>
+      </c>
+      <c r="K2" s="187" t="s">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="186">
+        <v>44028</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>1181</v>
       </c>
-      <c r="J2" s="119" t="s">
-        <v>894</v>
-      </c>
-      <c r="K2" s="188" t="s">
-        <v>1198</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="187">
-        <v>44028</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>1183</v>
-      </c>
       <c r="C3" s="8" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="D3" s="119" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="F3" s="119" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="G3" s="119">
         <v>0.78</v>
       </c>
       <c r="H3" s="119"/>
       <c r="I3" s="119" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="J3" s="119" t="s">
-        <v>894</v>
-      </c>
-      <c r="K3" s="189"/>
+        <v>893</v>
+      </c>
+      <c r="K3" s="188"/>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="187">
+      <c r="A4" s="186">
         <v>44029</v>
       </c>
       <c r="B4" s="8" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>1188</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>1190</v>
-      </c>
       <c r="D4" s="119" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="E4" s="8" t="s">
+        <v>1187</v>
+      </c>
+      <c r="F4" s="119" t="s">
         <v>1189</v>
-      </c>
-      <c r="F4" s="119" t="s">
-        <v>1191</v>
       </c>
       <c r="G4" s="119">
         <v>5.83</v>
@@ -18014,28 +18417,28 @@
       <c r="H4" s="119"/>
       <c r="I4" s="119"/>
       <c r="J4" s="119" t="s">
-        <v>894</v>
-      </c>
-      <c r="K4" s="189"/>
+        <v>893</v>
+      </c>
+      <c r="K4" s="188"/>
     </row>
     <row r="5" spans="1:11" ht="45">
-      <c r="A5" s="187">
+      <c r="A5" s="186">
         <v>44029</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="C5" s="8" t="s">
+        <v>1191</v>
+      </c>
+      <c r="D5" s="119" t="s">
+        <v>1175</v>
+      </c>
+      <c r="E5" s="18" t="s">
         <v>1193</v>
       </c>
-      <c r="D5" s="119" t="s">
-        <v>1177</v>
-      </c>
-      <c r="E5" s="18" t="s">
-        <v>1195</v>
-      </c>
       <c r="F5" s="119" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="G5" s="119">
         <v>2.21</v>
@@ -18043,196 +18446,196 @@
       <c r="H5" s="119"/>
       <c r="I5" s="119"/>
       <c r="J5" s="119" t="s">
-        <v>894</v>
-      </c>
-      <c r="K5" s="190"/>
+        <v>893</v>
+      </c>
+      <c r="K5" s="189"/>
     </row>
     <row r="6" spans="1:11" ht="60">
-      <c r="A6" s="187">
+      <c r="A6" s="186">
         <v>44029</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="D6" s="119" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="F6" s="119" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="G6" s="18" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="H6" s="18"/>
       <c r="I6" s="119" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="J6" s="8"/>
       <c r="K6" s="8" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="60">
-      <c r="A7" s="187">
+      <c r="A7" s="186">
         <v>44029</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="D7" s="119" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="F7" s="119" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="G7" s="18" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="H7" s="18"/>
       <c r="I7" s="119" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="J7" s="8"/>
       <c r="K7" s="8"/>
     </row>
     <row r="8" spans="1:11" ht="60">
-      <c r="A8" s="187">
+      <c r="A8" s="186">
         <v>44029</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="D8" s="119" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="F8" s="119" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="G8" s="18" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="H8" s="18" t="s">
-        <v>1246</v>
+        <v>1242</v>
       </c>
       <c r="I8" s="119" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="J8" s="8"/>
       <c r="K8" s="18" t="s">
-        <v>1252</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="60">
-      <c r="A9" s="187">
+      <c r="A9" s="186">
         <v>44029</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
       <c r="D9" s="119" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>1195</v>
-      </c>
-      <c r="F9" s="202" t="s">
-        <v>1249</v>
-      </c>
-      <c r="G9" s="18" t="s">
-        <v>1215</v>
-      </c>
-      <c r="H9" s="198" t="s">
-        <v>1247</v>
+        <v>1193</v>
+      </c>
+      <c r="F9" s="199" t="s">
+        <v>1245</v>
+      </c>
+      <c r="G9" s="200" t="s">
+        <v>1213</v>
+      </c>
+      <c r="H9" s="197" t="s">
+        <v>1243</v>
       </c>
       <c r="I9" s="119" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="J9" s="8"/>
       <c r="K9" s="18" t="s">
-        <v>1253</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="45">
-      <c r="A10" s="197" t="s">
-        <v>1232</v>
+      <c r="A10" s="196" t="s">
+        <v>1229</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="D10" s="119" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="F10" s="119" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="G10" s="18" t="s">
-        <v>1248</v>
+        <v>1244</v>
       </c>
       <c r="H10" s="18"/>
       <c r="I10" s="119" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="J10" s="8"/>
       <c r="K10" s="18" t="s">
-        <v>1250</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="45">
-      <c r="A11" s="195" t="s">
-        <v>1222</v>
+      <c r="A11" s="194" t="s">
+        <v>1220</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="D11" s="119" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="F11" s="119" t="s">
-        <v>1202</v>
-      </c>
-      <c r="G11" s="194" t="s">
-        <v>1251</v>
-      </c>
-      <c r="H11" s="194"/>
+        <v>1200</v>
+      </c>
+      <c r="G11" s="193" t="s">
+        <v>1247</v>
+      </c>
+      <c r="H11" s="193"/>
       <c r="I11" s="119" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="J11" s="8"/>
       <c r="K11" s="18" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -18242,16 +18645,16 @@
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
       <c r="F12" s="119" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="G12" s="8"/>
       <c r="H12" s="8"/>
       <c r="I12" s="119" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="J12" s="8"/>
       <c r="K12" s="8" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -18261,250 +18664,250 @@
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
       <c r="F13" s="119" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="G13" s="8"/>
       <c r="H13" s="8"/>
       <c r="I13" s="119" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="J13" s="8"/>
       <c r="K13" s="8" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="182"/>
+      <c r="B14" s="182"/>
+      <c r="C14" s="182"/>
+      <c r="D14" s="182"/>
+      <c r="E14" s="192" t="s">
+        <v>1218</v>
+      </c>
+      <c r="F14" s="183"/>
+      <c r="G14" s="192" t="s">
+        <v>1256</v>
+      </c>
+      <c r="H14" s="182"/>
+      <c r="I14" s="183"/>
+      <c r="J14" s="182"/>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="182"/>
+      <c r="B15" s="182"/>
+      <c r="C15" s="182"/>
+      <c r="D15" s="182"/>
+      <c r="E15" s="182"/>
+      <c r="F15" s="183"/>
+      <c r="G15" s="182" t="s">
+        <v>1235</v>
+      </c>
+      <c r="H15" s="182" t="s">
+        <v>1236</v>
+      </c>
+      <c r="I15" s="183"/>
+      <c r="J15" s="182"/>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="182"/>
+      <c r="B16" s="182"/>
+      <c r="C16" s="182"/>
+      <c r="D16" s="182"/>
+      <c r="E16" s="182"/>
+      <c r="G16" s="182"/>
+      <c r="H16" s="182"/>
+      <c r="I16" s="183"/>
+      <c r="J16" s="182"/>
+    </row>
+    <row r="17" spans="1:10" ht="15" customHeight="1">
+      <c r="A17" s="182"/>
+      <c r="B17" s="182"/>
+      <c r="C17" s="182"/>
+      <c r="D17" s="182"/>
+      <c r="E17" s="182"/>
+      <c r="F17" s="197"/>
+      <c r="G17" s="8" t="s">
+        <v>1258</v>
+      </c>
+      <c r="H17" s="128" t="s">
+        <v>1259</v>
+      </c>
+      <c r="I17" s="183"/>
+      <c r="J17" s="182"/>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="182"/>
+      <c r="B18" s="182"/>
+      <c r="C18" s="182"/>
+      <c r="D18" s="182"/>
+      <c r="E18" s="182"/>
+      <c r="F18" s="201" t="s">
+        <v>1241</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>1238</v>
+      </c>
+      <c r="H18" s="128" t="s">
+        <v>1253</v>
+      </c>
+      <c r="I18" s="183"/>
+      <c r="J18" s="182"/>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="F19" s="201"/>
+      <c r="G19" s="8" t="s">
+        <v>1237</v>
+      </c>
+      <c r="H19" s="202" t="s">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="F20" s="201"/>
+      <c r="G20" s="8" t="s">
+        <v>1239</v>
+      </c>
+      <c r="H20" s="128" t="s">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="F21" s="201"/>
+      <c r="G21" s="8" t="s">
+        <v>1240</v>
+      </c>
+      <c r="H21" s="202" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="G22" s="198"/>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="F23" s="195" t="s">
+        <v>1252</v>
+      </c>
+      <c r="G23" t="s">
+        <v>1221</v>
+      </c>
+      <c r="H23" t="s">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="F24" s="195" t="s">
+        <v>1208</v>
+      </c>
+      <c r="G24" s="81">
+        <v>1</v>
+      </c>
+      <c r="H24" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="F25" s="195" t="s">
+        <v>1208</v>
+      </c>
+      <c r="G25" s="81">
+        <v>8</v>
+      </c>
+      <c r="H25" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="F26" s="195" t="s">
+        <v>1199</v>
+      </c>
+      <c r="G26" s="81">
+        <v>1</v>
+      </c>
+      <c r="H26" t="s">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="F27" s="195" t="s">
+        <v>1199</v>
+      </c>
+      <c r="G27" s="81">
+        <v>4</v>
+      </c>
+      <c r="H27" t="s">
         <v>1233</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
-      <c r="A14" s="183"/>
-      <c r="B14" s="183"/>
-      <c r="C14" s="183"/>
-      <c r="D14" s="183"/>
-      <c r="E14" s="193" t="s">
-        <v>1220</v>
-      </c>
-      <c r="F14" s="184"/>
-      <c r="G14" s="193" t="s">
+    <row r="28" spans="1:10">
+      <c r="F28" s="195" t="s">
+        <v>1199</v>
+      </c>
+      <c r="G28" s="81">
+        <v>8</v>
+      </c>
+      <c r="H28" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="F29" s="195" t="s">
+        <v>1200</v>
+      </c>
+      <c r="G29" s="81">
+        <v>1</v>
+      </c>
+      <c r="H29" t="s">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="F30" s="195" t="s">
+        <v>1200</v>
+      </c>
+      <c r="G30" s="81">
+        <v>4</v>
+      </c>
+      <c r="H30" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="F31" s="195" t="s">
+        <v>1200</v>
+      </c>
+      <c r="G31" s="81">
+        <v>8</v>
+      </c>
+      <c r="H31" t="s">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="F32" s="195" t="s">
+        <v>1202</v>
+      </c>
+      <c r="G32" s="81">
+        <v>1</v>
+      </c>
+      <c r="H32" t="s">
         <v>1231</v>
       </c>
-      <c r="H14" s="183"/>
-      <c r="I14" s="184"/>
-      <c r="J14" s="183"/>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" s="183"/>
-      <c r="B15" s="183"/>
-      <c r="C15" s="183"/>
-      <c r="D15" s="183"/>
-      <c r="E15" s="183"/>
-      <c r="F15" s="184"/>
-      <c r="G15" s="183" t="s">
-        <v>1238</v>
-      </c>
-      <c r="H15" s="183" t="s">
-        <v>1239</v>
-      </c>
-      <c r="I15" s="184"/>
-      <c r="J15" s="183"/>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" s="183"/>
-      <c r="B16" s="183"/>
-      <c r="C16" s="183"/>
-      <c r="D16" s="183"/>
-      <c r="E16" s="183"/>
-      <c r="G16" s="183"/>
-      <c r="H16" s="183"/>
-      <c r="I16" s="184"/>
-      <c r="J16" s="183"/>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="183"/>
-      <c r="B17" s="183"/>
-      <c r="C17" s="183"/>
-      <c r="D17" s="183"/>
-      <c r="E17" s="183"/>
-      <c r="F17" s="200" t="s">
-        <v>1244</v>
-      </c>
-      <c r="G17" s="183" t="s">
-        <v>1257</v>
-      </c>
-      <c r="H17" s="118">
-        <v>0</v>
-      </c>
-      <c r="I17" s="184"/>
-      <c r="J17" s="183"/>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="183"/>
-      <c r="B18" s="183"/>
-      <c r="C18" s="183"/>
-      <c r="D18" s="183"/>
-      <c r="E18" s="183"/>
-      <c r="F18" s="199"/>
-      <c r="G18" s="183" t="s">
-        <v>1241</v>
-      </c>
-      <c r="H18" s="118" t="s">
-        <v>1258</v>
-      </c>
-      <c r="I18" s="184"/>
-      <c r="J18" s="183"/>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="F19" s="199"/>
-      <c r="G19" s="183" t="s">
-        <v>1240</v>
-      </c>
-      <c r="H19" s="203" t="s">
-        <v>1259</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="F20" s="199"/>
-      <c r="G20" s="183" t="s">
-        <v>1242</v>
-      </c>
-      <c r="H20" s="118" t="s">
-        <v>1258</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="F21" s="199"/>
-      <c r="G21" s="183" t="s">
-        <v>1243</v>
-      </c>
-      <c r="H21" s="203" t="s">
-        <v>1260</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="G22" s="201"/>
-    </row>
-    <row r="35" spans="5:7">
-      <c r="E35" s="196" t="s">
-        <v>1256</v>
-      </c>
-      <c r="F35" t="s">
-        <v>1223</v>
-      </c>
-      <c r="G35" t="s">
-        <v>1227</v>
-      </c>
-    </row>
-    <row r="36" spans="5:7">
-      <c r="E36" s="196" t="s">
-        <v>1210</v>
-      </c>
-      <c r="F36" s="81">
-        <v>1</v>
-      </c>
-      <c r="G36" t="s">
-        <v>1225</v>
-      </c>
-    </row>
-    <row r="37" spans="5:7">
-      <c r="E37" s="196" t="s">
-        <v>1210</v>
-      </c>
-      <c r="F37" s="81">
+    </row>
+    <row r="33" spans="6:8">
+      <c r="F33" s="195" t="s">
+        <v>1202</v>
+      </c>
+      <c r="G33" s="81">
         <v>8</v>
       </c>
-      <c r="G37" t="s">
-        <v>1224</v>
-      </c>
-    </row>
-    <row r="38" spans="5:7">
-      <c r="E38" s="196" t="s">
-        <v>1201</v>
-      </c>
-      <c r="F38" s="81">
-        <v>1</v>
-      </c>
-      <c r="G38" t="s">
-        <v>1228</v>
-      </c>
-    </row>
-    <row r="39" spans="5:7">
-      <c r="E39" s="196" t="s">
-        <v>1201</v>
-      </c>
-      <c r="F39" s="81">
-        <v>4</v>
-      </c>
-      <c r="G39" t="s">
-        <v>1236</v>
-      </c>
-    </row>
-    <row r="40" spans="5:7">
-      <c r="E40" s="196" t="s">
-        <v>1201</v>
-      </c>
-      <c r="F40" s="81">
-        <v>8</v>
-      </c>
-      <c r="G40" t="s">
-        <v>1226</v>
-      </c>
-    </row>
-    <row r="41" spans="5:7">
-      <c r="E41" s="196" t="s">
-        <v>1202</v>
-      </c>
-      <c r="F41" s="81">
-        <v>1</v>
-      </c>
-      <c r="G41" t="s">
-        <v>1229</v>
-      </c>
-    </row>
-    <row r="42" spans="5:7">
-      <c r="E42" s="196" t="s">
-        <v>1202</v>
-      </c>
-      <c r="F42" s="81">
-        <v>4</v>
-      </c>
-      <c r="G42" t="s">
-        <v>1237</v>
-      </c>
-    </row>
-    <row r="43" spans="5:7">
-      <c r="E43" s="196" t="s">
-        <v>1202</v>
-      </c>
-      <c r="F43" s="81">
-        <v>8</v>
-      </c>
-      <c r="G43" t="s">
-        <v>1230</v>
-      </c>
-    </row>
-    <row r="46" spans="5:7">
-      <c r="E46" s="196" t="s">
-        <v>1204</v>
-      </c>
-      <c r="F46" s="81">
-        <v>1</v>
-      </c>
-      <c r="G46" t="s">
-        <v>1234</v>
-      </c>
-    </row>
-    <row r="47" spans="5:7">
-      <c r="E47" s="196" t="s">
-        <v>1204</v>
-      </c>
-      <c r="F47" s="81">
-        <v>8</v>
-      </c>
-      <c r="G47" t="s">
-        <v>1235</v>
+      <c r="H33" t="s">
+        <v>1232</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="K2:K5"/>
-    <mergeCell ref="F17:F21"/>
+    <mergeCell ref="F18:F21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -18639,14 +19042,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="127" t="s">
+      <c r="A1" s="126" t="s">
+        <v>973</v>
+      </c>
+      <c r="B1" s="127" t="s">
+        <v>974</v>
+      </c>
+      <c r="C1" s="127" t="s">
         <v>975</v>
-      </c>
-      <c r="B1" s="128" t="s">
-        <v>976</v>
-      </c>
-      <c r="C1" s="128" t="s">
-        <v>977</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -18654,10 +19057,10 @@
         <v>758</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -18665,10 +19068,10 @@
         <v>758</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -18676,10 +19079,10 @@
         <v>758</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -18687,10 +19090,10 @@
         <v>758</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -18698,10 +19101,10 @@
         <v>758</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -18709,10 +19112,10 @@
         <v>758</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -18720,10 +19123,10 @@
         <v>758</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -18731,10 +19134,10 @@
         <v>758</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -18742,10 +19145,10 @@
         <v>758</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -18753,10 +19156,10 @@
         <v>758</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -18764,10 +19167,10 @@
         <v>758</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -18775,10 +19178,10 @@
         <v>758</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -18786,10 +19189,10 @@
         <v>758</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -18797,10 +19200,10 @@
         <v>758</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -18808,10 +19211,10 @@
         <v>758</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -18819,10 +19222,10 @@
         <v>758</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -18830,10 +19233,10 @@
         <v>758</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -18841,10 +19244,10 @@
         <v>758</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -18852,10 +19255,10 @@
         <v>758</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -18863,10 +19266,10 @@
         <v>758</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -18874,10 +19277,10 @@
         <v>758</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -18885,10 +19288,10 @@
         <v>758</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -18896,10 +19299,10 @@
         <v>758</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -18907,10 +19310,10 @@
         <v>758</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -18918,10 +19321,10 @@
         <v>758</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -18932,7 +19335,7 @@
         <v>838</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -18940,10 +19343,10 @@
         <v>758</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -18951,10 +19354,10 @@
         <v>758</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -18962,10 +19365,10 @@
         <v>758</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -18973,10 +19376,10 @@
         <v>758</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -18984,10 +19387,10 @@
         <v>758</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -18995,10 +19398,10 @@
         <v>758</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -19009,7 +19412,7 @@
         <v>836</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -19017,10 +19420,10 @@
         <v>758</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -19028,10 +19431,10 @@
         <v>758</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -19039,10 +19442,10 @@
         <v>758</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -19053,7 +19456,7 @@
         <v>834</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -19061,10 +19464,10 @@
         <v>758</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -19075,7 +19478,7 @@
         <v>837</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -19083,10 +19486,10 @@
         <v>758</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -19094,713 +19497,713 @@
         <v>758</v>
       </c>
       <c r="B42" s="19" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C42" s="19" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="128" t="s">
+        <v>385</v>
+      </c>
+      <c r="B43" s="128" t="s">
         <v>1053</v>
       </c>
-      <c r="C42" s="19" t="s">
+      <c r="C43" s="128" t="s">
         <v>1054</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="129" t="s">
+    <row r="44" spans="1:3">
+      <c r="A44" s="128" t="s">
         <v>385</v>
       </c>
-      <c r="B43" s="129" t="s">
+      <c r="B44" s="128" t="s">
         <v>1055</v>
       </c>
-      <c r="C43" s="129" t="s">
+      <c r="C44" s="128" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="128" t="s">
+        <v>385</v>
+      </c>
+      <c r="B45" s="128" t="s">
         <v>1056</v>
       </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="129" t="s">
+      <c r="C45" s="128" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="128" t="s">
         <v>385</v>
       </c>
-      <c r="B44" s="129" t="s">
-        <v>1057</v>
-      </c>
-      <c r="C44" s="129" t="s">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="129" t="s">
+      <c r="B46" s="128" t="s">
+        <v>619</v>
+      </c>
+      <c r="C46" s="128" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="128" t="s">
         <v>385</v>
       </c>
-      <c r="B45" s="129" t="s">
-        <v>1058</v>
-      </c>
-      <c r="C45" s="129" t="s">
+      <c r="B47" s="128" t="s">
+        <v>617</v>
+      </c>
+      <c r="C47" s="128" t="s">
         <v>1059</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="129" t="s">
+    <row r="48" spans="1:3">
+      <c r="A48" s="128" t="s">
         <v>385</v>
       </c>
-      <c r="B46" s="129" t="s">
-        <v>619</v>
-      </c>
-      <c r="C46" s="129" t="s">
+      <c r="B48" s="128" t="s">
         <v>1060</v>
       </c>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="129" t="s">
+      <c r="C48" s="128" t="s">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="128" t="s">
         <v>385</v>
       </c>
-      <c r="B47" s="129" t="s">
-        <v>617</v>
-      </c>
-      <c r="C47" s="129" t="s">
-        <v>1061</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="129" t="s">
+      <c r="B49" s="128" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C49" s="128" t="s">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="128" t="s">
         <v>385</v>
       </c>
-      <c r="B48" s="129" t="s">
-        <v>1062</v>
-      </c>
-      <c r="C48" s="129" t="s">
-        <v>1063</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="129" t="s">
+      <c r="B50" s="128" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C50" s="128" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="128" t="s">
         <v>385</v>
       </c>
-      <c r="B49" s="129" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C49" s="129" t="s">
-        <v>1065</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="129" t="s">
+      <c r="B51" s="128" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C51" s="128" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="128" t="s">
         <v>385</v>
       </c>
-      <c r="B50" s="129" t="s">
-        <v>1066</v>
-      </c>
-      <c r="C50" s="129" t="s">
-        <v>1067</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="129" t="s">
+      <c r="B52" s="128" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C52" s="128" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" s="128" t="s">
         <v>385</v>
       </c>
-      <c r="B51" s="129" t="s">
-        <v>1068</v>
-      </c>
-      <c r="C51" s="129" t="s">
-        <v>1069</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="129" t="s">
+      <c r="B53" s="128" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C53" s="19" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" s="128" t="s">
         <v>385</v>
       </c>
-      <c r="B52" s="129" t="s">
-        <v>1070</v>
-      </c>
-      <c r="C52" s="129" t="s">
-        <v>1071</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="129" t="s">
+      <c r="B54" s="128" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C54" s="19" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" s="128" t="s">
         <v>385</v>
       </c>
-      <c r="B53" s="129" t="s">
-        <v>1072</v>
-      </c>
-      <c r="C53" s="19" t="s">
-        <v>1073</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="129" t="s">
+      <c r="B55" s="19" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C55" s="19" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" s="128" t="s">
         <v>385</v>
       </c>
-      <c r="B54" s="129" t="s">
-        <v>1074</v>
-      </c>
-      <c r="C54" s="19" t="s">
-        <v>1075</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
-      <c r="A55" s="129" t="s">
+      <c r="B56" s="19" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C56" s="19" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" s="128" t="s">
         <v>385</v>
       </c>
-      <c r="B55" s="19" t="s">
-        <v>1076</v>
-      </c>
-      <c r="C55" s="19" t="s">
-        <v>1077</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="129" t="s">
+      <c r="B57" s="19" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C57" s="19" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="30">
+      <c r="A58" s="128" t="s">
         <v>385</v>
       </c>
-      <c r="B56" s="19" t="s">
-        <v>1078</v>
-      </c>
-      <c r="C56" s="19" t="s">
-        <v>1079</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="129" t="s">
+      <c r="B58" s="19" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C58" s="23" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" s="128" t="s">
         <v>385</v>
       </c>
-      <c r="B57" s="19" t="s">
-        <v>1080</v>
-      </c>
-      <c r="C57" s="19" t="s">
-        <v>1081</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" ht="30">
-      <c r="A58" s="129" t="s">
+      <c r="B59" s="19" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C59" s="19" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" s="128" t="s">
         <v>385</v>
       </c>
-      <c r="B58" s="19" t="s">
-        <v>1082</v>
-      </c>
-      <c r="C58" s="23" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3">
-      <c r="A59" s="129" t="s">
-        <v>385</v>
-      </c>
-      <c r="B59" s="19" t="s">
+      <c r="B60" s="19" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C60" s="19" t="s">
         <v>1084</v>
-      </c>
-      <c r="C59" s="19" t="s">
-        <v>1085</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3">
-      <c r="A60" s="129" t="s">
-        <v>385</v>
-      </c>
-      <c r="B60" s="19" t="s">
-        <v>1058</v>
-      </c>
-      <c r="C60" s="19" t="s">
-        <v>1086</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="16.5">
       <c r="A61" s="19" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B61" s="129" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C61" s="129" t="s">
         <v>1087</v>
-      </c>
-      <c r="B61" s="130" t="s">
-        <v>1088</v>
-      </c>
-      <c r="C61" s="130" t="s">
-        <v>1089</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="16.5">
       <c r="A62" s="19" t="s">
-        <v>1087</v>
-      </c>
-      <c r="B62" s="131" t="s">
-        <v>1090</v>
-      </c>
-      <c r="C62" s="131" t="s">
-        <v>1091</v>
+        <v>1085</v>
+      </c>
+      <c r="B62" s="130" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C62" s="130" t="s">
+        <v>1089</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="16.5">
       <c r="A63" s="19" t="s">
-        <v>1087</v>
-      </c>
-      <c r="B63" s="131" t="s">
-        <v>1092</v>
-      </c>
-      <c r="C63" s="131" t="s">
-        <v>1093</v>
+        <v>1085</v>
+      </c>
+      <c r="B63" s="130" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C63" s="130" t="s">
+        <v>1091</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="16.5">
       <c r="A64" s="19" t="s">
-        <v>1087</v>
-      </c>
-      <c r="B64" s="131" t="s">
-        <v>1094</v>
-      </c>
-      <c r="C64" s="131" t="s">
-        <v>1095</v>
+        <v>1085</v>
+      </c>
+      <c r="B64" s="130" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C64" s="130" t="s">
+        <v>1093</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="16.5">
       <c r="A65" s="19" t="s">
-        <v>1087</v>
-      </c>
-      <c r="B65" s="131" t="s">
-        <v>1096</v>
-      </c>
-      <c r="C65" s="131" t="s">
-        <v>1097</v>
+        <v>1085</v>
+      </c>
+      <c r="B65" s="130" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C65" s="130" t="s">
+        <v>1095</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="16.5">
       <c r="A66" s="19" t="s">
-        <v>1087</v>
-      </c>
-      <c r="B66" s="131" t="s">
-        <v>1098</v>
-      </c>
-      <c r="C66" s="131" t="s">
-        <v>1099</v>
+        <v>1085</v>
+      </c>
+      <c r="B66" s="130" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C66" s="130" t="s">
+        <v>1097</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="16.5">
       <c r="A67" s="19" t="s">
-        <v>1087</v>
-      </c>
-      <c r="B67" s="131" t="s">
-        <v>1100</v>
-      </c>
-      <c r="C67" s="131" t="s">
-        <v>1101</v>
+        <v>1085</v>
+      </c>
+      <c r="B67" s="130" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C67" s="130" t="s">
+        <v>1099</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="16.5">
       <c r="A68" s="19" t="s">
-        <v>1087</v>
-      </c>
-      <c r="B68" s="131" t="s">
-        <v>1102</v>
-      </c>
-      <c r="C68" s="131" t="s">
-        <v>1103</v>
+        <v>1085</v>
+      </c>
+      <c r="B68" s="130" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C68" s="130" t="s">
+        <v>1101</v>
       </c>
     </row>
     <row r="69" spans="1:3" ht="16.5">
       <c r="A69" s="19" t="s">
-        <v>1087</v>
-      </c>
-      <c r="B69" s="131" t="s">
-        <v>1104</v>
-      </c>
-      <c r="C69" s="131" t="s">
-        <v>1105</v>
+        <v>1085</v>
+      </c>
+      <c r="B69" s="130" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C69" s="130" t="s">
+        <v>1103</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="16.5">
       <c r="A70" s="19" t="s">
-        <v>1087</v>
-      </c>
-      <c r="B70" s="131" t="s">
-        <v>1106</v>
-      </c>
-      <c r="C70" s="131" t="s">
-        <v>1107</v>
+        <v>1085</v>
+      </c>
+      <c r="B70" s="130" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C70" s="130" t="s">
+        <v>1105</v>
       </c>
     </row>
     <row r="71" spans="1:3" ht="16.5">
       <c r="A71" s="19" t="s">
-        <v>1087</v>
-      </c>
-      <c r="B71" s="131" t="s">
-        <v>1108</v>
-      </c>
-      <c r="C71" s="131" t="s">
-        <v>1109</v>
+        <v>1085</v>
+      </c>
+      <c r="B71" s="130" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C71" s="130" t="s">
+        <v>1107</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="16.5">
       <c r="A72" s="19" t="s">
-        <v>1087</v>
-      </c>
-      <c r="B72" s="131" t="s">
-        <v>1110</v>
-      </c>
-      <c r="C72" s="131" t="s">
-        <v>1111</v>
+        <v>1085</v>
+      </c>
+      <c r="B72" s="130" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C72" s="130" t="s">
+        <v>1109</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="16.5">
       <c r="A73" s="19" t="s">
-        <v>1087</v>
-      </c>
-      <c r="B73" s="131" t="s">
-        <v>1112</v>
-      </c>
-      <c r="C73" s="131" t="s">
-        <v>1113</v>
+        <v>1085</v>
+      </c>
+      <c r="B73" s="130" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C73" s="130" t="s">
+        <v>1111</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="16.5">
       <c r="A74" s="19" t="s">
-        <v>1087</v>
-      </c>
-      <c r="B74" s="131" t="s">
-        <v>1114</v>
-      </c>
-      <c r="C74" s="131" t="s">
-        <v>1115</v>
+        <v>1085</v>
+      </c>
+      <c r="B74" s="130" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C74" s="130" t="s">
+        <v>1113</v>
       </c>
     </row>
     <row r="75" spans="1:3" ht="16.5">
       <c r="A75" s="19" t="s">
-        <v>1087</v>
-      </c>
-      <c r="B75" s="131" t="s">
-        <v>1116</v>
-      </c>
-      <c r="C75" s="131" t="s">
-        <v>1117</v>
+        <v>1085</v>
+      </c>
+      <c r="B75" s="130" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C75" s="130" t="s">
+        <v>1115</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="16.5">
       <c r="A76" s="19" t="s">
-        <v>1087</v>
-      </c>
-      <c r="B76" s="131" t="s">
-        <v>1118</v>
-      </c>
-      <c r="C76" s="131" t="s">
-        <v>1119</v>
+        <v>1085</v>
+      </c>
+      <c r="B76" s="130" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C76" s="130" t="s">
+        <v>1117</v>
       </c>
     </row>
     <row r="77" spans="1:3" ht="16.5">
       <c r="A77" s="19" t="s">
-        <v>1087</v>
-      </c>
-      <c r="B77" s="131" t="s">
-        <v>1120</v>
-      </c>
-      <c r="C77" s="131" t="s">
-        <v>1121</v>
+        <v>1085</v>
+      </c>
+      <c r="B77" s="130" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C77" s="130" t="s">
+        <v>1119</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="16.5">
       <c r="A78" s="19" t="s">
-        <v>1087</v>
-      </c>
-      <c r="B78" s="131" t="s">
-        <v>1122</v>
-      </c>
-      <c r="C78" s="131" t="s">
-        <v>1123</v>
+        <v>1085</v>
+      </c>
+      <c r="B78" s="130" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C78" s="130" t="s">
+        <v>1121</v>
       </c>
     </row>
     <row r="79" spans="1:3" ht="16.5">
       <c r="A79" s="19" t="s">
-        <v>1087</v>
-      </c>
-      <c r="B79" s="131" t="s">
-        <v>1124</v>
-      </c>
-      <c r="C79" s="131" t="s">
-        <v>1125</v>
+        <v>1085</v>
+      </c>
+      <c r="B79" s="130" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C79" s="130" t="s">
+        <v>1123</v>
       </c>
     </row>
     <row r="80" spans="1:3" ht="16.5">
       <c r="A80" s="19" t="s">
-        <v>1087</v>
-      </c>
-      <c r="B80" s="131" t="s">
-        <v>1126</v>
-      </c>
-      <c r="C80" s="131" t="s">
-        <v>1127</v>
+        <v>1085</v>
+      </c>
+      <c r="B80" s="130" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C80" s="130" t="s">
+        <v>1125</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="16.5">
       <c r="A81" s="19" t="s">
-        <v>1087</v>
-      </c>
-      <c r="B81" s="131" t="s">
-        <v>1128</v>
-      </c>
-      <c r="C81" s="131" t="s">
-        <v>1129</v>
+        <v>1085</v>
+      </c>
+      <c r="B81" s="130" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C81" s="130" t="s">
+        <v>1127</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="16.5">
       <c r="A82" s="19" t="s">
-        <v>1087</v>
-      </c>
-      <c r="B82" s="131" t="s">
-        <v>1130</v>
-      </c>
-      <c r="C82" s="131" t="s">
-        <v>1131</v>
+        <v>1085</v>
+      </c>
+      <c r="B82" s="130" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C82" s="130" t="s">
+        <v>1129</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="16.5">
       <c r="A83" s="19" t="s">
-        <v>1087</v>
-      </c>
-      <c r="B83" s="131" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C83" s="131" t="s">
-        <v>1133</v>
+        <v>1085</v>
+      </c>
+      <c r="B83" s="130" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C83" s="130" t="s">
+        <v>1131</v>
       </c>
     </row>
     <row r="84" spans="1:3" ht="16.5">
       <c r="A84" s="19" t="s">
-        <v>1134</v>
-      </c>
-      <c r="B84" s="131" t="s">
-        <v>1135</v>
-      </c>
-      <c r="C84" s="131" t="s">
-        <v>1109</v>
+        <v>1132</v>
+      </c>
+      <c r="B84" s="130" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C84" s="130" t="s">
+        <v>1107</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="16.5">
       <c r="A85" s="19" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B85" s="130" t="s">
         <v>1134</v>
       </c>
-      <c r="B85" s="131" t="s">
-        <v>1136</v>
-      </c>
-      <c r="C85" s="131" t="s">
-        <v>1137</v>
+      <c r="C85" s="130" t="s">
+        <v>1135</v>
       </c>
     </row>
     <row r="86" spans="1:3" ht="33">
       <c r="A86" s="19" t="s">
-        <v>1134</v>
-      </c>
-      <c r="B86" s="131" t="s">
-        <v>1138</v>
-      </c>
-      <c r="C86" s="131" t="s">
-        <v>1139</v>
+        <v>1132</v>
+      </c>
+      <c r="B86" s="130" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C86" s="130" t="s">
+        <v>1137</v>
       </c>
     </row>
     <row r="87" spans="1:3" ht="49.5">
       <c r="A87" s="19" t="s">
-        <v>1134</v>
-      </c>
-      <c r="B87" s="131" t="s">
-        <v>1140</v>
-      </c>
-      <c r="C87" s="131" t="s">
-        <v>1141</v>
+        <v>1132</v>
+      </c>
+      <c r="B87" s="130" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C87" s="130" t="s">
+        <v>1139</v>
       </c>
     </row>
     <row r="88" spans="1:3" ht="33">
       <c r="A88" s="19" t="s">
-        <v>1134</v>
-      </c>
-      <c r="B88" s="131" t="s">
-        <v>1142</v>
-      </c>
-      <c r="C88" s="131" t="s">
-        <v>1111</v>
+        <v>1132</v>
+      </c>
+      <c r="B88" s="130" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C88" s="130" t="s">
+        <v>1109</v>
       </c>
     </row>
     <row r="89" spans="1:3" ht="16.5">
       <c r="A89" s="19" t="s">
-        <v>1134</v>
-      </c>
-      <c r="B89" s="131" t="s">
-        <v>1143</v>
-      </c>
-      <c r="C89" s="131" t="s">
-        <v>1144</v>
+        <v>1132</v>
+      </c>
+      <c r="B89" s="130" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C89" s="130" t="s">
+        <v>1142</v>
       </c>
     </row>
     <row r="90" spans="1:3" ht="16.5">
       <c r="A90" s="19" t="s">
-        <v>1134</v>
-      </c>
-      <c r="B90" s="131" t="s">
-        <v>1145</v>
-      </c>
-      <c r="C90" s="131" t="s">
-        <v>1146</v>
+        <v>1132</v>
+      </c>
+      <c r="B90" s="130" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C90" s="130" t="s">
+        <v>1144</v>
       </c>
     </row>
     <row r="91" spans="1:3" ht="16.5">
       <c r="A91" s="19" t="s">
-        <v>1147</v>
-      </c>
-      <c r="B91" s="131" t="s">
-        <v>1148</v>
-      </c>
-      <c r="C91" s="131" t="s">
-        <v>1109</v>
+        <v>1145</v>
+      </c>
+      <c r="B91" s="130" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C91" s="130" t="s">
+        <v>1107</v>
       </c>
     </row>
     <row r="92" spans="1:3" ht="33">
       <c r="A92" s="19" t="s">
-        <v>1147</v>
-      </c>
-      <c r="B92" s="131" t="s">
-        <v>1138</v>
-      </c>
-      <c r="C92" s="131" t="s">
-        <v>1139</v>
+        <v>1145</v>
+      </c>
+      <c r="B92" s="130" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C92" s="130" t="s">
+        <v>1137</v>
       </c>
     </row>
     <row r="93" spans="1:3" ht="16.5">
       <c r="A93" s="19" t="s">
-        <v>1147</v>
-      </c>
-      <c r="B93" s="131" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B93" s="130" t="s">
         <v>313</v>
       </c>
-      <c r="C93" s="131" t="s">
-        <v>1089</v>
+      <c r="C93" s="130" t="s">
+        <v>1087</v>
       </c>
     </row>
     <row r="94" spans="1:3" ht="16.5">
       <c r="A94" s="19" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B94" s="130" t="s">
+        <v>811</v>
+      </c>
+      <c r="C94" s="130" t="s">
         <v>1147</v>
-      </c>
-      <c r="B94" s="131" t="s">
-        <v>811</v>
-      </c>
-      <c r="C94" s="131" t="s">
-        <v>1149</v>
       </c>
     </row>
     <row r="95" spans="1:3" ht="16.5">
       <c r="A95" s="19" t="s">
-        <v>1147</v>
-      </c>
-      <c r="B95" s="131" t="s">
-        <v>1150</v>
-      </c>
-      <c r="C95" s="131" t="s">
-        <v>1093</v>
+        <v>1145</v>
+      </c>
+      <c r="B95" s="130" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C95" s="130" t="s">
+        <v>1091</v>
       </c>
     </row>
     <row r="96" spans="1:3" ht="16.5">
       <c r="A96" s="19" t="s">
-        <v>1147</v>
-      </c>
-      <c r="B96" s="131" t="s">
-        <v>1151</v>
-      </c>
-      <c r="C96" s="131" t="s">
-        <v>1095</v>
+        <v>1145</v>
+      </c>
+      <c r="B96" s="130" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C96" s="130" t="s">
+        <v>1093</v>
       </c>
     </row>
     <row r="97" spans="1:3" ht="16.5">
       <c r="A97" s="19" t="s">
-        <v>1147</v>
-      </c>
-      <c r="B97" s="131" t="s">
-        <v>1152</v>
-      </c>
-      <c r="C97" s="131" t="s">
-        <v>1097</v>
+        <v>1145</v>
+      </c>
+      <c r="B97" s="130" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C97" s="130" t="s">
+        <v>1095</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="16.5">
       <c r="A98" s="19" t="s">
-        <v>1147</v>
-      </c>
-      <c r="B98" s="131" t="s">
-        <v>1153</v>
-      </c>
-      <c r="C98" s="131" t="s">
-        <v>1131</v>
+        <v>1145</v>
+      </c>
+      <c r="B98" s="130" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C98" s="130" t="s">
+        <v>1129</v>
       </c>
     </row>
     <row r="99" spans="1:3" ht="16.5">
       <c r="A99" s="19" t="s">
-        <v>1147</v>
-      </c>
-      <c r="B99" s="131" t="s">
-        <v>1154</v>
-      </c>
-      <c r="C99" s="131" t="s">
-        <v>1155</v>
+        <v>1145</v>
+      </c>
+      <c r="B99" s="130" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C99" s="130" t="s">
+        <v>1153</v>
       </c>
     </row>
     <row r="100" spans="1:3" ht="16.5">
       <c r="A100" s="19" t="s">
-        <v>1147</v>
-      </c>
-      <c r="B100" s="131" t="s">
-        <v>1156</v>
-      </c>
-      <c r="C100" s="131" t="s">
-        <v>1127</v>
+        <v>1145</v>
+      </c>
+      <c r="B100" s="130" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C100" s="130" t="s">
+        <v>1125</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="16.5">
       <c r="A101" s="19" t="s">
-        <v>1147</v>
-      </c>
-      <c r="B101" s="131" t="s">
-        <v>1143</v>
-      </c>
-      <c r="C101" s="131" t="s">
-        <v>1157</v>
+        <v>1145</v>
+      </c>
+      <c r="B101" s="130" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C101" s="130" t="s">
+        <v>1155</v>
       </c>
     </row>
     <row r="102" spans="1:3" ht="16.5">
       <c r="A102" s="19" t="s">
-        <v>1147</v>
-      </c>
-      <c r="B102" s="131" t="s">
-        <v>1158</v>
-      </c>
-      <c r="C102" s="131" t="s">
-        <v>1159</v>
+        <v>1145</v>
+      </c>
+      <c r="B102" s="130" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C102" s="130" t="s">
+        <v>1157</v>
       </c>
     </row>
     <row r="103" spans="1:3" ht="16.5">
       <c r="A103" s="19" t="s">
-        <v>1147</v>
-      </c>
-      <c r="B103" s="131" t="s">
-        <v>1160</v>
-      </c>
-      <c r="C103" s="131" t="s">
-        <v>1161</v>
+        <v>1145</v>
+      </c>
+      <c r="B103" s="130" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C103" s="130" t="s">
+        <v>1159</v>
       </c>
     </row>
     <row r="104" spans="1:3" ht="16.5">
       <c r="A104" s="19" t="s">
-        <v>1147</v>
-      </c>
-      <c r="B104" s="131" t="s">
-        <v>1162</v>
-      </c>
-      <c r="C104" s="131" t="s">
-        <v>1101</v>
+        <v>1145</v>
+      </c>
+      <c r="B104" s="130" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C104" s="130" t="s">
+        <v>1099</v>
       </c>
     </row>
     <row r="105" spans="1:3" ht="16.5">
       <c r="A105" s="19" t="s">
-        <v>1147</v>
-      </c>
-      <c r="B105" s="131" t="s">
-        <v>1163</v>
-      </c>
-      <c r="C105" s="131" t="s">
-        <v>1164</v>
+        <v>1145</v>
+      </c>
+      <c r="B105" s="130" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C105" s="130" t="s">
+        <v>1162</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107" s="7" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" s="7" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -19812,13 +20215,13 @@
       <c r="A112" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="B112" s="132"/>
+      <c r="B112" s="131"/>
     </row>
     <row r="113" spans="1:2" ht="16.5">
       <c r="A113" s="7" t="s">
-        <v>1167</v>
-      </c>
-      <c r="B113" s="132"/>
+        <v>1165</v>
+      </c>
+      <c r="B113" s="131"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -19862,7 +20265,7 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="179" t="s">
+      <c r="A2" s="178" t="s">
         <v>379</v>
       </c>
       <c r="B2" s="57" t="s">
@@ -19876,7 +20279,7 @@
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="179"/>
+      <c r="A3" s="178"/>
       <c r="B3" s="20" t="s">
         <v>262</v>
       </c>
@@ -19888,7 +20291,7 @@
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="179"/>
+      <c r="A4" s="178"/>
       <c r="B4" s="20" t="s">
         <v>385</v>
       </c>
@@ -19900,7 +20303,7 @@
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="179"/>
+      <c r="A5" s="178"/>
       <c r="B5" s="57" t="s">
         <v>544</v>
       </c>
@@ -19912,7 +20315,7 @@
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="179"/>
+      <c r="A6" s="178"/>
       <c r="B6" s="20" t="s">
         <v>388</v>
       </c>
@@ -19924,7 +20327,7 @@
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="179"/>
+      <c r="A7" s="178"/>
       <c r="B7" s="20" t="s">
         <v>390</v>
       </c>
@@ -21484,350 +21887,426 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AFB2ECB-8FBD-4799-95D6-EF37601202CB}">
-  <dimension ref="F4:V41"/>
+  <dimension ref="F4:X44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="11" max="11" width="10" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="17.42578125" customWidth="1"/>
-    <col min="22" max="22" width="21" customWidth="1"/>
+    <col min="12" max="12" width="10" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="17.42578125" customWidth="1"/>
+    <col min="24" max="24" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="11:15">
-      <c r="L4" t="s">
+    <row r="4" spans="11:18">
+      <c r="M4" t="s">
         <v>874</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>875</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>876</v>
       </c>
     </row>
-    <row r="5" spans="11:15">
-      <c r="L5" t="s">
+    <row r="5" spans="11:18">
+      <c r="M5" t="s">
         <v>870</v>
       </c>
-      <c r="M5" t="s">
+      <c r="N5" t="s">
         <v>878</v>
       </c>
-      <c r="O5" t="s">
+      <c r="P5" t="s">
         <v>879</v>
       </c>
     </row>
-    <row r="6" spans="11:15">
-      <c r="L6" t="s">
+    <row r="6" spans="11:18">
+      <c r="M6" t="s">
         <v>869</v>
       </c>
-      <c r="M6" t="s">
+      <c r="N6" t="s">
         <v>877</v>
       </c>
-      <c r="N6" t="s">
+      <c r="O6" t="s">
         <v>871</v>
       </c>
-      <c r="O6" t="s">
+      <c r="P6" t="s">
         <v>880</v>
       </c>
     </row>
-    <row r="7" spans="11:15">
-      <c r="N7" t="s">
+    <row r="7" spans="11:18">
+      <c r="O7" t="s">
         <v>872</v>
       </c>
     </row>
-    <row r="8" spans="11:15" ht="35.25" customHeight="1">
-      <c r="M8" s="107"/>
-      <c r="N8" s="107" t="s">
+    <row r="8" spans="11:18" ht="35.25" customHeight="1">
+      <c r="N8" s="107"/>
+      <c r="O8" s="107" t="s">
         <v>873</v>
       </c>
     </row>
-    <row r="10" spans="11:15">
-      <c r="K10" s="110" t="s">
+    <row r="9" spans="11:18">
+      <c r="K9" s="208" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="10" spans="11:18">
+      <c r="K10" s="208">
+        <v>0</v>
+      </c>
+      <c r="L10" s="110" t="s">
+        <v>909</v>
+      </c>
+      <c r="M10" s="110" t="s">
         <v>910</v>
       </c>
-      <c r="L10" s="110" t="s">
+      <c r="O10" s="5" t="s">
+        <v>1266</v>
+      </c>
+      <c r="P10" s="5" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="11" spans="11:18" ht="15.75" thickBot="1">
+      <c r="K11" s="208"/>
+      <c r="L11" s="206"/>
+      <c r="M11" s="206"/>
+      <c r="N11" s="206"/>
+      <c r="O11" s="206"/>
+      <c r="P11" s="206"/>
+      <c r="Q11" s="206"/>
+      <c r="R11" s="206"/>
+    </row>
+    <row r="12" spans="11:18">
+      <c r="K12" s="208">
+        <v>1</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="13" spans="11:18">
+      <c r="K13" s="208"/>
+      <c r="M13" t="s">
+        <v>881</v>
+      </c>
+      <c r="N13" t="s">
+        <v>882</v>
+      </c>
+      <c r="O13" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="14" spans="11:18">
+      <c r="K14" s="208"/>
+      <c r="L14" s="6" t="s">
+        <v>888</v>
+      </c>
+      <c r="M14" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="15" spans="11:18">
+      <c r="K15" s="208"/>
+      <c r="M15" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="16" spans="11:18">
+      <c r="K16" s="208"/>
+      <c r="O16" s="5" t="s">
+        <v>1268</v>
+      </c>
+      <c r="P16" s="5" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="17" spans="7:24">
+      <c r="K17" s="208"/>
+    </row>
+    <row r="18" spans="7:24">
+      <c r="K18" s="208"/>
+    </row>
+    <row r="19" spans="7:24">
+      <c r="K19" s="208"/>
+    </row>
+    <row r="20" spans="7:24">
+      <c r="K20" s="208"/>
+      <c r="L20" s="6" t="s">
+        <v>883</v>
+      </c>
+      <c r="M20" t="s">
+        <v>884</v>
+      </c>
+      <c r="N20" t="s">
+        <v>885</v>
+      </c>
+      <c r="O20" t="s">
+        <v>886</v>
+      </c>
+      <c r="P20" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="21" spans="7:24">
+      <c r="K21" s="208"/>
+      <c r="M21" t="s">
+        <v>889</v>
+      </c>
+      <c r="V21" s="94" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="22" spans="7:24">
+      <c r="K22" s="208"/>
+      <c r="V22" s="141" t="s">
+        <v>833</v>
+      </c>
+      <c r="W22" s="9" t="s">
+        <v>815</v>
+      </c>
+      <c r="X22" s="92" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="23" spans="7:24" ht="15.75" thickBot="1">
+      <c r="K23" s="208"/>
+      <c r="L23" s="206"/>
+      <c r="M23" s="206"/>
+      <c r="N23" s="206"/>
+      <c r="O23" s="207" t="s">
+        <v>1268</v>
+      </c>
+      <c r="P23" s="207" t="s">
+        <v>1270</v>
+      </c>
+      <c r="Q23" s="206"/>
+      <c r="R23" s="206"/>
+      <c r="V23" s="142"/>
+      <c r="W23" s="9" t="s">
+        <v>816</v>
+      </c>
+      <c r="X23" s="92" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="24" spans="7:24">
+      <c r="K24" s="208"/>
+      <c r="V24" s="142"/>
+      <c r="W24" s="9" t="s">
+        <v>817</v>
+      </c>
+      <c r="X24" s="92" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="25" spans="7:24">
+      <c r="K25" s="208">
+        <v>2</v>
+      </c>
+      <c r="L25" s="5" t="s">
+        <v>892</v>
+      </c>
+      <c r="V25" s="142"/>
+      <c r="W25" s="9" t="s">
+        <v>818</v>
+      </c>
+      <c r="X25" s="92" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="26" spans="7:24">
+      <c r="K26" s="208"/>
+      <c r="M26" s="111" t="s">
+        <v>894</v>
+      </c>
+      <c r="N26" t="s">
+        <v>896</v>
+      </c>
+      <c r="O26" t="s">
+        <v>898</v>
+      </c>
+      <c r="V26" s="142"/>
+      <c r="W26" s="9" t="s">
+        <v>825</v>
+      </c>
+      <c r="X26" s="92"/>
+    </row>
+    <row r="27" spans="7:24">
+      <c r="K27" s="208"/>
+      <c r="M27" t="s">
+        <v>895</v>
+      </c>
+      <c r="N27" t="s">
+        <v>897</v>
+      </c>
+      <c r="V27" s="142"/>
+      <c r="W27" s="9" t="s">
+        <v>826</v>
+      </c>
+      <c r="X27" s="92"/>
+    </row>
+    <row r="28" spans="7:24">
+      <c r="K28" s="208"/>
+      <c r="N28" t="s">
+        <v>899</v>
+      </c>
+      <c r="V28" s="142"/>
+      <c r="W28" s="9" t="s">
+        <v>827</v>
+      </c>
+      <c r="X28" s="92" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="29" spans="7:24">
+      <c r="K29" s="208"/>
+      <c r="N29" t="s">
+        <v>900</v>
+      </c>
+      <c r="V29" s="143"/>
+      <c r="W29" s="9" t="s">
+        <v>828</v>
+      </c>
+      <c r="X29" s="92" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="30" spans="7:24">
+      <c r="K30" s="208"/>
+      <c r="M30" t="s">
+        <v>901</v>
+      </c>
+      <c r="N30" t="s">
+        <v>853</v>
+      </c>
+      <c r="V30" s="138" t="s">
+        <v>832</v>
+      </c>
+      <c r="W30" s="49" t="s">
+        <v>822</v>
+      </c>
+      <c r="X30" s="113"/>
+    </row>
+    <row r="31" spans="7:24">
+      <c r="K31" s="208"/>
+      <c r="N31" t="s">
+        <v>902</v>
+      </c>
+      <c r="V31" s="139"/>
+      <c r="W31" s="49" t="s">
+        <v>823</v>
+      </c>
+      <c r="X31" s="113"/>
+    </row>
+    <row r="32" spans="7:24" ht="15.75" thickBot="1">
+      <c r="G32" t="s">
         <v>911</v>
       </c>
-    </row>
-    <row r="12" spans="11:15">
-      <c r="K12" s="5" t="s">
-        <v>890</v>
-      </c>
-    </row>
-    <row r="13" spans="11:15">
-      <c r="L13" t="s">
-        <v>881</v>
-      </c>
-      <c r="M13" t="s">
-        <v>882</v>
-      </c>
-      <c r="N13" t="s">
-        <v>883</v>
-      </c>
-    </row>
-    <row r="14" spans="11:15">
-      <c r="K14" t="s">
-        <v>888</v>
-      </c>
-      <c r="L14" t="s">
-        <v>884</v>
-      </c>
-    </row>
-    <row r="15" spans="11:15">
-      <c r="L15" t="s">
-        <v>885</v>
-      </c>
-    </row>
-    <row r="16" spans="11:15">
-      <c r="N16" s="5" t="s">
-        <v>893</v>
-      </c>
-      <c r="O16" s="5" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="20" spans="7:22">
-      <c r="K20" t="s">
-        <v>883</v>
-      </c>
-      <c r="L20" t="s">
-        <v>884</v>
-      </c>
-      <c r="M20" t="s">
-        <v>885</v>
-      </c>
-      <c r="N20" t="s">
-        <v>886</v>
-      </c>
-      <c r="O20" t="s">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="21" spans="7:22">
-      <c r="L21" t="s">
-        <v>889</v>
-      </c>
-      <c r="T21" s="94" t="s">
-        <v>831</v>
-      </c>
-    </row>
-    <row r="22" spans="7:22">
-      <c r="T22" s="142" t="s">
-        <v>833</v>
-      </c>
-      <c r="U22" s="9" t="s">
-        <v>815</v>
-      </c>
-      <c r="V22" s="92" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="23" spans="7:22">
-      <c r="N23" s="5" t="s">
-        <v>894</v>
-      </c>
-      <c r="O23" s="5" t="s">
-        <v>912</v>
-      </c>
-      <c r="T23" s="143"/>
-      <c r="U23" s="9" t="s">
-        <v>816</v>
-      </c>
-      <c r="V23" s="92" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="24" spans="7:22">
-      <c r="T24" s="143"/>
-      <c r="U24" s="9" t="s">
-        <v>817</v>
-      </c>
-      <c r="V24" s="92" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="25" spans="7:22">
-      <c r="K25" s="5" t="s">
-        <v>892</v>
-      </c>
-      <c r="T25" s="143"/>
-      <c r="U25" s="9" t="s">
-        <v>818</v>
-      </c>
-      <c r="V25" s="92" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="26" spans="7:22">
-      <c r="L26" s="111" t="s">
-        <v>895</v>
-      </c>
-      <c r="M26" t="s">
-        <v>897</v>
-      </c>
-      <c r="N26" t="s">
-        <v>899</v>
-      </c>
-      <c r="T26" s="143"/>
-      <c r="U26" s="9" t="s">
-        <v>825</v>
-      </c>
-      <c r="V26" s="92"/>
-    </row>
-    <row r="27" spans="7:22">
-      <c r="L27" t="s">
-        <v>896</v>
-      </c>
-      <c r="M27" t="s">
-        <v>898</v>
-      </c>
-      <c r="T27" s="143"/>
-      <c r="U27" s="9" t="s">
-        <v>826</v>
-      </c>
-      <c r="V27" s="92"/>
-    </row>
-    <row r="28" spans="7:22">
-      <c r="M28" t="s">
-        <v>900</v>
-      </c>
-      <c r="T28" s="143"/>
-      <c r="U28" s="9" t="s">
-        <v>827</v>
-      </c>
-      <c r="V28" s="92" t="s">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="29" spans="7:22">
-      <c r="M29" t="s">
-        <v>901</v>
-      </c>
-      <c r="T29" s="144"/>
-      <c r="U29" s="9" t="s">
-        <v>828</v>
-      </c>
-      <c r="V29" s="92" t="s">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="30" spans="7:22">
-      <c r="L30" t="s">
-        <v>902</v>
-      </c>
-      <c r="M30" t="s">
-        <v>853</v>
-      </c>
-      <c r="T30" s="139" t="s">
-        <v>832</v>
-      </c>
-      <c r="U30" s="49" t="s">
-        <v>822</v>
-      </c>
-      <c r="V30" s="113"/>
-    </row>
-    <row r="31" spans="7:22">
-      <c r="M31" t="s">
+      <c r="K32" s="208"/>
+      <c r="L32" s="206"/>
+      <c r="M32" s="206"/>
+      <c r="N32" s="206"/>
+      <c r="O32" s="207" t="s">
         <v>903</v>
       </c>
-      <c r="T31" s="140"/>
-      <c r="U31" s="49" t="s">
-        <v>823</v>
-      </c>
-      <c r="V31" s="113"/>
-    </row>
-    <row r="32" spans="7:22">
-      <c r="G32" t="s">
-        <v>913</v>
-      </c>
-      <c r="N32" s="5" t="s">
+      <c r="P32" s="207" t="s">
         <v>904</v>
       </c>
-      <c r="O32" s="5" t="s">
-        <v>905</v>
-      </c>
-      <c r="T32" s="141"/>
-      <c r="U32" s="49" t="s">
+      <c r="Q32" s="206"/>
+      <c r="R32" s="206"/>
+      <c r="V32" s="140"/>
+      <c r="W32" s="49" t="s">
         <v>824</v>
       </c>
-      <c r="V32" s="113"/>
-    </row>
-    <row r="33" spans="6:15">
+      <c r="X32" s="113"/>
+    </row>
+    <row r="33" spans="6:17">
       <c r="F33">
         <v>1</v>
       </c>
       <c r="G33" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="34" spans="6:15">
+        <v>912</v>
+      </c>
+      <c r="K33" s="208"/>
+    </row>
+    <row r="34" spans="6:17">
       <c r="F34">
         <v>2</v>
       </c>
       <c r="G34" t="s">
-        <v>915</v>
-      </c>
-      <c r="K34" s="5" t="s">
+        <v>913</v>
+      </c>
+      <c r="K34" s="208">
+        <v>3</v>
+      </c>
+      <c r="L34" s="5" t="s">
+        <v>905</v>
+      </c>
+      <c r="M34" t="s">
         <v>906</v>
       </c>
-      <c r="L34" t="s">
-        <v>907</v>
-      </c>
-    </row>
-    <row r="35" spans="6:15">
+    </row>
+    <row r="35" spans="6:17">
       <c r="F35">
         <v>2</v>
       </c>
       <c r="G35" t="s">
-        <v>916</v>
-      </c>
-      <c r="L35" t="s">
+        <v>914</v>
+      </c>
+      <c r="M35" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="36" spans="6:17">
+      <c r="F36" s="7" t="s">
+        <v>915</v>
+      </c>
+      <c r="M36" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="37" spans="6:17">
+      <c r="M37" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="38" spans="6:17">
+      <c r="M38" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="39" spans="6:17">
+      <c r="M39" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="40" spans="6:17">
+      <c r="M40" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="41" spans="6:17" ht="15.75" thickBot="1">
+      <c r="L41" s="206"/>
+      <c r="M41" s="206"/>
+      <c r="N41" s="206"/>
+      <c r="O41" s="207" t="s">
         <v>908</v>
       </c>
-    </row>
-    <row r="36" spans="6:15">
-      <c r="F36" s="7" t="s">
-        <v>917</v>
-      </c>
-      <c r="L36" t="s">
-        <v>884</v>
-      </c>
-    </row>
-    <row r="37" spans="6:15">
-      <c r="L37" t="s">
-        <v>885</v>
-      </c>
-    </row>
-    <row r="38" spans="6:15">
-      <c r="L38" t="s">
-        <v>895</v>
-      </c>
-    </row>
-    <row r="39" spans="6:15">
-      <c r="L39" t="s">
-        <v>896</v>
-      </c>
-    </row>
-    <row r="40" spans="6:15">
-      <c r="L40" t="s">
-        <v>902</v>
-      </c>
-    </row>
-    <row r="41" spans="6:15">
-      <c r="N41" s="5" t="s">
-        <v>909</v>
-      </c>
-      <c r="O41" s="5" t="s">
-        <v>894</v>
-      </c>
+      <c r="P41" s="207" t="s">
+        <v>893</v>
+      </c>
+      <c r="Q41" s="206"/>
+    </row>
+    <row r="44" spans="6:17">
+      <c r="P44" s="205"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="T30:T32"/>
-    <mergeCell ref="T22:T29"/>
+    <mergeCell ref="V30:V32"/>
+    <mergeCell ref="V22:V29"/>
   </mergeCells>
   <phoneticPr fontId="34" type="noConversion"/>
   <hyperlinks>
@@ -21878,7 +22357,7 @@
       <c r="R5" s="13" t="s">
         <v>352</v>
       </c>
-      <c r="S5" s="145" t="s">
+      <c r="S5" s="144" t="s">
         <v>810</v>
       </c>
     </row>
@@ -21895,7 +22374,7 @@
       <c r="R6" s="9" t="s">
         <v>602</v>
       </c>
-      <c r="S6" s="145"/>
+      <c r="S6" s="144"/>
     </row>
     <row r="7" spans="3:20">
       <c r="O7" s="81" t="s">
@@ -21910,7 +22389,7 @@
       <c r="R7" s="9" t="s">
         <v>603</v>
       </c>
-      <c r="S7" s="145"/>
+      <c r="S7" s="144"/>
     </row>
     <row r="8" spans="3:20">
       <c r="O8" s="81" t="s">
@@ -21925,7 +22404,7 @@
       <c r="R8" s="9" t="s">
         <v>350</v>
       </c>
-      <c r="S8" s="145"/>
+      <c r="S8" s="144"/>
     </row>
     <row r="9" spans="3:20">
       <c r="O9" s="81" t="s">
@@ -21940,7 +22419,7 @@
       <c r="R9" s="9" t="s">
         <v>349</v>
       </c>
-      <c r="S9" s="145"/>
+      <c r="S9" s="144"/>
     </row>
     <row r="10" spans="3:20">
       <c r="Q10" s="9" t="s">
@@ -21965,7 +22444,7 @@
       </c>
     </row>
     <row r="15" spans="3:20">
-      <c r="Q15" s="142" t="s">
+      <c r="Q15" s="141" t="s">
         <v>833</v>
       </c>
       <c r="R15" s="9" t="s">
@@ -22000,7 +22479,7 @@
       <c r="J16" s="10" t="s">
         <v>814</v>
       </c>
-      <c r="Q16" s="143"/>
+      <c r="Q16" s="142"/>
       <c r="R16" s="9" t="s">
         <v>816</v>
       </c>
@@ -22010,7 +22489,7 @@
     </row>
     <row r="17" spans="10:19">
       <c r="J17" s="81"/>
-      <c r="Q17" s="143"/>
+      <c r="Q17" s="142"/>
       <c r="R17" s="9" t="s">
         <v>817</v>
       </c>
@@ -22019,7 +22498,7 @@
       </c>
     </row>
     <row r="18" spans="10:19">
-      <c r="Q18" s="143"/>
+      <c r="Q18" s="142"/>
       <c r="R18" s="9" t="s">
         <v>818</v>
       </c>
@@ -22028,21 +22507,21 @@
       </c>
     </row>
     <row r="19" spans="10:19">
-      <c r="Q19" s="143"/>
+      <c r="Q19" s="142"/>
       <c r="R19" s="9" t="s">
         <v>825</v>
       </c>
       <c r="S19" s="92"/>
     </row>
     <row r="20" spans="10:19">
-      <c r="Q20" s="143"/>
+      <c r="Q20" s="142"/>
       <c r="R20" s="9" t="s">
         <v>826</v>
       </c>
       <c r="S20" s="92"/>
     </row>
     <row r="21" spans="10:19">
-      <c r="Q21" s="143"/>
+      <c r="Q21" s="142"/>
       <c r="R21" s="9" t="s">
         <v>827</v>
       </c>
@@ -22051,7 +22530,7 @@
       </c>
     </row>
     <row r="22" spans="10:19">
-      <c r="Q22" s="144"/>
+      <c r="Q22" s="143"/>
       <c r="R22" s="9" t="s">
         <v>828</v>
       </c>
@@ -22060,7 +22539,7 @@
       </c>
     </row>
     <row r="23" spans="10:19">
-      <c r="Q23" s="142" t="s">
+      <c r="Q23" s="141" t="s">
         <v>832</v>
       </c>
       <c r="R23" s="9" t="s">
@@ -22069,14 +22548,14 @@
       <c r="S23" s="92"/>
     </row>
     <row r="24" spans="10:19">
-      <c r="Q24" s="143"/>
+      <c r="Q24" s="142"/>
       <c r="R24" s="9" t="s">
         <v>823</v>
       </c>
       <c r="S24" s="92"/>
     </row>
     <row r="25" spans="10:19">
-      <c r="Q25" s="144"/>
+      <c r="Q25" s="143"/>
       <c r="R25" s="9" t="s">
         <v>824</v>
       </c>
@@ -22101,22 +22580,22 @@
   <sheetData>
     <row r="10" spans="14:14">
       <c r="N10" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
     </row>
     <row r="14" spans="14:14">
       <c r="N14" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
     </row>
     <row r="15" spans="14:14">
       <c r="N15" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
     </row>
     <row r="24" spans="14:14">
       <c r="N24" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
     </row>
   </sheetData>
@@ -22141,39 +22620,39 @@
       <c r="B1" t="s">
         <v>861</v>
       </c>
-      <c r="J1" s="146" t="s">
-        <v>956</v>
-      </c>
-      <c r="K1" s="147"/>
-      <c r="L1" s="147"/>
-      <c r="M1" s="147"/>
-      <c r="N1" s="147"/>
-      <c r="O1" s="147"/>
-      <c r="P1" s="147"/>
-      <c r="Q1" s="147"/>
+      <c r="J1" s="145" t="s">
+        <v>954</v>
+      </c>
+      <c r="K1" s="146"/>
+      <c r="L1" s="146"/>
+      <c r="M1" s="146"/>
+      <c r="N1" s="146"/>
+      <c r="O1" s="146"/>
+      <c r="P1" s="146"/>
+      <c r="Q1" s="146"/>
     </row>
     <row r="2" spans="1:17">
-      <c r="J2" s="147"/>
-      <c r="K2" s="147"/>
-      <c r="L2" s="147"/>
-      <c r="M2" s="147"/>
-      <c r="N2" s="147"/>
-      <c r="O2" s="147"/>
-      <c r="P2" s="147"/>
-      <c r="Q2" s="147"/>
+      <c r="J2" s="146"/>
+      <c r="K2" s="146"/>
+      <c r="L2" s="146"/>
+      <c r="M2" s="146"/>
+      <c r="N2" s="146"/>
+      <c r="O2" s="146"/>
+      <c r="P2" s="146"/>
+      <c r="Q2" s="146"/>
     </row>
     <row r="3" spans="1:17">
       <c r="A3" t="s">
         <v>862</v>
       </c>
-      <c r="J3" s="147"/>
-      <c r="K3" s="147"/>
-      <c r="L3" s="147"/>
-      <c r="M3" s="147"/>
-      <c r="N3" s="147"/>
-      <c r="O3" s="147"/>
-      <c r="P3" s="147"/>
-      <c r="Q3" s="147"/>
+      <c r="J3" s="146"/>
+      <c r="K3" s="146"/>
+      <c r="L3" s="146"/>
+      <c r="M3" s="146"/>
+      <c r="N3" s="146"/>
+      <c r="O3" s="146"/>
+      <c r="P3" s="146"/>
+      <c r="Q3" s="146"/>
     </row>
     <row r="4" spans="1:17">
       <c r="A4" t="s">
@@ -22185,270 +22664,270 @@
       <c r="D4" t="s">
         <v>864</v>
       </c>
-      <c r="J4" s="147"/>
-      <c r="K4" s="147"/>
-      <c r="L4" s="147"/>
-      <c r="M4" s="147"/>
-      <c r="N4" s="147"/>
-      <c r="O4" s="147"/>
-      <c r="P4" s="147"/>
-      <c r="Q4" s="147"/>
+      <c r="J4" s="146"/>
+      <c r="K4" s="146"/>
+      <c r="L4" s="146"/>
+      <c r="M4" s="146"/>
+      <c r="N4" s="146"/>
+      <c r="O4" s="146"/>
+      <c r="P4" s="146"/>
+      <c r="Q4" s="146"/>
     </row>
     <row r="5" spans="1:17">
-      <c r="J5" s="147"/>
-      <c r="K5" s="147"/>
-      <c r="L5" s="147"/>
-      <c r="M5" s="147"/>
-      <c r="N5" s="147"/>
-      <c r="O5" s="147"/>
-      <c r="P5" s="147"/>
-      <c r="Q5" s="147"/>
+      <c r="J5" s="146"/>
+      <c r="K5" s="146"/>
+      <c r="L5" s="146"/>
+      <c r="M5" s="146"/>
+      <c r="N5" s="146"/>
+      <c r="O5" s="146"/>
+      <c r="P5" s="146"/>
+      <c r="Q5" s="146"/>
     </row>
     <row r="6" spans="1:17" ht="15.75" thickBot="1">
       <c r="A6" t="s">
         <v>865</v>
       </c>
       <c r="E6" t="s">
-        <v>922</v>
-      </c>
-      <c r="J6" s="147"/>
-      <c r="K6" s="147"/>
-      <c r="L6" s="147"/>
-      <c r="M6" s="147"/>
-      <c r="N6" s="147"/>
-      <c r="O6" s="147"/>
-      <c r="P6" s="147"/>
-      <c r="Q6" s="147"/>
+        <v>920</v>
+      </c>
+      <c r="J6" s="146"/>
+      <c r="K6" s="146"/>
+      <c r="L6" s="146"/>
+      <c r="M6" s="146"/>
+      <c r="N6" s="146"/>
+      <c r="O6" s="146"/>
+      <c r="P6" s="146"/>
+      <c r="Q6" s="146"/>
     </row>
     <row r="7" spans="1:17" ht="15.75" thickBot="1">
       <c r="A7" s="106" t="s">
         <v>866</v>
       </c>
-      <c r="J7" s="147"/>
-      <c r="K7" s="147"/>
-      <c r="L7" s="147"/>
-      <c r="M7" s="147"/>
-      <c r="N7" s="147"/>
-      <c r="O7" s="147"/>
-      <c r="P7" s="147"/>
-      <c r="Q7" s="147"/>
+      <c r="J7" s="146"/>
+      <c r="K7" s="146"/>
+      <c r="L7" s="146"/>
+      <c r="M7" s="146"/>
+      <c r="N7" s="146"/>
+      <c r="O7" s="146"/>
+      <c r="P7" s="146"/>
+      <c r="Q7" s="146"/>
     </row>
     <row r="8" spans="1:17">
       <c r="A8" s="121"/>
-      <c r="J8" s="147"/>
-      <c r="K8" s="147"/>
-      <c r="L8" s="147"/>
-      <c r="M8" s="147"/>
-      <c r="N8" s="147"/>
-      <c r="O8" s="147"/>
-      <c r="P8" s="147"/>
-      <c r="Q8" s="147"/>
+      <c r="J8" s="146"/>
+      <c r="K8" s="146"/>
+      <c r="L8" s="146"/>
+      <c r="M8" s="146"/>
+      <c r="N8" s="146"/>
+      <c r="O8" s="146"/>
+      <c r="P8" s="146"/>
+      <c r="Q8" s="146"/>
     </row>
     <row r="9" spans="1:17">
       <c r="A9" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B9" t="s">
-        <v>928</v>
-      </c>
-      <c r="J9" s="147"/>
-      <c r="K9" s="147"/>
-      <c r="L9" s="147"/>
-      <c r="M9" s="147"/>
-      <c r="N9" s="147"/>
-      <c r="O9" s="147"/>
-      <c r="P9" s="147"/>
-      <c r="Q9" s="147"/>
+        <v>926</v>
+      </c>
+      <c r="J9" s="146"/>
+      <c r="K9" s="146"/>
+      <c r="L9" s="146"/>
+      <c r="M9" s="146"/>
+      <c r="N9" s="146"/>
+      <c r="O9" s="146"/>
+      <c r="P9" s="146"/>
+      <c r="Q9" s="146"/>
     </row>
     <row r="10" spans="1:17">
       <c r="A10" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="B10" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="E10" t="s">
+        <v>927</v>
+      </c>
+      <c r="F10" t="s">
+        <v>928</v>
+      </c>
+      <c r="G10" t="s">
         <v>929</v>
       </c>
-      <c r="F10" t="s">
-        <v>930</v>
-      </c>
-      <c r="G10" t="s">
-        <v>931</v>
-      </c>
       <c r="H10" t="s">
-        <v>954</v>
-      </c>
-      <c r="J10" s="147"/>
-      <c r="K10" s="147"/>
-      <c r="L10" s="147"/>
-      <c r="M10" s="147"/>
-      <c r="N10" s="147"/>
-      <c r="O10" s="147"/>
-      <c r="P10" s="147"/>
-      <c r="Q10" s="147"/>
+        <v>952</v>
+      </c>
+      <c r="J10" s="146"/>
+      <c r="K10" s="146"/>
+      <c r="L10" s="146"/>
+      <c r="M10" s="146"/>
+      <c r="N10" s="146"/>
+      <c r="O10" s="146"/>
+      <c r="P10" s="146"/>
+      <c r="Q10" s="146"/>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="B11" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="E11" t="s">
+        <v>951</v>
+      </c>
+      <c r="F11" t="s">
+        <v>930</v>
+      </c>
+      <c r="G11" t="s">
+        <v>931</v>
+      </c>
+      <c r="H11" t="s">
         <v>953</v>
       </c>
-      <c r="F11" t="s">
-        <v>932</v>
-      </c>
-      <c r="G11" t="s">
-        <v>933</v>
-      </c>
-      <c r="H11" t="s">
-        <v>955</v>
-      </c>
-      <c r="J11" s="147"/>
-      <c r="K11" s="147"/>
-      <c r="L11" s="147"/>
-      <c r="M11" s="147"/>
-      <c r="N11" s="147"/>
-      <c r="O11" s="147"/>
-      <c r="P11" s="147"/>
-      <c r="Q11" s="147"/>
+      <c r="J11" s="146"/>
+      <c r="K11" s="146"/>
+      <c r="L11" s="146"/>
+      <c r="M11" s="146"/>
+      <c r="N11" s="146"/>
+      <c r="O11" s="146"/>
+      <c r="P11" s="146"/>
+      <c r="Q11" s="146"/>
     </row>
     <row r="12" spans="1:17">
       <c r="B12" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="F12" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="G12" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="H12" t="s">
-        <v>955</v>
-      </c>
-      <c r="J12" s="147"/>
-      <c r="K12" s="147"/>
-      <c r="L12" s="147"/>
-      <c r="M12" s="147"/>
-      <c r="N12" s="147"/>
-      <c r="O12" s="147"/>
-      <c r="P12" s="147"/>
-      <c r="Q12" s="147"/>
+        <v>953</v>
+      </c>
+      <c r="J12" s="146"/>
+      <c r="K12" s="146"/>
+      <c r="L12" s="146"/>
+      <c r="M12" s="146"/>
+      <c r="N12" s="146"/>
+      <c r="O12" s="146"/>
+      <c r="P12" s="146"/>
+      <c r="Q12" s="146"/>
     </row>
     <row r="13" spans="1:17">
       <c r="F13" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="G13" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="H13" t="s">
-        <v>955</v>
-      </c>
-      <c r="J13" s="147"/>
-      <c r="K13" s="147"/>
-      <c r="L13" s="147"/>
-      <c r="M13" s="147"/>
-      <c r="N13" s="147"/>
-      <c r="O13" s="147"/>
-      <c r="P13" s="147"/>
-      <c r="Q13" s="147"/>
+        <v>953</v>
+      </c>
+      <c r="J13" s="146"/>
+      <c r="K13" s="146"/>
+      <c r="L13" s="146"/>
+      <c r="M13" s="146"/>
+      <c r="N13" s="146"/>
+      <c r="O13" s="146"/>
+      <c r="P13" s="146"/>
+      <c r="Q13" s="146"/>
     </row>
     <row r="14" spans="1:17">
-      <c r="J14" s="147"/>
-      <c r="K14" s="147"/>
-      <c r="L14" s="147"/>
-      <c r="M14" s="147"/>
-      <c r="N14" s="147"/>
-      <c r="O14" s="147"/>
-      <c r="P14" s="147"/>
-      <c r="Q14" s="147"/>
+      <c r="J14" s="146"/>
+      <c r="K14" s="146"/>
+      <c r="L14" s="146"/>
+      <c r="M14" s="146"/>
+      <c r="N14" s="146"/>
+      <c r="O14" s="146"/>
+      <c r="P14" s="146"/>
+      <c r="Q14" s="146"/>
     </row>
     <row r="15" spans="1:17">
       <c r="A15" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="C15" t="s">
-        <v>951</v>
-      </c>
-      <c r="J15" s="147"/>
-      <c r="K15" s="147"/>
-      <c r="L15" s="147"/>
-      <c r="M15" s="147"/>
-      <c r="N15" s="147"/>
-      <c r="O15" s="147"/>
-      <c r="P15" s="147"/>
-      <c r="Q15" s="147"/>
+        <v>949</v>
+      </c>
+      <c r="J15" s="146"/>
+      <c r="K15" s="146"/>
+      <c r="L15" s="146"/>
+      <c r="M15" s="146"/>
+      <c r="N15" s="146"/>
+      <c r="O15" s="146"/>
+      <c r="P15" s="146"/>
+      <c r="Q15" s="146"/>
     </row>
     <row r="16" spans="1:17">
       <c r="A16" t="s">
-        <v>941</v>
-      </c>
-      <c r="J16" s="147"/>
-      <c r="K16" s="147"/>
-      <c r="L16" s="147"/>
-      <c r="M16" s="147"/>
-      <c r="N16" s="147"/>
-      <c r="O16" s="147"/>
-      <c r="P16" s="147"/>
-      <c r="Q16" s="147"/>
+        <v>939</v>
+      </c>
+      <c r="J16" s="146"/>
+      <c r="K16" s="146"/>
+      <c r="L16" s="146"/>
+      <c r="M16" s="146"/>
+      <c r="N16" s="146"/>
+      <c r="O16" s="146"/>
+      <c r="P16" s="146"/>
+      <c r="Q16" s="146"/>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="5" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="5" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
     </row>
   </sheetData>
@@ -22616,19 +23095,19 @@
       <c r="E7" s="31" t="s">
         <v>449</v>
       </c>
-      <c r="F7" s="148" t="s">
+      <c r="F7" s="147" t="s">
         <v>441</v>
       </c>
-      <c r="G7" s="148"/>
-      <c r="H7" s="148"/>
-      <c r="I7" s="148"/>
-      <c r="J7" s="148"/>
-      <c r="K7" s="148"/>
-      <c r="L7" s="148"/>
-      <c r="M7" s="148"/>
-      <c r="N7" s="148"/>
-      <c r="O7" s="148"/>
-      <c r="P7" s="148"/>
+      <c r="G7" s="147"/>
+      <c r="H7" s="147"/>
+      <c r="I7" s="147"/>
+      <c r="J7" s="147"/>
+      <c r="K7" s="147"/>
+      <c r="L7" s="147"/>
+      <c r="M7" s="147"/>
+      <c r="N7" s="147"/>
+      <c r="O7" s="147"/>
+      <c r="P7" s="147"/>
     </row>
     <row r="8" spans="1:17">
       <c r="B8" s="32" t="s">
@@ -22810,7 +23289,7 @@
         <v>463</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -22852,40 +23331,40 @@
       <c r="A24" s="35" t="s">
         <v>455</v>
       </c>
-      <c r="B24" s="149" t="s">
+      <c r="B24" s="148" t="s">
         <v>457</v>
       </c>
-      <c r="C24" s="149"/>
-      <c r="D24" s="149"/>
-      <c r="E24" s="149"/>
-      <c r="F24" s="149"/>
-      <c r="G24" s="149"/>
+      <c r="C24" s="148"/>
+      <c r="D24" s="148"/>
+      <c r="E24" s="148"/>
+      <c r="F24" s="148"/>
+      <c r="G24" s="148"/>
     </row>
     <row r="25" spans="1:7" ht="30">
       <c r="A25" s="35" t="s">
         <v>462</v>
       </c>
-      <c r="B25" s="150" t="s">
+      <c r="B25" s="149" t="s">
         <v>464</v>
       </c>
-      <c r="C25" s="150"/>
-      <c r="D25" s="150"/>
-      <c r="E25" s="150"/>
-      <c r="F25" s="150"/>
-      <c r="G25" s="150"/>
+      <c r="C25" s="149"/>
+      <c r="D25" s="149"/>
+      <c r="E25" s="149"/>
+      <c r="F25" s="149"/>
+      <c r="G25" s="149"/>
     </row>
     <row r="26" spans="1:7" ht="159" customHeight="1">
       <c r="A26" s="35" t="s">
         <v>459</v>
       </c>
-      <c r="B26" s="149" t="s">
+      <c r="B26" s="148" t="s">
         <v>460</v>
       </c>
-      <c r="C26" s="149"/>
-      <c r="D26" s="149"/>
-      <c r="E26" s="149"/>
-      <c r="F26" s="149"/>
-      <c r="G26" s="149"/>
+      <c r="C26" s="148"/>
+      <c r="D26" s="148"/>
+      <c r="E26" s="148"/>
+      <c r="F26" s="148"/>
+      <c r="G26" s="148"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -23400,29 +23879,29 @@
       <c r="B27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="C27" s="153" t="s">
+      <c r="C27" s="152" t="s">
         <v>622</v>
       </c>
-      <c r="D27" s="154"/>
+      <c r="D27" s="153"/>
       <c r="E27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="F27" s="153" t="s">
+      <c r="F27" s="152" t="s">
         <v>622</v>
       </c>
-      <c r="G27" s="154"/>
+      <c r="G27" s="153"/>
       <c r="H27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="I27" s="153" t="s">
+      <c r="I27" s="152" t="s">
         <v>622</v>
       </c>
-      <c r="J27" s="154"/>
-      <c r="L27" s="165" t="s">
+      <c r="J27" s="153"/>
+      <c r="L27" s="164" t="s">
         <v>694</v>
       </c>
-      <c r="M27" s="165"/>
-      <c r="N27" s="165"/>
+      <c r="M27" s="164"/>
+      <c r="N27" s="164"/>
     </row>
     <row r="28" spans="1:14" ht="32.25" thickBot="1">
       <c r="A28" s="81">
@@ -23431,29 +23910,29 @@
       <c r="B28" s="69" t="s">
         <v>623</v>
       </c>
-      <c r="C28" s="151" t="s">
+      <c r="C28" s="150" t="s">
         <v>624</v>
       </c>
-      <c r="D28" s="152"/>
+      <c r="D28" s="151"/>
       <c r="E28" s="70" t="s">
         <v>645</v>
       </c>
-      <c r="F28" s="155" t="s">
+      <c r="F28" s="154" t="s">
         <v>646</v>
       </c>
-      <c r="G28" s="156"/>
+      <c r="G28" s="155"/>
       <c r="H28" s="69" t="s">
         <v>667</v>
       </c>
-      <c r="I28" s="151" t="s">
+      <c r="I28" s="150" t="s">
         <v>668</v>
       </c>
-      <c r="J28" s="152"/>
-      <c r="L28" s="166" t="s">
+      <c r="J28" s="151"/>
+      <c r="L28" s="165" t="s">
         <v>695</v>
       </c>
-      <c r="M28" s="166"/>
-      <c r="N28" s="166"/>
+      <c r="M28" s="165"/>
+      <c r="N28" s="165"/>
     </row>
     <row r="29" spans="1:14" ht="31.5" thickBot="1">
       <c r="A29" s="81">
@@ -23462,29 +23941,29 @@
       <c r="B29" s="70" t="s">
         <v>625</v>
       </c>
-      <c r="C29" s="155" t="s">
+      <c r="C29" s="154" t="s">
         <v>626</v>
       </c>
-      <c r="D29" s="156"/>
+      <c r="D29" s="155"/>
       <c r="E29" s="69" t="s">
         <v>647</v>
       </c>
-      <c r="F29" s="151" t="s">
+      <c r="F29" s="150" t="s">
         <v>648</v>
       </c>
-      <c r="G29" s="152"/>
+      <c r="G29" s="151"/>
       <c r="H29" s="70" t="s">
         <v>669</v>
       </c>
-      <c r="I29" s="159" t="s">
+      <c r="I29" s="158" t="s">
         <v>670</v>
       </c>
-      <c r="J29" s="160"/>
-      <c r="L29" s="165" t="s">
+      <c r="J29" s="159"/>
+      <c r="L29" s="164" t="s">
         <v>696</v>
       </c>
-      <c r="M29" s="165"/>
-      <c r="N29" s="165"/>
+      <c r="M29" s="164"/>
+      <c r="N29" s="164"/>
     </row>
     <row r="30" spans="1:14" ht="15.75" thickBot="1">
       <c r="A30" s="81">
@@ -23493,29 +23972,29 @@
       <c r="B30" s="69" t="s">
         <v>627</v>
       </c>
-      <c r="C30" s="151" t="s">
+      <c r="C30" s="150" t="s">
         <v>628</v>
       </c>
-      <c r="D30" s="152"/>
+      <c r="D30" s="151"/>
       <c r="E30" s="70" t="s">
         <v>649</v>
       </c>
-      <c r="F30" s="155" t="s">
+      <c r="F30" s="154" t="s">
         <v>650</v>
       </c>
-      <c r="G30" s="156"/>
+      <c r="G30" s="155"/>
       <c r="H30" s="69" t="s">
         <v>671</v>
       </c>
-      <c r="I30" s="151" t="s">
+      <c r="I30" s="150" t="s">
         <v>672</v>
       </c>
-      <c r="J30" s="152"/>
-      <c r="L30" s="166" t="s">
+      <c r="J30" s="151"/>
+      <c r="L30" s="165" t="s">
         <v>697</v>
       </c>
-      <c r="M30" s="166"/>
-      <c r="N30" s="166"/>
+      <c r="M30" s="165"/>
+      <c r="N30" s="165"/>
     </row>
     <row r="31" spans="1:14" ht="17.25" customHeight="1" thickBot="1">
       <c r="A31" s="81">
@@ -23524,29 +24003,29 @@
       <c r="B31" s="70" t="s">
         <v>629</v>
       </c>
-      <c r="C31" s="155" t="s">
+      <c r="C31" s="154" t="s">
         <v>630</v>
       </c>
-      <c r="D31" s="156"/>
+      <c r="D31" s="155"/>
       <c r="E31" s="69" t="s">
         <v>651</v>
       </c>
-      <c r="F31" s="151" t="s">
+      <c r="F31" s="150" t="s">
         <v>652</v>
       </c>
-      <c r="G31" s="152"/>
+      <c r="G31" s="151"/>
       <c r="H31" s="70" t="s">
         <v>673</v>
       </c>
-      <c r="I31" s="155" t="s">
+      <c r="I31" s="154" t="s">
         <v>674</v>
       </c>
-      <c r="J31" s="156"/>
-      <c r="L31" s="165" t="s">
+      <c r="J31" s="155"/>
+      <c r="L31" s="164" t="s">
         <v>698</v>
       </c>
-      <c r="M31" s="165"/>
-      <c r="N31" s="165"/>
+      <c r="M31" s="164"/>
+      <c r="N31" s="164"/>
     </row>
     <row r="32" spans="1:14" ht="43.5" customHeight="1" thickBot="1">
       <c r="A32" s="81">
@@ -23555,29 +24034,29 @@
       <c r="B32" s="69" t="s">
         <v>631</v>
       </c>
-      <c r="C32" s="151" t="s">
+      <c r="C32" s="150" t="s">
         <v>632</v>
       </c>
-      <c r="D32" s="152"/>
+      <c r="D32" s="151"/>
       <c r="E32" s="70" t="s">
         <v>653</v>
       </c>
-      <c r="F32" s="155" t="s">
+      <c r="F32" s="154" t="s">
         <v>654</v>
       </c>
-      <c r="G32" s="156"/>
+      <c r="G32" s="155"/>
       <c r="H32" s="69" t="s">
         <v>675</v>
       </c>
-      <c r="I32" s="151" t="s">
+      <c r="I32" s="150" t="s">
         <v>676</v>
       </c>
-      <c r="J32" s="152"/>
-      <c r="L32" s="166" t="s">
+      <c r="J32" s="151"/>
+      <c r="L32" s="165" t="s">
         <v>699</v>
       </c>
-      <c r="M32" s="166"/>
-      <c r="N32" s="166"/>
+      <c r="M32" s="165"/>
+      <c r="N32" s="165"/>
     </row>
     <row r="33" spans="1:14" ht="31.5" customHeight="1" thickBot="1">
       <c r="A33" s="81">
@@ -23586,29 +24065,29 @@
       <c r="B33" s="70" t="s">
         <v>633</v>
       </c>
-      <c r="C33" s="155" t="s">
+      <c r="C33" s="154" t="s">
         <v>634</v>
       </c>
-      <c r="D33" s="156"/>
+      <c r="D33" s="155"/>
       <c r="E33" s="69" t="s">
         <v>655</v>
       </c>
-      <c r="F33" s="151" t="s">
+      <c r="F33" s="150" t="s">
         <v>656</v>
       </c>
-      <c r="G33" s="152"/>
+      <c r="G33" s="151"/>
       <c r="H33" s="70" t="s">
         <v>677</v>
       </c>
-      <c r="I33" s="157" t="s">
+      <c r="I33" s="156" t="s">
         <v>678</v>
       </c>
-      <c r="J33" s="158"/>
-      <c r="L33" s="165" t="s">
+      <c r="J33" s="157"/>
+      <c r="L33" s="164" t="s">
         <v>700</v>
       </c>
-      <c r="M33" s="165"/>
-      <c r="N33" s="165"/>
+      <c r="M33" s="164"/>
+      <c r="N33" s="164"/>
     </row>
     <row r="34" spans="1:14" ht="28.5" customHeight="1" thickBot="1">
       <c r="A34" s="81">
@@ -23617,29 +24096,29 @@
       <c r="B34" s="69" t="s">
         <v>635</v>
       </c>
-      <c r="C34" s="151" t="s">
+      <c r="C34" s="150" t="s">
         <v>636</v>
       </c>
-      <c r="D34" s="152"/>
+      <c r="D34" s="151"/>
       <c r="E34" s="70" t="s">
         <v>657</v>
       </c>
-      <c r="F34" s="155" t="s">
+      <c r="F34" s="154" t="s">
         <v>658</v>
       </c>
-      <c r="G34" s="156"/>
+      <c r="G34" s="155"/>
       <c r="H34" s="69" t="s">
         <v>679</v>
       </c>
-      <c r="I34" s="161" t="s">
+      <c r="I34" s="160" t="s">
         <v>680</v>
       </c>
-      <c r="J34" s="162"/>
-      <c r="L34" s="166" t="s">
+      <c r="J34" s="161"/>
+      <c r="L34" s="165" t="s">
         <v>701</v>
       </c>
-      <c r="M34" s="166"/>
-      <c r="N34" s="166"/>
+      <c r="M34" s="165"/>
+      <c r="N34" s="165"/>
     </row>
     <row r="35" spans="1:14" ht="31.5" customHeight="1" thickBot="1">
       <c r="A35" s="81">
@@ -23648,29 +24127,29 @@
       <c r="B35" s="70" t="s">
         <v>637</v>
       </c>
-      <c r="C35" s="155" t="s">
+      <c r="C35" s="154" t="s">
         <v>638</v>
       </c>
-      <c r="D35" s="156"/>
+      <c r="D35" s="155"/>
       <c r="E35" s="69" t="s">
         <v>659</v>
       </c>
-      <c r="F35" s="151" t="s">
+      <c r="F35" s="150" t="s">
         <v>660</v>
       </c>
-      <c r="G35" s="152"/>
+      <c r="G35" s="151"/>
       <c r="H35" s="77" t="s">
         <v>681</v>
       </c>
-      <c r="I35" s="155" t="s">
+      <c r="I35" s="154" t="s">
         <v>682</v>
       </c>
-      <c r="J35" s="156"/>
-      <c r="L35" s="165" t="s">
+      <c r="J35" s="155"/>
+      <c r="L35" s="164" t="s">
         <v>702</v>
       </c>
-      <c r="M35" s="165"/>
-      <c r="N35" s="165"/>
+      <c r="M35" s="164"/>
+      <c r="N35" s="164"/>
     </row>
     <row r="36" spans="1:14" ht="60.75" thickBot="1">
       <c r="A36" s="81">
@@ -23679,17 +24158,17 @@
       <c r="B36" s="69" t="s">
         <v>639</v>
       </c>
-      <c r="C36" s="151" t="s">
+      <c r="C36" s="150" t="s">
         <v>640</v>
       </c>
-      <c r="D36" s="152"/>
+      <c r="D36" s="151"/>
       <c r="E36" s="70" t="s">
         <v>661</v>
       </c>
-      <c r="F36" s="155" t="s">
+      <c r="F36" s="154" t="s">
         <v>662</v>
       </c>
-      <c r="G36" s="156"/>
+      <c r="G36" s="155"/>
       <c r="H36" s="78"/>
       <c r="I36" s="71" t="s">
         <v>683</v>
@@ -23697,11 +24176,11 @@
       <c r="J36" s="72" t="s">
         <v>684</v>
       </c>
-      <c r="L36" s="166" t="s">
+      <c r="L36" s="165" t="s">
         <v>703</v>
       </c>
-      <c r="M36" s="166"/>
-      <c r="N36" s="166"/>
+      <c r="M36" s="165"/>
+      <c r="N36" s="165"/>
     </row>
     <row r="37" spans="1:14" ht="75.75" thickBot="1">
       <c r="A37" s="81">
@@ -23710,17 +24189,17 @@
       <c r="B37" s="70" t="s">
         <v>641</v>
       </c>
-      <c r="C37" s="155" t="s">
+      <c r="C37" s="154" t="s">
         <v>642</v>
       </c>
-      <c r="D37" s="156"/>
+      <c r="D37" s="155"/>
       <c r="E37" s="69" t="s">
         <v>663</v>
       </c>
-      <c r="F37" s="151" t="s">
+      <c r="F37" s="150" t="s">
         <v>664</v>
       </c>
-      <c r="G37" s="152"/>
+      <c r="G37" s="151"/>
       <c r="H37" s="78"/>
       <c r="I37" s="73" t="s">
         <v>685</v>
@@ -23736,17 +24215,17 @@
       <c r="B38" s="69" t="s">
         <v>643</v>
       </c>
-      <c r="C38" s="151" t="s">
+      <c r="C38" s="150" t="s">
         <v>644</v>
       </c>
-      <c r="D38" s="152"/>
+      <c r="D38" s="151"/>
       <c r="E38" s="70" t="s">
         <v>665</v>
       </c>
-      <c r="F38" s="155" t="s">
+      <c r="F38" s="154" t="s">
         <v>666</v>
       </c>
-      <c r="G38" s="156"/>
+      <c r="G38" s="155"/>
       <c r="H38" s="78"/>
       <c r="I38" s="75" t="s">
         <v>687</v>
@@ -23762,22 +24241,22 @@
       <c r="B39" s="70" t="s">
         <v>692</v>
       </c>
-      <c r="C39" s="157" t="s">
+      <c r="C39" s="156" t="s">
         <v>693</v>
       </c>
-      <c r="D39" s="158"/>
+      <c r="D39" s="157"/>
       <c r="E39" s="69" t="s">
         <v>690</v>
       </c>
-      <c r="F39" s="161" t="s">
+      <c r="F39" s="160" t="s">
         <v>691</v>
       </c>
-      <c r="G39" s="162"/>
+      <c r="G39" s="161"/>
       <c r="H39" s="79"/>
-      <c r="I39" s="163" t="s">
+      <c r="I39" s="162" t="s">
         <v>689</v>
       </c>
-      <c r="J39" s="164"/>
+      <c r="J39" s="163"/>
     </row>
     <row r="40" spans="1:14" ht="58.5" customHeight="1"/>
     <row r="42" spans="1:14" ht="31.5" customHeight="1"/>
@@ -23890,7 +24369,7 @@
         <v>583</v>
       </c>
       <c r="F2" s="32" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="G2" s="32" t="s">
         <v>415</v>
@@ -23971,12 +24450,12 @@
         <v>574</v>
       </c>
       <c r="F7" s="112" t="s">
-        <v>918</v>
-      </c>
-      <c r="I7" s="185" t="s">
-        <v>1170</v>
-      </c>
-      <c r="J7" s="185"/>
+        <v>916</v>
+      </c>
+      <c r="I7" s="184" t="s">
+        <v>1168</v>
+      </c>
+      <c r="J7" s="184"/>
       <c r="L7" s="49" t="s">
         <v>601</v>
       </c>
@@ -23994,7 +24473,7 @@
       <c r="D8" s="32" t="s">
         <v>582</v>
       </c>
-      <c r="E8" s="186" t="s">
+      <c r="E8" s="185" t="s">
         <v>583</v>
       </c>
       <c r="F8" s="36" t="s">
@@ -24316,10 +24795,10 @@
       <c r="L20" s="115" t="s">
         <v>568</v>
       </c>
-      <c r="M20" s="167" t="s">
-        <v>920</v>
-      </c>
-      <c r="N20" s="168"/>
+      <c r="M20" s="166" t="s">
+        <v>918</v>
+      </c>
+      <c r="N20" s="167"/>
     </row>
     <row r="21" spans="1:14">
       <c r="B21" s="85" t="s">
@@ -24425,41 +24904,41 @@
         <v>620</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="15.75" thickBot="1">
       <c r="F26" s="7" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="15.75" thickBot="1">
       <c r="B27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="C27" s="153" t="s">
+      <c r="C27" s="152" t="s">
         <v>622</v>
       </c>
-      <c r="D27" s="154"/>
+      <c r="D27" s="153"/>
       <c r="E27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="F27" s="153" t="s">
+      <c r="F27" s="152" t="s">
         <v>622</v>
       </c>
-      <c r="G27" s="154"/>
+      <c r="G27" s="153"/>
       <c r="H27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="I27" s="153" t="s">
+      <c r="I27" s="152" t="s">
         <v>622</v>
       </c>
-      <c r="J27" s="154"/>
-      <c r="L27" s="165" t="s">
+      <c r="J27" s="153"/>
+      <c r="L27" s="164" t="s">
         <v>694</v>
       </c>
-      <c r="M27" s="165"/>
-      <c r="N27" s="165"/>
+      <c r="M27" s="164"/>
+      <c r="N27" s="164"/>
     </row>
     <row r="28" spans="1:14" ht="49.5" customHeight="1" thickBot="1">
       <c r="A28" s="81">
@@ -24468,29 +24947,29 @@
       <c r="B28" s="69" t="s">
         <v>623</v>
       </c>
-      <c r="C28" s="151" t="s">
+      <c r="C28" s="150" t="s">
         <v>624</v>
       </c>
-      <c r="D28" s="152"/>
+      <c r="D28" s="151"/>
       <c r="E28" s="70" t="s">
         <v>645</v>
       </c>
-      <c r="F28" s="155" t="s">
-        <v>1182</v>
-      </c>
-      <c r="G28" s="156"/>
+      <c r="F28" s="154" t="s">
+        <v>1180</v>
+      </c>
+      <c r="G28" s="155"/>
       <c r="H28" s="69" t="s">
         <v>667</v>
       </c>
-      <c r="I28" s="151" t="s">
+      <c r="I28" s="150" t="s">
         <v>668</v>
       </c>
-      <c r="J28" s="152"/>
-      <c r="L28" s="166" t="s">
+      <c r="J28" s="151"/>
+      <c r="L28" s="165" t="s">
         <v>695</v>
       </c>
-      <c r="M28" s="166"/>
-      <c r="N28" s="166"/>
+      <c r="M28" s="165"/>
+      <c r="N28" s="165"/>
     </row>
     <row r="29" spans="1:14" ht="31.5" thickBot="1">
       <c r="A29" s="81">
@@ -24499,29 +24978,29 @@
       <c r="B29" s="70" t="s">
         <v>625</v>
       </c>
-      <c r="C29" s="155" t="s">
+      <c r="C29" s="154" t="s">
         <v>626</v>
       </c>
-      <c r="D29" s="156"/>
+      <c r="D29" s="155"/>
       <c r="E29" s="69" t="s">
         <v>647</v>
       </c>
-      <c r="F29" s="151" t="s">
+      <c r="F29" s="150" t="s">
         <v>648</v>
       </c>
-      <c r="G29" s="152"/>
+      <c r="G29" s="151"/>
       <c r="H29" s="70" t="s">
         <v>669</v>
       </c>
-      <c r="I29" s="159" t="s">
+      <c r="I29" s="158" t="s">
         <v>670</v>
       </c>
-      <c r="J29" s="160"/>
-      <c r="L29" s="165" t="s">
+      <c r="J29" s="159"/>
+      <c r="L29" s="164" t="s">
         <v>696</v>
       </c>
-      <c r="M29" s="165"/>
-      <c r="N29" s="165"/>
+      <c r="M29" s="164"/>
+      <c r="N29" s="164"/>
     </row>
     <row r="30" spans="1:14" ht="15.75" thickBot="1">
       <c r="A30" s="81">
@@ -24530,29 +25009,29 @@
       <c r="B30" s="69" t="s">
         <v>627</v>
       </c>
-      <c r="C30" s="151" t="s">
+      <c r="C30" s="150" t="s">
         <v>628</v>
       </c>
-      <c r="D30" s="152"/>
+      <c r="D30" s="151"/>
       <c r="E30" s="70" t="s">
         <v>649</v>
       </c>
-      <c r="F30" s="155" t="s">
+      <c r="F30" s="154" t="s">
         <v>650</v>
       </c>
-      <c r="G30" s="156"/>
+      <c r="G30" s="155"/>
       <c r="H30" s="69" t="s">
         <v>671</v>
       </c>
-      <c r="I30" s="151" t="s">
+      <c r="I30" s="150" t="s">
         <v>672</v>
       </c>
-      <c r="J30" s="152"/>
-      <c r="L30" s="166" t="s">
+      <c r="J30" s="151"/>
+      <c r="L30" s="165" t="s">
         <v>697</v>
       </c>
-      <c r="M30" s="166"/>
-      <c r="N30" s="166"/>
+      <c r="M30" s="165"/>
+      <c r="N30" s="165"/>
     </row>
     <row r="31" spans="1:14" ht="17.25" customHeight="1" thickBot="1">
       <c r="A31" s="81">
@@ -24561,29 +25040,29 @@
       <c r="B31" s="70" t="s">
         <v>629</v>
       </c>
-      <c r="C31" s="155" t="s">
+      <c r="C31" s="154" t="s">
         <v>630</v>
       </c>
-      <c r="D31" s="156"/>
+      <c r="D31" s="155"/>
       <c r="E31" s="69" t="s">
         <v>651</v>
       </c>
-      <c r="F31" s="151" t="s">
+      <c r="F31" s="150" t="s">
         <v>652</v>
       </c>
-      <c r="G31" s="152"/>
+      <c r="G31" s="151"/>
       <c r="H31" s="70" t="s">
         <v>673</v>
       </c>
-      <c r="I31" s="155" t="s">
+      <c r="I31" s="154" t="s">
         <v>674</v>
       </c>
-      <c r="J31" s="156"/>
-      <c r="L31" s="165" t="s">
+      <c r="J31" s="155"/>
+      <c r="L31" s="164" t="s">
         <v>698</v>
       </c>
-      <c r="M31" s="165"/>
-      <c r="N31" s="165"/>
+      <c r="M31" s="164"/>
+      <c r="N31" s="164"/>
     </row>
     <row r="32" spans="1:14" ht="43.5" customHeight="1" thickBot="1">
       <c r="A32" s="81">
@@ -24592,29 +25071,29 @@
       <c r="B32" s="69" t="s">
         <v>631</v>
       </c>
-      <c r="C32" s="151" t="s">
+      <c r="C32" s="150" t="s">
         <v>632</v>
       </c>
-      <c r="D32" s="152"/>
+      <c r="D32" s="151"/>
       <c r="E32" s="70" t="s">
         <v>653</v>
       </c>
-      <c r="F32" s="155" t="s">
+      <c r="F32" s="154" t="s">
         <v>654</v>
       </c>
-      <c r="G32" s="156"/>
+      <c r="G32" s="155"/>
       <c r="H32" s="69" t="s">
         <v>675</v>
       </c>
-      <c r="I32" s="151" t="s">
+      <c r="I32" s="150" t="s">
         <v>676</v>
       </c>
-      <c r="J32" s="152"/>
-      <c r="L32" s="166" t="s">
+      <c r="J32" s="151"/>
+      <c r="L32" s="165" t="s">
         <v>699</v>
       </c>
-      <c r="M32" s="166"/>
-      <c r="N32" s="166"/>
+      <c r="M32" s="165"/>
+      <c r="N32" s="165"/>
     </row>
     <row r="33" spans="1:14" ht="31.5" customHeight="1" thickBot="1">
       <c r="A33" s="81">
@@ -24623,29 +25102,29 @@
       <c r="B33" s="70" t="s">
         <v>633</v>
       </c>
-      <c r="C33" s="155" t="s">
+      <c r="C33" s="154" t="s">
         <v>634</v>
       </c>
-      <c r="D33" s="156"/>
+      <c r="D33" s="155"/>
       <c r="E33" s="69" t="s">
         <v>655</v>
       </c>
-      <c r="F33" s="151" t="s">
+      <c r="F33" s="150" t="s">
         <v>656</v>
       </c>
-      <c r="G33" s="152"/>
+      <c r="G33" s="151"/>
       <c r="H33" s="70" t="s">
         <v>677</v>
       </c>
-      <c r="I33" s="157" t="s">
+      <c r="I33" s="156" t="s">
         <v>678</v>
       </c>
-      <c r="J33" s="158"/>
-      <c r="L33" s="165" t="s">
+      <c r="J33" s="157"/>
+      <c r="L33" s="164" t="s">
         <v>700</v>
       </c>
-      <c r="M33" s="165"/>
-      <c r="N33" s="165"/>
+      <c r="M33" s="164"/>
+      <c r="N33" s="164"/>
     </row>
     <row r="34" spans="1:14" ht="28.5" customHeight="1" thickBot="1">
       <c r="A34" s="81">
@@ -24654,29 +25133,29 @@
       <c r="B34" s="69" t="s">
         <v>635</v>
       </c>
-      <c r="C34" s="151" t="s">
+      <c r="C34" s="150" t="s">
         <v>636</v>
       </c>
-      <c r="D34" s="152"/>
+      <c r="D34" s="151"/>
       <c r="E34" s="70" t="s">
         <v>657</v>
       </c>
-      <c r="F34" s="155" t="s">
+      <c r="F34" s="154" t="s">
         <v>658</v>
       </c>
-      <c r="G34" s="156"/>
+      <c r="G34" s="155"/>
       <c r="H34" s="69" t="s">
         <v>679</v>
       </c>
-      <c r="I34" s="161" t="s">
+      <c r="I34" s="160" t="s">
         <v>680</v>
       </c>
-      <c r="J34" s="162"/>
-      <c r="L34" s="166" t="s">
+      <c r="J34" s="161"/>
+      <c r="L34" s="165" t="s">
         <v>701</v>
       </c>
-      <c r="M34" s="166"/>
-      <c r="N34" s="166"/>
+      <c r="M34" s="165"/>
+      <c r="N34" s="165"/>
     </row>
     <row r="35" spans="1:14" ht="31.5" customHeight="1" thickBot="1">
       <c r="A35" s="81">
@@ -24685,29 +25164,29 @@
       <c r="B35" s="70" t="s">
         <v>637</v>
       </c>
-      <c r="C35" s="155" t="s">
+      <c r="C35" s="154" t="s">
         <v>638</v>
       </c>
-      <c r="D35" s="156"/>
+      <c r="D35" s="155"/>
       <c r="E35" s="69" t="s">
         <v>659</v>
       </c>
-      <c r="F35" s="151" t="s">
+      <c r="F35" s="150" t="s">
         <v>660</v>
       </c>
-      <c r="G35" s="152"/>
+      <c r="G35" s="151"/>
       <c r="H35" s="77" t="s">
         <v>681</v>
       </c>
-      <c r="I35" s="155" t="s">
+      <c r="I35" s="154" t="s">
         <v>682</v>
       </c>
-      <c r="J35" s="156"/>
-      <c r="L35" s="165" t="s">
+      <c r="J35" s="155"/>
+      <c r="L35" s="164" t="s">
         <v>702</v>
       </c>
-      <c r="M35" s="165"/>
-      <c r="N35" s="165"/>
+      <c r="M35" s="164"/>
+      <c r="N35" s="164"/>
     </row>
     <row r="36" spans="1:14" ht="60.75" thickBot="1">
       <c r="A36" s="81">
@@ -24716,17 +25195,17 @@
       <c r="B36" s="69" t="s">
         <v>639</v>
       </c>
-      <c r="C36" s="151" t="s">
+      <c r="C36" s="150" t="s">
         <v>640</v>
       </c>
-      <c r="D36" s="152"/>
+      <c r="D36" s="151"/>
       <c r="E36" s="70" t="s">
         <v>661</v>
       </c>
-      <c r="F36" s="155" t="s">
+      <c r="F36" s="154" t="s">
         <v>662</v>
       </c>
-      <c r="G36" s="156"/>
+      <c r="G36" s="155"/>
       <c r="H36" s="78"/>
       <c r="I36" s="71" t="s">
         <v>683</v>
@@ -24734,11 +25213,11 @@
       <c r="J36" s="72" t="s">
         <v>684</v>
       </c>
-      <c r="L36" s="166" t="s">
+      <c r="L36" s="165" t="s">
         <v>703</v>
       </c>
-      <c r="M36" s="166"/>
-      <c r="N36" s="166"/>
+      <c r="M36" s="165"/>
+      <c r="N36" s="165"/>
     </row>
     <row r="37" spans="1:14" ht="75.75" thickBot="1">
       <c r="A37" s="81">
@@ -24747,17 +25226,17 @@
       <c r="B37" s="70" t="s">
         <v>641</v>
       </c>
-      <c r="C37" s="155" t="s">
+      <c r="C37" s="154" t="s">
         <v>642</v>
       </c>
-      <c r="D37" s="156"/>
+      <c r="D37" s="155"/>
       <c r="E37" s="69" t="s">
         <v>663</v>
       </c>
-      <c r="F37" s="151" t="s">
+      <c r="F37" s="150" t="s">
         <v>664</v>
       </c>
-      <c r="G37" s="152"/>
+      <c r="G37" s="151"/>
       <c r="H37" s="78"/>
       <c r="I37" s="73" t="s">
         <v>685</v>
@@ -24773,17 +25252,17 @@
       <c r="B38" s="69" t="s">
         <v>643</v>
       </c>
-      <c r="C38" s="151" t="s">
+      <c r="C38" s="150" t="s">
         <v>644</v>
       </c>
-      <c r="D38" s="152"/>
+      <c r="D38" s="151"/>
       <c r="E38" s="70" t="s">
         <v>665</v>
       </c>
-      <c r="F38" s="155" t="s">
+      <c r="F38" s="154" t="s">
         <v>666</v>
       </c>
-      <c r="G38" s="156"/>
+      <c r="G38" s="155"/>
       <c r="H38" s="78"/>
       <c r="I38" s="75" t="s">
         <v>687</v>
@@ -24799,22 +25278,22 @@
       <c r="B39" s="70" t="s">
         <v>692</v>
       </c>
-      <c r="C39" s="157" t="s">
+      <c r="C39" s="156" t="s">
         <v>693</v>
       </c>
-      <c r="D39" s="158"/>
+      <c r="D39" s="157"/>
       <c r="E39" s="69" t="s">
         <v>690</v>
       </c>
-      <c r="F39" s="161" t="s">
+      <c r="F39" s="160" t="s">
         <v>691</v>
       </c>
-      <c r="G39" s="162"/>
+      <c r="G39" s="161"/>
       <c r="H39" s="79"/>
-      <c r="I39" s="163" t="s">
+      <c r="I39" s="162" t="s">
         <v>689</v>
       </c>
-      <c r="J39" s="164"/>
+      <c r="J39" s="163"/>
     </row>
     <row r="40" spans="1:14" ht="58.5" customHeight="1"/>
     <row r="41" spans="1:14">

--- a/2020_LogAnalyzer_Leeheesuk.xlsx
+++ b/2020_LogAnalyzer_Leeheesuk.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="22827"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0A825EA-7FF9-44F0-9FFE-78C8C1343DE3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98D4DA65-2946-463C-A7A5-F3F8B06B39E8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" firstSheet="5" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UI" sheetId="7" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2030" uniqueCount="1271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2031" uniqueCount="1273">
   <si>
     <t>구분</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -5675,6 +5675,12 @@
   </si>
   <si>
     <t>Next(Step2 or Step3)</t>
+  </si>
+  <si>
+    <t>Bar, Pie</t>
+  </si>
+  <si>
+    <t>시간축</t>
   </si>
 </sst>
 </file>
@@ -6337,7 +6343,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="209">
+  <cellXfs count="211">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6902,6 +6908,12 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -17318,7 +17330,7 @@
         <v>361</v>
       </c>
       <c r="O21" s="99" t="s">
-        <v>81</v>
+        <v>1271</v>
       </c>
       <c r="P21" s="103">
         <v>1</v>
@@ -17612,6 +17624,9 @@
       </c>
       <c r="O30" t="s">
         <v>1262</v>
+      </c>
+      <c r="P30" t="s">
+        <v>1272</v>
       </c>
     </row>
     <row r="31" spans="1:17">
@@ -18576,7 +18591,7 @@
         <v>1249</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="45">
+    <row r="10" spans="1:11" ht="64.5" customHeight="1">
       <c r="A10" s="196" t="s">
         <v>1229</v>
       </c>
@@ -18755,10 +18770,10 @@
     </row>
     <row r="19" spans="1:10">
       <c r="F19" s="201"/>
-      <c r="G19" s="8" t="s">
+      <c r="G19" s="209" t="s">
         <v>1237</v>
       </c>
-      <c r="H19" s="202" t="s">
+      <c r="H19" s="210" t="s">
         <v>1254</v>
       </c>
     </row>

--- a/2020_LogAnalyzer_Leeheesuk.xlsx
+++ b/2020_LogAnalyzer_Leeheesuk.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="22827"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98D4DA65-2946-463C-A7A5-F3F8B06B39E8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A83CF049-1490-4F7B-8FDA-8A1DDA29758E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" firstSheet="5" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UI" sheetId="7" r:id="rId1"/>
@@ -13,7 +13,7 @@
     <sheet name="UI_Initialization" sheetId="19" r:id="rId3"/>
     <sheet name="UI_Detail" sheetId="17" r:id="rId4"/>
     <sheet name="UI_LogFormat" sheetId="20" r:id="rId5"/>
-    <sheet name="ChartJS" sheetId="18" r:id="rId6"/>
+    <sheet name="Chart" sheetId="18" r:id="rId6"/>
     <sheet name="Table" sheetId="10" r:id="rId7"/>
     <sheet name="Table_0408" sheetId="15" r:id="rId8"/>
     <sheet name="Table_0619_0429" sheetId="16" r:id="rId9"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2031" uniqueCount="1273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2035" uniqueCount="1277">
   <si>
     <t>구분</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -5681,6 +5681,18 @@
   </si>
   <si>
     <t>시간축</t>
+  </si>
+  <si>
+    <t>1. vu-charts zoom plugin 사용</t>
+  </si>
+  <si>
+    <t>2. ApexChart (ApexCharts, Vue-ApexCharts ** MIT)</t>
+  </si>
+  <si>
+    <t>제약사항 : Chart Interaction (Zoom) - 극복방안</t>
+  </si>
+  <si>
+    <t>https://github.com/chartjs/chartjs-plugin-zoom</t>
   </si>
 </sst>
 </file>
@@ -22622,9 +22634,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40AA86BA-F3A4-4754-BF0E-F316D4665692}">
-  <dimension ref="A1:Q28"/>
+  <dimension ref="A1:Q32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
+    <col min="1" max="1" width="114" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -22657,7 +22670,7 @@
       <c r="Q2" s="146"/>
     </row>
     <row r="3" spans="1:17">
-      <c r="A3" t="s">
+      <c r="A3" s="6" t="s">
         <v>862</v>
       </c>
       <c r="J3" s="146"/>
@@ -22890,67 +22903,88 @@
       <c r="P16" s="146"/>
       <c r="Q16" s="146"/>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:2">
       <c r="A17" s="5" t="s">
         <v>940</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:2">
       <c r="A18" t="s">
         <v>941</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:2">
       <c r="A19" t="s">
         <v>942</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:2">
       <c r="A20" t="s">
         <v>943</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:2">
       <c r="A21" t="s">
         <v>944</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:2">
       <c r="A22" t="s">
         <v>945</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:2">
       <c r="A23" s="5" t="s">
         <v>946</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:2">
       <c r="A24" t="s">
         <v>937</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:2">
       <c r="A25" t="s">
         <v>938</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:2">
       <c r="A27" t="s">
         <v>948</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:2">
       <c r="A28" t="s">
         <v>947</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="6" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>1274</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="J1:Q16"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="B31" r:id="rId1" xr:uid="{BC9895F5-A7B3-41BE-B56E-AC43709DD161}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/2020_LogAnalyzer_Leeheesuk.xlsx
+++ b/2020_LogAnalyzer_Leeheesuk.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="22827"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A83CF049-1490-4F7B-8FDA-8A1DDA29758E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35D7A40F-C72C-4B25-A94E-D9A89389301A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15990" firstSheet="5" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UI" sheetId="7" r:id="rId1"/>

--- a/2020_LogAnalyzer_Leeheesuk.xlsx
+++ b/2020_LogAnalyzer_Leeheesuk.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="22827"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35D7A40F-C72C-4B25-A94E-D9A89389301A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEB160B1-85AF-44B1-8D7E-157372E211A5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15990" firstSheet="5" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" firstSheet="8" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UI" sheetId="7" r:id="rId1"/>
@@ -31,7 +31,7 @@
     <sheet name="기능 - goaccess" sheetId="3" r:id="rId21"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="11">기능요건!$A$1:$M$45</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="11">기능요건!$A$1:$M$46</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2035" uniqueCount="1277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2042" uniqueCount="1284">
   <si>
     <t>구분</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -5693,6 +5693,27 @@
   </si>
   <si>
     <t>https://github.com/chartjs/chartjs-plugin-zoom</t>
+  </si>
+  <si>
+    <t>Line Zoom</t>
+  </si>
+  <si>
+    <t>Line 차트에서 Zoom 기능</t>
+  </si>
+  <si>
+    <t>Request Count</t>
+  </si>
+  <si>
+    <t>Visitor</t>
+  </si>
+  <si>
+    <t>IP로 distinct 한 것</t>
+  </si>
+  <si>
+    <t>추가필요?</t>
+  </si>
+  <si>
+    <t>Visits Count  Top5</t>
   </si>
 </sst>
 </file>
@@ -6355,7 +6376,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="211">
+  <cellXfs count="215">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6670,6 +6691,9 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6926,6 +6950,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -9487,8 +9518,8 @@
       <xdr:rowOff>2</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>661147</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>176893</xdr:colOff>
       <xdr:row>15</xdr:row>
       <xdr:rowOff>78443</xdr:rowOff>
     </xdr:to>
@@ -9505,8 +9536,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="291353" y="2342031"/>
-          <a:ext cx="4471147" cy="930088"/>
+          <a:off x="291353" y="2095502"/>
+          <a:ext cx="4117361" cy="840441"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9719,6 +9750,115 @@
             </a:rPr>
             <a:t>)</a:t>
           </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-ea"/>
+              <a:ea typeface="+mn-ea"/>
+            </a:rPr>
+            <a:t>- </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-ea"/>
+              <a:ea typeface="+mn-ea"/>
+            </a:rPr>
+            <a:t>추가</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-ea"/>
+              <a:ea typeface="+mn-ea"/>
+            </a:rPr>
+            <a:t>(07/31) : </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-ea"/>
+              <a:ea typeface="+mn-ea"/>
+            </a:rPr>
+            <a:t>로그 건수</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-ea"/>
+              <a:ea typeface="+mn-ea"/>
+            </a:rPr>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-ea"/>
+              <a:ea typeface="+mn-ea"/>
+            </a:rPr>
+            <a:t>라인 수</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-ea"/>
+              <a:ea typeface="+mn-ea"/>
+            </a:rPr>
+            <a:t>), </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-ea"/>
+              <a:ea typeface="+mn-ea"/>
+            </a:rPr>
+            <a:t>시작 시간</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-ea"/>
+              <a:ea typeface="+mn-ea"/>
+            </a:rPr>
+            <a:t>/</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-ea"/>
+              <a:ea typeface="+mn-ea"/>
+            </a:rPr>
+            <a:t>끝 시간</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="1" baseline="0">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:latin typeface="+mn-ea"/>
+            <a:ea typeface="+mn-ea"/>
+          </a:endParaRPr>
         </a:p>
         <a:p>
           <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
@@ -11359,7 +11499,7 @@
         <a:p>
           <a:pPr algn="l"/>
           <a:r>
-            <a:rPr lang="en-US" sz="1100">
+            <a:rPr lang="en-US" sz="1100" b="1">
               <a:solidFill>
                 <a:srgbClr val="FF0000"/>
               </a:solidFill>
@@ -11367,7 +11507,7 @@
             <a:t>Async</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0">
+            <a:rPr lang="en-US" sz="1100" b="1" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="FF0000"/>
               </a:solidFill>
@@ -11375,7 +11515,7 @@
             <a:t> </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="FF0000"/>
               </a:solidFill>
@@ -11383,7 +11523,7 @@
             <a:t>처리 </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="FF0000"/>
               </a:solidFill>
@@ -11391,7 +11531,7 @@
             <a:t> - </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="FF0000"/>
               </a:solidFill>
@@ -11399,14 +11539,14 @@
             <a:t>분산비동기 처리 고려 </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="FF0000"/>
               </a:solidFill>
             </a:rPr>
             <a:t>(Celery?)</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" sz="1100">
+          <a:endParaRPr lang="en-US" sz="1100" b="1">
             <a:solidFill>
               <a:srgbClr val="FF0000"/>
             </a:solidFill>
@@ -16149,51 +16289,51 @@
     </row>
     <row r="17" spans="1:13">
       <c r="J17" s="19"/>
-      <c r="K17" s="132" t="s">
+      <c r="K17" s="133" t="s">
         <v>537</v>
       </c>
-      <c r="L17" s="133"/>
-      <c r="M17" s="134"/>
+      <c r="L17" s="134"/>
+      <c r="M17" s="135"/>
     </row>
     <row r="18" spans="1:13">
       <c r="J18" s="19">
         <v>1</v>
       </c>
-      <c r="K18" s="135" t="s">
+      <c r="K18" s="136" t="s">
         <v>538</v>
       </c>
-      <c r="L18" s="136"/>
-      <c r="M18" s="137"/>
+      <c r="L18" s="137"/>
+      <c r="M18" s="138"/>
     </row>
     <row r="19" spans="1:13">
       <c r="J19" s="19">
         <v>2</v>
       </c>
-      <c r="K19" s="135" t="s">
+      <c r="K19" s="136" t="s">
         <v>539</v>
       </c>
-      <c r="L19" s="136"/>
-      <c r="M19" s="137"/>
+      <c r="L19" s="137"/>
+      <c r="M19" s="138"/>
     </row>
     <row r="20" spans="1:13">
       <c r="J20" s="19">
         <v>3</v>
       </c>
-      <c r="K20" s="135" t="s">
+      <c r="K20" s="136" t="s">
         <v>540</v>
       </c>
-      <c r="L20" s="136"/>
-      <c r="M20" s="137"/>
+      <c r="L20" s="137"/>
+      <c r="M20" s="138"/>
     </row>
     <row r="21" spans="1:13">
       <c r="J21" s="19">
         <v>4</v>
       </c>
-      <c r="K21" s="135" t="s">
+      <c r="K21" s="136" t="s">
         <v>541</v>
       </c>
-      <c r="L21" s="136"/>
-      <c r="M21" s="137"/>
+      <c r="L21" s="137"/>
+      <c r="M21" s="138"/>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="43" t="s">
@@ -16755,7 +16895,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q45"/>
+  <dimension ref="A1:Q46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.140625" customWidth="1"/>
@@ -16769,7 +16909,7 @@
     <col min="9" max="9" width="10.140625" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" style="56" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.85546875" style="56" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="27.140625" customWidth="1"/>
     <col min="14" max="14" width="26.42578125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="21.42578125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="31.42578125" customWidth="1"/>
@@ -16814,16 +16954,16 @@
       </c>
     </row>
     <row r="2" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A2" s="168" t="s">
+      <c r="A2" s="169" t="s">
         <v>504</v>
       </c>
-      <c r="B2" s="174" t="s">
+      <c r="B2" s="175" t="s">
         <v>506</v>
       </c>
-      <c r="C2" s="168" t="s">
+      <c r="C2" s="169" t="s">
         <v>508</v>
       </c>
-      <c r="D2" s="168" t="s">
+      <c r="D2" s="169" t="s">
         <v>556</v>
       </c>
       <c r="E2" s="8"/>
@@ -16836,7 +16976,7 @@
       <c r="H2" s="10">
         <v>1</v>
       </c>
-      <c r="I2" s="122">
+      <c r="I2" s="123">
         <v>44043</v>
       </c>
       <c r="J2" s="10"/>
@@ -16846,10 +16986,10 @@
       </c>
     </row>
     <row r="3" spans="1:17">
-      <c r="A3" s="142"/>
-      <c r="B3" s="175"/>
-      <c r="C3" s="169"/>
-      <c r="D3" s="169"/>
+      <c r="A3" s="143"/>
+      <c r="B3" s="176"/>
+      <c r="C3" s="170"/>
+      <c r="D3" s="170"/>
       <c r="E3" s="11"/>
       <c r="F3" s="9" t="s">
         <v>310</v>
@@ -16860,7 +17000,7 @@
       <c r="H3" s="12">
         <v>2</v>
       </c>
-      <c r="I3" s="122"/>
+      <c r="I3" s="123"/>
       <c r="J3" s="10"/>
       <c r="K3" s="10"/>
       <c r="M3" s="19" t="s">
@@ -16868,10 +17008,10 @@
       </c>
     </row>
     <row r="4" spans="1:17">
-      <c r="A4" s="142"/>
-      <c r="B4" s="175"/>
-      <c r="C4" s="169"/>
-      <c r="D4" s="170"/>
+      <c r="A4" s="143"/>
+      <c r="B4" s="176"/>
+      <c r="C4" s="170"/>
+      <c r="D4" s="171"/>
       <c r="E4" s="11"/>
       <c r="F4" s="9" t="s">
         <v>311</v>
@@ -16882,14 +17022,14 @@
       <c r="H4" s="12">
         <v>2</v>
       </c>
-      <c r="I4" s="122"/>
+      <c r="I4" s="123"/>
       <c r="J4" s="10"/>
       <c r="K4" s="10"/>
     </row>
     <row r="5" spans="1:17">
-      <c r="A5" s="142"/>
-      <c r="B5" s="175"/>
-      <c r="C5" s="170"/>
+      <c r="A5" s="143"/>
+      <c r="B5" s="176"/>
+      <c r="C5" s="171"/>
       <c r="D5" s="46" t="s">
         <v>555</v>
       </c>
@@ -16903,7 +17043,7 @@
       <c r="H5" s="12" t="s">
         <v>962</v>
       </c>
-      <c r="I5" s="122">
+      <c r="I5" s="123">
         <v>44043</v>
       </c>
       <c r="J5" s="10" t="s">
@@ -16912,12 +17052,12 @@
       <c r="K5" s="10"/>
     </row>
     <row r="6" spans="1:17">
-      <c r="A6" s="142"/>
-      <c r="B6" s="175"/>
-      <c r="C6" s="168" t="s">
+      <c r="A6" s="143"/>
+      <c r="B6" s="176"/>
+      <c r="C6" s="169" t="s">
         <v>507</v>
       </c>
-      <c r="D6" s="168" t="s">
+      <c r="D6" s="169" t="s">
         <v>511</v>
       </c>
       <c r="E6" s="11"/>
@@ -16930,17 +17070,17 @@
       <c r="H6" s="12" t="s">
         <v>963</v>
       </c>
-      <c r="I6" s="122">
+      <c r="I6" s="123">
         <v>44043</v>
       </c>
       <c r="J6" s="10"/>
       <c r="K6" s="10"/>
     </row>
     <row r="7" spans="1:17">
-      <c r="A7" s="142"/>
-      <c r="B7" s="175"/>
-      <c r="C7" s="169"/>
-      <c r="D7" s="169"/>
+      <c r="A7" s="143"/>
+      <c r="B7" s="176"/>
+      <c r="C7" s="170"/>
+      <c r="D7" s="170"/>
       <c r="E7" s="11"/>
       <c r="F7" s="9" t="s">
         <v>313</v>
@@ -16951,17 +17091,17 @@
       <c r="H7" s="12">
         <v>1</v>
       </c>
-      <c r="I7" s="122">
+      <c r="I7" s="123">
         <v>44043</v>
       </c>
       <c r="J7" s="10"/>
       <c r="K7" s="10"/>
     </row>
     <row r="8" spans="1:17">
-      <c r="A8" s="142"/>
-      <c r="B8" s="175"/>
-      <c r="C8" s="169"/>
-      <c r="D8" s="169"/>
+      <c r="A8" s="143"/>
+      <c r="B8" s="176"/>
+      <c r="C8" s="170"/>
+      <c r="D8" s="170"/>
       <c r="E8" s="11"/>
       <c r="F8" s="9" t="s">
         <v>314</v>
@@ -16972,17 +17112,17 @@
       <c r="H8" s="12">
         <v>1</v>
       </c>
-      <c r="I8" s="122">
+      <c r="I8" s="123">
         <v>44043</v>
       </c>
       <c r="J8" s="10"/>
       <c r="K8" s="10"/>
     </row>
     <row r="9" spans="1:17">
-      <c r="A9" s="142"/>
-      <c r="B9" s="175"/>
-      <c r="C9" s="169"/>
-      <c r="D9" s="169"/>
+      <c r="A9" s="143"/>
+      <c r="B9" s="176"/>
+      <c r="C9" s="170"/>
+      <c r="D9" s="170"/>
       <c r="E9" s="8"/>
       <c r="F9" s="9" t="s">
         <v>345</v>
@@ -16993,17 +17133,17 @@
       <c r="H9" s="10">
         <v>1</v>
       </c>
-      <c r="I9" s="122">
+      <c r="I9" s="123">
         <v>44043</v>
       </c>
       <c r="J9" s="10"/>
       <c r="K9" s="10"/>
     </row>
     <row r="10" spans="1:17">
-      <c r="A10" s="142"/>
-      <c r="B10" s="175"/>
-      <c r="C10" s="169"/>
-      <c r="D10" s="169"/>
+      <c r="A10" s="143"/>
+      <c r="B10" s="176"/>
+      <c r="C10" s="170"/>
+      <c r="D10" s="170"/>
       <c r="E10" s="8"/>
       <c r="F10" s="9" t="s">
         <v>346</v>
@@ -17014,17 +17154,17 @@
       <c r="H10" s="10">
         <v>1</v>
       </c>
-      <c r="I10" s="122">
+      <c r="I10" s="123">
         <v>44043</v>
       </c>
       <c r="J10" s="10"/>
       <c r="K10" s="10"/>
     </row>
     <row r="11" spans="1:17">
-      <c r="A11" s="142"/>
-      <c r="B11" s="175"/>
-      <c r="C11" s="169"/>
-      <c r="D11" s="169"/>
+      <c r="A11" s="143"/>
+      <c r="B11" s="176"/>
+      <c r="C11" s="170"/>
+      <c r="D11" s="170"/>
       <c r="E11" s="8"/>
       <c r="F11" s="9" t="s">
         <v>315</v>
@@ -17035,17 +17175,17 @@
       <c r="H11" s="10">
         <v>1</v>
       </c>
-      <c r="I11" s="122">
+      <c r="I11" s="123">
         <v>44043</v>
       </c>
       <c r="J11" s="10"/>
       <c r="K11" s="10"/>
     </row>
     <row r="12" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A12" s="142"/>
-      <c r="B12" s="175"/>
-      <c r="C12" s="169"/>
-      <c r="D12" s="169"/>
+      <c r="A12" s="143"/>
+      <c r="B12" s="176"/>
+      <c r="C12" s="170"/>
+      <c r="D12" s="170"/>
       <c r="E12" s="8"/>
       <c r="F12" s="9" t="s">
         <v>347</v>
@@ -17056,17 +17196,17 @@
       <c r="H12" s="10">
         <v>1</v>
       </c>
-      <c r="I12" s="122">
+      <c r="I12" s="123">
         <v>44043</v>
       </c>
       <c r="J12" s="10"/>
       <c r="K12" s="10"/>
     </row>
     <row r="13" spans="1:17" ht="30">
-      <c r="A13" s="142"/>
-      <c r="B13" s="175"/>
-      <c r="C13" s="169"/>
-      <c r="D13" s="169"/>
+      <c r="A13" s="143"/>
+      <c r="B13" s="176"/>
+      <c r="C13" s="170"/>
+      <c r="D13" s="170"/>
       <c r="E13" s="11"/>
       <c r="F13" s="9" t="s">
         <v>316</v>
@@ -17077,7 +17217,7 @@
       <c r="H13" s="12">
         <v>3</v>
       </c>
-      <c r="I13" s="122"/>
+      <c r="I13" s="123"/>
       <c r="J13" s="10" t="s">
         <v>563</v>
       </c>
@@ -17087,10 +17227,10 @@
       </c>
     </row>
     <row r="14" spans="1:17">
-      <c r="A14" s="142"/>
-      <c r="B14" s="175"/>
-      <c r="C14" s="169"/>
-      <c r="D14" s="170"/>
+      <c r="A14" s="143"/>
+      <c r="B14" s="176"/>
+      <c r="C14" s="170"/>
+      <c r="D14" s="171"/>
       <c r="E14" s="11"/>
       <c r="F14" s="9" t="s">
         <v>318</v>
@@ -17101,14 +17241,14 @@
       <c r="H14" s="12">
         <v>2</v>
       </c>
-      <c r="I14" s="122"/>
+      <c r="I14" s="123"/>
       <c r="J14" s="10"/>
       <c r="K14" s="10"/>
     </row>
     <row r="15" spans="1:17" ht="30">
-      <c r="A15" s="142"/>
-      <c r="B15" s="175"/>
-      <c r="C15" s="169"/>
+      <c r="A15" s="143"/>
+      <c r="B15" s="176"/>
+      <c r="C15" s="170"/>
       <c r="D15" s="22" t="s">
         <v>512</v>
       </c>
@@ -17122,15 +17262,15 @@
       <c r="H15" s="12">
         <v>1</v>
       </c>
-      <c r="I15" s="122">
+      <c r="I15" s="123">
         <v>44043</v>
       </c>
       <c r="J15" s="10"/>
       <c r="K15" s="10"/>
-      <c r="M15" s="203" t="s">
+      <c r="M15" s="204" t="s">
         <v>852</v>
       </c>
-      <c r="N15" s="204"/>
+      <c r="N15" s="205"/>
       <c r="O15" s="118" t="s">
         <v>1260</v>
       </c>
@@ -17140,12 +17280,12 @@
       </c>
     </row>
     <row r="16" spans="1:17" ht="30">
-      <c r="A16" s="142"/>
-      <c r="B16" s="175"/>
-      <c r="C16" s="168" t="s">
+      <c r="A16" s="143"/>
+      <c r="B16" s="176"/>
+      <c r="C16" s="169" t="s">
         <v>509</v>
       </c>
-      <c r="D16" s="168" t="s">
+      <c r="D16" s="169" t="s">
         <v>513</v>
       </c>
       <c r="E16" s="11"/>
@@ -17158,7 +17298,7 @@
       <c r="H16" s="12">
         <v>1</v>
       </c>
-      <c r="I16" s="122">
+      <c r="I16" s="123">
         <v>44043</v>
       </c>
       <c r="J16" s="10"/>
@@ -17180,10 +17320,10 @@
       </c>
     </row>
     <row r="17" spans="1:17">
-      <c r="A17" s="142"/>
-      <c r="B17" s="175"/>
-      <c r="C17" s="169"/>
-      <c r="D17" s="169"/>
+      <c r="A17" s="143"/>
+      <c r="B17" s="176"/>
+      <c r="C17" s="170"/>
+      <c r="D17" s="170"/>
       <c r="E17" s="19"/>
       <c r="F17" s="9" t="s">
         <v>364</v>
@@ -17194,7 +17334,7 @@
       <c r="H17" s="12">
         <v>1</v>
       </c>
-      <c r="I17" s="122">
+      <c r="I17" s="123">
         <v>44043</v>
       </c>
       <c r="J17" s="10"/>
@@ -17213,10 +17353,10 @@
       </c>
     </row>
     <row r="18" spans="1:17">
-      <c r="A18" s="142"/>
-      <c r="B18" s="175"/>
-      <c r="C18" s="169"/>
-      <c r="D18" s="169"/>
+      <c r="A18" s="143"/>
+      <c r="B18" s="176"/>
+      <c r="C18" s="170"/>
+      <c r="D18" s="170"/>
       <c r="E18" s="19"/>
       <c r="F18" s="48" t="s">
         <v>559</v>
@@ -17227,7 +17367,7 @@
       <c r="H18" s="10">
         <v>1</v>
       </c>
-      <c r="I18" s="122">
+      <c r="I18" s="123">
         <v>44043</v>
       </c>
       <c r="J18" s="10" t="s">
@@ -17248,10 +17388,10 @@
       </c>
     </row>
     <row r="19" spans="1:17">
-      <c r="A19" s="142"/>
-      <c r="B19" s="175"/>
-      <c r="C19" s="169"/>
-      <c r="D19" s="169"/>
+      <c r="A19" s="143"/>
+      <c r="B19" s="176"/>
+      <c r="C19" s="170"/>
+      <c r="D19" s="170"/>
       <c r="E19" s="8"/>
       <c r="F19" s="9" t="s">
         <v>332</v>
@@ -17262,7 +17402,7 @@
       <c r="H19" s="10">
         <v>1</v>
       </c>
-      <c r="I19" s="122">
+      <c r="I19" s="123">
         <v>44043</v>
       </c>
       <c r="J19" s="10"/>
@@ -17282,10 +17422,10 @@
       <c r="Q19" s="91"/>
     </row>
     <row r="20" spans="1:17">
-      <c r="A20" s="142"/>
-      <c r="B20" s="175"/>
-      <c r="C20" s="169"/>
-      <c r="D20" s="169"/>
+      <c r="A20" s="143"/>
+      <c r="B20" s="176"/>
+      <c r="C20" s="170"/>
+      <c r="D20" s="170"/>
       <c r="E20" s="8"/>
       <c r="F20" s="9" t="s">
         <v>333</v>
@@ -17296,7 +17436,7 @@
       <c r="H20" s="10">
         <v>1</v>
       </c>
-      <c r="I20" s="122">
+      <c r="I20" s="123">
         <v>44043</v>
       </c>
       <c r="J20" s="10"/>
@@ -17316,10 +17456,10 @@
       <c r="Q20" s="91"/>
     </row>
     <row r="21" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A21" s="142"/>
-      <c r="B21" s="175"/>
-      <c r="C21" s="169"/>
-      <c r="D21" s="169"/>
+      <c r="A21" s="143"/>
+      <c r="B21" s="176"/>
+      <c r="C21" s="170"/>
+      <c r="D21" s="170"/>
       <c r="E21" s="14"/>
       <c r="F21" s="9" t="s">
         <v>334</v>
@@ -17330,7 +17470,7 @@
       <c r="H21" s="16">
         <v>3</v>
       </c>
-      <c r="I21" s="122"/>
+      <c r="I21" s="123"/>
       <c r="J21" s="10" t="s">
         <v>563</v>
       </c>
@@ -17352,10 +17492,10 @@
       </c>
     </row>
     <row r="22" spans="1:17">
-      <c r="A22" s="142"/>
-      <c r="B22" s="175"/>
-      <c r="C22" s="169"/>
-      <c r="D22" s="169"/>
+      <c r="A22" s="143"/>
+      <c r="B22" s="176"/>
+      <c r="C22" s="170"/>
+      <c r="D22" s="170"/>
       <c r="E22" s="14"/>
       <c r="F22" s="9" t="s">
         <v>335</v>
@@ -17366,7 +17506,7 @@
       <c r="H22" s="16">
         <v>1</v>
       </c>
-      <c r="I22" s="122">
+      <c r="I22" s="123">
         <v>44043</v>
       </c>
       <c r="J22" s="10"/>
@@ -17388,10 +17528,10 @@
       </c>
     </row>
     <row r="23" spans="1:17">
-      <c r="A23" s="142"/>
-      <c r="B23" s="175"/>
-      <c r="C23" s="169"/>
-      <c r="D23" s="169"/>
+      <c r="A23" s="143"/>
+      <c r="B23" s="176"/>
+      <c r="C23" s="170"/>
+      <c r="D23" s="170"/>
       <c r="E23" s="14"/>
       <c r="F23" s="9" t="s">
         <v>336</v>
@@ -17402,7 +17542,7 @@
       <c r="H23" s="16" t="s">
         <v>963</v>
       </c>
-      <c r="I23" s="122">
+      <c r="I23" s="123">
         <v>44043</v>
       </c>
       <c r="J23" s="10"/>
@@ -17422,10 +17562,10 @@
       <c r="Q23" s="91"/>
     </row>
     <row r="24" spans="1:17">
-      <c r="A24" s="142"/>
-      <c r="B24" s="175"/>
-      <c r="C24" s="169"/>
-      <c r="D24" s="169"/>
+      <c r="A24" s="143"/>
+      <c r="B24" s="176"/>
+      <c r="C24" s="170"/>
+      <c r="D24" s="170"/>
       <c r="E24" s="8"/>
       <c r="F24" s="9" t="s">
         <v>337</v>
@@ -17436,13 +17576,13 @@
       <c r="H24" s="10" t="s">
         <v>963</v>
       </c>
-      <c r="I24" s="122">
+      <c r="I24" s="123">
         <v>44043</v>
       </c>
       <c r="J24" s="10"/>
       <c r="K24" s="10"/>
-      <c r="M24" s="125" t="s">
-        <v>967</v>
+      <c r="M24" s="214" t="s">
+        <v>1283</v>
       </c>
       <c r="N24" s="98" t="s">
         <v>371</v>
@@ -17450,16 +17590,16 @@
       <c r="O24" s="99" t="s">
         <v>81</v>
       </c>
-      <c r="P24" s="100">
+      <c r="P24" s="105">
         <v>1</v>
       </c>
       <c r="Q24" s="91"/>
     </row>
     <row r="25" spans="1:17">
-      <c r="A25" s="142"/>
-      <c r="B25" s="175"/>
-      <c r="C25" s="169"/>
-      <c r="D25" s="169"/>
+      <c r="A25" s="143"/>
+      <c r="B25" s="176"/>
+      <c r="C25" s="170"/>
+      <c r="D25" s="170"/>
       <c r="E25" s="8"/>
       <c r="F25" s="9" t="s">
         <v>373</v>
@@ -17470,7 +17610,7 @@
       <c r="H25" s="10">
         <v>3</v>
       </c>
-      <c r="I25" s="122"/>
+      <c r="I25" s="123"/>
       <c r="J25" s="10" t="s">
         <v>563</v>
       </c>
@@ -17490,10 +17630,10 @@
       <c r="Q25" s="91"/>
     </row>
     <row r="26" spans="1:17">
-      <c r="A26" s="142"/>
-      <c r="B26" s="175"/>
-      <c r="C26" s="169"/>
-      <c r="D26" s="169"/>
+      <c r="A26" s="143"/>
+      <c r="B26" s="176"/>
+      <c r="C26" s="170"/>
+      <c r="D26" s="170"/>
       <c r="E26" s="8"/>
       <c r="F26" s="9" t="s">
         <v>338</v>
@@ -17504,7 +17644,7 @@
       <c r="H26" s="10">
         <v>2</v>
       </c>
-      <c r="I26" s="122"/>
+      <c r="I26" s="123"/>
       <c r="J26" s="10"/>
       <c r="K26" s="10"/>
       <c r="M26" s="99" t="s">
@@ -17522,10 +17662,10 @@
       <c r="Q26" s="91"/>
     </row>
     <row r="27" spans="1:17">
-      <c r="A27" s="142"/>
-      <c r="B27" s="175"/>
-      <c r="C27" s="169"/>
-      <c r="D27" s="169"/>
+      <c r="A27" s="143"/>
+      <c r="B27" s="176"/>
+      <c r="C27" s="170"/>
+      <c r="D27" s="170"/>
       <c r="E27" s="8"/>
       <c r="F27" s="9" t="s">
         <v>339</v>
@@ -17533,10 +17673,10 @@
       <c r="G27" s="13" t="s">
         <v>372</v>
       </c>
-      <c r="H27" s="123" t="s">
+      <c r="H27" s="124" t="s">
         <v>964</v>
       </c>
-      <c r="I27" s="122"/>
+      <c r="I27" s="123"/>
       <c r="J27" s="10"/>
       <c r="K27" s="10"/>
       <c r="M27" s="99" t="s">
@@ -17554,12 +17694,12 @@
       <c r="Q27" s="91"/>
     </row>
     <row r="28" spans="1:17">
-      <c r="A28" s="142"/>
-      <c r="B28" s="175"/>
-      <c r="C28" s="169"/>
-      <c r="D28" s="169"/>
+      <c r="A28" s="143"/>
+      <c r="B28" s="176"/>
+      <c r="C28" s="170"/>
+      <c r="D28" s="170"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="125" t="s">
+      <c r="F28" s="126" t="s">
         <v>967</v>
       </c>
       <c r="G28" s="13" t="s">
@@ -17568,7 +17708,7 @@
       <c r="H28" s="10">
         <v>1</v>
       </c>
-      <c r="I28" s="122">
+      <c r="I28" s="123">
         <v>44043</v>
       </c>
       <c r="J28" s="10"/>
@@ -17588,10 +17728,10 @@
       <c r="Q28" s="91"/>
     </row>
     <row r="29" spans="1:17">
-      <c r="A29" s="142"/>
-      <c r="B29" s="175"/>
-      <c r="C29" s="169"/>
-      <c r="D29" s="169"/>
+      <c r="A29" s="143"/>
+      <c r="B29" s="176"/>
+      <c r="C29" s="170"/>
+      <c r="D29" s="170"/>
       <c r="E29" s="8"/>
       <c r="F29" s="9" t="s">
         <v>957</v>
@@ -17602,17 +17742,17 @@
       <c r="H29" s="16">
         <v>2</v>
       </c>
-      <c r="I29" s="122"/>
+      <c r="I29" s="123"/>
       <c r="J29" s="10"/>
       <c r="K29" s="10" t="s">
         <v>956</v>
       </c>
     </row>
     <row r="30" spans="1:17">
-      <c r="A30" s="142"/>
-      <c r="B30" s="175"/>
-      <c r="C30" s="169"/>
-      <c r="D30" s="170"/>
+      <c r="A30" s="143"/>
+      <c r="B30" s="176"/>
+      <c r="C30" s="170"/>
+      <c r="D30" s="171"/>
       <c r="E30" s="8"/>
       <c r="F30" s="49" t="s">
         <v>323</v>
@@ -17623,9 +17763,9 @@
       <c r="H30" s="114">
         <v>3</v>
       </c>
-      <c r="I30" s="122"/>
+      <c r="I30" s="123"/>
       <c r="J30" s="10"/>
-      <c r="K30" s="171" t="s">
+      <c r="K30" s="172" t="s">
         <v>961</v>
       </c>
       <c r="M30" s="102" t="s">
@@ -17642,10 +17782,10 @@
       </c>
     </row>
     <row r="31" spans="1:17">
-      <c r="A31" s="142"/>
-      <c r="B31" s="175"/>
-      <c r="C31" s="169"/>
-      <c r="D31" s="168" t="s">
+      <c r="A31" s="143"/>
+      <c r="B31" s="176"/>
+      <c r="C31" s="170"/>
+      <c r="D31" s="169" t="s">
         <v>518</v>
       </c>
       <c r="E31" s="8"/>
@@ -17658,17 +17798,17 @@
       <c r="H31" s="16">
         <v>1</v>
       </c>
-      <c r="I31" s="122">
+      <c r="I31" s="123">
         <v>44043</v>
       </c>
       <c r="J31" s="10"/>
-      <c r="K31" s="172"/>
+      <c r="K31" s="173"/>
     </row>
     <row r="32" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A32" s="142"/>
-      <c r="B32" s="175"/>
-      <c r="C32" s="169"/>
-      <c r="D32" s="169"/>
+      <c r="A32" s="143"/>
+      <c r="B32" s="176"/>
+      <c r="C32" s="170"/>
+      <c r="D32" s="170"/>
       <c r="E32" s="8"/>
       <c r="F32" s="9" t="s">
         <v>325</v>
@@ -17679,17 +17819,20 @@
       <c r="H32" s="16">
         <v>1</v>
       </c>
-      <c r="I32" s="122">
+      <c r="I32" s="123">
         <v>44043</v>
       </c>
       <c r="J32" s="10"/>
-      <c r="K32" s="172"/>
-    </row>
-    <row r="33" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A33" s="142"/>
-      <c r="B33" s="175"/>
-      <c r="C33" s="169"/>
-      <c r="D33" s="169"/>
+      <c r="K32" s="173"/>
+      <c r="M32" s="212" t="s">
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" ht="16.5" customHeight="1">
+      <c r="A33" s="143"/>
+      <c r="B33" s="176"/>
+      <c r="C33" s="170"/>
+      <c r="D33" s="170"/>
       <c r="E33" s="8"/>
       <c r="F33" s="9" t="s">
         <v>959</v>
@@ -17700,275 +17843,305 @@
       <c r="H33" s="16">
         <v>2</v>
       </c>
-      <c r="I33" s="122">
+      <c r="I33" s="123">
         <v>44043</v>
       </c>
       <c r="J33" s="10" t="s">
         <v>956</v>
       </c>
-      <c r="K33" s="173"/>
-    </row>
-    <row r="34" spans="1:11">
-      <c r="A34" s="142"/>
-      <c r="B34" s="175"/>
+      <c r="K33" s="174"/>
+      <c r="M33" s="213" t="s">
+        <v>1280</v>
+      </c>
+      <c r="N33" s="5" t="s">
+        <v>1281</v>
+      </c>
+      <c r="O33" t="s">
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" ht="16.5" customHeight="1">
+      <c r="A34" s="143"/>
+      <c r="B34" s="176"/>
       <c r="C34" s="170"/>
       <c r="D34" s="170"/>
       <c r="E34" s="8"/>
-      <c r="F34" s="49" t="s">
+      <c r="F34" s="9" t="s">
+        <v>1277</v>
+      </c>
+      <c r="G34" s="9" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H34" s="122">
+        <v>2</v>
+      </c>
+      <c r="I34" s="123"/>
+      <c r="J34" s="10"/>
+      <c r="K34" s="10" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15">
+      <c r="A35" s="143"/>
+      <c r="B35" s="176"/>
+      <c r="C35" s="171"/>
+      <c r="D35" s="171"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="49" t="s">
         <v>322</v>
       </c>
-      <c r="G34" s="49" t="s">
+      <c r="G35" s="49" t="s">
         <v>321</v>
       </c>
-      <c r="H34" s="50">
+      <c r="H35" s="50">
         <v>3</v>
       </c>
-      <c r="I34" s="122"/>
-      <c r="J34" s="10"/>
-      <c r="K34" s="10"/>
-    </row>
-    <row r="35" spans="1:11">
-      <c r="A35" s="142"/>
-      <c r="B35" s="175"/>
-      <c r="C35" s="168" t="s">
-        <v>340</v>
-      </c>
-      <c r="D35" s="168" t="s">
-        <v>517</v>
-      </c>
-      <c r="E35" s="8"/>
-      <c r="F35" s="9" t="s">
-        <v>308</v>
-      </c>
-      <c r="G35" s="9" t="s">
-        <v>377</v>
-      </c>
-      <c r="H35" s="16">
-        <v>1</v>
-      </c>
-      <c r="I35" s="122">
-        <v>44043</v>
-      </c>
+      <c r="I35" s="123"/>
       <c r="J35" s="10"/>
       <c r="K35" s="10"/>
     </row>
-    <row r="36" spans="1:11">
-      <c r="A36" s="142"/>
+    <row r="36" spans="1:15">
+      <c r="A36" s="143"/>
       <c r="B36" s="176"/>
-      <c r="C36" s="170"/>
-      <c r="D36" s="170"/>
+      <c r="C36" s="169" t="s">
+        <v>340</v>
+      </c>
+      <c r="D36" s="169" t="s">
+        <v>517</v>
+      </c>
       <c r="E36" s="8"/>
       <c r="F36" s="9" t="s">
-        <v>331</v>
+        <v>308</v>
       </c>
       <c r="G36" s="9" t="s">
-        <v>376</v>
-      </c>
-      <c r="H36" s="124" t="s">
-        <v>965</v>
-      </c>
-      <c r="I36" s="122"/>
+        <v>377</v>
+      </c>
+      <c r="H36" s="16">
+        <v>1</v>
+      </c>
+      <c r="I36" s="123">
+        <v>44043</v>
+      </c>
       <c r="J36" s="10"/>
       <c r="K36" s="10"/>
     </row>
-    <row r="37" spans="1:11">
-      <c r="A37" s="142"/>
-      <c r="B37" s="29" t="s">
-        <v>328</v>
-      </c>
-      <c r="C37" s="27" t="s">
-        <v>330</v>
-      </c>
-      <c r="D37" s="27" t="s">
-        <v>330</v>
-      </c>
-      <c r="E37" s="28"/>
-      <c r="F37" s="27" t="s">
-        <v>330</v>
-      </c>
-      <c r="G37" s="10" t="s">
-        <v>329</v>
-      </c>
-      <c r="H37" s="16" t="s">
-        <v>330</v>
-      </c>
-      <c r="I37" s="122"/>
+    <row r="37" spans="1:15">
+      <c r="A37" s="143"/>
+      <c r="B37" s="177"/>
+      <c r="C37" s="171"/>
+      <c r="D37" s="171"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="G37" s="9" t="s">
+        <v>376</v>
+      </c>
+      <c r="H37" s="125" t="s">
+        <v>965</v>
+      </c>
+      <c r="I37" s="123"/>
       <c r="J37" s="10"/>
       <c r="K37" s="10"/>
     </row>
-    <row r="38" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A38" s="142"/>
-      <c r="B38" s="174" t="s">
-        <v>505</v>
-      </c>
-      <c r="C38" s="168" t="s">
-        <v>510</v>
-      </c>
-      <c r="D38" s="168" t="s">
-        <v>516</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>295</v>
-      </c>
-      <c r="F38" s="9" t="s">
-        <v>296</v>
-      </c>
-      <c r="G38" s="9" t="s">
-        <v>303</v>
-      </c>
-      <c r="H38" s="10">
-        <v>2</v>
-      </c>
-      <c r="I38" s="122"/>
+    <row r="38" spans="1:15">
+      <c r="A38" s="143"/>
+      <c r="B38" s="29" t="s">
+        <v>328</v>
+      </c>
+      <c r="C38" s="27" t="s">
+        <v>330</v>
+      </c>
+      <c r="D38" s="27" t="s">
+        <v>330</v>
+      </c>
+      <c r="E38" s="28"/>
+      <c r="F38" s="27" t="s">
+        <v>330</v>
+      </c>
+      <c r="G38" s="10" t="s">
+        <v>329</v>
+      </c>
+      <c r="H38" s="16" t="s">
+        <v>330</v>
+      </c>
+      <c r="I38" s="123"/>
       <c r="J38" s="10"/>
       <c r="K38" s="10"/>
     </row>
-    <row r="39" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A39" s="142"/>
-      <c r="B39" s="175"/>
-      <c r="C39" s="142"/>
-      <c r="D39" s="142"/>
-      <c r="E39" s="17"/>
+    <row r="39" spans="1:15" ht="16.5" customHeight="1">
+      <c r="A39" s="143"/>
+      <c r="B39" s="175" t="s">
+        <v>505</v>
+      </c>
+      <c r="C39" s="169" t="s">
+        <v>510</v>
+      </c>
+      <c r="D39" s="169" t="s">
+        <v>516</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>295</v>
+      </c>
       <c r="F39" s="9" t="s">
-        <v>304</v>
-      </c>
-      <c r="G39" s="15" t="s">
-        <v>306</v>
-      </c>
-      <c r="H39" s="16">
-        <v>1</v>
-      </c>
-      <c r="I39" s="122">
-        <v>44043</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="G39" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="H39" s="10">
+        <v>2</v>
+      </c>
+      <c r="I39" s="123"/>
       <c r="J39" s="10"/>
       <c r="K39" s="10"/>
     </row>
-    <row r="40" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A40" s="142"/>
-      <c r="B40" s="175"/>
-      <c r="C40" s="142"/>
-      <c r="D40" s="142"/>
+    <row r="40" spans="1:15" ht="16.5" customHeight="1">
+      <c r="A40" s="143"/>
+      <c r="B40" s="176"/>
+      <c r="C40" s="143"/>
+      <c r="D40" s="143"/>
       <c r="E40" s="17"/>
       <c r="F40" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G40" s="15" t="s">
-        <v>319</v>
+        <v>306</v>
       </c>
       <c r="H40" s="16">
         <v>1</v>
       </c>
-      <c r="I40" s="122">
+      <c r="I40" s="123">
         <v>44043</v>
       </c>
       <c r="J40" s="10"/>
       <c r="K40" s="10"/>
     </row>
-    <row r="41" spans="1:11">
-      <c r="A41" s="142"/>
-      <c r="B41" s="175"/>
-      <c r="C41" s="142"/>
+    <row r="41" spans="1:15" ht="16.5" customHeight="1">
+      <c r="A41" s="143"/>
+      <c r="B41" s="176"/>
+      <c r="C41" s="143"/>
       <c r="D41" s="143"/>
       <c r="E41" s="17"/>
       <c r="F41" s="9" t="s">
         <v>305</v>
       </c>
       <c r="G41" s="15" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H41" s="16">
-        <v>2</v>
-      </c>
-      <c r="I41" s="122"/>
+        <v>1</v>
+      </c>
+      <c r="I41" s="123">
+        <v>44043</v>
+      </c>
       <c r="J41" s="10"/>
       <c r="K41" s="10"/>
     </row>
-    <row r="42" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A42" s="142"/>
-      <c r="B42" s="175"/>
-      <c r="C42" s="142"/>
-      <c r="D42" s="168" t="s">
+    <row r="42" spans="1:15">
+      <c r="A42" s="143"/>
+      <c r="B42" s="176"/>
+      <c r="C42" s="143"/>
+      <c r="D42" s="144"/>
+      <c r="E42" s="17"/>
+      <c r="F42" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="G42" s="15" t="s">
+        <v>320</v>
+      </c>
+      <c r="H42" s="16">
+        <v>2</v>
+      </c>
+      <c r="I42" s="123"/>
+      <c r="J42" s="10"/>
+      <c r="K42" s="10"/>
+    </row>
+    <row r="43" spans="1:15" ht="16.5" customHeight="1">
+      <c r="A43" s="143"/>
+      <c r="B43" s="176"/>
+      <c r="C43" s="143"/>
+      <c r="D43" s="169" t="s">
         <v>515</v>
       </c>
-      <c r="E42" s="8"/>
-      <c r="F42" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="G42" s="9" t="s">
-        <v>298</v>
-      </c>
-      <c r="H42" s="10" t="s">
-        <v>963</v>
-      </c>
-      <c r="I42" s="122">
-        <v>44043</v>
-      </c>
-      <c r="J42" s="10"/>
-      <c r="K42" s="171" t="s">
-        <v>1166</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11">
-      <c r="A43" s="142"/>
-      <c r="B43" s="175"/>
-      <c r="C43" s="142"/>
-      <c r="D43" s="143"/>
       <c r="E43" s="8"/>
       <c r="F43" s="9" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H43" s="10" t="s">
         <v>963</v>
       </c>
-      <c r="I43" s="122">
+      <c r="I43" s="123">
         <v>44043</v>
       </c>
       <c r="J43" s="10"/>
-      <c r="K43" s="181"/>
-    </row>
-    <row r="44" spans="1:11">
-      <c r="A44" s="142"/>
-      <c r="B44" s="175"/>
-      <c r="C44" s="142"/>
-      <c r="D44" s="168" t="s">
-        <v>514</v>
-      </c>
+      <c r="K43" s="172" t="s">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15">
+      <c r="A44" s="143"/>
+      <c r="B44" s="176"/>
+      <c r="C44" s="143"/>
+      <c r="D44" s="144"/>
       <c r="E44" s="8"/>
       <c r="F44" s="9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>300</v>
-      </c>
-      <c r="H44" s="10">
-        <v>2</v>
-      </c>
-      <c r="I44" s="122"/>
+        <v>299</v>
+      </c>
+      <c r="H44" s="10" t="s">
+        <v>963</v>
+      </c>
+      <c r="I44" s="123">
+        <v>44043</v>
+      </c>
       <c r="J44" s="10"/>
-      <c r="K44" s="10"/>
-    </row>
-    <row r="45" spans="1:11">
+      <c r="K44" s="182"/>
+    </row>
+    <row r="45" spans="1:15">
       <c r="A45" s="143"/>
       <c r="B45" s="176"/>
       <c r="C45" s="143"/>
-      <c r="D45" s="143"/>
+      <c r="D45" s="169" t="s">
+        <v>514</v>
+      </c>
       <c r="E45" s="8"/>
       <c r="F45" s="9" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="H45" s="10">
         <v>2</v>
       </c>
-      <c r="I45" s="122"/>
+      <c r="I45" s="123"/>
       <c r="J45" s="10"/>
       <c r="K45" s="10"/>
+    </row>
+    <row r="46" spans="1:15">
+      <c r="A46" s="144"/>
+      <c r="B46" s="177"/>
+      <c r="C46" s="144"/>
+      <c r="D46" s="144"/>
+      <c r="E46" s="8"/>
+      <c r="F46" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="G46" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="H46" s="10">
+        <v>2</v>
+      </c>
+      <c r="I46" s="123"/>
+      <c r="J46" s="10"/>
+      <c r="K46" s="10"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="M16:P28">
@@ -17976,23 +18149,23 @@
   </sortState>
   <mergeCells count="19">
     <mergeCell ref="D6:D14"/>
-    <mergeCell ref="K42:K43"/>
+    <mergeCell ref="K43:K44"/>
     <mergeCell ref="M15:N15"/>
     <mergeCell ref="D16:D30"/>
     <mergeCell ref="K30:K33"/>
     <mergeCell ref="C2:C5"/>
     <mergeCell ref="C6:C15"/>
-    <mergeCell ref="A2:A45"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="B38:B45"/>
-    <mergeCell ref="C38:C45"/>
-    <mergeCell ref="D38:D41"/>
-    <mergeCell ref="B2:B36"/>
-    <mergeCell ref="C16:C34"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="D31:D34"/>
-    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="A2:A46"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="B39:B46"/>
+    <mergeCell ref="C39:C46"/>
+    <mergeCell ref="D39:D42"/>
+    <mergeCell ref="B2:B37"/>
+    <mergeCell ref="C16:C35"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="D31:D35"/>
+    <mergeCell ref="D36:D37"/>
     <mergeCell ref="D2:D4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -18032,11 +18205,11 @@
       <c r="B1" s="25" t="s">
         <v>327</v>
       </c>
-      <c r="E1" s="179" t="s">
+      <c r="E1" s="180" t="s">
         <v>724</v>
       </c>
-      <c r="F1" s="179"/>
-      <c r="G1" s="179"/>
+      <c r="F1" s="180"/>
+      <c r="G1" s="180"/>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="19" t="s">
@@ -18045,11 +18218,11 @@
       <c r="B2" s="19" t="s">
         <v>257</v>
       </c>
-      <c r="E2" s="180" t="s">
+      <c r="E2" s="181" t="s">
         <v>725</v>
       </c>
-      <c r="F2" s="180"/>
-      <c r="G2" s="180"/>
+      <c r="F2" s="181"/>
+      <c r="G2" s="181"/>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="19" t="s">
@@ -18066,10 +18239,10 @@
       <c r="B4" s="19" t="s">
         <v>259</v>
       </c>
-      <c r="E4" s="179" t="s">
+      <c r="E4" s="180" t="s">
         <v>722</v>
       </c>
-      <c r="F4" s="179"/>
+      <c r="F4" s="180"/>
       <c r="G4" s="25" t="s">
         <v>723</v>
       </c>
@@ -18081,16 +18254,16 @@
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="E5" s="178" t="s">
+      <c r="E5" s="179" t="s">
         <v>720</v>
       </c>
-      <c r="F5" s="178" t="s">
+      <c r="F5" s="179" t="s">
         <v>721</v>
       </c>
       <c r="G5" s="68" t="s">
         <v>747</v>
       </c>
-      <c r="H5" s="177" t="s">
+      <c r="H5" s="178" t="s">
         <v>748</v>
       </c>
       <c r="J5" t="s">
@@ -18101,12 +18274,12 @@
       <c r="A6" t="s">
         <v>261</v>
       </c>
-      <c r="E6" s="178"/>
-      <c r="F6" s="178"/>
+      <c r="E6" s="179"/>
+      <c r="F6" s="179"/>
       <c r="G6" s="68" t="s">
         <v>746</v>
       </c>
-      <c r="H6" s="178"/>
+      <c r="H6" s="179"/>
       <c r="J6" t="s">
         <v>729</v>
       </c>
@@ -18317,46 +18490,46 @@
     <col min="7" max="7" width="33" customWidth="1"/>
     <col min="8" max="8" width="38.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.140625" style="81" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="60.42578125" style="182" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="60.42578125" style="183" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30">
-      <c r="A1" s="190" t="s">
+      <c r="A1" s="191" t="s">
         <v>847</v>
       </c>
-      <c r="B1" s="190" t="s">
+      <c r="B1" s="191" t="s">
         <v>1171</v>
       </c>
-      <c r="C1" s="190" t="s">
+      <c r="C1" s="191" t="s">
         <v>640</v>
       </c>
-      <c r="D1" s="190" t="s">
+      <c r="D1" s="191" t="s">
         <v>1174</v>
       </c>
-      <c r="E1" s="190" t="s">
+      <c r="E1" s="191" t="s">
         <v>1169</v>
       </c>
-      <c r="F1" s="190" t="s">
+      <c r="F1" s="191" t="s">
         <v>1170</v>
       </c>
-      <c r="G1" s="191" t="s">
+      <c r="G1" s="192" t="s">
         <v>1204</v>
       </c>
-      <c r="H1" s="191" t="s">
+      <c r="H1" s="192" t="s">
         <v>1257</v>
       </c>
-      <c r="I1" s="190" t="s">
+      <c r="I1" s="191" t="s">
         <v>1178</v>
       </c>
-      <c r="J1" s="190" t="s">
+      <c r="J1" s="191" t="s">
         <v>1184</v>
       </c>
-      <c r="K1" s="190" t="s">
+      <c r="K1" s="191" t="s">
         <v>1190</v>
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="186">
+      <c r="A2" s="187">
         <v>44028</v>
       </c>
       <c r="B2" s="8" t="s">
@@ -18384,12 +18557,12 @@
       <c r="J2" s="119" t="s">
         <v>893</v>
       </c>
-      <c r="K2" s="187" t="s">
+      <c r="K2" s="188" t="s">
         <v>1196</v>
       </c>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="186">
+      <c r="A3" s="187">
         <v>44028</v>
       </c>
       <c r="B3" s="8" t="s">
@@ -18417,10 +18590,10 @@
       <c r="J3" s="119" t="s">
         <v>893</v>
       </c>
-      <c r="K3" s="188"/>
+      <c r="K3" s="189"/>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="186">
+      <c r="A4" s="187">
         <v>44029</v>
       </c>
       <c r="B4" s="8" t="s">
@@ -18446,10 +18619,10 @@
       <c r="J4" s="119" t="s">
         <v>893</v>
       </c>
-      <c r="K4" s="188"/>
+      <c r="K4" s="189"/>
     </row>
     <row r="5" spans="1:11" ht="45">
-      <c r="A5" s="186">
+      <c r="A5" s="187">
         <v>44029</v>
       </c>
       <c r="B5" s="8" t="s">
@@ -18475,10 +18648,10 @@
       <c r="J5" s="119" t="s">
         <v>893</v>
       </c>
-      <c r="K5" s="189"/>
+      <c r="K5" s="190"/>
     </row>
     <row r="6" spans="1:11" ht="60">
-      <c r="A6" s="186">
+      <c r="A6" s="187">
         <v>44029</v>
       </c>
       <c r="B6" s="8" t="s">
@@ -18509,7 +18682,7 @@
       </c>
     </row>
     <row r="7" spans="1:11" ht="60">
-      <c r="A7" s="186">
+      <c r="A7" s="187">
         <v>44029</v>
       </c>
       <c r="B7" s="8" t="s">
@@ -18538,7 +18711,7 @@
       <c r="K7" s="8"/>
     </row>
     <row r="8" spans="1:11" ht="60">
-      <c r="A8" s="186">
+      <c r="A8" s="187">
         <v>44029</v>
       </c>
       <c r="B8" s="8" t="s">
@@ -18571,7 +18744,7 @@
       </c>
     </row>
     <row r="9" spans="1:11" ht="60">
-      <c r="A9" s="186">
+      <c r="A9" s="187">
         <v>44029</v>
       </c>
       <c r="B9" s="8" t="s">
@@ -18586,13 +18759,13 @@
       <c r="E9" s="18" t="s">
         <v>1193</v>
       </c>
-      <c r="F9" s="199" t="s">
+      <c r="F9" s="200" t="s">
         <v>1245</v>
       </c>
-      <c r="G9" s="200" t="s">
+      <c r="G9" s="201" t="s">
         <v>1213</v>
       </c>
-      <c r="H9" s="197" t="s">
+      <c r="H9" s="198" t="s">
         <v>1243</v>
       </c>
       <c r="I9" s="119" t="s">
@@ -18604,7 +18777,7 @@
       </c>
     </row>
     <row r="10" spans="1:11" ht="64.5" customHeight="1">
-      <c r="A10" s="196" t="s">
+      <c r="A10" s="197" t="s">
         <v>1229</v>
       </c>
       <c r="B10" s="8" t="s">
@@ -18635,7 +18808,7 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="45">
-      <c r="A11" s="194" t="s">
+      <c r="A11" s="195" t="s">
         <v>1220</v>
       </c>
       <c r="B11" s="8" t="s">
@@ -18653,10 +18826,10 @@
       <c r="F11" s="119" t="s">
         <v>1200</v>
       </c>
-      <c r="G11" s="193" t="s">
+      <c r="G11" s="194" t="s">
         <v>1247</v>
       </c>
-      <c r="H11" s="193"/>
+      <c r="H11" s="194"/>
       <c r="I11" s="119" t="s">
         <v>1219</v>
       </c>
@@ -18704,114 +18877,114 @@
       </c>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="182"/>
-      <c r="B14" s="182"/>
-      <c r="C14" s="182"/>
-      <c r="D14" s="182"/>
-      <c r="E14" s="192" t="s">
+      <c r="A14" s="183"/>
+      <c r="B14" s="183"/>
+      <c r="C14" s="183"/>
+      <c r="D14" s="183"/>
+      <c r="E14" s="193" t="s">
         <v>1218</v>
       </c>
-      <c r="F14" s="183"/>
-      <c r="G14" s="192" t="s">
+      <c r="F14" s="184"/>
+      <c r="G14" s="193" t="s">
         <v>1256</v>
       </c>
-      <c r="H14" s="182"/>
-      <c r="I14" s="183"/>
-      <c r="J14" s="182"/>
+      <c r="H14" s="183"/>
+      <c r="I14" s="184"/>
+      <c r="J14" s="183"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="182"/>
-      <c r="B15" s="182"/>
-      <c r="C15" s="182"/>
-      <c r="D15" s="182"/>
-      <c r="E15" s="182"/>
-      <c r="F15" s="183"/>
-      <c r="G15" s="182" t="s">
+      <c r="A15" s="183"/>
+      <c r="B15" s="183"/>
+      <c r="C15" s="183"/>
+      <c r="D15" s="183"/>
+      <c r="E15" s="183"/>
+      <c r="F15" s="184"/>
+      <c r="G15" s="183" t="s">
         <v>1235</v>
       </c>
-      <c r="H15" s="182" t="s">
+      <c r="H15" s="183" t="s">
         <v>1236</v>
       </c>
-      <c r="I15" s="183"/>
-      <c r="J15" s="182"/>
+      <c r="I15" s="184"/>
+      <c r="J15" s="183"/>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="182"/>
-      <c r="B16" s="182"/>
-      <c r="C16" s="182"/>
-      <c r="D16" s="182"/>
-      <c r="E16" s="182"/>
-      <c r="G16" s="182"/>
-      <c r="H16" s="182"/>
-      <c r="I16" s="183"/>
-      <c r="J16" s="182"/>
+      <c r="A16" s="183"/>
+      <c r="B16" s="183"/>
+      <c r="C16" s="183"/>
+      <c r="D16" s="183"/>
+      <c r="E16" s="183"/>
+      <c r="G16" s="183"/>
+      <c r="H16" s="183"/>
+      <c r="I16" s="184"/>
+      <c r="J16" s="183"/>
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1">
-      <c r="A17" s="182"/>
-      <c r="B17" s="182"/>
-      <c r="C17" s="182"/>
-      <c r="D17" s="182"/>
-      <c r="E17" s="182"/>
-      <c r="F17" s="197"/>
+      <c r="A17" s="183"/>
+      <c r="B17" s="183"/>
+      <c r="C17" s="183"/>
+      <c r="D17" s="183"/>
+      <c r="E17" s="183"/>
+      <c r="F17" s="198"/>
       <c r="G17" s="8" t="s">
         <v>1258</v>
       </c>
-      <c r="H17" s="128" t="s">
+      <c r="H17" s="129" t="s">
         <v>1259</v>
       </c>
-      <c r="I17" s="183"/>
-      <c r="J17" s="182"/>
+      <c r="I17" s="184"/>
+      <c r="J17" s="183"/>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="182"/>
-      <c r="B18" s="182"/>
-      <c r="C18" s="182"/>
-      <c r="D18" s="182"/>
-      <c r="E18" s="182"/>
-      <c r="F18" s="201" t="s">
+      <c r="A18" s="183"/>
+      <c r="B18" s="183"/>
+      <c r="C18" s="183"/>
+      <c r="D18" s="183"/>
+      <c r="E18" s="183"/>
+      <c r="F18" s="202" t="s">
         <v>1241</v>
       </c>
       <c r="G18" s="8" t="s">
         <v>1238</v>
       </c>
-      <c r="H18" s="128" t="s">
+      <c r="H18" s="129" t="s">
         <v>1253</v>
       </c>
-      <c r="I18" s="183"/>
-      <c r="J18" s="182"/>
+      <c r="I18" s="184"/>
+      <c r="J18" s="183"/>
     </row>
     <row r="19" spans="1:10">
-      <c r="F19" s="201"/>
-      <c r="G19" s="209" t="s">
+      <c r="F19" s="202"/>
+      <c r="G19" s="210" t="s">
         <v>1237</v>
       </c>
-      <c r="H19" s="210" t="s">
+      <c r="H19" s="211" t="s">
         <v>1254</v>
       </c>
     </row>
     <row r="20" spans="1:10">
-      <c r="F20" s="201"/>
+      <c r="F20" s="202"/>
       <c r="G20" s="8" t="s">
         <v>1239</v>
       </c>
-      <c r="H20" s="128" t="s">
+      <c r="H20" s="129" t="s">
         <v>1253</v>
       </c>
     </row>
     <row r="21" spans="1:10">
-      <c r="F21" s="201"/>
+      <c r="F21" s="202"/>
       <c r="G21" s="8" t="s">
         <v>1240</v>
       </c>
-      <c r="H21" s="202" t="s">
+      <c r="H21" s="203" t="s">
         <v>1255</v>
       </c>
     </row>
     <row r="22" spans="1:10">
-      <c r="G22" s="198"/>
+      <c r="G22" s="199"/>
     </row>
     <row r="23" spans="1:10">
-      <c r="F23" s="195" t="s">
+      <c r="F23" s="196" t="s">
         <v>1252</v>
       </c>
       <c r="G23" t="s">
@@ -18822,7 +18995,7 @@
       </c>
     </row>
     <row r="24" spans="1:10">
-      <c r="F24" s="195" t="s">
+      <c r="F24" s="196" t="s">
         <v>1208</v>
       </c>
       <c r="G24" s="81">
@@ -18833,7 +19006,7 @@
       </c>
     </row>
     <row r="25" spans="1:10">
-      <c r="F25" s="195" t="s">
+      <c r="F25" s="196" t="s">
         <v>1208</v>
       </c>
       <c r="G25" s="81">
@@ -18844,7 +19017,7 @@
       </c>
     </row>
     <row r="26" spans="1:10">
-      <c r="F26" s="195" t="s">
+      <c r="F26" s="196" t="s">
         <v>1199</v>
       </c>
       <c r="G26" s="81">
@@ -18855,7 +19028,7 @@
       </c>
     </row>
     <row r="27" spans="1:10">
-      <c r="F27" s="195" t="s">
+      <c r="F27" s="196" t="s">
         <v>1199</v>
       </c>
       <c r="G27" s="81">
@@ -18866,7 +19039,7 @@
       </c>
     </row>
     <row r="28" spans="1:10">
-      <c r="F28" s="195" t="s">
+      <c r="F28" s="196" t="s">
         <v>1199</v>
       </c>
       <c r="G28" s="81">
@@ -18877,7 +19050,7 @@
       </c>
     </row>
     <row r="29" spans="1:10">
-      <c r="F29" s="195" t="s">
+      <c r="F29" s="196" t="s">
         <v>1200</v>
       </c>
       <c r="G29" s="81">
@@ -18888,7 +19061,7 @@
       </c>
     </row>
     <row r="30" spans="1:10">
-      <c r="F30" s="195" t="s">
+      <c r="F30" s="196" t="s">
         <v>1200</v>
       </c>
       <c r="G30" s="81">
@@ -18899,7 +19072,7 @@
       </c>
     </row>
     <row r="31" spans="1:10">
-      <c r="F31" s="195" t="s">
+      <c r="F31" s="196" t="s">
         <v>1200</v>
       </c>
       <c r="G31" s="81">
@@ -18910,7 +19083,7 @@
       </c>
     </row>
     <row r="32" spans="1:10">
-      <c r="F32" s="195" t="s">
+      <c r="F32" s="196" t="s">
         <v>1202</v>
       </c>
       <c r="G32" s="81">
@@ -18921,7 +19094,7 @@
       </c>
     </row>
     <row r="33" spans="6:8">
-      <c r="F33" s="195" t="s">
+      <c r="F33" s="196" t="s">
         <v>1202</v>
       </c>
       <c r="G33" s="81">
@@ -19069,13 +19242,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="126" t="s">
+      <c r="A1" s="127" t="s">
         <v>973</v>
       </c>
-      <c r="B1" s="127" t="s">
+      <c r="B1" s="128" t="s">
         <v>974</v>
       </c>
-      <c r="C1" s="127" t="s">
+      <c r="C1" s="128" t="s">
         <v>975</v>
       </c>
     </row>
@@ -19531,120 +19704,120 @@
       </c>
     </row>
     <row r="43" spans="1:3">
-      <c r="A43" s="128" t="s">
+      <c r="A43" s="129" t="s">
         <v>385</v>
       </c>
-      <c r="B43" s="128" t="s">
+      <c r="B43" s="129" t="s">
         <v>1053</v>
       </c>
-      <c r="C43" s="128" t="s">
+      <c r="C43" s="129" t="s">
         <v>1054</v>
       </c>
     </row>
     <row r="44" spans="1:3">
-      <c r="A44" s="128" t="s">
+      <c r="A44" s="129" t="s">
         <v>385</v>
       </c>
-      <c r="B44" s="128" t="s">
+      <c r="B44" s="129" t="s">
         <v>1055</v>
       </c>
-      <c r="C44" s="128" t="s">
+      <c r="C44" s="129" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="45" spans="1:3">
-      <c r="A45" s="128" t="s">
+      <c r="A45" s="129" t="s">
         <v>385</v>
       </c>
-      <c r="B45" s="128" t="s">
+      <c r="B45" s="129" t="s">
         <v>1056</v>
       </c>
-      <c r="C45" s="128" t="s">
+      <c r="C45" s="129" t="s">
         <v>1057</v>
       </c>
     </row>
     <row r="46" spans="1:3">
-      <c r="A46" s="128" t="s">
+      <c r="A46" s="129" t="s">
         <v>385</v>
       </c>
-      <c r="B46" s="128" t="s">
+      <c r="B46" s="129" t="s">
         <v>619</v>
       </c>
-      <c r="C46" s="128" t="s">
+      <c r="C46" s="129" t="s">
         <v>1058</v>
       </c>
     </row>
     <row r="47" spans="1:3">
-      <c r="A47" s="128" t="s">
+      <c r="A47" s="129" t="s">
         <v>385</v>
       </c>
-      <c r="B47" s="128" t="s">
+      <c r="B47" s="129" t="s">
         <v>617</v>
       </c>
-      <c r="C47" s="128" t="s">
+      <c r="C47" s="129" t="s">
         <v>1059</v>
       </c>
     </row>
     <row r="48" spans="1:3">
-      <c r="A48" s="128" t="s">
+      <c r="A48" s="129" t="s">
         <v>385</v>
       </c>
-      <c r="B48" s="128" t="s">
+      <c r="B48" s="129" t="s">
         <v>1060</v>
       </c>
-      <c r="C48" s="128" t="s">
+      <c r="C48" s="129" t="s">
         <v>1061</v>
       </c>
     </row>
     <row r="49" spans="1:3">
-      <c r="A49" s="128" t="s">
+      <c r="A49" s="129" t="s">
         <v>385</v>
       </c>
-      <c r="B49" s="128" t="s">
+      <c r="B49" s="129" t="s">
         <v>1062</v>
       </c>
-      <c r="C49" s="128" t="s">
+      <c r="C49" s="129" t="s">
         <v>1063</v>
       </c>
     </row>
     <row r="50" spans="1:3">
-      <c r="A50" s="128" t="s">
+      <c r="A50" s="129" t="s">
         <v>385</v>
       </c>
-      <c r="B50" s="128" t="s">
+      <c r="B50" s="129" t="s">
         <v>1064</v>
       </c>
-      <c r="C50" s="128" t="s">
+      <c r="C50" s="129" t="s">
         <v>1065</v>
       </c>
     </row>
     <row r="51" spans="1:3">
-      <c r="A51" s="128" t="s">
+      <c r="A51" s="129" t="s">
         <v>385</v>
       </c>
-      <c r="B51" s="128" t="s">
+      <c r="B51" s="129" t="s">
         <v>1066</v>
       </c>
-      <c r="C51" s="128" t="s">
+      <c r="C51" s="129" t="s">
         <v>1067</v>
       </c>
     </row>
     <row r="52" spans="1:3">
-      <c r="A52" s="128" t="s">
+      <c r="A52" s="129" t="s">
         <v>385</v>
       </c>
-      <c r="B52" s="128" t="s">
+      <c r="B52" s="129" t="s">
         <v>1068</v>
       </c>
-      <c r="C52" s="128" t="s">
+      <c r="C52" s="129" t="s">
         <v>1069</v>
       </c>
     </row>
     <row r="53" spans="1:3">
-      <c r="A53" s="128" t="s">
+      <c r="A53" s="129" t="s">
         <v>385</v>
       </c>
-      <c r="B53" s="128" t="s">
+      <c r="B53" s="129" t="s">
         <v>1070</v>
       </c>
       <c r="C53" s="19" t="s">
@@ -19652,10 +19825,10 @@
       </c>
     </row>
     <row r="54" spans="1:3">
-      <c r="A54" s="128" t="s">
+      <c r="A54" s="129" t="s">
         <v>385</v>
       </c>
-      <c r="B54" s="128" t="s">
+      <c r="B54" s="129" t="s">
         <v>1072</v>
       </c>
       <c r="C54" s="19" t="s">
@@ -19663,7 +19836,7 @@
       </c>
     </row>
     <row r="55" spans="1:3">
-      <c r="A55" s="128" t="s">
+      <c r="A55" s="129" t="s">
         <v>385</v>
       </c>
       <c r="B55" s="19" t="s">
@@ -19674,7 +19847,7 @@
       </c>
     </row>
     <row r="56" spans="1:3">
-      <c r="A56" s="128" t="s">
+      <c r="A56" s="129" t="s">
         <v>385</v>
       </c>
       <c r="B56" s="19" t="s">
@@ -19685,7 +19858,7 @@
       </c>
     </row>
     <row r="57" spans="1:3">
-      <c r="A57" s="128" t="s">
+      <c r="A57" s="129" t="s">
         <v>385</v>
       </c>
       <c r="B57" s="19" t="s">
@@ -19696,7 +19869,7 @@
       </c>
     </row>
     <row r="58" spans="1:3" ht="30">
-      <c r="A58" s="128" t="s">
+      <c r="A58" s="129" t="s">
         <v>385</v>
       </c>
       <c r="B58" s="19" t="s">
@@ -19707,7 +19880,7 @@
       </c>
     </row>
     <row r="59" spans="1:3">
-      <c r="A59" s="128" t="s">
+      <c r="A59" s="129" t="s">
         <v>385</v>
       </c>
       <c r="B59" s="19" t="s">
@@ -19718,7 +19891,7 @@
       </c>
     </row>
     <row r="60" spans="1:3">
-      <c r="A60" s="128" t="s">
+      <c r="A60" s="129" t="s">
         <v>385</v>
       </c>
       <c r="B60" s="19" t="s">
@@ -19732,10 +19905,10 @@
       <c r="A61" s="19" t="s">
         <v>1085</v>
       </c>
-      <c r="B61" s="129" t="s">
+      <c r="B61" s="130" t="s">
         <v>1086</v>
       </c>
-      <c r="C61" s="129" t="s">
+      <c r="C61" s="130" t="s">
         <v>1087</v>
       </c>
     </row>
@@ -19743,10 +19916,10 @@
       <c r="A62" s="19" t="s">
         <v>1085</v>
       </c>
-      <c r="B62" s="130" t="s">
+      <c r="B62" s="131" t="s">
         <v>1088</v>
       </c>
-      <c r="C62" s="130" t="s">
+      <c r="C62" s="131" t="s">
         <v>1089</v>
       </c>
     </row>
@@ -19754,10 +19927,10 @@
       <c r="A63" s="19" t="s">
         <v>1085</v>
       </c>
-      <c r="B63" s="130" t="s">
+      <c r="B63" s="131" t="s">
         <v>1090</v>
       </c>
-      <c r="C63" s="130" t="s">
+      <c r="C63" s="131" t="s">
         <v>1091</v>
       </c>
     </row>
@@ -19765,10 +19938,10 @@
       <c r="A64" s="19" t="s">
         <v>1085</v>
       </c>
-      <c r="B64" s="130" t="s">
+      <c r="B64" s="131" t="s">
         <v>1092</v>
       </c>
-      <c r="C64" s="130" t="s">
+      <c r="C64" s="131" t="s">
         <v>1093</v>
       </c>
     </row>
@@ -19776,10 +19949,10 @@
       <c r="A65" s="19" t="s">
         <v>1085</v>
       </c>
-      <c r="B65" s="130" t="s">
+      <c r="B65" s="131" t="s">
         <v>1094</v>
       </c>
-      <c r="C65" s="130" t="s">
+      <c r="C65" s="131" t="s">
         <v>1095</v>
       </c>
     </row>
@@ -19787,10 +19960,10 @@
       <c r="A66" s="19" t="s">
         <v>1085</v>
       </c>
-      <c r="B66" s="130" t="s">
+      <c r="B66" s="131" t="s">
         <v>1096</v>
       </c>
-      <c r="C66" s="130" t="s">
+      <c r="C66" s="131" t="s">
         <v>1097</v>
       </c>
     </row>
@@ -19798,10 +19971,10 @@
       <c r="A67" s="19" t="s">
         <v>1085</v>
       </c>
-      <c r="B67" s="130" t="s">
+      <c r="B67" s="131" t="s">
         <v>1098</v>
       </c>
-      <c r="C67" s="130" t="s">
+      <c r="C67" s="131" t="s">
         <v>1099</v>
       </c>
     </row>
@@ -19809,10 +19982,10 @@
       <c r="A68" s="19" t="s">
         <v>1085</v>
       </c>
-      <c r="B68" s="130" t="s">
+      <c r="B68" s="131" t="s">
         <v>1100</v>
       </c>
-      <c r="C68" s="130" t="s">
+      <c r="C68" s="131" t="s">
         <v>1101</v>
       </c>
     </row>
@@ -19820,10 +19993,10 @@
       <c r="A69" s="19" t="s">
         <v>1085</v>
       </c>
-      <c r="B69" s="130" t="s">
+      <c r="B69" s="131" t="s">
         <v>1102</v>
       </c>
-      <c r="C69" s="130" t="s">
+      <c r="C69" s="131" t="s">
         <v>1103</v>
       </c>
     </row>
@@ -19831,10 +20004,10 @@
       <c r="A70" s="19" t="s">
         <v>1085</v>
       </c>
-      <c r="B70" s="130" t="s">
+      <c r="B70" s="131" t="s">
         <v>1104</v>
       </c>
-      <c r="C70" s="130" t="s">
+      <c r="C70" s="131" t="s">
         <v>1105</v>
       </c>
     </row>
@@ -19842,10 +20015,10 @@
       <c r="A71" s="19" t="s">
         <v>1085</v>
       </c>
-      <c r="B71" s="130" t="s">
+      <c r="B71" s="131" t="s">
         <v>1106</v>
       </c>
-      <c r="C71" s="130" t="s">
+      <c r="C71" s="131" t="s">
         <v>1107</v>
       </c>
     </row>
@@ -19853,10 +20026,10 @@
       <c r="A72" s="19" t="s">
         <v>1085</v>
       </c>
-      <c r="B72" s="130" t="s">
+      <c r="B72" s="131" t="s">
         <v>1108</v>
       </c>
-      <c r="C72" s="130" t="s">
+      <c r="C72" s="131" t="s">
         <v>1109</v>
       </c>
     </row>
@@ -19864,10 +20037,10 @@
       <c r="A73" s="19" t="s">
         <v>1085</v>
       </c>
-      <c r="B73" s="130" t="s">
+      <c r="B73" s="131" t="s">
         <v>1110</v>
       </c>
-      <c r="C73" s="130" t="s">
+      <c r="C73" s="131" t="s">
         <v>1111</v>
       </c>
     </row>
@@ -19875,10 +20048,10 @@
       <c r="A74" s="19" t="s">
         <v>1085</v>
       </c>
-      <c r="B74" s="130" t="s">
+      <c r="B74" s="131" t="s">
         <v>1112</v>
       </c>
-      <c r="C74" s="130" t="s">
+      <c r="C74" s="131" t="s">
         <v>1113</v>
       </c>
     </row>
@@ -19886,10 +20059,10 @@
       <c r="A75" s="19" t="s">
         <v>1085</v>
       </c>
-      <c r="B75" s="130" t="s">
+      <c r="B75" s="131" t="s">
         <v>1114</v>
       </c>
-      <c r="C75" s="130" t="s">
+      <c r="C75" s="131" t="s">
         <v>1115</v>
       </c>
     </row>
@@ -19897,10 +20070,10 @@
       <c r="A76" s="19" t="s">
         <v>1085</v>
       </c>
-      <c r="B76" s="130" t="s">
+      <c r="B76" s="131" t="s">
         <v>1116</v>
       </c>
-      <c r="C76" s="130" t="s">
+      <c r="C76" s="131" t="s">
         <v>1117</v>
       </c>
     </row>
@@ -19908,10 +20081,10 @@
       <c r="A77" s="19" t="s">
         <v>1085</v>
       </c>
-      <c r="B77" s="130" t="s">
+      <c r="B77" s="131" t="s">
         <v>1118</v>
       </c>
-      <c r="C77" s="130" t="s">
+      <c r="C77" s="131" t="s">
         <v>1119</v>
       </c>
     </row>
@@ -19919,10 +20092,10 @@
       <c r="A78" s="19" t="s">
         <v>1085</v>
       </c>
-      <c r="B78" s="130" t="s">
+      <c r="B78" s="131" t="s">
         <v>1120</v>
       </c>
-      <c r="C78" s="130" t="s">
+      <c r="C78" s="131" t="s">
         <v>1121</v>
       </c>
     </row>
@@ -19930,10 +20103,10 @@
       <c r="A79" s="19" t="s">
         <v>1085</v>
       </c>
-      <c r="B79" s="130" t="s">
+      <c r="B79" s="131" t="s">
         <v>1122</v>
       </c>
-      <c r="C79" s="130" t="s">
+      <c r="C79" s="131" t="s">
         <v>1123</v>
       </c>
     </row>
@@ -19941,10 +20114,10 @@
       <c r="A80" s="19" t="s">
         <v>1085</v>
       </c>
-      <c r="B80" s="130" t="s">
+      <c r="B80" s="131" t="s">
         <v>1124</v>
       </c>
-      <c r="C80" s="130" t="s">
+      <c r="C80" s="131" t="s">
         <v>1125</v>
       </c>
     </row>
@@ -19952,10 +20125,10 @@
       <c r="A81" s="19" t="s">
         <v>1085</v>
       </c>
-      <c r="B81" s="130" t="s">
+      <c r="B81" s="131" t="s">
         <v>1126</v>
       </c>
-      <c r="C81" s="130" t="s">
+      <c r="C81" s="131" t="s">
         <v>1127</v>
       </c>
     </row>
@@ -19963,10 +20136,10 @@
       <c r="A82" s="19" t="s">
         <v>1085</v>
       </c>
-      <c r="B82" s="130" t="s">
+      <c r="B82" s="131" t="s">
         <v>1128</v>
       </c>
-      <c r="C82" s="130" t="s">
+      <c r="C82" s="131" t="s">
         <v>1129</v>
       </c>
     </row>
@@ -19974,10 +20147,10 @@
       <c r="A83" s="19" t="s">
         <v>1085</v>
       </c>
-      <c r="B83" s="130" t="s">
+      <c r="B83" s="131" t="s">
         <v>1130</v>
       </c>
-      <c r="C83" s="130" t="s">
+      <c r="C83" s="131" t="s">
         <v>1131</v>
       </c>
     </row>
@@ -19985,10 +20158,10 @@
       <c r="A84" s="19" t="s">
         <v>1132</v>
       </c>
-      <c r="B84" s="130" t="s">
+      <c r="B84" s="131" t="s">
         <v>1133</v>
       </c>
-      <c r="C84" s="130" t="s">
+      <c r="C84" s="131" t="s">
         <v>1107</v>
       </c>
     </row>
@@ -19996,10 +20169,10 @@
       <c r="A85" s="19" t="s">
         <v>1132</v>
       </c>
-      <c r="B85" s="130" t="s">
+      <c r="B85" s="131" t="s">
         <v>1134</v>
       </c>
-      <c r="C85" s="130" t="s">
+      <c r="C85" s="131" t="s">
         <v>1135</v>
       </c>
     </row>
@@ -20007,10 +20180,10 @@
       <c r="A86" s="19" t="s">
         <v>1132</v>
       </c>
-      <c r="B86" s="130" t="s">
+      <c r="B86" s="131" t="s">
         <v>1136</v>
       </c>
-      <c r="C86" s="130" t="s">
+      <c r="C86" s="131" t="s">
         <v>1137</v>
       </c>
     </row>
@@ -20018,10 +20191,10 @@
       <c r="A87" s="19" t="s">
         <v>1132</v>
       </c>
-      <c r="B87" s="130" t="s">
+      <c r="B87" s="131" t="s">
         <v>1138</v>
       </c>
-      <c r="C87" s="130" t="s">
+      <c r="C87" s="131" t="s">
         <v>1139</v>
       </c>
     </row>
@@ -20029,10 +20202,10 @@
       <c r="A88" s="19" t="s">
         <v>1132</v>
       </c>
-      <c r="B88" s="130" t="s">
+      <c r="B88" s="131" t="s">
         <v>1140</v>
       </c>
-      <c r="C88" s="130" t="s">
+      <c r="C88" s="131" t="s">
         <v>1109</v>
       </c>
     </row>
@@ -20040,10 +20213,10 @@
       <c r="A89" s="19" t="s">
         <v>1132</v>
       </c>
-      <c r="B89" s="130" t="s">
+      <c r="B89" s="131" t="s">
         <v>1141</v>
       </c>
-      <c r="C89" s="130" t="s">
+      <c r="C89" s="131" t="s">
         <v>1142</v>
       </c>
     </row>
@@ -20051,10 +20224,10 @@
       <c r="A90" s="19" t="s">
         <v>1132</v>
       </c>
-      <c r="B90" s="130" t="s">
+      <c r="B90" s="131" t="s">
         <v>1143</v>
       </c>
-      <c r="C90" s="130" t="s">
+      <c r="C90" s="131" t="s">
         <v>1144</v>
       </c>
     </row>
@@ -20062,10 +20235,10 @@
       <c r="A91" s="19" t="s">
         <v>1145</v>
       </c>
-      <c r="B91" s="130" t="s">
+      <c r="B91" s="131" t="s">
         <v>1146</v>
       </c>
-      <c r="C91" s="130" t="s">
+      <c r="C91" s="131" t="s">
         <v>1107</v>
       </c>
     </row>
@@ -20073,10 +20246,10 @@
       <c r="A92" s="19" t="s">
         <v>1145</v>
       </c>
-      <c r="B92" s="130" t="s">
+      <c r="B92" s="131" t="s">
         <v>1136</v>
       </c>
-      <c r="C92" s="130" t="s">
+      <c r="C92" s="131" t="s">
         <v>1137</v>
       </c>
     </row>
@@ -20084,10 +20257,10 @@
       <c r="A93" s="19" t="s">
         <v>1145</v>
       </c>
-      <c r="B93" s="130" t="s">
+      <c r="B93" s="131" t="s">
         <v>313</v>
       </c>
-      <c r="C93" s="130" t="s">
+      <c r="C93" s="131" t="s">
         <v>1087</v>
       </c>
     </row>
@@ -20095,10 +20268,10 @@
       <c r="A94" s="19" t="s">
         <v>1145</v>
       </c>
-      <c r="B94" s="130" t="s">
+      <c r="B94" s="131" t="s">
         <v>811</v>
       </c>
-      <c r="C94" s="130" t="s">
+      <c r="C94" s="131" t="s">
         <v>1147</v>
       </c>
     </row>
@@ -20106,10 +20279,10 @@
       <c r="A95" s="19" t="s">
         <v>1145</v>
       </c>
-      <c r="B95" s="130" t="s">
+      <c r="B95" s="131" t="s">
         <v>1148</v>
       </c>
-      <c r="C95" s="130" t="s">
+      <c r="C95" s="131" t="s">
         <v>1091</v>
       </c>
     </row>
@@ -20117,10 +20290,10 @@
       <c r="A96" s="19" t="s">
         <v>1145</v>
       </c>
-      <c r="B96" s="130" t="s">
+      <c r="B96" s="131" t="s">
         <v>1149</v>
       </c>
-      <c r="C96" s="130" t="s">
+      <c r="C96" s="131" t="s">
         <v>1093</v>
       </c>
     </row>
@@ -20128,10 +20301,10 @@
       <c r="A97" s="19" t="s">
         <v>1145</v>
       </c>
-      <c r="B97" s="130" t="s">
+      <c r="B97" s="131" t="s">
         <v>1150</v>
       </c>
-      <c r="C97" s="130" t="s">
+      <c r="C97" s="131" t="s">
         <v>1095</v>
       </c>
     </row>
@@ -20139,10 +20312,10 @@
       <c r="A98" s="19" t="s">
         <v>1145</v>
       </c>
-      <c r="B98" s="130" t="s">
+      <c r="B98" s="131" t="s">
         <v>1151</v>
       </c>
-      <c r="C98" s="130" t="s">
+      <c r="C98" s="131" t="s">
         <v>1129</v>
       </c>
     </row>
@@ -20150,10 +20323,10 @@
       <c r="A99" s="19" t="s">
         <v>1145</v>
       </c>
-      <c r="B99" s="130" t="s">
+      <c r="B99" s="131" t="s">
         <v>1152</v>
       </c>
-      <c r="C99" s="130" t="s">
+      <c r="C99" s="131" t="s">
         <v>1153</v>
       </c>
     </row>
@@ -20161,10 +20334,10 @@
       <c r="A100" s="19" t="s">
         <v>1145</v>
       </c>
-      <c r="B100" s="130" t="s">
+      <c r="B100" s="131" t="s">
         <v>1154</v>
       </c>
-      <c r="C100" s="130" t="s">
+      <c r="C100" s="131" t="s">
         <v>1125</v>
       </c>
     </row>
@@ -20172,10 +20345,10 @@
       <c r="A101" s="19" t="s">
         <v>1145</v>
       </c>
-      <c r="B101" s="130" t="s">
+      <c r="B101" s="131" t="s">
         <v>1141</v>
       </c>
-      <c r="C101" s="130" t="s">
+      <c r="C101" s="131" t="s">
         <v>1155</v>
       </c>
     </row>
@@ -20183,10 +20356,10 @@
       <c r="A102" s="19" t="s">
         <v>1145</v>
       </c>
-      <c r="B102" s="130" t="s">
+      <c r="B102" s="131" t="s">
         <v>1156</v>
       </c>
-      <c r="C102" s="130" t="s">
+      <c r="C102" s="131" t="s">
         <v>1157</v>
       </c>
     </row>
@@ -20194,10 +20367,10 @@
       <c r="A103" s="19" t="s">
         <v>1145</v>
       </c>
-      <c r="B103" s="130" t="s">
+      <c r="B103" s="131" t="s">
         <v>1158</v>
       </c>
-      <c r="C103" s="130" t="s">
+      <c r="C103" s="131" t="s">
         <v>1159</v>
       </c>
     </row>
@@ -20205,10 +20378,10 @@
       <c r="A104" s="19" t="s">
         <v>1145</v>
       </c>
-      <c r="B104" s="130" t="s">
+      <c r="B104" s="131" t="s">
         <v>1160</v>
       </c>
-      <c r="C104" s="130" t="s">
+      <c r="C104" s="131" t="s">
         <v>1099</v>
       </c>
     </row>
@@ -20216,10 +20389,10 @@
       <c r="A105" s="19" t="s">
         <v>1145</v>
       </c>
-      <c r="B105" s="130" t="s">
+      <c r="B105" s="131" t="s">
         <v>1161</v>
       </c>
-      <c r="C105" s="130" t="s">
+      <c r="C105" s="131" t="s">
         <v>1162</v>
       </c>
     </row>
@@ -20242,13 +20415,13 @@
       <c r="A112" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="B112" s="131"/>
+      <c r="B112" s="132"/>
     </row>
     <row r="113" spans="1:2" ht="16.5">
       <c r="A113" s="7" t="s">
         <v>1165</v>
       </c>
-      <c r="B113" s="131"/>
+      <c r="B113" s="132"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -20292,7 +20465,7 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="178" t="s">
+      <c r="A2" s="179" t="s">
         <v>379</v>
       </c>
       <c r="B2" s="57" t="s">
@@ -20306,7 +20479,7 @@
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="178"/>
+      <c r="A3" s="179"/>
       <c r="B3" s="20" t="s">
         <v>262</v>
       </c>
@@ -20318,7 +20491,7 @@
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="178"/>
+      <c r="A4" s="179"/>
       <c r="B4" s="20" t="s">
         <v>385</v>
       </c>
@@ -20330,7 +20503,7 @@
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="178"/>
+      <c r="A5" s="179"/>
       <c r="B5" s="57" t="s">
         <v>544</v>
       </c>
@@ -20342,7 +20515,7 @@
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="178"/>
+      <c r="A6" s="179"/>
       <c r="B6" s="20" t="s">
         <v>388</v>
       </c>
@@ -20354,7 +20527,7 @@
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="178"/>
+      <c r="A7" s="179"/>
       <c r="B7" s="20" t="s">
         <v>390</v>
       </c>
@@ -21975,12 +22148,12 @@
       </c>
     </row>
     <row r="9" spans="11:18">
-      <c r="K9" s="208" t="s">
+      <c r="K9" s="209" t="s">
         <v>1269</v>
       </c>
     </row>
     <row r="10" spans="11:18">
-      <c r="K10" s="208">
+      <c r="K10" s="209">
         <v>0</v>
       </c>
       <c r="L10" s="110" t="s">
@@ -21997,17 +22170,17 @@
       </c>
     </row>
     <row r="11" spans="11:18" ht="15.75" thickBot="1">
-      <c r="K11" s="208"/>
-      <c r="L11" s="206"/>
-      <c r="M11" s="206"/>
-      <c r="N11" s="206"/>
-      <c r="O11" s="206"/>
-      <c r="P11" s="206"/>
-      <c r="Q11" s="206"/>
-      <c r="R11" s="206"/>
+      <c r="K11" s="209"/>
+      <c r="L11" s="207"/>
+      <c r="M11" s="207"/>
+      <c r="N11" s="207"/>
+      <c r="O11" s="207"/>
+      <c r="P11" s="207"/>
+      <c r="Q11" s="207"/>
+      <c r="R11" s="207"/>
     </row>
     <row r="12" spans="11:18">
-      <c r="K12" s="208">
+      <c r="K12" s="209">
         <v>1</v>
       </c>
       <c r="L12" s="5" t="s">
@@ -22015,7 +22188,7 @@
       </c>
     </row>
     <row r="13" spans="11:18">
-      <c r="K13" s="208"/>
+      <c r="K13" s="209"/>
       <c r="M13" t="s">
         <v>881</v>
       </c>
@@ -22027,7 +22200,7 @@
       </c>
     </row>
     <row r="14" spans="11:18">
-      <c r="K14" s="208"/>
+      <c r="K14" s="209"/>
       <c r="L14" s="6" t="s">
         <v>888</v>
       </c>
@@ -22036,13 +22209,13 @@
       </c>
     </row>
     <row r="15" spans="11:18">
-      <c r="K15" s="208"/>
+      <c r="K15" s="209"/>
       <c r="M15" t="s">
         <v>885</v>
       </c>
     </row>
     <row r="16" spans="11:18">
-      <c r="K16" s="208"/>
+      <c r="K16" s="209"/>
       <c r="O16" s="5" t="s">
         <v>1268</v>
       </c>
@@ -22051,16 +22224,16 @@
       </c>
     </row>
     <row r="17" spans="7:24">
-      <c r="K17" s="208"/>
+      <c r="K17" s="209"/>
     </row>
     <row r="18" spans="7:24">
-      <c r="K18" s="208"/>
+      <c r="K18" s="209"/>
     </row>
     <row r="19" spans="7:24">
-      <c r="K19" s="208"/>
+      <c r="K19" s="209"/>
     </row>
     <row r="20" spans="7:24">
-      <c r="K20" s="208"/>
+      <c r="K20" s="209"/>
       <c r="L20" s="6" t="s">
         <v>883</v>
       </c>
@@ -22078,7 +22251,7 @@
       </c>
     </row>
     <row r="21" spans="7:24">
-      <c r="K21" s="208"/>
+      <c r="K21" s="209"/>
       <c r="M21" t="s">
         <v>889</v>
       </c>
@@ -22087,8 +22260,8 @@
       </c>
     </row>
     <row r="22" spans="7:24">
-      <c r="K22" s="208"/>
-      <c r="V22" s="141" t="s">
+      <c r="K22" s="209"/>
+      <c r="V22" s="142" t="s">
         <v>833</v>
       </c>
       <c r="W22" s="9" t="s">
@@ -22099,19 +22272,19 @@
       </c>
     </row>
     <row r="23" spans="7:24" ht="15.75" thickBot="1">
-      <c r="K23" s="208"/>
-      <c r="L23" s="206"/>
-      <c r="M23" s="206"/>
-      <c r="N23" s="206"/>
-      <c r="O23" s="207" t="s">
+      <c r="K23" s="209"/>
+      <c r="L23" s="207"/>
+      <c r="M23" s="207"/>
+      <c r="N23" s="207"/>
+      <c r="O23" s="208" t="s">
         <v>1268</v>
       </c>
-      <c r="P23" s="207" t="s">
+      <c r="P23" s="208" t="s">
         <v>1270</v>
       </c>
-      <c r="Q23" s="206"/>
-      <c r="R23" s="206"/>
-      <c r="V23" s="142"/>
+      <c r="Q23" s="207"/>
+      <c r="R23" s="207"/>
+      <c r="V23" s="143"/>
       <c r="W23" s="9" t="s">
         <v>816</v>
       </c>
@@ -22120,8 +22293,8 @@
       </c>
     </row>
     <row r="24" spans="7:24">
-      <c r="K24" s="208"/>
-      <c r="V24" s="142"/>
+      <c r="K24" s="209"/>
+      <c r="V24" s="143"/>
       <c r="W24" s="9" t="s">
         <v>817</v>
       </c>
@@ -22130,13 +22303,13 @@
       </c>
     </row>
     <row r="25" spans="7:24">
-      <c r="K25" s="208">
+      <c r="K25" s="209">
         <v>2</v>
       </c>
       <c r="L25" s="5" t="s">
         <v>892</v>
       </c>
-      <c r="V25" s="142"/>
+      <c r="V25" s="143"/>
       <c r="W25" s="9" t="s">
         <v>818</v>
       </c>
@@ -22145,7 +22318,7 @@
       </c>
     </row>
     <row r="26" spans="7:24">
-      <c r="K26" s="208"/>
+      <c r="K26" s="209"/>
       <c r="M26" s="111" t="s">
         <v>894</v>
       </c>
@@ -22155,32 +22328,32 @@
       <c r="O26" t="s">
         <v>898</v>
       </c>
-      <c r="V26" s="142"/>
+      <c r="V26" s="143"/>
       <c r="W26" s="9" t="s">
         <v>825</v>
       </c>
       <c r="X26" s="92"/>
     </row>
     <row r="27" spans="7:24">
-      <c r="K27" s="208"/>
+      <c r="K27" s="209"/>
       <c r="M27" t="s">
         <v>895</v>
       </c>
       <c r="N27" t="s">
         <v>897</v>
       </c>
-      <c r="V27" s="142"/>
+      <c r="V27" s="143"/>
       <c r="W27" s="9" t="s">
         <v>826</v>
       </c>
       <c r="X27" s="92"/>
     </row>
     <row r="28" spans="7:24">
-      <c r="K28" s="208"/>
+      <c r="K28" s="209"/>
       <c r="N28" t="s">
         <v>899</v>
       </c>
-      <c r="V28" s="142"/>
+      <c r="V28" s="143"/>
       <c r="W28" s="9" t="s">
         <v>827</v>
       </c>
@@ -22189,11 +22362,11 @@
       </c>
     </row>
     <row r="29" spans="7:24">
-      <c r="K29" s="208"/>
+      <c r="K29" s="209"/>
       <c r="N29" t="s">
         <v>900</v>
       </c>
-      <c r="V29" s="143"/>
+      <c r="V29" s="144"/>
       <c r="W29" s="9" t="s">
         <v>828</v>
       </c>
@@ -22202,14 +22375,14 @@
       </c>
     </row>
     <row r="30" spans="7:24">
-      <c r="K30" s="208"/>
+      <c r="K30" s="209"/>
       <c r="M30" t="s">
         <v>901</v>
       </c>
       <c r="N30" t="s">
         <v>853</v>
       </c>
-      <c r="V30" s="138" t="s">
+      <c r="V30" s="139" t="s">
         <v>832</v>
       </c>
       <c r="W30" s="49" t="s">
@@ -22218,11 +22391,11 @@
       <c r="X30" s="113"/>
     </row>
     <row r="31" spans="7:24">
-      <c r="K31" s="208"/>
+      <c r="K31" s="209"/>
       <c r="N31" t="s">
         <v>902</v>
       </c>
-      <c r="V31" s="139"/>
+      <c r="V31" s="140"/>
       <c r="W31" s="49" t="s">
         <v>823</v>
       </c>
@@ -22232,19 +22405,19 @@
       <c r="G32" t="s">
         <v>911</v>
       </c>
-      <c r="K32" s="208"/>
-      <c r="L32" s="206"/>
-      <c r="M32" s="206"/>
-      <c r="N32" s="206"/>
-      <c r="O32" s="207" t="s">
+      <c r="K32" s="209"/>
+      <c r="L32" s="207"/>
+      <c r="M32" s="207"/>
+      <c r="N32" s="207"/>
+      <c r="O32" s="208" t="s">
         <v>903</v>
       </c>
-      <c r="P32" s="207" t="s">
+      <c r="P32" s="208" t="s">
         <v>904</v>
       </c>
-      <c r="Q32" s="206"/>
-      <c r="R32" s="206"/>
-      <c r="V32" s="140"/>
+      <c r="Q32" s="207"/>
+      <c r="R32" s="207"/>
+      <c r="V32" s="141"/>
       <c r="W32" s="49" t="s">
         <v>824</v>
       </c>
@@ -22257,7 +22430,7 @@
       <c r="G33" t="s">
         <v>912</v>
       </c>
-      <c r="K33" s="208"/>
+      <c r="K33" s="209"/>
     </row>
     <row r="34" spans="6:17">
       <c r="F34">
@@ -22266,7 +22439,7 @@
       <c r="G34" t="s">
         <v>913</v>
       </c>
-      <c r="K34" s="208">
+      <c r="K34" s="209">
         <v>3</v>
       </c>
       <c r="L34" s="5" t="s">
@@ -22316,19 +22489,19 @@
       </c>
     </row>
     <row r="41" spans="6:17" ht="15.75" thickBot="1">
-      <c r="L41" s="206"/>
-      <c r="M41" s="206"/>
-      <c r="N41" s="206"/>
-      <c r="O41" s="207" t="s">
+      <c r="L41" s="207"/>
+      <c r="M41" s="207"/>
+      <c r="N41" s="207"/>
+      <c r="O41" s="208" t="s">
         <v>908</v>
       </c>
-      <c r="P41" s="207" t="s">
+      <c r="P41" s="208" t="s">
         <v>893</v>
       </c>
-      <c r="Q41" s="206"/>
+      <c r="Q41" s="207"/>
     </row>
     <row r="44" spans="6:17">
-      <c r="P44" s="205"/>
+      <c r="P44" s="206"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -22384,7 +22557,7 @@
       <c r="R5" s="13" t="s">
         <v>352</v>
       </c>
-      <c r="S5" s="144" t="s">
+      <c r="S5" s="145" t="s">
         <v>810</v>
       </c>
     </row>
@@ -22401,7 +22574,7 @@
       <c r="R6" s="9" t="s">
         <v>602</v>
       </c>
-      <c r="S6" s="144"/>
+      <c r="S6" s="145"/>
     </row>
     <row r="7" spans="3:20">
       <c r="O7" s="81" t="s">
@@ -22416,7 +22589,7 @@
       <c r="R7" s="9" t="s">
         <v>603</v>
       </c>
-      <c r="S7" s="144"/>
+      <c r="S7" s="145"/>
     </row>
     <row r="8" spans="3:20">
       <c r="O8" s="81" t="s">
@@ -22431,7 +22604,7 @@
       <c r="R8" s="9" t="s">
         <v>350</v>
       </c>
-      <c r="S8" s="144"/>
+      <c r="S8" s="145"/>
     </row>
     <row r="9" spans="3:20">
       <c r="O9" s="81" t="s">
@@ -22446,7 +22619,7 @@
       <c r="R9" s="9" t="s">
         <v>349</v>
       </c>
-      <c r="S9" s="144"/>
+      <c r="S9" s="145"/>
     </row>
     <row r="10" spans="3:20">
       <c r="Q10" s="9" t="s">
@@ -22471,7 +22644,7 @@
       </c>
     </row>
     <row r="15" spans="3:20">
-      <c r="Q15" s="141" t="s">
+      <c r="Q15" s="142" t="s">
         <v>833</v>
       </c>
       <c r="R15" s="9" t="s">
@@ -22506,7 +22679,7 @@
       <c r="J16" s="10" t="s">
         <v>814</v>
       </c>
-      <c r="Q16" s="142"/>
+      <c r="Q16" s="143"/>
       <c r="R16" s="9" t="s">
         <v>816</v>
       </c>
@@ -22516,7 +22689,7 @@
     </row>
     <row r="17" spans="10:19">
       <c r="J17" s="81"/>
-      <c r="Q17" s="142"/>
+      <c r="Q17" s="143"/>
       <c r="R17" s="9" t="s">
         <v>817</v>
       </c>
@@ -22525,7 +22698,7 @@
       </c>
     </row>
     <row r="18" spans="10:19">
-      <c r="Q18" s="142"/>
+      <c r="Q18" s="143"/>
       <c r="R18" s="9" t="s">
         <v>818</v>
       </c>
@@ -22534,21 +22707,21 @@
       </c>
     </row>
     <row r="19" spans="10:19">
-      <c r="Q19" s="142"/>
+      <c r="Q19" s="143"/>
       <c r="R19" s="9" t="s">
         <v>825</v>
       </c>
       <c r="S19" s="92"/>
     </row>
     <row r="20" spans="10:19">
-      <c r="Q20" s="142"/>
+      <c r="Q20" s="143"/>
       <c r="R20" s="9" t="s">
         <v>826</v>
       </c>
       <c r="S20" s="92"/>
     </row>
     <row r="21" spans="10:19">
-      <c r="Q21" s="142"/>
+      <c r="Q21" s="143"/>
       <c r="R21" s="9" t="s">
         <v>827</v>
       </c>
@@ -22557,7 +22730,7 @@
       </c>
     </row>
     <row r="22" spans="10:19">
-      <c r="Q22" s="143"/>
+      <c r="Q22" s="144"/>
       <c r="R22" s="9" t="s">
         <v>828</v>
       </c>
@@ -22566,7 +22739,7 @@
       </c>
     </row>
     <row r="23" spans="10:19">
-      <c r="Q23" s="141" t="s">
+      <c r="Q23" s="142" t="s">
         <v>832</v>
       </c>
       <c r="R23" s="9" t="s">
@@ -22575,14 +22748,14 @@
       <c r="S23" s="92"/>
     </row>
     <row r="24" spans="10:19">
-      <c r="Q24" s="142"/>
+      <c r="Q24" s="143"/>
       <c r="R24" s="9" t="s">
         <v>823</v>
       </c>
       <c r="S24" s="92"/>
     </row>
     <row r="25" spans="10:19">
-      <c r="Q25" s="143"/>
+      <c r="Q25" s="144"/>
       <c r="R25" s="9" t="s">
         <v>824</v>
       </c>
@@ -22648,39 +22821,39 @@
       <c r="B1" t="s">
         <v>861</v>
       </c>
-      <c r="J1" s="145" t="s">
+      <c r="J1" s="146" t="s">
         <v>954</v>
       </c>
-      <c r="K1" s="146"/>
-      <c r="L1" s="146"/>
-      <c r="M1" s="146"/>
-      <c r="N1" s="146"/>
-      <c r="O1" s="146"/>
-      <c r="P1" s="146"/>
-      <c r="Q1" s="146"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="147"/>
+      <c r="M1" s="147"/>
+      <c r="N1" s="147"/>
+      <c r="O1" s="147"/>
+      <c r="P1" s="147"/>
+      <c r="Q1" s="147"/>
     </row>
     <row r="2" spans="1:17">
-      <c r="J2" s="146"/>
-      <c r="K2" s="146"/>
-      <c r="L2" s="146"/>
-      <c r="M2" s="146"/>
-      <c r="N2" s="146"/>
-      <c r="O2" s="146"/>
-      <c r="P2" s="146"/>
-      <c r="Q2" s="146"/>
+      <c r="J2" s="147"/>
+      <c r="K2" s="147"/>
+      <c r="L2" s="147"/>
+      <c r="M2" s="147"/>
+      <c r="N2" s="147"/>
+      <c r="O2" s="147"/>
+      <c r="P2" s="147"/>
+      <c r="Q2" s="147"/>
     </row>
     <row r="3" spans="1:17">
       <c r="A3" s="6" t="s">
         <v>862</v>
       </c>
-      <c r="J3" s="146"/>
-      <c r="K3" s="146"/>
-      <c r="L3" s="146"/>
-      <c r="M3" s="146"/>
-      <c r="N3" s="146"/>
-      <c r="O3" s="146"/>
-      <c r="P3" s="146"/>
-      <c r="Q3" s="146"/>
+      <c r="J3" s="147"/>
+      <c r="K3" s="147"/>
+      <c r="L3" s="147"/>
+      <c r="M3" s="147"/>
+      <c r="N3" s="147"/>
+      <c r="O3" s="147"/>
+      <c r="P3" s="147"/>
+      <c r="Q3" s="147"/>
     </row>
     <row r="4" spans="1:17">
       <c r="A4" t="s">
@@ -22692,24 +22865,24 @@
       <c r="D4" t="s">
         <v>864</v>
       </c>
-      <c r="J4" s="146"/>
-      <c r="K4" s="146"/>
-      <c r="L4" s="146"/>
-      <c r="M4" s="146"/>
-      <c r="N4" s="146"/>
-      <c r="O4" s="146"/>
-      <c r="P4" s="146"/>
-      <c r="Q4" s="146"/>
+      <c r="J4" s="147"/>
+      <c r="K4" s="147"/>
+      <c r="L4" s="147"/>
+      <c r="M4" s="147"/>
+      <c r="N4" s="147"/>
+      <c r="O4" s="147"/>
+      <c r="P4" s="147"/>
+      <c r="Q4" s="147"/>
     </row>
     <row r="5" spans="1:17">
-      <c r="J5" s="146"/>
-      <c r="K5" s="146"/>
-      <c r="L5" s="146"/>
-      <c r="M5" s="146"/>
-      <c r="N5" s="146"/>
-      <c r="O5" s="146"/>
-      <c r="P5" s="146"/>
-      <c r="Q5" s="146"/>
+      <c r="J5" s="147"/>
+      <c r="K5" s="147"/>
+      <c r="L5" s="147"/>
+      <c r="M5" s="147"/>
+      <c r="N5" s="147"/>
+      <c r="O5" s="147"/>
+      <c r="P5" s="147"/>
+      <c r="Q5" s="147"/>
     </row>
     <row r="6" spans="1:17" ht="15.75" thickBot="1">
       <c r="A6" t="s">
@@ -22718,38 +22891,38 @@
       <c r="E6" t="s">
         <v>920</v>
       </c>
-      <c r="J6" s="146"/>
-      <c r="K6" s="146"/>
-      <c r="L6" s="146"/>
-      <c r="M6" s="146"/>
-      <c r="N6" s="146"/>
-      <c r="O6" s="146"/>
-      <c r="P6" s="146"/>
-      <c r="Q6" s="146"/>
+      <c r="J6" s="147"/>
+      <c r="K6" s="147"/>
+      <c r="L6" s="147"/>
+      <c r="M6" s="147"/>
+      <c r="N6" s="147"/>
+      <c r="O6" s="147"/>
+      <c r="P6" s="147"/>
+      <c r="Q6" s="147"/>
     </row>
     <row r="7" spans="1:17" ht="15.75" thickBot="1">
       <c r="A7" s="106" t="s">
         <v>866</v>
       </c>
-      <c r="J7" s="146"/>
-      <c r="K7" s="146"/>
-      <c r="L7" s="146"/>
-      <c r="M7" s="146"/>
-      <c r="N7" s="146"/>
-      <c r="O7" s="146"/>
-      <c r="P7" s="146"/>
-      <c r="Q7" s="146"/>
+      <c r="J7" s="147"/>
+      <c r="K7" s="147"/>
+      <c r="L7" s="147"/>
+      <c r="M7" s="147"/>
+      <c r="N7" s="147"/>
+      <c r="O7" s="147"/>
+      <c r="P7" s="147"/>
+      <c r="Q7" s="147"/>
     </row>
     <row r="8" spans="1:17">
       <c r="A8" s="121"/>
-      <c r="J8" s="146"/>
-      <c r="K8" s="146"/>
-      <c r="L8" s="146"/>
-      <c r="M8" s="146"/>
-      <c r="N8" s="146"/>
-      <c r="O8" s="146"/>
-      <c r="P8" s="146"/>
-      <c r="Q8" s="146"/>
+      <c r="J8" s="147"/>
+      <c r="K8" s="147"/>
+      <c r="L8" s="147"/>
+      <c r="M8" s="147"/>
+      <c r="N8" s="147"/>
+      <c r="O8" s="147"/>
+      <c r="P8" s="147"/>
+      <c r="Q8" s="147"/>
     </row>
     <row r="9" spans="1:17">
       <c r="A9" t="s">
@@ -22758,14 +22931,14 @@
       <c r="B9" t="s">
         <v>926</v>
       </c>
-      <c r="J9" s="146"/>
-      <c r="K9" s="146"/>
-      <c r="L9" s="146"/>
-      <c r="M9" s="146"/>
-      <c r="N9" s="146"/>
-      <c r="O9" s="146"/>
-      <c r="P9" s="146"/>
-      <c r="Q9" s="146"/>
+      <c r="J9" s="147"/>
+      <c r="K9" s="147"/>
+      <c r="L9" s="147"/>
+      <c r="M9" s="147"/>
+      <c r="N9" s="147"/>
+      <c r="O9" s="147"/>
+      <c r="P9" s="147"/>
+      <c r="Q9" s="147"/>
     </row>
     <row r="10" spans="1:17">
       <c r="A10" t="s">
@@ -22786,14 +22959,14 @@
       <c r="H10" t="s">
         <v>952</v>
       </c>
-      <c r="J10" s="146"/>
-      <c r="K10" s="146"/>
-      <c r="L10" s="146"/>
-      <c r="M10" s="146"/>
-      <c r="N10" s="146"/>
-      <c r="O10" s="146"/>
-      <c r="P10" s="146"/>
-      <c r="Q10" s="146"/>
+      <c r="J10" s="147"/>
+      <c r="K10" s="147"/>
+      <c r="L10" s="147"/>
+      <c r="M10" s="147"/>
+      <c r="N10" s="147"/>
+      <c r="O10" s="147"/>
+      <c r="P10" s="147"/>
+      <c r="Q10" s="147"/>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" t="s">
@@ -22814,14 +22987,14 @@
       <c r="H11" t="s">
         <v>953</v>
       </c>
-      <c r="J11" s="146"/>
-      <c r="K11" s="146"/>
-      <c r="L11" s="146"/>
-      <c r="M11" s="146"/>
-      <c r="N11" s="146"/>
-      <c r="O11" s="146"/>
-      <c r="P11" s="146"/>
-      <c r="Q11" s="146"/>
+      <c r="J11" s="147"/>
+      <c r="K11" s="147"/>
+      <c r="L11" s="147"/>
+      <c r="M11" s="147"/>
+      <c r="N11" s="147"/>
+      <c r="O11" s="147"/>
+      <c r="P11" s="147"/>
+      <c r="Q11" s="147"/>
     </row>
     <row r="12" spans="1:17">
       <c r="B12" t="s">
@@ -22836,14 +23009,14 @@
       <c r="H12" t="s">
         <v>953</v>
       </c>
-      <c r="J12" s="146"/>
-      <c r="K12" s="146"/>
-      <c r="L12" s="146"/>
-      <c r="M12" s="146"/>
-      <c r="N12" s="146"/>
-      <c r="O12" s="146"/>
-      <c r="P12" s="146"/>
-      <c r="Q12" s="146"/>
+      <c r="J12" s="147"/>
+      <c r="K12" s="147"/>
+      <c r="L12" s="147"/>
+      <c r="M12" s="147"/>
+      <c r="N12" s="147"/>
+      <c r="O12" s="147"/>
+      <c r="P12" s="147"/>
+      <c r="Q12" s="147"/>
     </row>
     <row r="13" spans="1:17">
       <c r="F13" t="s">
@@ -22855,24 +23028,24 @@
       <c r="H13" t="s">
         <v>953</v>
       </c>
-      <c r="J13" s="146"/>
-      <c r="K13" s="146"/>
-      <c r="L13" s="146"/>
-      <c r="M13" s="146"/>
-      <c r="N13" s="146"/>
-      <c r="O13" s="146"/>
-      <c r="P13" s="146"/>
-      <c r="Q13" s="146"/>
+      <c r="J13" s="147"/>
+      <c r="K13" s="147"/>
+      <c r="L13" s="147"/>
+      <c r="M13" s="147"/>
+      <c r="N13" s="147"/>
+      <c r="O13" s="147"/>
+      <c r="P13" s="147"/>
+      <c r="Q13" s="147"/>
     </row>
     <row r="14" spans="1:17">
-      <c r="J14" s="146"/>
-      <c r="K14" s="146"/>
-      <c r="L14" s="146"/>
-      <c r="M14" s="146"/>
-      <c r="N14" s="146"/>
-      <c r="O14" s="146"/>
-      <c r="P14" s="146"/>
-      <c r="Q14" s="146"/>
+      <c r="J14" s="147"/>
+      <c r="K14" s="147"/>
+      <c r="L14" s="147"/>
+      <c r="M14" s="147"/>
+      <c r="N14" s="147"/>
+      <c r="O14" s="147"/>
+      <c r="P14" s="147"/>
+      <c r="Q14" s="147"/>
     </row>
     <row r="15" spans="1:17">
       <c r="A15" t="s">
@@ -22881,27 +23054,27 @@
       <c r="C15" t="s">
         <v>949</v>
       </c>
-      <c r="J15" s="146"/>
-      <c r="K15" s="146"/>
-      <c r="L15" s="146"/>
-      <c r="M15" s="146"/>
-      <c r="N15" s="146"/>
-      <c r="O15" s="146"/>
-      <c r="P15" s="146"/>
-      <c r="Q15" s="146"/>
+      <c r="J15" s="147"/>
+      <c r="K15" s="147"/>
+      <c r="L15" s="147"/>
+      <c r="M15" s="147"/>
+      <c r="N15" s="147"/>
+      <c r="O15" s="147"/>
+      <c r="P15" s="147"/>
+      <c r="Q15" s="147"/>
     </row>
     <row r="16" spans="1:17">
       <c r="A16" t="s">
         <v>939</v>
       </c>
-      <c r="J16" s="146"/>
-      <c r="K16" s="146"/>
-      <c r="L16" s="146"/>
-      <c r="M16" s="146"/>
-      <c r="N16" s="146"/>
-      <c r="O16" s="146"/>
-      <c r="P16" s="146"/>
-      <c r="Q16" s="146"/>
+      <c r="J16" s="147"/>
+      <c r="K16" s="147"/>
+      <c r="L16" s="147"/>
+      <c r="M16" s="147"/>
+      <c r="N16" s="147"/>
+      <c r="O16" s="147"/>
+      <c r="P16" s="147"/>
+      <c r="Q16" s="147"/>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="5" t="s">
@@ -23144,19 +23317,19 @@
       <c r="E7" s="31" t="s">
         <v>449</v>
       </c>
-      <c r="F7" s="147" t="s">
+      <c r="F7" s="148" t="s">
         <v>441</v>
       </c>
-      <c r="G7" s="147"/>
-      <c r="H7" s="147"/>
-      <c r="I7" s="147"/>
-      <c r="J7" s="147"/>
-      <c r="K7" s="147"/>
-      <c r="L7" s="147"/>
-      <c r="M7" s="147"/>
-      <c r="N7" s="147"/>
-      <c r="O7" s="147"/>
-      <c r="P7" s="147"/>
+      <c r="G7" s="148"/>
+      <c r="H7" s="148"/>
+      <c r="I7" s="148"/>
+      <c r="J7" s="148"/>
+      <c r="K7" s="148"/>
+      <c r="L7" s="148"/>
+      <c r="M7" s="148"/>
+      <c r="N7" s="148"/>
+      <c r="O7" s="148"/>
+      <c r="P7" s="148"/>
     </row>
     <row r="8" spans="1:17">
       <c r="B8" s="32" t="s">
@@ -23380,40 +23553,40 @@
       <c r="A24" s="35" t="s">
         <v>455</v>
       </c>
-      <c r="B24" s="148" t="s">
+      <c r="B24" s="149" t="s">
         <v>457</v>
       </c>
-      <c r="C24" s="148"/>
-      <c r="D24" s="148"/>
-      <c r="E24" s="148"/>
-      <c r="F24" s="148"/>
-      <c r="G24" s="148"/>
+      <c r="C24" s="149"/>
+      <c r="D24" s="149"/>
+      <c r="E24" s="149"/>
+      <c r="F24" s="149"/>
+      <c r="G24" s="149"/>
     </row>
     <row r="25" spans="1:7" ht="30">
       <c r="A25" s="35" t="s">
         <v>462</v>
       </c>
-      <c r="B25" s="149" t="s">
+      <c r="B25" s="150" t="s">
         <v>464</v>
       </c>
-      <c r="C25" s="149"/>
-      <c r="D25" s="149"/>
-      <c r="E25" s="149"/>
-      <c r="F25" s="149"/>
-      <c r="G25" s="149"/>
+      <c r="C25" s="150"/>
+      <c r="D25" s="150"/>
+      <c r="E25" s="150"/>
+      <c r="F25" s="150"/>
+      <c r="G25" s="150"/>
     </row>
     <row r="26" spans="1:7" ht="159" customHeight="1">
       <c r="A26" s="35" t="s">
         <v>459</v>
       </c>
-      <c r="B26" s="148" t="s">
+      <c r="B26" s="149" t="s">
         <v>460</v>
       </c>
-      <c r="C26" s="148"/>
-      <c r="D26" s="148"/>
-      <c r="E26" s="148"/>
-      <c r="F26" s="148"/>
-      <c r="G26" s="148"/>
+      <c r="C26" s="149"/>
+      <c r="D26" s="149"/>
+      <c r="E26" s="149"/>
+      <c r="F26" s="149"/>
+      <c r="G26" s="149"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -23928,29 +24101,29 @@
       <c r="B27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="C27" s="152" t="s">
+      <c r="C27" s="153" t="s">
         <v>622</v>
       </c>
-      <c r="D27" s="153"/>
+      <c r="D27" s="154"/>
       <c r="E27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="F27" s="152" t="s">
+      <c r="F27" s="153" t="s">
         <v>622</v>
       </c>
-      <c r="G27" s="153"/>
+      <c r="G27" s="154"/>
       <c r="H27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="I27" s="152" t="s">
+      <c r="I27" s="153" t="s">
         <v>622</v>
       </c>
-      <c r="J27" s="153"/>
-      <c r="L27" s="164" t="s">
+      <c r="J27" s="154"/>
+      <c r="L27" s="165" t="s">
         <v>694</v>
       </c>
-      <c r="M27" s="164"/>
-      <c r="N27" s="164"/>
+      <c r="M27" s="165"/>
+      <c r="N27" s="165"/>
     </row>
     <row r="28" spans="1:14" ht="32.25" thickBot="1">
       <c r="A28" s="81">
@@ -23959,29 +24132,29 @@
       <c r="B28" s="69" t="s">
         <v>623</v>
       </c>
-      <c r="C28" s="150" t="s">
+      <c r="C28" s="151" t="s">
         <v>624</v>
       </c>
-      <c r="D28" s="151"/>
+      <c r="D28" s="152"/>
       <c r="E28" s="70" t="s">
         <v>645</v>
       </c>
-      <c r="F28" s="154" t="s">
+      <c r="F28" s="155" t="s">
         <v>646</v>
       </c>
-      <c r="G28" s="155"/>
+      <c r="G28" s="156"/>
       <c r="H28" s="69" t="s">
         <v>667</v>
       </c>
-      <c r="I28" s="150" t="s">
+      <c r="I28" s="151" t="s">
         <v>668</v>
       </c>
-      <c r="J28" s="151"/>
-      <c r="L28" s="165" t="s">
+      <c r="J28" s="152"/>
+      <c r="L28" s="166" t="s">
         <v>695</v>
       </c>
-      <c r="M28" s="165"/>
-      <c r="N28" s="165"/>
+      <c r="M28" s="166"/>
+      <c r="N28" s="166"/>
     </row>
     <row r="29" spans="1:14" ht="31.5" thickBot="1">
       <c r="A29" s="81">
@@ -23990,29 +24163,29 @@
       <c r="B29" s="70" t="s">
         <v>625</v>
       </c>
-      <c r="C29" s="154" t="s">
+      <c r="C29" s="155" t="s">
         <v>626</v>
       </c>
-      <c r="D29" s="155"/>
+      <c r="D29" s="156"/>
       <c r="E29" s="69" t="s">
         <v>647</v>
       </c>
-      <c r="F29" s="150" t="s">
+      <c r="F29" s="151" t="s">
         <v>648</v>
       </c>
-      <c r="G29" s="151"/>
+      <c r="G29" s="152"/>
       <c r="H29" s="70" t="s">
         <v>669</v>
       </c>
-      <c r="I29" s="158" t="s">
+      <c r="I29" s="159" t="s">
         <v>670</v>
       </c>
-      <c r="J29" s="159"/>
-      <c r="L29" s="164" t="s">
+      <c r="J29" s="160"/>
+      <c r="L29" s="165" t="s">
         <v>696</v>
       </c>
-      <c r="M29" s="164"/>
-      <c r="N29" s="164"/>
+      <c r="M29" s="165"/>
+      <c r="N29" s="165"/>
     </row>
     <row r="30" spans="1:14" ht="15.75" thickBot="1">
       <c r="A30" s="81">
@@ -24021,29 +24194,29 @@
       <c r="B30" s="69" t="s">
         <v>627</v>
       </c>
-      <c r="C30" s="150" t="s">
+      <c r="C30" s="151" t="s">
         <v>628</v>
       </c>
-      <c r="D30" s="151"/>
+      <c r="D30" s="152"/>
       <c r="E30" s="70" t="s">
         <v>649</v>
       </c>
-      <c r="F30" s="154" t="s">
+      <c r="F30" s="155" t="s">
         <v>650</v>
       </c>
-      <c r="G30" s="155"/>
+      <c r="G30" s="156"/>
       <c r="H30" s="69" t="s">
         <v>671</v>
       </c>
-      <c r="I30" s="150" t="s">
+      <c r="I30" s="151" t="s">
         <v>672</v>
       </c>
-      <c r="J30" s="151"/>
-      <c r="L30" s="165" t="s">
+      <c r="J30" s="152"/>
+      <c r="L30" s="166" t="s">
         <v>697</v>
       </c>
-      <c r="M30" s="165"/>
-      <c r="N30" s="165"/>
+      <c r="M30" s="166"/>
+      <c r="N30" s="166"/>
     </row>
     <row r="31" spans="1:14" ht="17.25" customHeight="1" thickBot="1">
       <c r="A31" s="81">
@@ -24052,29 +24225,29 @@
       <c r="B31" s="70" t="s">
         <v>629</v>
       </c>
-      <c r="C31" s="154" t="s">
+      <c r="C31" s="155" t="s">
         <v>630</v>
       </c>
-      <c r="D31" s="155"/>
+      <c r="D31" s="156"/>
       <c r="E31" s="69" t="s">
         <v>651</v>
       </c>
-      <c r="F31" s="150" t="s">
+      <c r="F31" s="151" t="s">
         <v>652</v>
       </c>
-      <c r="G31" s="151"/>
+      <c r="G31" s="152"/>
       <c r="H31" s="70" t="s">
         <v>673</v>
       </c>
-      <c r="I31" s="154" t="s">
+      <c r="I31" s="155" t="s">
         <v>674</v>
       </c>
-      <c r="J31" s="155"/>
-      <c r="L31" s="164" t="s">
+      <c r="J31" s="156"/>
+      <c r="L31" s="165" t="s">
         <v>698</v>
       </c>
-      <c r="M31" s="164"/>
-      <c r="N31" s="164"/>
+      <c r="M31" s="165"/>
+      <c r="N31" s="165"/>
     </row>
     <row r="32" spans="1:14" ht="43.5" customHeight="1" thickBot="1">
       <c r="A32" s="81">
@@ -24083,29 +24256,29 @@
       <c r="B32" s="69" t="s">
         <v>631</v>
       </c>
-      <c r="C32" s="150" t="s">
+      <c r="C32" s="151" t="s">
         <v>632</v>
       </c>
-      <c r="D32" s="151"/>
+      <c r="D32" s="152"/>
       <c r="E32" s="70" t="s">
         <v>653</v>
       </c>
-      <c r="F32" s="154" t="s">
+      <c r="F32" s="155" t="s">
         <v>654</v>
       </c>
-      <c r="G32" s="155"/>
+      <c r="G32" s="156"/>
       <c r="H32" s="69" t="s">
         <v>675</v>
       </c>
-      <c r="I32" s="150" t="s">
+      <c r="I32" s="151" t="s">
         <v>676</v>
       </c>
-      <c r="J32" s="151"/>
-      <c r="L32" s="165" t="s">
+      <c r="J32" s="152"/>
+      <c r="L32" s="166" t="s">
         <v>699</v>
       </c>
-      <c r="M32" s="165"/>
-      <c r="N32" s="165"/>
+      <c r="M32" s="166"/>
+      <c r="N32" s="166"/>
     </row>
     <row r="33" spans="1:14" ht="31.5" customHeight="1" thickBot="1">
       <c r="A33" s="81">
@@ -24114,29 +24287,29 @@
       <c r="B33" s="70" t="s">
         <v>633</v>
       </c>
-      <c r="C33" s="154" t="s">
+      <c r="C33" s="155" t="s">
         <v>634</v>
       </c>
-      <c r="D33" s="155"/>
+      <c r="D33" s="156"/>
       <c r="E33" s="69" t="s">
         <v>655</v>
       </c>
-      <c r="F33" s="150" t="s">
+      <c r="F33" s="151" t="s">
         <v>656</v>
       </c>
-      <c r="G33" s="151"/>
+      <c r="G33" s="152"/>
       <c r="H33" s="70" t="s">
         <v>677</v>
       </c>
-      <c r="I33" s="156" t="s">
+      <c r="I33" s="157" t="s">
         <v>678</v>
       </c>
-      <c r="J33" s="157"/>
-      <c r="L33" s="164" t="s">
+      <c r="J33" s="158"/>
+      <c r="L33" s="165" t="s">
         <v>700</v>
       </c>
-      <c r="M33" s="164"/>
-      <c r="N33" s="164"/>
+      <c r="M33" s="165"/>
+      <c r="N33" s="165"/>
     </row>
     <row r="34" spans="1:14" ht="28.5" customHeight="1" thickBot="1">
       <c r="A34" s="81">
@@ -24145,29 +24318,29 @@
       <c r="B34" s="69" t="s">
         <v>635</v>
       </c>
-      <c r="C34" s="150" t="s">
+      <c r="C34" s="151" t="s">
         <v>636</v>
       </c>
-      <c r="D34" s="151"/>
+      <c r="D34" s="152"/>
       <c r="E34" s="70" t="s">
         <v>657</v>
       </c>
-      <c r="F34" s="154" t="s">
+      <c r="F34" s="155" t="s">
         <v>658</v>
       </c>
-      <c r="G34" s="155"/>
+      <c r="G34" s="156"/>
       <c r="H34" s="69" t="s">
         <v>679</v>
       </c>
-      <c r="I34" s="160" t="s">
+      <c r="I34" s="161" t="s">
         <v>680</v>
       </c>
-      <c r="J34" s="161"/>
-      <c r="L34" s="165" t="s">
+      <c r="J34" s="162"/>
+      <c r="L34" s="166" t="s">
         <v>701</v>
       </c>
-      <c r="M34" s="165"/>
-      <c r="N34" s="165"/>
+      <c r="M34" s="166"/>
+      <c r="N34" s="166"/>
     </row>
     <row r="35" spans="1:14" ht="31.5" customHeight="1" thickBot="1">
       <c r="A35" s="81">
@@ -24176,29 +24349,29 @@
       <c r="B35" s="70" t="s">
         <v>637</v>
       </c>
-      <c r="C35" s="154" t="s">
+      <c r="C35" s="155" t="s">
         <v>638</v>
       </c>
-      <c r="D35" s="155"/>
+      <c r="D35" s="156"/>
       <c r="E35" s="69" t="s">
         <v>659</v>
       </c>
-      <c r="F35" s="150" t="s">
+      <c r="F35" s="151" t="s">
         <v>660</v>
       </c>
-      <c r="G35" s="151"/>
+      <c r="G35" s="152"/>
       <c r="H35" s="77" t="s">
         <v>681</v>
       </c>
-      <c r="I35" s="154" t="s">
+      <c r="I35" s="155" t="s">
         <v>682</v>
       </c>
-      <c r="J35" s="155"/>
-      <c r="L35" s="164" t="s">
+      <c r="J35" s="156"/>
+      <c r="L35" s="165" t="s">
         <v>702</v>
       </c>
-      <c r="M35" s="164"/>
-      <c r="N35" s="164"/>
+      <c r="M35" s="165"/>
+      <c r="N35" s="165"/>
     </row>
     <row r="36" spans="1:14" ht="60.75" thickBot="1">
       <c r="A36" s="81">
@@ -24207,17 +24380,17 @@
       <c r="B36" s="69" t="s">
         <v>639</v>
       </c>
-      <c r="C36" s="150" t="s">
+      <c r="C36" s="151" t="s">
         <v>640</v>
       </c>
-      <c r="D36" s="151"/>
+      <c r="D36" s="152"/>
       <c r="E36" s="70" t="s">
         <v>661</v>
       </c>
-      <c r="F36" s="154" t="s">
+      <c r="F36" s="155" t="s">
         <v>662</v>
       </c>
-      <c r="G36" s="155"/>
+      <c r="G36" s="156"/>
       <c r="H36" s="78"/>
       <c r="I36" s="71" t="s">
         <v>683</v>
@@ -24225,11 +24398,11 @@
       <c r="J36" s="72" t="s">
         <v>684</v>
       </c>
-      <c r="L36" s="165" t="s">
+      <c r="L36" s="166" t="s">
         <v>703</v>
       </c>
-      <c r="M36" s="165"/>
-      <c r="N36" s="165"/>
+      <c r="M36" s="166"/>
+      <c r="N36" s="166"/>
     </row>
     <row r="37" spans="1:14" ht="75.75" thickBot="1">
       <c r="A37" s="81">
@@ -24238,17 +24411,17 @@
       <c r="B37" s="70" t="s">
         <v>641</v>
       </c>
-      <c r="C37" s="154" t="s">
+      <c r="C37" s="155" t="s">
         <v>642</v>
       </c>
-      <c r="D37" s="155"/>
+      <c r="D37" s="156"/>
       <c r="E37" s="69" t="s">
         <v>663</v>
       </c>
-      <c r="F37" s="150" t="s">
+      <c r="F37" s="151" t="s">
         <v>664</v>
       </c>
-      <c r="G37" s="151"/>
+      <c r="G37" s="152"/>
       <c r="H37" s="78"/>
       <c r="I37" s="73" t="s">
         <v>685</v>
@@ -24264,17 +24437,17 @@
       <c r="B38" s="69" t="s">
         <v>643</v>
       </c>
-      <c r="C38" s="150" t="s">
+      <c r="C38" s="151" t="s">
         <v>644</v>
       </c>
-      <c r="D38" s="151"/>
+      <c r="D38" s="152"/>
       <c r="E38" s="70" t="s">
         <v>665</v>
       </c>
-      <c r="F38" s="154" t="s">
+      <c r="F38" s="155" t="s">
         <v>666</v>
       </c>
-      <c r="G38" s="155"/>
+      <c r="G38" s="156"/>
       <c r="H38" s="78"/>
       <c r="I38" s="75" t="s">
         <v>687</v>
@@ -24290,22 +24463,22 @@
       <c r="B39" s="70" t="s">
         <v>692</v>
       </c>
-      <c r="C39" s="156" t="s">
+      <c r="C39" s="157" t="s">
         <v>693</v>
       </c>
-      <c r="D39" s="157"/>
+      <c r="D39" s="158"/>
       <c r="E39" s="69" t="s">
         <v>690</v>
       </c>
-      <c r="F39" s="160" t="s">
+      <c r="F39" s="161" t="s">
         <v>691</v>
       </c>
-      <c r="G39" s="161"/>
+      <c r="G39" s="162"/>
       <c r="H39" s="79"/>
-      <c r="I39" s="162" t="s">
+      <c r="I39" s="163" t="s">
         <v>689</v>
       </c>
-      <c r="J39" s="163"/>
+      <c r="J39" s="164"/>
     </row>
     <row r="40" spans="1:14" ht="58.5" customHeight="1"/>
     <row r="42" spans="1:14" ht="31.5" customHeight="1"/>
@@ -24501,10 +24674,10 @@
       <c r="F7" s="112" t="s">
         <v>916</v>
       </c>
-      <c r="I7" s="184" t="s">
+      <c r="I7" s="185" t="s">
         <v>1168</v>
       </c>
-      <c r="J7" s="184"/>
+      <c r="J7" s="185"/>
       <c r="L7" s="49" t="s">
         <v>601</v>
       </c>
@@ -24522,7 +24695,7 @@
       <c r="D8" s="32" t="s">
         <v>582</v>
       </c>
-      <c r="E8" s="185" t="s">
+      <c r="E8" s="186" t="s">
         <v>583</v>
       </c>
       <c r="F8" s="36" t="s">
@@ -24844,10 +25017,10 @@
       <c r="L20" s="115" t="s">
         <v>568</v>
       </c>
-      <c r="M20" s="166" t="s">
+      <c r="M20" s="167" t="s">
         <v>918</v>
       </c>
-      <c r="N20" s="167"/>
+      <c r="N20" s="168"/>
     </row>
     <row r="21" spans="1:14">
       <c r="B21" s="85" t="s">
@@ -24965,29 +25138,29 @@
       <c r="B27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="C27" s="152" t="s">
+      <c r="C27" s="153" t="s">
         <v>622</v>
       </c>
-      <c r="D27" s="153"/>
+      <c r="D27" s="154"/>
       <c r="E27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="F27" s="152" t="s">
+      <c r="F27" s="153" t="s">
         <v>622</v>
       </c>
-      <c r="G27" s="153"/>
+      <c r="G27" s="154"/>
       <c r="H27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="I27" s="152" t="s">
+      <c r="I27" s="153" t="s">
         <v>622</v>
       </c>
-      <c r="J27" s="153"/>
-      <c r="L27" s="164" t="s">
+      <c r="J27" s="154"/>
+      <c r="L27" s="165" t="s">
         <v>694</v>
       </c>
-      <c r="M27" s="164"/>
-      <c r="N27" s="164"/>
+      <c r="M27" s="165"/>
+      <c r="N27" s="165"/>
     </row>
     <row r="28" spans="1:14" ht="49.5" customHeight="1" thickBot="1">
       <c r="A28" s="81">
@@ -24996,29 +25169,29 @@
       <c r="B28" s="69" t="s">
         <v>623</v>
       </c>
-      <c r="C28" s="150" t="s">
+      <c r="C28" s="151" t="s">
         <v>624</v>
       </c>
-      <c r="D28" s="151"/>
+      <c r="D28" s="152"/>
       <c r="E28" s="70" t="s">
         <v>645</v>
       </c>
-      <c r="F28" s="154" t="s">
+      <c r="F28" s="155" t="s">
         <v>1180</v>
       </c>
-      <c r="G28" s="155"/>
+      <c r="G28" s="156"/>
       <c r="H28" s="69" t="s">
         <v>667</v>
       </c>
-      <c r="I28" s="150" t="s">
+      <c r="I28" s="151" t="s">
         <v>668</v>
       </c>
-      <c r="J28" s="151"/>
-      <c r="L28" s="165" t="s">
+      <c r="J28" s="152"/>
+      <c r="L28" s="166" t="s">
         <v>695</v>
       </c>
-      <c r="M28" s="165"/>
-      <c r="N28" s="165"/>
+      <c r="M28" s="166"/>
+      <c r="N28" s="166"/>
     </row>
     <row r="29" spans="1:14" ht="31.5" thickBot="1">
       <c r="A29" s="81">
@@ -25027,29 +25200,29 @@
       <c r="B29" s="70" t="s">
         <v>625</v>
       </c>
-      <c r="C29" s="154" t="s">
+      <c r="C29" s="155" t="s">
         <v>626</v>
       </c>
-      <c r="D29" s="155"/>
+      <c r="D29" s="156"/>
       <c r="E29" s="69" t="s">
         <v>647</v>
       </c>
-      <c r="F29" s="150" t="s">
+      <c r="F29" s="151" t="s">
         <v>648</v>
       </c>
-      <c r="G29" s="151"/>
+      <c r="G29" s="152"/>
       <c r="H29" s="70" t="s">
         <v>669</v>
       </c>
-      <c r="I29" s="158" t="s">
+      <c r="I29" s="159" t="s">
         <v>670</v>
       </c>
-      <c r="J29" s="159"/>
-      <c r="L29" s="164" t="s">
+      <c r="J29" s="160"/>
+      <c r="L29" s="165" t="s">
         <v>696</v>
       </c>
-      <c r="M29" s="164"/>
-      <c r="N29" s="164"/>
+      <c r="M29" s="165"/>
+      <c r="N29" s="165"/>
     </row>
     <row r="30" spans="1:14" ht="15.75" thickBot="1">
       <c r="A30" s="81">
@@ -25058,29 +25231,29 @@
       <c r="B30" s="69" t="s">
         <v>627</v>
       </c>
-      <c r="C30" s="150" t="s">
+      <c r="C30" s="151" t="s">
         <v>628</v>
       </c>
-      <c r="D30" s="151"/>
+      <c r="D30" s="152"/>
       <c r="E30" s="70" t="s">
         <v>649</v>
       </c>
-      <c r="F30" s="154" t="s">
+      <c r="F30" s="155" t="s">
         <v>650</v>
       </c>
-      <c r="G30" s="155"/>
+      <c r="G30" s="156"/>
       <c r="H30" s="69" t="s">
         <v>671</v>
       </c>
-      <c r="I30" s="150" t="s">
+      <c r="I30" s="151" t="s">
         <v>672</v>
       </c>
-      <c r="J30" s="151"/>
-      <c r="L30" s="165" t="s">
+      <c r="J30" s="152"/>
+      <c r="L30" s="166" t="s">
         <v>697</v>
       </c>
-      <c r="M30" s="165"/>
-      <c r="N30" s="165"/>
+      <c r="M30" s="166"/>
+      <c r="N30" s="166"/>
     </row>
     <row r="31" spans="1:14" ht="17.25" customHeight="1" thickBot="1">
       <c r="A31" s="81">
@@ -25089,29 +25262,29 @@
       <c r="B31" s="70" t="s">
         <v>629</v>
       </c>
-      <c r="C31" s="154" t="s">
+      <c r="C31" s="155" t="s">
         <v>630</v>
       </c>
-      <c r="D31" s="155"/>
+      <c r="D31" s="156"/>
       <c r="E31" s="69" t="s">
         <v>651</v>
       </c>
-      <c r="F31" s="150" t="s">
+      <c r="F31" s="151" t="s">
         <v>652</v>
       </c>
-      <c r="G31" s="151"/>
+      <c r="G31" s="152"/>
       <c r="H31" s="70" t="s">
         <v>673</v>
       </c>
-      <c r="I31" s="154" t="s">
+      <c r="I31" s="155" t="s">
         <v>674</v>
       </c>
-      <c r="J31" s="155"/>
-      <c r="L31" s="164" t="s">
+      <c r="J31" s="156"/>
+      <c r="L31" s="165" t="s">
         <v>698</v>
       </c>
-      <c r="M31" s="164"/>
-      <c r="N31" s="164"/>
+      <c r="M31" s="165"/>
+      <c r="N31" s="165"/>
     </row>
     <row r="32" spans="1:14" ht="43.5" customHeight="1" thickBot="1">
       <c r="A32" s="81">
@@ -25120,29 +25293,29 @@
       <c r="B32" s="69" t="s">
         <v>631</v>
       </c>
-      <c r="C32" s="150" t="s">
+      <c r="C32" s="151" t="s">
         <v>632</v>
       </c>
-      <c r="D32" s="151"/>
+      <c r="D32" s="152"/>
       <c r="E32" s="70" t="s">
         <v>653</v>
       </c>
-      <c r="F32" s="154" t="s">
+      <c r="F32" s="155" t="s">
         <v>654</v>
       </c>
-      <c r="G32" s="155"/>
+      <c r="G32" s="156"/>
       <c r="H32" s="69" t="s">
         <v>675</v>
       </c>
-      <c r="I32" s="150" t="s">
+      <c r="I32" s="151" t="s">
         <v>676</v>
       </c>
-      <c r="J32" s="151"/>
-      <c r="L32" s="165" t="s">
+      <c r="J32" s="152"/>
+      <c r="L32" s="166" t="s">
         <v>699</v>
       </c>
-      <c r="M32" s="165"/>
-      <c r="N32" s="165"/>
+      <c r="M32" s="166"/>
+      <c r="N32" s="166"/>
     </row>
     <row r="33" spans="1:14" ht="31.5" customHeight="1" thickBot="1">
       <c r="A33" s="81">
@@ -25151,29 +25324,29 @@
       <c r="B33" s="70" t="s">
         <v>633</v>
       </c>
-      <c r="C33" s="154" t="s">
+      <c r="C33" s="155" t="s">
         <v>634</v>
       </c>
-      <c r="D33" s="155"/>
+      <c r="D33" s="156"/>
       <c r="E33" s="69" t="s">
         <v>655</v>
       </c>
-      <c r="F33" s="150" t="s">
+      <c r="F33" s="151" t="s">
         <v>656</v>
       </c>
-      <c r="G33" s="151"/>
+      <c r="G33" s="152"/>
       <c r="H33" s="70" t="s">
         <v>677</v>
       </c>
-      <c r="I33" s="156" t="s">
+      <c r="I33" s="157" t="s">
         <v>678</v>
       </c>
-      <c r="J33" s="157"/>
-      <c r="L33" s="164" t="s">
+      <c r="J33" s="158"/>
+      <c r="L33" s="165" t="s">
         <v>700</v>
       </c>
-      <c r="M33" s="164"/>
-      <c r="N33" s="164"/>
+      <c r="M33" s="165"/>
+      <c r="N33" s="165"/>
     </row>
     <row r="34" spans="1:14" ht="28.5" customHeight="1" thickBot="1">
       <c r="A34" s="81">
@@ -25182,29 +25355,29 @@
       <c r="B34" s="69" t="s">
         <v>635</v>
       </c>
-      <c r="C34" s="150" t="s">
+      <c r="C34" s="151" t="s">
         <v>636</v>
       </c>
-      <c r="D34" s="151"/>
+      <c r="D34" s="152"/>
       <c r="E34" s="70" t="s">
         <v>657</v>
       </c>
-      <c r="F34" s="154" t="s">
+      <c r="F34" s="155" t="s">
         <v>658</v>
       </c>
-      <c r="G34" s="155"/>
+      <c r="G34" s="156"/>
       <c r="H34" s="69" t="s">
         <v>679</v>
       </c>
-      <c r="I34" s="160" t="s">
+      <c r="I34" s="161" t="s">
         <v>680</v>
       </c>
-      <c r="J34" s="161"/>
-      <c r="L34" s="165" t="s">
+      <c r="J34" s="162"/>
+      <c r="L34" s="166" t="s">
         <v>701</v>
       </c>
-      <c r="M34" s="165"/>
-      <c r="N34" s="165"/>
+      <c r="M34" s="166"/>
+      <c r="N34" s="166"/>
     </row>
     <row r="35" spans="1:14" ht="31.5" customHeight="1" thickBot="1">
       <c r="A35" s="81">
@@ -25213,29 +25386,29 @@
       <c r="B35" s="70" t="s">
         <v>637</v>
       </c>
-      <c r="C35" s="154" t="s">
+      <c r="C35" s="155" t="s">
         <v>638</v>
       </c>
-      <c r="D35" s="155"/>
+      <c r="D35" s="156"/>
       <c r="E35" s="69" t="s">
         <v>659</v>
       </c>
-      <c r="F35" s="150" t="s">
+      <c r="F35" s="151" t="s">
         <v>660</v>
       </c>
-      <c r="G35" s="151"/>
+      <c r="G35" s="152"/>
       <c r="H35" s="77" t="s">
         <v>681</v>
       </c>
-      <c r="I35" s="154" t="s">
+      <c r="I35" s="155" t="s">
         <v>682</v>
       </c>
-      <c r="J35" s="155"/>
-      <c r="L35" s="164" t="s">
+      <c r="J35" s="156"/>
+      <c r="L35" s="165" t="s">
         <v>702</v>
       </c>
-      <c r="M35" s="164"/>
-      <c r="N35" s="164"/>
+      <c r="M35" s="165"/>
+      <c r="N35" s="165"/>
     </row>
     <row r="36" spans="1:14" ht="60.75" thickBot="1">
       <c r="A36" s="81">
@@ -25244,17 +25417,17 @@
       <c r="B36" s="69" t="s">
         <v>639</v>
       </c>
-      <c r="C36" s="150" t="s">
+      <c r="C36" s="151" t="s">
         <v>640</v>
       </c>
-      <c r="D36" s="151"/>
+      <c r="D36" s="152"/>
       <c r="E36" s="70" t="s">
         <v>661</v>
       </c>
-      <c r="F36" s="154" t="s">
+      <c r="F36" s="155" t="s">
         <v>662</v>
       </c>
-      <c r="G36" s="155"/>
+      <c r="G36" s="156"/>
       <c r="H36" s="78"/>
       <c r="I36" s="71" t="s">
         <v>683</v>
@@ -25262,11 +25435,11 @@
       <c r="J36" s="72" t="s">
         <v>684</v>
       </c>
-      <c r="L36" s="165" t="s">
+      <c r="L36" s="166" t="s">
         <v>703</v>
       </c>
-      <c r="M36" s="165"/>
-      <c r="N36" s="165"/>
+      <c r="M36" s="166"/>
+      <c r="N36" s="166"/>
     </row>
     <row r="37" spans="1:14" ht="75.75" thickBot="1">
       <c r="A37" s="81">
@@ -25275,17 +25448,17 @@
       <c r="B37" s="70" t="s">
         <v>641</v>
       </c>
-      <c r="C37" s="154" t="s">
+      <c r="C37" s="155" t="s">
         <v>642</v>
       </c>
-      <c r="D37" s="155"/>
+      <c r="D37" s="156"/>
       <c r="E37" s="69" t="s">
         <v>663</v>
       </c>
-      <c r="F37" s="150" t="s">
+      <c r="F37" s="151" t="s">
         <v>664</v>
       </c>
-      <c r="G37" s="151"/>
+      <c r="G37" s="152"/>
       <c r="H37" s="78"/>
       <c r="I37" s="73" t="s">
         <v>685</v>
@@ -25301,17 +25474,17 @@
       <c r="B38" s="69" t="s">
         <v>643</v>
       </c>
-      <c r="C38" s="150" t="s">
+      <c r="C38" s="151" t="s">
         <v>644</v>
       </c>
-      <c r="D38" s="151"/>
+      <c r="D38" s="152"/>
       <c r="E38" s="70" t="s">
         <v>665</v>
       </c>
-      <c r="F38" s="154" t="s">
+      <c r="F38" s="155" t="s">
         <v>666</v>
       </c>
-      <c r="G38" s="155"/>
+      <c r="G38" s="156"/>
       <c r="H38" s="78"/>
       <c r="I38" s="75" t="s">
         <v>687</v>
@@ -25327,22 +25500,22 @@
       <c r="B39" s="70" t="s">
         <v>692</v>
       </c>
-      <c r="C39" s="156" t="s">
+      <c r="C39" s="157" t="s">
         <v>693</v>
       </c>
-      <c r="D39" s="157"/>
+      <c r="D39" s="158"/>
       <c r="E39" s="69" t="s">
         <v>690</v>
       </c>
-      <c r="F39" s="160" t="s">
+      <c r="F39" s="161" t="s">
         <v>691</v>
       </c>
-      <c r="G39" s="161"/>
+      <c r="G39" s="162"/>
       <c r="H39" s="79"/>
-      <c r="I39" s="162" t="s">
+      <c r="I39" s="163" t="s">
         <v>689</v>
       </c>
-      <c r="J39" s="163"/>
+      <c r="J39" s="164"/>
     </row>
     <row r="40" spans="1:14" ht="58.5" customHeight="1"/>
     <row r="41" spans="1:14">

--- a/2020_LogAnalyzer_Leeheesuk.xlsx
+++ b/2020_LogAnalyzer_Leeheesuk.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="22827"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEB160B1-85AF-44B1-8D7E-157372E211A5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7C76806-779E-42C6-8F1E-B1C79AF713D3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" firstSheet="8" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" firstSheet="6" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UI" sheetId="7" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2042" uniqueCount="1284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2043" uniqueCount="1287">
   <si>
     <t>구분</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -5710,10 +5710,19 @@
     <t>IP로 distinct 한 것</t>
   </si>
   <si>
-    <t>추가필요?</t>
-  </si>
-  <si>
     <t>Visits Count  Top5</t>
+  </si>
+  <si>
+    <t>Top User Agents</t>
+  </si>
+  <si>
+    <t>추가완료</t>
+  </si>
+  <si>
+    <t>최다접속 Referers</t>
+  </si>
+  <si>
+    <t>의미가 없다</t>
   </si>
 </sst>
 </file>
@@ -6376,7 +6385,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="215">
+  <cellXfs count="216">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6956,6 +6965,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -17445,7 +17457,7 @@
         <v>336</v>
       </c>
       <c r="N20" s="98" t="s">
-        <v>369</v>
+        <v>1285</v>
       </c>
       <c r="O20" s="99" t="s">
         <v>1265</v>
@@ -17559,7 +17571,9 @@
       <c r="P23" s="100" t="s">
         <v>964</v>
       </c>
-      <c r="Q23" s="91"/>
+      <c r="Q23" s="215" t="s">
+        <v>1286</v>
+      </c>
     </row>
     <row r="24" spans="1:17">
       <c r="A24" s="143"/>
@@ -17568,7 +17582,7 @@
       <c r="D24" s="170"/>
       <c r="E24" s="8"/>
       <c r="F24" s="9" t="s">
-        <v>337</v>
+        <v>1283</v>
       </c>
       <c r="G24" s="13" t="s">
         <v>370</v>
@@ -17582,7 +17596,7 @@
       <c r="J24" s="10"/>
       <c r="K24" s="10"/>
       <c r="M24" s="214" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="N24" s="98" t="s">
         <v>371</v>
@@ -17857,7 +17871,7 @@
         <v>1281</v>
       </c>
       <c r="O33" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="34" spans="1:15" ht="16.5" customHeight="1">

--- a/2020_LogAnalyzer_Leeheesuk.xlsx
+++ b/2020_LogAnalyzer_Leeheesuk.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="22827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="23001"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7C76806-779E-42C6-8F1E-B1C79AF713D3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E0E0297-38EB-48A6-85F7-0A10846F7979}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" firstSheet="6" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" firstSheet="9" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UI" sheetId="7" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2043" uniqueCount="1287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2042" uniqueCount="1288">
   <si>
     <t>구분</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -5723,6 +5723,9 @@
   </si>
   <si>
     <t>의미가 없다</t>
+  </si>
+  <si>
+    <t>LogFormat "%h %l %u %t \"%r\" %&gt;s %b" common</t>
   </si>
 </sst>
 </file>
@@ -6703,9 +6706,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6726,6 +6726,78 @@
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -6781,11 +6853,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -6797,6 +6869,24 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6811,23 +6901,8 @@
     <xf numFmtId="0" fontId="23" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -6845,6 +6920,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6874,24 +6958,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -6901,74 +6967,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -16301,51 +16304,51 @@
     </row>
     <row r="17" spans="1:13">
       <c r="J17" s="19"/>
-      <c r="K17" s="133" t="s">
+      <c r="K17" s="158" t="s">
         <v>537</v>
       </c>
-      <c r="L17" s="134"/>
-      <c r="M17" s="135"/>
+      <c r="L17" s="159"/>
+      <c r="M17" s="160"/>
     </row>
     <row r="18" spans="1:13">
       <c r="J18" s="19">
         <v>1</v>
       </c>
-      <c r="K18" s="136" t="s">
+      <c r="K18" s="161" t="s">
         <v>538</v>
       </c>
-      <c r="L18" s="137"/>
-      <c r="M18" s="138"/>
+      <c r="L18" s="162"/>
+      <c r="M18" s="163"/>
     </row>
     <row r="19" spans="1:13">
       <c r="J19" s="19">
         <v>2</v>
       </c>
-      <c r="K19" s="136" t="s">
+      <c r="K19" s="161" t="s">
         <v>539</v>
       </c>
-      <c r="L19" s="137"/>
-      <c r="M19" s="138"/>
+      <c r="L19" s="162"/>
+      <c r="M19" s="163"/>
     </row>
     <row r="20" spans="1:13">
       <c r="J20" s="19">
         <v>3</v>
       </c>
-      <c r="K20" s="136" t="s">
+      <c r="K20" s="161" t="s">
         <v>540</v>
       </c>
-      <c r="L20" s="137"/>
-      <c r="M20" s="138"/>
+      <c r="L20" s="162"/>
+      <c r="M20" s="163"/>
     </row>
     <row r="21" spans="1:13">
       <c r="J21" s="19">
         <v>4</v>
       </c>
-      <c r="K21" s="136" t="s">
+      <c r="K21" s="161" t="s">
         <v>541</v>
       </c>
-      <c r="L21" s="137"/>
-      <c r="M21" s="138"/>
+      <c r="L21" s="162"/>
+      <c r="M21" s="163"/>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="43" t="s">
@@ -16918,7 +16921,7 @@
     <col min="6" max="6" width="31.85546875" customWidth="1"/>
     <col min="7" max="7" width="34.42578125" customWidth="1"/>
     <col min="8" max="8" width="10.42578125" customWidth="1"/>
-    <col min="9" max="9" width="10.140625" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" style="56" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.85546875" style="56" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="27.140625" customWidth="1"/>
@@ -16966,16 +16969,16 @@
       </c>
     </row>
     <row r="2" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A2" s="169" t="s">
+      <c r="A2" s="195" t="s">
         <v>504</v>
       </c>
-      <c r="B2" s="175" t="s">
+      <c r="B2" s="204" t="s">
         <v>506</v>
       </c>
-      <c r="C2" s="169" t="s">
+      <c r="C2" s="195" t="s">
         <v>508</v>
       </c>
-      <c r="D2" s="169" t="s">
+      <c r="D2" s="195" t="s">
         <v>556</v>
       </c>
       <c r="E2" s="8"/>
@@ -16988,7 +16991,7 @@
       <c r="H2" s="10">
         <v>1</v>
       </c>
-      <c r="I2" s="123">
+      <c r="I2" s="215">
         <v>44043</v>
       </c>
       <c r="J2" s="10"/>
@@ -16998,10 +17001,10 @@
       </c>
     </row>
     <row r="3" spans="1:17">
-      <c r="A3" s="143"/>
-      <c r="B3" s="176"/>
-      <c r="C3" s="170"/>
-      <c r="D3" s="170"/>
+      <c r="A3" s="168"/>
+      <c r="B3" s="205"/>
+      <c r="C3" s="196"/>
+      <c r="D3" s="196"/>
       <c r="E3" s="11"/>
       <c r="F3" s="9" t="s">
         <v>310</v>
@@ -17012,7 +17015,9 @@
       <c r="H3" s="12">
         <v>2</v>
       </c>
-      <c r="I3" s="123"/>
+      <c r="I3" s="215">
+        <v>44074</v>
+      </c>
       <c r="J3" s="10"/>
       <c r="K3" s="10"/>
       <c r="M3" s="19" t="s">
@@ -17020,10 +17025,10 @@
       </c>
     </row>
     <row r="4" spans="1:17">
-      <c r="A4" s="143"/>
-      <c r="B4" s="176"/>
-      <c r="C4" s="170"/>
-      <c r="D4" s="171"/>
+      <c r="A4" s="168"/>
+      <c r="B4" s="205"/>
+      <c r="C4" s="196"/>
+      <c r="D4" s="197"/>
       <c r="E4" s="11"/>
       <c r="F4" s="9" t="s">
         <v>311</v>
@@ -17031,17 +17036,17 @@
       <c r="G4" s="9" t="s">
         <v>358</v>
       </c>
-      <c r="H4" s="12">
-        <v>2</v>
-      </c>
-      <c r="I4" s="123"/>
+      <c r="H4" s="12" t="s">
+        <v>965</v>
+      </c>
+      <c r="I4" s="215"/>
       <c r="J4" s="10"/>
       <c r="K4" s="10"/>
     </row>
     <row r="5" spans="1:17">
-      <c r="A5" s="143"/>
-      <c r="B5" s="176"/>
-      <c r="C5" s="171"/>
+      <c r="A5" s="168"/>
+      <c r="B5" s="205"/>
+      <c r="C5" s="197"/>
       <c r="D5" s="46" t="s">
         <v>555</v>
       </c>
@@ -17055,7 +17060,7 @@
       <c r="H5" s="12" t="s">
         <v>962</v>
       </c>
-      <c r="I5" s="123">
+      <c r="I5" s="215">
         <v>44043</v>
       </c>
       <c r="J5" s="10" t="s">
@@ -17064,12 +17069,12 @@
       <c r="K5" s="10"/>
     </row>
     <row r="6" spans="1:17">
-      <c r="A6" s="143"/>
-      <c r="B6" s="176"/>
-      <c r="C6" s="169" t="s">
+      <c r="A6" s="168"/>
+      <c r="B6" s="205"/>
+      <c r="C6" s="195" t="s">
         <v>507</v>
       </c>
-      <c r="D6" s="169" t="s">
+      <c r="D6" s="195" t="s">
         <v>511</v>
       </c>
       <c r="E6" s="11"/>
@@ -17082,17 +17087,17 @@
       <c r="H6" s="12" t="s">
         <v>963</v>
       </c>
-      <c r="I6" s="123">
+      <c r="I6" s="215">
         <v>44043</v>
       </c>
       <c r="J6" s="10"/>
       <c r="K6" s="10"/>
     </row>
     <row r="7" spans="1:17">
-      <c r="A7" s="143"/>
-      <c r="B7" s="176"/>
-      <c r="C7" s="170"/>
-      <c r="D7" s="170"/>
+      <c r="A7" s="168"/>
+      <c r="B7" s="205"/>
+      <c r="C7" s="196"/>
+      <c r="D7" s="196"/>
       <c r="E7" s="11"/>
       <c r="F7" s="9" t="s">
         <v>313</v>
@@ -17103,17 +17108,17 @@
       <c r="H7" s="12">
         <v>1</v>
       </c>
-      <c r="I7" s="123">
+      <c r="I7" s="215">
         <v>44043</v>
       </c>
       <c r="J7" s="10"/>
       <c r="K7" s="10"/>
     </row>
     <row r="8" spans="1:17">
-      <c r="A8" s="143"/>
-      <c r="B8" s="176"/>
-      <c r="C8" s="170"/>
-      <c r="D8" s="170"/>
+      <c r="A8" s="168"/>
+      <c r="B8" s="205"/>
+      <c r="C8" s="196"/>
+      <c r="D8" s="196"/>
       <c r="E8" s="11"/>
       <c r="F8" s="9" t="s">
         <v>314</v>
@@ -17124,17 +17129,17 @@
       <c r="H8" s="12">
         <v>1</v>
       </c>
-      <c r="I8" s="123">
+      <c r="I8" s="215">
         <v>44043</v>
       </c>
       <c r="J8" s="10"/>
       <c r="K8" s="10"/>
     </row>
     <row r="9" spans="1:17">
-      <c r="A9" s="143"/>
-      <c r="B9" s="176"/>
-      <c r="C9" s="170"/>
-      <c r="D9" s="170"/>
+      <c r="A9" s="168"/>
+      <c r="B9" s="205"/>
+      <c r="C9" s="196"/>
+      <c r="D9" s="196"/>
       <c r="E9" s="8"/>
       <c r="F9" s="9" t="s">
         <v>345</v>
@@ -17145,17 +17150,17 @@
       <c r="H9" s="10">
         <v>1</v>
       </c>
-      <c r="I9" s="123">
+      <c r="I9" s="215">
         <v>44043</v>
       </c>
       <c r="J9" s="10"/>
       <c r="K9" s="10"/>
     </row>
     <row r="10" spans="1:17">
-      <c r="A10" s="143"/>
-      <c r="B10" s="176"/>
-      <c r="C10" s="170"/>
-      <c r="D10" s="170"/>
+      <c r="A10" s="168"/>
+      <c r="B10" s="205"/>
+      <c r="C10" s="196"/>
+      <c r="D10" s="196"/>
       <c r="E10" s="8"/>
       <c r="F10" s="9" t="s">
         <v>346</v>
@@ -17166,17 +17171,17 @@
       <c r="H10" s="10">
         <v>1</v>
       </c>
-      <c r="I10" s="123">
+      <c r="I10" s="215">
         <v>44043</v>
       </c>
       <c r="J10" s="10"/>
       <c r="K10" s="10"/>
     </row>
     <row r="11" spans="1:17">
-      <c r="A11" s="143"/>
-      <c r="B11" s="176"/>
-      <c r="C11" s="170"/>
-      <c r="D11" s="170"/>
+      <c r="A11" s="168"/>
+      <c r="B11" s="205"/>
+      <c r="C11" s="196"/>
+      <c r="D11" s="196"/>
       <c r="E11" s="8"/>
       <c r="F11" s="9" t="s">
         <v>315</v>
@@ -17187,17 +17192,17 @@
       <c r="H11" s="10">
         <v>1</v>
       </c>
-      <c r="I11" s="123">
+      <c r="I11" s="215">
         <v>44043</v>
       </c>
       <c r="J11" s="10"/>
       <c r="K11" s="10"/>
     </row>
     <row r="12" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A12" s="143"/>
-      <c r="B12" s="176"/>
-      <c r="C12" s="170"/>
-      <c r="D12" s="170"/>
+      <c r="A12" s="168"/>
+      <c r="B12" s="205"/>
+      <c r="C12" s="196"/>
+      <c r="D12" s="196"/>
       <c r="E12" s="8"/>
       <c r="F12" s="9" t="s">
         <v>347</v>
@@ -17208,17 +17213,17 @@
       <c r="H12" s="10">
         <v>1</v>
       </c>
-      <c r="I12" s="123">
+      <c r="I12" s="215">
         <v>44043</v>
       </c>
       <c r="J12" s="10"/>
       <c r="K12" s="10"/>
     </row>
     <row r="13" spans="1:17" ht="30">
-      <c r="A13" s="143"/>
-      <c r="B13" s="176"/>
-      <c r="C13" s="170"/>
-      <c r="D13" s="170"/>
+      <c r="A13" s="168"/>
+      <c r="B13" s="205"/>
+      <c r="C13" s="196"/>
+      <c r="D13" s="196"/>
       <c r="E13" s="11"/>
       <c r="F13" s="9" t="s">
         <v>316</v>
@@ -17229,7 +17234,7 @@
       <c r="H13" s="12">
         <v>3</v>
       </c>
-      <c r="I13" s="123"/>
+      <c r="I13" s="215"/>
       <c r="J13" s="10" t="s">
         <v>563</v>
       </c>
@@ -17239,10 +17244,10 @@
       </c>
     </row>
     <row r="14" spans="1:17">
-      <c r="A14" s="143"/>
-      <c r="B14" s="176"/>
-      <c r="C14" s="170"/>
-      <c r="D14" s="171"/>
+      <c r="A14" s="168"/>
+      <c r="B14" s="205"/>
+      <c r="C14" s="196"/>
+      <c r="D14" s="197"/>
       <c r="E14" s="11"/>
       <c r="F14" s="9" t="s">
         <v>318</v>
@@ -17253,14 +17258,16 @@
       <c r="H14" s="12">
         <v>2</v>
       </c>
-      <c r="I14" s="123"/>
+      <c r="I14" s="215">
+        <v>44074</v>
+      </c>
       <c r="J14" s="10"/>
       <c r="K14" s="10"/>
     </row>
     <row r="15" spans="1:17" ht="30">
-      <c r="A15" s="143"/>
-      <c r="B15" s="176"/>
-      <c r="C15" s="170"/>
+      <c r="A15" s="168"/>
+      <c r="B15" s="205"/>
+      <c r="C15" s="196"/>
       <c r="D15" s="22" t="s">
         <v>512</v>
       </c>
@@ -17274,15 +17281,15 @@
       <c r="H15" s="12">
         <v>1</v>
       </c>
-      <c r="I15" s="123">
+      <c r="I15" s="215">
         <v>44043</v>
       </c>
       <c r="J15" s="10"/>
       <c r="K15" s="10"/>
-      <c r="M15" s="204" t="s">
+      <c r="M15" s="200" t="s">
         <v>852</v>
       </c>
-      <c r="N15" s="205"/>
+      <c r="N15" s="201"/>
       <c r="O15" s="118" t="s">
         <v>1260</v>
       </c>
@@ -17292,12 +17299,12 @@
       </c>
     </row>
     <row r="16" spans="1:17" ht="30">
-      <c r="A16" s="143"/>
-      <c r="B16" s="176"/>
-      <c r="C16" s="169" t="s">
+      <c r="A16" s="168"/>
+      <c r="B16" s="205"/>
+      <c r="C16" s="195" t="s">
         <v>509</v>
       </c>
-      <c r="D16" s="169" t="s">
+      <c r="D16" s="195" t="s">
         <v>513</v>
       </c>
       <c r="E16" s="11"/>
@@ -17310,7 +17317,7 @@
       <c r="H16" s="12">
         <v>1</v>
       </c>
-      <c r="I16" s="123">
+      <c r="I16" s="215">
         <v>44043</v>
       </c>
       <c r="J16" s="10"/>
@@ -17332,10 +17339,10 @@
       </c>
     </row>
     <row r="17" spans="1:17">
-      <c r="A17" s="143"/>
-      <c r="B17" s="176"/>
-      <c r="C17" s="170"/>
-      <c r="D17" s="170"/>
+      <c r="A17" s="168"/>
+      <c r="B17" s="205"/>
+      <c r="C17" s="196"/>
+      <c r="D17" s="196"/>
       <c r="E17" s="19"/>
       <c r="F17" s="9" t="s">
         <v>364</v>
@@ -17346,7 +17353,7 @@
       <c r="H17" s="12">
         <v>1</v>
       </c>
-      <c r="I17" s="123">
+      <c r="I17" s="215">
         <v>44043</v>
       </c>
       <c r="J17" s="10"/>
@@ -17365,10 +17372,10 @@
       </c>
     </row>
     <row r="18" spans="1:17">
-      <c r="A18" s="143"/>
-      <c r="B18" s="176"/>
-      <c r="C18" s="170"/>
-      <c r="D18" s="170"/>
+      <c r="A18" s="168"/>
+      <c r="B18" s="205"/>
+      <c r="C18" s="196"/>
+      <c r="D18" s="196"/>
       <c r="E18" s="19"/>
       <c r="F18" s="48" t="s">
         <v>559</v>
@@ -17379,7 +17386,7 @@
       <c r="H18" s="10">
         <v>1</v>
       </c>
-      <c r="I18" s="123">
+      <c r="I18" s="215">
         <v>44043</v>
       </c>
       <c r="J18" s="10" t="s">
@@ -17400,10 +17407,10 @@
       </c>
     </row>
     <row r="19" spans="1:17">
-      <c r="A19" s="143"/>
-      <c r="B19" s="176"/>
-      <c r="C19" s="170"/>
-      <c r="D19" s="170"/>
+      <c r="A19" s="168"/>
+      <c r="B19" s="205"/>
+      <c r="C19" s="196"/>
+      <c r="D19" s="196"/>
       <c r="E19" s="8"/>
       <c r="F19" s="9" t="s">
         <v>332</v>
@@ -17414,7 +17421,7 @@
       <c r="H19" s="10">
         <v>1</v>
       </c>
-      <c r="I19" s="123">
+      <c r="I19" s="215">
         <v>44043</v>
       </c>
       <c r="J19" s="10"/>
@@ -17434,10 +17441,10 @@
       <c r="Q19" s="91"/>
     </row>
     <row r="20" spans="1:17">
-      <c r="A20" s="143"/>
-      <c r="B20" s="176"/>
-      <c r="C20" s="170"/>
-      <c r="D20" s="170"/>
+      <c r="A20" s="168"/>
+      <c r="B20" s="205"/>
+      <c r="C20" s="196"/>
+      <c r="D20" s="196"/>
       <c r="E20" s="8"/>
       <c r="F20" s="9" t="s">
         <v>333</v>
@@ -17448,7 +17455,7 @@
       <c r="H20" s="10">
         <v>1</v>
       </c>
-      <c r="I20" s="123">
+      <c r="I20" s="215">
         <v>44043</v>
       </c>
       <c r="J20" s="10"/>
@@ -17468,10 +17475,10 @@
       <c r="Q20" s="91"/>
     </row>
     <row r="21" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A21" s="143"/>
-      <c r="B21" s="176"/>
-      <c r="C21" s="170"/>
-      <c r="D21" s="170"/>
+      <c r="A21" s="168"/>
+      <c r="B21" s="205"/>
+      <c r="C21" s="196"/>
+      <c r="D21" s="196"/>
       <c r="E21" s="14"/>
       <c r="F21" s="9" t="s">
         <v>334</v>
@@ -17482,7 +17489,7 @@
       <c r="H21" s="16">
         <v>3</v>
       </c>
-      <c r="I21" s="123"/>
+      <c r="I21" s="215"/>
       <c r="J21" s="10" t="s">
         <v>563</v>
       </c>
@@ -17504,10 +17511,10 @@
       </c>
     </row>
     <row r="22" spans="1:17">
-      <c r="A22" s="143"/>
-      <c r="B22" s="176"/>
-      <c r="C22" s="170"/>
-      <c r="D22" s="170"/>
+      <c r="A22" s="168"/>
+      <c r="B22" s="205"/>
+      <c r="C22" s="196"/>
+      <c r="D22" s="196"/>
       <c r="E22" s="14"/>
       <c r="F22" s="9" t="s">
         <v>335</v>
@@ -17518,7 +17525,7 @@
       <c r="H22" s="16">
         <v>1</v>
       </c>
-      <c r="I22" s="123">
+      <c r="I22" s="215">
         <v>44043</v>
       </c>
       <c r="J22" s="10"/>
@@ -17540,10 +17547,10 @@
       </c>
     </row>
     <row r="23" spans="1:17">
-      <c r="A23" s="143"/>
-      <c r="B23" s="176"/>
-      <c r="C23" s="170"/>
-      <c r="D23" s="170"/>
+      <c r="A23" s="168"/>
+      <c r="B23" s="205"/>
+      <c r="C23" s="196"/>
+      <c r="D23" s="196"/>
       <c r="E23" s="14"/>
       <c r="F23" s="9" t="s">
         <v>336</v>
@@ -17551,11 +17558,11 @@
       <c r="G23" s="13" t="s">
         <v>369</v>
       </c>
-      <c r="H23" s="16" t="s">
-        <v>963</v>
-      </c>
-      <c r="I23" s="123">
-        <v>44043</v>
+      <c r="H23" s="16">
+        <v>2</v>
+      </c>
+      <c r="I23" s="215">
+        <v>44074</v>
       </c>
       <c r="J23" s="10"/>
       <c r="K23" s="10"/>
@@ -17571,15 +17578,15 @@
       <c r="P23" s="100" t="s">
         <v>964</v>
       </c>
-      <c r="Q23" s="215" t="s">
+      <c r="Q23" s="157" t="s">
         <v>1286</v>
       </c>
     </row>
     <row r="24" spans="1:17">
-      <c r="A24" s="143"/>
-      <c r="B24" s="176"/>
-      <c r="C24" s="170"/>
-      <c r="D24" s="170"/>
+      <c r="A24" s="168"/>
+      <c r="B24" s="205"/>
+      <c r="C24" s="196"/>
+      <c r="D24" s="196"/>
       <c r="E24" s="8"/>
       <c r="F24" s="9" t="s">
         <v>1283</v>
@@ -17587,15 +17594,15 @@
       <c r="G24" s="13" t="s">
         <v>370</v>
       </c>
-      <c r="H24" s="10" t="s">
-        <v>963</v>
-      </c>
-      <c r="I24" s="123">
-        <v>44043</v>
+      <c r="H24" s="10">
+        <v>2</v>
+      </c>
+      <c r="I24" s="215">
+        <v>44074</v>
       </c>
       <c r="J24" s="10"/>
       <c r="K24" s="10"/>
-      <c r="M24" s="214" t="s">
+      <c r="M24" s="156" t="s">
         <v>1282</v>
       </c>
       <c r="N24" s="98" t="s">
@@ -17610,10 +17617,10 @@
       <c r="Q24" s="91"/>
     </row>
     <row r="25" spans="1:17">
-      <c r="A25" s="143"/>
-      <c r="B25" s="176"/>
-      <c r="C25" s="170"/>
-      <c r="D25" s="170"/>
+      <c r="A25" s="168"/>
+      <c r="B25" s="205"/>
+      <c r="C25" s="196"/>
+      <c r="D25" s="196"/>
       <c r="E25" s="8"/>
       <c r="F25" s="9" t="s">
         <v>373</v>
@@ -17624,7 +17631,7 @@
       <c r="H25" s="10">
         <v>3</v>
       </c>
-      <c r="I25" s="123"/>
+      <c r="I25" s="215"/>
       <c r="J25" s="10" t="s">
         <v>563</v>
       </c>
@@ -17644,10 +17651,10 @@
       <c r="Q25" s="91"/>
     </row>
     <row r="26" spans="1:17">
-      <c r="A26" s="143"/>
-      <c r="B26" s="176"/>
-      <c r="C26" s="170"/>
-      <c r="D26" s="170"/>
+      <c r="A26" s="168"/>
+      <c r="B26" s="205"/>
+      <c r="C26" s="196"/>
+      <c r="D26" s="196"/>
       <c r="E26" s="8"/>
       <c r="F26" s="9" t="s">
         <v>338</v>
@@ -17658,7 +17665,9 @@
       <c r="H26" s="10">
         <v>2</v>
       </c>
-      <c r="I26" s="123"/>
+      <c r="I26" s="215">
+        <v>44074</v>
+      </c>
       <c r="J26" s="10"/>
       <c r="K26" s="10"/>
       <c r="M26" s="99" t="s">
@@ -17676,10 +17685,10 @@
       <c r="Q26" s="91"/>
     </row>
     <row r="27" spans="1:17">
-      <c r="A27" s="143"/>
-      <c r="B27" s="176"/>
-      <c r="C27" s="170"/>
-      <c r="D27" s="170"/>
+      <c r="A27" s="168"/>
+      <c r="B27" s="205"/>
+      <c r="C27" s="196"/>
+      <c r="D27" s="196"/>
       <c r="E27" s="8"/>
       <c r="F27" s="9" t="s">
         <v>339</v>
@@ -17687,10 +17696,10 @@
       <c r="G27" s="13" t="s">
         <v>372</v>
       </c>
-      <c r="H27" s="124" t="s">
+      <c r="H27" s="123" t="s">
         <v>964</v>
       </c>
-      <c r="I27" s="123"/>
+      <c r="I27" s="215"/>
       <c r="J27" s="10"/>
       <c r="K27" s="10"/>
       <c r="M27" s="99" t="s">
@@ -17708,12 +17717,12 @@
       <c r="Q27" s="91"/>
     </row>
     <row r="28" spans="1:17">
-      <c r="A28" s="143"/>
-      <c r="B28" s="176"/>
-      <c r="C28" s="170"/>
-      <c r="D28" s="170"/>
+      <c r="A28" s="168"/>
+      <c r="B28" s="205"/>
+      <c r="C28" s="196"/>
+      <c r="D28" s="196"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="126" t="s">
+      <c r="F28" s="125" t="s">
         <v>967</v>
       </c>
       <c r="G28" s="13" t="s">
@@ -17722,7 +17731,7 @@
       <c r="H28" s="10">
         <v>1</v>
       </c>
-      <c r="I28" s="123">
+      <c r="I28" s="215">
         <v>44043</v>
       </c>
       <c r="J28" s="10"/>
@@ -17742,10 +17751,10 @@
       <c r="Q28" s="91"/>
     </row>
     <row r="29" spans="1:17">
-      <c r="A29" s="143"/>
-      <c r="B29" s="176"/>
-      <c r="C29" s="170"/>
-      <c r="D29" s="170"/>
+      <c r="A29" s="168"/>
+      <c r="B29" s="205"/>
+      <c r="C29" s="196"/>
+      <c r="D29" s="196"/>
       <c r="E29" s="8"/>
       <c r="F29" s="9" t="s">
         <v>957</v>
@@ -17756,17 +17765,19 @@
       <c r="H29" s="16">
         <v>2</v>
       </c>
-      <c r="I29" s="123"/>
+      <c r="I29" s="215">
+        <v>44074</v>
+      </c>
       <c r="J29" s="10"/>
       <c r="K29" s="10" t="s">
         <v>956</v>
       </c>
     </row>
     <row r="30" spans="1:17">
-      <c r="A30" s="143"/>
-      <c r="B30" s="176"/>
-      <c r="C30" s="170"/>
-      <c r="D30" s="171"/>
+      <c r="A30" s="168"/>
+      <c r="B30" s="205"/>
+      <c r="C30" s="196"/>
+      <c r="D30" s="197"/>
       <c r="E30" s="8"/>
       <c r="F30" s="49" t="s">
         <v>323</v>
@@ -17777,9 +17788,9 @@
       <c r="H30" s="114">
         <v>3</v>
       </c>
-      <c r="I30" s="123"/>
+      <c r="I30" s="215"/>
       <c r="J30" s="10"/>
-      <c r="K30" s="172" t="s">
+      <c r="K30" s="198" t="s">
         <v>961</v>
       </c>
       <c r="M30" s="102" t="s">
@@ -17796,10 +17807,10 @@
       </c>
     </row>
     <row r="31" spans="1:17">
-      <c r="A31" s="143"/>
-      <c r="B31" s="176"/>
-      <c r="C31" s="170"/>
-      <c r="D31" s="169" t="s">
+      <c r="A31" s="168"/>
+      <c r="B31" s="205"/>
+      <c r="C31" s="196"/>
+      <c r="D31" s="195" t="s">
         <v>518</v>
       </c>
       <c r="E31" s="8"/>
@@ -17812,17 +17823,17 @@
       <c r="H31" s="16">
         <v>1</v>
       </c>
-      <c r="I31" s="123">
+      <c r="I31" s="215">
         <v>44043</v>
       </c>
       <c r="J31" s="10"/>
-      <c r="K31" s="173"/>
+      <c r="K31" s="202"/>
     </row>
     <row r="32" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A32" s="143"/>
-      <c r="B32" s="176"/>
-      <c r="C32" s="170"/>
-      <c r="D32" s="170"/>
+      <c r="A32" s="168"/>
+      <c r="B32" s="205"/>
+      <c r="C32" s="196"/>
+      <c r="D32" s="196"/>
       <c r="E32" s="8"/>
       <c r="F32" s="9" t="s">
         <v>325</v>
@@ -17833,20 +17844,20 @@
       <c r="H32" s="16">
         <v>1</v>
       </c>
-      <c r="I32" s="123">
+      <c r="I32" s="215">
         <v>44043</v>
       </c>
       <c r="J32" s="10"/>
-      <c r="K32" s="173"/>
-      <c r="M32" s="212" t="s">
+      <c r="K32" s="202"/>
+      <c r="M32" s="154" t="s">
         <v>1279</v>
       </c>
     </row>
     <row r="33" spans="1:15" ht="16.5" customHeight="1">
-      <c r="A33" s="143"/>
-      <c r="B33" s="176"/>
-      <c r="C33" s="170"/>
-      <c r="D33" s="170"/>
+      <c r="A33" s="168"/>
+      <c r="B33" s="205"/>
+      <c r="C33" s="196"/>
+      <c r="D33" s="196"/>
       <c r="E33" s="8"/>
       <c r="F33" s="9" t="s">
         <v>959</v>
@@ -17857,14 +17868,14 @@
       <c r="H33" s="16">
         <v>2</v>
       </c>
-      <c r="I33" s="123">
+      <c r="I33" s="215">
         <v>44043</v>
       </c>
       <c r="J33" s="10" t="s">
         <v>956</v>
       </c>
-      <c r="K33" s="174"/>
-      <c r="M33" s="213" t="s">
+      <c r="K33" s="203"/>
+      <c r="M33" s="155" t="s">
         <v>1280</v>
       </c>
       <c r="N33" s="5" t="s">
@@ -17875,10 +17886,10 @@
       </c>
     </row>
     <row r="34" spans="1:15" ht="16.5" customHeight="1">
-      <c r="A34" s="143"/>
-      <c r="B34" s="176"/>
-      <c r="C34" s="170"/>
-      <c r="D34" s="170"/>
+      <c r="A34" s="168"/>
+      <c r="B34" s="205"/>
+      <c r="C34" s="196"/>
+      <c r="D34" s="196"/>
       <c r="E34" s="8"/>
       <c r="F34" s="9" t="s">
         <v>1277</v>
@@ -17889,17 +17900,19 @@
       <c r="H34" s="122">
         <v>2</v>
       </c>
-      <c r="I34" s="123"/>
+      <c r="I34" s="215">
+        <v>44074</v>
+      </c>
       <c r="J34" s="10"/>
       <c r="K34" s="10" t="s">
         <v>956</v>
       </c>
     </row>
     <row r="35" spans="1:15">
-      <c r="A35" s="143"/>
-      <c r="B35" s="176"/>
-      <c r="C35" s="171"/>
-      <c r="D35" s="171"/>
+      <c r="A35" s="168"/>
+      <c r="B35" s="205"/>
+      <c r="C35" s="197"/>
+      <c r="D35" s="197"/>
       <c r="E35" s="8"/>
       <c r="F35" s="49" t="s">
         <v>322</v>
@@ -17910,17 +17923,17 @@
       <c r="H35" s="50">
         <v>3</v>
       </c>
-      <c r="I35" s="123"/>
+      <c r="I35" s="215"/>
       <c r="J35" s="10"/>
       <c r="K35" s="10"/>
     </row>
     <row r="36" spans="1:15">
-      <c r="A36" s="143"/>
-      <c r="B36" s="176"/>
-      <c r="C36" s="169" t="s">
+      <c r="A36" s="168"/>
+      <c r="B36" s="205"/>
+      <c r="C36" s="195" t="s">
         <v>340</v>
       </c>
-      <c r="D36" s="169" t="s">
+      <c r="D36" s="195" t="s">
         <v>517</v>
       </c>
       <c r="E36" s="8"/>
@@ -17933,17 +17946,17 @@
       <c r="H36" s="16">
         <v>1</v>
       </c>
-      <c r="I36" s="123">
+      <c r="I36" s="215">
         <v>44043</v>
       </c>
       <c r="J36" s="10"/>
       <c r="K36" s="10"/>
     </row>
     <row r="37" spans="1:15">
-      <c r="A37" s="143"/>
-      <c r="B37" s="177"/>
-      <c r="C37" s="171"/>
-      <c r="D37" s="171"/>
+      <c r="A37" s="168"/>
+      <c r="B37" s="206"/>
+      <c r="C37" s="197"/>
+      <c r="D37" s="197"/>
       <c r="E37" s="8"/>
       <c r="F37" s="9" t="s">
         <v>331</v>
@@ -17951,15 +17964,15 @@
       <c r="G37" s="9" t="s">
         <v>376</v>
       </c>
-      <c r="H37" s="125" t="s">
+      <c r="H37" s="124" t="s">
         <v>965</v>
       </c>
-      <c r="I37" s="123"/>
+      <c r="I37" s="215"/>
       <c r="J37" s="10"/>
       <c r="K37" s="10"/>
     </row>
     <row r="38" spans="1:15">
-      <c r="A38" s="143"/>
+      <c r="A38" s="168"/>
       <c r="B38" s="29" t="s">
         <v>328</v>
       </c>
@@ -17979,19 +17992,19 @@
       <c r="H38" s="16" t="s">
         <v>330</v>
       </c>
-      <c r="I38" s="123"/>
+      <c r="I38" s="215"/>
       <c r="J38" s="10"/>
       <c r="K38" s="10"/>
     </row>
     <row r="39" spans="1:15" ht="16.5" customHeight="1">
-      <c r="A39" s="143"/>
-      <c r="B39" s="175" t="s">
+      <c r="A39" s="168"/>
+      <c r="B39" s="204" t="s">
         <v>505</v>
       </c>
-      <c r="C39" s="169" t="s">
+      <c r="C39" s="195" t="s">
         <v>510</v>
       </c>
-      <c r="D39" s="169" t="s">
+      <c r="D39" s="195" t="s">
         <v>516</v>
       </c>
       <c r="E39" s="8" t="s">
@@ -18006,15 +18019,15 @@
       <c r="H39" s="10">
         <v>2</v>
       </c>
-      <c r="I39" s="123"/>
+      <c r="I39" s="215"/>
       <c r="J39" s="10"/>
       <c r="K39" s="10"/>
     </row>
     <row r="40" spans="1:15" ht="16.5" customHeight="1">
-      <c r="A40" s="143"/>
-      <c r="B40" s="176"/>
-      <c r="C40" s="143"/>
-      <c r="D40" s="143"/>
+      <c r="A40" s="168"/>
+      <c r="B40" s="205"/>
+      <c r="C40" s="168"/>
+      <c r="D40" s="168"/>
       <c r="E40" s="17"/>
       <c r="F40" s="9" t="s">
         <v>304</v>
@@ -18025,17 +18038,17 @@
       <c r="H40" s="16">
         <v>1</v>
       </c>
-      <c r="I40" s="123">
+      <c r="I40" s="215">
         <v>44043</v>
       </c>
       <c r="J40" s="10"/>
       <c r="K40" s="10"/>
     </row>
     <row r="41" spans="1:15" ht="16.5" customHeight="1">
-      <c r="A41" s="143"/>
-      <c r="B41" s="176"/>
-      <c r="C41" s="143"/>
-      <c r="D41" s="143"/>
+      <c r="A41" s="168"/>
+      <c r="B41" s="205"/>
+      <c r="C41" s="168"/>
+      <c r="D41" s="168"/>
       <c r="E41" s="17"/>
       <c r="F41" s="9" t="s">
         <v>305</v>
@@ -18046,17 +18059,17 @@
       <c r="H41" s="16">
         <v>1</v>
       </c>
-      <c r="I41" s="123">
+      <c r="I41" s="215">
         <v>44043</v>
       </c>
       <c r="J41" s="10"/>
       <c r="K41" s="10"/>
     </row>
     <row r="42" spans="1:15">
-      <c r="A42" s="143"/>
-      <c r="B42" s="176"/>
-      <c r="C42" s="143"/>
-      <c r="D42" s="144"/>
+      <c r="A42" s="168"/>
+      <c r="B42" s="205"/>
+      <c r="C42" s="168"/>
+      <c r="D42" s="169"/>
       <c r="E42" s="17"/>
       <c r="F42" s="9" t="s">
         <v>305</v>
@@ -18067,15 +18080,17 @@
       <c r="H42" s="16">
         <v>2</v>
       </c>
-      <c r="I42" s="123"/>
+      <c r="I42" s="215">
+        <v>44074</v>
+      </c>
       <c r="J42" s="10"/>
       <c r="K42" s="10"/>
     </row>
     <row r="43" spans="1:15" ht="16.5" customHeight="1">
-      <c r="A43" s="143"/>
-      <c r="B43" s="176"/>
-      <c r="C43" s="143"/>
-      <c r="D43" s="169" t="s">
+      <c r="A43" s="168"/>
+      <c r="B43" s="205"/>
+      <c r="C43" s="168"/>
+      <c r="D43" s="195" t="s">
         <v>515</v>
       </c>
       <c r="E43" s="8"/>
@@ -18088,19 +18103,19 @@
       <c r="H43" s="10" t="s">
         <v>963</v>
       </c>
-      <c r="I43" s="123">
+      <c r="I43" s="215">
         <v>44043</v>
       </c>
       <c r="J43" s="10"/>
-      <c r="K43" s="172" t="s">
+      <c r="K43" s="198" t="s">
         <v>1166</v>
       </c>
     </row>
     <row r="44" spans="1:15">
-      <c r="A44" s="143"/>
-      <c r="B44" s="176"/>
-      <c r="C44" s="143"/>
-      <c r="D44" s="144"/>
+      <c r="A44" s="168"/>
+      <c r="B44" s="205"/>
+      <c r="C44" s="168"/>
+      <c r="D44" s="169"/>
       <c r="E44" s="8"/>
       <c r="F44" s="9" t="s">
         <v>289</v>
@@ -18111,17 +18126,17 @@
       <c r="H44" s="10" t="s">
         <v>963</v>
       </c>
-      <c r="I44" s="123">
+      <c r="I44" s="215">
         <v>44043</v>
       </c>
       <c r="J44" s="10"/>
-      <c r="K44" s="182"/>
+      <c r="K44" s="199"/>
     </row>
     <row r="45" spans="1:15">
-      <c r="A45" s="143"/>
-      <c r="B45" s="176"/>
-      <c r="C45" s="143"/>
-      <c r="D45" s="169" t="s">
+      <c r="A45" s="168"/>
+      <c r="B45" s="205"/>
+      <c r="C45" s="168"/>
+      <c r="D45" s="195" t="s">
         <v>514</v>
       </c>
       <c r="E45" s="8"/>
@@ -18134,15 +18149,15 @@
       <c r="H45" s="10">
         <v>2</v>
       </c>
-      <c r="I45" s="123"/>
+      <c r="I45" s="215"/>
       <c r="J45" s="10"/>
       <c r="K45" s="10"/>
     </row>
     <row r="46" spans="1:15">
-      <c r="A46" s="144"/>
-      <c r="B46" s="177"/>
-      <c r="C46" s="144"/>
-      <c r="D46" s="144"/>
+      <c r="A46" s="169"/>
+      <c r="B46" s="206"/>
+      <c r="C46" s="169"/>
+      <c r="D46" s="169"/>
       <c r="E46" s="8"/>
       <c r="F46" s="9" t="s">
         <v>301</v>
@@ -18153,7 +18168,7 @@
       <c r="H46" s="10">
         <v>2</v>
       </c>
-      <c r="I46" s="123"/>
+      <c r="I46" s="215"/>
       <c r="J46" s="10"/>
       <c r="K46" s="10"/>
     </row>
@@ -18162,11 +18177,6 @@
     <sortCondition ref="P16:P28"/>
   </sortState>
   <mergeCells count="19">
-    <mergeCell ref="D6:D14"/>
-    <mergeCell ref="K43:K44"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="D16:D30"/>
-    <mergeCell ref="K30:K33"/>
     <mergeCell ref="C2:C5"/>
     <mergeCell ref="C6:C15"/>
     <mergeCell ref="A2:A46"/>
@@ -18181,6 +18191,11 @@
     <mergeCell ref="D31:D35"/>
     <mergeCell ref="D36:D37"/>
     <mergeCell ref="D2:D4"/>
+    <mergeCell ref="D6:D14"/>
+    <mergeCell ref="K43:K44"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="D16:D30"/>
+    <mergeCell ref="K30:K33"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18219,11 +18234,11 @@
       <c r="B1" s="25" t="s">
         <v>327</v>
       </c>
-      <c r="E1" s="180" t="s">
+      <c r="E1" s="209" t="s">
         <v>724</v>
       </c>
-      <c r="F1" s="180"/>
-      <c r="G1" s="180"/>
+      <c r="F1" s="209"/>
+      <c r="G1" s="209"/>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="19" t="s">
@@ -18232,11 +18247,11 @@
       <c r="B2" s="19" t="s">
         <v>257</v>
       </c>
-      <c r="E2" s="181" t="s">
+      <c r="E2" s="210" t="s">
         <v>725</v>
       </c>
-      <c r="F2" s="181"/>
-      <c r="G2" s="181"/>
+      <c r="F2" s="210"/>
+      <c r="G2" s="210"/>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="19" t="s">
@@ -18253,10 +18268,10 @@
       <c r="B4" s="19" t="s">
         <v>259</v>
       </c>
-      <c r="E4" s="180" t="s">
+      <c r="E4" s="209" t="s">
         <v>722</v>
       </c>
-      <c r="F4" s="180"/>
+      <c r="F4" s="209"/>
       <c r="G4" s="25" t="s">
         <v>723</v>
       </c>
@@ -18268,16 +18283,16 @@
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="E5" s="179" t="s">
+      <c r="E5" s="208" t="s">
         <v>720</v>
       </c>
-      <c r="F5" s="179" t="s">
+      <c r="F5" s="208" t="s">
         <v>721</v>
       </c>
       <c r="G5" s="68" t="s">
         <v>747</v>
       </c>
-      <c r="H5" s="178" t="s">
+      <c r="H5" s="207" t="s">
         <v>748</v>
       </c>
       <c r="J5" t="s">
@@ -18288,12 +18303,12 @@
       <c r="A6" t="s">
         <v>261</v>
       </c>
-      <c r="E6" s="179"/>
-      <c r="F6" s="179"/>
+      <c r="E6" s="208"/>
+      <c r="F6" s="208"/>
       <c r="G6" s="68" t="s">
         <v>746</v>
       </c>
-      <c r="H6" s="179"/>
+      <c r="H6" s="208"/>
       <c r="J6" t="s">
         <v>729</v>
       </c>
@@ -18504,46 +18519,46 @@
     <col min="7" max="7" width="33" customWidth="1"/>
     <col min="8" max="8" width="38.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.140625" style="81" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="60.42578125" style="183" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="60.42578125" style="132" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30">
-      <c r="A1" s="191" t="s">
+      <c r="A1" s="136" t="s">
         <v>847</v>
       </c>
-      <c r="B1" s="191" t="s">
+      <c r="B1" s="136" t="s">
         <v>1171</v>
       </c>
-      <c r="C1" s="191" t="s">
+      <c r="C1" s="136" t="s">
         <v>640</v>
       </c>
-      <c r="D1" s="191" t="s">
+      <c r="D1" s="136" t="s">
         <v>1174</v>
       </c>
-      <c r="E1" s="191" t="s">
+      <c r="E1" s="136" t="s">
         <v>1169</v>
       </c>
-      <c r="F1" s="191" t="s">
+      <c r="F1" s="136" t="s">
         <v>1170</v>
       </c>
-      <c r="G1" s="192" t="s">
+      <c r="G1" s="137" t="s">
         <v>1204</v>
       </c>
-      <c r="H1" s="192" t="s">
+      <c r="H1" s="137" t="s">
         <v>1257</v>
       </c>
-      <c r="I1" s="191" t="s">
+      <c r="I1" s="136" t="s">
         <v>1178</v>
       </c>
-      <c r="J1" s="191" t="s">
+      <c r="J1" s="136" t="s">
         <v>1184</v>
       </c>
-      <c r="K1" s="191" t="s">
+      <c r="K1" s="136" t="s">
         <v>1190</v>
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="187">
+      <c r="A2" s="135">
         <v>44028</v>
       </c>
       <c r="B2" s="8" t="s">
@@ -18571,12 +18586,12 @@
       <c r="J2" s="119" t="s">
         <v>893</v>
       </c>
-      <c r="K2" s="188" t="s">
+      <c r="K2" s="211" t="s">
         <v>1196</v>
       </c>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="187">
+      <c r="A3" s="135">
         <v>44028</v>
       </c>
       <c r="B3" s="8" t="s">
@@ -18604,10 +18619,10 @@
       <c r="J3" s="119" t="s">
         <v>893</v>
       </c>
-      <c r="K3" s="189"/>
+      <c r="K3" s="212"/>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="187">
+      <c r="A4" s="135">
         <v>44029</v>
       </c>
       <c r="B4" s="8" t="s">
@@ -18633,10 +18648,10 @@
       <c r="J4" s="119" t="s">
         <v>893</v>
       </c>
-      <c r="K4" s="189"/>
+      <c r="K4" s="212"/>
     </row>
     <row r="5" spans="1:11" ht="45">
-      <c r="A5" s="187">
+      <c r="A5" s="135">
         <v>44029</v>
       </c>
       <c r="B5" s="8" t="s">
@@ -18662,10 +18677,10 @@
       <c r="J5" s="119" t="s">
         <v>893</v>
       </c>
-      <c r="K5" s="190"/>
+      <c r="K5" s="213"/>
     </row>
     <row r="6" spans="1:11" ht="60">
-      <c r="A6" s="187">
+      <c r="A6" s="135">
         <v>44029</v>
       </c>
       <c r="B6" s="8" t="s">
@@ -18696,7 +18711,7 @@
       </c>
     </row>
     <row r="7" spans="1:11" ht="60">
-      <c r="A7" s="187">
+      <c r="A7" s="135">
         <v>44029</v>
       </c>
       <c r="B7" s="8" t="s">
@@ -18725,7 +18740,7 @@
       <c r="K7" s="8"/>
     </row>
     <row r="8" spans="1:11" ht="60">
-      <c r="A8" s="187">
+      <c r="A8" s="135">
         <v>44029</v>
       </c>
       <c r="B8" s="8" t="s">
@@ -18758,7 +18773,7 @@
       </c>
     </row>
     <row r="9" spans="1:11" ht="60">
-      <c r="A9" s="187">
+      <c r="A9" s="135">
         <v>44029</v>
       </c>
       <c r="B9" s="8" t="s">
@@ -18773,13 +18788,13 @@
       <c r="E9" s="18" t="s">
         <v>1193</v>
       </c>
-      <c r="F9" s="200" t="s">
+      <c r="F9" s="145" t="s">
         <v>1245</v>
       </c>
-      <c r="G9" s="201" t="s">
+      <c r="G9" s="146" t="s">
         <v>1213</v>
       </c>
-      <c r="H9" s="198" t="s">
+      <c r="H9" s="143" t="s">
         <v>1243</v>
       </c>
       <c r="I9" s="119" t="s">
@@ -18791,7 +18806,7 @@
       </c>
     </row>
     <row r="10" spans="1:11" ht="64.5" customHeight="1">
-      <c r="A10" s="197" t="s">
+      <c r="A10" s="142" t="s">
         <v>1229</v>
       </c>
       <c r="B10" s="8" t="s">
@@ -18822,7 +18837,7 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="45">
-      <c r="A11" s="195" t="s">
+      <c r="A11" s="140" t="s">
         <v>1220</v>
       </c>
       <c r="B11" s="8" t="s">
@@ -18840,10 +18855,10 @@
       <c r="F11" s="119" t="s">
         <v>1200</v>
       </c>
-      <c r="G11" s="194" t="s">
+      <c r="G11" s="139" t="s">
         <v>1247</v>
       </c>
-      <c r="H11" s="194"/>
+      <c r="H11" s="139"/>
       <c r="I11" s="119" t="s">
         <v>1219</v>
       </c>
@@ -18891,114 +18906,114 @@
       </c>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="183"/>
-      <c r="B14" s="183"/>
-      <c r="C14" s="183"/>
-      <c r="D14" s="183"/>
-      <c r="E14" s="193" t="s">
+      <c r="A14" s="132"/>
+      <c r="B14" s="132"/>
+      <c r="C14" s="132"/>
+      <c r="D14" s="132"/>
+      <c r="E14" s="138" t="s">
         <v>1218</v>
       </c>
-      <c r="F14" s="184"/>
-      <c r="G14" s="193" t="s">
+      <c r="F14" s="133"/>
+      <c r="G14" s="138" t="s">
         <v>1256</v>
       </c>
-      <c r="H14" s="183"/>
-      <c r="I14" s="184"/>
-      <c r="J14" s="183"/>
+      <c r="H14" s="132"/>
+      <c r="I14" s="133"/>
+      <c r="J14" s="132"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="183"/>
-      <c r="B15" s="183"/>
-      <c r="C15" s="183"/>
-      <c r="D15" s="183"/>
-      <c r="E15" s="183"/>
-      <c r="F15" s="184"/>
-      <c r="G15" s="183" t="s">
+      <c r="A15" s="132"/>
+      <c r="B15" s="132"/>
+      <c r="C15" s="132"/>
+      <c r="D15" s="132"/>
+      <c r="E15" s="132"/>
+      <c r="F15" s="133"/>
+      <c r="G15" s="132" t="s">
         <v>1235</v>
       </c>
-      <c r="H15" s="183" t="s">
+      <c r="H15" s="132" t="s">
         <v>1236</v>
       </c>
-      <c r="I15" s="184"/>
-      <c r="J15" s="183"/>
+      <c r="I15" s="133"/>
+      <c r="J15" s="132"/>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="183"/>
-      <c r="B16" s="183"/>
-      <c r="C16" s="183"/>
-      <c r="D16" s="183"/>
-      <c r="E16" s="183"/>
-      <c r="G16" s="183"/>
-      <c r="H16" s="183"/>
-      <c r="I16" s="184"/>
-      <c r="J16" s="183"/>
+      <c r="A16" s="132"/>
+      <c r="B16" s="132"/>
+      <c r="C16" s="132"/>
+      <c r="D16" s="132"/>
+      <c r="E16" s="132"/>
+      <c r="G16" s="132"/>
+      <c r="H16" s="132"/>
+      <c r="I16" s="133"/>
+      <c r="J16" s="132"/>
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1">
-      <c r="A17" s="183"/>
-      <c r="B17" s="183"/>
-      <c r="C17" s="183"/>
-      <c r="D17" s="183"/>
-      <c r="E17" s="183"/>
-      <c r="F17" s="198"/>
+      <c r="A17" s="132"/>
+      <c r="B17" s="132"/>
+      <c r="C17" s="132"/>
+      <c r="D17" s="132"/>
+      <c r="E17" s="132"/>
+      <c r="F17" s="143"/>
       <c r="G17" s="8" t="s">
         <v>1258</v>
       </c>
-      <c r="H17" s="129" t="s">
+      <c r="H17" s="128" t="s">
         <v>1259</v>
       </c>
-      <c r="I17" s="184"/>
-      <c r="J17" s="183"/>
+      <c r="I17" s="133"/>
+      <c r="J17" s="132"/>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="183"/>
-      <c r="B18" s="183"/>
-      <c r="C18" s="183"/>
-      <c r="D18" s="183"/>
-      <c r="E18" s="183"/>
-      <c r="F18" s="202" t="s">
+      <c r="A18" s="132"/>
+      <c r="B18" s="132"/>
+      <c r="C18" s="132"/>
+      <c r="D18" s="132"/>
+      <c r="E18" s="132"/>
+      <c r="F18" s="214" t="s">
         <v>1241</v>
       </c>
       <c r="G18" s="8" t="s">
         <v>1238</v>
       </c>
-      <c r="H18" s="129" t="s">
+      <c r="H18" s="128" t="s">
         <v>1253</v>
       </c>
-      <c r="I18" s="184"/>
-      <c r="J18" s="183"/>
+      <c r="I18" s="133"/>
+      <c r="J18" s="132"/>
     </row>
     <row r="19" spans="1:10">
-      <c r="F19" s="202"/>
-      <c r="G19" s="210" t="s">
+      <c r="F19" s="214"/>
+      <c r="G19" s="152" t="s">
         <v>1237</v>
       </c>
-      <c r="H19" s="211" t="s">
+      <c r="H19" s="153" t="s">
         <v>1254</v>
       </c>
     </row>
     <row r="20" spans="1:10">
-      <c r="F20" s="202"/>
+      <c r="F20" s="214"/>
       <c r="G20" s="8" t="s">
         <v>1239</v>
       </c>
-      <c r="H20" s="129" t="s">
+      <c r="H20" s="128" t="s">
         <v>1253</v>
       </c>
     </row>
     <row r="21" spans="1:10">
-      <c r="F21" s="202"/>
+      <c r="F21" s="214"/>
       <c r="G21" s="8" t="s">
         <v>1240</v>
       </c>
-      <c r="H21" s="203" t="s">
+      <c r="H21" s="147" t="s">
         <v>1255</v>
       </c>
     </row>
     <row r="22" spans="1:10">
-      <c r="G22" s="199"/>
+      <c r="G22" s="144"/>
     </row>
     <row r="23" spans="1:10">
-      <c r="F23" s="196" t="s">
+      <c r="F23" s="141" t="s">
         <v>1252</v>
       </c>
       <c r="G23" t="s">
@@ -19009,7 +19024,7 @@
       </c>
     </row>
     <row r="24" spans="1:10">
-      <c r="F24" s="196" t="s">
+      <c r="F24" s="141" t="s">
         <v>1208</v>
       </c>
       <c r="G24" s="81">
@@ -19020,7 +19035,7 @@
       </c>
     </row>
     <row r="25" spans="1:10">
-      <c r="F25" s="196" t="s">
+      <c r="F25" s="141" t="s">
         <v>1208</v>
       </c>
       <c r="G25" s="81">
@@ -19031,7 +19046,7 @@
       </c>
     </row>
     <row r="26" spans="1:10">
-      <c r="F26" s="196" t="s">
+      <c r="F26" s="141" t="s">
         <v>1199</v>
       </c>
       <c r="G26" s="81">
@@ -19042,7 +19057,7 @@
       </c>
     </row>
     <row r="27" spans="1:10">
-      <c r="F27" s="196" t="s">
+      <c r="F27" s="141" t="s">
         <v>1199</v>
       </c>
       <c r="G27" s="81">
@@ -19053,7 +19068,7 @@
       </c>
     </row>
     <row r="28" spans="1:10">
-      <c r="F28" s="196" t="s">
+      <c r="F28" s="141" t="s">
         <v>1199</v>
       </c>
       <c r="G28" s="81">
@@ -19064,7 +19079,7 @@
       </c>
     </row>
     <row r="29" spans="1:10">
-      <c r="F29" s="196" t="s">
+      <c r="F29" s="141" t="s">
         <v>1200</v>
       </c>
       <c r="G29" s="81">
@@ -19075,7 +19090,7 @@
       </c>
     </row>
     <row r="30" spans="1:10">
-      <c r="F30" s="196" t="s">
+      <c r="F30" s="141" t="s">
         <v>1200</v>
       </c>
       <c r="G30" s="81">
@@ -19086,7 +19101,7 @@
       </c>
     </row>
     <row r="31" spans="1:10">
-      <c r="F31" s="196" t="s">
+      <c r="F31" s="141" t="s">
         <v>1200</v>
       </c>
       <c r="G31" s="81">
@@ -19097,7 +19112,7 @@
       </c>
     </row>
     <row r="32" spans="1:10">
-      <c r="F32" s="196" t="s">
+      <c r="F32" s="141" t="s">
         <v>1202</v>
       </c>
       <c r="G32" s="81">
@@ -19108,7 +19123,7 @@
       </c>
     </row>
     <row r="33" spans="6:8">
-      <c r="F33" s="196" t="s">
+      <c r="F33" s="141" t="s">
         <v>1202</v>
       </c>
       <c r="G33" s="81">
@@ -19158,7 +19173,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>272</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -19256,13 +19271,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="127" t="s">
+      <c r="A1" s="126" t="s">
         <v>973</v>
       </c>
-      <c r="B1" s="128" t="s">
+      <c r="B1" s="127" t="s">
         <v>974</v>
       </c>
-      <c r="C1" s="128" t="s">
+      <c r="C1" s="127" t="s">
         <v>975</v>
       </c>
     </row>
@@ -19718,120 +19733,120 @@
       </c>
     </row>
     <row r="43" spans="1:3">
-      <c r="A43" s="129" t="s">
+      <c r="A43" s="128" t="s">
         <v>385</v>
       </c>
-      <c r="B43" s="129" t="s">
+      <c r="B43" s="128" t="s">
         <v>1053</v>
       </c>
-      <c r="C43" s="129" t="s">
+      <c r="C43" s="128" t="s">
         <v>1054</v>
       </c>
     </row>
     <row r="44" spans="1:3">
-      <c r="A44" s="129" t="s">
+      <c r="A44" s="128" t="s">
         <v>385</v>
       </c>
-      <c r="B44" s="129" t="s">
+      <c r="B44" s="128" t="s">
         <v>1055</v>
       </c>
-      <c r="C44" s="129" t="s">
+      <c r="C44" s="128" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="45" spans="1:3">
-      <c r="A45" s="129" t="s">
+      <c r="A45" s="128" t="s">
         <v>385</v>
       </c>
-      <c r="B45" s="129" t="s">
+      <c r="B45" s="128" t="s">
         <v>1056</v>
       </c>
-      <c r="C45" s="129" t="s">
+      <c r="C45" s="128" t="s">
         <v>1057</v>
       </c>
     </row>
     <row r="46" spans="1:3">
-      <c r="A46" s="129" t="s">
+      <c r="A46" s="128" t="s">
         <v>385</v>
       </c>
-      <c r="B46" s="129" t="s">
+      <c r="B46" s="128" t="s">
         <v>619</v>
       </c>
-      <c r="C46" s="129" t="s">
+      <c r="C46" s="128" t="s">
         <v>1058</v>
       </c>
     </row>
     <row r="47" spans="1:3">
-      <c r="A47" s="129" t="s">
+      <c r="A47" s="128" t="s">
         <v>385</v>
       </c>
-      <c r="B47" s="129" t="s">
+      <c r="B47" s="128" t="s">
         <v>617</v>
       </c>
-      <c r="C47" s="129" t="s">
+      <c r="C47" s="128" t="s">
         <v>1059</v>
       </c>
     </row>
     <row r="48" spans="1:3">
-      <c r="A48" s="129" t="s">
+      <c r="A48" s="128" t="s">
         <v>385</v>
       </c>
-      <c r="B48" s="129" t="s">
+      <c r="B48" s="128" t="s">
         <v>1060</v>
       </c>
-      <c r="C48" s="129" t="s">
+      <c r="C48" s="128" t="s">
         <v>1061</v>
       </c>
     </row>
     <row r="49" spans="1:3">
-      <c r="A49" s="129" t="s">
+      <c r="A49" s="128" t="s">
         <v>385</v>
       </c>
-      <c r="B49" s="129" t="s">
+      <c r="B49" s="128" t="s">
         <v>1062</v>
       </c>
-      <c r="C49" s="129" t="s">
+      <c r="C49" s="128" t="s">
         <v>1063</v>
       </c>
     </row>
     <row r="50" spans="1:3">
-      <c r="A50" s="129" t="s">
+      <c r="A50" s="128" t="s">
         <v>385</v>
       </c>
-      <c r="B50" s="129" t="s">
+      <c r="B50" s="128" t="s">
         <v>1064</v>
       </c>
-      <c r="C50" s="129" t="s">
+      <c r="C50" s="128" t="s">
         <v>1065</v>
       </c>
     </row>
     <row r="51" spans="1:3">
-      <c r="A51" s="129" t="s">
+      <c r="A51" s="128" t="s">
         <v>385</v>
       </c>
-      <c r="B51" s="129" t="s">
+      <c r="B51" s="128" t="s">
         <v>1066</v>
       </c>
-      <c r="C51" s="129" t="s">
+      <c r="C51" s="128" t="s">
         <v>1067</v>
       </c>
     </row>
     <row r="52" spans="1:3">
-      <c r="A52" s="129" t="s">
+      <c r="A52" s="128" t="s">
         <v>385</v>
       </c>
-      <c r="B52" s="129" t="s">
+      <c r="B52" s="128" t="s">
         <v>1068</v>
       </c>
-      <c r="C52" s="129" t="s">
+      <c r="C52" s="128" t="s">
         <v>1069</v>
       </c>
     </row>
     <row r="53" spans="1:3">
-      <c r="A53" s="129" t="s">
+      <c r="A53" s="128" t="s">
         <v>385</v>
       </c>
-      <c r="B53" s="129" t="s">
+      <c r="B53" s="128" t="s">
         <v>1070</v>
       </c>
       <c r="C53" s="19" t="s">
@@ -19839,10 +19854,10 @@
       </c>
     </row>
     <row r="54" spans="1:3">
-      <c r="A54" s="129" t="s">
+      <c r="A54" s="128" t="s">
         <v>385</v>
       </c>
-      <c r="B54" s="129" t="s">
+      <c r="B54" s="128" t="s">
         <v>1072</v>
       </c>
       <c r="C54" s="19" t="s">
@@ -19850,7 +19865,7 @@
       </c>
     </row>
     <row r="55" spans="1:3">
-      <c r="A55" s="129" t="s">
+      <c r="A55" s="128" t="s">
         <v>385</v>
       </c>
       <c r="B55" s="19" t="s">
@@ -19861,7 +19876,7 @@
       </c>
     </row>
     <row r="56" spans="1:3">
-      <c r="A56" s="129" t="s">
+      <c r="A56" s="128" t="s">
         <v>385</v>
       </c>
       <c r="B56" s="19" t="s">
@@ -19872,7 +19887,7 @@
       </c>
     </row>
     <row r="57" spans="1:3">
-      <c r="A57" s="129" t="s">
+      <c r="A57" s="128" t="s">
         <v>385</v>
       </c>
       <c r="B57" s="19" t="s">
@@ -19883,7 +19898,7 @@
       </c>
     </row>
     <row r="58" spans="1:3" ht="30">
-      <c r="A58" s="129" t="s">
+      <c r="A58" s="128" t="s">
         <v>385</v>
       </c>
       <c r="B58" s="19" t="s">
@@ -19894,7 +19909,7 @@
       </c>
     </row>
     <row r="59" spans="1:3">
-      <c r="A59" s="129" t="s">
+      <c r="A59" s="128" t="s">
         <v>385</v>
       </c>
       <c r="B59" s="19" t="s">
@@ -19905,7 +19920,7 @@
       </c>
     </row>
     <row r="60" spans="1:3">
-      <c r="A60" s="129" t="s">
+      <c r="A60" s="128" t="s">
         <v>385</v>
       </c>
       <c r="B60" s="19" t="s">
@@ -19919,10 +19934,10 @@
       <c r="A61" s="19" t="s">
         <v>1085</v>
       </c>
-      <c r="B61" s="130" t="s">
+      <c r="B61" s="129" t="s">
         <v>1086</v>
       </c>
-      <c r="C61" s="130" t="s">
+      <c r="C61" s="129" t="s">
         <v>1087</v>
       </c>
     </row>
@@ -19930,10 +19945,10 @@
       <c r="A62" s="19" t="s">
         <v>1085</v>
       </c>
-      <c r="B62" s="131" t="s">
+      <c r="B62" s="130" t="s">
         <v>1088</v>
       </c>
-      <c r="C62" s="131" t="s">
+      <c r="C62" s="130" t="s">
         <v>1089</v>
       </c>
     </row>
@@ -19941,10 +19956,10 @@
       <c r="A63" s="19" t="s">
         <v>1085</v>
       </c>
-      <c r="B63" s="131" t="s">
+      <c r="B63" s="130" t="s">
         <v>1090</v>
       </c>
-      <c r="C63" s="131" t="s">
+      <c r="C63" s="130" t="s">
         <v>1091</v>
       </c>
     </row>
@@ -19952,10 +19967,10 @@
       <c r="A64" s="19" t="s">
         <v>1085</v>
       </c>
-      <c r="B64" s="131" t="s">
+      <c r="B64" s="130" t="s">
         <v>1092</v>
       </c>
-      <c r="C64" s="131" t="s">
+      <c r="C64" s="130" t="s">
         <v>1093</v>
       </c>
     </row>
@@ -19963,10 +19978,10 @@
       <c r="A65" s="19" t="s">
         <v>1085</v>
       </c>
-      <c r="B65" s="131" t="s">
+      <c r="B65" s="130" t="s">
         <v>1094</v>
       </c>
-      <c r="C65" s="131" t="s">
+      <c r="C65" s="130" t="s">
         <v>1095</v>
       </c>
     </row>
@@ -19974,10 +19989,10 @@
       <c r="A66" s="19" t="s">
         <v>1085</v>
       </c>
-      <c r="B66" s="131" t="s">
+      <c r="B66" s="130" t="s">
         <v>1096</v>
       </c>
-      <c r="C66" s="131" t="s">
+      <c r="C66" s="130" t="s">
         <v>1097</v>
       </c>
     </row>
@@ -19985,10 +20000,10 @@
       <c r="A67" s="19" t="s">
         <v>1085</v>
       </c>
-      <c r="B67" s="131" t="s">
+      <c r="B67" s="130" t="s">
         <v>1098</v>
       </c>
-      <c r="C67" s="131" t="s">
+      <c r="C67" s="130" t="s">
         <v>1099</v>
       </c>
     </row>
@@ -19996,10 +20011,10 @@
       <c r="A68" s="19" t="s">
         <v>1085</v>
       </c>
-      <c r="B68" s="131" t="s">
+      <c r="B68" s="130" t="s">
         <v>1100</v>
       </c>
-      <c r="C68" s="131" t="s">
+      <c r="C68" s="130" t="s">
         <v>1101</v>
       </c>
     </row>
@@ -20007,10 +20022,10 @@
       <c r="A69" s="19" t="s">
         <v>1085</v>
       </c>
-      <c r="B69" s="131" t="s">
+      <c r="B69" s="130" t="s">
         <v>1102</v>
       </c>
-      <c r="C69" s="131" t="s">
+      <c r="C69" s="130" t="s">
         <v>1103</v>
       </c>
     </row>
@@ -20018,10 +20033,10 @@
       <c r="A70" s="19" t="s">
         <v>1085</v>
       </c>
-      <c r="B70" s="131" t="s">
+      <c r="B70" s="130" t="s">
         <v>1104</v>
       </c>
-      <c r="C70" s="131" t="s">
+      <c r="C70" s="130" t="s">
         <v>1105</v>
       </c>
     </row>
@@ -20029,10 +20044,10 @@
       <c r="A71" s="19" t="s">
         <v>1085</v>
       </c>
-      <c r="B71" s="131" t="s">
+      <c r="B71" s="130" t="s">
         <v>1106</v>
       </c>
-      <c r="C71" s="131" t="s">
+      <c r="C71" s="130" t="s">
         <v>1107</v>
       </c>
     </row>
@@ -20040,10 +20055,10 @@
       <c r="A72" s="19" t="s">
         <v>1085</v>
       </c>
-      <c r="B72" s="131" t="s">
+      <c r="B72" s="130" t="s">
         <v>1108</v>
       </c>
-      <c r="C72" s="131" t="s">
+      <c r="C72" s="130" t="s">
         <v>1109</v>
       </c>
     </row>
@@ -20051,10 +20066,10 @@
       <c r="A73" s="19" t="s">
         <v>1085</v>
       </c>
-      <c r="B73" s="131" t="s">
+      <c r="B73" s="130" t="s">
         <v>1110</v>
       </c>
-      <c r="C73" s="131" t="s">
+      <c r="C73" s="130" t="s">
         <v>1111</v>
       </c>
     </row>
@@ -20062,10 +20077,10 @@
       <c r="A74" s="19" t="s">
         <v>1085</v>
       </c>
-      <c r="B74" s="131" t="s">
+      <c r="B74" s="130" t="s">
         <v>1112</v>
       </c>
-      <c r="C74" s="131" t="s">
+      <c r="C74" s="130" t="s">
         <v>1113</v>
       </c>
     </row>
@@ -20073,10 +20088,10 @@
       <c r="A75" s="19" t="s">
         <v>1085</v>
       </c>
-      <c r="B75" s="131" t="s">
+      <c r="B75" s="130" t="s">
         <v>1114</v>
       </c>
-      <c r="C75" s="131" t="s">
+      <c r="C75" s="130" t="s">
         <v>1115</v>
       </c>
     </row>
@@ -20084,10 +20099,10 @@
       <c r="A76" s="19" t="s">
         <v>1085</v>
       </c>
-      <c r="B76" s="131" t="s">
+      <c r="B76" s="130" t="s">
         <v>1116</v>
       </c>
-      <c r="C76" s="131" t="s">
+      <c r="C76" s="130" t="s">
         <v>1117</v>
       </c>
     </row>
@@ -20095,10 +20110,10 @@
       <c r="A77" s="19" t="s">
         <v>1085</v>
       </c>
-      <c r="B77" s="131" t="s">
+      <c r="B77" s="130" t="s">
         <v>1118</v>
       </c>
-      <c r="C77" s="131" t="s">
+      <c r="C77" s="130" t="s">
         <v>1119</v>
       </c>
     </row>
@@ -20106,10 +20121,10 @@
       <c r="A78" s="19" t="s">
         <v>1085</v>
       </c>
-      <c r="B78" s="131" t="s">
+      <c r="B78" s="130" t="s">
         <v>1120</v>
       </c>
-      <c r="C78" s="131" t="s">
+      <c r="C78" s="130" t="s">
         <v>1121</v>
       </c>
     </row>
@@ -20117,10 +20132,10 @@
       <c r="A79" s="19" t="s">
         <v>1085</v>
       </c>
-      <c r="B79" s="131" t="s">
+      <c r="B79" s="130" t="s">
         <v>1122</v>
       </c>
-      <c r="C79" s="131" t="s">
+      <c r="C79" s="130" t="s">
         <v>1123</v>
       </c>
     </row>
@@ -20128,10 +20143,10 @@
       <c r="A80" s="19" t="s">
         <v>1085</v>
       </c>
-      <c r="B80" s="131" t="s">
+      <c r="B80" s="130" t="s">
         <v>1124</v>
       </c>
-      <c r="C80" s="131" t="s">
+      <c r="C80" s="130" t="s">
         <v>1125</v>
       </c>
     </row>
@@ -20139,10 +20154,10 @@
       <c r="A81" s="19" t="s">
         <v>1085</v>
       </c>
-      <c r="B81" s="131" t="s">
+      <c r="B81" s="130" t="s">
         <v>1126</v>
       </c>
-      <c r="C81" s="131" t="s">
+      <c r="C81" s="130" t="s">
         <v>1127</v>
       </c>
     </row>
@@ -20150,10 +20165,10 @@
       <c r="A82" s="19" t="s">
         <v>1085</v>
       </c>
-      <c r="B82" s="131" t="s">
+      <c r="B82" s="130" t="s">
         <v>1128</v>
       </c>
-      <c r="C82" s="131" t="s">
+      <c r="C82" s="130" t="s">
         <v>1129</v>
       </c>
     </row>
@@ -20161,10 +20176,10 @@
       <c r="A83" s="19" t="s">
         <v>1085</v>
       </c>
-      <c r="B83" s="131" t="s">
+      <c r="B83" s="130" t="s">
         <v>1130</v>
       </c>
-      <c r="C83" s="131" t="s">
+      <c r="C83" s="130" t="s">
         <v>1131</v>
       </c>
     </row>
@@ -20172,10 +20187,10 @@
       <c r="A84" s="19" t="s">
         <v>1132</v>
       </c>
-      <c r="B84" s="131" t="s">
+      <c r="B84" s="130" t="s">
         <v>1133</v>
       </c>
-      <c r="C84" s="131" t="s">
+      <c r="C84" s="130" t="s">
         <v>1107</v>
       </c>
     </row>
@@ -20183,10 +20198,10 @@
       <c r="A85" s="19" t="s">
         <v>1132</v>
       </c>
-      <c r="B85" s="131" t="s">
+      <c r="B85" s="130" t="s">
         <v>1134</v>
       </c>
-      <c r="C85" s="131" t="s">
+      <c r="C85" s="130" t="s">
         <v>1135</v>
       </c>
     </row>
@@ -20194,10 +20209,10 @@
       <c r="A86" s="19" t="s">
         <v>1132</v>
       </c>
-      <c r="B86" s="131" t="s">
+      <c r="B86" s="130" t="s">
         <v>1136</v>
       </c>
-      <c r="C86" s="131" t="s">
+      <c r="C86" s="130" t="s">
         <v>1137</v>
       </c>
     </row>
@@ -20205,10 +20220,10 @@
       <c r="A87" s="19" t="s">
         <v>1132</v>
       </c>
-      <c r="B87" s="131" t="s">
+      <c r="B87" s="130" t="s">
         <v>1138</v>
       </c>
-      <c r="C87" s="131" t="s">
+      <c r="C87" s="130" t="s">
         <v>1139</v>
       </c>
     </row>
@@ -20216,10 +20231,10 @@
       <c r="A88" s="19" t="s">
         <v>1132</v>
       </c>
-      <c r="B88" s="131" t="s">
+      <c r="B88" s="130" t="s">
         <v>1140</v>
       </c>
-      <c r="C88" s="131" t="s">
+      <c r="C88" s="130" t="s">
         <v>1109</v>
       </c>
     </row>
@@ -20227,10 +20242,10 @@
       <c r="A89" s="19" t="s">
         <v>1132</v>
       </c>
-      <c r="B89" s="131" t="s">
+      <c r="B89" s="130" t="s">
         <v>1141</v>
       </c>
-      <c r="C89" s="131" t="s">
+      <c r="C89" s="130" t="s">
         <v>1142</v>
       </c>
     </row>
@@ -20238,10 +20253,10 @@
       <c r="A90" s="19" t="s">
         <v>1132</v>
       </c>
-      <c r="B90" s="131" t="s">
+      <c r="B90" s="130" t="s">
         <v>1143</v>
       </c>
-      <c r="C90" s="131" t="s">
+      <c r="C90" s="130" t="s">
         <v>1144</v>
       </c>
     </row>
@@ -20249,10 +20264,10 @@
       <c r="A91" s="19" t="s">
         <v>1145</v>
       </c>
-      <c r="B91" s="131" t="s">
+      <c r="B91" s="130" t="s">
         <v>1146</v>
       </c>
-      <c r="C91" s="131" t="s">
+      <c r="C91" s="130" t="s">
         <v>1107</v>
       </c>
     </row>
@@ -20260,10 +20275,10 @@
       <c r="A92" s="19" t="s">
         <v>1145</v>
       </c>
-      <c r="B92" s="131" t="s">
+      <c r="B92" s="130" t="s">
         <v>1136</v>
       </c>
-      <c r="C92" s="131" t="s">
+      <c r="C92" s="130" t="s">
         <v>1137</v>
       </c>
     </row>
@@ -20271,10 +20286,10 @@
       <c r="A93" s="19" t="s">
         <v>1145</v>
       </c>
-      <c r="B93" s="131" t="s">
+      <c r="B93" s="130" t="s">
         <v>313</v>
       </c>
-      <c r="C93" s="131" t="s">
+      <c r="C93" s="130" t="s">
         <v>1087</v>
       </c>
     </row>
@@ -20282,10 +20297,10 @@
       <c r="A94" s="19" t="s">
         <v>1145</v>
       </c>
-      <c r="B94" s="131" t="s">
+      <c r="B94" s="130" t="s">
         <v>811</v>
       </c>
-      <c r="C94" s="131" t="s">
+      <c r="C94" s="130" t="s">
         <v>1147</v>
       </c>
     </row>
@@ -20293,10 +20308,10 @@
       <c r="A95" s="19" t="s">
         <v>1145</v>
       </c>
-      <c r="B95" s="131" t="s">
+      <c r="B95" s="130" t="s">
         <v>1148</v>
       </c>
-      <c r="C95" s="131" t="s">
+      <c r="C95" s="130" t="s">
         <v>1091</v>
       </c>
     </row>
@@ -20304,10 +20319,10 @@
       <c r="A96" s="19" t="s">
         <v>1145</v>
       </c>
-      <c r="B96" s="131" t="s">
+      <c r="B96" s="130" t="s">
         <v>1149</v>
       </c>
-      <c r="C96" s="131" t="s">
+      <c r="C96" s="130" t="s">
         <v>1093</v>
       </c>
     </row>
@@ -20315,10 +20330,10 @@
       <c r="A97" s="19" t="s">
         <v>1145</v>
       </c>
-      <c r="B97" s="131" t="s">
+      <c r="B97" s="130" t="s">
         <v>1150</v>
       </c>
-      <c r="C97" s="131" t="s">
+      <c r="C97" s="130" t="s">
         <v>1095</v>
       </c>
     </row>
@@ -20326,10 +20341,10 @@
       <c r="A98" s="19" t="s">
         <v>1145</v>
       </c>
-      <c r="B98" s="131" t="s">
+      <c r="B98" s="130" t="s">
         <v>1151</v>
       </c>
-      <c r="C98" s="131" t="s">
+      <c r="C98" s="130" t="s">
         <v>1129</v>
       </c>
     </row>
@@ -20337,10 +20352,10 @@
       <c r="A99" s="19" t="s">
         <v>1145</v>
       </c>
-      <c r="B99" s="131" t="s">
+      <c r="B99" s="130" t="s">
         <v>1152</v>
       </c>
-      <c r="C99" s="131" t="s">
+      <c r="C99" s="130" t="s">
         <v>1153</v>
       </c>
     </row>
@@ -20348,10 +20363,10 @@
       <c r="A100" s="19" t="s">
         <v>1145</v>
       </c>
-      <c r="B100" s="131" t="s">
+      <c r="B100" s="130" t="s">
         <v>1154</v>
       </c>
-      <c r="C100" s="131" t="s">
+      <c r="C100" s="130" t="s">
         <v>1125</v>
       </c>
     </row>
@@ -20359,10 +20374,10 @@
       <c r="A101" s="19" t="s">
         <v>1145</v>
       </c>
-      <c r="B101" s="131" t="s">
+      <c r="B101" s="130" t="s">
         <v>1141</v>
       </c>
-      <c r="C101" s="131" t="s">
+      <c r="C101" s="130" t="s">
         <v>1155</v>
       </c>
     </row>
@@ -20370,10 +20385,10 @@
       <c r="A102" s="19" t="s">
         <v>1145</v>
       </c>
-      <c r="B102" s="131" t="s">
+      <c r="B102" s="130" t="s">
         <v>1156</v>
       </c>
-      <c r="C102" s="131" t="s">
+      <c r="C102" s="130" t="s">
         <v>1157</v>
       </c>
     </row>
@@ -20381,10 +20396,10 @@
       <c r="A103" s="19" t="s">
         <v>1145</v>
       </c>
-      <c r="B103" s="131" t="s">
+      <c r="B103" s="130" t="s">
         <v>1158</v>
       </c>
-      <c r="C103" s="131" t="s">
+      <c r="C103" s="130" t="s">
         <v>1159</v>
       </c>
     </row>
@@ -20392,10 +20407,10 @@
       <c r="A104" s="19" t="s">
         <v>1145</v>
       </c>
-      <c r="B104" s="131" t="s">
+      <c r="B104" s="130" t="s">
         <v>1160</v>
       </c>
-      <c r="C104" s="131" t="s">
+      <c r="C104" s="130" t="s">
         <v>1099</v>
       </c>
     </row>
@@ -20403,10 +20418,10 @@
       <c r="A105" s="19" t="s">
         <v>1145</v>
       </c>
-      <c r="B105" s="131" t="s">
+      <c r="B105" s="130" t="s">
         <v>1161</v>
       </c>
-      <c r="C105" s="131" t="s">
+      <c r="C105" s="130" t="s">
         <v>1162</v>
       </c>
     </row>
@@ -20429,13 +20444,13 @@
       <c r="A112" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="B112" s="132"/>
+      <c r="B112" s="131"/>
     </row>
     <row r="113" spans="1:2" ht="16.5">
       <c r="A113" s="7" t="s">
         <v>1165</v>
       </c>
-      <c r="B113" s="132"/>
+      <c r="B113" s="131"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -20479,7 +20494,7 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="179" t="s">
+      <c r="A2" s="208" t="s">
         <v>379</v>
       </c>
       <c r="B2" s="57" t="s">
@@ -20493,7 +20508,7 @@
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="179"/>
+      <c r="A3" s="208"/>
       <c r="B3" s="20" t="s">
         <v>262</v>
       </c>
@@ -20505,7 +20520,7 @@
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="179"/>
+      <c r="A4" s="208"/>
       <c r="B4" s="20" t="s">
         <v>385</v>
       </c>
@@ -20517,7 +20532,7 @@
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="179"/>
+      <c r="A5" s="208"/>
       <c r="B5" s="57" t="s">
         <v>544</v>
       </c>
@@ -20529,7 +20544,7 @@
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="179"/>
+      <c r="A6" s="208"/>
       <c r="B6" s="20" t="s">
         <v>388</v>
       </c>
@@ -20541,7 +20556,7 @@
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="179"/>
+      <c r="A7" s="208"/>
       <c r="B7" s="20" t="s">
         <v>390</v>
       </c>
@@ -22162,12 +22177,12 @@
       </c>
     </row>
     <row r="9" spans="11:18">
-      <c r="K9" s="209" t="s">
+      <c r="K9" s="151" t="s">
         <v>1269</v>
       </c>
     </row>
     <row r="10" spans="11:18">
-      <c r="K10" s="209">
+      <c r="K10" s="151">
         <v>0</v>
       </c>
       <c r="L10" s="110" t="s">
@@ -22184,17 +22199,17 @@
       </c>
     </row>
     <row r="11" spans="11:18" ht="15.75" thickBot="1">
-      <c r="K11" s="209"/>
-      <c r="L11" s="207"/>
-      <c r="M11" s="207"/>
-      <c r="N11" s="207"/>
-      <c r="O11" s="207"/>
-      <c r="P11" s="207"/>
-      <c r="Q11" s="207"/>
-      <c r="R11" s="207"/>
+      <c r="K11" s="151"/>
+      <c r="L11" s="149"/>
+      <c r="M11" s="149"/>
+      <c r="N11" s="149"/>
+      <c r="O11" s="149"/>
+      <c r="P11" s="149"/>
+      <c r="Q11" s="149"/>
+      <c r="R11" s="149"/>
     </row>
     <row r="12" spans="11:18">
-      <c r="K12" s="209">
+      <c r="K12" s="151">
         <v>1</v>
       </c>
       <c r="L12" s="5" t="s">
@@ -22202,7 +22217,7 @@
       </c>
     </row>
     <row r="13" spans="11:18">
-      <c r="K13" s="209"/>
+      <c r="K13" s="151"/>
       <c r="M13" t="s">
         <v>881</v>
       </c>
@@ -22214,7 +22229,7 @@
       </c>
     </row>
     <row r="14" spans="11:18">
-      <c r="K14" s="209"/>
+      <c r="K14" s="151"/>
       <c r="L14" s="6" t="s">
         <v>888</v>
       </c>
@@ -22223,13 +22238,13 @@
       </c>
     </row>
     <row r="15" spans="11:18">
-      <c r="K15" s="209"/>
+      <c r="K15" s="151"/>
       <c r="M15" t="s">
         <v>885</v>
       </c>
     </row>
     <row r="16" spans="11:18">
-      <c r="K16" s="209"/>
+      <c r="K16" s="151"/>
       <c r="O16" s="5" t="s">
         <v>1268</v>
       </c>
@@ -22238,16 +22253,16 @@
       </c>
     </row>
     <row r="17" spans="7:24">
-      <c r="K17" s="209"/>
+      <c r="K17" s="151"/>
     </row>
     <row r="18" spans="7:24">
-      <c r="K18" s="209"/>
+      <c r="K18" s="151"/>
     </row>
     <row r="19" spans="7:24">
-      <c r="K19" s="209"/>
+      <c r="K19" s="151"/>
     </row>
     <row r="20" spans="7:24">
-      <c r="K20" s="209"/>
+      <c r="K20" s="151"/>
       <c r="L20" s="6" t="s">
         <v>883</v>
       </c>
@@ -22265,7 +22280,7 @@
       </c>
     </row>
     <row r="21" spans="7:24">
-      <c r="K21" s="209"/>
+      <c r="K21" s="151"/>
       <c r="M21" t="s">
         <v>889</v>
       </c>
@@ -22274,8 +22289,8 @@
       </c>
     </row>
     <row r="22" spans="7:24">
-      <c r="K22" s="209"/>
-      <c r="V22" s="142" t="s">
+      <c r="K22" s="151"/>
+      <c r="V22" s="167" t="s">
         <v>833</v>
       </c>
       <c r="W22" s="9" t="s">
@@ -22286,19 +22301,19 @@
       </c>
     </row>
     <row r="23" spans="7:24" ht="15.75" thickBot="1">
-      <c r="K23" s="209"/>
-      <c r="L23" s="207"/>
-      <c r="M23" s="207"/>
-      <c r="N23" s="207"/>
-      <c r="O23" s="208" t="s">
+      <c r="K23" s="151"/>
+      <c r="L23" s="149"/>
+      <c r="M23" s="149"/>
+      <c r="N23" s="149"/>
+      <c r="O23" s="150" t="s">
         <v>1268</v>
       </c>
-      <c r="P23" s="208" t="s">
+      <c r="P23" s="150" t="s">
         <v>1270</v>
       </c>
-      <c r="Q23" s="207"/>
-      <c r="R23" s="207"/>
-      <c r="V23" s="143"/>
+      <c r="Q23" s="149"/>
+      <c r="R23" s="149"/>
+      <c r="V23" s="168"/>
       <c r="W23" s="9" t="s">
         <v>816</v>
       </c>
@@ -22307,8 +22322,8 @@
       </c>
     </row>
     <row r="24" spans="7:24">
-      <c r="K24" s="209"/>
-      <c r="V24" s="143"/>
+      <c r="K24" s="151"/>
+      <c r="V24" s="168"/>
       <c r="W24" s="9" t="s">
         <v>817</v>
       </c>
@@ -22317,13 +22332,13 @@
       </c>
     </row>
     <row r="25" spans="7:24">
-      <c r="K25" s="209">
+      <c r="K25" s="151">
         <v>2</v>
       </c>
       <c r="L25" s="5" t="s">
         <v>892</v>
       </c>
-      <c r="V25" s="143"/>
+      <c r="V25" s="168"/>
       <c r="W25" s="9" t="s">
         <v>818</v>
       </c>
@@ -22332,7 +22347,7 @@
       </c>
     </row>
     <row r="26" spans="7:24">
-      <c r="K26" s="209"/>
+      <c r="K26" s="151"/>
       <c r="M26" s="111" t="s">
         <v>894</v>
       </c>
@@ -22342,32 +22357,32 @@
       <c r="O26" t="s">
         <v>898</v>
       </c>
-      <c r="V26" s="143"/>
+      <c r="V26" s="168"/>
       <c r="W26" s="9" t="s">
         <v>825</v>
       </c>
       <c r="X26" s="92"/>
     </row>
     <row r="27" spans="7:24">
-      <c r="K27" s="209"/>
+      <c r="K27" s="151"/>
       <c r="M27" t="s">
         <v>895</v>
       </c>
       <c r="N27" t="s">
         <v>897</v>
       </c>
-      <c r="V27" s="143"/>
+      <c r="V27" s="168"/>
       <c r="W27" s="9" t="s">
         <v>826</v>
       </c>
       <c r="X27" s="92"/>
     </row>
     <row r="28" spans="7:24">
-      <c r="K28" s="209"/>
+      <c r="K28" s="151"/>
       <c r="N28" t="s">
         <v>899</v>
       </c>
-      <c r="V28" s="143"/>
+      <c r="V28" s="168"/>
       <c r="W28" s="9" t="s">
         <v>827</v>
       </c>
@@ -22376,11 +22391,11 @@
       </c>
     </row>
     <row r="29" spans="7:24">
-      <c r="K29" s="209"/>
+      <c r="K29" s="151"/>
       <c r="N29" t="s">
         <v>900</v>
       </c>
-      <c r="V29" s="144"/>
+      <c r="V29" s="169"/>
       <c r="W29" s="9" t="s">
         <v>828</v>
       </c>
@@ -22389,14 +22404,14 @@
       </c>
     </row>
     <row r="30" spans="7:24">
-      <c r="K30" s="209"/>
+      <c r="K30" s="151"/>
       <c r="M30" t="s">
         <v>901</v>
       </c>
       <c r="N30" t="s">
         <v>853</v>
       </c>
-      <c r="V30" s="139" t="s">
+      <c r="V30" s="164" t="s">
         <v>832</v>
       </c>
       <c r="W30" s="49" t="s">
@@ -22405,11 +22420,11 @@
       <c r="X30" s="113"/>
     </row>
     <row r="31" spans="7:24">
-      <c r="K31" s="209"/>
+      <c r="K31" s="151"/>
       <c r="N31" t="s">
         <v>902</v>
       </c>
-      <c r="V31" s="140"/>
+      <c r="V31" s="165"/>
       <c r="W31" s="49" t="s">
         <v>823</v>
       </c>
@@ -22419,19 +22434,19 @@
       <c r="G32" t="s">
         <v>911</v>
       </c>
-      <c r="K32" s="209"/>
-      <c r="L32" s="207"/>
-      <c r="M32" s="207"/>
-      <c r="N32" s="207"/>
-      <c r="O32" s="208" t="s">
+      <c r="K32" s="151"/>
+      <c r="L32" s="149"/>
+      <c r="M32" s="149"/>
+      <c r="N32" s="149"/>
+      <c r="O32" s="150" t="s">
         <v>903</v>
       </c>
-      <c r="P32" s="208" t="s">
+      <c r="P32" s="150" t="s">
         <v>904</v>
       </c>
-      <c r="Q32" s="207"/>
-      <c r="R32" s="207"/>
-      <c r="V32" s="141"/>
+      <c r="Q32" s="149"/>
+      <c r="R32" s="149"/>
+      <c r="V32" s="166"/>
       <c r="W32" s="49" t="s">
         <v>824</v>
       </c>
@@ -22444,7 +22459,7 @@
       <c r="G33" t="s">
         <v>912</v>
       </c>
-      <c r="K33" s="209"/>
+      <c r="K33" s="151"/>
     </row>
     <row r="34" spans="6:17">
       <c r="F34">
@@ -22453,7 +22468,7 @@
       <c r="G34" t="s">
         <v>913</v>
       </c>
-      <c r="K34" s="209">
+      <c r="K34" s="151">
         <v>3</v>
       </c>
       <c r="L34" s="5" t="s">
@@ -22503,19 +22518,19 @@
       </c>
     </row>
     <row r="41" spans="6:17" ht="15.75" thickBot="1">
-      <c r="L41" s="207"/>
-      <c r="M41" s="207"/>
-      <c r="N41" s="207"/>
-      <c r="O41" s="208" t="s">
+      <c r="L41" s="149"/>
+      <c r="M41" s="149"/>
+      <c r="N41" s="149"/>
+      <c r="O41" s="150" t="s">
         <v>908</v>
       </c>
-      <c r="P41" s="208" t="s">
+      <c r="P41" s="150" t="s">
         <v>893</v>
       </c>
-      <c r="Q41" s="207"/>
+      <c r="Q41" s="149"/>
     </row>
     <row r="44" spans="6:17">
-      <c r="P44" s="206"/>
+      <c r="P44" s="148"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -22571,7 +22586,7 @@
       <c r="R5" s="13" t="s">
         <v>352</v>
       </c>
-      <c r="S5" s="145" t="s">
+      <c r="S5" s="170" t="s">
         <v>810</v>
       </c>
     </row>
@@ -22588,7 +22603,7 @@
       <c r="R6" s="9" t="s">
         <v>602</v>
       </c>
-      <c r="S6" s="145"/>
+      <c r="S6" s="170"/>
     </row>
     <row r="7" spans="3:20">
       <c r="O7" s="81" t="s">
@@ -22603,7 +22618,7 @@
       <c r="R7" s="9" t="s">
         <v>603</v>
       </c>
-      <c r="S7" s="145"/>
+      <c r="S7" s="170"/>
     </row>
     <row r="8" spans="3:20">
       <c r="O8" s="81" t="s">
@@ -22618,7 +22633,7 @@
       <c r="R8" s="9" t="s">
         <v>350</v>
       </c>
-      <c r="S8" s="145"/>
+      <c r="S8" s="170"/>
     </row>
     <row r="9" spans="3:20">
       <c r="O9" s="81" t="s">
@@ -22633,7 +22648,7 @@
       <c r="R9" s="9" t="s">
         <v>349</v>
       </c>
-      <c r="S9" s="145"/>
+      <c r="S9" s="170"/>
     </row>
     <row r="10" spans="3:20">
       <c r="Q10" s="9" t="s">
@@ -22658,7 +22673,7 @@
       </c>
     </row>
     <row r="15" spans="3:20">
-      <c r="Q15" s="142" t="s">
+      <c r="Q15" s="167" t="s">
         <v>833</v>
       </c>
       <c r="R15" s="9" t="s">
@@ -22693,7 +22708,7 @@
       <c r="J16" s="10" t="s">
         <v>814</v>
       </c>
-      <c r="Q16" s="143"/>
+      <c r="Q16" s="168"/>
       <c r="R16" s="9" t="s">
         <v>816</v>
       </c>
@@ -22703,7 +22718,7 @@
     </row>
     <row r="17" spans="10:19">
       <c r="J17" s="81"/>
-      <c r="Q17" s="143"/>
+      <c r="Q17" s="168"/>
       <c r="R17" s="9" t="s">
         <v>817</v>
       </c>
@@ -22712,7 +22727,7 @@
       </c>
     </row>
     <row r="18" spans="10:19">
-      <c r="Q18" s="143"/>
+      <c r="Q18" s="168"/>
       <c r="R18" s="9" t="s">
         <v>818</v>
       </c>
@@ -22721,21 +22736,21 @@
       </c>
     </row>
     <row r="19" spans="10:19">
-      <c r="Q19" s="143"/>
+      <c r="Q19" s="168"/>
       <c r="R19" s="9" t="s">
         <v>825</v>
       </c>
       <c r="S19" s="92"/>
     </row>
     <row r="20" spans="10:19">
-      <c r="Q20" s="143"/>
+      <c r="Q20" s="168"/>
       <c r="R20" s="9" t="s">
         <v>826</v>
       </c>
       <c r="S20" s="92"/>
     </row>
     <row r="21" spans="10:19">
-      <c r="Q21" s="143"/>
+      <c r="Q21" s="168"/>
       <c r="R21" s="9" t="s">
         <v>827</v>
       </c>
@@ -22744,7 +22759,7 @@
       </c>
     </row>
     <row r="22" spans="10:19">
-      <c r="Q22" s="144"/>
+      <c r="Q22" s="169"/>
       <c r="R22" s="9" t="s">
         <v>828</v>
       </c>
@@ -22753,7 +22768,7 @@
       </c>
     </row>
     <row r="23" spans="10:19">
-      <c r="Q23" s="142" t="s">
+      <c r="Q23" s="167" t="s">
         <v>832</v>
       </c>
       <c r="R23" s="9" t="s">
@@ -22762,14 +22777,14 @@
       <c r="S23" s="92"/>
     </row>
     <row r="24" spans="10:19">
-      <c r="Q24" s="143"/>
+      <c r="Q24" s="168"/>
       <c r="R24" s="9" t="s">
         <v>823</v>
       </c>
       <c r="S24" s="92"/>
     </row>
     <row r="25" spans="10:19">
-      <c r="Q25" s="144"/>
+      <c r="Q25" s="169"/>
       <c r="R25" s="9" t="s">
         <v>824</v>
       </c>
@@ -22835,39 +22850,39 @@
       <c r="B1" t="s">
         <v>861</v>
       </c>
-      <c r="J1" s="146" t="s">
+      <c r="J1" s="171" t="s">
         <v>954</v>
       </c>
-      <c r="K1" s="147"/>
-      <c r="L1" s="147"/>
-      <c r="M1" s="147"/>
-      <c r="N1" s="147"/>
-      <c r="O1" s="147"/>
-      <c r="P1" s="147"/>
-      <c r="Q1" s="147"/>
+      <c r="K1" s="172"/>
+      <c r="L1" s="172"/>
+      <c r="M1" s="172"/>
+      <c r="N1" s="172"/>
+      <c r="O1" s="172"/>
+      <c r="P1" s="172"/>
+      <c r="Q1" s="172"/>
     </row>
     <row r="2" spans="1:17">
-      <c r="J2" s="147"/>
-      <c r="K2" s="147"/>
-      <c r="L2" s="147"/>
-      <c r="M2" s="147"/>
-      <c r="N2" s="147"/>
-      <c r="O2" s="147"/>
-      <c r="P2" s="147"/>
-      <c r="Q2" s="147"/>
+      <c r="J2" s="172"/>
+      <c r="K2" s="172"/>
+      <c r="L2" s="172"/>
+      <c r="M2" s="172"/>
+      <c r="N2" s="172"/>
+      <c r="O2" s="172"/>
+      <c r="P2" s="172"/>
+      <c r="Q2" s="172"/>
     </row>
     <row r="3" spans="1:17">
       <c r="A3" s="6" t="s">
         <v>862</v>
       </c>
-      <c r="J3" s="147"/>
-      <c r="K3" s="147"/>
-      <c r="L3" s="147"/>
-      <c r="M3" s="147"/>
-      <c r="N3" s="147"/>
-      <c r="O3" s="147"/>
-      <c r="P3" s="147"/>
-      <c r="Q3" s="147"/>
+      <c r="J3" s="172"/>
+      <c r="K3" s="172"/>
+      <c r="L3" s="172"/>
+      <c r="M3" s="172"/>
+      <c r="N3" s="172"/>
+      <c r="O3" s="172"/>
+      <c r="P3" s="172"/>
+      <c r="Q3" s="172"/>
     </row>
     <row r="4" spans="1:17">
       <c r="A4" t="s">
@@ -22879,24 +22894,24 @@
       <c r="D4" t="s">
         <v>864</v>
       </c>
-      <c r="J4" s="147"/>
-      <c r="K4" s="147"/>
-      <c r="L4" s="147"/>
-      <c r="M4" s="147"/>
-      <c r="N4" s="147"/>
-      <c r="O4" s="147"/>
-      <c r="P4" s="147"/>
-      <c r="Q4" s="147"/>
+      <c r="J4" s="172"/>
+      <c r="K4" s="172"/>
+      <c r="L4" s="172"/>
+      <c r="M4" s="172"/>
+      <c r="N4" s="172"/>
+      <c r="O4" s="172"/>
+      <c r="P4" s="172"/>
+      <c r="Q4" s="172"/>
     </row>
     <row r="5" spans="1:17">
-      <c r="J5" s="147"/>
-      <c r="K5" s="147"/>
-      <c r="L5" s="147"/>
-      <c r="M5" s="147"/>
-      <c r="N5" s="147"/>
-      <c r="O5" s="147"/>
-      <c r="P5" s="147"/>
-      <c r="Q5" s="147"/>
+      <c r="J5" s="172"/>
+      <c r="K5" s="172"/>
+      <c r="L5" s="172"/>
+      <c r="M5" s="172"/>
+      <c r="N5" s="172"/>
+      <c r="O5" s="172"/>
+      <c r="P5" s="172"/>
+      <c r="Q5" s="172"/>
     </row>
     <row r="6" spans="1:17" ht="15.75" thickBot="1">
       <c r="A6" t="s">
@@ -22905,38 +22920,38 @@
       <c r="E6" t="s">
         <v>920</v>
       </c>
-      <c r="J6" s="147"/>
-      <c r="K6" s="147"/>
-      <c r="L6" s="147"/>
-      <c r="M6" s="147"/>
-      <c r="N6" s="147"/>
-      <c r="O6" s="147"/>
-      <c r="P6" s="147"/>
-      <c r="Q6" s="147"/>
+      <c r="J6" s="172"/>
+      <c r="K6" s="172"/>
+      <c r="L6" s="172"/>
+      <c r="M6" s="172"/>
+      <c r="N6" s="172"/>
+      <c r="O6" s="172"/>
+      <c r="P6" s="172"/>
+      <c r="Q6" s="172"/>
     </row>
     <row r="7" spans="1:17" ht="15.75" thickBot="1">
       <c r="A7" s="106" t="s">
         <v>866</v>
       </c>
-      <c r="J7" s="147"/>
-      <c r="K7" s="147"/>
-      <c r="L7" s="147"/>
-      <c r="M7" s="147"/>
-      <c r="N7" s="147"/>
-      <c r="O7" s="147"/>
-      <c r="P7" s="147"/>
-      <c r="Q7" s="147"/>
+      <c r="J7" s="172"/>
+      <c r="K7" s="172"/>
+      <c r="L7" s="172"/>
+      <c r="M7" s="172"/>
+      <c r="N7" s="172"/>
+      <c r="O7" s="172"/>
+      <c r="P7" s="172"/>
+      <c r="Q7" s="172"/>
     </row>
     <row r="8" spans="1:17">
       <c r="A8" s="121"/>
-      <c r="J8" s="147"/>
-      <c r="K8" s="147"/>
-      <c r="L8" s="147"/>
-      <c r="M8" s="147"/>
-      <c r="N8" s="147"/>
-      <c r="O8" s="147"/>
-      <c r="P8" s="147"/>
-      <c r="Q8" s="147"/>
+      <c r="J8" s="172"/>
+      <c r="K8" s="172"/>
+      <c r="L8" s="172"/>
+      <c r="M8" s="172"/>
+      <c r="N8" s="172"/>
+      <c r="O8" s="172"/>
+      <c r="P8" s="172"/>
+      <c r="Q8" s="172"/>
     </row>
     <row r="9" spans="1:17">
       <c r="A9" t="s">
@@ -22945,14 +22960,14 @@
       <c r="B9" t="s">
         <v>926</v>
       </c>
-      <c r="J9" s="147"/>
-      <c r="K9" s="147"/>
-      <c r="L9" s="147"/>
-      <c r="M9" s="147"/>
-      <c r="N9" s="147"/>
-      <c r="O9" s="147"/>
-      <c r="P9" s="147"/>
-      <c r="Q9" s="147"/>
+      <c r="J9" s="172"/>
+      <c r="K9" s="172"/>
+      <c r="L9" s="172"/>
+      <c r="M9" s="172"/>
+      <c r="N9" s="172"/>
+      <c r="O9" s="172"/>
+      <c r="P9" s="172"/>
+      <c r="Q9" s="172"/>
     </row>
     <row r="10" spans="1:17">
       <c r="A10" t="s">
@@ -22973,14 +22988,14 @@
       <c r="H10" t="s">
         <v>952</v>
       </c>
-      <c r="J10" s="147"/>
-      <c r="K10" s="147"/>
-      <c r="L10" s="147"/>
-      <c r="M10" s="147"/>
-      <c r="N10" s="147"/>
-      <c r="O10" s="147"/>
-      <c r="P10" s="147"/>
-      <c r="Q10" s="147"/>
+      <c r="J10" s="172"/>
+      <c r="K10" s="172"/>
+      <c r="L10" s="172"/>
+      <c r="M10" s="172"/>
+      <c r="N10" s="172"/>
+      <c r="O10" s="172"/>
+      <c r="P10" s="172"/>
+      <c r="Q10" s="172"/>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" t="s">
@@ -23001,14 +23016,14 @@
       <c r="H11" t="s">
         <v>953</v>
       </c>
-      <c r="J11" s="147"/>
-      <c r="K11" s="147"/>
-      <c r="L11" s="147"/>
-      <c r="M11" s="147"/>
-      <c r="N11" s="147"/>
-      <c r="O11" s="147"/>
-      <c r="P11" s="147"/>
-      <c r="Q11" s="147"/>
+      <c r="J11" s="172"/>
+      <c r="K11" s="172"/>
+      <c r="L11" s="172"/>
+      <c r="M11" s="172"/>
+      <c r="N11" s="172"/>
+      <c r="O11" s="172"/>
+      <c r="P11" s="172"/>
+      <c r="Q11" s="172"/>
     </row>
     <row r="12" spans="1:17">
       <c r="B12" t="s">
@@ -23023,14 +23038,14 @@
       <c r="H12" t="s">
         <v>953</v>
       </c>
-      <c r="J12" s="147"/>
-      <c r="K12" s="147"/>
-      <c r="L12" s="147"/>
-      <c r="M12" s="147"/>
-      <c r="N12" s="147"/>
-      <c r="O12" s="147"/>
-      <c r="P12" s="147"/>
-      <c r="Q12" s="147"/>
+      <c r="J12" s="172"/>
+      <c r="K12" s="172"/>
+      <c r="L12" s="172"/>
+      <c r="M12" s="172"/>
+      <c r="N12" s="172"/>
+      <c r="O12" s="172"/>
+      <c r="P12" s="172"/>
+      <c r="Q12" s="172"/>
     </row>
     <row r="13" spans="1:17">
       <c r="F13" t="s">
@@ -23042,24 +23057,24 @@
       <c r="H13" t="s">
         <v>953</v>
       </c>
-      <c r="J13" s="147"/>
-      <c r="K13" s="147"/>
-      <c r="L13" s="147"/>
-      <c r="M13" s="147"/>
-      <c r="N13" s="147"/>
-      <c r="O13" s="147"/>
-      <c r="P13" s="147"/>
-      <c r="Q13" s="147"/>
+      <c r="J13" s="172"/>
+      <c r="K13" s="172"/>
+      <c r="L13" s="172"/>
+      <c r="M13" s="172"/>
+      <c r="N13" s="172"/>
+      <c r="O13" s="172"/>
+      <c r="P13" s="172"/>
+      <c r="Q13" s="172"/>
     </row>
     <row r="14" spans="1:17">
-      <c r="J14" s="147"/>
-      <c r="K14" s="147"/>
-      <c r="L14" s="147"/>
-      <c r="M14" s="147"/>
-      <c r="N14" s="147"/>
-      <c r="O14" s="147"/>
-      <c r="P14" s="147"/>
-      <c r="Q14" s="147"/>
+      <c r="J14" s="172"/>
+      <c r="K14" s="172"/>
+      <c r="L14" s="172"/>
+      <c r="M14" s="172"/>
+      <c r="N14" s="172"/>
+      <c r="O14" s="172"/>
+      <c r="P14" s="172"/>
+      <c r="Q14" s="172"/>
     </row>
     <row r="15" spans="1:17">
       <c r="A15" t="s">
@@ -23068,27 +23083,27 @@
       <c r="C15" t="s">
         <v>949</v>
       </c>
-      <c r="J15" s="147"/>
-      <c r="K15" s="147"/>
-      <c r="L15" s="147"/>
-      <c r="M15" s="147"/>
-      <c r="N15" s="147"/>
-      <c r="O15" s="147"/>
-      <c r="P15" s="147"/>
-      <c r="Q15" s="147"/>
+      <c r="J15" s="172"/>
+      <c r="K15" s="172"/>
+      <c r="L15" s="172"/>
+      <c r="M15" s="172"/>
+      <c r="N15" s="172"/>
+      <c r="O15" s="172"/>
+      <c r="P15" s="172"/>
+      <c r="Q15" s="172"/>
     </row>
     <row r="16" spans="1:17">
       <c r="A16" t="s">
         <v>939</v>
       </c>
-      <c r="J16" s="147"/>
-      <c r="K16" s="147"/>
-      <c r="L16" s="147"/>
-      <c r="M16" s="147"/>
-      <c r="N16" s="147"/>
-      <c r="O16" s="147"/>
-      <c r="P16" s="147"/>
-      <c r="Q16" s="147"/>
+      <c r="J16" s="172"/>
+      <c r="K16" s="172"/>
+      <c r="L16" s="172"/>
+      <c r="M16" s="172"/>
+      <c r="N16" s="172"/>
+      <c r="O16" s="172"/>
+      <c r="P16" s="172"/>
+      <c r="Q16" s="172"/>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="5" t="s">
@@ -23331,19 +23346,19 @@
       <c r="E7" s="31" t="s">
         <v>449</v>
       </c>
-      <c r="F7" s="148" t="s">
+      <c r="F7" s="173" t="s">
         <v>441</v>
       </c>
-      <c r="G7" s="148"/>
-      <c r="H7" s="148"/>
-      <c r="I7" s="148"/>
-      <c r="J7" s="148"/>
-      <c r="K7" s="148"/>
-      <c r="L7" s="148"/>
-      <c r="M7" s="148"/>
-      <c r="N7" s="148"/>
-      <c r="O7" s="148"/>
-      <c r="P7" s="148"/>
+      <c r="G7" s="173"/>
+      <c r="H7" s="173"/>
+      <c r="I7" s="173"/>
+      <c r="J7" s="173"/>
+      <c r="K7" s="173"/>
+      <c r="L7" s="173"/>
+      <c r="M7" s="173"/>
+      <c r="N7" s="173"/>
+      <c r="O7" s="173"/>
+      <c r="P7" s="173"/>
     </row>
     <row r="8" spans="1:17">
       <c r="B8" s="32" t="s">
@@ -23567,40 +23582,40 @@
       <c r="A24" s="35" t="s">
         <v>455</v>
       </c>
-      <c r="B24" s="149" t="s">
+      <c r="B24" s="174" t="s">
         <v>457</v>
       </c>
-      <c r="C24" s="149"/>
-      <c r="D24" s="149"/>
-      <c r="E24" s="149"/>
-      <c r="F24" s="149"/>
-      <c r="G24" s="149"/>
+      <c r="C24" s="174"/>
+      <c r="D24" s="174"/>
+      <c r="E24" s="174"/>
+      <c r="F24" s="174"/>
+      <c r="G24" s="174"/>
     </row>
     <row r="25" spans="1:7" ht="30">
       <c r="A25" s="35" t="s">
         <v>462</v>
       </c>
-      <c r="B25" s="150" t="s">
+      <c r="B25" s="175" t="s">
         <v>464</v>
       </c>
-      <c r="C25" s="150"/>
-      <c r="D25" s="150"/>
-      <c r="E25" s="150"/>
-      <c r="F25" s="150"/>
-      <c r="G25" s="150"/>
+      <c r="C25" s="175"/>
+      <c r="D25" s="175"/>
+      <c r="E25" s="175"/>
+      <c r="F25" s="175"/>
+      <c r="G25" s="175"/>
     </row>
     <row r="26" spans="1:7" ht="159" customHeight="1">
       <c r="A26" s="35" t="s">
         <v>459</v>
       </c>
-      <c r="B26" s="149" t="s">
+      <c r="B26" s="174" t="s">
         <v>460</v>
       </c>
-      <c r="C26" s="149"/>
-      <c r="D26" s="149"/>
-      <c r="E26" s="149"/>
-      <c r="F26" s="149"/>
-      <c r="G26" s="149"/>
+      <c r="C26" s="174"/>
+      <c r="D26" s="174"/>
+      <c r="E26" s="174"/>
+      <c r="F26" s="174"/>
+      <c r="G26" s="174"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -24115,29 +24130,29 @@
       <c r="B27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="C27" s="153" t="s">
+      <c r="C27" s="178" t="s">
         <v>622</v>
       </c>
-      <c r="D27" s="154"/>
+      <c r="D27" s="179"/>
       <c r="E27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="F27" s="153" t="s">
+      <c r="F27" s="178" t="s">
         <v>622</v>
       </c>
-      <c r="G27" s="154"/>
+      <c r="G27" s="179"/>
       <c r="H27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="I27" s="153" t="s">
+      <c r="I27" s="178" t="s">
         <v>622</v>
       </c>
-      <c r="J27" s="154"/>
-      <c r="L27" s="165" t="s">
+      <c r="J27" s="179"/>
+      <c r="L27" s="176" t="s">
         <v>694</v>
       </c>
-      <c r="M27" s="165"/>
-      <c r="N27" s="165"/>
+      <c r="M27" s="176"/>
+      <c r="N27" s="176"/>
     </row>
     <row r="28" spans="1:14" ht="32.25" thickBot="1">
       <c r="A28" s="81">
@@ -24146,29 +24161,29 @@
       <c r="B28" s="69" t="s">
         <v>623</v>
       </c>
-      <c r="C28" s="151" t="s">
+      <c r="C28" s="186" t="s">
         <v>624</v>
       </c>
-      <c r="D28" s="152"/>
+      <c r="D28" s="187"/>
       <c r="E28" s="70" t="s">
         <v>645</v>
       </c>
-      <c r="F28" s="155" t="s">
+      <c r="F28" s="180" t="s">
         <v>646</v>
       </c>
-      <c r="G28" s="156"/>
+      <c r="G28" s="181"/>
       <c r="H28" s="69" t="s">
         <v>667</v>
       </c>
-      <c r="I28" s="151" t="s">
+      <c r="I28" s="186" t="s">
         <v>668</v>
       </c>
-      <c r="J28" s="152"/>
-      <c r="L28" s="166" t="s">
+      <c r="J28" s="187"/>
+      <c r="L28" s="177" t="s">
         <v>695</v>
       </c>
-      <c r="M28" s="166"/>
-      <c r="N28" s="166"/>
+      <c r="M28" s="177"/>
+      <c r="N28" s="177"/>
     </row>
     <row r="29" spans="1:14" ht="31.5" thickBot="1">
       <c r="A29" s="81">
@@ -24177,29 +24192,29 @@
       <c r="B29" s="70" t="s">
         <v>625</v>
       </c>
-      <c r="C29" s="155" t="s">
+      <c r="C29" s="180" t="s">
         <v>626</v>
       </c>
-      <c r="D29" s="156"/>
+      <c r="D29" s="181"/>
       <c r="E29" s="69" t="s">
         <v>647</v>
       </c>
-      <c r="F29" s="151" t="s">
+      <c r="F29" s="186" t="s">
         <v>648</v>
       </c>
-      <c r="G29" s="152"/>
+      <c r="G29" s="187"/>
       <c r="H29" s="70" t="s">
         <v>669</v>
       </c>
-      <c r="I29" s="159" t="s">
+      <c r="I29" s="190" t="s">
         <v>670</v>
       </c>
-      <c r="J29" s="160"/>
-      <c r="L29" s="165" t="s">
+      <c r="J29" s="191"/>
+      <c r="L29" s="176" t="s">
         <v>696</v>
       </c>
-      <c r="M29" s="165"/>
-      <c r="N29" s="165"/>
+      <c r="M29" s="176"/>
+      <c r="N29" s="176"/>
     </row>
     <row r="30" spans="1:14" ht="15.75" thickBot="1">
       <c r="A30" s="81">
@@ -24208,29 +24223,29 @@
       <c r="B30" s="69" t="s">
         <v>627</v>
       </c>
-      <c r="C30" s="151" t="s">
+      <c r="C30" s="186" t="s">
         <v>628</v>
       </c>
-      <c r="D30" s="152"/>
+      <c r="D30" s="187"/>
       <c r="E30" s="70" t="s">
         <v>649</v>
       </c>
-      <c r="F30" s="155" t="s">
+      <c r="F30" s="180" t="s">
         <v>650</v>
       </c>
-      <c r="G30" s="156"/>
+      <c r="G30" s="181"/>
       <c r="H30" s="69" t="s">
         <v>671</v>
       </c>
-      <c r="I30" s="151" t="s">
+      <c r="I30" s="186" t="s">
         <v>672</v>
       </c>
-      <c r="J30" s="152"/>
-      <c r="L30" s="166" t="s">
+      <c r="J30" s="187"/>
+      <c r="L30" s="177" t="s">
         <v>697</v>
       </c>
-      <c r="M30" s="166"/>
-      <c r="N30" s="166"/>
+      <c r="M30" s="177"/>
+      <c r="N30" s="177"/>
     </row>
     <row r="31" spans="1:14" ht="17.25" customHeight="1" thickBot="1">
       <c r="A31" s="81">
@@ -24239,29 +24254,29 @@
       <c r="B31" s="70" t="s">
         <v>629</v>
       </c>
-      <c r="C31" s="155" t="s">
+      <c r="C31" s="180" t="s">
         <v>630</v>
       </c>
-      <c r="D31" s="156"/>
+      <c r="D31" s="181"/>
       <c r="E31" s="69" t="s">
         <v>651</v>
       </c>
-      <c r="F31" s="151" t="s">
+      <c r="F31" s="186" t="s">
         <v>652</v>
       </c>
-      <c r="G31" s="152"/>
+      <c r="G31" s="187"/>
       <c r="H31" s="70" t="s">
         <v>673</v>
       </c>
-      <c r="I31" s="155" t="s">
+      <c r="I31" s="180" t="s">
         <v>674</v>
       </c>
-      <c r="J31" s="156"/>
-      <c r="L31" s="165" t="s">
+      <c r="J31" s="181"/>
+      <c r="L31" s="176" t="s">
         <v>698</v>
       </c>
-      <c r="M31" s="165"/>
-      <c r="N31" s="165"/>
+      <c r="M31" s="176"/>
+      <c r="N31" s="176"/>
     </row>
     <row r="32" spans="1:14" ht="43.5" customHeight="1" thickBot="1">
       <c r="A32" s="81">
@@ -24270,29 +24285,29 @@
       <c r="B32" s="69" t="s">
         <v>631</v>
       </c>
-      <c r="C32" s="151" t="s">
+      <c r="C32" s="186" t="s">
         <v>632</v>
       </c>
-      <c r="D32" s="152"/>
+      <c r="D32" s="187"/>
       <c r="E32" s="70" t="s">
         <v>653</v>
       </c>
-      <c r="F32" s="155" t="s">
+      <c r="F32" s="180" t="s">
         <v>654</v>
       </c>
-      <c r="G32" s="156"/>
+      <c r="G32" s="181"/>
       <c r="H32" s="69" t="s">
         <v>675</v>
       </c>
-      <c r="I32" s="151" t="s">
+      <c r="I32" s="186" t="s">
         <v>676</v>
       </c>
-      <c r="J32" s="152"/>
-      <c r="L32" s="166" t="s">
+      <c r="J32" s="187"/>
+      <c r="L32" s="177" t="s">
         <v>699</v>
       </c>
-      <c r="M32" s="166"/>
-      <c r="N32" s="166"/>
+      <c r="M32" s="177"/>
+      <c r="N32" s="177"/>
     </row>
     <row r="33" spans="1:14" ht="31.5" customHeight="1" thickBot="1">
       <c r="A33" s="81">
@@ -24301,29 +24316,29 @@
       <c r="B33" s="70" t="s">
         <v>633</v>
       </c>
-      <c r="C33" s="155" t="s">
+      <c r="C33" s="180" t="s">
         <v>634</v>
       </c>
-      <c r="D33" s="156"/>
+      <c r="D33" s="181"/>
       <c r="E33" s="69" t="s">
         <v>655</v>
       </c>
-      <c r="F33" s="151" t="s">
+      <c r="F33" s="186" t="s">
         <v>656</v>
       </c>
-      <c r="G33" s="152"/>
+      <c r="G33" s="187"/>
       <c r="H33" s="70" t="s">
         <v>677</v>
       </c>
-      <c r="I33" s="157" t="s">
+      <c r="I33" s="188" t="s">
         <v>678</v>
       </c>
-      <c r="J33" s="158"/>
-      <c r="L33" s="165" t="s">
+      <c r="J33" s="189"/>
+      <c r="L33" s="176" t="s">
         <v>700</v>
       </c>
-      <c r="M33" s="165"/>
-      <c r="N33" s="165"/>
+      <c r="M33" s="176"/>
+      <c r="N33" s="176"/>
     </row>
     <row r="34" spans="1:14" ht="28.5" customHeight="1" thickBot="1">
       <c r="A34" s="81">
@@ -24332,29 +24347,29 @@
       <c r="B34" s="69" t="s">
         <v>635</v>
       </c>
-      <c r="C34" s="151" t="s">
+      <c r="C34" s="186" t="s">
         <v>636</v>
       </c>
-      <c r="D34" s="152"/>
+      <c r="D34" s="187"/>
       <c r="E34" s="70" t="s">
         <v>657</v>
       </c>
-      <c r="F34" s="155" t="s">
+      <c r="F34" s="180" t="s">
         <v>658</v>
       </c>
-      <c r="G34" s="156"/>
+      <c r="G34" s="181"/>
       <c r="H34" s="69" t="s">
         <v>679</v>
       </c>
-      <c r="I34" s="161" t="s">
+      <c r="I34" s="184" t="s">
         <v>680</v>
       </c>
-      <c r="J34" s="162"/>
-      <c r="L34" s="166" t="s">
+      <c r="J34" s="185"/>
+      <c r="L34" s="177" t="s">
         <v>701</v>
       </c>
-      <c r="M34" s="166"/>
-      <c r="N34" s="166"/>
+      <c r="M34" s="177"/>
+      <c r="N34" s="177"/>
     </row>
     <row r="35" spans="1:14" ht="31.5" customHeight="1" thickBot="1">
       <c r="A35" s="81">
@@ -24363,29 +24378,29 @@
       <c r="B35" s="70" t="s">
         <v>637</v>
       </c>
-      <c r="C35" s="155" t="s">
+      <c r="C35" s="180" t="s">
         <v>638</v>
       </c>
-      <c r="D35" s="156"/>
+      <c r="D35" s="181"/>
       <c r="E35" s="69" t="s">
         <v>659</v>
       </c>
-      <c r="F35" s="151" t="s">
+      <c r="F35" s="186" t="s">
         <v>660</v>
       </c>
-      <c r="G35" s="152"/>
+      <c r="G35" s="187"/>
       <c r="H35" s="77" t="s">
         <v>681</v>
       </c>
-      <c r="I35" s="155" t="s">
+      <c r="I35" s="180" t="s">
         <v>682</v>
       </c>
-      <c r="J35" s="156"/>
-      <c r="L35" s="165" t="s">
+      <c r="J35" s="181"/>
+      <c r="L35" s="176" t="s">
         <v>702</v>
       </c>
-      <c r="M35" s="165"/>
-      <c r="N35" s="165"/>
+      <c r="M35" s="176"/>
+      <c r="N35" s="176"/>
     </row>
     <row r="36" spans="1:14" ht="60.75" thickBot="1">
       <c r="A36" s="81">
@@ -24394,17 +24409,17 @@
       <c r="B36" s="69" t="s">
         <v>639</v>
       </c>
-      <c r="C36" s="151" t="s">
+      <c r="C36" s="186" t="s">
         <v>640</v>
       </c>
-      <c r="D36" s="152"/>
+      <c r="D36" s="187"/>
       <c r="E36" s="70" t="s">
         <v>661</v>
       </c>
-      <c r="F36" s="155" t="s">
+      <c r="F36" s="180" t="s">
         <v>662</v>
       </c>
-      <c r="G36" s="156"/>
+      <c r="G36" s="181"/>
       <c r="H36" s="78"/>
       <c r="I36" s="71" t="s">
         <v>683</v>
@@ -24412,11 +24427,11 @@
       <c r="J36" s="72" t="s">
         <v>684</v>
       </c>
-      <c r="L36" s="166" t="s">
+      <c r="L36" s="177" t="s">
         <v>703</v>
       </c>
-      <c r="M36" s="166"/>
-      <c r="N36" s="166"/>
+      <c r="M36" s="177"/>
+      <c r="N36" s="177"/>
     </row>
     <row r="37" spans="1:14" ht="75.75" thickBot="1">
       <c r="A37" s="81">
@@ -24425,17 +24440,17 @@
       <c r="B37" s="70" t="s">
         <v>641</v>
       </c>
-      <c r="C37" s="155" t="s">
+      <c r="C37" s="180" t="s">
         <v>642</v>
       </c>
-      <c r="D37" s="156"/>
+      <c r="D37" s="181"/>
       <c r="E37" s="69" t="s">
         <v>663</v>
       </c>
-      <c r="F37" s="151" t="s">
+      <c r="F37" s="186" t="s">
         <v>664</v>
       </c>
-      <c r="G37" s="152"/>
+      <c r="G37" s="187"/>
       <c r="H37" s="78"/>
       <c r="I37" s="73" t="s">
         <v>685</v>
@@ -24451,17 +24466,17 @@
       <c r="B38" s="69" t="s">
         <v>643</v>
       </c>
-      <c r="C38" s="151" t="s">
+      <c r="C38" s="186" t="s">
         <v>644</v>
       </c>
-      <c r="D38" s="152"/>
+      <c r="D38" s="187"/>
       <c r="E38" s="70" t="s">
         <v>665</v>
       </c>
-      <c r="F38" s="155" t="s">
+      <c r="F38" s="180" t="s">
         <v>666</v>
       </c>
-      <c r="G38" s="156"/>
+      <c r="G38" s="181"/>
       <c r="H38" s="78"/>
       <c r="I38" s="75" t="s">
         <v>687</v>
@@ -24477,46 +24492,40 @@
       <c r="B39" s="70" t="s">
         <v>692</v>
       </c>
-      <c r="C39" s="157" t="s">
+      <c r="C39" s="188" t="s">
         <v>693</v>
       </c>
-      <c r="D39" s="158"/>
+      <c r="D39" s="189"/>
       <c r="E39" s="69" t="s">
         <v>690</v>
       </c>
-      <c r="F39" s="161" t="s">
+      <c r="F39" s="184" t="s">
         <v>691</v>
       </c>
-      <c r="G39" s="162"/>
+      <c r="G39" s="185"/>
       <c r="H39" s="79"/>
-      <c r="I39" s="163" t="s">
+      <c r="I39" s="182" t="s">
         <v>689</v>
       </c>
-      <c r="J39" s="164"/>
+      <c r="J39" s="183"/>
     </row>
     <row r="40" spans="1:14" ht="58.5" customHeight="1"/>
     <row r="42" spans="1:14" ht="31.5" customHeight="1"/>
     <row r="43" spans="1:14" ht="31.5" customHeight="1"/>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
     <mergeCell ref="C39:D39"/>
     <mergeCell ref="I29:J29"/>
     <mergeCell ref="I30:J30"/>
@@ -24533,18 +24542,24 @@
     <mergeCell ref="F30:G30"/>
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="F32:G32"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="L32:N32"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
@@ -24688,10 +24703,10 @@
       <c r="F7" s="112" t="s">
         <v>916</v>
       </c>
-      <c r="I7" s="185" t="s">
+      <c r="I7" s="192" t="s">
         <v>1168</v>
       </c>
-      <c r="J7" s="185"/>
+      <c r="J7" s="192"/>
       <c r="L7" s="49" t="s">
         <v>601</v>
       </c>
@@ -24709,7 +24724,7 @@
       <c r="D8" s="32" t="s">
         <v>582</v>
       </c>
-      <c r="E8" s="186" t="s">
+      <c r="E8" s="134" t="s">
         <v>583</v>
       </c>
       <c r="F8" s="36" t="s">
@@ -25031,10 +25046,10 @@
       <c r="L20" s="115" t="s">
         <v>568</v>
       </c>
-      <c r="M20" s="167" t="s">
+      <c r="M20" s="193" t="s">
         <v>918</v>
       </c>
-      <c r="N20" s="168"/>
+      <c r="N20" s="194"/>
     </row>
     <row r="21" spans="1:14">
       <c r="B21" s="85" t="s">
@@ -25152,29 +25167,29 @@
       <c r="B27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="C27" s="153" t="s">
+      <c r="C27" s="178" t="s">
         <v>622</v>
       </c>
-      <c r="D27" s="154"/>
+      <c r="D27" s="179"/>
       <c r="E27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="F27" s="153" t="s">
+      <c r="F27" s="178" t="s">
         <v>622</v>
       </c>
-      <c r="G27" s="154"/>
+      <c r="G27" s="179"/>
       <c r="H27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="I27" s="153" t="s">
+      <c r="I27" s="178" t="s">
         <v>622</v>
       </c>
-      <c r="J27" s="154"/>
-      <c r="L27" s="165" t="s">
+      <c r="J27" s="179"/>
+      <c r="L27" s="176" t="s">
         <v>694</v>
       </c>
-      <c r="M27" s="165"/>
-      <c r="N27" s="165"/>
+      <c r="M27" s="176"/>
+      <c r="N27" s="176"/>
     </row>
     <row r="28" spans="1:14" ht="49.5" customHeight="1" thickBot="1">
       <c r="A28" s="81">
@@ -25183,29 +25198,29 @@
       <c r="B28" s="69" t="s">
         <v>623</v>
       </c>
-      <c r="C28" s="151" t="s">
+      <c r="C28" s="186" t="s">
         <v>624</v>
       </c>
-      <c r="D28" s="152"/>
+      <c r="D28" s="187"/>
       <c r="E28" s="70" t="s">
         <v>645</v>
       </c>
-      <c r="F28" s="155" t="s">
+      <c r="F28" s="180" t="s">
         <v>1180</v>
       </c>
-      <c r="G28" s="156"/>
+      <c r="G28" s="181"/>
       <c r="H28" s="69" t="s">
         <v>667</v>
       </c>
-      <c r="I28" s="151" t="s">
+      <c r="I28" s="186" t="s">
         <v>668</v>
       </c>
-      <c r="J28" s="152"/>
-      <c r="L28" s="166" t="s">
+      <c r="J28" s="187"/>
+      <c r="L28" s="177" t="s">
         <v>695</v>
       </c>
-      <c r="M28" s="166"/>
-      <c r="N28" s="166"/>
+      <c r="M28" s="177"/>
+      <c r="N28" s="177"/>
     </row>
     <row r="29" spans="1:14" ht="31.5" thickBot="1">
       <c r="A29" s="81">
@@ -25214,29 +25229,29 @@
       <c r="B29" s="70" t="s">
         <v>625</v>
       </c>
-      <c r="C29" s="155" t="s">
+      <c r="C29" s="180" t="s">
         <v>626</v>
       </c>
-      <c r="D29" s="156"/>
+      <c r="D29" s="181"/>
       <c r="E29" s="69" t="s">
         <v>647</v>
       </c>
-      <c r="F29" s="151" t="s">
+      <c r="F29" s="186" t="s">
         <v>648</v>
       </c>
-      <c r="G29" s="152"/>
+      <c r="G29" s="187"/>
       <c r="H29" s="70" t="s">
         <v>669</v>
       </c>
-      <c r="I29" s="159" t="s">
+      <c r="I29" s="190" t="s">
         <v>670</v>
       </c>
-      <c r="J29" s="160"/>
-      <c r="L29" s="165" t="s">
+      <c r="J29" s="191"/>
+      <c r="L29" s="176" t="s">
         <v>696</v>
       </c>
-      <c r="M29" s="165"/>
-      <c r="N29" s="165"/>
+      <c r="M29" s="176"/>
+      <c r="N29" s="176"/>
     </row>
     <row r="30" spans="1:14" ht="15.75" thickBot="1">
       <c r="A30" s="81">
@@ -25245,29 +25260,29 @@
       <c r="B30" s="69" t="s">
         <v>627</v>
       </c>
-      <c r="C30" s="151" t="s">
+      <c r="C30" s="186" t="s">
         <v>628</v>
       </c>
-      <c r="D30" s="152"/>
+      <c r="D30" s="187"/>
       <c r="E30" s="70" t="s">
         <v>649</v>
       </c>
-      <c r="F30" s="155" t="s">
+      <c r="F30" s="180" t="s">
         <v>650</v>
       </c>
-      <c r="G30" s="156"/>
+      <c r="G30" s="181"/>
       <c r="H30" s="69" t="s">
         <v>671</v>
       </c>
-      <c r="I30" s="151" t="s">
+      <c r="I30" s="186" t="s">
         <v>672</v>
       </c>
-      <c r="J30" s="152"/>
-      <c r="L30" s="166" t="s">
+      <c r="J30" s="187"/>
+      <c r="L30" s="177" t="s">
         <v>697</v>
       </c>
-      <c r="M30" s="166"/>
-      <c r="N30" s="166"/>
+      <c r="M30" s="177"/>
+      <c r="N30" s="177"/>
     </row>
     <row r="31" spans="1:14" ht="17.25" customHeight="1" thickBot="1">
       <c r="A31" s="81">
@@ -25276,29 +25291,29 @@
       <c r="B31" s="70" t="s">
         <v>629</v>
       </c>
-      <c r="C31" s="155" t="s">
+      <c r="C31" s="180" t="s">
         <v>630</v>
       </c>
-      <c r="D31" s="156"/>
+      <c r="D31" s="181"/>
       <c r="E31" s="69" t="s">
         <v>651</v>
       </c>
-      <c r="F31" s="151" t="s">
+      <c r="F31" s="186" t="s">
         <v>652</v>
       </c>
-      <c r="G31" s="152"/>
+      <c r="G31" s="187"/>
       <c r="H31" s="70" t="s">
         <v>673</v>
       </c>
-      <c r="I31" s="155" t="s">
+      <c r="I31" s="180" t="s">
         <v>674</v>
       </c>
-      <c r="J31" s="156"/>
-      <c r="L31" s="165" t="s">
+      <c r="J31" s="181"/>
+      <c r="L31" s="176" t="s">
         <v>698</v>
       </c>
-      <c r="M31" s="165"/>
-      <c r="N31" s="165"/>
+      <c r="M31" s="176"/>
+      <c r="N31" s="176"/>
     </row>
     <row r="32" spans="1:14" ht="43.5" customHeight="1" thickBot="1">
       <c r="A32" s="81">
@@ -25307,29 +25322,29 @@
       <c r="B32" s="69" t="s">
         <v>631</v>
       </c>
-      <c r="C32" s="151" t="s">
+      <c r="C32" s="186" t="s">
         <v>632</v>
       </c>
-      <c r="D32" s="152"/>
+      <c r="D32" s="187"/>
       <c r="E32" s="70" t="s">
         <v>653</v>
       </c>
-      <c r="F32" s="155" t="s">
+      <c r="F32" s="180" t="s">
         <v>654</v>
       </c>
-      <c r="G32" s="156"/>
+      <c r="G32" s="181"/>
       <c r="H32" s="69" t="s">
         <v>675</v>
       </c>
-      <c r="I32" s="151" t="s">
+      <c r="I32" s="186" t="s">
         <v>676</v>
       </c>
-      <c r="J32" s="152"/>
-      <c r="L32" s="166" t="s">
+      <c r="J32" s="187"/>
+      <c r="L32" s="177" t="s">
         <v>699</v>
       </c>
-      <c r="M32" s="166"/>
-      <c r="N32" s="166"/>
+      <c r="M32" s="177"/>
+      <c r="N32" s="177"/>
     </row>
     <row r="33" spans="1:14" ht="31.5" customHeight="1" thickBot="1">
       <c r="A33" s="81">
@@ -25338,29 +25353,29 @@
       <c r="B33" s="70" t="s">
         <v>633</v>
       </c>
-      <c r="C33" s="155" t="s">
+      <c r="C33" s="180" t="s">
         <v>634</v>
       </c>
-      <c r="D33" s="156"/>
+      <c r="D33" s="181"/>
       <c r="E33" s="69" t="s">
         <v>655</v>
       </c>
-      <c r="F33" s="151" t="s">
+      <c r="F33" s="186" t="s">
         <v>656</v>
       </c>
-      <c r="G33" s="152"/>
+      <c r="G33" s="187"/>
       <c r="H33" s="70" t="s">
         <v>677</v>
       </c>
-      <c r="I33" s="157" t="s">
+      <c r="I33" s="188" t="s">
         <v>678</v>
       </c>
-      <c r="J33" s="158"/>
-      <c r="L33" s="165" t="s">
+      <c r="J33" s="189"/>
+      <c r="L33" s="176" t="s">
         <v>700</v>
       </c>
-      <c r="M33" s="165"/>
-      <c r="N33" s="165"/>
+      <c r="M33" s="176"/>
+      <c r="N33" s="176"/>
     </row>
     <row r="34" spans="1:14" ht="28.5" customHeight="1" thickBot="1">
       <c r="A34" s="81">
@@ -25369,29 +25384,29 @@
       <c r="B34" s="69" t="s">
         <v>635</v>
       </c>
-      <c r="C34" s="151" t="s">
+      <c r="C34" s="186" t="s">
         <v>636</v>
       </c>
-      <c r="D34" s="152"/>
+      <c r="D34" s="187"/>
       <c r="E34" s="70" t="s">
         <v>657</v>
       </c>
-      <c r="F34" s="155" t="s">
+      <c r="F34" s="180" t="s">
         <v>658</v>
       </c>
-      <c r="G34" s="156"/>
+      <c r="G34" s="181"/>
       <c r="H34" s="69" t="s">
         <v>679</v>
       </c>
-      <c r="I34" s="161" t="s">
+      <c r="I34" s="184" t="s">
         <v>680</v>
       </c>
-      <c r="J34" s="162"/>
-      <c r="L34" s="166" t="s">
+      <c r="J34" s="185"/>
+      <c r="L34" s="177" t="s">
         <v>701</v>
       </c>
-      <c r="M34" s="166"/>
-      <c r="N34" s="166"/>
+      <c r="M34" s="177"/>
+      <c r="N34" s="177"/>
     </row>
     <row r="35" spans="1:14" ht="31.5" customHeight="1" thickBot="1">
       <c r="A35" s="81">
@@ -25400,29 +25415,29 @@
       <c r="B35" s="70" t="s">
         <v>637</v>
       </c>
-      <c r="C35" s="155" t="s">
+      <c r="C35" s="180" t="s">
         <v>638</v>
       </c>
-      <c r="D35" s="156"/>
+      <c r="D35" s="181"/>
       <c r="E35" s="69" t="s">
         <v>659</v>
       </c>
-      <c r="F35" s="151" t="s">
+      <c r="F35" s="186" t="s">
         <v>660</v>
       </c>
-      <c r="G35" s="152"/>
+      <c r="G35" s="187"/>
       <c r="H35" s="77" t="s">
         <v>681</v>
       </c>
-      <c r="I35" s="155" t="s">
+      <c r="I35" s="180" t="s">
         <v>682</v>
       </c>
-      <c r="J35" s="156"/>
-      <c r="L35" s="165" t="s">
+      <c r="J35" s="181"/>
+      <c r="L35" s="176" t="s">
         <v>702</v>
       </c>
-      <c r="M35" s="165"/>
-      <c r="N35" s="165"/>
+      <c r="M35" s="176"/>
+      <c r="N35" s="176"/>
     </row>
     <row r="36" spans="1:14" ht="60.75" thickBot="1">
       <c r="A36" s="81">
@@ -25431,17 +25446,17 @@
       <c r="B36" s="69" t="s">
         <v>639</v>
       </c>
-      <c r="C36" s="151" t="s">
+      <c r="C36" s="186" t="s">
         <v>640</v>
       </c>
-      <c r="D36" s="152"/>
+      <c r="D36" s="187"/>
       <c r="E36" s="70" t="s">
         <v>661</v>
       </c>
-      <c r="F36" s="155" t="s">
+      <c r="F36" s="180" t="s">
         <v>662</v>
       </c>
-      <c r="G36" s="156"/>
+      <c r="G36" s="181"/>
       <c r="H36" s="78"/>
       <c r="I36" s="71" t="s">
         <v>683</v>
@@ -25449,11 +25464,11 @@
       <c r="J36" s="72" t="s">
         <v>684</v>
       </c>
-      <c r="L36" s="166" t="s">
+      <c r="L36" s="177" t="s">
         <v>703</v>
       </c>
-      <c r="M36" s="166"/>
-      <c r="N36" s="166"/>
+      <c r="M36" s="177"/>
+      <c r="N36" s="177"/>
     </row>
     <row r="37" spans="1:14" ht="75.75" thickBot="1">
       <c r="A37" s="81">
@@ -25462,17 +25477,17 @@
       <c r="B37" s="70" t="s">
         <v>641</v>
       </c>
-      <c r="C37" s="155" t="s">
+      <c r="C37" s="180" t="s">
         <v>642</v>
       </c>
-      <c r="D37" s="156"/>
+      <c r="D37" s="181"/>
       <c r="E37" s="69" t="s">
         <v>663</v>
       </c>
-      <c r="F37" s="151" t="s">
+      <c r="F37" s="186" t="s">
         <v>664</v>
       </c>
-      <c r="G37" s="152"/>
+      <c r="G37" s="187"/>
       <c r="H37" s="78"/>
       <c r="I37" s="73" t="s">
         <v>685</v>
@@ -25488,17 +25503,17 @@
       <c r="B38" s="69" t="s">
         <v>643</v>
       </c>
-      <c r="C38" s="151" t="s">
+      <c r="C38" s="186" t="s">
         <v>644</v>
       </c>
-      <c r="D38" s="152"/>
+      <c r="D38" s="187"/>
       <c r="E38" s="70" t="s">
         <v>665</v>
       </c>
-      <c r="F38" s="155" t="s">
+      <c r="F38" s="180" t="s">
         <v>666</v>
       </c>
-      <c r="G38" s="156"/>
+      <c r="G38" s="181"/>
       <c r="H38" s="78"/>
       <c r="I38" s="75" t="s">
         <v>687</v>
@@ -25514,22 +25529,22 @@
       <c r="B39" s="70" t="s">
         <v>692</v>
       </c>
-      <c r="C39" s="157" t="s">
+      <c r="C39" s="188" t="s">
         <v>693</v>
       </c>
-      <c r="D39" s="158"/>
+      <c r="D39" s="189"/>
       <c r="E39" s="69" t="s">
         <v>690</v>
       </c>
-      <c r="F39" s="161" t="s">
+      <c r="F39" s="184" t="s">
         <v>691</v>
       </c>
-      <c r="G39" s="162"/>
+      <c r="G39" s="185"/>
       <c r="H39" s="79"/>
-      <c r="I39" s="163" t="s">
+      <c r="I39" s="182" t="s">
         <v>689</v>
       </c>
-      <c r="J39" s="164"/>
+      <c r="J39" s="183"/>
     </row>
     <row r="40" spans="1:14" ht="58.5" customHeight="1"/>
     <row r="41" spans="1:14">
@@ -25823,44 +25838,6 @@
     </row>
   </sheetData>
   <mergeCells count="48">
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="L35:N35"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="F36:G36"/>
     <mergeCell ref="L36:N36"/>
@@ -25871,6 +25848,44 @@
     <mergeCell ref="F38:G38"/>
     <mergeCell ref="C39:D39"/>
     <mergeCell ref="F39:G39"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="L27:N27"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>

--- a/2020_LogAnalyzer_Leeheesuk.xlsx
+++ b/2020_LogAnalyzer_Leeheesuk.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="23001"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83105091-B529-4069-B4D6-FF2A21347560}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF9A85ED-2AD5-43C6-9062-F89FD91A2F39}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15" yWindow="0" windowWidth="22545" windowHeight="12885" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" firstSheet="7" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UI" sheetId="7" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2048" uniqueCount="1294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2051" uniqueCount="1297">
   <si>
     <t>구분</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3961,10 +3961,6 @@
   </si>
   <si>
     <t>세부 Steps : 전체 line 수 세기 -&gt; process 수만큼 병렬처리 -&gt; csv 파일생성</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>완료</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -4471,9 +4467,6 @@
     <t>creator</t>
   </si>
   <si>
-    <t>Multifile 차리위해 들고 있어야 한다.</t>
-  </si>
-  <si>
     <t>http://www.cdrf.co/3.1/rest_framework.viewsets/ModelViewSet.html#get_queryset</t>
   </si>
   <si>
@@ -5746,6 +5739,21 @@
   <si>
     <t>MIT License</t>
   </si>
+  <si>
+    <t>https://github.com/biigpongsatorn/vue-slide-bar</t>
+  </si>
+  <si>
+    <t>Loop로 해결</t>
+  </si>
+  <si>
+    <t>처리사간 3초 이상</t>
+  </si>
+  <si>
+    <t>완료 - Table명 : logdetail_"project_id"</t>
+  </si>
+  <si>
+    <t>https://djangopackages.org/grids/g/dynamic-models/</t>
+  </si>
 </sst>
 </file>
 
@@ -5754,7 +5762,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
-  <fonts count="40">
+  <fonts count="41">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6035,6 +6043,16 @@
       <sz val="11"/>
       <name val="Consolas"/>
       <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <strike/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="15">
@@ -6701,15 +6719,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -6923,12 +6932,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -6991,6 +6994,21 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -16323,51 +16341,51 @@
     </row>
     <row r="17" spans="1:13">
       <c r="J17" s="19"/>
-      <c r="K17" s="158" t="s">
+      <c r="K17" s="155" t="s">
         <v>537</v>
       </c>
-      <c r="L17" s="159"/>
-      <c r="M17" s="160"/>
+      <c r="L17" s="156"/>
+      <c r="M17" s="157"/>
     </row>
     <row r="18" spans="1:13">
       <c r="J18" s="19">
         <v>1</v>
       </c>
-      <c r="K18" s="161" t="s">
+      <c r="K18" s="158" t="s">
         <v>538</v>
       </c>
-      <c r="L18" s="162"/>
-      <c r="M18" s="163"/>
+      <c r="L18" s="159"/>
+      <c r="M18" s="160"/>
     </row>
     <row r="19" spans="1:13">
       <c r="J19" s="19">
         <v>2</v>
       </c>
-      <c r="K19" s="161" t="s">
+      <c r="K19" s="158" t="s">
         <v>539</v>
       </c>
-      <c r="L19" s="162"/>
-      <c r="M19" s="163"/>
+      <c r="L19" s="159"/>
+      <c r="M19" s="160"/>
     </row>
     <row r="20" spans="1:13">
       <c r="J20" s="19">
         <v>3</v>
       </c>
-      <c r="K20" s="161" t="s">
+      <c r="K20" s="158" t="s">
         <v>540</v>
       </c>
-      <c r="L20" s="162"/>
-      <c r="M20" s="163"/>
+      <c r="L20" s="159"/>
+      <c r="M20" s="160"/>
     </row>
     <row r="21" spans="1:13">
       <c r="J21" s="19">
         <v>4</v>
       </c>
-      <c r="K21" s="161" t="s">
+      <c r="K21" s="158" t="s">
         <v>541</v>
       </c>
-      <c r="L21" s="162"/>
-      <c r="M21" s="163"/>
+      <c r="L21" s="159"/>
+      <c r="M21" s="160"/>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="43" t="s">
@@ -16475,7 +16493,7 @@
         <v>583</v>
       </c>
       <c r="F2" s="32" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="G2" s="32" t="s">
         <v>415</v>
@@ -16489,7 +16507,7 @@
         <v>469</v>
       </c>
       <c r="D3" s="85" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="E3" s="108" t="s">
         <v>433</v>
@@ -16556,12 +16574,12 @@
         <v>574</v>
       </c>
       <c r="F7" s="112" t="s">
-        <v>916</v>
-      </c>
-      <c r="I7" s="192" t="s">
-        <v>1168</v>
-      </c>
-      <c r="J7" s="192"/>
+        <v>915</v>
+      </c>
+      <c r="I7" s="189" t="s">
+        <v>1166</v>
+      </c>
+      <c r="J7" s="189"/>
       <c r="L7" s="49" t="s">
         <v>601</v>
       </c>
@@ -16579,7 +16597,7 @@
       <c r="D8" s="32" t="s">
         <v>582</v>
       </c>
-      <c r="E8" s="134" t="s">
+      <c r="E8" s="131" t="s">
         <v>583</v>
       </c>
       <c r="F8" s="36" t="s">
@@ -16629,10 +16647,10 @@
       <c r="H9" s="85" t="s">
         <v>466</v>
       </c>
-      <c r="I9" s="120" t="s">
+      <c r="I9" s="117" t="s">
         <v>752</v>
       </c>
-      <c r="J9" s="120" t="s">
+      <c r="J9" s="117" t="s">
         <v>755</v>
       </c>
       <c r="L9" s="9" t="s">
@@ -16744,13 +16762,13 @@
         <v>423</v>
       </c>
       <c r="K14" s="32" t="s">
+        <v>838</v>
+      </c>
+      <c r="L14" s="32" t="s">
         <v>839</v>
       </c>
-      <c r="L14" s="32" t="s">
-        <v>840</v>
-      </c>
       <c r="M14" s="32" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -16764,13 +16782,13 @@
         <v>436</v>
       </c>
       <c r="E15" s="85" t="s">
+        <v>802</v>
+      </c>
+      <c r="F15" s="85" t="s">
         <v>803</v>
       </c>
-      <c r="F15" s="85" t="s">
+      <c r="G15" s="85" t="s">
         <v>804</v>
-      </c>
-      <c r="G15" s="85" t="s">
-        <v>805</v>
       </c>
       <c r="H15" s="85" t="s">
         <v>437</v>
@@ -16782,13 +16800,13 @@
         <v>439</v>
       </c>
       <c r="K15" s="95" t="s">
+        <v>846</v>
+      </c>
+      <c r="L15" s="95" t="s">
         <v>847</v>
       </c>
-      <c r="L15" s="95" t="s">
+      <c r="M15" s="95" t="s">
         <v>848</v>
-      </c>
-      <c r="M15" s="95" t="s">
-        <v>849</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="30">
@@ -16802,31 +16820,31 @@
         <v>572</v>
       </c>
       <c r="E16" s="96" t="s">
+        <v>843</v>
+      </c>
+      <c r="F16" s="96" t="s">
         <v>844</v>
       </c>
-      <c r="F16" s="96" t="s">
-        <v>845</v>
-      </c>
       <c r="G16" s="96" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="H16" s="96" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="I16" s="96" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="J16" s="96" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="K16" s="96" t="s">
+        <v>841</v>
+      </c>
+      <c r="L16" s="96" t="s">
         <v>842</v>
       </c>
-      <c r="L16" s="96" t="s">
-        <v>843</v>
-      </c>
       <c r="M16" s="96" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -16842,13 +16860,13 @@
       <c r="I17" s="65"/>
       <c r="J17" s="65"/>
       <c r="K17" s="97" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="L17" s="97" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="M17" s="97" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -16898,13 +16916,11 @@
       <c r="K20" s="32" t="s">
         <v>415</v>
       </c>
-      <c r="L20" s="115" t="s">
+      <c r="L20" s="211" t="s">
         <v>568</v>
       </c>
-      <c r="M20" s="193" t="s">
-        <v>918</v>
-      </c>
-      <c r="N20" s="194"/>
+      <c r="M20" s="214"/>
+      <c r="N20" s="215"/>
     </row>
     <row r="21" spans="1:14">
       <c r="B21" s="85" t="s">
@@ -16937,7 +16953,7 @@
       <c r="K21" s="85" t="s">
         <v>466</v>
       </c>
-      <c r="L21" s="116" t="s">
+      <c r="L21" s="212" t="s">
         <v>429</v>
       </c>
     </row>
@@ -16972,7 +16988,7 @@
       <c r="K22" s="62" t="s">
         <v>592</v>
       </c>
-      <c r="L22" s="117" t="s">
+      <c r="L22" s="213" t="s">
         <v>458</v>
       </c>
     </row>
@@ -17003,48 +17019,50 @@
         <v>200</v>
       </c>
       <c r="K23" s="64"/>
-      <c r="L23" s="116"/>
+      <c r="L23" s="212" t="s">
+        <v>1293</v>
+      </c>
     </row>
     <row r="25" spans="1:14">
       <c r="B25" s="7" t="s">
         <v>620</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="15.75" thickBot="1">
       <c r="F26" s="7" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="15.75" thickBot="1">
       <c r="B27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="C27" s="178" t="s">
+      <c r="C27" s="175" t="s">
         <v>622</v>
       </c>
-      <c r="D27" s="179"/>
+      <c r="D27" s="176"/>
       <c r="E27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="F27" s="178" t="s">
+      <c r="F27" s="175" t="s">
         <v>622</v>
       </c>
-      <c r="G27" s="179"/>
+      <c r="G27" s="176"/>
       <c r="H27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="I27" s="178" t="s">
+      <c r="I27" s="175" t="s">
         <v>622</v>
       </c>
-      <c r="J27" s="179"/>
-      <c r="L27" s="176" t="s">
+      <c r="J27" s="176"/>
+      <c r="L27" s="173" t="s">
         <v>694</v>
       </c>
-      <c r="M27" s="176"/>
-      <c r="N27" s="176"/>
+      <c r="M27" s="173"/>
+      <c r="N27" s="173"/>
     </row>
     <row r="28" spans="1:14" ht="49.5" customHeight="1" thickBot="1">
       <c r="A28" s="81">
@@ -17053,29 +17071,29 @@
       <c r="B28" s="69" t="s">
         <v>623</v>
       </c>
-      <c r="C28" s="186" t="s">
+      <c r="C28" s="183" t="s">
         <v>624</v>
       </c>
-      <c r="D28" s="187"/>
+      <c r="D28" s="184"/>
       <c r="E28" s="70" t="s">
         <v>645</v>
       </c>
-      <c r="F28" s="180" t="s">
-        <v>1180</v>
-      </c>
-      <c r="G28" s="181"/>
+      <c r="F28" s="177" t="s">
+        <v>1178</v>
+      </c>
+      <c r="G28" s="178"/>
       <c r="H28" s="69" t="s">
         <v>667</v>
       </c>
-      <c r="I28" s="186" t="s">
+      <c r="I28" s="183" t="s">
         <v>668</v>
       </c>
-      <c r="J28" s="187"/>
-      <c r="L28" s="177" t="s">
+      <c r="J28" s="184"/>
+      <c r="L28" s="174" t="s">
         <v>695</v>
       </c>
-      <c r="M28" s="177"/>
-      <c r="N28" s="177"/>
+      <c r="M28" s="174"/>
+      <c r="N28" s="174"/>
     </row>
     <row r="29" spans="1:14" ht="31.5" thickBot="1">
       <c r="A29" s="81">
@@ -17084,29 +17102,29 @@
       <c r="B29" s="70" t="s">
         <v>625</v>
       </c>
-      <c r="C29" s="180" t="s">
+      <c r="C29" s="177" t="s">
         <v>626</v>
       </c>
-      <c r="D29" s="181"/>
+      <c r="D29" s="178"/>
       <c r="E29" s="69" t="s">
         <v>647</v>
       </c>
-      <c r="F29" s="186" t="s">
+      <c r="F29" s="183" t="s">
         <v>648</v>
       </c>
-      <c r="G29" s="187"/>
+      <c r="G29" s="184"/>
       <c r="H29" s="70" t="s">
         <v>669</v>
       </c>
-      <c r="I29" s="190" t="s">
+      <c r="I29" s="187" t="s">
         <v>670</v>
       </c>
-      <c r="J29" s="191"/>
-      <c r="L29" s="176" t="s">
+      <c r="J29" s="188"/>
+      <c r="L29" s="173" t="s">
         <v>696</v>
       </c>
-      <c r="M29" s="176"/>
-      <c r="N29" s="176"/>
+      <c r="M29" s="173"/>
+      <c r="N29" s="173"/>
     </row>
     <row r="30" spans="1:14" ht="15.75" thickBot="1">
       <c r="A30" s="81">
@@ -17115,29 +17133,29 @@
       <c r="B30" s="69" t="s">
         <v>627</v>
       </c>
-      <c r="C30" s="186" t="s">
+      <c r="C30" s="183" t="s">
         <v>628</v>
       </c>
-      <c r="D30" s="187"/>
+      <c r="D30" s="184"/>
       <c r="E30" s="70" t="s">
         <v>649</v>
       </c>
-      <c r="F30" s="180" t="s">
+      <c r="F30" s="177" t="s">
         <v>650</v>
       </c>
-      <c r="G30" s="181"/>
+      <c r="G30" s="178"/>
       <c r="H30" s="69" t="s">
         <v>671</v>
       </c>
-      <c r="I30" s="186" t="s">
+      <c r="I30" s="183" t="s">
         <v>672</v>
       </c>
-      <c r="J30" s="187"/>
-      <c r="L30" s="177" t="s">
+      <c r="J30" s="184"/>
+      <c r="L30" s="174" t="s">
         <v>697</v>
       </c>
-      <c r="M30" s="177"/>
-      <c r="N30" s="177"/>
+      <c r="M30" s="174"/>
+      <c r="N30" s="174"/>
     </row>
     <row r="31" spans="1:14" ht="17.25" customHeight="1" thickBot="1">
       <c r="A31" s="81">
@@ -17146,29 +17164,29 @@
       <c r="B31" s="70" t="s">
         <v>629</v>
       </c>
-      <c r="C31" s="180" t="s">
+      <c r="C31" s="177" t="s">
         <v>630</v>
       </c>
-      <c r="D31" s="181"/>
+      <c r="D31" s="178"/>
       <c r="E31" s="69" t="s">
         <v>651</v>
       </c>
-      <c r="F31" s="186" t="s">
+      <c r="F31" s="183" t="s">
         <v>652</v>
       </c>
-      <c r="G31" s="187"/>
+      <c r="G31" s="184"/>
       <c r="H31" s="70" t="s">
         <v>673</v>
       </c>
-      <c r="I31" s="180" t="s">
+      <c r="I31" s="177" t="s">
         <v>674</v>
       </c>
-      <c r="J31" s="181"/>
-      <c r="L31" s="176" t="s">
+      <c r="J31" s="178"/>
+      <c r="L31" s="173" t="s">
         <v>698</v>
       </c>
-      <c r="M31" s="176"/>
-      <c r="N31" s="176"/>
+      <c r="M31" s="173"/>
+      <c r="N31" s="173"/>
     </row>
     <row r="32" spans="1:14" ht="43.5" customHeight="1" thickBot="1">
       <c r="A32" s="81">
@@ -17177,29 +17195,29 @@
       <c r="B32" s="69" t="s">
         <v>631</v>
       </c>
-      <c r="C32" s="186" t="s">
+      <c r="C32" s="183" t="s">
         <v>632</v>
       </c>
-      <c r="D32" s="187"/>
+      <c r="D32" s="184"/>
       <c r="E32" s="70" t="s">
         <v>653</v>
       </c>
-      <c r="F32" s="180" t="s">
+      <c r="F32" s="177" t="s">
         <v>654</v>
       </c>
-      <c r="G32" s="181"/>
+      <c r="G32" s="178"/>
       <c r="H32" s="69" t="s">
         <v>675</v>
       </c>
-      <c r="I32" s="186" t="s">
+      <c r="I32" s="183" t="s">
         <v>676</v>
       </c>
-      <c r="J32" s="187"/>
-      <c r="L32" s="177" t="s">
+      <c r="J32" s="184"/>
+      <c r="L32" s="174" t="s">
         <v>699</v>
       </c>
-      <c r="M32" s="177"/>
-      <c r="N32" s="177"/>
+      <c r="M32" s="174"/>
+      <c r="N32" s="174"/>
     </row>
     <row r="33" spans="1:14" ht="31.5" customHeight="1" thickBot="1">
       <c r="A33" s="81">
@@ -17208,29 +17226,29 @@
       <c r="B33" s="70" t="s">
         <v>633</v>
       </c>
-      <c r="C33" s="180" t="s">
+      <c r="C33" s="177" t="s">
         <v>634</v>
       </c>
-      <c r="D33" s="181"/>
+      <c r="D33" s="178"/>
       <c r="E33" s="69" t="s">
         <v>655</v>
       </c>
-      <c r="F33" s="186" t="s">
+      <c r="F33" s="183" t="s">
         <v>656</v>
       </c>
-      <c r="G33" s="187"/>
+      <c r="G33" s="184"/>
       <c r="H33" s="70" t="s">
         <v>677</v>
       </c>
-      <c r="I33" s="188" t="s">
+      <c r="I33" s="185" t="s">
         <v>678</v>
       </c>
-      <c r="J33" s="189"/>
-      <c r="L33" s="176" t="s">
+      <c r="J33" s="186"/>
+      <c r="L33" s="173" t="s">
         <v>700</v>
       </c>
-      <c r="M33" s="176"/>
-      <c r="N33" s="176"/>
+      <c r="M33" s="173"/>
+      <c r="N33" s="173"/>
     </row>
     <row r="34" spans="1:14" ht="28.5" customHeight="1" thickBot="1">
       <c r="A34" s="81">
@@ -17239,29 +17257,29 @@
       <c r="B34" s="69" t="s">
         <v>635</v>
       </c>
-      <c r="C34" s="186" t="s">
+      <c r="C34" s="183" t="s">
         <v>636</v>
       </c>
-      <c r="D34" s="187"/>
+      <c r="D34" s="184"/>
       <c r="E34" s="70" t="s">
         <v>657</v>
       </c>
-      <c r="F34" s="180" t="s">
+      <c r="F34" s="177" t="s">
         <v>658</v>
       </c>
-      <c r="G34" s="181"/>
+      <c r="G34" s="178"/>
       <c r="H34" s="69" t="s">
         <v>679</v>
       </c>
-      <c r="I34" s="184" t="s">
+      <c r="I34" s="181" t="s">
         <v>680</v>
       </c>
-      <c r="J34" s="185"/>
-      <c r="L34" s="177" t="s">
+      <c r="J34" s="182"/>
+      <c r="L34" s="174" t="s">
         <v>701</v>
       </c>
-      <c r="M34" s="177"/>
-      <c r="N34" s="177"/>
+      <c r="M34" s="174"/>
+      <c r="N34" s="174"/>
     </row>
     <row r="35" spans="1:14" ht="31.5" customHeight="1" thickBot="1">
       <c r="A35" s="81">
@@ -17270,29 +17288,29 @@
       <c r="B35" s="70" t="s">
         <v>637</v>
       </c>
-      <c r="C35" s="180" t="s">
+      <c r="C35" s="177" t="s">
         <v>638</v>
       </c>
-      <c r="D35" s="181"/>
+      <c r="D35" s="178"/>
       <c r="E35" s="69" t="s">
         <v>659</v>
       </c>
-      <c r="F35" s="186" t="s">
+      <c r="F35" s="183" t="s">
         <v>660</v>
       </c>
-      <c r="G35" s="187"/>
+      <c r="G35" s="184"/>
       <c r="H35" s="77" t="s">
         <v>681</v>
       </c>
-      <c r="I35" s="180" t="s">
+      <c r="I35" s="177" t="s">
         <v>682</v>
       </c>
-      <c r="J35" s="181"/>
-      <c r="L35" s="176" t="s">
+      <c r="J35" s="178"/>
+      <c r="L35" s="173" t="s">
         <v>702</v>
       </c>
-      <c r="M35" s="176"/>
-      <c r="N35" s="176"/>
+      <c r="M35" s="173"/>
+      <c r="N35" s="173"/>
     </row>
     <row r="36" spans="1:14" ht="60.75" thickBot="1">
       <c r="A36" s="81">
@@ -17301,17 +17319,17 @@
       <c r="B36" s="69" t="s">
         <v>639</v>
       </c>
-      <c r="C36" s="186" t="s">
+      <c r="C36" s="183" t="s">
         <v>640</v>
       </c>
-      <c r="D36" s="187"/>
+      <c r="D36" s="184"/>
       <c r="E36" s="70" t="s">
         <v>661</v>
       </c>
-      <c r="F36" s="180" t="s">
+      <c r="F36" s="177" t="s">
         <v>662</v>
       </c>
-      <c r="G36" s="181"/>
+      <c r="G36" s="178"/>
       <c r="H36" s="78"/>
       <c r="I36" s="71" t="s">
         <v>683</v>
@@ -17319,11 +17337,11 @@
       <c r="J36" s="72" t="s">
         <v>684</v>
       </c>
-      <c r="L36" s="177" t="s">
+      <c r="L36" s="174" t="s">
         <v>703</v>
       </c>
-      <c r="M36" s="177"/>
-      <c r="N36" s="177"/>
+      <c r="M36" s="174"/>
+      <c r="N36" s="174"/>
     </row>
     <row r="37" spans="1:14" ht="75.75" thickBot="1">
       <c r="A37" s="81">
@@ -17332,17 +17350,17 @@
       <c r="B37" s="70" t="s">
         <v>641</v>
       </c>
-      <c r="C37" s="180" t="s">
+      <c r="C37" s="177" t="s">
         <v>642</v>
       </c>
-      <c r="D37" s="181"/>
+      <c r="D37" s="178"/>
       <c r="E37" s="69" t="s">
         <v>663</v>
       </c>
-      <c r="F37" s="186" t="s">
+      <c r="F37" s="183" t="s">
         <v>664</v>
       </c>
-      <c r="G37" s="187"/>
+      <c r="G37" s="184"/>
       <c r="H37" s="78"/>
       <c r="I37" s="73" t="s">
         <v>685</v>
@@ -17358,17 +17376,17 @@
       <c r="B38" s="69" t="s">
         <v>643</v>
       </c>
-      <c r="C38" s="186" t="s">
+      <c r="C38" s="183" t="s">
         <v>644</v>
       </c>
-      <c r="D38" s="187"/>
+      <c r="D38" s="184"/>
       <c r="E38" s="70" t="s">
         <v>665</v>
       </c>
-      <c r="F38" s="180" t="s">
+      <c r="F38" s="177" t="s">
         <v>666</v>
       </c>
-      <c r="G38" s="181"/>
+      <c r="G38" s="178"/>
       <c r="H38" s="78"/>
       <c r="I38" s="75" t="s">
         <v>687</v>
@@ -17384,22 +17402,22 @@
       <c r="B39" s="70" t="s">
         <v>692</v>
       </c>
-      <c r="C39" s="188" t="s">
+      <c r="C39" s="185" t="s">
         <v>693</v>
       </c>
-      <c r="D39" s="189"/>
+      <c r="D39" s="186"/>
       <c r="E39" s="69" t="s">
         <v>690</v>
       </c>
-      <c r="F39" s="184" t="s">
+      <c r="F39" s="181" t="s">
         <v>691</v>
       </c>
-      <c r="G39" s="185"/>
+      <c r="G39" s="182"/>
       <c r="H39" s="79"/>
-      <c r="I39" s="182" t="s">
+      <c r="I39" s="179" t="s">
         <v>689</v>
       </c>
-      <c r="J39" s="183"/>
+      <c r="J39" s="180"/>
     </row>
     <row r="40" spans="1:14" ht="58.5" customHeight="1"/>
     <row r="41" spans="1:14">
@@ -17578,7 +17596,7 @@
       <c r="B49" s="85" t="s">
         <v>429</v>
       </c>
-      <c r="C49" s="120" t="s">
+      <c r="C49" s="117" t="s">
         <v>752</v>
       </c>
       <c r="D49" s="85" t="s">
@@ -17982,7 +18000,7 @@
         <v>487</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="F10" s="92" t="s">
         <v>502</v>
@@ -18005,7 +18023,7 @@
         <v>488</v>
       </c>
       <c r="E11" s="92" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="F11" s="92" t="s">
         <v>502</v>
@@ -18028,7 +18046,7 @@
         <v>489</v>
       </c>
       <c r="E12" s="92" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="F12" s="92" t="s">
         <v>502</v>
@@ -18051,7 +18069,7 @@
         <v>485</v>
       </c>
       <c r="E13" s="92" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="F13" s="92" t="s">
         <v>502</v>
@@ -18074,7 +18092,7 @@
         <v>486</v>
       </c>
       <c r="E14" s="92" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="F14" s="92" t="s">
         <v>502</v>
@@ -18097,7 +18115,7 @@
         <v>711</v>
       </c>
       <c r="E15" s="92" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="F15" s="92" t="s">
         <v>502</v>
@@ -18311,23 +18329,23 @@
         <v>560</v>
       </c>
       <c r="K1" s="26" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="M1" s="26" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A2" s="195" t="s">
+      <c r="A2" s="190" t="s">
         <v>504</v>
       </c>
-      <c r="B2" s="204" t="s">
+      <c r="B2" s="199" t="s">
         <v>506</v>
       </c>
-      <c r="C2" s="195" t="s">
+      <c r="C2" s="190" t="s">
         <v>508</v>
       </c>
-      <c r="D2" s="195" t="s">
+      <c r="D2" s="190" t="s">
         <v>556</v>
       </c>
       <c r="E2" s="8"/>
@@ -18340,7 +18358,7 @@
       <c r="H2" s="10">
         <v>1</v>
       </c>
-      <c r="I2" s="215">
+      <c r="I2" s="210">
         <v>44043</v>
       </c>
       <c r="J2" s="10"/>
@@ -18350,10 +18368,10 @@
       </c>
     </row>
     <row r="3" spans="1:17">
-      <c r="A3" s="168"/>
-      <c r="B3" s="205"/>
-      <c r="C3" s="196"/>
-      <c r="D3" s="196"/>
+      <c r="A3" s="165"/>
+      <c r="B3" s="200"/>
+      <c r="C3" s="191"/>
+      <c r="D3" s="191"/>
       <c r="E3" s="11"/>
       <c r="F3" s="9" t="s">
         <v>310</v>
@@ -18364,7 +18382,7 @@
       <c r="H3" s="12">
         <v>2</v>
       </c>
-      <c r="I3" s="215">
+      <c r="I3" s="210">
         <v>44074</v>
       </c>
       <c r="J3" s="10"/>
@@ -18374,10 +18392,10 @@
       </c>
     </row>
     <row r="4" spans="1:17">
-      <c r="A4" s="168"/>
-      <c r="B4" s="205"/>
-      <c r="C4" s="196"/>
-      <c r="D4" s="197"/>
+      <c r="A4" s="165"/>
+      <c r="B4" s="200"/>
+      <c r="C4" s="191"/>
+      <c r="D4" s="192"/>
       <c r="E4" s="11"/>
       <c r="F4" s="9" t="s">
         <v>311</v>
@@ -18386,16 +18404,19 @@
         <v>358</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>965</v>
-      </c>
-      <c r="I4" s="215"/>
+        <v>963</v>
+      </c>
+      <c r="I4" s="210"/>
       <c r="J4" s="10"/>
       <c r="K4" s="10"/>
+      <c r="M4" t="s">
+        <v>1294</v>
+      </c>
     </row>
     <row r="5" spans="1:17">
-      <c r="A5" s="168"/>
-      <c r="B5" s="205"/>
-      <c r="C5" s="197"/>
+      <c r="A5" s="165"/>
+      <c r="B5" s="200"/>
+      <c r="C5" s="192"/>
       <c r="D5" s="46" t="s">
         <v>555</v>
       </c>
@@ -18407,9 +18428,9 @@
         <v>557</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>962</v>
-      </c>
-      <c r="I5" s="215">
+        <v>960</v>
+      </c>
+      <c r="I5" s="210">
         <v>44043</v>
       </c>
       <c r="J5" s="10" t="s">
@@ -18418,12 +18439,12 @@
       <c r="K5" s="10"/>
     </row>
     <row r="6" spans="1:17">
-      <c r="A6" s="168"/>
-      <c r="B6" s="205"/>
-      <c r="C6" s="195" t="s">
+      <c r="A6" s="165"/>
+      <c r="B6" s="200"/>
+      <c r="C6" s="190" t="s">
         <v>507</v>
       </c>
-      <c r="D6" s="195" t="s">
+      <c r="D6" s="190" t="s">
         <v>511</v>
       </c>
       <c r="E6" s="11"/>
@@ -18434,19 +18455,19 @@
         <v>317</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>963</v>
-      </c>
-      <c r="I6" s="215">
+        <v>961</v>
+      </c>
+      <c r="I6" s="210">
         <v>44043</v>
       </c>
       <c r="J6" s="10"/>
       <c r="K6" s="10"/>
     </row>
     <row r="7" spans="1:17">
-      <c r="A7" s="168"/>
-      <c r="B7" s="205"/>
-      <c r="C7" s="196"/>
-      <c r="D7" s="196"/>
+      <c r="A7" s="165"/>
+      <c r="B7" s="200"/>
+      <c r="C7" s="191"/>
+      <c r="D7" s="191"/>
       <c r="E7" s="11"/>
       <c r="F7" s="9" t="s">
         <v>313</v>
@@ -18457,17 +18478,17 @@
       <c r="H7" s="12">
         <v>1</v>
       </c>
-      <c r="I7" s="215">
+      <c r="I7" s="210">
         <v>44043</v>
       </c>
       <c r="J7" s="10"/>
       <c r="K7" s="10"/>
     </row>
     <row r="8" spans="1:17">
-      <c r="A8" s="168"/>
-      <c r="B8" s="205"/>
-      <c r="C8" s="196"/>
-      <c r="D8" s="196"/>
+      <c r="A8" s="165"/>
+      <c r="B8" s="200"/>
+      <c r="C8" s="191"/>
+      <c r="D8" s="191"/>
       <c r="E8" s="11"/>
       <c r="F8" s="9" t="s">
         <v>314</v>
@@ -18478,17 +18499,17 @@
       <c r="H8" s="12">
         <v>1</v>
       </c>
-      <c r="I8" s="215">
+      <c r="I8" s="210">
         <v>44043</v>
       </c>
       <c r="J8" s="10"/>
       <c r="K8" s="10"/>
     </row>
     <row r="9" spans="1:17">
-      <c r="A9" s="168"/>
-      <c r="B9" s="205"/>
-      <c r="C9" s="196"/>
-      <c r="D9" s="196"/>
+      <c r="A9" s="165"/>
+      <c r="B9" s="200"/>
+      <c r="C9" s="191"/>
+      <c r="D9" s="191"/>
       <c r="E9" s="8"/>
       <c r="F9" s="9" t="s">
         <v>345</v>
@@ -18499,17 +18520,17 @@
       <c r="H9" s="10">
         <v>1</v>
       </c>
-      <c r="I9" s="215">
+      <c r="I9" s="210">
         <v>44043</v>
       </c>
       <c r="J9" s="10"/>
       <c r="K9" s="10"/>
     </row>
     <row r="10" spans="1:17">
-      <c r="A10" s="168"/>
-      <c r="B10" s="205"/>
-      <c r="C10" s="196"/>
-      <c r="D10" s="196"/>
+      <c r="A10" s="165"/>
+      <c r="B10" s="200"/>
+      <c r="C10" s="191"/>
+      <c r="D10" s="191"/>
       <c r="E10" s="8"/>
       <c r="F10" s="9" t="s">
         <v>346</v>
@@ -18520,17 +18541,17 @@
       <c r="H10" s="10">
         <v>1</v>
       </c>
-      <c r="I10" s="215">
+      <c r="I10" s="210">
         <v>44043</v>
       </c>
       <c r="J10" s="10"/>
       <c r="K10" s="10"/>
     </row>
     <row r="11" spans="1:17">
-      <c r="A11" s="168"/>
-      <c r="B11" s="205"/>
-      <c r="C11" s="196"/>
-      <c r="D11" s="196"/>
+      <c r="A11" s="165"/>
+      <c r="B11" s="200"/>
+      <c r="C11" s="191"/>
+      <c r="D11" s="191"/>
       <c r="E11" s="8"/>
       <c r="F11" s="9" t="s">
         <v>315</v>
@@ -18541,17 +18562,17 @@
       <c r="H11" s="10">
         <v>1</v>
       </c>
-      <c r="I11" s="215">
+      <c r="I11" s="210">
         <v>44043</v>
       </c>
       <c r="J11" s="10"/>
       <c r="K11" s="10"/>
     </row>
     <row r="12" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A12" s="168"/>
-      <c r="B12" s="205"/>
-      <c r="C12" s="196"/>
-      <c r="D12" s="196"/>
+      <c r="A12" s="165"/>
+      <c r="B12" s="200"/>
+      <c r="C12" s="191"/>
+      <c r="D12" s="191"/>
       <c r="E12" s="8"/>
       <c r="F12" s="9" t="s">
         <v>347</v>
@@ -18562,17 +18583,17 @@
       <c r="H12" s="10">
         <v>1</v>
       </c>
-      <c r="I12" s="215">
+      <c r="I12" s="210">
         <v>44043</v>
       </c>
       <c r="J12" s="10"/>
       <c r="K12" s="10"/>
     </row>
     <row r="13" spans="1:17" ht="30">
-      <c r="A13" s="168"/>
-      <c r="B13" s="205"/>
-      <c r="C13" s="196"/>
-      <c r="D13" s="196"/>
+      <c r="A13" s="165"/>
+      <c r="B13" s="200"/>
+      <c r="C13" s="191"/>
+      <c r="D13" s="191"/>
       <c r="E13" s="11"/>
       <c r="F13" s="9" t="s">
         <v>316</v>
@@ -18583,20 +18604,20 @@
       <c r="H13" s="12">
         <v>3</v>
       </c>
-      <c r="I13" s="215"/>
+      <c r="I13" s="210"/>
       <c r="J13" s="10" t="s">
         <v>563</v>
       </c>
       <c r="K13" s="10"/>
       <c r="O13" s="102" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="14" spans="1:17">
-      <c r="A14" s="168"/>
-      <c r="B14" s="205"/>
-      <c r="C14" s="196"/>
-      <c r="D14" s="197"/>
+      <c r="A14" s="165"/>
+      <c r="B14" s="200"/>
+      <c r="C14" s="191"/>
+      <c r="D14" s="192"/>
       <c r="E14" s="11"/>
       <c r="F14" s="9" t="s">
         <v>318</v>
@@ -18607,16 +18628,16 @@
       <c r="H14" s="12">
         <v>2</v>
       </c>
-      <c r="I14" s="215">
+      <c r="I14" s="210">
         <v>44074</v>
       </c>
       <c r="J14" s="10"/>
       <c r="K14" s="10"/>
     </row>
     <row r="15" spans="1:17" ht="30">
-      <c r="A15" s="168"/>
-      <c r="B15" s="205"/>
-      <c r="C15" s="196"/>
+      <c r="A15" s="165"/>
+      <c r="B15" s="200"/>
+      <c r="C15" s="191"/>
       <c r="D15" s="22" t="s">
         <v>512</v>
       </c>
@@ -18630,30 +18651,30 @@
       <c r="H15" s="12">
         <v>1</v>
       </c>
-      <c r="I15" s="215">
+      <c r="I15" s="210">
         <v>44043</v>
       </c>
       <c r="J15" s="10"/>
       <c r="K15" s="10"/>
-      <c r="M15" s="200" t="s">
-        <v>852</v>
-      </c>
-      <c r="N15" s="201"/>
-      <c r="O15" s="118" t="s">
-        <v>1260</v>
+      <c r="M15" s="195" t="s">
+        <v>851</v>
+      </c>
+      <c r="N15" s="196"/>
+      <c r="O15" s="115" t="s">
+        <v>1258</v>
       </c>
       <c r="P15" s="91"/>
       <c r="Q15" s="91" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="30">
-      <c r="A16" s="168"/>
-      <c r="B16" s="205"/>
-      <c r="C16" s="195" t="s">
+      <c r="A16" s="165"/>
+      <c r="B16" s="200"/>
+      <c r="C16" s="190" t="s">
         <v>509</v>
       </c>
-      <c r="D16" s="195" t="s">
+      <c r="D16" s="190" t="s">
         <v>513</v>
       </c>
       <c r="E16" s="11"/>
@@ -18666,7 +18687,7 @@
       <c r="H16" s="12">
         <v>1</v>
       </c>
-      <c r="I16" s="215">
+      <c r="I16" s="210">
         <v>44043</v>
       </c>
       <c r="J16" s="10"/>
@@ -18678,20 +18699,20 @@
         <v>360</v>
       </c>
       <c r="O16" s="99" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="P16" s="103">
         <v>1</v>
       </c>
       <c r="Q16" s="91" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="17" spans="1:17">
-      <c r="A17" s="168"/>
-      <c r="B17" s="205"/>
-      <c r="C17" s="196"/>
-      <c r="D17" s="196"/>
+      <c r="A17" s="165"/>
+      <c r="B17" s="200"/>
+      <c r="C17" s="191"/>
+      <c r="D17" s="191"/>
       <c r="E17" s="19"/>
       <c r="F17" s="9" t="s">
         <v>364</v>
@@ -18702,7 +18723,7 @@
       <c r="H17" s="12">
         <v>1</v>
       </c>
-      <c r="I17" s="215">
+      <c r="I17" s="210">
         <v>44043</v>
       </c>
       <c r="J17" s="10"/>
@@ -18714,28 +18735,28 @@
         <v>365</v>
       </c>
       <c r="O17" s="99" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="P17" s="104">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:17">
-      <c r="A18" s="168"/>
-      <c r="B18" s="205"/>
-      <c r="C18" s="196"/>
-      <c r="D18" s="196"/>
+      <c r="A18" s="165"/>
+      <c r="B18" s="200"/>
+      <c r="C18" s="191"/>
+      <c r="D18" s="191"/>
       <c r="E18" s="19"/>
       <c r="F18" s="48" t="s">
         <v>559</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="H18" s="10">
         <v>1</v>
       </c>
-      <c r="I18" s="215">
+      <c r="I18" s="210">
         <v>44043</v>
       </c>
       <c r="J18" s="10" t="s">
@@ -18749,17 +18770,17 @@
         <v>366</v>
       </c>
       <c r="O18" s="99" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="P18" s="104">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:17">
-      <c r="A19" s="168"/>
-      <c r="B19" s="205"/>
-      <c r="C19" s="196"/>
-      <c r="D19" s="196"/>
+      <c r="A19" s="165"/>
+      <c r="B19" s="200"/>
+      <c r="C19" s="191"/>
+      <c r="D19" s="191"/>
       <c r="E19" s="8"/>
       <c r="F19" s="9" t="s">
         <v>332</v>
@@ -18770,7 +18791,7 @@
       <c r="H19" s="10">
         <v>1</v>
       </c>
-      <c r="I19" s="215">
+      <c r="I19" s="210">
         <v>44043</v>
       </c>
       <c r="J19" s="10"/>
@@ -18782,7 +18803,7 @@
         <v>368</v>
       </c>
       <c r="O19" s="99" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="P19" s="105">
         <v>1</v>
@@ -18790,10 +18811,10 @@
       <c r="Q19" s="91"/>
     </row>
     <row r="20" spans="1:17">
-      <c r="A20" s="168"/>
-      <c r="B20" s="205"/>
-      <c r="C20" s="196"/>
-      <c r="D20" s="196"/>
+      <c r="A20" s="165"/>
+      <c r="B20" s="200"/>
+      <c r="C20" s="191"/>
+      <c r="D20" s="191"/>
       <c r="E20" s="8"/>
       <c r="F20" s="9" t="s">
         <v>333</v>
@@ -18804,7 +18825,7 @@
       <c r="H20" s="10">
         <v>1</v>
       </c>
-      <c r="I20" s="215">
+      <c r="I20" s="210">
         <v>44043</v>
       </c>
       <c r="J20" s="10"/>
@@ -18813,10 +18834,10 @@
         <v>336</v>
       </c>
       <c r="N20" s="98" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="O20" s="99" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="P20" s="99">
         <v>2</v>
@@ -18824,10 +18845,10 @@
       <c r="Q20" s="91"/>
     </row>
     <row r="21" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A21" s="168"/>
-      <c r="B21" s="205"/>
-      <c r="C21" s="196"/>
-      <c r="D21" s="196"/>
+      <c r="A21" s="165"/>
+      <c r="B21" s="200"/>
+      <c r="C21" s="191"/>
+      <c r="D21" s="191"/>
       <c r="E21" s="14"/>
       <c r="F21" s="9" t="s">
         <v>334</v>
@@ -18838,32 +18859,32 @@
       <c r="H21" s="16">
         <v>3</v>
       </c>
-      <c r="I21" s="215"/>
+      <c r="I21" s="210"/>
       <c r="J21" s="10" t="s">
         <v>563</v>
       </c>
       <c r="K21" s="10"/>
       <c r="M21" s="99" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="N21" s="98" t="s">
         <v>361</v>
       </c>
       <c r="O21" s="99" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="P21" s="103">
         <v>1</v>
       </c>
       <c r="Q21" s="91" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="22" spans="1:17">
-      <c r="A22" s="168"/>
-      <c r="B22" s="205"/>
-      <c r="C22" s="196"/>
-      <c r="D22" s="196"/>
+      <c r="A22" s="165"/>
+      <c r="B22" s="200"/>
+      <c r="C22" s="191"/>
+      <c r="D22" s="191"/>
       <c r="E22" s="14"/>
       <c r="F22" s="9" t="s">
         <v>335</v>
@@ -18874,13 +18895,13 @@
       <c r="H22" s="16">
         <v>1</v>
       </c>
-      <c r="I22" s="215">
+      <c r="I22" s="210">
         <v>44043</v>
       </c>
       <c r="J22" s="10"/>
       <c r="K22" s="10"/>
       <c r="M22" s="101" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="N22" s="98" t="s">
         <v>362</v>
@@ -18892,14 +18913,14 @@
         <v>1</v>
       </c>
       <c r="Q22" s="91" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="23" spans="1:17">
-      <c r="A23" s="168"/>
-      <c r="B23" s="205"/>
-      <c r="C23" s="196"/>
-      <c r="D23" s="196"/>
+      <c r="A23" s="165"/>
+      <c r="B23" s="200"/>
+      <c r="C23" s="191"/>
+      <c r="D23" s="191"/>
       <c r="E23" s="14"/>
       <c r="F23" s="9" t="s">
         <v>336</v>
@@ -18910,7 +18931,7 @@
       <c r="H23" s="16">
         <v>2</v>
       </c>
-      <c r="I23" s="215">
+      <c r="I23" s="210">
         <v>44074</v>
       </c>
       <c r="J23" s="10"/>
@@ -18925,20 +18946,20 @@
         <v>81</v>
       </c>
       <c r="P23" s="100" t="s">
-        <v>964</v>
-      </c>
-      <c r="Q23" s="157" t="s">
-        <v>1286</v>
+        <v>962</v>
+      </c>
+      <c r="Q23" s="154" t="s">
+        <v>1284</v>
       </c>
     </row>
     <row r="24" spans="1:17">
-      <c r="A24" s="168"/>
-      <c r="B24" s="205"/>
-      <c r="C24" s="196"/>
-      <c r="D24" s="196"/>
+      <c r="A24" s="165"/>
+      <c r="B24" s="200"/>
+      <c r="C24" s="191"/>
+      <c r="D24" s="191"/>
       <c r="E24" s="8"/>
       <c r="F24" s="9" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="G24" s="13" t="s">
         <v>370</v>
@@ -18946,13 +18967,13 @@
       <c r="H24" s="10">
         <v>2</v>
       </c>
-      <c r="I24" s="215">
+      <c r="I24" s="210">
         <v>44074</v>
       </c>
       <c r="J24" s="10"/>
       <c r="K24" s="10"/>
-      <c r="M24" s="156" t="s">
-        <v>1282</v>
+      <c r="M24" s="153" t="s">
+        <v>1280</v>
       </c>
       <c r="N24" s="98" t="s">
         <v>371</v>
@@ -18966,10 +18987,10 @@
       <c r="Q24" s="91"/>
     </row>
     <row r="25" spans="1:17">
-      <c r="A25" s="168"/>
-      <c r="B25" s="205"/>
-      <c r="C25" s="196"/>
-      <c r="D25" s="196"/>
+      <c r="A25" s="165"/>
+      <c r="B25" s="200"/>
+      <c r="C25" s="191"/>
+      <c r="D25" s="191"/>
       <c r="E25" s="8"/>
       <c r="F25" s="9" t="s">
         <v>373</v>
@@ -18980,7 +19001,7 @@
       <c r="H25" s="10">
         <v>3</v>
       </c>
-      <c r="I25" s="215"/>
+      <c r="I25" s="210"/>
       <c r="J25" s="10" t="s">
         <v>563</v>
       </c>
@@ -18992,7 +19013,7 @@
         <v>370</v>
       </c>
       <c r="O25" s="99" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="P25" s="99">
         <v>2</v>
@@ -19000,10 +19021,10 @@
       <c r="Q25" s="91"/>
     </row>
     <row r="26" spans="1:17">
-      <c r="A26" s="168"/>
-      <c r="B26" s="205"/>
-      <c r="C26" s="196"/>
-      <c r="D26" s="196"/>
+      <c r="A26" s="165"/>
+      <c r="B26" s="200"/>
+      <c r="C26" s="191"/>
+      <c r="D26" s="191"/>
       <c r="E26" s="8"/>
       <c r="F26" s="9" t="s">
         <v>338</v>
@@ -19014,7 +19035,7 @@
       <c r="H26" s="10">
         <v>2</v>
       </c>
-      <c r="I26" s="215">
+      <c r="I26" s="210">
         <v>44074</v>
       </c>
       <c r="J26" s="10"/>
@@ -19034,10 +19055,10 @@
       <c r="Q26" s="91"/>
     </row>
     <row r="27" spans="1:17">
-      <c r="A27" s="168"/>
-      <c r="B27" s="205"/>
-      <c r="C27" s="196"/>
-      <c r="D27" s="196"/>
+      <c r="A27" s="165"/>
+      <c r="B27" s="200"/>
+      <c r="C27" s="191"/>
+      <c r="D27" s="191"/>
       <c r="E27" s="8"/>
       <c r="F27" s="9" t="s">
         <v>339</v>
@@ -19045,10 +19066,10 @@
       <c r="G27" s="13" t="s">
         <v>372</v>
       </c>
-      <c r="H27" s="123" t="s">
-        <v>964</v>
-      </c>
-      <c r="I27" s="215"/>
+      <c r="H27" s="120" t="s">
+        <v>962</v>
+      </c>
+      <c r="I27" s="210"/>
       <c r="J27" s="10"/>
       <c r="K27" s="10"/>
       <c r="M27" s="99" t="s">
@@ -19058,7 +19079,7 @@
         <v>367</v>
       </c>
       <c r="O27" s="99" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="P27" s="98">
         <v>3</v>
@@ -19066,13 +19087,13 @@
       <c r="Q27" s="91"/>
     </row>
     <row r="28" spans="1:17">
-      <c r="A28" s="168"/>
-      <c r="B28" s="205"/>
-      <c r="C28" s="196"/>
-      <c r="D28" s="196"/>
+      <c r="A28" s="165"/>
+      <c r="B28" s="200"/>
+      <c r="C28" s="191"/>
+      <c r="D28" s="191"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="125" t="s">
-        <v>967</v>
+      <c r="F28" s="122" t="s">
+        <v>965</v>
       </c>
       <c r="G28" s="13" t="s">
         <v>371</v>
@@ -19080,7 +19101,7 @@
       <c r="H28" s="10">
         <v>1</v>
       </c>
-      <c r="I28" s="215">
+      <c r="I28" s="210">
         <v>44043</v>
       </c>
       <c r="J28" s="10"/>
@@ -19092,7 +19113,7 @@
         <v>374</v>
       </c>
       <c r="O28" s="99" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="P28" s="99">
         <v>3</v>
@@ -19100,33 +19121,33 @@
       <c r="Q28" s="91"/>
     </row>
     <row r="29" spans="1:17">
-      <c r="A29" s="168"/>
-      <c r="B29" s="205"/>
-      <c r="C29" s="196"/>
-      <c r="D29" s="196"/>
+      <c r="A29" s="165"/>
+      <c r="B29" s="200"/>
+      <c r="C29" s="191"/>
+      <c r="D29" s="191"/>
       <c r="E29" s="8"/>
       <c r="F29" s="9" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="H29" s="16">
         <v>2</v>
       </c>
-      <c r="I29" s="215">
+      <c r="I29" s="210">
         <v>44074</v>
       </c>
       <c r="J29" s="10"/>
       <c r="K29" s="10" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
     </row>
     <row r="30" spans="1:17">
-      <c r="A30" s="168"/>
-      <c r="B30" s="205"/>
-      <c r="C30" s="196"/>
-      <c r="D30" s="197"/>
+      <c r="A30" s="165"/>
+      <c r="B30" s="200"/>
+      <c r="C30" s="191"/>
+      <c r="D30" s="192"/>
       <c r="E30" s="8"/>
       <c r="F30" s="49" t="s">
         <v>323</v>
@@ -19137,29 +19158,29 @@
       <c r="H30" s="114">
         <v>3</v>
       </c>
-      <c r="I30" s="215"/>
+      <c r="I30" s="210"/>
       <c r="J30" s="10"/>
-      <c r="K30" s="198" t="s">
-        <v>961</v>
+      <c r="K30" s="193" t="s">
+        <v>959</v>
       </c>
       <c r="M30" s="102" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="N30" s="102" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="O30" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="P30" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="31" spans="1:17">
-      <c r="A31" s="168"/>
-      <c r="B31" s="205"/>
-      <c r="C31" s="196"/>
-      <c r="D31" s="195" t="s">
+      <c r="A31" s="165"/>
+      <c r="B31" s="200"/>
+      <c r="C31" s="191"/>
+      <c r="D31" s="190" t="s">
         <v>518</v>
       </c>
       <c r="E31" s="8"/>
@@ -19172,17 +19193,17 @@
       <c r="H31" s="16">
         <v>1</v>
       </c>
-      <c r="I31" s="215">
+      <c r="I31" s="210">
         <v>44043</v>
       </c>
       <c r="J31" s="10"/>
-      <c r="K31" s="202"/>
+      <c r="K31" s="197"/>
     </row>
     <row r="32" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A32" s="168"/>
-      <c r="B32" s="205"/>
-      <c r="C32" s="196"/>
-      <c r="D32" s="196"/>
+      <c r="A32" s="165"/>
+      <c r="B32" s="200"/>
+      <c r="C32" s="191"/>
+      <c r="D32" s="191"/>
       <c r="E32" s="8"/>
       <c r="F32" s="9" t="s">
         <v>325</v>
@@ -19193,75 +19214,75 @@
       <c r="H32" s="16">
         <v>1</v>
       </c>
-      <c r="I32" s="215">
+      <c r="I32" s="210">
         <v>44043</v>
       </c>
       <c r="J32" s="10"/>
-      <c r="K32" s="202"/>
-      <c r="M32" s="154" t="s">
-        <v>1279</v>
+      <c r="K32" s="197"/>
+      <c r="M32" s="151" t="s">
+        <v>1277</v>
       </c>
     </row>
     <row r="33" spans="1:15" ht="16.5" customHeight="1">
-      <c r="A33" s="168"/>
-      <c r="B33" s="205"/>
-      <c r="C33" s="196"/>
-      <c r="D33" s="196"/>
+      <c r="A33" s="165"/>
+      <c r="B33" s="200"/>
+      <c r="C33" s="191"/>
+      <c r="D33" s="191"/>
       <c r="E33" s="8"/>
       <c r="F33" s="9" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="H33" s="16">
         <v>2</v>
       </c>
-      <c r="I33" s="215">
+      <c r="I33" s="210">
         <v>44043</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>956</v>
-      </c>
-      <c r="K33" s="203"/>
-      <c r="M33" s="155" t="s">
-        <v>1280</v>
+        <v>954</v>
+      </c>
+      <c r="K33" s="198"/>
+      <c r="M33" s="152" t="s">
+        <v>1278</v>
       </c>
       <c r="N33" s="5" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="O33" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="34" spans="1:15" ht="16.5" customHeight="1">
-      <c r="A34" s="168"/>
-      <c r="B34" s="205"/>
-      <c r="C34" s="196"/>
-      <c r="D34" s="196"/>
+      <c r="A34" s="165"/>
+      <c r="B34" s="200"/>
+      <c r="C34" s="191"/>
+      <c r="D34" s="191"/>
       <c r="E34" s="8"/>
       <c r="F34" s="9" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>1278</v>
-      </c>
-      <c r="H34" s="122">
+        <v>1276</v>
+      </c>
+      <c r="H34" s="119">
         <v>2</v>
       </c>
-      <c r="I34" s="215">
+      <c r="I34" s="210">
         <v>44074</v>
       </c>
       <c r="J34" s="10"/>
       <c r="K34" s="10" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
     </row>
     <row r="35" spans="1:15">
-      <c r="A35" s="168"/>
-      <c r="B35" s="205"/>
-      <c r="C35" s="197"/>
-      <c r="D35" s="197"/>
+      <c r="A35" s="165"/>
+      <c r="B35" s="200"/>
+      <c r="C35" s="192"/>
+      <c r="D35" s="192"/>
       <c r="E35" s="8"/>
       <c r="F35" s="49" t="s">
         <v>322</v>
@@ -19272,17 +19293,17 @@
       <c r="H35" s="50">
         <v>3</v>
       </c>
-      <c r="I35" s="215"/>
+      <c r="I35" s="210"/>
       <c r="J35" s="10"/>
       <c r="K35" s="10"/>
     </row>
     <row r="36" spans="1:15">
-      <c r="A36" s="168"/>
-      <c r="B36" s="205"/>
-      <c r="C36" s="195" t="s">
+      <c r="A36" s="165"/>
+      <c r="B36" s="200"/>
+      <c r="C36" s="190" t="s">
         <v>340</v>
       </c>
-      <c r="D36" s="195" t="s">
+      <c r="D36" s="190" t="s">
         <v>517</v>
       </c>
       <c r="E36" s="8"/>
@@ -19295,17 +19316,17 @@
       <c r="H36" s="16">
         <v>1</v>
       </c>
-      <c r="I36" s="215">
+      <c r="I36" s="210">
         <v>44043</v>
       </c>
       <c r="J36" s="10"/>
       <c r="K36" s="10"/>
     </row>
     <row r="37" spans="1:15">
-      <c r="A37" s="168"/>
-      <c r="B37" s="206"/>
-      <c r="C37" s="197"/>
-      <c r="D37" s="197"/>
+      <c r="A37" s="165"/>
+      <c r="B37" s="201"/>
+      <c r="C37" s="192"/>
+      <c r="D37" s="192"/>
       <c r="E37" s="8"/>
       <c r="F37" s="9" t="s">
         <v>331</v>
@@ -19313,15 +19334,15 @@
       <c r="G37" s="9" t="s">
         <v>376</v>
       </c>
-      <c r="H37" s="124" t="s">
-        <v>965</v>
-      </c>
-      <c r="I37" s="215"/>
+      <c r="H37" s="121" t="s">
+        <v>963</v>
+      </c>
+      <c r="I37" s="210"/>
       <c r="J37" s="10"/>
       <c r="K37" s="10"/>
     </row>
     <row r="38" spans="1:15">
-      <c r="A38" s="168"/>
+      <c r="A38" s="165"/>
       <c r="B38" s="29" t="s">
         <v>328</v>
       </c>
@@ -19341,19 +19362,19 @@
       <c r="H38" s="16" t="s">
         <v>330</v>
       </c>
-      <c r="I38" s="215"/>
+      <c r="I38" s="210"/>
       <c r="J38" s="10"/>
       <c r="K38" s="10"/>
     </row>
     <row r="39" spans="1:15" ht="16.5" customHeight="1">
-      <c r="A39" s="168"/>
-      <c r="B39" s="204" t="s">
+      <c r="A39" s="165"/>
+      <c r="B39" s="199" t="s">
         <v>505</v>
       </c>
-      <c r="C39" s="195" t="s">
+      <c r="C39" s="190" t="s">
         <v>510</v>
       </c>
-      <c r="D39" s="195" t="s">
+      <c r="D39" s="190" t="s">
         <v>516</v>
       </c>
       <c r="E39" s="8" t="s">
@@ -19368,15 +19389,15 @@
       <c r="H39" s="10">
         <v>2</v>
       </c>
-      <c r="I39" s="215"/>
+      <c r="I39" s="210"/>
       <c r="J39" s="10"/>
       <c r="K39" s="10"/>
     </row>
     <row r="40" spans="1:15" ht="16.5" customHeight="1">
-      <c r="A40" s="168"/>
-      <c r="B40" s="205"/>
-      <c r="C40" s="168"/>
-      <c r="D40" s="168"/>
+      <c r="A40" s="165"/>
+      <c r="B40" s="200"/>
+      <c r="C40" s="165"/>
+      <c r="D40" s="165"/>
       <c r="E40" s="17"/>
       <c r="F40" s="9" t="s">
         <v>304</v>
@@ -19387,17 +19408,17 @@
       <c r="H40" s="16">
         <v>1</v>
       </c>
-      <c r="I40" s="215">
+      <c r="I40" s="210">
         <v>44043</v>
       </c>
       <c r="J40" s="10"/>
       <c r="K40" s="10"/>
     </row>
     <row r="41" spans="1:15" ht="16.5" customHeight="1">
-      <c r="A41" s="168"/>
-      <c r="B41" s="205"/>
-      <c r="C41" s="168"/>
-      <c r="D41" s="168"/>
+      <c r="A41" s="165"/>
+      <c r="B41" s="200"/>
+      <c r="C41" s="165"/>
+      <c r="D41" s="165"/>
       <c r="E41" s="17"/>
       <c r="F41" s="9" t="s">
         <v>305</v>
@@ -19408,17 +19429,17 @@
       <c r="H41" s="16">
         <v>1</v>
       </c>
-      <c r="I41" s="215">
+      <c r="I41" s="210">
         <v>44043</v>
       </c>
       <c r="J41" s="10"/>
       <c r="K41" s="10"/>
     </row>
     <row r="42" spans="1:15">
-      <c r="A42" s="168"/>
-      <c r="B42" s="205"/>
-      <c r="C42" s="168"/>
-      <c r="D42" s="169"/>
+      <c r="A42" s="165"/>
+      <c r="B42" s="200"/>
+      <c r="C42" s="165"/>
+      <c r="D42" s="166"/>
       <c r="E42" s="17"/>
       <c r="F42" s="9" t="s">
         <v>305</v>
@@ -19429,17 +19450,17 @@
       <c r="H42" s="16">
         <v>2</v>
       </c>
-      <c r="I42" s="215">
+      <c r="I42" s="210">
         <v>44074</v>
       </c>
       <c r="J42" s="10"/>
       <c r="K42" s="10"/>
     </row>
     <row r="43" spans="1:15" ht="16.5" customHeight="1">
-      <c r="A43" s="168"/>
-      <c r="B43" s="205"/>
-      <c r="C43" s="168"/>
-      <c r="D43" s="195" t="s">
+      <c r="A43" s="165"/>
+      <c r="B43" s="200"/>
+      <c r="C43" s="165"/>
+      <c r="D43" s="190" t="s">
         <v>515</v>
       </c>
       <c r="E43" s="8"/>
@@ -19450,21 +19471,21 @@
         <v>298</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>963</v>
-      </c>
-      <c r="I43" s="215">
+        <v>961</v>
+      </c>
+      <c r="I43" s="210">
         <v>44043</v>
       </c>
       <c r="J43" s="10"/>
-      <c r="K43" s="198" t="s">
-        <v>1166</v>
+      <c r="K43" s="193" t="s">
+        <v>1164</v>
       </c>
     </row>
     <row r="44" spans="1:15">
-      <c r="A44" s="168"/>
-      <c r="B44" s="205"/>
-      <c r="C44" s="168"/>
-      <c r="D44" s="169"/>
+      <c r="A44" s="165"/>
+      <c r="B44" s="200"/>
+      <c r="C44" s="165"/>
+      <c r="D44" s="166"/>
       <c r="E44" s="8"/>
       <c r="F44" s="9" t="s">
         <v>289</v>
@@ -19473,19 +19494,19 @@
         <v>299</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>963</v>
-      </c>
-      <c r="I44" s="215">
+        <v>961</v>
+      </c>
+      <c r="I44" s="210">
         <v>44043</v>
       </c>
       <c r="J44" s="10"/>
-      <c r="K44" s="199"/>
+      <c r="K44" s="194"/>
     </row>
     <row r="45" spans="1:15">
-      <c r="A45" s="168"/>
-      <c r="B45" s="205"/>
-      <c r="C45" s="168"/>
-      <c r="D45" s="195" t="s">
+      <c r="A45" s="165"/>
+      <c r="B45" s="200"/>
+      <c r="C45" s="165"/>
+      <c r="D45" s="190" t="s">
         <v>514</v>
       </c>
       <c r="E45" s="8"/>
@@ -19498,15 +19519,15 @@
       <c r="H45" s="10">
         <v>2</v>
       </c>
-      <c r="I45" s="215"/>
+      <c r="I45" s="210"/>
       <c r="J45" s="10"/>
       <c r="K45" s="10"/>
     </row>
     <row r="46" spans="1:15">
-      <c r="A46" s="169"/>
-      <c r="B46" s="206"/>
-      <c r="C46" s="169"/>
-      <c r="D46" s="169"/>
+      <c r="A46" s="166"/>
+      <c r="B46" s="201"/>
+      <c r="C46" s="166"/>
+      <c r="D46" s="166"/>
       <c r="E46" s="8"/>
       <c r="F46" s="9" t="s">
         <v>301</v>
@@ -19517,7 +19538,7 @@
       <c r="H46" s="10">
         <v>2</v>
       </c>
-      <c r="I46" s="215"/>
+      <c r="I46" s="210"/>
       <c r="J46" s="10"/>
       <c r="K46" s="10"/>
     </row>
@@ -19583,11 +19604,11 @@
       <c r="B1" s="25" t="s">
         <v>327</v>
       </c>
-      <c r="E1" s="209" t="s">
+      <c r="E1" s="204" t="s">
         <v>724</v>
       </c>
-      <c r="F1" s="209"/>
-      <c r="G1" s="209"/>
+      <c r="F1" s="204"/>
+      <c r="G1" s="204"/>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="19" t="s">
@@ -19596,11 +19617,11 @@
       <c r="B2" s="19" t="s">
         <v>257</v>
       </c>
-      <c r="E2" s="210" t="s">
+      <c r="E2" s="205" t="s">
         <v>725</v>
       </c>
-      <c r="F2" s="210"/>
-      <c r="G2" s="210"/>
+      <c r="F2" s="205"/>
+      <c r="G2" s="205"/>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="19" t="s">
@@ -19617,10 +19638,10 @@
       <c r="B4" s="19" t="s">
         <v>259</v>
       </c>
-      <c r="E4" s="209" t="s">
+      <c r="E4" s="204" t="s">
         <v>722</v>
       </c>
-      <c r="F4" s="209"/>
+      <c r="F4" s="204"/>
       <c r="G4" s="25" t="s">
         <v>723</v>
       </c>
@@ -19632,16 +19653,16 @@
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="E5" s="208" t="s">
+      <c r="E5" s="203" t="s">
         <v>720</v>
       </c>
-      <c r="F5" s="208" t="s">
+      <c r="F5" s="203" t="s">
         <v>721</v>
       </c>
       <c r="G5" s="68" t="s">
         <v>747</v>
       </c>
-      <c r="H5" s="207" t="s">
+      <c r="H5" s="202" t="s">
         <v>748</v>
       </c>
       <c r="J5" t="s">
@@ -19652,12 +19673,12 @@
       <c r="A6" t="s">
         <v>261</v>
       </c>
-      <c r="E6" s="208"/>
-      <c r="F6" s="208"/>
+      <c r="E6" s="203"/>
+      <c r="F6" s="203"/>
       <c r="G6" s="68" t="s">
         <v>746</v>
       </c>
-      <c r="H6" s="208"/>
+      <c r="H6" s="203"/>
       <c r="J6" t="s">
         <v>729</v>
       </c>
@@ -19689,7 +19710,7 @@
         <v>274</v>
       </c>
       <c r="B9" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="J9" t="s">
         <v>732</v>
@@ -19724,7 +19745,7 @@
         <v>790</v>
       </c>
       <c r="H13" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="J13" t="s">
         <v>735</v>
@@ -19744,7 +19765,7 @@
         <v>795</v>
       </c>
       <c r="H14" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
       <c r="J14" t="s">
         <v>736</v>
@@ -19761,7 +19782,7 @@
         <v>793</v>
       </c>
       <c r="G15" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="J15" t="s">
         <v>732</v>
@@ -19778,63 +19799,66 @@
         <v>792</v>
       </c>
       <c r="G16" t="s">
-        <v>796</v>
+        <v>1295</v>
       </c>
       <c r="J16" t="s">
         <v>737</v>
       </c>
     </row>
-    <row r="17" spans="10:10">
+    <row r="17" spans="7:10">
+      <c r="G17" s="7" t="s">
+        <v>1296</v>
+      </c>
       <c r="J17" t="s">
         <v>738</v>
       </c>
     </row>
-    <row r="18" spans="10:10">
+    <row r="18" spans="7:10">
       <c r="J18" t="s">
         <v>739</v>
       </c>
     </row>
-    <row r="19" spans="10:10">
+    <row r="19" spans="7:10">
       <c r="J19" t="s">
         <v>740</v>
       </c>
     </row>
-    <row r="20" spans="10:10">
+    <row r="20" spans="7:10">
       <c r="J20" t="s">
         <v>732</v>
       </c>
     </row>
-    <row r="21" spans="10:10">
+    <row r="21" spans="7:10">
       <c r="J21" s="6" t="s">
         <v>744</v>
       </c>
     </row>
-    <row r="22" spans="10:10">
+    <row r="22" spans="7:10">
       <c r="J22" t="s">
         <v>732</v>
       </c>
     </row>
-    <row r="23" spans="10:10">
+    <row r="23" spans="7:10">
       <c r="J23" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="24" spans="10:10">
+    <row r="24" spans="7:10">
       <c r="J24" t="s">
         <v>741</v>
       </c>
     </row>
-    <row r="25" spans="10:10">
+    <row r="25" spans="7:10">
       <c r="J25" t="s">
         <v>742</v>
       </c>
     </row>
-    <row r="26" spans="10:10">
+    <row r="26" spans="7:10">
       <c r="J26" t="s">
         <v>743</v>
       </c>
     </row>
-    <row r="27" spans="10:10">
+    <row r="27" spans="7:10">
       <c r="J27" t="s">
         <v>732</v>
       </c>
@@ -19849,8 +19873,11 @@
     <mergeCell ref="F5:F6"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="G17" r:id="rId1" xr:uid="{AFFE4D15-4037-4F6C-80C7-ADA30B10B0D3}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -19868,352 +19895,352 @@
     <col min="7" max="7" width="33" customWidth="1"/>
     <col min="8" max="8" width="38.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.140625" style="81" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="60.42578125" style="132" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="60.42578125" style="129" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30">
-      <c r="A1" s="136" t="s">
-        <v>847</v>
-      </c>
-      <c r="B1" s="136" t="s">
+      <c r="A1" s="133" t="s">
+        <v>846</v>
+      </c>
+      <c r="B1" s="133" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C1" s="133" t="s">
+        <v>640</v>
+      </c>
+      <c r="D1" s="133" t="s">
+        <v>1172</v>
+      </c>
+      <c r="E1" s="133" t="s">
+        <v>1167</v>
+      </c>
+      <c r="F1" s="133" t="s">
+        <v>1168</v>
+      </c>
+      <c r="G1" s="134" t="s">
+        <v>1202</v>
+      </c>
+      <c r="H1" s="134" t="s">
+        <v>1255</v>
+      </c>
+      <c r="I1" s="133" t="s">
+        <v>1176</v>
+      </c>
+      <c r="J1" s="133" t="s">
+        <v>1182</v>
+      </c>
+      <c r="K1" s="133" t="s">
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="132">
+        <v>44028</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>1171</v>
       </c>
-      <c r="C1" s="136" t="s">
-        <v>640</v>
-      </c>
-      <c r="D1" s="136" t="s">
+      <c r="D2" s="116" t="s">
+        <v>1173</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>1175</v>
+      </c>
+      <c r="F2" s="116" t="s">
         <v>1174</v>
       </c>
-      <c r="E1" s="136" t="s">
-        <v>1169</v>
-      </c>
-      <c r="F1" s="136" t="s">
-        <v>1170</v>
-      </c>
-      <c r="G1" s="137" t="s">
+      <c r="G2" s="116">
+        <v>0.36</v>
+      </c>
+      <c r="H2" s="116"/>
+      <c r="I2" s="116" t="s">
+        <v>1177</v>
+      </c>
+      <c r="J2" s="116" t="s">
+        <v>892</v>
+      </c>
+      <c r="K2" s="206" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="132">
+        <v>44028</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>1193</v>
+      </c>
+      <c r="D3" s="116" t="s">
+        <v>1173</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>1180</v>
+      </c>
+      <c r="F3" s="116" t="s">
+        <v>1192</v>
+      </c>
+      <c r="G3" s="116">
+        <v>0.78</v>
+      </c>
+      <c r="H3" s="116"/>
+      <c r="I3" s="116" t="s">
+        <v>1181</v>
+      </c>
+      <c r="J3" s="116" t="s">
+        <v>892</v>
+      </c>
+      <c r="K3" s="207"/>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="132">
+        <v>44029</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>1186</v>
+      </c>
+      <c r="D4" s="116" t="s">
+        <v>1173</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>1185</v>
+      </c>
+      <c r="F4" s="116" t="s">
+        <v>1187</v>
+      </c>
+      <c r="G4" s="116">
+        <v>5.83</v>
+      </c>
+      <c r="H4" s="116"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="116" t="s">
+        <v>892</v>
+      </c>
+      <c r="K4" s="207"/>
+    </row>
+    <row r="5" spans="1:11" ht="45">
+      <c r="A5" s="132">
+        <v>44029</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>1189</v>
+      </c>
+      <c r="D5" s="116" t="s">
+        <v>1173</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>1191</v>
+      </c>
+      <c r="F5" s="116" t="s">
+        <v>1190</v>
+      </c>
+      <c r="G5" s="116">
+        <v>2.21</v>
+      </c>
+      <c r="H5" s="116"/>
+      <c r="I5" s="116"/>
+      <c r="J5" s="116" t="s">
+        <v>892</v>
+      </c>
+      <c r="K5" s="208"/>
+    </row>
+    <row r="6" spans="1:11" ht="60">
+      <c r="A6" s="132">
+        <v>44029</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>1204</v>
       </c>
-      <c r="H1" s="137" t="s">
-        <v>1257</v>
-      </c>
-      <c r="I1" s="136" t="s">
-        <v>1178</v>
-      </c>
-      <c r="J1" s="136" t="s">
-        <v>1184</v>
-      </c>
-      <c r="K1" s="136" t="s">
-        <v>1190</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="135">
-        <v>44028</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>1172</v>
-      </c>
-      <c r="C2" s="8" t="s">
+      <c r="D6" s="116" t="s">
         <v>1173</v>
       </c>
-      <c r="D2" s="119" t="s">
-        <v>1175</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>1177</v>
-      </c>
-      <c r="F2" s="119" t="s">
-        <v>1176</v>
-      </c>
-      <c r="G2" s="119">
-        <v>0.36</v>
-      </c>
-      <c r="H2" s="119"/>
-      <c r="I2" s="119" t="s">
-        <v>1179</v>
-      </c>
-      <c r="J2" s="119" t="s">
-        <v>893</v>
-      </c>
-      <c r="K2" s="211" t="s">
-        <v>1196</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="135">
-        <v>44028</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>1181</v>
-      </c>
-      <c r="C3" s="8" t="s">
+      <c r="E6" s="18" t="s">
+        <v>1191</v>
+      </c>
+      <c r="F6" s="116" t="s">
         <v>1195</v>
       </c>
-      <c r="D3" s="119" t="s">
-        <v>1175</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>1182</v>
-      </c>
-      <c r="F3" s="119" t="s">
-        <v>1194</v>
-      </c>
-      <c r="G3" s="119">
-        <v>0.78</v>
-      </c>
-      <c r="H3" s="119"/>
-      <c r="I3" s="119" t="s">
-        <v>1183</v>
-      </c>
-      <c r="J3" s="119" t="s">
-        <v>893</v>
-      </c>
-      <c r="K3" s="212"/>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="135">
-        <v>44029</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>1186</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>1188</v>
-      </c>
-      <c r="D4" s="119" t="s">
-        <v>1175</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>1187</v>
-      </c>
-      <c r="F4" s="119" t="s">
-        <v>1189</v>
-      </c>
-      <c r="G4" s="119">
-        <v>5.83</v>
-      </c>
-      <c r="H4" s="119"/>
-      <c r="I4" s="119"/>
-      <c r="J4" s="119" t="s">
-        <v>893</v>
-      </c>
-      <c r="K4" s="212"/>
-    </row>
-    <row r="5" spans="1:11" ht="45">
-      <c r="A5" s="135">
-        <v>44029</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>1185</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>1191</v>
-      </c>
-      <c r="D5" s="119" t="s">
-        <v>1175</v>
-      </c>
-      <c r="E5" s="18" t="s">
-        <v>1193</v>
-      </c>
-      <c r="F5" s="119" t="s">
-        <v>1192</v>
-      </c>
-      <c r="G5" s="119">
-        <v>2.21</v>
-      </c>
-      <c r="H5" s="119"/>
-      <c r="I5" s="119"/>
-      <c r="J5" s="119" t="s">
-        <v>893</v>
-      </c>
-      <c r="K5" s="213"/>
-    </row>
-    <row r="6" spans="1:11" ht="60">
-      <c r="A6" s="135">
-        <v>44029</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>1185</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>1206</v>
-      </c>
-      <c r="D6" s="119" t="s">
-        <v>1175</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>1193</v>
-      </c>
-      <c r="F6" s="119" t="s">
-        <v>1197</v>
-      </c>
       <c r="G6" s="18" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="H6" s="18"/>
-      <c r="I6" s="119" t="s">
-        <v>1205</v>
+      <c r="I6" s="116" t="s">
+        <v>1203</v>
       </c>
       <c r="J6" s="8"/>
       <c r="K6" s="8" t="s">
+        <v>1201</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="60">
+      <c r="A7" s="132">
+        <v>44029</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>1215</v>
+      </c>
+      <c r="D7" s="116" t="s">
+        <v>1173</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>1191</v>
+      </c>
+      <c r="F7" s="116" t="s">
+        <v>1206</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>1207</v>
+      </c>
+      <c r="H7" s="18"/>
+      <c r="I7" s="116" t="s">
         <v>1203</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="60">
-      <c r="A7" s="135">
-        <v>44029</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>1185</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>1217</v>
-      </c>
-      <c r="D7" s="119" t="s">
-        <v>1175</v>
-      </c>
-      <c r="E7" s="18" t="s">
-        <v>1193</v>
-      </c>
-      <c r="F7" s="119" t="s">
-        <v>1208</v>
-      </c>
-      <c r="G7" s="18" t="s">
-        <v>1209</v>
-      </c>
-      <c r="H7" s="18"/>
-      <c r="I7" s="119" t="s">
-        <v>1205</v>
       </c>
       <c r="J7" s="8"/>
       <c r="K7" s="8"/>
     </row>
     <row r="8" spans="1:11" ht="60">
-      <c r="A8" s="135">
+      <c r="A8" s="132">
         <v>44029</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>1210</v>
-      </c>
-      <c r="D8" s="119" t="s">
-        <v>1175</v>
+        <v>1208</v>
+      </c>
+      <c r="D8" s="116" t="s">
+        <v>1173</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>1193</v>
-      </c>
-      <c r="F8" s="119" t="s">
-        <v>1198</v>
+        <v>1191</v>
+      </c>
+      <c r="F8" s="116" t="s">
+        <v>1196</v>
       </c>
       <c r="G8" s="18" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="H8" s="18" t="s">
-        <v>1242</v>
-      </c>
-      <c r="I8" s="119" t="s">
-        <v>1205</v>
+        <v>1240</v>
+      </c>
+      <c r="I8" s="116" t="s">
+        <v>1203</v>
       </c>
       <c r="J8" s="8"/>
       <c r="K8" s="18" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="60">
-      <c r="A9" s="135">
+      <c r="A9" s="132">
         <v>44029</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>1212</v>
-      </c>
-      <c r="D9" s="119" t="s">
-        <v>1175</v>
+        <v>1210</v>
+      </c>
+      <c r="D9" s="116" t="s">
+        <v>1173</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>1193</v>
-      </c>
-      <c r="F9" s="145" t="s">
-        <v>1245</v>
-      </c>
-      <c r="G9" s="146" t="s">
-        <v>1213</v>
-      </c>
-      <c r="H9" s="143" t="s">
+        <v>1191</v>
+      </c>
+      <c r="F9" s="142" t="s">
         <v>1243</v>
       </c>
-      <c r="I9" s="119" t="s">
-        <v>1205</v>
+      <c r="G9" s="143" t="s">
+        <v>1211</v>
+      </c>
+      <c r="H9" s="140" t="s">
+        <v>1241</v>
+      </c>
+      <c r="I9" s="116" t="s">
+        <v>1203</v>
       </c>
       <c r="J9" s="8"/>
       <c r="K9" s="18" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="64.5" customHeight="1">
-      <c r="A10" s="142" t="s">
-        <v>1229</v>
+      <c r="A10" s="139" t="s">
+        <v>1227</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>1216</v>
-      </c>
-      <c r="D10" s="119" t="s">
-        <v>1175</v>
+        <v>1214</v>
+      </c>
+      <c r="D10" s="116" t="s">
+        <v>1173</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>1193</v>
-      </c>
-      <c r="F10" s="119" t="s">
-        <v>1200</v>
+        <v>1191</v>
+      </c>
+      <c r="F10" s="116" t="s">
+        <v>1198</v>
       </c>
       <c r="G10" s="18" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="H10" s="18"/>
-      <c r="I10" s="119" t="s">
-        <v>1205</v>
+      <c r="I10" s="116" t="s">
+        <v>1203</v>
       </c>
       <c r="J10" s="8"/>
       <c r="K10" s="18" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="45">
-      <c r="A11" s="140" t="s">
-        <v>1220</v>
+      <c r="A11" s="137" t="s">
+        <v>1218</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>1216</v>
-      </c>
-      <c r="D11" s="119" t="s">
-        <v>1175</v>
+        <v>1214</v>
+      </c>
+      <c r="D11" s="116" t="s">
+        <v>1173</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>1193</v>
-      </c>
-      <c r="F11" s="119" t="s">
-        <v>1200</v>
-      </c>
-      <c r="G11" s="139" t="s">
-        <v>1247</v>
-      </c>
-      <c r="H11" s="139"/>
-      <c r="I11" s="119" t="s">
-        <v>1219</v>
+        <v>1191</v>
+      </c>
+      <c r="F11" s="116" t="s">
+        <v>1198</v>
+      </c>
+      <c r="G11" s="136" t="s">
+        <v>1245</v>
+      </c>
+      <c r="H11" s="136"/>
+      <c r="I11" s="116" t="s">
+        <v>1217</v>
       </c>
       <c r="J11" s="8"/>
       <c r="K11" s="18" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -20222,17 +20249,17 @@
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
-      <c r="F12" s="119" t="s">
-        <v>1201</v>
+      <c r="F12" s="116" t="s">
+        <v>1199</v>
       </c>
       <c r="G12" s="8"/>
       <c r="H12" s="8"/>
-      <c r="I12" s="119" t="s">
-        <v>1205</v>
+      <c r="I12" s="116" t="s">
+        <v>1203</v>
       </c>
       <c r="J12" s="8"/>
       <c r="K12" s="8" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -20241,245 +20268,245 @@
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
-      <c r="F13" s="119" t="s">
-        <v>1202</v>
+      <c r="F13" s="116" t="s">
+        <v>1200</v>
       </c>
       <c r="G13" s="8"/>
       <c r="H13" s="8"/>
-      <c r="I13" s="119" t="s">
-        <v>1205</v>
+      <c r="I13" s="116" t="s">
+        <v>1203</v>
       </c>
       <c r="J13" s="8"/>
       <c r="K13" s="8" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="132"/>
-      <c r="B14" s="132"/>
-      <c r="C14" s="132"/>
-      <c r="D14" s="132"/>
-      <c r="E14" s="138" t="s">
-        <v>1218</v>
-      </c>
-      <c r="F14" s="133"/>
-      <c r="G14" s="138" t="s">
+      <c r="A14" s="129"/>
+      <c r="B14" s="129"/>
+      <c r="C14" s="129"/>
+      <c r="D14" s="129"/>
+      <c r="E14" s="135" t="s">
+        <v>1216</v>
+      </c>
+      <c r="F14" s="130"/>
+      <c r="G14" s="135" t="s">
+        <v>1254</v>
+      </c>
+      <c r="H14" s="129"/>
+      <c r="I14" s="130"/>
+      <c r="J14" s="129"/>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="129"/>
+      <c r="B15" s="129"/>
+      <c r="C15" s="129"/>
+      <c r="D15" s="129"/>
+      <c r="E15" s="129"/>
+      <c r="F15" s="130"/>
+      <c r="G15" s="129" t="s">
+        <v>1233</v>
+      </c>
+      <c r="H15" s="129" t="s">
+        <v>1234</v>
+      </c>
+      <c r="I15" s="130"/>
+      <c r="J15" s="129"/>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="129"/>
+      <c r="B16" s="129"/>
+      <c r="C16" s="129"/>
+      <c r="D16" s="129"/>
+      <c r="E16" s="129"/>
+      <c r="G16" s="129"/>
+      <c r="H16" s="129"/>
+      <c r="I16" s="130"/>
+      <c r="J16" s="129"/>
+    </row>
+    <row r="17" spans="1:10" ht="15" customHeight="1">
+      <c r="A17" s="129"/>
+      <c r="B17" s="129"/>
+      <c r="C17" s="129"/>
+      <c r="D17" s="129"/>
+      <c r="E17" s="129"/>
+      <c r="F17" s="140"/>
+      <c r="G17" s="8" t="s">
         <v>1256</v>
       </c>
-      <c r="H14" s="132"/>
-      <c r="I14" s="133"/>
-      <c r="J14" s="132"/>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" s="132"/>
-      <c r="B15" s="132"/>
-      <c r="C15" s="132"/>
-      <c r="D15" s="132"/>
-      <c r="E15" s="132"/>
-      <c r="F15" s="133"/>
-      <c r="G15" s="132" t="s">
+      <c r="H17" s="125" t="s">
+        <v>1257</v>
+      </c>
+      <c r="I17" s="130"/>
+      <c r="J17" s="129"/>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="129"/>
+      <c r="B18" s="129"/>
+      <c r="C18" s="129"/>
+      <c r="D18" s="129"/>
+      <c r="E18" s="129"/>
+      <c r="F18" s="209" t="s">
+        <v>1239</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>1236</v>
+      </c>
+      <c r="H18" s="125" t="s">
+        <v>1251</v>
+      </c>
+      <c r="I18" s="130"/>
+      <c r="J18" s="129"/>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="F19" s="209"/>
+      <c r="G19" s="149" t="s">
         <v>1235</v>
       </c>
-      <c r="H15" s="132" t="s">
-        <v>1236</v>
-      </c>
-      <c r="I15" s="133"/>
-      <c r="J15" s="132"/>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" s="132"/>
-      <c r="B16" s="132"/>
-      <c r="C16" s="132"/>
-      <c r="D16" s="132"/>
-      <c r="E16" s="132"/>
-      <c r="G16" s="132"/>
-      <c r="H16" s="132"/>
-      <c r="I16" s="133"/>
-      <c r="J16" s="132"/>
-    </row>
-    <row r="17" spans="1:10" ht="15" customHeight="1">
-      <c r="A17" s="132"/>
-      <c r="B17" s="132"/>
-      <c r="C17" s="132"/>
-      <c r="D17" s="132"/>
-      <c r="E17" s="132"/>
-      <c r="F17" s="143"/>
-      <c r="G17" s="8" t="s">
-        <v>1258</v>
-      </c>
-      <c r="H17" s="128" t="s">
-        <v>1259</v>
-      </c>
-      <c r="I17" s="133"/>
-      <c r="J17" s="132"/>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="132"/>
-      <c r="B18" s="132"/>
-      <c r="C18" s="132"/>
-      <c r="D18" s="132"/>
-      <c r="E18" s="132"/>
-      <c r="F18" s="214" t="s">
-        <v>1241</v>
-      </c>
-      <c r="G18" s="8" t="s">
+      <c r="H19" s="150" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="F20" s="209"/>
+      <c r="G20" s="8" t="s">
+        <v>1237</v>
+      </c>
+      <c r="H20" s="125" t="s">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="F21" s="209"/>
+      <c r="G21" s="8" t="s">
         <v>1238</v>
       </c>
-      <c r="H18" s="128" t="s">
+      <c r="H21" s="144" t="s">
         <v>1253</v>
       </c>
-      <c r="I18" s="133"/>
-      <c r="J18" s="132"/>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="F19" s="214"/>
-      <c r="G19" s="152" t="s">
-        <v>1237</v>
-      </c>
-      <c r="H19" s="153" t="s">
-        <v>1254</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="F20" s="214"/>
-      <c r="G20" s="8" t="s">
-        <v>1239</v>
-      </c>
-      <c r="H20" s="128" t="s">
-        <v>1253</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="F21" s="214"/>
-      <c r="G21" s="8" t="s">
-        <v>1240</v>
-      </c>
-      <c r="H21" s="147" t="s">
-        <v>1255</v>
-      </c>
     </row>
     <row r="22" spans="1:10">
-      <c r="G22" s="144"/>
+      <c r="G22" s="141"/>
     </row>
     <row r="23" spans="1:10">
-      <c r="F23" s="141" t="s">
-        <v>1252</v>
+      <c r="F23" s="138" t="s">
+        <v>1250</v>
       </c>
       <c r="G23" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="H23" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="24" spans="1:10">
-      <c r="F24" s="141" t="s">
-        <v>1208</v>
+      <c r="F24" s="138" t="s">
+        <v>1206</v>
       </c>
       <c r="G24" s="81">
         <v>1</v>
       </c>
       <c r="H24" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="25" spans="1:10">
-      <c r="F25" s="141" t="s">
-        <v>1208</v>
+      <c r="F25" s="138" t="s">
+        <v>1206</v>
       </c>
       <c r="G25" s="81">
         <v>8</v>
       </c>
       <c r="H25" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="26" spans="1:10">
-      <c r="F26" s="141" t="s">
-        <v>1199</v>
+      <c r="F26" s="138" t="s">
+        <v>1197</v>
       </c>
       <c r="G26" s="81">
         <v>1</v>
       </c>
       <c r="H26" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="27" spans="1:10">
-      <c r="F27" s="141" t="s">
-        <v>1199</v>
+      <c r="F27" s="138" t="s">
+        <v>1197</v>
       </c>
       <c r="G27" s="81">
         <v>4</v>
       </c>
       <c r="H27" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="28" spans="1:10">
-      <c r="F28" s="141" t="s">
-        <v>1199</v>
+      <c r="F28" s="138" t="s">
+        <v>1197</v>
       </c>
       <c r="G28" s="81">
         <v>8</v>
       </c>
       <c r="H28" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="29" spans="1:10">
-      <c r="F29" s="141" t="s">
-        <v>1200</v>
+      <c r="F29" s="138" t="s">
+        <v>1198</v>
       </c>
       <c r="G29" s="81">
         <v>1</v>
       </c>
       <c r="H29" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="30" spans="1:10">
-      <c r="F30" s="141" t="s">
-        <v>1200</v>
+      <c r="F30" s="138" t="s">
+        <v>1198</v>
       </c>
       <c r="G30" s="81">
         <v>4</v>
       </c>
       <c r="H30" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="31" spans="1:10">
-      <c r="F31" s="141" t="s">
-        <v>1200</v>
+      <c r="F31" s="138" t="s">
+        <v>1198</v>
       </c>
       <c r="G31" s="81">
         <v>8</v>
       </c>
       <c r="H31" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="32" spans="1:10">
-      <c r="F32" s="141" t="s">
-        <v>1202</v>
+      <c r="F32" s="138" t="s">
+        <v>1200</v>
       </c>
       <c r="G32" s="81">
         <v>1</v>
       </c>
       <c r="H32" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="33" spans="6:8">
-      <c r="F33" s="141" t="s">
-        <v>1202</v>
+      <c r="F33" s="138" t="s">
+        <v>1200</v>
       </c>
       <c r="G33" s="81">
         <v>8</v>
       </c>
       <c r="H33" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
     </row>
   </sheetData>
@@ -20522,7 +20549,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -20620,14 +20647,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="126" t="s">
+      <c r="A1" s="123" t="s">
+        <v>971</v>
+      </c>
+      <c r="B1" s="124" t="s">
+        <v>972</v>
+      </c>
+      <c r="C1" s="124" t="s">
         <v>973</v>
-      </c>
-      <c r="B1" s="127" t="s">
-        <v>974</v>
-      </c>
-      <c r="C1" s="127" t="s">
-        <v>975</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -20635,10 +20662,10 @@
         <v>758</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -20646,10 +20673,10 @@
         <v>758</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -20657,10 +20684,10 @@
         <v>758</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -20668,10 +20695,10 @@
         <v>758</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -20679,10 +20706,10 @@
         <v>758</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -20690,10 +20717,10 @@
         <v>758</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -20701,10 +20728,10 @@
         <v>758</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -20712,10 +20739,10 @@
         <v>758</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -20723,10 +20750,10 @@
         <v>758</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -20734,10 +20761,10 @@
         <v>758</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -20745,10 +20772,10 @@
         <v>758</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -20756,10 +20783,10 @@
         <v>758</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -20767,10 +20794,10 @@
         <v>758</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -20778,10 +20805,10 @@
         <v>758</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -20789,10 +20816,10 @@
         <v>758</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -20800,10 +20827,10 @@
         <v>758</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -20811,10 +20838,10 @@
         <v>758</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -20822,10 +20849,10 @@
         <v>758</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -20833,10 +20860,10 @@
         <v>758</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -20844,10 +20871,10 @@
         <v>758</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -20855,10 +20882,10 @@
         <v>758</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -20866,10 +20893,10 @@
         <v>758</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -20877,10 +20904,10 @@
         <v>758</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -20888,10 +20915,10 @@
         <v>758</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -20899,10 +20926,10 @@
         <v>758</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -20910,10 +20937,10 @@
         <v>758</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -20921,10 +20948,10 @@
         <v>758</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -20932,10 +20959,10 @@
         <v>758</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -20943,10 +20970,10 @@
         <v>758</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -20954,10 +20981,10 @@
         <v>758</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -20965,10 +20992,10 @@
         <v>758</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -20976,10 +21003,10 @@
         <v>758</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -20987,10 +21014,10 @@
         <v>758</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -20998,10 +21025,10 @@
         <v>758</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -21009,10 +21036,10 @@
         <v>758</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -21020,10 +21047,10 @@
         <v>758</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -21031,10 +21058,10 @@
         <v>758</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -21042,10 +21069,10 @@
         <v>758</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -21053,10 +21080,10 @@
         <v>758</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -21064,10 +21091,10 @@
         <v>758</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -21075,713 +21102,713 @@
         <v>758</v>
       </c>
       <c r="B42" s="19" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C42" s="19" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="125" t="s">
+        <v>385</v>
+      </c>
+      <c r="B43" s="125" t="s">
         <v>1051</v>
       </c>
-      <c r="C42" s="19" t="s">
+      <c r="C43" s="125" t="s">
         <v>1052</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="128" t="s">
+    <row r="44" spans="1:3">
+      <c r="A44" s="125" t="s">
         <v>385</v>
       </c>
-      <c r="B43" s="128" t="s">
+      <c r="B44" s="125" t="s">
         <v>1053</v>
       </c>
-      <c r="C43" s="128" t="s">
+      <c r="C44" s="125" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="125" t="s">
+        <v>385</v>
+      </c>
+      <c r="B45" s="125" t="s">
         <v>1054</v>
       </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="128" t="s">
+      <c r="C45" s="125" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="125" t="s">
         <v>385</v>
       </c>
-      <c r="B44" s="128" t="s">
-        <v>1055</v>
-      </c>
-      <c r="C44" s="128" t="s">
-        <v>977</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="128" t="s">
+      <c r="B46" s="125" t="s">
+        <v>619</v>
+      </c>
+      <c r="C46" s="125" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="125" t="s">
         <v>385</v>
       </c>
-      <c r="B45" s="128" t="s">
-        <v>1056</v>
-      </c>
-      <c r="C45" s="128" t="s">
+      <c r="B47" s="125" t="s">
+        <v>617</v>
+      </c>
+      <c r="C47" s="125" t="s">
         <v>1057</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="128" t="s">
+    <row r="48" spans="1:3">
+      <c r="A48" s="125" t="s">
         <v>385</v>
       </c>
-      <c r="B46" s="128" t="s">
-        <v>619</v>
-      </c>
-      <c r="C46" s="128" t="s">
+      <c r="B48" s="125" t="s">
         <v>1058</v>
       </c>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="128" t="s">
+      <c r="C48" s="125" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="125" t="s">
         <v>385</v>
       </c>
-      <c r="B47" s="128" t="s">
-        <v>617</v>
-      </c>
-      <c r="C47" s="128" t="s">
-        <v>1059</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="128" t="s">
+      <c r="B49" s="125" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C49" s="125" t="s">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="125" t="s">
         <v>385</v>
       </c>
-      <c r="B48" s="128" t="s">
-        <v>1060</v>
-      </c>
-      <c r="C48" s="128" t="s">
-        <v>1061</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="128" t="s">
+      <c r="B50" s="125" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C50" s="125" t="s">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="125" t="s">
         <v>385</v>
       </c>
-      <c r="B49" s="128" t="s">
-        <v>1062</v>
-      </c>
-      <c r="C49" s="128" t="s">
-        <v>1063</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="128" t="s">
+      <c r="B51" s="125" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C51" s="125" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="125" t="s">
         <v>385</v>
       </c>
-      <c r="B50" s="128" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C50" s="128" t="s">
-        <v>1065</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="128" t="s">
+      <c r="B52" s="125" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C52" s="125" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" s="125" t="s">
         <v>385</v>
       </c>
-      <c r="B51" s="128" t="s">
-        <v>1066</v>
-      </c>
-      <c r="C51" s="128" t="s">
-        <v>1067</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="128" t="s">
+      <c r="B53" s="125" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C53" s="19" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" s="125" t="s">
         <v>385</v>
       </c>
-      <c r="B52" s="128" t="s">
-        <v>1068</v>
-      </c>
-      <c r="C52" s="128" t="s">
-        <v>1069</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="128" t="s">
+      <c r="B54" s="125" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C54" s="19" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" s="125" t="s">
         <v>385</v>
       </c>
-      <c r="B53" s="128" t="s">
-        <v>1070</v>
-      </c>
-      <c r="C53" s="19" t="s">
-        <v>1071</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="128" t="s">
+      <c r="B55" s="19" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C55" s="19" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" s="125" t="s">
         <v>385</v>
       </c>
-      <c r="B54" s="128" t="s">
-        <v>1072</v>
-      </c>
-      <c r="C54" s="19" t="s">
-        <v>1073</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
-      <c r="A55" s="128" t="s">
+      <c r="B56" s="19" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C56" s="19" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" s="125" t="s">
         <v>385</v>
       </c>
-      <c r="B55" s="19" t="s">
-        <v>1074</v>
-      </c>
-      <c r="C55" s="19" t="s">
-        <v>1075</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="128" t="s">
+      <c r="B57" s="19" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C57" s="19" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="30">
+      <c r="A58" s="125" t="s">
         <v>385</v>
       </c>
-      <c r="B56" s="19" t="s">
-        <v>1076</v>
-      </c>
-      <c r="C56" s="19" t="s">
-        <v>1077</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="128" t="s">
+      <c r="B58" s="19" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C58" s="23" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" s="125" t="s">
         <v>385</v>
       </c>
-      <c r="B57" s="19" t="s">
-        <v>1078</v>
-      </c>
-      <c r="C57" s="19" t="s">
-        <v>1079</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" ht="30">
-      <c r="A58" s="128" t="s">
+      <c r="B59" s="19" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C59" s="19" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" s="125" t="s">
         <v>385</v>
       </c>
-      <c r="B58" s="19" t="s">
-        <v>1080</v>
-      </c>
-      <c r="C58" s="23" t="s">
-        <v>1081</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3">
-      <c r="A59" s="128" t="s">
-        <v>385</v>
-      </c>
-      <c r="B59" s="19" t="s">
+      <c r="B60" s="19" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C60" s="19" t="s">
         <v>1082</v>
-      </c>
-      <c r="C59" s="19" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3">
-      <c r="A60" s="128" t="s">
-        <v>385</v>
-      </c>
-      <c r="B60" s="19" t="s">
-        <v>1056</v>
-      </c>
-      <c r="C60" s="19" t="s">
-        <v>1084</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="16.5">
       <c r="A61" s="19" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B61" s="126" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C61" s="126" t="s">
         <v>1085</v>
-      </c>
-      <c r="B61" s="129" t="s">
-        <v>1086</v>
-      </c>
-      <c r="C61" s="129" t="s">
-        <v>1087</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="16.5">
       <c r="A62" s="19" t="s">
-        <v>1085</v>
-      </c>
-      <c r="B62" s="130" t="s">
-        <v>1088</v>
-      </c>
-      <c r="C62" s="130" t="s">
-        <v>1089</v>
+        <v>1083</v>
+      </c>
+      <c r="B62" s="127" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C62" s="127" t="s">
+        <v>1087</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="16.5">
       <c r="A63" s="19" t="s">
-        <v>1085</v>
-      </c>
-      <c r="B63" s="130" t="s">
-        <v>1090</v>
-      </c>
-      <c r="C63" s="130" t="s">
-        <v>1091</v>
+        <v>1083</v>
+      </c>
+      <c r="B63" s="127" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C63" s="127" t="s">
+        <v>1089</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="16.5">
       <c r="A64" s="19" t="s">
-        <v>1085</v>
-      </c>
-      <c r="B64" s="130" t="s">
-        <v>1092</v>
-      </c>
-      <c r="C64" s="130" t="s">
-        <v>1093</v>
+        <v>1083</v>
+      </c>
+      <c r="B64" s="127" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C64" s="127" t="s">
+        <v>1091</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="16.5">
       <c r="A65" s="19" t="s">
-        <v>1085</v>
-      </c>
-      <c r="B65" s="130" t="s">
-        <v>1094</v>
-      </c>
-      <c r="C65" s="130" t="s">
-        <v>1095</v>
+        <v>1083</v>
+      </c>
+      <c r="B65" s="127" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C65" s="127" t="s">
+        <v>1093</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="16.5">
       <c r="A66" s="19" t="s">
-        <v>1085</v>
-      </c>
-      <c r="B66" s="130" t="s">
-        <v>1096</v>
-      </c>
-      <c r="C66" s="130" t="s">
-        <v>1097</v>
+        <v>1083</v>
+      </c>
+      <c r="B66" s="127" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C66" s="127" t="s">
+        <v>1095</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="16.5">
       <c r="A67" s="19" t="s">
-        <v>1085</v>
-      </c>
-      <c r="B67" s="130" t="s">
-        <v>1098</v>
-      </c>
-      <c r="C67" s="130" t="s">
-        <v>1099</v>
+        <v>1083</v>
+      </c>
+      <c r="B67" s="127" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C67" s="127" t="s">
+        <v>1097</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="16.5">
       <c r="A68" s="19" t="s">
-        <v>1085</v>
-      </c>
-      <c r="B68" s="130" t="s">
-        <v>1100</v>
-      </c>
-      <c r="C68" s="130" t="s">
-        <v>1101</v>
+        <v>1083</v>
+      </c>
+      <c r="B68" s="127" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C68" s="127" t="s">
+        <v>1099</v>
       </c>
     </row>
     <row r="69" spans="1:3" ht="16.5">
       <c r="A69" s="19" t="s">
-        <v>1085</v>
-      </c>
-      <c r="B69" s="130" t="s">
-        <v>1102</v>
-      </c>
-      <c r="C69" s="130" t="s">
-        <v>1103</v>
+        <v>1083</v>
+      </c>
+      <c r="B69" s="127" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C69" s="127" t="s">
+        <v>1101</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="16.5">
       <c r="A70" s="19" t="s">
-        <v>1085</v>
-      </c>
-      <c r="B70" s="130" t="s">
-        <v>1104</v>
-      </c>
-      <c r="C70" s="130" t="s">
-        <v>1105</v>
+        <v>1083</v>
+      </c>
+      <c r="B70" s="127" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C70" s="127" t="s">
+        <v>1103</v>
       </c>
     </row>
     <row r="71" spans="1:3" ht="16.5">
       <c r="A71" s="19" t="s">
-        <v>1085</v>
-      </c>
-      <c r="B71" s="130" t="s">
-        <v>1106</v>
-      </c>
-      <c r="C71" s="130" t="s">
-        <v>1107</v>
+        <v>1083</v>
+      </c>
+      <c r="B71" s="127" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C71" s="127" t="s">
+        <v>1105</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="16.5">
       <c r="A72" s="19" t="s">
-        <v>1085</v>
-      </c>
-      <c r="B72" s="130" t="s">
-        <v>1108</v>
-      </c>
-      <c r="C72" s="130" t="s">
-        <v>1109</v>
+        <v>1083</v>
+      </c>
+      <c r="B72" s="127" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C72" s="127" t="s">
+        <v>1107</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="16.5">
       <c r="A73" s="19" t="s">
-        <v>1085</v>
-      </c>
-      <c r="B73" s="130" t="s">
-        <v>1110</v>
-      </c>
-      <c r="C73" s="130" t="s">
-        <v>1111</v>
+        <v>1083</v>
+      </c>
+      <c r="B73" s="127" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C73" s="127" t="s">
+        <v>1109</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="16.5">
       <c r="A74" s="19" t="s">
-        <v>1085</v>
-      </c>
-      <c r="B74" s="130" t="s">
-        <v>1112</v>
-      </c>
-      <c r="C74" s="130" t="s">
-        <v>1113</v>
+        <v>1083</v>
+      </c>
+      <c r="B74" s="127" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C74" s="127" t="s">
+        <v>1111</v>
       </c>
     </row>
     <row r="75" spans="1:3" ht="16.5">
       <c r="A75" s="19" t="s">
-        <v>1085</v>
-      </c>
-      <c r="B75" s="130" t="s">
-        <v>1114</v>
-      </c>
-      <c r="C75" s="130" t="s">
-        <v>1115</v>
+        <v>1083</v>
+      </c>
+      <c r="B75" s="127" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C75" s="127" t="s">
+        <v>1113</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="16.5">
       <c r="A76" s="19" t="s">
-        <v>1085</v>
-      </c>
-      <c r="B76" s="130" t="s">
-        <v>1116</v>
-      </c>
-      <c r="C76" s="130" t="s">
-        <v>1117</v>
+        <v>1083</v>
+      </c>
+      <c r="B76" s="127" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C76" s="127" t="s">
+        <v>1115</v>
       </c>
     </row>
     <row r="77" spans="1:3" ht="16.5">
       <c r="A77" s="19" t="s">
-        <v>1085</v>
-      </c>
-      <c r="B77" s="130" t="s">
-        <v>1118</v>
-      </c>
-      <c r="C77" s="130" t="s">
-        <v>1119</v>
+        <v>1083</v>
+      </c>
+      <c r="B77" s="127" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C77" s="127" t="s">
+        <v>1117</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="16.5">
       <c r="A78" s="19" t="s">
-        <v>1085</v>
-      </c>
-      <c r="B78" s="130" t="s">
-        <v>1120</v>
-      </c>
-      <c r="C78" s="130" t="s">
-        <v>1121</v>
+        <v>1083</v>
+      </c>
+      <c r="B78" s="127" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C78" s="127" t="s">
+        <v>1119</v>
       </c>
     </row>
     <row r="79" spans="1:3" ht="16.5">
       <c r="A79" s="19" t="s">
-        <v>1085</v>
-      </c>
-      <c r="B79" s="130" t="s">
-        <v>1122</v>
-      </c>
-      <c r="C79" s="130" t="s">
-        <v>1123</v>
+        <v>1083</v>
+      </c>
+      <c r="B79" s="127" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C79" s="127" t="s">
+        <v>1121</v>
       </c>
     </row>
     <row r="80" spans="1:3" ht="16.5">
       <c r="A80" s="19" t="s">
-        <v>1085</v>
-      </c>
-      <c r="B80" s="130" t="s">
-        <v>1124</v>
-      </c>
-      <c r="C80" s="130" t="s">
-        <v>1125</v>
+        <v>1083</v>
+      </c>
+      <c r="B80" s="127" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C80" s="127" t="s">
+        <v>1123</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="16.5">
       <c r="A81" s="19" t="s">
-        <v>1085</v>
-      </c>
-      <c r="B81" s="130" t="s">
-        <v>1126</v>
-      </c>
-      <c r="C81" s="130" t="s">
-        <v>1127</v>
+        <v>1083</v>
+      </c>
+      <c r="B81" s="127" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C81" s="127" t="s">
+        <v>1125</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="16.5">
       <c r="A82" s="19" t="s">
-        <v>1085</v>
-      </c>
-      <c r="B82" s="130" t="s">
-        <v>1128</v>
-      </c>
-      <c r="C82" s="130" t="s">
-        <v>1129</v>
+        <v>1083</v>
+      </c>
+      <c r="B82" s="127" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C82" s="127" t="s">
+        <v>1127</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="16.5">
       <c r="A83" s="19" t="s">
-        <v>1085</v>
-      </c>
-      <c r="B83" s="130" t="s">
-        <v>1130</v>
-      </c>
-      <c r="C83" s="130" t="s">
-        <v>1131</v>
+        <v>1083</v>
+      </c>
+      <c r="B83" s="127" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C83" s="127" t="s">
+        <v>1129</v>
       </c>
     </row>
     <row r="84" spans="1:3" ht="16.5">
       <c r="A84" s="19" t="s">
-        <v>1132</v>
-      </c>
-      <c r="B84" s="130" t="s">
-        <v>1133</v>
-      </c>
-      <c r="C84" s="130" t="s">
-        <v>1107</v>
+        <v>1130</v>
+      </c>
+      <c r="B84" s="127" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C84" s="127" t="s">
+        <v>1105</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="16.5">
       <c r="A85" s="19" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B85" s="127" t="s">
         <v>1132</v>
       </c>
-      <c r="B85" s="130" t="s">
-        <v>1134</v>
-      </c>
-      <c r="C85" s="130" t="s">
-        <v>1135</v>
+      <c r="C85" s="127" t="s">
+        <v>1133</v>
       </c>
     </row>
     <row r="86" spans="1:3" ht="33">
       <c r="A86" s="19" t="s">
-        <v>1132</v>
-      </c>
-      <c r="B86" s="130" t="s">
-        <v>1136</v>
-      </c>
-      <c r="C86" s="130" t="s">
-        <v>1137</v>
+        <v>1130</v>
+      </c>
+      <c r="B86" s="127" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C86" s="127" t="s">
+        <v>1135</v>
       </c>
     </row>
     <row r="87" spans="1:3" ht="49.5">
       <c r="A87" s="19" t="s">
-        <v>1132</v>
-      </c>
-      <c r="B87" s="130" t="s">
-        <v>1138</v>
-      </c>
-      <c r="C87" s="130" t="s">
-        <v>1139</v>
+        <v>1130</v>
+      </c>
+      <c r="B87" s="127" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C87" s="127" t="s">
+        <v>1137</v>
       </c>
     </row>
     <row r="88" spans="1:3" ht="33">
       <c r="A88" s="19" t="s">
-        <v>1132</v>
-      </c>
-      <c r="B88" s="130" t="s">
-        <v>1140</v>
-      </c>
-      <c r="C88" s="130" t="s">
-        <v>1109</v>
+        <v>1130</v>
+      </c>
+      <c r="B88" s="127" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C88" s="127" t="s">
+        <v>1107</v>
       </c>
     </row>
     <row r="89" spans="1:3" ht="16.5">
       <c r="A89" s="19" t="s">
-        <v>1132</v>
-      </c>
-      <c r="B89" s="130" t="s">
-        <v>1141</v>
-      </c>
-      <c r="C89" s="130" t="s">
-        <v>1142</v>
+        <v>1130</v>
+      </c>
+      <c r="B89" s="127" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C89" s="127" t="s">
+        <v>1140</v>
       </c>
     </row>
     <row r="90" spans="1:3" ht="16.5">
       <c r="A90" s="19" t="s">
-        <v>1132</v>
-      </c>
-      <c r="B90" s="130" t="s">
-        <v>1143</v>
-      </c>
-      <c r="C90" s="130" t="s">
-        <v>1144</v>
+        <v>1130</v>
+      </c>
+      <c r="B90" s="127" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C90" s="127" t="s">
+        <v>1142</v>
       </c>
     </row>
     <row r="91" spans="1:3" ht="16.5">
       <c r="A91" s="19" t="s">
-        <v>1145</v>
-      </c>
-      <c r="B91" s="130" t="s">
-        <v>1146</v>
-      </c>
-      <c r="C91" s="130" t="s">
-        <v>1107</v>
+        <v>1143</v>
+      </c>
+      <c r="B91" s="127" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C91" s="127" t="s">
+        <v>1105</v>
       </c>
     </row>
     <row r="92" spans="1:3" ht="33">
       <c r="A92" s="19" t="s">
-        <v>1145</v>
-      </c>
-      <c r="B92" s="130" t="s">
-        <v>1136</v>
-      </c>
-      <c r="C92" s="130" t="s">
-        <v>1137</v>
+        <v>1143</v>
+      </c>
+      <c r="B92" s="127" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C92" s="127" t="s">
+        <v>1135</v>
       </c>
     </row>
     <row r="93" spans="1:3" ht="16.5">
       <c r="A93" s="19" t="s">
-        <v>1145</v>
-      </c>
-      <c r="B93" s="130" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B93" s="127" t="s">
         <v>313</v>
       </c>
-      <c r="C93" s="130" t="s">
-        <v>1087</v>
+      <c r="C93" s="127" t="s">
+        <v>1085</v>
       </c>
     </row>
     <row r="94" spans="1:3" ht="16.5">
       <c r="A94" s="19" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B94" s="127" t="s">
+        <v>810</v>
+      </c>
+      <c r="C94" s="127" t="s">
         <v>1145</v>
-      </c>
-      <c r="B94" s="130" t="s">
-        <v>811</v>
-      </c>
-      <c r="C94" s="130" t="s">
-        <v>1147</v>
       </c>
     </row>
     <row r="95" spans="1:3" ht="16.5">
       <c r="A95" s="19" t="s">
-        <v>1145</v>
-      </c>
-      <c r="B95" s="130" t="s">
-        <v>1148</v>
-      </c>
-      <c r="C95" s="130" t="s">
-        <v>1091</v>
+        <v>1143</v>
+      </c>
+      <c r="B95" s="127" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C95" s="127" t="s">
+        <v>1089</v>
       </c>
     </row>
     <row r="96" spans="1:3" ht="16.5">
       <c r="A96" s="19" t="s">
-        <v>1145</v>
-      </c>
-      <c r="B96" s="130" t="s">
-        <v>1149</v>
-      </c>
-      <c r="C96" s="130" t="s">
-        <v>1093</v>
+        <v>1143</v>
+      </c>
+      <c r="B96" s="127" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C96" s="127" t="s">
+        <v>1091</v>
       </c>
     </row>
     <row r="97" spans="1:3" ht="16.5">
       <c r="A97" s="19" t="s">
-        <v>1145</v>
-      </c>
-      <c r="B97" s="130" t="s">
-        <v>1150</v>
-      </c>
-      <c r="C97" s="130" t="s">
-        <v>1095</v>
+        <v>1143</v>
+      </c>
+      <c r="B97" s="127" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C97" s="127" t="s">
+        <v>1093</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="16.5">
       <c r="A98" s="19" t="s">
-        <v>1145</v>
-      </c>
-      <c r="B98" s="130" t="s">
-        <v>1151</v>
-      </c>
-      <c r="C98" s="130" t="s">
-        <v>1129</v>
+        <v>1143</v>
+      </c>
+      <c r="B98" s="127" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C98" s="127" t="s">
+        <v>1127</v>
       </c>
     </row>
     <row r="99" spans="1:3" ht="16.5">
       <c r="A99" s="19" t="s">
-        <v>1145</v>
-      </c>
-      <c r="B99" s="130" t="s">
-        <v>1152</v>
-      </c>
-      <c r="C99" s="130" t="s">
-        <v>1153</v>
+        <v>1143</v>
+      </c>
+      <c r="B99" s="127" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C99" s="127" t="s">
+        <v>1151</v>
       </c>
     </row>
     <row r="100" spans="1:3" ht="16.5">
       <c r="A100" s="19" t="s">
-        <v>1145</v>
-      </c>
-      <c r="B100" s="130" t="s">
-        <v>1154</v>
-      </c>
-      <c r="C100" s="130" t="s">
-        <v>1125</v>
+        <v>1143</v>
+      </c>
+      <c r="B100" s="127" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C100" s="127" t="s">
+        <v>1123</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="16.5">
       <c r="A101" s="19" t="s">
-        <v>1145</v>
-      </c>
-      <c r="B101" s="130" t="s">
-        <v>1141</v>
-      </c>
-      <c r="C101" s="130" t="s">
-        <v>1155</v>
+        <v>1143</v>
+      </c>
+      <c r="B101" s="127" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C101" s="127" t="s">
+        <v>1153</v>
       </c>
     </row>
     <row r="102" spans="1:3" ht="16.5">
       <c r="A102" s="19" t="s">
-        <v>1145</v>
-      </c>
-      <c r="B102" s="130" t="s">
-        <v>1156</v>
-      </c>
-      <c r="C102" s="130" t="s">
-        <v>1157</v>
+        <v>1143</v>
+      </c>
+      <c r="B102" s="127" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C102" s="127" t="s">
+        <v>1155</v>
       </c>
     </row>
     <row r="103" spans="1:3" ht="16.5">
       <c r="A103" s="19" t="s">
-        <v>1145</v>
-      </c>
-      <c r="B103" s="130" t="s">
-        <v>1158</v>
-      </c>
-      <c r="C103" s="130" t="s">
-        <v>1159</v>
+        <v>1143</v>
+      </c>
+      <c r="B103" s="127" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C103" s="127" t="s">
+        <v>1157</v>
       </c>
     </row>
     <row r="104" spans="1:3" ht="16.5">
       <c r="A104" s="19" t="s">
-        <v>1145</v>
-      </c>
-      <c r="B104" s="130" t="s">
-        <v>1160</v>
-      </c>
-      <c r="C104" s="130" t="s">
-        <v>1099</v>
+        <v>1143</v>
+      </c>
+      <c r="B104" s="127" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C104" s="127" t="s">
+        <v>1097</v>
       </c>
     </row>
     <row r="105" spans="1:3" ht="16.5">
       <c r="A105" s="19" t="s">
-        <v>1145</v>
-      </c>
-      <c r="B105" s="130" t="s">
-        <v>1161</v>
-      </c>
-      <c r="C105" s="130" t="s">
-        <v>1162</v>
+        <v>1143</v>
+      </c>
+      <c r="B105" s="127" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C105" s="127" t="s">
+        <v>1160</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107" s="7" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" s="7" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -21793,13 +21820,13 @@
       <c r="A112" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="B112" s="131"/>
+      <c r="B112" s="128"/>
     </row>
     <row r="113" spans="1:2" ht="16.5">
       <c r="A113" s="7" t="s">
-        <v>1165</v>
-      </c>
-      <c r="B113" s="131"/>
+        <v>1163</v>
+      </c>
+      <c r="B113" s="128"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -21843,7 +21870,7 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="208" t="s">
+      <c r="A2" s="203" t="s">
         <v>379</v>
       </c>
       <c r="B2" s="57" t="s">
@@ -21857,7 +21884,7 @@
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="208"/>
+      <c r="A3" s="203"/>
       <c r="B3" s="20" t="s">
         <v>262</v>
       </c>
@@ -21869,7 +21896,7 @@
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="208"/>
+      <c r="A4" s="203"/>
       <c r="B4" s="20" t="s">
         <v>385</v>
       </c>
@@ -21881,7 +21908,7 @@
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="208"/>
+      <c r="A5" s="203"/>
       <c r="B5" s="57" t="s">
         <v>544</v>
       </c>
@@ -21893,7 +21920,7 @@
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="208"/>
+      <c r="A6" s="203"/>
       <c r="B6" s="20" t="s">
         <v>388</v>
       </c>
@@ -21905,7 +21932,7 @@
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="208"/>
+      <c r="A7" s="203"/>
       <c r="B7" s="20" t="s">
         <v>390</v>
       </c>
@@ -22030,7 +22057,7 @@
       <c r="B2" s="53"/>
       <c r="C2" s="53"/>
       <c r="M2" s="5" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -22040,7 +22067,7 @@
       <c r="B3" s="53"/>
       <c r="C3" s="53"/>
       <c r="M3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -22050,7 +22077,7 @@
       <c r="B4" s="53"/>
       <c r="C4" s="53"/>
       <c r="M4" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -23480,324 +23507,324 @@
   <sheetData>
     <row r="4" spans="11:18">
       <c r="M4" t="s">
+        <v>873</v>
+      </c>
+      <c r="N4" t="s">
         <v>874</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>875</v>
-      </c>
-      <c r="O4" t="s">
-        <v>876</v>
       </c>
     </row>
     <row r="5" spans="11:18">
       <c r="M5" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="N5" t="s">
+        <v>877</v>
+      </c>
+      <c r="P5" t="s">
         <v>878</v>
-      </c>
-      <c r="P5" t="s">
-        <v>879</v>
       </c>
     </row>
     <row r="6" spans="11:18">
       <c r="M6" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="N6" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="O6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="P6" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="7" spans="11:18">
       <c r="O7" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="8" spans="11:18" ht="35.25" customHeight="1">
       <c r="N8" s="107"/>
       <c r="O8" s="107" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="9" spans="11:18">
-      <c r="K9" s="151" t="s">
-        <v>1269</v>
+      <c r="K9" s="148" t="s">
+        <v>1267</v>
       </c>
     </row>
     <row r="10" spans="11:18">
-      <c r="K10" s="151">
+      <c r="K10" s="148">
         <v>0</v>
       </c>
       <c r="L10" s="110" t="s">
+        <v>908</v>
+      </c>
+      <c r="M10" s="110" t="s">
         <v>909</v>
       </c>
-      <c r="M10" s="110" t="s">
-        <v>910</v>
-      </c>
       <c r="O10" s="5" t="s">
+        <v>1264</v>
+      </c>
+      <c r="P10" s="5" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="11" spans="11:18" ht="15.75" thickBot="1">
+      <c r="K11" s="148"/>
+      <c r="L11" s="146"/>
+      <c r="M11" s="146"/>
+      <c r="N11" s="146"/>
+      <c r="O11" s="146"/>
+      <c r="P11" s="146"/>
+      <c r="Q11" s="146"/>
+      <c r="R11" s="146"/>
+    </row>
+    <row r="12" spans="11:18">
+      <c r="K12" s="148">
+        <v>1</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="13" spans="11:18">
+      <c r="K13" s="148"/>
+      <c r="M13" t="s">
+        <v>880</v>
+      </c>
+      <c r="N13" t="s">
+        <v>881</v>
+      </c>
+      <c r="O13" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="14" spans="11:18">
+      <c r="K14" s="148"/>
+      <c r="L14" s="6" t="s">
+        <v>887</v>
+      </c>
+      <c r="M14" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="15" spans="11:18">
+      <c r="K15" s="148"/>
+      <c r="M15" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="16" spans="11:18">
+      <c r="K16" s="148"/>
+      <c r="O16" s="5" t="s">
         <v>1266</v>
       </c>
-      <c r="P10" s="5" t="s">
-        <v>1267</v>
-      </c>
-    </row>
-    <row r="11" spans="11:18" ht="15.75" thickBot="1">
-      <c r="K11" s="151"/>
-      <c r="L11" s="149"/>
-      <c r="M11" s="149"/>
-      <c r="N11" s="149"/>
-      <c r="O11" s="149"/>
-      <c r="P11" s="149"/>
-      <c r="Q11" s="149"/>
-      <c r="R11" s="149"/>
-    </row>
-    <row r="12" spans="11:18">
-      <c r="K12" s="151">
-        <v>1</v>
-      </c>
-      <c r="L12" s="5" t="s">
+      <c r="P16" s="5" t="s">
         <v>890</v>
       </c>
     </row>
-    <row r="13" spans="11:18">
-      <c r="K13" s="151"/>
-      <c r="M13" t="s">
-        <v>881</v>
-      </c>
-      <c r="N13" t="s">
+    <row r="17" spans="7:24">
+      <c r="K17" s="148"/>
+    </row>
+    <row r="18" spans="7:24">
+      <c r="K18" s="148"/>
+    </row>
+    <row r="19" spans="7:24">
+      <c r="K19" s="148"/>
+    </row>
+    <row r="20" spans="7:24">
+      <c r="K20" s="148"/>
+      <c r="L20" s="6" t="s">
         <v>882</v>
       </c>
-      <c r="O13" t="s">
+      <c r="M20" t="s">
         <v>883</v>
       </c>
-    </row>
-    <row r="14" spans="11:18">
-      <c r="K14" s="151"/>
-      <c r="L14" s="6" t="s">
+      <c r="N20" t="s">
+        <v>884</v>
+      </c>
+      <c r="O20" t="s">
+        <v>885</v>
+      </c>
+      <c r="P20" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="21" spans="7:24">
+      <c r="K21" s="148"/>
+      <c r="M21" t="s">
         <v>888</v>
       </c>
-      <c r="M14" t="s">
-        <v>884</v>
-      </c>
-    </row>
-    <row r="15" spans="11:18">
-      <c r="K15" s="151"/>
-      <c r="M15" t="s">
-        <v>885</v>
-      </c>
-    </row>
-    <row r="16" spans="11:18">
-      <c r="K16" s="151"/>
-      <c r="O16" s="5" t="s">
+      <c r="V21" s="94" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="22" spans="7:24">
+      <c r="K22" s="148"/>
+      <c r="V22" s="164" t="s">
+        <v>832</v>
+      </c>
+      <c r="W22" s="9" t="s">
+        <v>814</v>
+      </c>
+      <c r="X22" s="92" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="23" spans="7:24" ht="15.75" thickBot="1">
+      <c r="K23" s="148"/>
+      <c r="L23" s="146"/>
+      <c r="M23" s="146"/>
+      <c r="N23" s="146"/>
+      <c r="O23" s="147" t="s">
+        <v>1266</v>
+      </c>
+      <c r="P23" s="147" t="s">
         <v>1268</v>
       </c>
-      <c r="P16" s="5" t="s">
+      <c r="Q23" s="146"/>
+      <c r="R23" s="146"/>
+      <c r="V23" s="165"/>
+      <c r="W23" s="9" t="s">
+        <v>815</v>
+      </c>
+      <c r="X23" s="92" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="24" spans="7:24">
+      <c r="K24" s="148"/>
+      <c r="V24" s="165"/>
+      <c r="W24" s="9" t="s">
+        <v>816</v>
+      </c>
+      <c r="X24" s="92" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="25" spans="7:24">
+      <c r="K25" s="148">
+        <v>2</v>
+      </c>
+      <c r="L25" s="5" t="s">
         <v>891</v>
       </c>
-    </row>
-    <row r="17" spans="7:24">
-      <c r="K17" s="151"/>
-    </row>
-    <row r="18" spans="7:24">
-      <c r="K18" s="151"/>
-    </row>
-    <row r="19" spans="7:24">
-      <c r="K19" s="151"/>
-    </row>
-    <row r="20" spans="7:24">
-      <c r="K20" s="151"/>
-      <c r="L20" s="6" t="s">
-        <v>883</v>
-      </c>
-      <c r="M20" t="s">
-        <v>884</v>
-      </c>
-      <c r="N20" t="s">
-        <v>885</v>
-      </c>
-      <c r="O20" t="s">
-        <v>886</v>
-      </c>
-      <c r="P20" t="s">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="21" spans="7:24">
-      <c r="K21" s="151"/>
-      <c r="M21" t="s">
-        <v>889</v>
-      </c>
-      <c r="V21" s="94" t="s">
+      <c r="V25" s="165"/>
+      <c r="W25" s="9" t="s">
+        <v>817</v>
+      </c>
+      <c r="X25" s="92" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="26" spans="7:24">
+      <c r="K26" s="148"/>
+      <c r="M26" s="111" t="s">
+        <v>893</v>
+      </c>
+      <c r="N26" t="s">
+        <v>895</v>
+      </c>
+      <c r="O26" t="s">
+        <v>897</v>
+      </c>
+      <c r="V26" s="165"/>
+      <c r="W26" s="9" t="s">
+        <v>824</v>
+      </c>
+      <c r="X26" s="92"/>
+    </row>
+    <row r="27" spans="7:24">
+      <c r="K27" s="148"/>
+      <c r="M27" t="s">
+        <v>894</v>
+      </c>
+      <c r="N27" t="s">
+        <v>896</v>
+      </c>
+      <c r="V27" s="165"/>
+      <c r="W27" s="9" t="s">
+        <v>825</v>
+      </c>
+      <c r="X27" s="92"/>
+    </row>
+    <row r="28" spans="7:24">
+      <c r="K28" s="148"/>
+      <c r="N28" t="s">
+        <v>898</v>
+      </c>
+      <c r="V28" s="165"/>
+      <c r="W28" s="9" t="s">
+        <v>826</v>
+      </c>
+      <c r="X28" s="92" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="29" spans="7:24">
+      <c r="K29" s="148"/>
+      <c r="N29" t="s">
+        <v>899</v>
+      </c>
+      <c r="V29" s="166"/>
+      <c r="W29" s="9" t="s">
+        <v>827</v>
+      </c>
+      <c r="X29" s="92" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="30" spans="7:24">
+      <c r="K30" s="148"/>
+      <c r="M30" t="s">
+        <v>900</v>
+      </c>
+      <c r="N30" t="s">
+        <v>852</v>
+      </c>
+      <c r="V30" s="161" t="s">
         <v>831</v>
       </c>
-    </row>
-    <row r="22" spans="7:24">
-      <c r="K22" s="151"/>
-      <c r="V22" s="167" t="s">
-        <v>833</v>
-      </c>
-      <c r="W22" s="9" t="s">
-        <v>815</v>
-      </c>
-      <c r="X22" s="92" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="23" spans="7:24" ht="15.75" thickBot="1">
-      <c r="K23" s="151"/>
-      <c r="L23" s="149"/>
-      <c r="M23" s="149"/>
-      <c r="N23" s="149"/>
-      <c r="O23" s="150" t="s">
-        <v>1268</v>
-      </c>
-      <c r="P23" s="150" t="s">
-        <v>1270</v>
-      </c>
-      <c r="Q23" s="149"/>
-      <c r="R23" s="149"/>
-      <c r="V23" s="168"/>
-      <c r="W23" s="9" t="s">
-        <v>816</v>
-      </c>
-      <c r="X23" s="92" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="24" spans="7:24">
-      <c r="K24" s="151"/>
-      <c r="V24" s="168"/>
-      <c r="W24" s="9" t="s">
-        <v>817</v>
-      </c>
-      <c r="X24" s="92" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="25" spans="7:24">
-      <c r="K25" s="151">
-        <v>2</v>
-      </c>
-      <c r="L25" s="5" t="s">
-        <v>892</v>
-      </c>
-      <c r="V25" s="168"/>
-      <c r="W25" s="9" t="s">
-        <v>818</v>
-      </c>
-      <c r="X25" s="92" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="26" spans="7:24">
-      <c r="K26" s="151"/>
-      <c r="M26" s="111" t="s">
-        <v>894</v>
-      </c>
-      <c r="N26" t="s">
-        <v>896</v>
-      </c>
-      <c r="O26" t="s">
-        <v>898</v>
-      </c>
-      <c r="V26" s="168"/>
-      <c r="W26" s="9" t="s">
-        <v>825</v>
-      </c>
-      <c r="X26" s="92"/>
-    </row>
-    <row r="27" spans="7:24">
-      <c r="K27" s="151"/>
-      <c r="M27" t="s">
-        <v>895</v>
-      </c>
-      <c r="N27" t="s">
-        <v>897</v>
-      </c>
-      <c r="V27" s="168"/>
-      <c r="W27" s="9" t="s">
-        <v>826</v>
-      </c>
-      <c r="X27" s="92"/>
-    </row>
-    <row r="28" spans="7:24">
-      <c r="K28" s="151"/>
-      <c r="N28" t="s">
-        <v>899</v>
-      </c>
-      <c r="V28" s="168"/>
-      <c r="W28" s="9" t="s">
-        <v>827</v>
-      </c>
-      <c r="X28" s="92" t="s">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="29" spans="7:24">
-      <c r="K29" s="151"/>
-      <c r="N29" t="s">
-        <v>900</v>
-      </c>
-      <c r="V29" s="169"/>
-      <c r="W29" s="9" t="s">
-        <v>828</v>
-      </c>
-      <c r="X29" s="92" t="s">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="30" spans="7:24">
-      <c r="K30" s="151"/>
-      <c r="M30" t="s">
+      <c r="W30" s="49" t="s">
+        <v>821</v>
+      </c>
+      <c r="X30" s="113"/>
+    </row>
+    <row r="31" spans="7:24">
+      <c r="K31" s="148"/>
+      <c r="N31" t="s">
         <v>901</v>
       </c>
-      <c r="N30" t="s">
-        <v>853</v>
-      </c>
-      <c r="V30" s="164" t="s">
-        <v>832</v>
-      </c>
-      <c r="W30" s="49" t="s">
+      <c r="V31" s="162"/>
+      <c r="W31" s="49" t="s">
         <v>822</v>
-      </c>
-      <c r="X30" s="113"/>
-    </row>
-    <row r="31" spans="7:24">
-      <c r="K31" s="151"/>
-      <c r="N31" t="s">
-        <v>902</v>
-      </c>
-      <c r="V31" s="165"/>
-      <c r="W31" s="49" t="s">
-        <v>823</v>
       </c>
       <c r="X31" s="113"/>
     </row>
     <row r="32" spans="7:24" ht="15.75" thickBot="1">
       <c r="G32" t="s">
-        <v>911</v>
-      </c>
-      <c r="K32" s="151"/>
-      <c r="L32" s="149"/>
-      <c r="M32" s="149"/>
-      <c r="N32" s="149"/>
-      <c r="O32" s="150" t="s">
+        <v>910</v>
+      </c>
+      <c r="K32" s="148"/>
+      <c r="L32" s="146"/>
+      <c r="M32" s="146"/>
+      <c r="N32" s="146"/>
+      <c r="O32" s="147" t="s">
+        <v>902</v>
+      </c>
+      <c r="P32" s="147" t="s">
         <v>903</v>
       </c>
-      <c r="P32" s="150" t="s">
-        <v>904</v>
-      </c>
-      <c r="Q32" s="149"/>
-      <c r="R32" s="149"/>
-      <c r="V32" s="166"/>
+      <c r="Q32" s="146"/>
+      <c r="R32" s="146"/>
+      <c r="V32" s="163"/>
       <c r="W32" s="49" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="X32" s="113"/>
     </row>
@@ -23806,25 +23833,25 @@
         <v>1</v>
       </c>
       <c r="G33" t="s">
-        <v>912</v>
-      </c>
-      <c r="K33" s="151"/>
+        <v>911</v>
+      </c>
+      <c r="K33" s="148"/>
     </row>
     <row r="34" spans="6:17">
       <c r="F34">
         <v>2</v>
       </c>
       <c r="G34" t="s">
-        <v>913</v>
-      </c>
-      <c r="K34" s="151">
+        <v>912</v>
+      </c>
+      <c r="K34" s="148">
         <v>3</v>
       </c>
       <c r="L34" s="5" t="s">
+        <v>904</v>
+      </c>
+      <c r="M34" t="s">
         <v>905</v>
-      </c>
-      <c r="M34" t="s">
-        <v>906</v>
       </c>
     </row>
     <row r="35" spans="6:17">
@@ -23832,54 +23859,54 @@
         <v>2</v>
       </c>
       <c r="G35" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="M35" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="36" spans="6:17">
       <c r="F36" s="7" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="M36" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="37" spans="6:17">
       <c r="M37" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="38" spans="6:17">
       <c r="M38" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="39" spans="6:17">
       <c r="M39" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="40" spans="6:17">
       <c r="M40" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="41" spans="6:17" ht="15.75" thickBot="1">
-      <c r="L41" s="149"/>
-      <c r="M41" s="149"/>
-      <c r="N41" s="149"/>
-      <c r="O41" s="150" t="s">
-        <v>908</v>
-      </c>
-      <c r="P41" s="150" t="s">
-        <v>893</v>
-      </c>
-      <c r="Q41" s="149"/>
+      <c r="L41" s="146"/>
+      <c r="M41" s="146"/>
+      <c r="N41" s="146"/>
+      <c r="O41" s="147" t="s">
+        <v>907</v>
+      </c>
+      <c r="P41" s="147" t="s">
+        <v>892</v>
+      </c>
+      <c r="Q41" s="146"/>
     </row>
     <row r="44" spans="6:17">
-      <c r="P44" s="148"/>
+      <c r="P44" s="145"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -23916,15 +23943,15 @@
         <v>313</v>
       </c>
       <c r="R4" s="13" t="s">
+        <v>805</v>
+      </c>
+      <c r="S4" s="93" t="s">
         <v>806</v>
-      </c>
-      <c r="S4" s="93" t="s">
-        <v>807</v>
       </c>
     </row>
     <row r="5" spans="3:20">
       <c r="O5" s="81" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="P5" s="81">
         <v>1</v>
@@ -23935,13 +23962,13 @@
       <c r="R5" s="13" t="s">
         <v>352</v>
       </c>
-      <c r="S5" s="170" t="s">
-        <v>810</v>
+      <c r="S5" s="167" t="s">
+        <v>809</v>
       </c>
     </row>
     <row r="6" spans="3:20">
       <c r="O6" s="81" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="P6" s="81">
         <v>2</v>
@@ -23952,11 +23979,11 @@
       <c r="R6" s="9" t="s">
         <v>602</v>
       </c>
-      <c r="S6" s="170"/>
+      <c r="S6" s="167"/>
     </row>
     <row r="7" spans="3:20">
       <c r="O7" s="81" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="P7" s="81">
         <v>3</v>
@@ -23967,11 +23994,11 @@
       <c r="R7" s="9" t="s">
         <v>603</v>
       </c>
-      <c r="S7" s="170"/>
+      <c r="S7" s="167"/>
     </row>
     <row r="8" spans="3:20">
       <c r="O8" s="81" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="P8" s="81">
         <v>4</v>
@@ -23982,11 +24009,11 @@
       <c r="R8" s="9" t="s">
         <v>350</v>
       </c>
-      <c r="S8" s="170"/>
+      <c r="S8" s="167"/>
     </row>
     <row r="9" spans="3:20">
       <c r="O9" s="81" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="P9" s="81">
         <v>5</v>
@@ -23997,7 +24024,7 @@
       <c r="R9" s="9" t="s">
         <v>349</v>
       </c>
-      <c r="S9" s="170"/>
+      <c r="S9" s="167"/>
     </row>
     <row r="10" spans="3:20">
       <c r="Q10" s="9" t="s">
@@ -24007,29 +24034,29 @@
         <v>348</v>
       </c>
       <c r="S10" s="93" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="T10" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="14" spans="3:20">
       <c r="C14" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="Q14" s="94" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="15" spans="3:20">
-      <c r="Q15" s="167" t="s">
-        <v>833</v>
+      <c r="Q15" s="164" t="s">
+        <v>832</v>
       </c>
       <c r="R15" s="9" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="S15" s="92" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="16" spans="3:20">
@@ -24037,7 +24064,7 @@
         <v>313</v>
       </c>
       <c r="D16" s="92" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>314</v>
@@ -24046,96 +24073,96 @@
         <v>312</v>
       </c>
       <c r="G16" s="10" t="s">
+        <v>811</v>
+      </c>
+      <c r="H16" s="10" t="s">
         <v>812</v>
-      </c>
-      <c r="H16" s="10" t="s">
-        <v>813</v>
       </c>
       <c r="I16" s="10" t="s">
         <v>315</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>814</v>
-      </c>
-      <c r="Q16" s="168"/>
+        <v>813</v>
+      </c>
+      <c r="Q16" s="165"/>
       <c r="R16" s="9" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="S16" s="92" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="17" spans="10:19">
       <c r="J17" s="81"/>
-      <c r="Q17" s="168"/>
+      <c r="Q17" s="165"/>
       <c r="R17" s="9" t="s">
+        <v>816</v>
+      </c>
+      <c r="S17" s="92" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="18" spans="10:19">
+      <c r="Q18" s="165"/>
+      <c r="R18" s="9" t="s">
         <v>817</v>
       </c>
-      <c r="S17" s="92" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="18" spans="10:19">
-      <c r="Q18" s="168"/>
-      <c r="R18" s="9" t="s">
-        <v>818</v>
-      </c>
       <c r="S18" s="92" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="19" spans="10:19">
-      <c r="Q19" s="168"/>
+      <c r="Q19" s="165"/>
       <c r="R19" s="9" t="s">
+        <v>824</v>
+      </c>
+      <c r="S19" s="92"/>
+    </row>
+    <row r="20" spans="10:19">
+      <c r="Q20" s="165"/>
+      <c r="R20" s="9" t="s">
         <v>825</v>
       </c>
-      <c r="S19" s="92"/>
-    </row>
-    <row r="20" spans="10:19">
-      <c r="Q20" s="168"/>
-      <c r="R20" s="9" t="s">
+      <c r="S20" s="92"/>
+    </row>
+    <row r="21" spans="10:19">
+      <c r="Q21" s="165"/>
+      <c r="R21" s="9" t="s">
         <v>826</v>
       </c>
-      <c r="S20" s="92"/>
-    </row>
-    <row r="21" spans="10:19">
-      <c r="Q21" s="168"/>
-      <c r="R21" s="9" t="s">
+      <c r="S21" s="92" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="22" spans="10:19">
+      <c r="Q22" s="166"/>
+      <c r="R22" s="9" t="s">
         <v>827</v>
       </c>
-      <c r="S21" s="92" t="s">
+      <c r="S22" s="92" t="s">
         <v>829</v>
       </c>
     </row>
-    <row r="22" spans="10:19">
-      <c r="Q22" s="169"/>
-      <c r="R22" s="9" t="s">
-        <v>828</v>
-      </c>
-      <c r="S22" s="92" t="s">
-        <v>830</v>
-      </c>
-    </row>
     <row r="23" spans="10:19">
-      <c r="Q23" s="167" t="s">
-        <v>832</v>
+      <c r="Q23" s="164" t="s">
+        <v>831</v>
       </c>
       <c r="R23" s="9" t="s">
+        <v>821</v>
+      </c>
+      <c r="S23" s="92"/>
+    </row>
+    <row r="24" spans="10:19">
+      <c r="Q24" s="165"/>
+      <c r="R24" s="9" t="s">
         <v>822</v>
       </c>
-      <c r="S23" s="92"/>
-    </row>
-    <row r="24" spans="10:19">
-      <c r="Q24" s="168"/>
-      <c r="R24" s="9" t="s">
+      <c r="S24" s="92"/>
+    </row>
+    <row r="25" spans="10:19">
+      <c r="Q25" s="166"/>
+      <c r="R25" s="9" t="s">
         <v>823</v>
-      </c>
-      <c r="S24" s="92"/>
-    </row>
-    <row r="25" spans="10:19">
-      <c r="Q25" s="169"/>
-      <c r="R25" s="9" t="s">
-        <v>824</v>
       </c>
       <c r="S25" s="92"/>
     </row>
@@ -24158,22 +24185,22 @@
   <sheetData>
     <row r="10" spans="14:14">
       <c r="N10" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
     </row>
     <row r="14" spans="14:14">
       <c r="N14" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
     </row>
     <row r="15" spans="14:14">
       <c r="N15" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
     </row>
     <row r="24" spans="14:14">
       <c r="N24" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
     </row>
   </sheetData>
@@ -24194,337 +24221,337 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" t="s">
+        <v>859</v>
+      </c>
+      <c r="B1" t="s">
         <v>860</v>
       </c>
-      <c r="B1" t="s">
-        <v>861</v>
-      </c>
-      <c r="J1" s="171" t="s">
-        <v>954</v>
-      </c>
-      <c r="K1" s="172"/>
-      <c r="L1" s="172"/>
-      <c r="M1" s="172"/>
-      <c r="N1" s="172"/>
-      <c r="O1" s="172"/>
-      <c r="P1" s="172"/>
-      <c r="Q1" s="172"/>
+      <c r="J1" s="168" t="s">
+        <v>952</v>
+      </c>
+      <c r="K1" s="169"/>
+      <c r="L1" s="169"/>
+      <c r="M1" s="169"/>
+      <c r="N1" s="169"/>
+      <c r="O1" s="169"/>
+      <c r="P1" s="169"/>
+      <c r="Q1" s="169"/>
     </row>
     <row r="2" spans="1:17">
-      <c r="J2" s="172"/>
-      <c r="K2" s="172"/>
-      <c r="L2" s="172"/>
-      <c r="M2" s="172"/>
-      <c r="N2" s="172"/>
-      <c r="O2" s="172"/>
-      <c r="P2" s="172"/>
-      <c r="Q2" s="172"/>
+      <c r="J2" s="169"/>
+      <c r="K2" s="169"/>
+      <c r="L2" s="169"/>
+      <c r="M2" s="169"/>
+      <c r="N2" s="169"/>
+      <c r="O2" s="169"/>
+      <c r="P2" s="169"/>
+      <c r="Q2" s="169"/>
     </row>
     <row r="3" spans="1:17">
       <c r="A3" s="6" t="s">
-        <v>862</v>
-      </c>
-      <c r="J3" s="172"/>
-      <c r="K3" s="172"/>
-      <c r="L3" s="172"/>
-      <c r="M3" s="172"/>
-      <c r="N3" s="172"/>
-      <c r="O3" s="172"/>
-      <c r="P3" s="172"/>
-      <c r="Q3" s="172"/>
+        <v>861</v>
+      </c>
+      <c r="J3" s="169"/>
+      <c r="K3" s="169"/>
+      <c r="L3" s="169"/>
+      <c r="M3" s="169"/>
+      <c r="N3" s="169"/>
+      <c r="O3" s="169"/>
+      <c r="P3" s="169"/>
+      <c r="Q3" s="169"/>
     </row>
     <row r="4" spans="1:17">
       <c r="A4" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B4" t="s">
+        <v>862</v>
+      </c>
+      <c r="D4" t="s">
         <v>863</v>
       </c>
-      <c r="D4" t="s">
-        <v>864</v>
-      </c>
-      <c r="J4" s="172"/>
-      <c r="K4" s="172"/>
-      <c r="L4" s="172"/>
-      <c r="M4" s="172"/>
-      <c r="N4" s="172"/>
-      <c r="O4" s="172"/>
-      <c r="P4" s="172"/>
-      <c r="Q4" s="172"/>
+      <c r="J4" s="169"/>
+      <c r="K4" s="169"/>
+      <c r="L4" s="169"/>
+      <c r="M4" s="169"/>
+      <c r="N4" s="169"/>
+      <c r="O4" s="169"/>
+      <c r="P4" s="169"/>
+      <c r="Q4" s="169"/>
     </row>
     <row r="5" spans="1:17">
-      <c r="J5" s="172"/>
-      <c r="K5" s="172"/>
-      <c r="L5" s="172"/>
-      <c r="M5" s="172"/>
-      <c r="N5" s="172"/>
-      <c r="O5" s="172"/>
-      <c r="P5" s="172"/>
-      <c r="Q5" s="172"/>
+      <c r="J5" s="169"/>
+      <c r="K5" s="169"/>
+      <c r="L5" s="169"/>
+      <c r="M5" s="169"/>
+      <c r="N5" s="169"/>
+      <c r="O5" s="169"/>
+      <c r="P5" s="169"/>
+      <c r="Q5" s="169"/>
     </row>
     <row r="6" spans="1:17" ht="15.75" thickBot="1">
       <c r="A6" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="E6" t="s">
-        <v>920</v>
-      </c>
-      <c r="J6" s="172"/>
-      <c r="K6" s="172"/>
-      <c r="L6" s="172"/>
-      <c r="M6" s="172"/>
-      <c r="N6" s="172"/>
-      <c r="O6" s="172"/>
-      <c r="P6" s="172"/>
-      <c r="Q6" s="172"/>
+        <v>918</v>
+      </c>
+      <c r="J6" s="169"/>
+      <c r="K6" s="169"/>
+      <c r="L6" s="169"/>
+      <c r="M6" s="169"/>
+      <c r="N6" s="169"/>
+      <c r="O6" s="169"/>
+      <c r="P6" s="169"/>
+      <c r="Q6" s="169"/>
     </row>
     <row r="7" spans="1:17" ht="15.75" thickBot="1">
       <c r="A7" s="106" t="s">
-        <v>866</v>
-      </c>
-      <c r="J7" s="172"/>
-      <c r="K7" s="172"/>
-      <c r="L7" s="172"/>
-      <c r="M7" s="172"/>
-      <c r="N7" s="172"/>
-      <c r="O7" s="172"/>
-      <c r="P7" s="172"/>
-      <c r="Q7" s="172"/>
+        <v>865</v>
+      </c>
+      <c r="J7" s="169"/>
+      <c r="K7" s="169"/>
+      <c r="L7" s="169"/>
+      <c r="M7" s="169"/>
+      <c r="N7" s="169"/>
+      <c r="O7" s="169"/>
+      <c r="P7" s="169"/>
+      <c r="Q7" s="169"/>
     </row>
     <row r="8" spans="1:17">
-      <c r="A8" s="121"/>
-      <c r="J8" s="172"/>
-      <c r="K8" s="172"/>
-      <c r="L8" s="172"/>
-      <c r="M8" s="172"/>
-      <c r="N8" s="172"/>
-      <c r="O8" s="172"/>
-      <c r="P8" s="172"/>
-      <c r="Q8" s="172"/>
+      <c r="A8" s="118"/>
+      <c r="J8" s="169"/>
+      <c r="K8" s="169"/>
+      <c r="L8" s="169"/>
+      <c r="M8" s="169"/>
+      <c r="N8" s="169"/>
+      <c r="O8" s="169"/>
+      <c r="P8" s="169"/>
+      <c r="Q8" s="169"/>
     </row>
     <row r="9" spans="1:17">
       <c r="A9" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="B9" t="s">
-        <v>926</v>
-      </c>
-      <c r="J9" s="172"/>
-      <c r="K9" s="172"/>
-      <c r="L9" s="172"/>
-      <c r="M9" s="172"/>
-      <c r="N9" s="172"/>
-      <c r="O9" s="172"/>
-      <c r="P9" s="172"/>
-      <c r="Q9" s="172"/>
+        <v>924</v>
+      </c>
+      <c r="J9" s="169"/>
+      <c r="K9" s="169"/>
+      <c r="L9" s="169"/>
+      <c r="M9" s="169"/>
+      <c r="N9" s="169"/>
+      <c r="O9" s="169"/>
+      <c r="P9" s="169"/>
+      <c r="Q9" s="169"/>
     </row>
     <row r="10" spans="1:17">
       <c r="A10" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="B10" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="E10" t="s">
+        <v>925</v>
+      </c>
+      <c r="F10" t="s">
+        <v>926</v>
+      </c>
+      <c r="G10" t="s">
         <v>927</v>
       </c>
-      <c r="F10" t="s">
-        <v>928</v>
-      </c>
-      <c r="G10" t="s">
-        <v>929</v>
-      </c>
       <c r="H10" t="s">
-        <v>952</v>
-      </c>
-      <c r="J10" s="172"/>
-      <c r="K10" s="172"/>
-      <c r="L10" s="172"/>
-      <c r="M10" s="172"/>
-      <c r="N10" s="172"/>
-      <c r="O10" s="172"/>
-      <c r="P10" s="172"/>
-      <c r="Q10" s="172"/>
+        <v>950</v>
+      </c>
+      <c r="J10" s="169"/>
+      <c r="K10" s="169"/>
+      <c r="L10" s="169"/>
+      <c r="M10" s="169"/>
+      <c r="N10" s="169"/>
+      <c r="O10" s="169"/>
+      <c r="P10" s="169"/>
+      <c r="Q10" s="169"/>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="B11" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="E11" t="s">
+        <v>949</v>
+      </c>
+      <c r="F11" t="s">
+        <v>928</v>
+      </c>
+      <c r="G11" t="s">
+        <v>929</v>
+      </c>
+      <c r="H11" t="s">
         <v>951</v>
       </c>
-      <c r="F11" t="s">
-        <v>930</v>
-      </c>
-      <c r="G11" t="s">
-        <v>931</v>
-      </c>
-      <c r="H11" t="s">
-        <v>953</v>
-      </c>
-      <c r="J11" s="172"/>
-      <c r="K11" s="172"/>
-      <c r="L11" s="172"/>
-      <c r="M11" s="172"/>
-      <c r="N11" s="172"/>
-      <c r="O11" s="172"/>
-      <c r="P11" s="172"/>
-      <c r="Q11" s="172"/>
+      <c r="J11" s="169"/>
+      <c r="K11" s="169"/>
+      <c r="L11" s="169"/>
+      <c r="M11" s="169"/>
+      <c r="N11" s="169"/>
+      <c r="O11" s="169"/>
+      <c r="P11" s="169"/>
+      <c r="Q11" s="169"/>
     </row>
     <row r="12" spans="1:17">
       <c r="B12" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="F12" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="G12" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="H12" t="s">
-        <v>953</v>
-      </c>
-      <c r="J12" s="172"/>
-      <c r="K12" s="172"/>
-      <c r="L12" s="172"/>
-      <c r="M12" s="172"/>
-      <c r="N12" s="172"/>
-      <c r="O12" s="172"/>
-      <c r="P12" s="172"/>
-      <c r="Q12" s="172"/>
+        <v>951</v>
+      </c>
+      <c r="J12" s="169"/>
+      <c r="K12" s="169"/>
+      <c r="L12" s="169"/>
+      <c r="M12" s="169"/>
+      <c r="N12" s="169"/>
+      <c r="O12" s="169"/>
+      <c r="P12" s="169"/>
+      <c r="Q12" s="169"/>
     </row>
     <row r="13" spans="1:17">
       <c r="F13" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="G13" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="H13" t="s">
-        <v>953</v>
-      </c>
-      <c r="J13" s="172"/>
-      <c r="K13" s="172"/>
-      <c r="L13" s="172"/>
-      <c r="M13" s="172"/>
-      <c r="N13" s="172"/>
-      <c r="O13" s="172"/>
-      <c r="P13" s="172"/>
-      <c r="Q13" s="172"/>
+        <v>951</v>
+      </c>
+      <c r="J13" s="169"/>
+      <c r="K13" s="169"/>
+      <c r="L13" s="169"/>
+      <c r="M13" s="169"/>
+      <c r="N13" s="169"/>
+      <c r="O13" s="169"/>
+      <c r="P13" s="169"/>
+      <c r="Q13" s="169"/>
     </row>
     <row r="14" spans="1:17">
-      <c r="J14" s="172"/>
-      <c r="K14" s="172"/>
-      <c r="L14" s="172"/>
-      <c r="M14" s="172"/>
-      <c r="N14" s="172"/>
-      <c r="O14" s="172"/>
-      <c r="P14" s="172"/>
-      <c r="Q14" s="172"/>
+      <c r="J14" s="169"/>
+      <c r="K14" s="169"/>
+      <c r="L14" s="169"/>
+      <c r="M14" s="169"/>
+      <c r="N14" s="169"/>
+      <c r="O14" s="169"/>
+      <c r="P14" s="169"/>
+      <c r="Q14" s="169"/>
     </row>
     <row r="15" spans="1:17">
       <c r="A15" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="C15" t="s">
-        <v>949</v>
-      </c>
-      <c r="J15" s="172"/>
-      <c r="K15" s="172"/>
-      <c r="L15" s="172"/>
-      <c r="M15" s="172"/>
-      <c r="N15" s="172"/>
-      <c r="O15" s="172"/>
-      <c r="P15" s="172"/>
-      <c r="Q15" s="172"/>
+        <v>947</v>
+      </c>
+      <c r="J15" s="169"/>
+      <c r="K15" s="169"/>
+      <c r="L15" s="169"/>
+      <c r="M15" s="169"/>
+      <c r="N15" s="169"/>
+      <c r="O15" s="169"/>
+      <c r="P15" s="169"/>
+      <c r="Q15" s="169"/>
     </row>
     <row r="16" spans="1:17">
       <c r="A16" t="s">
-        <v>939</v>
-      </c>
-      <c r="J16" s="172"/>
-      <c r="K16" s="172"/>
-      <c r="L16" s="172"/>
-      <c r="M16" s="172"/>
-      <c r="N16" s="172"/>
-      <c r="O16" s="172"/>
-      <c r="P16" s="172"/>
-      <c r="Q16" s="172"/>
+        <v>937</v>
+      </c>
+      <c r="J16" s="169"/>
+      <c r="K16" s="169"/>
+      <c r="L16" s="169"/>
+      <c r="M16" s="169"/>
+      <c r="N16" s="169"/>
+      <c r="O16" s="169"/>
+      <c r="P16" s="169"/>
+      <c r="Q16" s="169"/>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="5" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="5" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="6" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
     </row>
   </sheetData>
@@ -24541,34 +24568,42 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E790F7E-BA47-4A84-BF83-ABFCCF3C4842}">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="D3" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
+        <v>1289</v>
+      </c>
+      <c r="G5" t="s">
+        <v>1290</v>
+      </c>
+      <c r="I5" t="s">
         <v>1291</v>
       </c>
-      <c r="G5" t="s">
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="7" t="s">
         <v>1292</v>
       </c>
-      <c r="I5" t="s">
-        <v>1293</v>
-      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A6" r:id="rId1" xr:uid="{0F35D8A4-95F2-4EB3-828B-8AAB2731E662}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -24729,19 +24764,19 @@
       <c r="E7" s="31" t="s">
         <v>449</v>
       </c>
-      <c r="F7" s="173" t="s">
+      <c r="F7" s="170" t="s">
         <v>441</v>
       </c>
-      <c r="G7" s="173"/>
-      <c r="H7" s="173"/>
-      <c r="I7" s="173"/>
-      <c r="J7" s="173"/>
-      <c r="K7" s="173"/>
-      <c r="L7" s="173"/>
-      <c r="M7" s="173"/>
-      <c r="N7" s="173"/>
-      <c r="O7" s="173"/>
-      <c r="P7" s="173"/>
+      <c r="G7" s="170"/>
+      <c r="H7" s="170"/>
+      <c r="I7" s="170"/>
+      <c r="J7" s="170"/>
+      <c r="K7" s="170"/>
+      <c r="L7" s="170"/>
+      <c r="M7" s="170"/>
+      <c r="N7" s="170"/>
+      <c r="O7" s="170"/>
+      <c r="P7" s="170"/>
     </row>
     <row r="8" spans="1:17">
       <c r="B8" s="32" t="s">
@@ -24923,7 +24958,7 @@
         <v>463</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -24965,40 +25000,40 @@
       <c r="A24" s="35" t="s">
         <v>455</v>
       </c>
-      <c r="B24" s="174" t="s">
+      <c r="B24" s="171" t="s">
         <v>457</v>
       </c>
-      <c r="C24" s="174"/>
-      <c r="D24" s="174"/>
-      <c r="E24" s="174"/>
-      <c r="F24" s="174"/>
-      <c r="G24" s="174"/>
+      <c r="C24" s="171"/>
+      <c r="D24" s="171"/>
+      <c r="E24" s="171"/>
+      <c r="F24" s="171"/>
+      <c r="G24" s="171"/>
     </row>
     <row r="25" spans="1:7" ht="30">
       <c r="A25" s="35" t="s">
         <v>462</v>
       </c>
-      <c r="B25" s="175" t="s">
+      <c r="B25" s="172" t="s">
         <v>464</v>
       </c>
-      <c r="C25" s="175"/>
-      <c r="D25" s="175"/>
-      <c r="E25" s="175"/>
-      <c r="F25" s="175"/>
-      <c r="G25" s="175"/>
+      <c r="C25" s="172"/>
+      <c r="D25" s="172"/>
+      <c r="E25" s="172"/>
+      <c r="F25" s="172"/>
+      <c r="G25" s="172"/>
     </row>
     <row r="26" spans="1:7" ht="159" customHeight="1">
       <c r="A26" s="35" t="s">
         <v>459</v>
       </c>
-      <c r="B26" s="174" t="s">
+      <c r="B26" s="171" t="s">
         <v>460</v>
       </c>
-      <c r="C26" s="174"/>
-      <c r="D26" s="174"/>
-      <c r="E26" s="174"/>
-      <c r="F26" s="174"/>
-      <c r="G26" s="174"/>
+      <c r="C26" s="171"/>
+      <c r="D26" s="171"/>
+      <c r="E26" s="171"/>
+      <c r="F26" s="171"/>
+      <c r="G26" s="171"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -25513,29 +25548,29 @@
       <c r="B27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="C27" s="178" t="s">
+      <c r="C27" s="175" t="s">
         <v>622</v>
       </c>
-      <c r="D27" s="179"/>
+      <c r="D27" s="176"/>
       <c r="E27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="F27" s="178" t="s">
+      <c r="F27" s="175" t="s">
         <v>622</v>
       </c>
-      <c r="G27" s="179"/>
+      <c r="G27" s="176"/>
       <c r="H27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="I27" s="178" t="s">
+      <c r="I27" s="175" t="s">
         <v>622</v>
       </c>
-      <c r="J27" s="179"/>
-      <c r="L27" s="176" t="s">
+      <c r="J27" s="176"/>
+      <c r="L27" s="173" t="s">
         <v>694</v>
       </c>
-      <c r="M27" s="176"/>
-      <c r="N27" s="176"/>
+      <c r="M27" s="173"/>
+      <c r="N27" s="173"/>
     </row>
     <row r="28" spans="1:14" ht="32.25" thickBot="1">
       <c r="A28" s="81">
@@ -25544,29 +25579,29 @@
       <c r="B28" s="69" t="s">
         <v>623</v>
       </c>
-      <c r="C28" s="186" t="s">
+      <c r="C28" s="183" t="s">
         <v>624</v>
       </c>
-      <c r="D28" s="187"/>
+      <c r="D28" s="184"/>
       <c r="E28" s="70" t="s">
         <v>645</v>
       </c>
-      <c r="F28" s="180" t="s">
+      <c r="F28" s="177" t="s">
         <v>646</v>
       </c>
-      <c r="G28" s="181"/>
+      <c r="G28" s="178"/>
       <c r="H28" s="69" t="s">
         <v>667</v>
       </c>
-      <c r="I28" s="186" t="s">
+      <c r="I28" s="183" t="s">
         <v>668</v>
       </c>
-      <c r="J28" s="187"/>
-      <c r="L28" s="177" t="s">
+      <c r="J28" s="184"/>
+      <c r="L28" s="174" t="s">
         <v>695</v>
       </c>
-      <c r="M28" s="177"/>
-      <c r="N28" s="177"/>
+      <c r="M28" s="174"/>
+      <c r="N28" s="174"/>
     </row>
     <row r="29" spans="1:14" ht="31.5" thickBot="1">
       <c r="A29" s="81">
@@ -25575,29 +25610,29 @@
       <c r="B29" s="70" t="s">
         <v>625</v>
       </c>
-      <c r="C29" s="180" t="s">
+      <c r="C29" s="177" t="s">
         <v>626</v>
       </c>
-      <c r="D29" s="181"/>
+      <c r="D29" s="178"/>
       <c r="E29" s="69" t="s">
         <v>647</v>
       </c>
-      <c r="F29" s="186" t="s">
+      <c r="F29" s="183" t="s">
         <v>648</v>
       </c>
-      <c r="G29" s="187"/>
+      <c r="G29" s="184"/>
       <c r="H29" s="70" t="s">
         <v>669</v>
       </c>
-      <c r="I29" s="190" t="s">
+      <c r="I29" s="187" t="s">
         <v>670</v>
       </c>
-      <c r="J29" s="191"/>
-      <c r="L29" s="176" t="s">
+      <c r="J29" s="188"/>
+      <c r="L29" s="173" t="s">
         <v>696</v>
       </c>
-      <c r="M29" s="176"/>
-      <c r="N29" s="176"/>
+      <c r="M29" s="173"/>
+      <c r="N29" s="173"/>
     </row>
     <row r="30" spans="1:14" ht="15.75" thickBot="1">
       <c r="A30" s="81">
@@ -25606,29 +25641,29 @@
       <c r="B30" s="69" t="s">
         <v>627</v>
       </c>
-      <c r="C30" s="186" t="s">
+      <c r="C30" s="183" t="s">
         <v>628</v>
       </c>
-      <c r="D30" s="187"/>
+      <c r="D30" s="184"/>
       <c r="E30" s="70" t="s">
         <v>649</v>
       </c>
-      <c r="F30" s="180" t="s">
+      <c r="F30" s="177" t="s">
         <v>650</v>
       </c>
-      <c r="G30" s="181"/>
+      <c r="G30" s="178"/>
       <c r="H30" s="69" t="s">
         <v>671</v>
       </c>
-      <c r="I30" s="186" t="s">
+      <c r="I30" s="183" t="s">
         <v>672</v>
       </c>
-      <c r="J30" s="187"/>
-      <c r="L30" s="177" t="s">
+      <c r="J30" s="184"/>
+      <c r="L30" s="174" t="s">
         <v>697</v>
       </c>
-      <c r="M30" s="177"/>
-      <c r="N30" s="177"/>
+      <c r="M30" s="174"/>
+      <c r="N30" s="174"/>
     </row>
     <row r="31" spans="1:14" ht="17.25" customHeight="1" thickBot="1">
       <c r="A31" s="81">
@@ -25637,29 +25672,29 @@
       <c r="B31" s="70" t="s">
         <v>629</v>
       </c>
-      <c r="C31" s="180" t="s">
+      <c r="C31" s="177" t="s">
         <v>630</v>
       </c>
-      <c r="D31" s="181"/>
+      <c r="D31" s="178"/>
       <c r="E31" s="69" t="s">
         <v>651</v>
       </c>
-      <c r="F31" s="186" t="s">
+      <c r="F31" s="183" t="s">
         <v>652</v>
       </c>
-      <c r="G31" s="187"/>
+      <c r="G31" s="184"/>
       <c r="H31" s="70" t="s">
         <v>673</v>
       </c>
-      <c r="I31" s="180" t="s">
+      <c r="I31" s="177" t="s">
         <v>674</v>
       </c>
-      <c r="J31" s="181"/>
-      <c r="L31" s="176" t="s">
+      <c r="J31" s="178"/>
+      <c r="L31" s="173" t="s">
         <v>698</v>
       </c>
-      <c r="M31" s="176"/>
-      <c r="N31" s="176"/>
+      <c r="M31" s="173"/>
+      <c r="N31" s="173"/>
     </row>
     <row r="32" spans="1:14" ht="43.5" customHeight="1" thickBot="1">
       <c r="A32" s="81">
@@ -25668,29 +25703,29 @@
       <c r="B32" s="69" t="s">
         <v>631</v>
       </c>
-      <c r="C32" s="186" t="s">
+      <c r="C32" s="183" t="s">
         <v>632</v>
       </c>
-      <c r="D32" s="187"/>
+      <c r="D32" s="184"/>
       <c r="E32" s="70" t="s">
         <v>653</v>
       </c>
-      <c r="F32" s="180" t="s">
+      <c r="F32" s="177" t="s">
         <v>654</v>
       </c>
-      <c r="G32" s="181"/>
+      <c r="G32" s="178"/>
       <c r="H32" s="69" t="s">
         <v>675</v>
       </c>
-      <c r="I32" s="186" t="s">
+      <c r="I32" s="183" t="s">
         <v>676</v>
       </c>
-      <c r="J32" s="187"/>
-      <c r="L32" s="177" t="s">
+      <c r="J32" s="184"/>
+      <c r="L32" s="174" t="s">
         <v>699</v>
       </c>
-      <c r="M32" s="177"/>
-      <c r="N32" s="177"/>
+      <c r="M32" s="174"/>
+      <c r="N32" s="174"/>
     </row>
     <row r="33" spans="1:14" ht="31.5" customHeight="1" thickBot="1">
       <c r="A33" s="81">
@@ -25699,29 +25734,29 @@
       <c r="B33" s="70" t="s">
         <v>633</v>
       </c>
-      <c r="C33" s="180" t="s">
+      <c r="C33" s="177" t="s">
         <v>634</v>
       </c>
-      <c r="D33" s="181"/>
+      <c r="D33" s="178"/>
       <c r="E33" s="69" t="s">
         <v>655</v>
       </c>
-      <c r="F33" s="186" t="s">
+      <c r="F33" s="183" t="s">
         <v>656</v>
       </c>
-      <c r="G33" s="187"/>
+      <c r="G33" s="184"/>
       <c r="H33" s="70" t="s">
         <v>677</v>
       </c>
-      <c r="I33" s="188" t="s">
+      <c r="I33" s="185" t="s">
         <v>678</v>
       </c>
-      <c r="J33" s="189"/>
-      <c r="L33" s="176" t="s">
+      <c r="J33" s="186"/>
+      <c r="L33" s="173" t="s">
         <v>700</v>
       </c>
-      <c r="M33" s="176"/>
-      <c r="N33" s="176"/>
+      <c r="M33" s="173"/>
+      <c r="N33" s="173"/>
     </row>
     <row r="34" spans="1:14" ht="28.5" customHeight="1" thickBot="1">
       <c r="A34" s="81">
@@ -25730,29 +25765,29 @@
       <c r="B34" s="69" t="s">
         <v>635</v>
       </c>
-      <c r="C34" s="186" t="s">
+      <c r="C34" s="183" t="s">
         <v>636</v>
       </c>
-      <c r="D34" s="187"/>
+      <c r="D34" s="184"/>
       <c r="E34" s="70" t="s">
         <v>657</v>
       </c>
-      <c r="F34" s="180" t="s">
+      <c r="F34" s="177" t="s">
         <v>658</v>
       </c>
-      <c r="G34" s="181"/>
+      <c r="G34" s="178"/>
       <c r="H34" s="69" t="s">
         <v>679</v>
       </c>
-      <c r="I34" s="184" t="s">
+      <c r="I34" s="181" t="s">
         <v>680</v>
       </c>
-      <c r="J34" s="185"/>
-      <c r="L34" s="177" t="s">
+      <c r="J34" s="182"/>
+      <c r="L34" s="174" t="s">
         <v>701</v>
       </c>
-      <c r="M34" s="177"/>
-      <c r="N34" s="177"/>
+      <c r="M34" s="174"/>
+      <c r="N34" s="174"/>
     </row>
     <row r="35" spans="1:14" ht="31.5" customHeight="1" thickBot="1">
       <c r="A35" s="81">
@@ -25761,29 +25796,29 @@
       <c r="B35" s="70" t="s">
         <v>637</v>
       </c>
-      <c r="C35" s="180" t="s">
+      <c r="C35" s="177" t="s">
         <v>638</v>
       </c>
-      <c r="D35" s="181"/>
+      <c r="D35" s="178"/>
       <c r="E35" s="69" t="s">
         <v>659</v>
       </c>
-      <c r="F35" s="186" t="s">
+      <c r="F35" s="183" t="s">
         <v>660</v>
       </c>
-      <c r="G35" s="187"/>
+      <c r="G35" s="184"/>
       <c r="H35" s="77" t="s">
         <v>681</v>
       </c>
-      <c r="I35" s="180" t="s">
+      <c r="I35" s="177" t="s">
         <v>682</v>
       </c>
-      <c r="J35" s="181"/>
-      <c r="L35" s="176" t="s">
+      <c r="J35" s="178"/>
+      <c r="L35" s="173" t="s">
         <v>702</v>
       </c>
-      <c r="M35" s="176"/>
-      <c r="N35" s="176"/>
+      <c r="M35" s="173"/>
+      <c r="N35" s="173"/>
     </row>
     <row r="36" spans="1:14" ht="60.75" thickBot="1">
       <c r="A36" s="81">
@@ -25792,17 +25827,17 @@
       <c r="B36" s="69" t="s">
         <v>639</v>
       </c>
-      <c r="C36" s="186" t="s">
+      <c r="C36" s="183" t="s">
         <v>640</v>
       </c>
-      <c r="D36" s="187"/>
+      <c r="D36" s="184"/>
       <c r="E36" s="70" t="s">
         <v>661</v>
       </c>
-      <c r="F36" s="180" t="s">
+      <c r="F36" s="177" t="s">
         <v>662</v>
       </c>
-      <c r="G36" s="181"/>
+      <c r="G36" s="178"/>
       <c r="H36" s="78"/>
       <c r="I36" s="71" t="s">
         <v>683</v>
@@ -25810,11 +25845,11 @@
       <c r="J36" s="72" t="s">
         <v>684</v>
       </c>
-      <c r="L36" s="177" t="s">
+      <c r="L36" s="174" t="s">
         <v>703</v>
       </c>
-      <c r="M36" s="177"/>
-      <c r="N36" s="177"/>
+      <c r="M36" s="174"/>
+      <c r="N36" s="174"/>
     </row>
     <row r="37" spans="1:14" ht="75.75" thickBot="1">
       <c r="A37" s="81">
@@ -25823,17 +25858,17 @@
       <c r="B37" s="70" t="s">
         <v>641</v>
       </c>
-      <c r="C37" s="180" t="s">
+      <c r="C37" s="177" t="s">
         <v>642</v>
       </c>
-      <c r="D37" s="181"/>
+      <c r="D37" s="178"/>
       <c r="E37" s="69" t="s">
         <v>663</v>
       </c>
-      <c r="F37" s="186" t="s">
+      <c r="F37" s="183" t="s">
         <v>664</v>
       </c>
-      <c r="G37" s="187"/>
+      <c r="G37" s="184"/>
       <c r="H37" s="78"/>
       <c r="I37" s="73" t="s">
         <v>685</v>
@@ -25849,17 +25884,17 @@
       <c r="B38" s="69" t="s">
         <v>643</v>
       </c>
-      <c r="C38" s="186" t="s">
+      <c r="C38" s="183" t="s">
         <v>644</v>
       </c>
-      <c r="D38" s="187"/>
+      <c r="D38" s="184"/>
       <c r="E38" s="70" t="s">
         <v>665</v>
       </c>
-      <c r="F38" s="180" t="s">
+      <c r="F38" s="177" t="s">
         <v>666</v>
       </c>
-      <c r="G38" s="181"/>
+      <c r="G38" s="178"/>
       <c r="H38" s="78"/>
       <c r="I38" s="75" t="s">
         <v>687</v>
@@ -25875,22 +25910,22 @@
       <c r="B39" s="70" t="s">
         <v>692</v>
       </c>
-      <c r="C39" s="188" t="s">
+      <c r="C39" s="185" t="s">
         <v>693</v>
       </c>
-      <c r="D39" s="189"/>
+      <c r="D39" s="186"/>
       <c r="E39" s="69" t="s">
         <v>690</v>
       </c>
-      <c r="F39" s="184" t="s">
+      <c r="F39" s="181" t="s">
         <v>691</v>
       </c>
-      <c r="G39" s="185"/>
+      <c r="G39" s="182"/>
       <c r="H39" s="79"/>
-      <c r="I39" s="182" t="s">
+      <c r="I39" s="179" t="s">
         <v>689</v>
       </c>
-      <c r="J39" s="183"/>
+      <c r="J39" s="180"/>
     </row>
     <row r="40" spans="1:14" ht="58.5" customHeight="1"/>
     <row r="42" spans="1:14" ht="31.5" customHeight="1"/>

--- a/2020_LogAnalyzer_Leeheesuk.xlsx
+++ b/2020_LogAnalyzer_Leeheesuk.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="23001"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF9A85ED-2AD5-43C6-9062-F89FD91A2F39}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE895595-84CC-4B89-BF76-3CDFF1D286B6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" firstSheet="7" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5752,7 +5752,7 @@
     <t>완료 - Table명 : logdetail_"project_id"</t>
   </si>
   <si>
-    <t>https://djangopackages.org/grids/g/dynamic-models/</t>
+    <t>https://pypi.org/project/django-dynamic-model/</t>
   </si>
 </sst>
 </file>
@@ -19874,7 +19874,7 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="G17" r:id="rId1" xr:uid="{AFFE4D15-4037-4F6C-80C7-ADA30B10B0D3}"/>
+    <hyperlink ref="G17" r:id="rId1" xr:uid="{423578C7-8A13-42FF-B0CB-7B3D59B70C8D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId2"/>

--- a/2020_LogAnalyzer_Leeheesuk.xlsx
+++ b/2020_LogAnalyzer_Leeheesuk.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="23001"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE895595-84CC-4B89-BF76-3CDFF1D286B6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1441DC8C-9C22-4B78-86EE-05E17F7B1EF2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" firstSheet="7" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" firstSheet="7" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UI" sheetId="7" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="Pilot" sheetId="11" r:id="rId11"/>
     <sheet name="아키텍처" sheetId="9" r:id="rId12"/>
     <sheet name="기능요건" sheetId="8" r:id="rId13"/>
-    <sheet name="기능요건_0401피드백" sheetId="14" r:id="rId14"/>
+    <sheet name="기능요건_피드백" sheetId="14" r:id="rId14"/>
     <sheet name="비기능요건" sheetId="6" r:id="rId15"/>
     <sheet name="성능테스트_0717" sheetId="22" r:id="rId16"/>
     <sheet name="지원포맷" sheetId="1" r:id="rId17"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2051" uniqueCount="1297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2113" uniqueCount="1351">
   <si>
     <t>구분</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -5746,13 +5746,175 @@
     <t>Loop로 해결</t>
   </si>
   <si>
-    <t>처리사간 3초 이상</t>
-  </si>
-  <si>
     <t>완료 - Table명 : logdetail_"project_id"</t>
   </si>
   <si>
     <t>https://pypi.org/project/django-dynamic-model/</t>
+  </si>
+  <si>
+    <t>https://github.com/rvinzent/django-dynamic-models/wiki/Introduction</t>
+  </si>
+  <si>
+    <t>1 -&gt; 2 -&gt; 3</t>
+  </si>
+  <si>
+    <t>2020-09-31</t>
+  </si>
+  <si>
+    <t>처리시간 3초 이상</t>
+  </si>
+  <si>
+    <t>4월1일</t>
+  </si>
+  <si>
+    <t>전력식 파트장님</t>
+  </si>
+  <si>
+    <t>8월6일</t>
+  </si>
+  <si>
+    <t>리뷰회의</t>
+  </si>
+  <si>
+    <t>피드백</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1)(완료) 메뉴 순서 변경 - Analysis Detail Comparison 으로 변경 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2)(완료) Analysis 차트를 맨 위로 올리기 - highlight 될 부분은 어디인가? 실제 사용시에... </t>
+  </si>
+  <si>
+    <t>-&gt; 다시 생각해보자. 기존게 나을 수 있다.</t>
+  </si>
+  <si>
+    <t>3) (TODO) 통계치에 % 추가</t>
+  </si>
+  <si>
+    <t>4) (완료) Top N으로 수정 - 선택할 수 있도록</t>
+  </si>
+  <si>
+    <t>4.1) (완료) 전체 건수는 Information으로 옮기자.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  -&gt;  var url = "http://127.0.0.1:8000/logdetail/statistics_top"+this.statisticsRow+"/"  // N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  -&gt; type = 0</t>
+  </si>
+  <si>
+    <t>5) (완료) 로딩Bar 약 10분 걸릴 예정임 - 멘트</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  - https://biigpongsatorn.github.io/#/vue-element-loading</t>
+  </si>
+  <si>
+    <t>6) (완료) substr 적용하여 UI 조정</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  -&gt; GridTable (완료)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  -&gt; Statistic 부분 (완료)</t>
+  </si>
+  <si>
+    <t>7)(완료) 실제 데이터 추가 수집 및 테스트 =&gt; ACS 추가 수집</t>
+  </si>
+  <si>
+    <t>8) 계속 사용해서 활용성 추가</t>
+  </si>
+  <si>
+    <t>9)(완료)Notice 부분 추가 (Issue Tracking)</t>
+  </si>
+  <si>
+    <t>(완료) Comparison 화면 UI정리</t>
+  </si>
+  <si>
+    <t>(완료) 멀티파일 지원코딩</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. (완료) start_end 부분 project_id로 가져오기 </t>
+  </si>
+  <si>
+    <t>2. (완료) Tab3에서 파일 목록 및 전체 파일의 start/end date 가져오기</t>
+  </si>
+  <si>
+    <t>3. (완료) Search시 왜 파일 1개의 결과만 가져오는지 확인필요</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   (기존) logfile_id로 되어 있다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   (변경) project_id 하위의 logfile_id 가져와야 한다. HOW? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">          logfile_id 개수만큼 Loop를 돌아서 result[]에 담아야 한다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   (완료) logdetail 중복생성 방지</t>
+  </si>
+  <si>
+    <t>4. (완료) Notice 부분, 1개</t>
+  </si>
+  <si>
+    <t>EN Only</t>
+  </si>
+  <si>
+    <t>불필요</t>
+  </si>
+  <si>
+    <t>완료</t>
+  </si>
+  <si>
+    <t>예정</t>
+  </si>
+  <si>
+    <t>9월2일</t>
+  </si>
+  <si>
+    <t>리뷰회의 피드백</t>
+  </si>
+  <si>
+    <t>주요 Feature Metric 부분 강조 - Value Added한 부분 - 장표내용</t>
+  </si>
+  <si>
+    <t>서버 올리고 베타테스트 준비가능? - 9월 - 가능여부 보고</t>
+  </si>
+  <si>
+    <t>Graph Chart</t>
+  </si>
+  <si>
+    <t>3-1 Request, Time-Taken 부분 하나로 통일</t>
+  </si>
+  <si>
+    <t>3-2 Y-axis TPS로 Scale 일치</t>
+  </si>
+  <si>
+    <t>사업부</t>
+  </si>
+  <si>
+    <t>Detail</t>
+  </si>
+  <si>
+    <t>4-1 전체로그 출력</t>
+  </si>
+  <si>
+    <t>4-2 Notice 등 Count에 대한 세부내역 출력 가능하도록</t>
+  </si>
+  <si>
+    <t>통계치에 % 추가</t>
+  </si>
+  <si>
+    <t>작명(Naming)</t>
+  </si>
+  <si>
+    <t>3-3 Statics files, 처리량(Bytes) 추가</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>TimeTaken 부분 UI 수정 - 단위(D/T)</t>
   </si>
 </sst>
 </file>
@@ -5762,7 +5924,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
-  <fonts count="41">
+  <fonts count="42">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6043,6 +6205,13 @@
       <sz val="11"/>
       <name val="Consolas"/>
       <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -6421,11 +6590,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="40" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="216">
+  <cellXfs count="220">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6674,9 +6844,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6995,7 +7162,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7010,8 +7177,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="백분율" xfId="2" builtinId="5"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
   </cellStyles>
@@ -15727,13 +15904,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>257176</xdr:colOff>
-      <xdr:row>0</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>85726</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>104776</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -15771,14 +15948,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>257176</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>190501</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>66675</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>200025</xdr:rowOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -15815,13 +15992,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>104776</xdr:colOff>
-      <xdr:row>0</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>276225</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:colOff>386129</xdr:colOff>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -15859,13 +16036,13 @@
     <xdr:from>
       <xdr:col>14</xdr:col>
       <xdr:colOff>323850</xdr:colOff>
-      <xdr:row>0</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
       <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -15903,13 +16080,13 @@
     <xdr:from>
       <xdr:col>14</xdr:col>
       <xdr:colOff>314326</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>38101</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
       <xdr:colOff>104776</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -16341,51 +16518,51 @@
     </row>
     <row r="17" spans="1:13">
       <c r="J17" s="19"/>
-      <c r="K17" s="155" t="s">
+      <c r="K17" s="154" t="s">
         <v>537</v>
       </c>
-      <c r="L17" s="156"/>
-      <c r="M17" s="157"/>
+      <c r="L17" s="155"/>
+      <c r="M17" s="156"/>
     </row>
     <row r="18" spans="1:13">
       <c r="J18" s="19">
         <v>1</v>
       </c>
-      <c r="K18" s="158" t="s">
+      <c r="K18" s="157" t="s">
         <v>538</v>
       </c>
-      <c r="L18" s="159"/>
-      <c r="M18" s="160"/>
+      <c r="L18" s="158"/>
+      <c r="M18" s="159"/>
     </row>
     <row r="19" spans="1:13">
       <c r="J19" s="19">
         <v>2</v>
       </c>
-      <c r="K19" s="158" t="s">
+      <c r="K19" s="157" t="s">
         <v>539</v>
       </c>
-      <c r="L19" s="159"/>
-      <c r="M19" s="160"/>
+      <c r="L19" s="158"/>
+      <c r="M19" s="159"/>
     </row>
     <row r="20" spans="1:13">
       <c r="J20" s="19">
         <v>3</v>
       </c>
-      <c r="K20" s="158" t="s">
+      <c r="K20" s="157" t="s">
         <v>540</v>
       </c>
-      <c r="L20" s="159"/>
-      <c r="M20" s="160"/>
+      <c r="L20" s="158"/>
+      <c r="M20" s="159"/>
     </row>
     <row r="21" spans="1:13">
       <c r="J21" s="19">
         <v>4</v>
       </c>
-      <c r="K21" s="158" t="s">
+      <c r="K21" s="157" t="s">
         <v>541</v>
       </c>
-      <c r="L21" s="159"/>
-      <c r="M21" s="160"/>
+      <c r="L21" s="158"/>
+      <c r="M21" s="159"/>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="43" t="s">
@@ -16509,7 +16686,7 @@
       <c r="D3" s="85" t="s">
         <v>820</v>
       </c>
-      <c r="E3" s="108" t="s">
+      <c r="E3" s="107" t="s">
         <v>433</v>
       </c>
       <c r="F3" s="85" t="s">
@@ -16529,7 +16706,7 @@
       <c r="D4" s="62" t="s">
         <v>572</v>
       </c>
-      <c r="E4" s="109" t="s">
+      <c r="E4" s="108" t="s">
         <v>452</v>
       </c>
       <c r="F4" s="62" t="s">
@@ -16547,7 +16724,7 @@
       <c r="D5" s="85">
         <v>300</v>
       </c>
-      <c r="E5" s="108">
+      <c r="E5" s="107">
         <v>100</v>
       </c>
       <c r="F5" s="85">
@@ -16573,13 +16750,13 @@
       <c r="A7" s="33" t="s">
         <v>574</v>
       </c>
-      <c r="F7" s="112" t="s">
+      <c r="F7" s="111" t="s">
         <v>915</v>
       </c>
-      <c r="I7" s="189" t="s">
+      <c r="I7" s="188" t="s">
         <v>1166</v>
       </c>
-      <c r="J7" s="189"/>
+      <c r="J7" s="188"/>
       <c r="L7" s="49" t="s">
         <v>601</v>
       </c>
@@ -16597,7 +16774,7 @@
       <c r="D8" s="32" t="s">
         <v>582</v>
       </c>
-      <c r="E8" s="131" t="s">
+      <c r="E8" s="130" t="s">
         <v>583</v>
       </c>
       <c r="F8" s="36" t="s">
@@ -16647,10 +16824,10 @@
       <c r="H9" s="85" t="s">
         <v>466</v>
       </c>
-      <c r="I9" s="117" t="s">
+      <c r="I9" s="116" t="s">
         <v>752</v>
       </c>
-      <c r="J9" s="117" t="s">
+      <c r="J9" s="116" t="s">
         <v>755</v>
       </c>
       <c r="L9" s="9" t="s">
@@ -16916,11 +17093,11 @@
       <c r="K20" s="32" t="s">
         <v>415</v>
       </c>
-      <c r="L20" s="211" t="s">
+      <c r="L20" s="210" t="s">
         <v>568</v>
       </c>
-      <c r="M20" s="214"/>
-      <c r="N20" s="215"/>
+      <c r="M20" s="213"/>
+      <c r="N20" s="214"/>
     </row>
     <row r="21" spans="1:14">
       <c r="B21" s="85" t="s">
@@ -16953,7 +17130,7 @@
       <c r="K21" s="85" t="s">
         <v>466</v>
       </c>
-      <c r="L21" s="212" t="s">
+      <c r="L21" s="211" t="s">
         <v>429</v>
       </c>
     </row>
@@ -16988,7 +17165,7 @@
       <c r="K22" s="62" t="s">
         <v>592</v>
       </c>
-      <c r="L22" s="213" t="s">
+      <c r="L22" s="212" t="s">
         <v>458</v>
       </c>
     </row>
@@ -17019,7 +17196,7 @@
         <v>200</v>
       </c>
       <c r="K23" s="64"/>
-      <c r="L23" s="212" t="s">
+      <c r="L23" s="211" t="s">
         <v>1293</v>
       </c>
     </row>
@@ -17040,29 +17217,29 @@
       <c r="B27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="C27" s="175" t="s">
+      <c r="C27" s="174" t="s">
         <v>622</v>
       </c>
-      <c r="D27" s="176"/>
+      <c r="D27" s="175"/>
       <c r="E27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="F27" s="175" t="s">
+      <c r="F27" s="174" t="s">
         <v>622</v>
       </c>
-      <c r="G27" s="176"/>
+      <c r="G27" s="175"/>
       <c r="H27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="I27" s="175" t="s">
+      <c r="I27" s="174" t="s">
         <v>622</v>
       </c>
-      <c r="J27" s="176"/>
-      <c r="L27" s="173" t="s">
+      <c r="J27" s="175"/>
+      <c r="L27" s="172" t="s">
         <v>694</v>
       </c>
-      <c r="M27" s="173"/>
-      <c r="N27" s="173"/>
+      <c r="M27" s="172"/>
+      <c r="N27" s="172"/>
     </row>
     <row r="28" spans="1:14" ht="49.5" customHeight="1" thickBot="1">
       <c r="A28" s="81">
@@ -17071,29 +17248,29 @@
       <c r="B28" s="69" t="s">
         <v>623</v>
       </c>
-      <c r="C28" s="183" t="s">
+      <c r="C28" s="182" t="s">
         <v>624</v>
       </c>
-      <c r="D28" s="184"/>
+      <c r="D28" s="183"/>
       <c r="E28" s="70" t="s">
         <v>645</v>
       </c>
-      <c r="F28" s="177" t="s">
+      <c r="F28" s="176" t="s">
         <v>1178</v>
       </c>
-      <c r="G28" s="178"/>
+      <c r="G28" s="177"/>
       <c r="H28" s="69" t="s">
         <v>667</v>
       </c>
-      <c r="I28" s="183" t="s">
+      <c r="I28" s="182" t="s">
         <v>668</v>
       </c>
-      <c r="J28" s="184"/>
-      <c r="L28" s="174" t="s">
+      <c r="J28" s="183"/>
+      <c r="L28" s="173" t="s">
         <v>695</v>
       </c>
-      <c r="M28" s="174"/>
-      <c r="N28" s="174"/>
+      <c r="M28" s="173"/>
+      <c r="N28" s="173"/>
     </row>
     <row r="29" spans="1:14" ht="31.5" thickBot="1">
       <c r="A29" s="81">
@@ -17102,29 +17279,29 @@
       <c r="B29" s="70" t="s">
         <v>625</v>
       </c>
-      <c r="C29" s="177" t="s">
+      <c r="C29" s="176" t="s">
         <v>626</v>
       </c>
-      <c r="D29" s="178"/>
+      <c r="D29" s="177"/>
       <c r="E29" s="69" t="s">
         <v>647</v>
       </c>
-      <c r="F29" s="183" t="s">
+      <c r="F29" s="182" t="s">
         <v>648</v>
       </c>
-      <c r="G29" s="184"/>
+      <c r="G29" s="183"/>
       <c r="H29" s="70" t="s">
         <v>669</v>
       </c>
-      <c r="I29" s="187" t="s">
+      <c r="I29" s="186" t="s">
         <v>670</v>
       </c>
-      <c r="J29" s="188"/>
-      <c r="L29" s="173" t="s">
+      <c r="J29" s="187"/>
+      <c r="L29" s="172" t="s">
         <v>696</v>
       </c>
-      <c r="M29" s="173"/>
-      <c r="N29" s="173"/>
+      <c r="M29" s="172"/>
+      <c r="N29" s="172"/>
     </row>
     <row r="30" spans="1:14" ht="15.75" thickBot="1">
       <c r="A30" s="81">
@@ -17133,29 +17310,29 @@
       <c r="B30" s="69" t="s">
         <v>627</v>
       </c>
-      <c r="C30" s="183" t="s">
+      <c r="C30" s="182" t="s">
         <v>628</v>
       </c>
-      <c r="D30" s="184"/>
+      <c r="D30" s="183"/>
       <c r="E30" s="70" t="s">
         <v>649</v>
       </c>
-      <c r="F30" s="177" t="s">
+      <c r="F30" s="176" t="s">
         <v>650</v>
       </c>
-      <c r="G30" s="178"/>
+      <c r="G30" s="177"/>
       <c r="H30" s="69" t="s">
         <v>671</v>
       </c>
-      <c r="I30" s="183" t="s">
+      <c r="I30" s="182" t="s">
         <v>672</v>
       </c>
-      <c r="J30" s="184"/>
-      <c r="L30" s="174" t="s">
+      <c r="J30" s="183"/>
+      <c r="L30" s="173" t="s">
         <v>697</v>
       </c>
-      <c r="M30" s="174"/>
-      <c r="N30" s="174"/>
+      <c r="M30" s="173"/>
+      <c r="N30" s="173"/>
     </row>
     <row r="31" spans="1:14" ht="17.25" customHeight="1" thickBot="1">
       <c r="A31" s="81">
@@ -17164,29 +17341,29 @@
       <c r="B31" s="70" t="s">
         <v>629</v>
       </c>
-      <c r="C31" s="177" t="s">
+      <c r="C31" s="176" t="s">
         <v>630</v>
       </c>
-      <c r="D31" s="178"/>
+      <c r="D31" s="177"/>
       <c r="E31" s="69" t="s">
         <v>651</v>
       </c>
-      <c r="F31" s="183" t="s">
+      <c r="F31" s="182" t="s">
         <v>652</v>
       </c>
-      <c r="G31" s="184"/>
+      <c r="G31" s="183"/>
       <c r="H31" s="70" t="s">
         <v>673</v>
       </c>
-      <c r="I31" s="177" t="s">
+      <c r="I31" s="176" t="s">
         <v>674</v>
       </c>
-      <c r="J31" s="178"/>
-      <c r="L31" s="173" t="s">
+      <c r="J31" s="177"/>
+      <c r="L31" s="172" t="s">
         <v>698</v>
       </c>
-      <c r="M31" s="173"/>
-      <c r="N31" s="173"/>
+      <c r="M31" s="172"/>
+      <c r="N31" s="172"/>
     </row>
     <row r="32" spans="1:14" ht="43.5" customHeight="1" thickBot="1">
       <c r="A32" s="81">
@@ -17195,29 +17372,29 @@
       <c r="B32" s="69" t="s">
         <v>631</v>
       </c>
-      <c r="C32" s="183" t="s">
+      <c r="C32" s="182" t="s">
         <v>632</v>
       </c>
-      <c r="D32" s="184"/>
+      <c r="D32" s="183"/>
       <c r="E32" s="70" t="s">
         <v>653</v>
       </c>
-      <c r="F32" s="177" t="s">
+      <c r="F32" s="176" t="s">
         <v>654</v>
       </c>
-      <c r="G32" s="178"/>
+      <c r="G32" s="177"/>
       <c r="H32" s="69" t="s">
         <v>675</v>
       </c>
-      <c r="I32" s="183" t="s">
+      <c r="I32" s="182" t="s">
         <v>676</v>
       </c>
-      <c r="J32" s="184"/>
-      <c r="L32" s="174" t="s">
+      <c r="J32" s="183"/>
+      <c r="L32" s="173" t="s">
         <v>699</v>
       </c>
-      <c r="M32" s="174"/>
-      <c r="N32" s="174"/>
+      <c r="M32" s="173"/>
+      <c r="N32" s="173"/>
     </row>
     <row r="33" spans="1:14" ht="31.5" customHeight="1" thickBot="1">
       <c r="A33" s="81">
@@ -17226,29 +17403,29 @@
       <c r="B33" s="70" t="s">
         <v>633</v>
       </c>
-      <c r="C33" s="177" t="s">
+      <c r="C33" s="176" t="s">
         <v>634</v>
       </c>
-      <c r="D33" s="178"/>
+      <c r="D33" s="177"/>
       <c r="E33" s="69" t="s">
         <v>655</v>
       </c>
-      <c r="F33" s="183" t="s">
+      <c r="F33" s="182" t="s">
         <v>656</v>
       </c>
-      <c r="G33" s="184"/>
+      <c r="G33" s="183"/>
       <c r="H33" s="70" t="s">
         <v>677</v>
       </c>
-      <c r="I33" s="185" t="s">
+      <c r="I33" s="184" t="s">
         <v>678</v>
       </c>
-      <c r="J33" s="186"/>
-      <c r="L33" s="173" t="s">
+      <c r="J33" s="185"/>
+      <c r="L33" s="172" t="s">
         <v>700</v>
       </c>
-      <c r="M33" s="173"/>
-      <c r="N33" s="173"/>
+      <c r="M33" s="172"/>
+      <c r="N33" s="172"/>
     </row>
     <row r="34" spans="1:14" ht="28.5" customHeight="1" thickBot="1">
       <c r="A34" s="81">
@@ -17257,29 +17434,29 @@
       <c r="B34" s="69" t="s">
         <v>635</v>
       </c>
-      <c r="C34" s="183" t="s">
+      <c r="C34" s="182" t="s">
         <v>636</v>
       </c>
-      <c r="D34" s="184"/>
+      <c r="D34" s="183"/>
       <c r="E34" s="70" t="s">
         <v>657</v>
       </c>
-      <c r="F34" s="177" t="s">
+      <c r="F34" s="176" t="s">
         <v>658</v>
       </c>
-      <c r="G34" s="178"/>
+      <c r="G34" s="177"/>
       <c r="H34" s="69" t="s">
         <v>679</v>
       </c>
-      <c r="I34" s="181" t="s">
+      <c r="I34" s="180" t="s">
         <v>680</v>
       </c>
-      <c r="J34" s="182"/>
-      <c r="L34" s="174" t="s">
+      <c r="J34" s="181"/>
+      <c r="L34" s="173" t="s">
         <v>701</v>
       </c>
-      <c r="M34" s="174"/>
-      <c r="N34" s="174"/>
+      <c r="M34" s="173"/>
+      <c r="N34" s="173"/>
     </row>
     <row r="35" spans="1:14" ht="31.5" customHeight="1" thickBot="1">
       <c r="A35" s="81">
@@ -17288,29 +17465,29 @@
       <c r="B35" s="70" t="s">
         <v>637</v>
       </c>
-      <c r="C35" s="177" t="s">
+      <c r="C35" s="176" t="s">
         <v>638</v>
       </c>
-      <c r="D35" s="178"/>
+      <c r="D35" s="177"/>
       <c r="E35" s="69" t="s">
         <v>659</v>
       </c>
-      <c r="F35" s="183" t="s">
+      <c r="F35" s="182" t="s">
         <v>660</v>
       </c>
-      <c r="G35" s="184"/>
+      <c r="G35" s="183"/>
       <c r="H35" s="77" t="s">
         <v>681</v>
       </c>
-      <c r="I35" s="177" t="s">
+      <c r="I35" s="176" t="s">
         <v>682</v>
       </c>
-      <c r="J35" s="178"/>
-      <c r="L35" s="173" t="s">
+      <c r="J35" s="177"/>
+      <c r="L35" s="172" t="s">
         <v>702</v>
       </c>
-      <c r="M35" s="173"/>
-      <c r="N35" s="173"/>
+      <c r="M35" s="172"/>
+      <c r="N35" s="172"/>
     </row>
     <row r="36" spans="1:14" ht="60.75" thickBot="1">
       <c r="A36" s="81">
@@ -17319,17 +17496,17 @@
       <c r="B36" s="69" t="s">
         <v>639</v>
       </c>
-      <c r="C36" s="183" t="s">
+      <c r="C36" s="182" t="s">
         <v>640</v>
       </c>
-      <c r="D36" s="184"/>
+      <c r="D36" s="183"/>
       <c r="E36" s="70" t="s">
         <v>661</v>
       </c>
-      <c r="F36" s="177" t="s">
+      <c r="F36" s="176" t="s">
         <v>662</v>
       </c>
-      <c r="G36" s="178"/>
+      <c r="G36" s="177"/>
       <c r="H36" s="78"/>
       <c r="I36" s="71" t="s">
         <v>683</v>
@@ -17337,11 +17514,11 @@
       <c r="J36" s="72" t="s">
         <v>684</v>
       </c>
-      <c r="L36" s="174" t="s">
+      <c r="L36" s="173" t="s">
         <v>703</v>
       </c>
-      <c r="M36" s="174"/>
-      <c r="N36" s="174"/>
+      <c r="M36" s="173"/>
+      <c r="N36" s="173"/>
     </row>
     <row r="37" spans="1:14" ht="75.75" thickBot="1">
       <c r="A37" s="81">
@@ -17350,17 +17527,17 @@
       <c r="B37" s="70" t="s">
         <v>641</v>
       </c>
-      <c r="C37" s="177" t="s">
+      <c r="C37" s="176" t="s">
         <v>642</v>
       </c>
-      <c r="D37" s="178"/>
+      <c r="D37" s="177"/>
       <c r="E37" s="69" t="s">
         <v>663</v>
       </c>
-      <c r="F37" s="183" t="s">
+      <c r="F37" s="182" t="s">
         <v>664</v>
       </c>
-      <c r="G37" s="184"/>
+      <c r="G37" s="183"/>
       <c r="H37" s="78"/>
       <c r="I37" s="73" t="s">
         <v>685</v>
@@ -17376,17 +17553,17 @@
       <c r="B38" s="69" t="s">
         <v>643</v>
       </c>
-      <c r="C38" s="183" t="s">
+      <c r="C38" s="182" t="s">
         <v>644</v>
       </c>
-      <c r="D38" s="184"/>
+      <c r="D38" s="183"/>
       <c r="E38" s="70" t="s">
         <v>665</v>
       </c>
-      <c r="F38" s="177" t="s">
+      <c r="F38" s="176" t="s">
         <v>666</v>
       </c>
-      <c r="G38" s="178"/>
+      <c r="G38" s="177"/>
       <c r="H38" s="78"/>
       <c r="I38" s="75" t="s">
         <v>687</v>
@@ -17402,22 +17579,22 @@
       <c r="B39" s="70" t="s">
         <v>692</v>
       </c>
-      <c r="C39" s="185" t="s">
+      <c r="C39" s="184" t="s">
         <v>693</v>
       </c>
-      <c r="D39" s="186"/>
+      <c r="D39" s="185"/>
       <c r="E39" s="69" t="s">
         <v>690</v>
       </c>
-      <c r="F39" s="181" t="s">
+      <c r="F39" s="180" t="s">
         <v>691</v>
       </c>
-      <c r="G39" s="182"/>
+      <c r="G39" s="181"/>
       <c r="H39" s="79"/>
-      <c r="I39" s="179" t="s">
+      <c r="I39" s="178" t="s">
         <v>689</v>
       </c>
-      <c r="J39" s="180"/>
+      <c r="J39" s="179"/>
     </row>
     <row r="40" spans="1:14" ht="58.5" customHeight="1"/>
     <row r="41" spans="1:14">
@@ -17596,7 +17773,7 @@
       <c r="B49" s="85" t="s">
         <v>429</v>
       </c>
-      <c r="C49" s="117" t="s">
+      <c r="C49" s="116" t="s">
         <v>752</v>
       </c>
       <c r="D49" s="85" t="s">
@@ -18277,7 +18454,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q46"/>
+  <dimension ref="A1:Q50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.140625" customWidth="1"/>
@@ -18288,7 +18465,7 @@
     <col min="6" max="6" width="31.85546875" customWidth="1"/>
     <col min="7" max="7" width="34.42578125" customWidth="1"/>
     <col min="8" max="8" width="10.42578125" customWidth="1"/>
-    <col min="9" max="9" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" style="56" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.85546875" style="56" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="27.140625" customWidth="1"/>
@@ -18336,16 +18513,16 @@
       </c>
     </row>
     <row r="2" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A2" s="190" t="s">
+      <c r="A2" s="189" t="s">
         <v>504</v>
       </c>
-      <c r="B2" s="199" t="s">
+      <c r="B2" s="198" t="s">
         <v>506</v>
       </c>
-      <c r="C2" s="190" t="s">
+      <c r="C2" s="189" t="s">
         <v>508</v>
       </c>
-      <c r="D2" s="190" t="s">
+      <c r="D2" s="189" t="s">
         <v>556</v>
       </c>
       <c r="E2" s="8"/>
@@ -18358,7 +18535,7 @@
       <c r="H2" s="10">
         <v>1</v>
       </c>
-      <c r="I2" s="210">
+      <c r="I2" s="209">
         <v>44043</v>
       </c>
       <c r="J2" s="10"/>
@@ -18368,10 +18545,10 @@
       </c>
     </row>
     <row r="3" spans="1:17">
-      <c r="A3" s="165"/>
-      <c r="B3" s="200"/>
-      <c r="C3" s="191"/>
-      <c r="D3" s="191"/>
+      <c r="A3" s="164"/>
+      <c r="B3" s="199"/>
+      <c r="C3" s="190"/>
+      <c r="D3" s="190"/>
       <c r="E3" s="11"/>
       <c r="F3" s="9" t="s">
         <v>310</v>
@@ -18382,7 +18559,7 @@
       <c r="H3" s="12">
         <v>2</v>
       </c>
-      <c r="I3" s="210">
+      <c r="I3" s="209">
         <v>44074</v>
       </c>
       <c r="J3" s="10"/>
@@ -18392,10 +18569,10 @@
       </c>
     </row>
     <row r="4" spans="1:17">
-      <c r="A4" s="165"/>
-      <c r="B4" s="200"/>
-      <c r="C4" s="191"/>
-      <c r="D4" s="192"/>
+      <c r="A4" s="164"/>
+      <c r="B4" s="199"/>
+      <c r="C4" s="190"/>
+      <c r="D4" s="191"/>
       <c r="E4" s="11"/>
       <c r="F4" s="9" t="s">
         <v>311</v>
@@ -18406,17 +18583,17 @@
       <c r="H4" s="12" t="s">
         <v>963</v>
       </c>
-      <c r="I4" s="210"/>
+      <c r="I4" s="209"/>
       <c r="J4" s="10"/>
       <c r="K4" s="10"/>
-      <c r="M4" t="s">
-        <v>1294</v>
+      <c r="M4" s="218" t="s">
+        <v>1299</v>
       </c>
     </row>
     <row r="5" spans="1:17">
-      <c r="A5" s="165"/>
-      <c r="B5" s="200"/>
-      <c r="C5" s="192"/>
+      <c r="A5" s="164"/>
+      <c r="B5" s="199"/>
+      <c r="C5" s="191"/>
       <c r="D5" s="46" t="s">
         <v>555</v>
       </c>
@@ -18430,7 +18607,7 @@
       <c r="H5" s="12" t="s">
         <v>960</v>
       </c>
-      <c r="I5" s="210">
+      <c r="I5" s="209">
         <v>44043</v>
       </c>
       <c r="J5" s="10" t="s">
@@ -18439,12 +18616,12 @@
       <c r="K5" s="10"/>
     </row>
     <row r="6" spans="1:17">
-      <c r="A6" s="165"/>
-      <c r="B6" s="200"/>
-      <c r="C6" s="190" t="s">
+      <c r="A6" s="164"/>
+      <c r="B6" s="199"/>
+      <c r="C6" s="189" t="s">
         <v>507</v>
       </c>
-      <c r="D6" s="190" t="s">
+      <c r="D6" s="189" t="s">
         <v>511</v>
       </c>
       <c r="E6" s="11"/>
@@ -18457,17 +18634,17 @@
       <c r="H6" s="12" t="s">
         <v>961</v>
       </c>
-      <c r="I6" s="210">
+      <c r="I6" s="209">
         <v>44043</v>
       </c>
       <c r="J6" s="10"/>
       <c r="K6" s="10"/>
     </row>
     <row r="7" spans="1:17">
-      <c r="A7" s="165"/>
-      <c r="B7" s="200"/>
-      <c r="C7" s="191"/>
-      <c r="D7" s="191"/>
+      <c r="A7" s="164"/>
+      <c r="B7" s="199"/>
+      <c r="C7" s="190"/>
+      <c r="D7" s="190"/>
       <c r="E7" s="11"/>
       <c r="F7" s="9" t="s">
         <v>313</v>
@@ -18478,17 +18655,17 @@
       <c r="H7" s="12">
         <v>1</v>
       </c>
-      <c r="I7" s="210">
+      <c r="I7" s="209">
         <v>44043</v>
       </c>
       <c r="J7" s="10"/>
       <c r="K7" s="10"/>
     </row>
     <row r="8" spans="1:17">
-      <c r="A8" s="165"/>
-      <c r="B8" s="200"/>
-      <c r="C8" s="191"/>
-      <c r="D8" s="191"/>
+      <c r="A8" s="164"/>
+      <c r="B8" s="199"/>
+      <c r="C8" s="190"/>
+      <c r="D8" s="190"/>
       <c r="E8" s="11"/>
       <c r="F8" s="9" t="s">
         <v>314</v>
@@ -18499,17 +18676,17 @@
       <c r="H8" s="12">
         <v>1</v>
       </c>
-      <c r="I8" s="210">
+      <c r="I8" s="209">
         <v>44043</v>
       </c>
       <c r="J8" s="10"/>
       <c r="K8" s="10"/>
     </row>
     <row r="9" spans="1:17">
-      <c r="A9" s="165"/>
-      <c r="B9" s="200"/>
-      <c r="C9" s="191"/>
-      <c r="D9" s="191"/>
+      <c r="A9" s="164"/>
+      <c r="B9" s="199"/>
+      <c r="C9" s="190"/>
+      <c r="D9" s="190"/>
       <c r="E9" s="8"/>
       <c r="F9" s="9" t="s">
         <v>345</v>
@@ -18520,17 +18697,17 @@
       <c r="H9" s="10">
         <v>1</v>
       </c>
-      <c r="I9" s="210">
+      <c r="I9" s="209">
         <v>44043</v>
       </c>
       <c r="J9" s="10"/>
       <c r="K9" s="10"/>
     </row>
     <row r="10" spans="1:17">
-      <c r="A10" s="165"/>
-      <c r="B10" s="200"/>
-      <c r="C10" s="191"/>
-      <c r="D10" s="191"/>
+      <c r="A10" s="164"/>
+      <c r="B10" s="199"/>
+      <c r="C10" s="190"/>
+      <c r="D10" s="190"/>
       <c r="E10" s="8"/>
       <c r="F10" s="9" t="s">
         <v>346</v>
@@ -18541,17 +18718,17 @@
       <c r="H10" s="10">
         <v>1</v>
       </c>
-      <c r="I10" s="210">
+      <c r="I10" s="209">
         <v>44043</v>
       </c>
       <c r="J10" s="10"/>
       <c r="K10" s="10"/>
     </row>
     <row r="11" spans="1:17">
-      <c r="A11" s="165"/>
-      <c r="B11" s="200"/>
-      <c r="C11" s="191"/>
-      <c r="D11" s="191"/>
+      <c r="A11" s="164"/>
+      <c r="B11" s="199"/>
+      <c r="C11" s="190"/>
+      <c r="D11" s="190"/>
       <c r="E11" s="8"/>
       <c r="F11" s="9" t="s">
         <v>315</v>
@@ -18562,17 +18739,17 @@
       <c r="H11" s="10">
         <v>1</v>
       </c>
-      <c r="I11" s="210">
+      <c r="I11" s="209">
         <v>44043</v>
       </c>
       <c r="J11" s="10"/>
       <c r="K11" s="10"/>
     </row>
     <row r="12" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A12" s="165"/>
-      <c r="B12" s="200"/>
-      <c r="C12" s="191"/>
-      <c r="D12" s="191"/>
+      <c r="A12" s="164"/>
+      <c r="B12" s="199"/>
+      <c r="C12" s="190"/>
+      <c r="D12" s="190"/>
       <c r="E12" s="8"/>
       <c r="F12" s="9" t="s">
         <v>347</v>
@@ -18583,17 +18760,17 @@
       <c r="H12" s="10">
         <v>1</v>
       </c>
-      <c r="I12" s="210">
+      <c r="I12" s="209">
         <v>44043</v>
       </c>
       <c r="J12" s="10"/>
       <c r="K12" s="10"/>
     </row>
     <row r="13" spans="1:17" ht="30">
-      <c r="A13" s="165"/>
-      <c r="B13" s="200"/>
-      <c r="C13" s="191"/>
-      <c r="D13" s="191"/>
+      <c r="A13" s="164"/>
+      <c r="B13" s="199"/>
+      <c r="C13" s="190"/>
+      <c r="D13" s="190"/>
       <c r="E13" s="11"/>
       <c r="F13" s="9" t="s">
         <v>316</v>
@@ -18604,20 +18781,20 @@
       <c r="H13" s="12">
         <v>3</v>
       </c>
-      <c r="I13" s="210"/>
+      <c r="I13" s="209"/>
       <c r="J13" s="10" t="s">
         <v>563</v>
       </c>
       <c r="K13" s="10"/>
-      <c r="O13" s="102" t="s">
+      <c r="O13" s="101" t="s">
         <v>858</v>
       </c>
     </row>
     <row r="14" spans="1:17">
-      <c r="A14" s="165"/>
-      <c r="B14" s="200"/>
-      <c r="C14" s="191"/>
-      <c r="D14" s="192"/>
+      <c r="A14" s="164"/>
+      <c r="B14" s="199"/>
+      <c r="C14" s="190"/>
+      <c r="D14" s="191"/>
       <c r="E14" s="11"/>
       <c r="F14" s="9" t="s">
         <v>318</v>
@@ -18625,19 +18802,19 @@
       <c r="G14" s="9" t="s">
         <v>354</v>
       </c>
-      <c r="H14" s="12">
-        <v>2</v>
-      </c>
-      <c r="I14" s="210">
-        <v>44074</v>
+      <c r="H14" s="12" t="s">
+        <v>963</v>
+      </c>
+      <c r="I14" s="209" t="s">
+        <v>1298</v>
       </c>
       <c r="J14" s="10"/>
       <c r="K14" s="10"/>
     </row>
     <row r="15" spans="1:17" ht="30">
-      <c r="A15" s="165"/>
-      <c r="B15" s="200"/>
-      <c r="C15" s="191"/>
+      <c r="A15" s="164"/>
+      <c r="B15" s="199"/>
+      <c r="C15" s="190"/>
       <c r="D15" s="22" t="s">
         <v>512</v>
       </c>
@@ -18651,16 +18828,16 @@
       <c r="H15" s="12">
         <v>1</v>
       </c>
-      <c r="I15" s="210">
+      <c r="I15" s="209">
         <v>44043</v>
       </c>
       <c r="J15" s="10"/>
       <c r="K15" s="10"/>
-      <c r="M15" s="195" t="s">
+      <c r="M15" s="194" t="s">
         <v>851</v>
       </c>
-      <c r="N15" s="196"/>
-      <c r="O15" s="115" t="s">
+      <c r="N15" s="195"/>
+      <c r="O15" s="114" t="s">
         <v>1258</v>
       </c>
       <c r="P15" s="91"/>
@@ -18669,12 +18846,12 @@
       </c>
     </row>
     <row r="16" spans="1:17" ht="30">
-      <c r="A16" s="165"/>
-      <c r="B16" s="200"/>
-      <c r="C16" s="190" t="s">
+      <c r="A16" s="164"/>
+      <c r="B16" s="199"/>
+      <c r="C16" s="189" t="s">
         <v>509</v>
       </c>
-      <c r="D16" s="190" t="s">
+      <c r="D16" s="189" t="s">
         <v>513</v>
       </c>
       <c r="E16" s="11"/>
@@ -18687,7 +18864,7 @@
       <c r="H16" s="12">
         <v>1</v>
       </c>
-      <c r="I16" s="210">
+      <c r="I16" s="209">
         <v>44043</v>
       </c>
       <c r="J16" s="10"/>
@@ -18701,7 +18878,7 @@
       <c r="O16" s="99" t="s">
         <v>1259</v>
       </c>
-      <c r="P16" s="103">
+      <c r="P16" s="102">
         <v>1</v>
       </c>
       <c r="Q16" s="91" t="s">
@@ -18709,10 +18886,10 @@
       </c>
     </row>
     <row r="17" spans="1:17">
-      <c r="A17" s="165"/>
-      <c r="B17" s="200"/>
-      <c r="C17" s="191"/>
-      <c r="D17" s="191"/>
+      <c r="A17" s="164"/>
+      <c r="B17" s="199"/>
+      <c r="C17" s="190"/>
+      <c r="D17" s="190"/>
       <c r="E17" s="19"/>
       <c r="F17" s="9" t="s">
         <v>364</v>
@@ -18723,7 +18900,7 @@
       <c r="H17" s="12">
         <v>1</v>
       </c>
-      <c r="I17" s="210">
+      <c r="I17" s="209">
         <v>44043</v>
       </c>
       <c r="J17" s="10"/>
@@ -18737,15 +18914,15 @@
       <c r="O17" s="99" t="s">
         <v>1263</v>
       </c>
-      <c r="P17" s="104">
+      <c r="P17" s="103">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:17">
-      <c r="A18" s="165"/>
-      <c r="B18" s="200"/>
-      <c r="C18" s="191"/>
-      <c r="D18" s="191"/>
+      <c r="A18" s="164"/>
+      <c r="B18" s="199"/>
+      <c r="C18" s="190"/>
+      <c r="D18" s="190"/>
       <c r="E18" s="19"/>
       <c r="F18" s="48" t="s">
         <v>559</v>
@@ -18756,7 +18933,7 @@
       <c r="H18" s="10">
         <v>1</v>
       </c>
-      <c r="I18" s="210">
+      <c r="I18" s="209">
         <v>44043</v>
       </c>
       <c r="J18" s="10" t="s">
@@ -18772,15 +18949,15 @@
       <c r="O18" s="99" t="s">
         <v>1263</v>
       </c>
-      <c r="P18" s="104">
+      <c r="P18" s="103">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:17">
-      <c r="A19" s="165"/>
-      <c r="B19" s="200"/>
-      <c r="C19" s="191"/>
-      <c r="D19" s="191"/>
+      <c r="A19" s="164"/>
+      <c r="B19" s="199"/>
+      <c r="C19" s="190"/>
+      <c r="D19" s="190"/>
       <c r="E19" s="8"/>
       <c r="F19" s="9" t="s">
         <v>332</v>
@@ -18791,7 +18968,7 @@
       <c r="H19" s="10">
         <v>1</v>
       </c>
-      <c r="I19" s="210">
+      <c r="I19" s="209">
         <v>44043</v>
       </c>
       <c r="J19" s="10"/>
@@ -18805,16 +18982,16 @@
       <c r="O19" s="99" t="s">
         <v>1263</v>
       </c>
-      <c r="P19" s="105">
+      <c r="P19" s="104">
         <v>1</v>
       </c>
       <c r="Q19" s="91"/>
     </row>
     <row r="20" spans="1:17">
-      <c r="A20" s="165"/>
-      <c r="B20" s="200"/>
-      <c r="C20" s="191"/>
-      <c r="D20" s="191"/>
+      <c r="A20" s="164"/>
+      <c r="B20" s="199"/>
+      <c r="C20" s="190"/>
+      <c r="D20" s="190"/>
       <c r="E20" s="8"/>
       <c r="F20" s="9" t="s">
         <v>333</v>
@@ -18825,7 +19002,7 @@
       <c r="H20" s="10">
         <v>1</v>
       </c>
-      <c r="I20" s="210">
+      <c r="I20" s="209">
         <v>44043</v>
       </c>
       <c r="J20" s="10"/>
@@ -18839,16 +19016,16 @@
       <c r="O20" s="99" t="s">
         <v>1263</v>
       </c>
-      <c r="P20" s="99">
+      <c r="P20" s="103">
         <v>2</v>
       </c>
       <c r="Q20" s="91"/>
     </row>
     <row r="21" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A21" s="165"/>
-      <c r="B21" s="200"/>
-      <c r="C21" s="191"/>
-      <c r="D21" s="191"/>
+      <c r="A21" s="164"/>
+      <c r="B21" s="199"/>
+      <c r="C21" s="190"/>
+      <c r="D21" s="190"/>
       <c r="E21" s="14"/>
       <c r="F21" s="9" t="s">
         <v>334</v>
@@ -18859,7 +19036,7 @@
       <c r="H21" s="16">
         <v>3</v>
       </c>
-      <c r="I21" s="210"/>
+      <c r="I21" s="209"/>
       <c r="J21" s="10" t="s">
         <v>563</v>
       </c>
@@ -18873,7 +19050,7 @@
       <c r="O21" s="99" t="s">
         <v>1269</v>
       </c>
-      <c r="P21" s="103">
+      <c r="P21" s="102">
         <v>1</v>
       </c>
       <c r="Q21" s="91" t="s">
@@ -18881,10 +19058,10 @@
       </c>
     </row>
     <row r="22" spans="1:17">
-      <c r="A22" s="165"/>
-      <c r="B22" s="200"/>
-      <c r="C22" s="191"/>
-      <c r="D22" s="191"/>
+      <c r="A22" s="164"/>
+      <c r="B22" s="199"/>
+      <c r="C22" s="190"/>
+      <c r="D22" s="190"/>
       <c r="E22" s="14"/>
       <c r="F22" s="9" t="s">
         <v>335</v>
@@ -18895,12 +19072,12 @@
       <c r="H22" s="16">
         <v>1</v>
       </c>
-      <c r="I22" s="210">
+      <c r="I22" s="209">
         <v>44043</v>
       </c>
       <c r="J22" s="10"/>
       <c r="K22" s="10"/>
-      <c r="M22" s="101" t="s">
+      <c r="M22" s="100" t="s">
         <v>855</v>
       </c>
       <c r="N22" s="98" t="s">
@@ -18909,7 +19086,7 @@
       <c r="O22" s="99" t="s">
         <v>81</v>
       </c>
-      <c r="P22" s="104">
+      <c r="P22" s="103">
         <v>1</v>
       </c>
       <c r="Q22" s="91" t="s">
@@ -18917,10 +19094,10 @@
       </c>
     </row>
     <row r="23" spans="1:17">
-      <c r="A23" s="165"/>
-      <c r="B23" s="200"/>
-      <c r="C23" s="191"/>
-      <c r="D23" s="191"/>
+      <c r="A23" s="164"/>
+      <c r="B23" s="199"/>
+      <c r="C23" s="190"/>
+      <c r="D23" s="190"/>
       <c r="E23" s="14"/>
       <c r="F23" s="9" t="s">
         <v>336</v>
@@ -18931,7 +19108,7 @@
       <c r="H23" s="16">
         <v>2</v>
       </c>
-      <c r="I23" s="210">
+      <c r="I23" s="209">
         <v>44074</v>
       </c>
       <c r="J23" s="10"/>
@@ -18945,18 +19122,18 @@
       <c r="O23" s="99" t="s">
         <v>81</v>
       </c>
-      <c r="P23" s="100" t="s">
+      <c r="P23" s="215" t="s">
         <v>962</v>
       </c>
-      <c r="Q23" s="154" t="s">
+      <c r="Q23" s="153" t="s">
         <v>1284</v>
       </c>
     </row>
     <row r="24" spans="1:17">
-      <c r="A24" s="165"/>
-      <c r="B24" s="200"/>
-      <c r="C24" s="191"/>
-      <c r="D24" s="191"/>
+      <c r="A24" s="164"/>
+      <c r="B24" s="199"/>
+      <c r="C24" s="190"/>
+      <c r="D24" s="190"/>
       <c r="E24" s="8"/>
       <c r="F24" s="9" t="s">
         <v>1281</v>
@@ -18967,12 +19144,12 @@
       <c r="H24" s="10">
         <v>2</v>
       </c>
-      <c r="I24" s="210">
+      <c r="I24" s="209">
         <v>44074</v>
       </c>
       <c r="J24" s="10"/>
       <c r="K24" s="10"/>
-      <c r="M24" s="153" t="s">
+      <c r="M24" s="152" t="s">
         <v>1280</v>
       </c>
       <c r="N24" s="98" t="s">
@@ -18981,16 +19158,16 @@
       <c r="O24" s="99" t="s">
         <v>81</v>
       </c>
-      <c r="P24" s="105">
+      <c r="P24" s="104">
         <v>1</v>
       </c>
       <c r="Q24" s="91"/>
     </row>
     <row r="25" spans="1:17">
-      <c r="A25" s="165"/>
-      <c r="B25" s="200"/>
-      <c r="C25" s="191"/>
-      <c r="D25" s="191"/>
+      <c r="A25" s="164"/>
+      <c r="B25" s="199"/>
+      <c r="C25" s="190"/>
+      <c r="D25" s="190"/>
       <c r="E25" s="8"/>
       <c r="F25" s="9" t="s">
         <v>373</v>
@@ -19001,7 +19178,7 @@
       <c r="H25" s="10">
         <v>3</v>
       </c>
-      <c r="I25" s="210"/>
+      <c r="I25" s="209"/>
       <c r="J25" s="10" t="s">
         <v>563</v>
       </c>
@@ -19015,16 +19192,16 @@
       <c r="O25" s="99" t="s">
         <v>1263</v>
       </c>
-      <c r="P25" s="99">
+      <c r="P25" s="103">
         <v>2</v>
       </c>
       <c r="Q25" s="91"/>
     </row>
     <row r="26" spans="1:17">
-      <c r="A26" s="165"/>
-      <c r="B26" s="200"/>
-      <c r="C26" s="191"/>
-      <c r="D26" s="191"/>
+      <c r="A26" s="164"/>
+      <c r="B26" s="199"/>
+      <c r="C26" s="190"/>
+      <c r="D26" s="190"/>
       <c r="E26" s="8"/>
       <c r="F26" s="9" t="s">
         <v>338</v>
@@ -19032,12 +19209,10 @@
       <c r="G26" s="13" t="s">
         <v>375</v>
       </c>
-      <c r="H26" s="10">
-        <v>2</v>
-      </c>
-      <c r="I26" s="210">
-        <v>44074</v>
-      </c>
+      <c r="H26" s="10" t="s">
+        <v>963</v>
+      </c>
+      <c r="I26" s="209"/>
       <c r="J26" s="10"/>
       <c r="K26" s="10"/>
       <c r="M26" s="99" t="s">
@@ -19055,10 +19230,10 @@
       <c r="Q26" s="91"/>
     </row>
     <row r="27" spans="1:17">
-      <c r="A27" s="165"/>
-      <c r="B27" s="200"/>
-      <c r="C27" s="191"/>
-      <c r="D27" s="191"/>
+      <c r="A27" s="164"/>
+      <c r="B27" s="199"/>
+      <c r="C27" s="190"/>
+      <c r="D27" s="190"/>
       <c r="E27" s="8"/>
       <c r="F27" s="9" t="s">
         <v>339</v>
@@ -19066,10 +19241,12 @@
       <c r="G27" s="13" t="s">
         <v>372</v>
       </c>
-      <c r="H27" s="120" t="s">
-        <v>962</v>
-      </c>
-      <c r="I27" s="210"/>
+      <c r="H27" s="119" t="s">
+        <v>1297</v>
+      </c>
+      <c r="I27" s="209" t="s">
+        <v>1332</v>
+      </c>
       <c r="J27" s="10"/>
       <c r="K27" s="10"/>
       <c r="M27" s="99" t="s">
@@ -19087,12 +19264,12 @@
       <c r="Q27" s="91"/>
     </row>
     <row r="28" spans="1:17">
-      <c r="A28" s="165"/>
-      <c r="B28" s="200"/>
-      <c r="C28" s="191"/>
-      <c r="D28" s="191"/>
+      <c r="A28" s="164"/>
+      <c r="B28" s="199"/>
+      <c r="C28" s="190"/>
+      <c r="D28" s="190"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="122" t="s">
+      <c r="F28" s="121" t="s">
         <v>965</v>
       </c>
       <c r="G28" s="13" t="s">
@@ -19101,7 +19278,7 @@
       <c r="H28" s="10">
         <v>1</v>
       </c>
-      <c r="I28" s="210">
+      <c r="I28" s="209">
         <v>44043</v>
       </c>
       <c r="J28" s="10"/>
@@ -19121,10 +19298,10 @@
       <c r="Q28" s="91"/>
     </row>
     <row r="29" spans="1:17">
-      <c r="A29" s="165"/>
-      <c r="B29" s="200"/>
-      <c r="C29" s="191"/>
-      <c r="D29" s="191"/>
+      <c r="A29" s="164"/>
+      <c r="B29" s="199"/>
+      <c r="C29" s="190"/>
+      <c r="D29" s="190"/>
       <c r="E29" s="8"/>
       <c r="F29" s="9" t="s">
         <v>955</v>
@@ -19132,11 +19309,11 @@
       <c r="G29" s="9" t="s">
         <v>956</v>
       </c>
-      <c r="H29" s="16">
-        <v>2</v>
-      </c>
-      <c r="I29" s="210">
-        <v>44074</v>
+      <c r="H29" s="16" t="s">
+        <v>963</v>
+      </c>
+      <c r="I29" s="209" t="s">
+        <v>1332</v>
       </c>
       <c r="J29" s="10"/>
       <c r="K29" s="10" t="s">
@@ -19144,10 +19321,10 @@
       </c>
     </row>
     <row r="30" spans="1:17">
-      <c r="A30" s="165"/>
-      <c r="B30" s="200"/>
-      <c r="C30" s="191"/>
-      <c r="D30" s="192"/>
+      <c r="A30" s="164"/>
+      <c r="B30" s="199"/>
+      <c r="C30" s="190"/>
+      <c r="D30" s="191"/>
       <c r="E30" s="8"/>
       <c r="F30" s="49" t="s">
         <v>323</v>
@@ -19155,18 +19332,20 @@
       <c r="G30" s="49" t="s">
         <v>357</v>
       </c>
-      <c r="H30" s="114">
+      <c r="H30" s="113">
         <v>3</v>
       </c>
-      <c r="I30" s="210"/>
+      <c r="I30" s="209" t="s">
+        <v>1332</v>
+      </c>
       <c r="J30" s="10"/>
-      <c r="K30" s="193" t="s">
+      <c r="K30" s="192" t="s">
         <v>959</v>
       </c>
-      <c r="M30" s="102" t="s">
+      <c r="M30" s="101" t="s">
         <v>1261</v>
       </c>
-      <c r="N30" s="102" t="s">
+      <c r="N30" s="101" t="s">
         <v>1262</v>
       </c>
       <c r="O30" t="s">
@@ -19177,10 +19356,10 @@
       </c>
     </row>
     <row r="31" spans="1:17">
-      <c r="A31" s="165"/>
-      <c r="B31" s="200"/>
-      <c r="C31" s="191"/>
-      <c r="D31" s="190" t="s">
+      <c r="A31" s="164"/>
+      <c r="B31" s="199"/>
+      <c r="C31" s="190"/>
+      <c r="D31" s="189" t="s">
         <v>518</v>
       </c>
       <c r="E31" s="8"/>
@@ -19193,17 +19372,17 @@
       <c r="H31" s="16">
         <v>1</v>
       </c>
-      <c r="I31" s="210">
+      <c r="I31" s="209">
         <v>44043</v>
       </c>
       <c r="J31" s="10"/>
-      <c r="K31" s="197"/>
+      <c r="K31" s="196"/>
     </row>
     <row r="32" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A32" s="165"/>
-      <c r="B32" s="200"/>
-      <c r="C32" s="191"/>
-      <c r="D32" s="191"/>
+      <c r="A32" s="164"/>
+      <c r="B32" s="199"/>
+      <c r="C32" s="190"/>
+      <c r="D32" s="190"/>
       <c r="E32" s="8"/>
       <c r="F32" s="9" t="s">
         <v>325</v>
@@ -19214,20 +19393,20 @@
       <c r="H32" s="16">
         <v>1</v>
       </c>
-      <c r="I32" s="210">
+      <c r="I32" s="209">
         <v>44043</v>
       </c>
       <c r="J32" s="10"/>
-      <c r="K32" s="197"/>
-      <c r="M32" s="151" t="s">
+      <c r="K32" s="196"/>
+      <c r="M32" s="150" t="s">
         <v>1277</v>
       </c>
     </row>
     <row r="33" spans="1:15" ht="16.5" customHeight="1">
-      <c r="A33" s="165"/>
-      <c r="B33" s="200"/>
-      <c r="C33" s="191"/>
-      <c r="D33" s="191"/>
+      <c r="A33" s="164"/>
+      <c r="B33" s="199"/>
+      <c r="C33" s="190"/>
+      <c r="D33" s="190"/>
       <c r="E33" s="8"/>
       <c r="F33" s="9" t="s">
         <v>957</v>
@@ -19238,14 +19417,14 @@
       <c r="H33" s="16">
         <v>2</v>
       </c>
-      <c r="I33" s="210">
+      <c r="I33" s="209">
         <v>44043</v>
       </c>
       <c r="J33" s="10" t="s">
         <v>954</v>
       </c>
-      <c r="K33" s="198"/>
-      <c r="M33" s="152" t="s">
+      <c r="K33" s="197"/>
+      <c r="M33" s="151" t="s">
         <v>1278</v>
       </c>
       <c r="N33" s="5" t="s">
@@ -19256,10 +19435,10 @@
       </c>
     </row>
     <row r="34" spans="1:15" ht="16.5" customHeight="1">
-      <c r="A34" s="165"/>
-      <c r="B34" s="200"/>
-      <c r="C34" s="191"/>
-      <c r="D34" s="191"/>
+      <c r="A34" s="164"/>
+      <c r="B34" s="199"/>
+      <c r="C34" s="190"/>
+      <c r="D34" s="190"/>
       <c r="E34" s="8"/>
       <c r="F34" s="9" t="s">
         <v>1275</v>
@@ -19267,10 +19446,10 @@
       <c r="G34" s="9" t="s">
         <v>1276</v>
       </c>
-      <c r="H34" s="119">
+      <c r="H34" s="118">
         <v>2</v>
       </c>
-      <c r="I34" s="210">
+      <c r="I34" s="209">
         <v>44074</v>
       </c>
       <c r="J34" s="10"/>
@@ -19279,10 +19458,10 @@
       </c>
     </row>
     <row r="35" spans="1:15">
-      <c r="A35" s="165"/>
-      <c r="B35" s="200"/>
-      <c r="C35" s="192"/>
-      <c r="D35" s="192"/>
+      <c r="A35" s="164"/>
+      <c r="B35" s="199"/>
+      <c r="C35" s="191"/>
+      <c r="D35" s="191"/>
       <c r="E35" s="8"/>
       <c r="F35" s="49" t="s">
         <v>322</v>
@@ -19293,17 +19472,19 @@
       <c r="H35" s="50">
         <v>3</v>
       </c>
-      <c r="I35" s="210"/>
+      <c r="I35" s="209" t="s">
+        <v>1332</v>
+      </c>
       <c r="J35" s="10"/>
       <c r="K35" s="10"/>
     </row>
     <row r="36" spans="1:15">
-      <c r="A36" s="165"/>
-      <c r="B36" s="200"/>
-      <c r="C36" s="190" t="s">
+      <c r="A36" s="164"/>
+      <c r="B36" s="199"/>
+      <c r="C36" s="189" t="s">
         <v>340</v>
       </c>
-      <c r="D36" s="190" t="s">
+      <c r="D36" s="189" t="s">
         <v>517</v>
       </c>
       <c r="E36" s="8"/>
@@ -19316,17 +19497,17 @@
       <c r="H36" s="16">
         <v>1</v>
       </c>
-      <c r="I36" s="210">
+      <c r="I36" s="209">
         <v>44043</v>
       </c>
       <c r="J36" s="10"/>
       <c r="K36" s="10"/>
     </row>
     <row r="37" spans="1:15">
-      <c r="A37" s="165"/>
-      <c r="B37" s="201"/>
-      <c r="C37" s="192"/>
-      <c r="D37" s="192"/>
+      <c r="A37" s="164"/>
+      <c r="B37" s="200"/>
+      <c r="C37" s="191"/>
+      <c r="D37" s="191"/>
       <c r="E37" s="8"/>
       <c r="F37" s="9" t="s">
         <v>331</v>
@@ -19334,15 +19515,15 @@
       <c r="G37" s="9" t="s">
         <v>376</v>
       </c>
-      <c r="H37" s="121" t="s">
+      <c r="H37" s="120" t="s">
         <v>963</v>
       </c>
-      <c r="I37" s="210"/>
+      <c r="I37" s="209"/>
       <c r="J37" s="10"/>
       <c r="K37" s="10"/>
     </row>
     <row r="38" spans="1:15">
-      <c r="A38" s="165"/>
+      <c r="A38" s="164"/>
       <c r="B38" s="29" t="s">
         <v>328</v>
       </c>
@@ -19362,19 +19543,19 @@
       <c r="H38" s="16" t="s">
         <v>330</v>
       </c>
-      <c r="I38" s="210"/>
+      <c r="I38" s="209"/>
       <c r="J38" s="10"/>
       <c r="K38" s="10"/>
     </row>
     <row r="39" spans="1:15" ht="16.5" customHeight="1">
-      <c r="A39" s="165"/>
-      <c r="B39" s="199" t="s">
+      <c r="A39" s="164"/>
+      <c r="B39" s="198" t="s">
         <v>505</v>
       </c>
-      <c r="C39" s="190" t="s">
+      <c r="C39" s="189" t="s">
         <v>510</v>
       </c>
-      <c r="D39" s="190" t="s">
+      <c r="D39" s="189" t="s">
         <v>516</v>
       </c>
       <c r="E39" s="8" t="s">
@@ -19389,15 +19570,17 @@
       <c r="H39" s="10">
         <v>2</v>
       </c>
-      <c r="I39" s="210"/>
+      <c r="I39" s="209" t="s">
+        <v>1331</v>
+      </c>
       <c r="J39" s="10"/>
       <c r="K39" s="10"/>
     </row>
     <row r="40" spans="1:15" ht="16.5" customHeight="1">
-      <c r="A40" s="165"/>
-      <c r="B40" s="200"/>
-      <c r="C40" s="165"/>
-      <c r="D40" s="165"/>
+      <c r="A40" s="164"/>
+      <c r="B40" s="199"/>
+      <c r="C40" s="164"/>
+      <c r="D40" s="164"/>
       <c r="E40" s="17"/>
       <c r="F40" s="9" t="s">
         <v>304</v>
@@ -19408,17 +19591,17 @@
       <c r="H40" s="16">
         <v>1</v>
       </c>
-      <c r="I40" s="210">
+      <c r="I40" s="209">
         <v>44043</v>
       </c>
       <c r="J40" s="10"/>
       <c r="K40" s="10"/>
     </row>
     <row r="41" spans="1:15" ht="16.5" customHeight="1">
-      <c r="A41" s="165"/>
-      <c r="B41" s="200"/>
-      <c r="C41" s="165"/>
-      <c r="D41" s="165"/>
+      <c r="A41" s="164"/>
+      <c r="B41" s="199"/>
+      <c r="C41" s="164"/>
+      <c r="D41" s="164"/>
       <c r="E41" s="17"/>
       <c r="F41" s="9" t="s">
         <v>305</v>
@@ -19429,17 +19612,17 @@
       <c r="H41" s="16">
         <v>1</v>
       </c>
-      <c r="I41" s="210">
+      <c r="I41" s="209">
         <v>44043</v>
       </c>
       <c r="J41" s="10"/>
       <c r="K41" s="10"/>
     </row>
     <row r="42" spans="1:15">
-      <c r="A42" s="165"/>
-      <c r="B42" s="200"/>
-      <c r="C42" s="165"/>
-      <c r="D42" s="166"/>
+      <c r="A42" s="164"/>
+      <c r="B42" s="199"/>
+      <c r="C42" s="164"/>
+      <c r="D42" s="165"/>
       <c r="E42" s="17"/>
       <c r="F42" s="9" t="s">
         <v>305</v>
@@ -19450,17 +19633,17 @@
       <c r="H42" s="16">
         <v>2</v>
       </c>
-      <c r="I42" s="210">
+      <c r="I42" s="209">
         <v>44074</v>
       </c>
       <c r="J42" s="10"/>
       <c r="K42" s="10"/>
     </row>
     <row r="43" spans="1:15" ht="16.5" customHeight="1">
-      <c r="A43" s="165"/>
-      <c r="B43" s="200"/>
-      <c r="C43" s="165"/>
-      <c r="D43" s="190" t="s">
+      <c r="A43" s="164"/>
+      <c r="B43" s="199"/>
+      <c r="C43" s="164"/>
+      <c r="D43" s="189" t="s">
         <v>515</v>
       </c>
       <c r="E43" s="8"/>
@@ -19473,19 +19656,19 @@
       <c r="H43" s="10" t="s">
         <v>961</v>
       </c>
-      <c r="I43" s="210">
+      <c r="I43" s="209">
         <v>44043</v>
       </c>
       <c r="J43" s="10"/>
-      <c r="K43" s="193" t="s">
+      <c r="K43" s="192" t="s">
         <v>1164</v>
       </c>
     </row>
     <row r="44" spans="1:15">
-      <c r="A44" s="165"/>
-      <c r="B44" s="200"/>
-      <c r="C44" s="165"/>
-      <c r="D44" s="166"/>
+      <c r="A44" s="164"/>
+      <c r="B44" s="199"/>
+      <c r="C44" s="164"/>
+      <c r="D44" s="165"/>
       <c r="E44" s="8"/>
       <c r="F44" s="9" t="s">
         <v>289</v>
@@ -19496,17 +19679,17 @@
       <c r="H44" s="10" t="s">
         <v>961</v>
       </c>
-      <c r="I44" s="210">
+      <c r="I44" s="209">
         <v>44043</v>
       </c>
       <c r="J44" s="10"/>
-      <c r="K44" s="194"/>
+      <c r="K44" s="193"/>
     </row>
     <row r="45" spans="1:15">
-      <c r="A45" s="165"/>
-      <c r="B45" s="200"/>
-      <c r="C45" s="165"/>
-      <c r="D45" s="190" t="s">
+      <c r="A45" s="164"/>
+      <c r="B45" s="199"/>
+      <c r="C45" s="164"/>
+      <c r="D45" s="189" t="s">
         <v>514</v>
       </c>
       <c r="E45" s="8"/>
@@ -19516,18 +19699,18 @@
       <c r="G45" s="9" t="s">
         <v>300</v>
       </c>
-      <c r="H45" s="10">
-        <v>2</v>
-      </c>
-      <c r="I45" s="210"/>
+      <c r="H45" s="10" t="s">
+        <v>963</v>
+      </c>
+      <c r="I45" s="209"/>
       <c r="J45" s="10"/>
       <c r="K45" s="10"/>
     </row>
     <row r="46" spans="1:15">
-      <c r="A46" s="166"/>
-      <c r="B46" s="201"/>
-      <c r="C46" s="166"/>
-      <c r="D46" s="166"/>
+      <c r="A46" s="165"/>
+      <c r="B46" s="200"/>
+      <c r="C46" s="165"/>
+      <c r="D46" s="165"/>
       <c r="E46" s="8"/>
       <c r="F46" s="9" t="s">
         <v>301</v>
@@ -19535,12 +19718,47 @@
       <c r="G46" s="9" t="s">
         <v>302</v>
       </c>
-      <c r="H46" s="10">
-        <v>2</v>
-      </c>
-      <c r="I46" s="210"/>
+      <c r="H46" s="10" t="s">
+        <v>963</v>
+      </c>
+      <c r="I46" s="209"/>
       <c r="J46" s="10"/>
       <c r="K46" s="10"/>
+    </row>
+    <row r="48" spans="1:15">
+      <c r="H48" s="216" t="s">
+        <v>1333</v>
+      </c>
+      <c r="I48">
+        <f>COUNTA($I$2:$I$46)</f>
+        <v>36</v>
+      </c>
+      <c r="J48" s="217">
+        <f>I48/$I$50</f>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="49" spans="8:10">
+      <c r="H49" s="216" t="s">
+        <v>1334</v>
+      </c>
+      <c r="I49">
+        <f>COUNTBLANK($I$2:$I$46)</f>
+        <v>9</v>
+      </c>
+      <c r="J49" s="217">
+        <f>I49/$I$50</f>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="50" spans="8:10">
+      <c r="H50" s="216" t="s">
+        <v>852</v>
+      </c>
+      <c r="I50">
+        <f>SUM(I48:I49)</f>
+        <v>45</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="M16:P28">
@@ -19575,9 +19793,233 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:R54"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col min="11" max="11" width="7.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="5" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1301</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18">
+      <c r="L22" t="s">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18">
+      <c r="A28" s="5" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C28" t="s">
+        <v>1304</v>
+      </c>
+      <c r="K28" t="s">
+        <v>1335</v>
+      </c>
+      <c r="L28" t="s">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18">
+      <c r="A29" t="s">
+        <v>1305</v>
+      </c>
+      <c r="K29">
+        <v>1</v>
+      </c>
+      <c r="L29" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18">
+      <c r="A30" t="s">
+        <v>1306</v>
+      </c>
+      <c r="K30">
+        <v>2</v>
+      </c>
+      <c r="L30" t="s">
+        <v>1338</v>
+      </c>
+      <c r="R30" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18">
+      <c r="B31" t="s">
+        <v>1307</v>
+      </c>
+      <c r="K31">
+        <v>3</v>
+      </c>
+      <c r="L31" t="s">
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18">
+      <c r="A32" t="s">
+        <v>1308</v>
+      </c>
+      <c r="L32" t="s">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12">
+      <c r="A33" t="s">
+        <v>1309</v>
+      </c>
+      <c r="L33" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12">
+      <c r="A34" t="s">
+        <v>1310</v>
+      </c>
+      <c r="L34" t="s">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12">
+      <c r="A35" t="s">
+        <v>1311</v>
+      </c>
+      <c r="K35">
+        <v>4</v>
+      </c>
+      <c r="L35" t="s">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12">
+      <c r="A36" t="s">
+        <v>1312</v>
+      </c>
+      <c r="L36" t="s">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12">
+      <c r="A37" t="s">
+        <v>1313</v>
+      </c>
+      <c r="L37" s="219" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12">
+      <c r="A38" t="s">
+        <v>1314</v>
+      </c>
+      <c r="K38">
+        <v>5</v>
+      </c>
+      <c r="L38" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12">
+      <c r="A39" t="s">
+        <v>1315</v>
+      </c>
+      <c r="K39">
+        <v>6</v>
+      </c>
+      <c r="L39" t="s">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12">
+      <c r="A40" t="s">
+        <v>1316</v>
+      </c>
+      <c r="K40">
+        <v>7</v>
+      </c>
+      <c r="L40" t="s">
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12">
+      <c r="A41" t="s">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12">
+      <c r="A42" t="s">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12">
+      <c r="A43" t="s">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12">
+      <c r="A44" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12">
+      <c r="A45" t="s">
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12">
+      <c r="A46" t="s">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12">
+      <c r="A47" t="s">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12">
+      <c r="A48" t="s">
+        <v>1324</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>1326</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>1327</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>1330</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -19604,11 +20046,11 @@
       <c r="B1" s="25" t="s">
         <v>327</v>
       </c>
-      <c r="E1" s="204" t="s">
+      <c r="E1" s="203" t="s">
         <v>724</v>
       </c>
-      <c r="F1" s="204"/>
-      <c r="G1" s="204"/>
+      <c r="F1" s="203"/>
+      <c r="G1" s="203"/>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="19" t="s">
@@ -19617,11 +20059,11 @@
       <c r="B2" s="19" t="s">
         <v>257</v>
       </c>
-      <c r="E2" s="205" t="s">
+      <c r="E2" s="204" t="s">
         <v>725</v>
       </c>
-      <c r="F2" s="205"/>
-      <c r="G2" s="205"/>
+      <c r="F2" s="204"/>
+      <c r="G2" s="204"/>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="19" t="s">
@@ -19638,10 +20080,10 @@
       <c r="B4" s="19" t="s">
         <v>259</v>
       </c>
-      <c r="E4" s="204" t="s">
+      <c r="E4" s="203" t="s">
         <v>722</v>
       </c>
-      <c r="F4" s="204"/>
+      <c r="F4" s="203"/>
       <c r="G4" s="25" t="s">
         <v>723</v>
       </c>
@@ -19653,16 +20095,16 @@
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="E5" s="203" t="s">
+      <c r="E5" s="202" t="s">
         <v>720</v>
       </c>
-      <c r="F5" s="203" t="s">
+      <c r="F5" s="202" t="s">
         <v>721</v>
       </c>
       <c r="G5" s="68" t="s">
         <v>747</v>
       </c>
-      <c r="H5" s="202" t="s">
+      <c r="H5" s="201" t="s">
         <v>748</v>
       </c>
       <c r="J5" t="s">
@@ -19673,12 +20115,12 @@
       <c r="A6" t="s">
         <v>261</v>
       </c>
-      <c r="E6" s="203"/>
-      <c r="F6" s="203"/>
+      <c r="E6" s="202"/>
+      <c r="F6" s="202"/>
       <c r="G6" s="68" t="s">
         <v>746</v>
       </c>
-      <c r="H6" s="203"/>
+      <c r="H6" s="202"/>
       <c r="J6" t="s">
         <v>729</v>
       </c>
@@ -19799,7 +20241,7 @@
         <v>792</v>
       </c>
       <c r="G16" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="J16" t="s">
         <v>737</v>
@@ -19807,13 +20249,16 @@
     </row>
     <row r="17" spans="7:10">
       <c r="G17" s="7" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="J17" t="s">
         <v>738</v>
       </c>
     </row>
     <row r="18" spans="7:10">
+      <c r="G18" s="7" t="s">
+        <v>1296</v>
+      </c>
       <c r="J18" t="s">
         <v>739</v>
       </c>
@@ -19875,9 +20320,10 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="G17" r:id="rId1" xr:uid="{423578C7-8A13-42FF-B0CB-7B3D59B70C8D}"/>
+    <hyperlink ref="G18" r:id="rId2" xr:uid="{82AA8FD9-C7EA-47DF-856E-670CB8EABA44}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -19895,46 +20341,46 @@
     <col min="7" max="7" width="33" customWidth="1"/>
     <col min="8" max="8" width="38.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.140625" style="81" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="60.42578125" style="129" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="60.42578125" style="128" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30">
-      <c r="A1" s="133" t="s">
+      <c r="A1" s="132" t="s">
         <v>846</v>
       </c>
-      <c r="B1" s="133" t="s">
+      <c r="B1" s="132" t="s">
         <v>1169</v>
       </c>
-      <c r="C1" s="133" t="s">
+      <c r="C1" s="132" t="s">
         <v>640</v>
       </c>
-      <c r="D1" s="133" t="s">
+      <c r="D1" s="132" t="s">
         <v>1172</v>
       </c>
-      <c r="E1" s="133" t="s">
+      <c r="E1" s="132" t="s">
         <v>1167</v>
       </c>
-      <c r="F1" s="133" t="s">
+      <c r="F1" s="132" t="s">
         <v>1168</v>
       </c>
-      <c r="G1" s="134" t="s">
+      <c r="G1" s="133" t="s">
         <v>1202</v>
       </c>
-      <c r="H1" s="134" t="s">
+      <c r="H1" s="133" t="s">
         <v>1255</v>
       </c>
-      <c r="I1" s="133" t="s">
+      <c r="I1" s="132" t="s">
         <v>1176</v>
       </c>
-      <c r="J1" s="133" t="s">
+      <c r="J1" s="132" t="s">
         <v>1182</v>
       </c>
-      <c r="K1" s="133" t="s">
+      <c r="K1" s="132" t="s">
         <v>1188</v>
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="132">
+      <c r="A2" s="131">
         <v>44028</v>
       </c>
       <c r="B2" s="8" t="s">
@@ -19943,31 +20389,31 @@
       <c r="C2" s="8" t="s">
         <v>1171</v>
       </c>
-      <c r="D2" s="116" t="s">
+      <c r="D2" s="115" t="s">
         <v>1173</v>
       </c>
       <c r="E2" s="8" t="s">
         <v>1175</v>
       </c>
-      <c r="F2" s="116" t="s">
+      <c r="F2" s="115" t="s">
         <v>1174</v>
       </c>
-      <c r="G2" s="116">
+      <c r="G2" s="115">
         <v>0.36</v>
       </c>
-      <c r="H2" s="116"/>
-      <c r="I2" s="116" t="s">
+      <c r="H2" s="115"/>
+      <c r="I2" s="115" t="s">
         <v>1177</v>
       </c>
-      <c r="J2" s="116" t="s">
+      <c r="J2" s="115" t="s">
         <v>892</v>
       </c>
-      <c r="K2" s="206" t="s">
+      <c r="K2" s="205" t="s">
         <v>1194</v>
       </c>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="132">
+      <c r="A3" s="131">
         <v>44028</v>
       </c>
       <c r="B3" s="8" t="s">
@@ -19976,29 +20422,29 @@
       <c r="C3" s="8" t="s">
         <v>1193</v>
       </c>
-      <c r="D3" s="116" t="s">
+      <c r="D3" s="115" t="s">
         <v>1173</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>1180</v>
       </c>
-      <c r="F3" s="116" t="s">
+      <c r="F3" s="115" t="s">
         <v>1192</v>
       </c>
-      <c r="G3" s="116">
+      <c r="G3" s="115">
         <v>0.78</v>
       </c>
-      <c r="H3" s="116"/>
-      <c r="I3" s="116" t="s">
+      <c r="H3" s="115"/>
+      <c r="I3" s="115" t="s">
         <v>1181</v>
       </c>
-      <c r="J3" s="116" t="s">
+      <c r="J3" s="115" t="s">
         <v>892</v>
       </c>
-      <c r="K3" s="207"/>
+      <c r="K3" s="206"/>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="132">
+      <c r="A4" s="131">
         <v>44029</v>
       </c>
       <c r="B4" s="8" t="s">
@@ -20007,27 +20453,27 @@
       <c r="C4" s="8" t="s">
         <v>1186</v>
       </c>
-      <c r="D4" s="116" t="s">
+      <c r="D4" s="115" t="s">
         <v>1173</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>1185</v>
       </c>
-      <c r="F4" s="116" t="s">
+      <c r="F4" s="115" t="s">
         <v>1187</v>
       </c>
-      <c r="G4" s="116">
+      <c r="G4" s="115">
         <v>5.83</v>
       </c>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="116" t="s">
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="115" t="s">
         <v>892</v>
       </c>
-      <c r="K4" s="207"/>
+      <c r="K4" s="206"/>
     </row>
     <row r="5" spans="1:11" ht="45">
-      <c r="A5" s="132">
+      <c r="A5" s="131">
         <v>44029</v>
       </c>
       <c r="B5" s="8" t="s">
@@ -20036,27 +20482,27 @@
       <c r="C5" s="8" t="s">
         <v>1189</v>
       </c>
-      <c r="D5" s="116" t="s">
+      <c r="D5" s="115" t="s">
         <v>1173</v>
       </c>
       <c r="E5" s="18" t="s">
         <v>1191</v>
       </c>
-      <c r="F5" s="116" t="s">
+      <c r="F5" s="115" t="s">
         <v>1190</v>
       </c>
-      <c r="G5" s="116">
+      <c r="G5" s="115">
         <v>2.21</v>
       </c>
-      <c r="H5" s="116"/>
-      <c r="I5" s="116"/>
-      <c r="J5" s="116" t="s">
+      <c r="H5" s="115"/>
+      <c r="I5" s="115"/>
+      <c r="J5" s="115" t="s">
         <v>892</v>
       </c>
-      <c r="K5" s="208"/>
+      <c r="K5" s="207"/>
     </row>
     <row r="6" spans="1:11" ht="60">
-      <c r="A6" s="132">
+      <c r="A6" s="131">
         <v>44029</v>
       </c>
       <c r="B6" s="8" t="s">
@@ -20065,20 +20511,20 @@
       <c r="C6" s="8" t="s">
         <v>1204</v>
       </c>
-      <c r="D6" s="116" t="s">
+      <c r="D6" s="115" t="s">
         <v>1173</v>
       </c>
       <c r="E6" s="18" t="s">
         <v>1191</v>
       </c>
-      <c r="F6" s="116" t="s">
+      <c r="F6" s="115" t="s">
         <v>1195</v>
       </c>
       <c r="G6" s="18" t="s">
         <v>1205</v>
       </c>
       <c r="H6" s="18"/>
-      <c r="I6" s="116" t="s">
+      <c r="I6" s="115" t="s">
         <v>1203</v>
       </c>
       <c r="J6" s="8"/>
@@ -20087,7 +20533,7 @@
       </c>
     </row>
     <row r="7" spans="1:11" ht="60">
-      <c r="A7" s="132">
+      <c r="A7" s="131">
         <v>44029</v>
       </c>
       <c r="B7" s="8" t="s">
@@ -20096,27 +20542,27 @@
       <c r="C7" s="8" t="s">
         <v>1215</v>
       </c>
-      <c r="D7" s="116" t="s">
+      <c r="D7" s="115" t="s">
         <v>1173</v>
       </c>
       <c r="E7" s="18" t="s">
         <v>1191</v>
       </c>
-      <c r="F7" s="116" t="s">
+      <c r="F7" s="115" t="s">
         <v>1206</v>
       </c>
       <c r="G7" s="18" t="s">
         <v>1207</v>
       </c>
       <c r="H7" s="18"/>
-      <c r="I7" s="116" t="s">
+      <c r="I7" s="115" t="s">
         <v>1203</v>
       </c>
       <c r="J7" s="8"/>
       <c r="K7" s="8"/>
     </row>
     <row r="8" spans="1:11" ht="60">
-      <c r="A8" s="132">
+      <c r="A8" s="131">
         <v>44029</v>
       </c>
       <c r="B8" s="8" t="s">
@@ -20125,13 +20571,13 @@
       <c r="C8" s="8" t="s">
         <v>1208</v>
       </c>
-      <c r="D8" s="116" t="s">
+      <c r="D8" s="115" t="s">
         <v>1173</v>
       </c>
       <c r="E8" s="18" t="s">
         <v>1191</v>
       </c>
-      <c r="F8" s="116" t="s">
+      <c r="F8" s="115" t="s">
         <v>1196</v>
       </c>
       <c r="G8" s="18" t="s">
@@ -20140,7 +20586,7 @@
       <c r="H8" s="18" t="s">
         <v>1240</v>
       </c>
-      <c r="I8" s="116" t="s">
+      <c r="I8" s="115" t="s">
         <v>1203</v>
       </c>
       <c r="J8" s="8"/>
@@ -20149,7 +20595,7 @@
       </c>
     </row>
     <row r="9" spans="1:11" ht="60">
-      <c r="A9" s="132">
+      <c r="A9" s="131">
         <v>44029</v>
       </c>
       <c r="B9" s="8" t="s">
@@ -20158,22 +20604,22 @@
       <c r="C9" s="8" t="s">
         <v>1210</v>
       </c>
-      <c r="D9" s="116" t="s">
+      <c r="D9" s="115" t="s">
         <v>1173</v>
       </c>
       <c r="E9" s="18" t="s">
         <v>1191</v>
       </c>
-      <c r="F9" s="142" t="s">
+      <c r="F9" s="141" t="s">
         <v>1243</v>
       </c>
-      <c r="G9" s="143" t="s">
+      <c r="G9" s="142" t="s">
         <v>1211</v>
       </c>
-      <c r="H9" s="140" t="s">
+      <c r="H9" s="139" t="s">
         <v>1241</v>
       </c>
-      <c r="I9" s="116" t="s">
+      <c r="I9" s="115" t="s">
         <v>1203</v>
       </c>
       <c r="J9" s="8"/>
@@ -20182,7 +20628,7 @@
       </c>
     </row>
     <row r="10" spans="1:11" ht="64.5" customHeight="1">
-      <c r="A10" s="139" t="s">
+      <c r="A10" s="138" t="s">
         <v>1227</v>
       </c>
       <c r="B10" s="8" t="s">
@@ -20191,20 +20637,20 @@
       <c r="C10" s="8" t="s">
         <v>1214</v>
       </c>
-      <c r="D10" s="116" t="s">
+      <c r="D10" s="115" t="s">
         <v>1173</v>
       </c>
       <c r="E10" s="18" t="s">
         <v>1191</v>
       </c>
-      <c r="F10" s="116" t="s">
+      <c r="F10" s="115" t="s">
         <v>1198</v>
       </c>
       <c r="G10" s="18" t="s">
         <v>1242</v>
       </c>
       <c r="H10" s="18"/>
-      <c r="I10" s="116" t="s">
+      <c r="I10" s="115" t="s">
         <v>1203</v>
       </c>
       <c r="J10" s="8"/>
@@ -20213,7 +20659,7 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="45">
-      <c r="A11" s="137" t="s">
+      <c r="A11" s="136" t="s">
         <v>1218</v>
       </c>
       <c r="B11" s="8" t="s">
@@ -20222,20 +20668,20 @@
       <c r="C11" s="8" t="s">
         <v>1214</v>
       </c>
-      <c r="D11" s="116" t="s">
+      <c r="D11" s="115" t="s">
         <v>1173</v>
       </c>
       <c r="E11" s="18" t="s">
         <v>1191</v>
       </c>
-      <c r="F11" s="116" t="s">
+      <c r="F11" s="115" t="s">
         <v>1198</v>
       </c>
-      <c r="G11" s="136" t="s">
+      <c r="G11" s="135" t="s">
         <v>1245</v>
       </c>
-      <c r="H11" s="136"/>
-      <c r="I11" s="116" t="s">
+      <c r="H11" s="135"/>
+      <c r="I11" s="115" t="s">
         <v>1217</v>
       </c>
       <c r="J11" s="8"/>
@@ -20249,12 +20695,12 @@
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
-      <c r="F12" s="116" t="s">
+      <c r="F12" s="115" t="s">
         <v>1199</v>
       </c>
       <c r="G12" s="8"/>
       <c r="H12" s="8"/>
-      <c r="I12" s="116" t="s">
+      <c r="I12" s="115" t="s">
         <v>1203</v>
       </c>
       <c r="J12" s="8"/>
@@ -20268,12 +20714,12 @@
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
-      <c r="F13" s="116" t="s">
+      <c r="F13" s="115" t="s">
         <v>1200</v>
       </c>
       <c r="G13" s="8"/>
       <c r="H13" s="8"/>
-      <c r="I13" s="116" t="s">
+      <c r="I13" s="115" t="s">
         <v>1203</v>
       </c>
       <c r="J13" s="8"/>
@@ -20282,114 +20728,114 @@
       </c>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="129"/>
-      <c r="B14" s="129"/>
-      <c r="C14" s="129"/>
-      <c r="D14" s="129"/>
-      <c r="E14" s="135" t="s">
+      <c r="A14" s="128"/>
+      <c r="B14" s="128"/>
+      <c r="C14" s="128"/>
+      <c r="D14" s="128"/>
+      <c r="E14" s="134" t="s">
         <v>1216</v>
       </c>
-      <c r="F14" s="130"/>
-      <c r="G14" s="135" t="s">
+      <c r="F14" s="129"/>
+      <c r="G14" s="134" t="s">
         <v>1254</v>
       </c>
-      <c r="H14" s="129"/>
-      <c r="I14" s="130"/>
-      <c r="J14" s="129"/>
+      <c r="H14" s="128"/>
+      <c r="I14" s="129"/>
+      <c r="J14" s="128"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="129"/>
-      <c r="B15" s="129"/>
-      <c r="C15" s="129"/>
-      <c r="D15" s="129"/>
-      <c r="E15" s="129"/>
-      <c r="F15" s="130"/>
-      <c r="G15" s="129" t="s">
+      <c r="A15" s="128"/>
+      <c r="B15" s="128"/>
+      <c r="C15" s="128"/>
+      <c r="D15" s="128"/>
+      <c r="E15" s="128"/>
+      <c r="F15" s="129"/>
+      <c r="G15" s="128" t="s">
         <v>1233</v>
       </c>
-      <c r="H15" s="129" t="s">
+      <c r="H15" s="128" t="s">
         <v>1234</v>
       </c>
-      <c r="I15" s="130"/>
-      <c r="J15" s="129"/>
+      <c r="I15" s="129"/>
+      <c r="J15" s="128"/>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="129"/>
-      <c r="B16" s="129"/>
-      <c r="C16" s="129"/>
-      <c r="D16" s="129"/>
-      <c r="E16" s="129"/>
-      <c r="G16" s="129"/>
-      <c r="H16" s="129"/>
-      <c r="I16" s="130"/>
-      <c r="J16" s="129"/>
+      <c r="A16" s="128"/>
+      <c r="B16" s="128"/>
+      <c r="C16" s="128"/>
+      <c r="D16" s="128"/>
+      <c r="E16" s="128"/>
+      <c r="G16" s="128"/>
+      <c r="H16" s="128"/>
+      <c r="I16" s="129"/>
+      <c r="J16" s="128"/>
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1">
-      <c r="A17" s="129"/>
-      <c r="B17" s="129"/>
-      <c r="C17" s="129"/>
-      <c r="D17" s="129"/>
-      <c r="E17" s="129"/>
-      <c r="F17" s="140"/>
+      <c r="A17" s="128"/>
+      <c r="B17" s="128"/>
+      <c r="C17" s="128"/>
+      <c r="D17" s="128"/>
+      <c r="E17" s="128"/>
+      <c r="F17" s="139"/>
       <c r="G17" s="8" t="s">
         <v>1256</v>
       </c>
-      <c r="H17" s="125" t="s">
+      <c r="H17" s="124" t="s">
         <v>1257</v>
       </c>
-      <c r="I17" s="130"/>
-      <c r="J17" s="129"/>
+      <c r="I17" s="129"/>
+      <c r="J17" s="128"/>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="129"/>
-      <c r="B18" s="129"/>
-      <c r="C18" s="129"/>
-      <c r="D18" s="129"/>
-      <c r="E18" s="129"/>
-      <c r="F18" s="209" t="s">
+      <c r="A18" s="128"/>
+      <c r="B18" s="128"/>
+      <c r="C18" s="128"/>
+      <c r="D18" s="128"/>
+      <c r="E18" s="128"/>
+      <c r="F18" s="208" t="s">
         <v>1239</v>
       </c>
       <c r="G18" s="8" t="s">
         <v>1236</v>
       </c>
-      <c r="H18" s="125" t="s">
+      <c r="H18" s="124" t="s">
         <v>1251</v>
       </c>
-      <c r="I18" s="130"/>
-      <c r="J18" s="129"/>
+      <c r="I18" s="129"/>
+      <c r="J18" s="128"/>
     </row>
     <row r="19" spans="1:10">
-      <c r="F19" s="209"/>
-      <c r="G19" s="149" t="s">
+      <c r="F19" s="208"/>
+      <c r="G19" s="148" t="s">
         <v>1235</v>
       </c>
-      <c r="H19" s="150" t="s">
+      <c r="H19" s="149" t="s">
         <v>1252</v>
       </c>
     </row>
     <row r="20" spans="1:10">
-      <c r="F20" s="209"/>
+      <c r="F20" s="208"/>
       <c r="G20" s="8" t="s">
         <v>1237</v>
       </c>
-      <c r="H20" s="125" t="s">
+      <c r="H20" s="124" t="s">
         <v>1251</v>
       </c>
     </row>
     <row r="21" spans="1:10">
-      <c r="F21" s="209"/>
+      <c r="F21" s="208"/>
       <c r="G21" s="8" t="s">
         <v>1238</v>
       </c>
-      <c r="H21" s="144" t="s">
+      <c r="H21" s="143" t="s">
         <v>1253</v>
       </c>
     </row>
     <row r="22" spans="1:10">
-      <c r="G22" s="141"/>
+      <c r="G22" s="140"/>
     </row>
     <row r="23" spans="1:10">
-      <c r="F23" s="138" t="s">
+      <c r="F23" s="137" t="s">
         <v>1250</v>
       </c>
       <c r="G23" t="s">
@@ -20400,7 +20846,7 @@
       </c>
     </row>
     <row r="24" spans="1:10">
-      <c r="F24" s="138" t="s">
+      <c r="F24" s="137" t="s">
         <v>1206</v>
       </c>
       <c r="G24" s="81">
@@ -20411,7 +20857,7 @@
       </c>
     </row>
     <row r="25" spans="1:10">
-      <c r="F25" s="138" t="s">
+      <c r="F25" s="137" t="s">
         <v>1206</v>
       </c>
       <c r="G25" s="81">
@@ -20422,7 +20868,7 @@
       </c>
     </row>
     <row r="26" spans="1:10">
-      <c r="F26" s="138" t="s">
+      <c r="F26" s="137" t="s">
         <v>1197</v>
       </c>
       <c r="G26" s="81">
@@ -20433,7 +20879,7 @@
       </c>
     </row>
     <row r="27" spans="1:10">
-      <c r="F27" s="138" t="s">
+      <c r="F27" s="137" t="s">
         <v>1197</v>
       </c>
       <c r="G27" s="81">
@@ -20444,7 +20890,7 @@
       </c>
     </row>
     <row r="28" spans="1:10">
-      <c r="F28" s="138" t="s">
+      <c r="F28" s="137" t="s">
         <v>1197</v>
       </c>
       <c r="G28" s="81">
@@ -20455,7 +20901,7 @@
       </c>
     </row>
     <row r="29" spans="1:10">
-      <c r="F29" s="138" t="s">
+      <c r="F29" s="137" t="s">
         <v>1198</v>
       </c>
       <c r="G29" s="81">
@@ -20466,7 +20912,7 @@
       </c>
     </row>
     <row r="30" spans="1:10">
-      <c r="F30" s="138" t="s">
+      <c r="F30" s="137" t="s">
         <v>1198</v>
       </c>
       <c r="G30" s="81">
@@ -20477,7 +20923,7 @@
       </c>
     </row>
     <row r="31" spans="1:10">
-      <c r="F31" s="138" t="s">
+      <c r="F31" s="137" t="s">
         <v>1198</v>
       </c>
       <c r="G31" s="81">
@@ -20488,7 +20934,7 @@
       </c>
     </row>
     <row r="32" spans="1:10">
-      <c r="F32" s="138" t="s">
+      <c r="F32" s="137" t="s">
         <v>1200</v>
       </c>
       <c r="G32" s="81">
@@ -20499,7 +20945,7 @@
       </c>
     </row>
     <row r="33" spans="6:8">
-      <c r="F33" s="138" t="s">
+      <c r="F33" s="137" t="s">
         <v>1200</v>
       </c>
       <c r="G33" s="81">
@@ -20647,13 +21093,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="123" t="s">
+      <c r="A1" s="122" t="s">
         <v>971</v>
       </c>
-      <c r="B1" s="124" t="s">
+      <c r="B1" s="123" t="s">
         <v>972</v>
       </c>
-      <c r="C1" s="124" t="s">
+      <c r="C1" s="123" t="s">
         <v>973</v>
       </c>
     </row>
@@ -21109,120 +21555,120 @@
       </c>
     </row>
     <row r="43" spans="1:3">
-      <c r="A43" s="125" t="s">
+      <c r="A43" s="124" t="s">
         <v>385</v>
       </c>
-      <c r="B43" s="125" t="s">
+      <c r="B43" s="124" t="s">
         <v>1051</v>
       </c>
-      <c r="C43" s="125" t="s">
+      <c r="C43" s="124" t="s">
         <v>1052</v>
       </c>
     </row>
     <row r="44" spans="1:3">
-      <c r="A44" s="125" t="s">
+      <c r="A44" s="124" t="s">
         <v>385</v>
       </c>
-      <c r="B44" s="125" t="s">
+      <c r="B44" s="124" t="s">
         <v>1053</v>
       </c>
-      <c r="C44" s="125" t="s">
+      <c r="C44" s="124" t="s">
         <v>975</v>
       </c>
     </row>
     <row r="45" spans="1:3">
-      <c r="A45" s="125" t="s">
+      <c r="A45" s="124" t="s">
         <v>385</v>
       </c>
-      <c r="B45" s="125" t="s">
+      <c r="B45" s="124" t="s">
         <v>1054</v>
       </c>
-      <c r="C45" s="125" t="s">
+      <c r="C45" s="124" t="s">
         <v>1055</v>
       </c>
     </row>
     <row r="46" spans="1:3">
-      <c r="A46" s="125" t="s">
+      <c r="A46" s="124" t="s">
         <v>385</v>
       </c>
-      <c r="B46" s="125" t="s">
+      <c r="B46" s="124" t="s">
         <v>619</v>
       </c>
-      <c r="C46" s="125" t="s">
+      <c r="C46" s="124" t="s">
         <v>1056</v>
       </c>
     </row>
     <row r="47" spans="1:3">
-      <c r="A47" s="125" t="s">
+      <c r="A47" s="124" t="s">
         <v>385</v>
       </c>
-      <c r="B47" s="125" t="s">
+      <c r="B47" s="124" t="s">
         <v>617</v>
       </c>
-      <c r="C47" s="125" t="s">
+      <c r="C47" s="124" t="s">
         <v>1057</v>
       </c>
     </row>
     <row r="48" spans="1:3">
-      <c r="A48" s="125" t="s">
+      <c r="A48" s="124" t="s">
         <v>385</v>
       </c>
-      <c r="B48" s="125" t="s">
+      <c r="B48" s="124" t="s">
         <v>1058</v>
       </c>
-      <c r="C48" s="125" t="s">
+      <c r="C48" s="124" t="s">
         <v>1059</v>
       </c>
     </row>
     <row r="49" spans="1:3">
-      <c r="A49" s="125" t="s">
+      <c r="A49" s="124" t="s">
         <v>385</v>
       </c>
-      <c r="B49" s="125" t="s">
+      <c r="B49" s="124" t="s">
         <v>1060</v>
       </c>
-      <c r="C49" s="125" t="s">
+      <c r="C49" s="124" t="s">
         <v>1061</v>
       </c>
     </row>
     <row r="50" spans="1:3">
-      <c r="A50" s="125" t="s">
+      <c r="A50" s="124" t="s">
         <v>385</v>
       </c>
-      <c r="B50" s="125" t="s">
+      <c r="B50" s="124" t="s">
         <v>1062</v>
       </c>
-      <c r="C50" s="125" t="s">
+      <c r="C50" s="124" t="s">
         <v>1063</v>
       </c>
     </row>
     <row r="51" spans="1:3">
-      <c r="A51" s="125" t="s">
+      <c r="A51" s="124" t="s">
         <v>385</v>
       </c>
-      <c r="B51" s="125" t="s">
+      <c r="B51" s="124" t="s">
         <v>1064</v>
       </c>
-      <c r="C51" s="125" t="s">
+      <c r="C51" s="124" t="s">
         <v>1065</v>
       </c>
     </row>
     <row r="52" spans="1:3">
-      <c r="A52" s="125" t="s">
+      <c r="A52" s="124" t="s">
         <v>385</v>
       </c>
-      <c r="B52" s="125" t="s">
+      <c r="B52" s="124" t="s">
         <v>1066</v>
       </c>
-      <c r="C52" s="125" t="s">
+      <c r="C52" s="124" t="s">
         <v>1067</v>
       </c>
     </row>
     <row r="53" spans="1:3">
-      <c r="A53" s="125" t="s">
+      <c r="A53" s="124" t="s">
         <v>385</v>
       </c>
-      <c r="B53" s="125" t="s">
+      <c r="B53" s="124" t="s">
         <v>1068</v>
       </c>
       <c r="C53" s="19" t="s">
@@ -21230,10 +21676,10 @@
       </c>
     </row>
     <row r="54" spans="1:3">
-      <c r="A54" s="125" t="s">
+      <c r="A54" s="124" t="s">
         <v>385</v>
       </c>
-      <c r="B54" s="125" t="s">
+      <c r="B54" s="124" t="s">
         <v>1070</v>
       </c>
       <c r="C54" s="19" t="s">
@@ -21241,7 +21687,7 @@
       </c>
     </row>
     <row r="55" spans="1:3">
-      <c r="A55" s="125" t="s">
+      <c r="A55" s="124" t="s">
         <v>385</v>
       </c>
       <c r="B55" s="19" t="s">
@@ -21252,7 +21698,7 @@
       </c>
     </row>
     <row r="56" spans="1:3">
-      <c r="A56" s="125" t="s">
+      <c r="A56" s="124" t="s">
         <v>385</v>
       </c>
       <c r="B56" s="19" t="s">
@@ -21263,7 +21709,7 @@
       </c>
     </row>
     <row r="57" spans="1:3">
-      <c r="A57" s="125" t="s">
+      <c r="A57" s="124" t="s">
         <v>385</v>
       </c>
       <c r="B57" s="19" t="s">
@@ -21274,7 +21720,7 @@
       </c>
     </row>
     <row r="58" spans="1:3" ht="30">
-      <c r="A58" s="125" t="s">
+      <c r="A58" s="124" t="s">
         <v>385</v>
       </c>
       <c r="B58" s="19" t="s">
@@ -21285,7 +21731,7 @@
       </c>
     </row>
     <row r="59" spans="1:3">
-      <c r="A59" s="125" t="s">
+      <c r="A59" s="124" t="s">
         <v>385</v>
       </c>
       <c r="B59" s="19" t="s">
@@ -21296,7 +21742,7 @@
       </c>
     </row>
     <row r="60" spans="1:3">
-      <c r="A60" s="125" t="s">
+      <c r="A60" s="124" t="s">
         <v>385</v>
       </c>
       <c r="B60" s="19" t="s">
@@ -21310,10 +21756,10 @@
       <c r="A61" s="19" t="s">
         <v>1083</v>
       </c>
-      <c r="B61" s="126" t="s">
+      <c r="B61" s="125" t="s">
         <v>1084</v>
       </c>
-      <c r="C61" s="126" t="s">
+      <c r="C61" s="125" t="s">
         <v>1085</v>
       </c>
     </row>
@@ -21321,10 +21767,10 @@
       <c r="A62" s="19" t="s">
         <v>1083</v>
       </c>
-      <c r="B62" s="127" t="s">
+      <c r="B62" s="126" t="s">
         <v>1086</v>
       </c>
-      <c r="C62" s="127" t="s">
+      <c r="C62" s="126" t="s">
         <v>1087</v>
       </c>
     </row>
@@ -21332,10 +21778,10 @@
       <c r="A63" s="19" t="s">
         <v>1083</v>
       </c>
-      <c r="B63" s="127" t="s">
+      <c r="B63" s="126" t="s">
         <v>1088</v>
       </c>
-      <c r="C63" s="127" t="s">
+      <c r="C63" s="126" t="s">
         <v>1089</v>
       </c>
     </row>
@@ -21343,10 +21789,10 @@
       <c r="A64" s="19" t="s">
         <v>1083</v>
       </c>
-      <c r="B64" s="127" t="s">
+      <c r="B64" s="126" t="s">
         <v>1090</v>
       </c>
-      <c r="C64" s="127" t="s">
+      <c r="C64" s="126" t="s">
         <v>1091</v>
       </c>
     </row>
@@ -21354,10 +21800,10 @@
       <c r="A65" s="19" t="s">
         <v>1083</v>
       </c>
-      <c r="B65" s="127" t="s">
+      <c r="B65" s="126" t="s">
         <v>1092</v>
       </c>
-      <c r="C65" s="127" t="s">
+      <c r="C65" s="126" t="s">
         <v>1093</v>
       </c>
     </row>
@@ -21365,10 +21811,10 @@
       <c r="A66" s="19" t="s">
         <v>1083</v>
       </c>
-      <c r="B66" s="127" t="s">
+      <c r="B66" s="126" t="s">
         <v>1094</v>
       </c>
-      <c r="C66" s="127" t="s">
+      <c r="C66" s="126" t="s">
         <v>1095</v>
       </c>
     </row>
@@ -21376,10 +21822,10 @@
       <c r="A67" s="19" t="s">
         <v>1083</v>
       </c>
-      <c r="B67" s="127" t="s">
+      <c r="B67" s="126" t="s">
         <v>1096</v>
       </c>
-      <c r="C67" s="127" t="s">
+      <c r="C67" s="126" t="s">
         <v>1097</v>
       </c>
     </row>
@@ -21387,10 +21833,10 @@
       <c r="A68" s="19" t="s">
         <v>1083</v>
       </c>
-      <c r="B68" s="127" t="s">
+      <c r="B68" s="126" t="s">
         <v>1098</v>
       </c>
-      <c r="C68" s="127" t="s">
+      <c r="C68" s="126" t="s">
         <v>1099</v>
       </c>
     </row>
@@ -21398,10 +21844,10 @@
       <c r="A69" s="19" t="s">
         <v>1083</v>
       </c>
-      <c r="B69" s="127" t="s">
+      <c r="B69" s="126" t="s">
         <v>1100</v>
       </c>
-      <c r="C69" s="127" t="s">
+      <c r="C69" s="126" t="s">
         <v>1101</v>
       </c>
     </row>
@@ -21409,10 +21855,10 @@
       <c r="A70" s="19" t="s">
         <v>1083</v>
       </c>
-      <c r="B70" s="127" t="s">
+      <c r="B70" s="126" t="s">
         <v>1102</v>
       </c>
-      <c r="C70" s="127" t="s">
+      <c r="C70" s="126" t="s">
         <v>1103</v>
       </c>
     </row>
@@ -21420,10 +21866,10 @@
       <c r="A71" s="19" t="s">
         <v>1083</v>
       </c>
-      <c r="B71" s="127" t="s">
+      <c r="B71" s="126" t="s">
         <v>1104</v>
       </c>
-      <c r="C71" s="127" t="s">
+      <c r="C71" s="126" t="s">
         <v>1105</v>
       </c>
     </row>
@@ -21431,10 +21877,10 @@
       <c r="A72" s="19" t="s">
         <v>1083</v>
       </c>
-      <c r="B72" s="127" t="s">
+      <c r="B72" s="126" t="s">
         <v>1106</v>
       </c>
-      <c r="C72" s="127" t="s">
+      <c r="C72" s="126" t="s">
         <v>1107</v>
       </c>
     </row>
@@ -21442,10 +21888,10 @@
       <c r="A73" s="19" t="s">
         <v>1083</v>
       </c>
-      <c r="B73" s="127" t="s">
+      <c r="B73" s="126" t="s">
         <v>1108</v>
       </c>
-      <c r="C73" s="127" t="s">
+      <c r="C73" s="126" t="s">
         <v>1109</v>
       </c>
     </row>
@@ -21453,10 +21899,10 @@
       <c r="A74" s="19" t="s">
         <v>1083</v>
       </c>
-      <c r="B74" s="127" t="s">
+      <c r="B74" s="126" t="s">
         <v>1110</v>
       </c>
-      <c r="C74" s="127" t="s">
+      <c r="C74" s="126" t="s">
         <v>1111</v>
       </c>
     </row>
@@ -21464,10 +21910,10 @@
       <c r="A75" s="19" t="s">
         <v>1083</v>
       </c>
-      <c r="B75" s="127" t="s">
+      <c r="B75" s="126" t="s">
         <v>1112</v>
       </c>
-      <c r="C75" s="127" t="s">
+      <c r="C75" s="126" t="s">
         <v>1113</v>
       </c>
     </row>
@@ -21475,10 +21921,10 @@
       <c r="A76" s="19" t="s">
         <v>1083</v>
       </c>
-      <c r="B76" s="127" t="s">
+      <c r="B76" s="126" t="s">
         <v>1114</v>
       </c>
-      <c r="C76" s="127" t="s">
+      <c r="C76" s="126" t="s">
         <v>1115</v>
       </c>
     </row>
@@ -21486,10 +21932,10 @@
       <c r="A77" s="19" t="s">
         <v>1083</v>
       </c>
-      <c r="B77" s="127" t="s">
+      <c r="B77" s="126" t="s">
         <v>1116</v>
       </c>
-      <c r="C77" s="127" t="s">
+      <c r="C77" s="126" t="s">
         <v>1117</v>
       </c>
     </row>
@@ -21497,10 +21943,10 @@
       <c r="A78" s="19" t="s">
         <v>1083</v>
       </c>
-      <c r="B78" s="127" t="s">
+      <c r="B78" s="126" t="s">
         <v>1118</v>
       </c>
-      <c r="C78" s="127" t="s">
+      <c r="C78" s="126" t="s">
         <v>1119</v>
       </c>
     </row>
@@ -21508,10 +21954,10 @@
       <c r="A79" s="19" t="s">
         <v>1083</v>
       </c>
-      <c r="B79" s="127" t="s">
+      <c r="B79" s="126" t="s">
         <v>1120</v>
       </c>
-      <c r="C79" s="127" t="s">
+      <c r="C79" s="126" t="s">
         <v>1121</v>
       </c>
     </row>
@@ -21519,10 +21965,10 @@
       <c r="A80" s="19" t="s">
         <v>1083</v>
       </c>
-      <c r="B80" s="127" t="s">
+      <c r="B80" s="126" t="s">
         <v>1122</v>
       </c>
-      <c r="C80" s="127" t="s">
+      <c r="C80" s="126" t="s">
         <v>1123</v>
       </c>
     </row>
@@ -21530,10 +21976,10 @@
       <c r="A81" s="19" t="s">
         <v>1083</v>
       </c>
-      <c r="B81" s="127" t="s">
+      <c r="B81" s="126" t="s">
         <v>1124</v>
       </c>
-      <c r="C81" s="127" t="s">
+      <c r="C81" s="126" t="s">
         <v>1125</v>
       </c>
     </row>
@@ -21541,10 +21987,10 @@
       <c r="A82" s="19" t="s">
         <v>1083</v>
       </c>
-      <c r="B82" s="127" t="s">
+      <c r="B82" s="126" t="s">
         <v>1126</v>
       </c>
-      <c r="C82" s="127" t="s">
+      <c r="C82" s="126" t="s">
         <v>1127</v>
       </c>
     </row>
@@ -21552,10 +21998,10 @@
       <c r="A83" s="19" t="s">
         <v>1083</v>
       </c>
-      <c r="B83" s="127" t="s">
+      <c r="B83" s="126" t="s">
         <v>1128</v>
       </c>
-      <c r="C83" s="127" t="s">
+      <c r="C83" s="126" t="s">
         <v>1129</v>
       </c>
     </row>
@@ -21563,10 +22009,10 @@
       <c r="A84" s="19" t="s">
         <v>1130</v>
       </c>
-      <c r="B84" s="127" t="s">
+      <c r="B84" s="126" t="s">
         <v>1131</v>
       </c>
-      <c r="C84" s="127" t="s">
+      <c r="C84" s="126" t="s">
         <v>1105</v>
       </c>
     </row>
@@ -21574,10 +22020,10 @@
       <c r="A85" s="19" t="s">
         <v>1130</v>
       </c>
-      <c r="B85" s="127" t="s">
+      <c r="B85" s="126" t="s">
         <v>1132</v>
       </c>
-      <c r="C85" s="127" t="s">
+      <c r="C85" s="126" t="s">
         <v>1133</v>
       </c>
     </row>
@@ -21585,10 +22031,10 @@
       <c r="A86" s="19" t="s">
         <v>1130</v>
       </c>
-      <c r="B86" s="127" t="s">
+      <c r="B86" s="126" t="s">
         <v>1134</v>
       </c>
-      <c r="C86" s="127" t="s">
+      <c r="C86" s="126" t="s">
         <v>1135</v>
       </c>
     </row>
@@ -21596,10 +22042,10 @@
       <c r="A87" s="19" t="s">
         <v>1130</v>
       </c>
-      <c r="B87" s="127" t="s">
+      <c r="B87" s="126" t="s">
         <v>1136</v>
       </c>
-      <c r="C87" s="127" t="s">
+      <c r="C87" s="126" t="s">
         <v>1137</v>
       </c>
     </row>
@@ -21607,10 +22053,10 @@
       <c r="A88" s="19" t="s">
         <v>1130</v>
       </c>
-      <c r="B88" s="127" t="s">
+      <c r="B88" s="126" t="s">
         <v>1138</v>
       </c>
-      <c r="C88" s="127" t="s">
+      <c r="C88" s="126" t="s">
         <v>1107</v>
       </c>
     </row>
@@ -21618,10 +22064,10 @@
       <c r="A89" s="19" t="s">
         <v>1130</v>
       </c>
-      <c r="B89" s="127" t="s">
+      <c r="B89" s="126" t="s">
         <v>1139</v>
       </c>
-      <c r="C89" s="127" t="s">
+      <c r="C89" s="126" t="s">
         <v>1140</v>
       </c>
     </row>
@@ -21629,10 +22075,10 @@
       <c r="A90" s="19" t="s">
         <v>1130</v>
       </c>
-      <c r="B90" s="127" t="s">
+      <c r="B90" s="126" t="s">
         <v>1141</v>
       </c>
-      <c r="C90" s="127" t="s">
+      <c r="C90" s="126" t="s">
         <v>1142</v>
       </c>
     </row>
@@ -21640,10 +22086,10 @@
       <c r="A91" s="19" t="s">
         <v>1143</v>
       </c>
-      <c r="B91" s="127" t="s">
+      <c r="B91" s="126" t="s">
         <v>1144</v>
       </c>
-      <c r="C91" s="127" t="s">
+      <c r="C91" s="126" t="s">
         <v>1105</v>
       </c>
     </row>
@@ -21651,10 +22097,10 @@
       <c r="A92" s="19" t="s">
         <v>1143</v>
       </c>
-      <c r="B92" s="127" t="s">
+      <c r="B92" s="126" t="s">
         <v>1134</v>
       </c>
-      <c r="C92" s="127" t="s">
+      <c r="C92" s="126" t="s">
         <v>1135</v>
       </c>
     </row>
@@ -21662,10 +22108,10 @@
       <c r="A93" s="19" t="s">
         <v>1143</v>
       </c>
-      <c r="B93" s="127" t="s">
+      <c r="B93" s="126" t="s">
         <v>313</v>
       </c>
-      <c r="C93" s="127" t="s">
+      <c r="C93" s="126" t="s">
         <v>1085</v>
       </c>
     </row>
@@ -21673,10 +22119,10 @@
       <c r="A94" s="19" t="s">
         <v>1143</v>
       </c>
-      <c r="B94" s="127" t="s">
+      <c r="B94" s="126" t="s">
         <v>810</v>
       </c>
-      <c r="C94" s="127" t="s">
+      <c r="C94" s="126" t="s">
         <v>1145</v>
       </c>
     </row>
@@ -21684,10 +22130,10 @@
       <c r="A95" s="19" t="s">
         <v>1143</v>
       </c>
-      <c r="B95" s="127" t="s">
+      <c r="B95" s="126" t="s">
         <v>1146</v>
       </c>
-      <c r="C95" s="127" t="s">
+      <c r="C95" s="126" t="s">
         <v>1089</v>
       </c>
     </row>
@@ -21695,10 +22141,10 @@
       <c r="A96" s="19" t="s">
         <v>1143</v>
       </c>
-      <c r="B96" s="127" t="s">
+      <c r="B96" s="126" t="s">
         <v>1147</v>
       </c>
-      <c r="C96" s="127" t="s">
+      <c r="C96" s="126" t="s">
         <v>1091</v>
       </c>
     </row>
@@ -21706,10 +22152,10 @@
       <c r="A97" s="19" t="s">
         <v>1143</v>
       </c>
-      <c r="B97" s="127" t="s">
+      <c r="B97" s="126" t="s">
         <v>1148</v>
       </c>
-      <c r="C97" s="127" t="s">
+      <c r="C97" s="126" t="s">
         <v>1093</v>
       </c>
     </row>
@@ -21717,10 +22163,10 @@
       <c r="A98" s="19" t="s">
         <v>1143</v>
       </c>
-      <c r="B98" s="127" t="s">
+      <c r="B98" s="126" t="s">
         <v>1149</v>
       </c>
-      <c r="C98" s="127" t="s">
+      <c r="C98" s="126" t="s">
         <v>1127</v>
       </c>
     </row>
@@ -21728,10 +22174,10 @@
       <c r="A99" s="19" t="s">
         <v>1143</v>
       </c>
-      <c r="B99" s="127" t="s">
+      <c r="B99" s="126" t="s">
         <v>1150</v>
       </c>
-      <c r="C99" s="127" t="s">
+      <c r="C99" s="126" t="s">
         <v>1151</v>
       </c>
     </row>
@@ -21739,10 +22185,10 @@
       <c r="A100" s="19" t="s">
         <v>1143</v>
       </c>
-      <c r="B100" s="127" t="s">
+      <c r="B100" s="126" t="s">
         <v>1152</v>
       </c>
-      <c r="C100" s="127" t="s">
+      <c r="C100" s="126" t="s">
         <v>1123</v>
       </c>
     </row>
@@ -21750,10 +22196,10 @@
       <c r="A101" s="19" t="s">
         <v>1143</v>
       </c>
-      <c r="B101" s="127" t="s">
+      <c r="B101" s="126" t="s">
         <v>1139</v>
       </c>
-      <c r="C101" s="127" t="s">
+      <c r="C101" s="126" t="s">
         <v>1153</v>
       </c>
     </row>
@@ -21761,10 +22207,10 @@
       <c r="A102" s="19" t="s">
         <v>1143</v>
       </c>
-      <c r="B102" s="127" t="s">
+      <c r="B102" s="126" t="s">
         <v>1154</v>
       </c>
-      <c r="C102" s="127" t="s">
+      <c r="C102" s="126" t="s">
         <v>1155</v>
       </c>
     </row>
@@ -21772,10 +22218,10 @@
       <c r="A103" s="19" t="s">
         <v>1143</v>
       </c>
-      <c r="B103" s="127" t="s">
+      <c r="B103" s="126" t="s">
         <v>1156</v>
       </c>
-      <c r="C103" s="127" t="s">
+      <c r="C103" s="126" t="s">
         <v>1157</v>
       </c>
     </row>
@@ -21783,10 +22229,10 @@
       <c r="A104" s="19" t="s">
         <v>1143</v>
       </c>
-      <c r="B104" s="127" t="s">
+      <c r="B104" s="126" t="s">
         <v>1158</v>
       </c>
-      <c r="C104" s="127" t="s">
+      <c r="C104" s="126" t="s">
         <v>1097</v>
       </c>
     </row>
@@ -21794,10 +22240,10 @@
       <c r="A105" s="19" t="s">
         <v>1143</v>
       </c>
-      <c r="B105" s="127" t="s">
+      <c r="B105" s="126" t="s">
         <v>1159</v>
       </c>
-      <c r="C105" s="127" t="s">
+      <c r="C105" s="126" t="s">
         <v>1160</v>
       </c>
     </row>
@@ -21820,13 +22266,13 @@
       <c r="A112" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="B112" s="128"/>
+      <c r="B112" s="127"/>
     </row>
     <row r="113" spans="1:2" ht="16.5">
       <c r="A113" s="7" t="s">
         <v>1163</v>
       </c>
-      <c r="B113" s="128"/>
+      <c r="B113" s="127"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -21870,7 +22316,7 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="203" t="s">
+      <c r="A2" s="202" t="s">
         <v>379</v>
       </c>
       <c r="B2" s="57" t="s">
@@ -21884,7 +22330,7 @@
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="203"/>
+      <c r="A3" s="202"/>
       <c r="B3" s="20" t="s">
         <v>262</v>
       </c>
@@ -21896,7 +22342,7 @@
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="203"/>
+      <c r="A4" s="202"/>
       <c r="B4" s="20" t="s">
         <v>385</v>
       </c>
@@ -21908,7 +22354,7 @@
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="203"/>
+      <c r="A5" s="202"/>
       <c r="B5" s="57" t="s">
         <v>544</v>
       </c>
@@ -21920,7 +22366,7 @@
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="203"/>
+      <c r="A6" s="202"/>
       <c r="B6" s="20" t="s">
         <v>388</v>
       </c>
@@ -21932,7 +22378,7 @@
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="203"/>
+      <c r="A7" s="202"/>
       <c r="B7" s="20" t="s">
         <v>390</v>
       </c>
@@ -23547,24 +23993,24 @@
       </c>
     </row>
     <row r="8" spans="11:18" ht="35.25" customHeight="1">
-      <c r="N8" s="107"/>
-      <c r="O8" s="107" t="s">
+      <c r="N8" s="106"/>
+      <c r="O8" s="106" t="s">
         <v>872</v>
       </c>
     </row>
     <row r="9" spans="11:18">
-      <c r="K9" s="148" t="s">
+      <c r="K9" s="147" t="s">
         <v>1267</v>
       </c>
     </row>
     <row r="10" spans="11:18">
-      <c r="K10" s="148">
+      <c r="K10" s="147">
         <v>0</v>
       </c>
-      <c r="L10" s="110" t="s">
+      <c r="L10" s="109" t="s">
         <v>908</v>
       </c>
-      <c r="M10" s="110" t="s">
+      <c r="M10" s="109" t="s">
         <v>909</v>
       </c>
       <c r="O10" s="5" t="s">
@@ -23575,17 +24021,17 @@
       </c>
     </row>
     <row r="11" spans="11:18" ht="15.75" thickBot="1">
-      <c r="K11" s="148"/>
-      <c r="L11" s="146"/>
-      <c r="M11" s="146"/>
-      <c r="N11" s="146"/>
-      <c r="O11" s="146"/>
-      <c r="P11" s="146"/>
-      <c r="Q11" s="146"/>
-      <c r="R11" s="146"/>
+      <c r="K11" s="147"/>
+      <c r="L11" s="145"/>
+      <c r="M11" s="145"/>
+      <c r="N11" s="145"/>
+      <c r="O11" s="145"/>
+      <c r="P11" s="145"/>
+      <c r="Q11" s="145"/>
+      <c r="R11" s="145"/>
     </row>
     <row r="12" spans="11:18">
-      <c r="K12" s="148">
+      <c r="K12" s="147">
         <v>1</v>
       </c>
       <c r="L12" s="5" t="s">
@@ -23593,7 +24039,7 @@
       </c>
     </row>
     <row r="13" spans="11:18">
-      <c r="K13" s="148"/>
+      <c r="K13" s="147"/>
       <c r="M13" t="s">
         <v>880</v>
       </c>
@@ -23605,7 +24051,7 @@
       </c>
     </row>
     <row r="14" spans="11:18">
-      <c r="K14" s="148"/>
+      <c r="K14" s="147"/>
       <c r="L14" s="6" t="s">
         <v>887</v>
       </c>
@@ -23614,13 +24060,13 @@
       </c>
     </row>
     <row r="15" spans="11:18">
-      <c r="K15" s="148"/>
+      <c r="K15" s="147"/>
       <c r="M15" t="s">
         <v>884</v>
       </c>
     </row>
     <row r="16" spans="11:18">
-      <c r="K16" s="148"/>
+      <c r="K16" s="147"/>
       <c r="O16" s="5" t="s">
         <v>1266</v>
       </c>
@@ -23629,16 +24075,16 @@
       </c>
     </row>
     <row r="17" spans="7:24">
-      <c r="K17" s="148"/>
+      <c r="K17" s="147"/>
     </row>
     <row r="18" spans="7:24">
-      <c r="K18" s="148"/>
+      <c r="K18" s="147"/>
     </row>
     <row r="19" spans="7:24">
-      <c r="K19" s="148"/>
+      <c r="K19" s="147"/>
     </row>
     <row r="20" spans="7:24">
-      <c r="K20" s="148"/>
+      <c r="K20" s="147"/>
       <c r="L20" s="6" t="s">
         <v>882</v>
       </c>
@@ -23656,7 +24102,7 @@
       </c>
     </row>
     <row r="21" spans="7:24">
-      <c r="K21" s="148"/>
+      <c r="K21" s="147"/>
       <c r="M21" t="s">
         <v>888</v>
       </c>
@@ -23665,8 +24111,8 @@
       </c>
     </row>
     <row r="22" spans="7:24">
-      <c r="K22" s="148"/>
-      <c r="V22" s="164" t="s">
+      <c r="K22" s="147"/>
+      <c r="V22" s="163" t="s">
         <v>832</v>
       </c>
       <c r="W22" s="9" t="s">
@@ -23677,19 +24123,19 @@
       </c>
     </row>
     <row r="23" spans="7:24" ht="15.75" thickBot="1">
-      <c r="K23" s="148"/>
-      <c r="L23" s="146"/>
-      <c r="M23" s="146"/>
-      <c r="N23" s="146"/>
-      <c r="O23" s="147" t="s">
+      <c r="K23" s="147"/>
+      <c r="L23" s="145"/>
+      <c r="M23" s="145"/>
+      <c r="N23" s="145"/>
+      <c r="O23" s="146" t="s">
         <v>1266</v>
       </c>
-      <c r="P23" s="147" t="s">
+      <c r="P23" s="146" t="s">
         <v>1268</v>
       </c>
-      <c r="Q23" s="146"/>
-      <c r="R23" s="146"/>
-      <c r="V23" s="165"/>
+      <c r="Q23" s="145"/>
+      <c r="R23" s="145"/>
+      <c r="V23" s="164"/>
       <c r="W23" s="9" t="s">
         <v>815</v>
       </c>
@@ -23698,8 +24144,8 @@
       </c>
     </row>
     <row r="24" spans="7:24">
-      <c r="K24" s="148"/>
-      <c r="V24" s="165"/>
+      <c r="K24" s="147"/>
+      <c r="V24" s="164"/>
       <c r="W24" s="9" t="s">
         <v>816</v>
       </c>
@@ -23708,13 +24154,13 @@
       </c>
     </row>
     <row r="25" spans="7:24">
-      <c r="K25" s="148">
+      <c r="K25" s="147">
         <v>2</v>
       </c>
       <c r="L25" s="5" t="s">
         <v>891</v>
       </c>
-      <c r="V25" s="165"/>
+      <c r="V25" s="164"/>
       <c r="W25" s="9" t="s">
         <v>817</v>
       </c>
@@ -23723,8 +24169,8 @@
       </c>
     </row>
     <row r="26" spans="7:24">
-      <c r="K26" s="148"/>
-      <c r="M26" s="111" t="s">
+      <c r="K26" s="147"/>
+      <c r="M26" s="110" t="s">
         <v>893</v>
       </c>
       <c r="N26" t="s">
@@ -23733,32 +24179,32 @@
       <c r="O26" t="s">
         <v>897</v>
       </c>
-      <c r="V26" s="165"/>
+      <c r="V26" s="164"/>
       <c r="W26" s="9" t="s">
         <v>824</v>
       </c>
       <c r="X26" s="92"/>
     </row>
     <row r="27" spans="7:24">
-      <c r="K27" s="148"/>
+      <c r="K27" s="147"/>
       <c r="M27" t="s">
         <v>894</v>
       </c>
       <c r="N27" t="s">
         <v>896</v>
       </c>
-      <c r="V27" s="165"/>
+      <c r="V27" s="164"/>
       <c r="W27" s="9" t="s">
         <v>825</v>
       </c>
       <c r="X27" s="92"/>
     </row>
     <row r="28" spans="7:24">
-      <c r="K28" s="148"/>
+      <c r="K28" s="147"/>
       <c r="N28" t="s">
         <v>898</v>
       </c>
-      <c r="V28" s="165"/>
+      <c r="V28" s="164"/>
       <c r="W28" s="9" t="s">
         <v>826</v>
       </c>
@@ -23767,11 +24213,11 @@
       </c>
     </row>
     <row r="29" spans="7:24">
-      <c r="K29" s="148"/>
+      <c r="K29" s="147"/>
       <c r="N29" t="s">
         <v>899</v>
       </c>
-      <c r="V29" s="166"/>
+      <c r="V29" s="165"/>
       <c r="W29" s="9" t="s">
         <v>827</v>
       </c>
@@ -23780,53 +24226,53 @@
       </c>
     </row>
     <row r="30" spans="7:24">
-      <c r="K30" s="148"/>
+      <c r="K30" s="147"/>
       <c r="M30" t="s">
         <v>900</v>
       </c>
       <c r="N30" t="s">
         <v>852</v>
       </c>
-      <c r="V30" s="161" t="s">
+      <c r="V30" s="160" t="s">
         <v>831</v>
       </c>
       <c r="W30" s="49" t="s">
         <v>821</v>
       </c>
-      <c r="X30" s="113"/>
+      <c r="X30" s="112"/>
     </row>
     <row r="31" spans="7:24">
-      <c r="K31" s="148"/>
+      <c r="K31" s="147"/>
       <c r="N31" t="s">
         <v>901</v>
       </c>
-      <c r="V31" s="162"/>
+      <c r="V31" s="161"/>
       <c r="W31" s="49" t="s">
         <v>822</v>
       </c>
-      <c r="X31" s="113"/>
+      <c r="X31" s="112"/>
     </row>
     <row r="32" spans="7:24" ht="15.75" thickBot="1">
       <c r="G32" t="s">
         <v>910</v>
       </c>
-      <c r="K32" s="148"/>
-      <c r="L32" s="146"/>
-      <c r="M32" s="146"/>
-      <c r="N32" s="146"/>
-      <c r="O32" s="147" t="s">
+      <c r="K32" s="147"/>
+      <c r="L32" s="145"/>
+      <c r="M32" s="145"/>
+      <c r="N32" s="145"/>
+      <c r="O32" s="146" t="s">
         <v>902</v>
       </c>
-      <c r="P32" s="147" t="s">
+      <c r="P32" s="146" t="s">
         <v>903</v>
       </c>
-      <c r="Q32" s="146"/>
-      <c r="R32" s="146"/>
-      <c r="V32" s="163"/>
+      <c r="Q32" s="145"/>
+      <c r="R32" s="145"/>
+      <c r="V32" s="162"/>
       <c r="W32" s="49" t="s">
         <v>823</v>
       </c>
-      <c r="X32" s="113"/>
+      <c r="X32" s="112"/>
     </row>
     <row r="33" spans="6:17">
       <c r="F33">
@@ -23835,7 +24281,7 @@
       <c r="G33" t="s">
         <v>911</v>
       </c>
-      <c r="K33" s="148"/>
+      <c r="K33" s="147"/>
     </row>
     <row r="34" spans="6:17">
       <c r="F34">
@@ -23844,7 +24290,7 @@
       <c r="G34" t="s">
         <v>912</v>
       </c>
-      <c r="K34" s="148">
+      <c r="K34" s="147">
         <v>3</v>
       </c>
       <c r="L34" s="5" t="s">
@@ -23894,19 +24340,19 @@
       </c>
     </row>
     <row r="41" spans="6:17" ht="15.75" thickBot="1">
-      <c r="L41" s="146"/>
-      <c r="M41" s="146"/>
-      <c r="N41" s="146"/>
-      <c r="O41" s="147" t="s">
+      <c r="L41" s="145"/>
+      <c r="M41" s="145"/>
+      <c r="N41" s="145"/>
+      <c r="O41" s="146" t="s">
         <v>907</v>
       </c>
-      <c r="P41" s="147" t="s">
+      <c r="P41" s="146" t="s">
         <v>892</v>
       </c>
-      <c r="Q41" s="146"/>
+      <c r="Q41" s="145"/>
     </row>
     <row r="44" spans="6:17">
-      <c r="P44" s="145"/>
+      <c r="P44" s="144"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -23962,7 +24408,7 @@
       <c r="R5" s="13" t="s">
         <v>352</v>
       </c>
-      <c r="S5" s="167" t="s">
+      <c r="S5" s="166" t="s">
         <v>809</v>
       </c>
     </row>
@@ -23979,7 +24425,7 @@
       <c r="R6" s="9" t="s">
         <v>602</v>
       </c>
-      <c r="S6" s="167"/>
+      <c r="S6" s="166"/>
     </row>
     <row r="7" spans="3:20">
       <c r="O7" s="81" t="s">
@@ -23994,7 +24440,7 @@
       <c r="R7" s="9" t="s">
         <v>603</v>
       </c>
-      <c r="S7" s="167"/>
+      <c r="S7" s="166"/>
     </row>
     <row r="8" spans="3:20">
       <c r="O8" s="81" t="s">
@@ -24009,7 +24455,7 @@
       <c r="R8" s="9" t="s">
         <v>350</v>
       </c>
-      <c r="S8" s="167"/>
+      <c r="S8" s="166"/>
     </row>
     <row r="9" spans="3:20">
       <c r="O9" s="81" t="s">
@@ -24024,7 +24470,7 @@
       <c r="R9" s="9" t="s">
         <v>349</v>
       </c>
-      <c r="S9" s="167"/>
+      <c r="S9" s="166"/>
     </row>
     <row r="10" spans="3:20">
       <c r="Q10" s="9" t="s">
@@ -24049,7 +24495,7 @@
       </c>
     </row>
     <row r="15" spans="3:20">
-      <c r="Q15" s="164" t="s">
+      <c r="Q15" s="163" t="s">
         <v>832</v>
       </c>
       <c r="R15" s="9" t="s">
@@ -24084,7 +24530,7 @@
       <c r="J16" s="10" t="s">
         <v>813</v>
       </c>
-      <c r="Q16" s="165"/>
+      <c r="Q16" s="164"/>
       <c r="R16" s="9" t="s">
         <v>815</v>
       </c>
@@ -24094,7 +24540,7 @@
     </row>
     <row r="17" spans="10:19">
       <c r="J17" s="81"/>
-      <c r="Q17" s="165"/>
+      <c r="Q17" s="164"/>
       <c r="R17" s="9" t="s">
         <v>816</v>
       </c>
@@ -24103,7 +24549,7 @@
       </c>
     </row>
     <row r="18" spans="10:19">
-      <c r="Q18" s="165"/>
+      <c r="Q18" s="164"/>
       <c r="R18" s="9" t="s">
         <v>817</v>
       </c>
@@ -24112,21 +24558,21 @@
       </c>
     </row>
     <row r="19" spans="10:19">
-      <c r="Q19" s="165"/>
+      <c r="Q19" s="164"/>
       <c r="R19" s="9" t="s">
         <v>824</v>
       </c>
       <c r="S19" s="92"/>
     </row>
     <row r="20" spans="10:19">
-      <c r="Q20" s="165"/>
+      <c r="Q20" s="164"/>
       <c r="R20" s="9" t="s">
         <v>825</v>
       </c>
       <c r="S20" s="92"/>
     </row>
     <row r="21" spans="10:19">
-      <c r="Q21" s="165"/>
+      <c r="Q21" s="164"/>
       <c r="R21" s="9" t="s">
         <v>826</v>
       </c>
@@ -24135,7 +24581,7 @@
       </c>
     </row>
     <row r="22" spans="10:19">
-      <c r="Q22" s="166"/>
+      <c r="Q22" s="165"/>
       <c r="R22" s="9" t="s">
         <v>827</v>
       </c>
@@ -24144,7 +24590,7 @@
       </c>
     </row>
     <row r="23" spans="10:19">
-      <c r="Q23" s="164" t="s">
+      <c r="Q23" s="163" t="s">
         <v>831</v>
       </c>
       <c r="R23" s="9" t="s">
@@ -24153,14 +24599,14 @@
       <c r="S23" s="92"/>
     </row>
     <row r="24" spans="10:19">
-      <c r="Q24" s="165"/>
+      <c r="Q24" s="164"/>
       <c r="R24" s="9" t="s">
         <v>822</v>
       </c>
       <c r="S24" s="92"/>
     </row>
     <row r="25" spans="10:19">
-      <c r="Q25" s="166"/>
+      <c r="Q25" s="165"/>
       <c r="R25" s="9" t="s">
         <v>823</v>
       </c>
@@ -24226,39 +24672,39 @@
       <c r="B1" t="s">
         <v>860</v>
       </c>
-      <c r="J1" s="168" t="s">
+      <c r="J1" s="167" t="s">
         <v>952</v>
       </c>
-      <c r="K1" s="169"/>
-      <c r="L1" s="169"/>
-      <c r="M1" s="169"/>
-      <c r="N1" s="169"/>
-      <c r="O1" s="169"/>
-      <c r="P1" s="169"/>
-      <c r="Q1" s="169"/>
+      <c r="K1" s="168"/>
+      <c r="L1" s="168"/>
+      <c r="M1" s="168"/>
+      <c r="N1" s="168"/>
+      <c r="O1" s="168"/>
+      <c r="P1" s="168"/>
+      <c r="Q1" s="168"/>
     </row>
     <row r="2" spans="1:17">
-      <c r="J2" s="169"/>
-      <c r="K2" s="169"/>
-      <c r="L2" s="169"/>
-      <c r="M2" s="169"/>
-      <c r="N2" s="169"/>
-      <c r="O2" s="169"/>
-      <c r="P2" s="169"/>
-      <c r="Q2" s="169"/>
+      <c r="J2" s="168"/>
+      <c r="K2" s="168"/>
+      <c r="L2" s="168"/>
+      <c r="M2" s="168"/>
+      <c r="N2" s="168"/>
+      <c r="O2" s="168"/>
+      <c r="P2" s="168"/>
+      <c r="Q2" s="168"/>
     </row>
     <row r="3" spans="1:17">
       <c r="A3" s="6" t="s">
         <v>861</v>
       </c>
-      <c r="J3" s="169"/>
-      <c r="K3" s="169"/>
-      <c r="L3" s="169"/>
-      <c r="M3" s="169"/>
-      <c r="N3" s="169"/>
-      <c r="O3" s="169"/>
-      <c r="P3" s="169"/>
-      <c r="Q3" s="169"/>
+      <c r="J3" s="168"/>
+      <c r="K3" s="168"/>
+      <c r="L3" s="168"/>
+      <c r="M3" s="168"/>
+      <c r="N3" s="168"/>
+      <c r="O3" s="168"/>
+      <c r="P3" s="168"/>
+      <c r="Q3" s="168"/>
     </row>
     <row r="4" spans="1:17">
       <c r="A4" t="s">
@@ -24270,24 +24716,24 @@
       <c r="D4" t="s">
         <v>863</v>
       </c>
-      <c r="J4" s="169"/>
-      <c r="K4" s="169"/>
-      <c r="L4" s="169"/>
-      <c r="M4" s="169"/>
-      <c r="N4" s="169"/>
-      <c r="O4" s="169"/>
-      <c r="P4" s="169"/>
-      <c r="Q4" s="169"/>
+      <c r="J4" s="168"/>
+      <c r="K4" s="168"/>
+      <c r="L4" s="168"/>
+      <c r="M4" s="168"/>
+      <c r="N4" s="168"/>
+      <c r="O4" s="168"/>
+      <c r="P4" s="168"/>
+      <c r="Q4" s="168"/>
     </row>
     <row r="5" spans="1:17">
-      <c r="J5" s="169"/>
-      <c r="K5" s="169"/>
-      <c r="L5" s="169"/>
-      <c r="M5" s="169"/>
-      <c r="N5" s="169"/>
-      <c r="O5" s="169"/>
-      <c r="P5" s="169"/>
-      <c r="Q5" s="169"/>
+      <c r="J5" s="168"/>
+      <c r="K5" s="168"/>
+      <c r="L5" s="168"/>
+      <c r="M5" s="168"/>
+      <c r="N5" s="168"/>
+      <c r="O5" s="168"/>
+      <c r="P5" s="168"/>
+      <c r="Q5" s="168"/>
     </row>
     <row r="6" spans="1:17" ht="15.75" thickBot="1">
       <c r="A6" t="s">
@@ -24296,38 +24742,38 @@
       <c r="E6" t="s">
         <v>918</v>
       </c>
-      <c r="J6" s="169"/>
-      <c r="K6" s="169"/>
-      <c r="L6" s="169"/>
-      <c r="M6" s="169"/>
-      <c r="N6" s="169"/>
-      <c r="O6" s="169"/>
-      <c r="P6" s="169"/>
-      <c r="Q6" s="169"/>
+      <c r="J6" s="168"/>
+      <c r="K6" s="168"/>
+      <c r="L6" s="168"/>
+      <c r="M6" s="168"/>
+      <c r="N6" s="168"/>
+      <c r="O6" s="168"/>
+      <c r="P6" s="168"/>
+      <c r="Q6" s="168"/>
     </row>
     <row r="7" spans="1:17" ht="15.75" thickBot="1">
-      <c r="A7" s="106" t="s">
+      <c r="A7" s="105" t="s">
         <v>865</v>
       </c>
-      <c r="J7" s="169"/>
-      <c r="K7" s="169"/>
-      <c r="L7" s="169"/>
-      <c r="M7" s="169"/>
-      <c r="N7" s="169"/>
-      <c r="O7" s="169"/>
-      <c r="P7" s="169"/>
-      <c r="Q7" s="169"/>
+      <c r="J7" s="168"/>
+      <c r="K7" s="168"/>
+      <c r="L7" s="168"/>
+      <c r="M7" s="168"/>
+      <c r="N7" s="168"/>
+      <c r="O7" s="168"/>
+      <c r="P7" s="168"/>
+      <c r="Q7" s="168"/>
     </row>
     <row r="8" spans="1:17">
-      <c r="A8" s="118"/>
-      <c r="J8" s="169"/>
-      <c r="K8" s="169"/>
-      <c r="L8" s="169"/>
-      <c r="M8" s="169"/>
-      <c r="N8" s="169"/>
-      <c r="O8" s="169"/>
-      <c r="P8" s="169"/>
-      <c r="Q8" s="169"/>
+      <c r="A8" s="117"/>
+      <c r="J8" s="168"/>
+      <c r="K8" s="168"/>
+      <c r="L8" s="168"/>
+      <c r="M8" s="168"/>
+      <c r="N8" s="168"/>
+      <c r="O8" s="168"/>
+      <c r="P8" s="168"/>
+      <c r="Q8" s="168"/>
     </row>
     <row r="9" spans="1:17">
       <c r="A9" t="s">
@@ -24336,14 +24782,14 @@
       <c r="B9" t="s">
         <v>924</v>
       </c>
-      <c r="J9" s="169"/>
-      <c r="K9" s="169"/>
-      <c r="L9" s="169"/>
-      <c r="M9" s="169"/>
-      <c r="N9" s="169"/>
-      <c r="O9" s="169"/>
-      <c r="P9" s="169"/>
-      <c r="Q9" s="169"/>
+      <c r="J9" s="168"/>
+      <c r="K9" s="168"/>
+      <c r="L9" s="168"/>
+      <c r="M9" s="168"/>
+      <c r="N9" s="168"/>
+      <c r="O9" s="168"/>
+      <c r="P9" s="168"/>
+      <c r="Q9" s="168"/>
     </row>
     <row r="10" spans="1:17">
       <c r="A10" t="s">
@@ -24364,14 +24810,14 @@
       <c r="H10" t="s">
         <v>950</v>
       </c>
-      <c r="J10" s="169"/>
-      <c r="K10" s="169"/>
-      <c r="L10" s="169"/>
-      <c r="M10" s="169"/>
-      <c r="N10" s="169"/>
-      <c r="O10" s="169"/>
-      <c r="P10" s="169"/>
-      <c r="Q10" s="169"/>
+      <c r="J10" s="168"/>
+      <c r="K10" s="168"/>
+      <c r="L10" s="168"/>
+      <c r="M10" s="168"/>
+      <c r="N10" s="168"/>
+      <c r="O10" s="168"/>
+      <c r="P10" s="168"/>
+      <c r="Q10" s="168"/>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" t="s">
@@ -24392,14 +24838,14 @@
       <c r="H11" t="s">
         <v>951</v>
       </c>
-      <c r="J11" s="169"/>
-      <c r="K11" s="169"/>
-      <c r="L11" s="169"/>
-      <c r="M11" s="169"/>
-      <c r="N11" s="169"/>
-      <c r="O11" s="169"/>
-      <c r="P11" s="169"/>
-      <c r="Q11" s="169"/>
+      <c r="J11" s="168"/>
+      <c r="K11" s="168"/>
+      <c r="L11" s="168"/>
+      <c r="M11" s="168"/>
+      <c r="N11" s="168"/>
+      <c r="O11" s="168"/>
+      <c r="P11" s="168"/>
+      <c r="Q11" s="168"/>
     </row>
     <row r="12" spans="1:17">
       <c r="B12" t="s">
@@ -24414,14 +24860,14 @@
       <c r="H12" t="s">
         <v>951</v>
       </c>
-      <c r="J12" s="169"/>
-      <c r="K12" s="169"/>
-      <c r="L12" s="169"/>
-      <c r="M12" s="169"/>
-      <c r="N12" s="169"/>
-      <c r="O12" s="169"/>
-      <c r="P12" s="169"/>
-      <c r="Q12" s="169"/>
+      <c r="J12" s="168"/>
+      <c r="K12" s="168"/>
+      <c r="L12" s="168"/>
+      <c r="M12" s="168"/>
+      <c r="N12" s="168"/>
+      <c r="O12" s="168"/>
+      <c r="P12" s="168"/>
+      <c r="Q12" s="168"/>
     </row>
     <row r="13" spans="1:17">
       <c r="F13" t="s">
@@ -24433,24 +24879,24 @@
       <c r="H13" t="s">
         <v>951</v>
       </c>
-      <c r="J13" s="169"/>
-      <c r="K13" s="169"/>
-      <c r="L13" s="169"/>
-      <c r="M13" s="169"/>
-      <c r="N13" s="169"/>
-      <c r="O13" s="169"/>
-      <c r="P13" s="169"/>
-      <c r="Q13" s="169"/>
+      <c r="J13" s="168"/>
+      <c r="K13" s="168"/>
+      <c r="L13" s="168"/>
+      <c r="M13" s="168"/>
+      <c r="N13" s="168"/>
+      <c r="O13" s="168"/>
+      <c r="P13" s="168"/>
+      <c r="Q13" s="168"/>
     </row>
     <row r="14" spans="1:17">
-      <c r="J14" s="169"/>
-      <c r="K14" s="169"/>
-      <c r="L14" s="169"/>
-      <c r="M14" s="169"/>
-      <c r="N14" s="169"/>
-      <c r="O14" s="169"/>
-      <c r="P14" s="169"/>
-      <c r="Q14" s="169"/>
+      <c r="J14" s="168"/>
+      <c r="K14" s="168"/>
+      <c r="L14" s="168"/>
+      <c r="M14" s="168"/>
+      <c r="N14" s="168"/>
+      <c r="O14" s="168"/>
+      <c r="P14" s="168"/>
+      <c r="Q14" s="168"/>
     </row>
     <row r="15" spans="1:17">
       <c r="A15" t="s">
@@ -24459,27 +24905,27 @@
       <c r="C15" t="s">
         <v>947</v>
       </c>
-      <c r="J15" s="169"/>
-      <c r="K15" s="169"/>
-      <c r="L15" s="169"/>
-      <c r="M15" s="169"/>
-      <c r="N15" s="169"/>
-      <c r="O15" s="169"/>
-      <c r="P15" s="169"/>
-      <c r="Q15" s="169"/>
+      <c r="J15" s="168"/>
+      <c r="K15" s="168"/>
+      <c r="L15" s="168"/>
+      <c r="M15" s="168"/>
+      <c r="N15" s="168"/>
+      <c r="O15" s="168"/>
+      <c r="P15" s="168"/>
+      <c r="Q15" s="168"/>
     </row>
     <row r="16" spans="1:17">
       <c r="A16" t="s">
         <v>937</v>
       </c>
-      <c r="J16" s="169"/>
-      <c r="K16" s="169"/>
-      <c r="L16" s="169"/>
-      <c r="M16" s="169"/>
-      <c r="N16" s="169"/>
-      <c r="O16" s="169"/>
-      <c r="P16" s="169"/>
-      <c r="Q16" s="169"/>
+      <c r="J16" s="168"/>
+      <c r="K16" s="168"/>
+      <c r="L16" s="168"/>
+      <c r="M16" s="168"/>
+      <c r="N16" s="168"/>
+      <c r="O16" s="168"/>
+      <c r="P16" s="168"/>
+      <c r="Q16" s="168"/>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="5" t="s">
@@ -24764,19 +25210,19 @@
       <c r="E7" s="31" t="s">
         <v>449</v>
       </c>
-      <c r="F7" s="170" t="s">
+      <c r="F7" s="169" t="s">
         <v>441</v>
       </c>
-      <c r="G7" s="170"/>
-      <c r="H7" s="170"/>
-      <c r="I7" s="170"/>
-      <c r="J7" s="170"/>
-      <c r="K7" s="170"/>
-      <c r="L7" s="170"/>
-      <c r="M7" s="170"/>
-      <c r="N7" s="170"/>
-      <c r="O7" s="170"/>
-      <c r="P7" s="170"/>
+      <c r="G7" s="169"/>
+      <c r="H7" s="169"/>
+      <c r="I7" s="169"/>
+      <c r="J7" s="169"/>
+      <c r="K7" s="169"/>
+      <c r="L7" s="169"/>
+      <c r="M7" s="169"/>
+      <c r="N7" s="169"/>
+      <c r="O7" s="169"/>
+      <c r="P7" s="169"/>
     </row>
     <row r="8" spans="1:17">
       <c r="B8" s="32" t="s">
@@ -25000,40 +25446,40 @@
       <c r="A24" s="35" t="s">
         <v>455</v>
       </c>
-      <c r="B24" s="171" t="s">
+      <c r="B24" s="170" t="s">
         <v>457</v>
       </c>
-      <c r="C24" s="171"/>
-      <c r="D24" s="171"/>
-      <c r="E24" s="171"/>
-      <c r="F24" s="171"/>
-      <c r="G24" s="171"/>
+      <c r="C24" s="170"/>
+      <c r="D24" s="170"/>
+      <c r="E24" s="170"/>
+      <c r="F24" s="170"/>
+      <c r="G24" s="170"/>
     </row>
     <row r="25" spans="1:7" ht="30">
       <c r="A25" s="35" t="s">
         <v>462</v>
       </c>
-      <c r="B25" s="172" t="s">
+      <c r="B25" s="171" t="s">
         <v>464</v>
       </c>
-      <c r="C25" s="172"/>
-      <c r="D25" s="172"/>
-      <c r="E25" s="172"/>
-      <c r="F25" s="172"/>
-      <c r="G25" s="172"/>
+      <c r="C25" s="171"/>
+      <c r="D25" s="171"/>
+      <c r="E25" s="171"/>
+      <c r="F25" s="171"/>
+      <c r="G25" s="171"/>
     </row>
     <row r="26" spans="1:7" ht="159" customHeight="1">
       <c r="A26" s="35" t="s">
         <v>459</v>
       </c>
-      <c r="B26" s="171" t="s">
+      <c r="B26" s="170" t="s">
         <v>460</v>
       </c>
-      <c r="C26" s="171"/>
-      <c r="D26" s="171"/>
-      <c r="E26" s="171"/>
-      <c r="F26" s="171"/>
-      <c r="G26" s="171"/>
+      <c r="C26" s="170"/>
+      <c r="D26" s="170"/>
+      <c r="E26" s="170"/>
+      <c r="F26" s="170"/>
+      <c r="G26" s="170"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -25548,29 +25994,29 @@
       <c r="B27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="C27" s="175" t="s">
+      <c r="C27" s="174" t="s">
         <v>622</v>
       </c>
-      <c r="D27" s="176"/>
+      <c r="D27" s="175"/>
       <c r="E27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="F27" s="175" t="s">
+      <c r="F27" s="174" t="s">
         <v>622</v>
       </c>
-      <c r="G27" s="176"/>
+      <c r="G27" s="175"/>
       <c r="H27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="I27" s="175" t="s">
+      <c r="I27" s="174" t="s">
         <v>622</v>
       </c>
-      <c r="J27" s="176"/>
-      <c r="L27" s="173" t="s">
+      <c r="J27" s="175"/>
+      <c r="L27" s="172" t="s">
         <v>694</v>
       </c>
-      <c r="M27" s="173"/>
-      <c r="N27" s="173"/>
+      <c r="M27" s="172"/>
+      <c r="N27" s="172"/>
     </row>
     <row r="28" spans="1:14" ht="32.25" thickBot="1">
       <c r="A28" s="81">
@@ -25579,29 +26025,29 @@
       <c r="B28" s="69" t="s">
         <v>623</v>
       </c>
-      <c r="C28" s="183" t="s">
+      <c r="C28" s="182" t="s">
         <v>624</v>
       </c>
-      <c r="D28" s="184"/>
+      <c r="D28" s="183"/>
       <c r="E28" s="70" t="s">
         <v>645</v>
       </c>
-      <c r="F28" s="177" t="s">
+      <c r="F28" s="176" t="s">
         <v>646</v>
       </c>
-      <c r="G28" s="178"/>
+      <c r="G28" s="177"/>
       <c r="H28" s="69" t="s">
         <v>667</v>
       </c>
-      <c r="I28" s="183" t="s">
+      <c r="I28" s="182" t="s">
         <v>668</v>
       </c>
-      <c r="J28" s="184"/>
-      <c r="L28" s="174" t="s">
+      <c r="J28" s="183"/>
+      <c r="L28" s="173" t="s">
         <v>695</v>
       </c>
-      <c r="M28" s="174"/>
-      <c r="N28" s="174"/>
+      <c r="M28" s="173"/>
+      <c r="N28" s="173"/>
     </row>
     <row r="29" spans="1:14" ht="31.5" thickBot="1">
       <c r="A29" s="81">
@@ -25610,29 +26056,29 @@
       <c r="B29" s="70" t="s">
         <v>625</v>
       </c>
-      <c r="C29" s="177" t="s">
+      <c r="C29" s="176" t="s">
         <v>626</v>
       </c>
-      <c r="D29" s="178"/>
+      <c r="D29" s="177"/>
       <c r="E29" s="69" t="s">
         <v>647</v>
       </c>
-      <c r="F29" s="183" t="s">
+      <c r="F29" s="182" t="s">
         <v>648</v>
       </c>
-      <c r="G29" s="184"/>
+      <c r="G29" s="183"/>
       <c r="H29" s="70" t="s">
         <v>669</v>
       </c>
-      <c r="I29" s="187" t="s">
+      <c r="I29" s="186" t="s">
         <v>670</v>
       </c>
-      <c r="J29" s="188"/>
-      <c r="L29" s="173" t="s">
+      <c r="J29" s="187"/>
+      <c r="L29" s="172" t="s">
         <v>696</v>
       </c>
-      <c r="M29" s="173"/>
-      <c r="N29" s="173"/>
+      <c r="M29" s="172"/>
+      <c r="N29" s="172"/>
     </row>
     <row r="30" spans="1:14" ht="15.75" thickBot="1">
       <c r="A30" s="81">
@@ -25641,29 +26087,29 @@
       <c r="B30" s="69" t="s">
         <v>627</v>
       </c>
-      <c r="C30" s="183" t="s">
+      <c r="C30" s="182" t="s">
         <v>628</v>
       </c>
-      <c r="D30" s="184"/>
+      <c r="D30" s="183"/>
       <c r="E30" s="70" t="s">
         <v>649</v>
       </c>
-      <c r="F30" s="177" t="s">
+      <c r="F30" s="176" t="s">
         <v>650</v>
       </c>
-      <c r="G30" s="178"/>
+      <c r="G30" s="177"/>
       <c r="H30" s="69" t="s">
         <v>671</v>
       </c>
-      <c r="I30" s="183" t="s">
+      <c r="I30" s="182" t="s">
         <v>672</v>
       </c>
-      <c r="J30" s="184"/>
-      <c r="L30" s="174" t="s">
+      <c r="J30" s="183"/>
+      <c r="L30" s="173" t="s">
         <v>697</v>
       </c>
-      <c r="M30" s="174"/>
-      <c r="N30" s="174"/>
+      <c r="M30" s="173"/>
+      <c r="N30" s="173"/>
     </row>
     <row r="31" spans="1:14" ht="17.25" customHeight="1" thickBot="1">
       <c r="A31" s="81">
@@ -25672,29 +26118,29 @@
       <c r="B31" s="70" t="s">
         <v>629</v>
       </c>
-      <c r="C31" s="177" t="s">
+      <c r="C31" s="176" t="s">
         <v>630</v>
       </c>
-      <c r="D31" s="178"/>
+      <c r="D31" s="177"/>
       <c r="E31" s="69" t="s">
         <v>651</v>
       </c>
-      <c r="F31" s="183" t="s">
+      <c r="F31" s="182" t="s">
         <v>652</v>
       </c>
-      <c r="G31" s="184"/>
+      <c r="G31" s="183"/>
       <c r="H31" s="70" t="s">
         <v>673</v>
       </c>
-      <c r="I31" s="177" t="s">
+      <c r="I31" s="176" t="s">
         <v>674</v>
       </c>
-      <c r="J31" s="178"/>
-      <c r="L31" s="173" t="s">
+      <c r="J31" s="177"/>
+      <c r="L31" s="172" t="s">
         <v>698</v>
       </c>
-      <c r="M31" s="173"/>
-      <c r="N31" s="173"/>
+      <c r="M31" s="172"/>
+      <c r="N31" s="172"/>
     </row>
     <row r="32" spans="1:14" ht="43.5" customHeight="1" thickBot="1">
       <c r="A32" s="81">
@@ -25703,29 +26149,29 @@
       <c r="B32" s="69" t="s">
         <v>631</v>
       </c>
-      <c r="C32" s="183" t="s">
+      <c r="C32" s="182" t="s">
         <v>632</v>
       </c>
-      <c r="D32" s="184"/>
+      <c r="D32" s="183"/>
       <c r="E32" s="70" t="s">
         <v>653</v>
       </c>
-      <c r="F32" s="177" t="s">
+      <c r="F32" s="176" t="s">
         <v>654</v>
       </c>
-      <c r="G32" s="178"/>
+      <c r="G32" s="177"/>
       <c r="H32" s="69" t="s">
         <v>675</v>
       </c>
-      <c r="I32" s="183" t="s">
+      <c r="I32" s="182" t="s">
         <v>676</v>
       </c>
-      <c r="J32" s="184"/>
-      <c r="L32" s="174" t="s">
+      <c r="J32" s="183"/>
+      <c r="L32" s="173" t="s">
         <v>699</v>
       </c>
-      <c r="M32" s="174"/>
-      <c r="N32" s="174"/>
+      <c r="M32" s="173"/>
+      <c r="N32" s="173"/>
     </row>
     <row r="33" spans="1:14" ht="31.5" customHeight="1" thickBot="1">
       <c r="A33" s="81">
@@ -25734,29 +26180,29 @@
       <c r="B33" s="70" t="s">
         <v>633</v>
       </c>
-      <c r="C33" s="177" t="s">
+      <c r="C33" s="176" t="s">
         <v>634</v>
       </c>
-      <c r="D33" s="178"/>
+      <c r="D33" s="177"/>
       <c r="E33" s="69" t="s">
         <v>655</v>
       </c>
-      <c r="F33" s="183" t="s">
+      <c r="F33" s="182" t="s">
         <v>656</v>
       </c>
-      <c r="G33" s="184"/>
+      <c r="G33" s="183"/>
       <c r="H33" s="70" t="s">
         <v>677</v>
       </c>
-      <c r="I33" s="185" t="s">
+      <c r="I33" s="184" t="s">
         <v>678</v>
       </c>
-      <c r="J33" s="186"/>
-      <c r="L33" s="173" t="s">
+      <c r="J33" s="185"/>
+      <c r="L33" s="172" t="s">
         <v>700</v>
       </c>
-      <c r="M33" s="173"/>
-      <c r="N33" s="173"/>
+      <c r="M33" s="172"/>
+      <c r="N33" s="172"/>
     </row>
     <row r="34" spans="1:14" ht="28.5" customHeight="1" thickBot="1">
       <c r="A34" s="81">
@@ -25765,29 +26211,29 @@
       <c r="B34" s="69" t="s">
         <v>635</v>
       </c>
-      <c r="C34" s="183" t="s">
+      <c r="C34" s="182" t="s">
         <v>636</v>
       </c>
-      <c r="D34" s="184"/>
+      <c r="D34" s="183"/>
       <c r="E34" s="70" t="s">
         <v>657</v>
       </c>
-      <c r="F34" s="177" t="s">
+      <c r="F34" s="176" t="s">
         <v>658</v>
       </c>
-      <c r="G34" s="178"/>
+      <c r="G34" s="177"/>
       <c r="H34" s="69" t="s">
         <v>679</v>
       </c>
-      <c r="I34" s="181" t="s">
+      <c r="I34" s="180" t="s">
         <v>680</v>
       </c>
-      <c r="J34" s="182"/>
-      <c r="L34" s="174" t="s">
+      <c r="J34" s="181"/>
+      <c r="L34" s="173" t="s">
         <v>701</v>
       </c>
-      <c r="M34" s="174"/>
-      <c r="N34" s="174"/>
+      <c r="M34" s="173"/>
+      <c r="N34" s="173"/>
     </row>
     <row r="35" spans="1:14" ht="31.5" customHeight="1" thickBot="1">
       <c r="A35" s="81">
@@ -25796,29 +26242,29 @@
       <c r="B35" s="70" t="s">
         <v>637</v>
       </c>
-      <c r="C35" s="177" t="s">
+      <c r="C35" s="176" t="s">
         <v>638</v>
       </c>
-      <c r="D35" s="178"/>
+      <c r="D35" s="177"/>
       <c r="E35" s="69" t="s">
         <v>659</v>
       </c>
-      <c r="F35" s="183" t="s">
+      <c r="F35" s="182" t="s">
         <v>660</v>
       </c>
-      <c r="G35" s="184"/>
+      <c r="G35" s="183"/>
       <c r="H35" s="77" t="s">
         <v>681</v>
       </c>
-      <c r="I35" s="177" t="s">
+      <c r="I35" s="176" t="s">
         <v>682</v>
       </c>
-      <c r="J35" s="178"/>
-      <c r="L35" s="173" t="s">
+      <c r="J35" s="177"/>
+      <c r="L35" s="172" t="s">
         <v>702</v>
       </c>
-      <c r="M35" s="173"/>
-      <c r="N35" s="173"/>
+      <c r="M35" s="172"/>
+      <c r="N35" s="172"/>
     </row>
     <row r="36" spans="1:14" ht="60.75" thickBot="1">
       <c r="A36" s="81">
@@ -25827,17 +26273,17 @@
       <c r="B36" s="69" t="s">
         <v>639</v>
       </c>
-      <c r="C36" s="183" t="s">
+      <c r="C36" s="182" t="s">
         <v>640</v>
       </c>
-      <c r="D36" s="184"/>
+      <c r="D36" s="183"/>
       <c r="E36" s="70" t="s">
         <v>661</v>
       </c>
-      <c r="F36" s="177" t="s">
+      <c r="F36" s="176" t="s">
         <v>662</v>
       </c>
-      <c r="G36" s="178"/>
+      <c r="G36" s="177"/>
       <c r="H36" s="78"/>
       <c r="I36" s="71" t="s">
         <v>683</v>
@@ -25845,11 +26291,11 @@
       <c r="J36" s="72" t="s">
         <v>684</v>
       </c>
-      <c r="L36" s="174" t="s">
+      <c r="L36" s="173" t="s">
         <v>703</v>
       </c>
-      <c r="M36" s="174"/>
-      <c r="N36" s="174"/>
+      <c r="M36" s="173"/>
+      <c r="N36" s="173"/>
     </row>
     <row r="37" spans="1:14" ht="75.75" thickBot="1">
       <c r="A37" s="81">
@@ -25858,17 +26304,17 @@
       <c r="B37" s="70" t="s">
         <v>641</v>
       </c>
-      <c r="C37" s="177" t="s">
+      <c r="C37" s="176" t="s">
         <v>642</v>
       </c>
-      <c r="D37" s="178"/>
+      <c r="D37" s="177"/>
       <c r="E37" s="69" t="s">
         <v>663</v>
       </c>
-      <c r="F37" s="183" t="s">
+      <c r="F37" s="182" t="s">
         <v>664</v>
       </c>
-      <c r="G37" s="184"/>
+      <c r="G37" s="183"/>
       <c r="H37" s="78"/>
       <c r="I37" s="73" t="s">
         <v>685</v>
@@ -25884,17 +26330,17 @@
       <c r="B38" s="69" t="s">
         <v>643</v>
       </c>
-      <c r="C38" s="183" t="s">
+      <c r="C38" s="182" t="s">
         <v>644</v>
       </c>
-      <c r="D38" s="184"/>
+      <c r="D38" s="183"/>
       <c r="E38" s="70" t="s">
         <v>665</v>
       </c>
-      <c r="F38" s="177" t="s">
+      <c r="F38" s="176" t="s">
         <v>666</v>
       </c>
-      <c r="G38" s="178"/>
+      <c r="G38" s="177"/>
       <c r="H38" s="78"/>
       <c r="I38" s="75" t="s">
         <v>687</v>
@@ -25910,22 +26356,22 @@
       <c r="B39" s="70" t="s">
         <v>692</v>
       </c>
-      <c r="C39" s="185" t="s">
+      <c r="C39" s="184" t="s">
         <v>693</v>
       </c>
-      <c r="D39" s="186"/>
+      <c r="D39" s="185"/>
       <c r="E39" s="69" t="s">
         <v>690</v>
       </c>
-      <c r="F39" s="181" t="s">
+      <c r="F39" s="180" t="s">
         <v>691</v>
       </c>
-      <c r="G39" s="182"/>
+      <c r="G39" s="181"/>
       <c r="H39" s="79"/>
-      <c r="I39" s="179" t="s">
+      <c r="I39" s="178" t="s">
         <v>689</v>
       </c>
-      <c r="J39" s="180"/>
+      <c r="J39" s="179"/>
     </row>
     <row r="40" spans="1:14" ht="58.5" customHeight="1"/>
     <row r="42" spans="1:14" ht="31.5" customHeight="1"/>

--- a/2020_LogAnalyzer_Leeheesuk.xlsx
+++ b/2020_LogAnalyzer_Leeheesuk.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="23001"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1441DC8C-9C22-4B78-86EE-05E17F7B1EF2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76E0110B-3929-49DF-9955-9F25FEE48F40}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" firstSheet="7" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15990" firstSheet="8" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UI" sheetId="7" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2113" uniqueCount="1351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2121" uniqueCount="1356">
   <si>
     <t>구분</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -5915,6 +5915,21 @@
   </si>
   <si>
     <t>TimeTaken 부분 UI 수정 - 단위(D/T)</t>
+  </si>
+  <si>
+    <t>fbyte</t>
+  </si>
+  <si>
+    <t>fstatic</t>
+  </si>
+  <si>
+    <t>fextension</t>
+  </si>
+  <si>
+    <t>진행중</t>
+  </si>
+  <si>
+    <t>평균 응답시간</t>
   </si>
 </sst>
 </file>
@@ -6310,7 +6325,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -6377,15 +6392,6 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -6595,7 +6601,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="40" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="220">
+  <cellXfs count="221">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6695,7 +6701,7 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -6718,10 +6724,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
@@ -6755,29 +6761,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -6785,10 +6794,7 @@
     <xf numFmtId="0" fontId="23" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -6861,7 +6867,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
@@ -6922,6 +6928,9 @@
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -6973,8 +6982,8 @@
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -6994,22 +7003,22 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7054,46 +7063,46 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7114,10 +7123,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7159,7 +7168,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7171,12 +7180,6 @@
     <xf numFmtId="0" fontId="35" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -7186,6 +7189,10 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="백분율" xfId="2" builtinId="5"/>
@@ -15352,7 +15359,7 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="66675" y="285750"/>
-          <a:ext cx="7564507" cy="2763581"/>
+          <a:ext cx="7540516" cy="2763581"/>
           <a:chOff x="534516" y="352896"/>
           <a:chExt cx="8439150" cy="3049331"/>
         </a:xfrm>
@@ -16518,51 +16525,51 @@
     </row>
     <row r="17" spans="1:13">
       <c r="J17" s="19"/>
-      <c r="K17" s="154" t="s">
+      <c r="K17" s="155" t="s">
         <v>537</v>
       </c>
-      <c r="L17" s="155"/>
-      <c r="M17" s="156"/>
+      <c r="L17" s="156"/>
+      <c r="M17" s="157"/>
     </row>
     <row r="18" spans="1:13">
       <c r="J18" s="19">
         <v>1</v>
       </c>
-      <c r="K18" s="157" t="s">
+      <c r="K18" s="158" t="s">
         <v>538</v>
       </c>
-      <c r="L18" s="158"/>
-      <c r="M18" s="159"/>
+      <c r="L18" s="159"/>
+      <c r="M18" s="160"/>
     </row>
     <row r="19" spans="1:13">
       <c r="J19" s="19">
         <v>2</v>
       </c>
-      <c r="K19" s="157" t="s">
+      <c r="K19" s="158" t="s">
         <v>539</v>
       </c>
-      <c r="L19" s="158"/>
-      <c r="M19" s="159"/>
+      <c r="L19" s="159"/>
+      <c r="M19" s="160"/>
     </row>
     <row r="20" spans="1:13">
       <c r="J20" s="19">
         <v>3</v>
       </c>
-      <c r="K20" s="157" t="s">
+      <c r="K20" s="158" t="s">
         <v>540</v>
       </c>
-      <c r="L20" s="158"/>
-      <c r="M20" s="159"/>
+      <c r="L20" s="159"/>
+      <c r="M20" s="160"/>
     </row>
     <row r="21" spans="1:13">
       <c r="J21" s="19">
         <v>4</v>
       </c>
-      <c r="K21" s="157" t="s">
+      <c r="K21" s="158" t="s">
         <v>541</v>
       </c>
-      <c r="L21" s="158"/>
-      <c r="M21" s="159"/>
+      <c r="L21" s="159"/>
+      <c r="M21" s="160"/>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="43" t="s">
@@ -16641,8 +16648,9 @@
     <col min="7" max="7" width="15" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17.42578125" customWidth="1"/>
     <col min="9" max="9" width="13.7109375" customWidth="1"/>
-    <col min="10" max="11" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="31.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.140625" customWidth="1"/>
+    <col min="12" max="12" width="24.28515625" customWidth="1"/>
     <col min="13" max="13" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="81.28515625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13.7109375" bestFit="1" customWidth="1"/>
@@ -16753,10 +16761,10 @@
       <c r="F7" s="111" t="s">
         <v>915</v>
       </c>
-      <c r="I7" s="188" t="s">
+      <c r="I7" s="189" t="s">
         <v>1166</v>
       </c>
-      <c r="J7" s="188"/>
+      <c r="J7" s="189"/>
       <c r="L7" s="49" t="s">
         <v>601</v>
       </c>
@@ -16774,7 +16782,7 @@
       <c r="D8" s="32" t="s">
         <v>582</v>
       </c>
-      <c r="E8" s="130" t="s">
+      <c r="E8" s="131" t="s">
         <v>583</v>
       </c>
       <c r="F8" s="36" t="s">
@@ -17059,8 +17067,8 @@
       <c r="I19" s="83"/>
       <c r="J19" s="83"/>
       <c r="K19" s="83"/>
-      <c r="L19" s="42"/>
-      <c r="M19" s="42"/>
+      <c r="L19" s="128"/>
+      <c r="M19" s="128"/>
     </row>
     <row r="20" spans="1:14">
       <c r="B20" s="32" t="s">
@@ -17091,13 +17099,17 @@
         <v>444</v>
       </c>
       <c r="K20" s="32" t="s">
+        <v>1351</v>
+      </c>
+      <c r="L20" s="32" t="s">
+        <v>1353</v>
+      </c>
+      <c r="M20" s="32" t="s">
         <v>415</v>
       </c>
-      <c r="L20" s="210" t="s">
+      <c r="N20" s="211" t="s">
         <v>568</v>
       </c>
-      <c r="M20" s="213"/>
-      <c r="N20" s="214"/>
     </row>
     <row r="21" spans="1:14">
       <c r="B21" s="85" t="s">
@@ -17127,10 +17139,16 @@
       <c r="J21" s="85" t="s">
         <v>445</v>
       </c>
-      <c r="K21" s="85" t="s">
+      <c r="K21" s="95" t="s">
+        <v>1352</v>
+      </c>
+      <c r="L21" s="95" t="s">
+        <v>1351</v>
+      </c>
+      <c r="M21" s="85" t="s">
         <v>466</v>
       </c>
-      <c r="L21" s="211" t="s">
+      <c r="N21" s="212" t="s">
         <v>429</v>
       </c>
     </row>
@@ -17162,10 +17180,16 @@
       <c r="J22" s="62" t="s">
         <v>587</v>
       </c>
-      <c r="K22" s="62" t="s">
+      <c r="K22" s="96" t="s">
+        <v>590</v>
+      </c>
+      <c r="L22" s="96" t="s">
+        <v>587</v>
+      </c>
+      <c r="M22" s="62" t="s">
         <v>592</v>
       </c>
-      <c r="L22" s="212" t="s">
+      <c r="N22" s="213" t="s">
         <v>458</v>
       </c>
     </row>
@@ -17195,8 +17219,12 @@
       <c r="J23" s="65">
         <v>200</v>
       </c>
-      <c r="K23" s="64"/>
-      <c r="L23" s="211" t="s">
+      <c r="K23" s="219"/>
+      <c r="L23" s="97">
+        <v>10</v>
+      </c>
+      <c r="M23" s="64"/>
+      <c r="N23" s="212" t="s">
         <v>1293</v>
       </c>
     </row>
@@ -17217,29 +17245,29 @@
       <c r="B27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="C27" s="174" t="s">
+      <c r="C27" s="175" t="s">
         <v>622</v>
       </c>
-      <c r="D27" s="175"/>
+      <c r="D27" s="176"/>
       <c r="E27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="F27" s="174" t="s">
+      <c r="F27" s="175" t="s">
         <v>622</v>
       </c>
-      <c r="G27" s="175"/>
+      <c r="G27" s="176"/>
       <c r="H27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="I27" s="174" t="s">
+      <c r="I27" s="175" t="s">
         <v>622</v>
       </c>
-      <c r="J27" s="175"/>
-      <c r="L27" s="172" t="s">
+      <c r="J27" s="176"/>
+      <c r="L27" s="173" t="s">
         <v>694</v>
       </c>
-      <c r="M27" s="172"/>
-      <c r="N27" s="172"/>
+      <c r="M27" s="173"/>
+      <c r="N27" s="173"/>
     </row>
     <row r="28" spans="1:14" ht="49.5" customHeight="1" thickBot="1">
       <c r="A28" s="81">
@@ -17248,29 +17276,29 @@
       <c r="B28" s="69" t="s">
         <v>623</v>
       </c>
-      <c r="C28" s="182" t="s">
+      <c r="C28" s="183" t="s">
         <v>624</v>
       </c>
-      <c r="D28" s="183"/>
+      <c r="D28" s="184"/>
       <c r="E28" s="70" t="s">
         <v>645</v>
       </c>
-      <c r="F28" s="176" t="s">
+      <c r="F28" s="177" t="s">
         <v>1178</v>
       </c>
-      <c r="G28" s="177"/>
+      <c r="G28" s="178"/>
       <c r="H28" s="69" t="s">
         <v>667</v>
       </c>
-      <c r="I28" s="182" t="s">
+      <c r="I28" s="183" t="s">
         <v>668</v>
       </c>
-      <c r="J28" s="183"/>
-      <c r="L28" s="173" t="s">
+      <c r="J28" s="184"/>
+      <c r="L28" s="174" t="s">
         <v>695</v>
       </c>
-      <c r="M28" s="173"/>
-      <c r="N28" s="173"/>
+      <c r="M28" s="174"/>
+      <c r="N28" s="174"/>
     </row>
     <row r="29" spans="1:14" ht="31.5" thickBot="1">
       <c r="A29" s="81">
@@ -17279,29 +17307,29 @@
       <c r="B29" s="70" t="s">
         <v>625</v>
       </c>
-      <c r="C29" s="176" t="s">
+      <c r="C29" s="177" t="s">
         <v>626</v>
       </c>
-      <c r="D29" s="177"/>
+      <c r="D29" s="178"/>
       <c r="E29" s="69" t="s">
         <v>647</v>
       </c>
-      <c r="F29" s="182" t="s">
+      <c r="F29" s="183" t="s">
         <v>648</v>
       </c>
-      <c r="G29" s="183"/>
+      <c r="G29" s="184"/>
       <c r="H29" s="70" t="s">
         <v>669</v>
       </c>
-      <c r="I29" s="186" t="s">
+      <c r="I29" s="187" t="s">
         <v>670</v>
       </c>
-      <c r="J29" s="187"/>
-      <c r="L29" s="172" t="s">
+      <c r="J29" s="188"/>
+      <c r="L29" s="173" t="s">
         <v>696</v>
       </c>
-      <c r="M29" s="172"/>
-      <c r="N29" s="172"/>
+      <c r="M29" s="173"/>
+      <c r="N29" s="173"/>
     </row>
     <row r="30" spans="1:14" ht="15.75" thickBot="1">
       <c r="A30" s="81">
@@ -17310,29 +17338,29 @@
       <c r="B30" s="69" t="s">
         <v>627</v>
       </c>
-      <c r="C30" s="182" t="s">
+      <c r="C30" s="183" t="s">
         <v>628</v>
       </c>
-      <c r="D30" s="183"/>
+      <c r="D30" s="184"/>
       <c r="E30" s="70" t="s">
         <v>649</v>
       </c>
-      <c r="F30" s="176" t="s">
+      <c r="F30" s="177" t="s">
         <v>650</v>
       </c>
-      <c r="G30" s="177"/>
+      <c r="G30" s="178"/>
       <c r="H30" s="69" t="s">
         <v>671</v>
       </c>
-      <c r="I30" s="182" t="s">
+      <c r="I30" s="183" t="s">
         <v>672</v>
       </c>
-      <c r="J30" s="183"/>
-      <c r="L30" s="173" t="s">
+      <c r="J30" s="184"/>
+      <c r="L30" s="174" t="s">
         <v>697</v>
       </c>
-      <c r="M30" s="173"/>
-      <c r="N30" s="173"/>
+      <c r="M30" s="174"/>
+      <c r="N30" s="174"/>
     </row>
     <row r="31" spans="1:14" ht="17.25" customHeight="1" thickBot="1">
       <c r="A31" s="81">
@@ -17341,29 +17369,29 @@
       <c r="B31" s="70" t="s">
         <v>629</v>
       </c>
-      <c r="C31" s="176" t="s">
+      <c r="C31" s="177" t="s">
         <v>630</v>
       </c>
-      <c r="D31" s="177"/>
+      <c r="D31" s="178"/>
       <c r="E31" s="69" t="s">
         <v>651</v>
       </c>
-      <c r="F31" s="182" t="s">
+      <c r="F31" s="183" t="s">
         <v>652</v>
       </c>
-      <c r="G31" s="183"/>
+      <c r="G31" s="184"/>
       <c r="H31" s="70" t="s">
         <v>673</v>
       </c>
-      <c r="I31" s="176" t="s">
+      <c r="I31" s="177" t="s">
         <v>674</v>
       </c>
-      <c r="J31" s="177"/>
-      <c r="L31" s="172" t="s">
+      <c r="J31" s="178"/>
+      <c r="L31" s="173" t="s">
         <v>698</v>
       </c>
-      <c r="M31" s="172"/>
-      <c r="N31" s="172"/>
+      <c r="M31" s="173"/>
+      <c r="N31" s="173"/>
     </row>
     <row r="32" spans="1:14" ht="43.5" customHeight="1" thickBot="1">
       <c r="A32" s="81">
@@ -17372,29 +17400,29 @@
       <c r="B32" s="69" t="s">
         <v>631</v>
       </c>
-      <c r="C32" s="182" t="s">
+      <c r="C32" s="183" t="s">
         <v>632</v>
       </c>
-      <c r="D32" s="183"/>
+      <c r="D32" s="184"/>
       <c r="E32" s="70" t="s">
         <v>653</v>
       </c>
-      <c r="F32" s="176" t="s">
+      <c r="F32" s="177" t="s">
         <v>654</v>
       </c>
-      <c r="G32" s="177"/>
+      <c r="G32" s="178"/>
       <c r="H32" s="69" t="s">
         <v>675</v>
       </c>
-      <c r="I32" s="182" t="s">
+      <c r="I32" s="183" t="s">
         <v>676</v>
       </c>
-      <c r="J32" s="183"/>
-      <c r="L32" s="173" t="s">
+      <c r="J32" s="184"/>
+      <c r="L32" s="174" t="s">
         <v>699</v>
       </c>
-      <c r="M32" s="173"/>
-      <c r="N32" s="173"/>
+      <c r="M32" s="174"/>
+      <c r="N32" s="174"/>
     </row>
     <row r="33" spans="1:14" ht="31.5" customHeight="1" thickBot="1">
       <c r="A33" s="81">
@@ -17403,29 +17431,29 @@
       <c r="B33" s="70" t="s">
         <v>633</v>
       </c>
-      <c r="C33" s="176" t="s">
+      <c r="C33" s="177" t="s">
         <v>634</v>
       </c>
-      <c r="D33" s="177"/>
+      <c r="D33" s="178"/>
       <c r="E33" s="69" t="s">
         <v>655</v>
       </c>
-      <c r="F33" s="182" t="s">
+      <c r="F33" s="183" t="s">
         <v>656</v>
       </c>
-      <c r="G33" s="183"/>
+      <c r="G33" s="184"/>
       <c r="H33" s="70" t="s">
         <v>677</v>
       </c>
-      <c r="I33" s="184" t="s">
+      <c r="I33" s="185" t="s">
         <v>678</v>
       </c>
-      <c r="J33" s="185"/>
-      <c r="L33" s="172" t="s">
+      <c r="J33" s="186"/>
+      <c r="L33" s="173" t="s">
         <v>700</v>
       </c>
-      <c r="M33" s="172"/>
-      <c r="N33" s="172"/>
+      <c r="M33" s="173"/>
+      <c r="N33" s="173"/>
     </row>
     <row r="34" spans="1:14" ht="28.5" customHeight="1" thickBot="1">
       <c r="A34" s="81">
@@ -17434,29 +17462,29 @@
       <c r="B34" s="69" t="s">
         <v>635</v>
       </c>
-      <c r="C34" s="182" t="s">
+      <c r="C34" s="183" t="s">
         <v>636</v>
       </c>
-      <c r="D34" s="183"/>
+      <c r="D34" s="184"/>
       <c r="E34" s="70" t="s">
         <v>657</v>
       </c>
-      <c r="F34" s="176" t="s">
+      <c r="F34" s="177" t="s">
         <v>658</v>
       </c>
-      <c r="G34" s="177"/>
+      <c r="G34" s="178"/>
       <c r="H34" s="69" t="s">
         <v>679</v>
       </c>
-      <c r="I34" s="180" t="s">
+      <c r="I34" s="181" t="s">
         <v>680</v>
       </c>
-      <c r="J34" s="181"/>
-      <c r="L34" s="173" t="s">
+      <c r="J34" s="182"/>
+      <c r="L34" s="174" t="s">
         <v>701</v>
       </c>
-      <c r="M34" s="173"/>
-      <c r="N34" s="173"/>
+      <c r="M34" s="174"/>
+      <c r="N34" s="174"/>
     </row>
     <row r="35" spans="1:14" ht="31.5" customHeight="1" thickBot="1">
       <c r="A35" s="81">
@@ -17465,29 +17493,29 @@
       <c r="B35" s="70" t="s">
         <v>637</v>
       </c>
-      <c r="C35" s="176" t="s">
+      <c r="C35" s="177" t="s">
         <v>638</v>
       </c>
-      <c r="D35" s="177"/>
+      <c r="D35" s="178"/>
       <c r="E35" s="69" t="s">
         <v>659</v>
       </c>
-      <c r="F35" s="182" t="s">
+      <c r="F35" s="183" t="s">
         <v>660</v>
       </c>
-      <c r="G35" s="183"/>
+      <c r="G35" s="184"/>
       <c r="H35" s="77" t="s">
         <v>681</v>
       </c>
-      <c r="I35" s="176" t="s">
+      <c r="I35" s="177" t="s">
         <v>682</v>
       </c>
-      <c r="J35" s="177"/>
-      <c r="L35" s="172" t="s">
+      <c r="J35" s="178"/>
+      <c r="L35" s="173" t="s">
         <v>702</v>
       </c>
-      <c r="M35" s="172"/>
-      <c r="N35" s="172"/>
+      <c r="M35" s="173"/>
+      <c r="N35" s="173"/>
     </row>
     <row r="36" spans="1:14" ht="60.75" thickBot="1">
       <c r="A36" s="81">
@@ -17496,17 +17524,17 @@
       <c r="B36" s="69" t="s">
         <v>639</v>
       </c>
-      <c r="C36" s="182" t="s">
+      <c r="C36" s="183" t="s">
         <v>640</v>
       </c>
-      <c r="D36" s="183"/>
+      <c r="D36" s="184"/>
       <c r="E36" s="70" t="s">
         <v>661</v>
       </c>
-      <c r="F36" s="176" t="s">
+      <c r="F36" s="177" t="s">
         <v>662</v>
       </c>
-      <c r="G36" s="177"/>
+      <c r="G36" s="178"/>
       <c r="H36" s="78"/>
       <c r="I36" s="71" t="s">
         <v>683</v>
@@ -17514,11 +17542,11 @@
       <c r="J36" s="72" t="s">
         <v>684</v>
       </c>
-      <c r="L36" s="173" t="s">
+      <c r="L36" s="174" t="s">
         <v>703</v>
       </c>
-      <c r="M36" s="173"/>
-      <c r="N36" s="173"/>
+      <c r="M36" s="174"/>
+      <c r="N36" s="174"/>
     </row>
     <row r="37" spans="1:14" ht="75.75" thickBot="1">
       <c r="A37" s="81">
@@ -17527,17 +17555,17 @@
       <c r="B37" s="70" t="s">
         <v>641</v>
       </c>
-      <c r="C37" s="176" t="s">
+      <c r="C37" s="177" t="s">
         <v>642</v>
       </c>
-      <c r="D37" s="177"/>
+      <c r="D37" s="178"/>
       <c r="E37" s="69" t="s">
         <v>663</v>
       </c>
-      <c r="F37" s="182" t="s">
+      <c r="F37" s="183" t="s">
         <v>664</v>
       </c>
-      <c r="G37" s="183"/>
+      <c r="G37" s="184"/>
       <c r="H37" s="78"/>
       <c r="I37" s="73" t="s">
         <v>685</v>
@@ -17553,17 +17581,17 @@
       <c r="B38" s="69" t="s">
         <v>643</v>
       </c>
-      <c r="C38" s="182" t="s">
+      <c r="C38" s="183" t="s">
         <v>644</v>
       </c>
-      <c r="D38" s="183"/>
+      <c r="D38" s="184"/>
       <c r="E38" s="70" t="s">
         <v>665</v>
       </c>
-      <c r="F38" s="176" t="s">
+      <c r="F38" s="177" t="s">
         <v>666</v>
       </c>
-      <c r="G38" s="177"/>
+      <c r="G38" s="178"/>
       <c r="H38" s="78"/>
       <c r="I38" s="75" t="s">
         <v>687</v>
@@ -17579,22 +17607,22 @@
       <c r="B39" s="70" t="s">
         <v>692</v>
       </c>
-      <c r="C39" s="184" t="s">
+      <c r="C39" s="185" t="s">
         <v>693</v>
       </c>
-      <c r="D39" s="185"/>
+      <c r="D39" s="186"/>
       <c r="E39" s="69" t="s">
         <v>690</v>
       </c>
-      <c r="F39" s="180" t="s">
+      <c r="F39" s="181" t="s">
         <v>691</v>
       </c>
-      <c r="G39" s="181"/>
+      <c r="G39" s="182"/>
       <c r="H39" s="79"/>
-      <c r="I39" s="178" t="s">
+      <c r="I39" s="179" t="s">
         <v>689</v>
       </c>
-      <c r="J39" s="179"/>
+      <c r="J39" s="180"/>
     </row>
     <row r="40" spans="1:14" ht="58.5" customHeight="1"/>
     <row r="41" spans="1:14">
@@ -17887,7 +17915,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="48">
+  <mergeCells count="47">
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="F36:G36"/>
     <mergeCell ref="L36:N36"/>
@@ -17931,7 +17959,6 @@
     <mergeCell ref="I29:J29"/>
     <mergeCell ref="L29:N29"/>
     <mergeCell ref="I7:J7"/>
-    <mergeCell ref="M20:N20"/>
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="I27:J27"/>
@@ -18513,16 +18540,16 @@
       </c>
     </row>
     <row r="2" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A2" s="189" t="s">
+      <c r="A2" s="190" t="s">
         <v>504</v>
       </c>
-      <c r="B2" s="198" t="s">
+      <c r="B2" s="199" t="s">
         <v>506</v>
       </c>
-      <c r="C2" s="189" t="s">
+      <c r="C2" s="190" t="s">
         <v>508</v>
       </c>
-      <c r="D2" s="189" t="s">
+      <c r="D2" s="190" t="s">
         <v>556</v>
       </c>
       <c r="E2" s="8"/>
@@ -18535,7 +18562,7 @@
       <c r="H2" s="10">
         <v>1</v>
       </c>
-      <c r="I2" s="209">
+      <c r="I2" s="210">
         <v>44043</v>
       </c>
       <c r="J2" s="10"/>
@@ -18545,10 +18572,10 @@
       </c>
     </row>
     <row r="3" spans="1:17">
-      <c r="A3" s="164"/>
-      <c r="B3" s="199"/>
-      <c r="C3" s="190"/>
-      <c r="D3" s="190"/>
+      <c r="A3" s="165"/>
+      <c r="B3" s="200"/>
+      <c r="C3" s="191"/>
+      <c r="D3" s="191"/>
       <c r="E3" s="11"/>
       <c r="F3" s="9" t="s">
         <v>310</v>
@@ -18559,7 +18586,7 @@
       <c r="H3" s="12">
         <v>2</v>
       </c>
-      <c r="I3" s="209">
+      <c r="I3" s="210">
         <v>44074</v>
       </c>
       <c r="J3" s="10"/>
@@ -18569,10 +18596,10 @@
       </c>
     </row>
     <row r="4" spans="1:17">
-      <c r="A4" s="164"/>
-      <c r="B4" s="199"/>
-      <c r="C4" s="190"/>
-      <c r="D4" s="191"/>
+      <c r="A4" s="165"/>
+      <c r="B4" s="200"/>
+      <c r="C4" s="191"/>
+      <c r="D4" s="192"/>
       <c r="E4" s="11"/>
       <c r="F4" s="9" t="s">
         <v>311</v>
@@ -18583,17 +18610,17 @@
       <c r="H4" s="12" t="s">
         <v>963</v>
       </c>
-      <c r="I4" s="209"/>
+      <c r="I4" s="210"/>
       <c r="J4" s="10"/>
       <c r="K4" s="10"/>
-      <c r="M4" s="218" t="s">
+      <c r="M4" s="217" t="s">
         <v>1299</v>
       </c>
     </row>
     <row r="5" spans="1:17">
-      <c r="A5" s="164"/>
-      <c r="B5" s="199"/>
-      <c r="C5" s="191"/>
+      <c r="A5" s="165"/>
+      <c r="B5" s="200"/>
+      <c r="C5" s="192"/>
       <c r="D5" s="46" t="s">
         <v>555</v>
       </c>
@@ -18607,7 +18634,7 @@
       <c r="H5" s="12" t="s">
         <v>960</v>
       </c>
-      <c r="I5" s="209">
+      <c r="I5" s="210">
         <v>44043</v>
       </c>
       <c r="J5" s="10" t="s">
@@ -18616,12 +18643,12 @@
       <c r="K5" s="10"/>
     </row>
     <row r="6" spans="1:17">
-      <c r="A6" s="164"/>
-      <c r="B6" s="199"/>
-      <c r="C6" s="189" t="s">
+      <c r="A6" s="165"/>
+      <c r="B6" s="200"/>
+      <c r="C6" s="190" t="s">
         <v>507</v>
       </c>
-      <c r="D6" s="189" t="s">
+      <c r="D6" s="190" t="s">
         <v>511</v>
       </c>
       <c r="E6" s="11"/>
@@ -18634,17 +18661,17 @@
       <c r="H6" s="12" t="s">
         <v>961</v>
       </c>
-      <c r="I6" s="209">
+      <c r="I6" s="210">
         <v>44043</v>
       </c>
       <c r="J6" s="10"/>
       <c r="K6" s="10"/>
     </row>
     <row r="7" spans="1:17">
-      <c r="A7" s="164"/>
-      <c r="B7" s="199"/>
-      <c r="C7" s="190"/>
-      <c r="D7" s="190"/>
+      <c r="A7" s="165"/>
+      <c r="B7" s="200"/>
+      <c r="C7" s="191"/>
+      <c r="D7" s="191"/>
       <c r="E7" s="11"/>
       <c r="F7" s="9" t="s">
         <v>313</v>
@@ -18655,17 +18682,17 @@
       <c r="H7" s="12">
         <v>1</v>
       </c>
-      <c r="I7" s="209">
+      <c r="I7" s="210">
         <v>44043</v>
       </c>
       <c r="J7" s="10"/>
       <c r="K7" s="10"/>
     </row>
     <row r="8" spans="1:17">
-      <c r="A8" s="164"/>
-      <c r="B8" s="199"/>
-      <c r="C8" s="190"/>
-      <c r="D8" s="190"/>
+      <c r="A8" s="165"/>
+      <c r="B8" s="200"/>
+      <c r="C8" s="191"/>
+      <c r="D8" s="191"/>
       <c r="E8" s="11"/>
       <c r="F8" s="9" t="s">
         <v>314</v>
@@ -18676,17 +18703,17 @@
       <c r="H8" s="12">
         <v>1</v>
       </c>
-      <c r="I8" s="209">
+      <c r="I8" s="210">
         <v>44043</v>
       </c>
       <c r="J8" s="10"/>
       <c r="K8" s="10"/>
     </row>
     <row r="9" spans="1:17">
-      <c r="A9" s="164"/>
-      <c r="B9" s="199"/>
-      <c r="C9" s="190"/>
-      <c r="D9" s="190"/>
+      <c r="A9" s="165"/>
+      <c r="B9" s="200"/>
+      <c r="C9" s="191"/>
+      <c r="D9" s="191"/>
       <c r="E9" s="8"/>
       <c r="F9" s="9" t="s">
         <v>345</v>
@@ -18697,17 +18724,17 @@
       <c r="H9" s="10">
         <v>1</v>
       </c>
-      <c r="I9" s="209">
+      <c r="I9" s="210">
         <v>44043</v>
       </c>
       <c r="J9" s="10"/>
       <c r="K9" s="10"/>
     </row>
     <row r="10" spans="1:17">
-      <c r="A10" s="164"/>
-      <c r="B10" s="199"/>
-      <c r="C10" s="190"/>
-      <c r="D10" s="190"/>
+      <c r="A10" s="165"/>
+      <c r="B10" s="200"/>
+      <c r="C10" s="191"/>
+      <c r="D10" s="191"/>
       <c r="E10" s="8"/>
       <c r="F10" s="9" t="s">
         <v>346</v>
@@ -18718,17 +18745,17 @@
       <c r="H10" s="10">
         <v>1</v>
       </c>
-      <c r="I10" s="209">
+      <c r="I10" s="210">
         <v>44043</v>
       </c>
       <c r="J10" s="10"/>
       <c r="K10" s="10"/>
     </row>
     <row r="11" spans="1:17">
-      <c r="A11" s="164"/>
-      <c r="B11" s="199"/>
-      <c r="C11" s="190"/>
-      <c r="D11" s="190"/>
+      <c r="A11" s="165"/>
+      <c r="B11" s="200"/>
+      <c r="C11" s="191"/>
+      <c r="D11" s="191"/>
       <c r="E11" s="8"/>
       <c r="F11" s="9" t="s">
         <v>315</v>
@@ -18739,17 +18766,17 @@
       <c r="H11" s="10">
         <v>1</v>
       </c>
-      <c r="I11" s="209">
+      <c r="I11" s="210">
         <v>44043</v>
       </c>
       <c r="J11" s="10"/>
       <c r="K11" s="10"/>
     </row>
     <row r="12" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A12" s="164"/>
-      <c r="B12" s="199"/>
-      <c r="C12" s="190"/>
-      <c r="D12" s="190"/>
+      <c r="A12" s="165"/>
+      <c r="B12" s="200"/>
+      <c r="C12" s="191"/>
+      <c r="D12" s="191"/>
       <c r="E12" s="8"/>
       <c r="F12" s="9" t="s">
         <v>347</v>
@@ -18760,17 +18787,17 @@
       <c r="H12" s="10">
         <v>1</v>
       </c>
-      <c r="I12" s="209">
+      <c r="I12" s="210">
         <v>44043</v>
       </c>
       <c r="J12" s="10"/>
       <c r="K12" s="10"/>
     </row>
     <row r="13" spans="1:17" ht="30">
-      <c r="A13" s="164"/>
-      <c r="B13" s="199"/>
-      <c r="C13" s="190"/>
-      <c r="D13" s="190"/>
+      <c r="A13" s="165"/>
+      <c r="B13" s="200"/>
+      <c r="C13" s="191"/>
+      <c r="D13" s="191"/>
       <c r="E13" s="11"/>
       <c r="F13" s="9" t="s">
         <v>316</v>
@@ -18781,7 +18808,7 @@
       <c r="H13" s="12">
         <v>3</v>
       </c>
-      <c r="I13" s="209"/>
+      <c r="I13" s="210"/>
       <c r="J13" s="10" t="s">
         <v>563</v>
       </c>
@@ -18791,10 +18818,10 @@
       </c>
     </row>
     <row r="14" spans="1:17">
-      <c r="A14" s="164"/>
-      <c r="B14" s="199"/>
-      <c r="C14" s="190"/>
-      <c r="D14" s="191"/>
+      <c r="A14" s="165"/>
+      <c r="B14" s="200"/>
+      <c r="C14" s="191"/>
+      <c r="D14" s="192"/>
       <c r="E14" s="11"/>
       <c r="F14" s="9" t="s">
         <v>318</v>
@@ -18805,16 +18832,16 @@
       <c r="H14" s="12" t="s">
         <v>963</v>
       </c>
-      <c r="I14" s="209" t="s">
+      <c r="I14" s="210" t="s">
         <v>1298</v>
       </c>
       <c r="J14" s="10"/>
       <c r="K14" s="10"/>
     </row>
     <row r="15" spans="1:17" ht="30">
-      <c r="A15" s="164"/>
-      <c r="B15" s="199"/>
-      <c r="C15" s="190"/>
+      <c r="A15" s="165"/>
+      <c r="B15" s="200"/>
+      <c r="C15" s="191"/>
       <c r="D15" s="22" t="s">
         <v>512</v>
       </c>
@@ -18828,15 +18855,15 @@
       <c r="H15" s="12">
         <v>1</v>
       </c>
-      <c r="I15" s="209">
+      <c r="I15" s="210">
         <v>44043</v>
       </c>
       <c r="J15" s="10"/>
       <c r="K15" s="10"/>
-      <c r="M15" s="194" t="s">
+      <c r="M15" s="195" t="s">
         <v>851</v>
       </c>
-      <c r="N15" s="195"/>
+      <c r="N15" s="196"/>
       <c r="O15" s="114" t="s">
         <v>1258</v>
       </c>
@@ -18846,12 +18873,12 @@
       </c>
     </row>
     <row r="16" spans="1:17" ht="30">
-      <c r="A16" s="164"/>
-      <c r="B16" s="199"/>
-      <c r="C16" s="189" t="s">
+      <c r="A16" s="165"/>
+      <c r="B16" s="200"/>
+      <c r="C16" s="190" t="s">
         <v>509</v>
       </c>
-      <c r="D16" s="189" t="s">
+      <c r="D16" s="190" t="s">
         <v>513</v>
       </c>
       <c r="E16" s="11"/>
@@ -18864,7 +18891,7 @@
       <c r="H16" s="12">
         <v>1</v>
       </c>
-      <c r="I16" s="209">
+      <c r="I16" s="210">
         <v>44043</v>
       </c>
       <c r="J16" s="10"/>
@@ -18886,10 +18913,10 @@
       </c>
     </row>
     <row r="17" spans="1:17">
-      <c r="A17" s="164"/>
-      <c r="B17" s="199"/>
-      <c r="C17" s="190"/>
-      <c r="D17" s="190"/>
+      <c r="A17" s="165"/>
+      <c r="B17" s="200"/>
+      <c r="C17" s="191"/>
+      <c r="D17" s="191"/>
       <c r="E17" s="19"/>
       <c r="F17" s="9" t="s">
         <v>364</v>
@@ -18900,7 +18927,7 @@
       <c r="H17" s="12">
         <v>1</v>
       </c>
-      <c r="I17" s="209">
+      <c r="I17" s="210">
         <v>44043</v>
       </c>
       <c r="J17" s="10"/>
@@ -18919,10 +18946,10 @@
       </c>
     </row>
     <row r="18" spans="1:17">
-      <c r="A18" s="164"/>
-      <c r="B18" s="199"/>
-      <c r="C18" s="190"/>
-      <c r="D18" s="190"/>
+      <c r="A18" s="165"/>
+      <c r="B18" s="200"/>
+      <c r="C18" s="191"/>
+      <c r="D18" s="191"/>
       <c r="E18" s="19"/>
       <c r="F18" s="48" t="s">
         <v>559</v>
@@ -18933,7 +18960,7 @@
       <c r="H18" s="10">
         <v>1</v>
       </c>
-      <c r="I18" s="209">
+      <c r="I18" s="210">
         <v>44043</v>
       </c>
       <c r="J18" s="10" t="s">
@@ -18954,10 +18981,10 @@
       </c>
     </row>
     <row r="19" spans="1:17">
-      <c r="A19" s="164"/>
-      <c r="B19" s="199"/>
-      <c r="C19" s="190"/>
-      <c r="D19" s="190"/>
+      <c r="A19" s="165"/>
+      <c r="B19" s="200"/>
+      <c r="C19" s="191"/>
+      <c r="D19" s="191"/>
       <c r="E19" s="8"/>
       <c r="F19" s="9" t="s">
         <v>332</v>
@@ -18968,7 +18995,7 @@
       <c r="H19" s="10">
         <v>1</v>
       </c>
-      <c r="I19" s="209">
+      <c r="I19" s="210">
         <v>44043</v>
       </c>
       <c r="J19" s="10"/>
@@ -18988,10 +19015,10 @@
       <c r="Q19" s="91"/>
     </row>
     <row r="20" spans="1:17">
-      <c r="A20" s="164"/>
-      <c r="B20" s="199"/>
-      <c r="C20" s="190"/>
-      <c r="D20" s="190"/>
+      <c r="A20" s="165"/>
+      <c r="B20" s="200"/>
+      <c r="C20" s="191"/>
+      <c r="D20" s="191"/>
       <c r="E20" s="8"/>
       <c r="F20" s="9" t="s">
         <v>333</v>
@@ -19002,7 +19029,7 @@
       <c r="H20" s="10">
         <v>1</v>
       </c>
-      <c r="I20" s="209">
+      <c r="I20" s="210">
         <v>44043</v>
       </c>
       <c r="J20" s="10"/>
@@ -19022,10 +19049,10 @@
       <c r="Q20" s="91"/>
     </row>
     <row r="21" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A21" s="164"/>
-      <c r="B21" s="199"/>
-      <c r="C21" s="190"/>
-      <c r="D21" s="190"/>
+      <c r="A21" s="165"/>
+      <c r="B21" s="200"/>
+      <c r="C21" s="191"/>
+      <c r="D21" s="191"/>
       <c r="E21" s="14"/>
       <c r="F21" s="9" t="s">
         <v>334</v>
@@ -19036,7 +19063,7 @@
       <c r="H21" s="16">
         <v>3</v>
       </c>
-      <c r="I21" s="209"/>
+      <c r="I21" s="210"/>
       <c r="J21" s="10" t="s">
         <v>563</v>
       </c>
@@ -19058,10 +19085,10 @@
       </c>
     </row>
     <row r="22" spans="1:17">
-      <c r="A22" s="164"/>
-      <c r="B22" s="199"/>
-      <c r="C22" s="190"/>
-      <c r="D22" s="190"/>
+      <c r="A22" s="165"/>
+      <c r="B22" s="200"/>
+      <c r="C22" s="191"/>
+      <c r="D22" s="191"/>
       <c r="E22" s="14"/>
       <c r="F22" s="9" t="s">
         <v>335</v>
@@ -19072,7 +19099,7 @@
       <c r="H22" s="16">
         <v>1</v>
       </c>
-      <c r="I22" s="209">
+      <c r="I22" s="210">
         <v>44043</v>
       </c>
       <c r="J22" s="10"/>
@@ -19094,10 +19121,10 @@
       </c>
     </row>
     <row r="23" spans="1:17">
-      <c r="A23" s="164"/>
-      <c r="B23" s="199"/>
-      <c r="C23" s="190"/>
-      <c r="D23" s="190"/>
+      <c r="A23" s="165"/>
+      <c r="B23" s="200"/>
+      <c r="C23" s="191"/>
+      <c r="D23" s="191"/>
       <c r="E23" s="14"/>
       <c r="F23" s="9" t="s">
         <v>336</v>
@@ -19108,7 +19135,7 @@
       <c r="H23" s="16">
         <v>2</v>
       </c>
-      <c r="I23" s="209">
+      <c r="I23" s="210">
         <v>44074</v>
       </c>
       <c r="J23" s="10"/>
@@ -19122,18 +19149,18 @@
       <c r="O23" s="99" t="s">
         <v>81</v>
       </c>
-      <c r="P23" s="215" t="s">
+      <c r="P23" s="214" t="s">
         <v>962</v>
       </c>
-      <c r="Q23" s="153" t="s">
+      <c r="Q23" s="154" t="s">
         <v>1284</v>
       </c>
     </row>
     <row r="24" spans="1:17">
-      <c r="A24" s="164"/>
-      <c r="B24" s="199"/>
-      <c r="C24" s="190"/>
-      <c r="D24" s="190"/>
+      <c r="A24" s="165"/>
+      <c r="B24" s="200"/>
+      <c r="C24" s="191"/>
+      <c r="D24" s="191"/>
       <c r="E24" s="8"/>
       <c r="F24" s="9" t="s">
         <v>1281</v>
@@ -19144,12 +19171,12 @@
       <c r="H24" s="10">
         <v>2</v>
       </c>
-      <c r="I24" s="209">
+      <c r="I24" s="210">
         <v>44074</v>
       </c>
       <c r="J24" s="10"/>
       <c r="K24" s="10"/>
-      <c r="M24" s="152" t="s">
+      <c r="M24" s="153" t="s">
         <v>1280</v>
       </c>
       <c r="N24" s="98" t="s">
@@ -19164,10 +19191,10 @@
       <c r="Q24" s="91"/>
     </row>
     <row r="25" spans="1:17">
-      <c r="A25" s="164"/>
-      <c r="B25" s="199"/>
-      <c r="C25" s="190"/>
-      <c r="D25" s="190"/>
+      <c r="A25" s="165"/>
+      <c r="B25" s="200"/>
+      <c r="C25" s="191"/>
+      <c r="D25" s="191"/>
       <c r="E25" s="8"/>
       <c r="F25" s="9" t="s">
         <v>373</v>
@@ -19178,7 +19205,7 @@
       <c r="H25" s="10">
         <v>3</v>
       </c>
-      <c r="I25" s="209"/>
+      <c r="I25" s="210"/>
       <c r="J25" s="10" t="s">
         <v>563</v>
       </c>
@@ -19198,10 +19225,10 @@
       <c r="Q25" s="91"/>
     </row>
     <row r="26" spans="1:17">
-      <c r="A26" s="164"/>
-      <c r="B26" s="199"/>
-      <c r="C26" s="190"/>
-      <c r="D26" s="190"/>
+      <c r="A26" s="165"/>
+      <c r="B26" s="200"/>
+      <c r="C26" s="191"/>
+      <c r="D26" s="191"/>
       <c r="E26" s="8"/>
       <c r="F26" s="9" t="s">
         <v>338</v>
@@ -19212,7 +19239,7 @@
       <c r="H26" s="10" t="s">
         <v>963</v>
       </c>
-      <c r="I26" s="209"/>
+      <c r="I26" s="210"/>
       <c r="J26" s="10"/>
       <c r="K26" s="10"/>
       <c r="M26" s="99" t="s">
@@ -19230,10 +19257,10 @@
       <c r="Q26" s="91"/>
     </row>
     <row r="27" spans="1:17">
-      <c r="A27" s="164"/>
-      <c r="B27" s="199"/>
-      <c r="C27" s="190"/>
-      <c r="D27" s="190"/>
+      <c r="A27" s="165"/>
+      <c r="B27" s="200"/>
+      <c r="C27" s="191"/>
+      <c r="D27" s="191"/>
       <c r="E27" s="8"/>
       <c r="F27" s="9" t="s">
         <v>339</v>
@@ -19244,7 +19271,7 @@
       <c r="H27" s="119" t="s">
         <v>1297</v>
       </c>
-      <c r="I27" s="209" t="s">
+      <c r="I27" s="210" t="s">
         <v>1332</v>
       </c>
       <c r="J27" s="10"/>
@@ -19264,10 +19291,10 @@
       <c r="Q27" s="91"/>
     </row>
     <row r="28" spans="1:17">
-      <c r="A28" s="164"/>
-      <c r="B28" s="199"/>
-      <c r="C28" s="190"/>
-      <c r="D28" s="190"/>
+      <c r="A28" s="165"/>
+      <c r="B28" s="200"/>
+      <c r="C28" s="191"/>
+      <c r="D28" s="191"/>
       <c r="E28" s="8"/>
       <c r="F28" s="121" t="s">
         <v>965</v>
@@ -19278,7 +19305,7 @@
       <c r="H28" s="10">
         <v>1</v>
       </c>
-      <c r="I28" s="209">
+      <c r="I28" s="210">
         <v>44043</v>
       </c>
       <c r="J28" s="10"/>
@@ -19298,10 +19325,10 @@
       <c r="Q28" s="91"/>
     </row>
     <row r="29" spans="1:17">
-      <c r="A29" s="164"/>
-      <c r="B29" s="199"/>
-      <c r="C29" s="190"/>
-      <c r="D29" s="190"/>
+      <c r="A29" s="165"/>
+      <c r="B29" s="200"/>
+      <c r="C29" s="191"/>
+      <c r="D29" s="191"/>
       <c r="E29" s="8"/>
       <c r="F29" s="9" t="s">
         <v>955</v>
@@ -19312,7 +19339,7 @@
       <c r="H29" s="16" t="s">
         <v>963</v>
       </c>
-      <c r="I29" s="209" t="s">
+      <c r="I29" s="210" t="s">
         <v>1332</v>
       </c>
       <c r="J29" s="10"/>
@@ -19321,10 +19348,10 @@
       </c>
     </row>
     <row r="30" spans="1:17">
-      <c r="A30" s="164"/>
-      <c r="B30" s="199"/>
-      <c r="C30" s="190"/>
-      <c r="D30" s="191"/>
+      <c r="A30" s="165"/>
+      <c r="B30" s="200"/>
+      <c r="C30" s="191"/>
+      <c r="D30" s="192"/>
       <c r="E30" s="8"/>
       <c r="F30" s="49" t="s">
         <v>323</v>
@@ -19335,11 +19362,11 @@
       <c r="H30" s="113">
         <v>3</v>
       </c>
-      <c r="I30" s="209" t="s">
+      <c r="I30" s="210" t="s">
         <v>1332</v>
       </c>
       <c r="J30" s="10"/>
-      <c r="K30" s="192" t="s">
+      <c r="K30" s="193" t="s">
         <v>959</v>
       </c>
       <c r="M30" s="101" t="s">
@@ -19356,10 +19383,10 @@
       </c>
     </row>
     <row r="31" spans="1:17">
-      <c r="A31" s="164"/>
-      <c r="B31" s="199"/>
-      <c r="C31" s="190"/>
-      <c r="D31" s="189" t="s">
+      <c r="A31" s="165"/>
+      <c r="B31" s="200"/>
+      <c r="C31" s="191"/>
+      <c r="D31" s="190" t="s">
         <v>518</v>
       </c>
       <c r="E31" s="8"/>
@@ -19372,17 +19399,17 @@
       <c r="H31" s="16">
         <v>1</v>
       </c>
-      <c r="I31" s="209">
+      <c r="I31" s="210">
         <v>44043</v>
       </c>
       <c r="J31" s="10"/>
-      <c r="K31" s="196"/>
+      <c r="K31" s="197"/>
     </row>
     <row r="32" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A32" s="164"/>
-      <c r="B32" s="199"/>
-      <c r="C32" s="190"/>
-      <c r="D32" s="190"/>
+      <c r="A32" s="165"/>
+      <c r="B32" s="200"/>
+      <c r="C32" s="191"/>
+      <c r="D32" s="191"/>
       <c r="E32" s="8"/>
       <c r="F32" s="9" t="s">
         <v>325</v>
@@ -19393,20 +19420,20 @@
       <c r="H32" s="16">
         <v>1</v>
       </c>
-      <c r="I32" s="209">
+      <c r="I32" s="210">
         <v>44043</v>
       </c>
       <c r="J32" s="10"/>
-      <c r="K32" s="196"/>
-      <c r="M32" s="150" t="s">
+      <c r="K32" s="197"/>
+      <c r="M32" s="151" t="s">
         <v>1277</v>
       </c>
     </row>
     <row r="33" spans="1:15" ht="16.5" customHeight="1">
-      <c r="A33" s="164"/>
-      <c r="B33" s="199"/>
-      <c r="C33" s="190"/>
-      <c r="D33" s="190"/>
+      <c r="A33" s="165"/>
+      <c r="B33" s="200"/>
+      <c r="C33" s="191"/>
+      <c r="D33" s="191"/>
       <c r="E33" s="8"/>
       <c r="F33" s="9" t="s">
         <v>957</v>
@@ -19417,14 +19444,14 @@
       <c r="H33" s="16">
         <v>2</v>
       </c>
-      <c r="I33" s="209">
+      <c r="I33" s="210">
         <v>44043</v>
       </c>
       <c r="J33" s="10" t="s">
         <v>954</v>
       </c>
-      <c r="K33" s="197"/>
-      <c r="M33" s="151" t="s">
+      <c r="K33" s="198"/>
+      <c r="M33" s="152" t="s">
         <v>1278</v>
       </c>
       <c r="N33" s="5" t="s">
@@ -19435,10 +19462,10 @@
       </c>
     </row>
     <row r="34" spans="1:15" ht="16.5" customHeight="1">
-      <c r="A34" s="164"/>
-      <c r="B34" s="199"/>
-      <c r="C34" s="190"/>
-      <c r="D34" s="190"/>
+      <c r="A34" s="165"/>
+      <c r="B34" s="200"/>
+      <c r="C34" s="191"/>
+      <c r="D34" s="191"/>
       <c r="E34" s="8"/>
       <c r="F34" s="9" t="s">
         <v>1275</v>
@@ -19449,7 +19476,7 @@
       <c r="H34" s="118">
         <v>2</v>
       </c>
-      <c r="I34" s="209">
+      <c r="I34" s="210">
         <v>44074</v>
       </c>
       <c r="J34" s="10"/>
@@ -19458,10 +19485,10 @@
       </c>
     </row>
     <row r="35" spans="1:15">
-      <c r="A35" s="164"/>
-      <c r="B35" s="199"/>
-      <c r="C35" s="191"/>
-      <c r="D35" s="191"/>
+      <c r="A35" s="165"/>
+      <c r="B35" s="200"/>
+      <c r="C35" s="192"/>
+      <c r="D35" s="192"/>
       <c r="E35" s="8"/>
       <c r="F35" s="49" t="s">
         <v>322</v>
@@ -19472,19 +19499,19 @@
       <c r="H35" s="50">
         <v>3</v>
       </c>
-      <c r="I35" s="209" t="s">
+      <c r="I35" s="210" t="s">
         <v>1332</v>
       </c>
       <c r="J35" s="10"/>
       <c r="K35" s="10"/>
     </row>
     <row r="36" spans="1:15">
-      <c r="A36" s="164"/>
-      <c r="B36" s="199"/>
-      <c r="C36" s="189" t="s">
+      <c r="A36" s="165"/>
+      <c r="B36" s="200"/>
+      <c r="C36" s="190" t="s">
         <v>340</v>
       </c>
-      <c r="D36" s="189" t="s">
+      <c r="D36" s="190" t="s">
         <v>517</v>
       </c>
       <c r="E36" s="8"/>
@@ -19497,17 +19524,17 @@
       <c r="H36" s="16">
         <v>1</v>
       </c>
-      <c r="I36" s="209">
+      <c r="I36" s="210">
         <v>44043</v>
       </c>
       <c r="J36" s="10"/>
       <c r="K36" s="10"/>
     </row>
     <row r="37" spans="1:15">
-      <c r="A37" s="164"/>
-      <c r="B37" s="200"/>
-      <c r="C37" s="191"/>
-      <c r="D37" s="191"/>
+      <c r="A37" s="165"/>
+      <c r="B37" s="201"/>
+      <c r="C37" s="192"/>
+      <c r="D37" s="192"/>
       <c r="E37" s="8"/>
       <c r="F37" s="9" t="s">
         <v>331</v>
@@ -19518,12 +19545,12 @@
       <c r="H37" s="120" t="s">
         <v>963</v>
       </c>
-      <c r="I37" s="209"/>
+      <c r="I37" s="210"/>
       <c r="J37" s="10"/>
       <c r="K37" s="10"/>
     </row>
     <row r="38" spans="1:15">
-      <c r="A38" s="164"/>
+      <c r="A38" s="165"/>
       <c r="B38" s="29" t="s">
         <v>328</v>
       </c>
@@ -19543,19 +19570,19 @@
       <c r="H38" s="16" t="s">
         <v>330</v>
       </c>
-      <c r="I38" s="209"/>
+      <c r="I38" s="210"/>
       <c r="J38" s="10"/>
       <c r="K38" s="10"/>
     </row>
     <row r="39" spans="1:15" ht="16.5" customHeight="1">
-      <c r="A39" s="164"/>
-      <c r="B39" s="198" t="s">
+      <c r="A39" s="165"/>
+      <c r="B39" s="199" t="s">
         <v>505</v>
       </c>
-      <c r="C39" s="189" t="s">
+      <c r="C39" s="190" t="s">
         <v>510</v>
       </c>
-      <c r="D39" s="189" t="s">
+      <c r="D39" s="190" t="s">
         <v>516</v>
       </c>
       <c r="E39" s="8" t="s">
@@ -19570,17 +19597,17 @@
       <c r="H39" s="10">
         <v>2</v>
       </c>
-      <c r="I39" s="209" t="s">
+      <c r="I39" s="210" t="s">
         <v>1331</v>
       </c>
       <c r="J39" s="10"/>
       <c r="K39" s="10"/>
     </row>
     <row r="40" spans="1:15" ht="16.5" customHeight="1">
-      <c r="A40" s="164"/>
-      <c r="B40" s="199"/>
-      <c r="C40" s="164"/>
-      <c r="D40" s="164"/>
+      <c r="A40" s="165"/>
+      <c r="B40" s="200"/>
+      <c r="C40" s="165"/>
+      <c r="D40" s="165"/>
       <c r="E40" s="17"/>
       <c r="F40" s="9" t="s">
         <v>304</v>
@@ -19591,17 +19618,17 @@
       <c r="H40" s="16">
         <v>1</v>
       </c>
-      <c r="I40" s="209">
+      <c r="I40" s="210">
         <v>44043</v>
       </c>
       <c r="J40" s="10"/>
       <c r="K40" s="10"/>
     </row>
     <row r="41" spans="1:15" ht="16.5" customHeight="1">
-      <c r="A41" s="164"/>
-      <c r="B41" s="199"/>
-      <c r="C41" s="164"/>
-      <c r="D41" s="164"/>
+      <c r="A41" s="165"/>
+      <c r="B41" s="200"/>
+      <c r="C41" s="165"/>
+      <c r="D41" s="165"/>
       <c r="E41" s="17"/>
       <c r="F41" s="9" t="s">
         <v>305</v>
@@ -19612,17 +19639,17 @@
       <c r="H41" s="16">
         <v>1</v>
       </c>
-      <c r="I41" s="209">
+      <c r="I41" s="210">
         <v>44043</v>
       </c>
       <c r="J41" s="10"/>
       <c r="K41" s="10"/>
     </row>
     <row r="42" spans="1:15">
-      <c r="A42" s="164"/>
-      <c r="B42" s="199"/>
-      <c r="C42" s="164"/>
-      <c r="D42" s="165"/>
+      <c r="A42" s="165"/>
+      <c r="B42" s="200"/>
+      <c r="C42" s="165"/>
+      <c r="D42" s="166"/>
       <c r="E42" s="17"/>
       <c r="F42" s="9" t="s">
         <v>305</v>
@@ -19633,17 +19660,17 @@
       <c r="H42" s="16">
         <v>2</v>
       </c>
-      <c r="I42" s="209">
+      <c r="I42" s="210">
         <v>44074</v>
       </c>
       <c r="J42" s="10"/>
       <c r="K42" s="10"/>
     </row>
     <row r="43" spans="1:15" ht="16.5" customHeight="1">
-      <c r="A43" s="164"/>
-      <c r="B43" s="199"/>
-      <c r="C43" s="164"/>
-      <c r="D43" s="189" t="s">
+      <c r="A43" s="165"/>
+      <c r="B43" s="200"/>
+      <c r="C43" s="165"/>
+      <c r="D43" s="190" t="s">
         <v>515</v>
       </c>
       <c r="E43" s="8"/>
@@ -19656,19 +19683,19 @@
       <c r="H43" s="10" t="s">
         <v>961</v>
       </c>
-      <c r="I43" s="209">
+      <c r="I43" s="210">
         <v>44043</v>
       </c>
       <c r="J43" s="10"/>
-      <c r="K43" s="192" t="s">
+      <c r="K43" s="193" t="s">
         <v>1164</v>
       </c>
     </row>
     <row r="44" spans="1:15">
-      <c r="A44" s="164"/>
-      <c r="B44" s="199"/>
-      <c r="C44" s="164"/>
-      <c r="D44" s="165"/>
+      <c r="A44" s="165"/>
+      <c r="B44" s="200"/>
+      <c r="C44" s="165"/>
+      <c r="D44" s="166"/>
       <c r="E44" s="8"/>
       <c r="F44" s="9" t="s">
         <v>289</v>
@@ -19679,17 +19706,17 @@
       <c r="H44" s="10" t="s">
         <v>961</v>
       </c>
-      <c r="I44" s="209">
+      <c r="I44" s="210">
         <v>44043</v>
       </c>
       <c r="J44" s="10"/>
-      <c r="K44" s="193"/>
+      <c r="K44" s="194"/>
     </row>
     <row r="45" spans="1:15">
-      <c r="A45" s="164"/>
-      <c r="B45" s="199"/>
-      <c r="C45" s="164"/>
-      <c r="D45" s="189" t="s">
+      <c r="A45" s="165"/>
+      <c r="B45" s="200"/>
+      <c r="C45" s="165"/>
+      <c r="D45" s="190" t="s">
         <v>514</v>
       </c>
       <c r="E45" s="8"/>
@@ -19702,15 +19729,15 @@
       <c r="H45" s="10" t="s">
         <v>963</v>
       </c>
-      <c r="I45" s="209"/>
+      <c r="I45" s="210"/>
       <c r="J45" s="10"/>
       <c r="K45" s="10"/>
     </row>
     <row r="46" spans="1:15">
-      <c r="A46" s="165"/>
-      <c r="B46" s="200"/>
-      <c r="C46" s="165"/>
-      <c r="D46" s="165"/>
+      <c r="A46" s="166"/>
+      <c r="B46" s="201"/>
+      <c r="C46" s="166"/>
+      <c r="D46" s="166"/>
       <c r="E46" s="8"/>
       <c r="F46" s="9" t="s">
         <v>301</v>
@@ -19721,38 +19748,38 @@
       <c r="H46" s="10" t="s">
         <v>963</v>
       </c>
-      <c r="I46" s="209"/>
+      <c r="I46" s="210"/>
       <c r="J46" s="10"/>
       <c r="K46" s="10"/>
     </row>
     <row r="48" spans="1:15">
-      <c r="H48" s="216" t="s">
+      <c r="H48" s="215" t="s">
         <v>1333</v>
       </c>
       <c r="I48">
         <f>COUNTA($I$2:$I$46)</f>
         <v>36</v>
       </c>
-      <c r="J48" s="217">
+      <c r="J48" s="216">
         <f>I48/$I$50</f>
         <v>0.8</v>
       </c>
     </row>
     <row r="49" spans="8:10">
-      <c r="H49" s="216" t="s">
+      <c r="H49" s="215" t="s">
         <v>1334</v>
       </c>
       <c r="I49">
         <f>COUNTBLANK($I$2:$I$46)</f>
         <v>9</v>
       </c>
-      <c r="J49" s="217">
+      <c r="J49" s="216">
         <f>I49/$I$50</f>
         <v>0.2</v>
       </c>
     </row>
     <row r="50" spans="8:10">
-      <c r="H50" s="216" t="s">
+      <c r="H50" s="215" t="s">
         <v>852</v>
       </c>
       <c r="I50">
@@ -19873,7 +19900,7 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="33" spans="1:12">
+    <row r="33" spans="1:16">
       <c r="A33" t="s">
         <v>1309</v>
       </c>
@@ -19881,15 +19908,18 @@
         <v>1341</v>
       </c>
     </row>
-    <row r="34" spans="1:12">
+    <row r="34" spans="1:16">
       <c r="A34" t="s">
         <v>1310</v>
       </c>
       <c r="L34" t="s">
         <v>1348</v>
       </c>
-    </row>
-    <row r="35" spans="1:12">
+      <c r="P34" s="220" t="s">
+        <v>1354</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16">
       <c r="A35" t="s">
         <v>1311</v>
       </c>
@@ -19900,7 +19930,7 @@
         <v>1343</v>
       </c>
     </row>
-    <row r="36" spans="1:12">
+    <row r="36" spans="1:16">
       <c r="A36" t="s">
         <v>1312</v>
       </c>
@@ -19908,15 +19938,15 @@
         <v>1344</v>
       </c>
     </row>
-    <row r="37" spans="1:12">
+    <row r="37" spans="1:16">
       <c r="A37" t="s">
         <v>1313</v>
       </c>
-      <c r="L37" s="219" t="s">
+      <c r="L37" s="218" t="s">
         <v>1345</v>
       </c>
     </row>
-    <row r="38" spans="1:12">
+    <row r="38" spans="1:16">
       <c r="A38" t="s">
         <v>1314</v>
       </c>
@@ -19927,7 +19957,7 @@
         <v>1346</v>
       </c>
     </row>
-    <row r="39" spans="1:12">
+    <row r="39" spans="1:16">
       <c r="A39" t="s">
         <v>1315</v>
       </c>
@@ -19938,7 +19968,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="40" spans="1:12">
+    <row r="40" spans="1:16">
       <c r="A40" t="s">
         <v>1316</v>
       </c>
@@ -19949,42 +19979,45 @@
         <v>1347</v>
       </c>
     </row>
-    <row r="41" spans="1:12">
+    <row r="41" spans="1:16">
       <c r="A41" t="s">
         <v>1317</v>
       </c>
     </row>
-    <row r="42" spans="1:12">
+    <row r="42" spans="1:16">
       <c r="A42" t="s">
         <v>1318</v>
       </c>
-    </row>
-    <row r="43" spans="1:12">
+      <c r="L42" t="s">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16">
       <c r="A43" t="s">
         <v>1319</v>
       </c>
     </row>
-    <row r="44" spans="1:12">
+    <row r="44" spans="1:16">
       <c r="A44" t="s">
         <v>1320</v>
       </c>
     </row>
-    <row r="45" spans="1:12">
+    <row r="45" spans="1:16">
       <c r="A45" t="s">
         <v>1321</v>
       </c>
     </row>
-    <row r="46" spans="1:12">
+    <row r="46" spans="1:16">
       <c r="A46" t="s">
         <v>1322</v>
       </c>
     </row>
-    <row r="47" spans="1:12">
+    <row r="47" spans="1:16">
       <c r="A47" t="s">
         <v>1323</v>
       </c>
     </row>
-    <row r="48" spans="1:12">
+    <row r="48" spans="1:16">
       <c r="A48" t="s">
         <v>1324</v>
       </c>
@@ -20046,11 +20079,11 @@
       <c r="B1" s="25" t="s">
         <v>327</v>
       </c>
-      <c r="E1" s="203" t="s">
+      <c r="E1" s="204" t="s">
         <v>724</v>
       </c>
-      <c r="F1" s="203"/>
-      <c r="G1" s="203"/>
+      <c r="F1" s="204"/>
+      <c r="G1" s="204"/>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="19" t="s">
@@ -20059,11 +20092,11 @@
       <c r="B2" s="19" t="s">
         <v>257</v>
       </c>
-      <c r="E2" s="204" t="s">
+      <c r="E2" s="205" t="s">
         <v>725</v>
       </c>
-      <c r="F2" s="204"/>
-      <c r="G2" s="204"/>
+      <c r="F2" s="205"/>
+      <c r="G2" s="205"/>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="19" t="s">
@@ -20080,10 +20113,10 @@
       <c r="B4" s="19" t="s">
         <v>259</v>
       </c>
-      <c r="E4" s="203" t="s">
+      <c r="E4" s="204" t="s">
         <v>722</v>
       </c>
-      <c r="F4" s="203"/>
+      <c r="F4" s="204"/>
       <c r="G4" s="25" t="s">
         <v>723</v>
       </c>
@@ -20095,16 +20128,16 @@
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="E5" s="202" t="s">
+      <c r="E5" s="203" t="s">
         <v>720</v>
       </c>
-      <c r="F5" s="202" t="s">
+      <c r="F5" s="203" t="s">
         <v>721</v>
       </c>
       <c r="G5" s="68" t="s">
         <v>747</v>
       </c>
-      <c r="H5" s="201" t="s">
+      <c r="H5" s="202" t="s">
         <v>748</v>
       </c>
       <c r="J5" t="s">
@@ -20115,12 +20148,12 @@
       <c r="A6" t="s">
         <v>261</v>
       </c>
-      <c r="E6" s="202"/>
-      <c r="F6" s="202"/>
+      <c r="E6" s="203"/>
+      <c r="F6" s="203"/>
       <c r="G6" s="68" t="s">
         <v>746</v>
       </c>
-      <c r="H6" s="202"/>
+      <c r="H6" s="203"/>
       <c r="J6" t="s">
         <v>729</v>
       </c>
@@ -20341,46 +20374,46 @@
     <col min="7" max="7" width="33" customWidth="1"/>
     <col min="8" max="8" width="38.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.140625" style="81" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="60.42578125" style="128" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="60.42578125" style="129" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="133" t="s">
         <v>846</v>
       </c>
-      <c r="B1" s="132" t="s">
+      <c r="B1" s="133" t="s">
         <v>1169</v>
       </c>
-      <c r="C1" s="132" t="s">
+      <c r="C1" s="133" t="s">
         <v>640</v>
       </c>
-      <c r="D1" s="132" t="s">
+      <c r="D1" s="133" t="s">
         <v>1172</v>
       </c>
-      <c r="E1" s="132" t="s">
+      <c r="E1" s="133" t="s">
         <v>1167</v>
       </c>
-      <c r="F1" s="132" t="s">
+      <c r="F1" s="133" t="s">
         <v>1168</v>
       </c>
-      <c r="G1" s="133" t="s">
+      <c r="G1" s="134" t="s">
         <v>1202</v>
       </c>
-      <c r="H1" s="133" t="s">
+      <c r="H1" s="134" t="s">
         <v>1255</v>
       </c>
-      <c r="I1" s="132" t="s">
+      <c r="I1" s="133" t="s">
         <v>1176</v>
       </c>
-      <c r="J1" s="132" t="s">
+      <c r="J1" s="133" t="s">
         <v>1182</v>
       </c>
-      <c r="K1" s="132" t="s">
+      <c r="K1" s="133" t="s">
         <v>1188</v>
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="131">
+      <c r="A2" s="132">
         <v>44028</v>
       </c>
       <c r="B2" s="8" t="s">
@@ -20408,12 +20441,12 @@
       <c r="J2" s="115" t="s">
         <v>892</v>
       </c>
-      <c r="K2" s="205" t="s">
+      <c r="K2" s="206" t="s">
         <v>1194</v>
       </c>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="131">
+      <c r="A3" s="132">
         <v>44028</v>
       </c>
       <c r="B3" s="8" t="s">
@@ -20441,10 +20474,10 @@
       <c r="J3" s="115" t="s">
         <v>892</v>
       </c>
-      <c r="K3" s="206"/>
+      <c r="K3" s="207"/>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="131">
+      <c r="A4" s="132">
         <v>44029</v>
       </c>
       <c r="B4" s="8" t="s">
@@ -20470,10 +20503,10 @@
       <c r="J4" s="115" t="s">
         <v>892</v>
       </c>
-      <c r="K4" s="206"/>
+      <c r="K4" s="207"/>
     </row>
     <row r="5" spans="1:11" ht="45">
-      <c r="A5" s="131">
+      <c r="A5" s="132">
         <v>44029</v>
       </c>
       <c r="B5" s="8" t="s">
@@ -20499,10 +20532,10 @@
       <c r="J5" s="115" t="s">
         <v>892</v>
       </c>
-      <c r="K5" s="207"/>
+      <c r="K5" s="208"/>
     </row>
     <row r="6" spans="1:11" ht="60">
-      <c r="A6" s="131">
+      <c r="A6" s="132">
         <v>44029</v>
       </c>
       <c r="B6" s="8" t="s">
@@ -20533,7 +20566,7 @@
       </c>
     </row>
     <row r="7" spans="1:11" ht="60">
-      <c r="A7" s="131">
+      <c r="A7" s="132">
         <v>44029</v>
       </c>
       <c r="B7" s="8" t="s">
@@ -20562,7 +20595,7 @@
       <c r="K7" s="8"/>
     </row>
     <row r="8" spans="1:11" ht="60">
-      <c r="A8" s="131">
+      <c r="A8" s="132">
         <v>44029</v>
       </c>
       <c r="B8" s="8" t="s">
@@ -20595,7 +20628,7 @@
       </c>
     </row>
     <row r="9" spans="1:11" ht="60">
-      <c r="A9" s="131">
+      <c r="A9" s="132">
         <v>44029</v>
       </c>
       <c r="B9" s="8" t="s">
@@ -20610,13 +20643,13 @@
       <c r="E9" s="18" t="s">
         <v>1191</v>
       </c>
-      <c r="F9" s="141" t="s">
+      <c r="F9" s="142" t="s">
         <v>1243</v>
       </c>
-      <c r="G9" s="142" t="s">
+      <c r="G9" s="143" t="s">
         <v>1211</v>
       </c>
-      <c r="H9" s="139" t="s">
+      <c r="H9" s="140" t="s">
         <v>1241</v>
       </c>
       <c r="I9" s="115" t="s">
@@ -20628,7 +20661,7 @@
       </c>
     </row>
     <row r="10" spans="1:11" ht="64.5" customHeight="1">
-      <c r="A10" s="138" t="s">
+      <c r="A10" s="139" t="s">
         <v>1227</v>
       </c>
       <c r="B10" s="8" t="s">
@@ -20659,7 +20692,7 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="45">
-      <c r="A11" s="136" t="s">
+      <c r="A11" s="137" t="s">
         <v>1218</v>
       </c>
       <c r="B11" s="8" t="s">
@@ -20677,10 +20710,10 @@
       <c r="F11" s="115" t="s">
         <v>1198</v>
       </c>
-      <c r="G11" s="135" t="s">
+      <c r="G11" s="136" t="s">
         <v>1245</v>
       </c>
-      <c r="H11" s="135"/>
+      <c r="H11" s="136"/>
       <c r="I11" s="115" t="s">
         <v>1217</v>
       </c>
@@ -20728,71 +20761,71 @@
       </c>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="128"/>
-      <c r="B14" s="128"/>
-      <c r="C14" s="128"/>
-      <c r="D14" s="128"/>
-      <c r="E14" s="134" t="s">
+      <c r="A14" s="129"/>
+      <c r="B14" s="129"/>
+      <c r="C14" s="129"/>
+      <c r="D14" s="129"/>
+      <c r="E14" s="135" t="s">
         <v>1216</v>
       </c>
-      <c r="F14" s="129"/>
-      <c r="G14" s="134" t="s">
+      <c r="F14" s="130"/>
+      <c r="G14" s="135" t="s">
         <v>1254</v>
       </c>
-      <c r="H14" s="128"/>
-      <c r="I14" s="129"/>
-      <c r="J14" s="128"/>
+      <c r="H14" s="129"/>
+      <c r="I14" s="130"/>
+      <c r="J14" s="129"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="128"/>
-      <c r="B15" s="128"/>
-      <c r="C15" s="128"/>
-      <c r="D15" s="128"/>
-      <c r="E15" s="128"/>
-      <c r="F15" s="129"/>
-      <c r="G15" s="128" t="s">
+      <c r="A15" s="129"/>
+      <c r="B15" s="129"/>
+      <c r="C15" s="129"/>
+      <c r="D15" s="129"/>
+      <c r="E15" s="129"/>
+      <c r="F15" s="130"/>
+      <c r="G15" s="129" t="s">
         <v>1233</v>
       </c>
-      <c r="H15" s="128" t="s">
+      <c r="H15" s="129" t="s">
         <v>1234</v>
       </c>
-      <c r="I15" s="129"/>
-      <c r="J15" s="128"/>
+      <c r="I15" s="130"/>
+      <c r="J15" s="129"/>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="128"/>
-      <c r="B16" s="128"/>
-      <c r="C16" s="128"/>
-      <c r="D16" s="128"/>
-      <c r="E16" s="128"/>
-      <c r="G16" s="128"/>
-      <c r="H16" s="128"/>
-      <c r="I16" s="129"/>
-      <c r="J16" s="128"/>
+      <c r="A16" s="129"/>
+      <c r="B16" s="129"/>
+      <c r="C16" s="129"/>
+      <c r="D16" s="129"/>
+      <c r="E16" s="129"/>
+      <c r="G16" s="129"/>
+      <c r="H16" s="129"/>
+      <c r="I16" s="130"/>
+      <c r="J16" s="129"/>
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1">
-      <c r="A17" s="128"/>
-      <c r="B17" s="128"/>
-      <c r="C17" s="128"/>
-      <c r="D17" s="128"/>
-      <c r="E17" s="128"/>
-      <c r="F17" s="139"/>
+      <c r="A17" s="129"/>
+      <c r="B17" s="129"/>
+      <c r="C17" s="129"/>
+      <c r="D17" s="129"/>
+      <c r="E17" s="129"/>
+      <c r="F17" s="140"/>
       <c r="G17" s="8" t="s">
         <v>1256</v>
       </c>
       <c r="H17" s="124" t="s">
         <v>1257</v>
       </c>
-      <c r="I17" s="129"/>
-      <c r="J17" s="128"/>
+      <c r="I17" s="130"/>
+      <c r="J17" s="129"/>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="128"/>
-      <c r="B18" s="128"/>
-      <c r="C18" s="128"/>
-      <c r="D18" s="128"/>
-      <c r="E18" s="128"/>
-      <c r="F18" s="208" t="s">
+      <c r="A18" s="129"/>
+      <c r="B18" s="129"/>
+      <c r="C18" s="129"/>
+      <c r="D18" s="129"/>
+      <c r="E18" s="129"/>
+      <c r="F18" s="209" t="s">
         <v>1239</v>
       </c>
       <c r="G18" s="8" t="s">
@@ -20801,20 +20834,20 @@
       <c r="H18" s="124" t="s">
         <v>1251</v>
       </c>
-      <c r="I18" s="129"/>
-      <c r="J18" s="128"/>
+      <c r="I18" s="130"/>
+      <c r="J18" s="129"/>
     </row>
     <row r="19" spans="1:10">
-      <c r="F19" s="208"/>
-      <c r="G19" s="148" t="s">
+      <c r="F19" s="209"/>
+      <c r="G19" s="149" t="s">
         <v>1235</v>
       </c>
-      <c r="H19" s="149" t="s">
+      <c r="H19" s="150" t="s">
         <v>1252</v>
       </c>
     </row>
     <row r="20" spans="1:10">
-      <c r="F20" s="208"/>
+      <c r="F20" s="209"/>
       <c r="G20" s="8" t="s">
         <v>1237</v>
       </c>
@@ -20823,19 +20856,19 @@
       </c>
     </row>
     <row r="21" spans="1:10">
-      <c r="F21" s="208"/>
+      <c r="F21" s="209"/>
       <c r="G21" s="8" t="s">
         <v>1238</v>
       </c>
-      <c r="H21" s="143" t="s">
+      <c r="H21" s="144" t="s">
         <v>1253</v>
       </c>
     </row>
     <row r="22" spans="1:10">
-      <c r="G22" s="140"/>
+      <c r="G22" s="141"/>
     </row>
     <row r="23" spans="1:10">
-      <c r="F23" s="137" t="s">
+      <c r="F23" s="138" t="s">
         <v>1250</v>
       </c>
       <c r="G23" t="s">
@@ -20846,7 +20879,7 @@
       </c>
     </row>
     <row r="24" spans="1:10">
-      <c r="F24" s="137" t="s">
+      <c r="F24" s="138" t="s">
         <v>1206</v>
       </c>
       <c r="G24" s="81">
@@ -20857,7 +20890,7 @@
       </c>
     </row>
     <row r="25" spans="1:10">
-      <c r="F25" s="137" t="s">
+      <c r="F25" s="138" t="s">
         <v>1206</v>
       </c>
       <c r="G25" s="81">
@@ -20868,7 +20901,7 @@
       </c>
     </row>
     <row r="26" spans="1:10">
-      <c r="F26" s="137" t="s">
+      <c r="F26" s="138" t="s">
         <v>1197</v>
       </c>
       <c r="G26" s="81">
@@ -20879,7 +20912,7 @@
       </c>
     </row>
     <row r="27" spans="1:10">
-      <c r="F27" s="137" t="s">
+      <c r="F27" s="138" t="s">
         <v>1197</v>
       </c>
       <c r="G27" s="81">
@@ -20890,7 +20923,7 @@
       </c>
     </row>
     <row r="28" spans="1:10">
-      <c r="F28" s="137" t="s">
+      <c r="F28" s="138" t="s">
         <v>1197</v>
       </c>
       <c r="G28" s="81">
@@ -20901,7 +20934,7 @@
       </c>
     </row>
     <row r="29" spans="1:10">
-      <c r="F29" s="137" t="s">
+      <c r="F29" s="138" t="s">
         <v>1198</v>
       </c>
       <c r="G29" s="81">
@@ -20912,7 +20945,7 @@
       </c>
     </row>
     <row r="30" spans="1:10">
-      <c r="F30" s="137" t="s">
+      <c r="F30" s="138" t="s">
         <v>1198</v>
       </c>
       <c r="G30" s="81">
@@ -20923,7 +20956,7 @@
       </c>
     </row>
     <row r="31" spans="1:10">
-      <c r="F31" s="137" t="s">
+      <c r="F31" s="138" t="s">
         <v>1198</v>
       </c>
       <c r="G31" s="81">
@@ -20934,7 +20967,7 @@
       </c>
     </row>
     <row r="32" spans="1:10">
-      <c r="F32" s="137" t="s">
+      <c r="F32" s="138" t="s">
         <v>1200</v>
       </c>
       <c r="G32" s="81">
@@ -20945,7 +20978,7 @@
       </c>
     </row>
     <row r="33" spans="6:8">
-      <c r="F33" s="137" t="s">
+      <c r="F33" s="138" t="s">
         <v>1200</v>
       </c>
       <c r="G33" s="81">
@@ -22316,7 +22349,7 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="202" t="s">
+      <c r="A2" s="203" t="s">
         <v>379</v>
       </c>
       <c r="B2" s="57" t="s">
@@ -22330,7 +22363,7 @@
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="202"/>
+      <c r="A3" s="203"/>
       <c r="B3" s="20" t="s">
         <v>262</v>
       </c>
@@ -22342,7 +22375,7 @@
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="202"/>
+      <c r="A4" s="203"/>
       <c r="B4" s="20" t="s">
         <v>385</v>
       </c>
@@ -22354,7 +22387,7 @@
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="202"/>
+      <c r="A5" s="203"/>
       <c r="B5" s="57" t="s">
         <v>544</v>
       </c>
@@ -22366,7 +22399,7 @@
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="202"/>
+      <c r="A6" s="203"/>
       <c r="B6" s="20" t="s">
         <v>388</v>
       </c>
@@ -22378,7 +22411,7 @@
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="202"/>
+      <c r="A7" s="203"/>
       <c r="B7" s="20" t="s">
         <v>390</v>
       </c>
@@ -23999,12 +24032,12 @@
       </c>
     </row>
     <row r="9" spans="11:18">
-      <c r="K9" s="147" t="s">
+      <c r="K9" s="148" t="s">
         <v>1267</v>
       </c>
     </row>
     <row r="10" spans="11:18">
-      <c r="K10" s="147">
+      <c r="K10" s="148">
         <v>0</v>
       </c>
       <c r="L10" s="109" t="s">
@@ -24021,17 +24054,17 @@
       </c>
     </row>
     <row r="11" spans="11:18" ht="15.75" thickBot="1">
-      <c r="K11" s="147"/>
-      <c r="L11" s="145"/>
-      <c r="M11" s="145"/>
-      <c r="N11" s="145"/>
-      <c r="O11" s="145"/>
-      <c r="P11" s="145"/>
-      <c r="Q11" s="145"/>
-      <c r="R11" s="145"/>
+      <c r="K11" s="148"/>
+      <c r="L11" s="146"/>
+      <c r="M11" s="146"/>
+      <c r="N11" s="146"/>
+      <c r="O11" s="146"/>
+      <c r="P11" s="146"/>
+      <c r="Q11" s="146"/>
+      <c r="R11" s="146"/>
     </row>
     <row r="12" spans="11:18">
-      <c r="K12" s="147">
+      <c r="K12" s="148">
         <v>1</v>
       </c>
       <c r="L12" s="5" t="s">
@@ -24039,7 +24072,7 @@
       </c>
     </row>
     <row r="13" spans="11:18">
-      <c r="K13" s="147"/>
+      <c r="K13" s="148"/>
       <c r="M13" t="s">
         <v>880</v>
       </c>
@@ -24051,7 +24084,7 @@
       </c>
     </row>
     <row r="14" spans="11:18">
-      <c r="K14" s="147"/>
+      <c r="K14" s="148"/>
       <c r="L14" s="6" t="s">
         <v>887</v>
       </c>
@@ -24060,13 +24093,13 @@
       </c>
     </row>
     <row r="15" spans="11:18">
-      <c r="K15" s="147"/>
+      <c r="K15" s="148"/>
       <c r="M15" t="s">
         <v>884</v>
       </c>
     </row>
     <row r="16" spans="11:18">
-      <c r="K16" s="147"/>
+      <c r="K16" s="148"/>
       <c r="O16" s="5" t="s">
         <v>1266</v>
       </c>
@@ -24075,16 +24108,16 @@
       </c>
     </row>
     <row r="17" spans="7:24">
-      <c r="K17" s="147"/>
+      <c r="K17" s="148"/>
     </row>
     <row r="18" spans="7:24">
-      <c r="K18" s="147"/>
+      <c r="K18" s="148"/>
     </row>
     <row r="19" spans="7:24">
-      <c r="K19" s="147"/>
+      <c r="K19" s="148"/>
     </row>
     <row r="20" spans="7:24">
-      <c r="K20" s="147"/>
+      <c r="K20" s="148"/>
       <c r="L20" s="6" t="s">
         <v>882</v>
       </c>
@@ -24102,7 +24135,7 @@
       </c>
     </row>
     <row r="21" spans="7:24">
-      <c r="K21" s="147"/>
+      <c r="K21" s="148"/>
       <c r="M21" t="s">
         <v>888</v>
       </c>
@@ -24111,8 +24144,8 @@
       </c>
     </row>
     <row r="22" spans="7:24">
-      <c r="K22" s="147"/>
-      <c r="V22" s="163" t="s">
+      <c r="K22" s="148"/>
+      <c r="V22" s="164" t="s">
         <v>832</v>
       </c>
       <c r="W22" s="9" t="s">
@@ -24123,19 +24156,19 @@
       </c>
     </row>
     <row r="23" spans="7:24" ht="15.75" thickBot="1">
-      <c r="K23" s="147"/>
-      <c r="L23" s="145"/>
-      <c r="M23" s="145"/>
-      <c r="N23" s="145"/>
-      <c r="O23" s="146" t="s">
+      <c r="K23" s="148"/>
+      <c r="L23" s="146"/>
+      <c r="M23" s="146"/>
+      <c r="N23" s="146"/>
+      <c r="O23" s="147" t="s">
         <v>1266</v>
       </c>
-      <c r="P23" s="146" t="s">
+      <c r="P23" s="147" t="s">
         <v>1268</v>
       </c>
-      <c r="Q23" s="145"/>
-      <c r="R23" s="145"/>
-      <c r="V23" s="164"/>
+      <c r="Q23" s="146"/>
+      <c r="R23" s="146"/>
+      <c r="V23" s="165"/>
       <c r="W23" s="9" t="s">
         <v>815</v>
       </c>
@@ -24144,8 +24177,8 @@
       </c>
     </row>
     <row r="24" spans="7:24">
-      <c r="K24" s="147"/>
-      <c r="V24" s="164"/>
+      <c r="K24" s="148"/>
+      <c r="V24" s="165"/>
       <c r="W24" s="9" t="s">
         <v>816</v>
       </c>
@@ -24154,13 +24187,13 @@
       </c>
     </row>
     <row r="25" spans="7:24">
-      <c r="K25" s="147">
+      <c r="K25" s="148">
         <v>2</v>
       </c>
       <c r="L25" s="5" t="s">
         <v>891</v>
       </c>
-      <c r="V25" s="164"/>
+      <c r="V25" s="165"/>
       <c r="W25" s="9" t="s">
         <v>817</v>
       </c>
@@ -24169,7 +24202,7 @@
       </c>
     </row>
     <row r="26" spans="7:24">
-      <c r="K26" s="147"/>
+      <c r="K26" s="148"/>
       <c r="M26" s="110" t="s">
         <v>893</v>
       </c>
@@ -24179,32 +24212,32 @@
       <c r="O26" t="s">
         <v>897</v>
       </c>
-      <c r="V26" s="164"/>
+      <c r="V26" s="165"/>
       <c r="W26" s="9" t="s">
         <v>824</v>
       </c>
       <c r="X26" s="92"/>
     </row>
     <row r="27" spans="7:24">
-      <c r="K27" s="147"/>
+      <c r="K27" s="148"/>
       <c r="M27" t="s">
         <v>894</v>
       </c>
       <c r="N27" t="s">
         <v>896</v>
       </c>
-      <c r="V27" s="164"/>
+      <c r="V27" s="165"/>
       <c r="W27" s="9" t="s">
         <v>825</v>
       </c>
       <c r="X27" s="92"/>
     </row>
     <row r="28" spans="7:24">
-      <c r="K28" s="147"/>
+      <c r="K28" s="148"/>
       <c r="N28" t="s">
         <v>898</v>
       </c>
-      <c r="V28" s="164"/>
+      <c r="V28" s="165"/>
       <c r="W28" s="9" t="s">
         <v>826</v>
       </c>
@@ -24213,11 +24246,11 @@
       </c>
     </row>
     <row r="29" spans="7:24">
-      <c r="K29" s="147"/>
+      <c r="K29" s="148"/>
       <c r="N29" t="s">
         <v>899</v>
       </c>
-      <c r="V29" s="165"/>
+      <c r="V29" s="166"/>
       <c r="W29" s="9" t="s">
         <v>827</v>
       </c>
@@ -24226,14 +24259,14 @@
       </c>
     </row>
     <row r="30" spans="7:24">
-      <c r="K30" s="147"/>
+      <c r="K30" s="148"/>
       <c r="M30" t="s">
         <v>900</v>
       </c>
       <c r="N30" t="s">
         <v>852</v>
       </c>
-      <c r="V30" s="160" t="s">
+      <c r="V30" s="161" t="s">
         <v>831</v>
       </c>
       <c r="W30" s="49" t="s">
@@ -24242,11 +24275,11 @@
       <c r="X30" s="112"/>
     </row>
     <row r="31" spans="7:24">
-      <c r="K31" s="147"/>
+      <c r="K31" s="148"/>
       <c r="N31" t="s">
         <v>901</v>
       </c>
-      <c r="V31" s="161"/>
+      <c r="V31" s="162"/>
       <c r="W31" s="49" t="s">
         <v>822</v>
       </c>
@@ -24256,19 +24289,19 @@
       <c r="G32" t="s">
         <v>910</v>
       </c>
-      <c r="K32" s="147"/>
-      <c r="L32" s="145"/>
-      <c r="M32" s="145"/>
-      <c r="N32" s="145"/>
-      <c r="O32" s="146" t="s">
+      <c r="K32" s="148"/>
+      <c r="L32" s="146"/>
+      <c r="M32" s="146"/>
+      <c r="N32" s="146"/>
+      <c r="O32" s="147" t="s">
         <v>902</v>
       </c>
-      <c r="P32" s="146" t="s">
+      <c r="P32" s="147" t="s">
         <v>903</v>
       </c>
-      <c r="Q32" s="145"/>
-      <c r="R32" s="145"/>
-      <c r="V32" s="162"/>
+      <c r="Q32" s="146"/>
+      <c r="R32" s="146"/>
+      <c r="V32" s="163"/>
       <c r="W32" s="49" t="s">
         <v>823</v>
       </c>
@@ -24281,7 +24314,7 @@
       <c r="G33" t="s">
         <v>911</v>
       </c>
-      <c r="K33" s="147"/>
+      <c r="K33" s="148"/>
     </row>
     <row r="34" spans="6:17">
       <c r="F34">
@@ -24290,7 +24323,7 @@
       <c r="G34" t="s">
         <v>912</v>
       </c>
-      <c r="K34" s="147">
+      <c r="K34" s="148">
         <v>3</v>
       </c>
       <c r="L34" s="5" t="s">
@@ -24340,19 +24373,19 @@
       </c>
     </row>
     <row r="41" spans="6:17" ht="15.75" thickBot="1">
-      <c r="L41" s="145"/>
-      <c r="M41" s="145"/>
-      <c r="N41" s="145"/>
-      <c r="O41" s="146" t="s">
+      <c r="L41" s="146"/>
+      <c r="M41" s="146"/>
+      <c r="N41" s="146"/>
+      <c r="O41" s="147" t="s">
         <v>907</v>
       </c>
-      <c r="P41" s="146" t="s">
+      <c r="P41" s="147" t="s">
         <v>892</v>
       </c>
-      <c r="Q41" s="145"/>
+      <c r="Q41" s="146"/>
     </row>
     <row r="44" spans="6:17">
-      <c r="P44" s="144"/>
+      <c r="P44" s="145"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -24408,7 +24441,7 @@
       <c r="R5" s="13" t="s">
         <v>352</v>
       </c>
-      <c r="S5" s="166" t="s">
+      <c r="S5" s="167" t="s">
         <v>809</v>
       </c>
     </row>
@@ -24425,7 +24458,7 @@
       <c r="R6" s="9" t="s">
         <v>602</v>
       </c>
-      <c r="S6" s="166"/>
+      <c r="S6" s="167"/>
     </row>
     <row r="7" spans="3:20">
       <c r="O7" s="81" t="s">
@@ -24440,7 +24473,7 @@
       <c r="R7" s="9" t="s">
         <v>603</v>
       </c>
-      <c r="S7" s="166"/>
+      <c r="S7" s="167"/>
     </row>
     <row r="8" spans="3:20">
       <c r="O8" s="81" t="s">
@@ -24455,7 +24488,7 @@
       <c r="R8" s="9" t="s">
         <v>350</v>
       </c>
-      <c r="S8" s="166"/>
+      <c r="S8" s="167"/>
     </row>
     <row r="9" spans="3:20">
       <c r="O9" s="81" t="s">
@@ -24470,7 +24503,7 @@
       <c r="R9" s="9" t="s">
         <v>349</v>
       </c>
-      <c r="S9" s="166"/>
+      <c r="S9" s="167"/>
     </row>
     <row r="10" spans="3:20">
       <c r="Q10" s="9" t="s">
@@ -24495,7 +24528,7 @@
       </c>
     </row>
     <row r="15" spans="3:20">
-      <c r="Q15" s="163" t="s">
+      <c r="Q15" s="164" t="s">
         <v>832</v>
       </c>
       <c r="R15" s="9" t="s">
@@ -24530,7 +24563,7 @@
       <c r="J16" s="10" t="s">
         <v>813</v>
       </c>
-      <c r="Q16" s="164"/>
+      <c r="Q16" s="165"/>
       <c r="R16" s="9" t="s">
         <v>815</v>
       </c>
@@ -24540,7 +24573,7 @@
     </row>
     <row r="17" spans="10:19">
       <c r="J17" s="81"/>
-      <c r="Q17" s="164"/>
+      <c r="Q17" s="165"/>
       <c r="R17" s="9" t="s">
         <v>816</v>
       </c>
@@ -24549,7 +24582,7 @@
       </c>
     </row>
     <row r="18" spans="10:19">
-      <c r="Q18" s="164"/>
+      <c r="Q18" s="165"/>
       <c r="R18" s="9" t="s">
         <v>817</v>
       </c>
@@ -24558,21 +24591,21 @@
       </c>
     </row>
     <row r="19" spans="10:19">
-      <c r="Q19" s="164"/>
+      <c r="Q19" s="165"/>
       <c r="R19" s="9" t="s">
         <v>824</v>
       </c>
       <c r="S19" s="92"/>
     </row>
     <row r="20" spans="10:19">
-      <c r="Q20" s="164"/>
+      <c r="Q20" s="165"/>
       <c r="R20" s="9" t="s">
         <v>825</v>
       </c>
       <c r="S20" s="92"/>
     </row>
     <row r="21" spans="10:19">
-      <c r="Q21" s="164"/>
+      <c r="Q21" s="165"/>
       <c r="R21" s="9" t="s">
         <v>826</v>
       </c>
@@ -24581,7 +24614,7 @@
       </c>
     </row>
     <row r="22" spans="10:19">
-      <c r="Q22" s="165"/>
+      <c r="Q22" s="166"/>
       <c r="R22" s="9" t="s">
         <v>827</v>
       </c>
@@ -24590,7 +24623,7 @@
       </c>
     </row>
     <row r="23" spans="10:19">
-      <c r="Q23" s="163" t="s">
+      <c r="Q23" s="164" t="s">
         <v>831</v>
       </c>
       <c r="R23" s="9" t="s">
@@ -24599,14 +24632,14 @@
       <c r="S23" s="92"/>
     </row>
     <row r="24" spans="10:19">
-      <c r="Q24" s="164"/>
+      <c r="Q24" s="165"/>
       <c r="R24" s="9" t="s">
         <v>822</v>
       </c>
       <c r="S24" s="92"/>
     </row>
     <row r="25" spans="10:19">
-      <c r="Q25" s="165"/>
+      <c r="Q25" s="166"/>
       <c r="R25" s="9" t="s">
         <v>823</v>
       </c>
@@ -24672,39 +24705,39 @@
       <c r="B1" t="s">
         <v>860</v>
       </c>
-      <c r="J1" s="167" t="s">
+      <c r="J1" s="168" t="s">
         <v>952</v>
       </c>
-      <c r="K1" s="168"/>
-      <c r="L1" s="168"/>
-      <c r="M1" s="168"/>
-      <c r="N1" s="168"/>
-      <c r="O1" s="168"/>
-      <c r="P1" s="168"/>
-      <c r="Q1" s="168"/>
+      <c r="K1" s="169"/>
+      <c r="L1" s="169"/>
+      <c r="M1" s="169"/>
+      <c r="N1" s="169"/>
+      <c r="O1" s="169"/>
+      <c r="P1" s="169"/>
+      <c r="Q1" s="169"/>
     </row>
     <row r="2" spans="1:17">
-      <c r="J2" s="168"/>
-      <c r="K2" s="168"/>
-      <c r="L2" s="168"/>
-      <c r="M2" s="168"/>
-      <c r="N2" s="168"/>
-      <c r="O2" s="168"/>
-      <c r="P2" s="168"/>
-      <c r="Q2" s="168"/>
+      <c r="J2" s="169"/>
+      <c r="K2" s="169"/>
+      <c r="L2" s="169"/>
+      <c r="M2" s="169"/>
+      <c r="N2" s="169"/>
+      <c r="O2" s="169"/>
+      <c r="P2" s="169"/>
+      <c r="Q2" s="169"/>
     </row>
     <row r="3" spans="1:17">
       <c r="A3" s="6" t="s">
         <v>861</v>
       </c>
-      <c r="J3" s="168"/>
-      <c r="K3" s="168"/>
-      <c r="L3" s="168"/>
-      <c r="M3" s="168"/>
-      <c r="N3" s="168"/>
-      <c r="O3" s="168"/>
-      <c r="P3" s="168"/>
-      <c r="Q3" s="168"/>
+      <c r="J3" s="169"/>
+      <c r="K3" s="169"/>
+      <c r="L3" s="169"/>
+      <c r="M3" s="169"/>
+      <c r="N3" s="169"/>
+      <c r="O3" s="169"/>
+      <c r="P3" s="169"/>
+      <c r="Q3" s="169"/>
     </row>
     <row r="4" spans="1:17">
       <c r="A4" t="s">
@@ -24716,24 +24749,24 @@
       <c r="D4" t="s">
         <v>863</v>
       </c>
-      <c r="J4" s="168"/>
-      <c r="K4" s="168"/>
-      <c r="L4" s="168"/>
-      <c r="M4" s="168"/>
-      <c r="N4" s="168"/>
-      <c r="O4" s="168"/>
-      <c r="P4" s="168"/>
-      <c r="Q4" s="168"/>
+      <c r="J4" s="169"/>
+      <c r="K4" s="169"/>
+      <c r="L4" s="169"/>
+      <c r="M4" s="169"/>
+      <c r="N4" s="169"/>
+      <c r="O4" s="169"/>
+      <c r="P4" s="169"/>
+      <c r="Q4" s="169"/>
     </row>
     <row r="5" spans="1:17">
-      <c r="J5" s="168"/>
-      <c r="K5" s="168"/>
-      <c r="L5" s="168"/>
-      <c r="M5" s="168"/>
-      <c r="N5" s="168"/>
-      <c r="O5" s="168"/>
-      <c r="P5" s="168"/>
-      <c r="Q5" s="168"/>
+      <c r="J5" s="169"/>
+      <c r="K5" s="169"/>
+      <c r="L5" s="169"/>
+      <c r="M5" s="169"/>
+      <c r="N5" s="169"/>
+      <c r="O5" s="169"/>
+      <c r="P5" s="169"/>
+      <c r="Q5" s="169"/>
     </row>
     <row r="6" spans="1:17" ht="15.75" thickBot="1">
       <c r="A6" t="s">
@@ -24742,38 +24775,38 @@
       <c r="E6" t="s">
         <v>918</v>
       </c>
-      <c r="J6" s="168"/>
-      <c r="K6" s="168"/>
-      <c r="L6" s="168"/>
-      <c r="M6" s="168"/>
-      <c r="N6" s="168"/>
-      <c r="O6" s="168"/>
-      <c r="P6" s="168"/>
-      <c r="Q6" s="168"/>
+      <c r="J6" s="169"/>
+      <c r="K6" s="169"/>
+      <c r="L6" s="169"/>
+      <c r="M6" s="169"/>
+      <c r="N6" s="169"/>
+      <c r="O6" s="169"/>
+      <c r="P6" s="169"/>
+      <c r="Q6" s="169"/>
     </row>
     <row r="7" spans="1:17" ht="15.75" thickBot="1">
       <c r="A7" s="105" t="s">
         <v>865</v>
       </c>
-      <c r="J7" s="168"/>
-      <c r="K7" s="168"/>
-      <c r="L7" s="168"/>
-      <c r="M7" s="168"/>
-      <c r="N7" s="168"/>
-      <c r="O7" s="168"/>
-      <c r="P7" s="168"/>
-      <c r="Q7" s="168"/>
+      <c r="J7" s="169"/>
+      <c r="K7" s="169"/>
+      <c r="L7" s="169"/>
+      <c r="M7" s="169"/>
+      <c r="N7" s="169"/>
+      <c r="O7" s="169"/>
+      <c r="P7" s="169"/>
+      <c r="Q7" s="169"/>
     </row>
     <row r="8" spans="1:17">
       <c r="A8" s="117"/>
-      <c r="J8" s="168"/>
-      <c r="K8" s="168"/>
-      <c r="L8" s="168"/>
-      <c r="M8" s="168"/>
-      <c r="N8" s="168"/>
-      <c r="O8" s="168"/>
-      <c r="P8" s="168"/>
-      <c r="Q8" s="168"/>
+      <c r="J8" s="169"/>
+      <c r="K8" s="169"/>
+      <c r="L8" s="169"/>
+      <c r="M8" s="169"/>
+      <c r="N8" s="169"/>
+      <c r="O8" s="169"/>
+      <c r="P8" s="169"/>
+      <c r="Q8" s="169"/>
     </row>
     <row r="9" spans="1:17">
       <c r="A9" t="s">
@@ -24782,14 +24815,14 @@
       <c r="B9" t="s">
         <v>924</v>
       </c>
-      <c r="J9" s="168"/>
-      <c r="K9" s="168"/>
-      <c r="L9" s="168"/>
-      <c r="M9" s="168"/>
-      <c r="N9" s="168"/>
-      <c r="O9" s="168"/>
-      <c r="P9" s="168"/>
-      <c r="Q9" s="168"/>
+      <c r="J9" s="169"/>
+      <c r="K9" s="169"/>
+      <c r="L9" s="169"/>
+      <c r="M9" s="169"/>
+      <c r="N9" s="169"/>
+      <c r="O9" s="169"/>
+      <c r="P9" s="169"/>
+      <c r="Q9" s="169"/>
     </row>
     <row r="10" spans="1:17">
       <c r="A10" t="s">
@@ -24810,14 +24843,14 @@
       <c r="H10" t="s">
         <v>950</v>
       </c>
-      <c r="J10" s="168"/>
-      <c r="K10" s="168"/>
-      <c r="L10" s="168"/>
-      <c r="M10" s="168"/>
-      <c r="N10" s="168"/>
-      <c r="O10" s="168"/>
-      <c r="P10" s="168"/>
-      <c r="Q10" s="168"/>
+      <c r="J10" s="169"/>
+      <c r="K10" s="169"/>
+      <c r="L10" s="169"/>
+      <c r="M10" s="169"/>
+      <c r="N10" s="169"/>
+      <c r="O10" s="169"/>
+      <c r="P10" s="169"/>
+      <c r="Q10" s="169"/>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" t="s">
@@ -24838,14 +24871,14 @@
       <c r="H11" t="s">
         <v>951</v>
       </c>
-      <c r="J11" s="168"/>
-      <c r="K11" s="168"/>
-      <c r="L11" s="168"/>
-      <c r="M11" s="168"/>
-      <c r="N11" s="168"/>
-      <c r="O11" s="168"/>
-      <c r="P11" s="168"/>
-      <c r="Q11" s="168"/>
+      <c r="J11" s="169"/>
+      <c r="K11" s="169"/>
+      <c r="L11" s="169"/>
+      <c r="M11" s="169"/>
+      <c r="N11" s="169"/>
+      <c r="O11" s="169"/>
+      <c r="P11" s="169"/>
+      <c r="Q11" s="169"/>
     </row>
     <row r="12" spans="1:17">
       <c r="B12" t="s">
@@ -24860,14 +24893,14 @@
       <c r="H12" t="s">
         <v>951</v>
       </c>
-      <c r="J12" s="168"/>
-      <c r="K12" s="168"/>
-      <c r="L12" s="168"/>
-      <c r="M12" s="168"/>
-      <c r="N12" s="168"/>
-      <c r="O12" s="168"/>
-      <c r="P12" s="168"/>
-      <c r="Q12" s="168"/>
+      <c r="J12" s="169"/>
+      <c r="K12" s="169"/>
+      <c r="L12" s="169"/>
+      <c r="M12" s="169"/>
+      <c r="N12" s="169"/>
+      <c r="O12" s="169"/>
+      <c r="P12" s="169"/>
+      <c r="Q12" s="169"/>
     </row>
     <row r="13" spans="1:17">
       <c r="F13" t="s">
@@ -24879,24 +24912,24 @@
       <c r="H13" t="s">
         <v>951</v>
       </c>
-      <c r="J13" s="168"/>
-      <c r="K13" s="168"/>
-      <c r="L13" s="168"/>
-      <c r="M13" s="168"/>
-      <c r="N13" s="168"/>
-      <c r="O13" s="168"/>
-      <c r="P13" s="168"/>
-      <c r="Q13" s="168"/>
+      <c r="J13" s="169"/>
+      <c r="K13" s="169"/>
+      <c r="L13" s="169"/>
+      <c r="M13" s="169"/>
+      <c r="N13" s="169"/>
+      <c r="O13" s="169"/>
+      <c r="P13" s="169"/>
+      <c r="Q13" s="169"/>
     </row>
     <row r="14" spans="1:17">
-      <c r="J14" s="168"/>
-      <c r="K14" s="168"/>
-      <c r="L14" s="168"/>
-      <c r="M14" s="168"/>
-      <c r="N14" s="168"/>
-      <c r="O14" s="168"/>
-      <c r="P14" s="168"/>
-      <c r="Q14" s="168"/>
+      <c r="J14" s="169"/>
+      <c r="K14" s="169"/>
+      <c r="L14" s="169"/>
+      <c r="M14" s="169"/>
+      <c r="N14" s="169"/>
+      <c r="O14" s="169"/>
+      <c r="P14" s="169"/>
+      <c r="Q14" s="169"/>
     </row>
     <row r="15" spans="1:17">
       <c r="A15" t="s">
@@ -24905,27 +24938,27 @@
       <c r="C15" t="s">
         <v>947</v>
       </c>
-      <c r="J15" s="168"/>
-      <c r="K15" s="168"/>
-      <c r="L15" s="168"/>
-      <c r="M15" s="168"/>
-      <c r="N15" s="168"/>
-      <c r="O15" s="168"/>
-      <c r="P15" s="168"/>
-      <c r="Q15" s="168"/>
+      <c r="J15" s="169"/>
+      <c r="K15" s="169"/>
+      <c r="L15" s="169"/>
+      <c r="M15" s="169"/>
+      <c r="N15" s="169"/>
+      <c r="O15" s="169"/>
+      <c r="P15" s="169"/>
+      <c r="Q15" s="169"/>
     </row>
     <row r="16" spans="1:17">
       <c r="A16" t="s">
         <v>937</v>
       </c>
-      <c r="J16" s="168"/>
-      <c r="K16" s="168"/>
-      <c r="L16" s="168"/>
-      <c r="M16" s="168"/>
-      <c r="N16" s="168"/>
-      <c r="O16" s="168"/>
-      <c r="P16" s="168"/>
-      <c r="Q16" s="168"/>
+      <c r="J16" s="169"/>
+      <c r="K16" s="169"/>
+      <c r="L16" s="169"/>
+      <c r="M16" s="169"/>
+      <c r="N16" s="169"/>
+      <c r="O16" s="169"/>
+      <c r="P16" s="169"/>
+      <c r="Q16" s="169"/>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="5" t="s">
@@ -25210,19 +25243,19 @@
       <c r="E7" s="31" t="s">
         <v>449</v>
       </c>
-      <c r="F7" s="169" t="s">
+      <c r="F7" s="170" t="s">
         <v>441</v>
       </c>
-      <c r="G7" s="169"/>
-      <c r="H7" s="169"/>
-      <c r="I7" s="169"/>
-      <c r="J7" s="169"/>
-      <c r="K7" s="169"/>
-      <c r="L7" s="169"/>
-      <c r="M7" s="169"/>
-      <c r="N7" s="169"/>
-      <c r="O7" s="169"/>
-      <c r="P7" s="169"/>
+      <c r="G7" s="170"/>
+      <c r="H7" s="170"/>
+      <c r="I7" s="170"/>
+      <c r="J7" s="170"/>
+      <c r="K7" s="170"/>
+      <c r="L7" s="170"/>
+      <c r="M7" s="170"/>
+      <c r="N7" s="170"/>
+      <c r="O7" s="170"/>
+      <c r="P7" s="170"/>
     </row>
     <row r="8" spans="1:17">
       <c r="B8" s="32" t="s">
@@ -25446,40 +25479,40 @@
       <c r="A24" s="35" t="s">
         <v>455</v>
       </c>
-      <c r="B24" s="170" t="s">
+      <c r="B24" s="171" t="s">
         <v>457</v>
       </c>
-      <c r="C24" s="170"/>
-      <c r="D24" s="170"/>
-      <c r="E24" s="170"/>
-      <c r="F24" s="170"/>
-      <c r="G24" s="170"/>
+      <c r="C24" s="171"/>
+      <c r="D24" s="171"/>
+      <c r="E24" s="171"/>
+      <c r="F24" s="171"/>
+      <c r="G24" s="171"/>
     </row>
     <row r="25" spans="1:7" ht="30">
       <c r="A25" s="35" t="s">
         <v>462</v>
       </c>
-      <c r="B25" s="171" t="s">
+      <c r="B25" s="172" t="s">
         <v>464</v>
       </c>
-      <c r="C25" s="171"/>
-      <c r="D25" s="171"/>
-      <c r="E25" s="171"/>
-      <c r="F25" s="171"/>
-      <c r="G25" s="171"/>
+      <c r="C25" s="172"/>
+      <c r="D25" s="172"/>
+      <c r="E25" s="172"/>
+      <c r="F25" s="172"/>
+      <c r="G25" s="172"/>
     </row>
     <row r="26" spans="1:7" ht="159" customHeight="1">
       <c r="A26" s="35" t="s">
         <v>459</v>
       </c>
-      <c r="B26" s="170" t="s">
+      <c r="B26" s="171" t="s">
         <v>460</v>
       </c>
-      <c r="C26" s="170"/>
-      <c r="D26" s="170"/>
-      <c r="E26" s="170"/>
-      <c r="F26" s="170"/>
-      <c r="G26" s="170"/>
+      <c r="C26" s="171"/>
+      <c r="D26" s="171"/>
+      <c r="E26" s="171"/>
+      <c r="F26" s="171"/>
+      <c r="G26" s="171"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -25994,29 +26027,29 @@
       <c r="B27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="C27" s="174" t="s">
+      <c r="C27" s="175" t="s">
         <v>622</v>
       </c>
-      <c r="D27" s="175"/>
+      <c r="D27" s="176"/>
       <c r="E27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="F27" s="174" t="s">
+      <c r="F27" s="175" t="s">
         <v>622</v>
       </c>
-      <c r="G27" s="175"/>
+      <c r="G27" s="176"/>
       <c r="H27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="I27" s="174" t="s">
+      <c r="I27" s="175" t="s">
         <v>622</v>
       </c>
-      <c r="J27" s="175"/>
-      <c r="L27" s="172" t="s">
+      <c r="J27" s="176"/>
+      <c r="L27" s="173" t="s">
         <v>694</v>
       </c>
-      <c r="M27" s="172"/>
-      <c r="N27" s="172"/>
+      <c r="M27" s="173"/>
+      <c r="N27" s="173"/>
     </row>
     <row r="28" spans="1:14" ht="32.25" thickBot="1">
       <c r="A28" s="81">
@@ -26025,29 +26058,29 @@
       <c r="B28" s="69" t="s">
         <v>623</v>
       </c>
-      <c r="C28" s="182" t="s">
+      <c r="C28" s="183" t="s">
         <v>624</v>
       </c>
-      <c r="D28" s="183"/>
+      <c r="D28" s="184"/>
       <c r="E28" s="70" t="s">
         <v>645</v>
       </c>
-      <c r="F28" s="176" t="s">
+      <c r="F28" s="177" t="s">
         <v>646</v>
       </c>
-      <c r="G28" s="177"/>
+      <c r="G28" s="178"/>
       <c r="H28" s="69" t="s">
         <v>667</v>
       </c>
-      <c r="I28" s="182" t="s">
+      <c r="I28" s="183" t="s">
         <v>668</v>
       </c>
-      <c r="J28" s="183"/>
-      <c r="L28" s="173" t="s">
+      <c r="J28" s="184"/>
+      <c r="L28" s="174" t="s">
         <v>695</v>
       </c>
-      <c r="M28" s="173"/>
-      <c r="N28" s="173"/>
+      <c r="M28" s="174"/>
+      <c r="N28" s="174"/>
     </row>
     <row r="29" spans="1:14" ht="31.5" thickBot="1">
       <c r="A29" s="81">
@@ -26056,29 +26089,29 @@
       <c r="B29" s="70" t="s">
         <v>625</v>
       </c>
-      <c r="C29" s="176" t="s">
+      <c r="C29" s="177" t="s">
         <v>626</v>
       </c>
-      <c r="D29" s="177"/>
+      <c r="D29" s="178"/>
       <c r="E29" s="69" t="s">
         <v>647</v>
       </c>
-      <c r="F29" s="182" t="s">
+      <c r="F29" s="183" t="s">
         <v>648</v>
       </c>
-      <c r="G29" s="183"/>
+      <c r="G29" s="184"/>
       <c r="H29" s="70" t="s">
         <v>669</v>
       </c>
-      <c r="I29" s="186" t="s">
+      <c r="I29" s="187" t="s">
         <v>670</v>
       </c>
-      <c r="J29" s="187"/>
-      <c r="L29" s="172" t="s">
+      <c r="J29" s="188"/>
+      <c r="L29" s="173" t="s">
         <v>696</v>
       </c>
-      <c r="M29" s="172"/>
-      <c r="N29" s="172"/>
+      <c r="M29" s="173"/>
+      <c r="N29" s="173"/>
     </row>
     <row r="30" spans="1:14" ht="15.75" thickBot="1">
       <c r="A30" s="81">
@@ -26087,29 +26120,29 @@
       <c r="B30" s="69" t="s">
         <v>627</v>
       </c>
-      <c r="C30" s="182" t="s">
+      <c r="C30" s="183" t="s">
         <v>628</v>
       </c>
-      <c r="D30" s="183"/>
+      <c r="D30" s="184"/>
       <c r="E30" s="70" t="s">
         <v>649</v>
       </c>
-      <c r="F30" s="176" t="s">
+      <c r="F30" s="177" t="s">
         <v>650</v>
       </c>
-      <c r="G30" s="177"/>
+      <c r="G30" s="178"/>
       <c r="H30" s="69" t="s">
         <v>671</v>
       </c>
-      <c r="I30" s="182" t="s">
+      <c r="I30" s="183" t="s">
         <v>672</v>
       </c>
-      <c r="J30" s="183"/>
-      <c r="L30" s="173" t="s">
+      <c r="J30" s="184"/>
+      <c r="L30" s="174" t="s">
         <v>697</v>
       </c>
-      <c r="M30" s="173"/>
-      <c r="N30" s="173"/>
+      <c r="M30" s="174"/>
+      <c r="N30" s="174"/>
     </row>
     <row r="31" spans="1:14" ht="17.25" customHeight="1" thickBot="1">
       <c r="A31" s="81">
@@ -26118,29 +26151,29 @@
       <c r="B31" s="70" t="s">
         <v>629</v>
       </c>
-      <c r="C31" s="176" t="s">
+      <c r="C31" s="177" t="s">
         <v>630</v>
       </c>
-      <c r="D31" s="177"/>
+      <c r="D31" s="178"/>
       <c r="E31" s="69" t="s">
         <v>651</v>
       </c>
-      <c r="F31" s="182" t="s">
+      <c r="F31" s="183" t="s">
         <v>652</v>
       </c>
-      <c r="G31" s="183"/>
+      <c r="G31" s="184"/>
       <c r="H31" s="70" t="s">
         <v>673</v>
       </c>
-      <c r="I31" s="176" t="s">
+      <c r="I31" s="177" t="s">
         <v>674</v>
       </c>
-      <c r="J31" s="177"/>
-      <c r="L31" s="172" t="s">
+      <c r="J31" s="178"/>
+      <c r="L31" s="173" t="s">
         <v>698</v>
       </c>
-      <c r="M31" s="172"/>
-      <c r="N31" s="172"/>
+      <c r="M31" s="173"/>
+      <c r="N31" s="173"/>
     </row>
     <row r="32" spans="1:14" ht="43.5" customHeight="1" thickBot="1">
       <c r="A32" s="81">
@@ -26149,29 +26182,29 @@
       <c r="B32" s="69" t="s">
         <v>631</v>
       </c>
-      <c r="C32" s="182" t="s">
+      <c r="C32" s="183" t="s">
         <v>632</v>
       </c>
-      <c r="D32" s="183"/>
+      <c r="D32" s="184"/>
       <c r="E32" s="70" t="s">
         <v>653</v>
       </c>
-      <c r="F32" s="176" t="s">
+      <c r="F32" s="177" t="s">
         <v>654</v>
       </c>
-      <c r="G32" s="177"/>
+      <c r="G32" s="178"/>
       <c r="H32" s="69" t="s">
         <v>675</v>
       </c>
-      <c r="I32" s="182" t="s">
+      <c r="I32" s="183" t="s">
         <v>676</v>
       </c>
-      <c r="J32" s="183"/>
-      <c r="L32" s="173" t="s">
+      <c r="J32" s="184"/>
+      <c r="L32" s="174" t="s">
         <v>699</v>
       </c>
-      <c r="M32" s="173"/>
-      <c r="N32" s="173"/>
+      <c r="M32" s="174"/>
+      <c r="N32" s="174"/>
     </row>
     <row r="33" spans="1:14" ht="31.5" customHeight="1" thickBot="1">
       <c r="A33" s="81">
@@ -26180,29 +26213,29 @@
       <c r="B33" s="70" t="s">
         <v>633</v>
       </c>
-      <c r="C33" s="176" t="s">
+      <c r="C33" s="177" t="s">
         <v>634</v>
       </c>
-      <c r="D33" s="177"/>
+      <c r="D33" s="178"/>
       <c r="E33" s="69" t="s">
         <v>655</v>
       </c>
-      <c r="F33" s="182" t="s">
+      <c r="F33" s="183" t="s">
         <v>656</v>
       </c>
-      <c r="G33" s="183"/>
+      <c r="G33" s="184"/>
       <c r="H33" s="70" t="s">
         <v>677</v>
       </c>
-      <c r="I33" s="184" t="s">
+      <c r="I33" s="185" t="s">
         <v>678</v>
       </c>
-      <c r="J33" s="185"/>
-      <c r="L33" s="172" t="s">
+      <c r="J33" s="186"/>
+      <c r="L33" s="173" t="s">
         <v>700</v>
       </c>
-      <c r="M33" s="172"/>
-      <c r="N33" s="172"/>
+      <c r="M33" s="173"/>
+      <c r="N33" s="173"/>
     </row>
     <row r="34" spans="1:14" ht="28.5" customHeight="1" thickBot="1">
       <c r="A34" s="81">
@@ -26211,29 +26244,29 @@
       <c r="B34" s="69" t="s">
         <v>635</v>
       </c>
-      <c r="C34" s="182" t="s">
+      <c r="C34" s="183" t="s">
         <v>636</v>
       </c>
-      <c r="D34" s="183"/>
+      <c r="D34" s="184"/>
       <c r="E34" s="70" t="s">
         <v>657</v>
       </c>
-      <c r="F34" s="176" t="s">
+      <c r="F34" s="177" t="s">
         <v>658</v>
       </c>
-      <c r="G34" s="177"/>
+      <c r="G34" s="178"/>
       <c r="H34" s="69" t="s">
         <v>679</v>
       </c>
-      <c r="I34" s="180" t="s">
+      <c r="I34" s="181" t="s">
         <v>680</v>
       </c>
-      <c r="J34" s="181"/>
-      <c r="L34" s="173" t="s">
+      <c r="J34" s="182"/>
+      <c r="L34" s="174" t="s">
         <v>701</v>
       </c>
-      <c r="M34" s="173"/>
-      <c r="N34" s="173"/>
+      <c r="M34" s="174"/>
+      <c r="N34" s="174"/>
     </row>
     <row r="35" spans="1:14" ht="31.5" customHeight="1" thickBot="1">
       <c r="A35" s="81">
@@ -26242,29 +26275,29 @@
       <c r="B35" s="70" t="s">
         <v>637</v>
       </c>
-      <c r="C35" s="176" t="s">
+      <c r="C35" s="177" t="s">
         <v>638</v>
       </c>
-      <c r="D35" s="177"/>
+      <c r="D35" s="178"/>
       <c r="E35" s="69" t="s">
         <v>659</v>
       </c>
-      <c r="F35" s="182" t="s">
+      <c r="F35" s="183" t="s">
         <v>660</v>
       </c>
-      <c r="G35" s="183"/>
+      <c r="G35" s="184"/>
       <c r="H35" s="77" t="s">
         <v>681</v>
       </c>
-      <c r="I35" s="176" t="s">
+      <c r="I35" s="177" t="s">
         <v>682</v>
       </c>
-      <c r="J35" s="177"/>
-      <c r="L35" s="172" t="s">
+      <c r="J35" s="178"/>
+      <c r="L35" s="173" t="s">
         <v>702</v>
       </c>
-      <c r="M35" s="172"/>
-      <c r="N35" s="172"/>
+      <c r="M35" s="173"/>
+      <c r="N35" s="173"/>
     </row>
     <row r="36" spans="1:14" ht="60.75" thickBot="1">
       <c r="A36" s="81">
@@ -26273,17 +26306,17 @@
       <c r="B36" s="69" t="s">
         <v>639</v>
       </c>
-      <c r="C36" s="182" t="s">
+      <c r="C36" s="183" t="s">
         <v>640</v>
       </c>
-      <c r="D36" s="183"/>
+      <c r="D36" s="184"/>
       <c r="E36" s="70" t="s">
         <v>661</v>
       </c>
-      <c r="F36" s="176" t="s">
+      <c r="F36" s="177" t="s">
         <v>662</v>
       </c>
-      <c r="G36" s="177"/>
+      <c r="G36" s="178"/>
       <c r="H36" s="78"/>
       <c r="I36" s="71" t="s">
         <v>683</v>
@@ -26291,11 +26324,11 @@
       <c r="J36" s="72" t="s">
         <v>684</v>
       </c>
-      <c r="L36" s="173" t="s">
+      <c r="L36" s="174" t="s">
         <v>703</v>
       </c>
-      <c r="M36" s="173"/>
-      <c r="N36" s="173"/>
+      <c r="M36" s="174"/>
+      <c r="N36" s="174"/>
     </row>
     <row r="37" spans="1:14" ht="75.75" thickBot="1">
       <c r="A37" s="81">
@@ -26304,17 +26337,17 @@
       <c r="B37" s="70" t="s">
         <v>641</v>
       </c>
-      <c r="C37" s="176" t="s">
+      <c r="C37" s="177" t="s">
         <v>642</v>
       </c>
-      <c r="D37" s="177"/>
+      <c r="D37" s="178"/>
       <c r="E37" s="69" t="s">
         <v>663</v>
       </c>
-      <c r="F37" s="182" t="s">
+      <c r="F37" s="183" t="s">
         <v>664</v>
       </c>
-      <c r="G37" s="183"/>
+      <c r="G37" s="184"/>
       <c r="H37" s="78"/>
       <c r="I37" s="73" t="s">
         <v>685</v>
@@ -26330,17 +26363,17 @@
       <c r="B38" s="69" t="s">
         <v>643</v>
       </c>
-      <c r="C38" s="182" t="s">
+      <c r="C38" s="183" t="s">
         <v>644</v>
       </c>
-      <c r="D38" s="183"/>
+      <c r="D38" s="184"/>
       <c r="E38" s="70" t="s">
         <v>665</v>
       </c>
-      <c r="F38" s="176" t="s">
+      <c r="F38" s="177" t="s">
         <v>666</v>
       </c>
-      <c r="G38" s="177"/>
+      <c r="G38" s="178"/>
       <c r="H38" s="78"/>
       <c r="I38" s="75" t="s">
         <v>687</v>
@@ -26356,22 +26389,22 @@
       <c r="B39" s="70" t="s">
         <v>692</v>
       </c>
-      <c r="C39" s="184" t="s">
+      <c r="C39" s="185" t="s">
         <v>693</v>
       </c>
-      <c r="D39" s="185"/>
+      <c r="D39" s="186"/>
       <c r="E39" s="69" t="s">
         <v>690</v>
       </c>
-      <c r="F39" s="180" t="s">
+      <c r="F39" s="181" t="s">
         <v>691</v>
       </c>
-      <c r="G39" s="181"/>
+      <c r="G39" s="182"/>
       <c r="H39" s="79"/>
-      <c r="I39" s="178" t="s">
+      <c r="I39" s="179" t="s">
         <v>689</v>
       </c>
-      <c r="J39" s="179"/>
+      <c r="J39" s="180"/>
     </row>
     <row r="40" spans="1:14" ht="58.5" customHeight="1"/>
     <row r="42" spans="1:14" ht="31.5" customHeight="1"/>

--- a/2020_LogAnalyzer_Leeheesuk.xlsx
+++ b/2020_LogAnalyzer_Leeheesuk.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="23001"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76E0110B-3929-49DF-9955-9F25FEE48F40}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75FC3E78-A92A-4FCA-8C41-CC36531C4B61}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15990" firstSheet="8" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-16050" yWindow="120" windowWidth="15990" windowHeight="14790" firstSheet="9" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UI" sheetId="7" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2121" uniqueCount="1356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2130" uniqueCount="1364">
   <si>
     <t>구분</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -5929,7 +5929,31 @@
     <t>진행중</t>
   </si>
   <si>
-    <t>평균 응답시간</t>
+    <t>평균 응답시간(주어진 기간)</t>
+  </si>
+  <si>
+    <t>평균 처리량(주어진 기간)</t>
+  </si>
+  <si>
+    <t>Top N fextension</t>
+  </si>
+  <si>
+    <t>Top N fbyte</t>
+  </si>
+  <si>
+    <t>Statistic</t>
+  </si>
+  <si>
+    <t>Chart</t>
+  </si>
+  <si>
+    <t>Chart제거</t>
+  </si>
+  <si>
+    <t>static file 크기 2MB 이상</t>
+  </si>
+  <si>
+    <t>임계치 테이블 필요</t>
   </si>
 </sst>
 </file>
@@ -6601,7 +6625,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="40" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="221">
+  <cellXfs count="222">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -7193,6 +7217,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="백분율" xfId="2" builtinId="5"/>
@@ -15359,7 +15386,7 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="66675" y="285750"/>
-          <a:ext cx="7540516" cy="2763581"/>
+          <a:ext cx="7564507" cy="2763581"/>
           <a:chOff x="534516" y="352896"/>
           <a:chExt cx="8439150" cy="3049331"/>
         </a:xfrm>
@@ -18538,6 +18565,9 @@
       <c r="M1" s="26" t="s">
         <v>407</v>
       </c>
+      <c r="N1" s="221" t="s">
+        <v>1363</v>
+      </c>
     </row>
     <row r="2" spans="1:17" ht="16.5" customHeight="1">
       <c r="A2" s="190" t="s">
@@ -18641,6 +18671,9 @@
         <v>561</v>
       </c>
       <c r="K5" s="10"/>
+      <c r="M5" s="19" t="s">
+        <v>1362</v>
+      </c>
     </row>
     <row r="6" spans="1:17">
       <c r="A6" s="165"/>
@@ -19820,7 +19853,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:R54"/>
+  <dimension ref="A1:T54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="11" max="11" width="7.42578125" bestFit="1" customWidth="1"/>
@@ -19899,8 +19932,11 @@
       <c r="L32" t="s">
         <v>1340</v>
       </c>
-    </row>
-    <row r="33" spans="1:16">
+      <c r="Q32" t="s">
+        <v>1361</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20">
       <c r="A33" t="s">
         <v>1309</v>
       </c>
@@ -19908,7 +19944,7 @@
         <v>1341</v>
       </c>
     </row>
-    <row r="34" spans="1:16">
+    <row r="34" spans="1:20">
       <c r="A34" t="s">
         <v>1310</v>
       </c>
@@ -19918,8 +19954,17 @@
       <c r="P34" s="220" t="s">
         <v>1354</v>
       </c>
-    </row>
-    <row r="35" spans="1:16">
+      <c r="Q34" t="s">
+        <v>1357</v>
+      </c>
+      <c r="S34" t="s">
+        <v>1359</v>
+      </c>
+      <c r="T34" t="s">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20">
       <c r="A35" t="s">
         <v>1311</v>
       </c>
@@ -19929,8 +19974,14 @@
       <c r="L35" t="s">
         <v>1343</v>
       </c>
-    </row>
-    <row r="36" spans="1:16">
+      <c r="Q35" t="s">
+        <v>1358</v>
+      </c>
+      <c r="S35" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20">
       <c r="A36" t="s">
         <v>1312</v>
       </c>
@@ -19938,7 +19989,7 @@
         <v>1344</v>
       </c>
     </row>
-    <row r="37" spans="1:16">
+    <row r="37" spans="1:20">
       <c r="A37" t="s">
         <v>1313</v>
       </c>
@@ -19946,7 +19997,7 @@
         <v>1345</v>
       </c>
     </row>
-    <row r="38" spans="1:16">
+    <row r="38" spans="1:20">
       <c r="A38" t="s">
         <v>1314</v>
       </c>
@@ -19957,7 +20008,7 @@
         <v>1346</v>
       </c>
     </row>
-    <row r="39" spans="1:16">
+    <row r="39" spans="1:20">
       <c r="A39" t="s">
         <v>1315</v>
       </c>
@@ -19968,7 +20019,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="40" spans="1:16">
+    <row r="40" spans="1:20">
       <c r="A40" t="s">
         <v>1316</v>
       </c>
@@ -19979,45 +20030,48 @@
         <v>1347</v>
       </c>
     </row>
-    <row r="41" spans="1:16">
+    <row r="41" spans="1:20">
       <c r="A41" t="s">
         <v>1317</v>
       </c>
     </row>
-    <row r="42" spans="1:16">
+    <row r="42" spans="1:20">
       <c r="A42" t="s">
         <v>1318</v>
       </c>
-      <c r="L42" t="s">
-        <v>1355</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16">
+    </row>
+    <row r="43" spans="1:20">
       <c r="A43" t="s">
         <v>1319</v>
       </c>
-    </row>
-    <row r="44" spans="1:16">
+      <c r="L43" t="s">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20">
       <c r="A44" t="s">
         <v>1320</v>
       </c>
-    </row>
-    <row r="45" spans="1:16">
+      <c r="L44" t="s">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20">
       <c r="A45" t="s">
         <v>1321</v>
       </c>
     </row>
-    <row r="46" spans="1:16">
+    <row r="46" spans="1:20">
       <c r="A46" t="s">
         <v>1322</v>
       </c>
     </row>
-    <row r="47" spans="1:16">
+    <row r="47" spans="1:20">
       <c r="A47" t="s">
         <v>1323</v>
       </c>
     </row>
-    <row r="48" spans="1:16">
+    <row r="48" spans="1:20">
       <c r="A48" t="s">
         <v>1324</v>
       </c>

--- a/2020_LogAnalyzer_Leeheesuk.xlsx
+++ b/2020_LogAnalyzer_Leeheesuk.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="23001"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="23127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75FC3E78-A92A-4FCA-8C41-CC36531C4B61}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5ECDA6D2-1019-4C2A-8E6C-E213C7BBD78C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16050" yWindow="120" windowWidth="15990" windowHeight="14790" firstSheet="9" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" firstSheet="9" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UI" sheetId="7" r:id="rId1"/>
@@ -35,6 +35,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="12">기능요건!$A$1:$M$46</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -7027,6 +7028,34 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -7081,11 +7110,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -7097,24 +7126,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7129,6 +7140,24 @@
     <xf numFmtId="0" fontId="23" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7139,6 +7168,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7158,15 +7196,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -7191,34 +7220,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -16552,51 +16553,51 @@
     </row>
     <row r="17" spans="1:13">
       <c r="J17" s="19"/>
-      <c r="K17" s="155" t="s">
+      <c r="K17" s="167" t="s">
         <v>537</v>
       </c>
-      <c r="L17" s="156"/>
-      <c r="M17" s="157"/>
+      <c r="L17" s="168"/>
+      <c r="M17" s="169"/>
     </row>
     <row r="18" spans="1:13">
       <c r="J18" s="19">
         <v>1</v>
       </c>
-      <c r="K18" s="158" t="s">
+      <c r="K18" s="170" t="s">
         <v>538</v>
       </c>
-      <c r="L18" s="159"/>
-      <c r="M18" s="160"/>
+      <c r="L18" s="171"/>
+      <c r="M18" s="172"/>
     </row>
     <row r="19" spans="1:13">
       <c r="J19" s="19">
         <v>2</v>
       </c>
-      <c r="K19" s="158" t="s">
+      <c r="K19" s="170" t="s">
         <v>539</v>
       </c>
-      <c r="L19" s="159"/>
-      <c r="M19" s="160"/>
+      <c r="L19" s="171"/>
+      <c r="M19" s="172"/>
     </row>
     <row r="20" spans="1:13">
       <c r="J20" s="19">
         <v>3</v>
       </c>
-      <c r="K20" s="158" t="s">
+      <c r="K20" s="170" t="s">
         <v>540</v>
       </c>
-      <c r="L20" s="159"/>
-      <c r="M20" s="160"/>
+      <c r="L20" s="171"/>
+      <c r="M20" s="172"/>
     </row>
     <row r="21" spans="1:13">
       <c r="J21" s="19">
         <v>4</v>
       </c>
-      <c r="K21" s="158" t="s">
+      <c r="K21" s="170" t="s">
         <v>541</v>
       </c>
-      <c r="L21" s="159"/>
-      <c r="M21" s="160"/>
+      <c r="L21" s="171"/>
+      <c r="M21" s="172"/>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="43" t="s">
@@ -16788,10 +16789,10 @@
       <c r="F7" s="111" t="s">
         <v>915</v>
       </c>
-      <c r="I7" s="189" t="s">
+      <c r="I7" s="201" t="s">
         <v>1166</v>
       </c>
-      <c r="J7" s="189"/>
+      <c r="J7" s="201"/>
       <c r="L7" s="49" t="s">
         <v>601</v>
       </c>
@@ -17134,7 +17135,7 @@
       <c r="M20" s="32" t="s">
         <v>415</v>
       </c>
-      <c r="N20" s="211" t="s">
+      <c r="N20" s="156" t="s">
         <v>568</v>
       </c>
     </row>
@@ -17175,7 +17176,7 @@
       <c r="M21" s="85" t="s">
         <v>466</v>
       </c>
-      <c r="N21" s="212" t="s">
+      <c r="N21" s="157" t="s">
         <v>429</v>
       </c>
     </row>
@@ -17216,7 +17217,7 @@
       <c r="M22" s="62" t="s">
         <v>592</v>
       </c>
-      <c r="N22" s="213" t="s">
+      <c r="N22" s="158" t="s">
         <v>458</v>
       </c>
     </row>
@@ -17246,12 +17247,12 @@
       <c r="J23" s="65">
         <v>200</v>
       </c>
-      <c r="K23" s="219"/>
+      <c r="K23" s="164"/>
       <c r="L23" s="97">
         <v>10</v>
       </c>
       <c r="M23" s="64"/>
-      <c r="N23" s="212" t="s">
+      <c r="N23" s="157" t="s">
         <v>1293</v>
       </c>
     </row>
@@ -17272,29 +17273,29 @@
       <c r="B27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="C27" s="175" t="s">
+      <c r="C27" s="187" t="s">
         <v>622</v>
       </c>
-      <c r="D27" s="176"/>
+      <c r="D27" s="188"/>
       <c r="E27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="F27" s="175" t="s">
+      <c r="F27" s="187" t="s">
         <v>622</v>
       </c>
-      <c r="G27" s="176"/>
+      <c r="G27" s="188"/>
       <c r="H27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="I27" s="175" t="s">
+      <c r="I27" s="187" t="s">
         <v>622</v>
       </c>
-      <c r="J27" s="176"/>
-      <c r="L27" s="173" t="s">
+      <c r="J27" s="188"/>
+      <c r="L27" s="199" t="s">
         <v>694</v>
       </c>
-      <c r="M27" s="173"/>
-      <c r="N27" s="173"/>
+      <c r="M27" s="199"/>
+      <c r="N27" s="199"/>
     </row>
     <row r="28" spans="1:14" ht="49.5" customHeight="1" thickBot="1">
       <c r="A28" s="81">
@@ -17303,29 +17304,29 @@
       <c r="B28" s="69" t="s">
         <v>623</v>
       </c>
-      <c r="C28" s="183" t="s">
+      <c r="C28" s="185" t="s">
         <v>624</v>
       </c>
-      <c r="D28" s="184"/>
+      <c r="D28" s="186"/>
       <c r="E28" s="70" t="s">
         <v>645</v>
       </c>
-      <c r="F28" s="177" t="s">
+      <c r="F28" s="189" t="s">
         <v>1178</v>
       </c>
-      <c r="G28" s="178"/>
+      <c r="G28" s="190"/>
       <c r="H28" s="69" t="s">
         <v>667</v>
       </c>
-      <c r="I28" s="183" t="s">
+      <c r="I28" s="185" t="s">
         <v>668</v>
       </c>
-      <c r="J28" s="184"/>
-      <c r="L28" s="174" t="s">
+      <c r="J28" s="186"/>
+      <c r="L28" s="200" t="s">
         <v>695</v>
       </c>
-      <c r="M28" s="174"/>
-      <c r="N28" s="174"/>
+      <c r="M28" s="200"/>
+      <c r="N28" s="200"/>
     </row>
     <row r="29" spans="1:14" ht="31.5" thickBot="1">
       <c r="A29" s="81">
@@ -17334,29 +17335,29 @@
       <c r="B29" s="70" t="s">
         <v>625</v>
       </c>
-      <c r="C29" s="177" t="s">
+      <c r="C29" s="189" t="s">
         <v>626</v>
       </c>
-      <c r="D29" s="178"/>
+      <c r="D29" s="190"/>
       <c r="E29" s="69" t="s">
         <v>647</v>
       </c>
-      <c r="F29" s="183" t="s">
+      <c r="F29" s="185" t="s">
         <v>648</v>
       </c>
-      <c r="G29" s="184"/>
+      <c r="G29" s="186"/>
       <c r="H29" s="70" t="s">
         <v>669</v>
       </c>
-      <c r="I29" s="187" t="s">
+      <c r="I29" s="193" t="s">
         <v>670</v>
       </c>
-      <c r="J29" s="188"/>
-      <c r="L29" s="173" t="s">
+      <c r="J29" s="194"/>
+      <c r="L29" s="199" t="s">
         <v>696</v>
       </c>
-      <c r="M29" s="173"/>
-      <c r="N29" s="173"/>
+      <c r="M29" s="199"/>
+      <c r="N29" s="199"/>
     </row>
     <row r="30" spans="1:14" ht="15.75" thickBot="1">
       <c r="A30" s="81">
@@ -17365,29 +17366,29 @@
       <c r="B30" s="69" t="s">
         <v>627</v>
       </c>
-      <c r="C30" s="183" t="s">
+      <c r="C30" s="185" t="s">
         <v>628</v>
       </c>
-      <c r="D30" s="184"/>
+      <c r="D30" s="186"/>
       <c r="E30" s="70" t="s">
         <v>649</v>
       </c>
-      <c r="F30" s="177" t="s">
+      <c r="F30" s="189" t="s">
         <v>650</v>
       </c>
-      <c r="G30" s="178"/>
+      <c r="G30" s="190"/>
       <c r="H30" s="69" t="s">
         <v>671</v>
       </c>
-      <c r="I30" s="183" t="s">
+      <c r="I30" s="185" t="s">
         <v>672</v>
       </c>
-      <c r="J30" s="184"/>
-      <c r="L30" s="174" t="s">
+      <c r="J30" s="186"/>
+      <c r="L30" s="200" t="s">
         <v>697</v>
       </c>
-      <c r="M30" s="174"/>
-      <c r="N30" s="174"/>
+      <c r="M30" s="200"/>
+      <c r="N30" s="200"/>
     </row>
     <row r="31" spans="1:14" ht="17.25" customHeight="1" thickBot="1">
       <c r="A31" s="81">
@@ -17396,29 +17397,29 @@
       <c r="B31" s="70" t="s">
         <v>629</v>
       </c>
-      <c r="C31" s="177" t="s">
+      <c r="C31" s="189" t="s">
         <v>630</v>
       </c>
-      <c r="D31" s="178"/>
+      <c r="D31" s="190"/>
       <c r="E31" s="69" t="s">
         <v>651</v>
       </c>
-      <c r="F31" s="183" t="s">
+      <c r="F31" s="185" t="s">
         <v>652</v>
       </c>
-      <c r="G31" s="184"/>
+      <c r="G31" s="186"/>
       <c r="H31" s="70" t="s">
         <v>673</v>
       </c>
-      <c r="I31" s="177" t="s">
+      <c r="I31" s="189" t="s">
         <v>674</v>
       </c>
-      <c r="J31" s="178"/>
-      <c r="L31" s="173" t="s">
+      <c r="J31" s="190"/>
+      <c r="L31" s="199" t="s">
         <v>698</v>
       </c>
-      <c r="M31" s="173"/>
-      <c r="N31" s="173"/>
+      <c r="M31" s="199"/>
+      <c r="N31" s="199"/>
     </row>
     <row r="32" spans="1:14" ht="43.5" customHeight="1" thickBot="1">
       <c r="A32" s="81">
@@ -17427,29 +17428,29 @@
       <c r="B32" s="69" t="s">
         <v>631</v>
       </c>
-      <c r="C32" s="183" t="s">
+      <c r="C32" s="185" t="s">
         <v>632</v>
       </c>
-      <c r="D32" s="184"/>
+      <c r="D32" s="186"/>
       <c r="E32" s="70" t="s">
         <v>653</v>
       </c>
-      <c r="F32" s="177" t="s">
+      <c r="F32" s="189" t="s">
         <v>654</v>
       </c>
-      <c r="G32" s="178"/>
+      <c r="G32" s="190"/>
       <c r="H32" s="69" t="s">
         <v>675</v>
       </c>
-      <c r="I32" s="183" t="s">
+      <c r="I32" s="185" t="s">
         <v>676</v>
       </c>
-      <c r="J32" s="184"/>
-      <c r="L32" s="174" t="s">
+      <c r="J32" s="186"/>
+      <c r="L32" s="200" t="s">
         <v>699</v>
       </c>
-      <c r="M32" s="174"/>
-      <c r="N32" s="174"/>
+      <c r="M32" s="200"/>
+      <c r="N32" s="200"/>
     </row>
     <row r="33" spans="1:14" ht="31.5" customHeight="1" thickBot="1">
       <c r="A33" s="81">
@@ -17458,29 +17459,29 @@
       <c r="B33" s="70" t="s">
         <v>633</v>
       </c>
-      <c r="C33" s="177" t="s">
+      <c r="C33" s="189" t="s">
         <v>634</v>
       </c>
-      <c r="D33" s="178"/>
+      <c r="D33" s="190"/>
       <c r="E33" s="69" t="s">
         <v>655</v>
       </c>
-      <c r="F33" s="183" t="s">
+      <c r="F33" s="185" t="s">
         <v>656</v>
       </c>
-      <c r="G33" s="184"/>
+      <c r="G33" s="186"/>
       <c r="H33" s="70" t="s">
         <v>677</v>
       </c>
-      <c r="I33" s="185" t="s">
+      <c r="I33" s="191" t="s">
         <v>678</v>
       </c>
-      <c r="J33" s="186"/>
-      <c r="L33" s="173" t="s">
+      <c r="J33" s="192"/>
+      <c r="L33" s="199" t="s">
         <v>700</v>
       </c>
-      <c r="M33" s="173"/>
-      <c r="N33" s="173"/>
+      <c r="M33" s="199"/>
+      <c r="N33" s="199"/>
     </row>
     <row r="34" spans="1:14" ht="28.5" customHeight="1" thickBot="1">
       <c r="A34" s="81">
@@ -17489,29 +17490,29 @@
       <c r="B34" s="69" t="s">
         <v>635</v>
       </c>
-      <c r="C34" s="183" t="s">
+      <c r="C34" s="185" t="s">
         <v>636</v>
       </c>
-      <c r="D34" s="184"/>
+      <c r="D34" s="186"/>
       <c r="E34" s="70" t="s">
         <v>657</v>
       </c>
-      <c r="F34" s="177" t="s">
+      <c r="F34" s="189" t="s">
         <v>658</v>
       </c>
-      <c r="G34" s="178"/>
+      <c r="G34" s="190"/>
       <c r="H34" s="69" t="s">
         <v>679</v>
       </c>
-      <c r="I34" s="181" t="s">
+      <c r="I34" s="195" t="s">
         <v>680</v>
       </c>
-      <c r="J34" s="182"/>
-      <c r="L34" s="174" t="s">
+      <c r="J34" s="196"/>
+      <c r="L34" s="200" t="s">
         <v>701</v>
       </c>
-      <c r="M34" s="174"/>
-      <c r="N34" s="174"/>
+      <c r="M34" s="200"/>
+      <c r="N34" s="200"/>
     </row>
     <row r="35" spans="1:14" ht="31.5" customHeight="1" thickBot="1">
       <c r="A35" s="81">
@@ -17520,29 +17521,29 @@
       <c r="B35" s="70" t="s">
         <v>637</v>
       </c>
-      <c r="C35" s="177" t="s">
+      <c r="C35" s="189" t="s">
         <v>638</v>
       </c>
-      <c r="D35" s="178"/>
+      <c r="D35" s="190"/>
       <c r="E35" s="69" t="s">
         <v>659</v>
       </c>
-      <c r="F35" s="183" t="s">
+      <c r="F35" s="185" t="s">
         <v>660</v>
       </c>
-      <c r="G35" s="184"/>
+      <c r="G35" s="186"/>
       <c r="H35" s="77" t="s">
         <v>681</v>
       </c>
-      <c r="I35" s="177" t="s">
+      <c r="I35" s="189" t="s">
         <v>682</v>
       </c>
-      <c r="J35" s="178"/>
-      <c r="L35" s="173" t="s">
+      <c r="J35" s="190"/>
+      <c r="L35" s="199" t="s">
         <v>702</v>
       </c>
-      <c r="M35" s="173"/>
-      <c r="N35" s="173"/>
+      <c r="M35" s="199"/>
+      <c r="N35" s="199"/>
     </row>
     <row r="36" spans="1:14" ht="60.75" thickBot="1">
       <c r="A36" s="81">
@@ -17551,17 +17552,17 @@
       <c r="B36" s="69" t="s">
         <v>639</v>
       </c>
-      <c r="C36" s="183" t="s">
+      <c r="C36" s="185" t="s">
         <v>640</v>
       </c>
-      <c r="D36" s="184"/>
+      <c r="D36" s="186"/>
       <c r="E36" s="70" t="s">
         <v>661</v>
       </c>
-      <c r="F36" s="177" t="s">
+      <c r="F36" s="189" t="s">
         <v>662</v>
       </c>
-      <c r="G36" s="178"/>
+      <c r="G36" s="190"/>
       <c r="H36" s="78"/>
       <c r="I36" s="71" t="s">
         <v>683</v>
@@ -17569,11 +17570,11 @@
       <c r="J36" s="72" t="s">
         <v>684</v>
       </c>
-      <c r="L36" s="174" t="s">
+      <c r="L36" s="200" t="s">
         <v>703</v>
       </c>
-      <c r="M36" s="174"/>
-      <c r="N36" s="174"/>
+      <c r="M36" s="200"/>
+      <c r="N36" s="200"/>
     </row>
     <row r="37" spans="1:14" ht="75.75" thickBot="1">
       <c r="A37" s="81">
@@ -17582,17 +17583,17 @@
       <c r="B37" s="70" t="s">
         <v>641</v>
       </c>
-      <c r="C37" s="177" t="s">
+      <c r="C37" s="189" t="s">
         <v>642</v>
       </c>
-      <c r="D37" s="178"/>
+      <c r="D37" s="190"/>
       <c r="E37" s="69" t="s">
         <v>663</v>
       </c>
-      <c r="F37" s="183" t="s">
+      <c r="F37" s="185" t="s">
         <v>664</v>
       </c>
-      <c r="G37" s="184"/>
+      <c r="G37" s="186"/>
       <c r="H37" s="78"/>
       <c r="I37" s="73" t="s">
         <v>685</v>
@@ -17608,17 +17609,17 @@
       <c r="B38" s="69" t="s">
         <v>643</v>
       </c>
-      <c r="C38" s="183" t="s">
+      <c r="C38" s="185" t="s">
         <v>644</v>
       </c>
-      <c r="D38" s="184"/>
+      <c r="D38" s="186"/>
       <c r="E38" s="70" t="s">
         <v>665</v>
       </c>
-      <c r="F38" s="177" t="s">
+      <c r="F38" s="189" t="s">
         <v>666</v>
       </c>
-      <c r="G38" s="178"/>
+      <c r="G38" s="190"/>
       <c r="H38" s="78"/>
       <c r="I38" s="75" t="s">
         <v>687</v>
@@ -17634,22 +17635,22 @@
       <c r="B39" s="70" t="s">
         <v>692</v>
       </c>
-      <c r="C39" s="185" t="s">
+      <c r="C39" s="191" t="s">
         <v>693</v>
       </c>
-      <c r="D39" s="186"/>
+      <c r="D39" s="192"/>
       <c r="E39" s="69" t="s">
         <v>690</v>
       </c>
-      <c r="F39" s="181" t="s">
+      <c r="F39" s="195" t="s">
         <v>691</v>
       </c>
-      <c r="G39" s="182"/>
+      <c r="G39" s="196"/>
       <c r="H39" s="79"/>
-      <c r="I39" s="179" t="s">
+      <c r="I39" s="197" t="s">
         <v>689</v>
       </c>
-      <c r="J39" s="180"/>
+      <c r="J39" s="198"/>
     </row>
     <row r="40" spans="1:14" ht="58.5" customHeight="1"/>
     <row r="41" spans="1:14">
@@ -17943,6 +17944,43 @@
     </row>
   </sheetData>
   <mergeCells count="47">
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="L35:N35"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="F36:G36"/>
     <mergeCell ref="L36:N36"/>
@@ -17953,43 +17991,6 @@
     <mergeCell ref="F38:G38"/>
     <mergeCell ref="C39:D39"/>
     <mergeCell ref="F39:G39"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="L27:N27"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
@@ -18565,21 +18566,21 @@
       <c r="M1" s="26" t="s">
         <v>407</v>
       </c>
-      <c r="N1" s="221" t="s">
+      <c r="N1" s="166" t="s">
         <v>1363</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A2" s="190" t="s">
+      <c r="A2" s="202" t="s">
         <v>504</v>
       </c>
-      <c r="B2" s="199" t="s">
+      <c r="B2" s="205" t="s">
         <v>506</v>
       </c>
-      <c r="C2" s="190" t="s">
+      <c r="C2" s="202" t="s">
         <v>508</v>
       </c>
-      <c r="D2" s="190" t="s">
+      <c r="D2" s="202" t="s">
         <v>556</v>
       </c>
       <c r="E2" s="8"/>
@@ -18592,7 +18593,7 @@
       <c r="H2" s="10">
         <v>1</v>
       </c>
-      <c r="I2" s="210">
+      <c r="I2" s="155">
         <v>44043</v>
       </c>
       <c r="J2" s="10"/>
@@ -18600,12 +18601,13 @@
       <c r="M2" s="19" t="s">
         <v>406</v>
       </c>
+      <c r="N2" s="19"/>
     </row>
     <row r="3" spans="1:17">
-      <c r="A3" s="165"/>
-      <c r="B3" s="200"/>
-      <c r="C3" s="191"/>
-      <c r="D3" s="191"/>
+      <c r="A3" s="177"/>
+      <c r="B3" s="206"/>
+      <c r="C3" s="203"/>
+      <c r="D3" s="203"/>
       <c r="E3" s="11"/>
       <c r="F3" s="9" t="s">
         <v>310</v>
@@ -18616,7 +18618,7 @@
       <c r="H3" s="12">
         <v>2</v>
       </c>
-      <c r="I3" s="210">
+      <c r="I3" s="155">
         <v>44074</v>
       </c>
       <c r="J3" s="10"/>
@@ -18624,12 +18626,13 @@
       <c r="M3" s="19" t="s">
         <v>547</v>
       </c>
+      <c r="N3" s="19"/>
     </row>
     <row r="4" spans="1:17">
-      <c r="A4" s="165"/>
-      <c r="B4" s="200"/>
-      <c r="C4" s="191"/>
-      <c r="D4" s="192"/>
+      <c r="A4" s="177"/>
+      <c r="B4" s="206"/>
+      <c r="C4" s="203"/>
+      <c r="D4" s="204"/>
       <c r="E4" s="11"/>
       <c r="F4" s="9" t="s">
         <v>311</v>
@@ -18640,17 +18643,18 @@
       <c r="H4" s="12" t="s">
         <v>963</v>
       </c>
-      <c r="I4" s="210"/>
+      <c r="I4" s="155"/>
       <c r="J4" s="10"/>
       <c r="K4" s="10"/>
-      <c r="M4" s="217" t="s">
+      <c r="M4" s="162" t="s">
         <v>1299</v>
       </c>
+      <c r="N4" s="19"/>
     </row>
     <row r="5" spans="1:17">
-      <c r="A5" s="165"/>
-      <c r="B5" s="200"/>
-      <c r="C5" s="192"/>
+      <c r="A5" s="177"/>
+      <c r="B5" s="206"/>
+      <c r="C5" s="204"/>
       <c r="D5" s="46" t="s">
         <v>555</v>
       </c>
@@ -18664,7 +18668,7 @@
       <c r="H5" s="12" t="s">
         <v>960</v>
       </c>
-      <c r="I5" s="210">
+      <c r="I5" s="155">
         <v>44043</v>
       </c>
       <c r="J5" s="10" t="s">
@@ -18674,14 +18678,15 @@
       <c r="M5" s="19" t="s">
         <v>1362</v>
       </c>
+      <c r="N5" s="19"/>
     </row>
     <row r="6" spans="1:17">
-      <c r="A6" s="165"/>
-      <c r="B6" s="200"/>
-      <c r="C6" s="190" t="s">
+      <c r="A6" s="177"/>
+      <c r="B6" s="206"/>
+      <c r="C6" s="202" t="s">
         <v>507</v>
       </c>
-      <c r="D6" s="190" t="s">
+      <c r="D6" s="202" t="s">
         <v>511</v>
       </c>
       <c r="E6" s="11"/>
@@ -18694,17 +18699,17 @@
       <c r="H6" s="12" t="s">
         <v>961</v>
       </c>
-      <c r="I6" s="210">
+      <c r="I6" s="155">
         <v>44043</v>
       </c>
       <c r="J6" s="10"/>
       <c r="K6" s="10"/>
     </row>
     <row r="7" spans="1:17">
-      <c r="A7" s="165"/>
-      <c r="B7" s="200"/>
-      <c r="C7" s="191"/>
-      <c r="D7" s="191"/>
+      <c r="A7" s="177"/>
+      <c r="B7" s="206"/>
+      <c r="C7" s="203"/>
+      <c r="D7" s="203"/>
       <c r="E7" s="11"/>
       <c r="F7" s="9" t="s">
         <v>313</v>
@@ -18715,17 +18720,17 @@
       <c r="H7" s="12">
         <v>1</v>
       </c>
-      <c r="I7" s="210">
+      <c r="I7" s="155">
         <v>44043</v>
       </c>
       <c r="J7" s="10"/>
       <c r="K7" s="10"/>
     </row>
     <row r="8" spans="1:17">
-      <c r="A8" s="165"/>
-      <c r="B8" s="200"/>
-      <c r="C8" s="191"/>
-      <c r="D8" s="191"/>
+      <c r="A8" s="177"/>
+      <c r="B8" s="206"/>
+      <c r="C8" s="203"/>
+      <c r="D8" s="203"/>
       <c r="E8" s="11"/>
       <c r="F8" s="9" t="s">
         <v>314</v>
@@ -18736,17 +18741,17 @@
       <c r="H8" s="12">
         <v>1</v>
       </c>
-      <c r="I8" s="210">
+      <c r="I8" s="155">
         <v>44043</v>
       </c>
       <c r="J8" s="10"/>
       <c r="K8" s="10"/>
     </row>
     <row r="9" spans="1:17">
-      <c r="A9" s="165"/>
-      <c r="B9" s="200"/>
-      <c r="C9" s="191"/>
-      <c r="D9" s="191"/>
+      <c r="A9" s="177"/>
+      <c r="B9" s="206"/>
+      <c r="C9" s="203"/>
+      <c r="D9" s="203"/>
       <c r="E9" s="8"/>
       <c r="F9" s="9" t="s">
         <v>345</v>
@@ -18757,17 +18762,17 @@
       <c r="H9" s="10">
         <v>1</v>
       </c>
-      <c r="I9" s="210">
+      <c r="I9" s="155">
         <v>44043</v>
       </c>
       <c r="J9" s="10"/>
       <c r="K9" s="10"/>
     </row>
     <row r="10" spans="1:17">
-      <c r="A10" s="165"/>
-      <c r="B10" s="200"/>
-      <c r="C10" s="191"/>
-      <c r="D10" s="191"/>
+      <c r="A10" s="177"/>
+      <c r="B10" s="206"/>
+      <c r="C10" s="203"/>
+      <c r="D10" s="203"/>
       <c r="E10" s="8"/>
       <c r="F10" s="9" t="s">
         <v>346</v>
@@ -18778,17 +18783,17 @@
       <c r="H10" s="10">
         <v>1</v>
       </c>
-      <c r="I10" s="210">
+      <c r="I10" s="155">
         <v>44043</v>
       </c>
       <c r="J10" s="10"/>
       <c r="K10" s="10"/>
     </row>
     <row r="11" spans="1:17">
-      <c r="A11" s="165"/>
-      <c r="B11" s="200"/>
-      <c r="C11" s="191"/>
-      <c r="D11" s="191"/>
+      <c r="A11" s="177"/>
+      <c r="B11" s="206"/>
+      <c r="C11" s="203"/>
+      <c r="D11" s="203"/>
       <c r="E11" s="8"/>
       <c r="F11" s="9" t="s">
         <v>315</v>
@@ -18799,17 +18804,17 @@
       <c r="H11" s="10">
         <v>1</v>
       </c>
-      <c r="I11" s="210">
+      <c r="I11" s="155">
         <v>44043</v>
       </c>
       <c r="J11" s="10"/>
       <c r="K11" s="10"/>
     </row>
     <row r="12" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A12" s="165"/>
-      <c r="B12" s="200"/>
-      <c r="C12" s="191"/>
-      <c r="D12" s="191"/>
+      <c r="A12" s="177"/>
+      <c r="B12" s="206"/>
+      <c r="C12" s="203"/>
+      <c r="D12" s="203"/>
       <c r="E12" s="8"/>
       <c r="F12" s="9" t="s">
         <v>347</v>
@@ -18820,17 +18825,17 @@
       <c r="H12" s="10">
         <v>1</v>
       </c>
-      <c r="I12" s="210">
+      <c r="I12" s="155">
         <v>44043</v>
       </c>
       <c r="J12" s="10"/>
       <c r="K12" s="10"/>
     </row>
     <row r="13" spans="1:17" ht="30">
-      <c r="A13" s="165"/>
-      <c r="B13" s="200"/>
-      <c r="C13" s="191"/>
-      <c r="D13" s="191"/>
+      <c r="A13" s="177"/>
+      <c r="B13" s="206"/>
+      <c r="C13" s="203"/>
+      <c r="D13" s="203"/>
       <c r="E13" s="11"/>
       <c r="F13" s="9" t="s">
         <v>316</v>
@@ -18841,7 +18846,7 @@
       <c r="H13" s="12">
         <v>3</v>
       </c>
-      <c r="I13" s="210"/>
+      <c r="I13" s="155"/>
       <c r="J13" s="10" t="s">
         <v>563</v>
       </c>
@@ -18851,10 +18856,10 @@
       </c>
     </row>
     <row r="14" spans="1:17">
-      <c r="A14" s="165"/>
-      <c r="B14" s="200"/>
-      <c r="C14" s="191"/>
-      <c r="D14" s="192"/>
+      <c r="A14" s="177"/>
+      <c r="B14" s="206"/>
+      <c r="C14" s="203"/>
+      <c r="D14" s="204"/>
       <c r="E14" s="11"/>
       <c r="F14" s="9" t="s">
         <v>318</v>
@@ -18865,16 +18870,16 @@
       <c r="H14" s="12" t="s">
         <v>963</v>
       </c>
-      <c r="I14" s="210" t="s">
+      <c r="I14" s="155" t="s">
         <v>1298</v>
       </c>
       <c r="J14" s="10"/>
       <c r="K14" s="10"/>
     </row>
     <row r="15" spans="1:17" ht="30">
-      <c r="A15" s="165"/>
-      <c r="B15" s="200"/>
-      <c r="C15" s="191"/>
+      <c r="A15" s="177"/>
+      <c r="B15" s="206"/>
+      <c r="C15" s="203"/>
       <c r="D15" s="22" t="s">
         <v>512</v>
       </c>
@@ -18888,15 +18893,15 @@
       <c r="H15" s="12">
         <v>1</v>
       </c>
-      <c r="I15" s="210">
+      <c r="I15" s="155">
         <v>44043</v>
       </c>
       <c r="J15" s="10"/>
       <c r="K15" s="10"/>
-      <c r="M15" s="195" t="s">
+      <c r="M15" s="210" t="s">
         <v>851</v>
       </c>
-      <c r="N15" s="196"/>
+      <c r="N15" s="211"/>
       <c r="O15" s="114" t="s">
         <v>1258</v>
       </c>
@@ -18906,12 +18911,12 @@
       </c>
     </row>
     <row r="16" spans="1:17" ht="30">
-      <c r="A16" s="165"/>
-      <c r="B16" s="200"/>
-      <c r="C16" s="190" t="s">
+      <c r="A16" s="177"/>
+      <c r="B16" s="206"/>
+      <c r="C16" s="202" t="s">
         <v>509</v>
       </c>
-      <c r="D16" s="190" t="s">
+      <c r="D16" s="202" t="s">
         <v>513</v>
       </c>
       <c r="E16" s="11"/>
@@ -18924,7 +18929,7 @@
       <c r="H16" s="12">
         <v>1</v>
       </c>
-      <c r="I16" s="210">
+      <c r="I16" s="155">
         <v>44043</v>
       </c>
       <c r="J16" s="10"/>
@@ -18946,10 +18951,10 @@
       </c>
     </row>
     <row r="17" spans="1:17">
-      <c r="A17" s="165"/>
-      <c r="B17" s="200"/>
-      <c r="C17" s="191"/>
-      <c r="D17" s="191"/>
+      <c r="A17" s="177"/>
+      <c r="B17" s="206"/>
+      <c r="C17" s="203"/>
+      <c r="D17" s="203"/>
       <c r="E17" s="19"/>
       <c r="F17" s="9" t="s">
         <v>364</v>
@@ -18960,7 +18965,7 @@
       <c r="H17" s="12">
         <v>1</v>
       </c>
-      <c r="I17" s="210">
+      <c r="I17" s="155">
         <v>44043</v>
       </c>
       <c r="J17" s="10"/>
@@ -18979,10 +18984,10 @@
       </c>
     </row>
     <row r="18" spans="1:17">
-      <c r="A18" s="165"/>
-      <c r="B18" s="200"/>
-      <c r="C18" s="191"/>
-      <c r="D18" s="191"/>
+      <c r="A18" s="177"/>
+      <c r="B18" s="206"/>
+      <c r="C18" s="203"/>
+      <c r="D18" s="203"/>
       <c r="E18" s="19"/>
       <c r="F18" s="48" t="s">
         <v>559</v>
@@ -18993,7 +18998,7 @@
       <c r="H18" s="10">
         <v>1</v>
       </c>
-      <c r="I18" s="210">
+      <c r="I18" s="155">
         <v>44043</v>
       </c>
       <c r="J18" s="10" t="s">
@@ -19014,10 +19019,10 @@
       </c>
     </row>
     <row r="19" spans="1:17">
-      <c r="A19" s="165"/>
-      <c r="B19" s="200"/>
-      <c r="C19" s="191"/>
-      <c r="D19" s="191"/>
+      <c r="A19" s="177"/>
+      <c r="B19" s="206"/>
+      <c r="C19" s="203"/>
+      <c r="D19" s="203"/>
       <c r="E19" s="8"/>
       <c r="F19" s="9" t="s">
         <v>332</v>
@@ -19028,7 +19033,7 @@
       <c r="H19" s="10">
         <v>1</v>
       </c>
-      <c r="I19" s="210">
+      <c r="I19" s="155">
         <v>44043</v>
       </c>
       <c r="J19" s="10"/>
@@ -19048,10 +19053,10 @@
       <c r="Q19" s="91"/>
     </row>
     <row r="20" spans="1:17">
-      <c r="A20" s="165"/>
-      <c r="B20" s="200"/>
-      <c r="C20" s="191"/>
-      <c r="D20" s="191"/>
+      <c r="A20" s="177"/>
+      <c r="B20" s="206"/>
+      <c r="C20" s="203"/>
+      <c r="D20" s="203"/>
       <c r="E20" s="8"/>
       <c r="F20" s="9" t="s">
         <v>333</v>
@@ -19062,7 +19067,7 @@
       <c r="H20" s="10">
         <v>1</v>
       </c>
-      <c r="I20" s="210">
+      <c r="I20" s="155">
         <v>44043</v>
       </c>
       <c r="J20" s="10"/>
@@ -19082,10 +19087,10 @@
       <c r="Q20" s="91"/>
     </row>
     <row r="21" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A21" s="165"/>
-      <c r="B21" s="200"/>
-      <c r="C21" s="191"/>
-      <c r="D21" s="191"/>
+      <c r="A21" s="177"/>
+      <c r="B21" s="206"/>
+      <c r="C21" s="203"/>
+      <c r="D21" s="203"/>
       <c r="E21" s="14"/>
       <c r="F21" s="9" t="s">
         <v>334</v>
@@ -19096,7 +19101,7 @@
       <c r="H21" s="16">
         <v>3</v>
       </c>
-      <c r="I21" s="210"/>
+      <c r="I21" s="155"/>
       <c r="J21" s="10" t="s">
         <v>563</v>
       </c>
@@ -19118,10 +19123,10 @@
       </c>
     </row>
     <row r="22" spans="1:17">
-      <c r="A22" s="165"/>
-      <c r="B22" s="200"/>
-      <c r="C22" s="191"/>
-      <c r="D22" s="191"/>
+      <c r="A22" s="177"/>
+      <c r="B22" s="206"/>
+      <c r="C22" s="203"/>
+      <c r="D22" s="203"/>
       <c r="E22" s="14"/>
       <c r="F22" s="9" t="s">
         <v>335</v>
@@ -19132,7 +19137,7 @@
       <c r="H22" s="16">
         <v>1</v>
       </c>
-      <c r="I22" s="210">
+      <c r="I22" s="155">
         <v>44043</v>
       </c>
       <c r="J22" s="10"/>
@@ -19154,10 +19159,10 @@
       </c>
     </row>
     <row r="23" spans="1:17">
-      <c r="A23" s="165"/>
-      <c r="B23" s="200"/>
-      <c r="C23" s="191"/>
-      <c r="D23" s="191"/>
+      <c r="A23" s="177"/>
+      <c r="B23" s="206"/>
+      <c r="C23" s="203"/>
+      <c r="D23" s="203"/>
       <c r="E23" s="14"/>
       <c r="F23" s="9" t="s">
         <v>336</v>
@@ -19168,7 +19173,7 @@
       <c r="H23" s="16">
         <v>2</v>
       </c>
-      <c r="I23" s="210">
+      <c r="I23" s="155">
         <v>44074</v>
       </c>
       <c r="J23" s="10"/>
@@ -19182,7 +19187,7 @@
       <c r="O23" s="99" t="s">
         <v>81</v>
       </c>
-      <c r="P23" s="214" t="s">
+      <c r="P23" s="159" t="s">
         <v>962</v>
       </c>
       <c r="Q23" s="154" t="s">
@@ -19190,10 +19195,10 @@
       </c>
     </row>
     <row r="24" spans="1:17">
-      <c r="A24" s="165"/>
-      <c r="B24" s="200"/>
-      <c r="C24" s="191"/>
-      <c r="D24" s="191"/>
+      <c r="A24" s="177"/>
+      <c r="B24" s="206"/>
+      <c r="C24" s="203"/>
+      <c r="D24" s="203"/>
       <c r="E24" s="8"/>
       <c r="F24" s="9" t="s">
         <v>1281</v>
@@ -19204,7 +19209,7 @@
       <c r="H24" s="10">
         <v>2</v>
       </c>
-      <c r="I24" s="210">
+      <c r="I24" s="155">
         <v>44074</v>
       </c>
       <c r="J24" s="10"/>
@@ -19224,10 +19229,10 @@
       <c r="Q24" s="91"/>
     </row>
     <row r="25" spans="1:17">
-      <c r="A25" s="165"/>
-      <c r="B25" s="200"/>
-      <c r="C25" s="191"/>
-      <c r="D25" s="191"/>
+      <c r="A25" s="177"/>
+      <c r="B25" s="206"/>
+      <c r="C25" s="203"/>
+      <c r="D25" s="203"/>
       <c r="E25" s="8"/>
       <c r="F25" s="9" t="s">
         <v>373</v>
@@ -19238,7 +19243,7 @@
       <c r="H25" s="10">
         <v>3</v>
       </c>
-      <c r="I25" s="210"/>
+      <c r="I25" s="155"/>
       <c r="J25" s="10" t="s">
         <v>563</v>
       </c>
@@ -19258,10 +19263,10 @@
       <c r="Q25" s="91"/>
     </row>
     <row r="26" spans="1:17">
-      <c r="A26" s="165"/>
-      <c r="B26" s="200"/>
-      <c r="C26" s="191"/>
-      <c r="D26" s="191"/>
+      <c r="A26" s="177"/>
+      <c r="B26" s="206"/>
+      <c r="C26" s="203"/>
+      <c r="D26" s="203"/>
       <c r="E26" s="8"/>
       <c r="F26" s="9" t="s">
         <v>338</v>
@@ -19272,7 +19277,7 @@
       <c r="H26" s="10" t="s">
         <v>963</v>
       </c>
-      <c r="I26" s="210"/>
+      <c r="I26" s="155"/>
       <c r="J26" s="10"/>
       <c r="K26" s="10"/>
       <c r="M26" s="99" t="s">
@@ -19290,10 +19295,10 @@
       <c r="Q26" s="91"/>
     </row>
     <row r="27" spans="1:17">
-      <c r="A27" s="165"/>
-      <c r="B27" s="200"/>
-      <c r="C27" s="191"/>
-      <c r="D27" s="191"/>
+      <c r="A27" s="177"/>
+      <c r="B27" s="206"/>
+      <c r="C27" s="203"/>
+      <c r="D27" s="203"/>
       <c r="E27" s="8"/>
       <c r="F27" s="9" t="s">
         <v>339</v>
@@ -19304,7 +19309,7 @@
       <c r="H27" s="119" t="s">
         <v>1297</v>
       </c>
-      <c r="I27" s="210" t="s">
+      <c r="I27" s="155" t="s">
         <v>1332</v>
       </c>
       <c r="J27" s="10"/>
@@ -19324,10 +19329,10 @@
       <c r="Q27" s="91"/>
     </row>
     <row r="28" spans="1:17">
-      <c r="A28" s="165"/>
-      <c r="B28" s="200"/>
-      <c r="C28" s="191"/>
-      <c r="D28" s="191"/>
+      <c r="A28" s="177"/>
+      <c r="B28" s="206"/>
+      <c r="C28" s="203"/>
+      <c r="D28" s="203"/>
       <c r="E28" s="8"/>
       <c r="F28" s="121" t="s">
         <v>965</v>
@@ -19338,7 +19343,7 @@
       <c r="H28" s="10">
         <v>1</v>
       </c>
-      <c r="I28" s="210">
+      <c r="I28" s="155">
         <v>44043</v>
       </c>
       <c r="J28" s="10"/>
@@ -19358,10 +19363,10 @@
       <c r="Q28" s="91"/>
     </row>
     <row r="29" spans="1:17">
-      <c r="A29" s="165"/>
-      <c r="B29" s="200"/>
-      <c r="C29" s="191"/>
-      <c r="D29" s="191"/>
+      <c r="A29" s="177"/>
+      <c r="B29" s="206"/>
+      <c r="C29" s="203"/>
+      <c r="D29" s="203"/>
       <c r="E29" s="8"/>
       <c r="F29" s="9" t="s">
         <v>955</v>
@@ -19372,7 +19377,7 @@
       <c r="H29" s="16" t="s">
         <v>963</v>
       </c>
-      <c r="I29" s="210" t="s">
+      <c r="I29" s="155" t="s">
         <v>1332</v>
       </c>
       <c r="J29" s="10"/>
@@ -19381,10 +19386,10 @@
       </c>
     </row>
     <row r="30" spans="1:17">
-      <c r="A30" s="165"/>
-      <c r="B30" s="200"/>
-      <c r="C30" s="191"/>
-      <c r="D30" s="192"/>
+      <c r="A30" s="177"/>
+      <c r="B30" s="206"/>
+      <c r="C30" s="203"/>
+      <c r="D30" s="204"/>
       <c r="E30" s="8"/>
       <c r="F30" s="49" t="s">
         <v>323</v>
@@ -19395,11 +19400,11 @@
       <c r="H30" s="113">
         <v>3</v>
       </c>
-      <c r="I30" s="210" t="s">
+      <c r="I30" s="155" t="s">
         <v>1332</v>
       </c>
       <c r="J30" s="10"/>
-      <c r="K30" s="193" t="s">
+      <c r="K30" s="208" t="s">
         <v>959</v>
       </c>
       <c r="M30" s="101" t="s">
@@ -19416,10 +19421,10 @@
       </c>
     </row>
     <row r="31" spans="1:17">
-      <c r="A31" s="165"/>
-      <c r="B31" s="200"/>
-      <c r="C31" s="191"/>
-      <c r="D31" s="190" t="s">
+      <c r="A31" s="177"/>
+      <c r="B31" s="206"/>
+      <c r="C31" s="203"/>
+      <c r="D31" s="202" t="s">
         <v>518</v>
       </c>
       <c r="E31" s="8"/>
@@ -19432,17 +19437,17 @@
       <c r="H31" s="16">
         <v>1</v>
       </c>
-      <c r="I31" s="210">
+      <c r="I31" s="155">
         <v>44043</v>
       </c>
       <c r="J31" s="10"/>
-      <c r="K31" s="197"/>
+      <c r="K31" s="212"/>
     </row>
     <row r="32" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A32" s="165"/>
-      <c r="B32" s="200"/>
-      <c r="C32" s="191"/>
-      <c r="D32" s="191"/>
+      <c r="A32" s="177"/>
+      <c r="B32" s="206"/>
+      <c r="C32" s="203"/>
+      <c r="D32" s="203"/>
       <c r="E32" s="8"/>
       <c r="F32" s="9" t="s">
         <v>325</v>
@@ -19453,20 +19458,20 @@
       <c r="H32" s="16">
         <v>1</v>
       </c>
-      <c r="I32" s="210">
+      <c r="I32" s="155">
         <v>44043</v>
       </c>
       <c r="J32" s="10"/>
-      <c r="K32" s="197"/>
+      <c r="K32" s="212"/>
       <c r="M32" s="151" t="s">
         <v>1277</v>
       </c>
     </row>
     <row r="33" spans="1:15" ht="16.5" customHeight="1">
-      <c r="A33" s="165"/>
-      <c r="B33" s="200"/>
-      <c r="C33" s="191"/>
-      <c r="D33" s="191"/>
+      <c r="A33" s="177"/>
+      <c r="B33" s="206"/>
+      <c r="C33" s="203"/>
+      <c r="D33" s="203"/>
       <c r="E33" s="8"/>
       <c r="F33" s="9" t="s">
         <v>957</v>
@@ -19477,13 +19482,13 @@
       <c r="H33" s="16">
         <v>2</v>
       </c>
-      <c r="I33" s="210">
+      <c r="I33" s="155">
         <v>44043</v>
       </c>
       <c r="J33" s="10" t="s">
         <v>954</v>
       </c>
-      <c r="K33" s="198"/>
+      <c r="K33" s="213"/>
       <c r="M33" s="152" t="s">
         <v>1278</v>
       </c>
@@ -19495,10 +19500,10 @@
       </c>
     </row>
     <row r="34" spans="1:15" ht="16.5" customHeight="1">
-      <c r="A34" s="165"/>
-      <c r="B34" s="200"/>
-      <c r="C34" s="191"/>
-      <c r="D34" s="191"/>
+      <c r="A34" s="177"/>
+      <c r="B34" s="206"/>
+      <c r="C34" s="203"/>
+      <c r="D34" s="203"/>
       <c r="E34" s="8"/>
       <c r="F34" s="9" t="s">
         <v>1275</v>
@@ -19509,7 +19514,7 @@
       <c r="H34" s="118">
         <v>2</v>
       </c>
-      <c r="I34" s="210">
+      <c r="I34" s="155">
         <v>44074</v>
       </c>
       <c r="J34" s="10"/>
@@ -19518,10 +19523,10 @@
       </c>
     </row>
     <row r="35" spans="1:15">
-      <c r="A35" s="165"/>
-      <c r="B35" s="200"/>
-      <c r="C35" s="192"/>
-      <c r="D35" s="192"/>
+      <c r="A35" s="177"/>
+      <c r="B35" s="206"/>
+      <c r="C35" s="204"/>
+      <c r="D35" s="204"/>
       <c r="E35" s="8"/>
       <c r="F35" s="49" t="s">
         <v>322</v>
@@ -19532,19 +19537,19 @@
       <c r="H35" s="50">
         <v>3</v>
       </c>
-      <c r="I35" s="210" t="s">
+      <c r="I35" s="155" t="s">
         <v>1332</v>
       </c>
       <c r="J35" s="10"/>
       <c r="K35" s="10"/>
     </row>
     <row r="36" spans="1:15">
-      <c r="A36" s="165"/>
-      <c r="B36" s="200"/>
-      <c r="C36" s="190" t="s">
+      <c r="A36" s="177"/>
+      <c r="B36" s="206"/>
+      <c r="C36" s="202" t="s">
         <v>340</v>
       </c>
-      <c r="D36" s="190" t="s">
+      <c r="D36" s="202" t="s">
         <v>517</v>
       </c>
       <c r="E36" s="8"/>
@@ -19557,17 +19562,17 @@
       <c r="H36" s="16">
         <v>1</v>
       </c>
-      <c r="I36" s="210">
+      <c r="I36" s="155">
         <v>44043</v>
       </c>
       <c r="J36" s="10"/>
       <c r="K36" s="10"/>
     </row>
     <row r="37" spans="1:15">
-      <c r="A37" s="165"/>
-      <c r="B37" s="201"/>
-      <c r="C37" s="192"/>
-      <c r="D37" s="192"/>
+      <c r="A37" s="177"/>
+      <c r="B37" s="207"/>
+      <c r="C37" s="204"/>
+      <c r="D37" s="204"/>
       <c r="E37" s="8"/>
       <c r="F37" s="9" t="s">
         <v>331</v>
@@ -19578,12 +19583,12 @@
       <c r="H37" s="120" t="s">
         <v>963</v>
       </c>
-      <c r="I37" s="210"/>
+      <c r="I37" s="155"/>
       <c r="J37" s="10"/>
       <c r="K37" s="10"/>
     </row>
     <row r="38" spans="1:15">
-      <c r="A38" s="165"/>
+      <c r="A38" s="177"/>
       <c r="B38" s="29" t="s">
         <v>328</v>
       </c>
@@ -19603,19 +19608,19 @@
       <c r="H38" s="16" t="s">
         <v>330</v>
       </c>
-      <c r="I38" s="210"/>
+      <c r="I38" s="155"/>
       <c r="J38" s="10"/>
       <c r="K38" s="10"/>
     </row>
     <row r="39" spans="1:15" ht="16.5" customHeight="1">
-      <c r="A39" s="165"/>
-      <c r="B39" s="199" t="s">
+      <c r="A39" s="177"/>
+      <c r="B39" s="205" t="s">
         <v>505</v>
       </c>
-      <c r="C39" s="190" t="s">
+      <c r="C39" s="202" t="s">
         <v>510</v>
       </c>
-      <c r="D39" s="190" t="s">
+      <c r="D39" s="202" t="s">
         <v>516</v>
       </c>
       <c r="E39" s="8" t="s">
@@ -19630,17 +19635,17 @@
       <c r="H39" s="10">
         <v>2</v>
       </c>
-      <c r="I39" s="210" t="s">
+      <c r="I39" s="155" t="s">
         <v>1331</v>
       </c>
       <c r="J39" s="10"/>
       <c r="K39" s="10"/>
     </row>
     <row r="40" spans="1:15" ht="16.5" customHeight="1">
-      <c r="A40" s="165"/>
-      <c r="B40" s="200"/>
-      <c r="C40" s="165"/>
-      <c r="D40" s="165"/>
+      <c r="A40" s="177"/>
+      <c r="B40" s="206"/>
+      <c r="C40" s="177"/>
+      <c r="D40" s="177"/>
       <c r="E40" s="17"/>
       <c r="F40" s="9" t="s">
         <v>304</v>
@@ -19651,17 +19656,17 @@
       <c r="H40" s="16">
         <v>1</v>
       </c>
-      <c r="I40" s="210">
+      <c r="I40" s="155">
         <v>44043</v>
       </c>
       <c r="J40" s="10"/>
       <c r="K40" s="10"/>
     </row>
     <row r="41" spans="1:15" ht="16.5" customHeight="1">
-      <c r="A41" s="165"/>
-      <c r="B41" s="200"/>
-      <c r="C41" s="165"/>
-      <c r="D41" s="165"/>
+      <c r="A41" s="177"/>
+      <c r="B41" s="206"/>
+      <c r="C41" s="177"/>
+      <c r="D41" s="177"/>
       <c r="E41" s="17"/>
       <c r="F41" s="9" t="s">
         <v>305</v>
@@ -19672,17 +19677,17 @@
       <c r="H41" s="16">
         <v>1</v>
       </c>
-      <c r="I41" s="210">
+      <c r="I41" s="155">
         <v>44043</v>
       </c>
       <c r="J41" s="10"/>
       <c r="K41" s="10"/>
     </row>
     <row r="42" spans="1:15">
-      <c r="A42" s="165"/>
-      <c r="B42" s="200"/>
-      <c r="C42" s="165"/>
-      <c r="D42" s="166"/>
+      <c r="A42" s="177"/>
+      <c r="B42" s="206"/>
+      <c r="C42" s="177"/>
+      <c r="D42" s="178"/>
       <c r="E42" s="17"/>
       <c r="F42" s="9" t="s">
         <v>305</v>
@@ -19693,17 +19698,17 @@
       <c r="H42" s="16">
         <v>2</v>
       </c>
-      <c r="I42" s="210">
+      <c r="I42" s="155">
         <v>44074</v>
       </c>
       <c r="J42" s="10"/>
       <c r="K42" s="10"/>
     </row>
     <row r="43" spans="1:15" ht="16.5" customHeight="1">
-      <c r="A43" s="165"/>
-      <c r="B43" s="200"/>
-      <c r="C43" s="165"/>
-      <c r="D43" s="190" t="s">
+      <c r="A43" s="177"/>
+      <c r="B43" s="206"/>
+      <c r="C43" s="177"/>
+      <c r="D43" s="202" t="s">
         <v>515</v>
       </c>
       <c r="E43" s="8"/>
@@ -19716,19 +19721,19 @@
       <c r="H43" s="10" t="s">
         <v>961</v>
       </c>
-      <c r="I43" s="210">
+      <c r="I43" s="155">
         <v>44043</v>
       </c>
       <c r="J43" s="10"/>
-      <c r="K43" s="193" t="s">
+      <c r="K43" s="208" t="s">
         <v>1164</v>
       </c>
     </row>
     <row r="44" spans="1:15">
-      <c r="A44" s="165"/>
-      <c r="B44" s="200"/>
-      <c r="C44" s="165"/>
-      <c r="D44" s="166"/>
+      <c r="A44" s="177"/>
+      <c r="B44" s="206"/>
+      <c r="C44" s="177"/>
+      <c r="D44" s="178"/>
       <c r="E44" s="8"/>
       <c r="F44" s="9" t="s">
         <v>289</v>
@@ -19739,17 +19744,17 @@
       <c r="H44" s="10" t="s">
         <v>961</v>
       </c>
-      <c r="I44" s="210">
+      <c r="I44" s="155">
         <v>44043</v>
       </c>
       <c r="J44" s="10"/>
-      <c r="K44" s="194"/>
+      <c r="K44" s="209"/>
     </row>
     <row r="45" spans="1:15">
-      <c r="A45" s="165"/>
-      <c r="B45" s="200"/>
-      <c r="C45" s="165"/>
-      <c r="D45" s="190" t="s">
+      <c r="A45" s="177"/>
+      <c r="B45" s="206"/>
+      <c r="C45" s="177"/>
+      <c r="D45" s="202" t="s">
         <v>514</v>
       </c>
       <c r="E45" s="8"/>
@@ -19762,15 +19767,15 @@
       <c r="H45" s="10" t="s">
         <v>963</v>
       </c>
-      <c r="I45" s="210"/>
+      <c r="I45" s="155"/>
       <c r="J45" s="10"/>
       <c r="K45" s="10"/>
     </row>
     <row r="46" spans="1:15">
-      <c r="A46" s="166"/>
-      <c r="B46" s="201"/>
-      <c r="C46" s="166"/>
-      <c r="D46" s="166"/>
+      <c r="A46" s="178"/>
+      <c r="B46" s="207"/>
+      <c r="C46" s="178"/>
+      <c r="D46" s="178"/>
       <c r="E46" s="8"/>
       <c r="F46" s="9" t="s">
         <v>301</v>
@@ -19781,38 +19786,38 @@
       <c r="H46" s="10" t="s">
         <v>963</v>
       </c>
-      <c r="I46" s="210"/>
+      <c r="I46" s="155"/>
       <c r="J46" s="10"/>
       <c r="K46" s="10"/>
     </row>
     <row r="48" spans="1:15">
-      <c r="H48" s="215" t="s">
+      <c r="H48" s="160" t="s">
         <v>1333</v>
       </c>
       <c r="I48">
         <f>COUNTA($I$2:$I$46)</f>
         <v>36</v>
       </c>
-      <c r="J48" s="216">
+      <c r="J48" s="161">
         <f>I48/$I$50</f>
         <v>0.8</v>
       </c>
     </row>
     <row r="49" spans="8:10">
-      <c r="H49" s="215" t="s">
+      <c r="H49" s="160" t="s">
         <v>1334</v>
       </c>
       <c r="I49">
         <f>COUNTBLANK($I$2:$I$46)</f>
         <v>9</v>
       </c>
-      <c r="J49" s="216">
+      <c r="J49" s="161">
         <f>I49/$I$50</f>
         <v>0.2</v>
       </c>
     </row>
     <row r="50" spans="8:10">
-      <c r="H50" s="215" t="s">
+      <c r="H50" s="160" t="s">
         <v>852</v>
       </c>
       <c r="I50">
@@ -19825,6 +19830,10 @@
     <sortCondition ref="P16:P28"/>
   </sortState>
   <mergeCells count="19">
+    <mergeCell ref="K43:K44"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="D16:D30"/>
+    <mergeCell ref="K30:K33"/>
     <mergeCell ref="C2:C5"/>
     <mergeCell ref="C6:C15"/>
     <mergeCell ref="A2:A46"/>
@@ -19840,10 +19849,6 @@
     <mergeCell ref="D36:D37"/>
     <mergeCell ref="D2:D4"/>
     <mergeCell ref="D6:D14"/>
-    <mergeCell ref="K43:K44"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="D16:D30"/>
-    <mergeCell ref="K30:K33"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19951,7 +19956,7 @@
       <c r="L34" t="s">
         <v>1348</v>
       </c>
-      <c r="P34" s="220" t="s">
+      <c r="P34" s="165" t="s">
         <v>1354</v>
       </c>
       <c r="Q34" t="s">
@@ -19993,7 +19998,7 @@
       <c r="A37" t="s">
         <v>1313</v>
       </c>
-      <c r="L37" s="218" t="s">
+      <c r="L37" s="163" t="s">
         <v>1345</v>
       </c>
     </row>
@@ -20133,11 +20138,11 @@
       <c r="B1" s="25" t="s">
         <v>327</v>
       </c>
-      <c r="E1" s="204" t="s">
+      <c r="E1" s="216" t="s">
         <v>724</v>
       </c>
-      <c r="F1" s="204"/>
-      <c r="G1" s="204"/>
+      <c r="F1" s="216"/>
+      <c r="G1" s="216"/>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="19" t="s">
@@ -20146,11 +20151,11 @@
       <c r="B2" s="19" t="s">
         <v>257</v>
       </c>
-      <c r="E2" s="205" t="s">
+      <c r="E2" s="217" t="s">
         <v>725</v>
       </c>
-      <c r="F2" s="205"/>
-      <c r="G2" s="205"/>
+      <c r="F2" s="217"/>
+      <c r="G2" s="217"/>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="19" t="s">
@@ -20167,10 +20172,10 @@
       <c r="B4" s="19" t="s">
         <v>259</v>
       </c>
-      <c r="E4" s="204" t="s">
+      <c r="E4" s="216" t="s">
         <v>722</v>
       </c>
-      <c r="F4" s="204"/>
+      <c r="F4" s="216"/>
       <c r="G4" s="25" t="s">
         <v>723</v>
       </c>
@@ -20182,16 +20187,16 @@
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="E5" s="203" t="s">
+      <c r="E5" s="215" t="s">
         <v>720</v>
       </c>
-      <c r="F5" s="203" t="s">
+      <c r="F5" s="215" t="s">
         <v>721</v>
       </c>
       <c r="G5" s="68" t="s">
         <v>747</v>
       </c>
-      <c r="H5" s="202" t="s">
+      <c r="H5" s="214" t="s">
         <v>748</v>
       </c>
       <c r="J5" t="s">
@@ -20202,12 +20207,12 @@
       <c r="A6" t="s">
         <v>261</v>
       </c>
-      <c r="E6" s="203"/>
-      <c r="F6" s="203"/>
+      <c r="E6" s="215"/>
+      <c r="F6" s="215"/>
       <c r="G6" s="68" t="s">
         <v>746</v>
       </c>
-      <c r="H6" s="203"/>
+      <c r="H6" s="215"/>
       <c r="J6" t="s">
         <v>729</v>
       </c>
@@ -20495,7 +20500,7 @@
       <c r="J2" s="115" t="s">
         <v>892</v>
       </c>
-      <c r="K2" s="206" t="s">
+      <c r="K2" s="218" t="s">
         <v>1194</v>
       </c>
     </row>
@@ -20528,7 +20533,7 @@
       <c r="J3" s="115" t="s">
         <v>892</v>
       </c>
-      <c r="K3" s="207"/>
+      <c r="K3" s="219"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="132">
@@ -20557,7 +20562,7 @@
       <c r="J4" s="115" t="s">
         <v>892</v>
       </c>
-      <c r="K4" s="207"/>
+      <c r="K4" s="219"/>
     </row>
     <row r="5" spans="1:11" ht="45">
       <c r="A5" s="132">
@@ -20586,7 +20591,7 @@
       <c r="J5" s="115" t="s">
         <v>892</v>
       </c>
-      <c r="K5" s="208"/>
+      <c r="K5" s="220"/>
     </row>
     <row r="6" spans="1:11" ht="60">
       <c r="A6" s="132">
@@ -20879,7 +20884,7 @@
       <c r="C18" s="129"/>
       <c r="D18" s="129"/>
       <c r="E18" s="129"/>
-      <c r="F18" s="209" t="s">
+      <c r="F18" s="221" t="s">
         <v>1239</v>
       </c>
       <c r="G18" s="8" t="s">
@@ -20892,7 +20897,7 @@
       <c r="J18" s="129"/>
     </row>
     <row r="19" spans="1:10">
-      <c r="F19" s="209"/>
+      <c r="F19" s="221"/>
       <c r="G19" s="149" t="s">
         <v>1235</v>
       </c>
@@ -20901,7 +20906,7 @@
       </c>
     </row>
     <row r="20" spans="1:10">
-      <c r="F20" s="209"/>
+      <c r="F20" s="221"/>
       <c r="G20" s="8" t="s">
         <v>1237</v>
       </c>
@@ -20910,7 +20915,7 @@
       </c>
     </row>
     <row r="21" spans="1:10">
-      <c r="F21" s="209"/>
+      <c r="F21" s="221"/>
       <c r="G21" s="8" t="s">
         <v>1238</v>
       </c>
@@ -22403,7 +22408,7 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="203" t="s">
+      <c r="A2" s="215" t="s">
         <v>379</v>
       </c>
       <c r="B2" s="57" t="s">
@@ -22417,7 +22422,7 @@
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="203"/>
+      <c r="A3" s="215"/>
       <c r="B3" s="20" t="s">
         <v>262</v>
       </c>
@@ -22429,7 +22434,7 @@
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="203"/>
+      <c r="A4" s="215"/>
       <c r="B4" s="20" t="s">
         <v>385</v>
       </c>
@@ -22441,7 +22446,7 @@
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="203"/>
+      <c r="A5" s="215"/>
       <c r="B5" s="57" t="s">
         <v>544</v>
       </c>
@@ -22453,7 +22458,7 @@
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="203"/>
+      <c r="A6" s="215"/>
       <c r="B6" s="20" t="s">
         <v>388</v>
       </c>
@@ -22465,7 +22470,7 @@
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="203"/>
+      <c r="A7" s="215"/>
       <c r="B7" s="20" t="s">
         <v>390</v>
       </c>
@@ -24199,7 +24204,7 @@
     </row>
     <row r="22" spans="7:24">
       <c r="K22" s="148"/>
-      <c r="V22" s="164" t="s">
+      <c r="V22" s="176" t="s">
         <v>832</v>
       </c>
       <c r="W22" s="9" t="s">
@@ -24222,7 +24227,7 @@
       </c>
       <c r="Q23" s="146"/>
       <c r="R23" s="146"/>
-      <c r="V23" s="165"/>
+      <c r="V23" s="177"/>
       <c r="W23" s="9" t="s">
         <v>815</v>
       </c>
@@ -24232,7 +24237,7 @@
     </row>
     <row r="24" spans="7:24">
       <c r="K24" s="148"/>
-      <c r="V24" s="165"/>
+      <c r="V24" s="177"/>
       <c r="W24" s="9" t="s">
         <v>816</v>
       </c>
@@ -24247,7 +24252,7 @@
       <c r="L25" s="5" t="s">
         <v>891</v>
       </c>
-      <c r="V25" s="165"/>
+      <c r="V25" s="177"/>
       <c r="W25" s="9" t="s">
         <v>817</v>
       </c>
@@ -24266,7 +24271,7 @@
       <c r="O26" t="s">
         <v>897</v>
       </c>
-      <c r="V26" s="165"/>
+      <c r="V26" s="177"/>
       <c r="W26" s="9" t="s">
         <v>824</v>
       </c>
@@ -24280,7 +24285,7 @@
       <c r="N27" t="s">
         <v>896</v>
       </c>
-      <c r="V27" s="165"/>
+      <c r="V27" s="177"/>
       <c r="W27" s="9" t="s">
         <v>825</v>
       </c>
@@ -24291,7 +24296,7 @@
       <c r="N28" t="s">
         <v>898</v>
       </c>
-      <c r="V28" s="165"/>
+      <c r="V28" s="177"/>
       <c r="W28" s="9" t="s">
         <v>826</v>
       </c>
@@ -24304,7 +24309,7 @@
       <c r="N29" t="s">
         <v>899</v>
       </c>
-      <c r="V29" s="166"/>
+      <c r="V29" s="178"/>
       <c r="W29" s="9" t="s">
         <v>827</v>
       </c>
@@ -24320,7 +24325,7 @@
       <c r="N30" t="s">
         <v>852</v>
       </c>
-      <c r="V30" s="161" t="s">
+      <c r="V30" s="173" t="s">
         <v>831</v>
       </c>
       <c r="W30" s="49" t="s">
@@ -24333,7 +24338,7 @@
       <c r="N31" t="s">
         <v>901</v>
       </c>
-      <c r="V31" s="162"/>
+      <c r="V31" s="174"/>
       <c r="W31" s="49" t="s">
         <v>822</v>
       </c>
@@ -24355,7 +24360,7 @@
       </c>
       <c r="Q32" s="146"/>
       <c r="R32" s="146"/>
-      <c r="V32" s="163"/>
+      <c r="V32" s="175"/>
       <c r="W32" s="49" t="s">
         <v>823</v>
       </c>
@@ -24495,7 +24500,7 @@
       <c r="R5" s="13" t="s">
         <v>352</v>
       </c>
-      <c r="S5" s="167" t="s">
+      <c r="S5" s="179" t="s">
         <v>809</v>
       </c>
     </row>
@@ -24512,7 +24517,7 @@
       <c r="R6" s="9" t="s">
         <v>602</v>
       </c>
-      <c r="S6" s="167"/>
+      <c r="S6" s="179"/>
     </row>
     <row r="7" spans="3:20">
       <c r="O7" s="81" t="s">
@@ -24527,7 +24532,7 @@
       <c r="R7" s="9" t="s">
         <v>603</v>
       </c>
-      <c r="S7" s="167"/>
+      <c r="S7" s="179"/>
     </row>
     <row r="8" spans="3:20">
       <c r="O8" s="81" t="s">
@@ -24542,7 +24547,7 @@
       <c r="R8" s="9" t="s">
         <v>350</v>
       </c>
-      <c r="S8" s="167"/>
+      <c r="S8" s="179"/>
     </row>
     <row r="9" spans="3:20">
       <c r="O9" s="81" t="s">
@@ -24557,7 +24562,7 @@
       <c r="R9" s="9" t="s">
         <v>349</v>
       </c>
-      <c r="S9" s="167"/>
+      <c r="S9" s="179"/>
     </row>
     <row r="10" spans="3:20">
       <c r="Q10" s="9" t="s">
@@ -24582,7 +24587,7 @@
       </c>
     </row>
     <row r="15" spans="3:20">
-      <c r="Q15" s="164" t="s">
+      <c r="Q15" s="176" t="s">
         <v>832</v>
       </c>
       <c r="R15" s="9" t="s">
@@ -24617,7 +24622,7 @@
       <c r="J16" s="10" t="s">
         <v>813</v>
       </c>
-      <c r="Q16" s="165"/>
+      <c r="Q16" s="177"/>
       <c r="R16" s="9" t="s">
         <v>815</v>
       </c>
@@ -24627,7 +24632,7 @@
     </row>
     <row r="17" spans="10:19">
       <c r="J17" s="81"/>
-      <c r="Q17" s="165"/>
+      <c r="Q17" s="177"/>
       <c r="R17" s="9" t="s">
         <v>816</v>
       </c>
@@ -24636,7 +24641,7 @@
       </c>
     </row>
     <row r="18" spans="10:19">
-      <c r="Q18" s="165"/>
+      <c r="Q18" s="177"/>
       <c r="R18" s="9" t="s">
         <v>817</v>
       </c>
@@ -24645,21 +24650,21 @@
       </c>
     </row>
     <row r="19" spans="10:19">
-      <c r="Q19" s="165"/>
+      <c r="Q19" s="177"/>
       <c r="R19" s="9" t="s">
         <v>824</v>
       </c>
       <c r="S19" s="92"/>
     </row>
     <row r="20" spans="10:19">
-      <c r="Q20" s="165"/>
+      <c r="Q20" s="177"/>
       <c r="R20" s="9" t="s">
         <v>825</v>
       </c>
       <c r="S20" s="92"/>
     </row>
     <row r="21" spans="10:19">
-      <c r="Q21" s="165"/>
+      <c r="Q21" s="177"/>
       <c r="R21" s="9" t="s">
         <v>826</v>
       </c>
@@ -24668,7 +24673,7 @@
       </c>
     </row>
     <row r="22" spans="10:19">
-      <c r="Q22" s="166"/>
+      <c r="Q22" s="178"/>
       <c r="R22" s="9" t="s">
         <v>827</v>
       </c>
@@ -24677,7 +24682,7 @@
       </c>
     </row>
     <row r="23" spans="10:19">
-      <c r="Q23" s="164" t="s">
+      <c r="Q23" s="176" t="s">
         <v>831</v>
       </c>
       <c r="R23" s="9" t="s">
@@ -24686,14 +24691,14 @@
       <c r="S23" s="92"/>
     </row>
     <row r="24" spans="10:19">
-      <c r="Q24" s="165"/>
+      <c r="Q24" s="177"/>
       <c r="R24" s="9" t="s">
         <v>822</v>
       </c>
       <c r="S24" s="92"/>
     </row>
     <row r="25" spans="10:19">
-      <c r="Q25" s="166"/>
+      <c r="Q25" s="178"/>
       <c r="R25" s="9" t="s">
         <v>823</v>
       </c>
@@ -24759,39 +24764,39 @@
       <c r="B1" t="s">
         <v>860</v>
       </c>
-      <c r="J1" s="168" t="s">
+      <c r="J1" s="180" t="s">
         <v>952</v>
       </c>
-      <c r="K1" s="169"/>
-      <c r="L1" s="169"/>
-      <c r="M1" s="169"/>
-      <c r="N1" s="169"/>
-      <c r="O1" s="169"/>
-      <c r="P1" s="169"/>
-      <c r="Q1" s="169"/>
+      <c r="K1" s="181"/>
+      <c r="L1" s="181"/>
+      <c r="M1" s="181"/>
+      <c r="N1" s="181"/>
+      <c r="O1" s="181"/>
+      <c r="P1" s="181"/>
+      <c r="Q1" s="181"/>
     </row>
     <row r="2" spans="1:17">
-      <c r="J2" s="169"/>
-      <c r="K2" s="169"/>
-      <c r="L2" s="169"/>
-      <c r="M2" s="169"/>
-      <c r="N2" s="169"/>
-      <c r="O2" s="169"/>
-      <c r="P2" s="169"/>
-      <c r="Q2" s="169"/>
+      <c r="J2" s="181"/>
+      <c r="K2" s="181"/>
+      <c r="L2" s="181"/>
+      <c r="M2" s="181"/>
+      <c r="N2" s="181"/>
+      <c r="O2" s="181"/>
+      <c r="P2" s="181"/>
+      <c r="Q2" s="181"/>
     </row>
     <row r="3" spans="1:17">
       <c r="A3" s="6" t="s">
         <v>861</v>
       </c>
-      <c r="J3" s="169"/>
-      <c r="K3" s="169"/>
-      <c r="L3" s="169"/>
-      <c r="M3" s="169"/>
-      <c r="N3" s="169"/>
-      <c r="O3" s="169"/>
-      <c r="P3" s="169"/>
-      <c r="Q3" s="169"/>
+      <c r="J3" s="181"/>
+      <c r="K3" s="181"/>
+      <c r="L3" s="181"/>
+      <c r="M3" s="181"/>
+      <c r="N3" s="181"/>
+      <c r="O3" s="181"/>
+      <c r="P3" s="181"/>
+      <c r="Q3" s="181"/>
     </row>
     <row r="4" spans="1:17">
       <c r="A4" t="s">
@@ -24803,24 +24808,24 @@
       <c r="D4" t="s">
         <v>863</v>
       </c>
-      <c r="J4" s="169"/>
-      <c r="K4" s="169"/>
-      <c r="L4" s="169"/>
-      <c r="M4" s="169"/>
-      <c r="N4" s="169"/>
-      <c r="O4" s="169"/>
-      <c r="P4" s="169"/>
-      <c r="Q4" s="169"/>
+      <c r="J4" s="181"/>
+      <c r="K4" s="181"/>
+      <c r="L4" s="181"/>
+      <c r="M4" s="181"/>
+      <c r="N4" s="181"/>
+      <c r="O4" s="181"/>
+      <c r="P4" s="181"/>
+      <c r="Q4" s="181"/>
     </row>
     <row r="5" spans="1:17">
-      <c r="J5" s="169"/>
-      <c r="K5" s="169"/>
-      <c r="L5" s="169"/>
-      <c r="M5" s="169"/>
-      <c r="N5" s="169"/>
-      <c r="O5" s="169"/>
-      <c r="P5" s="169"/>
-      <c r="Q5" s="169"/>
+      <c r="J5" s="181"/>
+      <c r="K5" s="181"/>
+      <c r="L5" s="181"/>
+      <c r="M5" s="181"/>
+      <c r="N5" s="181"/>
+      <c r="O5" s="181"/>
+      <c r="P5" s="181"/>
+      <c r="Q5" s="181"/>
     </row>
     <row r="6" spans="1:17" ht="15.75" thickBot="1">
       <c r="A6" t="s">
@@ -24829,38 +24834,38 @@
       <c r="E6" t="s">
         <v>918</v>
       </c>
-      <c r="J6" s="169"/>
-      <c r="K6" s="169"/>
-      <c r="L6" s="169"/>
-      <c r="M6" s="169"/>
-      <c r="N6" s="169"/>
-      <c r="O6" s="169"/>
-      <c r="P6" s="169"/>
-      <c r="Q6" s="169"/>
+      <c r="J6" s="181"/>
+      <c r="K6" s="181"/>
+      <c r="L6" s="181"/>
+      <c r="M6" s="181"/>
+      <c r="N6" s="181"/>
+      <c r="O6" s="181"/>
+      <c r="P6" s="181"/>
+      <c r="Q6" s="181"/>
     </row>
     <row r="7" spans="1:17" ht="15.75" thickBot="1">
       <c r="A7" s="105" t="s">
         <v>865</v>
       </c>
-      <c r="J7" s="169"/>
-      <c r="K7" s="169"/>
-      <c r="L7" s="169"/>
-      <c r="M7" s="169"/>
-      <c r="N7" s="169"/>
-      <c r="O7" s="169"/>
-      <c r="P7" s="169"/>
-      <c r="Q7" s="169"/>
+      <c r="J7" s="181"/>
+      <c r="K7" s="181"/>
+      <c r="L7" s="181"/>
+      <c r="M7" s="181"/>
+      <c r="N7" s="181"/>
+      <c r="O7" s="181"/>
+      <c r="P7" s="181"/>
+      <c r="Q7" s="181"/>
     </row>
     <row r="8" spans="1:17">
       <c r="A8" s="117"/>
-      <c r="J8" s="169"/>
-      <c r="K8" s="169"/>
-      <c r="L8" s="169"/>
-      <c r="M8" s="169"/>
-      <c r="N8" s="169"/>
-      <c r="O8" s="169"/>
-      <c r="P8" s="169"/>
-      <c r="Q8" s="169"/>
+      <c r="J8" s="181"/>
+      <c r="K8" s="181"/>
+      <c r="L8" s="181"/>
+      <c r="M8" s="181"/>
+      <c r="N8" s="181"/>
+      <c r="O8" s="181"/>
+      <c r="P8" s="181"/>
+      <c r="Q8" s="181"/>
     </row>
     <row r="9" spans="1:17">
       <c r="A9" t="s">
@@ -24869,14 +24874,14 @@
       <c r="B9" t="s">
         <v>924</v>
       </c>
-      <c r="J9" s="169"/>
-      <c r="K9" s="169"/>
-      <c r="L9" s="169"/>
-      <c r="M9" s="169"/>
-      <c r="N9" s="169"/>
-      <c r="O9" s="169"/>
-      <c r="P9" s="169"/>
-      <c r="Q9" s="169"/>
+      <c r="J9" s="181"/>
+      <c r="K9" s="181"/>
+      <c r="L9" s="181"/>
+      <c r="M9" s="181"/>
+      <c r="N9" s="181"/>
+      <c r="O9" s="181"/>
+      <c r="P9" s="181"/>
+      <c r="Q9" s="181"/>
     </row>
     <row r="10" spans="1:17">
       <c r="A10" t="s">
@@ -24897,14 +24902,14 @@
       <c r="H10" t="s">
         <v>950</v>
       </c>
-      <c r="J10" s="169"/>
-      <c r="K10" s="169"/>
-      <c r="L10" s="169"/>
-      <c r="M10" s="169"/>
-      <c r="N10" s="169"/>
-      <c r="O10" s="169"/>
-      <c r="P10" s="169"/>
-      <c r="Q10" s="169"/>
+      <c r="J10" s="181"/>
+      <c r="K10" s="181"/>
+      <c r="L10" s="181"/>
+      <c r="M10" s="181"/>
+      <c r="N10" s="181"/>
+      <c r="O10" s="181"/>
+      <c r="P10" s="181"/>
+      <c r="Q10" s="181"/>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" t="s">
@@ -24925,14 +24930,14 @@
       <c r="H11" t="s">
         <v>951</v>
       </c>
-      <c r="J11" s="169"/>
-      <c r="K11" s="169"/>
-      <c r="L11" s="169"/>
-      <c r="M11" s="169"/>
-      <c r="N11" s="169"/>
-      <c r="O11" s="169"/>
-      <c r="P11" s="169"/>
-      <c r="Q11" s="169"/>
+      <c r="J11" s="181"/>
+      <c r="K11" s="181"/>
+      <c r="L11" s="181"/>
+      <c r="M11" s="181"/>
+      <c r="N11" s="181"/>
+      <c r="O11" s="181"/>
+      <c r="P11" s="181"/>
+      <c r="Q11" s="181"/>
     </row>
     <row r="12" spans="1:17">
       <c r="B12" t="s">
@@ -24947,14 +24952,14 @@
       <c r="H12" t="s">
         <v>951</v>
       </c>
-      <c r="J12" s="169"/>
-      <c r="K12" s="169"/>
-      <c r="L12" s="169"/>
-      <c r="M12" s="169"/>
-      <c r="N12" s="169"/>
-      <c r="O12" s="169"/>
-      <c r="P12" s="169"/>
-      <c r="Q12" s="169"/>
+      <c r="J12" s="181"/>
+      <c r="K12" s="181"/>
+      <c r="L12" s="181"/>
+      <c r="M12" s="181"/>
+      <c r="N12" s="181"/>
+      <c r="O12" s="181"/>
+      <c r="P12" s="181"/>
+      <c r="Q12" s="181"/>
     </row>
     <row r="13" spans="1:17">
       <c r="F13" t="s">
@@ -24966,24 +24971,24 @@
       <c r="H13" t="s">
         <v>951</v>
       </c>
-      <c r="J13" s="169"/>
-      <c r="K13" s="169"/>
-      <c r="L13" s="169"/>
-      <c r="M13" s="169"/>
-      <c r="N13" s="169"/>
-      <c r="O13" s="169"/>
-      <c r="P13" s="169"/>
-      <c r="Q13" s="169"/>
+      <c r="J13" s="181"/>
+      <c r="K13" s="181"/>
+      <c r="L13" s="181"/>
+      <c r="M13" s="181"/>
+      <c r="N13" s="181"/>
+      <c r="O13" s="181"/>
+      <c r="P13" s="181"/>
+      <c r="Q13" s="181"/>
     </row>
     <row r="14" spans="1:17">
-      <c r="J14" s="169"/>
-      <c r="K14" s="169"/>
-      <c r="L14" s="169"/>
-      <c r="M14" s="169"/>
-      <c r="N14" s="169"/>
-      <c r="O14" s="169"/>
-      <c r="P14" s="169"/>
-      <c r="Q14" s="169"/>
+      <c r="J14" s="181"/>
+      <c r="K14" s="181"/>
+      <c r="L14" s="181"/>
+      <c r="M14" s="181"/>
+      <c r="N14" s="181"/>
+      <c r="O14" s="181"/>
+      <c r="P14" s="181"/>
+      <c r="Q14" s="181"/>
     </row>
     <row r="15" spans="1:17">
       <c r="A15" t="s">
@@ -24992,27 +24997,27 @@
       <c r="C15" t="s">
         <v>947</v>
       </c>
-      <c r="J15" s="169"/>
-      <c r="K15" s="169"/>
-      <c r="L15" s="169"/>
-      <c r="M15" s="169"/>
-      <c r="N15" s="169"/>
-      <c r="O15" s="169"/>
-      <c r="P15" s="169"/>
-      <c r="Q15" s="169"/>
+      <c r="J15" s="181"/>
+      <c r="K15" s="181"/>
+      <c r="L15" s="181"/>
+      <c r="M15" s="181"/>
+      <c r="N15" s="181"/>
+      <c r="O15" s="181"/>
+      <c r="P15" s="181"/>
+      <c r="Q15" s="181"/>
     </row>
     <row r="16" spans="1:17">
       <c r="A16" t="s">
         <v>937</v>
       </c>
-      <c r="J16" s="169"/>
-      <c r="K16" s="169"/>
-      <c r="L16" s="169"/>
-      <c r="M16" s="169"/>
-      <c r="N16" s="169"/>
-      <c r="O16" s="169"/>
-      <c r="P16" s="169"/>
-      <c r="Q16" s="169"/>
+      <c r="J16" s="181"/>
+      <c r="K16" s="181"/>
+      <c r="L16" s="181"/>
+      <c r="M16" s="181"/>
+      <c r="N16" s="181"/>
+      <c r="O16" s="181"/>
+      <c r="P16" s="181"/>
+      <c r="Q16" s="181"/>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="5" t="s">
@@ -25297,19 +25302,19 @@
       <c r="E7" s="31" t="s">
         <v>449</v>
       </c>
-      <c r="F7" s="170" t="s">
+      <c r="F7" s="182" t="s">
         <v>441</v>
       </c>
-      <c r="G7" s="170"/>
-      <c r="H7" s="170"/>
-      <c r="I7" s="170"/>
-      <c r="J7" s="170"/>
-      <c r="K7" s="170"/>
-      <c r="L7" s="170"/>
-      <c r="M7" s="170"/>
-      <c r="N7" s="170"/>
-      <c r="O7" s="170"/>
-      <c r="P7" s="170"/>
+      <c r="G7" s="182"/>
+      <c r="H7" s="182"/>
+      <c r="I7" s="182"/>
+      <c r="J7" s="182"/>
+      <c r="K7" s="182"/>
+      <c r="L7" s="182"/>
+      <c r="M7" s="182"/>
+      <c r="N7" s="182"/>
+      <c r="O7" s="182"/>
+      <c r="P7" s="182"/>
     </row>
     <row r="8" spans="1:17">
       <c r="B8" s="32" t="s">
@@ -25533,40 +25538,40 @@
       <c r="A24" s="35" t="s">
         <v>455</v>
       </c>
-      <c r="B24" s="171" t="s">
+      <c r="B24" s="183" t="s">
         <v>457</v>
       </c>
-      <c r="C24" s="171"/>
-      <c r="D24" s="171"/>
-      <c r="E24" s="171"/>
-      <c r="F24" s="171"/>
-      <c r="G24" s="171"/>
+      <c r="C24" s="183"/>
+      <c r="D24" s="183"/>
+      <c r="E24" s="183"/>
+      <c r="F24" s="183"/>
+      <c r="G24" s="183"/>
     </row>
     <row r="25" spans="1:7" ht="30">
       <c r="A25" s="35" t="s">
         <v>462</v>
       </c>
-      <c r="B25" s="172" t="s">
+      <c r="B25" s="184" t="s">
         <v>464</v>
       </c>
-      <c r="C25" s="172"/>
-      <c r="D25" s="172"/>
-      <c r="E25" s="172"/>
-      <c r="F25" s="172"/>
-      <c r="G25" s="172"/>
+      <c r="C25" s="184"/>
+      <c r="D25" s="184"/>
+      <c r="E25" s="184"/>
+      <c r="F25" s="184"/>
+      <c r="G25" s="184"/>
     </row>
     <row r="26" spans="1:7" ht="159" customHeight="1">
       <c r="A26" s="35" t="s">
         <v>459</v>
       </c>
-      <c r="B26" s="171" t="s">
+      <c r="B26" s="183" t="s">
         <v>460</v>
       </c>
-      <c r="C26" s="171"/>
-      <c r="D26" s="171"/>
-      <c r="E26" s="171"/>
-      <c r="F26" s="171"/>
-      <c r="G26" s="171"/>
+      <c r="C26" s="183"/>
+      <c r="D26" s="183"/>
+      <c r="E26" s="183"/>
+      <c r="F26" s="183"/>
+      <c r="G26" s="183"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -26081,29 +26086,29 @@
       <c r="B27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="C27" s="175" t="s">
+      <c r="C27" s="187" t="s">
         <v>622</v>
       </c>
-      <c r="D27" s="176"/>
+      <c r="D27" s="188"/>
       <c r="E27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="F27" s="175" t="s">
+      <c r="F27" s="187" t="s">
         <v>622</v>
       </c>
-      <c r="G27" s="176"/>
+      <c r="G27" s="188"/>
       <c r="H27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="I27" s="175" t="s">
+      <c r="I27" s="187" t="s">
         <v>622</v>
       </c>
-      <c r="J27" s="176"/>
-      <c r="L27" s="173" t="s">
+      <c r="J27" s="188"/>
+      <c r="L27" s="199" t="s">
         <v>694</v>
       </c>
-      <c r="M27" s="173"/>
-      <c r="N27" s="173"/>
+      <c r="M27" s="199"/>
+      <c r="N27" s="199"/>
     </row>
     <row r="28" spans="1:14" ht="32.25" thickBot="1">
       <c r="A28" s="81">
@@ -26112,29 +26117,29 @@
       <c r="B28" s="69" t="s">
         <v>623</v>
       </c>
-      <c r="C28" s="183" t="s">
+      <c r="C28" s="185" t="s">
         <v>624</v>
       </c>
-      <c r="D28" s="184"/>
+      <c r="D28" s="186"/>
       <c r="E28" s="70" t="s">
         <v>645</v>
       </c>
-      <c r="F28" s="177" t="s">
+      <c r="F28" s="189" t="s">
         <v>646</v>
       </c>
-      <c r="G28" s="178"/>
+      <c r="G28" s="190"/>
       <c r="H28" s="69" t="s">
         <v>667</v>
       </c>
-      <c r="I28" s="183" t="s">
+      <c r="I28" s="185" t="s">
         <v>668</v>
       </c>
-      <c r="J28" s="184"/>
-      <c r="L28" s="174" t="s">
+      <c r="J28" s="186"/>
+      <c r="L28" s="200" t="s">
         <v>695</v>
       </c>
-      <c r="M28" s="174"/>
-      <c r="N28" s="174"/>
+      <c r="M28" s="200"/>
+      <c r="N28" s="200"/>
     </row>
     <row r="29" spans="1:14" ht="31.5" thickBot="1">
       <c r="A29" s="81">
@@ -26143,29 +26148,29 @@
       <c r="B29" s="70" t="s">
         <v>625</v>
       </c>
-      <c r="C29" s="177" t="s">
+      <c r="C29" s="189" t="s">
         <v>626</v>
       </c>
-      <c r="D29" s="178"/>
+      <c r="D29" s="190"/>
       <c r="E29" s="69" t="s">
         <v>647</v>
       </c>
-      <c r="F29" s="183" t="s">
+      <c r="F29" s="185" t="s">
         <v>648</v>
       </c>
-      <c r="G29" s="184"/>
+      <c r="G29" s="186"/>
       <c r="H29" s="70" t="s">
         <v>669</v>
       </c>
-      <c r="I29" s="187" t="s">
+      <c r="I29" s="193" t="s">
         <v>670</v>
       </c>
-      <c r="J29" s="188"/>
-      <c r="L29" s="173" t="s">
+      <c r="J29" s="194"/>
+      <c r="L29" s="199" t="s">
         <v>696</v>
       </c>
-      <c r="M29" s="173"/>
-      <c r="N29" s="173"/>
+      <c r="M29" s="199"/>
+      <c r="N29" s="199"/>
     </row>
     <row r="30" spans="1:14" ht="15.75" thickBot="1">
       <c r="A30" s="81">
@@ -26174,29 +26179,29 @@
       <c r="B30" s="69" t="s">
         <v>627</v>
       </c>
-      <c r="C30" s="183" t="s">
+      <c r="C30" s="185" t="s">
         <v>628</v>
       </c>
-      <c r="D30" s="184"/>
+      <c r="D30" s="186"/>
       <c r="E30" s="70" t="s">
         <v>649</v>
       </c>
-      <c r="F30" s="177" t="s">
+      <c r="F30" s="189" t="s">
         <v>650</v>
       </c>
-      <c r="G30" s="178"/>
+      <c r="G30" s="190"/>
       <c r="H30" s="69" t="s">
         <v>671</v>
       </c>
-      <c r="I30" s="183" t="s">
+      <c r="I30" s="185" t="s">
         <v>672</v>
       </c>
-      <c r="J30" s="184"/>
-      <c r="L30" s="174" t="s">
+      <c r="J30" s="186"/>
+      <c r="L30" s="200" t="s">
         <v>697</v>
       </c>
-      <c r="M30" s="174"/>
-      <c r="N30" s="174"/>
+      <c r="M30" s="200"/>
+      <c r="N30" s="200"/>
     </row>
     <row r="31" spans="1:14" ht="17.25" customHeight="1" thickBot="1">
       <c r="A31" s="81">
@@ -26205,29 +26210,29 @@
       <c r="B31" s="70" t="s">
         <v>629</v>
       </c>
-      <c r="C31" s="177" t="s">
+      <c r="C31" s="189" t="s">
         <v>630</v>
       </c>
-      <c r="D31" s="178"/>
+      <c r="D31" s="190"/>
       <c r="E31" s="69" t="s">
         <v>651</v>
       </c>
-      <c r="F31" s="183" t="s">
+      <c r="F31" s="185" t="s">
         <v>652</v>
       </c>
-      <c r="G31" s="184"/>
+      <c r="G31" s="186"/>
       <c r="H31" s="70" t="s">
         <v>673</v>
       </c>
-      <c r="I31" s="177" t="s">
+      <c r="I31" s="189" t="s">
         <v>674</v>
       </c>
-      <c r="J31" s="178"/>
-      <c r="L31" s="173" t="s">
+      <c r="J31" s="190"/>
+      <c r="L31" s="199" t="s">
         <v>698</v>
       </c>
-      <c r="M31" s="173"/>
-      <c r="N31" s="173"/>
+      <c r="M31" s="199"/>
+      <c r="N31" s="199"/>
     </row>
     <row r="32" spans="1:14" ht="43.5" customHeight="1" thickBot="1">
       <c r="A32" s="81">
@@ -26236,29 +26241,29 @@
       <c r="B32" s="69" t="s">
         <v>631</v>
       </c>
-      <c r="C32" s="183" t="s">
+      <c r="C32" s="185" t="s">
         <v>632</v>
       </c>
-      <c r="D32" s="184"/>
+      <c r="D32" s="186"/>
       <c r="E32" s="70" t="s">
         <v>653</v>
       </c>
-      <c r="F32" s="177" t="s">
+      <c r="F32" s="189" t="s">
         <v>654</v>
       </c>
-      <c r="G32" s="178"/>
+      <c r="G32" s="190"/>
       <c r="H32" s="69" t="s">
         <v>675</v>
       </c>
-      <c r="I32" s="183" t="s">
+      <c r="I32" s="185" t="s">
         <v>676</v>
       </c>
-      <c r="J32" s="184"/>
-      <c r="L32" s="174" t="s">
+      <c r="J32" s="186"/>
+      <c r="L32" s="200" t="s">
         <v>699</v>
       </c>
-      <c r="M32" s="174"/>
-      <c r="N32" s="174"/>
+      <c r="M32" s="200"/>
+      <c r="N32" s="200"/>
     </row>
     <row r="33" spans="1:14" ht="31.5" customHeight="1" thickBot="1">
       <c r="A33" s="81">
@@ -26267,29 +26272,29 @@
       <c r="B33" s="70" t="s">
         <v>633</v>
       </c>
-      <c r="C33" s="177" t="s">
+      <c r="C33" s="189" t="s">
         <v>634</v>
       </c>
-      <c r="D33" s="178"/>
+      <c r="D33" s="190"/>
       <c r="E33" s="69" t="s">
         <v>655</v>
       </c>
-      <c r="F33" s="183" t="s">
+      <c r="F33" s="185" t="s">
         <v>656</v>
       </c>
-      <c r="G33" s="184"/>
+      <c r="G33" s="186"/>
       <c r="H33" s="70" t="s">
         <v>677</v>
       </c>
-      <c r="I33" s="185" t="s">
+      <c r="I33" s="191" t="s">
         <v>678</v>
       </c>
-      <c r="J33" s="186"/>
-      <c r="L33" s="173" t="s">
+      <c r="J33" s="192"/>
+      <c r="L33" s="199" t="s">
         <v>700</v>
       </c>
-      <c r="M33" s="173"/>
-      <c r="N33" s="173"/>
+      <c r="M33" s="199"/>
+      <c r="N33" s="199"/>
     </row>
     <row r="34" spans="1:14" ht="28.5" customHeight="1" thickBot="1">
       <c r="A34" s="81">
@@ -26298,29 +26303,29 @@
       <c r="B34" s="69" t="s">
         <v>635</v>
       </c>
-      <c r="C34" s="183" t="s">
+      <c r="C34" s="185" t="s">
         <v>636</v>
       </c>
-      <c r="D34" s="184"/>
+      <c r="D34" s="186"/>
       <c r="E34" s="70" t="s">
         <v>657</v>
       </c>
-      <c r="F34" s="177" t="s">
+      <c r="F34" s="189" t="s">
         <v>658</v>
       </c>
-      <c r="G34" s="178"/>
+      <c r="G34" s="190"/>
       <c r="H34" s="69" t="s">
         <v>679</v>
       </c>
-      <c r="I34" s="181" t="s">
+      <c r="I34" s="195" t="s">
         <v>680</v>
       </c>
-      <c r="J34" s="182"/>
-      <c r="L34" s="174" t="s">
+      <c r="J34" s="196"/>
+      <c r="L34" s="200" t="s">
         <v>701</v>
       </c>
-      <c r="M34" s="174"/>
-      <c r="N34" s="174"/>
+      <c r="M34" s="200"/>
+      <c r="N34" s="200"/>
     </row>
     <row r="35" spans="1:14" ht="31.5" customHeight="1" thickBot="1">
       <c r="A35" s="81">
@@ -26329,29 +26334,29 @@
       <c r="B35" s="70" t="s">
         <v>637</v>
       </c>
-      <c r="C35" s="177" t="s">
+      <c r="C35" s="189" t="s">
         <v>638</v>
       </c>
-      <c r="D35" s="178"/>
+      <c r="D35" s="190"/>
       <c r="E35" s="69" t="s">
         <v>659</v>
       </c>
-      <c r="F35" s="183" t="s">
+      <c r="F35" s="185" t="s">
         <v>660</v>
       </c>
-      <c r="G35" s="184"/>
+      <c r="G35" s="186"/>
       <c r="H35" s="77" t="s">
         <v>681</v>
       </c>
-      <c r="I35" s="177" t="s">
+      <c r="I35" s="189" t="s">
         <v>682</v>
       </c>
-      <c r="J35" s="178"/>
-      <c r="L35" s="173" t="s">
+      <c r="J35" s="190"/>
+      <c r="L35" s="199" t="s">
         <v>702</v>
       </c>
-      <c r="M35" s="173"/>
-      <c r="N35" s="173"/>
+      <c r="M35" s="199"/>
+      <c r="N35" s="199"/>
     </row>
     <row r="36" spans="1:14" ht="60.75" thickBot="1">
       <c r="A36" s="81">
@@ -26360,17 +26365,17 @@
       <c r="B36" s="69" t="s">
         <v>639</v>
       </c>
-      <c r="C36" s="183" t="s">
+      <c r="C36" s="185" t="s">
         <v>640</v>
       </c>
-      <c r="D36" s="184"/>
+      <c r="D36" s="186"/>
       <c r="E36" s="70" t="s">
         <v>661</v>
       </c>
-      <c r="F36" s="177" t="s">
+      <c r="F36" s="189" t="s">
         <v>662</v>
       </c>
-      <c r="G36" s="178"/>
+      <c r="G36" s="190"/>
       <c r="H36" s="78"/>
       <c r="I36" s="71" t="s">
         <v>683</v>
@@ -26378,11 +26383,11 @@
       <c r="J36" s="72" t="s">
         <v>684</v>
       </c>
-      <c r="L36" s="174" t="s">
+      <c r="L36" s="200" t="s">
         <v>703</v>
       </c>
-      <c r="M36" s="174"/>
-      <c r="N36" s="174"/>
+      <c r="M36" s="200"/>
+      <c r="N36" s="200"/>
     </row>
     <row r="37" spans="1:14" ht="75.75" thickBot="1">
       <c r="A37" s="81">
@@ -26391,17 +26396,17 @@
       <c r="B37" s="70" t="s">
         <v>641</v>
       </c>
-      <c r="C37" s="177" t="s">
+      <c r="C37" s="189" t="s">
         <v>642</v>
       </c>
-      <c r="D37" s="178"/>
+      <c r="D37" s="190"/>
       <c r="E37" s="69" t="s">
         <v>663</v>
       </c>
-      <c r="F37" s="183" t="s">
+      <c r="F37" s="185" t="s">
         <v>664</v>
       </c>
-      <c r="G37" s="184"/>
+      <c r="G37" s="186"/>
       <c r="H37" s="78"/>
       <c r="I37" s="73" t="s">
         <v>685</v>
@@ -26417,17 +26422,17 @@
       <c r="B38" s="69" t="s">
         <v>643</v>
       </c>
-      <c r="C38" s="183" t="s">
+      <c r="C38" s="185" t="s">
         <v>644</v>
       </c>
-      <c r="D38" s="184"/>
+      <c r="D38" s="186"/>
       <c r="E38" s="70" t="s">
         <v>665</v>
       </c>
-      <c r="F38" s="177" t="s">
+      <c r="F38" s="189" t="s">
         <v>666</v>
       </c>
-      <c r="G38" s="178"/>
+      <c r="G38" s="190"/>
       <c r="H38" s="78"/>
       <c r="I38" s="75" t="s">
         <v>687</v>
@@ -26443,40 +26448,46 @@
       <c r="B39" s="70" t="s">
         <v>692</v>
       </c>
-      <c r="C39" s="185" t="s">
+      <c r="C39" s="191" t="s">
         <v>693</v>
       </c>
-      <c r="D39" s="186"/>
+      <c r="D39" s="192"/>
       <c r="E39" s="69" t="s">
         <v>690</v>
       </c>
-      <c r="F39" s="181" t="s">
+      <c r="F39" s="195" t="s">
         <v>691</v>
       </c>
-      <c r="G39" s="182"/>
+      <c r="G39" s="196"/>
       <c r="H39" s="79"/>
-      <c r="I39" s="179" t="s">
+      <c r="I39" s="197" t="s">
         <v>689</v>
       </c>
-      <c r="J39" s="180"/>
+      <c r="J39" s="198"/>
     </row>
     <row r="40" spans="1:14" ht="58.5" customHeight="1"/>
     <row r="42" spans="1:14" ht="31.5" customHeight="1"/>
     <row r="43" spans="1:14" ht="31.5" customHeight="1"/>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F33:G33"/>
     <mergeCell ref="C39:D39"/>
     <mergeCell ref="I29:J29"/>
     <mergeCell ref="I30:J30"/>
@@ -26493,24 +26504,18 @@
     <mergeCell ref="F30:G30"/>
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="F32:G32"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>

--- a/2020_LogAnalyzer_Leeheesuk.xlsx
+++ b/2020_LogAnalyzer_Leeheesuk.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="23127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5ECDA6D2-1019-4C2A-8E6C-E213C7BBD78C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45BC12FE-732B-4474-8A27-F4D66EB03724}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" firstSheet="9" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" firstSheet="9" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UI" sheetId="7" r:id="rId1"/>
@@ -35,20 +35,11 @@
     <definedName name="_xlnm.Print_Area" localSheetId="12">기능요건!$A$1:$M$46</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
-  <fileRecoveryPr repairLoad="1"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2130" uniqueCount="1364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2221" uniqueCount="1409">
   <si>
     <t>구분</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -5927,9 +5918,6 @@
     <t>fextension</t>
   </si>
   <si>
-    <t>진행중</t>
-  </si>
-  <si>
     <t>평균 응답시간(주어진 기간)</t>
   </si>
   <si>
@@ -5955,6 +5943,144 @@
   </si>
   <si>
     <t>임계치 테이블 필요</t>
+  </si>
+  <si>
+    <t>https://www.w3.org/TR/WD-logfile.html</t>
+  </si>
+  <si>
+    <t>https://tomcat.apache.org/tomcat-8.0-doc/config/valve.html#Access_Log_Valve</t>
+  </si>
+  <si>
+    <t>%a</t>
+  </si>
+  <si>
+    <t>%A</t>
+  </si>
+  <si>
+    <t>%b</t>
+  </si>
+  <si>
+    <t>%B</t>
+  </si>
+  <si>
+    <t>%h</t>
+  </si>
+  <si>
+    <t>%H</t>
+  </si>
+  <si>
+    <t>%l</t>
+  </si>
+  <si>
+    <t>%m</t>
+  </si>
+  <si>
+    <t>%p</t>
+  </si>
+  <si>
+    <t>%q</t>
+  </si>
+  <si>
+    <t>%r</t>
+  </si>
+  <si>
+    <t>%s</t>
+  </si>
+  <si>
+    <t>%S</t>
+  </si>
+  <si>
+    <t>%t</t>
+  </si>
+  <si>
+    <t>%u</t>
+  </si>
+  <si>
+    <t>%U</t>
+  </si>
+  <si>
+    <t>%v</t>
+  </si>
+  <si>
+    <t>%D</t>
+  </si>
+  <si>
+    <t>%T</t>
+  </si>
+  <si>
+    <t>%F</t>
+  </si>
+  <si>
+    <t>%I</t>
+  </si>
+  <si>
+    <t>Remote IP address</t>
+  </si>
+  <si>
+    <t>Local IP address</t>
+  </si>
+  <si>
+    <t>Bytes sent, excluding HTTP headers, or '-' if zero</t>
+  </si>
+  <si>
+    <t>Bytes sent, excluding HTTP headers</t>
+  </si>
+  <si>
+    <t>Remote host name (or IP address if enableLookups for the connector is false)</t>
+  </si>
+  <si>
+    <t>Request protocol</t>
+  </si>
+  <si>
+    <t>Remote logical username from identd (always returns '-')</t>
+  </si>
+  <si>
+    <t>Request method (GET, POST, etc.)</t>
+  </si>
+  <si>
+    <t>Local port on which this request was received. See also %{xxx}p below.</t>
+  </si>
+  <si>
+    <t>Query string (prepended with a '?' if it exists)</t>
+  </si>
+  <si>
+    <t>First line of the request (method and request URI)</t>
+  </si>
+  <si>
+    <t>HTTP status code of the response</t>
+  </si>
+  <si>
+    <t>User session ID</t>
+  </si>
+  <si>
+    <t>Date and time, in Common Log Format</t>
+  </si>
+  <si>
+    <t>Remote user that was authenticated (if any), else '-'</t>
+  </si>
+  <si>
+    <t>Requested URL path</t>
+  </si>
+  <si>
+    <t>Local server name</t>
+  </si>
+  <si>
+    <t>Time taken to process the request, in millis</t>
+  </si>
+  <si>
+    <t>Time taken to process the request, in seconds</t>
+  </si>
+  <si>
+    <t>Time taken to commit the response, in millis</t>
+  </si>
+  <si>
+    <t>Current request thread name (can compare later with stacktraces)</t>
+  </si>
+  <si>
+    <t>Tomcat</t>
+  </si>
+  <si>
+    <t>apache 동일여부</t>
   </si>
 </sst>
 </file>
@@ -6264,7 +6390,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -6340,12 +6466,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -6626,7 +6746,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="40" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="222">
+  <cellXfs count="226">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6941,14 +7061,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -7056,6 +7170,12 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -7110,11 +7230,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -7126,6 +7246,24 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7140,44 +7278,8 @@
     <xf numFmtId="0" fontId="23" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -7191,11 +7293,29 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -7220,6 +7340,22 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -16553,51 +16689,51 @@
     </row>
     <row r="17" spans="1:13">
       <c r="J17" s="19"/>
-      <c r="K17" s="167" t="s">
+      <c r="K17" s="165" t="s">
         <v>537</v>
       </c>
-      <c r="L17" s="168"/>
-      <c r="M17" s="169"/>
+      <c r="L17" s="166"/>
+      <c r="M17" s="167"/>
     </row>
     <row r="18" spans="1:13">
       <c r="J18" s="19">
         <v>1</v>
       </c>
-      <c r="K18" s="170" t="s">
+      <c r="K18" s="168" t="s">
         <v>538</v>
       </c>
-      <c r="L18" s="171"/>
-      <c r="M18" s="172"/>
+      <c r="L18" s="169"/>
+      <c r="M18" s="170"/>
     </row>
     <row r="19" spans="1:13">
       <c r="J19" s="19">
         <v>2</v>
       </c>
-      <c r="K19" s="170" t="s">
+      <c r="K19" s="168" t="s">
         <v>539</v>
       </c>
-      <c r="L19" s="171"/>
-      <c r="M19" s="172"/>
+      <c r="L19" s="169"/>
+      <c r="M19" s="170"/>
     </row>
     <row r="20" spans="1:13">
       <c r="J20" s="19">
         <v>3</v>
       </c>
-      <c r="K20" s="170" t="s">
+      <c r="K20" s="168" t="s">
         <v>540</v>
       </c>
-      <c r="L20" s="171"/>
-      <c r="M20" s="172"/>
+      <c r="L20" s="169"/>
+      <c r="M20" s="170"/>
     </row>
     <row r="21" spans="1:13">
       <c r="J21" s="19">
         <v>4</v>
       </c>
-      <c r="K21" s="170" t="s">
+      <c r="K21" s="168" t="s">
         <v>541</v>
       </c>
-      <c r="L21" s="171"/>
-      <c r="M21" s="172"/>
+      <c r="L21" s="169"/>
+      <c r="M21" s="170"/>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="43" t="s">
@@ -16789,10 +16925,10 @@
       <c r="F7" s="111" t="s">
         <v>915</v>
       </c>
-      <c r="I7" s="201" t="s">
+      <c r="I7" s="199" t="s">
         <v>1166</v>
       </c>
-      <c r="J7" s="201"/>
+      <c r="J7" s="199"/>
       <c r="L7" s="49" t="s">
         <v>601</v>
       </c>
@@ -16810,7 +16946,7 @@
       <c r="D8" s="32" t="s">
         <v>582</v>
       </c>
-      <c r="E8" s="131" t="s">
+      <c r="E8" s="127" t="s">
         <v>583</v>
       </c>
       <c r="F8" s="36" t="s">
@@ -17095,8 +17231,8 @@
       <c r="I19" s="83"/>
       <c r="J19" s="83"/>
       <c r="K19" s="83"/>
-      <c r="L19" s="128"/>
-      <c r="M19" s="128"/>
+      <c r="L19" s="124"/>
+      <c r="M19" s="124"/>
     </row>
     <row r="20" spans="1:14">
       <c r="B20" s="32" t="s">
@@ -17135,7 +17271,7 @@
       <c r="M20" s="32" t="s">
         <v>415</v>
       </c>
-      <c r="N20" s="156" t="s">
+      <c r="N20" s="152" t="s">
         <v>568</v>
       </c>
     </row>
@@ -17176,7 +17312,7 @@
       <c r="M21" s="85" t="s">
         <v>466</v>
       </c>
-      <c r="N21" s="157" t="s">
+      <c r="N21" s="153" t="s">
         <v>429</v>
       </c>
     </row>
@@ -17217,7 +17353,7 @@
       <c r="M22" s="62" t="s">
         <v>592</v>
       </c>
-      <c r="N22" s="158" t="s">
+      <c r="N22" s="154" t="s">
         <v>458</v>
       </c>
     </row>
@@ -17247,12 +17383,12 @@
       <c r="J23" s="65">
         <v>200</v>
       </c>
-      <c r="K23" s="164"/>
+      <c r="K23" s="160"/>
       <c r="L23" s="97">
         <v>10</v>
       </c>
       <c r="M23" s="64"/>
-      <c r="N23" s="157" t="s">
+      <c r="N23" s="153" t="s">
         <v>1293</v>
       </c>
     </row>
@@ -17273,29 +17409,29 @@
       <c r="B27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="C27" s="187" t="s">
+      <c r="C27" s="185" t="s">
         <v>622</v>
       </c>
-      <c r="D27" s="188"/>
+      <c r="D27" s="186"/>
       <c r="E27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="F27" s="187" t="s">
+      <c r="F27" s="185" t="s">
         <v>622</v>
       </c>
-      <c r="G27" s="188"/>
+      <c r="G27" s="186"/>
       <c r="H27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="I27" s="187" t="s">
+      <c r="I27" s="185" t="s">
         <v>622</v>
       </c>
-      <c r="J27" s="188"/>
-      <c r="L27" s="199" t="s">
+      <c r="J27" s="186"/>
+      <c r="L27" s="183" t="s">
         <v>694</v>
       </c>
-      <c r="M27" s="199"/>
-      <c r="N27" s="199"/>
+      <c r="M27" s="183"/>
+      <c r="N27" s="183"/>
     </row>
     <row r="28" spans="1:14" ht="49.5" customHeight="1" thickBot="1">
       <c r="A28" s="81">
@@ -17304,29 +17440,29 @@
       <c r="B28" s="69" t="s">
         <v>623</v>
       </c>
-      <c r="C28" s="185" t="s">
+      <c r="C28" s="193" t="s">
         <v>624</v>
       </c>
-      <c r="D28" s="186"/>
+      <c r="D28" s="194"/>
       <c r="E28" s="70" t="s">
         <v>645</v>
       </c>
-      <c r="F28" s="189" t="s">
+      <c r="F28" s="187" t="s">
         <v>1178</v>
       </c>
-      <c r="G28" s="190"/>
+      <c r="G28" s="188"/>
       <c r="H28" s="69" t="s">
         <v>667</v>
       </c>
-      <c r="I28" s="185" t="s">
+      <c r="I28" s="193" t="s">
         <v>668</v>
       </c>
-      <c r="J28" s="186"/>
-      <c r="L28" s="200" t="s">
+      <c r="J28" s="194"/>
+      <c r="L28" s="184" t="s">
         <v>695</v>
       </c>
-      <c r="M28" s="200"/>
-      <c r="N28" s="200"/>
+      <c r="M28" s="184"/>
+      <c r="N28" s="184"/>
     </row>
     <row r="29" spans="1:14" ht="31.5" thickBot="1">
       <c r="A29" s="81">
@@ -17335,29 +17471,29 @@
       <c r="B29" s="70" t="s">
         <v>625</v>
       </c>
-      <c r="C29" s="189" t="s">
+      <c r="C29" s="187" t="s">
         <v>626</v>
       </c>
-      <c r="D29" s="190"/>
+      <c r="D29" s="188"/>
       <c r="E29" s="69" t="s">
         <v>647</v>
       </c>
-      <c r="F29" s="185" t="s">
+      <c r="F29" s="193" t="s">
         <v>648</v>
       </c>
-      <c r="G29" s="186"/>
+      <c r="G29" s="194"/>
       <c r="H29" s="70" t="s">
         <v>669</v>
       </c>
-      <c r="I29" s="193" t="s">
+      <c r="I29" s="197" t="s">
         <v>670</v>
       </c>
-      <c r="J29" s="194"/>
-      <c r="L29" s="199" t="s">
+      <c r="J29" s="198"/>
+      <c r="L29" s="183" t="s">
         <v>696</v>
       </c>
-      <c r="M29" s="199"/>
-      <c r="N29" s="199"/>
+      <c r="M29" s="183"/>
+      <c r="N29" s="183"/>
     </row>
     <row r="30" spans="1:14" ht="15.75" thickBot="1">
       <c r="A30" s="81">
@@ -17366,29 +17502,29 @@
       <c r="B30" s="69" t="s">
         <v>627</v>
       </c>
-      <c r="C30" s="185" t="s">
+      <c r="C30" s="193" t="s">
         <v>628</v>
       </c>
-      <c r="D30" s="186"/>
+      <c r="D30" s="194"/>
       <c r="E30" s="70" t="s">
         <v>649</v>
       </c>
-      <c r="F30" s="189" t="s">
+      <c r="F30" s="187" t="s">
         <v>650</v>
       </c>
-      <c r="G30" s="190"/>
+      <c r="G30" s="188"/>
       <c r="H30" s="69" t="s">
         <v>671</v>
       </c>
-      <c r="I30" s="185" t="s">
+      <c r="I30" s="193" t="s">
         <v>672</v>
       </c>
-      <c r="J30" s="186"/>
-      <c r="L30" s="200" t="s">
+      <c r="J30" s="194"/>
+      <c r="L30" s="184" t="s">
         <v>697</v>
       </c>
-      <c r="M30" s="200"/>
-      <c r="N30" s="200"/>
+      <c r="M30" s="184"/>
+      <c r="N30" s="184"/>
     </row>
     <row r="31" spans="1:14" ht="17.25" customHeight="1" thickBot="1">
       <c r="A31" s="81">
@@ -17397,29 +17533,29 @@
       <c r="B31" s="70" t="s">
         <v>629</v>
       </c>
-      <c r="C31" s="189" t="s">
+      <c r="C31" s="187" t="s">
         <v>630</v>
       </c>
-      <c r="D31" s="190"/>
+      <c r="D31" s="188"/>
       <c r="E31" s="69" t="s">
         <v>651</v>
       </c>
-      <c r="F31" s="185" t="s">
+      <c r="F31" s="193" t="s">
         <v>652</v>
       </c>
-      <c r="G31" s="186"/>
+      <c r="G31" s="194"/>
       <c r="H31" s="70" t="s">
         <v>673</v>
       </c>
-      <c r="I31" s="189" t="s">
+      <c r="I31" s="187" t="s">
         <v>674</v>
       </c>
-      <c r="J31" s="190"/>
-      <c r="L31" s="199" t="s">
+      <c r="J31" s="188"/>
+      <c r="L31" s="183" t="s">
         <v>698</v>
       </c>
-      <c r="M31" s="199"/>
-      <c r="N31" s="199"/>
+      <c r="M31" s="183"/>
+      <c r="N31" s="183"/>
     </row>
     <row r="32" spans="1:14" ht="43.5" customHeight="1" thickBot="1">
       <c r="A32" s="81">
@@ -17428,29 +17564,29 @@
       <c r="B32" s="69" t="s">
         <v>631</v>
       </c>
-      <c r="C32" s="185" t="s">
+      <c r="C32" s="193" t="s">
         <v>632</v>
       </c>
-      <c r="D32" s="186"/>
+      <c r="D32" s="194"/>
       <c r="E32" s="70" t="s">
         <v>653</v>
       </c>
-      <c r="F32" s="189" t="s">
+      <c r="F32" s="187" t="s">
         <v>654</v>
       </c>
-      <c r="G32" s="190"/>
+      <c r="G32" s="188"/>
       <c r="H32" s="69" t="s">
         <v>675</v>
       </c>
-      <c r="I32" s="185" t="s">
+      <c r="I32" s="193" t="s">
         <v>676</v>
       </c>
-      <c r="J32" s="186"/>
-      <c r="L32" s="200" t="s">
+      <c r="J32" s="194"/>
+      <c r="L32" s="184" t="s">
         <v>699</v>
       </c>
-      <c r="M32" s="200"/>
-      <c r="N32" s="200"/>
+      <c r="M32" s="184"/>
+      <c r="N32" s="184"/>
     </row>
     <row r="33" spans="1:14" ht="31.5" customHeight="1" thickBot="1">
       <c r="A33" s="81">
@@ -17459,29 +17595,29 @@
       <c r="B33" s="70" t="s">
         <v>633</v>
       </c>
-      <c r="C33" s="189" t="s">
+      <c r="C33" s="187" t="s">
         <v>634</v>
       </c>
-      <c r="D33" s="190"/>
+      <c r="D33" s="188"/>
       <c r="E33" s="69" t="s">
         <v>655</v>
       </c>
-      <c r="F33" s="185" t="s">
+      <c r="F33" s="193" t="s">
         <v>656</v>
       </c>
-      <c r="G33" s="186"/>
+      <c r="G33" s="194"/>
       <c r="H33" s="70" t="s">
         <v>677</v>
       </c>
-      <c r="I33" s="191" t="s">
+      <c r="I33" s="195" t="s">
         <v>678</v>
       </c>
-      <c r="J33" s="192"/>
-      <c r="L33" s="199" t="s">
+      <c r="J33" s="196"/>
+      <c r="L33" s="183" t="s">
         <v>700</v>
       </c>
-      <c r="M33" s="199"/>
-      <c r="N33" s="199"/>
+      <c r="M33" s="183"/>
+      <c r="N33" s="183"/>
     </row>
     <row r="34" spans="1:14" ht="28.5" customHeight="1" thickBot="1">
       <c r="A34" s="81">
@@ -17490,29 +17626,29 @@
       <c r="B34" s="69" t="s">
         <v>635</v>
       </c>
-      <c r="C34" s="185" t="s">
+      <c r="C34" s="193" t="s">
         <v>636</v>
       </c>
-      <c r="D34" s="186"/>
+      <c r="D34" s="194"/>
       <c r="E34" s="70" t="s">
         <v>657</v>
       </c>
-      <c r="F34" s="189" t="s">
+      <c r="F34" s="187" t="s">
         <v>658</v>
       </c>
-      <c r="G34" s="190"/>
+      <c r="G34" s="188"/>
       <c r="H34" s="69" t="s">
         <v>679</v>
       </c>
-      <c r="I34" s="195" t="s">
+      <c r="I34" s="191" t="s">
         <v>680</v>
       </c>
-      <c r="J34" s="196"/>
-      <c r="L34" s="200" t="s">
+      <c r="J34" s="192"/>
+      <c r="L34" s="184" t="s">
         <v>701</v>
       </c>
-      <c r="M34" s="200"/>
-      <c r="N34" s="200"/>
+      <c r="M34" s="184"/>
+      <c r="N34" s="184"/>
     </row>
     <row r="35" spans="1:14" ht="31.5" customHeight="1" thickBot="1">
       <c r="A35" s="81">
@@ -17521,29 +17657,29 @@
       <c r="B35" s="70" t="s">
         <v>637</v>
       </c>
-      <c r="C35" s="189" t="s">
+      <c r="C35" s="187" t="s">
         <v>638</v>
       </c>
-      <c r="D35" s="190"/>
+      <c r="D35" s="188"/>
       <c r="E35" s="69" t="s">
         <v>659</v>
       </c>
-      <c r="F35" s="185" t="s">
+      <c r="F35" s="193" t="s">
         <v>660</v>
       </c>
-      <c r="G35" s="186"/>
+      <c r="G35" s="194"/>
       <c r="H35" s="77" t="s">
         <v>681</v>
       </c>
-      <c r="I35" s="189" t="s">
+      <c r="I35" s="187" t="s">
         <v>682</v>
       </c>
-      <c r="J35" s="190"/>
-      <c r="L35" s="199" t="s">
+      <c r="J35" s="188"/>
+      <c r="L35" s="183" t="s">
         <v>702</v>
       </c>
-      <c r="M35" s="199"/>
-      <c r="N35" s="199"/>
+      <c r="M35" s="183"/>
+      <c r="N35" s="183"/>
     </row>
     <row r="36" spans="1:14" ht="60.75" thickBot="1">
       <c r="A36" s="81">
@@ -17552,17 +17688,17 @@
       <c r="B36" s="69" t="s">
         <v>639</v>
       </c>
-      <c r="C36" s="185" t="s">
+      <c r="C36" s="193" t="s">
         <v>640</v>
       </c>
-      <c r="D36" s="186"/>
+      <c r="D36" s="194"/>
       <c r="E36" s="70" t="s">
         <v>661</v>
       </c>
-      <c r="F36" s="189" t="s">
+      <c r="F36" s="187" t="s">
         <v>662</v>
       </c>
-      <c r="G36" s="190"/>
+      <c r="G36" s="188"/>
       <c r="H36" s="78"/>
       <c r="I36" s="71" t="s">
         <v>683</v>
@@ -17570,11 +17706,11 @@
       <c r="J36" s="72" t="s">
         <v>684</v>
       </c>
-      <c r="L36" s="200" t="s">
+      <c r="L36" s="184" t="s">
         <v>703</v>
       </c>
-      <c r="M36" s="200"/>
-      <c r="N36" s="200"/>
+      <c r="M36" s="184"/>
+      <c r="N36" s="184"/>
     </row>
     <row r="37" spans="1:14" ht="75.75" thickBot="1">
       <c r="A37" s="81">
@@ -17583,17 +17719,17 @@
       <c r="B37" s="70" t="s">
         <v>641</v>
       </c>
-      <c r="C37" s="189" t="s">
+      <c r="C37" s="187" t="s">
         <v>642</v>
       </c>
-      <c r="D37" s="190"/>
+      <c r="D37" s="188"/>
       <c r="E37" s="69" t="s">
         <v>663</v>
       </c>
-      <c r="F37" s="185" t="s">
+      <c r="F37" s="193" t="s">
         <v>664</v>
       </c>
-      <c r="G37" s="186"/>
+      <c r="G37" s="194"/>
       <c r="H37" s="78"/>
       <c r="I37" s="73" t="s">
         <v>685</v>
@@ -17609,17 +17745,17 @@
       <c r="B38" s="69" t="s">
         <v>643</v>
       </c>
-      <c r="C38" s="185" t="s">
+      <c r="C38" s="193" t="s">
         <v>644</v>
       </c>
-      <c r="D38" s="186"/>
+      <c r="D38" s="194"/>
       <c r="E38" s="70" t="s">
         <v>665</v>
       </c>
-      <c r="F38" s="189" t="s">
+      <c r="F38" s="187" t="s">
         <v>666</v>
       </c>
-      <c r="G38" s="190"/>
+      <c r="G38" s="188"/>
       <c r="H38" s="78"/>
       <c r="I38" s="75" t="s">
         <v>687</v>
@@ -17635,22 +17771,22 @@
       <c r="B39" s="70" t="s">
         <v>692</v>
       </c>
-      <c r="C39" s="191" t="s">
+      <c r="C39" s="195" t="s">
         <v>693</v>
       </c>
-      <c r="D39" s="192"/>
+      <c r="D39" s="196"/>
       <c r="E39" s="69" t="s">
         <v>690</v>
       </c>
-      <c r="F39" s="195" t="s">
+      <c r="F39" s="191" t="s">
         <v>691</v>
       </c>
-      <c r="G39" s="196"/>
+      <c r="G39" s="192"/>
       <c r="H39" s="79"/>
-      <c r="I39" s="197" t="s">
+      <c r="I39" s="189" t="s">
         <v>689</v>
       </c>
-      <c r="J39" s="198"/>
+      <c r="J39" s="190"/>
     </row>
     <row r="40" spans="1:14" ht="58.5" customHeight="1"/>
     <row r="41" spans="1:14">
@@ -17944,43 +18080,6 @@
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="L35:N35"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="F36:G36"/>
     <mergeCell ref="L36:N36"/>
@@ -17991,6 +18090,43 @@
     <mergeCell ref="F38:G38"/>
     <mergeCell ref="C39:D39"/>
     <mergeCell ref="F39:G39"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="L27:N27"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
@@ -18566,21 +18702,21 @@
       <c r="M1" s="26" t="s">
         <v>407</v>
       </c>
-      <c r="N1" s="166" t="s">
-        <v>1363</v>
+      <c r="N1" s="162" t="s">
+        <v>1362</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A2" s="202" t="s">
+      <c r="A2" s="204" t="s">
         <v>504</v>
       </c>
-      <c r="B2" s="205" t="s">
+      <c r="B2" s="209" t="s">
         <v>506</v>
       </c>
-      <c r="C2" s="202" t="s">
+      <c r="C2" s="204" t="s">
         <v>508</v>
       </c>
-      <c r="D2" s="202" t="s">
+      <c r="D2" s="204" t="s">
         <v>556</v>
       </c>
       <c r="E2" s="8"/>
@@ -18593,7 +18729,7 @@
       <c r="H2" s="10">
         <v>1</v>
       </c>
-      <c r="I2" s="155">
+      <c r="I2" s="151">
         <v>44043</v>
       </c>
       <c r="J2" s="10"/>
@@ -18604,10 +18740,10 @@
       <c r="N2" s="19"/>
     </row>
     <row r="3" spans="1:17">
-      <c r="A3" s="177"/>
-      <c r="B3" s="206"/>
-      <c r="C3" s="203"/>
-      <c r="D3" s="203"/>
+      <c r="A3" s="175"/>
+      <c r="B3" s="210"/>
+      <c r="C3" s="205"/>
+      <c r="D3" s="205"/>
       <c r="E3" s="11"/>
       <c r="F3" s="9" t="s">
         <v>310</v>
@@ -18618,7 +18754,7 @@
       <c r="H3" s="12">
         <v>2</v>
       </c>
-      <c r="I3" s="155">
+      <c r="I3" s="151">
         <v>44074</v>
       </c>
       <c r="J3" s="10"/>
@@ -18629,10 +18765,10 @@
       <c r="N3" s="19"/>
     </row>
     <row r="4" spans="1:17">
-      <c r="A4" s="177"/>
-      <c r="B4" s="206"/>
-      <c r="C4" s="203"/>
-      <c r="D4" s="204"/>
+      <c r="A4" s="175"/>
+      <c r="B4" s="210"/>
+      <c r="C4" s="205"/>
+      <c r="D4" s="206"/>
       <c r="E4" s="11"/>
       <c r="F4" s="9" t="s">
         <v>311</v>
@@ -18643,18 +18779,18 @@
       <c r="H4" s="12" t="s">
         <v>963</v>
       </c>
-      <c r="I4" s="155"/>
+      <c r="I4" s="151"/>
       <c r="J4" s="10"/>
       <c r="K4" s="10"/>
-      <c r="M4" s="162" t="s">
+      <c r="M4" s="158" t="s">
         <v>1299</v>
       </c>
       <c r="N4" s="19"/>
     </row>
     <row r="5" spans="1:17">
-      <c r="A5" s="177"/>
-      <c r="B5" s="206"/>
-      <c r="C5" s="204"/>
+      <c r="A5" s="175"/>
+      <c r="B5" s="210"/>
+      <c r="C5" s="206"/>
       <c r="D5" s="46" t="s">
         <v>555</v>
       </c>
@@ -18668,7 +18804,7 @@
       <c r="H5" s="12" t="s">
         <v>960</v>
       </c>
-      <c r="I5" s="155">
+      <c r="I5" s="151">
         <v>44043</v>
       </c>
       <c r="J5" s="10" t="s">
@@ -18676,17 +18812,17 @@
       </c>
       <c r="K5" s="10"/>
       <c r="M5" s="19" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="N5" s="19"/>
     </row>
     <row r="6" spans="1:17">
-      <c r="A6" s="177"/>
-      <c r="B6" s="206"/>
-      <c r="C6" s="202" t="s">
+      <c r="A6" s="175"/>
+      <c r="B6" s="210"/>
+      <c r="C6" s="204" t="s">
         <v>507</v>
       </c>
-      <c r="D6" s="202" t="s">
+      <c r="D6" s="204" t="s">
         <v>511</v>
       </c>
       <c r="E6" s="11"/>
@@ -18699,17 +18835,17 @@
       <c r="H6" s="12" t="s">
         <v>961</v>
       </c>
-      <c r="I6" s="155">
+      <c r="I6" s="151">
         <v>44043</v>
       </c>
       <c r="J6" s="10"/>
       <c r="K6" s="10"/>
     </row>
     <row r="7" spans="1:17">
-      <c r="A7" s="177"/>
-      <c r="B7" s="206"/>
-      <c r="C7" s="203"/>
-      <c r="D7" s="203"/>
+      <c r="A7" s="175"/>
+      <c r="B7" s="210"/>
+      <c r="C7" s="205"/>
+      <c r="D7" s="205"/>
       <c r="E7" s="11"/>
       <c r="F7" s="9" t="s">
         <v>313</v>
@@ -18720,17 +18856,17 @@
       <c r="H7" s="12">
         <v>1</v>
       </c>
-      <c r="I7" s="155">
+      <c r="I7" s="151">
         <v>44043</v>
       </c>
       <c r="J7" s="10"/>
       <c r="K7" s="10"/>
     </row>
     <row r="8" spans="1:17">
-      <c r="A8" s="177"/>
-      <c r="B8" s="206"/>
-      <c r="C8" s="203"/>
-      <c r="D8" s="203"/>
+      <c r="A8" s="175"/>
+      <c r="B8" s="210"/>
+      <c r="C8" s="205"/>
+      <c r="D8" s="205"/>
       <c r="E8" s="11"/>
       <c r="F8" s="9" t="s">
         <v>314</v>
@@ -18741,17 +18877,17 @@
       <c r="H8" s="12">
         <v>1</v>
       </c>
-      <c r="I8" s="155">
+      <c r="I8" s="151">
         <v>44043</v>
       </c>
       <c r="J8" s="10"/>
       <c r="K8" s="10"/>
     </row>
     <row r="9" spans="1:17">
-      <c r="A9" s="177"/>
-      <c r="B9" s="206"/>
-      <c r="C9" s="203"/>
-      <c r="D9" s="203"/>
+      <c r="A9" s="175"/>
+      <c r="B9" s="210"/>
+      <c r="C9" s="205"/>
+      <c r="D9" s="205"/>
       <c r="E9" s="8"/>
       <c r="F9" s="9" t="s">
         <v>345</v>
@@ -18762,17 +18898,17 @@
       <c r="H9" s="10">
         <v>1</v>
       </c>
-      <c r="I9" s="155">
+      <c r="I9" s="151">
         <v>44043</v>
       </c>
       <c r="J9" s="10"/>
       <c r="K9" s="10"/>
     </row>
     <row r="10" spans="1:17">
-      <c r="A10" s="177"/>
-      <c r="B10" s="206"/>
-      <c r="C10" s="203"/>
-      <c r="D10" s="203"/>
+      <c r="A10" s="175"/>
+      <c r="B10" s="210"/>
+      <c r="C10" s="205"/>
+      <c r="D10" s="205"/>
       <c r="E10" s="8"/>
       <c r="F10" s="9" t="s">
         <v>346</v>
@@ -18783,17 +18919,17 @@
       <c r="H10" s="10">
         <v>1</v>
       </c>
-      <c r="I10" s="155">
+      <c r="I10" s="151">
         <v>44043</v>
       </c>
       <c r="J10" s="10"/>
       <c r="K10" s="10"/>
     </row>
     <row r="11" spans="1:17">
-      <c r="A11" s="177"/>
-      <c r="B11" s="206"/>
-      <c r="C11" s="203"/>
-      <c r="D11" s="203"/>
+      <c r="A11" s="175"/>
+      <c r="B11" s="210"/>
+      <c r="C11" s="205"/>
+      <c r="D11" s="205"/>
       <c r="E11" s="8"/>
       <c r="F11" s="9" t="s">
         <v>315</v>
@@ -18804,17 +18940,17 @@
       <c r="H11" s="10">
         <v>1</v>
       </c>
-      <c r="I11" s="155">
+      <c r="I11" s="151">
         <v>44043</v>
       </c>
       <c r="J11" s="10"/>
       <c r="K11" s="10"/>
     </row>
     <row r="12" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A12" s="177"/>
-      <c r="B12" s="206"/>
-      <c r="C12" s="203"/>
-      <c r="D12" s="203"/>
+      <c r="A12" s="175"/>
+      <c r="B12" s="210"/>
+      <c r="C12" s="205"/>
+      <c r="D12" s="205"/>
       <c r="E12" s="8"/>
       <c r="F12" s="9" t="s">
         <v>347</v>
@@ -18825,17 +18961,17 @@
       <c r="H12" s="10">
         <v>1</v>
       </c>
-      <c r="I12" s="155">
+      <c r="I12" s="151">
         <v>44043</v>
       </c>
       <c r="J12" s="10"/>
       <c r="K12" s="10"/>
     </row>
     <row r="13" spans="1:17" ht="30">
-      <c r="A13" s="177"/>
-      <c r="B13" s="206"/>
-      <c r="C13" s="203"/>
-      <c r="D13" s="203"/>
+      <c r="A13" s="175"/>
+      <c r="B13" s="210"/>
+      <c r="C13" s="205"/>
+      <c r="D13" s="205"/>
       <c r="E13" s="11"/>
       <c r="F13" s="9" t="s">
         <v>316</v>
@@ -18846,7 +18982,7 @@
       <c r="H13" s="12">
         <v>3</v>
       </c>
-      <c r="I13" s="155"/>
+      <c r="I13" s="151"/>
       <c r="J13" s="10" t="s">
         <v>563</v>
       </c>
@@ -18856,10 +18992,10 @@
       </c>
     </row>
     <row r="14" spans="1:17">
-      <c r="A14" s="177"/>
-      <c r="B14" s="206"/>
-      <c r="C14" s="203"/>
-      <c r="D14" s="204"/>
+      <c r="A14" s="175"/>
+      <c r="B14" s="210"/>
+      <c r="C14" s="205"/>
+      <c r="D14" s="206"/>
       <c r="E14" s="11"/>
       <c r="F14" s="9" t="s">
         <v>318</v>
@@ -18870,16 +19006,16 @@
       <c r="H14" s="12" t="s">
         <v>963</v>
       </c>
-      <c r="I14" s="155" t="s">
+      <c r="I14" s="151" t="s">
         <v>1298</v>
       </c>
       <c r="J14" s="10"/>
       <c r="K14" s="10"/>
     </row>
     <row r="15" spans="1:17" ht="30">
-      <c r="A15" s="177"/>
-      <c r="B15" s="206"/>
-      <c r="C15" s="203"/>
+      <c r="A15" s="175"/>
+      <c r="B15" s="210"/>
+      <c r="C15" s="205"/>
       <c r="D15" s="22" t="s">
         <v>512</v>
       </c>
@@ -18893,15 +19029,15 @@
       <c r="H15" s="12">
         <v>1</v>
       </c>
-      <c r="I15" s="155">
+      <c r="I15" s="151">
         <v>44043</v>
       </c>
       <c r="J15" s="10"/>
       <c r="K15" s="10"/>
-      <c r="M15" s="210" t="s">
+      <c r="M15" s="202" t="s">
         <v>851</v>
       </c>
-      <c r="N15" s="211"/>
+      <c r="N15" s="203"/>
       <c r="O15" s="114" t="s">
         <v>1258</v>
       </c>
@@ -18911,12 +19047,12 @@
       </c>
     </row>
     <row r="16" spans="1:17" ht="30">
-      <c r="A16" s="177"/>
-      <c r="B16" s="206"/>
-      <c r="C16" s="202" t="s">
+      <c r="A16" s="175"/>
+      <c r="B16" s="210"/>
+      <c r="C16" s="204" t="s">
         <v>509</v>
       </c>
-      <c r="D16" s="202" t="s">
+      <c r="D16" s="204" t="s">
         <v>513</v>
       </c>
       <c r="E16" s="11"/>
@@ -18929,7 +19065,7 @@
       <c r="H16" s="12">
         <v>1</v>
       </c>
-      <c r="I16" s="155">
+      <c r="I16" s="151">
         <v>44043</v>
       </c>
       <c r="J16" s="10"/>
@@ -18951,10 +19087,10 @@
       </c>
     </row>
     <row r="17" spans="1:17">
-      <c r="A17" s="177"/>
-      <c r="B17" s="206"/>
-      <c r="C17" s="203"/>
-      <c r="D17" s="203"/>
+      <c r="A17" s="175"/>
+      <c r="B17" s="210"/>
+      <c r="C17" s="205"/>
+      <c r="D17" s="205"/>
       <c r="E17" s="19"/>
       <c r="F17" s="9" t="s">
         <v>364</v>
@@ -18965,7 +19101,7 @@
       <c r="H17" s="12">
         <v>1</v>
       </c>
-      <c r="I17" s="155">
+      <c r="I17" s="151">
         <v>44043</v>
       </c>
       <c r="J17" s="10"/>
@@ -18984,10 +19120,10 @@
       </c>
     </row>
     <row r="18" spans="1:17">
-      <c r="A18" s="177"/>
-      <c r="B18" s="206"/>
-      <c r="C18" s="203"/>
-      <c r="D18" s="203"/>
+      <c r="A18" s="175"/>
+      <c r="B18" s="210"/>
+      <c r="C18" s="205"/>
+      <c r="D18" s="205"/>
       <c r="E18" s="19"/>
       <c r="F18" s="48" t="s">
         <v>559</v>
@@ -18998,7 +19134,7 @@
       <c r="H18" s="10">
         <v>1</v>
       </c>
-      <c r="I18" s="155">
+      <c r="I18" s="151">
         <v>44043</v>
       </c>
       <c r="J18" s="10" t="s">
@@ -19019,10 +19155,10 @@
       </c>
     </row>
     <row r="19" spans="1:17">
-      <c r="A19" s="177"/>
-      <c r="B19" s="206"/>
-      <c r="C19" s="203"/>
-      <c r="D19" s="203"/>
+      <c r="A19" s="175"/>
+      <c r="B19" s="210"/>
+      <c r="C19" s="205"/>
+      <c r="D19" s="205"/>
       <c r="E19" s="8"/>
       <c r="F19" s="9" t="s">
         <v>332</v>
@@ -19033,7 +19169,7 @@
       <c r="H19" s="10">
         <v>1</v>
       </c>
-      <c r="I19" s="155">
+      <c r="I19" s="151">
         <v>44043</v>
       </c>
       <c r="J19" s="10"/>
@@ -19053,10 +19189,10 @@
       <c r="Q19" s="91"/>
     </row>
     <row r="20" spans="1:17">
-      <c r="A20" s="177"/>
-      <c r="B20" s="206"/>
-      <c r="C20" s="203"/>
-      <c r="D20" s="203"/>
+      <c r="A20" s="175"/>
+      <c r="B20" s="210"/>
+      <c r="C20" s="205"/>
+      <c r="D20" s="205"/>
       <c r="E20" s="8"/>
       <c r="F20" s="9" t="s">
         <v>333</v>
@@ -19067,7 +19203,7 @@
       <c r="H20" s="10">
         <v>1</v>
       </c>
-      <c r="I20" s="155">
+      <c r="I20" s="151">
         <v>44043</v>
       </c>
       <c r="J20" s="10"/>
@@ -19087,10 +19223,10 @@
       <c r="Q20" s="91"/>
     </row>
     <row r="21" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A21" s="177"/>
-      <c r="B21" s="206"/>
-      <c r="C21" s="203"/>
-      <c r="D21" s="203"/>
+      <c r="A21" s="175"/>
+      <c r="B21" s="210"/>
+      <c r="C21" s="205"/>
+      <c r="D21" s="205"/>
       <c r="E21" s="14"/>
       <c r="F21" s="9" t="s">
         <v>334</v>
@@ -19101,7 +19237,7 @@
       <c r="H21" s="16">
         <v>3</v>
       </c>
-      <c r="I21" s="155"/>
+      <c r="I21" s="151"/>
       <c r="J21" s="10" t="s">
         <v>563</v>
       </c>
@@ -19123,10 +19259,10 @@
       </c>
     </row>
     <row r="22" spans="1:17">
-      <c r="A22" s="177"/>
-      <c r="B22" s="206"/>
-      <c r="C22" s="203"/>
-      <c r="D22" s="203"/>
+      <c r="A22" s="175"/>
+      <c r="B22" s="210"/>
+      <c r="C22" s="205"/>
+      <c r="D22" s="205"/>
       <c r="E22" s="14"/>
       <c r="F22" s="9" t="s">
         <v>335</v>
@@ -19137,7 +19273,7 @@
       <c r="H22" s="16">
         <v>1</v>
       </c>
-      <c r="I22" s="155">
+      <c r="I22" s="151">
         <v>44043</v>
       </c>
       <c r="J22" s="10"/>
@@ -19159,10 +19295,10 @@
       </c>
     </row>
     <row r="23" spans="1:17">
-      <c r="A23" s="177"/>
-      <c r="B23" s="206"/>
-      <c r="C23" s="203"/>
-      <c r="D23" s="203"/>
+      <c r="A23" s="175"/>
+      <c r="B23" s="210"/>
+      <c r="C23" s="205"/>
+      <c r="D23" s="205"/>
       <c r="E23" s="14"/>
       <c r="F23" s="9" t="s">
         <v>336</v>
@@ -19173,7 +19309,7 @@
       <c r="H23" s="16">
         <v>2</v>
       </c>
-      <c r="I23" s="155">
+      <c r="I23" s="151">
         <v>44074</v>
       </c>
       <c r="J23" s="10"/>
@@ -19187,18 +19323,18 @@
       <c r="O23" s="99" t="s">
         <v>81</v>
       </c>
-      <c r="P23" s="159" t="s">
+      <c r="P23" s="155" t="s">
         <v>962</v>
       </c>
-      <c r="Q23" s="154" t="s">
+      <c r="Q23" s="150" t="s">
         <v>1284</v>
       </c>
     </row>
     <row r="24" spans="1:17">
-      <c r="A24" s="177"/>
-      <c r="B24" s="206"/>
-      <c r="C24" s="203"/>
-      <c r="D24" s="203"/>
+      <c r="A24" s="175"/>
+      <c r="B24" s="210"/>
+      <c r="C24" s="205"/>
+      <c r="D24" s="205"/>
       <c r="E24" s="8"/>
       <c r="F24" s="9" t="s">
         <v>1281</v>
@@ -19209,12 +19345,12 @@
       <c r="H24" s="10">
         <v>2</v>
       </c>
-      <c r="I24" s="155">
+      <c r="I24" s="151">
         <v>44074</v>
       </c>
       <c r="J24" s="10"/>
       <c r="K24" s="10"/>
-      <c r="M24" s="153" t="s">
+      <c r="M24" s="149" t="s">
         <v>1280</v>
       </c>
       <c r="N24" s="98" t="s">
@@ -19229,10 +19365,10 @@
       <c r="Q24" s="91"/>
     </row>
     <row r="25" spans="1:17">
-      <c r="A25" s="177"/>
-      <c r="B25" s="206"/>
-      <c r="C25" s="203"/>
-      <c r="D25" s="203"/>
+      <c r="A25" s="175"/>
+      <c r="B25" s="210"/>
+      <c r="C25" s="205"/>
+      <c r="D25" s="205"/>
       <c r="E25" s="8"/>
       <c r="F25" s="9" t="s">
         <v>373</v>
@@ -19243,7 +19379,7 @@
       <c r="H25" s="10">
         <v>3</v>
       </c>
-      <c r="I25" s="155"/>
+      <c r="I25" s="151"/>
       <c r="J25" s="10" t="s">
         <v>563</v>
       </c>
@@ -19263,10 +19399,10 @@
       <c r="Q25" s="91"/>
     </row>
     <row r="26" spans="1:17">
-      <c r="A26" s="177"/>
-      <c r="B26" s="206"/>
-      <c r="C26" s="203"/>
-      <c r="D26" s="203"/>
+      <c r="A26" s="175"/>
+      <c r="B26" s="210"/>
+      <c r="C26" s="205"/>
+      <c r="D26" s="205"/>
       <c r="E26" s="8"/>
       <c r="F26" s="9" t="s">
         <v>338</v>
@@ -19277,7 +19413,7 @@
       <c r="H26" s="10" t="s">
         <v>963</v>
       </c>
-      <c r="I26" s="155"/>
+      <c r="I26" s="151"/>
       <c r="J26" s="10"/>
       <c r="K26" s="10"/>
       <c r="M26" s="99" t="s">
@@ -19295,10 +19431,10 @@
       <c r="Q26" s="91"/>
     </row>
     <row r="27" spans="1:17">
-      <c r="A27" s="177"/>
-      <c r="B27" s="206"/>
-      <c r="C27" s="203"/>
-      <c r="D27" s="203"/>
+      <c r="A27" s="175"/>
+      <c r="B27" s="210"/>
+      <c r="C27" s="205"/>
+      <c r="D27" s="205"/>
       <c r="E27" s="8"/>
       <c r="F27" s="9" t="s">
         <v>339</v>
@@ -19309,7 +19445,7 @@
       <c r="H27" s="119" t="s">
         <v>1297</v>
       </c>
-      <c r="I27" s="155" t="s">
+      <c r="I27" s="151" t="s">
         <v>1332</v>
       </c>
       <c r="J27" s="10"/>
@@ -19329,10 +19465,10 @@
       <c r="Q27" s="91"/>
     </row>
     <row r="28" spans="1:17">
-      <c r="A28" s="177"/>
-      <c r="B28" s="206"/>
-      <c r="C28" s="203"/>
-      <c r="D28" s="203"/>
+      <c r="A28" s="175"/>
+      <c r="B28" s="210"/>
+      <c r="C28" s="205"/>
+      <c r="D28" s="205"/>
       <c r="E28" s="8"/>
       <c r="F28" s="121" t="s">
         <v>965</v>
@@ -19343,7 +19479,7 @@
       <c r="H28" s="10">
         <v>1</v>
       </c>
-      <c r="I28" s="155">
+      <c r="I28" s="151">
         <v>44043</v>
       </c>
       <c r="J28" s="10"/>
@@ -19363,10 +19499,10 @@
       <c r="Q28" s="91"/>
     </row>
     <row r="29" spans="1:17">
-      <c r="A29" s="177"/>
-      <c r="B29" s="206"/>
-      <c r="C29" s="203"/>
-      <c r="D29" s="203"/>
+      <c r="A29" s="175"/>
+      <c r="B29" s="210"/>
+      <c r="C29" s="205"/>
+      <c r="D29" s="205"/>
       <c r="E29" s="8"/>
       <c r="F29" s="9" t="s">
         <v>955</v>
@@ -19377,7 +19513,7 @@
       <c r="H29" s="16" t="s">
         <v>963</v>
       </c>
-      <c r="I29" s="155" t="s">
+      <c r="I29" s="151" t="s">
         <v>1332</v>
       </c>
       <c r="J29" s="10"/>
@@ -19386,10 +19522,10 @@
       </c>
     </row>
     <row r="30" spans="1:17">
-      <c r="A30" s="177"/>
-      <c r="B30" s="206"/>
-      <c r="C30" s="203"/>
-      <c r="D30" s="204"/>
+      <c r="A30" s="175"/>
+      <c r="B30" s="210"/>
+      <c r="C30" s="205"/>
+      <c r="D30" s="206"/>
       <c r="E30" s="8"/>
       <c r="F30" s="49" t="s">
         <v>323</v>
@@ -19400,11 +19536,11 @@
       <c r="H30" s="113">
         <v>3</v>
       </c>
-      <c r="I30" s="155" t="s">
+      <c r="I30" s="151" t="s">
         <v>1332</v>
       </c>
       <c r="J30" s="10"/>
-      <c r="K30" s="208" t="s">
+      <c r="K30" s="200" t="s">
         <v>959</v>
       </c>
       <c r="M30" s="101" t="s">
@@ -19421,10 +19557,10 @@
       </c>
     </row>
     <row r="31" spans="1:17">
-      <c r="A31" s="177"/>
-      <c r="B31" s="206"/>
-      <c r="C31" s="203"/>
-      <c r="D31" s="202" t="s">
+      <c r="A31" s="175"/>
+      <c r="B31" s="210"/>
+      <c r="C31" s="205"/>
+      <c r="D31" s="204" t="s">
         <v>518</v>
       </c>
       <c r="E31" s="8"/>
@@ -19437,17 +19573,17 @@
       <c r="H31" s="16">
         <v>1</v>
       </c>
-      <c r="I31" s="155">
+      <c r="I31" s="151">
         <v>44043</v>
       </c>
       <c r="J31" s="10"/>
-      <c r="K31" s="212"/>
+      <c r="K31" s="207"/>
     </row>
     <row r="32" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A32" s="177"/>
-      <c r="B32" s="206"/>
-      <c r="C32" s="203"/>
-      <c r="D32" s="203"/>
+      <c r="A32" s="175"/>
+      <c r="B32" s="210"/>
+      <c r="C32" s="205"/>
+      <c r="D32" s="205"/>
       <c r="E32" s="8"/>
       <c r="F32" s="9" t="s">
         <v>325</v>
@@ -19458,20 +19594,20 @@
       <c r="H32" s="16">
         <v>1</v>
       </c>
-      <c r="I32" s="155">
+      <c r="I32" s="151">
         <v>44043</v>
       </c>
       <c r="J32" s="10"/>
-      <c r="K32" s="212"/>
-      <c r="M32" s="151" t="s">
+      <c r="K32" s="207"/>
+      <c r="M32" s="147" t="s">
         <v>1277</v>
       </c>
     </row>
     <row r="33" spans="1:15" ht="16.5" customHeight="1">
-      <c r="A33" s="177"/>
-      <c r="B33" s="206"/>
-      <c r="C33" s="203"/>
-      <c r="D33" s="203"/>
+      <c r="A33" s="175"/>
+      <c r="B33" s="210"/>
+      <c r="C33" s="205"/>
+      <c r="D33" s="205"/>
       <c r="E33" s="8"/>
       <c r="F33" s="9" t="s">
         <v>957</v>
@@ -19482,14 +19618,14 @@
       <c r="H33" s="16">
         <v>2</v>
       </c>
-      <c r="I33" s="155">
+      <c r="I33" s="151">
         <v>44043</v>
       </c>
       <c r="J33" s="10" t="s">
         <v>954</v>
       </c>
-      <c r="K33" s="213"/>
-      <c r="M33" s="152" t="s">
+      <c r="K33" s="208"/>
+      <c r="M33" s="148" t="s">
         <v>1278</v>
       </c>
       <c r="N33" s="5" t="s">
@@ -19500,10 +19636,10 @@
       </c>
     </row>
     <row r="34" spans="1:15" ht="16.5" customHeight="1">
-      <c r="A34" s="177"/>
-      <c r="B34" s="206"/>
-      <c r="C34" s="203"/>
-      <c r="D34" s="203"/>
+      <c r="A34" s="175"/>
+      <c r="B34" s="210"/>
+      <c r="C34" s="205"/>
+      <c r="D34" s="205"/>
       <c r="E34" s="8"/>
       <c r="F34" s="9" t="s">
         <v>1275</v>
@@ -19514,7 +19650,7 @@
       <c r="H34" s="118">
         <v>2</v>
       </c>
-      <c r="I34" s="155">
+      <c r="I34" s="151">
         <v>44074</v>
       </c>
       <c r="J34" s="10"/>
@@ -19523,10 +19659,10 @@
       </c>
     </row>
     <row r="35" spans="1:15">
-      <c r="A35" s="177"/>
-      <c r="B35" s="206"/>
-      <c r="C35" s="204"/>
-      <c r="D35" s="204"/>
+      <c r="A35" s="175"/>
+      <c r="B35" s="210"/>
+      <c r="C35" s="206"/>
+      <c r="D35" s="206"/>
       <c r="E35" s="8"/>
       <c r="F35" s="49" t="s">
         <v>322</v>
@@ -19537,19 +19673,19 @@
       <c r="H35" s="50">
         <v>3</v>
       </c>
-      <c r="I35" s="155" t="s">
+      <c r="I35" s="151" t="s">
         <v>1332</v>
       </c>
       <c r="J35" s="10"/>
       <c r="K35" s="10"/>
     </row>
     <row r="36" spans="1:15">
-      <c r="A36" s="177"/>
-      <c r="B36" s="206"/>
-      <c r="C36" s="202" t="s">
+      <c r="A36" s="175"/>
+      <c r="B36" s="210"/>
+      <c r="C36" s="204" t="s">
         <v>340</v>
       </c>
-      <c r="D36" s="202" t="s">
+      <c r="D36" s="204" t="s">
         <v>517</v>
       </c>
       <c r="E36" s="8"/>
@@ -19562,17 +19698,17 @@
       <c r="H36" s="16">
         <v>1</v>
       </c>
-      <c r="I36" s="155">
+      <c r="I36" s="151">
         <v>44043</v>
       </c>
       <c r="J36" s="10"/>
       <c r="K36" s="10"/>
     </row>
     <row r="37" spans="1:15">
-      <c r="A37" s="177"/>
-      <c r="B37" s="207"/>
-      <c r="C37" s="204"/>
-      <c r="D37" s="204"/>
+      <c r="A37" s="175"/>
+      <c r="B37" s="211"/>
+      <c r="C37" s="206"/>
+      <c r="D37" s="206"/>
       <c r="E37" s="8"/>
       <c r="F37" s="9" t="s">
         <v>331</v>
@@ -19583,12 +19719,12 @@
       <c r="H37" s="120" t="s">
         <v>963</v>
       </c>
-      <c r="I37" s="155"/>
+      <c r="I37" s="151"/>
       <c r="J37" s="10"/>
       <c r="K37" s="10"/>
     </row>
     <row r="38" spans="1:15">
-      <c r="A38" s="177"/>
+      <c r="A38" s="175"/>
       <c r="B38" s="29" t="s">
         <v>328</v>
       </c>
@@ -19608,19 +19744,19 @@
       <c r="H38" s="16" t="s">
         <v>330</v>
       </c>
-      <c r="I38" s="155"/>
+      <c r="I38" s="151"/>
       <c r="J38" s="10"/>
       <c r="K38" s="10"/>
     </row>
     <row r="39" spans="1:15" ht="16.5" customHeight="1">
-      <c r="A39" s="177"/>
-      <c r="B39" s="205" t="s">
+      <c r="A39" s="175"/>
+      <c r="B39" s="209" t="s">
         <v>505</v>
       </c>
-      <c r="C39" s="202" t="s">
+      <c r="C39" s="204" t="s">
         <v>510</v>
       </c>
-      <c r="D39" s="202" t="s">
+      <c r="D39" s="204" t="s">
         <v>516</v>
       </c>
       <c r="E39" s="8" t="s">
@@ -19635,17 +19771,17 @@
       <c r="H39" s="10">
         <v>2</v>
       </c>
-      <c r="I39" s="155" t="s">
+      <c r="I39" s="151" t="s">
         <v>1331</v>
       </c>
       <c r="J39" s="10"/>
       <c r="K39" s="10"/>
     </row>
     <row r="40" spans="1:15" ht="16.5" customHeight="1">
-      <c r="A40" s="177"/>
-      <c r="B40" s="206"/>
-      <c r="C40" s="177"/>
-      <c r="D40" s="177"/>
+      <c r="A40" s="175"/>
+      <c r="B40" s="210"/>
+      <c r="C40" s="175"/>
+      <c r="D40" s="175"/>
       <c r="E40" s="17"/>
       <c r="F40" s="9" t="s">
         <v>304</v>
@@ -19656,17 +19792,17 @@
       <c r="H40" s="16">
         <v>1</v>
       </c>
-      <c r="I40" s="155">
+      <c r="I40" s="151">
         <v>44043</v>
       </c>
       <c r="J40" s="10"/>
       <c r="K40" s="10"/>
     </row>
     <row r="41" spans="1:15" ht="16.5" customHeight="1">
-      <c r="A41" s="177"/>
-      <c r="B41" s="206"/>
-      <c r="C41" s="177"/>
-      <c r="D41" s="177"/>
+      <c r="A41" s="175"/>
+      <c r="B41" s="210"/>
+      <c r="C41" s="175"/>
+      <c r="D41" s="175"/>
       <c r="E41" s="17"/>
       <c r="F41" s="9" t="s">
         <v>305</v>
@@ -19677,17 +19813,17 @@
       <c r="H41" s="16">
         <v>1</v>
       </c>
-      <c r="I41" s="155">
+      <c r="I41" s="151">
         <v>44043</v>
       </c>
       <c r="J41" s="10"/>
       <c r="K41" s="10"/>
     </row>
     <row r="42" spans="1:15">
-      <c r="A42" s="177"/>
-      <c r="B42" s="206"/>
-      <c r="C42" s="177"/>
-      <c r="D42" s="178"/>
+      <c r="A42" s="175"/>
+      <c r="B42" s="210"/>
+      <c r="C42" s="175"/>
+      <c r="D42" s="176"/>
       <c r="E42" s="17"/>
       <c r="F42" s="9" t="s">
         <v>305</v>
@@ -19698,17 +19834,17 @@
       <c r="H42" s="16">
         <v>2</v>
       </c>
-      <c r="I42" s="155">
+      <c r="I42" s="151">
         <v>44074</v>
       </c>
       <c r="J42" s="10"/>
       <c r="K42" s="10"/>
     </row>
     <row r="43" spans="1:15" ht="16.5" customHeight="1">
-      <c r="A43" s="177"/>
-      <c r="B43" s="206"/>
-      <c r="C43" s="177"/>
-      <c r="D43" s="202" t="s">
+      <c r="A43" s="175"/>
+      <c r="B43" s="210"/>
+      <c r="C43" s="175"/>
+      <c r="D43" s="204" t="s">
         <v>515</v>
       </c>
       <c r="E43" s="8"/>
@@ -19721,19 +19857,19 @@
       <c r="H43" s="10" t="s">
         <v>961</v>
       </c>
-      <c r="I43" s="155">
+      <c r="I43" s="151">
         <v>44043</v>
       </c>
       <c r="J43" s="10"/>
-      <c r="K43" s="208" t="s">
+      <c r="K43" s="200" t="s">
         <v>1164</v>
       </c>
     </row>
     <row r="44" spans="1:15">
-      <c r="A44" s="177"/>
-      <c r="B44" s="206"/>
-      <c r="C44" s="177"/>
-      <c r="D44" s="178"/>
+      <c r="A44" s="175"/>
+      <c r="B44" s="210"/>
+      <c r="C44" s="175"/>
+      <c r="D44" s="176"/>
       <c r="E44" s="8"/>
       <c r="F44" s="9" t="s">
         <v>289</v>
@@ -19744,17 +19880,17 @@
       <c r="H44" s="10" t="s">
         <v>961</v>
       </c>
-      <c r="I44" s="155">
+      <c r="I44" s="151">
         <v>44043</v>
       </c>
       <c r="J44" s="10"/>
-      <c r="K44" s="209"/>
+      <c r="K44" s="201"/>
     </row>
     <row r="45" spans="1:15">
-      <c r="A45" s="177"/>
-      <c r="B45" s="206"/>
-      <c r="C45" s="177"/>
-      <c r="D45" s="202" t="s">
+      <c r="A45" s="175"/>
+      <c r="B45" s="210"/>
+      <c r="C45" s="175"/>
+      <c r="D45" s="204" t="s">
         <v>514</v>
       </c>
       <c r="E45" s="8"/>
@@ -19767,15 +19903,15 @@
       <c r="H45" s="10" t="s">
         <v>963</v>
       </c>
-      <c r="I45" s="155"/>
+      <c r="I45" s="151"/>
       <c r="J45" s="10"/>
       <c r="K45" s="10"/>
     </row>
     <row r="46" spans="1:15">
-      <c r="A46" s="178"/>
-      <c r="B46" s="207"/>
-      <c r="C46" s="178"/>
-      <c r="D46" s="178"/>
+      <c r="A46" s="176"/>
+      <c r="B46" s="211"/>
+      <c r="C46" s="176"/>
+      <c r="D46" s="176"/>
       <c r="E46" s="8"/>
       <c r="F46" s="9" t="s">
         <v>301</v>
@@ -19786,38 +19922,38 @@
       <c r="H46" s="10" t="s">
         <v>963</v>
       </c>
-      <c r="I46" s="155"/>
+      <c r="I46" s="151"/>
       <c r="J46" s="10"/>
       <c r="K46" s="10"/>
     </row>
     <row r="48" spans="1:15">
-      <c r="H48" s="160" t="s">
+      <c r="H48" s="156" t="s">
         <v>1333</v>
       </c>
       <c r="I48">
         <f>COUNTA($I$2:$I$46)</f>
         <v>36</v>
       </c>
-      <c r="J48" s="161">
+      <c r="J48" s="157">
         <f>I48/$I$50</f>
         <v>0.8</v>
       </c>
     </row>
     <row r="49" spans="8:10">
-      <c r="H49" s="160" t="s">
+      <c r="H49" s="156" t="s">
         <v>1334</v>
       </c>
       <c r="I49">
         <f>COUNTBLANK($I$2:$I$46)</f>
         <v>9</v>
       </c>
-      <c r="J49" s="161">
+      <c r="J49" s="157">
         <f>I49/$I$50</f>
         <v>0.2</v>
       </c>
     </row>
     <row r="50" spans="8:10">
-      <c r="H50" s="160" t="s">
+      <c r="H50" s="156" t="s">
         <v>852</v>
       </c>
       <c r="I50">
@@ -19830,12 +19966,6 @@
     <sortCondition ref="P16:P28"/>
   </sortState>
   <mergeCells count="19">
-    <mergeCell ref="K43:K44"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="D16:D30"/>
-    <mergeCell ref="K30:K33"/>
-    <mergeCell ref="C2:C5"/>
-    <mergeCell ref="C6:C15"/>
     <mergeCell ref="A2:A46"/>
     <mergeCell ref="D43:D44"/>
     <mergeCell ref="D45:D46"/>
@@ -19849,6 +19979,12 @@
     <mergeCell ref="D36:D37"/>
     <mergeCell ref="D2:D4"/>
     <mergeCell ref="D6:D14"/>
+    <mergeCell ref="K43:K44"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="D16:D30"/>
+    <mergeCell ref="K30:K33"/>
+    <mergeCell ref="C2:C5"/>
+    <mergeCell ref="C6:C15"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19938,7 +20074,7 @@
         <v>1340</v>
       </c>
       <c r="Q32" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="33" spans="1:20">
@@ -19956,17 +20092,17 @@
       <c r="L34" t="s">
         <v>1348</v>
       </c>
-      <c r="P34" s="165" t="s">
-        <v>1354</v>
+      <c r="P34" s="161" t="s">
+        <v>1333</v>
       </c>
       <c r="Q34" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="S34" t="s">
+        <v>1358</v>
+      </c>
+      <c r="T34" t="s">
         <v>1359</v>
-      </c>
-      <c r="T34" t="s">
-        <v>1360</v>
       </c>
     </row>
     <row r="35" spans="1:20">
@@ -19980,10 +20116,10 @@
         <v>1343</v>
       </c>
       <c r="Q35" t="s">
+        <v>1357</v>
+      </c>
+      <c r="S35" t="s">
         <v>1358</v>
-      </c>
-      <c r="S35" t="s">
-        <v>1359</v>
       </c>
     </row>
     <row r="36" spans="1:20">
@@ -19998,7 +20134,7 @@
       <c r="A37" t="s">
         <v>1313</v>
       </c>
-      <c r="L37" s="163" t="s">
+      <c r="L37" s="159" t="s">
         <v>1345</v>
       </c>
     </row>
@@ -20050,7 +20186,7 @@
         <v>1319</v>
       </c>
       <c r="L43" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="44" spans="1:20">
@@ -20058,7 +20194,7 @@
         <v>1320</v>
       </c>
       <c r="L44" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="45" spans="1:20">
@@ -20138,11 +20274,11 @@
       <c r="B1" s="25" t="s">
         <v>327</v>
       </c>
-      <c r="E1" s="216" t="s">
+      <c r="E1" s="214" t="s">
         <v>724</v>
       </c>
-      <c r="F1" s="216"/>
-      <c r="G1" s="216"/>
+      <c r="F1" s="214"/>
+      <c r="G1" s="214"/>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="19" t="s">
@@ -20151,11 +20287,11 @@
       <c r="B2" s="19" t="s">
         <v>257</v>
       </c>
-      <c r="E2" s="217" t="s">
+      <c r="E2" s="215" t="s">
         <v>725</v>
       </c>
-      <c r="F2" s="217"/>
-      <c r="G2" s="217"/>
+      <c r="F2" s="215"/>
+      <c r="G2" s="215"/>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="19" t="s">
@@ -20172,10 +20308,10 @@
       <c r="B4" s="19" t="s">
         <v>259</v>
       </c>
-      <c r="E4" s="216" t="s">
+      <c r="E4" s="214" t="s">
         <v>722</v>
       </c>
-      <c r="F4" s="216"/>
+      <c r="F4" s="214"/>
       <c r="G4" s="25" t="s">
         <v>723</v>
       </c>
@@ -20187,16 +20323,16 @@
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="E5" s="215" t="s">
+      <c r="E5" s="213" t="s">
         <v>720</v>
       </c>
-      <c r="F5" s="215" t="s">
+      <c r="F5" s="213" t="s">
         <v>721</v>
       </c>
       <c r="G5" s="68" t="s">
         <v>747</v>
       </c>
-      <c r="H5" s="214" t="s">
+      <c r="H5" s="212" t="s">
         <v>748</v>
       </c>
       <c r="J5" t="s">
@@ -20207,12 +20343,12 @@
       <c r="A6" t="s">
         <v>261</v>
       </c>
-      <c r="E6" s="215"/>
-      <c r="F6" s="215"/>
+      <c r="E6" s="213"/>
+      <c r="F6" s="213"/>
       <c r="G6" s="68" t="s">
         <v>746</v>
       </c>
-      <c r="H6" s="215"/>
+      <c r="H6" s="213"/>
       <c r="J6" t="s">
         <v>729</v>
       </c>
@@ -20433,46 +20569,46 @@
     <col min="7" max="7" width="33" customWidth="1"/>
     <col min="8" max="8" width="38.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.140625" style="81" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="60.42578125" style="129" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="60.42578125" style="125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30">
-      <c r="A1" s="133" t="s">
+      <c r="A1" s="129" t="s">
         <v>846</v>
       </c>
-      <c r="B1" s="133" t="s">
+      <c r="B1" s="129" t="s">
         <v>1169</v>
       </c>
-      <c r="C1" s="133" t="s">
+      <c r="C1" s="129" t="s">
         <v>640</v>
       </c>
-      <c r="D1" s="133" t="s">
+      <c r="D1" s="129" t="s">
         <v>1172</v>
       </c>
-      <c r="E1" s="133" t="s">
+      <c r="E1" s="129" t="s">
         <v>1167</v>
       </c>
-      <c r="F1" s="133" t="s">
+      <c r="F1" s="129" t="s">
         <v>1168</v>
       </c>
-      <c r="G1" s="134" t="s">
+      <c r="G1" s="130" t="s">
         <v>1202</v>
       </c>
-      <c r="H1" s="134" t="s">
+      <c r="H1" s="130" t="s">
         <v>1255</v>
       </c>
-      <c r="I1" s="133" t="s">
+      <c r="I1" s="129" t="s">
         <v>1176</v>
       </c>
-      <c r="J1" s="133" t="s">
+      <c r="J1" s="129" t="s">
         <v>1182</v>
       </c>
-      <c r="K1" s="133" t="s">
+      <c r="K1" s="129" t="s">
         <v>1188</v>
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="132">
+      <c r="A2" s="128">
         <v>44028</v>
       </c>
       <c r="B2" s="8" t="s">
@@ -20500,12 +20636,12 @@
       <c r="J2" s="115" t="s">
         <v>892</v>
       </c>
-      <c r="K2" s="218" t="s">
+      <c r="K2" s="216" t="s">
         <v>1194</v>
       </c>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="132">
+      <c r="A3" s="128">
         <v>44028</v>
       </c>
       <c r="B3" s="8" t="s">
@@ -20533,10 +20669,10 @@
       <c r="J3" s="115" t="s">
         <v>892</v>
       </c>
-      <c r="K3" s="219"/>
+      <c r="K3" s="217"/>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="132">
+      <c r="A4" s="128">
         <v>44029</v>
       </c>
       <c r="B4" s="8" t="s">
@@ -20562,10 +20698,10 @@
       <c r="J4" s="115" t="s">
         <v>892</v>
       </c>
-      <c r="K4" s="219"/>
+      <c r="K4" s="217"/>
     </row>
     <row r="5" spans="1:11" ht="45">
-      <c r="A5" s="132">
+      <c r="A5" s="128">
         <v>44029</v>
       </c>
       <c r="B5" s="8" t="s">
@@ -20591,10 +20727,10 @@
       <c r="J5" s="115" t="s">
         <v>892</v>
       </c>
-      <c r="K5" s="220"/>
+      <c r="K5" s="218"/>
     </row>
     <row r="6" spans="1:11" ht="60">
-      <c r="A6" s="132">
+      <c r="A6" s="128">
         <v>44029</v>
       </c>
       <c r="B6" s="8" t="s">
@@ -20625,7 +20761,7 @@
       </c>
     </row>
     <row r="7" spans="1:11" ht="60">
-      <c r="A7" s="132">
+      <c r="A7" s="128">
         <v>44029</v>
       </c>
       <c r="B7" s="8" t="s">
@@ -20654,7 +20790,7 @@
       <c r="K7" s="8"/>
     </row>
     <row r="8" spans="1:11" ht="60">
-      <c r="A8" s="132">
+      <c r="A8" s="128">
         <v>44029</v>
       </c>
       <c r="B8" s="8" t="s">
@@ -20687,7 +20823,7 @@
       </c>
     </row>
     <row r="9" spans="1:11" ht="60">
-      <c r="A9" s="132">
+      <c r="A9" s="128">
         <v>44029</v>
       </c>
       <c r="B9" s="8" t="s">
@@ -20702,13 +20838,13 @@
       <c r="E9" s="18" t="s">
         <v>1191</v>
       </c>
-      <c r="F9" s="142" t="s">
+      <c r="F9" s="138" t="s">
         <v>1243</v>
       </c>
-      <c r="G9" s="143" t="s">
+      <c r="G9" s="139" t="s">
         <v>1211</v>
       </c>
-      <c r="H9" s="140" t="s">
+      <c r="H9" s="136" t="s">
         <v>1241</v>
       </c>
       <c r="I9" s="115" t="s">
@@ -20720,7 +20856,7 @@
       </c>
     </row>
     <row r="10" spans="1:11" ht="64.5" customHeight="1">
-      <c r="A10" s="139" t="s">
+      <c r="A10" s="135" t="s">
         <v>1227</v>
       </c>
       <c r="B10" s="8" t="s">
@@ -20751,7 +20887,7 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="45">
-      <c r="A11" s="137" t="s">
+      <c r="A11" s="133" t="s">
         <v>1218</v>
       </c>
       <c r="B11" s="8" t="s">
@@ -20769,10 +20905,10 @@
       <c r="F11" s="115" t="s">
         <v>1198</v>
       </c>
-      <c r="G11" s="136" t="s">
+      <c r="G11" s="132" t="s">
         <v>1245</v>
       </c>
-      <c r="H11" s="136"/>
+      <c r="H11" s="132"/>
       <c r="I11" s="115" t="s">
         <v>1217</v>
       </c>
@@ -20820,114 +20956,114 @@
       </c>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="129"/>
-      <c r="B14" s="129"/>
-      <c r="C14" s="129"/>
-      <c r="D14" s="129"/>
-      <c r="E14" s="135" t="s">
+      <c r="A14" s="125"/>
+      <c r="B14" s="125"/>
+      <c r="C14" s="125"/>
+      <c r="D14" s="125"/>
+      <c r="E14" s="131" t="s">
         <v>1216</v>
       </c>
-      <c r="F14" s="130"/>
-      <c r="G14" s="135" t="s">
+      <c r="F14" s="126"/>
+      <c r="G14" s="131" t="s">
         <v>1254</v>
       </c>
-      <c r="H14" s="129"/>
-      <c r="I14" s="130"/>
-      <c r="J14" s="129"/>
+      <c r="H14" s="125"/>
+      <c r="I14" s="126"/>
+      <c r="J14" s="125"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="129"/>
-      <c r="B15" s="129"/>
-      <c r="C15" s="129"/>
-      <c r="D15" s="129"/>
-      <c r="E15" s="129"/>
-      <c r="F15" s="130"/>
-      <c r="G15" s="129" t="s">
+      <c r="A15" s="125"/>
+      <c r="B15" s="125"/>
+      <c r="C15" s="125"/>
+      <c r="D15" s="125"/>
+      <c r="E15" s="125"/>
+      <c r="F15" s="126"/>
+      <c r="G15" s="125" t="s">
         <v>1233</v>
       </c>
-      <c r="H15" s="129" t="s">
+      <c r="H15" s="125" t="s">
         <v>1234</v>
       </c>
-      <c r="I15" s="130"/>
-      <c r="J15" s="129"/>
+      <c r="I15" s="126"/>
+      <c r="J15" s="125"/>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="129"/>
-      <c r="B16" s="129"/>
-      <c r="C16" s="129"/>
-      <c r="D16" s="129"/>
-      <c r="E16" s="129"/>
-      <c r="G16" s="129"/>
-      <c r="H16" s="129"/>
-      <c r="I16" s="130"/>
-      <c r="J16" s="129"/>
+      <c r="A16" s="125"/>
+      <c r="B16" s="125"/>
+      <c r="C16" s="125"/>
+      <c r="D16" s="125"/>
+      <c r="E16" s="125"/>
+      <c r="G16" s="125"/>
+      <c r="H16" s="125"/>
+      <c r="I16" s="126"/>
+      <c r="J16" s="125"/>
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1">
-      <c r="A17" s="129"/>
-      <c r="B17" s="129"/>
-      <c r="C17" s="129"/>
-      <c r="D17" s="129"/>
-      <c r="E17" s="129"/>
-      <c r="F17" s="140"/>
+      <c r="A17" s="125"/>
+      <c r="B17" s="125"/>
+      <c r="C17" s="125"/>
+      <c r="D17" s="125"/>
+      <c r="E17" s="125"/>
+      <c r="F17" s="136"/>
       <c r="G17" s="8" t="s">
         <v>1256</v>
       </c>
-      <c r="H17" s="124" t="s">
+      <c r="H17" s="122" t="s">
         <v>1257</v>
       </c>
-      <c r="I17" s="130"/>
-      <c r="J17" s="129"/>
+      <c r="I17" s="126"/>
+      <c r="J17" s="125"/>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="129"/>
-      <c r="B18" s="129"/>
-      <c r="C18" s="129"/>
-      <c r="D18" s="129"/>
-      <c r="E18" s="129"/>
-      <c r="F18" s="221" t="s">
+      <c r="A18" s="125"/>
+      <c r="B18" s="125"/>
+      <c r="C18" s="125"/>
+      <c r="D18" s="125"/>
+      <c r="E18" s="125"/>
+      <c r="F18" s="219" t="s">
         <v>1239</v>
       </c>
       <c r="G18" s="8" t="s">
         <v>1236</v>
       </c>
-      <c r="H18" s="124" t="s">
+      <c r="H18" s="122" t="s">
         <v>1251</v>
       </c>
-      <c r="I18" s="130"/>
-      <c r="J18" s="129"/>
+      <c r="I18" s="126"/>
+      <c r="J18" s="125"/>
     </row>
     <row r="19" spans="1:10">
-      <c r="F19" s="221"/>
-      <c r="G19" s="149" t="s">
+      <c r="F19" s="219"/>
+      <c r="G19" s="145" t="s">
         <v>1235</v>
       </c>
-      <c r="H19" s="150" t="s">
+      <c r="H19" s="146" t="s">
         <v>1252</v>
       </c>
     </row>
     <row r="20" spans="1:10">
-      <c r="F20" s="221"/>
+      <c r="F20" s="219"/>
       <c r="G20" s="8" t="s">
         <v>1237</v>
       </c>
-      <c r="H20" s="124" t="s">
+      <c r="H20" s="122" t="s">
         <v>1251</v>
       </c>
     </row>
     <row r="21" spans="1:10">
-      <c r="F21" s="221"/>
+      <c r="F21" s="219"/>
       <c r="G21" s="8" t="s">
         <v>1238</v>
       </c>
-      <c r="H21" s="144" t="s">
+      <c r="H21" s="140" t="s">
         <v>1253</v>
       </c>
     </row>
     <row r="22" spans="1:10">
-      <c r="G22" s="141"/>
+      <c r="G22" s="137"/>
     </row>
     <row r="23" spans="1:10">
-      <c r="F23" s="138" t="s">
+      <c r="F23" s="134" t="s">
         <v>1250</v>
       </c>
       <c r="G23" t="s">
@@ -20938,7 +21074,7 @@
       </c>
     </row>
     <row r="24" spans="1:10">
-      <c r="F24" s="138" t="s">
+      <c r="F24" s="134" t="s">
         <v>1206</v>
       </c>
       <c r="G24" s="81">
@@ -20949,7 +21085,7 @@
       </c>
     </row>
     <row r="25" spans="1:10">
-      <c r="F25" s="138" t="s">
+      <c r="F25" s="134" t="s">
         <v>1206</v>
       </c>
       <c r="G25" s="81">
@@ -20960,7 +21096,7 @@
       </c>
     </row>
     <row r="26" spans="1:10">
-      <c r="F26" s="138" t="s">
+      <c r="F26" s="134" t="s">
         <v>1197</v>
       </c>
       <c r="G26" s="81">
@@ -20971,7 +21107,7 @@
       </c>
     </row>
     <row r="27" spans="1:10">
-      <c r="F27" s="138" t="s">
+      <c r="F27" s="134" t="s">
         <v>1197</v>
       </c>
       <c r="G27" s="81">
@@ -20982,7 +21118,7 @@
       </c>
     </row>
     <row r="28" spans="1:10">
-      <c r="F28" s="138" t="s">
+      <c r="F28" s="134" t="s">
         <v>1197</v>
       </c>
       <c r="G28" s="81">
@@ -20993,7 +21129,7 @@
       </c>
     </row>
     <row r="29" spans="1:10">
-      <c r="F29" s="138" t="s">
+      <c r="F29" s="134" t="s">
         <v>1198</v>
       </c>
       <c r="G29" s="81">
@@ -21004,7 +21140,7 @@
       </c>
     </row>
     <row r="30" spans="1:10">
-      <c r="F30" s="138" t="s">
+      <c r="F30" s="134" t="s">
         <v>1198</v>
       </c>
       <c r="G30" s="81">
@@ -21015,7 +21151,7 @@
       </c>
     </row>
     <row r="31" spans="1:10">
-      <c r="F31" s="138" t="s">
+      <c r="F31" s="134" t="s">
         <v>1198</v>
       </c>
       <c r="G31" s="81">
@@ -21026,7 +21162,7 @@
       </c>
     </row>
     <row r="32" spans="1:10">
-      <c r="F32" s="138" t="s">
+      <c r="F32" s="134" t="s">
         <v>1200</v>
       </c>
       <c r="G32" s="81">
@@ -21037,7 +21173,7 @@
       </c>
     </row>
     <row r="33" spans="6:8">
-      <c r="F33" s="138" t="s">
+      <c r="F33" s="134" t="s">
         <v>1200</v>
       </c>
       <c r="G33" s="81">
@@ -21060,7 +21196,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.7109375" bestFit="1" customWidth="1"/>
@@ -21163,1179 +21299,1453 @@
       </c>
       <c r="C9" s="19"/>
     </row>
+    <row r="12" spans="1:3">
+      <c r="C12" s="7" t="s">
+        <v>1363</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="C4" r:id="rId1" xr:uid="{00000000-0004-0000-0A00-000000000000}"/>
     <hyperlink ref="C6" r:id="rId2" xr:uid="{00000000-0004-0000-0A00-000001000000}"/>
+    <hyperlink ref="C12" r:id="rId3" xr:uid="{3E7AA98A-DA0C-4CAA-9E1E-F9DAABC6C48F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId4"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37379847-1933-4532-BA71-36026569AE7D}">
-  <dimension ref="A1:C113"/>
+  <dimension ref="A1:H115"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.85546875" customWidth="1"/>
-    <col min="3" max="3" width="172" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" customWidth="1"/>
+    <col min="3" max="3" width="163.7109375" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="74.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="122" t="s">
+    <row r="1" spans="1:8">
+      <c r="A1" s="220" t="s">
         <v>971</v>
       </c>
-      <c r="B1" s="123" t="s">
+      <c r="B1" s="221" t="s">
         <v>972</v>
       </c>
-      <c r="C1" s="123" t="s">
+      <c r="C1" s="221" t="s">
         <v>973</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="19" t="s">
+      <c r="E1" s="220" t="s">
+        <v>971</v>
+      </c>
+      <c r="F1" s="221" t="s">
+        <v>972</v>
+      </c>
+      <c r="G1" s="221" t="s">
+        <v>973</v>
+      </c>
+      <c r="H1" s="221" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="8" t="s">
         <v>758</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="8" t="s">
         <v>974</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="8" t="s">
         <v>975</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="19" t="s">
+      <c r="E2" s="164" t="s">
+        <v>1407</v>
+      </c>
+      <c r="F2" s="164" t="s">
+        <v>1365</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>1386</v>
+      </c>
+      <c r="H2" s="164" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="8" t="s">
         <v>758</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="8" t="s">
         <v>976</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="8" t="s">
         <v>977</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="19" t="s">
+      <c r="E3" s="164" t="s">
+        <v>1407</v>
+      </c>
+      <c r="F3" s="164" t="s">
+        <v>1366</v>
+      </c>
+      <c r="G3" s="19" t="s">
+        <v>1387</v>
+      </c>
+      <c r="H3" s="164" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="8" t="s">
         <v>758</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="8" t="s">
         <v>978</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="8" t="s">
         <v>979</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="19" t="s">
+      <c r="E4" s="164" t="s">
+        <v>1407</v>
+      </c>
+      <c r="F4" s="164" t="s">
+        <v>1367</v>
+      </c>
+      <c r="G4" s="19" t="s">
+        <v>1388</v>
+      </c>
+      <c r="H4" s="164" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="8" t="s">
         <v>758</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="8" t="s">
         <v>980</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="8" t="s">
         <v>981</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="19" t="s">
+      <c r="E5" s="164" t="s">
+        <v>1407</v>
+      </c>
+      <c r="F5" s="164" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>1389</v>
+      </c>
+      <c r="H5" s="164" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="8" t="s">
         <v>758</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="8" t="s">
         <v>982</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="8" t="s">
         <v>983</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="19" t="s">
+      <c r="E6" s="164" t="s">
+        <v>1407</v>
+      </c>
+      <c r="F6" s="164" t="s">
+        <v>1369</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>1390</v>
+      </c>
+      <c r="H6" s="164" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="8" t="s">
         <v>758</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="8" t="s">
         <v>984</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="8" t="s">
         <v>985</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="19" t="s">
+      <c r="E7" s="164" t="s">
+        <v>1407</v>
+      </c>
+      <c r="F7" s="164" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>1391</v>
+      </c>
+      <c r="H7" s="164" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="223" t="s">
         <v>758</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="223" t="s">
         <v>986</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="223" t="s">
         <v>987</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="19" t="s">
+      <c r="E8" s="164" t="s">
+        <v>1407</v>
+      </c>
+      <c r="F8" s="164" t="s">
+        <v>1371</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>1392</v>
+      </c>
+      <c r="H8" s="164" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="8" t="s">
         <v>758</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="8" t="s">
         <v>988</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="8" t="s">
         <v>989</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="19" t="s">
+      <c r="E9" s="164" t="s">
+        <v>1407</v>
+      </c>
+      <c r="F9" s="164" t="s">
+        <v>1372</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>1393</v>
+      </c>
+      <c r="H9" s="164" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="8" t="s">
         <v>758</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="8" t="s">
         <v>990</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="8" t="s">
         <v>991</v>
       </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="19" t="s">
+      <c r="E10" s="164" t="s">
+        <v>1407</v>
+      </c>
+      <c r="F10" s="164" t="s">
+        <v>1373</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>1394</v>
+      </c>
+      <c r="H10" s="164" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="8" t="s">
         <v>758</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="8" t="s">
         <v>992</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="8" t="s">
         <v>993</v>
       </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="19" t="s">
+      <c r="E11" s="164" t="s">
+        <v>1407</v>
+      </c>
+      <c r="F11" s="164" t="s">
+        <v>1374</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>1395</v>
+      </c>
+      <c r="H11" s="164" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="8" t="s">
         <v>758</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="8" t="s">
         <v>994</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="8" t="s">
         <v>995</v>
       </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="19" t="s">
+      <c r="E12" s="164" t="s">
+        <v>1407</v>
+      </c>
+      <c r="F12" s="164" t="s">
+        <v>1375</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>1396</v>
+      </c>
+      <c r="H12" s="164" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="8" t="s">
         <v>758</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="8" t="s">
         <v>996</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="8" t="s">
         <v>997</v>
       </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="19" t="s">
+      <c r="E13" s="164" t="s">
+        <v>1407</v>
+      </c>
+      <c r="F13" s="164" t="s">
+        <v>1376</v>
+      </c>
+      <c r="G13" s="19" t="s">
+        <v>1397</v>
+      </c>
+      <c r="H13" s="164" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="8" t="s">
         <v>758</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="8" t="s">
         <v>998</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="8" t="s">
         <v>999</v>
       </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="19" t="s">
+      <c r="E14" s="164" t="s">
+        <v>1407</v>
+      </c>
+      <c r="F14" s="164" t="s">
+        <v>1377</v>
+      </c>
+      <c r="G14" s="19" t="s">
+        <v>1398</v>
+      </c>
+      <c r="H14" s="164" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="8" t="s">
         <v>758</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="8" t="s">
         <v>1000</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="8" t="s">
         <v>1001</v>
       </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="19" t="s">
+      <c r="E15" s="164" t="s">
+        <v>1407</v>
+      </c>
+      <c r="F15" s="164" t="s">
+        <v>1378</v>
+      </c>
+      <c r="G15" s="19" t="s">
+        <v>1399</v>
+      </c>
+      <c r="H15" s="164" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="8" t="s">
         <v>758</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="8" t="s">
         <v>1002</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="8" t="s">
         <v>1003</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="19" t="s">
+      <c r="E16" s="164" t="s">
+        <v>1407</v>
+      </c>
+      <c r="F16" s="164" t="s">
+        <v>1379</v>
+      </c>
+      <c r="G16" s="19" t="s">
+        <v>1400</v>
+      </c>
+      <c r="H16" s="164" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="8" t="s">
         <v>758</v>
       </c>
-      <c r="B17" s="19" t="s">
+      <c r="B17" s="8" t="s">
         <v>1004</v>
       </c>
-      <c r="C17" s="19" t="s">
+      <c r="C17" s="8" t="s">
         <v>1005</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="19" t="s">
+      <c r="E17" s="164" t="s">
+        <v>1407</v>
+      </c>
+      <c r="F17" s="164" t="s">
+        <v>1380</v>
+      </c>
+      <c r="G17" s="19" t="s">
+        <v>1401</v>
+      </c>
+      <c r="H17" s="164" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="8" t="s">
         <v>758</v>
       </c>
-      <c r="B18" s="19" t="s">
+      <c r="B18" s="8" t="s">
         <v>1006</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="C18" s="8" t="s">
         <v>1007</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="19" t="s">
+      <c r="E18" s="164" t="s">
+        <v>1407</v>
+      </c>
+      <c r="F18" s="164" t="s">
+        <v>1381</v>
+      </c>
+      <c r="G18" s="19" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H18" s="164" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="8" t="s">
         <v>758</v>
       </c>
-      <c r="B19" s="19" t="s">
+      <c r="B19" s="8" t="s">
         <v>1008</v>
       </c>
-      <c r="C19" s="19" t="s">
+      <c r="C19" s="8" t="s">
         <v>1009</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="19" t="s">
+      <c r="E19" s="163" t="s">
+        <v>1407</v>
+      </c>
+      <c r="F19" s="163" t="s">
+        <v>1382</v>
+      </c>
+      <c r="G19" s="222" t="s">
+        <v>1403</v>
+      </c>
+      <c r="H19" s="163" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="8" t="s">
         <v>758</v>
       </c>
-      <c r="B20" s="19" t="s">
+      <c r="B20" s="8" t="s">
         <v>1010</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C20" s="8" t="s">
         <v>1011</v>
       </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="19" t="s">
+      <c r="E20" s="164" t="s">
+        <v>1407</v>
+      </c>
+      <c r="F20" s="164" t="s">
+        <v>1383</v>
+      </c>
+      <c r="G20" s="19" t="s">
+        <v>1404</v>
+      </c>
+      <c r="H20" s="164" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="8" t="s">
         <v>758</v>
       </c>
-      <c r="B21" s="19" t="s">
+      <c r="B21" s="8" t="s">
         <v>1012</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="C21" s="8" t="s">
         <v>1013</v>
       </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="19" t="s">
+      <c r="E21" s="164" t="s">
+        <v>1407</v>
+      </c>
+      <c r="F21" s="164" t="s">
+        <v>1384</v>
+      </c>
+      <c r="G21" s="19" t="s">
+        <v>1405</v>
+      </c>
+      <c r="H21" s="164" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="8" t="s">
         <v>758</v>
       </c>
-      <c r="B22" s="19" t="s">
+      <c r="B22" s="8" t="s">
         <v>1014</v>
       </c>
-      <c r="C22" s="19" t="s">
+      <c r="C22" s="8" t="s">
         <v>1015</v>
       </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="19" t="s">
+      <c r="E22" s="164" t="s">
+        <v>1407</v>
+      </c>
+      <c r="F22" s="164" t="s">
+        <v>1385</v>
+      </c>
+      <c r="G22" s="19" t="s">
+        <v>1406</v>
+      </c>
+      <c r="H22" s="164" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="8" t="s">
         <v>758</v>
       </c>
-      <c r="B23" s="19" t="s">
+      <c r="B23" s="8" t="s">
         <v>1016</v>
       </c>
-      <c r="C23" s="19" t="s">
+      <c r="C23" s="8" t="s">
         <v>1017</v>
       </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="19" t="s">
+      <c r="F23" s="81"/>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="8" t="s">
         <v>758</v>
       </c>
-      <c r="B24" s="19" t="s">
+      <c r="B24" s="8" t="s">
         <v>1018</v>
       </c>
-      <c r="C24" s="19" t="s">
+      <c r="C24" s="8" t="s">
         <v>1019</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="19" t="s">
+    <row r="25" spans="1:8">
+      <c r="A25" s="8" t="s">
         <v>758</v>
       </c>
-      <c r="B25" s="19" t="s">
+      <c r="B25" s="8" t="s">
         <v>1020</v>
       </c>
-      <c r="C25" s="19" t="s">
+      <c r="C25" s="8" t="s">
         <v>1021</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="19" t="s">
+    <row r="26" spans="1:8">
+      <c r="A26" s="8" t="s">
         <v>758</v>
       </c>
-      <c r="B26" s="19" t="s">
+      <c r="B26" s="8" t="s">
         <v>1022</v>
       </c>
-      <c r="C26" s="19" t="s">
+      <c r="C26" s="8" t="s">
         <v>1023</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="19" t="s">
+    <row r="27" spans="1:8">
+      <c r="A27" s="8" t="s">
         <v>758</v>
       </c>
-      <c r="B27" s="19" t="s">
+      <c r="B27" s="8" t="s">
         <v>837</v>
       </c>
-      <c r="C27" s="19" t="s">
+      <c r="C27" s="8" t="s">
         <v>1024</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="19" t="s">
+    <row r="28" spans="1:8">
+      <c r="A28" s="8" t="s">
         <v>758</v>
       </c>
-      <c r="B28" s="19" t="s">
+      <c r="B28" s="8" t="s">
         <v>1025</v>
       </c>
-      <c r="C28" s="19" t="s">
+      <c r="C28" s="8" t="s">
         <v>1026</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="19" t="s">
+    <row r="29" spans="1:8">
+      <c r="A29" s="8" t="s">
         <v>758</v>
       </c>
-      <c r="B29" s="19" t="s">
+      <c r="B29" s="8" t="s">
         <v>1027</v>
       </c>
-      <c r="C29" s="19" t="s">
+      <c r="C29" s="8" t="s">
         <v>1028</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="19" t="s">
+    <row r="30" spans="1:8">
+      <c r="A30" s="8" t="s">
         <v>758</v>
       </c>
-      <c r="B30" s="19" t="s">
+      <c r="B30" s="8" t="s">
         <v>1029</v>
       </c>
-      <c r="C30" s="19" t="s">
+      <c r="C30" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="19" t="s">
+    <row r="31" spans="1:8">
+      <c r="A31" s="8" t="s">
         <v>758</v>
       </c>
-      <c r="B31" s="19" t="s">
+      <c r="B31" s="8" t="s">
         <v>1031</v>
       </c>
-      <c r="C31" s="19" t="s">
+      <c r="C31" s="8" t="s">
         <v>1032</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="19" t="s">
+    <row r="32" spans="1:8">
+      <c r="A32" s="8" t="s">
         <v>758</v>
       </c>
-      <c r="B32" s="19" t="s">
+      <c r="B32" s="8" t="s">
         <v>1033</v>
       </c>
-      <c r="C32" s="19" t="s">
+      <c r="C32" s="8" t="s">
         <v>1034</v>
       </c>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="19" t="s">
+      <c r="A33" s="8" t="s">
         <v>758</v>
       </c>
-      <c r="B33" s="19" t="s">
+      <c r="B33" s="8" t="s">
         <v>1035</v>
       </c>
-      <c r="C33" s="19" t="s">
+      <c r="C33" s="8" t="s">
         <v>1036</v>
       </c>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="19" t="s">
+      <c r="A34" s="8" t="s">
         <v>758</v>
       </c>
-      <c r="B34" s="19" t="s">
+      <c r="B34" s="8" t="s">
         <v>835</v>
       </c>
-      <c r="C34" s="19" t="s">
+      <c r="C34" s="8" t="s">
         <v>1037</v>
       </c>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="19" t="s">
+      <c r="A35" s="8" t="s">
         <v>758</v>
       </c>
-      <c r="B35" s="19" t="s">
+      <c r="B35" s="8" t="s">
         <v>1038</v>
       </c>
-      <c r="C35" s="19" t="s">
+      <c r="C35" s="8" t="s">
         <v>1039</v>
       </c>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="19" t="s">
+      <c r="A36" s="8" t="s">
         <v>758</v>
       </c>
-      <c r="B36" s="19" t="s">
+      <c r="B36" s="8" t="s">
         <v>1040</v>
       </c>
-      <c r="C36" s="19" t="s">
+      <c r="C36" s="8" t="s">
         <v>1041</v>
       </c>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37" s="19" t="s">
+      <c r="A37" s="8" t="s">
         <v>758</v>
       </c>
-      <c r="B37" s="19" t="s">
+      <c r="B37" s="8" t="s">
         <v>948</v>
       </c>
-      <c r="C37" s="19" t="s">
+      <c r="C37" s="8" t="s">
         <v>1042</v>
       </c>
     </row>
     <row r="38" spans="1:3">
-      <c r="A38" s="19" t="s">
+      <c r="A38" s="8" t="s">
         <v>758</v>
       </c>
-      <c r="B38" s="19" t="s">
+      <c r="B38" s="8" t="s">
         <v>833</v>
       </c>
-      <c r="C38" s="19" t="s">
+      <c r="C38" s="8" t="s">
         <v>1043</v>
       </c>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="19" t="s">
+      <c r="A39" s="8" t="s">
         <v>758</v>
       </c>
-      <c r="B39" s="19" t="s">
+      <c r="B39" s="8" t="s">
         <v>1044</v>
       </c>
-      <c r="C39" s="19" t="s">
+      <c r="C39" s="8" t="s">
         <v>1045</v>
       </c>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="19" t="s">
+      <c r="A40" s="8" t="s">
         <v>758</v>
       </c>
-      <c r="B40" s="19" t="s">
+      <c r="B40" s="8" t="s">
         <v>836</v>
       </c>
-      <c r="C40" s="19" t="s">
+      <c r="C40" s="8" t="s">
         <v>1046</v>
       </c>
     </row>
     <row r="41" spans="1:3">
-      <c r="A41" s="19" t="s">
+      <c r="A41" s="8" t="s">
         <v>758</v>
       </c>
-      <c r="B41" s="19" t="s">
+      <c r="B41" s="8" t="s">
         <v>1047</v>
       </c>
-      <c r="C41" s="19" t="s">
+      <c r="C41" s="8" t="s">
         <v>1048</v>
       </c>
     </row>
     <row r="42" spans="1:3">
-      <c r="A42" s="19" t="s">
+      <c r="A42" s="8" t="s">
         <v>758</v>
       </c>
-      <c r="B42" s="19" t="s">
+      <c r="B42" s="8" t="s">
         <v>1049</v>
       </c>
-      <c r="C42" s="19" t="s">
+      <c r="C42" s="8" t="s">
         <v>1050</v>
       </c>
     </row>
     <row r="43" spans="1:3">
-      <c r="A43" s="124" t="s">
+      <c r="A43" s="122" t="s">
         <v>385</v>
       </c>
-      <c r="B43" s="124" t="s">
+      <c r="B43" s="122" t="s">
         <v>1051</v>
       </c>
-      <c r="C43" s="124" t="s">
+      <c r="C43" s="122" t="s">
         <v>1052</v>
       </c>
     </row>
     <row r="44" spans="1:3">
-      <c r="A44" s="124" t="s">
+      <c r="A44" s="122" t="s">
         <v>385</v>
       </c>
-      <c r="B44" s="124" t="s">
+      <c r="B44" s="122" t="s">
         <v>1053</v>
       </c>
-      <c r="C44" s="124" t="s">
+      <c r="C44" s="122" t="s">
         <v>975</v>
       </c>
     </row>
     <row r="45" spans="1:3">
-      <c r="A45" s="124" t="s">
+      <c r="A45" s="122" t="s">
         <v>385</v>
       </c>
-      <c r="B45" s="124" t="s">
+      <c r="B45" s="122" t="s">
         <v>1054</v>
       </c>
-      <c r="C45" s="124" t="s">
+      <c r="C45" s="122" t="s">
         <v>1055</v>
       </c>
     </row>
     <row r="46" spans="1:3">
-      <c r="A46" s="124" t="s">
+      <c r="A46" s="122" t="s">
         <v>385</v>
       </c>
-      <c r="B46" s="124" t="s">
+      <c r="B46" s="122" t="s">
         <v>619</v>
       </c>
-      <c r="C46" s="124" t="s">
+      <c r="C46" s="122" t="s">
         <v>1056</v>
       </c>
     </row>
     <row r="47" spans="1:3">
-      <c r="A47" s="124" t="s">
+      <c r="A47" s="122" t="s">
         <v>385</v>
       </c>
-      <c r="B47" s="124" t="s">
+      <c r="B47" s="122" t="s">
         <v>617</v>
       </c>
-      <c r="C47" s="124" t="s">
+      <c r="C47" s="122" t="s">
         <v>1057</v>
       </c>
     </row>
     <row r="48" spans="1:3">
-      <c r="A48" s="124" t="s">
+      <c r="A48" s="122" t="s">
         <v>385</v>
       </c>
-      <c r="B48" s="124" t="s">
+      <c r="B48" s="122" t="s">
         <v>1058</v>
       </c>
-      <c r="C48" s="124" t="s">
+      <c r="C48" s="122" t="s">
         <v>1059</v>
       </c>
     </row>
     <row r="49" spans="1:3">
-      <c r="A49" s="124" t="s">
+      <c r="A49" s="122" t="s">
         <v>385</v>
       </c>
-      <c r="B49" s="124" t="s">
+      <c r="B49" s="122" t="s">
         <v>1060</v>
       </c>
-      <c r="C49" s="124" t="s">
+      <c r="C49" s="122" t="s">
         <v>1061</v>
       </c>
     </row>
     <row r="50" spans="1:3">
-      <c r="A50" s="124" t="s">
+      <c r="A50" s="122" t="s">
         <v>385</v>
       </c>
-      <c r="B50" s="124" t="s">
+      <c r="B50" s="122" t="s">
         <v>1062</v>
       </c>
-      <c r="C50" s="124" t="s">
+      <c r="C50" s="122" t="s">
         <v>1063</v>
       </c>
     </row>
     <row r="51" spans="1:3">
-      <c r="A51" s="124" t="s">
+      <c r="A51" s="122" t="s">
         <v>385</v>
       </c>
-      <c r="B51" s="124" t="s">
+      <c r="B51" s="122" t="s">
         <v>1064</v>
       </c>
-      <c r="C51" s="124" t="s">
+      <c r="C51" s="122" t="s">
         <v>1065</v>
       </c>
     </row>
     <row r="52" spans="1:3">
-      <c r="A52" s="124" t="s">
+      <c r="A52" s="122" t="s">
         <v>385</v>
       </c>
-      <c r="B52" s="124" t="s">
+      <c r="B52" s="122" t="s">
         <v>1066</v>
       </c>
-      <c r="C52" s="124" t="s">
+      <c r="C52" s="122" t="s">
         <v>1067</v>
       </c>
     </row>
     <row r="53" spans="1:3">
-      <c r="A53" s="124" t="s">
+      <c r="A53" s="122" t="s">
         <v>385</v>
       </c>
-      <c r="B53" s="124" t="s">
+      <c r="B53" s="122" t="s">
         <v>1068</v>
       </c>
-      <c r="C53" s="19" t="s">
+      <c r="C53" s="8" t="s">
         <v>1069</v>
       </c>
     </row>
     <row r="54" spans="1:3">
-      <c r="A54" s="124" t="s">
+      <c r="A54" s="122" t="s">
         <v>385</v>
       </c>
-      <c r="B54" s="124" t="s">
+      <c r="B54" s="122" t="s">
         <v>1070</v>
       </c>
-      <c r="C54" s="19" t="s">
+      <c r="C54" s="8" t="s">
         <v>1071</v>
       </c>
     </row>
     <row r="55" spans="1:3">
-      <c r="A55" s="124" t="s">
+      <c r="A55" s="122" t="s">
         <v>385</v>
       </c>
-      <c r="B55" s="19" t="s">
+      <c r="B55" s="8" t="s">
         <v>1072</v>
       </c>
-      <c r="C55" s="19" t="s">
+      <c r="C55" s="8" t="s">
         <v>1073</v>
       </c>
     </row>
     <row r="56" spans="1:3">
-      <c r="A56" s="124" t="s">
+      <c r="A56" s="122" t="s">
         <v>385</v>
       </c>
-      <c r="B56" s="19" t="s">
+      <c r="B56" s="8" t="s">
         <v>1074</v>
       </c>
-      <c r="C56" s="19" t="s">
+      <c r="C56" s="8" t="s">
         <v>1075</v>
       </c>
     </row>
     <row r="57" spans="1:3">
-      <c r="A57" s="124" t="s">
+      <c r="A57" s="122" t="s">
         <v>385</v>
       </c>
-      <c r="B57" s="19" t="s">
+      <c r="B57" s="8" t="s">
         <v>1076</v>
       </c>
-      <c r="C57" s="19" t="s">
+      <c r="C57" s="8" t="s">
         <v>1077</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="30">
-      <c r="A58" s="124" t="s">
+      <c r="A58" s="122" t="s">
         <v>385</v>
       </c>
-      <c r="B58" s="19" t="s">
+      <c r="B58" s="8" t="s">
         <v>1078</v>
       </c>
-      <c r="C58" s="23" t="s">
+      <c r="C58" s="18" t="s">
         <v>1079</v>
       </c>
     </row>
     <row r="59" spans="1:3">
-      <c r="A59" s="124" t="s">
+      <c r="A59" s="122" t="s">
         <v>385</v>
       </c>
-      <c r="B59" s="19" t="s">
+      <c r="B59" s="8" t="s">
         <v>1080</v>
       </c>
-      <c r="C59" s="19" t="s">
+      <c r="C59" s="8" t="s">
         <v>1081</v>
       </c>
     </row>
     <row r="60" spans="1:3">
-      <c r="A60" s="124" t="s">
+      <c r="A60" s="122" t="s">
         <v>385</v>
       </c>
-      <c r="B60" s="19" t="s">
+      <c r="B60" s="8" t="s">
         <v>1054</v>
       </c>
-      <c r="C60" s="19" t="s">
+      <c r="C60" s="8" t="s">
         <v>1082</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="16.5">
-      <c r="A61" s="19" t="s">
+      <c r="A61" s="8" t="s">
         <v>1083</v>
       </c>
-      <c r="B61" s="125" t="s">
+      <c r="B61" s="224" t="s">
         <v>1084</v>
       </c>
-      <c r="C61" s="125" t="s">
+      <c r="C61" s="224" t="s">
         <v>1085</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="16.5">
-      <c r="A62" s="19" t="s">
+      <c r="A62" s="8" t="s">
         <v>1083</v>
       </c>
-      <c r="B62" s="126" t="s">
+      <c r="B62" s="225" t="s">
         <v>1086</v>
       </c>
-      <c r="C62" s="126" t="s">
+      <c r="C62" s="225" t="s">
         <v>1087</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="16.5">
-      <c r="A63" s="19" t="s">
+      <c r="A63" s="8" t="s">
         <v>1083</v>
       </c>
-      <c r="B63" s="126" t="s">
+      <c r="B63" s="225" t="s">
         <v>1088</v>
       </c>
-      <c r="C63" s="126" t="s">
+      <c r="C63" s="225" t="s">
         <v>1089</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="16.5">
-      <c r="A64" s="19" t="s">
+    <row r="64" spans="1:3" ht="19.5" customHeight="1">
+      <c r="A64" s="8" t="s">
         <v>1083</v>
       </c>
-      <c r="B64" s="126" t="s">
+      <c r="B64" s="225" t="s">
         <v>1090</v>
       </c>
-      <c r="C64" s="126" t="s">
+      <c r="C64" s="225" t="s">
         <v>1091</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="16.5">
-      <c r="A65" s="19" t="s">
+      <c r="A65" s="8" t="s">
         <v>1083</v>
       </c>
-      <c r="B65" s="126" t="s">
+      <c r="B65" s="225" t="s">
         <v>1092</v>
       </c>
-      <c r="C65" s="126" t="s">
+      <c r="C65" s="225" t="s">
         <v>1093</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="16.5">
-      <c r="A66" s="19" t="s">
+      <c r="A66" s="8" t="s">
         <v>1083</v>
       </c>
-      <c r="B66" s="126" t="s">
+      <c r="B66" s="225" t="s">
         <v>1094</v>
       </c>
-      <c r="C66" s="126" t="s">
+      <c r="C66" s="225" t="s">
         <v>1095</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="16.5">
-      <c r="A67" s="19" t="s">
+      <c r="A67" s="8" t="s">
         <v>1083</v>
       </c>
-      <c r="B67" s="126" t="s">
+      <c r="B67" s="225" t="s">
         <v>1096</v>
       </c>
-      <c r="C67" s="126" t="s">
+      <c r="C67" s="225" t="s">
         <v>1097</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="16.5">
-      <c r="A68" s="19" t="s">
+      <c r="A68" s="8" t="s">
         <v>1083</v>
       </c>
-      <c r="B68" s="126" t="s">
+      <c r="B68" s="225" t="s">
         <v>1098</v>
       </c>
-      <c r="C68" s="126" t="s">
+      <c r="C68" s="225" t="s">
         <v>1099</v>
       </c>
     </row>
     <row r="69" spans="1:3" ht="16.5">
-      <c r="A69" s="19" t="s">
+      <c r="A69" s="8" t="s">
         <v>1083</v>
       </c>
-      <c r="B69" s="126" t="s">
+      <c r="B69" s="225" t="s">
         <v>1100</v>
       </c>
-      <c r="C69" s="126" t="s">
+      <c r="C69" s="225" t="s">
         <v>1101</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="16.5">
-      <c r="A70" s="19" t="s">
+      <c r="A70" s="8" t="s">
         <v>1083</v>
       </c>
-      <c r="B70" s="126" t="s">
+      <c r="B70" s="225" t="s">
         <v>1102</v>
       </c>
-      <c r="C70" s="126" t="s">
+      <c r="C70" s="225" t="s">
         <v>1103</v>
       </c>
     </row>
     <row r="71" spans="1:3" ht="16.5">
-      <c r="A71" s="19" t="s">
+      <c r="A71" s="8" t="s">
         <v>1083</v>
       </c>
-      <c r="B71" s="126" t="s">
+      <c r="B71" s="225" t="s">
         <v>1104</v>
       </c>
-      <c r="C71" s="126" t="s">
+      <c r="C71" s="225" t="s">
         <v>1105</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="16.5">
-      <c r="A72" s="19" t="s">
+      <c r="A72" s="8" t="s">
         <v>1083</v>
       </c>
-      <c r="B72" s="126" t="s">
+      <c r="B72" s="225" t="s">
         <v>1106</v>
       </c>
-      <c r="C72" s="126" t="s">
+      <c r="C72" s="225" t="s">
         <v>1107</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="16.5">
-      <c r="A73" s="19" t="s">
+      <c r="A73" s="8" t="s">
         <v>1083</v>
       </c>
-      <c r="B73" s="126" t="s">
+      <c r="B73" s="225" t="s">
         <v>1108</v>
       </c>
-      <c r="C73" s="126" t="s">
+      <c r="C73" s="225" t="s">
         <v>1109</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="16.5">
-      <c r="A74" s="19" t="s">
+      <c r="A74" s="8" t="s">
         <v>1083</v>
       </c>
-      <c r="B74" s="126" t="s">
+      <c r="B74" s="225" t="s">
         <v>1110</v>
       </c>
-      <c r="C74" s="126" t="s">
+      <c r="C74" s="225" t="s">
         <v>1111</v>
       </c>
     </row>
     <row r="75" spans="1:3" ht="16.5">
-      <c r="A75" s="19" t="s">
+      <c r="A75" s="8" t="s">
         <v>1083</v>
       </c>
-      <c r="B75" s="126" t="s">
+      <c r="B75" s="225" t="s">
         <v>1112</v>
       </c>
-      <c r="C75" s="126" t="s">
+      <c r="C75" s="225" t="s">
         <v>1113</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="16.5">
-      <c r="A76" s="19" t="s">
+      <c r="A76" s="8" t="s">
         <v>1083</v>
       </c>
-      <c r="B76" s="126" t="s">
+      <c r="B76" s="225" t="s">
         <v>1114</v>
       </c>
-      <c r="C76" s="126" t="s">
+      <c r="C76" s="225" t="s">
         <v>1115</v>
       </c>
     </row>
     <row r="77" spans="1:3" ht="16.5">
-      <c r="A77" s="19" t="s">
+      <c r="A77" s="8" t="s">
         <v>1083</v>
       </c>
-      <c r="B77" s="126" t="s">
+      <c r="B77" s="225" t="s">
         <v>1116</v>
       </c>
-      <c r="C77" s="126" t="s">
+      <c r="C77" s="225" t="s">
         <v>1117</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="16.5">
-      <c r="A78" s="19" t="s">
+      <c r="A78" s="8" t="s">
         <v>1083</v>
       </c>
-      <c r="B78" s="126" t="s">
+      <c r="B78" s="225" t="s">
         <v>1118</v>
       </c>
-      <c r="C78" s="126" t="s">
+      <c r="C78" s="225" t="s">
         <v>1119</v>
       </c>
     </row>
     <row r="79" spans="1:3" ht="16.5">
-      <c r="A79" s="19" t="s">
+      <c r="A79" s="8" t="s">
         <v>1083</v>
       </c>
-      <c r="B79" s="126" t="s">
+      <c r="B79" s="225" t="s">
         <v>1120</v>
       </c>
-      <c r="C79" s="126" t="s">
+      <c r="C79" s="225" t="s">
         <v>1121</v>
       </c>
     </row>
     <row r="80" spans="1:3" ht="16.5">
-      <c r="A80" s="19" t="s">
+      <c r="A80" s="8" t="s">
         <v>1083</v>
       </c>
-      <c r="B80" s="126" t="s">
+      <c r="B80" s="225" t="s">
         <v>1122</v>
       </c>
-      <c r="C80" s="126" t="s">
+      <c r="C80" s="225" t="s">
         <v>1123</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="16.5">
-      <c r="A81" s="19" t="s">
+      <c r="A81" s="8" t="s">
         <v>1083</v>
       </c>
-      <c r="B81" s="126" t="s">
+      <c r="B81" s="225" t="s">
         <v>1124</v>
       </c>
-      <c r="C81" s="126" t="s">
+      <c r="C81" s="225" t="s">
         <v>1125</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="16.5">
-      <c r="A82" s="19" t="s">
+      <c r="A82" s="8" t="s">
         <v>1083</v>
       </c>
-      <c r="B82" s="126" t="s">
+      <c r="B82" s="225" t="s">
         <v>1126</v>
       </c>
-      <c r="C82" s="126" t="s">
+      <c r="C82" s="225" t="s">
         <v>1127</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="16.5">
-      <c r="A83" s="19" t="s">
+      <c r="A83" s="8" t="s">
         <v>1083</v>
       </c>
-      <c r="B83" s="126" t="s">
+      <c r="B83" s="225" t="s">
         <v>1128</v>
       </c>
-      <c r="C83" s="126" t="s">
+      <c r="C83" s="225" t="s">
         <v>1129</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="16.5">
-      <c r="A84" s="19" t="s">
+    <row r="84" spans="1:3" ht="33">
+      <c r="A84" s="8" t="s">
         <v>1130</v>
       </c>
-      <c r="B84" s="126" t="s">
+      <c r="B84" s="225" t="s">
         <v>1131</v>
       </c>
-      <c r="C84" s="126" t="s">
+      <c r="C84" s="225" t="s">
         <v>1105</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="16.5">
-      <c r="A85" s="19" t="s">
+    <row r="85" spans="1:3" ht="33">
+      <c r="A85" s="8" t="s">
         <v>1130</v>
       </c>
-      <c r="B85" s="126" t="s">
+      <c r="B85" s="225" t="s">
         <v>1132</v>
       </c>
-      <c r="C85" s="126" t="s">
+      <c r="C85" s="225" t="s">
         <v>1133</v>
       </c>
     </row>
     <row r="86" spans="1:3" ht="33">
-      <c r="A86" s="19" t="s">
+      <c r="A86" s="8" t="s">
         <v>1130</v>
       </c>
-      <c r="B86" s="126" t="s">
+      <c r="B86" s="225" t="s">
         <v>1134</v>
       </c>
-      <c r="C86" s="126" t="s">
+      <c r="C86" s="225" t="s">
         <v>1135</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="49.5">
-      <c r="A87" s="19" t="s">
+    <row r="87" spans="1:3" ht="66">
+      <c r="A87" s="8" t="s">
         <v>1130</v>
       </c>
-      <c r="B87" s="126" t="s">
+      <c r="B87" s="225" t="s">
         <v>1136</v>
       </c>
-      <c r="C87" s="126" t="s">
+      <c r="C87" s="225" t="s">
         <v>1137</v>
       </c>
     </row>
     <row r="88" spans="1:3" ht="33">
-      <c r="A88" s="19" t="s">
+      <c r="A88" s="8" t="s">
         <v>1130</v>
       </c>
-      <c r="B88" s="126" t="s">
+      <c r="B88" s="225" t="s">
         <v>1138</v>
       </c>
-      <c r="C88" s="126" t="s">
+      <c r="C88" s="225" t="s">
         <v>1107</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="16.5">
-      <c r="A89" s="19" t="s">
+    <row r="89" spans="1:3" ht="33">
+      <c r="A89" s="8" t="s">
         <v>1130</v>
       </c>
-      <c r="B89" s="126" t="s">
+      <c r="B89" s="225" t="s">
         <v>1139</v>
       </c>
-      <c r="C89" s="126" t="s">
+      <c r="C89" s="225" t="s">
         <v>1140</v>
       </c>
     </row>
     <row r="90" spans="1:3" ht="16.5">
-      <c r="A90" s="19" t="s">
+      <c r="A90" s="8" t="s">
         <v>1130</v>
       </c>
-      <c r="B90" s="126" t="s">
+      <c r="B90" s="225" t="s">
         <v>1141</v>
       </c>
-      <c r="C90" s="126" t="s">
+      <c r="C90" s="225" t="s">
         <v>1142</v>
       </c>
     </row>
     <row r="91" spans="1:3" ht="16.5">
-      <c r="A91" s="19" t="s">
+      <c r="A91" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="B91" s="126" t="s">
+      <c r="B91" s="225" t="s">
         <v>1144</v>
       </c>
-      <c r="C91" s="126" t="s">
+      <c r="C91" s="225" t="s">
         <v>1105</v>
       </c>
     </row>
     <row r="92" spans="1:3" ht="33">
-      <c r="A92" s="19" t="s">
+      <c r="A92" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="B92" s="126" t="s">
+      <c r="B92" s="225" t="s">
         <v>1134</v>
       </c>
-      <c r="C92" s="126" t="s">
+      <c r="C92" s="225" t="s">
         <v>1135</v>
       </c>
     </row>
     <row r="93" spans="1:3" ht="16.5">
-      <c r="A93" s="19" t="s">
+      <c r="A93" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="B93" s="126" t="s">
+      <c r="B93" s="225" t="s">
         <v>313</v>
       </c>
-      <c r="C93" s="126" t="s">
+      <c r="C93" s="225" t="s">
         <v>1085</v>
       </c>
     </row>
     <row r="94" spans="1:3" ht="16.5">
-      <c r="A94" s="19" t="s">
+      <c r="A94" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="B94" s="126" t="s">
+      <c r="B94" s="225" t="s">
         <v>810</v>
       </c>
-      <c r="C94" s="126" t="s">
+      <c r="C94" s="225" t="s">
         <v>1145</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="16.5">
-      <c r="A95" s="19" t="s">
+    <row r="95" spans="1:3" ht="33">
+      <c r="A95" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="B95" s="126" t="s">
+      <c r="B95" s="225" t="s">
         <v>1146</v>
       </c>
-      <c r="C95" s="126" t="s">
+      <c r="C95" s="225" t="s">
         <v>1089</v>
       </c>
     </row>
     <row r="96" spans="1:3" ht="16.5">
-      <c r="A96" s="19" t="s">
+      <c r="A96" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="B96" s="126" t="s">
+      <c r="B96" s="225" t="s">
         <v>1147</v>
       </c>
-      <c r="C96" s="126" t="s">
+      <c r="C96" s="225" t="s">
         <v>1091</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="16.5">
-      <c r="A97" s="19" t="s">
+    <row r="97" spans="1:3" ht="33">
+      <c r="A97" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="B97" s="126" t="s">
+      <c r="B97" s="225" t="s">
         <v>1148</v>
       </c>
-      <c r="C97" s="126" t="s">
+      <c r="C97" s="225" t="s">
         <v>1093</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="16.5">
-      <c r="A98" s="19" t="s">
+      <c r="A98" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="B98" s="126" t="s">
+      <c r="B98" s="225" t="s">
         <v>1149</v>
       </c>
-      <c r="C98" s="126" t="s">
+      <c r="C98" s="225" t="s">
         <v>1127</v>
       </c>
     </row>
     <row r="99" spans="1:3" ht="16.5">
-      <c r="A99" s="19" t="s">
+      <c r="A99" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="B99" s="126" t="s">
+      <c r="B99" s="225" t="s">
         <v>1150</v>
       </c>
-      <c r="C99" s="126" t="s">
+      <c r="C99" s="225" t="s">
         <v>1151</v>
       </c>
     </row>
-    <row r="100" spans="1:3" ht="16.5">
-      <c r="A100" s="19" t="s">
+    <row r="100" spans="1:3" ht="33">
+      <c r="A100" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="B100" s="126" t="s">
+      <c r="B100" s="225" t="s">
         <v>1152</v>
       </c>
-      <c r="C100" s="126" t="s">
+      <c r="C100" s="225" t="s">
         <v>1123</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="16.5">
-      <c r="A101" s="19" t="s">
+    <row r="101" spans="1:3" ht="33">
+      <c r="A101" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="B101" s="126" t="s">
+      <c r="B101" s="225" t="s">
         <v>1139</v>
       </c>
-      <c r="C101" s="126" t="s">
+      <c r="C101" s="225" t="s">
         <v>1153</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="16.5">
-      <c r="A102" s="19" t="s">
+    <row r="102" spans="1:3" ht="33">
+      <c r="A102" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="B102" s="126" t="s">
+      <c r="B102" s="225" t="s">
         <v>1154</v>
       </c>
-      <c r="C102" s="126" t="s">
+      <c r="C102" s="225" t="s">
         <v>1155</v>
       </c>
     </row>
     <row r="103" spans="1:3" ht="16.5">
-      <c r="A103" s="19" t="s">
+      <c r="A103" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="B103" s="126" t="s">
+      <c r="B103" s="225" t="s">
         <v>1156</v>
       </c>
-      <c r="C103" s="126" t="s">
+      <c r="C103" s="225" t="s">
         <v>1157</v>
       </c>
     </row>
-    <row r="104" spans="1:3" ht="16.5">
-      <c r="A104" s="19" t="s">
+    <row r="104" spans="1:3" ht="33">
+      <c r="A104" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="B104" s="126" t="s">
+      <c r="B104" s="225" t="s">
         <v>1158</v>
       </c>
-      <c r="C104" s="126" t="s">
+      <c r="C104" s="225" t="s">
         <v>1097</v>
       </c>
     </row>
     <row r="105" spans="1:3" ht="16.5">
-      <c r="A105" s="19" t="s">
+      <c r="A105" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="B105" s="126" t="s">
+      <c r="B105" s="225" t="s">
         <v>1159</v>
       </c>
-      <c r="C105" s="126" t="s">
+      <c r="C105" s="225" t="s">
         <v>1160</v>
       </c>
     </row>
@@ -22358,13 +22768,23 @@
       <c r="A112" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="B112" s="127"/>
+      <c r="B112" s="123"/>
     </row>
     <row r="113" spans="1:2" ht="16.5">
       <c r="A113" s="7" t="s">
         <v>1163</v>
       </c>
-      <c r="B113" s="127"/>
+      <c r="B113" s="123"/>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" s="7" t="s">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="7" t="s">
+        <v>1364</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -22373,9 +22793,11 @@
     <hyperlink ref="A111" r:id="rId3" xr:uid="{E175D41D-64C5-47F9-B506-B0F465F0D6E1}"/>
     <hyperlink ref="A112" r:id="rId4" xr:uid="{8270CEE3-8746-440A-B7C6-EF5D1D17561E}"/>
     <hyperlink ref="A113" r:id="rId5" xr:uid="{0D920FAD-D933-4929-8E3D-78B04A8578BE}"/>
+    <hyperlink ref="A114" r:id="rId6" xr:uid="{F59092A8-E091-4E62-A4E8-B1766D61B7FF}"/>
+    <hyperlink ref="A115" r:id="rId7" location="Access_Log_Valve" xr:uid="{FE163D57-19AF-44B5-9620-A2EE256B10BC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId6"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="300" r:id="rId8"/>
 </worksheet>
 </file>
 
@@ -22408,7 +22830,7 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="215" t="s">
+      <c r="A2" s="213" t="s">
         <v>379</v>
       </c>
       <c r="B2" s="57" t="s">
@@ -22422,7 +22844,7 @@
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="215"/>
+      <c r="A3" s="213"/>
       <c r="B3" s="20" t="s">
         <v>262</v>
       </c>
@@ -22434,7 +22856,7 @@
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="215"/>
+      <c r="A4" s="213"/>
       <c r="B4" s="20" t="s">
         <v>385</v>
       </c>
@@ -22446,7 +22868,7 @@
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="215"/>
+      <c r="A5" s="213"/>
       <c r="B5" s="57" t="s">
         <v>544</v>
       </c>
@@ -22458,7 +22880,7 @@
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="215"/>
+      <c r="A6" s="213"/>
       <c r="B6" s="20" t="s">
         <v>388</v>
       </c>
@@ -22470,7 +22892,7 @@
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="215"/>
+      <c r="A7" s="213"/>
       <c r="B7" s="20" t="s">
         <v>390</v>
       </c>
@@ -24091,12 +24513,12 @@
       </c>
     </row>
     <row r="9" spans="11:18">
-      <c r="K9" s="148" t="s">
+      <c r="K9" s="144" t="s">
         <v>1267</v>
       </c>
     </row>
     <row r="10" spans="11:18">
-      <c r="K10" s="148">
+      <c r="K10" s="144">
         <v>0</v>
       </c>
       <c r="L10" s="109" t="s">
@@ -24113,17 +24535,17 @@
       </c>
     </row>
     <row r="11" spans="11:18" ht="15.75" thickBot="1">
-      <c r="K11" s="148"/>
-      <c r="L11" s="146"/>
-      <c r="M11" s="146"/>
-      <c r="N11" s="146"/>
-      <c r="O11" s="146"/>
-      <c r="P11" s="146"/>
-      <c r="Q11" s="146"/>
-      <c r="R11" s="146"/>
+      <c r="K11" s="144"/>
+      <c r="L11" s="142"/>
+      <c r="M11" s="142"/>
+      <c r="N11" s="142"/>
+      <c r="O11" s="142"/>
+      <c r="P11" s="142"/>
+      <c r="Q11" s="142"/>
+      <c r="R11" s="142"/>
     </row>
     <row r="12" spans="11:18">
-      <c r="K12" s="148">
+      <c r="K12" s="144">
         <v>1</v>
       </c>
       <c r="L12" s="5" t="s">
@@ -24131,7 +24553,7 @@
       </c>
     </row>
     <row r="13" spans="11:18">
-      <c r="K13" s="148"/>
+      <c r="K13" s="144"/>
       <c r="M13" t="s">
         <v>880</v>
       </c>
@@ -24143,7 +24565,7 @@
       </c>
     </row>
     <row r="14" spans="11:18">
-      <c r="K14" s="148"/>
+      <c r="K14" s="144"/>
       <c r="L14" s="6" t="s">
         <v>887</v>
       </c>
@@ -24152,13 +24574,13 @@
       </c>
     </row>
     <row r="15" spans="11:18">
-      <c r="K15" s="148"/>
+      <c r="K15" s="144"/>
       <c r="M15" t="s">
         <v>884</v>
       </c>
     </row>
     <row r="16" spans="11:18">
-      <c r="K16" s="148"/>
+      <c r="K16" s="144"/>
       <c r="O16" s="5" t="s">
         <v>1266</v>
       </c>
@@ -24167,16 +24589,16 @@
       </c>
     </row>
     <row r="17" spans="7:24">
-      <c r="K17" s="148"/>
+      <c r="K17" s="144"/>
     </row>
     <row r="18" spans="7:24">
-      <c r="K18" s="148"/>
+      <c r="K18" s="144"/>
     </row>
     <row r="19" spans="7:24">
-      <c r="K19" s="148"/>
+      <c r="K19" s="144"/>
     </row>
     <row r="20" spans="7:24">
-      <c r="K20" s="148"/>
+      <c r="K20" s="144"/>
       <c r="L20" s="6" t="s">
         <v>882</v>
       </c>
@@ -24194,7 +24616,7 @@
       </c>
     </row>
     <row r="21" spans="7:24">
-      <c r="K21" s="148"/>
+      <c r="K21" s="144"/>
       <c r="M21" t="s">
         <v>888</v>
       </c>
@@ -24203,8 +24625,8 @@
       </c>
     </row>
     <row r="22" spans="7:24">
-      <c r="K22" s="148"/>
-      <c r="V22" s="176" t="s">
+      <c r="K22" s="144"/>
+      <c r="V22" s="174" t="s">
         <v>832</v>
       </c>
       <c r="W22" s="9" t="s">
@@ -24215,19 +24637,19 @@
       </c>
     </row>
     <row r="23" spans="7:24" ht="15.75" thickBot="1">
-      <c r="K23" s="148"/>
-      <c r="L23" s="146"/>
-      <c r="M23" s="146"/>
-      <c r="N23" s="146"/>
-      <c r="O23" s="147" t="s">
+      <c r="K23" s="144"/>
+      <c r="L23" s="142"/>
+      <c r="M23" s="142"/>
+      <c r="N23" s="142"/>
+      <c r="O23" s="143" t="s">
         <v>1266</v>
       </c>
-      <c r="P23" s="147" t="s">
+      <c r="P23" s="143" t="s">
         <v>1268</v>
       </c>
-      <c r="Q23" s="146"/>
-      <c r="R23" s="146"/>
-      <c r="V23" s="177"/>
+      <c r="Q23" s="142"/>
+      <c r="R23" s="142"/>
+      <c r="V23" s="175"/>
       <c r="W23" s="9" t="s">
         <v>815</v>
       </c>
@@ -24236,8 +24658,8 @@
       </c>
     </row>
     <row r="24" spans="7:24">
-      <c r="K24" s="148"/>
-      <c r="V24" s="177"/>
+      <c r="K24" s="144"/>
+      <c r="V24" s="175"/>
       <c r="W24" s="9" t="s">
         <v>816</v>
       </c>
@@ -24246,13 +24668,13 @@
       </c>
     </row>
     <row r="25" spans="7:24">
-      <c r="K25" s="148">
+      <c r="K25" s="144">
         <v>2</v>
       </c>
       <c r="L25" s="5" t="s">
         <v>891</v>
       </c>
-      <c r="V25" s="177"/>
+      <c r="V25" s="175"/>
       <c r="W25" s="9" t="s">
         <v>817</v>
       </c>
@@ -24261,7 +24683,7 @@
       </c>
     </row>
     <row r="26" spans="7:24">
-      <c r="K26" s="148"/>
+      <c r="K26" s="144"/>
       <c r="M26" s="110" t="s">
         <v>893</v>
       </c>
@@ -24271,32 +24693,32 @@
       <c r="O26" t="s">
         <v>897</v>
       </c>
-      <c r="V26" s="177"/>
+      <c r="V26" s="175"/>
       <c r="W26" s="9" t="s">
         <v>824</v>
       </c>
       <c r="X26" s="92"/>
     </row>
     <row r="27" spans="7:24">
-      <c r="K27" s="148"/>
+      <c r="K27" s="144"/>
       <c r="M27" t="s">
         <v>894</v>
       </c>
       <c r="N27" t="s">
         <v>896</v>
       </c>
-      <c r="V27" s="177"/>
+      <c r="V27" s="175"/>
       <c r="W27" s="9" t="s">
         <v>825</v>
       </c>
       <c r="X27" s="92"/>
     </row>
     <row r="28" spans="7:24">
-      <c r="K28" s="148"/>
+      <c r="K28" s="144"/>
       <c r="N28" t="s">
         <v>898</v>
       </c>
-      <c r="V28" s="177"/>
+      <c r="V28" s="175"/>
       <c r="W28" s="9" t="s">
         <v>826</v>
       </c>
@@ -24305,11 +24727,11 @@
       </c>
     </row>
     <row r="29" spans="7:24">
-      <c r="K29" s="148"/>
+      <c r="K29" s="144"/>
       <c r="N29" t="s">
         <v>899</v>
       </c>
-      <c r="V29" s="178"/>
+      <c r="V29" s="176"/>
       <c r="W29" s="9" t="s">
         <v>827</v>
       </c>
@@ -24318,14 +24740,14 @@
       </c>
     </row>
     <row r="30" spans="7:24">
-      <c r="K30" s="148"/>
+      <c r="K30" s="144"/>
       <c r="M30" t="s">
         <v>900</v>
       </c>
       <c r="N30" t="s">
         <v>852</v>
       </c>
-      <c r="V30" s="173" t="s">
+      <c r="V30" s="171" t="s">
         <v>831</v>
       </c>
       <c r="W30" s="49" t="s">
@@ -24334,11 +24756,11 @@
       <c r="X30" s="112"/>
     </row>
     <row r="31" spans="7:24">
-      <c r="K31" s="148"/>
+      <c r="K31" s="144"/>
       <c r="N31" t="s">
         <v>901</v>
       </c>
-      <c r="V31" s="174"/>
+      <c r="V31" s="172"/>
       <c r="W31" s="49" t="s">
         <v>822</v>
       </c>
@@ -24348,19 +24770,19 @@
       <c r="G32" t="s">
         <v>910</v>
       </c>
-      <c r="K32" s="148"/>
-      <c r="L32" s="146"/>
-      <c r="M32" s="146"/>
-      <c r="N32" s="146"/>
-      <c r="O32" s="147" t="s">
+      <c r="K32" s="144"/>
+      <c r="L32" s="142"/>
+      <c r="M32" s="142"/>
+      <c r="N32" s="142"/>
+      <c r="O32" s="143" t="s">
         <v>902</v>
       </c>
-      <c r="P32" s="147" t="s">
+      <c r="P32" s="143" t="s">
         <v>903</v>
       </c>
-      <c r="Q32" s="146"/>
-      <c r="R32" s="146"/>
-      <c r="V32" s="175"/>
+      <c r="Q32" s="142"/>
+      <c r="R32" s="142"/>
+      <c r="V32" s="173"/>
       <c r="W32" s="49" t="s">
         <v>823</v>
       </c>
@@ -24373,7 +24795,7 @@
       <c r="G33" t="s">
         <v>911</v>
       </c>
-      <c r="K33" s="148"/>
+      <c r="K33" s="144"/>
     </row>
     <row r="34" spans="6:17">
       <c r="F34">
@@ -24382,7 +24804,7 @@
       <c r="G34" t="s">
         <v>912</v>
       </c>
-      <c r="K34" s="148">
+      <c r="K34" s="144">
         <v>3</v>
       </c>
       <c r="L34" s="5" t="s">
@@ -24432,19 +24854,19 @@
       </c>
     </row>
     <row r="41" spans="6:17" ht="15.75" thickBot="1">
-      <c r="L41" s="146"/>
-      <c r="M41" s="146"/>
-      <c r="N41" s="146"/>
-      <c r="O41" s="147" t="s">
+      <c r="L41" s="142"/>
+      <c r="M41" s="142"/>
+      <c r="N41" s="142"/>
+      <c r="O41" s="143" t="s">
         <v>907</v>
       </c>
-      <c r="P41" s="147" t="s">
+      <c r="P41" s="143" t="s">
         <v>892</v>
       </c>
-      <c r="Q41" s="146"/>
+      <c r="Q41" s="142"/>
     </row>
     <row r="44" spans="6:17">
-      <c r="P44" s="145"/>
+      <c r="P44" s="141"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -24500,7 +24922,7 @@
       <c r="R5" s="13" t="s">
         <v>352</v>
       </c>
-      <c r="S5" s="179" t="s">
+      <c r="S5" s="177" t="s">
         <v>809</v>
       </c>
     </row>
@@ -24517,7 +24939,7 @@
       <c r="R6" s="9" t="s">
         <v>602</v>
       </c>
-      <c r="S6" s="179"/>
+      <c r="S6" s="177"/>
     </row>
     <row r="7" spans="3:20">
       <c r="O7" s="81" t="s">
@@ -24532,7 +24954,7 @@
       <c r="R7" s="9" t="s">
         <v>603</v>
       </c>
-      <c r="S7" s="179"/>
+      <c r="S7" s="177"/>
     </row>
     <row r="8" spans="3:20">
       <c r="O8" s="81" t="s">
@@ -24547,7 +24969,7 @@
       <c r="R8" s="9" t="s">
         <v>350</v>
       </c>
-      <c r="S8" s="179"/>
+      <c r="S8" s="177"/>
     </row>
     <row r="9" spans="3:20">
       <c r="O9" s="81" t="s">
@@ -24562,7 +24984,7 @@
       <c r="R9" s="9" t="s">
         <v>349</v>
       </c>
-      <c r="S9" s="179"/>
+      <c r="S9" s="177"/>
     </row>
     <row r="10" spans="3:20">
       <c r="Q10" s="9" t="s">
@@ -24587,7 +25009,7 @@
       </c>
     </row>
     <row r="15" spans="3:20">
-      <c r="Q15" s="176" t="s">
+      <c r="Q15" s="174" t="s">
         <v>832</v>
       </c>
       <c r="R15" s="9" t="s">
@@ -24622,7 +25044,7 @@
       <c r="J16" s="10" t="s">
         <v>813</v>
       </c>
-      <c r="Q16" s="177"/>
+      <c r="Q16" s="175"/>
       <c r="R16" s="9" t="s">
         <v>815</v>
       </c>
@@ -24632,7 +25054,7 @@
     </row>
     <row r="17" spans="10:19">
       <c r="J17" s="81"/>
-      <c r="Q17" s="177"/>
+      <c r="Q17" s="175"/>
       <c r="R17" s="9" t="s">
         <v>816</v>
       </c>
@@ -24641,7 +25063,7 @@
       </c>
     </row>
     <row r="18" spans="10:19">
-      <c r="Q18" s="177"/>
+      <c r="Q18" s="175"/>
       <c r="R18" s="9" t="s">
         <v>817</v>
       </c>
@@ -24650,21 +25072,21 @@
       </c>
     </row>
     <row r="19" spans="10:19">
-      <c r="Q19" s="177"/>
+      <c r="Q19" s="175"/>
       <c r="R19" s="9" t="s">
         <v>824</v>
       </c>
       <c r="S19" s="92"/>
     </row>
     <row r="20" spans="10:19">
-      <c r="Q20" s="177"/>
+      <c r="Q20" s="175"/>
       <c r="R20" s="9" t="s">
         <v>825</v>
       </c>
       <c r="S20" s="92"/>
     </row>
     <row r="21" spans="10:19">
-      <c r="Q21" s="177"/>
+      <c r="Q21" s="175"/>
       <c r="R21" s="9" t="s">
         <v>826</v>
       </c>
@@ -24673,7 +25095,7 @@
       </c>
     </row>
     <row r="22" spans="10:19">
-      <c r="Q22" s="178"/>
+      <c r="Q22" s="176"/>
       <c r="R22" s="9" t="s">
         <v>827</v>
       </c>
@@ -24682,7 +25104,7 @@
       </c>
     </row>
     <row r="23" spans="10:19">
-      <c r="Q23" s="176" t="s">
+      <c r="Q23" s="174" t="s">
         <v>831</v>
       </c>
       <c r="R23" s="9" t="s">
@@ -24691,14 +25113,14 @@
       <c r="S23" s="92"/>
     </row>
     <row r="24" spans="10:19">
-      <c r="Q24" s="177"/>
+      <c r="Q24" s="175"/>
       <c r="R24" s="9" t="s">
         <v>822</v>
       </c>
       <c r="S24" s="92"/>
     </row>
     <row r="25" spans="10:19">
-      <c r="Q25" s="178"/>
+      <c r="Q25" s="176"/>
       <c r="R25" s="9" t="s">
         <v>823</v>
       </c>
@@ -24764,39 +25186,39 @@
       <c r="B1" t="s">
         <v>860</v>
       </c>
-      <c r="J1" s="180" t="s">
+      <c r="J1" s="178" t="s">
         <v>952</v>
       </c>
-      <c r="K1" s="181"/>
-      <c r="L1" s="181"/>
-      <c r="M1" s="181"/>
-      <c r="N1" s="181"/>
-      <c r="O1" s="181"/>
-      <c r="P1" s="181"/>
-      <c r="Q1" s="181"/>
+      <c r="K1" s="179"/>
+      <c r="L1" s="179"/>
+      <c r="M1" s="179"/>
+      <c r="N1" s="179"/>
+      <c r="O1" s="179"/>
+      <c r="P1" s="179"/>
+      <c r="Q1" s="179"/>
     </row>
     <row r="2" spans="1:17">
-      <c r="J2" s="181"/>
-      <c r="K2" s="181"/>
-      <c r="L2" s="181"/>
-      <c r="M2" s="181"/>
-      <c r="N2" s="181"/>
-      <c r="O2" s="181"/>
-      <c r="P2" s="181"/>
-      <c r="Q2" s="181"/>
+      <c r="J2" s="179"/>
+      <c r="K2" s="179"/>
+      <c r="L2" s="179"/>
+      <c r="M2" s="179"/>
+      <c r="N2" s="179"/>
+      <c r="O2" s="179"/>
+      <c r="P2" s="179"/>
+      <c r="Q2" s="179"/>
     </row>
     <row r="3" spans="1:17">
       <c r="A3" s="6" t="s">
         <v>861</v>
       </c>
-      <c r="J3" s="181"/>
-      <c r="K3" s="181"/>
-      <c r="L3" s="181"/>
-      <c r="M3" s="181"/>
-      <c r="N3" s="181"/>
-      <c r="O3" s="181"/>
-      <c r="P3" s="181"/>
-      <c r="Q3" s="181"/>
+      <c r="J3" s="179"/>
+      <c r="K3" s="179"/>
+      <c r="L3" s="179"/>
+      <c r="M3" s="179"/>
+      <c r="N3" s="179"/>
+      <c r="O3" s="179"/>
+      <c r="P3" s="179"/>
+      <c r="Q3" s="179"/>
     </row>
     <row r="4" spans="1:17">
       <c r="A4" t="s">
@@ -24808,24 +25230,24 @@
       <c r="D4" t="s">
         <v>863</v>
       </c>
-      <c r="J4" s="181"/>
-      <c r="K4" s="181"/>
-      <c r="L4" s="181"/>
-      <c r="M4" s="181"/>
-      <c r="N4" s="181"/>
-      <c r="O4" s="181"/>
-      <c r="P4" s="181"/>
-      <c r="Q4" s="181"/>
+      <c r="J4" s="179"/>
+      <c r="K4" s="179"/>
+      <c r="L4" s="179"/>
+      <c r="M4" s="179"/>
+      <c r="N4" s="179"/>
+      <c r="O4" s="179"/>
+      <c r="P4" s="179"/>
+      <c r="Q4" s="179"/>
     </row>
     <row r="5" spans="1:17">
-      <c r="J5" s="181"/>
-      <c r="K5" s="181"/>
-      <c r="L5" s="181"/>
-      <c r="M5" s="181"/>
-      <c r="N5" s="181"/>
-      <c r="O5" s="181"/>
-      <c r="P5" s="181"/>
-      <c r="Q5" s="181"/>
+      <c r="J5" s="179"/>
+      <c r="K5" s="179"/>
+      <c r="L5" s="179"/>
+      <c r="M5" s="179"/>
+      <c r="N5" s="179"/>
+      <c r="O5" s="179"/>
+      <c r="P5" s="179"/>
+      <c r="Q5" s="179"/>
     </row>
     <row r="6" spans="1:17" ht="15.75" thickBot="1">
       <c r="A6" t="s">
@@ -24834,38 +25256,38 @@
       <c r="E6" t="s">
         <v>918</v>
       </c>
-      <c r="J6" s="181"/>
-      <c r="K6" s="181"/>
-      <c r="L6" s="181"/>
-      <c r="M6" s="181"/>
-      <c r="N6" s="181"/>
-      <c r="O6" s="181"/>
-      <c r="P6" s="181"/>
-      <c r="Q6" s="181"/>
+      <c r="J6" s="179"/>
+      <c r="K6" s="179"/>
+      <c r="L6" s="179"/>
+      <c r="M6" s="179"/>
+      <c r="N6" s="179"/>
+      <c r="O6" s="179"/>
+      <c r="P6" s="179"/>
+      <c r="Q6" s="179"/>
     </row>
     <row r="7" spans="1:17" ht="15.75" thickBot="1">
       <c r="A7" s="105" t="s">
         <v>865</v>
       </c>
-      <c r="J7" s="181"/>
-      <c r="K7" s="181"/>
-      <c r="L7" s="181"/>
-      <c r="M7" s="181"/>
-      <c r="N7" s="181"/>
-      <c r="O7" s="181"/>
-      <c r="P7" s="181"/>
-      <c r="Q7" s="181"/>
+      <c r="J7" s="179"/>
+      <c r="K7" s="179"/>
+      <c r="L7" s="179"/>
+      <c r="M7" s="179"/>
+      <c r="N7" s="179"/>
+      <c r="O7" s="179"/>
+      <c r="P7" s="179"/>
+      <c r="Q7" s="179"/>
     </row>
     <row r="8" spans="1:17">
       <c r="A8" s="117"/>
-      <c r="J8" s="181"/>
-      <c r="K8" s="181"/>
-      <c r="L8" s="181"/>
-      <c r="M8" s="181"/>
-      <c r="N8" s="181"/>
-      <c r="O8" s="181"/>
-      <c r="P8" s="181"/>
-      <c r="Q8" s="181"/>
+      <c r="J8" s="179"/>
+      <c r="K8" s="179"/>
+      <c r="L8" s="179"/>
+      <c r="M8" s="179"/>
+      <c r="N8" s="179"/>
+      <c r="O8" s="179"/>
+      <c r="P8" s="179"/>
+      <c r="Q8" s="179"/>
     </row>
     <row r="9" spans="1:17">
       <c r="A9" t="s">
@@ -24874,14 +25296,14 @@
       <c r="B9" t="s">
         <v>924</v>
       </c>
-      <c r="J9" s="181"/>
-      <c r="K9" s="181"/>
-      <c r="L9" s="181"/>
-      <c r="M9" s="181"/>
-      <c r="N9" s="181"/>
-      <c r="O9" s="181"/>
-      <c r="P9" s="181"/>
-      <c r="Q9" s="181"/>
+      <c r="J9" s="179"/>
+      <c r="K9" s="179"/>
+      <c r="L9" s="179"/>
+      <c r="M9" s="179"/>
+      <c r="N9" s="179"/>
+      <c r="O9" s="179"/>
+      <c r="P9" s="179"/>
+      <c r="Q9" s="179"/>
     </row>
     <row r="10" spans="1:17">
       <c r="A10" t="s">
@@ -24902,14 +25324,14 @@
       <c r="H10" t="s">
         <v>950</v>
       </c>
-      <c r="J10" s="181"/>
-      <c r="K10" s="181"/>
-      <c r="L10" s="181"/>
-      <c r="M10" s="181"/>
-      <c r="N10" s="181"/>
-      <c r="O10" s="181"/>
-      <c r="P10" s="181"/>
-      <c r="Q10" s="181"/>
+      <c r="J10" s="179"/>
+      <c r="K10" s="179"/>
+      <c r="L10" s="179"/>
+      <c r="M10" s="179"/>
+      <c r="N10" s="179"/>
+      <c r="O10" s="179"/>
+      <c r="P10" s="179"/>
+      <c r="Q10" s="179"/>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" t="s">
@@ -24930,14 +25352,14 @@
       <c r="H11" t="s">
         <v>951</v>
       </c>
-      <c r="J11" s="181"/>
-      <c r="K11" s="181"/>
-      <c r="L11" s="181"/>
-      <c r="M11" s="181"/>
-      <c r="N11" s="181"/>
-      <c r="O11" s="181"/>
-      <c r="P11" s="181"/>
-      <c r="Q11" s="181"/>
+      <c r="J11" s="179"/>
+      <c r="K11" s="179"/>
+      <c r="L11" s="179"/>
+      <c r="M11" s="179"/>
+      <c r="N11" s="179"/>
+      <c r="O11" s="179"/>
+      <c r="P11" s="179"/>
+      <c r="Q11" s="179"/>
     </row>
     <row r="12" spans="1:17">
       <c r="B12" t="s">
@@ -24952,14 +25374,14 @@
       <c r="H12" t="s">
         <v>951</v>
       </c>
-      <c r="J12" s="181"/>
-      <c r="K12" s="181"/>
-      <c r="L12" s="181"/>
-      <c r="M12" s="181"/>
-      <c r="N12" s="181"/>
-      <c r="O12" s="181"/>
-      <c r="P12" s="181"/>
-      <c r="Q12" s="181"/>
+      <c r="J12" s="179"/>
+      <c r="K12" s="179"/>
+      <c r="L12" s="179"/>
+      <c r="M12" s="179"/>
+      <c r="N12" s="179"/>
+      <c r="O12" s="179"/>
+      <c r="P12" s="179"/>
+      <c r="Q12" s="179"/>
     </row>
     <row r="13" spans="1:17">
       <c r="F13" t="s">
@@ -24971,24 +25393,24 @@
       <c r="H13" t="s">
         <v>951</v>
       </c>
-      <c r="J13" s="181"/>
-      <c r="K13" s="181"/>
-      <c r="L13" s="181"/>
-      <c r="M13" s="181"/>
-      <c r="N13" s="181"/>
-      <c r="O13" s="181"/>
-      <c r="P13" s="181"/>
-      <c r="Q13" s="181"/>
+      <c r="J13" s="179"/>
+      <c r="K13" s="179"/>
+      <c r="L13" s="179"/>
+      <c r="M13" s="179"/>
+      <c r="N13" s="179"/>
+      <c r="O13" s="179"/>
+      <c r="P13" s="179"/>
+      <c r="Q13" s="179"/>
     </row>
     <row r="14" spans="1:17">
-      <c r="J14" s="181"/>
-      <c r="K14" s="181"/>
-      <c r="L14" s="181"/>
-      <c r="M14" s="181"/>
-      <c r="N14" s="181"/>
-      <c r="O14" s="181"/>
-      <c r="P14" s="181"/>
-      <c r="Q14" s="181"/>
+      <c r="J14" s="179"/>
+      <c r="K14" s="179"/>
+      <c r="L14" s="179"/>
+      <c r="M14" s="179"/>
+      <c r="N14" s="179"/>
+      <c r="O14" s="179"/>
+      <c r="P14" s="179"/>
+      <c r="Q14" s="179"/>
     </row>
     <row r="15" spans="1:17">
       <c r="A15" t="s">
@@ -24997,27 +25419,27 @@
       <c r="C15" t="s">
         <v>947</v>
       </c>
-      <c r="J15" s="181"/>
-      <c r="K15" s="181"/>
-      <c r="L15" s="181"/>
-      <c r="M15" s="181"/>
-      <c r="N15" s="181"/>
-      <c r="O15" s="181"/>
-      <c r="P15" s="181"/>
-      <c r="Q15" s="181"/>
+      <c r="J15" s="179"/>
+      <c r="K15" s="179"/>
+      <c r="L15" s="179"/>
+      <c r="M15" s="179"/>
+      <c r="N15" s="179"/>
+      <c r="O15" s="179"/>
+      <c r="P15" s="179"/>
+      <c r="Q15" s="179"/>
     </row>
     <row r="16" spans="1:17">
       <c r="A16" t="s">
         <v>937</v>
       </c>
-      <c r="J16" s="181"/>
-      <c r="K16" s="181"/>
-      <c r="L16" s="181"/>
-      <c r="M16" s="181"/>
-      <c r="N16" s="181"/>
-      <c r="O16" s="181"/>
-      <c r="P16" s="181"/>
-      <c r="Q16" s="181"/>
+      <c r="J16" s="179"/>
+      <c r="K16" s="179"/>
+      <c r="L16" s="179"/>
+      <c r="M16" s="179"/>
+      <c r="N16" s="179"/>
+      <c r="O16" s="179"/>
+      <c r="P16" s="179"/>
+      <c r="Q16" s="179"/>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="5" t="s">
@@ -25302,19 +25724,19 @@
       <c r="E7" s="31" t="s">
         <v>449</v>
       </c>
-      <c r="F7" s="182" t="s">
+      <c r="F7" s="180" t="s">
         <v>441</v>
       </c>
-      <c r="G7" s="182"/>
-      <c r="H7" s="182"/>
-      <c r="I7" s="182"/>
-      <c r="J7" s="182"/>
-      <c r="K7" s="182"/>
-      <c r="L7" s="182"/>
-      <c r="M7" s="182"/>
-      <c r="N7" s="182"/>
-      <c r="O7" s="182"/>
-      <c r="P7" s="182"/>
+      <c r="G7" s="180"/>
+      <c r="H7" s="180"/>
+      <c r="I7" s="180"/>
+      <c r="J7" s="180"/>
+      <c r="K7" s="180"/>
+      <c r="L7" s="180"/>
+      <c r="M7" s="180"/>
+      <c r="N7" s="180"/>
+      <c r="O7" s="180"/>
+      <c r="P7" s="180"/>
     </row>
     <row r="8" spans="1:17">
       <c r="B8" s="32" t="s">
@@ -25538,40 +25960,40 @@
       <c r="A24" s="35" t="s">
         <v>455</v>
       </c>
-      <c r="B24" s="183" t="s">
+      <c r="B24" s="181" t="s">
         <v>457</v>
       </c>
-      <c r="C24" s="183"/>
-      <c r="D24" s="183"/>
-      <c r="E24" s="183"/>
-      <c r="F24" s="183"/>
-      <c r="G24" s="183"/>
+      <c r="C24" s="181"/>
+      <c r="D24" s="181"/>
+      <c r="E24" s="181"/>
+      <c r="F24" s="181"/>
+      <c r="G24" s="181"/>
     </row>
     <row r="25" spans="1:7" ht="30">
       <c r="A25" s="35" t="s">
         <v>462</v>
       </c>
-      <c r="B25" s="184" t="s">
+      <c r="B25" s="182" t="s">
         <v>464</v>
       </c>
-      <c r="C25" s="184"/>
-      <c r="D25" s="184"/>
-      <c r="E25" s="184"/>
-      <c r="F25" s="184"/>
-      <c r="G25" s="184"/>
+      <c r="C25" s="182"/>
+      <c r="D25" s="182"/>
+      <c r="E25" s="182"/>
+      <c r="F25" s="182"/>
+      <c r="G25" s="182"/>
     </row>
     <row r="26" spans="1:7" ht="159" customHeight="1">
       <c r="A26" s="35" t="s">
         <v>459</v>
       </c>
-      <c r="B26" s="183" t="s">
+      <c r="B26" s="181" t="s">
         <v>460</v>
       </c>
-      <c r="C26" s="183"/>
-      <c r="D26" s="183"/>
-      <c r="E26" s="183"/>
-      <c r="F26" s="183"/>
-      <c r="G26" s="183"/>
+      <c r="C26" s="181"/>
+      <c r="D26" s="181"/>
+      <c r="E26" s="181"/>
+      <c r="F26" s="181"/>
+      <c r="G26" s="181"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -26086,29 +26508,29 @@
       <c r="B27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="C27" s="187" t="s">
+      <c r="C27" s="185" t="s">
         <v>622</v>
       </c>
-      <c r="D27" s="188"/>
+      <c r="D27" s="186"/>
       <c r="E27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="F27" s="187" t="s">
+      <c r="F27" s="185" t="s">
         <v>622</v>
       </c>
-      <c r="G27" s="188"/>
+      <c r="G27" s="186"/>
       <c r="H27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="I27" s="187" t="s">
+      <c r="I27" s="185" t="s">
         <v>622</v>
       </c>
-      <c r="J27" s="188"/>
-      <c r="L27" s="199" t="s">
+      <c r="J27" s="186"/>
+      <c r="L27" s="183" t="s">
         <v>694</v>
       </c>
-      <c r="M27" s="199"/>
-      <c r="N27" s="199"/>
+      <c r="M27" s="183"/>
+      <c r="N27" s="183"/>
     </row>
     <row r="28" spans="1:14" ht="32.25" thickBot="1">
       <c r="A28" s="81">
@@ -26117,29 +26539,29 @@
       <c r="B28" s="69" t="s">
         <v>623</v>
       </c>
-      <c r="C28" s="185" t="s">
+      <c r="C28" s="193" t="s">
         <v>624</v>
       </c>
-      <c r="D28" s="186"/>
+      <c r="D28" s="194"/>
       <c r="E28" s="70" t="s">
         <v>645</v>
       </c>
-      <c r="F28" s="189" t="s">
+      <c r="F28" s="187" t="s">
         <v>646</v>
       </c>
-      <c r="G28" s="190"/>
+      <c r="G28" s="188"/>
       <c r="H28" s="69" t="s">
         <v>667</v>
       </c>
-      <c r="I28" s="185" t="s">
+      <c r="I28" s="193" t="s">
         <v>668</v>
       </c>
-      <c r="J28" s="186"/>
-      <c r="L28" s="200" t="s">
+      <c r="J28" s="194"/>
+      <c r="L28" s="184" t="s">
         <v>695</v>
       </c>
-      <c r="M28" s="200"/>
-      <c r="N28" s="200"/>
+      <c r="M28" s="184"/>
+      <c r="N28" s="184"/>
     </row>
     <row r="29" spans="1:14" ht="31.5" thickBot="1">
       <c r="A29" s="81">
@@ -26148,29 +26570,29 @@
       <c r="B29" s="70" t="s">
         <v>625</v>
       </c>
-      <c r="C29" s="189" t="s">
+      <c r="C29" s="187" t="s">
         <v>626</v>
       </c>
-      <c r="D29" s="190"/>
+      <c r="D29" s="188"/>
       <c r="E29" s="69" t="s">
         <v>647</v>
       </c>
-      <c r="F29" s="185" t="s">
+      <c r="F29" s="193" t="s">
         <v>648</v>
       </c>
-      <c r="G29" s="186"/>
+      <c r="G29" s="194"/>
       <c r="H29" s="70" t="s">
         <v>669</v>
       </c>
-      <c r="I29" s="193" t="s">
+      <c r="I29" s="197" t="s">
         <v>670</v>
       </c>
-      <c r="J29" s="194"/>
-      <c r="L29" s="199" t="s">
+      <c r="J29" s="198"/>
+      <c r="L29" s="183" t="s">
         <v>696</v>
       </c>
-      <c r="M29" s="199"/>
-      <c r="N29" s="199"/>
+      <c r="M29" s="183"/>
+      <c r="N29" s="183"/>
     </row>
     <row r="30" spans="1:14" ht="15.75" thickBot="1">
       <c r="A30" s="81">
@@ -26179,29 +26601,29 @@
       <c r="B30" s="69" t="s">
         <v>627</v>
       </c>
-      <c r="C30" s="185" t="s">
+      <c r="C30" s="193" t="s">
         <v>628</v>
       </c>
-      <c r="D30" s="186"/>
+      <c r="D30" s="194"/>
       <c r="E30" s="70" t="s">
         <v>649</v>
       </c>
-      <c r="F30" s="189" t="s">
+      <c r="F30" s="187" t="s">
         <v>650</v>
       </c>
-      <c r="G30" s="190"/>
+      <c r="G30" s="188"/>
       <c r="H30" s="69" t="s">
         <v>671</v>
       </c>
-      <c r="I30" s="185" t="s">
+      <c r="I30" s="193" t="s">
         <v>672</v>
       </c>
-      <c r="J30" s="186"/>
-      <c r="L30" s="200" t="s">
+      <c r="J30" s="194"/>
+      <c r="L30" s="184" t="s">
         <v>697</v>
       </c>
-      <c r="M30" s="200"/>
-      <c r="N30" s="200"/>
+      <c r="M30" s="184"/>
+      <c r="N30" s="184"/>
     </row>
     <row r="31" spans="1:14" ht="17.25" customHeight="1" thickBot="1">
       <c r="A31" s="81">
@@ -26210,29 +26632,29 @@
       <c r="B31" s="70" t="s">
         <v>629</v>
       </c>
-      <c r="C31" s="189" t="s">
+      <c r="C31" s="187" t="s">
         <v>630</v>
       </c>
-      <c r="D31" s="190"/>
+      <c r="D31" s="188"/>
       <c r="E31" s="69" t="s">
         <v>651</v>
       </c>
-      <c r="F31" s="185" t="s">
+      <c r="F31" s="193" t="s">
         <v>652</v>
       </c>
-      <c r="G31" s="186"/>
+      <c r="G31" s="194"/>
       <c r="H31" s="70" t="s">
         <v>673</v>
       </c>
-      <c r="I31" s="189" t="s">
+      <c r="I31" s="187" t="s">
         <v>674</v>
       </c>
-      <c r="J31" s="190"/>
-      <c r="L31" s="199" t="s">
+      <c r="J31" s="188"/>
+      <c r="L31" s="183" t="s">
         <v>698</v>
       </c>
-      <c r="M31" s="199"/>
-      <c r="N31" s="199"/>
+      <c r="M31" s="183"/>
+      <c r="N31" s="183"/>
     </row>
     <row r="32" spans="1:14" ht="43.5" customHeight="1" thickBot="1">
       <c r="A32" s="81">
@@ -26241,29 +26663,29 @@
       <c r="B32" s="69" t="s">
         <v>631</v>
       </c>
-      <c r="C32" s="185" t="s">
+      <c r="C32" s="193" t="s">
         <v>632</v>
       </c>
-      <c r="D32" s="186"/>
+      <c r="D32" s="194"/>
       <c r="E32" s="70" t="s">
         <v>653</v>
       </c>
-      <c r="F32" s="189" t="s">
+      <c r="F32" s="187" t="s">
         <v>654</v>
       </c>
-      <c r="G32" s="190"/>
+      <c r="G32" s="188"/>
       <c r="H32" s="69" t="s">
         <v>675</v>
       </c>
-      <c r="I32" s="185" t="s">
+      <c r="I32" s="193" t="s">
         <v>676</v>
       </c>
-      <c r="J32" s="186"/>
-      <c r="L32" s="200" t="s">
+      <c r="J32" s="194"/>
+      <c r="L32" s="184" t="s">
         <v>699</v>
       </c>
-      <c r="M32" s="200"/>
-      <c r="N32" s="200"/>
+      <c r="M32" s="184"/>
+      <c r="N32" s="184"/>
     </row>
     <row r="33" spans="1:14" ht="31.5" customHeight="1" thickBot="1">
       <c r="A33" s="81">
@@ -26272,29 +26694,29 @@
       <c r="B33" s="70" t="s">
         <v>633</v>
       </c>
-      <c r="C33" s="189" t="s">
+      <c r="C33" s="187" t="s">
         <v>634</v>
       </c>
-      <c r="D33" s="190"/>
+      <c r="D33" s="188"/>
       <c r="E33" s="69" t="s">
         <v>655</v>
       </c>
-      <c r="F33" s="185" t="s">
+      <c r="F33" s="193" t="s">
         <v>656</v>
       </c>
-      <c r="G33" s="186"/>
+      <c r="G33" s="194"/>
       <c r="H33" s="70" t="s">
         <v>677</v>
       </c>
-      <c r="I33" s="191" t="s">
+      <c r="I33" s="195" t="s">
         <v>678</v>
       </c>
-      <c r="J33" s="192"/>
-      <c r="L33" s="199" t="s">
+      <c r="J33" s="196"/>
+      <c r="L33" s="183" t="s">
         <v>700</v>
       </c>
-      <c r="M33" s="199"/>
-      <c r="N33" s="199"/>
+      <c r="M33" s="183"/>
+      <c r="N33" s="183"/>
     </row>
     <row r="34" spans="1:14" ht="28.5" customHeight="1" thickBot="1">
       <c r="A34" s="81">
@@ -26303,29 +26725,29 @@
       <c r="B34" s="69" t="s">
         <v>635</v>
       </c>
-      <c r="C34" s="185" t="s">
+      <c r="C34" s="193" t="s">
         <v>636</v>
       </c>
-      <c r="D34" s="186"/>
+      <c r="D34" s="194"/>
       <c r="E34" s="70" t="s">
         <v>657</v>
       </c>
-      <c r="F34" s="189" t="s">
+      <c r="F34" s="187" t="s">
         <v>658</v>
       </c>
-      <c r="G34" s="190"/>
+      <c r="G34" s="188"/>
       <c r="H34" s="69" t="s">
         <v>679</v>
       </c>
-      <c r="I34" s="195" t="s">
+      <c r="I34" s="191" t="s">
         <v>680</v>
       </c>
-      <c r="J34" s="196"/>
-      <c r="L34" s="200" t="s">
+      <c r="J34" s="192"/>
+      <c r="L34" s="184" t="s">
         <v>701</v>
       </c>
-      <c r="M34" s="200"/>
-      <c r="N34" s="200"/>
+      <c r="M34" s="184"/>
+      <c r="N34" s="184"/>
     </row>
     <row r="35" spans="1:14" ht="31.5" customHeight="1" thickBot="1">
       <c r="A35" s="81">
@@ -26334,29 +26756,29 @@
       <c r="B35" s="70" t="s">
         <v>637</v>
       </c>
-      <c r="C35" s="189" t="s">
+      <c r="C35" s="187" t="s">
         <v>638</v>
       </c>
-      <c r="D35" s="190"/>
+      <c r="D35" s="188"/>
       <c r="E35" s="69" t="s">
         <v>659</v>
       </c>
-      <c r="F35" s="185" t="s">
+      <c r="F35" s="193" t="s">
         <v>660</v>
       </c>
-      <c r="G35" s="186"/>
+      <c r="G35" s="194"/>
       <c r="H35" s="77" t="s">
         <v>681</v>
       </c>
-      <c r="I35" s="189" t="s">
+      <c r="I35" s="187" t="s">
         <v>682</v>
       </c>
-      <c r="J35" s="190"/>
-      <c r="L35" s="199" t="s">
+      <c r="J35" s="188"/>
+      <c r="L35" s="183" t="s">
         <v>702</v>
       </c>
-      <c r="M35" s="199"/>
-      <c r="N35" s="199"/>
+      <c r="M35" s="183"/>
+      <c r="N35" s="183"/>
     </row>
     <row r="36" spans="1:14" ht="60.75" thickBot="1">
       <c r="A36" s="81">
@@ -26365,17 +26787,17 @@
       <c r="B36" s="69" t="s">
         <v>639</v>
       </c>
-      <c r="C36" s="185" t="s">
+      <c r="C36" s="193" t="s">
         <v>640</v>
       </c>
-      <c r="D36" s="186"/>
+      <c r="D36" s="194"/>
       <c r="E36" s="70" t="s">
         <v>661</v>
       </c>
-      <c r="F36" s="189" t="s">
+      <c r="F36" s="187" t="s">
         <v>662</v>
       </c>
-      <c r="G36" s="190"/>
+      <c r="G36" s="188"/>
       <c r="H36" s="78"/>
       <c r="I36" s="71" t="s">
         <v>683</v>
@@ -26383,11 +26805,11 @@
       <c r="J36" s="72" t="s">
         <v>684</v>
       </c>
-      <c r="L36" s="200" t="s">
+      <c r="L36" s="184" t="s">
         <v>703</v>
       </c>
-      <c r="M36" s="200"/>
-      <c r="N36" s="200"/>
+      <c r="M36" s="184"/>
+      <c r="N36" s="184"/>
     </row>
     <row r="37" spans="1:14" ht="75.75" thickBot="1">
       <c r="A37" s="81">
@@ -26396,17 +26818,17 @@
       <c r="B37" s="70" t="s">
         <v>641</v>
       </c>
-      <c r="C37" s="189" t="s">
+      <c r="C37" s="187" t="s">
         <v>642</v>
       </c>
-      <c r="D37" s="190"/>
+      <c r="D37" s="188"/>
       <c r="E37" s="69" t="s">
         <v>663</v>
       </c>
-      <c r="F37" s="185" t="s">
+      <c r="F37" s="193" t="s">
         <v>664</v>
       </c>
-      <c r="G37" s="186"/>
+      <c r="G37" s="194"/>
       <c r="H37" s="78"/>
       <c r="I37" s="73" t="s">
         <v>685</v>
@@ -26422,17 +26844,17 @@
       <c r="B38" s="69" t="s">
         <v>643</v>
       </c>
-      <c r="C38" s="185" t="s">
+      <c r="C38" s="193" t="s">
         <v>644</v>
       </c>
-      <c r="D38" s="186"/>
+      <c r="D38" s="194"/>
       <c r="E38" s="70" t="s">
         <v>665</v>
       </c>
-      <c r="F38" s="189" t="s">
+      <c r="F38" s="187" t="s">
         <v>666</v>
       </c>
-      <c r="G38" s="190"/>
+      <c r="G38" s="188"/>
       <c r="H38" s="78"/>
       <c r="I38" s="75" t="s">
         <v>687</v>
@@ -26448,46 +26870,40 @@
       <c r="B39" s="70" t="s">
         <v>692</v>
       </c>
-      <c r="C39" s="191" t="s">
+      <c r="C39" s="195" t="s">
         <v>693</v>
       </c>
-      <c r="D39" s="192"/>
+      <c r="D39" s="196"/>
       <c r="E39" s="69" t="s">
         <v>690</v>
       </c>
-      <c r="F39" s="195" t="s">
+      <c r="F39" s="191" t="s">
         <v>691</v>
       </c>
-      <c r="G39" s="196"/>
+      <c r="G39" s="192"/>
       <c r="H39" s="79"/>
-      <c r="I39" s="197" t="s">
+      <c r="I39" s="189" t="s">
         <v>689</v>
       </c>
-      <c r="J39" s="198"/>
+      <c r="J39" s="190"/>
     </row>
     <row r="40" spans="1:14" ht="58.5" customHeight="1"/>
     <row r="42" spans="1:14" ht="31.5" customHeight="1"/>
     <row r="43" spans="1:14" ht="31.5" customHeight="1"/>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
     <mergeCell ref="C39:D39"/>
     <mergeCell ref="I29:J29"/>
     <mergeCell ref="I30:J30"/>
@@ -26504,18 +26920,24 @@
     <mergeCell ref="F30:G30"/>
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="F32:G32"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="L32:N32"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>

--- a/2020_LogAnalyzer_Leeheesuk.xlsx
+++ b/2020_LogAnalyzer_Leeheesuk.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="23127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="23231"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45BC12FE-732B-4474-8A27-F4D66EB03724}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1876940-838C-4A6B-A148-16106ECF4BAF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" firstSheet="9" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" firstSheet="6" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UI" sheetId="7" r:id="rId1"/>
@@ -21,15 +21,17 @@
     <sheet name="Pilot" sheetId="11" r:id="rId11"/>
     <sheet name="아키텍처" sheetId="9" r:id="rId12"/>
     <sheet name="기능요건" sheetId="8" r:id="rId13"/>
-    <sheet name="기능요건_피드백" sheetId="14" r:id="rId14"/>
-    <sheet name="비기능요건" sheetId="6" r:id="rId15"/>
-    <sheet name="성능테스트_0717" sheetId="22" r:id="rId16"/>
-    <sheet name="지원포맷" sheetId="1" r:id="rId17"/>
-    <sheet name="로그로맷 항목설명" sheetId="21" r:id="rId18"/>
-    <sheet name="고려사항" sheetId="5" r:id="rId19"/>
-    <sheet name="기능 - AWStats" sheetId="2" r:id="rId20"/>
-    <sheet name="기능 - apachelogviewer" sheetId="4" r:id="rId21"/>
-    <sheet name="기능 - goaccess" sheetId="3" r:id="rId22"/>
+    <sheet name="추가기능_베타서비스포함_TODO" sheetId="24" r:id="rId14"/>
+    <sheet name="기능요건_피드백" sheetId="14" r:id="rId15"/>
+    <sheet name="비기능요건" sheetId="6" r:id="rId16"/>
+    <sheet name="배포정리_TODO" sheetId="25" r:id="rId17"/>
+    <sheet name="성능테스트_0717" sheetId="22" r:id="rId18"/>
+    <sheet name="지원포맷" sheetId="1" r:id="rId19"/>
+    <sheet name="로그로맷 항목설명" sheetId="21" r:id="rId20"/>
+    <sheet name="고려사항" sheetId="5" r:id="rId21"/>
+    <sheet name="기능 - AWStats" sheetId="2" r:id="rId22"/>
+    <sheet name="기능 - apachelogviewer" sheetId="4" r:id="rId23"/>
+    <sheet name="기능 - goaccess" sheetId="3" r:id="rId24"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="12">기능요건!$A$1:$M$46</definedName>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2221" uniqueCount="1409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2257" uniqueCount="1438">
   <si>
     <t>구분</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -6081,6 +6083,93 @@
   </si>
   <si>
     <t>apache 동일여부</t>
+  </si>
+  <si>
+    <t>추가기능</t>
+  </si>
+  <si>
+    <t>멀티파일 업로드</t>
+  </si>
+  <si>
+    <t>대용량 데이터 Split 처리</t>
+  </si>
+  <si>
+    <t>신규등록</t>
+  </si>
+  <si>
+    <t>기존 프로젝트 가져오기</t>
+  </si>
+  <si>
+    <t>분석화면</t>
+  </si>
+  <si>
+    <t>순서(시-&gt;분-&gt;초)</t>
+  </si>
+  <si>
+    <t>디테일 화면</t>
+  </si>
+  <si>
+    <t>로그포맷 등록</t>
+  </si>
+  <si>
+    <t>비교화면-통계</t>
+  </si>
+  <si>
+    <t>비교화면-차트</t>
+  </si>
+  <si>
+    <t>소개자료</t>
+  </si>
+  <si>
+    <t>파일추가</t>
+  </si>
+  <si>
+    <t>압축파일</t>
+  </si>
+  <si>
+    <t>압축파일 권장</t>
+  </si>
+  <si>
+    <t xml:space="preserve">파일은 1GB단위로 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">커스터마이징 </t>
+  </si>
+  <si>
+    <t>필요한 화면만</t>
+  </si>
+  <si>
+    <t>머신러닝</t>
+  </si>
+  <si>
+    <t>Notice</t>
+  </si>
+  <si>
+    <t>로그포맷지원</t>
+  </si>
+  <si>
+    <t>Webtob</t>
+  </si>
+  <si>
+    <t>Nginx, IIS</t>
+  </si>
+  <si>
+    <t>관리기능 생성</t>
+  </si>
+  <si>
+    <t>Linesplitter</t>
+  </si>
+  <si>
+    <t>메뉴얼 시나리오</t>
+  </si>
+  <si>
+    <t>성능테스트</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spinner </t>
+  </si>
+  <si>
+    <t>로딩문자 수정</t>
   </si>
 </sst>
 </file>
@@ -6746,7 +6835,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="40" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="226">
+  <cellXfs count="227">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -7176,6 +7265,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -7230,11 +7336,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -7246,24 +7352,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7278,8 +7366,44 @@
     <xf numFmtId="0" fontId="23" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -7293,29 +7417,11 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -7340,22 +7446,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -16073,6 +16163,55 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>561975</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>161288</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{79E27C04-57CB-43EF-B539-6F92F9F670DD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6686550" y="990600"/>
+          <a:ext cx="1724025" cy="2790188"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>257176</xdr:colOff>
       <xdr:row>1</xdr:row>
@@ -16294,7 +16433,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -16689,51 +16828,51 @@
     </row>
     <row r="17" spans="1:13">
       <c r="J17" s="19"/>
-      <c r="K17" s="165" t="s">
+      <c r="K17" s="172" t="s">
         <v>537</v>
       </c>
-      <c r="L17" s="166"/>
-      <c r="M17" s="167"/>
+      <c r="L17" s="173"/>
+      <c r="M17" s="174"/>
     </row>
     <row r="18" spans="1:13">
       <c r="J18" s="19">
         <v>1</v>
       </c>
-      <c r="K18" s="168" t="s">
+      <c r="K18" s="175" t="s">
         <v>538</v>
       </c>
-      <c r="L18" s="169"/>
-      <c r="M18" s="170"/>
+      <c r="L18" s="176"/>
+      <c r="M18" s="177"/>
     </row>
     <row r="19" spans="1:13">
       <c r="J19" s="19">
         <v>2</v>
       </c>
-      <c r="K19" s="168" t="s">
+      <c r="K19" s="175" t="s">
         <v>539</v>
       </c>
-      <c r="L19" s="169"/>
-      <c r="M19" s="170"/>
+      <c r="L19" s="176"/>
+      <c r="M19" s="177"/>
     </row>
     <row r="20" spans="1:13">
       <c r="J20" s="19">
         <v>3</v>
       </c>
-      <c r="K20" s="168" t="s">
+      <c r="K20" s="175" t="s">
         <v>540</v>
       </c>
-      <c r="L20" s="169"/>
-      <c r="M20" s="170"/>
+      <c r="L20" s="176"/>
+      <c r="M20" s="177"/>
     </row>
     <row r="21" spans="1:13">
       <c r="J21" s="19">
         <v>4</v>
       </c>
-      <c r="K21" s="168" t="s">
+      <c r="K21" s="175" t="s">
         <v>541</v>
       </c>
-      <c r="L21" s="169"/>
-      <c r="M21" s="170"/>
+      <c r="L21" s="176"/>
+      <c r="M21" s="177"/>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="43" t="s">
@@ -16925,10 +17064,10 @@
       <c r="F7" s="111" t="s">
         <v>915</v>
       </c>
-      <c r="I7" s="199" t="s">
+      <c r="I7" s="206" t="s">
         <v>1166</v>
       </c>
-      <c r="J7" s="199"/>
+      <c r="J7" s="206"/>
       <c r="L7" s="49" t="s">
         <v>601</v>
       </c>
@@ -17409,29 +17548,29 @@
       <c r="B27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="C27" s="185" t="s">
+      <c r="C27" s="192" t="s">
         <v>622</v>
       </c>
-      <c r="D27" s="186"/>
+      <c r="D27" s="193"/>
       <c r="E27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="F27" s="185" t="s">
+      <c r="F27" s="192" t="s">
         <v>622</v>
       </c>
-      <c r="G27" s="186"/>
+      <c r="G27" s="193"/>
       <c r="H27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="I27" s="185" t="s">
+      <c r="I27" s="192" t="s">
         <v>622</v>
       </c>
-      <c r="J27" s="186"/>
-      <c r="L27" s="183" t="s">
+      <c r="J27" s="193"/>
+      <c r="L27" s="204" t="s">
         <v>694</v>
       </c>
-      <c r="M27" s="183"/>
-      <c r="N27" s="183"/>
+      <c r="M27" s="204"/>
+      <c r="N27" s="204"/>
     </row>
     <row r="28" spans="1:14" ht="49.5" customHeight="1" thickBot="1">
       <c r="A28" s="81">
@@ -17440,29 +17579,29 @@
       <c r="B28" s="69" t="s">
         <v>623</v>
       </c>
-      <c r="C28" s="193" t="s">
+      <c r="C28" s="190" t="s">
         <v>624</v>
       </c>
-      <c r="D28" s="194"/>
+      <c r="D28" s="191"/>
       <c r="E28" s="70" t="s">
         <v>645</v>
       </c>
-      <c r="F28" s="187" t="s">
+      <c r="F28" s="194" t="s">
         <v>1178</v>
       </c>
-      <c r="G28" s="188"/>
+      <c r="G28" s="195"/>
       <c r="H28" s="69" t="s">
         <v>667</v>
       </c>
-      <c r="I28" s="193" t="s">
+      <c r="I28" s="190" t="s">
         <v>668</v>
       </c>
-      <c r="J28" s="194"/>
-      <c r="L28" s="184" t="s">
+      <c r="J28" s="191"/>
+      <c r="L28" s="205" t="s">
         <v>695</v>
       </c>
-      <c r="M28" s="184"/>
-      <c r="N28" s="184"/>
+      <c r="M28" s="205"/>
+      <c r="N28" s="205"/>
     </row>
     <row r="29" spans="1:14" ht="31.5" thickBot="1">
       <c r="A29" s="81">
@@ -17471,29 +17610,29 @@
       <c r="B29" s="70" t="s">
         <v>625</v>
       </c>
-      <c r="C29" s="187" t="s">
+      <c r="C29" s="194" t="s">
         <v>626</v>
       </c>
-      <c r="D29" s="188"/>
+      <c r="D29" s="195"/>
       <c r="E29" s="69" t="s">
         <v>647</v>
       </c>
-      <c r="F29" s="193" t="s">
+      <c r="F29" s="190" t="s">
         <v>648</v>
       </c>
-      <c r="G29" s="194"/>
+      <c r="G29" s="191"/>
       <c r="H29" s="70" t="s">
         <v>669</v>
       </c>
-      <c r="I29" s="197" t="s">
+      <c r="I29" s="198" t="s">
         <v>670</v>
       </c>
-      <c r="J29" s="198"/>
-      <c r="L29" s="183" t="s">
+      <c r="J29" s="199"/>
+      <c r="L29" s="204" t="s">
         <v>696</v>
       </c>
-      <c r="M29" s="183"/>
-      <c r="N29" s="183"/>
+      <c r="M29" s="204"/>
+      <c r="N29" s="204"/>
     </row>
     <row r="30" spans="1:14" ht="15.75" thickBot="1">
       <c r="A30" s="81">
@@ -17502,29 +17641,29 @@
       <c r="B30" s="69" t="s">
         <v>627</v>
       </c>
-      <c r="C30" s="193" t="s">
+      <c r="C30" s="190" t="s">
         <v>628</v>
       </c>
-      <c r="D30" s="194"/>
+      <c r="D30" s="191"/>
       <c r="E30" s="70" t="s">
         <v>649</v>
       </c>
-      <c r="F30" s="187" t="s">
+      <c r="F30" s="194" t="s">
         <v>650</v>
       </c>
-      <c r="G30" s="188"/>
+      <c r="G30" s="195"/>
       <c r="H30" s="69" t="s">
         <v>671</v>
       </c>
-      <c r="I30" s="193" t="s">
+      <c r="I30" s="190" t="s">
         <v>672</v>
       </c>
-      <c r="J30" s="194"/>
-      <c r="L30" s="184" t="s">
+      <c r="J30" s="191"/>
+      <c r="L30" s="205" t="s">
         <v>697</v>
       </c>
-      <c r="M30" s="184"/>
-      <c r="N30" s="184"/>
+      <c r="M30" s="205"/>
+      <c r="N30" s="205"/>
     </row>
     <row r="31" spans="1:14" ht="17.25" customHeight="1" thickBot="1">
       <c r="A31" s="81">
@@ -17533,29 +17672,29 @@
       <c r="B31" s="70" t="s">
         <v>629</v>
       </c>
-      <c r="C31" s="187" t="s">
+      <c r="C31" s="194" t="s">
         <v>630</v>
       </c>
-      <c r="D31" s="188"/>
+      <c r="D31" s="195"/>
       <c r="E31" s="69" t="s">
         <v>651</v>
       </c>
-      <c r="F31" s="193" t="s">
+      <c r="F31" s="190" t="s">
         <v>652</v>
       </c>
-      <c r="G31" s="194"/>
+      <c r="G31" s="191"/>
       <c r="H31" s="70" t="s">
         <v>673</v>
       </c>
-      <c r="I31" s="187" t="s">
+      <c r="I31" s="194" t="s">
         <v>674</v>
       </c>
-      <c r="J31" s="188"/>
-      <c r="L31" s="183" t="s">
+      <c r="J31" s="195"/>
+      <c r="L31" s="204" t="s">
         <v>698</v>
       </c>
-      <c r="M31" s="183"/>
-      <c r="N31" s="183"/>
+      <c r="M31" s="204"/>
+      <c r="N31" s="204"/>
     </row>
     <row r="32" spans="1:14" ht="43.5" customHeight="1" thickBot="1">
       <c r="A32" s="81">
@@ -17564,29 +17703,29 @@
       <c r="B32" s="69" t="s">
         <v>631</v>
       </c>
-      <c r="C32" s="193" t="s">
+      <c r="C32" s="190" t="s">
         <v>632</v>
       </c>
-      <c r="D32" s="194"/>
+      <c r="D32" s="191"/>
       <c r="E32" s="70" t="s">
         <v>653</v>
       </c>
-      <c r="F32" s="187" t="s">
+      <c r="F32" s="194" t="s">
         <v>654</v>
       </c>
-      <c r="G32" s="188"/>
+      <c r="G32" s="195"/>
       <c r="H32" s="69" t="s">
         <v>675</v>
       </c>
-      <c r="I32" s="193" t="s">
+      <c r="I32" s="190" t="s">
         <v>676</v>
       </c>
-      <c r="J32" s="194"/>
-      <c r="L32" s="184" t="s">
+      <c r="J32" s="191"/>
+      <c r="L32" s="205" t="s">
         <v>699</v>
       </c>
-      <c r="M32" s="184"/>
-      <c r="N32" s="184"/>
+      <c r="M32" s="205"/>
+      <c r="N32" s="205"/>
     </row>
     <row r="33" spans="1:14" ht="31.5" customHeight="1" thickBot="1">
       <c r="A33" s="81">
@@ -17595,29 +17734,29 @@
       <c r="B33" s="70" t="s">
         <v>633</v>
       </c>
-      <c r="C33" s="187" t="s">
+      <c r="C33" s="194" t="s">
         <v>634</v>
       </c>
-      <c r="D33" s="188"/>
+      <c r="D33" s="195"/>
       <c r="E33" s="69" t="s">
         <v>655</v>
       </c>
-      <c r="F33" s="193" t="s">
+      <c r="F33" s="190" t="s">
         <v>656</v>
       </c>
-      <c r="G33" s="194"/>
+      <c r="G33" s="191"/>
       <c r="H33" s="70" t="s">
         <v>677</v>
       </c>
-      <c r="I33" s="195" t="s">
+      <c r="I33" s="196" t="s">
         <v>678</v>
       </c>
-      <c r="J33" s="196"/>
-      <c r="L33" s="183" t="s">
+      <c r="J33" s="197"/>
+      <c r="L33" s="204" t="s">
         <v>700</v>
       </c>
-      <c r="M33" s="183"/>
-      <c r="N33" s="183"/>
+      <c r="M33" s="204"/>
+      <c r="N33" s="204"/>
     </row>
     <row r="34" spans="1:14" ht="28.5" customHeight="1" thickBot="1">
       <c r="A34" s="81">
@@ -17626,29 +17765,29 @@
       <c r="B34" s="69" t="s">
         <v>635</v>
       </c>
-      <c r="C34" s="193" t="s">
+      <c r="C34" s="190" t="s">
         <v>636</v>
       </c>
-      <c r="D34" s="194"/>
+      <c r="D34" s="191"/>
       <c r="E34" s="70" t="s">
         <v>657</v>
       </c>
-      <c r="F34" s="187" t="s">
+      <c r="F34" s="194" t="s">
         <v>658</v>
       </c>
-      <c r="G34" s="188"/>
+      <c r="G34" s="195"/>
       <c r="H34" s="69" t="s">
         <v>679</v>
       </c>
-      <c r="I34" s="191" t="s">
+      <c r="I34" s="200" t="s">
         <v>680</v>
       </c>
-      <c r="J34" s="192"/>
-      <c r="L34" s="184" t="s">
+      <c r="J34" s="201"/>
+      <c r="L34" s="205" t="s">
         <v>701</v>
       </c>
-      <c r="M34" s="184"/>
-      <c r="N34" s="184"/>
+      <c r="M34" s="205"/>
+      <c r="N34" s="205"/>
     </row>
     <row r="35" spans="1:14" ht="31.5" customHeight="1" thickBot="1">
       <c r="A35" s="81">
@@ -17657,29 +17796,29 @@
       <c r="B35" s="70" t="s">
         <v>637</v>
       </c>
-      <c r="C35" s="187" t="s">
+      <c r="C35" s="194" t="s">
         <v>638</v>
       </c>
-      <c r="D35" s="188"/>
+      <c r="D35" s="195"/>
       <c r="E35" s="69" t="s">
         <v>659</v>
       </c>
-      <c r="F35" s="193" t="s">
+      <c r="F35" s="190" t="s">
         <v>660</v>
       </c>
-      <c r="G35" s="194"/>
+      <c r="G35" s="191"/>
       <c r="H35" s="77" t="s">
         <v>681</v>
       </c>
-      <c r="I35" s="187" t="s">
+      <c r="I35" s="194" t="s">
         <v>682</v>
       </c>
-      <c r="J35" s="188"/>
-      <c r="L35" s="183" t="s">
+      <c r="J35" s="195"/>
+      <c r="L35" s="204" t="s">
         <v>702</v>
       </c>
-      <c r="M35" s="183"/>
-      <c r="N35" s="183"/>
+      <c r="M35" s="204"/>
+      <c r="N35" s="204"/>
     </row>
     <row r="36" spans="1:14" ht="60.75" thickBot="1">
       <c r="A36" s="81">
@@ -17688,17 +17827,17 @@
       <c r="B36" s="69" t="s">
         <v>639</v>
       </c>
-      <c r="C36" s="193" t="s">
+      <c r="C36" s="190" t="s">
         <v>640</v>
       </c>
-      <c r="D36" s="194"/>
+      <c r="D36" s="191"/>
       <c r="E36" s="70" t="s">
         <v>661</v>
       </c>
-      <c r="F36" s="187" t="s">
+      <c r="F36" s="194" t="s">
         <v>662</v>
       </c>
-      <c r="G36" s="188"/>
+      <c r="G36" s="195"/>
       <c r="H36" s="78"/>
       <c r="I36" s="71" t="s">
         <v>683</v>
@@ -17706,11 +17845,11 @@
       <c r="J36" s="72" t="s">
         <v>684</v>
       </c>
-      <c r="L36" s="184" t="s">
+      <c r="L36" s="205" t="s">
         <v>703</v>
       </c>
-      <c r="M36" s="184"/>
-      <c r="N36" s="184"/>
+      <c r="M36" s="205"/>
+      <c r="N36" s="205"/>
     </row>
     <row r="37" spans="1:14" ht="75.75" thickBot="1">
       <c r="A37" s="81">
@@ -17719,17 +17858,17 @@
       <c r="B37" s="70" t="s">
         <v>641</v>
       </c>
-      <c r="C37" s="187" t="s">
+      <c r="C37" s="194" t="s">
         <v>642</v>
       </c>
-      <c r="D37" s="188"/>
+      <c r="D37" s="195"/>
       <c r="E37" s="69" t="s">
         <v>663</v>
       </c>
-      <c r="F37" s="193" t="s">
+      <c r="F37" s="190" t="s">
         <v>664</v>
       </c>
-      <c r="G37" s="194"/>
+      <c r="G37" s="191"/>
       <c r="H37" s="78"/>
       <c r="I37" s="73" t="s">
         <v>685</v>
@@ -17745,17 +17884,17 @@
       <c r="B38" s="69" t="s">
         <v>643</v>
       </c>
-      <c r="C38" s="193" t="s">
+      <c r="C38" s="190" t="s">
         <v>644</v>
       </c>
-      <c r="D38" s="194"/>
+      <c r="D38" s="191"/>
       <c r="E38" s="70" t="s">
         <v>665</v>
       </c>
-      <c r="F38" s="187" t="s">
+      <c r="F38" s="194" t="s">
         <v>666</v>
       </c>
-      <c r="G38" s="188"/>
+      <c r="G38" s="195"/>
       <c r="H38" s="78"/>
       <c r="I38" s="75" t="s">
         <v>687</v>
@@ -17771,22 +17910,22 @@
       <c r="B39" s="70" t="s">
         <v>692</v>
       </c>
-      <c r="C39" s="195" t="s">
+      <c r="C39" s="196" t="s">
         <v>693</v>
       </c>
-      <c r="D39" s="196"/>
+      <c r="D39" s="197"/>
       <c r="E39" s="69" t="s">
         <v>690</v>
       </c>
-      <c r="F39" s="191" t="s">
+      <c r="F39" s="200" t="s">
         <v>691</v>
       </c>
-      <c r="G39" s="192"/>
+      <c r="G39" s="201"/>
       <c r="H39" s="79"/>
-      <c r="I39" s="189" t="s">
+      <c r="I39" s="202" t="s">
         <v>689</v>
       </c>
-      <c r="J39" s="190"/>
+      <c r="J39" s="203"/>
     </row>
     <row r="40" spans="1:14" ht="58.5" customHeight="1"/>
     <row r="41" spans="1:14">
@@ -18080,6 +18219,43 @@
     </row>
   </sheetData>
   <mergeCells count="47">
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="L35:N35"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="F36:G36"/>
     <mergeCell ref="L36:N36"/>
@@ -18090,43 +18266,6 @@
     <mergeCell ref="F38:G38"/>
     <mergeCell ref="C39:D39"/>
     <mergeCell ref="F39:G39"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="L27:N27"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
@@ -18707,16 +18846,16 @@
       </c>
     </row>
     <row r="2" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A2" s="204" t="s">
+      <c r="A2" s="207" t="s">
         <v>504</v>
       </c>
-      <c r="B2" s="209" t="s">
+      <c r="B2" s="208" t="s">
         <v>506</v>
       </c>
-      <c r="C2" s="204" t="s">
+      <c r="C2" s="207" t="s">
         <v>508</v>
       </c>
-      <c r="D2" s="204" t="s">
+      <c r="D2" s="207" t="s">
         <v>556</v>
       </c>
       <c r="E2" s="8"/>
@@ -18740,10 +18879,10 @@
       <c r="N2" s="19"/>
     </row>
     <row r="3" spans="1:17">
-      <c r="A3" s="175"/>
-      <c r="B3" s="210"/>
-      <c r="C3" s="205"/>
-      <c r="D3" s="205"/>
+      <c r="A3" s="182"/>
+      <c r="B3" s="209"/>
+      <c r="C3" s="211"/>
+      <c r="D3" s="211"/>
       <c r="E3" s="11"/>
       <c r="F3" s="9" t="s">
         <v>310</v>
@@ -18751,11 +18890,9 @@
       <c r="G3" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="H3" s="12">
-        <v>2</v>
-      </c>
-      <c r="I3" s="151">
-        <v>44074</v>
+      <c r="H3" s="12"/>
+      <c r="I3" s="151" t="s">
+        <v>1218</v>
       </c>
       <c r="J3" s="10"/>
       <c r="K3" s="10"/>
@@ -18765,10 +18902,10 @@
       <c r="N3" s="19"/>
     </row>
     <row r="4" spans="1:17">
-      <c r="A4" s="175"/>
-      <c r="B4" s="210"/>
-      <c r="C4" s="205"/>
-      <c r="D4" s="206"/>
+      <c r="A4" s="182"/>
+      <c r="B4" s="209"/>
+      <c r="C4" s="211"/>
+      <c r="D4" s="212"/>
       <c r="E4" s="11"/>
       <c r="F4" s="9" t="s">
         <v>311</v>
@@ -18779,7 +18916,9 @@
       <c r="H4" s="12" t="s">
         <v>963</v>
       </c>
-      <c r="I4" s="151"/>
+      <c r="I4" s="151">
+        <v>44074</v>
+      </c>
       <c r="J4" s="10"/>
       <c r="K4" s="10"/>
       <c r="M4" s="158" t="s">
@@ -18788,9 +18927,9 @@
       <c r="N4" s="19"/>
     </row>
     <row r="5" spans="1:17">
-      <c r="A5" s="175"/>
-      <c r="B5" s="210"/>
-      <c r="C5" s="206"/>
+      <c r="A5" s="182"/>
+      <c r="B5" s="209"/>
+      <c r="C5" s="212"/>
       <c r="D5" s="46" t="s">
         <v>555</v>
       </c>
@@ -18817,12 +18956,12 @@
       <c r="N5" s="19"/>
     </row>
     <row r="6" spans="1:17">
-      <c r="A6" s="175"/>
-      <c r="B6" s="210"/>
-      <c r="C6" s="204" t="s">
+      <c r="A6" s="182"/>
+      <c r="B6" s="209"/>
+      <c r="C6" s="207" t="s">
         <v>507</v>
       </c>
-      <c r="D6" s="204" t="s">
+      <c r="D6" s="207" t="s">
         <v>511</v>
       </c>
       <c r="E6" s="11"/>
@@ -18842,10 +18981,10 @@
       <c r="K6" s="10"/>
     </row>
     <row r="7" spans="1:17">
-      <c r="A7" s="175"/>
-      <c r="B7" s="210"/>
-      <c r="C7" s="205"/>
-      <c r="D7" s="205"/>
+      <c r="A7" s="182"/>
+      <c r="B7" s="209"/>
+      <c r="C7" s="211"/>
+      <c r="D7" s="211"/>
       <c r="E7" s="11"/>
       <c r="F7" s="9" t="s">
         <v>313</v>
@@ -18863,10 +19002,10 @@
       <c r="K7" s="10"/>
     </row>
     <row r="8" spans="1:17">
-      <c r="A8" s="175"/>
-      <c r="B8" s="210"/>
-      <c r="C8" s="205"/>
-      <c r="D8" s="205"/>
+      <c r="A8" s="182"/>
+      <c r="B8" s="209"/>
+      <c r="C8" s="211"/>
+      <c r="D8" s="211"/>
       <c r="E8" s="11"/>
       <c r="F8" s="9" t="s">
         <v>314</v>
@@ -18884,10 +19023,10 @@
       <c r="K8" s="10"/>
     </row>
     <row r="9" spans="1:17">
-      <c r="A9" s="175"/>
-      <c r="B9" s="210"/>
-      <c r="C9" s="205"/>
-      <c r="D9" s="205"/>
+      <c r="A9" s="182"/>
+      <c r="B9" s="209"/>
+      <c r="C9" s="211"/>
+      <c r="D9" s="211"/>
       <c r="E9" s="8"/>
       <c r="F9" s="9" t="s">
         <v>345</v>
@@ -18905,10 +19044,10 @@
       <c r="K9" s="10"/>
     </row>
     <row r="10" spans="1:17">
-      <c r="A10" s="175"/>
-      <c r="B10" s="210"/>
-      <c r="C10" s="205"/>
-      <c r="D10" s="205"/>
+      <c r="A10" s="182"/>
+      <c r="B10" s="209"/>
+      <c r="C10" s="211"/>
+      <c r="D10" s="211"/>
       <c r="E10" s="8"/>
       <c r="F10" s="9" t="s">
         <v>346</v>
@@ -18926,10 +19065,10 @@
       <c r="K10" s="10"/>
     </row>
     <row r="11" spans="1:17">
-      <c r="A11" s="175"/>
-      <c r="B11" s="210"/>
-      <c r="C11" s="205"/>
-      <c r="D11" s="205"/>
+      <c r="A11" s="182"/>
+      <c r="B11" s="209"/>
+      <c r="C11" s="211"/>
+      <c r="D11" s="211"/>
       <c r="E11" s="8"/>
       <c r="F11" s="9" t="s">
         <v>315</v>
@@ -18947,10 +19086,10 @@
       <c r="K11" s="10"/>
     </row>
     <row r="12" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A12" s="175"/>
-      <c r="B12" s="210"/>
-      <c r="C12" s="205"/>
-      <c r="D12" s="205"/>
+      <c r="A12" s="182"/>
+      <c r="B12" s="209"/>
+      <c r="C12" s="211"/>
+      <c r="D12" s="211"/>
       <c r="E12" s="8"/>
       <c r="F12" s="9" t="s">
         <v>347</v>
@@ -18968,10 +19107,10 @@
       <c r="K12" s="10"/>
     </row>
     <row r="13" spans="1:17" ht="30">
-      <c r="A13" s="175"/>
-      <c r="B13" s="210"/>
-      <c r="C13" s="205"/>
-      <c r="D13" s="205"/>
+      <c r="A13" s="182"/>
+      <c r="B13" s="209"/>
+      <c r="C13" s="211"/>
+      <c r="D13" s="211"/>
       <c r="E13" s="11"/>
       <c r="F13" s="9" t="s">
         <v>316</v>
@@ -18992,10 +19131,10 @@
       </c>
     </row>
     <row r="14" spans="1:17">
-      <c r="A14" s="175"/>
-      <c r="B14" s="210"/>
-      <c r="C14" s="205"/>
-      <c r="D14" s="206"/>
+      <c r="A14" s="182"/>
+      <c r="B14" s="209"/>
+      <c r="C14" s="211"/>
+      <c r="D14" s="212"/>
       <c r="E14" s="11"/>
       <c r="F14" s="9" t="s">
         <v>318</v>
@@ -19013,9 +19152,9 @@
       <c r="K14" s="10"/>
     </row>
     <row r="15" spans="1:17" ht="30">
-      <c r="A15" s="175"/>
-      <c r="B15" s="210"/>
-      <c r="C15" s="205"/>
+      <c r="A15" s="182"/>
+      <c r="B15" s="209"/>
+      <c r="C15" s="211"/>
       <c r="D15" s="22" t="s">
         <v>512</v>
       </c>
@@ -19034,10 +19173,10 @@
       </c>
       <c r="J15" s="10"/>
       <c r="K15" s="10"/>
-      <c r="M15" s="202" t="s">
+      <c r="M15" s="215" t="s">
         <v>851</v>
       </c>
-      <c r="N15" s="203"/>
+      <c r="N15" s="216"/>
       <c r="O15" s="114" t="s">
         <v>1258</v>
       </c>
@@ -19047,12 +19186,12 @@
       </c>
     </row>
     <row r="16" spans="1:17" ht="30">
-      <c r="A16" s="175"/>
-      <c r="B16" s="210"/>
-      <c r="C16" s="204" t="s">
+      <c r="A16" s="182"/>
+      <c r="B16" s="209"/>
+      <c r="C16" s="207" t="s">
         <v>509</v>
       </c>
-      <c r="D16" s="204" t="s">
+      <c r="D16" s="207" t="s">
         <v>513</v>
       </c>
       <c r="E16" s="11"/>
@@ -19087,10 +19226,10 @@
       </c>
     </row>
     <row r="17" spans="1:17">
-      <c r="A17" s="175"/>
-      <c r="B17" s="210"/>
-      <c r="C17" s="205"/>
-      <c r="D17" s="205"/>
+      <c r="A17" s="182"/>
+      <c r="B17" s="209"/>
+      <c r="C17" s="211"/>
+      <c r="D17" s="211"/>
       <c r="E17" s="19"/>
       <c r="F17" s="9" t="s">
         <v>364</v>
@@ -19120,10 +19259,10 @@
       </c>
     </row>
     <row r="18" spans="1:17">
-      <c r="A18" s="175"/>
-      <c r="B18" s="210"/>
-      <c r="C18" s="205"/>
-      <c r="D18" s="205"/>
+      <c r="A18" s="182"/>
+      <c r="B18" s="209"/>
+      <c r="C18" s="211"/>
+      <c r="D18" s="211"/>
       <c r="E18" s="19"/>
       <c r="F18" s="48" t="s">
         <v>559</v>
@@ -19155,10 +19294,10 @@
       </c>
     </row>
     <row r="19" spans="1:17">
-      <c r="A19" s="175"/>
-      <c r="B19" s="210"/>
-      <c r="C19" s="205"/>
-      <c r="D19" s="205"/>
+      <c r="A19" s="182"/>
+      <c r="B19" s="209"/>
+      <c r="C19" s="211"/>
+      <c r="D19" s="211"/>
       <c r="E19" s="8"/>
       <c r="F19" s="9" t="s">
         <v>332</v>
@@ -19189,10 +19328,10 @@
       <c r="Q19" s="91"/>
     </row>
     <row r="20" spans="1:17">
-      <c r="A20" s="175"/>
-      <c r="B20" s="210"/>
-      <c r="C20" s="205"/>
-      <c r="D20" s="205"/>
+      <c r="A20" s="182"/>
+      <c r="B20" s="209"/>
+      <c r="C20" s="211"/>
+      <c r="D20" s="211"/>
       <c r="E20" s="8"/>
       <c r="F20" s="9" t="s">
         <v>333</v>
@@ -19223,10 +19362,10 @@
       <c r="Q20" s="91"/>
     </row>
     <row r="21" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A21" s="175"/>
-      <c r="B21" s="210"/>
-      <c r="C21" s="205"/>
-      <c r="D21" s="205"/>
+      <c r="A21" s="182"/>
+      <c r="B21" s="209"/>
+      <c r="C21" s="211"/>
+      <c r="D21" s="211"/>
       <c r="E21" s="14"/>
       <c r="F21" s="9" t="s">
         <v>334</v>
@@ -19259,10 +19398,10 @@
       </c>
     </row>
     <row r="22" spans="1:17">
-      <c r="A22" s="175"/>
-      <c r="B22" s="210"/>
-      <c r="C22" s="205"/>
-      <c r="D22" s="205"/>
+      <c r="A22" s="182"/>
+      <c r="B22" s="209"/>
+      <c r="C22" s="211"/>
+      <c r="D22" s="211"/>
       <c r="E22" s="14"/>
       <c r="F22" s="9" t="s">
         <v>335</v>
@@ -19295,10 +19434,10 @@
       </c>
     </row>
     <row r="23" spans="1:17">
-      <c r="A23" s="175"/>
-      <c r="B23" s="210"/>
-      <c r="C23" s="205"/>
-      <c r="D23" s="205"/>
+      <c r="A23" s="182"/>
+      <c r="B23" s="209"/>
+      <c r="C23" s="211"/>
+      <c r="D23" s="211"/>
       <c r="E23" s="14"/>
       <c r="F23" s="9" t="s">
         <v>336</v>
@@ -19331,10 +19470,10 @@
       </c>
     </row>
     <row r="24" spans="1:17">
-      <c r="A24" s="175"/>
-      <c r="B24" s="210"/>
-      <c r="C24" s="205"/>
-      <c r="D24" s="205"/>
+      <c r="A24" s="182"/>
+      <c r="B24" s="209"/>
+      <c r="C24" s="211"/>
+      <c r="D24" s="211"/>
       <c r="E24" s="8"/>
       <c r="F24" s="9" t="s">
         <v>1281</v>
@@ -19365,10 +19504,10 @@
       <c r="Q24" s="91"/>
     </row>
     <row r="25" spans="1:17">
-      <c r="A25" s="175"/>
-      <c r="B25" s="210"/>
-      <c r="C25" s="205"/>
-      <c r="D25" s="205"/>
+      <c r="A25" s="182"/>
+      <c r="B25" s="209"/>
+      <c r="C25" s="211"/>
+      <c r="D25" s="211"/>
       <c r="E25" s="8"/>
       <c r="F25" s="9" t="s">
         <v>373</v>
@@ -19399,10 +19538,10 @@
       <c r="Q25" s="91"/>
     </row>
     <row r="26" spans="1:17">
-      <c r="A26" s="175"/>
-      <c r="B26" s="210"/>
-      <c r="C26" s="205"/>
-      <c r="D26" s="205"/>
+      <c r="A26" s="182"/>
+      <c r="B26" s="209"/>
+      <c r="C26" s="211"/>
+      <c r="D26" s="211"/>
       <c r="E26" s="8"/>
       <c r="F26" s="9" t="s">
         <v>338</v>
@@ -19431,10 +19570,10 @@
       <c r="Q26" s="91"/>
     </row>
     <row r="27" spans="1:17">
-      <c r="A27" s="175"/>
-      <c r="B27" s="210"/>
-      <c r="C27" s="205"/>
-      <c r="D27" s="205"/>
+      <c r="A27" s="182"/>
+      <c r="B27" s="209"/>
+      <c r="C27" s="211"/>
+      <c r="D27" s="211"/>
       <c r="E27" s="8"/>
       <c r="F27" s="9" t="s">
         <v>339</v>
@@ -19465,10 +19604,10 @@
       <c r="Q27" s="91"/>
     </row>
     <row r="28" spans="1:17">
-      <c r="A28" s="175"/>
-      <c r="B28" s="210"/>
-      <c r="C28" s="205"/>
-      <c r="D28" s="205"/>
+      <c r="A28" s="182"/>
+      <c r="B28" s="209"/>
+      <c r="C28" s="211"/>
+      <c r="D28" s="211"/>
       <c r="E28" s="8"/>
       <c r="F28" s="121" t="s">
         <v>965</v>
@@ -19499,10 +19638,10 @@
       <c r="Q28" s="91"/>
     </row>
     <row r="29" spans="1:17">
-      <c r="A29" s="175"/>
-      <c r="B29" s="210"/>
-      <c r="C29" s="205"/>
-      <c r="D29" s="205"/>
+      <c r="A29" s="182"/>
+      <c r="B29" s="209"/>
+      <c r="C29" s="211"/>
+      <c r="D29" s="211"/>
       <c r="E29" s="8"/>
       <c r="F29" s="9" t="s">
         <v>955</v>
@@ -19522,10 +19661,10 @@
       </c>
     </row>
     <row r="30" spans="1:17">
-      <c r="A30" s="175"/>
-      <c r="B30" s="210"/>
-      <c r="C30" s="205"/>
-      <c r="D30" s="206"/>
+      <c r="A30" s="182"/>
+      <c r="B30" s="209"/>
+      <c r="C30" s="211"/>
+      <c r="D30" s="212"/>
       <c r="E30" s="8"/>
       <c r="F30" s="49" t="s">
         <v>323</v>
@@ -19540,7 +19679,7 @@
         <v>1332</v>
       </c>
       <c r="J30" s="10"/>
-      <c r="K30" s="200" t="s">
+      <c r="K30" s="213" t="s">
         <v>959</v>
       </c>
       <c r="M30" s="101" t="s">
@@ -19557,10 +19696,10 @@
       </c>
     </row>
     <row r="31" spans="1:17">
-      <c r="A31" s="175"/>
-      <c r="B31" s="210"/>
-      <c r="C31" s="205"/>
-      <c r="D31" s="204" t="s">
+      <c r="A31" s="182"/>
+      <c r="B31" s="209"/>
+      <c r="C31" s="211"/>
+      <c r="D31" s="207" t="s">
         <v>518</v>
       </c>
       <c r="E31" s="8"/>
@@ -19577,13 +19716,13 @@
         <v>44043</v>
       </c>
       <c r="J31" s="10"/>
-      <c r="K31" s="207"/>
+      <c r="K31" s="217"/>
     </row>
     <row r="32" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A32" s="175"/>
-      <c r="B32" s="210"/>
-      <c r="C32" s="205"/>
-      <c r="D32" s="205"/>
+      <c r="A32" s="182"/>
+      <c r="B32" s="209"/>
+      <c r="C32" s="211"/>
+      <c r="D32" s="211"/>
       <c r="E32" s="8"/>
       <c r="F32" s="9" t="s">
         <v>325</v>
@@ -19598,16 +19737,16 @@
         <v>44043</v>
       </c>
       <c r="J32" s="10"/>
-      <c r="K32" s="207"/>
+      <c r="K32" s="217"/>
       <c r="M32" s="147" t="s">
         <v>1277</v>
       </c>
     </row>
     <row r="33" spans="1:15" ht="16.5" customHeight="1">
-      <c r="A33" s="175"/>
-      <c r="B33" s="210"/>
-      <c r="C33" s="205"/>
-      <c r="D33" s="205"/>
+      <c r="A33" s="182"/>
+      <c r="B33" s="209"/>
+      <c r="C33" s="211"/>
+      <c r="D33" s="211"/>
       <c r="E33" s="8"/>
       <c r="F33" s="9" t="s">
         <v>957</v>
@@ -19624,7 +19763,7 @@
       <c r="J33" s="10" t="s">
         <v>954</v>
       </c>
-      <c r="K33" s="208"/>
+      <c r="K33" s="218"/>
       <c r="M33" s="148" t="s">
         <v>1278</v>
       </c>
@@ -19636,10 +19775,10 @@
       </c>
     </row>
     <row r="34" spans="1:15" ht="16.5" customHeight="1">
-      <c r="A34" s="175"/>
-      <c r="B34" s="210"/>
-      <c r="C34" s="205"/>
-      <c r="D34" s="205"/>
+      <c r="A34" s="182"/>
+      <c r="B34" s="209"/>
+      <c r="C34" s="211"/>
+      <c r="D34" s="211"/>
       <c r="E34" s="8"/>
       <c r="F34" s="9" t="s">
         <v>1275</v>
@@ -19659,10 +19798,10 @@
       </c>
     </row>
     <row r="35" spans="1:15">
-      <c r="A35" s="175"/>
-      <c r="B35" s="210"/>
-      <c r="C35" s="206"/>
-      <c r="D35" s="206"/>
+      <c r="A35" s="182"/>
+      <c r="B35" s="209"/>
+      <c r="C35" s="212"/>
+      <c r="D35" s="212"/>
       <c r="E35" s="8"/>
       <c r="F35" s="49" t="s">
         <v>322</v>
@@ -19680,12 +19819,12 @@
       <c r="K35" s="10"/>
     </row>
     <row r="36" spans="1:15">
-      <c r="A36" s="175"/>
-      <c r="B36" s="210"/>
-      <c r="C36" s="204" t="s">
+      <c r="A36" s="182"/>
+      <c r="B36" s="209"/>
+      <c r="C36" s="207" t="s">
         <v>340</v>
       </c>
-      <c r="D36" s="204" t="s">
+      <c r="D36" s="207" t="s">
         <v>517</v>
       </c>
       <c r="E36" s="8"/>
@@ -19705,10 +19844,10 @@
       <c r="K36" s="10"/>
     </row>
     <row r="37" spans="1:15">
-      <c r="A37" s="175"/>
-      <c r="B37" s="211"/>
-      <c r="C37" s="206"/>
-      <c r="D37" s="206"/>
+      <c r="A37" s="182"/>
+      <c r="B37" s="210"/>
+      <c r="C37" s="212"/>
+      <c r="D37" s="212"/>
       <c r="E37" s="8"/>
       <c r="F37" s="9" t="s">
         <v>331</v>
@@ -19724,7 +19863,7 @@
       <c r="K37" s="10"/>
     </row>
     <row r="38" spans="1:15">
-      <c r="A38" s="175"/>
+      <c r="A38" s="182"/>
       <c r="B38" s="29" t="s">
         <v>328</v>
       </c>
@@ -19749,14 +19888,14 @@
       <c r="K38" s="10"/>
     </row>
     <row r="39" spans="1:15" ht="16.5" customHeight="1">
-      <c r="A39" s="175"/>
-      <c r="B39" s="209" t="s">
+      <c r="A39" s="182"/>
+      <c r="B39" s="208" t="s">
         <v>505</v>
       </c>
-      <c r="C39" s="204" t="s">
+      <c r="C39" s="207" t="s">
         <v>510</v>
       </c>
-      <c r="D39" s="204" t="s">
+      <c r="D39" s="207" t="s">
         <v>516</v>
       </c>
       <c r="E39" s="8" t="s">
@@ -19778,10 +19917,10 @@
       <c r="K39" s="10"/>
     </row>
     <row r="40" spans="1:15" ht="16.5" customHeight="1">
-      <c r="A40" s="175"/>
-      <c r="B40" s="210"/>
-      <c r="C40" s="175"/>
-      <c r="D40" s="175"/>
+      <c r="A40" s="182"/>
+      <c r="B40" s="209"/>
+      <c r="C40" s="182"/>
+      <c r="D40" s="182"/>
       <c r="E40" s="17"/>
       <c r="F40" s="9" t="s">
         <v>304</v>
@@ -19799,10 +19938,10 @@
       <c r="K40" s="10"/>
     </row>
     <row r="41" spans="1:15" ht="16.5" customHeight="1">
-      <c r="A41" s="175"/>
-      <c r="B41" s="210"/>
-      <c r="C41" s="175"/>
-      <c r="D41" s="175"/>
+      <c r="A41" s="182"/>
+      <c r="B41" s="209"/>
+      <c r="C41" s="182"/>
+      <c r="D41" s="182"/>
       <c r="E41" s="17"/>
       <c r="F41" s="9" t="s">
         <v>305</v>
@@ -19820,10 +19959,10 @@
       <c r="K41" s="10"/>
     </row>
     <row r="42" spans="1:15">
-      <c r="A42" s="175"/>
-      <c r="B42" s="210"/>
-      <c r="C42" s="175"/>
-      <c r="D42" s="176"/>
+      <c r="A42" s="182"/>
+      <c r="B42" s="209"/>
+      <c r="C42" s="182"/>
+      <c r="D42" s="183"/>
       <c r="E42" s="17"/>
       <c r="F42" s="9" t="s">
         <v>305</v>
@@ -19841,10 +19980,10 @@
       <c r="K42" s="10"/>
     </row>
     <row r="43" spans="1:15" ht="16.5" customHeight="1">
-      <c r="A43" s="175"/>
-      <c r="B43" s="210"/>
-      <c r="C43" s="175"/>
-      <c r="D43" s="204" t="s">
+      <c r="A43" s="182"/>
+      <c r="B43" s="209"/>
+      <c r="C43" s="182"/>
+      <c r="D43" s="207" t="s">
         <v>515</v>
       </c>
       <c r="E43" s="8"/>
@@ -19861,15 +20000,15 @@
         <v>44043</v>
       </c>
       <c r="J43" s="10"/>
-      <c r="K43" s="200" t="s">
+      <c r="K43" s="213" t="s">
         <v>1164</v>
       </c>
     </row>
     <row r="44" spans="1:15">
-      <c r="A44" s="175"/>
-      <c r="B44" s="210"/>
-      <c r="C44" s="175"/>
-      <c r="D44" s="176"/>
+      <c r="A44" s="182"/>
+      <c r="B44" s="209"/>
+      <c r="C44" s="182"/>
+      <c r="D44" s="183"/>
       <c r="E44" s="8"/>
       <c r="F44" s="9" t="s">
         <v>289</v>
@@ -19884,13 +20023,13 @@
         <v>44043</v>
       </c>
       <c r="J44" s="10"/>
-      <c r="K44" s="201"/>
+      <c r="K44" s="214"/>
     </row>
     <row r="45" spans="1:15">
-      <c r="A45" s="175"/>
-      <c r="B45" s="210"/>
-      <c r="C45" s="175"/>
-      <c r="D45" s="204" t="s">
+      <c r="A45" s="182"/>
+      <c r="B45" s="209"/>
+      <c r="C45" s="182"/>
+      <c r="D45" s="207" t="s">
         <v>514</v>
       </c>
       <c r="E45" s="8"/>
@@ -19908,10 +20047,10 @@
       <c r="K45" s="10"/>
     </row>
     <row r="46" spans="1:15">
-      <c r="A46" s="176"/>
-      <c r="B46" s="211"/>
-      <c r="C46" s="176"/>
-      <c r="D46" s="176"/>
+      <c r="A46" s="183"/>
+      <c r="B46" s="210"/>
+      <c r="C46" s="183"/>
+      <c r="D46" s="183"/>
       <c r="E46" s="8"/>
       <c r="F46" s="9" t="s">
         <v>301</v>
@@ -19932,11 +20071,11 @@
       </c>
       <c r="I48">
         <f>COUNTA($I$2:$I$46)</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J48" s="157">
         <f>I48/$I$50</f>
-        <v>0.8</v>
+        <v>0.82222222222222219</v>
       </c>
     </row>
     <row r="49" spans="8:10">
@@ -19945,11 +20084,11 @@
       </c>
       <c r="I49">
         <f>COUNTBLANK($I$2:$I$46)</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J49" s="157">
         <f>I49/$I$50</f>
-        <v>0.2</v>
+        <v>0.17777777777777778</v>
       </c>
     </row>
     <row r="50" spans="8:10">
@@ -19966,6 +20105,12 @@
     <sortCondition ref="P16:P28"/>
   </sortState>
   <mergeCells count="19">
+    <mergeCell ref="K43:K44"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="D16:D30"/>
+    <mergeCell ref="K30:K33"/>
+    <mergeCell ref="C2:C5"/>
+    <mergeCell ref="C6:C15"/>
     <mergeCell ref="A2:A46"/>
     <mergeCell ref="D43:D44"/>
     <mergeCell ref="D45:D46"/>
@@ -19979,12 +20124,6 @@
     <mergeCell ref="D36:D37"/>
     <mergeCell ref="D2:D4"/>
     <mergeCell ref="D6:D14"/>
-    <mergeCell ref="K43:K44"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="D16:D30"/>
-    <mergeCell ref="K30:K33"/>
-    <mergeCell ref="C2:C5"/>
-    <mergeCell ref="C6:C15"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19993,6 +20132,214 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9083B312-1FF5-48BB-A2F4-8C3780BC6634}">
+  <dimension ref="A1:M16"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="B1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1410</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1411</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
+        <v>1417</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1422</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="G4" t="s">
+        <v>1412</v>
+      </c>
+      <c r="H4" t="s">
+        <v>1421</v>
+      </c>
+      <c r="K4" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1428</v>
+      </c>
+      <c r="C5" s="171" t="s">
+        <v>406</v>
+      </c>
+      <c r="D5" s="171" t="s">
+        <v>1432</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5" t="s">
+        <v>1413</v>
+      </c>
+      <c r="H5" t="s">
+        <v>1421</v>
+      </c>
+      <c r="K5" t="s">
+        <v>1424</v>
+      </c>
+      <c r="M5" t="s">
+        <v>1433</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="C6" s="171" t="s">
+        <v>547</v>
+      </c>
+      <c r="D6" s="171"/>
+      <c r="F6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="C7" s="171" t="s">
+        <v>1299</v>
+      </c>
+      <c r="D7" s="171"/>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="C8" s="171" t="s">
+        <v>1361</v>
+      </c>
+      <c r="D8" s="171"/>
+      <c r="F8">
+        <v>5</v>
+      </c>
+      <c r="G8" t="s">
+        <v>1414</v>
+      </c>
+      <c r="H8" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9">
+        <v>5</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1429</v>
+      </c>
+      <c r="C9" s="171" t="s">
+        <v>1407</v>
+      </c>
+      <c r="F9">
+        <v>6</v>
+      </c>
+      <c r="G9" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="C10" s="171" t="s">
+        <v>1430</v>
+      </c>
+      <c r="F10">
+        <v>7</v>
+      </c>
+      <c r="G10" t="s">
+        <v>1418</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="C11" s="171" t="s">
+        <v>1431</v>
+      </c>
+      <c r="F11">
+        <v>8</v>
+      </c>
+      <c r="G11" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12">
+        <v>6</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1435</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13">
+        <v>7</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1436</v>
+      </c>
+      <c r="C13" t="s">
+        <v>1437</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15">
+        <v>8</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1425</v>
+      </c>
+      <c r="C15" t="s">
+        <v>1426</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16">
+        <v>9</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:T54"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -20254,7 +20601,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:J27"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -20274,11 +20621,11 @@
       <c r="B1" s="25" t="s">
         <v>327</v>
       </c>
-      <c r="E1" s="214" t="s">
+      <c r="E1" s="221" t="s">
         <v>724</v>
       </c>
-      <c r="F1" s="214"/>
-      <c r="G1" s="214"/>
+      <c r="F1" s="221"/>
+      <c r="G1" s="221"/>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="19" t="s">
@@ -20287,11 +20634,11 @@
       <c r="B2" s="19" t="s">
         <v>257</v>
       </c>
-      <c r="E2" s="215" t="s">
+      <c r="E2" s="222" t="s">
         <v>725</v>
       </c>
-      <c r="F2" s="215"/>
-      <c r="G2" s="215"/>
+      <c r="F2" s="222"/>
+      <c r="G2" s="222"/>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="19" t="s">
@@ -20308,10 +20655,10 @@
       <c r="B4" s="19" t="s">
         <v>259</v>
       </c>
-      <c r="E4" s="214" t="s">
+      <c r="E4" s="221" t="s">
         <v>722</v>
       </c>
-      <c r="F4" s="214"/>
+      <c r="F4" s="221"/>
       <c r="G4" s="25" t="s">
         <v>723</v>
       </c>
@@ -20323,16 +20670,16 @@
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="E5" s="213" t="s">
+      <c r="E5" s="220" t="s">
         <v>720</v>
       </c>
-      <c r="F5" s="213" t="s">
+      <c r="F5" s="220" t="s">
         <v>721</v>
       </c>
       <c r="G5" s="68" t="s">
         <v>747</v>
       </c>
-      <c r="H5" s="212" t="s">
+      <c r="H5" s="219" t="s">
         <v>748</v>
       </c>
       <c r="J5" t="s">
@@ -20343,12 +20690,12 @@
       <c r="A6" t="s">
         <v>261</v>
       </c>
-      <c r="E6" s="213"/>
-      <c r="F6" s="213"/>
+      <c r="E6" s="220"/>
+      <c r="F6" s="220"/>
       <c r="G6" s="68" t="s">
         <v>746</v>
       </c>
-      <c r="H6" s="213"/>
+      <c r="H6" s="220"/>
       <c r="J6" t="s">
         <v>729</v>
       </c>
@@ -20555,7 +20902,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27976F48-F7B1-448F-ACBC-34923B225806}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F01B713B-7546-4B5B-BF06-08BB58B1A0C8}">
   <dimension ref="A1:K33"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -20636,7 +20992,7 @@
       <c r="J2" s="115" t="s">
         <v>892</v>
       </c>
-      <c r="K2" s="216" t="s">
+      <c r="K2" s="223" t="s">
         <v>1194</v>
       </c>
     </row>
@@ -20669,7 +21025,7 @@
       <c r="J3" s="115" t="s">
         <v>892</v>
       </c>
-      <c r="K3" s="217"/>
+      <c r="K3" s="224"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="128">
@@ -20698,7 +21054,7 @@
       <c r="J4" s="115" t="s">
         <v>892</v>
       </c>
-      <c r="K4" s="217"/>
+      <c r="K4" s="224"/>
     </row>
     <row r="5" spans="1:11" ht="45">
       <c r="A5" s="128">
@@ -20727,7 +21083,7 @@
       <c r="J5" s="115" t="s">
         <v>892</v>
       </c>
-      <c r="K5" s="218"/>
+      <c r="K5" s="225"/>
     </row>
     <row r="6" spans="1:11" ht="60">
       <c r="A6" s="128">
@@ -21020,7 +21376,7 @@
       <c r="C18" s="125"/>
       <c r="D18" s="125"/>
       <c r="E18" s="125"/>
-      <c r="F18" s="219" t="s">
+      <c r="F18" s="226" t="s">
         <v>1239</v>
       </c>
       <c r="G18" s="8" t="s">
@@ -21033,7 +21389,7 @@
       <c r="J18" s="125"/>
     </row>
     <row r="19" spans="1:10">
-      <c r="F19" s="219"/>
+      <c r="F19" s="226"/>
       <c r="G19" s="145" t="s">
         <v>1235</v>
       </c>
@@ -21042,7 +21398,7 @@
       </c>
     </row>
     <row r="20" spans="1:10">
-      <c r="F20" s="219"/>
+      <c r="F20" s="226"/>
       <c r="G20" s="8" t="s">
         <v>1237</v>
       </c>
@@ -21051,7 +21407,7 @@
       </c>
     </row>
     <row r="21" spans="1:10">
-      <c r="F21" s="219"/>
+      <c r="F21" s="226"/>
       <c r="G21" s="8" t="s">
         <v>1238</v>
       </c>
@@ -21194,7 +21550,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -21313,1681 +21669,6 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId4"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37379847-1933-4532-BA71-36026569AE7D}">
-  <dimension ref="A1:H115"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.140625" customWidth="1"/>
-    <col min="3" max="3" width="163.7109375" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="74.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.5703125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="220" t="s">
-        <v>971</v>
-      </c>
-      <c r="B1" s="221" t="s">
-        <v>972</v>
-      </c>
-      <c r="C1" s="221" t="s">
-        <v>973</v>
-      </c>
-      <c r="E1" s="220" t="s">
-        <v>971</v>
-      </c>
-      <c r="F1" s="221" t="s">
-        <v>972</v>
-      </c>
-      <c r="G1" s="221" t="s">
-        <v>973</v>
-      </c>
-      <c r="H1" s="221" t="s">
-        <v>1408</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="8" t="s">
-        <v>758</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>974</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>975</v>
-      </c>
-      <c r="E2" s="164" t="s">
-        <v>1407</v>
-      </c>
-      <c r="F2" s="164" t="s">
-        <v>1365</v>
-      </c>
-      <c r="G2" s="19" t="s">
-        <v>1386</v>
-      </c>
-      <c r="H2" s="164" t="s">
-        <v>1044</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="8" t="s">
-        <v>758</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>976</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>977</v>
-      </c>
-      <c r="E3" s="164" t="s">
-        <v>1407</v>
-      </c>
-      <c r="F3" s="164" t="s">
-        <v>1366</v>
-      </c>
-      <c r="G3" s="19" t="s">
-        <v>1387</v>
-      </c>
-      <c r="H3" s="164" t="s">
-        <v>1044</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="8" t="s">
-        <v>758</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>978</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>979</v>
-      </c>
-      <c r="E4" s="164" t="s">
-        <v>1407</v>
-      </c>
-      <c r="F4" s="164" t="s">
-        <v>1367</v>
-      </c>
-      <c r="G4" s="19" t="s">
-        <v>1388</v>
-      </c>
-      <c r="H4" s="164" t="s">
-        <v>1044</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="8" t="s">
-        <v>758</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>980</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>981</v>
-      </c>
-      <c r="E5" s="164" t="s">
-        <v>1407</v>
-      </c>
-      <c r="F5" s="164" t="s">
-        <v>1368</v>
-      </c>
-      <c r="G5" s="19" t="s">
-        <v>1389</v>
-      </c>
-      <c r="H5" s="164" t="s">
-        <v>1044</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="8" t="s">
-        <v>758</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>982</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>983</v>
-      </c>
-      <c r="E6" s="164" t="s">
-        <v>1407</v>
-      </c>
-      <c r="F6" s="164" t="s">
-        <v>1369</v>
-      </c>
-      <c r="G6" s="19" t="s">
-        <v>1390</v>
-      </c>
-      <c r="H6" s="164" t="s">
-        <v>1044</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="8" t="s">
-        <v>758</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>984</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>985</v>
-      </c>
-      <c r="E7" s="164" t="s">
-        <v>1407</v>
-      </c>
-      <c r="F7" s="164" t="s">
-        <v>1370</v>
-      </c>
-      <c r="G7" s="19" t="s">
-        <v>1391</v>
-      </c>
-      <c r="H7" s="164" t="s">
-        <v>1044</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="223" t="s">
-        <v>758</v>
-      </c>
-      <c r="B8" s="223" t="s">
-        <v>986</v>
-      </c>
-      <c r="C8" s="223" t="s">
-        <v>987</v>
-      </c>
-      <c r="E8" s="164" t="s">
-        <v>1407</v>
-      </c>
-      <c r="F8" s="164" t="s">
-        <v>1371</v>
-      </c>
-      <c r="G8" s="19" t="s">
-        <v>1392</v>
-      </c>
-      <c r="H8" s="164" t="s">
-        <v>1044</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="8" t="s">
-        <v>758</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>988</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>989</v>
-      </c>
-      <c r="E9" s="164" t="s">
-        <v>1407</v>
-      </c>
-      <c r="F9" s="164" t="s">
-        <v>1372</v>
-      </c>
-      <c r="G9" s="19" t="s">
-        <v>1393</v>
-      </c>
-      <c r="H9" s="164" t="s">
-        <v>1044</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="8" t="s">
-        <v>758</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>990</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>991</v>
-      </c>
-      <c r="E10" s="164" t="s">
-        <v>1407</v>
-      </c>
-      <c r="F10" s="164" t="s">
-        <v>1373</v>
-      </c>
-      <c r="G10" s="19" t="s">
-        <v>1394</v>
-      </c>
-      <c r="H10" s="164" t="s">
-        <v>1044</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="8" t="s">
-        <v>758</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>992</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>993</v>
-      </c>
-      <c r="E11" s="164" t="s">
-        <v>1407</v>
-      </c>
-      <c r="F11" s="164" t="s">
-        <v>1374</v>
-      </c>
-      <c r="G11" s="19" t="s">
-        <v>1395</v>
-      </c>
-      <c r="H11" s="164" t="s">
-        <v>1044</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="8" t="s">
-        <v>758</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>994</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>995</v>
-      </c>
-      <c r="E12" s="164" t="s">
-        <v>1407</v>
-      </c>
-      <c r="F12" s="164" t="s">
-        <v>1375</v>
-      </c>
-      <c r="G12" s="19" t="s">
-        <v>1396</v>
-      </c>
-      <c r="H12" s="164" t="s">
-        <v>1044</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="8" t="s">
-        <v>758</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>996</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>997</v>
-      </c>
-      <c r="E13" s="164" t="s">
-        <v>1407</v>
-      </c>
-      <c r="F13" s="164" t="s">
-        <v>1376</v>
-      </c>
-      <c r="G13" s="19" t="s">
-        <v>1397</v>
-      </c>
-      <c r="H13" s="164" t="s">
-        <v>1044</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="8" t="s">
-        <v>758</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>998</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>999</v>
-      </c>
-      <c r="E14" s="164" t="s">
-        <v>1407</v>
-      </c>
-      <c r="F14" s="164" t="s">
-        <v>1377</v>
-      </c>
-      <c r="G14" s="19" t="s">
-        <v>1398</v>
-      </c>
-      <c r="H14" s="164" t="s">
-        <v>948</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="8" t="s">
-        <v>758</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>1000</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>1001</v>
-      </c>
-      <c r="E15" s="164" t="s">
-        <v>1407</v>
-      </c>
-      <c r="F15" s="164" t="s">
-        <v>1378</v>
-      </c>
-      <c r="G15" s="19" t="s">
-        <v>1399</v>
-      </c>
-      <c r="H15" s="164" t="s">
-        <v>1044</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="8" t="s">
-        <v>758</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>1002</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>1003</v>
-      </c>
-      <c r="E16" s="164" t="s">
-        <v>1407</v>
-      </c>
-      <c r="F16" s="164" t="s">
-        <v>1379</v>
-      </c>
-      <c r="G16" s="19" t="s">
-        <v>1400</v>
-      </c>
-      <c r="H16" s="164" t="s">
-        <v>1044</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="8" t="s">
-        <v>758</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>1004</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>1005</v>
-      </c>
-      <c r="E17" s="164" t="s">
-        <v>1407</v>
-      </c>
-      <c r="F17" s="164" t="s">
-        <v>1380</v>
-      </c>
-      <c r="G17" s="19" t="s">
-        <v>1401</v>
-      </c>
-      <c r="H17" s="164" t="s">
-        <v>1044</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="8" t="s">
-        <v>758</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>1006</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>1007</v>
-      </c>
-      <c r="E18" s="164" t="s">
-        <v>1407</v>
-      </c>
-      <c r="F18" s="164" t="s">
-        <v>1381</v>
-      </c>
-      <c r="G18" s="19" t="s">
-        <v>1402</v>
-      </c>
-      <c r="H18" s="164" t="s">
-        <v>1044</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="8" t="s">
-        <v>758</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>1008</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>1009</v>
-      </c>
-      <c r="E19" s="163" t="s">
-        <v>1407</v>
-      </c>
-      <c r="F19" s="163" t="s">
-        <v>1382</v>
-      </c>
-      <c r="G19" s="222" t="s">
-        <v>1403</v>
-      </c>
-      <c r="H19" s="163" t="s">
-        <v>948</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="8" t="s">
-        <v>758</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>1010</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>1011</v>
-      </c>
-      <c r="E20" s="164" t="s">
-        <v>1407</v>
-      </c>
-      <c r="F20" s="164" t="s">
-        <v>1383</v>
-      </c>
-      <c r="G20" s="19" t="s">
-        <v>1404</v>
-      </c>
-      <c r="H20" s="164" t="s">
-        <v>1044</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="8" t="s">
-        <v>758</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>1012</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>1013</v>
-      </c>
-      <c r="E21" s="164" t="s">
-        <v>1407</v>
-      </c>
-      <c r="F21" s="164" t="s">
-        <v>1384</v>
-      </c>
-      <c r="G21" s="19" t="s">
-        <v>1405</v>
-      </c>
-      <c r="H21" s="164" t="s">
-        <v>948</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="8" t="s">
-        <v>758</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>1014</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>1015</v>
-      </c>
-      <c r="E22" s="164" t="s">
-        <v>1407</v>
-      </c>
-      <c r="F22" s="164" t="s">
-        <v>1385</v>
-      </c>
-      <c r="G22" s="19" t="s">
-        <v>1406</v>
-      </c>
-      <c r="H22" s="164" t="s">
-        <v>948</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="8" t="s">
-        <v>758</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>1016</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>1017</v>
-      </c>
-      <c r="F23" s="81"/>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="8" t="s">
-        <v>758</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>1018</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="8" t="s">
-        <v>758</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>1020</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>1021</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="8" t="s">
-        <v>758</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>1022</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>1023</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="8" t="s">
-        <v>758</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>837</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>1024</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="8" t="s">
-        <v>758</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>1025</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>1026</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="8" t="s">
-        <v>758</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>1027</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="8" t="s">
-        <v>758</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>1029</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>1030</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="8" t="s">
-        <v>758</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>1031</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>1032</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="8" t="s">
-        <v>758</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>1033</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>1034</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="8" t="s">
-        <v>758</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>1035</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>1036</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="8" t="s">
-        <v>758</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>835</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>1037</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="8" t="s">
-        <v>758</v>
-      </c>
-      <c r="B35" s="8" t="s">
-        <v>1038</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>1039</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="8" t="s">
-        <v>758</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>1040</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>1041</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="8" t="s">
-        <v>758</v>
-      </c>
-      <c r="B37" s="8" t="s">
-        <v>948</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>1042</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="8" t="s">
-        <v>758</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>833</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>1043</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="8" t="s">
-        <v>758</v>
-      </c>
-      <c r="B39" s="8" t="s">
-        <v>1044</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>1045</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="8" t="s">
-        <v>758</v>
-      </c>
-      <c r="B40" s="8" t="s">
-        <v>836</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>1046</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="8" t="s">
-        <v>758</v>
-      </c>
-      <c r="B41" s="8" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>1048</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="8" t="s">
-        <v>758</v>
-      </c>
-      <c r="B42" s="8" t="s">
-        <v>1049</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>1050</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="122" t="s">
-        <v>385</v>
-      </c>
-      <c r="B43" s="122" t="s">
-        <v>1051</v>
-      </c>
-      <c r="C43" s="122" t="s">
-        <v>1052</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="122" t="s">
-        <v>385</v>
-      </c>
-      <c r="B44" s="122" t="s">
-        <v>1053</v>
-      </c>
-      <c r="C44" s="122" t="s">
-        <v>975</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="122" t="s">
-        <v>385</v>
-      </c>
-      <c r="B45" s="122" t="s">
-        <v>1054</v>
-      </c>
-      <c r="C45" s="122" t="s">
-        <v>1055</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="122" t="s">
-        <v>385</v>
-      </c>
-      <c r="B46" s="122" t="s">
-        <v>619</v>
-      </c>
-      <c r="C46" s="122" t="s">
-        <v>1056</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="122" t="s">
-        <v>385</v>
-      </c>
-      <c r="B47" s="122" t="s">
-        <v>617</v>
-      </c>
-      <c r="C47" s="122" t="s">
-        <v>1057</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="122" t="s">
-        <v>385</v>
-      </c>
-      <c r="B48" s="122" t="s">
-        <v>1058</v>
-      </c>
-      <c r="C48" s="122" t="s">
-        <v>1059</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="122" t="s">
-        <v>385</v>
-      </c>
-      <c r="B49" s="122" t="s">
-        <v>1060</v>
-      </c>
-      <c r="C49" s="122" t="s">
-        <v>1061</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="122" t="s">
-        <v>385</v>
-      </c>
-      <c r="B50" s="122" t="s">
-        <v>1062</v>
-      </c>
-      <c r="C50" s="122" t="s">
-        <v>1063</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="122" t="s">
-        <v>385</v>
-      </c>
-      <c r="B51" s="122" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C51" s="122" t="s">
-        <v>1065</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="122" t="s">
-        <v>385</v>
-      </c>
-      <c r="B52" s="122" t="s">
-        <v>1066</v>
-      </c>
-      <c r="C52" s="122" t="s">
-        <v>1067</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="122" t="s">
-        <v>385</v>
-      </c>
-      <c r="B53" s="122" t="s">
-        <v>1068</v>
-      </c>
-      <c r="C53" s="8" t="s">
-        <v>1069</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="122" t="s">
-        <v>385</v>
-      </c>
-      <c r="B54" s="122" t="s">
-        <v>1070</v>
-      </c>
-      <c r="C54" s="8" t="s">
-        <v>1071</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
-      <c r="A55" s="122" t="s">
-        <v>385</v>
-      </c>
-      <c r="B55" s="8" t="s">
-        <v>1072</v>
-      </c>
-      <c r="C55" s="8" t="s">
-        <v>1073</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="122" t="s">
-        <v>385</v>
-      </c>
-      <c r="B56" s="8" t="s">
-        <v>1074</v>
-      </c>
-      <c r="C56" s="8" t="s">
-        <v>1075</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="122" t="s">
-        <v>385</v>
-      </c>
-      <c r="B57" s="8" t="s">
-        <v>1076</v>
-      </c>
-      <c r="C57" s="8" t="s">
-        <v>1077</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" ht="30">
-      <c r="A58" s="122" t="s">
-        <v>385</v>
-      </c>
-      <c r="B58" s="8" t="s">
-        <v>1078</v>
-      </c>
-      <c r="C58" s="18" t="s">
-        <v>1079</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3">
-      <c r="A59" s="122" t="s">
-        <v>385</v>
-      </c>
-      <c r="B59" s="8" t="s">
-        <v>1080</v>
-      </c>
-      <c r="C59" s="8" t="s">
-        <v>1081</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3">
-      <c r="A60" s="122" t="s">
-        <v>385</v>
-      </c>
-      <c r="B60" s="8" t="s">
-        <v>1054</v>
-      </c>
-      <c r="C60" s="8" t="s">
-        <v>1082</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" ht="16.5">
-      <c r="A61" s="8" t="s">
-        <v>1083</v>
-      </c>
-      <c r="B61" s="224" t="s">
-        <v>1084</v>
-      </c>
-      <c r="C61" s="224" t="s">
-        <v>1085</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" ht="16.5">
-      <c r="A62" s="8" t="s">
-        <v>1083</v>
-      </c>
-      <c r="B62" s="225" t="s">
-        <v>1086</v>
-      </c>
-      <c r="C62" s="225" t="s">
-        <v>1087</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" ht="16.5">
-      <c r="A63" s="8" t="s">
-        <v>1083</v>
-      </c>
-      <c r="B63" s="225" t="s">
-        <v>1088</v>
-      </c>
-      <c r="C63" s="225" t="s">
-        <v>1089</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" ht="19.5" customHeight="1">
-      <c r="A64" s="8" t="s">
-        <v>1083</v>
-      </c>
-      <c r="B64" s="225" t="s">
-        <v>1090</v>
-      </c>
-      <c r="C64" s="225" t="s">
-        <v>1091</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" ht="16.5">
-      <c r="A65" s="8" t="s">
-        <v>1083</v>
-      </c>
-      <c r="B65" s="225" t="s">
-        <v>1092</v>
-      </c>
-      <c r="C65" s="225" t="s">
-        <v>1093</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" ht="16.5">
-      <c r="A66" s="8" t="s">
-        <v>1083</v>
-      </c>
-      <c r="B66" s="225" t="s">
-        <v>1094</v>
-      </c>
-      <c r="C66" s="225" t="s">
-        <v>1095</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" ht="16.5">
-      <c r="A67" s="8" t="s">
-        <v>1083</v>
-      </c>
-      <c r="B67" s="225" t="s">
-        <v>1096</v>
-      </c>
-      <c r="C67" s="225" t="s">
-        <v>1097</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" ht="16.5">
-      <c r="A68" s="8" t="s">
-        <v>1083</v>
-      </c>
-      <c r="B68" s="225" t="s">
-        <v>1098</v>
-      </c>
-      <c r="C68" s="225" t="s">
-        <v>1099</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" ht="16.5">
-      <c r="A69" s="8" t="s">
-        <v>1083</v>
-      </c>
-      <c r="B69" s="225" t="s">
-        <v>1100</v>
-      </c>
-      <c r="C69" s="225" t="s">
-        <v>1101</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" ht="16.5">
-      <c r="A70" s="8" t="s">
-        <v>1083</v>
-      </c>
-      <c r="B70" s="225" t="s">
-        <v>1102</v>
-      </c>
-      <c r="C70" s="225" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" ht="16.5">
-      <c r="A71" s="8" t="s">
-        <v>1083</v>
-      </c>
-      <c r="B71" s="225" t="s">
-        <v>1104</v>
-      </c>
-      <c r="C71" s="225" t="s">
-        <v>1105</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" ht="16.5">
-      <c r="A72" s="8" t="s">
-        <v>1083</v>
-      </c>
-      <c r="B72" s="225" t="s">
-        <v>1106</v>
-      </c>
-      <c r="C72" s="225" t="s">
-        <v>1107</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" ht="16.5">
-      <c r="A73" s="8" t="s">
-        <v>1083</v>
-      </c>
-      <c r="B73" s="225" t="s">
-        <v>1108</v>
-      </c>
-      <c r="C73" s="225" t="s">
-        <v>1109</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" ht="16.5">
-      <c r="A74" s="8" t="s">
-        <v>1083</v>
-      </c>
-      <c r="B74" s="225" t="s">
-        <v>1110</v>
-      </c>
-      <c r="C74" s="225" t="s">
-        <v>1111</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" ht="16.5">
-      <c r="A75" s="8" t="s">
-        <v>1083</v>
-      </c>
-      <c r="B75" s="225" t="s">
-        <v>1112</v>
-      </c>
-      <c r="C75" s="225" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" ht="16.5">
-      <c r="A76" s="8" t="s">
-        <v>1083</v>
-      </c>
-      <c r="B76" s="225" t="s">
-        <v>1114</v>
-      </c>
-      <c r="C76" s="225" t="s">
-        <v>1115</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" ht="16.5">
-      <c r="A77" s="8" t="s">
-        <v>1083</v>
-      </c>
-      <c r="B77" s="225" t="s">
-        <v>1116</v>
-      </c>
-      <c r="C77" s="225" t="s">
-        <v>1117</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" ht="16.5">
-      <c r="A78" s="8" t="s">
-        <v>1083</v>
-      </c>
-      <c r="B78" s="225" t="s">
-        <v>1118</v>
-      </c>
-      <c r="C78" s="225" t="s">
-        <v>1119</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" ht="16.5">
-      <c r="A79" s="8" t="s">
-        <v>1083</v>
-      </c>
-      <c r="B79" s="225" t="s">
-        <v>1120</v>
-      </c>
-      <c r="C79" s="225" t="s">
-        <v>1121</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" ht="16.5">
-      <c r="A80" s="8" t="s">
-        <v>1083</v>
-      </c>
-      <c r="B80" s="225" t="s">
-        <v>1122</v>
-      </c>
-      <c r="C80" s="225" t="s">
-        <v>1123</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" ht="16.5">
-      <c r="A81" s="8" t="s">
-        <v>1083</v>
-      </c>
-      <c r="B81" s="225" t="s">
-        <v>1124</v>
-      </c>
-      <c r="C81" s="225" t="s">
-        <v>1125</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" ht="16.5">
-      <c r="A82" s="8" t="s">
-        <v>1083</v>
-      </c>
-      <c r="B82" s="225" t="s">
-        <v>1126</v>
-      </c>
-      <c r="C82" s="225" t="s">
-        <v>1127</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" ht="16.5">
-      <c r="A83" s="8" t="s">
-        <v>1083</v>
-      </c>
-      <c r="B83" s="225" t="s">
-        <v>1128</v>
-      </c>
-      <c r="C83" s="225" t="s">
-        <v>1129</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" ht="33">
-      <c r="A84" s="8" t="s">
-        <v>1130</v>
-      </c>
-      <c r="B84" s="225" t="s">
-        <v>1131</v>
-      </c>
-      <c r="C84" s="225" t="s">
-        <v>1105</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" ht="33">
-      <c r="A85" s="8" t="s">
-        <v>1130</v>
-      </c>
-      <c r="B85" s="225" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C85" s="225" t="s">
-        <v>1133</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" ht="33">
-      <c r="A86" s="8" t="s">
-        <v>1130</v>
-      </c>
-      <c r="B86" s="225" t="s">
-        <v>1134</v>
-      </c>
-      <c r="C86" s="225" t="s">
-        <v>1135</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" ht="66">
-      <c r="A87" s="8" t="s">
-        <v>1130</v>
-      </c>
-      <c r="B87" s="225" t="s">
-        <v>1136</v>
-      </c>
-      <c r="C87" s="225" t="s">
-        <v>1137</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" ht="33">
-      <c r="A88" s="8" t="s">
-        <v>1130</v>
-      </c>
-      <c r="B88" s="225" t="s">
-        <v>1138</v>
-      </c>
-      <c r="C88" s="225" t="s">
-        <v>1107</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" ht="33">
-      <c r="A89" s="8" t="s">
-        <v>1130</v>
-      </c>
-      <c r="B89" s="225" t="s">
-        <v>1139</v>
-      </c>
-      <c r="C89" s="225" t="s">
-        <v>1140</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" ht="16.5">
-      <c r="A90" s="8" t="s">
-        <v>1130</v>
-      </c>
-      <c r="B90" s="225" t="s">
-        <v>1141</v>
-      </c>
-      <c r="C90" s="225" t="s">
-        <v>1142</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" ht="16.5">
-      <c r="A91" s="8" t="s">
-        <v>1143</v>
-      </c>
-      <c r="B91" s="225" t="s">
-        <v>1144</v>
-      </c>
-      <c r="C91" s="225" t="s">
-        <v>1105</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" ht="33">
-      <c r="A92" s="8" t="s">
-        <v>1143</v>
-      </c>
-      <c r="B92" s="225" t="s">
-        <v>1134</v>
-      </c>
-      <c r="C92" s="225" t="s">
-        <v>1135</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" ht="16.5">
-      <c r="A93" s="8" t="s">
-        <v>1143</v>
-      </c>
-      <c r="B93" s="225" t="s">
-        <v>313</v>
-      </c>
-      <c r="C93" s="225" t="s">
-        <v>1085</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" ht="16.5">
-      <c r="A94" s="8" t="s">
-        <v>1143</v>
-      </c>
-      <c r="B94" s="225" t="s">
-        <v>810</v>
-      </c>
-      <c r="C94" s="225" t="s">
-        <v>1145</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" ht="33">
-      <c r="A95" s="8" t="s">
-        <v>1143</v>
-      </c>
-      <c r="B95" s="225" t="s">
-        <v>1146</v>
-      </c>
-      <c r="C95" s="225" t="s">
-        <v>1089</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" ht="16.5">
-      <c r="A96" s="8" t="s">
-        <v>1143</v>
-      </c>
-      <c r="B96" s="225" t="s">
-        <v>1147</v>
-      </c>
-      <c r="C96" s="225" t="s">
-        <v>1091</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" ht="33">
-      <c r="A97" s="8" t="s">
-        <v>1143</v>
-      </c>
-      <c r="B97" s="225" t="s">
-        <v>1148</v>
-      </c>
-      <c r="C97" s="225" t="s">
-        <v>1093</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" ht="16.5">
-      <c r="A98" s="8" t="s">
-        <v>1143</v>
-      </c>
-      <c r="B98" s="225" t="s">
-        <v>1149</v>
-      </c>
-      <c r="C98" s="225" t="s">
-        <v>1127</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" ht="16.5">
-      <c r="A99" s="8" t="s">
-        <v>1143</v>
-      </c>
-      <c r="B99" s="225" t="s">
-        <v>1150</v>
-      </c>
-      <c r="C99" s="225" t="s">
-        <v>1151</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" ht="33">
-      <c r="A100" s="8" t="s">
-        <v>1143</v>
-      </c>
-      <c r="B100" s="225" t="s">
-        <v>1152</v>
-      </c>
-      <c r="C100" s="225" t="s">
-        <v>1123</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" ht="33">
-      <c r="A101" s="8" t="s">
-        <v>1143</v>
-      </c>
-      <c r="B101" s="225" t="s">
-        <v>1139</v>
-      </c>
-      <c r="C101" s="225" t="s">
-        <v>1153</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" ht="33">
-      <c r="A102" s="8" t="s">
-        <v>1143</v>
-      </c>
-      <c r="B102" s="225" t="s">
-        <v>1154</v>
-      </c>
-      <c r="C102" s="225" t="s">
-        <v>1155</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" ht="16.5">
-      <c r="A103" s="8" t="s">
-        <v>1143</v>
-      </c>
-      <c r="B103" s="225" t="s">
-        <v>1156</v>
-      </c>
-      <c r="C103" s="225" t="s">
-        <v>1157</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" ht="33">
-      <c r="A104" s="8" t="s">
-        <v>1143</v>
-      </c>
-      <c r="B104" s="225" t="s">
-        <v>1158</v>
-      </c>
-      <c r="C104" s="225" t="s">
-        <v>1097</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" ht="16.5">
-      <c r="A105" s="8" t="s">
-        <v>1143</v>
-      </c>
-      <c r="B105" s="225" t="s">
-        <v>1159</v>
-      </c>
-      <c r="C105" s="225" t="s">
-        <v>1160</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3">
-      <c r="A107" s="7" t="s">
-        <v>1161</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3">
-      <c r="A109" s="7" t="s">
-        <v>1162</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3">
-      <c r="A111" s="7" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" ht="16.5">
-      <c r="A112" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="B112" s="123"/>
-    </row>
-    <row r="113" spans="1:2" ht="16.5">
-      <c r="A113" s="7" t="s">
-        <v>1163</v>
-      </c>
-      <c r="B113" s="123"/>
-    </row>
-    <row r="114" spans="1:2">
-      <c r="A114" s="7" t="s">
-        <v>1363</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2">
-      <c r="A115" s="7" t="s">
-        <v>1364</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A107" r:id="rId1" xr:uid="{401D9987-07E3-4647-BB2B-7A903C380234}"/>
-    <hyperlink ref="A109" r:id="rId2" location="log_format" display="https://nginx.org/en/docs/http/ngx_http_log_module.html - log_format" xr:uid="{DFDD8B62-3E12-40AE-AD46-FA136CBC8814}"/>
-    <hyperlink ref="A111" r:id="rId3" xr:uid="{E175D41D-64C5-47F9-B506-B0F465F0D6E1}"/>
-    <hyperlink ref="A112" r:id="rId4" xr:uid="{8270CEE3-8746-440A-B7C6-EF5D1D17561E}"/>
-    <hyperlink ref="A113" r:id="rId5" xr:uid="{0D920FAD-D933-4929-8E3D-78B04A8578BE}"/>
-    <hyperlink ref="A114" r:id="rId6" xr:uid="{F59092A8-E091-4E62-A4E8-B1766D61B7FF}"/>
-    <hyperlink ref="A115" r:id="rId7" location="Access_Log_Valve" xr:uid="{FE163D57-19AF-44B5-9620-A2EE256B10BC}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="300" r:id="rId8"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="80.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20.42578125" customWidth="1"/>
-    <col min="12" max="12" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="70.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="25" t="s">
-        <v>378</v>
-      </c>
-      <c r="B1" s="25" t="s">
-        <v>380</v>
-      </c>
-      <c r="C1" s="25" t="s">
-        <v>381</v>
-      </c>
-      <c r="D1" s="25" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="213" t="s">
-        <v>379</v>
-      </c>
-      <c r="B2" s="57" t="s">
-        <v>382</v>
-      </c>
-      <c r="C2" s="57" t="s">
-        <v>383</v>
-      </c>
-      <c r="D2" s="58" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="213"/>
-      <c r="B3" s="20" t="s">
-        <v>262</v>
-      </c>
-      <c r="C3" s="20" t="s">
-        <v>384</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="213"/>
-      <c r="B4" s="20" t="s">
-        <v>385</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>386</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="213"/>
-      <c r="B5" s="57" t="s">
-        <v>544</v>
-      </c>
-      <c r="C5" s="57" t="s">
-        <v>387</v>
-      </c>
-      <c r="D5" s="58" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="213"/>
-      <c r="B6" s="20" t="s">
-        <v>388</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>389</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="213"/>
-      <c r="B7" s="20" t="s">
-        <v>390</v>
-      </c>
-      <c r="C7" s="20" t="s">
-        <v>393</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="25" t="s">
-        <v>276</v>
-      </c>
-      <c r="B9" s="25" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="20">
-        <v>1</v>
-      </c>
-      <c r="B10" s="19" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="20">
-        <v>2</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="20">
-        <v>3</v>
-      </c>
-      <c r="B12" s="19" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="20">
-        <v>3</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="20">
-        <v>4</v>
-      </c>
-      <c r="B14" s="19" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="20">
-        <v>5</v>
-      </c>
-      <c r="B15" s="19" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" t="s">
-        <v>283</v>
-      </c>
-      <c r="B19" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" t="s">
-        <v>284</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:A7"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -23112,6 +21793,1681 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37379847-1933-4532-BA71-36026569AE7D}">
+  <dimension ref="A1:H115"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" customWidth="1"/>
+    <col min="3" max="3" width="163.7109375" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="74.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="165" t="s">
+        <v>971</v>
+      </c>
+      <c r="B1" s="166" t="s">
+        <v>972</v>
+      </c>
+      <c r="C1" s="166" t="s">
+        <v>973</v>
+      </c>
+      <c r="E1" s="165" t="s">
+        <v>971</v>
+      </c>
+      <c r="F1" s="166" t="s">
+        <v>972</v>
+      </c>
+      <c r="G1" s="166" t="s">
+        <v>973</v>
+      </c>
+      <c r="H1" s="166" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>974</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>975</v>
+      </c>
+      <c r="E2" s="164" t="s">
+        <v>1407</v>
+      </c>
+      <c r="F2" s="164" t="s">
+        <v>1365</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>1386</v>
+      </c>
+      <c r="H2" s="164" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>976</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>977</v>
+      </c>
+      <c r="E3" s="164" t="s">
+        <v>1407</v>
+      </c>
+      <c r="F3" s="164" t="s">
+        <v>1366</v>
+      </c>
+      <c r="G3" s="19" t="s">
+        <v>1387</v>
+      </c>
+      <c r="H3" s="164" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>978</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>979</v>
+      </c>
+      <c r="E4" s="164" t="s">
+        <v>1407</v>
+      </c>
+      <c r="F4" s="164" t="s">
+        <v>1367</v>
+      </c>
+      <c r="G4" s="19" t="s">
+        <v>1388</v>
+      </c>
+      <c r="H4" s="164" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>980</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>981</v>
+      </c>
+      <c r="E5" s="164" t="s">
+        <v>1407</v>
+      </c>
+      <c r="F5" s="164" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>1389</v>
+      </c>
+      <c r="H5" s="164" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>982</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>983</v>
+      </c>
+      <c r="E6" s="164" t="s">
+        <v>1407</v>
+      </c>
+      <c r="F6" s="164" t="s">
+        <v>1369</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>1390</v>
+      </c>
+      <c r="H6" s="164" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>984</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>985</v>
+      </c>
+      <c r="E7" s="164" t="s">
+        <v>1407</v>
+      </c>
+      <c r="F7" s="164" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>1391</v>
+      </c>
+      <c r="H7" s="164" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="168" t="s">
+        <v>758</v>
+      </c>
+      <c r="B8" s="168" t="s">
+        <v>986</v>
+      </c>
+      <c r="C8" s="168" t="s">
+        <v>987</v>
+      </c>
+      <c r="E8" s="164" t="s">
+        <v>1407</v>
+      </c>
+      <c r="F8" s="164" t="s">
+        <v>1371</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>1392</v>
+      </c>
+      <c r="H8" s="164" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>988</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>989</v>
+      </c>
+      <c r="E9" s="164" t="s">
+        <v>1407</v>
+      </c>
+      <c r="F9" s="164" t="s">
+        <v>1372</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>1393</v>
+      </c>
+      <c r="H9" s="164" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>990</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>991</v>
+      </c>
+      <c r="E10" s="164" t="s">
+        <v>1407</v>
+      </c>
+      <c r="F10" s="164" t="s">
+        <v>1373</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>1394</v>
+      </c>
+      <c r="H10" s="164" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>992</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>993</v>
+      </c>
+      <c r="E11" s="164" t="s">
+        <v>1407</v>
+      </c>
+      <c r="F11" s="164" t="s">
+        <v>1374</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>1395</v>
+      </c>
+      <c r="H11" s="164" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>994</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>995</v>
+      </c>
+      <c r="E12" s="164" t="s">
+        <v>1407</v>
+      </c>
+      <c r="F12" s="164" t="s">
+        <v>1375</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>1396</v>
+      </c>
+      <c r="H12" s="164" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>996</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>997</v>
+      </c>
+      <c r="E13" s="164" t="s">
+        <v>1407</v>
+      </c>
+      <c r="F13" s="164" t="s">
+        <v>1376</v>
+      </c>
+      <c r="G13" s="19" t="s">
+        <v>1397</v>
+      </c>
+      <c r="H13" s="164" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>998</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>999</v>
+      </c>
+      <c r="E14" s="164" t="s">
+        <v>1407</v>
+      </c>
+      <c r="F14" s="164" t="s">
+        <v>1377</v>
+      </c>
+      <c r="G14" s="19" t="s">
+        <v>1398</v>
+      </c>
+      <c r="H14" s="164" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>1001</v>
+      </c>
+      <c r="E15" s="164" t="s">
+        <v>1407</v>
+      </c>
+      <c r="F15" s="164" t="s">
+        <v>1378</v>
+      </c>
+      <c r="G15" s="19" t="s">
+        <v>1399</v>
+      </c>
+      <c r="H15" s="164" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>1003</v>
+      </c>
+      <c r="E16" s="164" t="s">
+        <v>1407</v>
+      </c>
+      <c r="F16" s="164" t="s">
+        <v>1379</v>
+      </c>
+      <c r="G16" s="19" t="s">
+        <v>1400</v>
+      </c>
+      <c r="H16" s="164" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>1005</v>
+      </c>
+      <c r="E17" s="164" t="s">
+        <v>1407</v>
+      </c>
+      <c r="F17" s="164" t="s">
+        <v>1380</v>
+      </c>
+      <c r="G17" s="19" t="s">
+        <v>1401</v>
+      </c>
+      <c r="H17" s="164" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>1007</v>
+      </c>
+      <c r="E18" s="164" t="s">
+        <v>1407</v>
+      </c>
+      <c r="F18" s="164" t="s">
+        <v>1381</v>
+      </c>
+      <c r="G18" s="19" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H18" s="164" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>1009</v>
+      </c>
+      <c r="E19" s="163" t="s">
+        <v>1407</v>
+      </c>
+      <c r="F19" s="163" t="s">
+        <v>1382</v>
+      </c>
+      <c r="G19" s="167" t="s">
+        <v>1403</v>
+      </c>
+      <c r="H19" s="163" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E20" s="164" t="s">
+        <v>1407</v>
+      </c>
+      <c r="F20" s="164" t="s">
+        <v>1383</v>
+      </c>
+      <c r="G20" s="19" t="s">
+        <v>1404</v>
+      </c>
+      <c r="H20" s="164" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>1013</v>
+      </c>
+      <c r="E21" s="164" t="s">
+        <v>1407</v>
+      </c>
+      <c r="F21" s="164" t="s">
+        <v>1384</v>
+      </c>
+      <c r="G21" s="19" t="s">
+        <v>1405</v>
+      </c>
+      <c r="H21" s="164" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E22" s="164" t="s">
+        <v>1407</v>
+      </c>
+      <c r="F22" s="164" t="s">
+        <v>1385</v>
+      </c>
+      <c r="G22" s="19" t="s">
+        <v>1406</v>
+      </c>
+      <c r="H22" s="164" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F23" s="81"/>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>837</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>835</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>948</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>833</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>836</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="122" t="s">
+        <v>385</v>
+      </c>
+      <c r="B43" s="122" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C43" s="122" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="122" t="s">
+        <v>385</v>
+      </c>
+      <c r="B44" s="122" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C44" s="122" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="122" t="s">
+        <v>385</v>
+      </c>
+      <c r="B45" s="122" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C45" s="122" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="122" t="s">
+        <v>385</v>
+      </c>
+      <c r="B46" s="122" t="s">
+        <v>619</v>
+      </c>
+      <c r="C46" s="122" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="122" t="s">
+        <v>385</v>
+      </c>
+      <c r="B47" s="122" t="s">
+        <v>617</v>
+      </c>
+      <c r="C47" s="122" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="122" t="s">
+        <v>385</v>
+      </c>
+      <c r="B48" s="122" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C48" s="122" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="122" t="s">
+        <v>385</v>
+      </c>
+      <c r="B49" s="122" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C49" s="122" t="s">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="122" t="s">
+        <v>385</v>
+      </c>
+      <c r="B50" s="122" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C50" s="122" t="s">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="122" t="s">
+        <v>385</v>
+      </c>
+      <c r="B51" s="122" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C51" s="122" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="122" t="s">
+        <v>385</v>
+      </c>
+      <c r="B52" s="122" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C52" s="122" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" s="122" t="s">
+        <v>385</v>
+      </c>
+      <c r="B53" s="122" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" s="122" t="s">
+        <v>385</v>
+      </c>
+      <c r="B54" s="122" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" s="122" t="s">
+        <v>385</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" s="122" t="s">
+        <v>385</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" s="122" t="s">
+        <v>385</v>
+      </c>
+      <c r="B57" s="8" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="30">
+      <c r="A58" s="122" t="s">
+        <v>385</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C58" s="18" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" s="122" t="s">
+        <v>385</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C59" s="8" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" s="122" t="s">
+        <v>385</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="16.5">
+      <c r="A61" s="8" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B61" s="169" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C61" s="169" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="16.5">
+      <c r="A62" s="8" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B62" s="170" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C62" s="170" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="16.5">
+      <c r="A63" s="8" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B63" s="170" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C63" s="170" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="19.5" customHeight="1">
+      <c r="A64" s="8" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B64" s="170" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C64" s="170" t="s">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" ht="16.5">
+      <c r="A65" s="8" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B65" s="170" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C65" s="170" t="s">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="16.5">
+      <c r="A66" s="8" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B66" s="170" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C66" s="170" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" ht="16.5">
+      <c r="A67" s="8" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B67" s="170" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C67" s="170" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" ht="16.5">
+      <c r="A68" s="8" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B68" s="170" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C68" s="170" t="s">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" ht="16.5">
+      <c r="A69" s="8" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B69" s="170" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C69" s="170" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" ht="16.5">
+      <c r="A70" s="8" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B70" s="170" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C70" s="170" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" ht="16.5">
+      <c r="A71" s="8" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B71" s="170" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C71" s="170" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" ht="16.5">
+      <c r="A72" s="8" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B72" s="170" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C72" s="170" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" ht="16.5">
+      <c r="A73" s="8" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B73" s="170" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C73" s="170" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" ht="16.5">
+      <c r="A74" s="8" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B74" s="170" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C74" s="170" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" ht="16.5">
+      <c r="A75" s="8" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B75" s="170" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C75" s="170" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" ht="16.5">
+      <c r="A76" s="8" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B76" s="170" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C76" s="170" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" ht="16.5">
+      <c r="A77" s="8" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B77" s="170" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C77" s="170" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="16.5">
+      <c r="A78" s="8" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B78" s="170" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C78" s="170" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" ht="16.5">
+      <c r="A79" s="8" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B79" s="170" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C79" s="170" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" ht="16.5">
+      <c r="A80" s="8" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B80" s="170" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C80" s="170" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" ht="16.5">
+      <c r="A81" s="8" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B81" s="170" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C81" s="170" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" ht="16.5">
+      <c r="A82" s="8" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B82" s="170" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C82" s="170" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" ht="16.5">
+      <c r="A83" s="8" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B83" s="170" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C83" s="170" t="s">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" ht="16.5">
+      <c r="A84" s="8" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B84" s="170" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C84" s="170" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" ht="16.5">
+      <c r="A85" s="8" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B85" s="170" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C85" s="170" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" ht="33">
+      <c r="A86" s="8" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B86" s="170" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C86" s="170" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" ht="49.5">
+      <c r="A87" s="8" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B87" s="170" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C87" s="170" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" ht="33">
+      <c r="A88" s="8" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B88" s="170" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C88" s="170" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" ht="16.5">
+      <c r="A89" s="8" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B89" s="170" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C89" s="170" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" ht="16.5">
+      <c r="A90" s="8" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B90" s="170" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C90" s="170" t="s">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" ht="16.5">
+      <c r="A91" s="8" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B91" s="170" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C91" s="170" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" ht="33">
+      <c r="A92" s="8" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B92" s="170" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C92" s="170" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" ht="16.5">
+      <c r="A93" s="8" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B93" s="170" t="s">
+        <v>313</v>
+      </c>
+      <c r="C93" s="170" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" ht="16.5">
+      <c r="A94" s="8" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B94" s="170" t="s">
+        <v>810</v>
+      </c>
+      <c r="C94" s="170" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" ht="16.5">
+      <c r="A95" s="8" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B95" s="170" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C95" s="170" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" ht="16.5">
+      <c r="A96" s="8" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B96" s="170" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C96" s="170" t="s">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" ht="16.5">
+      <c r="A97" s="8" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B97" s="170" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C97" s="170" t="s">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" ht="16.5">
+      <c r="A98" s="8" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B98" s="170" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C98" s="170" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" ht="16.5">
+      <c r="A99" s="8" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B99" s="170" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C99" s="170" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" ht="16.5">
+      <c r="A100" s="8" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B100" s="170" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C100" s="170" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" ht="16.5">
+      <c r="A101" s="8" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B101" s="170" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C101" s="170" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" ht="16.5">
+      <c r="A102" s="8" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B102" s="170" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C102" s="170" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" ht="16.5">
+      <c r="A103" s="8" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B103" s="170" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C103" s="170" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" ht="16.5">
+      <c r="A104" s="8" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B104" s="170" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C104" s="170" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" ht="16.5">
+      <c r="A105" s="8" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B105" s="170" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C105" s="170" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
+      <c r="A107" s="7" t="s">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109" s="7" t="s">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111" s="7" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" ht="16.5">
+      <c r="A112" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="B112" s="123"/>
+    </row>
+    <row r="113" spans="1:2" ht="16.5">
+      <c r="A113" s="7" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B113" s="123"/>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" s="7" t="s">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="7" t="s">
+        <v>1364</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A107" r:id="rId1" xr:uid="{401D9987-07E3-4647-BB2B-7A903C380234}"/>
+    <hyperlink ref="A109" r:id="rId2" location="log_format" display="https://nginx.org/en/docs/http/ngx_http_log_module.html - log_format" xr:uid="{DFDD8B62-3E12-40AE-AD46-FA136CBC8814}"/>
+    <hyperlink ref="A111" r:id="rId3" xr:uid="{E175D41D-64C5-47F9-B506-B0F465F0D6E1}"/>
+    <hyperlink ref="A112" r:id="rId4" xr:uid="{8270CEE3-8746-440A-B7C6-EF5D1D17561E}"/>
+    <hyperlink ref="A113" r:id="rId5" xr:uid="{0D920FAD-D933-4929-8E3D-78B04A8578BE}"/>
+    <hyperlink ref="A114" r:id="rId6" xr:uid="{F59092A8-E091-4E62-A4E8-B1766D61B7FF}"/>
+    <hyperlink ref="A115" r:id="rId7" location="Access_Log_Valve" xr:uid="{FE163D57-19AF-44B5-9620-A2EE256B10BC}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="300" r:id="rId8"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+  <dimension ref="A1:D20"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="80.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.42578125" customWidth="1"/>
+    <col min="12" max="12" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="70.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="25" t="s">
+        <v>378</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>380</v>
+      </c>
+      <c r="C1" s="25" t="s">
+        <v>381</v>
+      </c>
+      <c r="D1" s="25" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="220" t="s">
+        <v>379</v>
+      </c>
+      <c r="B2" s="57" t="s">
+        <v>382</v>
+      </c>
+      <c r="C2" s="57" t="s">
+        <v>383</v>
+      </c>
+      <c r="D2" s="58" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="220"/>
+      <c r="B3" s="20" t="s">
+        <v>262</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>384</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="220"/>
+      <c r="B4" s="20" t="s">
+        <v>385</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>386</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="220"/>
+      <c r="B5" s="57" t="s">
+        <v>544</v>
+      </c>
+      <c r="C5" s="57" t="s">
+        <v>387</v>
+      </c>
+      <c r="D5" s="58" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="220"/>
+      <c r="B6" s="20" t="s">
+        <v>388</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>389</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="220"/>
+      <c r="B7" s="20" t="s">
+        <v>390</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>393</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="25" t="s">
+        <v>276</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="20">
+        <v>1</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="20">
+        <v>2</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="20">
+        <v>3</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="20">
+        <v>3</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="20">
+        <v>4</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="20">
+        <v>5</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>283</v>
+      </c>
+      <c r="B19" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>284</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:A7"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:B48"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -23372,7 +23728,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:E96"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -24255,7 +24611,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:E28"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -24626,7 +24982,7 @@
     </row>
     <row r="22" spans="7:24">
       <c r="K22" s="144"/>
-      <c r="V22" s="174" t="s">
+      <c r="V22" s="181" t="s">
         <v>832</v>
       </c>
       <c r="W22" s="9" t="s">
@@ -24649,7 +25005,7 @@
       </c>
       <c r="Q23" s="142"/>
       <c r="R23" s="142"/>
-      <c r="V23" s="175"/>
+      <c r="V23" s="182"/>
       <c r="W23" s="9" t="s">
         <v>815</v>
       </c>
@@ -24659,7 +25015,7 @@
     </row>
     <row r="24" spans="7:24">
       <c r="K24" s="144"/>
-      <c r="V24" s="175"/>
+      <c r="V24" s="182"/>
       <c r="W24" s="9" t="s">
         <v>816</v>
       </c>
@@ -24674,7 +25030,7 @@
       <c r="L25" s="5" t="s">
         <v>891</v>
       </c>
-      <c r="V25" s="175"/>
+      <c r="V25" s="182"/>
       <c r="W25" s="9" t="s">
         <v>817</v>
       </c>
@@ -24693,7 +25049,7 @@
       <c r="O26" t="s">
         <v>897</v>
       </c>
-      <c r="V26" s="175"/>
+      <c r="V26" s="182"/>
       <c r="W26" s="9" t="s">
         <v>824</v>
       </c>
@@ -24707,7 +25063,7 @@
       <c r="N27" t="s">
         <v>896</v>
       </c>
-      <c r="V27" s="175"/>
+      <c r="V27" s="182"/>
       <c r="W27" s="9" t="s">
         <v>825</v>
       </c>
@@ -24718,7 +25074,7 @@
       <c r="N28" t="s">
         <v>898</v>
       </c>
-      <c r="V28" s="175"/>
+      <c r="V28" s="182"/>
       <c r="W28" s="9" t="s">
         <v>826</v>
       </c>
@@ -24731,7 +25087,7 @@
       <c r="N29" t="s">
         <v>899</v>
       </c>
-      <c r="V29" s="176"/>
+      <c r="V29" s="183"/>
       <c r="W29" s="9" t="s">
         <v>827</v>
       </c>
@@ -24747,7 +25103,7 @@
       <c r="N30" t="s">
         <v>852</v>
       </c>
-      <c r="V30" s="171" t="s">
+      <c r="V30" s="178" t="s">
         <v>831</v>
       </c>
       <c r="W30" s="49" t="s">
@@ -24760,7 +25116,7 @@
       <c r="N31" t="s">
         <v>901</v>
       </c>
-      <c r="V31" s="172"/>
+      <c r="V31" s="179"/>
       <c r="W31" s="49" t="s">
         <v>822</v>
       </c>
@@ -24782,7 +25138,7 @@
       </c>
       <c r="Q32" s="142"/>
       <c r="R32" s="142"/>
-      <c r="V32" s="173"/>
+      <c r="V32" s="180"/>
       <c r="W32" s="49" t="s">
         <v>823</v>
       </c>
@@ -24922,7 +25278,7 @@
       <c r="R5" s="13" t="s">
         <v>352</v>
       </c>
-      <c r="S5" s="177" t="s">
+      <c r="S5" s="184" t="s">
         <v>809</v>
       </c>
     </row>
@@ -24939,7 +25295,7 @@
       <c r="R6" s="9" t="s">
         <v>602</v>
       </c>
-      <c r="S6" s="177"/>
+      <c r="S6" s="184"/>
     </row>
     <row r="7" spans="3:20">
       <c r="O7" s="81" t="s">
@@ -24954,7 +25310,7 @@
       <c r="R7" s="9" t="s">
         <v>603</v>
       </c>
-      <c r="S7" s="177"/>
+      <c r="S7" s="184"/>
     </row>
     <row r="8" spans="3:20">
       <c r="O8" s="81" t="s">
@@ -24969,7 +25325,7 @@
       <c r="R8" s="9" t="s">
         <v>350</v>
       </c>
-      <c r="S8" s="177"/>
+      <c r="S8" s="184"/>
     </row>
     <row r="9" spans="3:20">
       <c r="O9" s="81" t="s">
@@ -24984,7 +25340,7 @@
       <c r="R9" s="9" t="s">
         <v>349</v>
       </c>
-      <c r="S9" s="177"/>
+      <c r="S9" s="184"/>
     </row>
     <row r="10" spans="3:20">
       <c r="Q10" s="9" t="s">
@@ -25009,7 +25365,7 @@
       </c>
     </row>
     <row r="15" spans="3:20">
-      <c r="Q15" s="174" t="s">
+      <c r="Q15" s="181" t="s">
         <v>832</v>
       </c>
       <c r="R15" s="9" t="s">
@@ -25044,7 +25400,7 @@
       <c r="J16" s="10" t="s">
         <v>813</v>
       </c>
-      <c r="Q16" s="175"/>
+      <c r="Q16" s="182"/>
       <c r="R16" s="9" t="s">
         <v>815</v>
       </c>
@@ -25054,7 +25410,7 @@
     </row>
     <row r="17" spans="10:19">
       <c r="J17" s="81"/>
-      <c r="Q17" s="175"/>
+      <c r="Q17" s="182"/>
       <c r="R17" s="9" t="s">
         <v>816</v>
       </c>
@@ -25063,7 +25419,7 @@
       </c>
     </row>
     <row r="18" spans="10:19">
-      <c r="Q18" s="175"/>
+      <c r="Q18" s="182"/>
       <c r="R18" s="9" t="s">
         <v>817</v>
       </c>
@@ -25072,21 +25428,21 @@
       </c>
     </row>
     <row r="19" spans="10:19">
-      <c r="Q19" s="175"/>
+      <c r="Q19" s="182"/>
       <c r="R19" s="9" t="s">
         <v>824</v>
       </c>
       <c r="S19" s="92"/>
     </row>
     <row r="20" spans="10:19">
-      <c r="Q20" s="175"/>
+      <c r="Q20" s="182"/>
       <c r="R20" s="9" t="s">
         <v>825</v>
       </c>
       <c r="S20" s="92"/>
     </row>
     <row r="21" spans="10:19">
-      <c r="Q21" s="175"/>
+      <c r="Q21" s="182"/>
       <c r="R21" s="9" t="s">
         <v>826</v>
       </c>
@@ -25095,7 +25451,7 @@
       </c>
     </row>
     <row r="22" spans="10:19">
-      <c r="Q22" s="176"/>
+      <c r="Q22" s="183"/>
       <c r="R22" s="9" t="s">
         <v>827</v>
       </c>
@@ -25104,7 +25460,7 @@
       </c>
     </row>
     <row r="23" spans="10:19">
-      <c r="Q23" s="174" t="s">
+      <c r="Q23" s="181" t="s">
         <v>831</v>
       </c>
       <c r="R23" s="9" t="s">
@@ -25113,14 +25469,14 @@
       <c r="S23" s="92"/>
     </row>
     <row r="24" spans="10:19">
-      <c r="Q24" s="175"/>
+      <c r="Q24" s="182"/>
       <c r="R24" s="9" t="s">
         <v>822</v>
       </c>
       <c r="S24" s="92"/>
     </row>
     <row r="25" spans="10:19">
-      <c r="Q25" s="176"/>
+      <c r="Q25" s="183"/>
       <c r="R25" s="9" t="s">
         <v>823</v>
       </c>
@@ -25186,39 +25542,39 @@
       <c r="B1" t="s">
         <v>860</v>
       </c>
-      <c r="J1" s="178" t="s">
+      <c r="J1" s="185" t="s">
         <v>952</v>
       </c>
-      <c r="K1" s="179"/>
-      <c r="L1" s="179"/>
-      <c r="M1" s="179"/>
-      <c r="N1" s="179"/>
-      <c r="O1" s="179"/>
-      <c r="P1" s="179"/>
-      <c r="Q1" s="179"/>
+      <c r="K1" s="186"/>
+      <c r="L1" s="186"/>
+      <c r="M1" s="186"/>
+      <c r="N1" s="186"/>
+      <c r="O1" s="186"/>
+      <c r="P1" s="186"/>
+      <c r="Q1" s="186"/>
     </row>
     <row r="2" spans="1:17">
-      <c r="J2" s="179"/>
-      <c r="K2" s="179"/>
-      <c r="L2" s="179"/>
-      <c r="M2" s="179"/>
-      <c r="N2" s="179"/>
-      <c r="O2" s="179"/>
-      <c r="P2" s="179"/>
-      <c r="Q2" s="179"/>
+      <c r="J2" s="186"/>
+      <c r="K2" s="186"/>
+      <c r="L2" s="186"/>
+      <c r="M2" s="186"/>
+      <c r="N2" s="186"/>
+      <c r="O2" s="186"/>
+      <c r="P2" s="186"/>
+      <c r="Q2" s="186"/>
     </row>
     <row r="3" spans="1:17">
       <c r="A3" s="6" t="s">
         <v>861</v>
       </c>
-      <c r="J3" s="179"/>
-      <c r="K3" s="179"/>
-      <c r="L3" s="179"/>
-      <c r="M3" s="179"/>
-      <c r="N3" s="179"/>
-      <c r="O3" s="179"/>
-      <c r="P3" s="179"/>
-      <c r="Q3" s="179"/>
+      <c r="J3" s="186"/>
+      <c r="K3" s="186"/>
+      <c r="L3" s="186"/>
+      <c r="M3" s="186"/>
+      <c r="N3" s="186"/>
+      <c r="O3" s="186"/>
+      <c r="P3" s="186"/>
+      <c r="Q3" s="186"/>
     </row>
     <row r="4" spans="1:17">
       <c r="A4" t="s">
@@ -25230,24 +25586,24 @@
       <c r="D4" t="s">
         <v>863</v>
       </c>
-      <c r="J4" s="179"/>
-      <c r="K4" s="179"/>
-      <c r="L4" s="179"/>
-      <c r="M4" s="179"/>
-      <c r="N4" s="179"/>
-      <c r="O4" s="179"/>
-      <c r="P4" s="179"/>
-      <c r="Q4" s="179"/>
+      <c r="J4" s="186"/>
+      <c r="K4" s="186"/>
+      <c r="L4" s="186"/>
+      <c r="M4" s="186"/>
+      <c r="N4" s="186"/>
+      <c r="O4" s="186"/>
+      <c r="P4" s="186"/>
+      <c r="Q4" s="186"/>
     </row>
     <row r="5" spans="1:17">
-      <c r="J5" s="179"/>
-      <c r="K5" s="179"/>
-      <c r="L5" s="179"/>
-      <c r="M5" s="179"/>
-      <c r="N5" s="179"/>
-      <c r="O5" s="179"/>
-      <c r="P5" s="179"/>
-      <c r="Q5" s="179"/>
+      <c r="J5" s="186"/>
+      <c r="K5" s="186"/>
+      <c r="L5" s="186"/>
+      <c r="M5" s="186"/>
+      <c r="N5" s="186"/>
+      <c r="O5" s="186"/>
+      <c r="P5" s="186"/>
+      <c r="Q5" s="186"/>
     </row>
     <row r="6" spans="1:17" ht="15.75" thickBot="1">
       <c r="A6" t="s">
@@ -25256,38 +25612,38 @@
       <c r="E6" t="s">
         <v>918</v>
       </c>
-      <c r="J6" s="179"/>
-      <c r="K6" s="179"/>
-      <c r="L6" s="179"/>
-      <c r="M6" s="179"/>
-      <c r="N6" s="179"/>
-      <c r="O6" s="179"/>
-      <c r="P6" s="179"/>
-      <c r="Q6" s="179"/>
+      <c r="J6" s="186"/>
+      <c r="K6" s="186"/>
+      <c r="L6" s="186"/>
+      <c r="M6" s="186"/>
+      <c r="N6" s="186"/>
+      <c r="O6" s="186"/>
+      <c r="P6" s="186"/>
+      <c r="Q6" s="186"/>
     </row>
     <row r="7" spans="1:17" ht="15.75" thickBot="1">
       <c r="A7" s="105" t="s">
         <v>865</v>
       </c>
-      <c r="J7" s="179"/>
-      <c r="K7" s="179"/>
-      <c r="L7" s="179"/>
-      <c r="M7" s="179"/>
-      <c r="N7" s="179"/>
-      <c r="O7" s="179"/>
-      <c r="P7" s="179"/>
-      <c r="Q7" s="179"/>
+      <c r="J7" s="186"/>
+      <c r="K7" s="186"/>
+      <c r="L7" s="186"/>
+      <c r="M7" s="186"/>
+      <c r="N7" s="186"/>
+      <c r="O7" s="186"/>
+      <c r="P7" s="186"/>
+      <c r="Q7" s="186"/>
     </row>
     <row r="8" spans="1:17">
       <c r="A8" s="117"/>
-      <c r="J8" s="179"/>
-      <c r="K8" s="179"/>
-      <c r="L8" s="179"/>
-      <c r="M8" s="179"/>
-      <c r="N8" s="179"/>
-      <c r="O8" s="179"/>
-      <c r="P8" s="179"/>
-      <c r="Q8" s="179"/>
+      <c r="J8" s="186"/>
+      <c r="K8" s="186"/>
+      <c r="L8" s="186"/>
+      <c r="M8" s="186"/>
+      <c r="N8" s="186"/>
+      <c r="O8" s="186"/>
+      <c r="P8" s="186"/>
+      <c r="Q8" s="186"/>
     </row>
     <row r="9" spans="1:17">
       <c r="A9" t="s">
@@ -25296,14 +25652,14 @@
       <c r="B9" t="s">
         <v>924</v>
       </c>
-      <c r="J9" s="179"/>
-      <c r="K9" s="179"/>
-      <c r="L9" s="179"/>
-      <c r="M9" s="179"/>
-      <c r="N9" s="179"/>
-      <c r="O9" s="179"/>
-      <c r="P9" s="179"/>
-      <c r="Q9" s="179"/>
+      <c r="J9" s="186"/>
+      <c r="K9" s="186"/>
+      <c r="L9" s="186"/>
+      <c r="M9" s="186"/>
+      <c r="N9" s="186"/>
+      <c r="O9" s="186"/>
+      <c r="P9" s="186"/>
+      <c r="Q9" s="186"/>
     </row>
     <row r="10" spans="1:17">
       <c r="A10" t="s">
@@ -25324,14 +25680,14 @@
       <c r="H10" t="s">
         <v>950</v>
       </c>
-      <c r="J10" s="179"/>
-      <c r="K10" s="179"/>
-      <c r="L10" s="179"/>
-      <c r="M10" s="179"/>
-      <c r="N10" s="179"/>
-      <c r="O10" s="179"/>
-      <c r="P10" s="179"/>
-      <c r="Q10" s="179"/>
+      <c r="J10" s="186"/>
+      <c r="K10" s="186"/>
+      <c r="L10" s="186"/>
+      <c r="M10" s="186"/>
+      <c r="N10" s="186"/>
+      <c r="O10" s="186"/>
+      <c r="P10" s="186"/>
+      <c r="Q10" s="186"/>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" t="s">
@@ -25352,14 +25708,14 @@
       <c r="H11" t="s">
         <v>951</v>
       </c>
-      <c r="J11" s="179"/>
-      <c r="K11" s="179"/>
-      <c r="L11" s="179"/>
-      <c r="M11" s="179"/>
-      <c r="N11" s="179"/>
-      <c r="O11" s="179"/>
-      <c r="P11" s="179"/>
-      <c r="Q11" s="179"/>
+      <c r="J11" s="186"/>
+      <c r="K11" s="186"/>
+      <c r="L11" s="186"/>
+      <c r="M11" s="186"/>
+      <c r="N11" s="186"/>
+      <c r="O11" s="186"/>
+      <c r="P11" s="186"/>
+      <c r="Q11" s="186"/>
     </row>
     <row r="12" spans="1:17">
       <c r="B12" t="s">
@@ -25374,14 +25730,14 @@
       <c r="H12" t="s">
         <v>951</v>
       </c>
-      <c r="J12" s="179"/>
-      <c r="K12" s="179"/>
-      <c r="L12" s="179"/>
-      <c r="M12" s="179"/>
-      <c r="N12" s="179"/>
-      <c r="O12" s="179"/>
-      <c r="P12" s="179"/>
-      <c r="Q12" s="179"/>
+      <c r="J12" s="186"/>
+      <c r="K12" s="186"/>
+      <c r="L12" s="186"/>
+      <c r="M12" s="186"/>
+      <c r="N12" s="186"/>
+      <c r="O12" s="186"/>
+      <c r="P12" s="186"/>
+      <c r="Q12" s="186"/>
     </row>
     <row r="13" spans="1:17">
       <c r="F13" t="s">
@@ -25393,24 +25749,24 @@
       <c r="H13" t="s">
         <v>951</v>
       </c>
-      <c r="J13" s="179"/>
-      <c r="K13" s="179"/>
-      <c r="L13" s="179"/>
-      <c r="M13" s="179"/>
-      <c r="N13" s="179"/>
-      <c r="O13" s="179"/>
-      <c r="P13" s="179"/>
-      <c r="Q13" s="179"/>
+      <c r="J13" s="186"/>
+      <c r="K13" s="186"/>
+      <c r="L13" s="186"/>
+      <c r="M13" s="186"/>
+      <c r="N13" s="186"/>
+      <c r="O13" s="186"/>
+      <c r="P13" s="186"/>
+      <c r="Q13" s="186"/>
     </row>
     <row r="14" spans="1:17">
-      <c r="J14" s="179"/>
-      <c r="K14" s="179"/>
-      <c r="L14" s="179"/>
-      <c r="M14" s="179"/>
-      <c r="N14" s="179"/>
-      <c r="O14" s="179"/>
-      <c r="P14" s="179"/>
-      <c r="Q14" s="179"/>
+      <c r="J14" s="186"/>
+      <c r="K14" s="186"/>
+      <c r="L14" s="186"/>
+      <c r="M14" s="186"/>
+      <c r="N14" s="186"/>
+      <c r="O14" s="186"/>
+      <c r="P14" s="186"/>
+      <c r="Q14" s="186"/>
     </row>
     <row r="15" spans="1:17">
       <c r="A15" t="s">
@@ -25419,27 +25775,27 @@
       <c r="C15" t="s">
         <v>947</v>
       </c>
-      <c r="J15" s="179"/>
-      <c r="K15" s="179"/>
-      <c r="L15" s="179"/>
-      <c r="M15" s="179"/>
-      <c r="N15" s="179"/>
-      <c r="O15" s="179"/>
-      <c r="P15" s="179"/>
-      <c r="Q15" s="179"/>
+      <c r="J15" s="186"/>
+      <c r="K15" s="186"/>
+      <c r="L15" s="186"/>
+      <c r="M15" s="186"/>
+      <c r="N15" s="186"/>
+      <c r="O15" s="186"/>
+      <c r="P15" s="186"/>
+      <c r="Q15" s="186"/>
     </row>
     <row r="16" spans="1:17">
       <c r="A16" t="s">
         <v>937</v>
       </c>
-      <c r="J16" s="179"/>
-      <c r="K16" s="179"/>
-      <c r="L16" s="179"/>
-      <c r="M16" s="179"/>
-      <c r="N16" s="179"/>
-      <c r="O16" s="179"/>
-      <c r="P16" s="179"/>
-      <c r="Q16" s="179"/>
+      <c r="J16" s="186"/>
+      <c r="K16" s="186"/>
+      <c r="L16" s="186"/>
+      <c r="M16" s="186"/>
+      <c r="N16" s="186"/>
+      <c r="O16" s="186"/>
+      <c r="P16" s="186"/>
+      <c r="Q16" s="186"/>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="5" t="s">
@@ -25724,19 +26080,19 @@
       <c r="E7" s="31" t="s">
         <v>449</v>
       </c>
-      <c r="F7" s="180" t="s">
+      <c r="F7" s="187" t="s">
         <v>441</v>
       </c>
-      <c r="G7" s="180"/>
-      <c r="H7" s="180"/>
-      <c r="I7" s="180"/>
-      <c r="J7" s="180"/>
-      <c r="K7" s="180"/>
-      <c r="L7" s="180"/>
-      <c r="M7" s="180"/>
-      <c r="N7" s="180"/>
-      <c r="O7" s="180"/>
-      <c r="P7" s="180"/>
+      <c r="G7" s="187"/>
+      <c r="H7" s="187"/>
+      <c r="I7" s="187"/>
+      <c r="J7" s="187"/>
+      <c r="K7" s="187"/>
+      <c r="L7" s="187"/>
+      <c r="M7" s="187"/>
+      <c r="N7" s="187"/>
+      <c r="O7" s="187"/>
+      <c r="P7" s="187"/>
     </row>
     <row r="8" spans="1:17">
       <c r="B8" s="32" t="s">
@@ -25960,40 +26316,40 @@
       <c r="A24" s="35" t="s">
         <v>455</v>
       </c>
-      <c r="B24" s="181" t="s">
+      <c r="B24" s="188" t="s">
         <v>457</v>
       </c>
-      <c r="C24" s="181"/>
-      <c r="D24" s="181"/>
-      <c r="E24" s="181"/>
-      <c r="F24" s="181"/>
-      <c r="G24" s="181"/>
+      <c r="C24" s="188"/>
+      <c r="D24" s="188"/>
+      <c r="E24" s="188"/>
+      <c r="F24" s="188"/>
+      <c r="G24" s="188"/>
     </row>
     <row r="25" spans="1:7" ht="30">
       <c r="A25" s="35" t="s">
         <v>462</v>
       </c>
-      <c r="B25" s="182" t="s">
+      <c r="B25" s="189" t="s">
         <v>464</v>
       </c>
-      <c r="C25" s="182"/>
-      <c r="D25" s="182"/>
-      <c r="E25" s="182"/>
-      <c r="F25" s="182"/>
-      <c r="G25" s="182"/>
+      <c r="C25" s="189"/>
+      <c r="D25" s="189"/>
+      <c r="E25" s="189"/>
+      <c r="F25" s="189"/>
+      <c r="G25" s="189"/>
     </row>
     <row r="26" spans="1:7" ht="159" customHeight="1">
       <c r="A26" s="35" t="s">
         <v>459</v>
       </c>
-      <c r="B26" s="181" t="s">
+      <c r="B26" s="188" t="s">
         <v>460</v>
       </c>
-      <c r="C26" s="181"/>
-      <c r="D26" s="181"/>
-      <c r="E26" s="181"/>
-      <c r="F26" s="181"/>
-      <c r="G26" s="181"/>
+      <c r="C26" s="188"/>
+      <c r="D26" s="188"/>
+      <c r="E26" s="188"/>
+      <c r="F26" s="188"/>
+      <c r="G26" s="188"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -26508,29 +26864,29 @@
       <c r="B27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="C27" s="185" t="s">
+      <c r="C27" s="192" t="s">
         <v>622</v>
       </c>
-      <c r="D27" s="186"/>
+      <c r="D27" s="193"/>
       <c r="E27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="F27" s="185" t="s">
+      <c r="F27" s="192" t="s">
         <v>622</v>
       </c>
-      <c r="G27" s="186"/>
+      <c r="G27" s="193"/>
       <c r="H27" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="I27" s="185" t="s">
+      <c r="I27" s="192" t="s">
         <v>622</v>
       </c>
-      <c r="J27" s="186"/>
-      <c r="L27" s="183" t="s">
+      <c r="J27" s="193"/>
+      <c r="L27" s="204" t="s">
         <v>694</v>
       </c>
-      <c r="M27" s="183"/>
-      <c r="N27" s="183"/>
+      <c r="M27" s="204"/>
+      <c r="N27" s="204"/>
     </row>
     <row r="28" spans="1:14" ht="32.25" thickBot="1">
       <c r="A28" s="81">
@@ -26539,29 +26895,29 @@
       <c r="B28" s="69" t="s">
         <v>623</v>
       </c>
-      <c r="C28" s="193" t="s">
+      <c r="C28" s="190" t="s">
         <v>624</v>
       </c>
-      <c r="D28" s="194"/>
+      <c r="D28" s="191"/>
       <c r="E28" s="70" t="s">
         <v>645</v>
       </c>
-      <c r="F28" s="187" t="s">
+      <c r="F28" s="194" t="s">
         <v>646</v>
       </c>
-      <c r="G28" s="188"/>
+      <c r="G28" s="195"/>
       <c r="H28" s="69" t="s">
         <v>667</v>
       </c>
-      <c r="I28" s="193" t="s">
+      <c r="I28" s="190" t="s">
         <v>668</v>
       </c>
-      <c r="J28" s="194"/>
-      <c r="L28" s="184" t="s">
+      <c r="J28" s="191"/>
+      <c r="L28" s="205" t="s">
         <v>695</v>
       </c>
-      <c r="M28" s="184"/>
-      <c r="N28" s="184"/>
+      <c r="M28" s="205"/>
+      <c r="N28" s="205"/>
     </row>
     <row r="29" spans="1:14" ht="31.5" thickBot="1">
       <c r="A29" s="81">
@@ -26570,29 +26926,29 @@
       <c r="B29" s="70" t="s">
         <v>625</v>
       </c>
-      <c r="C29" s="187" t="s">
+      <c r="C29" s="194" t="s">
         <v>626</v>
       </c>
-      <c r="D29" s="188"/>
+      <c r="D29" s="195"/>
       <c r="E29" s="69" t="s">
         <v>647</v>
       </c>
-      <c r="F29" s="193" t="s">
+      <c r="F29" s="190" t="s">
         <v>648</v>
       </c>
-      <c r="G29" s="194"/>
+      <c r="G29" s="191"/>
       <c r="H29" s="70" t="s">
         <v>669</v>
       </c>
-      <c r="I29" s="197" t="s">
+      <c r="I29" s="198" t="s">
         <v>670</v>
       </c>
-      <c r="J29" s="198"/>
-      <c r="L29" s="183" t="s">
+      <c r="J29" s="199"/>
+      <c r="L29" s="204" t="s">
         <v>696</v>
       </c>
-      <c r="M29" s="183"/>
-      <c r="N29" s="183"/>
+      <c r="M29" s="204"/>
+      <c r="N29" s="204"/>
     </row>
     <row r="30" spans="1:14" ht="15.75" thickBot="1">
       <c r="A30" s="81">
@@ -26601,29 +26957,29 @@
       <c r="B30" s="69" t="s">
         <v>627</v>
       </c>
-      <c r="C30" s="193" t="s">
+      <c r="C30" s="190" t="s">
         <v>628</v>
       </c>
-      <c r="D30" s="194"/>
+      <c r="D30" s="191"/>
       <c r="E30" s="70" t="s">
         <v>649</v>
       </c>
-      <c r="F30" s="187" t="s">
+      <c r="F30" s="194" t="s">
         <v>650</v>
       </c>
-      <c r="G30" s="188"/>
+      <c r="G30" s="195"/>
       <c r="H30" s="69" t="s">
         <v>671</v>
       </c>
-      <c r="I30" s="193" t="s">
+      <c r="I30" s="190" t="s">
         <v>672</v>
       </c>
-      <c r="J30" s="194"/>
-      <c r="L30" s="184" t="s">
+      <c r="J30" s="191"/>
+      <c r="L30" s="205" t="s">
         <v>697</v>
       </c>
-      <c r="M30" s="184"/>
-      <c r="N30" s="184"/>
+      <c r="M30" s="205"/>
+      <c r="N30" s="205"/>
     </row>
     <row r="31" spans="1:14" ht="17.25" customHeight="1" thickBot="1">
       <c r="A31" s="81">
@@ -26632,29 +26988,29 @@
       <c r="B31" s="70" t="s">
         <v>629</v>
       </c>
-      <c r="C31" s="187" t="s">
+      <c r="C31" s="194" t="s">
         <v>630</v>
       </c>
-      <c r="D31" s="188"/>
+      <c r="D31" s="195"/>
       <c r="E31" s="69" t="s">
         <v>651</v>
       </c>
-      <c r="F31" s="193" t="s">
+      <c r="F31" s="190" t="s">
         <v>652</v>
       </c>
-      <c r="G31" s="194"/>
+      <c r="G31" s="191"/>
       <c r="H31" s="70" t="s">
         <v>673</v>
       </c>
-      <c r="I31" s="187" t="s">
+      <c r="I31" s="194" t="s">
         <v>674</v>
       </c>
-      <c r="J31" s="188"/>
-      <c r="L31" s="183" t="s">
+      <c r="J31" s="195"/>
+      <c r="L31" s="204" t="s">
         <v>698</v>
       </c>
-      <c r="M31" s="183"/>
-      <c r="N31" s="183"/>
+      <c r="M31" s="204"/>
+      <c r="N31" s="204"/>
     </row>
     <row r="32" spans="1:14" ht="43.5" customHeight="1" thickBot="1">
       <c r="A32" s="81">
@@ -26663,29 +27019,29 @@
       <c r="B32" s="69" t="s">
         <v>631</v>
       </c>
-      <c r="C32" s="193" t="s">
+      <c r="C32" s="190" t="s">
         <v>632</v>
       </c>
-      <c r="D32" s="194"/>
+      <c r="D32" s="191"/>
       <c r="E32" s="70" t="s">
         <v>653</v>
       </c>
-      <c r="F32" s="187" t="s">
+      <c r="F32" s="194" t="s">
         <v>654</v>
       </c>
-      <c r="G32" s="188"/>
+      <c r="G32" s="195"/>
       <c r="H32" s="69" t="s">
         <v>675</v>
       </c>
-      <c r="I32" s="193" t="s">
+      <c r="I32" s="190" t="s">
         <v>676</v>
       </c>
-      <c r="J32" s="194"/>
-      <c r="L32" s="184" t="s">
+      <c r="J32" s="191"/>
+      <c r="L32" s="205" t="s">
         <v>699</v>
       </c>
-      <c r="M32" s="184"/>
-      <c r="N32" s="184"/>
+      <c r="M32" s="205"/>
+      <c r="N32" s="205"/>
     </row>
     <row r="33" spans="1:14" ht="31.5" customHeight="1" thickBot="1">
       <c r="A33" s="81">
@@ -26694,29 +27050,29 @@
       <c r="B33" s="70" t="s">
         <v>633</v>
       </c>
-      <c r="C33" s="187" t="s">
+      <c r="C33" s="194" t="s">
         <v>634</v>
       </c>
-      <c r="D33" s="188"/>
+      <c r="D33" s="195"/>
       <c r="E33" s="69" t="s">
         <v>655</v>
       </c>
-      <c r="F33" s="193" t="s">
+      <c r="F33" s="190" t="s">
         <v>656</v>
       </c>
-      <c r="G33" s="194"/>
+      <c r="G33" s="191"/>
       <c r="H33" s="70" t="s">
         <v>677</v>
       </c>
-      <c r="I33" s="195" t="s">
+      <c r="I33" s="196" t="s">
         <v>678</v>
       </c>
-      <c r="J33" s="196"/>
-      <c r="L33" s="183" t="s">
+      <c r="J33" s="197"/>
+      <c r="L33" s="204" t="s">
         <v>700</v>
       </c>
-      <c r="M33" s="183"/>
-      <c r="N33" s="183"/>
+      <c r="M33" s="204"/>
+      <c r="N33" s="204"/>
     </row>
     <row r="34" spans="1:14" ht="28.5" customHeight="1" thickBot="1">
       <c r="A34" s="81">
@@ -26725,29 +27081,29 @@
       <c r="B34" s="69" t="s">
         <v>635</v>
       </c>
-      <c r="C34" s="193" t="s">
+      <c r="C34" s="190" t="s">
         <v>636</v>
       </c>
-      <c r="D34" s="194"/>
+      <c r="D34" s="191"/>
       <c r="E34" s="70" t="s">
         <v>657</v>
       </c>
-      <c r="F34" s="187" t="s">
+      <c r="F34" s="194" t="s">
         <v>658</v>
       </c>
-      <c r="G34" s="188"/>
+      <c r="G34" s="195"/>
       <c r="H34" s="69" t="s">
         <v>679</v>
       </c>
-      <c r="I34" s="191" t="s">
+      <c r="I34" s="200" t="s">
         <v>680</v>
       </c>
-      <c r="J34" s="192"/>
-      <c r="L34" s="184" t="s">
+      <c r="J34" s="201"/>
+      <c r="L34" s="205" t="s">
         <v>701</v>
       </c>
-      <c r="M34" s="184"/>
-      <c r="N34" s="184"/>
+      <c r="M34" s="205"/>
+      <c r="N34" s="205"/>
     </row>
     <row r="35" spans="1:14" ht="31.5" customHeight="1" thickBot="1">
       <c r="A35" s="81">
@@ -26756,29 +27112,29 @@
       <c r="B35" s="70" t="s">
         <v>637</v>
       </c>
-      <c r="C35" s="187" t="s">
+      <c r="C35" s="194" t="s">
         <v>638</v>
       </c>
-      <c r="D35" s="188"/>
+      <c r="D35" s="195"/>
       <c r="E35" s="69" t="s">
         <v>659</v>
       </c>
-      <c r="F35" s="193" t="s">
+      <c r="F35" s="190" t="s">
         <v>660</v>
       </c>
-      <c r="G35" s="194"/>
+      <c r="G35" s="191"/>
       <c r="H35" s="77" t="s">
         <v>681</v>
       </c>
-      <c r="I35" s="187" t="s">
+      <c r="I35" s="194" t="s">
         <v>682</v>
       </c>
-      <c r="J35" s="188"/>
-      <c r="L35" s="183" t="s">
+      <c r="J35" s="195"/>
+      <c r="L35" s="204" t="s">
         <v>702</v>
       </c>
-      <c r="M35" s="183"/>
-      <c r="N35" s="183"/>
+      <c r="M35" s="204"/>
+      <c r="N35" s="204"/>
     </row>
     <row r="36" spans="1:14" ht="60.75" thickBot="1">
       <c r="A36" s="81">
@@ -26787,17 +27143,17 @@
       <c r="B36" s="69" t="s">
         <v>639</v>
       </c>
-      <c r="C36" s="193" t="s">
+      <c r="C36" s="190" t="s">
         <v>640</v>
       </c>
-      <c r="D36" s="194"/>
+      <c r="D36" s="191"/>
       <c r="E36" s="70" t="s">
         <v>661</v>
       </c>
-      <c r="F36" s="187" t="s">
+      <c r="F36" s="194" t="s">
         <v>662</v>
       </c>
-      <c r="G36" s="188"/>
+      <c r="G36" s="195"/>
       <c r="H36" s="78"/>
       <c r="I36" s="71" t="s">
         <v>683</v>
@@ -26805,11 +27161,11 @@
       <c r="J36" s="72" t="s">
         <v>684</v>
       </c>
-      <c r="L36" s="184" t="s">
+      <c r="L36" s="205" t="s">
         <v>703</v>
       </c>
-      <c r="M36" s="184"/>
-      <c r="N36" s="184"/>
+      <c r="M36" s="205"/>
+      <c r="N36" s="205"/>
     </row>
     <row r="37" spans="1:14" ht="75.75" thickBot="1">
       <c r="A37" s="81">
@@ -26818,17 +27174,17 @@
       <c r="B37" s="70" t="s">
         <v>641</v>
       </c>
-      <c r="C37" s="187" t="s">
+      <c r="C37" s="194" t="s">
         <v>642</v>
       </c>
-      <c r="D37" s="188"/>
+      <c r="D37" s="195"/>
       <c r="E37" s="69" t="s">
         <v>663</v>
       </c>
-      <c r="F37" s="193" t="s">
+      <c r="F37" s="190" t="s">
         <v>664</v>
       </c>
-      <c r="G37" s="194"/>
+      <c r="G37" s="191"/>
       <c r="H37" s="78"/>
       <c r="I37" s="73" t="s">
         <v>685</v>
@@ -26844,17 +27200,17 @@
       <c r="B38" s="69" t="s">
         <v>643</v>
       </c>
-      <c r="C38" s="193" t="s">
+      <c r="C38" s="190" t="s">
         <v>644</v>
       </c>
-      <c r="D38" s="194"/>
+      <c r="D38" s="191"/>
       <c r="E38" s="70" t="s">
         <v>665</v>
       </c>
-      <c r="F38" s="187" t="s">
+      <c r="F38" s="194" t="s">
         <v>666</v>
       </c>
-      <c r="G38" s="188"/>
+      <c r="G38" s="195"/>
       <c r="H38" s="78"/>
       <c r="I38" s="75" t="s">
         <v>687</v>
@@ -26870,40 +27226,46 @@
       <c r="B39" s="70" t="s">
         <v>692</v>
       </c>
-      <c r="C39" s="195" t="s">
+      <c r="C39" s="196" t="s">
         <v>693</v>
       </c>
-      <c r="D39" s="196"/>
+      <c r="D39" s="197"/>
       <c r="E39" s="69" t="s">
         <v>690</v>
       </c>
-      <c r="F39" s="191" t="s">
+      <c r="F39" s="200" t="s">
         <v>691</v>
       </c>
-      <c r="G39" s="192"/>
+      <c r="G39" s="201"/>
       <c r="H39" s="79"/>
-      <c r="I39" s="189" t="s">
+      <c r="I39" s="202" t="s">
         <v>689</v>
       </c>
-      <c r="J39" s="190"/>
+      <c r="J39" s="203"/>
     </row>
     <row r="40" spans="1:14" ht="58.5" customHeight="1"/>
     <row r="42" spans="1:14" ht="31.5" customHeight="1"/>
     <row r="43" spans="1:14" ht="31.5" customHeight="1"/>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F33:G33"/>
     <mergeCell ref="C39:D39"/>
     <mergeCell ref="I29:J29"/>
     <mergeCell ref="I30:J30"/>
@@ -26920,24 +27282,18 @@
     <mergeCell ref="F30:G30"/>
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="F32:G32"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>

--- a/2020_LogAnalyzer_Leeheesuk.xlsx
+++ b/2020_LogAnalyzer_Leeheesuk.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="23328"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E648ADD7-31CD-4C7C-9136-9E6138B38EA2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6555E7F-976D-4261-A81F-B0FF405CD531}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1425" yWindow="540" windowWidth="25755" windowHeight="14835" firstSheet="17" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" firstSheet="6" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UI" sheetId="7" r:id="rId1"/>
@@ -18,30 +18,31 @@
     <sheet name="Table" sheetId="10" r:id="rId8"/>
     <sheet name="Table_0408" sheetId="15" r:id="rId9"/>
     <sheet name="Table_0619_0429" sheetId="16" r:id="rId10"/>
-    <sheet name="Pilot" sheetId="11" r:id="rId11"/>
-    <sheet name="아키텍처" sheetId="9" r:id="rId12"/>
-    <sheet name="기능요건" sheetId="8" r:id="rId13"/>
-    <sheet name="추가기능_베타서비스포함_TODO" sheetId="24" r:id="rId14"/>
-    <sheet name="기능요건_피드백" sheetId="14" r:id="rId15"/>
-    <sheet name="비기능요건" sheetId="6" r:id="rId16"/>
-    <sheet name="배포정리_TODO" sheetId="25" r:id="rId17"/>
-    <sheet name="성능테스트_0717" sheetId="22" r:id="rId18"/>
-    <sheet name="지원포맷" sheetId="1" r:id="rId19"/>
-    <sheet name="로그로맷 항목설명" sheetId="21" r:id="rId20"/>
-    <sheet name="고려사항" sheetId="5" r:id="rId21"/>
-    <sheet name="기능 - AWStats" sheetId="2" r:id="rId22"/>
-    <sheet name="기능 - apachelogviewer" sheetId="4" r:id="rId23"/>
-    <sheet name="기능 - goaccess" sheetId="3" r:id="rId24"/>
+    <sheet name="Table_2021" sheetId="26" r:id="rId11"/>
+    <sheet name="Pilot" sheetId="11" r:id="rId12"/>
+    <sheet name="아키텍처" sheetId="9" r:id="rId13"/>
+    <sheet name="기능요건" sheetId="8" r:id="rId14"/>
+    <sheet name="추가기능_베타서비스포함_TODO" sheetId="24" r:id="rId15"/>
+    <sheet name="기능요건_피드백" sheetId="14" r:id="rId16"/>
+    <sheet name="비기능요건" sheetId="6" r:id="rId17"/>
+    <sheet name="배포정리_TODO" sheetId="25" r:id="rId18"/>
+    <sheet name="성능테스트_0717" sheetId="22" r:id="rId19"/>
+    <sheet name="지원포맷" sheetId="1" r:id="rId20"/>
+    <sheet name="로그로맷 항목설명" sheetId="21" r:id="rId21"/>
+    <sheet name="고려사항" sheetId="5" r:id="rId22"/>
+    <sheet name="기능 - AWStats" sheetId="2" r:id="rId23"/>
+    <sheet name="기능 - apachelogviewer" sheetId="4" r:id="rId24"/>
+    <sheet name="기능 - goaccess" sheetId="3" r:id="rId25"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="12">기능요건!$A$1:$M$46</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="13">기능요건!$A$1:$M$46</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2264" uniqueCount="1446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2649" uniqueCount="1479">
   <si>
     <t>구분</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4912,18 +4913,10 @@
     <t>The contents of VARNAME: trailer line(s) in the response sent from the server.</t>
   </si>
   <si>
-    <t>remote_user</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>HTTP Authenticated User. When the user name is not set, this field shows</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>remote_addr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>time_local</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -4940,34 +4933,18 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>body_bytes_sent</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>number of bytes sent to a client, not counting the response header</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>http_referer</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>identifies the address of the URI which is linked to the resource being requested</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>http_user_agent</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>value of standard User Agent HTTP request field</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>http_x_forwarded_for</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>identifying the originating IP address of a client</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5015,10 +4992,6 @@
   </si>
   <si>
     <t>request length (including request line, header, and request body)</t>
-  </si>
-  <si>
-    <t>request_time</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>request processing time in seconds with a milliseconds resolution; time elapsed between the first bytes were read from the client and the log write after the last bytes were sent to the client</t>
@@ -6194,6 +6167,126 @@
   </si>
   <si>
     <t>이면 apache와 동일 로직(LogFormat 불필요, 정해져 있다.)</t>
+  </si>
+  <si>
+    <t>request_time</t>
+  </si>
+  <si>
+    <t>http_x_forwarded_for</t>
+  </si>
+  <si>
+    <t>remote_user</t>
+  </si>
+  <si>
+    <t>remote_addr</t>
+  </si>
+  <si>
+    <t>time_local</t>
+  </si>
+  <si>
+    <t>http_user_agent</t>
+  </si>
+  <si>
+    <t>http_referer</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>body_bytes_sent</t>
+  </si>
+  <si>
+    <t>cs(Referer)</t>
+  </si>
+  <si>
+    <t>::1</t>
+  </si>
+  <si>
+    <t>GET</t>
+  </si>
+  <si>
+    <t>/</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Mozilla/5.0+(Windows+NT+10.0;+Win64;+x64)+AppleWebKit/537.36+(KHTML,+like+Gecko)+Chrome/86.0.4240.111+Safari/537.36</t>
+  </si>
+  <si>
+    <t>IIS-W3C</t>
+  </si>
+  <si>
+    <t>Metrics</t>
+  </si>
+  <si>
+    <t>metric_id(PK)</t>
+  </si>
+  <si>
+    <t>Metric 구분</t>
+  </si>
+  <si>
+    <t>metric_kind</t>
+  </si>
+  <si>
+    <t>metric_definition</t>
+  </si>
+  <si>
+    <t>Metric 설명</t>
+  </si>
+  <si>
+    <t>Metric 단위</t>
+  </si>
+  <si>
+    <t>metric_unit</t>
+  </si>
+  <si>
+    <t>metric_min</t>
+  </si>
+  <si>
+    <t>metric_max</t>
+  </si>
+  <si>
+    <t>사용</t>
+  </si>
+  <si>
+    <t>IntegerField</t>
+  </si>
+  <si>
+    <t>사용(동일)</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>TPS</t>
+  </si>
+  <si>
+    <t>범위(Scope)</t>
+  </si>
+  <si>
+    <t>임계값(Threshold)</t>
+  </si>
+  <si>
+    <t>logmaster_metric</t>
+  </si>
+  <si>
+    <t>logmaster_metric_id(PK)</t>
+  </si>
+  <si>
+    <t>project_id</t>
+  </si>
+  <si>
+    <t>metric_id</t>
+  </si>
+  <si>
+    <t>metric_filter</t>
+  </si>
+  <si>
+    <t>Metric 적용필터</t>
+  </si>
+  <si>
+    <t>millis, micros</t>
   </si>
 </sst>
 </file>
@@ -6866,7 +6959,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="40" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="232">
+  <cellXfs count="242">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -7313,6 +7406,21 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -7492,6 +7600,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -16874,51 +16991,51 @@
     </row>
     <row r="17" spans="1:13">
       <c r="J17" s="19"/>
-      <c r="K17" s="172" t="s">
+      <c r="K17" s="177" t="s">
         <v>536</v>
       </c>
-      <c r="L17" s="173"/>
-      <c r="M17" s="174"/>
+      <c r="L17" s="178"/>
+      <c r="M17" s="179"/>
     </row>
     <row r="18" spans="1:13">
       <c r="J18" s="19">
         <v>1</v>
       </c>
-      <c r="K18" s="175" t="s">
+      <c r="K18" s="180" t="s">
         <v>537</v>
       </c>
-      <c r="L18" s="176"/>
-      <c r="M18" s="177"/>
+      <c r="L18" s="181"/>
+      <c r="M18" s="182"/>
     </row>
     <row r="19" spans="1:13">
       <c r="J19" s="19">
         <v>2</v>
       </c>
-      <c r="K19" s="175" t="s">
+      <c r="K19" s="180" t="s">
         <v>538</v>
       </c>
-      <c r="L19" s="176"/>
-      <c r="M19" s="177"/>
+      <c r="L19" s="181"/>
+      <c r="M19" s="182"/>
     </row>
     <row r="20" spans="1:13">
       <c r="J20" s="19">
         <v>3</v>
       </c>
-      <c r="K20" s="175" t="s">
+      <c r="K20" s="180" t="s">
         <v>539</v>
       </c>
-      <c r="L20" s="176"/>
-      <c r="M20" s="177"/>
+      <c r="L20" s="181"/>
+      <c r="M20" s="182"/>
     </row>
     <row r="21" spans="1:13">
       <c r="J21" s="19">
         <v>4</v>
       </c>
-      <c r="K21" s="175" t="s">
+      <c r="K21" s="180" t="s">
         <v>540</v>
       </c>
-      <c r="L21" s="176"/>
-      <c r="M21" s="177"/>
+      <c r="L21" s="181"/>
+      <c r="M21" s="182"/>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="43" t="s">
@@ -16989,15 +17106,15 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.42578125" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" customWidth="1"/>
     <col min="3" max="3" width="21.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.85546875" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" customWidth="1"/>
-    <col min="7" max="7" width="15" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.140625" customWidth="1"/>
+    <col min="7" max="7" width="19.7109375" customWidth="1"/>
     <col min="8" max="8" width="17.42578125" customWidth="1"/>
-    <col min="9" max="9" width="13.7109375" customWidth="1"/>
-    <col min="10" max="10" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.85546875" customWidth="1"/>
+    <col min="10" max="10" width="18.5703125" customWidth="1"/>
     <col min="11" max="11" width="18.140625" customWidth="1"/>
     <col min="12" max="12" width="24.28515625" customWidth="1"/>
     <col min="13" max="13" width="25.5703125" bestFit="1" customWidth="1"/>
@@ -17110,10 +17227,10 @@
       <c r="F7" s="111" t="s">
         <v>914</v>
       </c>
-      <c r="I7" s="206" t="s">
-        <v>1165</v>
-      </c>
-      <c r="J7" s="206"/>
+      <c r="I7" s="211" t="s">
+        <v>1158</v>
+      </c>
+      <c r="J7" s="211"/>
       <c r="L7" s="49" t="s">
         <v>600</v>
       </c>
@@ -17448,10 +17565,10 @@
         <v>443</v>
       </c>
       <c r="K20" s="32" t="s">
-        <v>1350</v>
+        <v>1343</v>
       </c>
       <c r="L20" s="32" t="s">
-        <v>1352</v>
+        <v>1345</v>
       </c>
       <c r="M20" s="32" t="s">
         <v>414</v>
@@ -17489,10 +17606,10 @@
         <v>444</v>
       </c>
       <c r="K21" s="95" t="s">
-        <v>1351</v>
+        <v>1344</v>
       </c>
       <c r="L21" s="95" t="s">
-        <v>1350</v>
+        <v>1343</v>
       </c>
       <c r="M21" s="85" t="s">
         <v>465</v>
@@ -17574,7 +17691,7 @@
       </c>
       <c r="M23" s="64"/>
       <c r="N23" s="153" t="s">
-        <v>1292</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -17587,36 +17704,36 @@
     </row>
     <row r="26" spans="1:14" ht="15.75" thickBot="1">
       <c r="F26" s="7" t="s">
-        <v>1164</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="15.75" thickBot="1">
       <c r="B27" s="80" t="s">
         <v>620</v>
       </c>
-      <c r="C27" s="192" t="s">
+      <c r="C27" s="197" t="s">
         <v>621</v>
       </c>
-      <c r="D27" s="193"/>
+      <c r="D27" s="198"/>
       <c r="E27" s="80" t="s">
         <v>620</v>
       </c>
-      <c r="F27" s="192" t="s">
+      <c r="F27" s="197" t="s">
         <v>621</v>
       </c>
-      <c r="G27" s="193"/>
+      <c r="G27" s="198"/>
       <c r="H27" s="80" t="s">
         <v>620</v>
       </c>
-      <c r="I27" s="192" t="s">
+      <c r="I27" s="197" t="s">
         <v>621</v>
       </c>
-      <c r="J27" s="193"/>
-      <c r="L27" s="190" t="s">
+      <c r="J27" s="198"/>
+      <c r="L27" s="195" t="s">
         <v>693</v>
       </c>
-      <c r="M27" s="190"/>
-      <c r="N27" s="190"/>
+      <c r="M27" s="195"/>
+      <c r="N27" s="195"/>
     </row>
     <row r="28" spans="1:14" ht="49.5" customHeight="1" thickBot="1">
       <c r="A28" s="81">
@@ -17625,29 +17742,29 @@
       <c r="B28" s="69" t="s">
         <v>622</v>
       </c>
-      <c r="C28" s="200" t="s">
+      <c r="C28" s="205" t="s">
         <v>623</v>
       </c>
-      <c r="D28" s="201"/>
+      <c r="D28" s="206"/>
       <c r="E28" s="70" t="s">
         <v>644</v>
       </c>
-      <c r="F28" s="194" t="s">
-        <v>1177</v>
-      </c>
-      <c r="G28" s="195"/>
+      <c r="F28" s="199" t="s">
+        <v>1170</v>
+      </c>
+      <c r="G28" s="200"/>
       <c r="H28" s="69" t="s">
         <v>666</v>
       </c>
-      <c r="I28" s="200" t="s">
+      <c r="I28" s="205" t="s">
         <v>667</v>
       </c>
-      <c r="J28" s="201"/>
-      <c r="L28" s="191" t="s">
+      <c r="J28" s="206"/>
+      <c r="L28" s="196" t="s">
         <v>694</v>
       </c>
-      <c r="M28" s="191"/>
-      <c r="N28" s="191"/>
+      <c r="M28" s="196"/>
+      <c r="N28" s="196"/>
     </row>
     <row r="29" spans="1:14" ht="31.5" thickBot="1">
       <c r="A29" s="81">
@@ -17656,29 +17773,29 @@
       <c r="B29" s="70" t="s">
         <v>624</v>
       </c>
-      <c r="C29" s="194" t="s">
+      <c r="C29" s="199" t="s">
         <v>625</v>
       </c>
-      <c r="D29" s="195"/>
+      <c r="D29" s="200"/>
       <c r="E29" s="69" t="s">
         <v>646</v>
       </c>
-      <c r="F29" s="200" t="s">
+      <c r="F29" s="205" t="s">
         <v>647</v>
       </c>
-      <c r="G29" s="201"/>
+      <c r="G29" s="206"/>
       <c r="H29" s="70" t="s">
         <v>668</v>
       </c>
-      <c r="I29" s="204" t="s">
+      <c r="I29" s="209" t="s">
         <v>669</v>
       </c>
-      <c r="J29" s="205"/>
-      <c r="L29" s="190" t="s">
+      <c r="J29" s="210"/>
+      <c r="L29" s="195" t="s">
         <v>695</v>
       </c>
-      <c r="M29" s="190"/>
-      <c r="N29" s="190"/>
+      <c r="M29" s="195"/>
+      <c r="N29" s="195"/>
     </row>
     <row r="30" spans="1:14" ht="15.75" thickBot="1">
       <c r="A30" s="81">
@@ -17687,29 +17804,29 @@
       <c r="B30" s="69" t="s">
         <v>626</v>
       </c>
-      <c r="C30" s="200" t="s">
+      <c r="C30" s="205" t="s">
         <v>627</v>
       </c>
-      <c r="D30" s="201"/>
+      <c r="D30" s="206"/>
       <c r="E30" s="70" t="s">
         <v>648</v>
       </c>
-      <c r="F30" s="194" t="s">
+      <c r="F30" s="199" t="s">
         <v>649</v>
       </c>
-      <c r="G30" s="195"/>
+      <c r="G30" s="200"/>
       <c r="H30" s="69" t="s">
         <v>670</v>
       </c>
-      <c r="I30" s="200" t="s">
+      <c r="I30" s="205" t="s">
         <v>671</v>
       </c>
-      <c r="J30" s="201"/>
-      <c r="L30" s="191" t="s">
+      <c r="J30" s="206"/>
+      <c r="L30" s="196" t="s">
         <v>696</v>
       </c>
-      <c r="M30" s="191"/>
-      <c r="N30" s="191"/>
+      <c r="M30" s="196"/>
+      <c r="N30" s="196"/>
     </row>
     <row r="31" spans="1:14" ht="17.25" customHeight="1" thickBot="1">
       <c r="A31" s="81">
@@ -17718,29 +17835,29 @@
       <c r="B31" s="70" t="s">
         <v>628</v>
       </c>
-      <c r="C31" s="194" t="s">
+      <c r="C31" s="199" t="s">
         <v>629</v>
       </c>
-      <c r="D31" s="195"/>
+      <c r="D31" s="200"/>
       <c r="E31" s="69" t="s">
         <v>650</v>
       </c>
-      <c r="F31" s="200" t="s">
+      <c r="F31" s="205" t="s">
         <v>651</v>
       </c>
-      <c r="G31" s="201"/>
+      <c r="G31" s="206"/>
       <c r="H31" s="70" t="s">
         <v>672</v>
       </c>
-      <c r="I31" s="194" t="s">
+      <c r="I31" s="199" t="s">
         <v>673</v>
       </c>
-      <c r="J31" s="195"/>
-      <c r="L31" s="190" t="s">
+      <c r="J31" s="200"/>
+      <c r="L31" s="195" t="s">
         <v>697</v>
       </c>
-      <c r="M31" s="190"/>
-      <c r="N31" s="190"/>
+      <c r="M31" s="195"/>
+      <c r="N31" s="195"/>
     </row>
     <row r="32" spans="1:14" ht="43.5" customHeight="1" thickBot="1">
       <c r="A32" s="81">
@@ -17749,29 +17866,29 @@
       <c r="B32" s="69" t="s">
         <v>630</v>
       </c>
-      <c r="C32" s="200" t="s">
+      <c r="C32" s="205" t="s">
         <v>631</v>
       </c>
-      <c r="D32" s="201"/>
+      <c r="D32" s="206"/>
       <c r="E32" s="70" t="s">
         <v>652</v>
       </c>
-      <c r="F32" s="194" t="s">
+      <c r="F32" s="199" t="s">
         <v>653</v>
       </c>
-      <c r="G32" s="195"/>
+      <c r="G32" s="200"/>
       <c r="H32" s="69" t="s">
         <v>674</v>
       </c>
-      <c r="I32" s="200" t="s">
+      <c r="I32" s="205" t="s">
         <v>675</v>
       </c>
-      <c r="J32" s="201"/>
-      <c r="L32" s="191" t="s">
+      <c r="J32" s="206"/>
+      <c r="L32" s="196" t="s">
         <v>698</v>
       </c>
-      <c r="M32" s="191"/>
-      <c r="N32" s="191"/>
+      <c r="M32" s="196"/>
+      <c r="N32" s="196"/>
     </row>
     <row r="33" spans="1:14" ht="31.5" customHeight="1" thickBot="1">
       <c r="A33" s="81">
@@ -17780,29 +17897,29 @@
       <c r="B33" s="70" t="s">
         <v>632</v>
       </c>
-      <c r="C33" s="194" t="s">
+      <c r="C33" s="199" t="s">
         <v>633</v>
       </c>
-      <c r="D33" s="195"/>
+      <c r="D33" s="200"/>
       <c r="E33" s="69" t="s">
         <v>654</v>
       </c>
-      <c r="F33" s="200" t="s">
+      <c r="F33" s="205" t="s">
         <v>655</v>
       </c>
-      <c r="G33" s="201"/>
+      <c r="G33" s="206"/>
       <c r="H33" s="70" t="s">
         <v>676</v>
       </c>
-      <c r="I33" s="202" t="s">
+      <c r="I33" s="207" t="s">
         <v>677</v>
       </c>
-      <c r="J33" s="203"/>
-      <c r="L33" s="190" t="s">
+      <c r="J33" s="208"/>
+      <c r="L33" s="195" t="s">
         <v>699</v>
       </c>
-      <c r="M33" s="190"/>
-      <c r="N33" s="190"/>
+      <c r="M33" s="195"/>
+      <c r="N33" s="195"/>
     </row>
     <row r="34" spans="1:14" ht="28.5" customHeight="1" thickBot="1">
       <c r="A34" s="81">
@@ -17811,29 +17928,29 @@
       <c r="B34" s="69" t="s">
         <v>634</v>
       </c>
-      <c r="C34" s="200" t="s">
+      <c r="C34" s="205" t="s">
         <v>635</v>
       </c>
-      <c r="D34" s="201"/>
+      <c r="D34" s="206"/>
       <c r="E34" s="70" t="s">
         <v>656</v>
       </c>
-      <c r="F34" s="194" t="s">
+      <c r="F34" s="199" t="s">
         <v>657</v>
       </c>
-      <c r="G34" s="195"/>
+      <c r="G34" s="200"/>
       <c r="H34" s="69" t="s">
         <v>678</v>
       </c>
-      <c r="I34" s="198" t="s">
+      <c r="I34" s="203" t="s">
         <v>679</v>
       </c>
-      <c r="J34" s="199"/>
-      <c r="L34" s="191" t="s">
+      <c r="J34" s="204"/>
+      <c r="L34" s="196" t="s">
         <v>700</v>
       </c>
-      <c r="M34" s="191"/>
-      <c r="N34" s="191"/>
+      <c r="M34" s="196"/>
+      <c r="N34" s="196"/>
     </row>
     <row r="35" spans="1:14" ht="31.5" customHeight="1" thickBot="1">
       <c r="A35" s="81">
@@ -17842,29 +17959,29 @@
       <c r="B35" s="70" t="s">
         <v>636</v>
       </c>
-      <c r="C35" s="194" t="s">
+      <c r="C35" s="199" t="s">
         <v>637</v>
       </c>
-      <c r="D35" s="195"/>
+      <c r="D35" s="200"/>
       <c r="E35" s="69" t="s">
         <v>658</v>
       </c>
-      <c r="F35" s="200" t="s">
+      <c r="F35" s="205" t="s">
         <v>659</v>
       </c>
-      <c r="G35" s="201"/>
+      <c r="G35" s="206"/>
       <c r="H35" s="77" t="s">
         <v>680</v>
       </c>
-      <c r="I35" s="194" t="s">
+      <c r="I35" s="199" t="s">
         <v>681</v>
       </c>
-      <c r="J35" s="195"/>
-      <c r="L35" s="190" t="s">
+      <c r="J35" s="200"/>
+      <c r="L35" s="195" t="s">
         <v>701</v>
       </c>
-      <c r="M35" s="190"/>
-      <c r="N35" s="190"/>
+      <c r="M35" s="195"/>
+      <c r="N35" s="195"/>
     </row>
     <row r="36" spans="1:14" ht="60.75" thickBot="1">
       <c r="A36" s="81">
@@ -17873,17 +17990,17 @@
       <c r="B36" s="69" t="s">
         <v>638</v>
       </c>
-      <c r="C36" s="200" t="s">
+      <c r="C36" s="205" t="s">
         <v>639</v>
       </c>
-      <c r="D36" s="201"/>
+      <c r="D36" s="206"/>
       <c r="E36" s="70" t="s">
         <v>660</v>
       </c>
-      <c r="F36" s="194" t="s">
+      <c r="F36" s="199" t="s">
         <v>661</v>
       </c>
-      <c r="G36" s="195"/>
+      <c r="G36" s="200"/>
       <c r="H36" s="78"/>
       <c r="I36" s="71" t="s">
         <v>682</v>
@@ -17891,11 +18008,11 @@
       <c r="J36" s="72" t="s">
         <v>683</v>
       </c>
-      <c r="L36" s="191" t="s">
+      <c r="L36" s="196" t="s">
         <v>702</v>
       </c>
-      <c r="M36" s="191"/>
-      <c r="N36" s="191"/>
+      <c r="M36" s="196"/>
+      <c r="N36" s="196"/>
     </row>
     <row r="37" spans="1:14" ht="75.75" thickBot="1">
       <c r="A37" s="81">
@@ -17904,17 +18021,17 @@
       <c r="B37" s="70" t="s">
         <v>640</v>
       </c>
-      <c r="C37" s="194" t="s">
+      <c r="C37" s="199" t="s">
         <v>641</v>
       </c>
-      <c r="D37" s="195"/>
+      <c r="D37" s="200"/>
       <c r="E37" s="69" t="s">
         <v>662</v>
       </c>
-      <c r="F37" s="200" t="s">
+      <c r="F37" s="205" t="s">
         <v>663</v>
       </c>
-      <c r="G37" s="201"/>
+      <c r="G37" s="206"/>
       <c r="H37" s="78"/>
       <c r="I37" s="73" t="s">
         <v>684</v>
@@ -17930,17 +18047,17 @@
       <c r="B38" s="69" t="s">
         <v>642</v>
       </c>
-      <c r="C38" s="200" t="s">
+      <c r="C38" s="205" t="s">
         <v>643</v>
       </c>
-      <c r="D38" s="201"/>
+      <c r="D38" s="206"/>
       <c r="E38" s="70" t="s">
         <v>664</v>
       </c